--- a/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>27.04.2026 18:52:52</t>
+    <t>28.04.2026 18:41:33</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2402,12 +2402,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
     <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="169" formatCode="###0.000;-###0.000;0"/>
+    <numFmt numFmtId="170" formatCode="###0.0000;-###0.0000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -2477,7 +2479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2503,6 +2505,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2907,19 +2915,19 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D6" s="7">
-        <v>0.101515</v>
+        <v>0.101638</v>
       </c>
       <c r="E6" s="8">
-        <v>47362492558.73</v>
+        <v>47346699237.61</v>
       </c>
       <c r="F6" s="9">
-        <v>644881</v>
+        <v>644747</v>
       </c>
       <c r="G6" s="8">
-        <v>4808008365.13</v>
+        <v>4812218649.22</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2930,19 +2938,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D7" s="7">
-        <v>0.396941</v>
+        <v>0.399289</v>
       </c>
       <c r="E7" s="8">
-        <v>17098360161.78</v>
+        <v>17096684919.48</v>
       </c>
       <c r="F7" s="9">
-        <v>151736</v>
+        <v>151719</v>
       </c>
       <c r="G7" s="8">
-        <v>6787046359.13</v>
+        <v>6826510143.98</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2953,19 +2961,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D8" s="7">
-        <v>0.085936</v>
+        <v>0.086026</v>
       </c>
       <c r="E8" s="8">
-        <v>8089666358.34</v>
+        <v>8029770634.85</v>
       </c>
       <c r="F8" s="9">
-        <v>143659</v>
+        <v>142903</v>
       </c>
       <c r="G8" s="8">
-        <v>695196279.86</v>
+        <v>690766141.06</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2976,19 +2984,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D9" s="7">
-        <v>0.366241</v>
+        <v>0.366644</v>
       </c>
       <c r="E9" s="8">
-        <v>139803184223.14</v>
+        <v>140662118569.18</v>
       </c>
       <c r="F9" s="9">
-        <v>486032</v>
+        <v>486361</v>
       </c>
       <c r="G9" s="8">
-        <v>51201706963.17</v>
+        <v>51572935118.67</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2999,19 +3007,19 @@
         <v>20</v>
       </c>
       <c r="C10" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D10" s="7">
-        <v>0.334506</v>
+        <v>0.334124</v>
       </c>
       <c r="E10" s="8">
-        <v>23220947186.32</v>
+        <v>23179686625.69</v>
       </c>
       <c r="F10" s="9">
-        <v>329459</v>
+        <v>329347</v>
       </c>
       <c r="G10" s="8">
-        <v>7767536051.85</v>
+        <v>7744879079.45</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3022,19 +3030,19 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D11" s="7">
-        <v>0.994923</v>
+        <v>1.003077</v>
       </c>
       <c r="E11" s="8">
-        <v>11619834718.54</v>
+        <v>11605332846.53</v>
       </c>
       <c r="F11" s="9">
-        <v>289293</v>
+        <v>289190</v>
       </c>
       <c r="G11" s="8">
-        <v>11560835717.23</v>
+        <v>11641045735.28</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3045,19 +3053,19 @@
         <v>24</v>
       </c>
       <c r="C12" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D12" s="7">
-        <v>0.718657</v>
+        <v>0.716822</v>
       </c>
       <c r="E12" s="8">
-        <v>136992251362.86</v>
+        <v>136885441909.42</v>
       </c>
       <c r="F12" s="9">
-        <v>726413</v>
+        <v>726136</v>
       </c>
       <c r="G12" s="8">
-        <v>98450508010.83</v>
+        <v>98122487602.24</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3068,19 +3076,19 @@
         <v>26</v>
       </c>
       <c r="C13" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D13" s="7">
-        <v>2.009072</v>
+        <v>2.025322</v>
       </c>
       <c r="E13" s="8">
-        <v>1362489916.17</v>
+        <v>1360996687.75</v>
       </c>
       <c r="F13" s="9">
-        <v>32574</v>
+        <v>32545</v>
       </c>
       <c r="G13" s="8">
-        <v>2737340507.57</v>
+        <v>2756456075.13</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3091,19 +3099,19 @@
         <v>28</v>
       </c>
       <c r="C14" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D14" s="7">
-        <v>0.136467</v>
+        <v>0.136814</v>
       </c>
       <c r="E14" s="8">
-        <v>251020945.58</v>
+        <v>249905599.92</v>
       </c>
       <c r="F14" s="9">
         <v>92</v>
       </c>
       <c r="G14" s="8">
-        <v>34255970.72</v>
+        <v>34190704.65</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3114,19 +3122,19 @@
         <v>30</v>
       </c>
       <c r="C15" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D15" s="7">
-        <v>1.372998</v>
+        <v>1.384607</v>
       </c>
       <c r="E15" s="8">
-        <v>16059952842.38</v>
+        <v>16063710127.42</v>
       </c>
       <c r="F15" s="9">
-        <v>485829</v>
+        <v>486060</v>
       </c>
       <c r="G15" s="8">
-        <v>22050276312.12</v>
+        <v>22241918145.35</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3137,19 +3145,19 @@
         <v>32</v>
       </c>
       <c r="C16" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D16" s="7">
-        <v>0.093429</v>
+        <v>0.093752</v>
       </c>
       <c r="E16" s="8">
-        <v>560686515226.08</v>
+        <v>560302288770.74</v>
       </c>
       <c r="F16" s="9">
-        <v>1925775</v>
+        <v>1924799</v>
       </c>
       <c r="G16" s="8">
-        <v>52384295275.88</v>
+        <v>52529706680.4</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3160,19 +3168,19 @@
         <v>34</v>
       </c>
       <c r="C17" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D17" s="7">
-        <v>0.348299</v>
+        <v>0.347945</v>
       </c>
       <c r="E17" s="8">
-        <v>2117001114.97</v>
+        <v>2111711739.58</v>
       </c>
       <c r="F17" s="9">
-        <v>13389</v>
+        <v>13349</v>
       </c>
       <c r="G17" s="8">
-        <v>737349580.17</v>
+        <v>734760512.44</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3183,19 +3191,19 @@
         <v>36</v>
       </c>
       <c r="C18" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D18" s="7">
-        <v>0.144577</v>
+        <v>0.145097</v>
       </c>
       <c r="E18" s="8">
-        <v>33025881586.26</v>
+        <v>32990778012.1</v>
       </c>
       <c r="F18" s="9">
-        <v>239544</v>
+        <v>239454</v>
       </c>
       <c r="G18" s="8">
-        <v>4774787530.21</v>
+        <v>4786871667.58</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3206,19 +3214,19 @@
         <v>38</v>
       </c>
       <c r="C19" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D19" s="7">
-        <v>0.370213</v>
+        <v>0.371745</v>
       </c>
       <c r="E19" s="8">
-        <v>1434398518.13</v>
+        <v>1434505645.8</v>
       </c>
       <c r="F19" s="9">
         <v>537</v>
       </c>
       <c r="G19" s="8">
-        <v>531033249.57</v>
+        <v>533269804.57</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3229,19 +3237,19 @@
         <v>40</v>
       </c>
       <c r="C20" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D20" s="7">
-        <v>0.136944</v>
+        <v>0.137846</v>
       </c>
       <c r="E20" s="8">
-        <v>14499934516.63</v>
+        <v>14499071274.9</v>
       </c>
       <c r="F20" s="9">
-        <v>519135</v>
+        <v>519070</v>
       </c>
       <c r="G20" s="8">
-        <v>1985684811.99</v>
+        <v>1998642735.35</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3252,19 +3260,19 @@
         <v>42</v>
       </c>
       <c r="C21" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D21" s="7">
-        <v>0.097421</v>
+        <v>0.097611</v>
       </c>
       <c r="E21" s="8">
-        <v>502475885391.88</v>
+        <v>502176106007.28</v>
       </c>
       <c r="F21" s="9">
-        <v>2273267</v>
+        <v>2272635</v>
       </c>
       <c r="G21" s="8">
-        <v>48951611068.15</v>
+        <v>49018084153.9</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3275,19 +3283,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D22" s="7">
-        <v>0.396748</v>
+        <v>0.400866</v>
       </c>
       <c r="E22" s="8">
-        <v>3297507824.2</v>
+        <v>3325076316.19</v>
       </c>
       <c r="F22" s="9">
-        <v>18941</v>
+        <v>18988</v>
       </c>
       <c r="G22" s="8">
-        <v>1308278246.15</v>
+        <v>1332911110.42</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3298,10 +3306,10 @@
         <v>46</v>
       </c>
       <c r="C23" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D23" s="10">
-        <v>0.09398</v>
+        <v>46140</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.094152</v>
       </c>
       <c r="E23" s="8">
         <v>572171617.61</v>
@@ -3310,7 +3318,7 @@
         <v>4545</v>
       </c>
       <c r="G23" s="8">
-        <v>53772952.63</v>
+        <v>53870931.37</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3321,19 +3329,19 @@
         <v>48</v>
       </c>
       <c r="C24" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D24" s="7">
-        <v>0.226665</v>
+        <v>0.227112</v>
       </c>
       <c r="E24" s="8">
-        <v>1221949493.32</v>
+        <v>1219080711.46</v>
       </c>
       <c r="F24" s="9">
-        <v>4996</v>
+        <v>4993</v>
       </c>
       <c r="G24" s="8">
-        <v>276973356.95</v>
+        <v>276868229.16</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3344,19 +3352,19 @@
         <v>50</v>
       </c>
       <c r="C25" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D25" s="7">
-        <v>0.105905</v>
+        <v>0.106001</v>
       </c>
       <c r="E25" s="8">
-        <v>66629212376.27</v>
+        <v>66608499413.17</v>
       </c>
       <c r="F25" s="9">
-        <v>764786</v>
+        <v>764907</v>
       </c>
       <c r="G25" s="8">
-        <v>7056338203.76</v>
+        <v>7060552300.06</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3367,19 +3375,19 @@
         <v>52</v>
       </c>
       <c r="C26" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D26" s="7">
-        <v>0.097532</v>
+        <v>0.097751</v>
       </c>
       <c r="E26" s="8">
-        <v>1683406882.65</v>
+        <v>1683061086.64</v>
       </c>
       <c r="F26" s="9">
-        <v>3253</v>
+        <v>3249</v>
       </c>
       <c r="G26" s="8">
-        <v>164185972.57</v>
+        <v>164520221.08</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3390,19 +3398,19 @@
         <v>54</v>
       </c>
       <c r="C27" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D27" s="7">
-        <v>0.093083</v>
+        <v>0.093322</v>
       </c>
       <c r="E27" s="8">
-        <v>61444565561.15</v>
+        <v>61760408563.81</v>
       </c>
       <c r="F27" s="9">
-        <v>715403</v>
+        <v>715690</v>
       </c>
       <c r="G27" s="8">
-        <v>5719469356.92</v>
+        <v>5763580200.63</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3413,19 +3421,19 @@
         <v>56</v>
       </c>
       <c r="C28" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D28" s="7">
-        <v>0.387768</v>
+        <v>0.387495</v>
       </c>
       <c r="E28" s="8">
-        <v>1051328136.92</v>
+        <v>1050955071.34</v>
       </c>
       <c r="F28" s="9">
-        <v>7929</v>
+        <v>7922</v>
       </c>
       <c r="G28" s="8">
-        <v>407671011.49</v>
+        <v>407240275.93</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3436,19 +3444,19 @@
         <v>58</v>
       </c>
       <c r="C29" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D29" s="7">
-        <v>0.644677</v>
+        <v>0.646255</v>
       </c>
       <c r="E29" s="8">
-        <v>211585213.98</v>
+        <v>210010787.9</v>
       </c>
       <c r="F29" s="9">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="G29" s="8">
-        <v>136404117.94</v>
+        <v>135720586.22</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3459,19 +3467,19 @@
         <v>60</v>
       </c>
       <c r="C30" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D30" s="10">
-        <v>2.36548</v>
+        <v>46140</v>
+      </c>
+      <c r="D30" s="7">
+        <v>2.382151</v>
       </c>
       <c r="E30" s="8">
-        <v>870610738.43</v>
+        <v>871065397.63</v>
       </c>
       <c r="F30" s="9">
-        <v>19467</v>
+        <v>19482</v>
       </c>
       <c r="G30" s="8">
-        <v>2059412025.53</v>
+        <v>2075009700.49</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3482,19 +3490,19 @@
         <v>62</v>
       </c>
       <c r="C31" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D31" s="7">
-        <v>0.523244</v>
+        <v>0.523764</v>
       </c>
       <c r="E31" s="8">
-        <v>2425186466.98</v>
+        <v>2423688091.46</v>
       </c>
       <c r="F31" s="9">
-        <v>13871</v>
+        <v>13861</v>
       </c>
       <c r="G31" s="8">
-        <v>1268963735.49</v>
+        <v>1269440762.73</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3505,19 +3513,19 @@
         <v>64</v>
       </c>
       <c r="C32" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D32" s="7">
-        <v>0.864921</v>
+        <v>0.864557</v>
       </c>
       <c r="E32" s="8">
-        <v>12457038722.12</v>
+        <v>12436627481.27</v>
       </c>
       <c r="F32" s="9">
-        <v>77005</v>
+        <v>76979</v>
       </c>
       <c r="G32" s="8">
-        <v>10774353400.73</v>
+        <v>10752168030.1</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3528,19 +3536,19 @@
         <v>66</v>
       </c>
       <c r="C33" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D33" s="7">
-        <v>0.262253</v>
+        <v>0.264404</v>
       </c>
       <c r="E33" s="8">
-        <v>1315981737.99</v>
+        <v>1316420324.56</v>
       </c>
       <c r="F33" s="9">
-        <v>16208</v>
+        <v>16203</v>
       </c>
       <c r="G33" s="8">
-        <v>345120100.47</v>
+        <v>348067010.48</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3551,19 +3559,19 @@
         <v>68</v>
       </c>
       <c r="C34" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D34" s="7">
-        <v>0.124681</v>
+        <v>0.125378</v>
       </c>
       <c r="E34" s="8">
-        <v>3348756219.13</v>
+        <v>3344428325.06</v>
       </c>
       <c r="F34" s="9">
-        <v>53976</v>
+        <v>53951</v>
       </c>
       <c r="G34" s="8">
-        <v>417525118.94</v>
+        <v>419318973.26</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3574,19 +3582,19 @@
         <v>70</v>
       </c>
       <c r="C35" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D35" s="7">
-        <v>0.174593</v>
+        <v>0.175059</v>
       </c>
       <c r="E35" s="8">
-        <v>10674085802.8</v>
+        <v>10657155061.78</v>
       </c>
       <c r="F35" s="9">
-        <v>36562</v>
+        <v>36593</v>
       </c>
       <c r="G35" s="8">
-        <v>1863616979.23</v>
+        <v>1865632946.36</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3597,19 +3605,19 @@
         <v>72</v>
       </c>
       <c r="C36" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D36" s="7">
-        <v>0.200669</v>
+        <v>0.202259</v>
       </c>
       <c r="E36" s="8">
-        <v>1495512835.02</v>
+        <v>1494936887.82</v>
       </c>
       <c r="F36" s="9">
-        <v>32781</v>
+        <v>32758</v>
       </c>
       <c r="G36" s="8">
-        <v>300102768.87</v>
+        <v>302364241.77</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3620,19 +3628,19 @@
         <v>74</v>
       </c>
       <c r="C37" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D37" s="7">
-        <v>0.817595</v>
+        <v>0.825047</v>
       </c>
       <c r="E37" s="8">
-        <v>2446962356.19</v>
+        <v>2445579044.34</v>
       </c>
       <c r="F37" s="9">
-        <v>52333</v>
+        <v>52311</v>
       </c>
       <c r="G37" s="8">
-        <v>2000624340.27</v>
+        <v>2017717168.43</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3643,19 +3651,19 @@
         <v>76</v>
       </c>
       <c r="C38" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D38" s="7">
-        <v>0.168418</v>
+        <v>0.168606</v>
       </c>
       <c r="E38" s="8">
-        <v>3688716916.06</v>
+        <v>3692232902.71</v>
       </c>
       <c r="F38" s="9">
-        <v>53264</v>
+        <v>53234</v>
       </c>
       <c r="G38" s="8">
-        <v>621245866.79</v>
+        <v>622532808.63</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3666,19 +3674,19 @@
         <v>78</v>
       </c>
       <c r="C39" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D39" s="7">
-        <v>0.105161</v>
+        <v>0.106358</v>
       </c>
       <c r="E39" s="8">
-        <v>8049903724.12</v>
+        <v>8044581548.41</v>
       </c>
       <c r="F39" s="9">
-        <v>95838</v>
+        <v>95790</v>
       </c>
       <c r="G39" s="8">
-        <v>846539345.59</v>
+        <v>855602621.93</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3689,19 +3697,19 @@
         <v>80</v>
       </c>
       <c r="C40" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D40" s="7">
-        <v>0.339287</v>
+        <v>0.338924</v>
       </c>
       <c r="E40" s="8">
-        <v>14215985470.16</v>
+        <v>14195291479.6</v>
       </c>
       <c r="F40" s="9">
-        <v>158459</v>
+        <v>158289</v>
       </c>
       <c r="G40" s="8">
-        <v>4823292152.26</v>
+        <v>4811119155.24</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3712,19 +3720,19 @@
         <v>82</v>
       </c>
       <c r="C41" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D41" s="7">
-        <v>0.363117</v>
+        <v>0.363505</v>
       </c>
       <c r="E41" s="8">
-        <v>75894117098.86</v>
+        <v>76578336478.28</v>
       </c>
       <c r="F41" s="9">
-        <v>163359</v>
+        <v>166409</v>
       </c>
       <c r="G41" s="8">
-        <v>27558473775.93</v>
+        <v>27836596594.84</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3735,19 +3743,19 @@
         <v>84</v>
       </c>
       <c r="C42" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D42" s="7">
-        <v>0.955244</v>
+        <v>0.956603</v>
       </c>
       <c r="E42" s="8">
-        <v>12784626665.83</v>
+        <v>12781093297.35</v>
       </c>
       <c r="F42" s="9">
-        <v>235333</v>
+        <v>235258</v>
       </c>
       <c r="G42" s="8">
-        <v>12212434453.03</v>
+        <v>12226437686.87</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3758,19 +3766,19 @@
         <v>86</v>
       </c>
       <c r="C43" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D43" s="7">
-        <v>0.687183</v>
+        <v>0.691037</v>
       </c>
       <c r="E43" s="8">
-        <v>8854575733.97</v>
+        <v>8844353752.75</v>
       </c>
       <c r="F43" s="9">
-        <v>121508</v>
+        <v>121453</v>
       </c>
       <c r="G43" s="8">
-        <v>6084712380.88</v>
+        <v>6111772917.85</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3781,19 +3789,19 @@
         <v>88</v>
       </c>
       <c r="C44" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D44" s="7">
-        <v>2.986163</v>
+        <v>2.997551</v>
       </c>
       <c r="E44" s="8">
-        <v>8635449135.06</v>
+        <v>8627309095.52</v>
       </c>
       <c r="F44" s="9">
-        <v>364747</v>
+        <v>364916</v>
       </c>
       <c r="G44" s="8">
-        <v>25786856190.22</v>
+        <v>25860798308.49</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3804,19 +3812,19 @@
         <v>90</v>
       </c>
       <c r="C45" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D45" s="10">
-        <v>1.12952</v>
+        <v>46140</v>
+      </c>
+      <c r="D45" s="7">
+        <v>1.138768</v>
       </c>
       <c r="E45" s="8">
-        <v>3661341397.39</v>
+        <v>3660522289.94</v>
       </c>
       <c r="F45" s="9">
-        <v>85810</v>
+        <v>85784</v>
       </c>
       <c r="G45" s="8">
-        <v>4135557253.47</v>
+        <v>4168484095.43</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3827,19 +3835,19 @@
         <v>92</v>
       </c>
       <c r="C46" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D46" s="7">
-        <v>0.422255</v>
+        <v>46140</v>
+      </c>
+      <c r="D46" s="10">
+        <v>0.42203</v>
       </c>
       <c r="E46" s="8">
-        <v>23935737531.07</v>
+        <v>23922918770.64</v>
       </c>
       <c r="F46" s="9">
-        <v>219771</v>
+        <v>219756</v>
       </c>
       <c r="G46" s="8">
-        <v>10106978492.91</v>
+        <v>10096199002.75</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3850,19 +3858,19 @@
         <v>94</v>
       </c>
       <c r="C47" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D47" s="7">
-        <v>1.002634</v>
+        <v>1.005162</v>
       </c>
       <c r="E47" s="8">
-        <v>9131110129.43</v>
+        <v>9122186121.15</v>
       </c>
       <c r="F47" s="9">
-        <v>177653</v>
+        <v>177603</v>
       </c>
       <c r="G47" s="8">
-        <v>9155163594.35</v>
+        <v>9169271897.33</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3873,19 +3881,19 @@
         <v>96</v>
       </c>
       <c r="C48" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D48" s="7">
-        <v>1.346932</v>
+        <v>1.356378</v>
       </c>
       <c r="E48" s="8">
-        <v>730048557.58</v>
+        <v>728990828.22</v>
       </c>
       <c r="F48" s="9">
-        <v>7285</v>
+        <v>7277</v>
       </c>
       <c r="G48" s="8">
-        <v>983325688.16</v>
+        <v>988787132.92</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3896,19 +3904,19 @@
         <v>98</v>
       </c>
       <c r="C49" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D49" s="7">
-        <v>0.129407</v>
+        <v>0.129551</v>
       </c>
       <c r="E49" s="8">
-        <v>93203152130.36</v>
+        <v>93325666229.86</v>
       </c>
       <c r="F49" s="9">
-        <v>207859</v>
+        <v>207969</v>
       </c>
       <c r="G49" s="8">
-        <v>12061147907.33</v>
+        <v>12090396927.34</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3919,19 +3927,19 @@
         <v>100</v>
       </c>
       <c r="C50" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D50" s="7">
-        <v>0.098836</v>
+        <v>0.098946</v>
       </c>
       <c r="E50" s="8">
-        <v>13909326590.99</v>
+        <v>13856602968</v>
       </c>
       <c r="F50" s="9">
-        <v>130511</v>
+        <v>130198</v>
       </c>
       <c r="G50" s="8">
-        <v>1374741417.61</v>
+        <v>1371049272.99</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3942,19 +3950,19 @@
         <v>102</v>
       </c>
       <c r="C51" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D51" s="7">
-        <v>0.494746</v>
+        <v>0.495905</v>
       </c>
       <c r="E51" s="8">
-        <v>20471007320.79</v>
+        <v>20458929234.13</v>
       </c>
       <c r="F51" s="9">
-        <v>138235</v>
+        <v>138130</v>
       </c>
       <c r="G51" s="8">
-        <v>10127946544.11</v>
+        <v>10145687408.34</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3965,19 +3973,19 @@
         <v>104</v>
       </c>
       <c r="C52" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D52" s="7">
-        <v>0.209981</v>
+        <v>46140</v>
+      </c>
+      <c r="D52" s="10">
+        <v>0.21236</v>
       </c>
       <c r="E52" s="8">
-        <v>2623990449.18</v>
+        <v>2627945681.08</v>
       </c>
       <c r="F52" s="9">
-        <v>10409</v>
+        <v>10426</v>
       </c>
       <c r="G52" s="8">
-        <v>550987851.97</v>
+        <v>558071505.74</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3988,19 +3996,19 @@
         <v>106</v>
       </c>
       <c r="C53" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D53" s="7">
-        <v>0.264415</v>
+        <v>0.267671</v>
       </c>
       <c r="E53" s="8">
-        <v>2880850552.96</v>
+        <v>2884334956.73</v>
       </c>
       <c r="F53" s="9">
-        <v>10726</v>
+        <v>10733</v>
       </c>
       <c r="G53" s="8">
-        <v>761738683.28</v>
+        <v>772054261.42</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -4011,19 +4019,19 @@
         <v>108</v>
       </c>
       <c r="C54" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D54" s="7">
-        <v>0.332235</v>
+        <v>0.332551</v>
       </c>
       <c r="E54" s="8">
-        <v>4542433378.21</v>
+        <v>4535881948.44</v>
       </c>
       <c r="F54" s="9">
-        <v>15943</v>
+        <v>15945</v>
       </c>
       <c r="G54" s="8">
-        <v>1509156977.17</v>
+        <v>1508410413.44</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4034,19 +4042,19 @@
         <v>110</v>
       </c>
       <c r="C55" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D55" s="7">
-        <v>0.313077</v>
+        <v>0.313084</v>
       </c>
       <c r="E55" s="8">
-        <v>2566036643.65</v>
+        <v>2566321141.41</v>
       </c>
       <c r="F55" s="9">
-        <v>10200</v>
+        <v>10216</v>
       </c>
       <c r="G55" s="8">
-        <v>803366130.49</v>
+        <v>803473939.84</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -4057,19 +4065,19 @@
         <v>112</v>
       </c>
       <c r="C56" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D56" s="10">
-        <v>0.22232</v>
+        <v>46140</v>
+      </c>
+      <c r="D56" s="7">
+        <v>0.222348</v>
       </c>
       <c r="E56" s="8">
-        <v>1891860702.2</v>
+        <v>1887342587.5</v>
       </c>
       <c r="F56" s="9">
-        <v>6701</v>
+        <v>6706</v>
       </c>
       <c r="G56" s="8">
-        <v>420598231.74</v>
+        <v>419646089.86</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4080,19 +4088,19 @@
         <v>114</v>
       </c>
       <c r="C57" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D57" s="7">
-        <v>0.114478</v>
+        <v>0.114583</v>
       </c>
       <c r="E57" s="8">
-        <v>1638165938.06</v>
+        <v>1637991946.82</v>
       </c>
       <c r="F57" s="9">
         <v>3929</v>
       </c>
       <c r="G57" s="8">
-        <v>187533934.27</v>
+        <v>187685665.56</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -4103,19 +4111,19 @@
         <v>116</v>
       </c>
       <c r="C58" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D58" s="7">
-        <v>0.306302</v>
+        <v>0.307757</v>
       </c>
       <c r="E58" s="8">
-        <v>4423265309.11</v>
+        <v>4427999634.69</v>
       </c>
       <c r="F58" s="9">
-        <v>16734</v>
+        <v>16750</v>
       </c>
       <c r="G58" s="8">
-        <v>1354854455.07</v>
+        <v>1362749134.91</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -4126,19 +4134,19 @@
         <v>118</v>
       </c>
       <c r="C59" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D59" s="7">
-        <v>0.243539</v>
+        <v>0.244935</v>
       </c>
       <c r="E59" s="8">
-        <v>2793690468.87</v>
+        <v>2794855219.51</v>
       </c>
       <c r="F59" s="9">
-        <v>11278</v>
+        <v>11296</v>
       </c>
       <c r="G59" s="8">
-        <v>680373801.84</v>
+        <v>684558253.31</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -4149,19 +4157,19 @@
         <v>120</v>
       </c>
       <c r="C60" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D60" s="7">
-        <v>0.176138</v>
+        <v>0.177692</v>
       </c>
       <c r="E60" s="8">
-        <v>180109297.26</v>
+        <v>180502067.42</v>
       </c>
       <c r="F60" s="9">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G60" s="8">
-        <v>31724174.77</v>
+        <v>32073717.95</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -4172,19 +4180,19 @@
         <v>122</v>
       </c>
       <c r="C61" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D61" s="7">
-        <v>0.380416</v>
+        <v>0.381819</v>
       </c>
       <c r="E61" s="8">
-        <v>864280705.66</v>
+        <v>862881124.4</v>
       </c>
       <c r="F61" s="9">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G61" s="8">
-        <v>328785863.52</v>
+        <v>329464692.99</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -4195,19 +4203,19 @@
         <v>124</v>
       </c>
       <c r="C62" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D62" s="7">
-        <v>0.073081</v>
+        <v>0.073115</v>
       </c>
       <c r="E62" s="8">
-        <v>173968838.95</v>
+        <v>174034376.25</v>
       </c>
       <c r="F62" s="9">
         <v>224</v>
       </c>
       <c r="G62" s="8">
-        <v>12713799.42</v>
+        <v>12724532.88</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -4218,19 +4226,19 @@
         <v>126</v>
       </c>
       <c r="C63" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D63" s="7">
-        <v>0.142238</v>
+        <v>0.143474</v>
       </c>
       <c r="E63" s="8">
-        <v>109491935.24</v>
+        <v>109441120.31</v>
       </c>
       <c r="F63" s="9">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G63" s="8">
-        <v>15573952.67</v>
+        <v>15701964.42</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -4241,19 +4249,19 @@
         <v>128</v>
       </c>
       <c r="C64" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D64" s="7">
-        <v>0.257268</v>
+        <v>0.258843</v>
       </c>
       <c r="E64" s="8">
-        <v>217515297.16</v>
+        <v>215075027.4</v>
       </c>
       <c r="F64" s="9">
         <v>333</v>
       </c>
       <c r="G64" s="8">
-        <v>55959649.89</v>
+        <v>55670559.15</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4264,19 +4272,19 @@
         <v>130</v>
       </c>
       <c r="C65" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D65" s="7">
-        <v>0.332137</v>
+        <v>0.334767</v>
       </c>
       <c r="E65" s="8">
-        <v>639961691.07</v>
+        <v>639289054.72</v>
       </c>
       <c r="F65" s="9">
         <v>445</v>
       </c>
       <c r="G65" s="8">
-        <v>212555168.07</v>
+        <v>214012856.77</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -4287,19 +4295,19 @@
         <v>132</v>
       </c>
       <c r="C66" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D66" s="7">
-        <v>0.592507</v>
+        <v>0.593251</v>
       </c>
       <c r="E66" s="8">
-        <v>13017077791.81</v>
+        <v>12979115994.99</v>
       </c>
       <c r="F66" s="9">
-        <v>128208</v>
+        <v>127875</v>
       </c>
       <c r="G66" s="8">
-        <v>7712708065.79</v>
+        <v>7699871441.03</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4310,19 +4318,19 @@
         <v>134</v>
       </c>
       <c r="C67" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D67" s="7">
-        <v>0.259418</v>
+        <v>0.261514</v>
       </c>
       <c r="E67" s="8">
-        <v>2019779191.41</v>
+        <v>2017861704.82</v>
       </c>
       <c r="F67" s="9">
-        <v>6117</v>
+        <v>6116</v>
       </c>
       <c r="G67" s="8">
-        <v>523966428.61</v>
+        <v>527698434.66</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -4333,19 +4341,19 @@
         <v>136</v>
       </c>
       <c r="C68" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D68" s="7">
-        <v>1.999853</v>
+        <v>2.012008</v>
       </c>
       <c r="E68" s="8">
-        <v>7027046389.53</v>
+        <v>7016855831.26</v>
       </c>
       <c r="F68" s="9">
-        <v>236485</v>
+        <v>236384</v>
       </c>
       <c r="G68" s="8">
-        <v>14053061287.49</v>
+        <v>14117969065.53</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -4356,19 +4364,19 @@
         <v>138</v>
       </c>
       <c r="C69" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D69" s="7">
-        <v>1.002633</v>
+        <v>1.005128</v>
       </c>
       <c r="E69" s="8">
-        <v>6564002591.83</v>
+        <v>6560182681.27</v>
       </c>
       <c r="F69" s="9">
-        <v>163661</v>
+        <v>163606</v>
       </c>
       <c r="G69" s="8">
-        <v>6581284722.93</v>
+        <v>6593820782.13</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -4379,19 +4387,19 @@
         <v>140</v>
       </c>
       <c r="C70" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D70" s="10">
-        <v>0.32358</v>
+        <v>46140</v>
+      </c>
+      <c r="D70" s="7">
+        <v>0.325856</v>
       </c>
       <c r="E70" s="8">
-        <v>12180884099.69</v>
+        <v>12167121737.01</v>
       </c>
       <c r="F70" s="9">
-        <v>189894</v>
+        <v>189827</v>
       </c>
       <c r="G70" s="8">
-        <v>3941494762.02</v>
+        <v>3964728957.07</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4402,19 +4410,19 @@
         <v>142</v>
       </c>
       <c r="C71" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D71" s="7">
-        <v>0.098042</v>
+        <v>0.098147</v>
       </c>
       <c r="E71" s="8">
-        <v>7559638011.39</v>
+        <v>7412461772.88</v>
       </c>
       <c r="F71" s="9">
-        <v>117218</v>
+        <v>116056</v>
       </c>
       <c r="G71" s="8">
-        <v>741160322.28</v>
+        <v>727512790.75</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -4425,19 +4433,19 @@
         <v>144</v>
       </c>
       <c r="C72" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D72" s="7">
-        <v>0.096313</v>
+        <v>0.096508</v>
       </c>
       <c r="E72" s="8">
-        <v>386563865775.01</v>
+        <v>386321414209.02</v>
       </c>
       <c r="F72" s="9">
-        <v>1408995</v>
+        <v>1408343</v>
       </c>
       <c r="G72" s="8">
-        <v>37231161008.97</v>
+        <v>37283107140.32</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4448,19 +4456,19 @@
         <v>146</v>
       </c>
       <c r="C73" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D73" s="7">
-        <v>1.096794</v>
+        <v>1.098602</v>
       </c>
       <c r="E73" s="8">
-        <v>6408629307.92</v>
+        <v>6402957014.41</v>
       </c>
       <c r="F73" s="9">
-        <v>263159</v>
+        <v>262961</v>
       </c>
       <c r="G73" s="8">
-        <v>7028947140.47</v>
+        <v>7034299653.56</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4471,19 +4479,19 @@
         <v>148</v>
       </c>
       <c r="C74" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D74" s="7">
-        <v>0.507778</v>
+        <v>0.508683</v>
       </c>
       <c r="E74" s="8">
-        <v>6771346402.13</v>
+        <v>6752121549.88</v>
       </c>
       <c r="F74" s="9">
-        <v>65979</v>
+        <v>65914</v>
       </c>
       <c r="G74" s="8">
-        <v>3438341790.39</v>
+        <v>3434689133.89</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -4494,19 +4502,19 @@
         <v>150</v>
       </c>
       <c r="C75" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D75" s="7">
-        <v>1.537753</v>
+        <v>1.547221</v>
       </c>
       <c r="E75" s="8">
-        <v>492399818.57</v>
+        <v>492406409.32</v>
       </c>
       <c r="F75" s="9">
         <v>4986</v>
       </c>
       <c r="G75" s="8">
-        <v>757189256.66</v>
+        <v>761861688.66</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4517,19 +4525,19 @@
         <v>152</v>
       </c>
       <c r="C76" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D76" s="7">
-        <v>0.708447</v>
+        <v>0.708689</v>
       </c>
       <c r="E76" s="8">
-        <v>213299843908.75</v>
+        <v>212755846162.82</v>
       </c>
       <c r="F76" s="9">
-        <v>721183</v>
+        <v>721376</v>
       </c>
       <c r="G76" s="8">
-        <v>151111708028.88</v>
+        <v>150777731699.54</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4540,19 +4548,19 @@
         <v>154</v>
       </c>
       <c r="C77" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D77" s="7">
-        <v>0.577296</v>
+        <v>0.579326</v>
       </c>
       <c r="E77" s="8">
-        <v>194377062.39</v>
+        <v>194378885.35</v>
       </c>
       <c r="F77" s="9">
-        <v>22328</v>
+        <v>22329</v>
       </c>
       <c r="G77" s="8">
-        <v>112213045.21</v>
+        <v>112608662.17</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4563,19 +4571,19 @@
         <v>156</v>
       </c>
       <c r="C78" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D78" s="10">
-        <v>0.30175</v>
+        <v>46140</v>
+      </c>
+      <c r="D78" s="7">
+        <v>0.301386</v>
       </c>
       <c r="E78" s="8">
-        <v>395596695.66</v>
+        <v>395600857.66</v>
       </c>
       <c r="F78" s="9">
-        <v>33156</v>
+        <v>33157</v>
       </c>
       <c r="G78" s="8">
-        <v>119371482.12</v>
+        <v>119228515.56</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4586,19 +4594,19 @@
         <v>158</v>
       </c>
       <c r="C79" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D79" s="7">
-        <v>0.158327</v>
+        <v>0.159641</v>
       </c>
       <c r="E79" s="8">
-        <v>3118555170.08</v>
+        <v>3115666716.56</v>
       </c>
       <c r="F79" s="9">
-        <v>6946</v>
+        <v>6945</v>
       </c>
       <c r="G79" s="8">
-        <v>493752614.77</v>
+        <v>497387941.02</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4609,19 +4617,19 @@
         <v>160</v>
       </c>
       <c r="C80" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D80" s="10">
-        <v>0.33214</v>
+        <v>46140</v>
+      </c>
+      <c r="D80" s="7">
+        <v>0.332585</v>
       </c>
       <c r="E80" s="8">
-        <v>236481092.13</v>
+        <v>236543105.41</v>
       </c>
       <c r="F80" s="9">
-        <v>20840</v>
+        <v>20837</v>
       </c>
       <c r="G80" s="8">
-        <v>78544759.29</v>
+        <v>78670770.63</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4632,19 +4640,19 @@
         <v>162</v>
       </c>
       <c r="C81" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D81" s="7">
-        <v>0.176928</v>
+        <v>0.178493</v>
       </c>
       <c r="E81" s="8">
-        <v>702581108.31</v>
+        <v>702558017.8</v>
       </c>
       <c r="F81" s="9">
         <v>2353</v>
       </c>
       <c r="G81" s="8">
-        <v>124306047.53</v>
+        <v>125401838.86</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4655,19 +4663,19 @@
         <v>164</v>
       </c>
       <c r="C82" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D82" s="7">
-        <v>1.882886</v>
+        <v>1.888729</v>
       </c>
       <c r="E82" s="8">
-        <v>84211800.74</v>
+        <v>84217518.3</v>
       </c>
       <c r="F82" s="9">
-        <v>13724</v>
+        <v>13725</v>
       </c>
       <c r="G82" s="8">
-        <v>158561180.36</v>
+        <v>159064100.59</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4678,19 +4686,19 @@
         <v>166</v>
       </c>
       <c r="C83" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D83" s="7">
-        <v>0.094886</v>
+        <v>46140</v>
+      </c>
+      <c r="D83" s="10">
+        <v>0.09499</v>
       </c>
       <c r="E83" s="8">
-        <v>10118443449.65</v>
+        <v>10153121185.29</v>
       </c>
       <c r="F83" s="9">
-        <v>169804</v>
+        <v>169371</v>
       </c>
       <c r="G83" s="8">
-        <v>960098682.14</v>
+        <v>964448376.44</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4701,19 +4709,19 @@
         <v>168</v>
       </c>
       <c r="C84" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D84" s="7">
-        <v>0.083158</v>
+        <v>0.083246</v>
       </c>
       <c r="E84" s="8">
-        <v>9405190906.6</v>
+        <v>9029538307.12</v>
       </c>
       <c r="F84" s="9">
-        <v>140774</v>
+        <v>140293</v>
       </c>
       <c r="G84" s="8">
-        <v>782118649.82</v>
+        <v>751674817.1</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4724,19 +4732,19 @@
         <v>170</v>
       </c>
       <c r="C85" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D85" s="7">
-        <v>0.267813</v>
+        <v>0.269657</v>
       </c>
       <c r="E85" s="8">
-        <v>4273637583.7</v>
+        <v>4271507680.33</v>
       </c>
       <c r="F85" s="9">
-        <v>80640</v>
+        <v>80144</v>
       </c>
       <c r="G85" s="8">
-        <v>1144534232.04</v>
+        <v>1151841662.7</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4747,19 +4755,19 @@
         <v>172</v>
       </c>
       <c r="C86" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D86" s="10">
-        <v>0.91774</v>
+        <v>46140</v>
+      </c>
+      <c r="D86" s="7">
+        <v>0.908166</v>
       </c>
       <c r="E86" s="8">
-        <v>4629965973.46</v>
+        <v>4620425427.65</v>
       </c>
       <c r="F86" s="9">
-        <v>87315</v>
+        <v>87247</v>
       </c>
       <c r="G86" s="8">
-        <v>4249105098.12</v>
+        <v>4196115108.55</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4770,19 +4778,19 @@
         <v>174</v>
       </c>
       <c r="C87" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D87" s="7">
-        <v>0.225246</v>
+        <v>0.225567</v>
       </c>
       <c r="E87" s="8">
-        <v>12583250767.35</v>
+        <v>12573597945.65</v>
       </c>
       <c r="F87" s="9">
-        <v>143700</v>
+        <v>143818</v>
       </c>
       <c r="G87" s="8">
-        <v>2834326984.04</v>
+        <v>2836193899.75</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4793,19 +4801,19 @@
         <v>176</v>
       </c>
       <c r="C88" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D88" s="7">
-        <v>0.165543</v>
+        <v>0.165861</v>
       </c>
       <c r="E88" s="8">
-        <v>18414326616.78</v>
+        <v>18406957619.42</v>
       </c>
       <c r="F88" s="9">
-        <v>90995</v>
+        <v>90964</v>
       </c>
       <c r="G88" s="8">
-        <v>3048370146.19</v>
+        <v>3052992414.47</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4816,19 +4824,19 @@
         <v>178</v>
       </c>
       <c r="C89" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D89" s="7">
-        <v>0.633992</v>
+        <v>0.635126</v>
       </c>
       <c r="E89" s="8">
-        <v>2288908284.78</v>
+        <v>2284046554.7</v>
       </c>
       <c r="F89" s="9">
-        <v>36070</v>
+        <v>36037</v>
       </c>
       <c r="G89" s="8">
-        <v>1451150447.03</v>
+        <v>1450656886.21</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4839,19 +4847,19 @@
         <v>180</v>
       </c>
       <c r="C90" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D90" s="7">
-        <v>0.845023</v>
+        <v>0.846386</v>
       </c>
       <c r="E90" s="8">
-        <v>19282717140.67</v>
+        <v>19247520226.99</v>
       </c>
       <c r="F90" s="9">
-        <v>273889</v>
+        <v>273650</v>
       </c>
       <c r="G90" s="8">
-        <v>16294347159.92</v>
+        <v>16290826888.91</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4862,19 +4870,19 @@
         <v>182</v>
       </c>
       <c r="C91" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D91" s="7">
-        <v>0.789533</v>
+        <v>0.795831</v>
       </c>
       <c r="E91" s="8">
-        <v>3483473318.24</v>
+        <v>3488922932.16</v>
       </c>
       <c r="F91" s="9">
-        <v>29037</v>
+        <v>29082</v>
       </c>
       <c r="G91" s="8">
-        <v>2750317638.81</v>
+        <v>2776591709.79</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4885,19 +4893,19 @@
         <v>184</v>
       </c>
       <c r="C92" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D92" s="7">
-        <v>0.830609</v>
+        <v>0.832532</v>
       </c>
       <c r="E92" s="8">
-        <v>12376077578.08</v>
+        <v>12360119203.21</v>
       </c>
       <c r="F92" s="9">
-        <v>189524</v>
+        <v>189396</v>
       </c>
       <c r="G92" s="8">
-        <v>10279687376.57</v>
+        <v>10290193096.29</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4908,19 +4916,19 @@
         <v>186</v>
       </c>
       <c r="C93" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D93" s="7">
-        <v>0.087411</v>
+        <v>0.087501</v>
       </c>
       <c r="E93" s="8">
-        <v>7649751258.84</v>
+        <v>7631860281.44</v>
       </c>
       <c r="F93" s="9">
-        <v>156705</v>
+        <v>156504</v>
       </c>
       <c r="G93" s="8">
-        <v>668669064.18</v>
+        <v>667797873.54</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4931,19 +4939,19 @@
         <v>188</v>
       </c>
       <c r="C94" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D94" s="7">
-        <v>0.120098</v>
+        <v>0.120312</v>
       </c>
       <c r="E94" s="8">
-        <v>12000547152.21</v>
+        <v>11943441031.43</v>
       </c>
       <c r="F94" s="9">
-        <v>33389</v>
+        <v>33336</v>
       </c>
       <c r="G94" s="8">
-        <v>1441247504.04</v>
+        <v>1436934385.7</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4954,19 +4962,19 @@
         <v>190</v>
       </c>
       <c r="C95" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D95" s="7">
-        <v>0.126872</v>
+        <v>0.127018</v>
       </c>
       <c r="E95" s="8">
-        <v>72539076811.07</v>
+        <v>72430044386.53</v>
       </c>
       <c r="F95" s="9">
-        <v>212819</v>
+        <v>212656</v>
       </c>
       <c r="G95" s="8">
-        <v>9203153420.52</v>
+        <v>9199885428.42</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4977,19 +4985,19 @@
         <v>192</v>
       </c>
       <c r="C96" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D96" s="7">
-        <v>0.446403</v>
+        <v>0.448796</v>
       </c>
       <c r="E96" s="8">
-        <v>31512882419.26</v>
+        <v>31525720881.64</v>
       </c>
       <c r="F96" s="9">
-        <v>280202</v>
+        <v>280627</v>
       </c>
       <c r="G96" s="8">
-        <v>14067458384.49</v>
+        <v>14148606766.32</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -5000,19 +5008,19 @@
         <v>194</v>
       </c>
       <c r="C97" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D97" s="10">
-        <v>0.09555</v>
+        <v>46140</v>
+      </c>
+      <c r="D97" s="7">
+        <v>0.095908</v>
       </c>
       <c r="E97" s="8">
-        <v>24582381865.74</v>
+        <v>24562829986.81</v>
       </c>
       <c r="F97" s="9">
-        <v>442362</v>
+        <v>442248</v>
       </c>
       <c r="G97" s="8">
-        <v>2348849738.28</v>
+        <v>2355771553.37</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -5023,19 +5031,19 @@
         <v>196</v>
       </c>
       <c r="C98" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D98" s="7">
-        <v>0.245143</v>
+        <v>0.244919</v>
       </c>
       <c r="E98" s="8">
-        <v>1294252581.08</v>
+        <v>1291717634.86</v>
       </c>
       <c r="F98" s="9">
-        <v>7132</v>
+        <v>7087</v>
       </c>
       <c r="G98" s="8">
-        <v>317277223.58</v>
+        <v>316365582.94</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -5046,19 +5054,19 @@
         <v>198</v>
       </c>
       <c r="C99" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D99" s="7">
-        <v>1.043758</v>
+        <v>1.046751</v>
       </c>
       <c r="E99" s="8">
-        <v>1922518256.15</v>
+        <v>2251871682.4</v>
       </c>
       <c r="F99" s="9">
-        <v>36761</v>
+        <v>38452</v>
       </c>
       <c r="G99" s="8">
-        <v>2006642849.27</v>
+        <v>2357148845.61</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5069,19 +5077,19 @@
         <v>200</v>
       </c>
       <c r="C100" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D100" s="7">
-        <v>2.592013</v>
+        <v>2.610295</v>
       </c>
       <c r="E100" s="8">
-        <v>12112865687.38</v>
+        <v>12083482042.61</v>
       </c>
       <c r="F100" s="9">
-        <v>304895</v>
+        <v>305065</v>
       </c>
       <c r="G100" s="8">
-        <v>31396709772.26</v>
+        <v>31541454786.1</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5092,19 +5100,19 @@
         <v>202</v>
       </c>
       <c r="C101" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D101" s="7">
-        <v>0.355676</v>
+        <v>0.355392</v>
       </c>
       <c r="E101" s="8">
-        <v>31834488261.32</v>
+        <v>28470379250.66</v>
       </c>
       <c r="F101" s="9">
-        <v>339881</v>
+        <v>336884</v>
       </c>
       <c r="G101" s="8">
-        <v>11322761407.6</v>
+        <v>10118149463.49</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5115,19 +5123,19 @@
         <v>204</v>
       </c>
       <c r="C102" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D102" s="10">
-        <v>0.36565</v>
+        <v>46140</v>
+      </c>
+      <c r="D102" s="7">
+        <v>0.365982</v>
       </c>
       <c r="E102" s="8">
-        <v>204511358107.5</v>
+        <v>207903047197.34</v>
       </c>
       <c r="F102" s="9">
-        <v>355318</v>
+        <v>356810</v>
       </c>
       <c r="G102" s="8">
-        <v>74779656526.71</v>
+        <v>76088868615.6</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5138,19 +5146,19 @@
         <v>206</v>
       </c>
       <c r="C103" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D103" s="7">
-        <v>0.123966</v>
+        <v>0.124207</v>
       </c>
       <c r="E103" s="8">
-        <v>9145601340.73</v>
+        <v>9154881071.99</v>
       </c>
       <c r="F103" s="9">
-        <v>28545</v>
+        <v>28549</v>
       </c>
       <c r="G103" s="8">
-        <v>1133744177.27</v>
+        <v>1137097967</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -5161,19 +5169,19 @@
         <v>208</v>
       </c>
       <c r="C104" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D104" s="7">
-        <v>0.280924</v>
+        <v>0.279963</v>
       </c>
       <c r="E104" s="8">
-        <v>1728334037.38</v>
+        <v>1723720090.19</v>
       </c>
       <c r="F104" s="9">
-        <v>7821</v>
+        <v>7822</v>
       </c>
       <c r="G104" s="8">
-        <v>485530130.1</v>
+        <v>482577834.72</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -5184,19 +5192,19 @@
         <v>210</v>
       </c>
       <c r="C105" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D105" s="7">
-        <v>1.042793</v>
+        <v>46140</v>
+      </c>
+      <c r="D105" s="10">
+        <v>1.05357</v>
       </c>
       <c r="E105" s="8">
-        <v>247101740.68</v>
+        <v>247223130.95</v>
       </c>
       <c r="F105" s="9">
-        <v>4065</v>
+        <v>4070</v>
       </c>
       <c r="G105" s="8">
-        <v>257675867.57</v>
+        <v>260466917.63</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5207,19 +5215,19 @@
         <v>212</v>
       </c>
       <c r="C106" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D106" s="7">
-        <v>0.987703</v>
+        <v>0.994175</v>
       </c>
       <c r="E106" s="8">
-        <v>582156101.25</v>
+        <v>588563303.48</v>
       </c>
       <c r="F106" s="9">
-        <v>15301</v>
+        <v>15324</v>
       </c>
       <c r="G106" s="8">
-        <v>574997469.01</v>
+        <v>585134708.15</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5230,19 +5238,19 @@
         <v>214</v>
       </c>
       <c r="C107" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D107" s="7">
-        <v>0.176395</v>
+        <v>0.177296</v>
       </c>
       <c r="E107" s="8">
-        <v>374413365.78</v>
+        <v>375736105.32</v>
       </c>
       <c r="F107" s="9">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="G107" s="8">
-        <v>66044655.3</v>
+        <v>66616427.15</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -5253,19 +5261,19 @@
         <v>216</v>
       </c>
       <c r="C108" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D108" s="7">
-        <v>1.461052</v>
+        <v>1.465272</v>
       </c>
       <c r="E108" s="8">
-        <v>1008904479.31</v>
+        <v>1012498283.93</v>
       </c>
       <c r="F108" s="9">
-        <v>21939</v>
+        <v>21935</v>
       </c>
       <c r="G108" s="8">
-        <v>1474061958.6</v>
+        <v>1483585885.77</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -5276,19 +5284,19 @@
         <v>218</v>
       </c>
       <c r="C109" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D109" s="7">
-        <v>0.096242</v>
+        <v>0.096422</v>
       </c>
       <c r="E109" s="8">
-        <v>5454200890.49</v>
+        <v>5443602637.64</v>
       </c>
       <c r="F109" s="9">
-        <v>24087</v>
+        <v>24065</v>
       </c>
       <c r="G109" s="8">
-        <v>524921859.68</v>
+        <v>524882849.74</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -5299,19 +5307,19 @@
         <v>220</v>
       </c>
       <c r="C110" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D110" s="7">
-        <v>0.287193</v>
+        <v>0.286914</v>
       </c>
       <c r="E110" s="8">
-        <v>1637033397.47</v>
+        <v>1638131477.2</v>
       </c>
       <c r="F110" s="9">
-        <v>33162</v>
+        <v>33181</v>
       </c>
       <c r="G110" s="8">
-        <v>470143739.3</v>
+        <v>470003600.93</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5322,19 +5330,19 @@
         <v>222</v>
       </c>
       <c r="C111" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D111" s="10">
-        <v>0.21045</v>
+        <v>46140</v>
+      </c>
+      <c r="D111" s="7">
+        <v>0.211521</v>
       </c>
       <c r="E111" s="8">
-        <v>589336198.47</v>
+        <v>590368789.06</v>
       </c>
       <c r="F111" s="9">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G111" s="8">
-        <v>124025730.8</v>
+        <v>124875187.13</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -5345,19 +5353,19 @@
         <v>224</v>
       </c>
       <c r="C112" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D112" s="7">
-        <v>0.407765</v>
+        <v>46140</v>
+      </c>
+      <c r="D112" s="10">
+        <v>0.40473</v>
       </c>
       <c r="E112" s="8">
-        <v>141347272.81</v>
+        <v>144029814.05</v>
       </c>
       <c r="F112" s="9">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="G112" s="8">
-        <v>57636406.95</v>
+        <v>58293220.13</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -5368,19 +5376,19 @@
         <v>226</v>
       </c>
       <c r="C113" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D113" s="7">
-        <v>0.109079</v>
+        <v>0.108916</v>
       </c>
       <c r="E113" s="8">
-        <v>194478288.39</v>
+        <v>194540892.5</v>
       </c>
       <c r="F113" s="9">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="G113" s="8">
-        <v>21213458.34</v>
+        <v>21188661.26</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5391,19 +5399,19 @@
         <v>228</v>
       </c>
       <c r="C114" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D114" s="7">
-        <v>0.064202</v>
+        <v>46140</v>
+      </c>
+      <c r="D114" s="10">
+        <v>0.06413</v>
       </c>
       <c r="E114" s="8">
-        <v>1217759402240.95</v>
+        <v>1217548689402.59</v>
       </c>
       <c r="F114" s="9">
-        <v>788182</v>
+        <v>788157</v>
       </c>
       <c r="G114" s="8">
-        <v>78182742507.9</v>
+        <v>78081637864.9</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -5414,19 +5422,19 @@
         <v>230</v>
       </c>
       <c r="C115" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D115" s="7">
-        <v>0.015336</v>
+        <v>0.015353</v>
       </c>
       <c r="E115" s="8">
-        <v>6301396269.66</v>
+        <v>6398971181.81</v>
       </c>
       <c r="F115" s="9">
-        <v>1250</v>
+        <v>1262</v>
       </c>
       <c r="G115" s="8">
-        <v>96636734.36</v>
+        <v>98240491.88</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -5437,19 +5445,19 @@
         <v>232</v>
       </c>
       <c r="C116" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D116" s="7">
-        <v>0.124603</v>
+        <v>46140</v>
+      </c>
+      <c r="D116" s="10">
+        <v>0.12527</v>
       </c>
       <c r="E116" s="8">
-        <v>7382362450.21</v>
+        <v>7392381365.4</v>
       </c>
       <c r="F116" s="9">
-        <v>24534</v>
+        <v>24577</v>
       </c>
       <c r="G116" s="8">
-        <v>919862169.56</v>
+        <v>926041702.13</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -5460,19 +5468,19 @@
         <v>234</v>
       </c>
       <c r="C117" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D117" s="7">
-        <v>0.120158</v>
+        <v>0.122199</v>
       </c>
       <c r="E117" s="8">
-        <v>27199974795.88</v>
+        <v>27504561615.08</v>
       </c>
       <c r="F117" s="9">
-        <v>67697</v>
+        <v>67897</v>
       </c>
       <c r="G117" s="8">
-        <v>3268307727.89</v>
+        <v>3361019982.39</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -5483,19 +5491,19 @@
         <v>236</v>
       </c>
       <c r="C118" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D118" s="7">
-        <v>0.569577</v>
+        <v>0.570429</v>
       </c>
       <c r="E118" s="8">
-        <v>90877388.1</v>
+        <v>90881237.94</v>
       </c>
       <c r="F118" s="9">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G118" s="8">
-        <v>51761666.7</v>
+        <v>51841337.91</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -5506,19 +5514,19 @@
         <v>238</v>
       </c>
       <c r="C119" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D119" s="7">
-        <v>0.752273</v>
+        <v>0.753663</v>
       </c>
       <c r="E119" s="8">
-        <v>22916390152.18</v>
+        <v>22920009488.15</v>
       </c>
       <c r="F119" s="9">
-        <v>149168</v>
+        <v>149161</v>
       </c>
       <c r="G119" s="8">
-        <v>17239379697.02</v>
+        <v>17273957478.93</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5529,19 +5537,19 @@
         <v>240</v>
       </c>
       <c r="C120" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D120" s="7">
-        <v>0.122402</v>
+        <v>0.122501</v>
       </c>
       <c r="E120" s="8">
-        <v>14837751735.93</v>
+        <v>14820253235.39</v>
       </c>
       <c r="F120" s="9">
-        <v>44631</v>
+        <v>44613</v>
       </c>
       <c r="G120" s="8">
-        <v>1816175581.36</v>
+        <v>1815502797.59</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5552,19 +5560,19 @@
         <v>242</v>
       </c>
       <c r="C121" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D121" s="7">
-        <v>0.105103</v>
+        <v>0.105339</v>
       </c>
       <c r="E121" s="8">
-        <v>42491887166.29</v>
+        <v>42452719955.32</v>
       </c>
       <c r="F121" s="9">
-        <v>335179</v>
+        <v>335088</v>
       </c>
       <c r="G121" s="8">
-        <v>4466034687.89</v>
+        <v>4471926530.73</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -5575,19 +5583,19 @@
         <v>244</v>
       </c>
       <c r="C122" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D122" s="7">
-        <v>0.093703</v>
+        <v>0.093573</v>
       </c>
       <c r="E122" s="8">
-        <v>9697836736.1</v>
+        <v>9695290545.2</v>
       </c>
       <c r="F122" s="9">
-        <v>148031</v>
+        <v>148029</v>
       </c>
       <c r="G122" s="8">
-        <v>908719919.49</v>
+        <v>907213524.03</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -5598,19 +5606,19 @@
         <v>246</v>
       </c>
       <c r="C123" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D123" s="7">
-        <v>0.048105</v>
+        <v>0.048141</v>
       </c>
       <c r="E123" s="8">
-        <v>28007378193.5</v>
+        <v>28004712009.79</v>
       </c>
       <c r="F123" s="9">
-        <v>34428</v>
+        <v>34420</v>
       </c>
       <c r="G123" s="8">
-        <v>1347284237.09</v>
+        <v>1348169506.01</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -5621,19 +5629,19 @@
         <v>248</v>
       </c>
       <c r="C124" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D124" s="7">
-        <v>0.118675</v>
+        <v>0.118465</v>
       </c>
       <c r="E124" s="8">
-        <v>6280086430.13</v>
+        <v>6280305944.37</v>
       </c>
       <c r="F124" s="9">
-        <v>43259</v>
+        <v>43245</v>
       </c>
       <c r="G124" s="8">
-        <v>745290234.79</v>
+        <v>743995087.97</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5644,19 +5652,19 @@
         <v>250</v>
       </c>
       <c r="C125" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D125" s="7">
-        <v>0.090163</v>
+        <v>0.090316</v>
       </c>
       <c r="E125" s="8">
-        <v>2965629621.74</v>
+        <v>2967066369.79</v>
       </c>
       <c r="F125" s="9">
-        <v>83377</v>
+        <v>83402</v>
       </c>
       <c r="G125" s="8">
-        <v>267388859.53</v>
+        <v>267973843.41</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5667,19 +5675,19 @@
         <v>252</v>
       </c>
       <c r="C126" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D126" s="7">
-        <v>0.082362</v>
+        <v>0.083084</v>
       </c>
       <c r="E126" s="8">
-        <v>1121418125.75</v>
+        <v>1120510821.94</v>
       </c>
       <c r="F126" s="9">
-        <v>121893</v>
+        <v>121885</v>
       </c>
       <c r="G126" s="8">
-        <v>92362501.11</v>
+        <v>93096948.15</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5690,19 +5698,19 @@
         <v>254</v>
       </c>
       <c r="C127" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D127" s="7">
-        <v>0.769379</v>
+        <v>0.770874</v>
       </c>
       <c r="E127" s="8">
-        <v>1636152884.38</v>
+        <v>1636802291.38</v>
       </c>
       <c r="F127" s="9">
-        <v>49952</v>
+        <v>49936</v>
       </c>
       <c r="G127" s="8">
-        <v>1258822035.77</v>
+        <v>1261768641.46</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5713,19 +5721,19 @@
         <v>256</v>
       </c>
       <c r="C128" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D128" s="7">
-        <v>0.148743</v>
+        <v>0.148671</v>
       </c>
       <c r="E128" s="8">
-        <v>1287791076.04</v>
+        <v>1288121078.97</v>
       </c>
       <c r="F128" s="9">
-        <v>12569</v>
+        <v>12568</v>
       </c>
       <c r="G128" s="8">
-        <v>191549336.38</v>
+        <v>191506462.81</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5736,19 +5744,19 @@
         <v>258</v>
       </c>
       <c r="C129" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D129" s="7">
-        <v>0.239364</v>
+        <v>0.239255</v>
       </c>
       <c r="E129" s="8">
-        <v>5273018178.52</v>
+        <v>5265059054.35</v>
       </c>
       <c r="F129" s="9">
-        <v>69587</v>
+        <v>69569</v>
       </c>
       <c r="G129" s="8">
-        <v>1262169188.4</v>
+        <v>1259690489.65</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5759,19 +5767,19 @@
         <v>260</v>
       </c>
       <c r="C130" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D130" s="7">
-        <v>1.868365</v>
+        <v>1.866155</v>
       </c>
       <c r="E130" s="8">
-        <v>2359060136.51</v>
+        <v>2361324208.03</v>
       </c>
       <c r="F130" s="9">
-        <v>52800</v>
+        <v>52801</v>
       </c>
       <c r="G130" s="8">
-        <v>4407586031.45</v>
+        <v>4406596324.88</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5782,19 +5790,19 @@
         <v>262</v>
       </c>
       <c r="C131" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D131" s="7">
-        <v>0.356136</v>
+        <v>0.354356</v>
       </c>
       <c r="E131" s="8">
-        <v>558397721.05</v>
+        <v>559026061.31</v>
       </c>
       <c r="F131" s="9">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G131" s="8">
-        <v>198865593</v>
+        <v>198094236.98</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5805,19 +5813,19 @@
         <v>264</v>
       </c>
       <c r="C132" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D132" s="7">
-        <v>0.160319</v>
+        <v>0.160596</v>
       </c>
       <c r="E132" s="8">
-        <v>132144564.59</v>
+        <v>132410491.65</v>
       </c>
       <c r="F132" s="9">
         <v>461</v>
       </c>
       <c r="G132" s="8">
-        <v>21185333.3</v>
+        <v>21264593.46</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5828,19 +5836,19 @@
         <v>266</v>
       </c>
       <c r="C133" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D133" s="10">
-        <v>0.70255</v>
+        <v>46140</v>
+      </c>
+      <c r="D133" s="7">
+        <v>0.703628</v>
       </c>
       <c r="E133" s="8">
-        <v>1253867574.83</v>
+        <v>1255152995</v>
       </c>
       <c r="F133" s="9">
-        <v>21218</v>
+        <v>21212</v>
       </c>
       <c r="G133" s="8">
-        <v>880905073.19</v>
+        <v>883160378.92</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5851,19 +5859,19 @@
         <v>268</v>
       </c>
       <c r="C134" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D134" s="7">
-        <v>0.367809</v>
+        <v>0.368353</v>
       </c>
       <c r="E134" s="8">
-        <v>7339639722.5</v>
+        <v>7360968324.6</v>
       </c>
       <c r="F134" s="9">
-        <v>93130</v>
+        <v>95806</v>
       </c>
       <c r="G134" s="8">
-        <v>2699587385.38</v>
+        <v>2711437872.67</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5874,19 +5882,19 @@
         <v>270</v>
       </c>
       <c r="C135" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D135" s="7">
-        <v>0.203463</v>
+        <v>0.203926</v>
       </c>
       <c r="E135" s="8">
-        <v>200254539.23</v>
+        <v>199857183.32</v>
       </c>
       <c r="F135" s="9">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G135" s="8">
-        <v>40744479.4</v>
+        <v>40756037.14</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5897,19 +5905,19 @@
         <v>272</v>
       </c>
       <c r="C136" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D136" s="7">
-        <v>0.257716</v>
+        <v>0.259091</v>
       </c>
       <c r="E136" s="8">
-        <v>401989580.9</v>
+        <v>402392345.58</v>
       </c>
       <c r="F136" s="9">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="G136" s="8">
-        <v>103599271.57</v>
+        <v>104256268.47</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5920,19 +5928,19 @@
         <v>274</v>
       </c>
       <c r="C137" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D137" s="7">
-        <v>0.099916</v>
+        <v>0.100125</v>
       </c>
       <c r="E137" s="8">
-        <v>293830619.62</v>
+        <v>294044387.21</v>
       </c>
       <c r="F137" s="9">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G137" s="8">
-        <v>29358505.37</v>
+        <v>29441112.57</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5943,19 +5951,19 @@
         <v>276</v>
       </c>
       <c r="C138" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D138" s="7">
-        <v>0.389856</v>
+        <v>0.391958</v>
       </c>
       <c r="E138" s="8">
-        <v>623051448.35</v>
+        <v>623940097.6</v>
       </c>
       <c r="F138" s="9">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="G138" s="8">
-        <v>242900185.45</v>
+        <v>244558489.16</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5966,19 +5974,19 @@
         <v>278</v>
       </c>
       <c r="C139" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D139" s="7">
-        <v>0.696045</v>
+        <v>46140</v>
+      </c>
+      <c r="D139" s="10">
+        <v>0.69681</v>
       </c>
       <c r="E139" s="8">
-        <v>2936950606.82</v>
+        <v>2932432386.99</v>
       </c>
       <c r="F139" s="9">
-        <v>42132</v>
+        <v>42120</v>
       </c>
       <c r="G139" s="8">
-        <v>2044248557.43</v>
+        <v>2043348117.26</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5989,19 +5997,19 @@
         <v>280</v>
       </c>
       <c r="C140" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D140" s="10">
-        <v>0.01391</v>
+        <v>46140</v>
+      </c>
+      <c r="D140" s="7">
+        <v>0.013986</v>
       </c>
       <c r="E140" s="8">
-        <v>2486278428.32</v>
+        <v>2509236473.53</v>
       </c>
       <c r="F140" s="9">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="G140" s="8">
-        <v>34583015.34</v>
+        <v>35094583.93</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -6012,19 +6020,19 @@
         <v>282</v>
       </c>
       <c r="C141" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D141" s="7">
-        <v>0.071494</v>
+        <v>0.072079</v>
       </c>
       <c r="E141" s="8">
-        <v>20775471497.35</v>
+        <v>20910431011.88</v>
       </c>
       <c r="F141" s="9">
-        <v>23309</v>
+        <v>23335</v>
       </c>
       <c r="G141" s="8">
-        <v>1485312311.73</v>
+        <v>1507209521.92</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -6035,19 +6043,19 @@
         <v>284</v>
       </c>
       <c r="C142" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D142" s="10">
-        <v>0.28503</v>
+        <v>46140</v>
+      </c>
+      <c r="D142" s="7">
+        <v>0.286299</v>
       </c>
       <c r="E142" s="8">
-        <v>20694946109.67</v>
+        <v>20689548863.63</v>
       </c>
       <c r="F142" s="9">
-        <v>4736</v>
+        <v>4733</v>
       </c>
       <c r="G142" s="8">
-        <v>5898690180.18</v>
+        <v>5923395606.19</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -6058,19 +6066,19 @@
         <v>286</v>
       </c>
       <c r="C143" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D143" s="7">
-        <v>0.090002</v>
+        <v>0.090091</v>
       </c>
       <c r="E143" s="8">
-        <v>629500143.46</v>
+        <v>629374725.29</v>
       </c>
       <c r="F143" s="9">
-        <v>10720</v>
+        <v>10759</v>
       </c>
       <c r="G143" s="8">
-        <v>56656039.24</v>
+        <v>56701021.71</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -6081,19 +6089,19 @@
         <v>288</v>
       </c>
       <c r="C144" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D144" s="7">
-        <v>0.054108</v>
+        <v>0.054079</v>
       </c>
       <c r="E144" s="8">
-        <v>1371968984.93</v>
+        <v>1424189122.17</v>
       </c>
       <c r="F144" s="9">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G144" s="8">
-        <v>74234153.7</v>
+        <v>77019041.67</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -6104,19 +6112,19 @@
         <v>290</v>
       </c>
       <c r="C145" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D145" s="7">
-        <v>0.113396</v>
+        <v>0.113494</v>
       </c>
       <c r="E145" s="8">
-        <v>1795632336.76</v>
+        <v>1821369632.23</v>
       </c>
       <c r="F145" s="9">
         <v>1068</v>
       </c>
       <c r="G145" s="8">
-        <v>203616745.11</v>
+        <v>206714584.19</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -6127,19 +6135,19 @@
         <v>292</v>
       </c>
       <c r="C146" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D146" s="7">
-        <v>0.111807</v>
+        <v>0.112214</v>
       </c>
       <c r="E146" s="8">
-        <v>1970839606.86</v>
+        <v>1969747531.35</v>
       </c>
       <c r="F146" s="9">
-        <v>65247</v>
+        <v>65242</v>
       </c>
       <c r="G146" s="8">
-        <v>220354286.06</v>
+        <v>221033132.79</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6150,19 +6158,19 @@
         <v>294</v>
       </c>
       <c r="C147" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D147" s="10">
-        <v>0.07545</v>
+        <v>46140</v>
+      </c>
+      <c r="D147" s="7">
+        <v>0.076053</v>
       </c>
       <c r="E147" s="8">
-        <v>568554324.07</v>
+        <v>568269443.39</v>
       </c>
       <c r="F147" s="9">
-        <v>51699</v>
+        <v>51692</v>
       </c>
       <c r="G147" s="8">
-        <v>42897294.37</v>
+        <v>43218730.07</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -6173,19 +6181,19 @@
         <v>296</v>
       </c>
       <c r="C148" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D148" s="7">
-        <v>0.081636</v>
+        <v>0.081721</v>
       </c>
       <c r="E148" s="8">
-        <v>359008320.56</v>
+        <v>357059181.11</v>
       </c>
       <c r="F148" s="9">
-        <v>9592</v>
+        <v>9537</v>
       </c>
       <c r="G148" s="8">
-        <v>29308009.02</v>
+        <v>29179330.37</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6196,19 +6204,19 @@
         <v>298</v>
       </c>
       <c r="C149" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D149" s="7">
-        <v>0.364793</v>
+        <v>0.365242</v>
       </c>
       <c r="E149" s="8">
-        <v>147444360.99</v>
+        <v>147461344.23</v>
       </c>
       <c r="F149" s="9">
         <v>1770</v>
       </c>
       <c r="G149" s="8">
-        <v>53786727.42</v>
+        <v>53859026.94</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -6219,19 +6227,19 @@
         <v>300</v>
       </c>
       <c r="C150" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D150" s="7">
-        <v>0.099083</v>
+        <v>0.098997</v>
       </c>
       <c r="E150" s="8">
-        <v>333860125.76</v>
+        <v>333953122.73</v>
       </c>
       <c r="F150" s="9">
         <v>1839</v>
       </c>
       <c r="G150" s="8">
-        <v>33079811.29</v>
+        <v>33060334.43</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6242,19 +6250,19 @@
         <v>302</v>
       </c>
       <c r="C151" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D151" s="7">
-        <v>0.289238</v>
+        <v>0.290018</v>
       </c>
       <c r="E151" s="8">
-        <v>142945484.98</v>
+        <v>142238108.99</v>
       </c>
       <c r="F151" s="9">
         <v>203</v>
       </c>
       <c r="G151" s="8">
-        <v>41345248.17</v>
+        <v>41251610.71</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -6265,19 +6273,19 @@
         <v>304</v>
       </c>
       <c r="C152" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D152" s="7">
-        <v>0.117027</v>
+        <v>0.117237</v>
       </c>
       <c r="E152" s="8">
-        <v>587804567.05</v>
+        <v>587597587.17</v>
       </c>
       <c r="F152" s="9">
         <v>92</v>
       </c>
       <c r="G152" s="8">
-        <v>68788849.89</v>
+        <v>68888287.54</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -6288,19 +6296,19 @@
         <v>306</v>
       </c>
       <c r="C153" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D153" s="7">
-        <v>0.391969</v>
+        <v>0.395831</v>
       </c>
       <c r="E153" s="8">
-        <v>1309689759.07</v>
+        <v>1308647518.37</v>
       </c>
       <c r="F153" s="9">
         <v>124</v>
       </c>
       <c r="G153" s="8">
-        <v>513358089.15</v>
+        <v>518003482.33</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -6311,19 +6319,19 @@
         <v>308</v>
       </c>
       <c r="C154" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D154" s="7">
-        <v>0.513435</v>
+        <v>0.515536</v>
       </c>
       <c r="E154" s="8">
-        <v>595464758.2</v>
+        <v>594612998.24</v>
       </c>
       <c r="F154" s="9">
         <v>379</v>
       </c>
       <c r="G154" s="8">
-        <v>305732513.62</v>
+        <v>306544667.86</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -6334,19 +6342,19 @@
         <v>310</v>
       </c>
       <c r="C155" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D155" s="7">
-        <v>1.681904</v>
+        <v>1.685616</v>
       </c>
       <c r="E155" s="8">
-        <v>908234462.67</v>
+        <v>908011200.26</v>
       </c>
       <c r="F155" s="9">
-        <v>10202</v>
+        <v>10199</v>
       </c>
       <c r="G155" s="8">
-        <v>1527563050.64</v>
+        <v>1530558494.05</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -6357,19 +6365,19 @@
         <v>312</v>
       </c>
       <c r="C156" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D156" s="7">
-        <v>0.275253</v>
+        <v>0.277142</v>
       </c>
       <c r="E156" s="8">
-        <v>185283925.05</v>
+        <v>183219687.39</v>
       </c>
       <c r="F156" s="9">
         <v>90</v>
       </c>
       <c r="G156" s="8">
-        <v>51000025.04</v>
+        <v>50777959.1</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -6380,19 +6388,19 @@
         <v>314</v>
       </c>
       <c r="C157" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D157" s="7">
-        <v>0.143842</v>
+        <v>0.143805</v>
       </c>
       <c r="E157" s="8">
-        <v>4616493871.18</v>
+        <v>4635955369.91</v>
       </c>
       <c r="F157" s="9">
-        <v>28870</v>
+        <v>28862</v>
       </c>
       <c r="G157" s="8">
-        <v>664047081.51</v>
+        <v>666671623.9</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -6403,19 +6411,19 @@
         <v>316</v>
       </c>
       <c r="C158" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D158" s="7">
-        <v>0.165838</v>
+        <v>46140</v>
+      </c>
+      <c r="D158" s="10">
+        <v>0.16606</v>
       </c>
       <c r="E158" s="8">
-        <v>3242047814.1</v>
+        <v>3260528464.65</v>
       </c>
       <c r="F158" s="9">
-        <v>12367</v>
+        <v>12788</v>
       </c>
       <c r="G158" s="8">
-        <v>537655372.31</v>
+        <v>541443962.48</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -6426,19 +6434,19 @@
         <v>318</v>
       </c>
       <c r="C159" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D159" s="7">
-        <v>0.688014</v>
+        <v>0.689623</v>
       </c>
       <c r="E159" s="8">
-        <v>756270351.84</v>
+        <v>758108482.84</v>
       </c>
       <c r="F159" s="9">
         <v>5168</v>
       </c>
       <c r="G159" s="8">
-        <v>520324911.26</v>
+        <v>522809076.22</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -6449,19 +6457,19 @@
         <v>320</v>
       </c>
       <c r="C160" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D160" s="7">
-        <v>0.377668</v>
+        <v>0.378478</v>
       </c>
       <c r="E160" s="8">
-        <v>1353713905.78</v>
+        <v>1352677793.82</v>
       </c>
       <c r="F160" s="9">
-        <v>23929</v>
+        <v>23925</v>
       </c>
       <c r="G160" s="8">
-        <v>511254068.05</v>
+        <v>511958829.64</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -6472,19 +6480,19 @@
         <v>322</v>
       </c>
       <c r="C161" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D161" s="7">
-        <v>0.373766</v>
+        <v>0.371818</v>
       </c>
       <c r="E161" s="8">
-        <v>168872727.16</v>
+        <v>167644568.99</v>
       </c>
       <c r="F161" s="9">
         <v>252</v>
       </c>
       <c r="G161" s="8">
-        <v>63118800.99</v>
+        <v>62333311.27</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -6495,19 +6503,19 @@
         <v>324</v>
       </c>
       <c r="C162" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D162" s="7">
-        <v>0.143312</v>
+        <v>0.143518</v>
       </c>
       <c r="E162" s="8">
-        <v>1028721521.15</v>
+        <v>1029098876.69</v>
       </c>
       <c r="F162" s="9">
-        <v>2961</v>
+        <v>2963</v>
       </c>
       <c r="G162" s="8">
-        <v>147427673.29</v>
+        <v>147694233.96</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -6518,19 +6526,19 @@
         <v>326</v>
       </c>
       <c r="C163" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D163" s="7">
-        <v>0.118242</v>
+        <v>0.118565</v>
       </c>
       <c r="E163" s="8">
-        <v>7523737982.29</v>
+        <v>7517313474.17</v>
       </c>
       <c r="F163" s="9">
-        <v>79215</v>
+        <v>79201</v>
       </c>
       <c r="G163" s="8">
-        <v>889620984.31</v>
+        <v>891287510.7</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -6541,19 +6549,19 @@
         <v>328</v>
       </c>
       <c r="C164" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D164" s="7">
-        <v>0.108362</v>
+        <v>0.108503</v>
       </c>
       <c r="E164" s="8">
-        <v>3276352408.12</v>
+        <v>3275252850.83</v>
       </c>
       <c r="F164" s="9">
-        <v>64756</v>
+        <v>64750</v>
       </c>
       <c r="G164" s="8">
-        <v>355032660.44</v>
+        <v>355374078.01</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -6564,19 +6572,19 @@
         <v>330</v>
       </c>
       <c r="C165" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D165" s="7">
-        <v>0.014787</v>
+        <v>0.014868</v>
       </c>
       <c r="E165" s="8">
-        <v>425240089238.58</v>
+        <v>425811088168.86</v>
       </c>
       <c r="F165" s="9">
-        <v>71841</v>
+        <v>72055</v>
       </c>
       <c r="G165" s="8">
-        <v>6287956612.12</v>
+        <v>6330771823.19</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -6587,19 +6595,19 @@
         <v>332</v>
       </c>
       <c r="C166" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D166" s="7">
-        <v>0.360937</v>
+        <v>0.361104</v>
       </c>
       <c r="E166" s="8">
-        <v>686546481.63</v>
+        <v>686336471</v>
       </c>
       <c r="F166" s="9">
-        <v>6857</v>
+        <v>6849</v>
       </c>
       <c r="G166" s="8">
-        <v>247799756.1</v>
+        <v>247838658.43</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -6610,19 +6618,19 @@
         <v>334</v>
       </c>
       <c r="C167" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D167" s="7">
-        <v>0.013491</v>
+        <v>0.013661</v>
       </c>
       <c r="E167" s="8">
-        <v>31313081358.26</v>
+        <v>32029077573.34</v>
       </c>
       <c r="F167" s="9">
-        <v>5412</v>
+        <v>5471</v>
       </c>
       <c r="G167" s="8">
-        <v>422430583.37</v>
+        <v>437562585.06</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6633,19 +6641,19 @@
         <v>336</v>
       </c>
       <c r="C168" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D168" s="7">
-        <v>0.681037</v>
+        <v>0.685938</v>
       </c>
       <c r="E168" s="8">
-        <v>1951912993.38</v>
+        <v>1953217021.99</v>
       </c>
       <c r="F168" s="9">
-        <v>32713</v>
+        <v>32714</v>
       </c>
       <c r="G168" s="8">
-        <v>1329324538.24</v>
+        <v>1339785071.73</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6656,19 +6664,19 @@
         <v>338</v>
       </c>
       <c r="C169" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D169" s="10">
-        <v>0.38564</v>
+        <v>46140</v>
+      </c>
+      <c r="D169" s="7">
+        <v>0.386774</v>
       </c>
       <c r="E169" s="8">
-        <v>1980443114.02</v>
+        <v>1982945134.9</v>
       </c>
       <c r="F169" s="9">
-        <v>21046</v>
+        <v>21031</v>
       </c>
       <c r="G169" s="8">
-        <v>763738572.17</v>
+        <v>766950752.29</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6679,19 +6687,19 @@
         <v>340</v>
       </c>
       <c r="C170" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D170" s="7">
-        <v>0.140488</v>
+        <v>0.140287</v>
       </c>
       <c r="E170" s="8">
-        <v>1585365841.73</v>
+        <v>1586147489.86</v>
       </c>
       <c r="F170" s="9">
-        <v>16371</v>
+        <v>16369</v>
       </c>
       <c r="G170" s="8">
-        <v>222725078.52</v>
+        <v>222516235.81</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6702,19 +6710,19 @@
         <v>342</v>
       </c>
       <c r="C171" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D171" s="7">
-        <v>1.251021</v>
+        <v>1.253016</v>
       </c>
       <c r="E171" s="8">
-        <v>1388784329.38</v>
+        <v>1388430280.32</v>
       </c>
       <c r="F171" s="9">
-        <v>23802</v>
+        <v>23801</v>
       </c>
       <c r="G171" s="8">
-        <v>1737398474.13</v>
+        <v>1739725218.99</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6725,19 +6733,19 @@
         <v>344</v>
       </c>
       <c r="C172" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D172" s="7">
-        <v>0.568441</v>
+        <v>0.568833</v>
       </c>
       <c r="E172" s="8">
-        <v>2359566688.52</v>
+        <v>2359418828.6</v>
       </c>
       <c r="F172" s="9">
-        <v>35210</v>
+        <v>35141</v>
       </c>
       <c r="G172" s="8">
-        <v>1341275271.94</v>
+        <v>1342115773.29</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6748,19 +6756,19 @@
         <v>346</v>
       </c>
       <c r="C173" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D173" s="7">
-        <v>0.016891</v>
+        <v>0.016984</v>
       </c>
       <c r="E173" s="8">
-        <v>69732338402.36</v>
+        <v>69883473903.41</v>
       </c>
       <c r="F173" s="9">
-        <v>16857</v>
+        <v>17002</v>
       </c>
       <c r="G173" s="8">
-        <v>1177876665.08</v>
+        <v>1186928619.4</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6771,19 +6779,19 @@
         <v>348</v>
       </c>
       <c r="C174" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D174" s="7">
-        <v>0.089513</v>
+        <v>0.089469</v>
       </c>
       <c r="E174" s="8">
-        <v>2181415144.64</v>
+        <v>2175679638.87</v>
       </c>
       <c r="F174" s="9">
-        <v>5166</v>
+        <v>5162</v>
       </c>
       <c r="G174" s="8">
-        <v>195265862.09</v>
+        <v>194655325.33</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6794,19 +6802,19 @@
         <v>350</v>
       </c>
       <c r="C175" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D175" s="7">
-        <v>0.121233</v>
+        <v>0.121278</v>
       </c>
       <c r="E175" s="8">
-        <v>1676895106.36</v>
+        <v>1668150876.95</v>
       </c>
       <c r="F175" s="9">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="G175" s="8">
-        <v>203294578.14</v>
+        <v>202309869.13</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6817,19 +6825,19 @@
         <v>352</v>
       </c>
       <c r="C176" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D176" s="7">
-        <v>0.310183</v>
+        <v>0.310604</v>
       </c>
       <c r="E176" s="8">
-        <v>756577060.1</v>
+        <v>756992456.24</v>
       </c>
       <c r="F176" s="9">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="G176" s="8">
-        <v>234677353.53</v>
+        <v>235124982.33</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6840,19 +6848,19 @@
         <v>354</v>
       </c>
       <c r="C177" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D177" s="7">
-        <v>0.090841</v>
+        <v>46140</v>
+      </c>
+      <c r="D177" s="10">
+        <v>0.09107</v>
       </c>
       <c r="E177" s="8">
-        <v>41465166473.64</v>
+        <v>41435437602.29</v>
       </c>
       <c r="F177" s="9">
-        <v>281562</v>
+        <v>281494</v>
       </c>
       <c r="G177" s="8">
-        <v>3766746663.77</v>
+        <v>3773541362.82</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6863,19 +6871,19 @@
         <v>356</v>
       </c>
       <c r="C178" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D178" s="7">
-        <v>0.065315</v>
+        <v>0.065146</v>
       </c>
       <c r="E178" s="8">
-        <v>657106168.15</v>
+        <v>666320918.39</v>
       </c>
       <c r="F178" s="9">
-        <v>6097</v>
+        <v>6094</v>
       </c>
       <c r="G178" s="8">
-        <v>42918704.31</v>
+        <v>43407923.54</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6886,19 +6894,19 @@
         <v>358</v>
       </c>
       <c r="C179" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D179" s="7">
-        <v>0.246709</v>
+        <v>46140</v>
+      </c>
+      <c r="D179" s="10">
+        <v>0.24846</v>
       </c>
       <c r="E179" s="8">
-        <v>553948513.07</v>
+        <v>552712685.67</v>
       </c>
       <c r="F179" s="9">
         <v>1765</v>
       </c>
       <c r="G179" s="8">
-        <v>136664248.93</v>
+        <v>137326733.39</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6909,19 +6917,19 @@
         <v>360</v>
       </c>
       <c r="C180" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D180" s="7">
-        <v>0.391754</v>
+        <v>0.392971</v>
       </c>
       <c r="E180" s="8">
-        <v>362063781.28</v>
+        <v>362532452.67</v>
       </c>
       <c r="F180" s="9">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="G180" s="8">
-        <v>141840025.46</v>
+        <v>142464831.74</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6932,19 +6940,19 @@
         <v>362</v>
       </c>
       <c r="C181" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D181" s="7">
-        <v>0.110868</v>
+        <v>0.110995</v>
       </c>
       <c r="E181" s="8">
-        <v>14718936810.14</v>
+        <v>14699932870.44</v>
       </c>
       <c r="F181" s="9">
-        <v>32262</v>
+        <v>32242</v>
       </c>
       <c r="G181" s="8">
-        <v>1631861635.42</v>
+        <v>1631622148.25</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6955,19 +6963,19 @@
         <v>364</v>
       </c>
       <c r="C182" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D182" s="7">
-        <v>0.114844</v>
+        <v>0.114961</v>
       </c>
       <c r="E182" s="8">
-        <v>22416614815.71</v>
+        <v>22493067923.71</v>
       </c>
       <c r="F182" s="9">
-        <v>44302</v>
+        <v>43705</v>
       </c>
       <c r="G182" s="8">
-        <v>2574414815.92</v>
+        <v>2585815256.81</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6978,19 +6986,19 @@
         <v>366</v>
       </c>
       <c r="C183" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D183" s="7">
-        <v>0.090722</v>
+        <v>0.092114</v>
       </c>
       <c r="E183" s="8">
-        <v>30523364370.76</v>
+        <v>30597789312.14</v>
       </c>
       <c r="F183" s="9">
-        <v>29529</v>
+        <v>29589</v>
       </c>
       <c r="G183" s="8">
-        <v>2769126233.28</v>
+        <v>2818496723.69</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7001,19 +7009,19 @@
         <v>368</v>
       </c>
       <c r="C184" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D184" s="7">
-        <v>0.084371</v>
+        <v>0.084803</v>
       </c>
       <c r="E184" s="8">
-        <v>6525484408.34</v>
+        <v>6496688817.03</v>
       </c>
       <c r="F184" s="9">
-        <v>5111</v>
+        <v>5094</v>
       </c>
       <c r="G184" s="8">
-        <v>550561889.1</v>
+        <v>550935575.84</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7024,19 +7032,19 @@
         <v>370</v>
       </c>
       <c r="C185" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D185" s="7">
-        <v>0.073281</v>
+        <v>0.073268</v>
       </c>
       <c r="E185" s="8">
-        <v>13975519559.32</v>
+        <v>13965782990.6</v>
       </c>
       <c r="F185" s="9">
-        <v>184338</v>
+        <v>184334</v>
       </c>
       <c r="G185" s="8">
-        <v>1024139310.01</v>
+        <v>1023246856.44</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7047,19 +7055,19 @@
         <v>372</v>
       </c>
       <c r="C186" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D186" s="7">
-        <v>0.098024</v>
+        <v>0.098291</v>
       </c>
       <c r="E186" s="8">
-        <v>4074078728.49</v>
+        <v>4069832483.24</v>
       </c>
       <c r="F186" s="9">
-        <v>117682</v>
+        <v>117675</v>
       </c>
       <c r="G186" s="8">
-        <v>399359322.28</v>
+        <v>400026398.09</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7070,19 +7078,19 @@
         <v>374</v>
       </c>
       <c r="C187" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D187" s="7">
-        <v>0.234411</v>
+        <v>0.238856</v>
       </c>
       <c r="E187" s="8">
-        <v>670258171.72</v>
+        <v>667891784.25</v>
       </c>
       <c r="F187" s="9">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="G187" s="8">
-        <v>157116014.03</v>
+        <v>159529847.56</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7093,19 +7101,19 @@
         <v>376</v>
       </c>
       <c r="C188" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D188" s="7">
-        <v>0.084172</v>
+        <v>0.084308</v>
       </c>
       <c r="E188" s="8">
-        <v>2759075645.86</v>
+        <v>2758707423.49</v>
       </c>
       <c r="F188" s="9">
-        <v>42639</v>
+        <v>42827</v>
       </c>
       <c r="G188" s="8">
-        <v>232236453.63</v>
+        <v>232580234.54</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7116,19 +7124,19 @@
         <v>378</v>
       </c>
       <c r="C189" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D189" s="7">
-        <v>0.245263</v>
+        <v>46140</v>
+      </c>
+      <c r="D189" s="10">
+        <v>0.24584</v>
       </c>
       <c r="E189" s="8">
-        <v>3430466738.69</v>
+        <v>3439654011.5</v>
       </c>
       <c r="F189" s="9">
-        <v>6470</v>
+        <v>6505</v>
       </c>
       <c r="G189" s="8">
-        <v>841367709.19</v>
+        <v>845605901.54</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7139,19 +7147,19 @@
         <v>380</v>
       </c>
       <c r="C190" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D190" s="7">
-        <v>0.160626</v>
+        <v>0.161067</v>
       </c>
       <c r="E190" s="8">
-        <v>703347575.13</v>
+        <v>701276690.75</v>
       </c>
       <c r="F190" s="9">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="G190" s="8">
-        <v>112976147.32</v>
+        <v>112952277.61</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7162,19 +7170,19 @@
         <v>382</v>
       </c>
       <c r="C191" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D191" s="7">
-        <v>0.149772</v>
+        <v>0.149931</v>
       </c>
       <c r="E191" s="8">
-        <v>492941716.96</v>
+        <v>491145554.2</v>
       </c>
       <c r="F191" s="9">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="G191" s="8">
-        <v>73828895.78</v>
+        <v>73638041.13</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7185,19 +7193,19 @@
         <v>384</v>
       </c>
       <c r="C192" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D192" s="7">
-        <v>0.099235</v>
+        <v>0.100155</v>
       </c>
       <c r="E192" s="8">
-        <v>1156628396.13</v>
+        <v>1156475012.03</v>
       </c>
       <c r="F192" s="9">
-        <v>116565</v>
+        <v>116552</v>
       </c>
       <c r="G192" s="8">
-        <v>114778003.61</v>
+        <v>115826214.64</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7208,19 +7216,19 @@
         <v>386</v>
       </c>
       <c r="C193" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D193" s="7">
-        <v>0.198739</v>
+        <v>0.200016</v>
       </c>
       <c r="E193" s="8">
-        <v>1913364366.44</v>
+        <v>1906691563.91</v>
       </c>
       <c r="F193" s="9">
-        <v>1450</v>
+        <v>1459</v>
       </c>
       <c r="G193" s="8">
-        <v>380259758.93</v>
+        <v>381367879.04</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7231,19 +7239,19 @@
         <v>388</v>
       </c>
       <c r="C194" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D194" s="7">
-        <v>0.157474</v>
+        <v>0.157479</v>
       </c>
       <c r="E194" s="8">
-        <v>600910541.48</v>
+        <v>600691733.98</v>
       </c>
       <c r="F194" s="9">
-        <v>2655</v>
+        <v>2658</v>
       </c>
       <c r="G194" s="8">
-        <v>94627555.59</v>
+        <v>94596416.61</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7254,19 +7262,19 @@
         <v>390</v>
       </c>
       <c r="C195" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D195" s="7">
-        <v>0.274742</v>
+        <v>0.274574</v>
       </c>
       <c r="E195" s="8">
-        <v>2885530306.03</v>
+        <v>2877178186.14</v>
       </c>
       <c r="F195" s="9">
-        <v>7773</v>
+        <v>7769</v>
       </c>
       <c r="G195" s="8">
-        <v>792775908.47</v>
+        <v>789998146.65</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7277,19 +7285,19 @@
         <v>392</v>
       </c>
       <c r="C196" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D196" s="7">
-        <v>0.097452</v>
+        <v>0.097888</v>
       </c>
       <c r="E196" s="8">
-        <v>102698070.74</v>
+        <v>103076819.4</v>
       </c>
       <c r="F196" s="9">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G196" s="8">
-        <v>10008102.21</v>
+        <v>10089964.26</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7300,19 +7308,19 @@
         <v>394</v>
       </c>
       <c r="C197" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D197" s="7">
-        <v>0.213189</v>
+        <v>0.215607</v>
       </c>
       <c r="E197" s="8">
-        <v>320359087.61</v>
+        <v>319705882.75</v>
       </c>
       <c r="F197" s="9">
         <v>969</v>
       </c>
       <c r="G197" s="8">
-        <v>68296984.47</v>
+        <v>68930808.17</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7323,19 +7331,19 @@
         <v>396</v>
       </c>
       <c r="C198" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D198" s="7">
-        <v>0.170139</v>
+        <v>0.171743</v>
       </c>
       <c r="E198" s="8">
-        <v>270807207.62</v>
+        <v>269775175.88</v>
       </c>
       <c r="F198" s="9">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="G198" s="8">
-        <v>46074836.81</v>
+        <v>46331929.9</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7346,19 +7354,19 @@
         <v>398</v>
       </c>
       <c r="C199" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D199" s="10">
-        <v>0.08726</v>
+        <v>46140</v>
+      </c>
+      <c r="D199" s="7">
+        <v>0.087349</v>
       </c>
       <c r="E199" s="8">
-        <v>2657266598.24</v>
+        <v>2653994797.24</v>
       </c>
       <c r="F199" s="9">
-        <v>40343</v>
+        <v>40291</v>
       </c>
       <c r="G199" s="8">
-        <v>231874069.92</v>
+        <v>231824360.51</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7369,19 +7377,19 @@
         <v>400</v>
       </c>
       <c r="C200" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D200" s="7">
-        <v>0.089736</v>
+        <v>0.089798</v>
       </c>
       <c r="E200" s="8">
-        <v>827829035.09</v>
+        <v>825809693.55</v>
       </c>
       <c r="F200" s="9">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G200" s="8">
-        <v>74286070.3</v>
+        <v>74155804.99</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7392,19 +7400,19 @@
         <v>402</v>
       </c>
       <c r="C201" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D201" s="7">
-        <v>0.147503</v>
+        <v>0.148636</v>
       </c>
       <c r="E201" s="8">
-        <v>9992909157.19</v>
+        <v>9870491611.39</v>
       </c>
       <c r="F201" s="9">
-        <v>9605</v>
+        <v>9556</v>
       </c>
       <c r="G201" s="8">
-        <v>1473984706.35</v>
+        <v>1467112994.04</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7415,19 +7423,19 @@
         <v>404</v>
       </c>
       <c r="C202" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D202" s="7">
-        <v>0.014431</v>
+        <v>0.014467</v>
       </c>
       <c r="E202" s="8">
-        <v>9061201998.47</v>
+        <v>8889568789.37</v>
       </c>
       <c r="F202" s="9">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="G202" s="8">
-        <v>130764161.83</v>
+        <v>128609315.02</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7438,19 +7446,19 @@
         <v>406</v>
       </c>
       <c r="C203" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D203" s="7">
-        <v>0.027989</v>
+        <v>0.028135</v>
       </c>
       <c r="E203" s="8">
-        <v>1308249979.62</v>
+        <v>1308404621.65</v>
       </c>
       <c r="F203" s="9">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G203" s="8">
-        <v>36616064.34</v>
+        <v>36811914.09</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7461,19 +7469,19 @@
         <v>408</v>
       </c>
       <c r="C204" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D204" s="7">
-        <v>0.117122</v>
+        <v>46140</v>
+      </c>
+      <c r="D204" s="10">
+        <v>0.11842</v>
       </c>
       <c r="E204" s="8">
-        <v>3189993465.5</v>
+        <v>3188256211.9</v>
       </c>
       <c r="F204" s="9">
-        <v>308597</v>
+        <v>308518</v>
       </c>
       <c r="G204" s="8">
-        <v>373619484.2</v>
+        <v>377554037.85</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7484,19 +7492,19 @@
         <v>410</v>
       </c>
       <c r="C205" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D205" s="7">
-        <v>0.155206</v>
+        <v>0.155936</v>
       </c>
       <c r="E205" s="8">
-        <v>389424181.69</v>
+        <v>419034593.84</v>
       </c>
       <c r="F205" s="9">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="G205" s="8">
-        <v>60441115.25</v>
+        <v>65342598.97</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -7507,19 +7515,19 @@
         <v>412</v>
       </c>
       <c r="C206" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D206" s="7">
-        <v>0.131064</v>
+        <v>0.131725</v>
       </c>
       <c r="E206" s="8">
-        <v>2874381484.06</v>
+        <v>2875201963.53</v>
       </c>
       <c r="F206" s="9">
-        <v>5743</v>
+        <v>5751</v>
       </c>
       <c r="G206" s="8">
-        <v>376727796.17</v>
+        <v>378735225.91</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7530,19 +7538,19 @@
         <v>414</v>
       </c>
       <c r="C207" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D207" s="7">
-        <v>0.102775</v>
+        <v>0.103915</v>
       </c>
       <c r="E207" s="8">
-        <v>4283284731.36</v>
+        <v>4276511399.46</v>
       </c>
       <c r="F207" s="9">
-        <v>343541</v>
+        <v>343390</v>
       </c>
       <c r="G207" s="8">
-        <v>440213052.42</v>
+        <v>444395166.84</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7553,19 +7561,19 @@
         <v>416</v>
       </c>
       <c r="C208" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D208" s="7">
-        <v>0.105023</v>
+        <v>46140</v>
+      </c>
+      <c r="D208" s="10">
+        <v>0.10546</v>
       </c>
       <c r="E208" s="8">
-        <v>46508663614.68</v>
+        <v>46479071651.57</v>
       </c>
       <c r="F208" s="9">
-        <v>712186</v>
+        <v>712038</v>
       </c>
       <c r="G208" s="8">
-        <v>4884470282.31</v>
+        <v>4901660592.3</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7576,19 +7584,19 @@
         <v>418</v>
       </c>
       <c r="C209" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D209" s="7">
-        <v>0.061657</v>
+        <v>0.062683</v>
       </c>
       <c r="E209" s="8">
-        <v>54796597035.86</v>
+        <v>55232833723.82</v>
       </c>
       <c r="F209" s="9">
-        <v>59081</v>
+        <v>59266</v>
       </c>
       <c r="G209" s="8">
-        <v>3378596950.89</v>
+        <v>3462175231.18</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7599,19 +7607,19 @@
         <v>420</v>
       </c>
       <c r="C210" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D210" s="7">
-        <v>0.106558</v>
+        <v>0.106593</v>
       </c>
       <c r="E210" s="8">
-        <v>64798467657.07</v>
+        <v>64759401531.9</v>
       </c>
       <c r="F210" s="9">
-        <v>913739</v>
+        <v>913711</v>
       </c>
       <c r="G210" s="8">
-        <v>6904811432.99</v>
+        <v>6902900557.77</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -7622,19 +7630,19 @@
         <v>422</v>
       </c>
       <c r="C211" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D211" s="7">
-        <v>0.069231</v>
+        <v>0.069426</v>
       </c>
       <c r="E211" s="8">
-        <v>55150916322.78</v>
+        <v>55118793534.15</v>
       </c>
       <c r="F211" s="9">
-        <v>55785</v>
+        <v>55728</v>
       </c>
       <c r="G211" s="8">
-        <v>3818127343.37</v>
+        <v>3826659756.69</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7645,19 +7653,19 @@
         <v>424</v>
       </c>
       <c r="C212" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D212" s="7">
-        <v>0.096605</v>
+        <v>0.096704</v>
       </c>
       <c r="E212" s="8">
-        <v>16291272570.72</v>
+        <v>16251775301.15</v>
       </c>
       <c r="F212" s="9">
-        <v>343799</v>
+        <v>343695</v>
       </c>
       <c r="G212" s="8">
-        <v>1573819586.67</v>
+        <v>1571618843.63</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7668,19 +7676,19 @@
         <v>426</v>
       </c>
       <c r="C213" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D213" s="7">
-        <v>0.051072</v>
+        <v>0.051367</v>
       </c>
       <c r="E213" s="8">
-        <v>84989250568.09</v>
+        <v>84129428530.05</v>
       </c>
       <c r="F213" s="9">
-        <v>35206</v>
+        <v>35132</v>
       </c>
       <c r="G213" s="8">
-        <v>4340609015.21</v>
+        <v>4321450483.4</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -7691,19 +7699,19 @@
         <v>428</v>
       </c>
       <c r="C214" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D214" s="10">
-        <v>0.08519</v>
+        <v>46140</v>
+      </c>
+      <c r="D214" s="7">
+        <v>0.085281</v>
       </c>
       <c r="E214" s="8">
-        <v>14045830480.01</v>
+        <v>14008833696.51</v>
       </c>
       <c r="F214" s="9">
-        <v>238527</v>
+        <v>237530</v>
       </c>
       <c r="G214" s="8">
-        <v>1196569935.76</v>
+        <v>1194688879.64</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7714,19 +7722,19 @@
         <v>430</v>
       </c>
       <c r="C215" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D215" s="7">
-        <v>0.311158</v>
+        <v>0.314175</v>
       </c>
       <c r="E215" s="8">
-        <v>12083387718.1</v>
+        <v>12089608675.23</v>
       </c>
       <c r="F215" s="9">
-        <v>57231</v>
+        <v>57315</v>
       </c>
       <c r="G215" s="8">
-        <v>3759845882.37</v>
+        <v>3798251874.47</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -7737,19 +7745,19 @@
         <v>432</v>
       </c>
       <c r="C216" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D216" s="7">
-        <v>0.218602</v>
+        <v>46140</v>
+      </c>
+      <c r="D216" s="10">
+        <v>0.22024</v>
       </c>
       <c r="E216" s="8">
-        <v>10238431573.57</v>
+        <v>10250574700.56</v>
       </c>
       <c r="F216" s="9">
-        <v>39072</v>
+        <v>39150</v>
       </c>
       <c r="G216" s="8">
-        <v>2238137155.65</v>
+        <v>2257583913.71</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -7760,19 +7768,19 @@
         <v>434</v>
       </c>
       <c r="C217" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D217" s="10">
-        <v>1.01236</v>
+        <v>46140</v>
+      </c>
+      <c r="D217" s="7">
+        <v>1.014556</v>
       </c>
       <c r="E217" s="8">
-        <v>748233410.45</v>
+        <v>746552327.02</v>
       </c>
       <c r="F217" s="9">
-        <v>4371</v>
+        <v>4368</v>
       </c>
       <c r="G217" s="8">
-        <v>757481445.48</v>
+        <v>757418813.38</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7783,19 +7791,19 @@
         <v>436</v>
       </c>
       <c r="C218" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D218" s="7">
-        <v>0.724109</v>
+        <v>46140</v>
+      </c>
+      <c r="D218" s="10">
+        <v>0.72646</v>
       </c>
       <c r="E218" s="8">
-        <v>5937642640.25</v>
+        <v>5936035733.88</v>
       </c>
       <c r="F218" s="9">
-        <v>10986</v>
+        <v>10980</v>
       </c>
       <c r="G218" s="8">
-        <v>4299497718.79</v>
+        <v>4312291050.37</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -7806,19 +7814,19 @@
         <v>438</v>
       </c>
       <c r="C219" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D219" s="10">
-        <v>2.85083</v>
+        <v>46140</v>
+      </c>
+      <c r="D219" s="7">
+        <v>2.858392</v>
       </c>
       <c r="E219" s="8">
-        <v>6292515832.73</v>
+        <v>6293163234.83</v>
       </c>
       <c r="F219" s="9">
-        <v>272549</v>
+        <v>272667</v>
       </c>
       <c r="G219" s="8">
-        <v>17938891402.45</v>
+        <v>17988325603.55</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -7829,19 +7837,19 @@
         <v>440</v>
       </c>
       <c r="C220" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D220" s="7">
-        <v>0.408164</v>
+        <v>0.407224</v>
       </c>
       <c r="E220" s="8">
-        <v>9452592979.16</v>
+        <v>9441323142.24</v>
       </c>
       <c r="F220" s="9">
-        <v>165964</v>
+        <v>165861</v>
       </c>
       <c r="G220" s="8">
-        <v>3858206205.64</v>
+        <v>3844735827.95</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -7852,19 +7860,19 @@
         <v>442</v>
       </c>
       <c r="C221" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D221" s="7">
-        <v>0.392372</v>
+        <v>0.392764</v>
       </c>
       <c r="E221" s="8">
-        <v>172813284284.15</v>
+        <v>173446212244.86</v>
       </c>
       <c r="F221" s="9">
-        <v>388823</v>
+        <v>399083</v>
       </c>
       <c r="G221" s="8">
-        <v>67807180026.93</v>
+        <v>68123395601.15</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -7875,19 +7883,19 @@
         <v>444</v>
       </c>
       <c r="C222" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D222" s="7">
-        <v>0.152143</v>
+        <v>0.152805</v>
       </c>
       <c r="E222" s="8">
-        <v>6398561251.71</v>
+        <v>6411433761.49</v>
       </c>
       <c r="F222" s="9">
-        <v>25276</v>
+        <v>25278</v>
       </c>
       <c r="G222" s="8">
-        <v>973498890.23</v>
+        <v>979695985.78</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -7898,19 +7906,19 @@
         <v>446</v>
       </c>
       <c r="C223" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D223" s="7">
-        <v>0.517373</v>
+        <v>0.518229</v>
       </c>
       <c r="E223" s="8">
-        <v>8903850232.79</v>
+        <v>8751779062.87</v>
       </c>
       <c r="F223" s="9">
-        <v>35808</v>
+        <v>35793</v>
       </c>
       <c r="G223" s="8">
-        <v>4606611400.32</v>
+        <v>4535422771.04</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -7921,19 +7929,19 @@
         <v>448</v>
       </c>
       <c r="C224" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D224" s="7">
-        <v>0.075271</v>
+        <v>0.075584</v>
       </c>
       <c r="E224" s="8">
-        <v>2520457903091.21</v>
+        <v>2518256030880.74</v>
       </c>
       <c r="F224" s="9">
-        <v>1247726</v>
+        <v>1247459</v>
       </c>
       <c r="G224" s="8">
-        <v>189717769964.25</v>
+        <v>190340558663.64</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -7944,19 +7952,19 @@
         <v>450</v>
       </c>
       <c r="C225" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D225" s="7">
-        <v>0.073592</v>
+        <v>0.074105</v>
       </c>
       <c r="E225" s="8">
-        <v>26419893271.1</v>
+        <v>26549268162.36</v>
       </c>
       <c r="F225" s="9">
-        <v>95524</v>
+        <v>95486</v>
       </c>
       <c r="G225" s="8">
-        <v>1944305465.02</v>
+        <v>1967426146.32</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -7967,19 +7975,19 @@
         <v>452</v>
       </c>
       <c r="C226" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D226" s="7">
-        <v>0.015649</v>
+        <v>0.015515</v>
       </c>
       <c r="E226" s="8">
-        <v>520926129432.18</v>
+        <v>520754377916.59</v>
       </c>
       <c r="F226" s="9">
-        <v>50870</v>
+        <v>50874</v>
       </c>
       <c r="G226" s="8">
-        <v>8151774412.2</v>
+        <v>8079504229.02</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -7990,19 +7998,19 @@
         <v>454</v>
       </c>
       <c r="C227" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D227" s="7">
-        <v>0.799268</v>
+        <v>0.798694</v>
       </c>
       <c r="E227" s="8">
-        <v>171216723873.33</v>
+        <v>171241236639.96</v>
       </c>
       <c r="F227" s="9">
-        <v>821927</v>
+        <v>822520</v>
       </c>
       <c r="G227" s="8">
-        <v>136848127204.21</v>
+        <v>136769363728.72</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8013,19 +8021,19 @@
         <v>456</v>
       </c>
       <c r="C228" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D228" s="7">
-        <v>0.138876</v>
+        <v>0.138981</v>
       </c>
       <c r="E228" s="8">
-        <v>27008060437.21</v>
+        <v>27036500331.39</v>
       </c>
       <c r="F228" s="9">
-        <v>195068</v>
+        <v>195043</v>
       </c>
       <c r="G228" s="8">
-        <v>3750765560.39</v>
+        <v>3757565398.19</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8036,19 +8044,19 @@
         <v>458</v>
       </c>
       <c r="C229" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D229" s="7">
-        <v>1.110003</v>
+        <v>1.112742</v>
       </c>
       <c r="E229" s="8">
-        <v>2645672200.16</v>
+        <v>2642082845.13</v>
       </c>
       <c r="F229" s="9">
-        <v>49196</v>
+        <v>49188</v>
       </c>
       <c r="G229" s="8">
-        <v>2936703735.37</v>
+        <v>2939957605.97</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8059,19 +8067,19 @@
         <v>460</v>
       </c>
       <c r="C230" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D230" s="7">
-        <v>0.283878</v>
+        <v>0.283125</v>
       </c>
       <c r="E230" s="8">
-        <v>2539200194.38</v>
+        <v>2536760158.97</v>
       </c>
       <c r="F230" s="9">
-        <v>11034</v>
+        <v>11024</v>
       </c>
       <c r="G230" s="8">
-        <v>720823321.64</v>
+        <v>718221059.45</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8082,19 +8090,19 @@
         <v>462</v>
       </c>
       <c r="C231" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D231" s="7">
-        <v>1.124415</v>
+        <v>1.126966</v>
       </c>
       <c r="E231" s="8">
-        <v>5219874168.47</v>
+        <v>5216498632.3</v>
       </c>
       <c r="F231" s="9">
-        <v>63817</v>
+        <v>63786</v>
       </c>
       <c r="G231" s="8">
-        <v>5869303147.71</v>
+        <v>5878816793.74</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8105,19 +8113,19 @@
         <v>464</v>
       </c>
       <c r="C232" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D232" s="10">
-        <v>0.37576</v>
+        <v>46140</v>
+      </c>
+      <c r="D232" s="7">
+        <v>0.378277</v>
       </c>
       <c r="E232" s="8">
-        <v>18387548964.08</v>
+        <v>18483590849.33</v>
       </c>
       <c r="F232" s="9">
-        <v>149124</v>
+        <v>149345</v>
       </c>
       <c r="G232" s="8">
-        <v>6909306166.01</v>
+        <v>6991913184.68</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8128,19 +8136,19 @@
         <v>466</v>
       </c>
       <c r="C233" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D233" s="7">
-        <v>0.108403</v>
+        <v>0.108617</v>
       </c>
       <c r="E233" s="8">
-        <v>278390054281.86</v>
+        <v>278206650503.94</v>
       </c>
       <c r="F233" s="9">
-        <v>1511370</v>
+        <v>1511076</v>
       </c>
       <c r="G233" s="8">
-        <v>30178406006.2</v>
+        <v>30217936781.63</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8151,19 +8159,19 @@
         <v>468</v>
       </c>
       <c r="C234" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D234" s="7">
-        <v>0.264449</v>
+        <v>0.265681</v>
       </c>
       <c r="E234" s="8">
-        <v>3266187474.74</v>
+        <v>3267836280.87</v>
       </c>
       <c r="F234" s="9">
         <v>10504</v>
       </c>
       <c r="G234" s="8">
-        <v>863741275.46</v>
+        <v>868203472.06</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8174,19 +8182,19 @@
         <v>470</v>
       </c>
       <c r="C235" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D235" s="7">
-        <v>0.786035</v>
+        <v>46140</v>
+      </c>
+      <c r="D235" s="10">
+        <v>0.78785</v>
       </c>
       <c r="E235" s="8">
-        <v>1345195823.28</v>
+        <v>1343927411.55</v>
       </c>
       <c r="F235" s="9">
-        <v>7464</v>
+        <v>7459</v>
       </c>
       <c r="G235" s="8">
-        <v>1057371611.91</v>
+        <v>1058813613.25</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8197,19 +8205,19 @@
         <v>472</v>
       </c>
       <c r="C236" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D236" s="10">
-        <v>0.15095</v>
+        <v>46140</v>
+      </c>
+      <c r="D236" s="7">
+        <v>0.152458</v>
       </c>
       <c r="E236" s="8">
-        <v>71332572874.85</v>
+        <v>71193659098.01</v>
       </c>
       <c r="F236" s="9">
-        <v>825400</v>
+        <v>825177</v>
       </c>
       <c r="G236" s="8">
-        <v>10767671852.67</v>
+        <v>10854075485.42</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8220,19 +8228,19 @@
         <v>474</v>
       </c>
       <c r="C237" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D237" s="7">
-        <v>0.223222</v>
+        <v>0.223869</v>
       </c>
       <c r="E237" s="8">
-        <v>2424985169.4</v>
+        <v>2427150744.31</v>
       </c>
       <c r="F237" s="9">
-        <v>7582</v>
+        <v>7578</v>
       </c>
       <c r="G237" s="8">
-        <v>541310089.93</v>
+        <v>543365010.46</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -8243,19 +8251,19 @@
         <v>476</v>
       </c>
       <c r="C238" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D238" s="7">
-        <v>0.196911</v>
+        <v>46140</v>
+      </c>
+      <c r="D238" s="10">
+        <v>0.19746</v>
       </c>
       <c r="E238" s="8">
-        <v>2325996423.14</v>
+        <v>2320956484.77</v>
       </c>
       <c r="F238" s="9">
-        <v>7322</v>
+        <v>7330</v>
       </c>
       <c r="G238" s="8">
-        <v>458013962.32</v>
+        <v>458297080.31</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -8266,19 +8274,19 @@
         <v>478</v>
       </c>
       <c r="C239" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D239" s="7">
-        <v>0.340119</v>
+        <v>0.341929</v>
       </c>
       <c r="E239" s="8">
-        <v>31197502330.51</v>
+        <v>31232705041.2</v>
       </c>
       <c r="F239" s="9">
-        <v>119779</v>
+        <v>119843</v>
       </c>
       <c r="G239" s="8">
-        <v>10610863133.72</v>
+        <v>10679376695.01</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -8289,19 +8297,19 @@
         <v>480</v>
       </c>
       <c r="C240" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D240" s="7">
-        <v>0.126049</v>
+        <v>0.126139</v>
       </c>
       <c r="E240" s="8">
-        <v>3802302829.56</v>
+        <v>3797519984.02</v>
       </c>
       <c r="F240" s="9">
-        <v>7450</v>
+        <v>7438</v>
       </c>
       <c r="G240" s="8">
-        <v>479275749.27</v>
+        <v>479015647.58</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -8312,19 +8320,19 @@
         <v>482</v>
       </c>
       <c r="C241" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D241" s="7">
-        <v>0.127437</v>
+        <v>0.127835</v>
       </c>
       <c r="E241" s="8">
-        <v>89763956804.98</v>
+        <v>89728480914.85</v>
       </c>
       <c r="F241" s="9">
-        <v>403681</v>
+        <v>403673</v>
       </c>
       <c r="G241" s="8">
-        <v>11439277256.64</v>
+        <v>11470396991.5</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -8335,19 +8343,19 @@
         <v>484</v>
       </c>
       <c r="C242" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D242" s="7">
-        <v>0.298556</v>
+        <v>0.302607</v>
       </c>
       <c r="E242" s="8">
-        <v>3843862007.09</v>
+        <v>3846246351.58</v>
       </c>
       <c r="F242" s="9">
-        <v>18017</v>
+        <v>18039</v>
       </c>
       <c r="G242" s="8">
-        <v>1147609644.23</v>
+        <v>1163900785.28</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8358,19 +8366,19 @@
         <v>486</v>
       </c>
       <c r="C243" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D243" s="7">
-        <v>0.080846</v>
+        <v>0.080928</v>
       </c>
       <c r="E243" s="8">
-        <v>3857642425.89</v>
+        <v>3853921291.11</v>
       </c>
       <c r="F243" s="9">
-        <v>9208</v>
+        <v>9204</v>
       </c>
       <c r="G243" s="8">
-        <v>311874271.93</v>
+        <v>311888691.9</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -8381,19 +8389,19 @@
         <v>488</v>
       </c>
       <c r="C244" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D244" s="7">
-        <v>0.241034</v>
+        <v>0.243449</v>
       </c>
       <c r="E244" s="8">
-        <v>2831790164.73</v>
+        <v>2834866378.78</v>
       </c>
       <c r="F244" s="9">
-        <v>13977</v>
+        <v>13990</v>
       </c>
       <c r="G244" s="8">
-        <v>682556607.47</v>
+        <v>690146465.42</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8404,19 +8412,19 @@
         <v>490</v>
       </c>
       <c r="C245" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D245" s="7">
-        <v>0.068558</v>
+        <v>0.068628</v>
       </c>
       <c r="E245" s="8">
-        <v>4046220475.66</v>
+        <v>4044064990.83</v>
       </c>
       <c r="F245" s="9">
-        <v>7803</v>
+        <v>7797</v>
       </c>
       <c r="G245" s="8">
-        <v>277401955.84</v>
+        <v>277535071.79</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -8427,19 +8435,19 @@
         <v>492</v>
       </c>
       <c r="C246" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D246" s="7">
-        <v>0.177969</v>
+        <v>0.178116</v>
       </c>
       <c r="E246" s="8">
-        <v>14249196920.65</v>
+        <v>14286536768.32</v>
       </c>
       <c r="F246" s="9">
-        <v>48537</v>
+        <v>48580</v>
       </c>
       <c r="G246" s="8">
-        <v>2535915080.94</v>
+        <v>2544661851.55</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8450,19 +8458,19 @@
         <v>494</v>
       </c>
       <c r="C247" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D247" s="7">
-        <v>0.024732</v>
+        <v>0.024567</v>
       </c>
       <c r="E247" s="8">
-        <v>970929035598.27</v>
+        <v>968791962455.41</v>
       </c>
       <c r="F247" s="9">
-        <v>187708</v>
+        <v>187553</v>
       </c>
       <c r="G247" s="8">
-        <v>24013278711.1</v>
+        <v>23800334794.64</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8473,19 +8481,19 @@
         <v>496</v>
       </c>
       <c r="C248" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D248" s="7">
-        <v>0.752866</v>
+        <v>0.753853</v>
       </c>
       <c r="E248" s="8">
-        <v>15416304312.35</v>
+        <v>15403893004.77</v>
       </c>
       <c r="F248" s="9">
-        <v>79476</v>
+        <v>79506</v>
       </c>
       <c r="G248" s="8">
-        <v>11606405330.34</v>
+        <v>11612264090.97</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8496,19 +8504,19 @@
         <v>498</v>
       </c>
       <c r="C249" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D249" s="7">
-        <v>0.655533</v>
+        <v>0.653593</v>
       </c>
       <c r="E249" s="8">
-        <v>8194338167.33</v>
+        <v>8202182999.93</v>
       </c>
       <c r="F249" s="9">
-        <v>74015</v>
+        <v>74331</v>
       </c>
       <c r="G249" s="8">
-        <v>5371661251.15</v>
+        <v>5360890761.08</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8519,19 +8527,19 @@
         <v>500</v>
       </c>
       <c r="C250" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D250" s="7">
-        <v>0.161808</v>
+        <v>0.162165</v>
       </c>
       <c r="E250" s="8">
-        <v>2785049743.67</v>
+        <v>2778491379.81</v>
       </c>
       <c r="F250" s="9">
-        <v>11272</v>
+        <v>11282</v>
       </c>
       <c r="G250" s="8">
-        <v>450643091.38</v>
+        <v>450573217.54</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8542,19 +8550,19 @@
         <v>502</v>
       </c>
       <c r="C251" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D251" s="7">
-        <v>0.096427</v>
+        <v>46140</v>
+      </c>
+      <c r="D251" s="10">
+        <v>0.09652</v>
       </c>
       <c r="E251" s="8">
-        <v>4852132774.89</v>
+        <v>4853405760.81</v>
       </c>
       <c r="F251" s="9">
-        <v>69412</v>
+        <v>69429</v>
       </c>
       <c r="G251" s="8">
-        <v>467877564.37</v>
+        <v>468451840.85</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8565,19 +8573,19 @@
         <v>504</v>
       </c>
       <c r="C252" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D252" s="7">
-        <v>0.328819</v>
+        <v>0.329496</v>
       </c>
       <c r="E252" s="8">
-        <v>2197106444.89</v>
+        <v>2197737606.45</v>
       </c>
       <c r="F252" s="9">
-        <v>20920</v>
+        <v>20953</v>
       </c>
       <c r="G252" s="8">
-        <v>722449709.73</v>
+        <v>724145653.88</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8588,19 +8596,19 @@
         <v>506</v>
       </c>
       <c r="C253" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D253" s="7">
-        <v>0.139846</v>
+        <v>0.140596</v>
       </c>
       <c r="E253" s="8">
-        <v>657811778.84</v>
+        <v>658681666.39</v>
       </c>
       <c r="F253" s="9">
-        <v>2348</v>
+        <v>2355</v>
       </c>
       <c r="G253" s="8">
-        <v>91992033.49</v>
+        <v>92607914.6</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8611,19 +8619,19 @@
         <v>508</v>
       </c>
       <c r="C254" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D254" s="7">
-        <v>0.082261</v>
+        <v>0.082347</v>
       </c>
       <c r="E254" s="8">
-        <v>644084953.87</v>
+        <v>641556392.23</v>
       </c>
       <c r="F254" s="9">
-        <v>14018</v>
+        <v>14053</v>
       </c>
       <c r="G254" s="8">
-        <v>52982998.03</v>
+        <v>52830332.71</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8634,19 +8642,19 @@
         <v>510</v>
       </c>
       <c r="C255" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D255" s="7">
-        <v>0.095567</v>
+        <v>0.095943</v>
       </c>
       <c r="E255" s="8">
-        <v>4034640881.66</v>
+        <v>4030219957.25</v>
       </c>
       <c r="F255" s="9">
-        <v>78513</v>
+        <v>78490</v>
       </c>
       <c r="G255" s="8">
-        <v>385579122.58</v>
+        <v>386670389.46</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8657,19 +8665,19 @@
         <v>512</v>
       </c>
       <c r="C256" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D256" s="7">
-        <v>0.127393</v>
+        <v>46140</v>
+      </c>
+      <c r="D256" s="10">
+        <v>0.12768</v>
       </c>
       <c r="E256" s="8">
-        <v>3766721474.75</v>
+        <v>3762688454.83</v>
       </c>
       <c r="F256" s="9">
-        <v>19607</v>
+        <v>19625</v>
       </c>
       <c r="G256" s="8">
-        <v>479852239.76</v>
+        <v>480418424.22</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8680,19 +8688,19 @@
         <v>514</v>
       </c>
       <c r="C257" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D257" s="10">
-        <v>0.09306</v>
+        <v>46140</v>
+      </c>
+      <c r="D257" s="7">
+        <v>0.093152</v>
       </c>
       <c r="E257" s="8">
-        <v>584459336.42</v>
+        <v>576456367.44</v>
       </c>
       <c r="F257" s="9">
-        <v>10496</v>
+        <v>10372</v>
       </c>
       <c r="G257" s="8">
-        <v>54389535.72</v>
+        <v>53697825.01</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -8703,19 +8711,19 @@
         <v>516</v>
       </c>
       <c r="C258" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D258" s="7">
-        <v>0.131662</v>
+        <v>0.131793</v>
       </c>
       <c r="E258" s="8">
-        <v>4421961761.49</v>
+        <v>4432530457.46</v>
       </c>
       <c r="F258" s="9">
-        <v>19388</v>
+        <v>19538</v>
       </c>
       <c r="G258" s="8">
-        <v>582202349.21</v>
+        <v>584176608.23</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -8726,19 +8734,19 @@
         <v>518</v>
       </c>
       <c r="C259" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D259" s="7">
-        <v>0.153125</v>
+        <v>46140</v>
+      </c>
+      <c r="D259" s="10">
+        <v>0.15438</v>
       </c>
       <c r="E259" s="8">
-        <v>1197686820.92</v>
+        <v>1197565225.89</v>
       </c>
       <c r="F259" s="9">
-        <v>58204</v>
+        <v>58196</v>
       </c>
       <c r="G259" s="8">
-        <v>183395312.94</v>
+        <v>184879832.3</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -8749,19 +8757,19 @@
         <v>520</v>
       </c>
       <c r="C260" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D260" s="7">
-        <v>0.776283</v>
+        <v>0.778667</v>
       </c>
       <c r="E260" s="8">
-        <v>8944185210.41</v>
+        <v>8940020752.72</v>
       </c>
       <c r="F260" s="9">
-        <v>25892</v>
+        <v>25931</v>
       </c>
       <c r="G260" s="8">
-        <v>6943214691.97</v>
+        <v>6961295395.99</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -8772,19 +8780,19 @@
         <v>522</v>
       </c>
       <c r="C261" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D261" s="7">
-        <v>0.102656</v>
+        <v>0.103012</v>
       </c>
       <c r="E261" s="8">
-        <v>13808081885.84</v>
+        <v>13805980885.63</v>
       </c>
       <c r="F261" s="9">
-        <v>126101</v>
+        <v>126091</v>
       </c>
       <c r="G261" s="8">
-        <v>1417483436.51</v>
+        <v>1422182963.9</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -8795,19 +8803,19 @@
         <v>524</v>
       </c>
       <c r="C262" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D262" s="7">
-        <v>0.013123</v>
+        <v>0.013207</v>
       </c>
       <c r="E262" s="8">
-        <v>135732481774.45</v>
+        <v>138069927380.39</v>
       </c>
       <c r="F262" s="9">
-        <v>1585</v>
+        <v>1601</v>
       </c>
       <c r="G262" s="8">
-        <v>1781182548.45</v>
+        <v>1823470184.05</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -8818,19 +8826,19 @@
         <v>526</v>
       </c>
       <c r="C263" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D263" s="7">
-        <v>0.281949</v>
+        <v>0.283953</v>
       </c>
       <c r="E263" s="8">
-        <v>5728448171.73</v>
+        <v>5715995915.19</v>
       </c>
       <c r="F263" s="9">
-        <v>44198</v>
+        <v>44129</v>
       </c>
       <c r="G263" s="8">
-        <v>1615129355.53</v>
+        <v>1623073182.61</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -8841,19 +8849,19 @@
         <v>528</v>
       </c>
       <c r="C264" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D264" s="7">
-        <v>0.401193</v>
+        <v>46140</v>
+      </c>
+      <c r="D264" s="10">
+        <v>0.40509</v>
       </c>
       <c r="E264" s="8">
-        <v>1951407561.57</v>
+        <v>1948301520.95</v>
       </c>
       <c r="F264" s="9">
-        <v>21846</v>
+        <v>21821</v>
       </c>
       <c r="G264" s="8">
-        <v>782890313.16</v>
+        <v>789237380</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -8864,19 +8872,19 @@
         <v>530</v>
       </c>
       <c r="C265" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D265" s="7">
-        <v>0.131146</v>
+        <v>0.131595</v>
       </c>
       <c r="E265" s="8">
-        <v>31679691837.59</v>
+        <v>33504314840.91</v>
       </c>
       <c r="F265" s="9">
-        <v>101074</v>
+        <v>101433</v>
       </c>
       <c r="G265" s="8">
-        <v>4154656105.55</v>
+        <v>4409016218.1</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -8887,19 +8895,19 @@
         <v>532</v>
       </c>
       <c r="C266" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D266" s="7">
-        <v>0.238353</v>
+        <v>46140</v>
+      </c>
+      <c r="D266" s="10">
+        <v>0.23788</v>
       </c>
       <c r="E266" s="8">
-        <v>2671931456.93</v>
+        <v>2676383226.61</v>
       </c>
       <c r="F266" s="9">
-        <v>24249</v>
+        <v>24247</v>
       </c>
       <c r="G266" s="8">
-        <v>636863197.31</v>
+        <v>636658804.54</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -8910,19 +8918,19 @@
         <v>534</v>
       </c>
       <c r="C267" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D267" s="7">
-        <v>0.012863</v>
+        <v>0.012913</v>
       </c>
       <c r="E267" s="8">
-        <v>615060829376.52</v>
+        <v>630870119017.41</v>
       </c>
       <c r="F267" s="9">
-        <v>69403</v>
+        <v>70204</v>
       </c>
       <c r="G267" s="8">
-        <v>7911404073.49</v>
+        <v>8146621596.35</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -8933,19 +8941,19 @@
         <v>536</v>
       </c>
       <c r="C268" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D268" s="7">
-        <v>0.499748</v>
+        <v>0.500982</v>
       </c>
       <c r="E268" s="8">
-        <v>5697654391.94</v>
+        <v>5699401657.21</v>
       </c>
       <c r="F268" s="9">
-        <v>72669</v>
+        <v>72513</v>
       </c>
       <c r="G268" s="8">
-        <v>2847392400.94</v>
+        <v>2855295322.96</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -8956,19 +8964,19 @@
         <v>538</v>
       </c>
       <c r="C269" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D269" s="7">
-        <v>0.304919</v>
+        <v>0.304491</v>
       </c>
       <c r="E269" s="8">
-        <v>1839267498.18</v>
+        <v>1839652850.11</v>
       </c>
       <c r="F269" s="9">
-        <v>95886</v>
+        <v>95875</v>
       </c>
       <c r="G269" s="8">
-        <v>560828441.49</v>
+        <v>560158449.32</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -8979,19 +8987,19 @@
         <v>540</v>
       </c>
       <c r="C270" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D270" s="7">
-        <v>0.790588</v>
+        <v>0.790621</v>
       </c>
       <c r="E270" s="8">
-        <v>2057400134.21</v>
+        <v>2054448940.72</v>
       </c>
       <c r="F270" s="9">
-        <v>112185</v>
+        <v>111833</v>
       </c>
       <c r="G270" s="8">
-        <v>1626556630.81</v>
+        <v>1624290287.92</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9002,19 +9010,19 @@
         <v>542</v>
       </c>
       <c r="C271" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D271" s="7">
-        <v>0.533872</v>
+        <v>0.533884</v>
       </c>
       <c r="E271" s="8">
-        <v>1499633245.61</v>
+        <v>1497734352.84</v>
       </c>
       <c r="F271" s="9">
-        <v>37841</v>
+        <v>37744</v>
       </c>
       <c r="G271" s="8">
-        <v>800611609.22</v>
+        <v>799617100.47</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9025,19 +9033,19 @@
         <v>544</v>
       </c>
       <c r="C272" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D272" s="7">
-        <v>0.285931</v>
+        <v>0.285721</v>
       </c>
       <c r="E272" s="8">
-        <v>2833637218.32</v>
+        <v>2836998092.57</v>
       </c>
       <c r="F272" s="9">
-        <v>87671</v>
+        <v>87643</v>
       </c>
       <c r="G272" s="8">
-        <v>810223679.22</v>
+        <v>810589298.26</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9048,19 +9056,19 @@
         <v>546</v>
       </c>
       <c r="C273" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D273" s="7">
-        <v>2.468442</v>
+        <v>2.464484</v>
       </c>
       <c r="E273" s="8">
-        <v>1893961826.39</v>
+        <v>1893379015.35</v>
       </c>
       <c r="F273" s="9">
-        <v>57738</v>
+        <v>57686</v>
       </c>
       <c r="G273" s="8">
-        <v>4675135712.35</v>
+        <v>4666202058.28</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9071,19 +9079,19 @@
         <v>548</v>
       </c>
       <c r="C274" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D274" s="7">
-        <v>0.909173</v>
+        <v>0.912284</v>
       </c>
       <c r="E274" s="8">
-        <v>768227548.47</v>
+        <v>767181212.79</v>
       </c>
       <c r="F274" s="9">
-        <v>83726</v>
+        <v>83480</v>
       </c>
       <c r="G274" s="8">
-        <v>698451721.7</v>
+        <v>699887343.58</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9094,19 +9102,19 @@
         <v>550</v>
       </c>
       <c r="C275" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D275" s="7">
-        <v>0.372565</v>
+        <v>0.373083</v>
       </c>
       <c r="E275" s="8">
-        <v>8901635342.85</v>
+        <v>8933797440.24</v>
       </c>
       <c r="F275" s="9">
-        <v>103679</v>
+        <v>103673</v>
       </c>
       <c r="G275" s="8">
-        <v>3316438689.53</v>
+        <v>3333045704.6</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9117,19 +9125,19 @@
         <v>552</v>
       </c>
       <c r="C276" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D276" s="7">
-        <v>0.110659</v>
+        <v>0.110876</v>
       </c>
       <c r="E276" s="8">
-        <v>54385208572.22</v>
+        <v>54316573901.08</v>
       </c>
       <c r="F276" s="9">
-        <v>198618</v>
+        <v>198323</v>
       </c>
       <c r="G276" s="8">
-        <v>6018198688.26</v>
+        <v>6022388551.51</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9140,19 +9148,19 @@
         <v>554</v>
       </c>
       <c r="C277" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D277" s="7">
-        <v>0.113263</v>
+        <v>0.114357</v>
       </c>
       <c r="E277" s="8">
-        <v>82215809810.06</v>
+        <v>82171626608.23</v>
       </c>
       <c r="F277" s="9">
-        <v>1067074</v>
+        <v>1066800</v>
       </c>
       <c r="G277" s="8">
-        <v>9312039596.85</v>
+        <v>9396913518.09</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9163,19 +9171,19 @@
         <v>556</v>
       </c>
       <c r="C278" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D278" s="10">
-        <v>0.14063</v>
+        <v>46140</v>
+      </c>
+      <c r="D278" s="7">
+        <v>0.141466</v>
       </c>
       <c r="E278" s="8">
-        <v>33170056912.18</v>
+        <v>33134907138.76</v>
       </c>
       <c r="F278" s="9">
-        <v>328740</v>
+        <v>328702</v>
       </c>
       <c r="G278" s="8">
-        <v>4664717831.97</v>
+        <v>4687477986.87</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9186,19 +9194,19 @@
         <v>558</v>
       </c>
       <c r="C279" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D279" s="10">
-        <v>0.16748</v>
+        <v>46140</v>
+      </c>
+      <c r="D279" s="7">
+        <v>0.168805</v>
       </c>
       <c r="E279" s="8">
-        <v>3126956674.38</v>
+        <v>3129402940.97</v>
       </c>
       <c r="F279" s="9">
-        <v>27414</v>
+        <v>27407</v>
       </c>
       <c r="G279" s="8">
-        <v>523704068.06</v>
+        <v>528259566.84</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9209,19 +9217,19 @@
         <v>560</v>
       </c>
       <c r="C280" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D280" s="7">
-        <v>0.740983</v>
+        <v>0.741073</v>
       </c>
       <c r="E280" s="8">
-        <v>44344606438.28</v>
+        <v>44335414206.19</v>
       </c>
       <c r="F280" s="9">
-        <v>673068</v>
+        <v>673252</v>
       </c>
       <c r="G280" s="8">
-        <v>32858592925.51</v>
+        <v>32855773589.13</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -9232,19 +9240,19 @@
         <v>562</v>
       </c>
       <c r="C281" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D281" s="7">
-        <v>0.260458</v>
+        <v>46140</v>
+      </c>
+      <c r="D281" s="10">
+        <v>0.26133</v>
       </c>
       <c r="E281" s="8">
-        <v>8735439756.13</v>
+        <v>8726275298.67</v>
       </c>
       <c r="F281" s="9">
-        <v>108483</v>
+        <v>108642</v>
       </c>
       <c r="G281" s="8">
-        <v>2275215808.86</v>
+        <v>2280438449.74</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -9255,19 +9263,19 @@
         <v>564</v>
       </c>
       <c r="C282" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D282" s="7">
-        <v>0.531288</v>
+        <v>0.535807</v>
       </c>
       <c r="E282" s="8">
-        <v>11565070575.48</v>
+        <v>11580933959.74</v>
       </c>
       <c r="F282" s="9">
-        <v>138960</v>
+        <v>138947</v>
       </c>
       <c r="G282" s="8">
-        <v>6144386904.35</v>
+        <v>6205148580.76</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -9278,19 +9286,19 @@
         <v>566</v>
       </c>
       <c r="C283" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D283" s="7">
-        <v>0.303352</v>
+        <v>0.305804</v>
       </c>
       <c r="E283" s="8">
-        <v>2285261411.23</v>
+        <v>2286269921.57</v>
       </c>
       <c r="F283" s="9">
-        <v>37420</v>
+        <v>37409</v>
       </c>
       <c r="G283" s="8">
-        <v>693239469.69</v>
+        <v>699149485.62</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -9301,19 +9309,19 @@
         <v>568</v>
       </c>
       <c r="C284" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D284" s="7">
-        <v>0.196478</v>
+        <v>46140</v>
+      </c>
+      <c r="D284" s="10">
+        <v>0.19673</v>
       </c>
       <c r="E284" s="8">
-        <v>9515059843.73</v>
+        <v>9505397484.23</v>
       </c>
       <c r="F284" s="9">
-        <v>108352</v>
+        <v>108304</v>
       </c>
       <c r="G284" s="8">
-        <v>1869496915.89</v>
+        <v>1869994432.28</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -9324,19 +9332,19 @@
         <v>570</v>
       </c>
       <c r="C285" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D285" s="7">
-        <v>0.274922</v>
+        <v>0.276981</v>
       </c>
       <c r="E285" s="8">
-        <v>790645136.63</v>
+        <v>788500373.54</v>
       </c>
       <c r="F285" s="9">
-        <v>2810</v>
+        <v>2812</v>
       </c>
       <c r="G285" s="8">
-        <v>217365714.11</v>
+        <v>218399510.27</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -9347,19 +9355,19 @@
         <v>572</v>
       </c>
       <c r="C286" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D286" s="7">
-        <v>0.087158</v>
+        <v>0.087249</v>
       </c>
       <c r="E286" s="8">
-        <v>4201269562.88</v>
+        <v>4189488298.4</v>
       </c>
       <c r="F286" s="9">
-        <v>146350</v>
+        <v>146098</v>
       </c>
       <c r="G286" s="8">
-        <v>366172747.4</v>
+        <v>365529430.19</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -9370,19 +9378,19 @@
         <v>574</v>
       </c>
       <c r="C287" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D287" s="7">
-        <v>0.470537</v>
+        <v>0.476551</v>
       </c>
       <c r="E287" s="8">
-        <v>1575624978.15</v>
+        <v>1574374540.64</v>
       </c>
       <c r="F287" s="9">
-        <v>4270</v>
+        <v>4273</v>
       </c>
       <c r="G287" s="8">
-        <v>741390378.77</v>
+        <v>750268984.21</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -9393,19 +9401,19 @@
         <v>576</v>
       </c>
       <c r="C288" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D288" s="7">
-        <v>0.015527</v>
+        <v>0.015597</v>
       </c>
       <c r="E288" s="8">
-        <v>5636676186.83</v>
+        <v>5663123564.2</v>
       </c>
       <c r="F288" s="9">
-        <v>3631</v>
+        <v>3626</v>
       </c>
       <c r="G288" s="8">
-        <v>87520312.09</v>
+        <v>88326538.47</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -9416,19 +9424,19 @@
         <v>578</v>
       </c>
       <c r="C289" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D289" s="7">
-        <v>0.018192</v>
+        <v>0.017744</v>
       </c>
       <c r="E289" s="8">
-        <v>154202545128.12</v>
+        <v>154130751682.73</v>
       </c>
       <c r="F289" s="9">
-        <v>31751</v>
+        <v>31735</v>
       </c>
       <c r="G289" s="8">
-        <v>2805191833.92</v>
+        <v>2734829867.06</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -9439,19 +9447,19 @@
         <v>580</v>
       </c>
       <c r="C290" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D290" s="7">
-        <v>0.010706</v>
+        <v>0.010737</v>
       </c>
       <c r="E290" s="8">
-        <v>5236872635.97</v>
+        <v>5515358418</v>
       </c>
       <c r="F290" s="9">
-        <v>837</v>
+        <v>933</v>
       </c>
       <c r="G290" s="8">
-        <v>56066165.45</v>
+        <v>59219488.76</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -9462,19 +9470,19 @@
         <v>582</v>
       </c>
       <c r="C291" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D291" s="7">
-        <v>0.136506</v>
+        <v>0.135175</v>
       </c>
       <c r="E291" s="8">
-        <v>53021383544.08</v>
+        <v>52976783138.85</v>
       </c>
       <c r="F291" s="9">
-        <v>107796</v>
+        <v>107819</v>
       </c>
       <c r="G291" s="8">
-        <v>7237740528.17</v>
+        <v>7161123315.51</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -9485,19 +9493,19 @@
         <v>584</v>
       </c>
       <c r="C292" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D292" s="7">
-        <v>0.050828</v>
+        <v>46140</v>
+      </c>
+      <c r="D292" s="10">
+        <v>0.05088</v>
       </c>
       <c r="E292" s="8">
-        <v>12188874104.25</v>
+        <v>12182372020.99</v>
       </c>
       <c r="F292" s="9">
-        <v>28368</v>
+        <v>28395</v>
       </c>
       <c r="G292" s="8">
-        <v>619535488.33</v>
+        <v>619841225.67</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -9508,19 +9516,19 @@
         <v>586</v>
       </c>
       <c r="C293" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D293" s="7">
-        <v>0.021869</v>
+        <v>46140</v>
+      </c>
+      <c r="D293" s="10">
+        <v>0.02189</v>
       </c>
       <c r="E293" s="8">
-        <v>56225409906.11</v>
+        <v>56235227997.55</v>
       </c>
       <c r="F293" s="9">
-        <v>10748</v>
+        <v>10733</v>
       </c>
       <c r="G293" s="8">
-        <v>1229603253.34</v>
+        <v>1230973334.67</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -9531,19 +9539,19 @@
         <v>588</v>
       </c>
       <c r="C294" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D294" s="7">
-        <v>0.030921</v>
+        <v>0.031431</v>
       </c>
       <c r="E294" s="8">
-        <v>54355410060.84</v>
+        <v>54351059648.01</v>
       </c>
       <c r="F294" s="9">
-        <v>33006</v>
+        <v>33034</v>
       </c>
       <c r="G294" s="8">
-        <v>1680718086.68</v>
+        <v>1708295002.51</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -9554,19 +9562,19 @@
         <v>590</v>
       </c>
       <c r="C295" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D295" s="10">
-        <v>0.01945</v>
+        <v>46140</v>
+      </c>
+      <c r="D295" s="7">
+        <v>0.019694</v>
       </c>
       <c r="E295" s="8">
-        <v>975197234838.02</v>
+        <v>970642249513.15</v>
       </c>
       <c r="F295" s="9">
-        <v>179492</v>
+        <v>179357</v>
       </c>
       <c r="G295" s="8">
-        <v>18967744398.61</v>
+        <v>19115577633.87</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -9577,19 +9585,19 @@
         <v>592</v>
       </c>
       <c r="C296" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D296" s="7">
-        <v>0.101554</v>
+        <v>0.101677</v>
       </c>
       <c r="E296" s="8">
-        <v>37054192851.26</v>
+        <v>37129964256.44</v>
       </c>
       <c r="F296" s="9">
-        <v>382752</v>
+        <v>382867</v>
       </c>
       <c r="G296" s="8">
-        <v>3763018623.15</v>
+        <v>3775273904.46</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -9600,19 +9608,19 @@
         <v>594</v>
       </c>
       <c r="C297" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D297" s="7">
-        <v>0.086034</v>
+        <v>0.086256</v>
       </c>
       <c r="E297" s="8">
-        <v>38575581041.85</v>
+        <v>38495944349.28</v>
       </c>
       <c r="F297" s="9">
-        <v>48515</v>
+        <v>48302</v>
       </c>
       <c r="G297" s="8">
-        <v>3318814271.24</v>
+        <v>3320524516.08</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -9623,19 +9631,19 @@
         <v>596</v>
       </c>
       <c r="C298" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D298" s="7">
-        <v>0.094008</v>
+        <v>0.094407</v>
       </c>
       <c r="E298" s="8">
-        <v>39261904408.26</v>
+        <v>39233721664.46</v>
       </c>
       <c r="F298" s="9">
-        <v>527919</v>
+        <v>527807</v>
       </c>
       <c r="G298" s="8">
-        <v>3690940861.46</v>
+        <v>3703922542.66</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -9646,19 +9654,19 @@
         <v>598</v>
       </c>
       <c r="C299" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D299" s="7">
-        <v>0.019963</v>
+        <v>0.020101</v>
       </c>
       <c r="E299" s="8">
-        <v>33414718757.23</v>
+        <v>33837634121.36</v>
       </c>
       <c r="F299" s="9">
-        <v>24315</v>
+        <v>24549</v>
       </c>
       <c r="G299" s="8">
-        <v>667051957.59</v>
+        <v>680159938.24</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -9669,19 +9677,19 @@
         <v>600</v>
       </c>
       <c r="C300" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D300" s="7">
-        <v>0.010244</v>
+        <v>0.010255</v>
       </c>
       <c r="E300" s="8">
-        <v>1684003039.02</v>
+        <v>1822011246.93</v>
       </c>
       <c r="F300" s="9">
-        <v>396</v>
+        <v>436</v>
       </c>
       <c r="G300" s="8">
-        <v>17251067.19</v>
+        <v>18684400.88</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -9692,19 +9700,19 @@
         <v>602</v>
       </c>
       <c r="C301" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D301" s="7">
-        <v>0.015068</v>
+        <v>46140</v>
+      </c>
+      <c r="D301" s="10">
+        <v>0.01532</v>
       </c>
       <c r="E301" s="8">
-        <v>23391940742.74</v>
+        <v>23740582083.79</v>
       </c>
       <c r="F301" s="9">
-        <v>10935</v>
+        <v>10924</v>
       </c>
       <c r="G301" s="8">
-        <v>352467086.86</v>
+        <v>363716663.95</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -9715,19 +9723,19 @@
         <v>604</v>
       </c>
       <c r="C302" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D302" s="7">
-        <v>0.017746</v>
+        <v>0.017914</v>
       </c>
       <c r="E302" s="8">
-        <v>11916333331.75</v>
+        <v>11918703897.44</v>
       </c>
       <c r="F302" s="9">
-        <v>6677</v>
+        <v>6673</v>
       </c>
       <c r="G302" s="8">
-        <v>211465594.18</v>
+        <v>213517250.73</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -9738,19 +9746,19 @@
         <v>606</v>
       </c>
       <c r="C303" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D303" s="7">
-        <v>0.093827</v>
+        <v>46140</v>
+      </c>
+      <c r="D303" s="11">
+        <v>0.094</v>
       </c>
       <c r="E303" s="8">
-        <v>21299053803.37</v>
+        <v>21296679115.61</v>
       </c>
       <c r="F303" s="9">
-        <v>347581</v>
+        <v>347541</v>
       </c>
       <c r="G303" s="8">
-        <v>1998419459.9</v>
+        <v>2001888664.41</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -9761,19 +9769,19 @@
         <v>608</v>
       </c>
       <c r="C304" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D304" s="7">
-        <v>0.019038</v>
+        <v>0.019045</v>
       </c>
       <c r="E304" s="8">
-        <v>10535885662.07</v>
+        <v>10409323616.04</v>
       </c>
       <c r="F304" s="9">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G304" s="8">
-        <v>200585462.99</v>
+        <v>198247436.51</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -9784,19 +9792,19 @@
         <v>610</v>
       </c>
       <c r="C305" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D305" s="7">
-        <v>0.015669</v>
+        <v>0.015711</v>
       </c>
       <c r="E305" s="8">
-        <v>9119801888.62</v>
+        <v>9126815577.66</v>
       </c>
       <c r="F305" s="9">
         <v>389</v>
       </c>
       <c r="G305" s="8">
-        <v>142895615.2</v>
+        <v>143390871.91</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -9807,19 +9815,19 @@
         <v>612</v>
       </c>
       <c r="C306" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D306" s="7">
-        <v>0.015777</v>
+        <v>0.015794</v>
       </c>
       <c r="E306" s="8">
-        <v>1011249042.4</v>
+        <v>1017516255.19</v>
       </c>
       <c r="F306" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G306" s="8">
-        <v>15954681.16</v>
+        <v>16070477.41</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -9830,19 +9838,19 @@
         <v>614</v>
       </c>
       <c r="C307" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D307" s="7">
-        <v>0.231988</v>
+        <v>46140</v>
+      </c>
+      <c r="D307" s="10">
+        <v>0.23318</v>
       </c>
       <c r="E307" s="8">
-        <v>48613630213.31</v>
+        <v>48675245106.98</v>
       </c>
       <c r="F307" s="9">
-        <v>174224</v>
+        <v>174352</v>
       </c>
       <c r="G307" s="8">
-        <v>11277764163.47</v>
+        <v>11350099215.48</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -9853,19 +9861,19 @@
         <v>616</v>
       </c>
       <c r="C308" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D308" s="7">
-        <v>0.011224</v>
+        <v>0.011205</v>
       </c>
       <c r="E308" s="8">
-        <v>2088607117.94</v>
+        <v>2097192071.25</v>
       </c>
       <c r="F308" s="9">
-        <v>1889</v>
+        <v>1900</v>
       </c>
       <c r="G308" s="8">
-        <v>23442724.61</v>
+        <v>23500038.33</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -9876,19 +9884,19 @@
         <v>618</v>
       </c>
       <c r="C309" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D309" s="7">
-        <v>0.028313</v>
+        <v>0.028806</v>
       </c>
       <c r="E309" s="8">
-        <v>12176073640.23</v>
+        <v>12282710470.9</v>
       </c>
       <c r="F309" s="9">
-        <v>17246</v>
+        <v>17286</v>
       </c>
       <c r="G309" s="8">
-        <v>344743187.62</v>
+        <v>353818110.05</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -9899,19 +9907,19 @@
         <v>620</v>
       </c>
       <c r="C310" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D310" s="7">
-        <v>0.024774</v>
+        <v>0.024891</v>
       </c>
       <c r="E310" s="8">
-        <v>2912011878.19</v>
+        <v>2937465075.83</v>
       </c>
       <c r="F310" s="9">
-        <v>10161</v>
+        <v>10190</v>
       </c>
       <c r="G310" s="8">
-        <v>72143050.55</v>
+        <v>73115769.63</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -9922,19 +9930,19 @@
         <v>622</v>
       </c>
       <c r="C311" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D311" s="7">
-        <v>0.121549</v>
+        <v>0.122608</v>
       </c>
       <c r="E311" s="8">
-        <v>612136063.53</v>
+        <v>611735126.04</v>
       </c>
       <c r="F311" s="9">
-        <v>92444</v>
+        <v>92425</v>
       </c>
       <c r="G311" s="8">
-        <v>74404737.7</v>
+        <v>75003605.5</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -9945,19 +9953,19 @@
         <v>624</v>
       </c>
       <c r="C312" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D312" s="7">
-        <v>0.090223</v>
+        <v>0.090309</v>
       </c>
       <c r="E312" s="8">
-        <v>1359304543.63</v>
+        <v>1349027661.83</v>
       </c>
       <c r="F312" s="9">
-        <v>25524</v>
+        <v>25171</v>
       </c>
       <c r="G312" s="8">
-        <v>122640586.59</v>
+        <v>121829212.15</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -9968,19 +9976,19 @@
         <v>626</v>
       </c>
       <c r="C313" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D313" s="10">
-        <v>0.07981</v>
+        <v>46140</v>
+      </c>
+      <c r="D313" s="7">
+        <v>0.079895</v>
       </c>
       <c r="E313" s="8">
-        <v>2384955971.4</v>
+        <v>2374415168.74</v>
       </c>
       <c r="F313" s="9">
-        <v>75272</v>
+        <v>75019</v>
       </c>
       <c r="G313" s="8">
-        <v>190343088.58</v>
+        <v>189704060.58</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -9991,19 +9999,19 @@
         <v>628</v>
       </c>
       <c r="C314" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D314" s="7">
-        <v>0.386944</v>
+        <v>0.387835</v>
       </c>
       <c r="E314" s="8">
-        <v>5191840895.17</v>
+        <v>5200274187.12</v>
       </c>
       <c r="F314" s="9">
-        <v>71755</v>
+        <v>71709</v>
       </c>
       <c r="G314" s="8">
-        <v>2008952323.3</v>
+        <v>2016845872.11</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -10014,19 +10022,19 @@
         <v>630</v>
       </c>
       <c r="C315" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D315" s="7">
-        <v>0.205029</v>
+        <v>0.204997</v>
       </c>
       <c r="E315" s="8">
-        <v>5826077119.1</v>
+        <v>5826946681.57</v>
       </c>
       <c r="F315" s="9">
-        <v>56519</v>
+        <v>56501</v>
       </c>
       <c r="G315" s="8">
-        <v>1194515011.69</v>
+        <v>1194508439.98</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -10037,19 +10045,19 @@
         <v>632</v>
       </c>
       <c r="C316" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D316" s="7">
-        <v>0.112728</v>
+        <v>0.112556</v>
       </c>
       <c r="E316" s="8">
-        <v>2294236753.28</v>
+        <v>2290854776.19</v>
       </c>
       <c r="F316" s="9">
-        <v>8358</v>
+        <v>8353</v>
       </c>
       <c r="G316" s="8">
-        <v>258625660.3</v>
+        <v>257848918.33</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -10060,19 +10068,19 @@
         <v>634</v>
       </c>
       <c r="C317" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D317" s="7">
-        <v>0.557152</v>
+        <v>0.558197</v>
       </c>
       <c r="E317" s="8">
-        <v>3972498318.11</v>
+        <v>3980018656.9</v>
       </c>
       <c r="F317" s="9">
-        <v>50359</v>
+        <v>50403</v>
       </c>
       <c r="G317" s="8">
-        <v>2213285743.88</v>
+        <v>2221635026.71</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -10083,19 +10091,19 @@
         <v>636</v>
       </c>
       <c r="C318" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D318" s="7">
-        <v>0.084247</v>
+        <v>0.084613</v>
       </c>
       <c r="E318" s="8">
-        <v>8868603074.47</v>
+        <v>8864130074.77</v>
       </c>
       <c r="F318" s="9">
-        <v>188168</v>
+        <v>188191</v>
       </c>
       <c r="G318" s="8">
-        <v>747154790.08</v>
+        <v>750017611.56</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -10106,19 +10114,19 @@
         <v>638</v>
       </c>
       <c r="C319" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D319" s="7">
-        <v>0.109328</v>
+        <v>0.109256</v>
       </c>
       <c r="E319" s="8">
-        <v>23061321591.58</v>
+        <v>23097358561.01</v>
       </c>
       <c r="F319" s="9">
-        <v>138093</v>
+        <v>138055</v>
       </c>
       <c r="G319" s="8">
-        <v>2521244258.66</v>
+        <v>2523516980.41</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -10129,19 +10137,19 @@
         <v>640</v>
       </c>
       <c r="C320" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D320" s="7">
-        <v>0.150789</v>
+        <v>0.150923</v>
       </c>
       <c r="E320" s="8">
-        <v>13310804430.58</v>
+        <v>13264219501.72</v>
       </c>
       <c r="F320" s="9">
-        <v>46467</v>
+        <v>43693</v>
       </c>
       <c r="G320" s="8">
-        <v>2007124868.84</v>
+        <v>2001872211.07</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -10152,19 +10160,19 @@
         <v>642</v>
       </c>
       <c r="C321" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D321" s="7">
-        <v>0.132745</v>
+        <v>0.133031</v>
       </c>
       <c r="E321" s="8">
-        <v>531854604.44</v>
+        <v>527825190.24</v>
       </c>
       <c r="F321" s="9">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G321" s="8">
-        <v>70600812.97</v>
+        <v>70216966.26</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -10175,19 +10183,19 @@
         <v>644</v>
       </c>
       <c r="C322" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D322" s="7">
-        <v>0.137515</v>
+        <v>0.137701</v>
       </c>
       <c r="E322" s="8">
-        <v>225032544.06</v>
+        <v>225013949.54</v>
       </c>
       <c r="F322" s="9">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G322" s="8">
-        <v>30945247.01</v>
+        <v>30984664.62</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -10198,19 +10206,19 @@
         <v>646</v>
       </c>
       <c r="C323" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D323" s="7">
-        <v>0.168315</v>
+        <v>46140</v>
+      </c>
+      <c r="D323" s="10">
+        <v>0.16855</v>
       </c>
       <c r="E323" s="8">
-        <v>295748366.27</v>
+        <v>295704426.41</v>
       </c>
       <c r="F323" s="9">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G323" s="8">
-        <v>49778811.9</v>
+        <v>49840868.25</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -10221,19 +10229,19 @@
         <v>648</v>
       </c>
       <c r="C324" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D324" s="7">
-        <v>0.200449</v>
+        <v>0.200566</v>
       </c>
       <c r="E324" s="8">
-        <v>358432545.01</v>
+        <v>359917126.39</v>
       </c>
       <c r="F324" s="9">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="G324" s="8">
-        <v>71847524.4</v>
+        <v>72187315.26</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -10244,19 +10252,19 @@
         <v>650</v>
       </c>
       <c r="C325" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D325" s="10">
-        <v>0.14067</v>
+        <v>46140</v>
+      </c>
+      <c r="D325" s="7">
+        <v>0.141178</v>
       </c>
       <c r="E325" s="8">
-        <v>412463716.82</v>
+        <v>412261535.92</v>
       </c>
       <c r="F325" s="9">
-        <v>2005</v>
+        <v>2029</v>
       </c>
       <c r="G325" s="8">
-        <v>58021143.82</v>
+        <v>58202354.2</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -10267,19 +10275,19 @@
         <v>652</v>
       </c>
       <c r="C326" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D326" s="7">
-        <v>0.098628</v>
+        <v>0.098676</v>
       </c>
       <c r="E326" s="8">
-        <v>40116948260.28</v>
+        <v>40071742924.08</v>
       </c>
       <c r="F326" s="9">
-        <v>367946</v>
+        <v>367796</v>
       </c>
       <c r="G326" s="8">
-        <v>3956640652.34</v>
+        <v>3954117544.13</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -10290,19 +10298,19 @@
         <v>654</v>
       </c>
       <c r="C327" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D327" s="10">
-        <v>0.17116</v>
+        <v>46140</v>
+      </c>
+      <c r="D327" s="7">
+        <v>0.172389</v>
       </c>
       <c r="E327" s="8">
-        <v>192168074</v>
+        <v>192282968.83</v>
       </c>
       <c r="F327" s="9">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G327" s="8">
-        <v>32891469.87</v>
+        <v>33147563.71</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -10313,19 +10321,19 @@
         <v>656</v>
       </c>
       <c r="C328" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D328" s="7">
-        <v>0.200594</v>
+        <v>0.202224</v>
       </c>
       <c r="E328" s="8">
-        <v>238424290.85</v>
+        <v>238829783.26</v>
       </c>
       <c r="F328" s="9">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G328" s="8">
-        <v>47826583.04</v>
+        <v>48297163.34</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -10336,19 +10344,19 @@
         <v>658</v>
       </c>
       <c r="C329" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D329" s="7">
-        <v>0.292789</v>
+        <v>0.293045</v>
       </c>
       <c r="E329" s="8">
-        <v>1254023232.92</v>
+        <v>1253301934.94</v>
       </c>
       <c r="F329" s="9">
-        <v>8771</v>
+        <v>8767</v>
       </c>
       <c r="G329" s="8">
-        <v>367163949</v>
+        <v>367274275.3</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -10359,19 +10367,19 @@
         <v>660</v>
       </c>
       <c r="C330" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D330" s="7">
-        <v>0.092418</v>
+        <v>46140</v>
+      </c>
+      <c r="D330" s="10">
+        <v>0.09234</v>
       </c>
       <c r="E330" s="8">
-        <v>6842282745.65</v>
+        <v>6843135481.29</v>
       </c>
       <c r="F330" s="9">
-        <v>123059</v>
+        <v>123280</v>
       </c>
       <c r="G330" s="8">
-        <v>632351864.86</v>
+        <v>631892047.62</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
@@ -10382,19 +10390,19 @@
         <v>662</v>
       </c>
       <c r="C331" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D331" s="7">
-        <v>0.073985</v>
+        <v>0.074245</v>
       </c>
       <c r="E331" s="8">
-        <v>102910163737.17</v>
+        <v>102998781692.14</v>
       </c>
       <c r="F331" s="9">
-        <v>147713</v>
+        <v>147797</v>
       </c>
       <c r="G331" s="8">
-        <v>7613819049.26</v>
+        <v>7647176245.77</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
@@ -10405,19 +10413,19 @@
         <v>664</v>
       </c>
       <c r="C332" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D332" s="7">
-        <v>0.065655</v>
+        <v>0.065807</v>
       </c>
       <c r="E332" s="8">
-        <v>111277546136.9</v>
+        <v>111232569103.78</v>
       </c>
       <c r="F332" s="9">
-        <v>99070</v>
+        <v>99107</v>
       </c>
       <c r="G332" s="8">
-        <v>7305962122.13</v>
+        <v>7319838446.05</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
@@ -10428,19 +10436,19 @@
         <v>666</v>
       </c>
       <c r="C333" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D333" s="7">
-        <v>0.086149</v>
+        <v>0.086561</v>
       </c>
       <c r="E333" s="8">
-        <v>64565931551.17</v>
+        <v>64580514450.25</v>
       </c>
       <c r="F333" s="9">
-        <v>122726</v>
+        <v>122815</v>
       </c>
       <c r="G333" s="8">
-        <v>5562282017.82</v>
+        <v>5590126321.32</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
@@ -10451,19 +10459,19 @@
         <v>668</v>
       </c>
       <c r="C334" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D334" s="7">
-        <v>0.458931</v>
+        <v>0.459731</v>
       </c>
       <c r="E334" s="8">
-        <v>52629993991.95</v>
+        <v>52581597529.82</v>
       </c>
       <c r="F334" s="9">
-        <v>127303</v>
+        <v>127188</v>
       </c>
       <c r="G334" s="8">
-        <v>24153554255.75</v>
+        <v>24173412679.75</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
@@ -10474,19 +10482,19 @@
         <v>670</v>
       </c>
       <c r="C335" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D335" s="7">
-        <v>0.098048</v>
+        <v>46140</v>
+      </c>
+      <c r="D335" s="10">
+        <v>0.09824</v>
       </c>
       <c r="E335" s="8">
-        <v>5286252954.6</v>
+        <v>5281969048.38</v>
       </c>
       <c r="F335" s="9">
-        <v>8816</v>
+        <v>8805</v>
       </c>
       <c r="G335" s="8">
-        <v>518304351.54</v>
+        <v>518899229.33</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
@@ -10497,19 +10505,19 @@
         <v>672</v>
       </c>
       <c r="C336" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D336" s="7">
-        <v>0.358724</v>
+        <v>0.358448</v>
       </c>
       <c r="E336" s="8">
-        <v>15892753140.41</v>
+        <v>15868917882.77</v>
       </c>
       <c r="F336" s="9">
-        <v>28649</v>
+        <v>28637</v>
       </c>
       <c r="G336" s="8">
-        <v>5701108394.79</v>
+        <v>5688179148.97</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
@@ -10520,19 +10528,19 @@
         <v>674</v>
       </c>
       <c r="C337" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D337" s="7">
-        <v>0.010297</v>
+        <v>0.010335</v>
       </c>
       <c r="E337" s="8">
-        <v>75012527666.74</v>
+        <v>75247307912.35</v>
       </c>
       <c r="F337" s="9">
-        <v>3993</v>
+        <v>4116</v>
       </c>
       <c r="G337" s="8">
-        <v>772379219.76</v>
+        <v>777683822.25</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
@@ -10543,19 +10551,19 @@
         <v>676</v>
       </c>
       <c r="C338" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D338" s="7">
-        <v>0.081363</v>
+        <v>0.081447</v>
       </c>
       <c r="E338" s="8">
-        <v>3726162337.49</v>
+        <v>3721884349.94</v>
       </c>
       <c r="F338" s="9">
-        <v>78598</v>
+        <v>78652</v>
       </c>
       <c r="G338" s="8">
-        <v>303171568.76</v>
+        <v>303135265.68</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
@@ -10566,19 +10574,19 @@
         <v>678</v>
       </c>
       <c r="C339" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D339" s="7">
-        <v>0.090868</v>
+        <v>46140</v>
+      </c>
+      <c r="D339" s="10">
+        <v>0.09105</v>
       </c>
       <c r="E339" s="8">
-        <v>629387688.47</v>
+        <v>633025355.74</v>
       </c>
       <c r="F339" s="9">
-        <v>12452</v>
+        <v>12555</v>
       </c>
       <c r="G339" s="8">
-        <v>57191036.65</v>
+        <v>57637072.87</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
@@ -10589,19 +10597,19 @@
         <v>680</v>
       </c>
       <c r="C340" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D340" s="7">
-        <v>0.042742</v>
+        <v>46140</v>
+      </c>
+      <c r="D340" s="10">
+        <v>0.04294</v>
       </c>
       <c r="E340" s="8">
-        <v>1020398560.58</v>
+        <v>1025088784.38</v>
       </c>
       <c r="F340" s="9">
-        <v>2175</v>
+        <v>2183</v>
       </c>
       <c r="G340" s="8">
-        <v>43614106.94</v>
+        <v>44017425.65</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -10612,19 +10620,19 @@
         <v>682</v>
       </c>
       <c r="C341" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D341" s="7">
-        <v>0.049933</v>
+        <v>0.050019</v>
       </c>
       <c r="E341" s="8">
-        <v>3906139411.3</v>
+        <v>3910411639.38</v>
       </c>
       <c r="F341" s="9">
-        <v>4258</v>
+        <v>4276</v>
       </c>
       <c r="G341" s="8">
-        <v>195046668.62</v>
+        <v>195595053.35</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
@@ -10635,19 +10643,19 @@
         <v>684</v>
       </c>
       <c r="C342" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D342" s="7">
-        <v>0.014096</v>
+        <v>0.014122</v>
       </c>
       <c r="E342" s="8">
-        <v>34278597118.85</v>
+        <v>34435002007.46</v>
       </c>
       <c r="F342" s="9">
-        <v>26583</v>
+        <v>26741</v>
       </c>
       <c r="G342" s="8">
-        <v>483196522.45</v>
+        <v>486292511.52</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
@@ -10658,19 +10666,19 @@
         <v>686</v>
       </c>
       <c r="C343" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D343" s="7">
-        <v>0.070296</v>
+        <v>0.071579</v>
       </c>
       <c r="E343" s="8">
-        <v>46031013075.44</v>
+        <v>46382703478.87</v>
       </c>
       <c r="F343" s="9">
-        <v>119114</v>
+        <v>119466</v>
       </c>
       <c r="G343" s="8">
-        <v>3235781592.89</v>
+        <v>3320028931.97</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
@@ -10681,19 +10689,19 @@
         <v>688</v>
       </c>
       <c r="C344" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D344" s="7">
-        <v>0.012677</v>
+        <v>0.012712</v>
       </c>
       <c r="E344" s="8">
-        <v>14359316597.19</v>
+        <v>14493830541.93</v>
       </c>
       <c r="F344" s="9">
-        <v>5214</v>
+        <v>5250</v>
       </c>
       <c r="G344" s="8">
-        <v>182035584.26</v>
+        <v>184246739.46</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
@@ -10704,19 +10712,19 @@
         <v>690</v>
       </c>
       <c r="C345" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D345" s="7">
-        <v>0.014737</v>
+        <v>0.014752</v>
       </c>
       <c r="E345" s="8">
-        <v>64077658122.73</v>
+        <v>67436749344.36</v>
       </c>
       <c r="F345" s="9">
-        <v>18033</v>
+        <v>18219</v>
       </c>
       <c r="G345" s="8">
-        <v>944315678.31</v>
+        <v>994819919.55</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
@@ -10727,19 +10735,19 @@
         <v>692</v>
       </c>
       <c r="C346" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D346" s="7">
-        <v>0.049625</v>
+        <v>0.049557</v>
       </c>
       <c r="E346" s="8">
-        <v>7333905164.78</v>
+        <v>7316107766.75</v>
       </c>
       <c r="F346" s="9">
-        <v>9316</v>
+        <v>9323</v>
       </c>
       <c r="G346" s="8">
-        <v>363943615.65</v>
+        <v>362567230.53</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
@@ -10750,19 +10758,19 @@
         <v>694</v>
       </c>
       <c r="C347" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D347" s="7">
-        <v>0.086285</v>
+        <v>0.086373</v>
       </c>
       <c r="E347" s="8">
-        <v>598566233.67</v>
+        <v>594648586.95</v>
       </c>
       <c r="F347" s="9">
-        <v>7133</v>
+        <v>6997</v>
       </c>
       <c r="G347" s="8">
-        <v>51647001.98</v>
+        <v>51361679.26</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
@@ -10773,19 +10781,19 @@
         <v>696</v>
       </c>
       <c r="C348" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D348" s="7">
-        <v>0.049189</v>
+        <v>0.049061</v>
       </c>
       <c r="E348" s="8">
-        <v>3918824331.94</v>
+        <v>3911879612.09</v>
       </c>
       <c r="F348" s="9">
-        <v>5958</v>
+        <v>5953</v>
       </c>
       <c r="G348" s="8">
-        <v>192761576.5</v>
+        <v>191920682.55</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
@@ -10796,19 +10804,19 @@
         <v>698</v>
       </c>
       <c r="C349" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D349" s="7">
-        <v>0.020416</v>
+        <v>0.020576</v>
       </c>
       <c r="E349" s="8">
-        <v>8823073763.44</v>
+        <v>8696617488.68</v>
       </c>
       <c r="F349" s="9">
         <v>336</v>
       </c>
       <c r="G349" s="8">
-        <v>180131638.07</v>
+        <v>178939360.85</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
@@ -10819,19 +10827,19 @@
         <v>700</v>
       </c>
       <c r="C350" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D350" s="7">
-        <v>0.015126</v>
+        <v>0.015225</v>
       </c>
       <c r="E350" s="8">
-        <v>15505909154.18</v>
+        <v>15530635539.16</v>
       </c>
       <c r="F350" s="9">
-        <v>5815</v>
+        <v>5835</v>
       </c>
       <c r="G350" s="8">
-        <v>234534693.67</v>
+        <v>236459424.16</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
@@ -10842,19 +10850,19 @@
         <v>702</v>
       </c>
       <c r="C351" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D351" s="10">
-        <v>0.01379</v>
+        <v>46140</v>
+      </c>
+      <c r="D351" s="7">
+        <v>0.013757</v>
       </c>
       <c r="E351" s="8">
-        <v>21970306403.37</v>
+        <v>22037722144.37</v>
       </c>
       <c r="F351" s="9">
-        <v>5550</v>
+        <v>5596</v>
       </c>
       <c r="G351" s="8">
-        <v>302968195.02</v>
+        <v>303164161.61</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -10865,19 +10873,19 @@
         <v>704</v>
       </c>
       <c r="C352" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D352" s="7">
-        <v>0.014308</v>
+        <v>0.014259</v>
       </c>
       <c r="E352" s="8">
-        <v>22851826236.07</v>
+        <v>23293839112.68</v>
       </c>
       <c r="F352" s="9">
-        <v>10548</v>
+        <v>10558</v>
       </c>
       <c r="G352" s="8">
-        <v>326964046.01</v>
+        <v>332151663.81</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -10888,19 +10896,19 @@
         <v>706</v>
       </c>
       <c r="C353" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D353" s="7">
-        <v>0.014858</v>
+        <v>0.015218</v>
       </c>
       <c r="E353" s="8">
-        <v>36428759428.25</v>
+        <v>36588334333.84</v>
       </c>
       <c r="F353" s="9">
-        <v>9897</v>
+        <v>9961</v>
       </c>
       <c r="G353" s="8">
-        <v>541267765.08</v>
+        <v>556798002.93</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
@@ -10911,19 +10919,19 @@
         <v>708</v>
       </c>
       <c r="C354" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D354" s="7">
-        <v>0.049413</v>
+        <v>46140</v>
+      </c>
+      <c r="D354" s="10">
+        <v>0.04928</v>
       </c>
       <c r="E354" s="8">
-        <v>2906610309.42</v>
+        <v>2913735442.17</v>
       </c>
       <c r="F354" s="9">
-        <v>5172</v>
+        <v>5170</v>
       </c>
       <c r="G354" s="8">
-        <v>143622914.35</v>
+        <v>143588263.07</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -10934,19 +10942,19 @@
         <v>710</v>
       </c>
       <c r="C355" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D355" s="7">
-        <v>0.223515</v>
+        <v>0.226347</v>
       </c>
       <c r="E355" s="8">
-        <v>8774918342.54</v>
+        <v>8775157111.01</v>
       </c>
       <c r="F355" s="9">
-        <v>47702</v>
+        <v>47712</v>
       </c>
       <c r="G355" s="8">
-        <v>1961322584.12</v>
+        <v>1986227276.2</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
@@ -10957,19 +10965,19 @@
         <v>712</v>
       </c>
       <c r="C356" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D356" s="7">
-        <v>0.082271</v>
+        <v>0.082345</v>
       </c>
       <c r="E356" s="8">
-        <v>11877397421.66</v>
+        <v>11846151833.3</v>
       </c>
       <c r="F356" s="9">
-        <v>21804</v>
+        <v>21760</v>
       </c>
       <c r="G356" s="8">
-        <v>977169496.82</v>
+        <v>975466898.8</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
@@ -10980,19 +10988,19 @@
         <v>714</v>
       </c>
       <c r="C357" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D357" s="7">
-        <v>0.306948</v>
+        <v>46140</v>
+      </c>
+      <c r="D357" s="10">
+        <v>0.30839</v>
       </c>
       <c r="E357" s="8">
-        <v>3864202575.24</v>
+        <v>3861897679.02</v>
       </c>
       <c r="F357" s="9">
-        <v>27655</v>
+        <v>27637</v>
       </c>
       <c r="G357" s="8">
-        <v>1186110900.61</v>
+        <v>1190969176.58</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
@@ -11003,19 +11011,19 @@
         <v>716</v>
       </c>
       <c r="C358" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D358" s="7">
-        <v>1.383141</v>
+        <v>1.382147</v>
       </c>
       <c r="E358" s="8">
-        <v>8876378060.61</v>
+        <v>8831154245.18</v>
       </c>
       <c r="F358" s="9">
-        <v>244612</v>
+        <v>244811</v>
       </c>
       <c r="G358" s="8">
-        <v>12277283673.37</v>
+        <v>12205952945.28</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
@@ -11026,19 +11034,19 @@
         <v>718</v>
       </c>
       <c r="C359" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D359" s="10">
-        <v>0.09675</v>
+        <v>46140</v>
+      </c>
+      <c r="D359" s="7">
+        <v>0.096512</v>
       </c>
       <c r="E359" s="8">
-        <v>535496181465.84</v>
+        <v>534906820780.14</v>
       </c>
       <c r="F359" s="9">
-        <v>2771686</v>
+        <v>2769500</v>
       </c>
       <c r="G359" s="8">
-        <v>51809396622</v>
+        <v>51624959230.43</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
@@ -11049,19 +11057,19 @@
         <v>720</v>
       </c>
       <c r="C360" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D360" s="7">
-        <v>0.321866</v>
+        <v>46140</v>
+      </c>
+      <c r="D360" s="12">
+        <v>0.3222</v>
       </c>
       <c r="E360" s="8">
-        <v>23908285717.9</v>
+        <v>23892771297.09</v>
       </c>
       <c r="F360" s="9">
-        <v>423799</v>
+        <v>423549</v>
       </c>
       <c r="G360" s="8">
-        <v>7695260266.79</v>
+        <v>7698246794.35</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
@@ -11072,19 +11080,19 @@
         <v>722</v>
       </c>
       <c r="C361" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D361" s="7">
-        <v>0.347557</v>
+        <v>0.347947</v>
       </c>
       <c r="E361" s="8">
-        <v>82856040504.43</v>
+        <v>83179400115.47</v>
       </c>
       <c r="F361" s="9">
-        <v>388165</v>
+        <v>425118</v>
       </c>
       <c r="G361" s="8">
-        <v>28797162120.92</v>
+        <v>28941994323.8</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
@@ -11095,19 +11103,19 @@
         <v>724</v>
       </c>
       <c r="C362" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D362" s="7">
-        <v>0.219226</v>
+        <v>0.222188</v>
       </c>
       <c r="E362" s="8">
-        <v>20318898769.38</v>
+        <v>20314820559.14</v>
       </c>
       <c r="F362" s="9">
-        <v>69896</v>
+        <v>69884</v>
       </c>
       <c r="G362" s="8">
-        <v>4454431147.57</v>
+        <v>4513715533.06</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
@@ -11118,19 +11126,19 @@
         <v>726</v>
       </c>
       <c r="C363" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D363" s="7">
-        <v>0.101596</v>
+        <v>0.101652</v>
       </c>
       <c r="E363" s="8">
-        <v>3773583614.82</v>
+        <v>3765539285.07</v>
       </c>
       <c r="F363" s="9">
-        <v>8009</v>
+        <v>8000</v>
       </c>
       <c r="G363" s="8">
-        <v>383379458.45</v>
+        <v>382775659.2</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
@@ -11141,19 +11149,19 @@
         <v>728</v>
       </c>
       <c r="C364" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D364" s="7">
-        <v>0.135274</v>
+        <v>0.136689</v>
       </c>
       <c r="E364" s="8">
-        <v>102478534272.94</v>
+        <v>102361259267.4</v>
       </c>
       <c r="F364" s="9">
-        <v>1889186</v>
+        <v>1887748</v>
       </c>
       <c r="G364" s="8">
-        <v>13862696324.99</v>
+        <v>13991631579.87</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
@@ -11164,19 +11172,19 @@
         <v>730</v>
       </c>
       <c r="C365" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D365" s="7">
-        <v>0.135704</v>
+        <v>0.135742</v>
       </c>
       <c r="E365" s="8">
-        <v>58384668632.27</v>
+        <v>58260488455.76</v>
       </c>
       <c r="F365" s="9">
-        <v>120084</v>
+        <v>120062</v>
       </c>
       <c r="G365" s="8">
-        <v>7923039736.72</v>
+        <v>7908384229.32</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
@@ -11187,19 +11195,19 @@
         <v>732</v>
       </c>
       <c r="C366" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D366" s="10">
-        <v>0.73282</v>
+        <v>46140</v>
+      </c>
+      <c r="D366" s="7">
+        <v>0.733663</v>
       </c>
       <c r="E366" s="8">
-        <v>16764223140.66</v>
+        <v>16788299653.05</v>
       </c>
       <c r="F366" s="9">
-        <v>342059</v>
+        <v>342141</v>
       </c>
       <c r="G366" s="8">
-        <v>12285154540.73</v>
+        <v>12316949610.97</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
@@ -11210,19 +11218,19 @@
         <v>734</v>
       </c>
       <c r="C367" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D367" s="7">
-        <v>0.146864</v>
+        <v>0.146636</v>
       </c>
       <c r="E367" s="8">
-        <v>31281588505.28</v>
+        <v>31261012571.88</v>
       </c>
       <c r="F367" s="9">
-        <v>93691</v>
+        <v>93595</v>
       </c>
       <c r="G367" s="8">
-        <v>4594139165.77</v>
+        <v>4583988361.87</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
@@ -11233,19 +11241,19 @@
         <v>736</v>
       </c>
       <c r="C368" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D368" s="7">
-        <v>0.170303</v>
+        <v>0.170582</v>
       </c>
       <c r="E368" s="8">
-        <v>2091963071.24</v>
+        <v>2085031993.4</v>
       </c>
       <c r="F368" s="9">
-        <v>7386</v>
+        <v>7376</v>
       </c>
       <c r="G368" s="8">
-        <v>356267015.69</v>
+        <v>355668377.57</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
@@ -11256,19 +11264,19 @@
         <v>738</v>
       </c>
       <c r="C369" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D369" s="10">
-        <v>0.38081</v>
+        <v>46140</v>
+      </c>
+      <c r="D369" s="7">
+        <v>0.381199</v>
       </c>
       <c r="E369" s="8">
-        <v>4858788585.2</v>
+        <v>4863975922.71</v>
       </c>
       <c r="F369" s="9">
-        <v>18517</v>
+        <v>18559</v>
       </c>
       <c r="G369" s="8">
-        <v>1850275299.19</v>
+        <v>1854144988.42</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
@@ -11279,19 +11287,19 @@
         <v>740</v>
       </c>
       <c r="C370" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D370" s="7">
-        <v>0.788579</v>
+        <v>0.787131</v>
       </c>
       <c r="E370" s="8">
-        <v>329658144283.71</v>
+        <v>329467240000.36</v>
       </c>
       <c r="F370" s="9">
-        <v>2051210</v>
+        <v>2049518</v>
       </c>
       <c r="G370" s="8">
-        <v>259961401727.66</v>
+        <v>259333926329.67</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
@@ -11302,19 +11310,19 @@
         <v>742</v>
       </c>
       <c r="C371" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D371" s="7">
-        <v>0.156698</v>
+        <v>0.157514</v>
       </c>
       <c r="E371" s="8">
-        <v>23855343628.83</v>
+        <v>23881658966.46</v>
       </c>
       <c r="F371" s="9">
-        <v>109426</v>
+        <v>109352</v>
       </c>
       <c r="G371" s="8">
-        <v>3738077323.26</v>
+        <v>3761703587.78</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
@@ -11325,19 +11333,19 @@
         <v>744</v>
       </c>
       <c r="C372" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D372" s="7">
-        <v>0.193997</v>
+        <v>0.194225</v>
       </c>
       <c r="E372" s="8">
-        <v>3633231456.78</v>
+        <v>3620005611.63</v>
       </c>
       <c r="F372" s="9">
-        <v>11603</v>
+        <v>11576</v>
       </c>
       <c r="G372" s="8">
-        <v>704834939.7</v>
+        <v>703094597.27</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
@@ -11348,19 +11356,19 @@
         <v>746</v>
       </c>
       <c r="C373" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D373" s="7">
-        <v>0.421401</v>
+        <v>0.423466</v>
       </c>
       <c r="E373" s="8">
-        <v>56749270834.22</v>
+        <v>56507071120.67</v>
       </c>
       <c r="F373" s="9">
-        <v>293191</v>
+        <v>292274</v>
       </c>
       <c r="G373" s="8">
-        <v>23914225590.24</v>
+        <v>23928817270.81</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
@@ -11371,19 +11379,19 @@
         <v>748</v>
       </c>
       <c r="C374" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D374" s="7">
-        <v>0.523773</v>
+        <v>0.525649</v>
       </c>
       <c r="E374" s="8">
-        <v>1226768130.63</v>
+        <v>1240262230.7</v>
       </c>
       <c r="F374" s="9">
-        <v>13854</v>
+        <v>13984</v>
       </c>
       <c r="G374" s="8">
-        <v>642547892.67</v>
+        <v>651942026.92</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
@@ -11394,19 +11402,19 @@
         <v>750</v>
       </c>
       <c r="C375" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D375" s="7">
-        <v>0.184666</v>
+        <v>0.186122</v>
       </c>
       <c r="E375" s="8">
-        <v>6858531617.2</v>
+        <v>6852910788.36</v>
       </c>
       <c r="F375" s="9">
-        <v>16352</v>
+        <v>16329</v>
       </c>
       <c r="G375" s="8">
-        <v>1266535251.81</v>
+        <v>1275475828.78</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
@@ -11417,19 +11425,19 @@
         <v>752</v>
       </c>
       <c r="C376" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D376" s="7">
-        <v>0.118201</v>
+        <v>46140</v>
+      </c>
+      <c r="D376" s="10">
+        <v>0.11863</v>
       </c>
       <c r="E376" s="8">
-        <v>7648393243.12</v>
+        <v>7635197032.11</v>
       </c>
       <c r="F376" s="9">
-        <v>24046</v>
+        <v>24013</v>
       </c>
       <c r="G376" s="8">
-        <v>904049096.96</v>
+        <v>905762932.24</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
@@ -11440,19 +11448,19 @@
         <v>754</v>
       </c>
       <c r="C377" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D377" s="7">
-        <v>0.176332</v>
+        <v>46140</v>
+      </c>
+      <c r="D377" s="10">
+        <v>0.17857</v>
       </c>
       <c r="E377" s="8">
-        <v>14244767088.32</v>
+        <v>14220243736.92</v>
       </c>
       <c r="F377" s="9">
-        <v>51063</v>
+        <v>50999</v>
       </c>
       <c r="G377" s="8">
-        <v>2511809411.54</v>
+        <v>2539303499.39</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
@@ -11463,19 +11471,19 @@
         <v>756</v>
       </c>
       <c r="C378" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D378" s="7">
-        <v>0.087872</v>
+        <v>0.088184</v>
       </c>
       <c r="E378" s="8">
-        <v>397978663056.76</v>
+        <v>397259246642.01</v>
       </c>
       <c r="F378" s="9">
-        <v>1946682</v>
+        <v>1945291</v>
       </c>
       <c r="G378" s="8">
-        <v>34971149479.83</v>
+        <v>35031717841.33</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
@@ -11486,19 +11494,19 @@
         <v>758</v>
       </c>
       <c r="C379" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D379" s="7">
-        <v>0.153701</v>
+        <v>0.155762</v>
       </c>
       <c r="E379" s="8">
-        <v>1165867437.98</v>
+        <v>1163541433.56</v>
       </c>
       <c r="F379" s="9">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="G379" s="8">
-        <v>179194413.76</v>
+        <v>181235648.94</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
@@ -11509,19 +11517,19 @@
         <v>760</v>
       </c>
       <c r="C380" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D380" s="7">
-        <v>0.190605</v>
+        <v>0.190896</v>
       </c>
       <c r="E380" s="8">
-        <v>1031417771.51</v>
+        <v>1031418130.88</v>
       </c>
       <c r="F380" s="9">
         <v>1805</v>
       </c>
       <c r="G380" s="8">
-        <v>196593026.32</v>
+        <v>196893879.87</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
@@ -11532,19 +11540,19 @@
         <v>762</v>
       </c>
       <c r="C381" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D381" s="7">
-        <v>0.174549</v>
+        <v>0.174211</v>
       </c>
       <c r="E381" s="8">
-        <v>587929443.13</v>
+        <v>587016860.51</v>
       </c>
       <c r="F381" s="9">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="G381" s="8">
-        <v>102622674.23</v>
+        <v>102264832.37</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
@@ -11555,19 +11563,19 @@
         <v>764</v>
       </c>
       <c r="C382" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D382" s="7">
-        <v>0.092594</v>
+        <v>0.092521</v>
       </c>
       <c r="E382" s="8">
-        <v>98290197547.7</v>
+        <v>98097587665.2</v>
       </c>
       <c r="F382" s="9">
-        <v>665991</v>
+        <v>665527</v>
       </c>
       <c r="G382" s="8">
-        <v>9101060311.35</v>
+        <v>9076098307.31</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
@@ -11578,19 +11586,19 @@
         <v>766</v>
       </c>
       <c r="C383" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D383" s="7">
-        <v>0.089269</v>
+        <v>0.089359</v>
       </c>
       <c r="E383" s="8">
-        <v>42666624508.84</v>
+        <v>42700129193.37</v>
       </c>
       <c r="F383" s="9">
-        <v>444750</v>
+        <v>443274</v>
       </c>
       <c r="G383" s="8">
-        <v>3808797404.44</v>
+        <v>3815623815.86</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
@@ -11601,19 +11609,19 @@
         <v>768</v>
       </c>
       <c r="C384" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D384" s="7">
-        <v>0.093668</v>
+        <v>0.093769</v>
       </c>
       <c r="E384" s="8">
-        <v>16527098132.18</v>
+        <v>16522129552.61</v>
       </c>
       <c r="F384" s="9">
-        <v>124405</v>
+        <v>124305</v>
       </c>
       <c r="G384" s="8">
-        <v>1548068090.22</v>
+        <v>1549261421.7</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
@@ -11624,19 +11632,19 @@
         <v>770</v>
       </c>
       <c r="C385" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D385" s="7">
-        <v>0.262527</v>
+        <v>0.264574</v>
       </c>
       <c r="E385" s="8">
-        <v>3508563420.35</v>
+        <v>3514341277.9</v>
       </c>
       <c r="F385" s="9">
-        <v>10517</v>
+        <v>10531</v>
       </c>
       <c r="G385" s="8">
-        <v>921092045.2</v>
+        <v>929804901.38</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
@@ -11647,19 +11655,19 @@
         <v>772</v>
       </c>
       <c r="C386" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D386" s="7">
-        <v>0.189363</v>
+        <v>0.191012</v>
       </c>
       <c r="E386" s="8">
-        <v>2311782582.71</v>
+        <v>2310684631.9</v>
       </c>
       <c r="F386" s="9">
-        <v>7093</v>
+        <v>7102</v>
       </c>
       <c r="G386" s="8">
-        <v>437765852.99</v>
+        <v>441367671.94</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
@@ -11670,19 +11678,19 @@
         <v>774</v>
       </c>
       <c r="C387" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D387" s="7">
-        <v>0.172108</v>
+        <v>0.173509</v>
       </c>
       <c r="E387" s="8">
-        <v>2450500859.59</v>
+        <v>2455321364.92</v>
       </c>
       <c r="F387" s="9">
-        <v>7587</v>
+        <v>7594</v>
       </c>
       <c r="G387" s="8">
-        <v>421749746.04</v>
+        <v>426021568.3</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
@@ -11693,19 +11701,19 @@
         <v>776</v>
       </c>
       <c r="C388" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D388" s="7">
-        <v>0.098842</v>
+        <v>0.099038</v>
       </c>
       <c r="E388" s="8">
-        <v>3866162622.52</v>
+        <v>3859453285.66</v>
       </c>
       <c r="F388" s="9">
-        <v>7273</v>
+        <v>7269</v>
       </c>
       <c r="G388" s="8">
-        <v>382140521.47</v>
+        <v>382231001.43</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -11716,19 +11724,19 @@
         <v>778</v>
       </c>
       <c r="C389" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D389" s="7">
-        <v>0.226379</v>
+        <v>0.228925</v>
       </c>
       <c r="E389" s="8">
-        <v>1480448635.45</v>
+        <v>1480498275.36</v>
       </c>
       <c r="F389" s="9">
         <v>5800</v>
       </c>
       <c r="G389" s="8">
-        <v>335142237.82</v>
+        <v>338923596.72</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
@@ -11739,19 +11747,19 @@
         <v>780</v>
       </c>
       <c r="C390" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D390" s="7">
-        <v>0.318028</v>
+        <v>0.321931</v>
       </c>
       <c r="E390" s="8">
-        <v>1898802097.56</v>
+        <v>1899481898.05</v>
       </c>
       <c r="F390" s="9">
-        <v>6284</v>
+        <v>6291</v>
       </c>
       <c r="G390" s="8">
-        <v>603872320.02</v>
+        <v>611502917.12</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
@@ -11762,19 +11770,19 @@
         <v>782</v>
       </c>
       <c r="C391" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D391" s="7">
-        <v>0.269039</v>
+        <v>0.273345</v>
       </c>
       <c r="E391" s="8">
-        <v>13862342367.09</v>
+        <v>13826528805.79</v>
       </c>
       <c r="F391" s="9">
-        <v>66354</v>
+        <v>66471</v>
       </c>
       <c r="G391" s="8">
-        <v>3729515215.58</v>
+        <v>3779413803.17</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
@@ -11785,19 +11793,19 @@
         <v>784</v>
       </c>
       <c r="C392" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D392" s="7">
-        <v>0.057334</v>
+        <v>0.058293</v>
       </c>
       <c r="E392" s="8">
-        <v>54282035743.64</v>
+        <v>54529829713.24</v>
       </c>
       <c r="F392" s="9">
-        <v>40864</v>
+        <v>40958</v>
       </c>
       <c r="G392" s="8">
-        <v>3112196782.57</v>
+        <v>3178697551.58</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
@@ -11808,19 +11816,19 @@
         <v>786</v>
       </c>
       <c r="C393" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D393" s="7">
-        <v>0.338058</v>
+        <v>0.340507</v>
       </c>
       <c r="E393" s="8">
-        <v>13108802195.64</v>
+        <v>13302637141.36</v>
       </c>
       <c r="F393" s="9">
-        <v>215266</v>
+        <v>215684</v>
       </c>
       <c r="G393" s="8">
-        <v>4431529317.2</v>
+        <v>4529640747.44</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
@@ -11831,19 +11839,19 @@
         <v>788</v>
       </c>
       <c r="C394" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D394" s="7">
-        <v>0.370834</v>
+        <v>0.371364</v>
       </c>
       <c r="E394" s="8">
-        <v>4677569304.9</v>
+        <v>4717386906.38</v>
       </c>
       <c r="F394" s="9">
-        <v>52510</v>
+        <v>52935</v>
       </c>
       <c r="G394" s="8">
-        <v>1734602533.76</v>
+        <v>1751865457.02</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
@@ -11854,19 +11862,19 @@
         <v>790</v>
       </c>
       <c r="C395" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D395" s="7">
-        <v>0.220029</v>
+        <v>0.220173</v>
       </c>
       <c r="E395" s="8">
-        <v>69130721715.31</v>
+        <v>69077100308.27</v>
       </c>
       <c r="F395" s="9">
-        <v>520052</v>
+        <v>519730</v>
       </c>
       <c r="G395" s="8">
-        <v>15210742722.57</v>
+        <v>15208882914.13</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
@@ -11877,19 +11885,19 @@
         <v>792</v>
       </c>
       <c r="C396" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D396" s="7">
-        <v>0.131252</v>
+        <v>0.131864</v>
       </c>
       <c r="E396" s="8">
-        <v>12877661043.92</v>
+        <v>12859695611.99</v>
       </c>
       <c r="F396" s="9">
-        <v>45355</v>
+        <v>45336</v>
       </c>
       <c r="G396" s="8">
-        <v>1690213888.02</v>
+        <v>1695727757.4</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -11900,19 +11908,19 @@
         <v>794</v>
       </c>
       <c r="C397" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D397" s="7">
-        <v>0.063448</v>
+        <v>0.063338</v>
       </c>
       <c r="E397" s="8">
-        <v>58552806404.03</v>
+        <v>58528742231.75</v>
       </c>
       <c r="F397" s="9">
-        <v>324442</v>
+        <v>324264</v>
       </c>
       <c r="G397" s="8">
-        <v>3715053709.09</v>
+        <v>3707084839.24</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>28.04.2026 18:41:33</t>
+    <t>29.04.2026 18:50:27</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2402,14 +2402,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
     <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
-    <numFmt numFmtId="169" formatCode="###0.000;-###0.000;0"/>
-    <numFmt numFmtId="170" formatCode="###0.0000;-###0.0000;0"/>
+    <numFmt numFmtId="169" formatCode="###0.0000;-###0.0000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -2479,7 +2478,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2508,9 +2507,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2915,19 +2911,19 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D6" s="7">
-        <v>0.101638</v>
+        <v>0.101093</v>
       </c>
       <c r="E6" s="8">
-        <v>47346699237.61</v>
+        <v>47301738951.15</v>
       </c>
       <c r="F6" s="9">
-        <v>644747</v>
+        <v>644498</v>
       </c>
       <c r="G6" s="8">
-        <v>4812218649.22</v>
+        <v>4781858874.26</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2938,19 +2934,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D7" s="7">
-        <v>0.399289</v>
+        <v>0.398282</v>
       </c>
       <c r="E7" s="8">
-        <v>17096684919.48</v>
+        <v>17107112337.73</v>
       </c>
       <c r="F7" s="9">
         <v>151719</v>
       </c>
       <c r="G7" s="8">
-        <v>6826510143.98</v>
+        <v>6813457443.95</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2961,19 +2957,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D8" s="7">
-        <v>0.086026</v>
+        <v>0.086025</v>
       </c>
       <c r="E8" s="8">
-        <v>8029770634.85</v>
+        <v>8000764105.4</v>
       </c>
       <c r="F8" s="9">
-        <v>142903</v>
+        <v>142512</v>
       </c>
       <c r="G8" s="8">
-        <v>690766141.06</v>
+        <v>688262500.81</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2984,19 +2980,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0.366644</v>
+        <v>46141</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0.36696</v>
       </c>
       <c r="E9" s="8">
-        <v>140662118569.18</v>
+        <v>140931211819.4</v>
       </c>
       <c r="F9" s="9">
-        <v>486361</v>
+        <v>487108</v>
       </c>
       <c r="G9" s="8">
-        <v>51572935118.67</v>
+        <v>51716134325.98</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3007,19 +3003,19 @@
         <v>20</v>
       </c>
       <c r="C10" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D10" s="7">
-        <v>0.334124</v>
+        <v>0.332648</v>
       </c>
       <c r="E10" s="8">
-        <v>23179686625.69</v>
+        <v>23160411515.13</v>
       </c>
       <c r="F10" s="9">
-        <v>329347</v>
+        <v>329426</v>
       </c>
       <c r="G10" s="8">
-        <v>7744879079.45</v>
+        <v>7704268942.78</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3030,19 +3026,19 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D11" s="7">
-        <v>1.003077</v>
+        <v>0.993106</v>
       </c>
       <c r="E11" s="8">
-        <v>11605332846.53</v>
+        <v>11589047161.69</v>
       </c>
       <c r="F11" s="9">
-        <v>289190</v>
+        <v>289116</v>
       </c>
       <c r="G11" s="8">
-        <v>11641045735.28</v>
+        <v>11509149326.45</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3053,19 +3049,19 @@
         <v>24</v>
       </c>
       <c r="C12" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D12" s="7">
-        <v>0.716822</v>
+        <v>0.700638</v>
       </c>
       <c r="E12" s="8">
-        <v>136885441909.42</v>
+        <v>136892499596.86</v>
       </c>
       <c r="F12" s="9">
         <v>726136</v>
       </c>
       <c r="G12" s="8">
-        <v>98122487602.24</v>
+        <v>95912095628.21</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3076,19 +3072,19 @@
         <v>26</v>
       </c>
       <c r="C13" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D13" s="7">
-        <v>2.025322</v>
+        <v>1.995602</v>
       </c>
       <c r="E13" s="8">
-        <v>1360996687.75</v>
+        <v>1361267909.18</v>
       </c>
       <c r="F13" s="9">
-        <v>32545</v>
+        <v>32521</v>
       </c>
       <c r="G13" s="8">
-        <v>2756456075.13</v>
+        <v>2716548613.42</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3099,10 +3095,10 @@
         <v>28</v>
       </c>
       <c r="C14" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D14" s="7">
-        <v>0.136814</v>
+        <v>0.136637</v>
       </c>
       <c r="E14" s="8">
         <v>249905599.92</v>
@@ -3111,7 +3107,7 @@
         <v>92</v>
       </c>
       <c r="G14" s="8">
-        <v>34190704.65</v>
+        <v>34146427.53</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3122,19 +3118,19 @@
         <v>30</v>
       </c>
       <c r="C15" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D15" s="7">
-        <v>1.384607</v>
+        <v>1.365204</v>
       </c>
       <c r="E15" s="8">
-        <v>16063710127.42</v>
+        <v>16089345194.29</v>
       </c>
       <c r="F15" s="9">
-        <v>486060</v>
+        <v>486449</v>
       </c>
       <c r="G15" s="8">
-        <v>22241918145.35</v>
+        <v>21965239482.45</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3145,19 +3141,19 @@
         <v>32</v>
       </c>
       <c r="C16" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D16" s="7">
-        <v>0.093752</v>
+        <v>0.092773</v>
       </c>
       <c r="E16" s="8">
-        <v>560302288770.74</v>
+        <v>559868215659.5</v>
       </c>
       <c r="F16" s="9">
-        <v>1924799</v>
+        <v>1923799</v>
       </c>
       <c r="G16" s="8">
-        <v>52529706680.4</v>
+        <v>51940694109.56</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3168,19 +3164,19 @@
         <v>34</v>
       </c>
       <c r="C17" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D17" s="7">
-        <v>0.347945</v>
+        <v>0.346562</v>
       </c>
       <c r="E17" s="8">
-        <v>2111711739.58</v>
+        <v>2108770697.87</v>
       </c>
       <c r="F17" s="9">
-        <v>13349</v>
+        <v>13320</v>
       </c>
       <c r="G17" s="8">
-        <v>734760512.44</v>
+        <v>730820708.77</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3191,19 +3187,19 @@
         <v>36</v>
       </c>
       <c r="C18" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D18" s="7">
-        <v>0.145097</v>
+        <v>0.144636</v>
       </c>
       <c r="E18" s="8">
-        <v>32990778012.1</v>
+        <v>33038128097.78</v>
       </c>
       <c r="F18" s="9">
-        <v>239454</v>
+        <v>239430</v>
       </c>
       <c r="G18" s="8">
-        <v>4786871667.58</v>
+        <v>4778512383.6</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3214,19 +3210,19 @@
         <v>38</v>
       </c>
       <c r="C19" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D19" s="7">
-        <v>0.371745</v>
+        <v>0.368171</v>
       </c>
       <c r="E19" s="8">
-        <v>1434505645.8</v>
+        <v>1434511839.18</v>
       </c>
       <c r="F19" s="9">
         <v>537</v>
       </c>
       <c r="G19" s="8">
-        <v>533269804.57</v>
+        <v>528146210.61</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3237,19 +3233,19 @@
         <v>40</v>
       </c>
       <c r="C20" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D20" s="7">
-        <v>0.137846</v>
+        <v>0.137129</v>
       </c>
       <c r="E20" s="8">
-        <v>14499071274.9</v>
+        <v>14503274580.34</v>
       </c>
       <c r="F20" s="9">
         <v>519070</v>
       </c>
       <c r="G20" s="8">
-        <v>1998642735.35</v>
+        <v>1988824975.95</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3260,19 +3256,19 @@
         <v>42</v>
       </c>
       <c r="C21" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D21" s="7">
-        <v>0.097611</v>
+        <v>0.096624</v>
       </c>
       <c r="E21" s="8">
-        <v>502176106007.28</v>
+        <v>501885958699.14</v>
       </c>
       <c r="F21" s="9">
         <v>2272635</v>
       </c>
       <c r="G21" s="8">
-        <v>49018084153.9</v>
+        <v>48494184589.55</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3283,19 +3279,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D22" s="7">
-        <v>0.400866</v>
+        <v>0.396356</v>
       </c>
       <c r="E22" s="8">
-        <v>3325076316.19</v>
+        <v>3339818323.18</v>
       </c>
       <c r="F22" s="9">
-        <v>18988</v>
+        <v>19026</v>
       </c>
       <c r="G22" s="8">
-        <v>1332911110.42</v>
+        <v>1323756423.23</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3306,10 +3302,10 @@
         <v>46</v>
       </c>
       <c r="C23" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D23" s="7">
-        <v>0.094152</v>
+        <v>0.093106</v>
       </c>
       <c r="E23" s="8">
         <v>572171617.61</v>
@@ -3318,7 +3314,7 @@
         <v>4545</v>
       </c>
       <c r="G23" s="8">
-        <v>53870931.37</v>
+        <v>53272493.33</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3329,19 +3325,19 @@
         <v>48</v>
       </c>
       <c r="C24" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D24" s="7">
-        <v>0.227112</v>
+        <v>0.224734</v>
       </c>
       <c r="E24" s="8">
-        <v>1219080711.46</v>
+        <v>1214055433.68</v>
       </c>
       <c r="F24" s="9">
         <v>4993</v>
       </c>
       <c r="G24" s="8">
-        <v>276868229.16</v>
+        <v>272839647.19</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3352,19 +3348,19 @@
         <v>50</v>
       </c>
       <c r="C25" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D25" s="7">
-        <v>0.106001</v>
+        <v>0.105422</v>
       </c>
       <c r="E25" s="8">
-        <v>66608499413.17</v>
+        <v>66642617155.49</v>
       </c>
       <c r="F25" s="9">
         <v>764907</v>
       </c>
       <c r="G25" s="8">
-        <v>7060552300.06</v>
+        <v>7025627322.07</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3375,19 +3371,19 @@
         <v>52</v>
       </c>
       <c r="C26" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D26" s="7">
-        <v>0.097751</v>
+        <v>0.097462</v>
       </c>
       <c r="E26" s="8">
-        <v>1683061086.64</v>
+        <v>1676318610.65</v>
       </c>
       <c r="F26" s="9">
-        <v>3249</v>
+        <v>3243</v>
       </c>
       <c r="G26" s="8">
-        <v>164520221.08</v>
+        <v>163377960.33</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3398,19 +3394,19 @@
         <v>54</v>
       </c>
       <c r="C27" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D27" s="7">
-        <v>0.093322</v>
+        <v>0.092949</v>
       </c>
       <c r="E27" s="8">
-        <v>61760408563.81</v>
+        <v>61742973383.22</v>
       </c>
       <c r="F27" s="9">
         <v>715690</v>
       </c>
       <c r="G27" s="8">
-        <v>5763580200.63</v>
+        <v>5738928767.55</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3421,19 +3417,19 @@
         <v>56</v>
       </c>
       <c r="C28" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D28" s="7">
-        <v>0.387495</v>
+        <v>0.386578</v>
       </c>
       <c r="E28" s="8">
-        <v>1050955071.34</v>
+        <v>1050281788.05</v>
       </c>
       <c r="F28" s="9">
         <v>7922</v>
       </c>
       <c r="G28" s="8">
-        <v>407240275.93</v>
+        <v>406015778.12</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3444,19 +3440,19 @@
         <v>58</v>
       </c>
       <c r="C29" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D29" s="7">
-        <v>0.646255</v>
+        <v>0.643921</v>
       </c>
       <c r="E29" s="8">
-        <v>210010787.9</v>
+        <v>209996741.87</v>
       </c>
       <c r="F29" s="9">
         <v>1671</v>
       </c>
       <c r="G29" s="8">
-        <v>135720586.22</v>
+        <v>135221406.99</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3467,19 +3463,19 @@
         <v>60</v>
       </c>
       <c r="C30" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D30" s="7">
-        <v>2.382151</v>
+        <v>2.344858</v>
       </c>
       <c r="E30" s="8">
-        <v>871065397.63</v>
+        <v>843120893.02</v>
       </c>
       <c r="F30" s="9">
         <v>19482</v>
       </c>
       <c r="G30" s="8">
-        <v>2075009700.49</v>
+        <v>1976999186.39</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3490,19 +3486,19 @@
         <v>62</v>
       </c>
       <c r="C31" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D31" s="7">
-        <v>0.523764</v>
+        <v>46141</v>
+      </c>
+      <c r="D31" s="11">
+        <v>0.5215</v>
       </c>
       <c r="E31" s="8">
-        <v>2423688091.46</v>
+        <v>2405377461.62</v>
       </c>
       <c r="F31" s="9">
         <v>13861</v>
       </c>
       <c r="G31" s="8">
-        <v>1269440762.73</v>
+        <v>1254405064.47</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3513,19 +3509,19 @@
         <v>64</v>
       </c>
       <c r="C32" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D32" s="7">
-        <v>0.864557</v>
+        <v>0.844686</v>
       </c>
       <c r="E32" s="8">
-        <v>12436627481.27</v>
+        <v>12401023487.12</v>
       </c>
       <c r="F32" s="9">
-        <v>76979</v>
+        <v>77071</v>
       </c>
       <c r="G32" s="8">
-        <v>10752168030.1</v>
+        <v>10474967296.15</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3536,19 +3532,19 @@
         <v>66</v>
       </c>
       <c r="C33" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D33" s="7">
-        <v>0.264404</v>
+        <v>0.261192</v>
       </c>
       <c r="E33" s="8">
-        <v>1316420324.56</v>
+        <v>1311305092.75</v>
       </c>
       <c r="F33" s="9">
-        <v>16203</v>
+        <v>16197</v>
       </c>
       <c r="G33" s="8">
-        <v>348067010.48</v>
+        <v>342502301.95</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3559,19 +3555,19 @@
         <v>68</v>
       </c>
       <c r="C34" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D34" s="7">
-        <v>0.125378</v>
+        <v>0.124583</v>
       </c>
       <c r="E34" s="8">
-        <v>3344428325.06</v>
+        <v>3333312470.66</v>
       </c>
       <c r="F34" s="9">
-        <v>53951</v>
+        <v>53945</v>
       </c>
       <c r="G34" s="8">
-        <v>419318973.26</v>
+        <v>415275343.77</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3582,19 +3578,19 @@
         <v>70</v>
       </c>
       <c r="C35" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D35" s="7">
-        <v>0.175059</v>
+        <v>0.174548</v>
       </c>
       <c r="E35" s="8">
-        <v>10657155061.78</v>
+        <v>10659017489.79</v>
       </c>
       <c r="F35" s="9">
         <v>36593</v>
       </c>
       <c r="G35" s="8">
-        <v>1865632946.36</v>
+        <v>1860514674.22</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3605,19 +3601,19 @@
         <v>72</v>
       </c>
       <c r="C36" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D36" s="7">
-        <v>0.202259</v>
+        <v>0.200046</v>
       </c>
       <c r="E36" s="8">
-        <v>1494936887.82</v>
+        <v>1495509032.29</v>
       </c>
       <c r="F36" s="9">
-        <v>32758</v>
+        <v>32752</v>
       </c>
       <c r="G36" s="8">
-        <v>302364241.77</v>
+        <v>299170839.6</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3628,19 +3624,19 @@
         <v>74</v>
       </c>
       <c r="C37" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D37" s="7">
-        <v>0.825047</v>
+        <v>0.819503</v>
       </c>
       <c r="E37" s="8">
-        <v>2445579044.34</v>
+        <v>2444382827.56</v>
       </c>
       <c r="F37" s="9">
-        <v>52311</v>
+        <v>52323</v>
       </c>
       <c r="G37" s="8">
-        <v>2017717168.43</v>
+        <v>2003178800.79</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3651,19 +3647,19 @@
         <v>76</v>
       </c>
       <c r="C38" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D38" s="7">
-        <v>0.168606</v>
+        <v>46141</v>
+      </c>
+      <c r="D38" s="10">
+        <v>0.16874</v>
       </c>
       <c r="E38" s="8">
-        <v>3692232902.71</v>
+        <v>3691323338.82</v>
       </c>
       <c r="F38" s="9">
-        <v>53234</v>
+        <v>53219</v>
       </c>
       <c r="G38" s="8">
-        <v>622532808.63</v>
+        <v>622875534.31</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3674,19 +3670,19 @@
         <v>78</v>
       </c>
       <c r="C39" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D39" s="7">
-        <v>0.106358</v>
+        <v>46141</v>
+      </c>
+      <c r="D39" s="10">
+        <v>0.10547</v>
       </c>
       <c r="E39" s="8">
-        <v>8044581548.41</v>
+        <v>8023250683.01</v>
       </c>
       <c r="F39" s="9">
-        <v>95790</v>
+        <v>95725</v>
       </c>
       <c r="G39" s="8">
-        <v>855602621.93</v>
+        <v>846210613.55</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3697,19 +3693,19 @@
         <v>80</v>
       </c>
       <c r="C40" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D40" s="7">
-        <v>0.338924</v>
+        <v>0.337902</v>
       </c>
       <c r="E40" s="8">
-        <v>14195291479.6</v>
+        <v>14163554884.05</v>
       </c>
       <c r="F40" s="9">
         <v>158289</v>
       </c>
       <c r="G40" s="8">
-        <v>4811119155.24</v>
+        <v>4785900172.42</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3720,19 +3716,19 @@
         <v>82</v>
       </c>
       <c r="C41" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D41" s="7">
-        <v>0.363505</v>
+        <v>0.363843</v>
       </c>
       <c r="E41" s="8">
-        <v>76578336478.28</v>
+        <v>76425807769.16</v>
       </c>
       <c r="F41" s="9">
         <v>166409</v>
       </c>
       <c r="G41" s="8">
-        <v>27836596594.84</v>
+        <v>27807031242.49</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3743,19 +3739,19 @@
         <v>84</v>
       </c>
       <c r="C42" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D42" s="7">
-        <v>0.956603</v>
+        <v>0.953993</v>
       </c>
       <c r="E42" s="8">
-        <v>12781093297.35</v>
+        <v>12814148583.73</v>
       </c>
       <c r="F42" s="9">
         <v>235258</v>
       </c>
       <c r="G42" s="8">
-        <v>12226437686.87</v>
+        <v>12224609047.53</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3766,19 +3762,19 @@
         <v>86</v>
       </c>
       <c r="C43" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D43" s="7">
-        <v>0.691037</v>
+        <v>0.686792</v>
       </c>
       <c r="E43" s="8">
-        <v>8844353752.75</v>
+        <v>8861552119.1</v>
       </c>
       <c r="F43" s="9">
         <v>121453</v>
       </c>
       <c r="G43" s="8">
-        <v>6111772917.85</v>
+        <v>6086038764.52</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3789,19 +3785,19 @@
         <v>88</v>
       </c>
       <c r="C44" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D44" s="7">
-        <v>2.997551</v>
+        <v>2.946217</v>
       </c>
       <c r="E44" s="8">
-        <v>8627309095.52</v>
+        <v>8458096028.67</v>
       </c>
       <c r="F44" s="9">
         <v>364916</v>
       </c>
       <c r="G44" s="8">
-        <v>25860798308.49</v>
+        <v>24919388351.9</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3812,19 +3808,19 @@
         <v>90</v>
       </c>
       <c r="C45" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D45" s="7">
-        <v>1.138768</v>
+        <v>1.131118</v>
       </c>
       <c r="E45" s="8">
-        <v>3660522289.94</v>
+        <v>3663560507.02</v>
       </c>
       <c r="F45" s="9">
         <v>85784</v>
       </c>
       <c r="G45" s="8">
-        <v>4168484095.43</v>
+        <v>4143917580.94</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3835,19 +3831,19 @@
         <v>92</v>
       </c>
       <c r="C46" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D46" s="10">
-        <v>0.42203</v>
+        <v>46141</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0.421029</v>
       </c>
       <c r="E46" s="8">
-        <v>23922918770.64</v>
+        <v>23904038767.7</v>
       </c>
       <c r="F46" s="9">
         <v>219756</v>
       </c>
       <c r="G46" s="8">
-        <v>10096199002.75</v>
+        <v>10064286291.16</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3858,19 +3854,19 @@
         <v>94</v>
       </c>
       <c r="C47" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D47" s="7">
-        <v>1.005162</v>
+        <v>0.994791</v>
       </c>
       <c r="E47" s="8">
-        <v>9122186121.15</v>
+        <v>9125792074.81</v>
       </c>
       <c r="F47" s="9">
         <v>177603</v>
       </c>
       <c r="G47" s="8">
-        <v>9169271897.33</v>
+        <v>9078254772.77</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3881,19 +3877,19 @@
         <v>96</v>
       </c>
       <c r="C48" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D48" s="7">
-        <v>1.356378</v>
+        <v>1.335108</v>
       </c>
       <c r="E48" s="8">
-        <v>728990828.22</v>
+        <v>712756030.44</v>
       </c>
       <c r="F48" s="9">
         <v>7277</v>
       </c>
       <c r="G48" s="8">
-        <v>988787132.92</v>
+        <v>951606219.28</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3904,19 +3900,19 @@
         <v>98</v>
       </c>
       <c r="C49" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D49" s="7">
-        <v>0.129551</v>
+        <v>0.129682</v>
       </c>
       <c r="E49" s="8">
-        <v>93325666229.86</v>
+        <v>93407787666.84</v>
       </c>
       <c r="F49" s="9">
         <v>207969</v>
       </c>
       <c r="G49" s="8">
-        <v>12090396927.34</v>
+        <v>12113302428.13</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3927,19 +3923,19 @@
         <v>100</v>
       </c>
       <c r="C50" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D50" s="7">
-        <v>0.098946</v>
+        <v>0.099032</v>
       </c>
       <c r="E50" s="8">
-        <v>13856602968</v>
+        <v>13819444852.85</v>
       </c>
       <c r="F50" s="9">
-        <v>130198</v>
+        <v>129778</v>
       </c>
       <c r="G50" s="8">
-        <v>1371049272.99</v>
+        <v>1368564307.97</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3950,19 +3946,19 @@
         <v>102</v>
       </c>
       <c r="C51" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D51" s="7">
-        <v>0.495905</v>
+        <v>0.489457</v>
       </c>
       <c r="E51" s="8">
-        <v>20458929234.13</v>
+        <v>20446778085.37</v>
       </c>
       <c r="F51" s="9">
         <v>138130</v>
       </c>
       <c r="G51" s="8">
-        <v>10145687408.34</v>
+        <v>10007828158.07</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3973,19 +3969,19 @@
         <v>104</v>
       </c>
       <c r="C52" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D52" s="10">
-        <v>0.21236</v>
+        <v>46141</v>
+      </c>
+      <c r="D52" s="7">
+        <v>0.210221</v>
       </c>
       <c r="E52" s="8">
-        <v>2627945681.08</v>
+        <v>2630758140.91</v>
       </c>
       <c r="F52" s="9">
-        <v>10426</v>
+        <v>10432</v>
       </c>
       <c r="G52" s="8">
-        <v>558071505.74</v>
+        <v>553041616.92</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3996,19 +3992,19 @@
         <v>106</v>
       </c>
       <c r="C53" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D53" s="7">
-        <v>0.267671</v>
+        <v>0.265003</v>
       </c>
       <c r="E53" s="8">
-        <v>2884334956.73</v>
+        <v>2882305208.03</v>
       </c>
       <c r="F53" s="9">
         <v>10733</v>
       </c>
       <c r="G53" s="8">
-        <v>772054261.42</v>
+        <v>763819437.34</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -4019,19 +4015,19 @@
         <v>108</v>
       </c>
       <c r="C54" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D54" s="7">
-        <v>0.332551</v>
+        <v>0.328737</v>
       </c>
       <c r="E54" s="8">
-        <v>4535881948.44</v>
+        <v>4537122250.81</v>
       </c>
       <c r="F54" s="9">
         <v>15945</v>
       </c>
       <c r="G54" s="8">
-        <v>1508410413.44</v>
+        <v>1491519884.15</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4042,19 +4038,19 @@
         <v>110</v>
       </c>
       <c r="C55" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D55" s="7">
-        <v>0.313084</v>
+        <v>0.310206</v>
       </c>
       <c r="E55" s="8">
-        <v>2566321141.41</v>
+        <v>2568047389.31</v>
       </c>
       <c r="F55" s="9">
         <v>10216</v>
       </c>
       <c r="G55" s="8">
-        <v>803473939.84</v>
+        <v>796623952.34</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -4065,19 +4061,19 @@
         <v>112</v>
       </c>
       <c r="C56" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D56" s="7">
-        <v>0.222348</v>
+        <v>0.220073</v>
       </c>
       <c r="E56" s="8">
-        <v>1887342587.5</v>
+        <v>1888463997.85</v>
       </c>
       <c r="F56" s="9">
         <v>6706</v>
       </c>
       <c r="G56" s="8">
-        <v>419646089.86</v>
+        <v>415600239.02</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4088,19 +4084,19 @@
         <v>114</v>
       </c>
       <c r="C57" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D57" s="7">
-        <v>0.114583</v>
+        <v>0.114107</v>
       </c>
       <c r="E57" s="8">
-        <v>1637991946.82</v>
+        <v>1637639018.51</v>
       </c>
       <c r="F57" s="9">
         <v>3929</v>
       </c>
       <c r="G57" s="8">
-        <v>187685665.56</v>
+        <v>186865978.03</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -4111,19 +4107,19 @@
         <v>116</v>
       </c>
       <c r="C58" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D58" s="7">
-        <v>0.307757</v>
+        <v>0.304579</v>
       </c>
       <c r="E58" s="8">
-        <v>4427999634.69</v>
+        <v>4437209996.68</v>
       </c>
       <c r="F58" s="9">
         <v>16750</v>
       </c>
       <c r="G58" s="8">
-        <v>1362749134.91</v>
+        <v>1351482437.21</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -4134,19 +4130,19 @@
         <v>118</v>
       </c>
       <c r="C59" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D59" s="7">
-        <v>0.244935</v>
+        <v>0.242175</v>
       </c>
       <c r="E59" s="8">
-        <v>2794855219.51</v>
+        <v>2802471521.7</v>
       </c>
       <c r="F59" s="9">
         <v>11296</v>
       </c>
       <c r="G59" s="8">
-        <v>684558253.31</v>
+        <v>678689085.4</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -4157,19 +4153,19 @@
         <v>120</v>
       </c>
       <c r="C60" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D60" s="7">
-        <v>0.177692</v>
+        <v>0.175816</v>
       </c>
       <c r="E60" s="8">
-        <v>180502067.42</v>
+        <v>180547706.41</v>
       </c>
       <c r="F60" s="9">
         <v>452</v>
       </c>
       <c r="G60" s="8">
-        <v>32073717.95</v>
+        <v>31743197.47</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -4180,19 +4176,19 @@
         <v>122</v>
       </c>
       <c r="C61" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D61" s="7">
-        <v>0.381819</v>
+        <v>0.375204</v>
       </c>
       <c r="E61" s="8">
-        <v>862881124.4</v>
+        <v>859107356.46</v>
       </c>
       <c r="F61" s="9">
         <v>613</v>
       </c>
       <c r="G61" s="8">
-        <v>329464692.99</v>
+        <v>322340208.72</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -4203,19 +4199,19 @@
         <v>124</v>
       </c>
       <c r="C62" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D62" s="7">
-        <v>0.073115</v>
+        <v>0.072952</v>
       </c>
       <c r="E62" s="8">
-        <v>174034376.25</v>
+        <v>174048053.33</v>
       </c>
       <c r="F62" s="9">
         <v>224</v>
       </c>
       <c r="G62" s="8">
-        <v>12724532.88</v>
+        <v>12697155.74</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -4226,19 +4222,19 @@
         <v>126</v>
       </c>
       <c r="C63" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D63" s="7">
-        <v>0.143474</v>
+        <v>0.142185</v>
       </c>
       <c r="E63" s="8">
-        <v>109441120.31</v>
+        <v>109474812.33</v>
       </c>
       <c r="F63" s="9">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G63" s="8">
-        <v>15701964.42</v>
+        <v>15565636.38</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -4249,19 +4245,19 @@
         <v>128</v>
       </c>
       <c r="C64" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D64" s="7">
-        <v>0.258843</v>
+        <v>0.256206</v>
       </c>
       <c r="E64" s="8">
-        <v>215075027.4</v>
+        <v>214838481.26</v>
       </c>
       <c r="F64" s="9">
         <v>333</v>
       </c>
       <c r="G64" s="8">
-        <v>55670559.15</v>
+        <v>55042825.85</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4272,19 +4268,19 @@
         <v>130</v>
       </c>
       <c r="C65" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D65" s="7">
-        <v>0.334767</v>
+        <v>0.330415</v>
       </c>
       <c r="E65" s="8">
-        <v>639289054.72</v>
+        <v>639403854.68</v>
       </c>
       <c r="F65" s="9">
         <v>445</v>
       </c>
       <c r="G65" s="8">
-        <v>214012856.77</v>
+        <v>211268561.76</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -4295,19 +4291,19 @@
         <v>132</v>
       </c>
       <c r="C66" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D66" s="7">
-        <v>0.593251</v>
+        <v>0.582461</v>
       </c>
       <c r="E66" s="8">
-        <v>12979115994.99</v>
+        <v>12965977058.84</v>
       </c>
       <c r="F66" s="9">
-        <v>127875</v>
+        <v>127732</v>
       </c>
       <c r="G66" s="8">
-        <v>7699871441.03</v>
+        <v>7552176825.24</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4318,19 +4314,19 @@
         <v>134</v>
       </c>
       <c r="C67" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D67" s="7">
-        <v>0.261514</v>
+        <v>46141</v>
+      </c>
+      <c r="D67" s="10">
+        <v>0.25784</v>
       </c>
       <c r="E67" s="8">
-        <v>2017861704.82</v>
+        <v>2016378022.7</v>
       </c>
       <c r="F67" s="9">
-        <v>6116</v>
+        <v>6118</v>
       </c>
       <c r="G67" s="8">
-        <v>527698434.66</v>
+        <v>519902998.65</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -4341,19 +4337,19 @@
         <v>136</v>
       </c>
       <c r="C68" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D68" s="7">
-        <v>2.012008</v>
+        <v>1.998937</v>
       </c>
       <c r="E68" s="8">
-        <v>7016855831.26</v>
+        <v>7020314407.05</v>
       </c>
       <c r="F68" s="9">
-        <v>236384</v>
+        <v>236318</v>
       </c>
       <c r="G68" s="8">
-        <v>14117969065.53</v>
+        <v>14033164651.98</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -4364,19 +4360,19 @@
         <v>138</v>
       </c>
       <c r="C69" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D69" s="7">
-        <v>1.005128</v>
+        <v>0.996959</v>
       </c>
       <c r="E69" s="8">
-        <v>6560182681.27</v>
+        <v>6551630874.17</v>
       </c>
       <c r="F69" s="9">
-        <v>163606</v>
+        <v>163559</v>
       </c>
       <c r="G69" s="8">
-        <v>6593820782.13</v>
+        <v>6531707322.55</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -4387,19 +4383,19 @@
         <v>140</v>
       </c>
       <c r="C70" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D70" s="7">
-        <v>0.325856</v>
+        <v>0.321053</v>
       </c>
       <c r="E70" s="8">
-        <v>12167121737.01</v>
+        <v>12154559315.62</v>
       </c>
       <c r="F70" s="9">
-        <v>189827</v>
+        <v>189795</v>
       </c>
       <c r="G70" s="8">
-        <v>3964728957.07</v>
+        <v>3902259533.82</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4410,19 +4406,19 @@
         <v>142</v>
       </c>
       <c r="C71" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D71" s="7">
-        <v>0.098147</v>
+        <v>46141</v>
+      </c>
+      <c r="D71" s="10">
+        <v>0.09823</v>
       </c>
       <c r="E71" s="8">
-        <v>7412461772.88</v>
+        <v>7412595473.66</v>
       </c>
       <c r="F71" s="9">
-        <v>116056</v>
+        <v>115882</v>
       </c>
       <c r="G71" s="8">
-        <v>727512790.75</v>
+        <v>728142951.26</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -4433,19 +4429,19 @@
         <v>144</v>
       </c>
       <c r="C72" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D72" s="7">
-        <v>0.096508</v>
+        <v>0.095556</v>
       </c>
       <c r="E72" s="8">
-        <v>386321414209.02</v>
+        <v>386032392335.52</v>
       </c>
       <c r="F72" s="9">
-        <v>1408343</v>
+        <v>1407635</v>
       </c>
       <c r="G72" s="8">
-        <v>37283107140.32</v>
+        <v>36887720484.32</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4456,19 +4452,19 @@
         <v>146</v>
       </c>
       <c r="C73" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D73" s="7">
-        <v>1.098602</v>
+        <v>46141</v>
+      </c>
+      <c r="D73" s="10">
+        <v>1.09395</v>
       </c>
       <c r="E73" s="8">
-        <v>6402957014.41</v>
+        <v>6402609436.04</v>
       </c>
       <c r="F73" s="9">
-        <v>262961</v>
+        <v>262754</v>
       </c>
       <c r="G73" s="8">
-        <v>7034299653.56</v>
+        <v>7004133320.05</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4479,19 +4475,19 @@
         <v>148</v>
       </c>
       <c r="C74" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D74" s="7">
-        <v>0.508683</v>
+        <v>0.507701</v>
       </c>
       <c r="E74" s="8">
-        <v>6752121549.88</v>
+        <v>6749848306.22</v>
       </c>
       <c r="F74" s="9">
-        <v>65914</v>
+        <v>65843</v>
       </c>
       <c r="G74" s="8">
-        <v>3434689133.89</v>
+        <v>3426901763.32</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -4502,19 +4498,19 @@
         <v>150</v>
       </c>
       <c r="C75" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D75" s="7">
-        <v>1.547221</v>
+        <v>46141</v>
+      </c>
+      <c r="D75" s="10">
+        <v>1.53781</v>
       </c>
       <c r="E75" s="8">
-        <v>492406409.32</v>
+        <v>493904197.39</v>
       </c>
       <c r="F75" s="9">
-        <v>4986</v>
+        <v>4991</v>
       </c>
       <c r="G75" s="8">
-        <v>761861688.66</v>
+        <v>759530591.91</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4525,19 +4521,19 @@
         <v>152</v>
       </c>
       <c r="C76" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D76" s="7">
-        <v>0.708689</v>
+        <v>0.691136</v>
       </c>
       <c r="E76" s="8">
-        <v>212755846162.82</v>
+        <v>212689152195.15</v>
       </c>
       <c r="F76" s="9">
-        <v>721376</v>
+        <v>721070</v>
       </c>
       <c r="G76" s="8">
-        <v>150777731699.54</v>
+        <v>146997209934.39</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4548,19 +4544,19 @@
         <v>154</v>
       </c>
       <c r="C77" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D77" s="7">
-        <v>0.579326</v>
+        <v>0.574096</v>
       </c>
       <c r="E77" s="8">
-        <v>194378885.35</v>
+        <v>194280517.16</v>
       </c>
       <c r="F77" s="9">
         <v>22329</v>
       </c>
       <c r="G77" s="8">
-        <v>112608662.17</v>
+        <v>111535639.56</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4571,19 +4567,19 @@
         <v>156</v>
       </c>
       <c r="C78" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D78" s="7">
-        <v>0.301386</v>
+        <v>0.299011</v>
       </c>
       <c r="E78" s="8">
-        <v>395600857.66</v>
+        <v>395637866.15</v>
       </c>
       <c r="F78" s="9">
         <v>33157</v>
       </c>
       <c r="G78" s="8">
-        <v>119228515.56</v>
+        <v>118299879.66</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4594,19 +4590,19 @@
         <v>158</v>
       </c>
       <c r="C79" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D79" s="7">
-        <v>0.159641</v>
+        <v>0.158332</v>
       </c>
       <c r="E79" s="8">
-        <v>3115666716.56</v>
+        <v>3115449349.1</v>
       </c>
       <c r="F79" s="9">
-        <v>6945</v>
+        <v>6959</v>
       </c>
       <c r="G79" s="8">
-        <v>497387941.02</v>
+        <v>493276376.1</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4617,19 +4613,19 @@
         <v>160</v>
       </c>
       <c r="C80" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D80" s="7">
-        <v>0.332585</v>
+        <v>0.332829</v>
       </c>
       <c r="E80" s="8">
-        <v>236543105.41</v>
+        <v>236522689.35</v>
       </c>
       <c r="F80" s="9">
         <v>20837</v>
       </c>
       <c r="G80" s="8">
-        <v>78670770.63</v>
+        <v>78721531.57</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4640,19 +4636,19 @@
         <v>162</v>
       </c>
       <c r="C81" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D81" s="7">
-        <v>0.178493</v>
+        <v>0.176667</v>
       </c>
       <c r="E81" s="8">
-        <v>702558017.8</v>
+        <v>701679357.94</v>
       </c>
       <c r="F81" s="9">
-        <v>2353</v>
+        <v>2356</v>
       </c>
       <c r="G81" s="8">
-        <v>125401838.86</v>
+        <v>123963545.21</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4663,19 +4659,19 @@
         <v>164</v>
       </c>
       <c r="C82" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D82" s="7">
-        <v>1.888729</v>
+        <v>1.855609</v>
       </c>
       <c r="E82" s="8">
-        <v>84217518.3</v>
+        <v>84219621.14</v>
       </c>
       <c r="F82" s="9">
         <v>13725</v>
       </c>
       <c r="G82" s="8">
-        <v>159064100.59</v>
+        <v>156278656.99</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4686,19 +4682,19 @@
         <v>166</v>
       </c>
       <c r="C83" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D83" s="10">
-        <v>0.09499</v>
+        <v>46141</v>
+      </c>
+      <c r="D83" s="7">
+        <v>0.095077</v>
       </c>
       <c r="E83" s="8">
-        <v>10153121185.29</v>
+        <v>10102627960.3</v>
       </c>
       <c r="F83" s="9">
         <v>169371</v>
       </c>
       <c r="G83" s="8">
-        <v>964448376.44</v>
+        <v>960531285.21</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4709,19 +4705,19 @@
         <v>168</v>
       </c>
       <c r="C84" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D84" s="7">
-        <v>0.083246</v>
+        <v>0.083316</v>
       </c>
       <c r="E84" s="8">
-        <v>9029538307.12</v>
+        <v>9122976454.11</v>
       </c>
       <c r="F84" s="9">
         <v>140293</v>
       </c>
       <c r="G84" s="8">
-        <v>751674817.1</v>
+        <v>760085871.82</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4732,19 +4728,19 @@
         <v>170</v>
       </c>
       <c r="C85" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D85" s="7">
-        <v>0.269657</v>
+        <v>0.267679</v>
       </c>
       <c r="E85" s="8">
-        <v>4271507680.33</v>
+        <v>4308166554.83</v>
       </c>
       <c r="F85" s="9">
-        <v>80144</v>
+        <v>79997</v>
       </c>
       <c r="G85" s="8">
-        <v>1151841662.7</v>
+        <v>1153206281.48</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4755,19 +4751,19 @@
         <v>172</v>
       </c>
       <c r="C86" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D86" s="7">
-        <v>0.908166</v>
+        <v>0.896242</v>
       </c>
       <c r="E86" s="8">
-        <v>4620425427.65</v>
+        <v>4621876641.38</v>
       </c>
       <c r="F86" s="9">
         <v>87247</v>
       </c>
       <c r="G86" s="8">
-        <v>4196115108.55</v>
+        <v>4142322234.67</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4778,19 +4774,19 @@
         <v>174</v>
       </c>
       <c r="C87" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D87" s="7">
-        <v>0.225567</v>
+        <v>0.224082</v>
       </c>
       <c r="E87" s="8">
-        <v>12573597945.65</v>
+        <v>12590347802.23</v>
       </c>
       <c r="F87" s="9">
         <v>143818</v>
       </c>
       <c r="G87" s="8">
-        <v>2836193899.75</v>
+        <v>2821266401.35</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4801,19 +4797,19 @@
         <v>176</v>
       </c>
       <c r="C88" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D88" s="7">
-        <v>0.165861</v>
+        <v>0.163389</v>
       </c>
       <c r="E88" s="8">
-        <v>18406957619.42</v>
+        <v>18412068718.98</v>
       </c>
       <c r="F88" s="9">
-        <v>90964</v>
+        <v>90886</v>
       </c>
       <c r="G88" s="8">
-        <v>3052992414.47</v>
+        <v>3008338127.63</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4824,19 +4820,19 @@
         <v>178</v>
       </c>
       <c r="C89" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D89" s="7">
-        <v>0.635126</v>
+        <v>0.633692</v>
       </c>
       <c r="E89" s="8">
-        <v>2284046554.7</v>
+        <v>2277011283.51</v>
       </c>
       <c r="F89" s="9">
-        <v>36037</v>
+        <v>35997</v>
       </c>
       <c r="G89" s="8">
-        <v>1450656886.21</v>
+        <v>1442924313.39</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4847,19 +4843,19 @@
         <v>180</v>
       </c>
       <c r="C90" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D90" s="7">
-        <v>0.846386</v>
+        <v>0.843794</v>
       </c>
       <c r="E90" s="8">
-        <v>19247520226.99</v>
+        <v>19239895962.15</v>
       </c>
       <c r="F90" s="9">
-        <v>273650</v>
+        <v>273301</v>
       </c>
       <c r="G90" s="8">
-        <v>16290826888.91</v>
+        <v>16234513547.48</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4870,19 +4866,19 @@
         <v>182</v>
       </c>
       <c r="C91" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D91" s="7">
-        <v>0.795831</v>
+        <v>46141</v>
+      </c>
+      <c r="D91" s="10">
+        <v>0.78612</v>
       </c>
       <c r="E91" s="8">
-        <v>3488922932.16</v>
+        <v>3476296523.66</v>
       </c>
       <c r="F91" s="9">
-        <v>29082</v>
+        <v>29185</v>
       </c>
       <c r="G91" s="8">
-        <v>2776591709.79</v>
+        <v>2732785625.61</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4893,19 +4889,19 @@
         <v>184</v>
       </c>
       <c r="C92" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D92" s="7">
-        <v>0.832532</v>
+        <v>0.830365</v>
       </c>
       <c r="E92" s="8">
-        <v>12360119203.21</v>
+        <v>12349482013.15</v>
       </c>
       <c r="F92" s="9">
-        <v>189396</v>
+        <v>189279</v>
       </c>
       <c r="G92" s="8">
-        <v>10290193096.29</v>
+        <v>10254576903.85</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4916,19 +4912,19 @@
         <v>186</v>
       </c>
       <c r="C93" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D93" s="7">
-        <v>0.087501</v>
+        <v>0.087496</v>
       </c>
       <c r="E93" s="8">
-        <v>7631860281.44</v>
+        <v>7583910379.02</v>
       </c>
       <c r="F93" s="9">
-        <v>156504</v>
+        <v>156166</v>
       </c>
       <c r="G93" s="8">
-        <v>667797873.54</v>
+        <v>663561480.63</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4939,19 +4935,19 @@
         <v>188</v>
       </c>
       <c r="C94" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D94" s="7">
-        <v>0.120312</v>
+        <v>0.119466</v>
       </c>
       <c r="E94" s="8">
-        <v>11943441031.43</v>
+        <v>11924828338.26</v>
       </c>
       <c r="F94" s="9">
-        <v>33336</v>
+        <v>33325</v>
       </c>
       <c r="G94" s="8">
-        <v>1436934385.7</v>
+        <v>1424613039.77</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4962,19 +4958,19 @@
         <v>190</v>
       </c>
       <c r="C95" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D95" s="7">
-        <v>0.127018</v>
+        <v>0.127148</v>
       </c>
       <c r="E95" s="8">
-        <v>72430044386.53</v>
+        <v>72207867774.75</v>
       </c>
       <c r="F95" s="9">
-        <v>212656</v>
+        <v>212684</v>
       </c>
       <c r="G95" s="8">
-        <v>9199885428.42</v>
+        <v>9181081775.69</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4985,19 +4981,19 @@
         <v>192</v>
       </c>
       <c r="C96" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D96" s="7">
-        <v>0.448796</v>
+        <v>0.442173</v>
       </c>
       <c r="E96" s="8">
-        <v>31525720881.64</v>
+        <v>31660058299.83</v>
       </c>
       <c r="F96" s="9">
-        <v>280627</v>
+        <v>281376</v>
       </c>
       <c r="G96" s="8">
-        <v>14148606766.32</v>
+        <v>13999235244.96</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -5008,19 +5004,19 @@
         <v>194</v>
       </c>
       <c r="C97" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D97" s="7">
-        <v>0.095908</v>
+        <v>0.095688</v>
       </c>
       <c r="E97" s="8">
-        <v>24562829986.81</v>
+        <v>24529306243.23</v>
       </c>
       <c r="F97" s="9">
-        <v>442248</v>
+        <v>442113</v>
       </c>
       <c r="G97" s="8">
-        <v>2355771553.37</v>
+        <v>2347166922.89</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -5031,19 +5027,19 @@
         <v>196</v>
       </c>
       <c r="C98" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D98" s="7">
-        <v>0.244919</v>
+        <v>0.244085</v>
       </c>
       <c r="E98" s="8">
-        <v>1291717634.86</v>
+        <v>1294590746.91</v>
       </c>
       <c r="F98" s="9">
-        <v>7087</v>
+        <v>7098</v>
       </c>
       <c r="G98" s="8">
-        <v>316365582.94</v>
+        <v>315990807.32</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -5054,19 +5050,19 @@
         <v>198</v>
       </c>
       <c r="C99" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D99" s="7">
-        <v>1.046751</v>
+        <v>1.035365</v>
       </c>
       <c r="E99" s="8">
-        <v>2251871682.4</v>
+        <v>3618130979.54</v>
       </c>
       <c r="F99" s="9">
-        <v>38452</v>
+        <v>42318</v>
       </c>
       <c r="G99" s="8">
-        <v>2357148845.61</v>
+        <v>3746086568.72</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5077,19 +5073,19 @@
         <v>200</v>
       </c>
       <c r="C100" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D100" s="7">
-        <v>2.610295</v>
+        <v>2.569433</v>
       </c>
       <c r="E100" s="8">
-        <v>12083482042.61</v>
+        <v>12064571974.24</v>
       </c>
       <c r="F100" s="9">
-        <v>305065</v>
+        <v>305320</v>
       </c>
       <c r="G100" s="8">
-        <v>31541454786.1</v>
+        <v>30999107048.69</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5100,19 +5096,19 @@
         <v>202</v>
       </c>
       <c r="C101" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D101" s="7">
-        <v>0.355392</v>
+        <v>0.353988</v>
       </c>
       <c r="E101" s="8">
-        <v>28470379250.66</v>
+        <v>27492156745.99</v>
       </c>
       <c r="F101" s="9">
-        <v>336884</v>
+        <v>335569</v>
       </c>
       <c r="G101" s="8">
-        <v>10118149463.49</v>
+        <v>9731892871.41</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5123,19 +5119,19 @@
         <v>204</v>
       </c>
       <c r="C102" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D102" s="7">
-        <v>0.365982</v>
+        <v>46141</v>
+      </c>
+      <c r="D102" s="10">
+        <v>0.36631</v>
       </c>
       <c r="E102" s="8">
-        <v>207903047197.34</v>
+        <v>203621698682.37</v>
       </c>
       <c r="F102" s="9">
-        <v>356810</v>
+        <v>346103</v>
       </c>
       <c r="G102" s="8">
-        <v>76088868615.6</v>
+        <v>74588569269.66</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5146,19 +5142,19 @@
         <v>206</v>
       </c>
       <c r="C103" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D103" s="7">
-        <v>0.124207</v>
+        <v>0.123354</v>
       </c>
       <c r="E103" s="8">
-        <v>9154881071.99</v>
+        <v>9074234229.47</v>
       </c>
       <c r="F103" s="9">
-        <v>28549</v>
+        <v>28556</v>
       </c>
       <c r="G103" s="8">
-        <v>1137097967</v>
+        <v>1119339429.5</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -5169,19 +5165,19 @@
         <v>208</v>
       </c>
       <c r="C104" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D104" s="7">
-        <v>0.279963</v>
+        <v>0.278655</v>
       </c>
       <c r="E104" s="8">
-        <v>1723720090.19</v>
+        <v>1723253869.7</v>
       </c>
       <c r="F104" s="9">
-        <v>7822</v>
+        <v>7831</v>
       </c>
       <c r="G104" s="8">
-        <v>482577834.72</v>
+        <v>480194026.76</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -5192,19 +5188,19 @@
         <v>210</v>
       </c>
       <c r="C105" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D105" s="10">
-        <v>1.05357</v>
+        <v>46141</v>
+      </c>
+      <c r="D105" s="7">
+        <v>1.040293</v>
       </c>
       <c r="E105" s="8">
-        <v>247223130.95</v>
+        <v>248238654.9</v>
       </c>
       <c r="F105" s="9">
-        <v>4070</v>
+        <v>4079</v>
       </c>
       <c r="G105" s="8">
-        <v>260466917.63</v>
+        <v>258240919.09</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5215,19 +5211,19 @@
         <v>212</v>
       </c>
       <c r="C106" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D106" s="7">
-        <v>0.994175</v>
+        <v>0.981056</v>
       </c>
       <c r="E106" s="8">
-        <v>588563303.48</v>
+        <v>602486086.61</v>
       </c>
       <c r="F106" s="9">
-        <v>15324</v>
+        <v>15382</v>
       </c>
       <c r="G106" s="8">
-        <v>585134708.15</v>
+        <v>591072554.66</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5238,19 +5234,19 @@
         <v>214</v>
       </c>
       <c r="C107" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D107" s="7">
-        <v>0.177296</v>
+        <v>0.176171</v>
       </c>
       <c r="E107" s="8">
-        <v>375736105.32</v>
+        <v>375108703.45</v>
       </c>
       <c r="F107" s="9">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="G107" s="8">
-        <v>66616427.15</v>
+        <v>66083161.48</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -5261,19 +5257,19 @@
         <v>216</v>
       </c>
       <c r="C108" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D108" s="7">
-        <v>1.465272</v>
+        <v>1.443027</v>
       </c>
       <c r="E108" s="8">
-        <v>1012498283.93</v>
+        <v>1015564325.08</v>
       </c>
       <c r="F108" s="9">
         <v>21935</v>
       </c>
       <c r="G108" s="8">
-        <v>1483585885.77</v>
+        <v>1465486235.23</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -5284,19 +5280,19 @@
         <v>218</v>
       </c>
       <c r="C109" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D109" s="7">
-        <v>0.096422</v>
+        <v>0.096332</v>
       </c>
       <c r="E109" s="8">
-        <v>5443602637.64</v>
+        <v>5430182001.47</v>
       </c>
       <c r="F109" s="9">
-        <v>24065</v>
+        <v>24050</v>
       </c>
       <c r="G109" s="8">
-        <v>524882849.74</v>
+        <v>523097795.44</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -5307,19 +5303,19 @@
         <v>220</v>
       </c>
       <c r="C110" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D110" s="7">
-        <v>0.286914</v>
+        <v>46141</v>
+      </c>
+      <c r="D110" s="10">
+        <v>0.28581</v>
       </c>
       <c r="E110" s="8">
-        <v>1638131477.2</v>
+        <v>1640233712.08</v>
       </c>
       <c r="F110" s="9">
-        <v>33181</v>
+        <v>33199</v>
       </c>
       <c r="G110" s="8">
-        <v>470003600.93</v>
+        <v>468795810.9</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5330,19 +5326,19 @@
         <v>222</v>
       </c>
       <c r="C111" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D111" s="7">
-        <v>0.211521</v>
+        <v>46141</v>
+      </c>
+      <c r="D111" s="10">
+        <v>0.21018</v>
       </c>
       <c r="E111" s="8">
-        <v>590368789.06</v>
+        <v>590183866.73</v>
       </c>
       <c r="F111" s="9">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="G111" s="8">
-        <v>124875187.13</v>
+        <v>124045077.29</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -5353,19 +5349,19 @@
         <v>224</v>
       </c>
       <c r="C112" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D112" s="10">
-        <v>0.40473</v>
+        <v>46141</v>
+      </c>
+      <c r="D112" s="7">
+        <v>0.404248</v>
       </c>
       <c r="E112" s="8">
-        <v>144029814.05</v>
+        <v>145362747.9</v>
       </c>
       <c r="F112" s="9">
-        <v>1187</v>
+        <v>1197</v>
       </c>
       <c r="G112" s="8">
-        <v>58293220.13</v>
+        <v>58762576.47</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -5376,19 +5372,19 @@
         <v>226</v>
       </c>
       <c r="C113" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D113" s="7">
-        <v>0.108916</v>
+        <v>0.108599</v>
       </c>
       <c r="E113" s="8">
-        <v>194540892.5</v>
+        <v>194581055.56</v>
       </c>
       <c r="F113" s="9">
         <v>888</v>
       </c>
       <c r="G113" s="8">
-        <v>21188661.26</v>
+        <v>21131394.66</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5399,19 +5395,19 @@
         <v>228</v>
       </c>
       <c r="C114" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D114" s="10">
-        <v>0.06413</v>
+        <v>0.06285</v>
       </c>
       <c r="E114" s="8">
-        <v>1217548689402.59</v>
+        <v>1218088939523.93</v>
       </c>
       <c r="F114" s="9">
         <v>788157</v>
       </c>
       <c r="G114" s="8">
-        <v>78081637864.9</v>
+        <v>76556924314.44</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -5422,19 +5418,19 @@
         <v>230</v>
       </c>
       <c r="C115" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D115" s="7">
-        <v>0.015353</v>
+        <v>0.015368</v>
       </c>
       <c r="E115" s="8">
-        <v>6398971181.81</v>
+        <v>6399751054.98</v>
       </c>
       <c r="F115" s="9">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="G115" s="8">
-        <v>98240491.88</v>
+        <v>98354430.85</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -5445,19 +5441,19 @@
         <v>232</v>
       </c>
       <c r="C116" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D116" s="10">
-        <v>0.12527</v>
+        <v>46141</v>
+      </c>
+      <c r="D116" s="7">
+        <v>0.123868</v>
       </c>
       <c r="E116" s="8">
-        <v>7392381365.4</v>
+        <v>7436732971.66</v>
       </c>
       <c r="F116" s="9">
         <v>24577</v>
       </c>
       <c r="G116" s="8">
-        <v>926041702.13</v>
+        <v>921175019.68</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -5468,19 +5464,19 @@
         <v>234</v>
       </c>
       <c r="C117" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D117" s="7">
-        <v>0.122199</v>
+        <v>46141</v>
+      </c>
+      <c r="D117" s="10">
+        <v>0.12228</v>
       </c>
       <c r="E117" s="8">
-        <v>27504561615.08</v>
+        <v>27750180251.25</v>
       </c>
       <c r="F117" s="9">
         <v>67897</v>
       </c>
       <c r="G117" s="8">
-        <v>3361019982.39</v>
+        <v>3393281349.27</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -5491,19 +5487,19 @@
         <v>236</v>
       </c>
       <c r="C118" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D118" s="7">
-        <v>0.570429</v>
+        <v>0.569119</v>
       </c>
       <c r="E118" s="8">
-        <v>90881237.94</v>
+        <v>91026399.1</v>
       </c>
       <c r="F118" s="9">
         <v>845</v>
       </c>
       <c r="G118" s="8">
-        <v>51841337.91</v>
+        <v>51804855.13</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -5514,19 +5510,19 @@
         <v>238</v>
       </c>
       <c r="C119" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D119" s="7">
-        <v>0.753663</v>
+        <v>0.735433</v>
       </c>
       <c r="E119" s="8">
-        <v>22920009488.15</v>
+        <v>22913580727.2</v>
       </c>
       <c r="F119" s="9">
-        <v>149161</v>
+        <v>149317</v>
       </c>
       <c r="G119" s="8">
-        <v>17273957478.93</v>
+        <v>16851413649.46</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5537,19 +5533,19 @@
         <v>240</v>
       </c>
       <c r="C120" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D120" s="7">
-        <v>0.122501</v>
+        <v>0.122565</v>
       </c>
       <c r="E120" s="8">
-        <v>14820253235.39</v>
+        <v>14774622696.54</v>
       </c>
       <c r="F120" s="9">
-        <v>44613</v>
+        <v>44612</v>
       </c>
       <c r="G120" s="8">
-        <v>1815502797.59</v>
+        <v>1810853485.8</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5560,19 +5556,19 @@
         <v>242</v>
       </c>
       <c r="C121" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D121" s="7">
-        <v>0.105339</v>
+        <v>0.104437</v>
       </c>
       <c r="E121" s="8">
-        <v>42452719955.32</v>
+        <v>42456724855.67</v>
       </c>
       <c r="F121" s="9">
-        <v>335088</v>
+        <v>335017</v>
       </c>
       <c r="G121" s="8">
-        <v>4471926530.73</v>
+        <v>4434050521.82</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -5583,19 +5579,19 @@
         <v>244</v>
       </c>
       <c r="C122" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D122" s="7">
-        <v>0.093573</v>
+        <v>46141</v>
+      </c>
+      <c r="D122" s="10">
+        <v>0.09307</v>
       </c>
       <c r="E122" s="8">
-        <v>9695290545.2</v>
+        <v>9691223495.54</v>
       </c>
       <c r="F122" s="9">
-        <v>148029</v>
+        <v>148037</v>
       </c>
       <c r="G122" s="8">
-        <v>907213524.03</v>
+        <v>901964685.95</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -5606,19 +5602,19 @@
         <v>246</v>
       </c>
       <c r="C123" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D123" s="7">
-        <v>0.048141</v>
+        <v>46141</v>
+      </c>
+      <c r="D123" s="10">
+        <v>0.04772</v>
       </c>
       <c r="E123" s="8">
-        <v>28004712009.79</v>
+        <v>28035194635.36</v>
       </c>
       <c r="F123" s="9">
         <v>34420</v>
       </c>
       <c r="G123" s="8">
-        <v>1348169506.01</v>
+        <v>1337848918.97</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -5629,19 +5625,19 @@
         <v>248</v>
       </c>
       <c r="C124" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D124" s="7">
-        <v>0.118465</v>
+        <v>0.117638</v>
       </c>
       <c r="E124" s="8">
-        <v>6280305944.37</v>
+        <v>6283842434.12</v>
       </c>
       <c r="F124" s="9">
-        <v>43245</v>
+        <v>43234</v>
       </c>
       <c r="G124" s="8">
-        <v>743995087.97</v>
+        <v>739218771.25</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5652,19 +5648,19 @@
         <v>250</v>
       </c>
       <c r="C125" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D125" s="7">
-        <v>0.090316</v>
+        <v>0.090142</v>
       </c>
       <c r="E125" s="8">
-        <v>2967066369.79</v>
+        <v>2962461852.95</v>
       </c>
       <c r="F125" s="9">
-        <v>83402</v>
+        <v>83459</v>
       </c>
       <c r="G125" s="8">
-        <v>267973843.41</v>
+        <v>267041651.92</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5675,19 +5671,19 @@
         <v>252</v>
       </c>
       <c r="C126" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D126" s="7">
-        <v>0.083084</v>
+        <v>0.082376</v>
       </c>
       <c r="E126" s="8">
-        <v>1120510821.94</v>
+        <v>1120427188.15</v>
       </c>
       <c r="F126" s="9">
-        <v>121885</v>
+        <v>121870</v>
       </c>
       <c r="G126" s="8">
-        <v>93096948.15</v>
+        <v>92295924.39</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5698,19 +5694,19 @@
         <v>254</v>
       </c>
       <c r="C127" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D127" s="7">
-        <v>0.770874</v>
+        <v>46141</v>
+      </c>
+      <c r="D127" s="10">
+        <v>0.76274</v>
       </c>
       <c r="E127" s="8">
-        <v>1636802291.38</v>
+        <v>1639314908.17</v>
       </c>
       <c r="F127" s="9">
-        <v>49936</v>
+        <v>49950</v>
       </c>
       <c r="G127" s="8">
-        <v>1261768641.46</v>
+        <v>1250371140.24</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5721,19 +5717,19 @@
         <v>256</v>
       </c>
       <c r="C128" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D128" s="7">
-        <v>0.148671</v>
+        <v>46141</v>
+      </c>
+      <c r="D128" s="10">
+        <v>0.14805</v>
       </c>
       <c r="E128" s="8">
-        <v>1288121078.97</v>
+        <v>1287933161</v>
       </c>
       <c r="F128" s="9">
-        <v>12568</v>
+        <v>12562</v>
       </c>
       <c r="G128" s="8">
-        <v>191506462.81</v>
+        <v>190678365.5</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5744,19 +5740,19 @@
         <v>258</v>
       </c>
       <c r="C129" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D129" s="7">
-        <v>0.239255</v>
+        <v>0.238234</v>
       </c>
       <c r="E129" s="8">
-        <v>5265059054.35</v>
+        <v>5209001444.94</v>
       </c>
       <c r="F129" s="9">
-        <v>69569</v>
+        <v>69565</v>
       </c>
       <c r="G129" s="8">
-        <v>1259690489.65</v>
+        <v>1240959549.65</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5767,19 +5763,19 @@
         <v>260</v>
       </c>
       <c r="C130" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D130" s="7">
-        <v>1.866155</v>
+        <v>1.834265</v>
       </c>
       <c r="E130" s="8">
-        <v>2361324208.03</v>
+        <v>2364384228.47</v>
       </c>
       <c r="F130" s="9">
-        <v>52801</v>
+        <v>52834</v>
       </c>
       <c r="G130" s="8">
-        <v>4406596324.88</v>
+        <v>4336906512.62</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5790,19 +5786,19 @@
         <v>262</v>
       </c>
       <c r="C131" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D131" s="7">
-        <v>0.354356</v>
+        <v>46141</v>
+      </c>
+      <c r="D131" s="10">
+        <v>0.34792</v>
       </c>
       <c r="E131" s="8">
-        <v>559026061.31</v>
+        <v>558950926.6</v>
       </c>
       <c r="F131" s="9">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G131" s="8">
-        <v>198094236.98</v>
+        <v>194470176.03</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5813,19 +5809,19 @@
         <v>264</v>
       </c>
       <c r="C132" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D132" s="7">
-        <v>0.160596</v>
+        <v>0.159032</v>
       </c>
       <c r="E132" s="8">
-        <v>132410491.65</v>
+        <v>132120724.4</v>
       </c>
       <c r="F132" s="9">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G132" s="8">
-        <v>21264593.46</v>
+        <v>21011404.41</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5836,19 +5832,19 @@
         <v>266</v>
       </c>
       <c r="C133" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D133" s="7">
-        <v>0.703628</v>
+        <v>0.703738</v>
       </c>
       <c r="E133" s="8">
-        <v>1255152995</v>
+        <v>1255648502.03</v>
       </c>
       <c r="F133" s="9">
-        <v>21212</v>
+        <v>21207</v>
       </c>
       <c r="G133" s="8">
-        <v>883160378.92</v>
+        <v>883647995.68</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5859,19 +5855,19 @@
         <v>268</v>
       </c>
       <c r="C134" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D134" s="7">
-        <v>0.368353</v>
+        <v>0.368675</v>
       </c>
       <c r="E134" s="8">
-        <v>7360968324.6</v>
+        <v>7358027365.21</v>
       </c>
       <c r="F134" s="9">
-        <v>95806</v>
+        <v>91874</v>
       </c>
       <c r="G134" s="8">
-        <v>2711437872.67</v>
+        <v>2712722852.7</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5882,19 +5878,19 @@
         <v>270</v>
       </c>
       <c r="C135" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D135" s="7">
-        <v>0.203926</v>
+        <v>0.201566</v>
       </c>
       <c r="E135" s="8">
-        <v>199857183.32</v>
+        <v>199971202.63</v>
       </c>
       <c r="F135" s="9">
         <v>614</v>
       </c>
       <c r="G135" s="8">
-        <v>40756037.14</v>
+        <v>40307416.14</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5905,19 +5901,19 @@
         <v>272</v>
       </c>
       <c r="C136" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D136" s="7">
-        <v>0.259091</v>
+        <v>0.254812</v>
       </c>
       <c r="E136" s="8">
-        <v>402392345.58</v>
+        <v>402372807.83</v>
       </c>
       <c r="F136" s="9">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G136" s="8">
-        <v>104256268.47</v>
+        <v>102529560.5</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5928,19 +5924,19 @@
         <v>274</v>
       </c>
       <c r="C137" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D137" s="7">
-        <v>0.100125</v>
+        <v>46141</v>
+      </c>
+      <c r="D137" s="10">
+        <v>0.09996</v>
       </c>
       <c r="E137" s="8">
-        <v>294044387.21</v>
+        <v>296563103.7</v>
       </c>
       <c r="F137" s="9">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G137" s="8">
-        <v>29441112.57</v>
+        <v>29644342.4</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5951,19 +5947,19 @@
         <v>276</v>
       </c>
       <c r="C138" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D138" s="7">
-        <v>0.391958</v>
+        <v>0.384897</v>
       </c>
       <c r="E138" s="8">
-        <v>623940097.6</v>
+        <v>623995432.8</v>
       </c>
       <c r="F138" s="9">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="G138" s="8">
-        <v>244558489.16</v>
+        <v>240173870.05</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5974,19 +5970,19 @@
         <v>278</v>
       </c>
       <c r="C139" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D139" s="10">
-        <v>0.69681</v>
+        <v>46141</v>
+      </c>
+      <c r="D139" s="7">
+        <v>0.695352</v>
       </c>
       <c r="E139" s="8">
-        <v>2932432386.99</v>
+        <v>2932980750.04</v>
       </c>
       <c r="F139" s="9">
-        <v>42120</v>
+        <v>42102</v>
       </c>
       <c r="G139" s="8">
-        <v>2043348117.26</v>
+        <v>2039454324.02</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5997,19 +5993,19 @@
         <v>280</v>
       </c>
       <c r="C140" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D140" s="7">
-        <v>0.013986</v>
+        <v>0.013874</v>
       </c>
       <c r="E140" s="8">
-        <v>2509236473.53</v>
+        <v>2517262794.2</v>
       </c>
       <c r="F140" s="9">
-        <v>1033</v>
+        <v>1046</v>
       </c>
       <c r="G140" s="8">
-        <v>35094583.93</v>
+        <v>34925636.88</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -6020,19 +6016,19 @@
         <v>282</v>
       </c>
       <c r="C141" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D141" s="7">
-        <v>0.072079</v>
+        <v>0.071334</v>
       </c>
       <c r="E141" s="8">
-        <v>20910431011.88</v>
+        <v>21182808063.74</v>
       </c>
       <c r="F141" s="9">
-        <v>23335</v>
+        <v>23377</v>
       </c>
       <c r="G141" s="8">
-        <v>1507209521.92</v>
+        <v>1511059186.13</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -6043,19 +6039,19 @@
         <v>284</v>
       </c>
       <c r="C142" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D142" s="7">
-        <v>0.286299</v>
+        <v>0.280103</v>
       </c>
       <c r="E142" s="8">
-        <v>20689548863.63</v>
+        <v>20685654488.25</v>
       </c>
       <c r="F142" s="9">
-        <v>4733</v>
+        <v>4729</v>
       </c>
       <c r="G142" s="8">
-        <v>5923395606.19</v>
+        <v>5794113174.17</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -6066,19 +6062,19 @@
         <v>286</v>
       </c>
       <c r="C143" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D143" s="7">
-        <v>0.090091</v>
+        <v>0.090163</v>
       </c>
       <c r="E143" s="8">
-        <v>629374725.29</v>
+        <v>626110981.33</v>
       </c>
       <c r="F143" s="9">
-        <v>10759</v>
+        <v>10693</v>
       </c>
       <c r="G143" s="8">
-        <v>56701021.71</v>
+        <v>56452244.06</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -6089,19 +6085,19 @@
         <v>288</v>
       </c>
       <c r="C144" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D144" s="7">
-        <v>0.054079</v>
+        <v>46141</v>
+      </c>
+      <c r="D144" s="10">
+        <v>0.05393</v>
       </c>
       <c r="E144" s="8">
-        <v>1424189122.17</v>
+        <v>1437914881.59</v>
       </c>
       <c r="F144" s="9">
         <v>317</v>
       </c>
       <c r="G144" s="8">
-        <v>77019041.67</v>
+        <v>77546541.2</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -6112,19 +6108,19 @@
         <v>290</v>
       </c>
       <c r="C145" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D145" s="7">
-        <v>0.113494</v>
+        <v>0.113271</v>
       </c>
       <c r="E145" s="8">
-        <v>1821369632.23</v>
+        <v>1823106377.51</v>
       </c>
       <c r="F145" s="9">
         <v>1068</v>
       </c>
       <c r="G145" s="8">
-        <v>206714584.19</v>
+        <v>206504710.97</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -6135,19 +6131,19 @@
         <v>292</v>
       </c>
       <c r="C146" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D146" s="7">
-        <v>0.112214</v>
+        <v>0.111902</v>
       </c>
       <c r="E146" s="8">
-        <v>1969747531.35</v>
+        <v>1967090564.72</v>
       </c>
       <c r="F146" s="9">
-        <v>65242</v>
+        <v>65275</v>
       </c>
       <c r="G146" s="8">
-        <v>221033132.79</v>
+        <v>220121251.32</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6158,19 +6154,19 @@
         <v>294</v>
       </c>
       <c r="C147" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D147" s="7">
-        <v>0.076053</v>
+        <v>0.075465</v>
       </c>
       <c r="E147" s="8">
-        <v>568269443.39</v>
+        <v>567959391.85</v>
       </c>
       <c r="F147" s="9">
-        <v>51692</v>
+        <v>51681</v>
       </c>
       <c r="G147" s="8">
-        <v>43218730.07</v>
+        <v>42861083.73</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -6181,19 +6177,19 @@
         <v>296</v>
       </c>
       <c r="C148" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D148" s="7">
-        <v>0.081721</v>
+        <v>0.081749</v>
       </c>
       <c r="E148" s="8">
-        <v>357059181.11</v>
+        <v>356624310.88</v>
       </c>
       <c r="F148" s="9">
-        <v>9537</v>
+        <v>9514</v>
       </c>
       <c r="G148" s="8">
-        <v>29179330.37</v>
+        <v>29153652.18</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6204,19 +6200,19 @@
         <v>298</v>
       </c>
       <c r="C149" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D149" s="7">
-        <v>0.365242</v>
+        <v>0.361553</v>
       </c>
       <c r="E149" s="8">
-        <v>147461344.23</v>
+        <v>147559990.43</v>
       </c>
       <c r="F149" s="9">
         <v>1770</v>
       </c>
       <c r="G149" s="8">
-        <v>53859026.94</v>
+        <v>53350693.15</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -6227,19 +6223,19 @@
         <v>300</v>
       </c>
       <c r="C150" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D150" s="7">
-        <v>0.098997</v>
+        <v>0.098682</v>
       </c>
       <c r="E150" s="8">
-        <v>333953122.73</v>
+        <v>334398931.8</v>
       </c>
       <c r="F150" s="9">
         <v>1839</v>
       </c>
       <c r="G150" s="8">
-        <v>33060334.43</v>
+        <v>32999138.04</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6250,19 +6246,19 @@
         <v>302</v>
       </c>
       <c r="C151" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D151" s="7">
-        <v>0.290018</v>
+        <v>0.287079</v>
       </c>
       <c r="E151" s="8">
-        <v>142238108.99</v>
+        <v>142188010.19</v>
       </c>
       <c r="F151" s="9">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G151" s="8">
-        <v>41251610.71</v>
+        <v>40819128.64</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -6273,19 +6269,19 @@
         <v>304</v>
       </c>
       <c r="C152" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D152" s="7">
-        <v>0.117237</v>
+        <v>0.117058</v>
       </c>
       <c r="E152" s="8">
-        <v>587597587.17</v>
+        <v>587042062.35</v>
       </c>
       <c r="F152" s="9">
         <v>92</v>
       </c>
       <c r="G152" s="8">
-        <v>68888287.54</v>
+        <v>68717749.43</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -6296,19 +6292,19 @@
         <v>306</v>
       </c>
       <c r="C153" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D153" s="7">
-        <v>0.395831</v>
+        <v>0.389583</v>
       </c>
       <c r="E153" s="8">
-        <v>1308647518.37</v>
+        <v>1307878515.65</v>
       </c>
       <c r="F153" s="9">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G153" s="8">
-        <v>518003482.33</v>
+        <v>509526791.33</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -6319,19 +6315,19 @@
         <v>308</v>
       </c>
       <c r="C154" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D154" s="7">
-        <v>0.515536</v>
+        <v>0.504504</v>
       </c>
       <c r="E154" s="8">
-        <v>594612998.24</v>
+        <v>594662663.96</v>
       </c>
       <c r="F154" s="9">
         <v>379</v>
       </c>
       <c r="G154" s="8">
-        <v>306544667.86</v>
+        <v>300009553.96</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -6342,19 +6338,19 @@
         <v>310</v>
       </c>
       <c r="C155" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D155" s="7">
-        <v>1.685616</v>
+        <v>1.660314</v>
       </c>
       <c r="E155" s="8">
-        <v>908011200.26</v>
+        <v>907404002.61</v>
       </c>
       <c r="F155" s="9">
-        <v>10199</v>
+        <v>10193</v>
       </c>
       <c r="G155" s="8">
-        <v>1530558494.05</v>
+        <v>1506575515.88</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -6365,19 +6361,19 @@
         <v>312</v>
       </c>
       <c r="C156" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D156" s="7">
-        <v>0.277142</v>
+        <v>0.273955</v>
       </c>
       <c r="E156" s="8">
-        <v>183219687.39</v>
+        <v>183411747.1</v>
       </c>
       <c r="F156" s="9">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G156" s="8">
-        <v>50777959.1</v>
+        <v>50246608.09</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -6388,19 +6384,19 @@
         <v>314</v>
       </c>
       <c r="C157" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D157" s="7">
-        <v>0.143805</v>
+        <v>0.143392</v>
       </c>
       <c r="E157" s="8">
-        <v>4635955369.91</v>
+        <v>4633018170.82</v>
       </c>
       <c r="F157" s="9">
-        <v>28862</v>
+        <v>28848</v>
       </c>
       <c r="G157" s="8">
-        <v>666671623.9</v>
+        <v>664336438.72</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -6411,19 +6407,19 @@
         <v>316</v>
       </c>
       <c r="C158" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D158" s="10">
-        <v>0.16606</v>
+        <v>46141</v>
+      </c>
+      <c r="D158" s="7">
+        <v>0.166179</v>
       </c>
       <c r="E158" s="8">
-        <v>3260528464.65</v>
+        <v>3240752327.86</v>
       </c>
       <c r="F158" s="9">
-        <v>12788</v>
+        <v>12012</v>
       </c>
       <c r="G158" s="8">
-        <v>541443962.48</v>
+        <v>538544880.99</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -6434,19 +6430,19 @@
         <v>318</v>
       </c>
       <c r="C159" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D159" s="7">
-        <v>0.689623</v>
+        <v>0.682933</v>
       </c>
       <c r="E159" s="8">
-        <v>758108482.84</v>
+        <v>757352707.33</v>
       </c>
       <c r="F159" s="9">
-        <v>5168</v>
+        <v>5165</v>
       </c>
       <c r="G159" s="8">
-        <v>522809076.22</v>
+        <v>517220895.06</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -6457,19 +6453,19 @@
         <v>320</v>
       </c>
       <c r="C160" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D160" s="7">
-        <v>0.378478</v>
+        <v>0.373442</v>
       </c>
       <c r="E160" s="8">
-        <v>1352677793.82</v>
+        <v>1353899288</v>
       </c>
       <c r="F160" s="9">
-        <v>23925</v>
+        <v>23916</v>
       </c>
       <c r="G160" s="8">
-        <v>511958829.64</v>
+        <v>505602219.16</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -6480,19 +6476,19 @@
         <v>322</v>
       </c>
       <c r="C161" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D161" s="7">
-        <v>0.371818</v>
+        <v>0.366381</v>
       </c>
       <c r="E161" s="8">
-        <v>167644568.99</v>
+        <v>167530626.98</v>
       </c>
       <c r="F161" s="9">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G161" s="8">
-        <v>62333311.27</v>
+        <v>61380055.06</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -6503,19 +6499,19 @@
         <v>324</v>
       </c>
       <c r="C162" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D162" s="7">
-        <v>0.143518</v>
+        <v>46141</v>
+      </c>
+      <c r="D162" s="10">
+        <v>0.14241</v>
       </c>
       <c r="E162" s="8">
-        <v>1029098876.69</v>
+        <v>1027082753.93</v>
       </c>
       <c r="F162" s="9">
-        <v>2963</v>
+        <v>2968</v>
       </c>
       <c r="G162" s="8">
-        <v>147694233.96</v>
+        <v>146266426.64</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -6526,19 +6522,19 @@
         <v>326</v>
       </c>
       <c r="C163" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D163" s="7">
-        <v>0.118565</v>
+        <v>0.117108</v>
       </c>
       <c r="E163" s="8">
-        <v>7517313474.17</v>
+        <v>7516452956</v>
       </c>
       <c r="F163" s="9">
-        <v>79201</v>
+        <v>79163</v>
       </c>
       <c r="G163" s="8">
-        <v>891287510.7</v>
+        <v>880233276.79</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -6549,19 +6545,19 @@
         <v>328</v>
       </c>
       <c r="C164" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D164" s="7">
-        <v>0.108503</v>
+        <v>0.107763</v>
       </c>
       <c r="E164" s="8">
-        <v>3275252850.83</v>
+        <v>3276559155.42</v>
       </c>
       <c r="F164" s="9">
-        <v>64750</v>
+        <v>64756</v>
       </c>
       <c r="G164" s="8">
-        <v>355374078.01</v>
+        <v>353093129.57</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -6572,19 +6568,19 @@
         <v>330</v>
       </c>
       <c r="C165" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D165" s="7">
-        <v>0.014868</v>
+        <v>0.014577</v>
       </c>
       <c r="E165" s="8">
-        <v>425811088168.86</v>
+        <v>426355760606.58</v>
       </c>
       <c r="F165" s="9">
-        <v>72055</v>
+        <v>72500</v>
       </c>
       <c r="G165" s="8">
-        <v>6330771823.19</v>
+        <v>6215169725.47</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -6595,19 +6591,19 @@
         <v>332</v>
       </c>
       <c r="C166" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D166" s="7">
-        <v>0.361104</v>
+        <v>0.358411</v>
       </c>
       <c r="E166" s="8">
-        <v>686336471</v>
+        <v>686559087.19</v>
       </c>
       <c r="F166" s="9">
-        <v>6849</v>
+        <v>6843</v>
       </c>
       <c r="G166" s="8">
-        <v>247838658.43</v>
+        <v>246070274.33</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -6618,19 +6614,19 @@
         <v>334</v>
       </c>
       <c r="C167" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D167" s="7">
-        <v>0.013661</v>
+        <v>0.013498</v>
       </c>
       <c r="E167" s="8">
-        <v>32029077573.34</v>
+        <v>31971898409</v>
       </c>
       <c r="F167" s="9">
-        <v>5471</v>
+        <v>5563</v>
       </c>
       <c r="G167" s="8">
-        <v>437562585.06</v>
+        <v>431566405.54</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6641,19 +6637,19 @@
         <v>336</v>
       </c>
       <c r="C168" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D168" s="7">
-        <v>0.685938</v>
+        <v>0.678155</v>
       </c>
       <c r="E168" s="8">
-        <v>1953217021.99</v>
+        <v>1952177204.81</v>
       </c>
       <c r="F168" s="9">
-        <v>32714</v>
+        <v>32703</v>
       </c>
       <c r="G168" s="8">
-        <v>1339785071.73</v>
+        <v>1323878727.98</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6664,19 +6660,19 @@
         <v>338</v>
       </c>
       <c r="C169" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D169" s="7">
-        <v>0.386774</v>
+        <v>0.385259</v>
       </c>
       <c r="E169" s="8">
-        <v>1982945134.9</v>
+        <v>1982723722.93</v>
       </c>
       <c r="F169" s="9">
-        <v>21031</v>
+        <v>21019</v>
       </c>
       <c r="G169" s="8">
-        <v>766950752.29</v>
+        <v>763863008.47</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6687,19 +6683,19 @@
         <v>340</v>
       </c>
       <c r="C170" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D170" s="7">
-        <v>0.140287</v>
+        <v>0.139584</v>
       </c>
       <c r="E170" s="8">
-        <v>1586147489.86</v>
+        <v>1586309087</v>
       </c>
       <c r="F170" s="9">
-        <v>16369</v>
+        <v>16368</v>
       </c>
       <c r="G170" s="8">
-        <v>222516235.81</v>
+        <v>221423653.95</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6710,19 +6706,19 @@
         <v>342</v>
       </c>
       <c r="C171" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D171" s="7">
-        <v>1.253016</v>
+        <v>1.233349</v>
       </c>
       <c r="E171" s="8">
-        <v>1388430280.32</v>
+        <v>1388695604.93</v>
       </c>
       <c r="F171" s="9">
-        <v>23801</v>
+        <v>23800</v>
       </c>
       <c r="G171" s="8">
-        <v>1739725218.99</v>
+        <v>1712745836.85</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6733,19 +6729,19 @@
         <v>344</v>
       </c>
       <c r="C172" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D172" s="7">
-        <v>0.568833</v>
+        <v>0.567482</v>
       </c>
       <c r="E172" s="8">
-        <v>2359418828.6</v>
+        <v>2358332962.92</v>
       </c>
       <c r="F172" s="9">
-        <v>35141</v>
+        <v>35103</v>
       </c>
       <c r="G172" s="8">
-        <v>1342115773.29</v>
+        <v>1338312170.64</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6756,19 +6752,19 @@
         <v>346</v>
       </c>
       <c r="C173" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D173" s="7">
-        <v>0.016984</v>
+        <v>0.016779</v>
       </c>
       <c r="E173" s="8">
-        <v>69883473903.41</v>
+        <v>70178099947.71</v>
       </c>
       <c r="F173" s="9">
-        <v>17002</v>
+        <v>17159</v>
       </c>
       <c r="G173" s="8">
-        <v>1186928619.4</v>
+        <v>1177533413.3</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6779,19 +6775,19 @@
         <v>348</v>
       </c>
       <c r="C174" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D174" s="7">
-        <v>0.089469</v>
+        <v>0.089042</v>
       </c>
       <c r="E174" s="8">
-        <v>2175679638.87</v>
+        <v>2175328962.53</v>
       </c>
       <c r="F174" s="9">
-        <v>5162</v>
+        <v>5154</v>
       </c>
       <c r="G174" s="8">
-        <v>194655325.33</v>
+        <v>193695262.61</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6802,19 +6798,19 @@
         <v>350</v>
       </c>
       <c r="C175" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D175" s="7">
-        <v>0.121278</v>
+        <v>0.121403</v>
       </c>
       <c r="E175" s="8">
-        <v>1668150876.95</v>
+        <v>1668453469.5</v>
       </c>
       <c r="F175" s="9">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="G175" s="8">
-        <v>202309869.13</v>
+        <v>202556053.93</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6825,19 +6821,19 @@
         <v>352</v>
       </c>
       <c r="C176" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D176" s="7">
-        <v>0.310604</v>
+        <v>0.308787</v>
       </c>
       <c r="E176" s="8">
-        <v>756992456.24</v>
+        <v>757806739.51</v>
       </c>
       <c r="F176" s="9">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="G176" s="8">
-        <v>235124982.33</v>
+        <v>234000778.69</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6848,19 +6844,19 @@
         <v>354</v>
       </c>
       <c r="C177" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D177" s="10">
-        <v>0.09107</v>
+        <v>46141</v>
+      </c>
+      <c r="D177" s="7">
+        <v>0.090295</v>
       </c>
       <c r="E177" s="8">
-        <v>41435437602.29</v>
+        <v>41400256444.95</v>
       </c>
       <c r="F177" s="9">
-        <v>281494</v>
+        <v>281408</v>
       </c>
       <c r="G177" s="8">
-        <v>3773541362.82</v>
+        <v>3738244274.95</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6871,19 +6867,19 @@
         <v>356</v>
       </c>
       <c r="C178" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D178" s="7">
-        <v>0.065146</v>
+        <v>0.064775</v>
       </c>
       <c r="E178" s="8">
-        <v>666320918.39</v>
+        <v>665597639.74</v>
       </c>
       <c r="F178" s="9">
-        <v>6094</v>
+        <v>6089</v>
       </c>
       <c r="G178" s="8">
-        <v>43407923.54</v>
+        <v>43114344.73</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6894,19 +6890,19 @@
         <v>358</v>
       </c>
       <c r="C179" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D179" s="10">
-        <v>0.24846</v>
+        <v>0.24746</v>
       </c>
       <c r="E179" s="8">
-        <v>552712685.67</v>
+        <v>552293373.31</v>
       </c>
       <c r="F179" s="9">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="G179" s="8">
-        <v>137326733.39</v>
+        <v>136670362.18</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6917,19 +6913,19 @@
         <v>360</v>
       </c>
       <c r="C180" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D180" s="7">
-        <v>0.392971</v>
+        <v>0.389162</v>
       </c>
       <c r="E180" s="8">
-        <v>362532452.67</v>
+        <v>362664863.9</v>
       </c>
       <c r="F180" s="9">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="G180" s="8">
-        <v>142464831.74</v>
+        <v>141135467.59</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6940,19 +6936,19 @@
         <v>362</v>
       </c>
       <c r="C181" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D181" s="7">
-        <v>0.110995</v>
+        <v>0.110601</v>
       </c>
       <c r="E181" s="8">
-        <v>14699932870.44</v>
+        <v>14659715652.53</v>
       </c>
       <c r="F181" s="9">
-        <v>32242</v>
+        <v>32214</v>
       </c>
       <c r="G181" s="8">
-        <v>1631622148.25</v>
+        <v>1621372465.6</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6963,19 +6959,19 @@
         <v>364</v>
       </c>
       <c r="C182" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D182" s="7">
-        <v>0.114961</v>
+        <v>0.115064</v>
       </c>
       <c r="E182" s="8">
-        <v>22493067923.71</v>
+        <v>22476795869.91</v>
       </c>
       <c r="F182" s="9">
-        <v>43705</v>
+        <v>41632</v>
       </c>
       <c r="G182" s="8">
-        <v>2585815256.81</v>
+        <v>2586279383.38</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6986,19 +6982,19 @@
         <v>366</v>
       </c>
       <c r="C183" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D183" s="7">
-        <v>0.092114</v>
+        <v>46141</v>
+      </c>
+      <c r="D183" s="11">
+        <v>0.0907</v>
       </c>
       <c r="E183" s="8">
-        <v>30597789312.14</v>
+        <v>30727079651.31</v>
       </c>
       <c r="F183" s="9">
-        <v>29589</v>
+        <v>29670</v>
       </c>
       <c r="G183" s="8">
-        <v>2818496723.69</v>
+        <v>2786953983.19</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7009,19 +7005,19 @@
         <v>368</v>
       </c>
       <c r="C184" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D184" s="7">
-        <v>0.084803</v>
+        <v>0.083776</v>
       </c>
       <c r="E184" s="8">
-        <v>6496688817.03</v>
+        <v>6475105120.96</v>
       </c>
       <c r="F184" s="9">
-        <v>5094</v>
+        <v>5078</v>
       </c>
       <c r="G184" s="8">
-        <v>550935575.84</v>
+        <v>542457193.99</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7032,19 +7028,19 @@
         <v>370</v>
       </c>
       <c r="C185" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D185" s="7">
-        <v>0.073268</v>
+        <v>46141</v>
+      </c>
+      <c r="D185" s="10">
+        <v>0.07296</v>
       </c>
       <c r="E185" s="8">
-        <v>13965782990.6</v>
+        <v>13965637896.59</v>
       </c>
       <c r="F185" s="9">
-        <v>184334</v>
+        <v>184381</v>
       </c>
       <c r="G185" s="8">
-        <v>1023246856.44</v>
+        <v>1018926348.71</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7055,19 +7051,19 @@
         <v>372</v>
       </c>
       <c r="C186" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D186" s="7">
-        <v>0.098291</v>
+        <v>0.098097</v>
       </c>
       <c r="E186" s="8">
-        <v>4069832483.24</v>
+        <v>4069654235.32</v>
       </c>
       <c r="F186" s="9">
-        <v>117675</v>
+        <v>117678</v>
       </c>
       <c r="G186" s="8">
-        <v>400026398.09</v>
+        <v>399220876.41</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7078,19 +7074,19 @@
         <v>374</v>
       </c>
       <c r="C187" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D187" s="7">
-        <v>0.238856</v>
+        <v>0.236447</v>
       </c>
       <c r="E187" s="8">
-        <v>667891784.25</v>
+        <v>667768338.99</v>
       </c>
       <c r="F187" s="9">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="G187" s="8">
-        <v>159529847.56</v>
+        <v>157891814.12</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7101,19 +7097,19 @@
         <v>376</v>
       </c>
       <c r="C188" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D188" s="7">
-        <v>0.084308</v>
+        <v>0.084376</v>
       </c>
       <c r="E188" s="8">
-        <v>2758707423.49</v>
+        <v>2743797823.61</v>
       </c>
       <c r="F188" s="9">
-        <v>42827</v>
+        <v>42453</v>
       </c>
       <c r="G188" s="8">
-        <v>232580234.54</v>
+        <v>231509485.65</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7124,19 +7120,19 @@
         <v>378</v>
       </c>
       <c r="C189" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D189" s="10">
-        <v>0.24584</v>
+        <v>46141</v>
+      </c>
+      <c r="D189" s="7">
+        <v>0.242317</v>
       </c>
       <c r="E189" s="8">
-        <v>3439654011.5</v>
+        <v>3445930384.19</v>
       </c>
       <c r="F189" s="9">
-        <v>6505</v>
+        <v>6526</v>
       </c>
       <c r="G189" s="8">
-        <v>845605901.54</v>
+        <v>835006840.58</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7147,19 +7143,19 @@
         <v>380</v>
       </c>
       <c r="C190" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D190" s="7">
-        <v>0.161067</v>
+        <v>0.159868</v>
       </c>
       <c r="E190" s="8">
-        <v>701276690.75</v>
+        <v>702806935.16</v>
       </c>
       <c r="F190" s="9">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="G190" s="8">
-        <v>112952277.61</v>
+        <v>112356044.92</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7170,19 +7166,19 @@
         <v>382</v>
       </c>
       <c r="C191" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D191" s="7">
-        <v>0.149931</v>
+        <v>0.148671</v>
       </c>
       <c r="E191" s="8">
-        <v>491145554.2</v>
+        <v>491162226.17</v>
       </c>
       <c r="F191" s="9">
-        <v>1362</v>
+        <v>1359</v>
       </c>
       <c r="G191" s="8">
-        <v>73638041.13</v>
+        <v>73021422.71</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7193,19 +7189,19 @@
         <v>384</v>
       </c>
       <c r="C192" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D192" s="7">
-        <v>0.100155</v>
+        <v>0.099615</v>
       </c>
       <c r="E192" s="8">
-        <v>1156475012.03</v>
+        <v>1155833630.03</v>
       </c>
       <c r="F192" s="9">
-        <v>116552</v>
+        <v>116526</v>
       </c>
       <c r="G192" s="8">
-        <v>115826214.64</v>
+        <v>115138781.14</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7216,19 +7212,19 @@
         <v>386</v>
       </c>
       <c r="C193" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D193" s="7">
-        <v>0.200016</v>
+        <v>0.198996</v>
       </c>
       <c r="E193" s="8">
-        <v>1906691563.91</v>
+        <v>1938944214.5</v>
       </c>
       <c r="F193" s="9">
-        <v>1459</v>
+        <v>1491</v>
       </c>
       <c r="G193" s="8">
-        <v>381367879.04</v>
+        <v>385841750.71</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7239,19 +7235,19 @@
         <v>388</v>
       </c>
       <c r="C194" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D194" s="7">
-        <v>0.157479</v>
+        <v>46141</v>
+      </c>
+      <c r="D194" s="10">
+        <v>0.15694</v>
       </c>
       <c r="E194" s="8">
-        <v>600691733.98</v>
+        <v>599375716.2</v>
       </c>
       <c r="F194" s="9">
         <v>2658</v>
       </c>
       <c r="G194" s="8">
-        <v>94596416.61</v>
+        <v>94065844.28</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7262,19 +7258,19 @@
         <v>390</v>
       </c>
       <c r="C195" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D195" s="7">
-        <v>0.274574</v>
+        <v>0.272147</v>
       </c>
       <c r="E195" s="8">
-        <v>2877178186.14</v>
+        <v>2857011369</v>
       </c>
       <c r="F195" s="9">
-        <v>7769</v>
+        <v>7759</v>
       </c>
       <c r="G195" s="8">
-        <v>789998146.65</v>
+        <v>777528102.6</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7285,19 +7281,19 @@
         <v>392</v>
       </c>
       <c r="C196" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D196" s="7">
-        <v>0.097888</v>
+        <v>0.097773</v>
       </c>
       <c r="E196" s="8">
-        <v>103076819.4</v>
+        <v>103545411.89</v>
       </c>
       <c r="F196" s="9">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="G196" s="8">
-        <v>10089964.26</v>
+        <v>10123901.59</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7308,19 +7304,19 @@
         <v>394</v>
       </c>
       <c r="C197" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D197" s="7">
-        <v>0.215607</v>
+        <v>0.213701</v>
       </c>
       <c r="E197" s="8">
-        <v>319705882.75</v>
+        <v>320141317.71</v>
       </c>
       <c r="F197" s="9">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="G197" s="8">
-        <v>68930808.17</v>
+        <v>68414553.91</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7331,19 +7327,19 @@
         <v>396</v>
       </c>
       <c r="C198" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D198" s="7">
-        <v>0.171743</v>
+        <v>46141</v>
+      </c>
+      <c r="D198" s="10">
+        <v>0.17055</v>
       </c>
       <c r="E198" s="8">
-        <v>269775175.88</v>
+        <v>269869689.36</v>
       </c>
       <c r="F198" s="9">
         <v>838</v>
       </c>
       <c r="G198" s="8">
-        <v>46331929.9</v>
+        <v>46026298.99</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7354,19 +7350,19 @@
         <v>398</v>
       </c>
       <c r="C199" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D199" s="7">
-        <v>0.087349</v>
+        <v>0.087438</v>
       </c>
       <c r="E199" s="8">
-        <v>2653994797.24</v>
+        <v>2652674647.38</v>
       </c>
       <c r="F199" s="9">
-        <v>40291</v>
+        <v>40238</v>
       </c>
       <c r="G199" s="8">
-        <v>231824360.51</v>
+        <v>231945504.76</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7377,19 +7373,19 @@
         <v>400</v>
       </c>
       <c r="C200" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D200" s="7">
-        <v>0.089798</v>
+        <v>46141</v>
+      </c>
+      <c r="D200" s="10">
+        <v>0.08975</v>
       </c>
       <c r="E200" s="8">
-        <v>825809693.55</v>
+        <v>825211083.77</v>
       </c>
       <c r="F200" s="9">
         <v>1375</v>
       </c>
       <c r="G200" s="8">
-        <v>74155804.99</v>
+        <v>74062898.62</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7400,19 +7396,19 @@
         <v>402</v>
       </c>
       <c r="C201" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D201" s="7">
-        <v>0.148636</v>
+        <v>0.148666</v>
       </c>
       <c r="E201" s="8">
-        <v>9870491611.39</v>
+        <v>9830823041.45</v>
       </c>
       <c r="F201" s="9">
-        <v>9556</v>
+        <v>9520</v>
       </c>
       <c r="G201" s="8">
-        <v>1467112994.04</v>
+        <v>1461507690.2</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7423,19 +7419,19 @@
         <v>404</v>
       </c>
       <c r="C202" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D202" s="7">
-        <v>0.014467</v>
+        <v>0.014373</v>
       </c>
       <c r="E202" s="8">
-        <v>8889568789.37</v>
+        <v>9019277732.87</v>
       </c>
       <c r="F202" s="9">
-        <v>1219</v>
+        <v>1224</v>
       </c>
       <c r="G202" s="8">
-        <v>128609315.02</v>
+        <v>129637910.72</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7446,19 +7442,19 @@
         <v>406</v>
       </c>
       <c r="C203" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D203" s="7">
-        <v>0.028135</v>
+        <v>0.027854</v>
       </c>
       <c r="E203" s="8">
-        <v>1308404621.65</v>
+        <v>1309091019.36</v>
       </c>
       <c r="F203" s="9">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="G203" s="8">
-        <v>36811914.09</v>
+        <v>36463610.74</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7469,19 +7465,19 @@
         <v>408</v>
       </c>
       <c r="C204" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D204" s="10">
-        <v>0.11842</v>
+        <v>46141</v>
+      </c>
+      <c r="D204" s="7">
+        <v>0.117435</v>
       </c>
       <c r="E204" s="8">
-        <v>3188256211.9</v>
+        <v>3185988325.47</v>
       </c>
       <c r="F204" s="9">
-        <v>308518</v>
+        <v>308436</v>
       </c>
       <c r="G204" s="8">
-        <v>377554037.85</v>
+        <v>374145221.39</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7492,19 +7488,19 @@
         <v>410</v>
       </c>
       <c r="C205" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D205" s="7">
-        <v>0.155936</v>
+        <v>46141</v>
+      </c>
+      <c r="D205" s="10">
+        <v>0.15523</v>
       </c>
       <c r="E205" s="8">
-        <v>419034593.84</v>
+        <v>443305955.02</v>
       </c>
       <c r="F205" s="9">
-        <v>827</v>
+        <v>860</v>
       </c>
       <c r="G205" s="8">
-        <v>65342598.97</v>
+        <v>68814191.07</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -7515,19 +7511,19 @@
         <v>412</v>
       </c>
       <c r="C206" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D206" s="7">
-        <v>0.131725</v>
+        <v>0.131128</v>
       </c>
       <c r="E206" s="8">
-        <v>2875201963.53</v>
+        <v>2844018973.13</v>
       </c>
       <c r="F206" s="9">
-        <v>5751</v>
+        <v>5747</v>
       </c>
       <c r="G206" s="8">
-        <v>378735225.91</v>
+        <v>372930737.08</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7538,19 +7534,19 @@
         <v>414</v>
       </c>
       <c r="C207" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D207" s="7">
-        <v>0.103915</v>
+        <v>0.103225</v>
       </c>
       <c r="E207" s="8">
-        <v>4276511399.46</v>
+        <v>4272676036.99</v>
       </c>
       <c r="F207" s="9">
-        <v>343390</v>
+        <v>343280</v>
       </c>
       <c r="G207" s="8">
-        <v>444395166.84</v>
+        <v>441048905.42</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7561,19 +7557,19 @@
         <v>416</v>
       </c>
       <c r="C208" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D208" s="10">
-        <v>0.10546</v>
+        <v>46141</v>
+      </c>
+      <c r="D208" s="7">
+        <v>0.105094</v>
       </c>
       <c r="E208" s="8">
-        <v>46479071651.57</v>
+        <v>46448190135.49</v>
       </c>
       <c r="F208" s="9">
-        <v>712038</v>
+        <v>712042</v>
       </c>
       <c r="G208" s="8">
-        <v>4901660592.3</v>
+        <v>4881432755.15</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7584,19 +7580,19 @@
         <v>418</v>
       </c>
       <c r="C209" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D209" s="7">
-        <v>0.062683</v>
+        <v>0.062393</v>
       </c>
       <c r="E209" s="8">
-        <v>55232833723.82</v>
+        <v>55667796935.32</v>
       </c>
       <c r="F209" s="9">
-        <v>59266</v>
+        <v>59497</v>
       </c>
       <c r="G209" s="8">
-        <v>3462175231.18</v>
+        <v>3473279847.29</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7607,19 +7603,19 @@
         <v>420</v>
       </c>
       <c r="C210" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D210" s="7">
-        <v>0.106593</v>
+        <v>46141</v>
+      </c>
+      <c r="D210" s="10">
+        <v>0.10609</v>
       </c>
       <c r="E210" s="8">
-        <v>64759401531.9</v>
+        <v>64718454002.69</v>
       </c>
       <c r="F210" s="9">
-        <v>913711</v>
+        <v>913737</v>
       </c>
       <c r="G210" s="8">
-        <v>6902900557.77</v>
+        <v>6866000570.75</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -7630,19 +7626,19 @@
         <v>422</v>
       </c>
       <c r="C211" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D211" s="7">
-        <v>0.069426</v>
+        <v>0.069473</v>
       </c>
       <c r="E211" s="8">
-        <v>55118793534.15</v>
+        <v>54943757342.75</v>
       </c>
       <c r="F211" s="9">
-        <v>55728</v>
+        <v>55693</v>
       </c>
       <c r="G211" s="8">
-        <v>3826659756.69</v>
+        <v>3817096340.79</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7653,19 +7649,19 @@
         <v>424</v>
       </c>
       <c r="C212" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D212" s="7">
-        <v>0.096704</v>
+        <v>46141</v>
+      </c>
+      <c r="D212" s="11">
+        <v>0.0968</v>
       </c>
       <c r="E212" s="8">
-        <v>16251775301.15</v>
+        <v>16215993278.19</v>
       </c>
       <c r="F212" s="9">
-        <v>343695</v>
+        <v>342152</v>
       </c>
       <c r="G212" s="8">
-        <v>1571618843.63</v>
+        <v>1569710965.25</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7676,19 +7672,19 @@
         <v>426</v>
       </c>
       <c r="C213" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D213" s="7">
-        <v>0.051367</v>
+        <v>0.050747</v>
       </c>
       <c r="E213" s="8">
-        <v>84129428530.05</v>
+        <v>83779499591.35</v>
       </c>
       <c r="F213" s="9">
-        <v>35132</v>
+        <v>35053</v>
       </c>
       <c r="G213" s="8">
-        <v>4321450483.4</v>
+        <v>4251560505.76</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -7699,19 +7695,19 @@
         <v>428</v>
       </c>
       <c r="C214" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D214" s="7">
-        <v>0.085281</v>
+        <v>0.085356</v>
       </c>
       <c r="E214" s="8">
-        <v>14008833696.51</v>
+        <v>13980231807.1</v>
       </c>
       <c r="F214" s="9">
-        <v>237530</v>
+        <v>237055</v>
       </c>
       <c r="G214" s="8">
-        <v>1194688879.64</v>
+        <v>1193295400.99</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7722,19 +7718,19 @@
         <v>430</v>
       </c>
       <c r="C215" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D215" s="7">
-        <v>0.314175</v>
+        <v>0.311049</v>
       </c>
       <c r="E215" s="8">
-        <v>12089608675.23</v>
+        <v>12105327840.67</v>
       </c>
       <c r="F215" s="9">
-        <v>57315</v>
+        <v>57384</v>
       </c>
       <c r="G215" s="8">
-        <v>3798251874.47</v>
+        <v>3765353969.33</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -7745,19 +7741,19 @@
         <v>432</v>
       </c>
       <c r="C216" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D216" s="10">
-        <v>0.22024</v>
+        <v>46141</v>
+      </c>
+      <c r="D216" s="7">
+        <v>0.217732</v>
       </c>
       <c r="E216" s="8">
-        <v>10250574700.56</v>
+        <v>10281179919.44</v>
       </c>
       <c r="F216" s="9">
-        <v>39150</v>
+        <v>39231</v>
       </c>
       <c r="G216" s="8">
-        <v>2257583913.71</v>
+        <v>2238542087.05</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -7768,19 +7764,19 @@
         <v>434</v>
       </c>
       <c r="C217" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D217" s="7">
-        <v>1.014556</v>
+        <v>1.004845</v>
       </c>
       <c r="E217" s="8">
-        <v>746552327.02</v>
+        <v>746388220</v>
       </c>
       <c r="F217" s="9">
-        <v>4368</v>
+        <v>4357</v>
       </c>
       <c r="G217" s="8">
-        <v>757418813.38</v>
+        <v>750004112.63</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7791,19 +7787,19 @@
         <v>436</v>
       </c>
       <c r="C218" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D218" s="10">
-        <v>0.72646</v>
+        <v>46141</v>
+      </c>
+      <c r="D218" s="7">
+        <v>0.714832</v>
       </c>
       <c r="E218" s="8">
-        <v>5936035733.88</v>
+        <v>5934769759.01</v>
       </c>
       <c r="F218" s="9">
-        <v>10980</v>
+        <v>10987</v>
       </c>
       <c r="G218" s="8">
-        <v>4312291050.37</v>
+        <v>4242365729.53</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -7814,19 +7810,19 @@
         <v>438</v>
       </c>
       <c r="C219" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D219" s="7">
-        <v>2.858392</v>
+        <v>2.813218</v>
       </c>
       <c r="E219" s="8">
-        <v>6293163234.83</v>
+        <v>6296784937.05</v>
       </c>
       <c r="F219" s="9">
-        <v>272667</v>
+        <v>272726</v>
       </c>
       <c r="G219" s="8">
-        <v>17988325603.55</v>
+        <v>17714229723.75</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -7837,19 +7833,19 @@
         <v>440</v>
       </c>
       <c r="C220" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D220" s="7">
-        <v>0.407224</v>
+        <v>0.405956</v>
       </c>
       <c r="E220" s="8">
-        <v>9441323142.24</v>
+        <v>9433717829.88</v>
       </c>
       <c r="F220" s="9">
-        <v>165861</v>
+        <v>165749</v>
       </c>
       <c r="G220" s="8">
-        <v>3844735827.95</v>
+        <v>3829674873.55</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -7860,19 +7856,19 @@
         <v>442</v>
       </c>
       <c r="C221" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D221" s="7">
-        <v>0.392764</v>
+        <v>0.393117</v>
       </c>
       <c r="E221" s="8">
-        <v>173446212244.86</v>
+        <v>173894140656.9</v>
       </c>
       <c r="F221" s="9">
-        <v>399083</v>
+        <v>380685</v>
       </c>
       <c r="G221" s="8">
-        <v>68123395601.15</v>
+        <v>68360757041.88</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -7883,19 +7879,19 @@
         <v>444</v>
       </c>
       <c r="C222" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D222" s="7">
-        <v>0.152805</v>
+        <v>0.152202</v>
       </c>
       <c r="E222" s="8">
-        <v>6411433761.49</v>
+        <v>6420511794.66</v>
       </c>
       <c r="F222" s="9">
-        <v>25278</v>
+        <v>25256</v>
       </c>
       <c r="G222" s="8">
-        <v>979695985.78</v>
+        <v>977213984.07</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -7906,19 +7902,19 @@
         <v>446</v>
       </c>
       <c r="C223" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D223" s="7">
-        <v>0.518229</v>
+        <v>0.518782</v>
       </c>
       <c r="E223" s="8">
-        <v>8751779062.87</v>
+        <v>8113525178.59</v>
       </c>
       <c r="F223" s="9">
-        <v>35793</v>
+        <v>35791</v>
       </c>
       <c r="G223" s="8">
-        <v>4535422771.04</v>
+        <v>4209153058.33</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -7929,19 +7925,19 @@
         <v>448</v>
       </c>
       <c r="C224" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D224" s="7">
-        <v>0.075584</v>
+        <v>0.073886</v>
       </c>
       <c r="E224" s="8">
-        <v>2518256030880.74</v>
+        <v>2517793740672.07</v>
       </c>
       <c r="F224" s="9">
-        <v>1247459</v>
+        <v>1247813</v>
       </c>
       <c r="G224" s="8">
-        <v>190340558663.64</v>
+        <v>186029114361.24</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -7952,19 +7948,19 @@
         <v>450</v>
       </c>
       <c r="C225" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D225" s="7">
-        <v>0.074105</v>
+        <v>0.073154</v>
       </c>
       <c r="E225" s="8">
-        <v>26549268162.36</v>
+        <v>26598433785.77</v>
       </c>
       <c r="F225" s="9">
-        <v>95486</v>
+        <v>95478</v>
       </c>
       <c r="G225" s="8">
-        <v>1967426146.32</v>
+        <v>1945791435.97</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -7975,19 +7971,19 @@
         <v>452</v>
       </c>
       <c r="C226" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D226" s="7">
-        <v>0.015515</v>
+        <v>0.015143</v>
       </c>
       <c r="E226" s="8">
-        <v>520754377916.59</v>
+        <v>519783228917.47</v>
       </c>
       <c r="F226" s="9">
-        <v>50874</v>
+        <v>50909</v>
       </c>
       <c r="G226" s="8">
-        <v>8079504229.02</v>
+        <v>7871270709.54</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -7998,19 +7994,19 @@
         <v>454</v>
       </c>
       <c r="C227" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D227" s="7">
-        <v>0.798694</v>
+        <v>46141</v>
+      </c>
+      <c r="D227" s="10">
+        <v>0.77916</v>
       </c>
       <c r="E227" s="8">
-        <v>171241236639.96</v>
+        <v>171063136658.29</v>
       </c>
       <c r="F227" s="9">
-        <v>822520</v>
+        <v>822650</v>
       </c>
       <c r="G227" s="8">
-        <v>136769363728.72</v>
+        <v>133285558365.09</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8021,19 +8017,19 @@
         <v>456</v>
       </c>
       <c r="C228" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D228" s="7">
-        <v>0.138981</v>
+        <v>0.138172</v>
       </c>
       <c r="E228" s="8">
-        <v>27036500331.39</v>
+        <v>27007614721.87</v>
       </c>
       <c r="F228" s="9">
-        <v>195043</v>
+        <v>194931</v>
       </c>
       <c r="G228" s="8">
-        <v>3757565398.19</v>
+        <v>3731695716.49</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8044,19 +8040,19 @@
         <v>458</v>
       </c>
       <c r="C229" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D229" s="7">
-        <v>1.112742</v>
+        <v>1.102071</v>
       </c>
       <c r="E229" s="8">
-        <v>2642082845.13</v>
+        <v>2639997894.37</v>
       </c>
       <c r="F229" s="9">
-        <v>49188</v>
+        <v>49164</v>
       </c>
       <c r="G229" s="8">
-        <v>2939957605.97</v>
+        <v>2909466433.42</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8067,19 +8063,19 @@
         <v>460</v>
       </c>
       <c r="C230" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D230" s="7">
-        <v>0.283125</v>
+        <v>0.282346</v>
       </c>
       <c r="E230" s="8">
-        <v>2536760158.97</v>
+        <v>2536534079.3</v>
       </c>
       <c r="F230" s="9">
-        <v>11024</v>
+        <v>11239</v>
       </c>
       <c r="G230" s="8">
-        <v>718221059.45</v>
+        <v>716180345.63</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8090,19 +8086,19 @@
         <v>462</v>
       </c>
       <c r="C231" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D231" s="7">
-        <v>1.126966</v>
+        <v>1.123211</v>
       </c>
       <c r="E231" s="8">
-        <v>5216498632.3</v>
+        <v>5217940147.84</v>
       </c>
       <c r="F231" s="9">
-        <v>63786</v>
+        <v>63782</v>
       </c>
       <c r="G231" s="8">
-        <v>5878816793.74</v>
+        <v>5860846151.87</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8113,19 +8109,19 @@
         <v>464</v>
       </c>
       <c r="C232" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D232" s="7">
-        <v>0.378277</v>
+        <v>0.375143</v>
       </c>
       <c r="E232" s="8">
-        <v>18483590849.33</v>
+        <v>18542018146.13</v>
       </c>
       <c r="F232" s="9">
-        <v>149345</v>
+        <v>149588</v>
       </c>
       <c r="G232" s="8">
-        <v>6991913184.68</v>
+        <v>6955900831.97</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8136,19 +8132,19 @@
         <v>466</v>
       </c>
       <c r="C233" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D233" s="7">
-        <v>0.108617</v>
+        <v>0.107548</v>
       </c>
       <c r="E233" s="8">
-        <v>278206650503.94</v>
+        <v>278000281558.02</v>
       </c>
       <c r="F233" s="9">
-        <v>1511076</v>
+        <v>1510210</v>
       </c>
       <c r="G233" s="8">
-        <v>30217936781.63</v>
+        <v>29898466579.45</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8159,19 +8155,19 @@
         <v>468</v>
       </c>
       <c r="C234" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D234" s="7">
-        <v>0.265681</v>
+        <v>0.262337</v>
       </c>
       <c r="E234" s="8">
-        <v>3267836280.87</v>
+        <v>3265366887.4</v>
       </c>
       <c r="F234" s="9">
-        <v>10504</v>
+        <v>10508</v>
       </c>
       <c r="G234" s="8">
-        <v>868203472.06</v>
+        <v>856625444.05</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8182,19 +8178,19 @@
         <v>470</v>
       </c>
       <c r="C235" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D235" s="10">
-        <v>0.78785</v>
+        <v>46141</v>
+      </c>
+      <c r="D235" s="7">
+        <v>0.785263</v>
       </c>
       <c r="E235" s="8">
-        <v>1343927411.55</v>
+        <v>1344096983.87</v>
       </c>
       <c r="F235" s="9">
-        <v>7459</v>
+        <v>7642</v>
       </c>
       <c r="G235" s="8">
-        <v>1058813613.25</v>
+        <v>1055470279.89</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8205,19 +8201,19 @@
         <v>472</v>
       </c>
       <c r="C236" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D236" s="7">
-        <v>0.152458</v>
+        <v>0.151377</v>
       </c>
       <c r="E236" s="8">
-        <v>71193659098.01</v>
+        <v>71106188111.84</v>
       </c>
       <c r="F236" s="9">
-        <v>825177</v>
+        <v>824534</v>
       </c>
       <c r="G236" s="8">
-        <v>10854075485.42</v>
+        <v>10763815316.91</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8228,19 +8224,19 @@
         <v>474</v>
       </c>
       <c r="C237" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D237" s="7">
-        <v>0.223869</v>
+        <v>0.221831</v>
       </c>
       <c r="E237" s="8">
-        <v>2427150744.31</v>
+        <v>2428402068.08</v>
       </c>
       <c r="F237" s="9">
-        <v>7578</v>
+        <v>7584</v>
       </c>
       <c r="G237" s="8">
-        <v>543365010.46</v>
+        <v>538694118.32</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -8251,19 +8247,19 @@
         <v>476</v>
       </c>
       <c r="C238" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D238" s="10">
-        <v>0.19746</v>
+        <v>46141</v>
+      </c>
+      <c r="D238" s="7">
+        <v>0.195619</v>
       </c>
       <c r="E238" s="8">
-        <v>2320956484.77</v>
+        <v>2322066100.25</v>
       </c>
       <c r="F238" s="9">
-        <v>7330</v>
+        <v>7333</v>
       </c>
       <c r="G238" s="8">
-        <v>458297080.31</v>
+        <v>454240038.32</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -8274,19 +8270,19 @@
         <v>478</v>
       </c>
       <c r="C239" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D239" s="7">
-        <v>0.341929</v>
+        <v>0.339138</v>
       </c>
       <c r="E239" s="8">
-        <v>31232705041.2</v>
+        <v>31285651277.78</v>
       </c>
       <c r="F239" s="9">
-        <v>119843</v>
+        <v>119974</v>
       </c>
       <c r="G239" s="8">
-        <v>10679376695.01</v>
+        <v>10610164056.25</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -8297,19 +8293,19 @@
         <v>480</v>
       </c>
       <c r="C240" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D240" s="7">
-        <v>0.126139</v>
+        <v>0.125866</v>
       </c>
       <c r="E240" s="8">
-        <v>3797519984.02</v>
+        <v>3793668407.47</v>
       </c>
       <c r="F240" s="9">
-        <v>7438</v>
+        <v>7437</v>
       </c>
       <c r="G240" s="8">
-        <v>479015647.58</v>
+        <v>477494358.29</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -8320,19 +8316,19 @@
         <v>482</v>
       </c>
       <c r="C241" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D241" s="7">
-        <v>0.127835</v>
+        <v>0.127039</v>
       </c>
       <c r="E241" s="8">
-        <v>89728480914.85</v>
+        <v>89615779460.91</v>
       </c>
       <c r="F241" s="9">
-        <v>403673</v>
+        <v>403445</v>
       </c>
       <c r="G241" s="8">
-        <v>11470396991.5</v>
+        <v>11384694540.32</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -8343,19 +8339,19 @@
         <v>484</v>
       </c>
       <c r="C242" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D242" s="7">
-        <v>0.302607</v>
+        <v>0.299947</v>
       </c>
       <c r="E242" s="8">
-        <v>3846246351.58</v>
+        <v>3853187009.6</v>
       </c>
       <c r="F242" s="9">
-        <v>18039</v>
+        <v>18075</v>
       </c>
       <c r="G242" s="8">
-        <v>1163900785.28</v>
+        <v>1155753485.28</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8366,19 +8362,19 @@
         <v>486</v>
       </c>
       <c r="C243" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D243" s="7">
-        <v>0.080928</v>
+        <v>0.080989</v>
       </c>
       <c r="E243" s="8">
-        <v>3853921291.11</v>
+        <v>3844546281.23</v>
       </c>
       <c r="F243" s="9">
-        <v>9204</v>
+        <v>9208</v>
       </c>
       <c r="G243" s="8">
-        <v>311888691.9</v>
+        <v>311366625.3</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -8389,19 +8385,19 @@
         <v>488</v>
       </c>
       <c r="C244" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D244" s="7">
-        <v>0.243449</v>
+        <v>0.241844</v>
       </c>
       <c r="E244" s="8">
-        <v>2834866378.78</v>
+        <v>2835432687.44</v>
       </c>
       <c r="F244" s="9">
-        <v>13990</v>
+        <v>14013</v>
       </c>
       <c r="G244" s="8">
-        <v>690146465.42</v>
+        <v>685732228.39</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8412,19 +8408,19 @@
         <v>490</v>
       </c>
       <c r="C245" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D245" s="7">
-        <v>0.068628</v>
+        <v>46141</v>
+      </c>
+      <c r="D245" s="10">
+        <v>0.06868</v>
       </c>
       <c r="E245" s="8">
-        <v>4044064990.83</v>
+        <v>4038059488.43</v>
       </c>
       <c r="F245" s="9">
-        <v>7797</v>
+        <v>7793</v>
       </c>
       <c r="G245" s="8">
-        <v>277535071.79</v>
+        <v>277334323.24</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -8435,19 +8431,19 @@
         <v>492</v>
       </c>
       <c r="C246" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D246" s="7">
-        <v>0.178116</v>
+        <v>0.178278</v>
       </c>
       <c r="E246" s="8">
-        <v>14286536768.32</v>
+        <v>14275666117.29</v>
       </c>
       <c r="F246" s="9">
-        <v>48580</v>
+        <v>48620</v>
       </c>
       <c r="G246" s="8">
-        <v>2544661851.55</v>
+        <v>2545034807.55</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8458,19 +8454,19 @@
         <v>494</v>
       </c>
       <c r="C247" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D247" s="7">
-        <v>0.024567</v>
+        <v>0.023928</v>
       </c>
       <c r="E247" s="8">
-        <v>968791962455.41</v>
+        <v>967020000578.09</v>
       </c>
       <c r="F247" s="9">
         <v>187553</v>
       </c>
       <c r="G247" s="8">
-        <v>23800334794.64</v>
+        <v>23138997643.39</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8481,19 +8477,19 @@
         <v>496</v>
       </c>
       <c r="C248" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D248" s="7">
-        <v>0.753853</v>
+        <v>0.735659</v>
       </c>
       <c r="E248" s="8">
-        <v>15403893004.77</v>
+        <v>15385417173.43</v>
       </c>
       <c r="F248" s="9">
-        <v>79506</v>
+        <v>79516</v>
       </c>
       <c r="G248" s="8">
-        <v>11612264090.97</v>
+        <v>11318418498.06</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8504,19 +8500,19 @@
         <v>498</v>
       </c>
       <c r="C249" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D249" s="7">
-        <v>0.653593</v>
+        <v>0.639305</v>
       </c>
       <c r="E249" s="8">
-        <v>8202182999.93</v>
+        <v>8210364110.18</v>
       </c>
       <c r="F249" s="9">
-        <v>74331</v>
+        <v>74457</v>
       </c>
       <c r="G249" s="8">
-        <v>5360890761.08</v>
+        <v>5248923628.85</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8527,19 +8523,19 @@
         <v>500</v>
       </c>
       <c r="C250" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D250" s="7">
-        <v>0.162165</v>
+        <v>0.160978</v>
       </c>
       <c r="E250" s="8">
-        <v>2778491379.81</v>
+        <v>2778714335.86</v>
       </c>
       <c r="F250" s="9">
-        <v>11282</v>
+        <v>11312</v>
       </c>
       <c r="G250" s="8">
-        <v>450573217.54</v>
+        <v>447311806.35</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8550,19 +8546,19 @@
         <v>502</v>
       </c>
       <c r="C251" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D251" s="10">
-        <v>0.09652</v>
+        <v>0.09599</v>
       </c>
       <c r="E251" s="8">
-        <v>4853405760.81</v>
+        <v>4857553745.87</v>
       </c>
       <c r="F251" s="9">
-        <v>69429</v>
+        <v>69485</v>
       </c>
       <c r="G251" s="8">
-        <v>468451840.85</v>
+        <v>466274757.16</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8573,19 +8569,19 @@
         <v>504</v>
       </c>
       <c r="C252" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D252" s="7">
-        <v>0.329496</v>
+        <v>0.328574</v>
       </c>
       <c r="E252" s="8">
-        <v>2197737606.45</v>
+        <v>2197898273.46</v>
       </c>
       <c r="F252" s="9">
-        <v>20953</v>
+        <v>20959</v>
       </c>
       <c r="G252" s="8">
-        <v>724145653.88</v>
+        <v>722171923.19</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8596,19 +8592,19 @@
         <v>506</v>
       </c>
       <c r="C253" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D253" s="7">
-        <v>0.140596</v>
+        <v>0.139984</v>
       </c>
       <c r="E253" s="8">
-        <v>658681666.39</v>
+        <v>658499130.57</v>
       </c>
       <c r="F253" s="9">
-        <v>2355</v>
+        <v>2352</v>
       </c>
       <c r="G253" s="8">
-        <v>92607914.6</v>
+        <v>92179463.02</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8619,19 +8615,19 @@
         <v>508</v>
       </c>
       <c r="C254" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D254" s="7">
-        <v>0.082347</v>
+        <v>0.082416</v>
       </c>
       <c r="E254" s="8">
-        <v>641556392.23</v>
+        <v>640246570.8</v>
       </c>
       <c r="F254" s="9">
-        <v>14053</v>
+        <v>13944</v>
       </c>
       <c r="G254" s="8">
-        <v>52830332.71</v>
+        <v>52766457.71</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8642,19 +8638,19 @@
         <v>510</v>
       </c>
       <c r="C255" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D255" s="7">
-        <v>0.095943</v>
+        <v>0.095699</v>
       </c>
       <c r="E255" s="8">
-        <v>4030219957.25</v>
+        <v>4027134800.3</v>
       </c>
       <c r="F255" s="9">
-        <v>78490</v>
+        <v>78547</v>
       </c>
       <c r="G255" s="8">
-        <v>386670389.46</v>
+        <v>385391441.58</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8665,19 +8661,19 @@
         <v>512</v>
       </c>
       <c r="C256" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D256" s="10">
-        <v>0.12768</v>
+        <v>46141</v>
+      </c>
+      <c r="D256" s="7">
+        <v>0.126809</v>
       </c>
       <c r="E256" s="8">
-        <v>3762688454.83</v>
+        <v>3758424863.8</v>
       </c>
       <c r="F256" s="9">
-        <v>19625</v>
+        <v>19630</v>
       </c>
       <c r="G256" s="8">
-        <v>480418424.22</v>
+        <v>476600420.23</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8688,19 +8684,19 @@
         <v>514</v>
       </c>
       <c r="C257" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D257" s="7">
-        <v>0.093152</v>
+        <v>0.093246</v>
       </c>
       <c r="E257" s="8">
-        <v>576456367.44</v>
+        <v>585937224.82</v>
       </c>
       <c r="F257" s="9">
-        <v>10372</v>
+        <v>10594</v>
       </c>
       <c r="G257" s="8">
-        <v>53697825.01</v>
+        <v>54636217.45</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -8711,19 +8707,19 @@
         <v>516</v>
       </c>
       <c r="C258" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D258" s="7">
-        <v>0.131793</v>
+        <v>0.131911</v>
       </c>
       <c r="E258" s="8">
-        <v>4432530457.46</v>
+        <v>4428574691.65</v>
       </c>
       <c r="F258" s="9">
-        <v>19538</v>
+        <v>18356</v>
       </c>
       <c r="G258" s="8">
-        <v>584176608.23</v>
+        <v>584176817.46</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -8734,19 +8730,19 @@
         <v>518</v>
       </c>
       <c r="C259" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D259" s="10">
-        <v>0.15438</v>
+        <v>46141</v>
+      </c>
+      <c r="D259" s="7">
+        <v>0.153043</v>
       </c>
       <c r="E259" s="8">
-        <v>1197565225.89</v>
+        <v>1196825814.88</v>
       </c>
       <c r="F259" s="9">
-        <v>58196</v>
+        <v>58187</v>
       </c>
       <c r="G259" s="8">
-        <v>184879832.3</v>
+        <v>183165673.38</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -8757,19 +8753,19 @@
         <v>520</v>
       </c>
       <c r="C260" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D260" s="7">
-        <v>0.778667</v>
+        <v>0.764824</v>
       </c>
       <c r="E260" s="8">
-        <v>8940020752.72</v>
+        <v>8930088711.27</v>
       </c>
       <c r="F260" s="9">
-        <v>25931</v>
+        <v>25955</v>
       </c>
       <c r="G260" s="8">
-        <v>6961295395.99</v>
+        <v>6829949381.75</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -8780,19 +8776,19 @@
         <v>522</v>
       </c>
       <c r="C261" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D261" s="7">
-        <v>0.103012</v>
+        <v>0.101851</v>
       </c>
       <c r="E261" s="8">
-        <v>13805980885.63</v>
+        <v>13792489849.86</v>
       </c>
       <c r="F261" s="9">
-        <v>126091</v>
+        <v>126055</v>
       </c>
       <c r="G261" s="8">
-        <v>1422182963.9</v>
+        <v>1404773379.28</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -8803,19 +8799,19 @@
         <v>524</v>
       </c>
       <c r="C262" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D262" s="7">
-        <v>0.013207</v>
+        <v>0.013082</v>
       </c>
       <c r="E262" s="8">
-        <v>138069927380.39</v>
+        <v>138945963105.6</v>
       </c>
       <c r="F262" s="9">
-        <v>1601</v>
+        <v>1615</v>
       </c>
       <c r="G262" s="8">
-        <v>1823470184.05</v>
+        <v>1817732011.57</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -8826,19 +8822,19 @@
         <v>526</v>
       </c>
       <c r="C263" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D263" s="7">
-        <v>0.283953</v>
+        <v>0.279659</v>
       </c>
       <c r="E263" s="8">
-        <v>5715995915.19</v>
+        <v>5705138568.5</v>
       </c>
       <c r="F263" s="9">
-        <v>44129</v>
+        <v>44090</v>
       </c>
       <c r="G263" s="8">
-        <v>1623073182.61</v>
+        <v>1595496053.16</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -8849,19 +8845,19 @@
         <v>528</v>
       </c>
       <c r="C264" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D264" s="10">
-        <v>0.40509</v>
+        <v>46141</v>
+      </c>
+      <c r="D264" s="7">
+        <v>0.401815</v>
       </c>
       <c r="E264" s="8">
-        <v>1948301520.95</v>
+        <v>1949645999.27</v>
       </c>
       <c r="F264" s="9">
-        <v>21821</v>
+        <v>21817</v>
       </c>
       <c r="G264" s="8">
-        <v>789237380</v>
+        <v>783396544.92</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -8872,19 +8868,19 @@
         <v>530</v>
       </c>
       <c r="C265" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D265" s="7">
-        <v>0.131595</v>
+        <v>0.130539</v>
       </c>
       <c r="E265" s="8">
-        <v>33504314840.91</v>
+        <v>33759101872.08</v>
       </c>
       <c r="F265" s="9">
-        <v>101433</v>
+        <v>101934</v>
       </c>
       <c r="G265" s="8">
-        <v>4409016218.1</v>
+        <v>4406877482.2</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -8895,19 +8891,19 @@
         <v>532</v>
       </c>
       <c r="C266" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D266" s="10">
-        <v>0.23788</v>
+        <v>46141</v>
+      </c>
+      <c r="D266" s="7">
+        <v>0.237135</v>
       </c>
       <c r="E266" s="8">
-        <v>2676383226.61</v>
+        <v>2678688809.22</v>
       </c>
       <c r="F266" s="9">
         <v>24247</v>
       </c>
       <c r="G266" s="8">
-        <v>636658804.54</v>
+        <v>635210392.57</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -8918,19 +8914,19 @@
         <v>534</v>
       </c>
       <c r="C267" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D267" s="7">
-        <v>0.012913</v>
+        <v>0.012692</v>
       </c>
       <c r="E267" s="8">
-        <v>630870119017.41</v>
+        <v>688356287059.04</v>
       </c>
       <c r="F267" s="9">
-        <v>70204</v>
+        <v>70644</v>
       </c>
       <c r="G267" s="8">
-        <v>8146621596.35</v>
+        <v>8736397931.83</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -8941,19 +8937,19 @@
         <v>536</v>
       </c>
       <c r="C268" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D268" s="7">
-        <v>0.500982</v>
+        <v>0.499777</v>
       </c>
       <c r="E268" s="8">
-        <v>5699401657.21</v>
+        <v>5693178381</v>
       </c>
       <c r="F268" s="9">
-        <v>72513</v>
+        <v>72424</v>
       </c>
       <c r="G268" s="8">
-        <v>2855295322.96</v>
+        <v>2845319439.06</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -8964,19 +8960,19 @@
         <v>538</v>
       </c>
       <c r="C269" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D269" s="7">
-        <v>0.304491</v>
+        <v>0.302416</v>
       </c>
       <c r="E269" s="8">
-        <v>1839652850.11</v>
+        <v>1834552554.35</v>
       </c>
       <c r="F269" s="9">
-        <v>95875</v>
+        <v>95728</v>
       </c>
       <c r="G269" s="8">
-        <v>560158449.32</v>
+        <v>554797674.44</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -8987,19 +8983,19 @@
         <v>540</v>
       </c>
       <c r="C270" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D270" s="7">
-        <v>0.790621</v>
+        <v>46141</v>
+      </c>
+      <c r="D270" s="10">
+        <v>0.78236</v>
       </c>
       <c r="E270" s="8">
-        <v>2054448940.72</v>
+        <v>2055404229.39</v>
       </c>
       <c r="F270" s="9">
-        <v>111833</v>
+        <v>111780</v>
       </c>
       <c r="G270" s="8">
-        <v>1624290287.92</v>
+        <v>1608065759.75</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9010,19 +9006,19 @@
         <v>542</v>
       </c>
       <c r="C271" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D271" s="7">
-        <v>0.533884</v>
+        <v>0.527174</v>
       </c>
       <c r="E271" s="8">
-        <v>1497734352.84</v>
+        <v>1502621742.38</v>
       </c>
       <c r="F271" s="9">
-        <v>37744</v>
+        <v>37731</v>
       </c>
       <c r="G271" s="8">
-        <v>799617100.47</v>
+        <v>792143516.89</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9033,19 +9029,19 @@
         <v>544</v>
       </c>
       <c r="C272" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D272" s="7">
-        <v>0.285721</v>
+        <v>0.284569</v>
       </c>
       <c r="E272" s="8">
-        <v>2836998092.57</v>
+        <v>2821640674.1</v>
       </c>
       <c r="F272" s="9">
-        <v>87643</v>
+        <v>87422</v>
       </c>
       <c r="G272" s="8">
-        <v>810589298.26</v>
+        <v>802951202.34</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9056,19 +9052,19 @@
         <v>546</v>
       </c>
       <c r="C273" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D273" s="7">
-        <v>2.464484</v>
+        <v>2.423214</v>
       </c>
       <c r="E273" s="8">
-        <v>1893379015.35</v>
+        <v>1895378432.32</v>
       </c>
       <c r="F273" s="9">
-        <v>57686</v>
+        <v>57654</v>
       </c>
       <c r="G273" s="8">
-        <v>4666202058.28</v>
+        <v>4592907724.88</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9079,19 +9075,19 @@
         <v>548</v>
       </c>
       <c r="C274" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D274" s="7">
-        <v>0.912284</v>
+        <v>46141</v>
+      </c>
+      <c r="D274" s="10">
+        <v>0.90416</v>
       </c>
       <c r="E274" s="8">
-        <v>767181212.79</v>
+        <v>768749156.17</v>
       </c>
       <c r="F274" s="9">
-        <v>83480</v>
+        <v>83410</v>
       </c>
       <c r="G274" s="8">
-        <v>699887343.58</v>
+        <v>695072583.21</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9102,19 +9098,19 @@
         <v>550</v>
       </c>
       <c r="C275" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D275" s="7">
-        <v>0.373083</v>
+        <v>46141</v>
+      </c>
+      <c r="D275" s="10">
+        <v>0.37341</v>
       </c>
       <c r="E275" s="8">
-        <v>8933797440.24</v>
+        <v>8974941871.71</v>
       </c>
       <c r="F275" s="9">
-        <v>103673</v>
+        <v>101619</v>
       </c>
       <c r="G275" s="8">
-        <v>3333045704.6</v>
+        <v>3351336484.97</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9125,19 +9121,19 @@
         <v>552</v>
       </c>
       <c r="C276" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D276" s="7">
-        <v>0.110876</v>
+        <v>0.109958</v>
       </c>
       <c r="E276" s="8">
-        <v>54316573901.08</v>
+        <v>54265171981.15</v>
       </c>
       <c r="F276" s="9">
-        <v>198323</v>
+        <v>198172</v>
       </c>
       <c r="G276" s="8">
-        <v>6022388551.51</v>
+        <v>5966888738.81</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9148,19 +9144,19 @@
         <v>554</v>
       </c>
       <c r="C277" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D277" s="7">
-        <v>0.114357</v>
+        <v>0.113688</v>
       </c>
       <c r="E277" s="8">
-        <v>82171626608.23</v>
+        <v>82095872418.96</v>
       </c>
       <c r="F277" s="9">
-        <v>1066800</v>
+        <v>1066373</v>
       </c>
       <c r="G277" s="8">
-        <v>9396913518.09</v>
+        <v>9333292510.96</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9171,19 +9167,19 @@
         <v>556</v>
       </c>
       <c r="C278" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D278" s="7">
-        <v>0.141466</v>
+        <v>0.140836</v>
       </c>
       <c r="E278" s="8">
-        <v>33134907138.76</v>
+        <v>33142021927.7</v>
       </c>
       <c r="F278" s="9">
-        <v>328702</v>
+        <v>328694</v>
       </c>
       <c r="G278" s="8">
-        <v>4687477986.87</v>
+        <v>4667583107.15</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9194,19 +9190,19 @@
         <v>558</v>
       </c>
       <c r="C279" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D279" s="7">
-        <v>0.168805</v>
+        <v>0.166843</v>
       </c>
       <c r="E279" s="8">
-        <v>3129402940.97</v>
+        <v>3122038143.05</v>
       </c>
       <c r="F279" s="9">
-        <v>27407</v>
+        <v>27399</v>
       </c>
       <c r="G279" s="8">
-        <v>528259566.84</v>
+        <v>520890106.4</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9217,19 +9213,19 @@
         <v>560</v>
       </c>
       <c r="C280" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D280" s="7">
-        <v>0.741073</v>
+        <v>0.722404</v>
       </c>
       <c r="E280" s="8">
-        <v>44335414206.19</v>
+        <v>44316728794.72</v>
       </c>
       <c r="F280" s="9">
-        <v>673252</v>
+        <v>673696</v>
       </c>
       <c r="G280" s="8">
-        <v>32855773589.13</v>
+        <v>32014587232.76</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -9240,19 +9236,19 @@
         <v>562</v>
       </c>
       <c r="C281" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D281" s="10">
-        <v>0.26133</v>
+        <v>46141</v>
+      </c>
+      <c r="D281" s="7">
+        <v>0.260639</v>
       </c>
       <c r="E281" s="8">
-        <v>8726275298.67</v>
+        <v>8738878558.88</v>
       </c>
       <c r="F281" s="9">
-        <v>108642</v>
+        <v>108579</v>
       </c>
       <c r="G281" s="8">
-        <v>2280438449.74</v>
+        <v>2277691941.16</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -9263,19 +9259,19 @@
         <v>564</v>
       </c>
       <c r="C282" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D282" s="7">
-        <v>0.535807</v>
+        <v>0.529558</v>
       </c>
       <c r="E282" s="8">
-        <v>11580933959.74</v>
+        <v>11605363993.96</v>
       </c>
       <c r="F282" s="9">
-        <v>138947</v>
+        <v>138971</v>
       </c>
       <c r="G282" s="8">
-        <v>6205148580.76</v>
+        <v>6145718554.64</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -9286,19 +9282,19 @@
         <v>566</v>
       </c>
       <c r="C283" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D283" s="7">
-        <v>0.305804</v>
+        <v>0.301243</v>
       </c>
       <c r="E283" s="8">
-        <v>2286269921.57</v>
+        <v>2288387573.72</v>
       </c>
       <c r="F283" s="9">
-        <v>37409</v>
+        <v>37408</v>
       </c>
       <c r="G283" s="8">
-        <v>699149485.62</v>
+        <v>689359731.08</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -9309,19 +9305,19 @@
         <v>568</v>
       </c>
       <c r="C284" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D284" s="10">
-        <v>0.19673</v>
+        <v>46141</v>
+      </c>
+      <c r="D284" s="7">
+        <v>0.196737</v>
       </c>
       <c r="E284" s="8">
-        <v>9505397484.23</v>
+        <v>9520104601.01</v>
       </c>
       <c r="F284" s="9">
-        <v>108304</v>
+        <v>108282</v>
       </c>
       <c r="G284" s="8">
-        <v>1869994432.28</v>
+        <v>1872957847.09</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -9332,19 +9328,19 @@
         <v>570</v>
       </c>
       <c r="C285" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D285" s="7">
-        <v>0.276981</v>
+        <v>0.274903</v>
       </c>
       <c r="E285" s="8">
-        <v>788500373.54</v>
+        <v>787815582.88</v>
       </c>
       <c r="F285" s="9">
-        <v>2812</v>
+        <v>2807</v>
       </c>
       <c r="G285" s="8">
-        <v>218399510.27</v>
+        <v>216572937.77</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -9355,19 +9351,19 @@
         <v>572</v>
       </c>
       <c r="C286" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D286" s="7">
-        <v>0.087249</v>
+        <v>0.087341</v>
       </c>
       <c r="E286" s="8">
-        <v>4189488298.4</v>
+        <v>4171921319.57</v>
       </c>
       <c r="F286" s="9">
-        <v>146098</v>
+        <v>145692</v>
       </c>
       <c r="G286" s="8">
-        <v>365529430.19</v>
+        <v>364378737.81</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -9378,19 +9374,19 @@
         <v>574</v>
       </c>
       <c r="C287" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D287" s="7">
-        <v>0.476551</v>
+        <v>0.472332</v>
       </c>
       <c r="E287" s="8">
-        <v>1574374540.64</v>
+        <v>1574639738.39</v>
       </c>
       <c r="F287" s="9">
-        <v>4273</v>
+        <v>4274</v>
       </c>
       <c r="G287" s="8">
-        <v>750268984.21</v>
+        <v>743752642.69</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -9401,19 +9397,19 @@
         <v>576</v>
       </c>
       <c r="C288" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D288" s="7">
-        <v>0.015597</v>
+        <v>46141</v>
+      </c>
+      <c r="D288" s="11">
+        <v>0.0155</v>
       </c>
       <c r="E288" s="8">
-        <v>5663123564.2</v>
+        <v>5656365496.91</v>
       </c>
       <c r="F288" s="9">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="G288" s="8">
-        <v>88326538.47</v>
+        <v>87671054.97</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -9424,19 +9420,19 @@
         <v>578</v>
       </c>
       <c r="C289" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D289" s="7">
-        <v>0.017744</v>
+        <v>0.017321</v>
       </c>
       <c r="E289" s="8">
-        <v>154130751682.73</v>
+        <v>152483264046.77</v>
       </c>
       <c r="F289" s="9">
-        <v>31735</v>
+        <v>31715</v>
       </c>
       <c r="G289" s="8">
-        <v>2734829867.06</v>
+        <v>2641108578.27</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -9447,19 +9443,19 @@
         <v>580</v>
       </c>
       <c r="C290" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D290" s="7">
-        <v>0.010737</v>
+        <v>0.010584</v>
       </c>
       <c r="E290" s="8">
-        <v>5515358418</v>
+        <v>6055906905.09</v>
       </c>
       <c r="F290" s="9">
         <v>933</v>
       </c>
       <c r="G290" s="8">
-        <v>59219488.76</v>
+        <v>64094960.41</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -9470,19 +9466,19 @@
         <v>582</v>
       </c>
       <c r="C291" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D291" s="7">
-        <v>0.135175</v>
+        <v>0.132272</v>
       </c>
       <c r="E291" s="8">
-        <v>52976783138.85</v>
+        <v>52919291646.02</v>
       </c>
       <c r="F291" s="9">
-        <v>107819</v>
+        <v>107862</v>
       </c>
       <c r="G291" s="8">
-        <v>7161123315.51</v>
+        <v>6999744863.81</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -9493,19 +9489,19 @@
         <v>584</v>
       </c>
       <c r="C292" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D292" s="10">
-        <v>0.05088</v>
+        <v>46141</v>
+      </c>
+      <c r="D292" s="7">
+        <v>0.050936</v>
       </c>
       <c r="E292" s="8">
-        <v>12182372020.99</v>
+        <v>12218901995.93</v>
       </c>
       <c r="F292" s="9">
-        <v>28395</v>
+        <v>28478</v>
       </c>
       <c r="G292" s="8">
-        <v>619841225.67</v>
+        <v>622379548.89</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -9516,19 +9512,19 @@
         <v>586</v>
       </c>
       <c r="C293" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D293" s="10">
-        <v>0.02189</v>
+        <v>46141</v>
+      </c>
+      <c r="D293" s="7">
+        <v>0.021911</v>
       </c>
       <c r="E293" s="8">
-        <v>56235227997.55</v>
+        <v>56148025020.09</v>
       </c>
       <c r="F293" s="9">
-        <v>10733</v>
+        <v>10722</v>
       </c>
       <c r="G293" s="8">
-        <v>1230973334.67</v>
+        <v>1230276642.43</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -9539,19 +9535,19 @@
         <v>588</v>
       </c>
       <c r="C294" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D294" s="7">
-        <v>0.031431</v>
+        <v>0.031162</v>
       </c>
       <c r="E294" s="8">
-        <v>54351059648.01</v>
+        <v>54560224838.31</v>
       </c>
       <c r="F294" s="9">
-        <v>33034</v>
+        <v>33109</v>
       </c>
       <c r="G294" s="8">
-        <v>1708295002.51</v>
+        <v>1700220746.88</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -9562,19 +9558,19 @@
         <v>590</v>
       </c>
       <c r="C295" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D295" s="7">
-        <v>0.019694</v>
+        <v>0.019247</v>
       </c>
       <c r="E295" s="8">
-        <v>970642249513.15</v>
+        <v>967605521962.45</v>
       </c>
       <c r="F295" s="9">
-        <v>179357</v>
+        <v>179400</v>
       </c>
       <c r="G295" s="8">
-        <v>19115577633.87</v>
+        <v>18623671053.2</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -9585,19 +9581,19 @@
         <v>592</v>
       </c>
       <c r="C296" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D296" s="7">
-        <v>0.101677</v>
+        <v>0.101132</v>
       </c>
       <c r="E296" s="8">
-        <v>37129964256.44</v>
+        <v>37094236482.2</v>
       </c>
       <c r="F296" s="9">
-        <v>382867</v>
+        <v>382744</v>
       </c>
       <c r="G296" s="8">
-        <v>3775273904.46</v>
+        <v>3751431152.15</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -9608,19 +9604,19 @@
         <v>594</v>
       </c>
       <c r="C297" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D297" s="7">
-        <v>0.086256</v>
+        <v>0.085904</v>
       </c>
       <c r="E297" s="8">
-        <v>38495944349.28</v>
+        <v>38426944921.22</v>
       </c>
       <c r="F297" s="9">
-        <v>48302</v>
+        <v>48212</v>
       </c>
       <c r="G297" s="8">
-        <v>3320524516.08</v>
+        <v>3301024521.17</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -9631,19 +9627,19 @@
         <v>596</v>
       </c>
       <c r="C298" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D298" s="7">
-        <v>0.094407</v>
+        <v>0.094154</v>
       </c>
       <c r="E298" s="8">
-        <v>39233721664.46</v>
+        <v>39136096470.62</v>
       </c>
       <c r="F298" s="9">
-        <v>527807</v>
+        <v>527622</v>
       </c>
       <c r="G298" s="8">
-        <v>3703922542.66</v>
+        <v>3684837734.26</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -9654,19 +9650,19 @@
         <v>598</v>
       </c>
       <c r="C299" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D299" s="7">
-        <v>0.020101</v>
+        <v>0.020004</v>
       </c>
       <c r="E299" s="8">
-        <v>33837634121.36</v>
+        <v>34406609096.89</v>
       </c>
       <c r="F299" s="9">
-        <v>24549</v>
+        <v>24738</v>
       </c>
       <c r="G299" s="8">
-        <v>680159938.24</v>
+        <v>688260245.26</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -9677,19 +9673,19 @@
         <v>600</v>
       </c>
       <c r="C300" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D300" s="7">
-        <v>0.010255</v>
+        <v>0.010262</v>
       </c>
       <c r="E300" s="8">
-        <v>1822011246.93</v>
+        <v>2048890132.37</v>
       </c>
       <c r="F300" s="9">
         <v>436</v>
       </c>
       <c r="G300" s="8">
-        <v>18684400.88</v>
+        <v>21026155.28</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -9700,19 +9696,19 @@
         <v>602</v>
       </c>
       <c r="C301" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D301" s="10">
-        <v>0.01532</v>
+        <v>46141</v>
+      </c>
+      <c r="D301" s="7">
+        <v>0.015178</v>
       </c>
       <c r="E301" s="8">
-        <v>23740582083.79</v>
+        <v>23792394381.58</v>
       </c>
       <c r="F301" s="9">
-        <v>10924</v>
+        <v>10946</v>
       </c>
       <c r="G301" s="8">
-        <v>363716663.95</v>
+        <v>361130266.38</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -9723,19 +9719,19 @@
         <v>604</v>
       </c>
       <c r="C302" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D302" s="7">
-        <v>0.017914</v>
+        <v>0.017716</v>
       </c>
       <c r="E302" s="8">
-        <v>11918703897.44</v>
+        <v>11889133333.05</v>
       </c>
       <c r="F302" s="9">
-        <v>6673</v>
+        <v>6664</v>
       </c>
       <c r="G302" s="8">
-        <v>213517250.73</v>
+        <v>210627519.99</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -9746,19 +9742,19 @@
         <v>606</v>
       </c>
       <c r="C303" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D303" s="11">
-        <v>0.094</v>
+        <v>46141</v>
+      </c>
+      <c r="D303" s="7">
+        <v>0.093968</v>
       </c>
       <c r="E303" s="8">
-        <v>21296679115.61</v>
+        <v>21287606753.8</v>
       </c>
       <c r="F303" s="9">
-        <v>347541</v>
+        <v>347503</v>
       </c>
       <c r="G303" s="8">
-        <v>2001888664.41</v>
+        <v>2000351717.98</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -9769,19 +9765,19 @@
         <v>608</v>
       </c>
       <c r="C304" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D304" s="7">
-        <v>0.019045</v>
+        <v>0.018851</v>
       </c>
       <c r="E304" s="8">
-        <v>10409323616.04</v>
+        <v>10528013632.95</v>
       </c>
       <c r="F304" s="9">
         <v>514</v>
       </c>
       <c r="G304" s="8">
-        <v>198247436.51</v>
+        <v>198467214.54</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -9792,19 +9788,19 @@
         <v>610</v>
       </c>
       <c r="C305" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D305" s="7">
-        <v>0.015711</v>
+        <v>0.015561</v>
       </c>
       <c r="E305" s="8">
-        <v>9126815577.66</v>
+        <v>9151732155.5</v>
       </c>
       <c r="F305" s="9">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G305" s="8">
-        <v>143390871.91</v>
+        <v>142414615.18</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -9815,19 +9811,19 @@
         <v>612</v>
       </c>
       <c r="C306" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D306" s="7">
-        <v>0.015794</v>
+        <v>46141</v>
+      </c>
+      <c r="D306" s="11">
+        <v>0.0158</v>
       </c>
       <c r="E306" s="8">
-        <v>1017516255.19</v>
+        <v>1225480970.93</v>
       </c>
       <c r="F306" s="9">
         <v>23</v>
       </c>
       <c r="G306" s="8">
-        <v>16070477.41</v>
+        <v>19362749.4</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -9838,19 +9834,19 @@
         <v>614</v>
       </c>
       <c r="C307" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D307" s="10">
-        <v>0.23318</v>
+        <v>46141</v>
+      </c>
+      <c r="D307" s="7">
+        <v>0.228535</v>
       </c>
       <c r="E307" s="8">
-        <v>48675245106.98</v>
+        <v>48694341558.91</v>
       </c>
       <c r="F307" s="9">
-        <v>174352</v>
+        <v>174379</v>
       </c>
       <c r="G307" s="8">
-        <v>11350099215.48</v>
+        <v>11128372467.53</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -9861,19 +9857,19 @@
         <v>616</v>
       </c>
       <c r="C308" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D308" s="7">
-        <v>0.011205</v>
+        <v>0.011147</v>
       </c>
       <c r="E308" s="8">
-        <v>2097192071.25</v>
+        <v>2104823064.42</v>
       </c>
       <c r="F308" s="9">
-        <v>1900</v>
+        <v>1915</v>
       </c>
       <c r="G308" s="8">
-        <v>23500038.33</v>
+        <v>23461850.64</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -9884,19 +9880,19 @@
         <v>618</v>
       </c>
       <c r="C309" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D309" s="7">
-        <v>0.028806</v>
+        <v>0.028694</v>
       </c>
       <c r="E309" s="8">
-        <v>12282710470.9</v>
+        <v>12302451976.36</v>
       </c>
       <c r="F309" s="9">
-        <v>17286</v>
+        <v>17327</v>
       </c>
       <c r="G309" s="8">
-        <v>353818110.05</v>
+        <v>353005759.87</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -9907,19 +9903,19 @@
         <v>620</v>
       </c>
       <c r="C310" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D310" s="7">
-        <v>0.024891</v>
+        <v>0.024743</v>
       </c>
       <c r="E310" s="8">
-        <v>2937465075.83</v>
+        <v>2948902539.48</v>
       </c>
       <c r="F310" s="9">
-        <v>10190</v>
+        <v>10201</v>
       </c>
       <c r="G310" s="8">
-        <v>73115769.63</v>
+        <v>72963851.68</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -9930,19 +9926,19 @@
         <v>622</v>
       </c>
       <c r="C311" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D311" s="7">
-        <v>0.122608</v>
+        <v>0.121808</v>
       </c>
       <c r="E311" s="8">
-        <v>611735126.04</v>
+        <v>611138919.5</v>
       </c>
       <c r="F311" s="9">
-        <v>92425</v>
+        <v>92410</v>
       </c>
       <c r="G311" s="8">
-        <v>75003605.5</v>
+        <v>74441606.74</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -9953,19 +9949,19 @@
         <v>624</v>
       </c>
       <c r="C312" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D312" s="7">
-        <v>0.090309</v>
+        <v>0.090392</v>
       </c>
       <c r="E312" s="8">
-        <v>1349027661.83</v>
+        <v>1339390737.37</v>
       </c>
       <c r="F312" s="9">
-        <v>25171</v>
+        <v>25058</v>
       </c>
       <c r="G312" s="8">
-        <v>121829212.15</v>
+        <v>121070409.54</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -9976,19 +9972,19 @@
         <v>626</v>
       </c>
       <c r="C313" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D313" s="7">
-        <v>0.079895</v>
+        <v>0.079951</v>
       </c>
       <c r="E313" s="8">
-        <v>2374415168.74</v>
+        <v>2367582651.71</v>
       </c>
       <c r="F313" s="9">
-        <v>75019</v>
+        <v>74867</v>
       </c>
       <c r="G313" s="8">
-        <v>189704060.58</v>
+        <v>189290672.08</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -9999,19 +9995,19 @@
         <v>628</v>
       </c>
       <c r="C314" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D314" s="7">
-        <v>0.387835</v>
+        <v>0.387426</v>
       </c>
       <c r="E314" s="8">
-        <v>5200274187.12</v>
+        <v>5201816524.95</v>
       </c>
       <c r="F314" s="9">
-        <v>71709</v>
+        <v>71687</v>
       </c>
       <c r="G314" s="8">
-        <v>2016845872.11</v>
+        <v>2015321195.43</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -10022,19 +10018,19 @@
         <v>630</v>
       </c>
       <c r="C315" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D315" s="7">
-        <v>0.204997</v>
+        <v>0.204838</v>
       </c>
       <c r="E315" s="8">
-        <v>5826946681.57</v>
+        <v>5826448523.99</v>
       </c>
       <c r="F315" s="9">
         <v>56501</v>
       </c>
       <c r="G315" s="8">
-        <v>1194508439.98</v>
+        <v>1193480007.19</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -10045,19 +10041,19 @@
         <v>632</v>
       </c>
       <c r="C316" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D316" s="7">
-        <v>0.112556</v>
+        <v>0.112067</v>
       </c>
       <c r="E316" s="8">
-        <v>2290854776.19</v>
+        <v>2289541748.35</v>
       </c>
       <c r="F316" s="9">
-        <v>8353</v>
+        <v>8346</v>
       </c>
       <c r="G316" s="8">
-        <v>257848918.33</v>
+        <v>256580967.56</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -10068,19 +10064,19 @@
         <v>634</v>
       </c>
       <c r="C317" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D317" s="7">
-        <v>0.558197</v>
+        <v>0.548666</v>
       </c>
       <c r="E317" s="8">
-        <v>3980018656.9</v>
+        <v>3983183813.85</v>
       </c>
       <c r="F317" s="9">
-        <v>50403</v>
+        <v>50416</v>
       </c>
       <c r="G317" s="8">
-        <v>2221635026.71</v>
+        <v>2185436990.11</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -10091,19 +10087,19 @@
         <v>636</v>
       </c>
       <c r="C318" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D318" s="7">
-        <v>0.084613</v>
+        <v>0.084404</v>
       </c>
       <c r="E318" s="8">
-        <v>8864130074.77</v>
+        <v>8853817244.09</v>
       </c>
       <c r="F318" s="9">
-        <v>188191</v>
+        <v>188136</v>
       </c>
       <c r="G318" s="8">
-        <v>750017611.56</v>
+        <v>747297997.05</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -10114,19 +10110,19 @@
         <v>638</v>
       </c>
       <c r="C319" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D319" s="7">
-        <v>0.109256</v>
+        <v>0.108464</v>
       </c>
       <c r="E319" s="8">
-        <v>23097358561.01</v>
+        <v>23103713481.23</v>
       </c>
       <c r="F319" s="9">
-        <v>138055</v>
+        <v>138028</v>
       </c>
       <c r="G319" s="8">
-        <v>2523516980.41</v>
+        <v>2505919583.81</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -10137,19 +10133,19 @@
         <v>640</v>
       </c>
       <c r="C320" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D320" s="7">
-        <v>0.150923</v>
+        <v>0.151062</v>
       </c>
       <c r="E320" s="8">
-        <v>13264219501.72</v>
+        <v>13096809631.03</v>
       </c>
       <c r="F320" s="9">
-        <v>43693</v>
+        <v>33366</v>
       </c>
       <c r="G320" s="8">
-        <v>2001872211.07</v>
+        <v>1978436317.01</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -10160,19 +10156,19 @@
         <v>642</v>
       </c>
       <c r="C321" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D321" s="7">
-        <v>0.133031</v>
+        <v>0.132731</v>
       </c>
       <c r="E321" s="8">
-        <v>527825190.24</v>
+        <v>526651989.45</v>
       </c>
       <c r="F321" s="9">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G321" s="8">
-        <v>70216966.26</v>
+        <v>69902833.79</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -10183,19 +10179,19 @@
         <v>644</v>
       </c>
       <c r="C322" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D322" s="7">
-        <v>0.137701</v>
+        <v>0.136493</v>
       </c>
       <c r="E322" s="8">
-        <v>225013949.54</v>
+        <v>225378524.35</v>
       </c>
       <c r="F322" s="9">
         <v>416</v>
       </c>
       <c r="G322" s="8">
-        <v>30984664.62</v>
+        <v>30762531.77</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -10206,19 +10202,19 @@
         <v>646</v>
       </c>
       <c r="C323" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D323" s="10">
-        <v>0.16855</v>
+        <v>46141</v>
+      </c>
+      <c r="D323" s="7">
+        <v>0.166641</v>
       </c>
       <c r="E323" s="8">
-        <v>295704426.41</v>
+        <v>296335531.53</v>
       </c>
       <c r="F323" s="9">
         <v>527</v>
       </c>
       <c r="G323" s="8">
-        <v>49840868.25</v>
+        <v>49381683.57</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -10229,19 +10225,19 @@
         <v>648</v>
       </c>
       <c r="C324" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D324" s="7">
-        <v>0.200566</v>
+        <v>0.197673</v>
       </c>
       <c r="E324" s="8">
-        <v>359917126.39</v>
+        <v>359848968.94</v>
       </c>
       <c r="F324" s="9">
         <v>595</v>
       </c>
       <c r="G324" s="8">
-        <v>72187315.26</v>
+        <v>71132483.57</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -10252,19 +10248,19 @@
         <v>650</v>
       </c>
       <c r="C325" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D325" s="7">
-        <v>0.141178</v>
+        <v>0.140784</v>
       </c>
       <c r="E325" s="8">
-        <v>412261535.92</v>
+        <v>412825700.69</v>
       </c>
       <c r="F325" s="9">
-        <v>2029</v>
+        <v>2038</v>
       </c>
       <c r="G325" s="8">
-        <v>58202354.2</v>
+        <v>58119121.96</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -10275,19 +10271,19 @@
         <v>652</v>
       </c>
       <c r="C326" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D326" s="7">
-        <v>0.098676</v>
+        <v>0.097541</v>
       </c>
       <c r="E326" s="8">
-        <v>40071742924.08</v>
+        <v>40035656762.98</v>
       </c>
       <c r="F326" s="9">
-        <v>367796</v>
+        <v>367630</v>
       </c>
       <c r="G326" s="8">
-        <v>3954117544.13</v>
+        <v>3905117419.72</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -10298,19 +10294,19 @@
         <v>654</v>
       </c>
       <c r="C327" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D327" s="7">
-        <v>0.172389</v>
+        <v>0.170914</v>
       </c>
       <c r="E327" s="8">
-        <v>192282968.83</v>
+        <v>192585616.64</v>
       </c>
       <c r="F327" s="9">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="G327" s="8">
-        <v>33147563.71</v>
+        <v>32915532.33</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -10321,19 +10317,19 @@
         <v>656</v>
       </c>
       <c r="C328" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D328" s="7">
-        <v>0.202224</v>
+        <v>46141</v>
+      </c>
+      <c r="D328" s="10">
+        <v>0.20018</v>
       </c>
       <c r="E328" s="8">
-        <v>238829783.26</v>
+        <v>239051169.55</v>
       </c>
       <c r="F328" s="9">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="G328" s="8">
-        <v>48297163.34</v>
+        <v>47853162.59</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -10344,19 +10340,19 @@
         <v>658</v>
       </c>
       <c r="C329" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D329" s="7">
-        <v>0.293045</v>
+        <v>0.290344</v>
       </c>
       <c r="E329" s="8">
-        <v>1253301934.94</v>
+        <v>1254197087.51</v>
       </c>
       <c r="F329" s="9">
-        <v>8767</v>
+        <v>8755</v>
       </c>
       <c r="G329" s="8">
-        <v>367274275.3</v>
+        <v>364148828.92</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -10367,19 +10363,19 @@
         <v>660</v>
       </c>
       <c r="C330" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D330" s="10">
-        <v>0.09234</v>
+        <v>46141</v>
+      </c>
+      <c r="D330" s="7">
+        <v>0.091782</v>
       </c>
       <c r="E330" s="8">
-        <v>6843135481.29</v>
+        <v>6844986440.23</v>
       </c>
       <c r="F330" s="9">
-        <v>123280</v>
+        <v>123353</v>
       </c>
       <c r="G330" s="8">
-        <v>631892047.62</v>
+        <v>628249831</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
@@ -10390,19 +10386,19 @@
         <v>662</v>
       </c>
       <c r="C331" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D331" s="7">
-        <v>0.074245</v>
+        <v>0.073537</v>
       </c>
       <c r="E331" s="8">
-        <v>102998781692.14</v>
+        <v>103236066790.69</v>
       </c>
       <c r="F331" s="9">
-        <v>147797</v>
+        <v>148066</v>
       </c>
       <c r="G331" s="8">
-        <v>7647176245.77</v>
+        <v>7591624940.83</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
@@ -10413,19 +10409,19 @@
         <v>664</v>
       </c>
       <c r="C332" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D332" s="7">
-        <v>0.065807</v>
+        <v>46141</v>
+      </c>
+      <c r="D332" s="10">
+        <v>0.06525</v>
       </c>
       <c r="E332" s="8">
-        <v>111232569103.78</v>
+        <v>111366672380.88</v>
       </c>
       <c r="F332" s="9">
-        <v>99107</v>
+        <v>99261</v>
       </c>
       <c r="G332" s="8">
-        <v>7319838446.05</v>
+        <v>7266699757.48</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
@@ -10436,19 +10432,19 @@
         <v>666</v>
       </c>
       <c r="C333" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D333" s="7">
-        <v>0.086561</v>
+        <v>0.085621</v>
       </c>
       <c r="E333" s="8">
-        <v>64580514450.25</v>
+        <v>64778912888.54</v>
       </c>
       <c r="F333" s="9">
-        <v>122815</v>
+        <v>122984</v>
       </c>
       <c r="G333" s="8">
-        <v>5590126321.32</v>
+        <v>5546440378.12</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
@@ -10459,19 +10455,19 @@
         <v>668</v>
       </c>
       <c r="C334" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D334" s="7">
-        <v>0.459731</v>
+        <v>0.448193</v>
       </c>
       <c r="E334" s="8">
-        <v>52581597529.82</v>
+        <v>52565706477.75</v>
       </c>
       <c r="F334" s="9">
-        <v>127188</v>
+        <v>127094</v>
       </c>
       <c r="G334" s="8">
-        <v>24173412679.75</v>
+        <v>23559581559.43</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
@@ -10482,19 +10478,19 @@
         <v>670</v>
       </c>
       <c r="C335" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D335" s="10">
-        <v>0.09824</v>
+        <v>46141</v>
+      </c>
+      <c r="D335" s="7">
+        <v>0.098462</v>
       </c>
       <c r="E335" s="8">
-        <v>5281969048.38</v>
+        <v>5285506881.7</v>
       </c>
       <c r="F335" s="9">
-        <v>8805</v>
+        <v>8802</v>
       </c>
       <c r="G335" s="8">
-        <v>518899229.33</v>
+        <v>520422319.34</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
@@ -10505,19 +10501,19 @@
         <v>672</v>
       </c>
       <c r="C336" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D336" s="7">
-        <v>0.358448</v>
+        <v>0.352613</v>
       </c>
       <c r="E336" s="8">
-        <v>15868917882.77</v>
+        <v>15879804609.8</v>
       </c>
       <c r="F336" s="9">
         <v>28637</v>
       </c>
       <c r="G336" s="8">
-        <v>5688179148.97</v>
+        <v>5599432290.32</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
@@ -10528,19 +10524,19 @@
         <v>674</v>
       </c>
       <c r="C337" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D337" s="7">
-        <v>0.010335</v>
+        <v>0.010145</v>
       </c>
       <c r="E337" s="8">
-        <v>75247307912.35</v>
+        <v>75180104936.98</v>
       </c>
       <c r="F337" s="9">
-        <v>4116</v>
+        <v>4166</v>
       </c>
       <c r="G337" s="8">
-        <v>777683822.25</v>
+        <v>762692353.35</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
@@ -10551,19 +10547,19 @@
         <v>676</v>
       </c>
       <c r="C338" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D338" s="7">
-        <v>0.081447</v>
+        <v>0.081496</v>
       </c>
       <c r="E338" s="8">
-        <v>3721884349.94</v>
+        <v>3722348905.29</v>
       </c>
       <c r="F338" s="9">
-        <v>78652</v>
+        <v>78569</v>
       </c>
       <c r="G338" s="8">
-        <v>303135265.68</v>
+        <v>303354857.12</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
@@ -10574,19 +10570,19 @@
         <v>678</v>
       </c>
       <c r="C339" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D339" s="10">
-        <v>0.09105</v>
+        <v>46141</v>
+      </c>
+      <c r="D339" s="7">
+        <v>0.091137</v>
       </c>
       <c r="E339" s="8">
-        <v>633025355.74</v>
+        <v>625914567.67</v>
       </c>
       <c r="F339" s="9">
-        <v>12555</v>
+        <v>12385</v>
       </c>
       <c r="G339" s="8">
-        <v>57637072.87</v>
+        <v>57043815.06</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
@@ -10597,19 +10593,19 @@
         <v>680</v>
       </c>
       <c r="C340" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D340" s="10">
-        <v>0.04294</v>
+        <v>46141</v>
+      </c>
+      <c r="D340" s="7">
+        <v>0.042707</v>
       </c>
       <c r="E340" s="8">
-        <v>1025088784.38</v>
+        <v>1030234085.7</v>
       </c>
       <c r="F340" s="9">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="G340" s="8">
-        <v>44017425.65</v>
+        <v>43998190.31</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -10620,19 +10616,19 @@
         <v>682</v>
       </c>
       <c r="C341" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D341" s="7">
-        <v>0.050019</v>
+        <v>0.049836</v>
       </c>
       <c r="E341" s="8">
-        <v>3910411639.38</v>
+        <v>3915346264.31</v>
       </c>
       <c r="F341" s="9">
-        <v>4276</v>
+        <v>4282</v>
       </c>
       <c r="G341" s="8">
-        <v>195595053.35</v>
+        <v>195123396.42</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
@@ -10643,19 +10639,19 @@
         <v>684</v>
       </c>
       <c r="C342" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D342" s="7">
-        <v>0.014122</v>
+        <v>0.013905</v>
       </c>
       <c r="E342" s="8">
-        <v>34435002007.46</v>
+        <v>34705570611.52</v>
       </c>
       <c r="F342" s="9">
-        <v>26741</v>
+        <v>27046</v>
       </c>
       <c r="G342" s="8">
-        <v>486292511.52</v>
+        <v>482564124.25</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
@@ -10666,19 +10662,19 @@
         <v>686</v>
       </c>
       <c r="C343" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D343" s="7">
-        <v>0.071579</v>
+        <v>0.071035</v>
       </c>
       <c r="E343" s="8">
-        <v>46382703478.87</v>
+        <v>46965104245.68</v>
       </c>
       <c r="F343" s="9">
-        <v>119466</v>
+        <v>119940</v>
       </c>
       <c r="G343" s="8">
-        <v>3320028931.97</v>
+        <v>3336182749.53</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
@@ -10689,19 +10685,19 @@
         <v>688</v>
       </c>
       <c r="C344" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D344" s="7">
-        <v>0.012712</v>
+        <v>0.012727</v>
       </c>
       <c r="E344" s="8">
-        <v>14493830541.93</v>
+        <v>14608944241.5</v>
       </c>
       <c r="F344" s="9">
-        <v>5250</v>
+        <v>5299</v>
       </c>
       <c r="G344" s="8">
-        <v>184246739.46</v>
+        <v>185927685.3</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
@@ -10712,19 +10708,19 @@
         <v>690</v>
       </c>
       <c r="C345" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D345" s="7">
-        <v>0.014752</v>
+        <v>46141</v>
+      </c>
+      <c r="D345" s="10">
+        <v>0.01477</v>
       </c>
       <c r="E345" s="8">
-        <v>67436749344.36</v>
+        <v>68525006981.54</v>
       </c>
       <c r="F345" s="9">
-        <v>18219</v>
+        <v>18343</v>
       </c>
       <c r="G345" s="8">
-        <v>994819919.55</v>
+        <v>1012089371.53</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
@@ -10735,19 +10731,19 @@
         <v>692</v>
       </c>
       <c r="C346" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D346" s="7">
-        <v>0.049557</v>
+        <v>0.049537</v>
       </c>
       <c r="E346" s="8">
-        <v>7316107766.75</v>
+        <v>7340426206.33</v>
       </c>
       <c r="F346" s="9">
-        <v>9323</v>
+        <v>9334</v>
       </c>
       <c r="G346" s="8">
-        <v>362567230.53</v>
+        <v>363622186.5</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
@@ -10758,19 +10754,19 @@
         <v>694</v>
       </c>
       <c r="C347" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D347" s="7">
-        <v>0.086373</v>
+        <v>0.086462</v>
       </c>
       <c r="E347" s="8">
-        <v>594648586.95</v>
+        <v>592289695.11</v>
       </c>
       <c r="F347" s="9">
-        <v>6997</v>
+        <v>6990</v>
       </c>
       <c r="G347" s="8">
-        <v>51361679.26</v>
+        <v>51210559.52</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
@@ -10781,19 +10777,19 @@
         <v>696</v>
       </c>
       <c r="C348" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D348" s="7">
-        <v>0.049061</v>
+        <v>0.048876</v>
       </c>
       <c r="E348" s="8">
-        <v>3911879612.09</v>
+        <v>3904236858.64</v>
       </c>
       <c r="F348" s="9">
-        <v>5953</v>
+        <v>5945</v>
       </c>
       <c r="G348" s="8">
-        <v>191920682.55</v>
+        <v>190822942.54</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
@@ -10804,19 +10800,19 @@
         <v>698</v>
       </c>
       <c r="C349" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D349" s="7">
-        <v>0.020576</v>
+        <v>0.020358</v>
       </c>
       <c r="E349" s="8">
-        <v>8696617488.68</v>
+        <v>8719942439.6</v>
       </c>
       <c r="F349" s="9">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G349" s="8">
-        <v>178939360.85</v>
+        <v>177516329.06</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
@@ -10827,19 +10823,19 @@
         <v>700</v>
       </c>
       <c r="C350" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D350" s="7">
-        <v>0.015225</v>
+        <v>0.015094</v>
       </c>
       <c r="E350" s="8">
-        <v>15530635539.16</v>
+        <v>15638325199.75</v>
       </c>
       <c r="F350" s="9">
-        <v>5835</v>
+        <v>5860</v>
       </c>
       <c r="G350" s="8">
-        <v>236459424.16</v>
+        <v>236050722.12</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
@@ -10850,19 +10846,19 @@
         <v>702</v>
       </c>
       <c r="C351" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D351" s="7">
-        <v>0.013757</v>
+        <v>0.013651</v>
       </c>
       <c r="E351" s="8">
-        <v>22037722144.37</v>
+        <v>22118244625.32</v>
       </c>
       <c r="F351" s="9">
-        <v>5596</v>
+        <v>5658</v>
       </c>
       <c r="G351" s="8">
-        <v>303164161.61</v>
+        <v>301944977.49</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -10873,19 +10869,19 @@
         <v>704</v>
       </c>
       <c r="C352" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D352" s="7">
-        <v>0.014259</v>
+        <v>0.014302</v>
       </c>
       <c r="E352" s="8">
-        <v>23293839112.68</v>
+        <v>23344622697.7</v>
       </c>
       <c r="F352" s="9">
         <v>10558</v>
       </c>
       <c r="G352" s="8">
-        <v>332151663.81</v>
+        <v>333866920.41</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -10896,19 +10892,19 @@
         <v>706</v>
       </c>
       <c r="C353" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D353" s="7">
-        <v>0.015218</v>
+        <v>0.015135</v>
       </c>
       <c r="E353" s="8">
-        <v>36588334333.84</v>
+        <v>37084866595.72</v>
       </c>
       <c r="F353" s="9">
-        <v>9961</v>
+        <v>10073</v>
       </c>
       <c r="G353" s="8">
-        <v>556798002.93</v>
+        <v>561288454.05</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
@@ -10919,19 +10915,19 @@
         <v>708</v>
       </c>
       <c r="C354" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D354" s="10">
-        <v>0.04928</v>
+        <v>46141</v>
+      </c>
+      <c r="D354" s="7">
+        <v>0.049044</v>
       </c>
       <c r="E354" s="8">
-        <v>2913735442.17</v>
+        <v>2914716422.01</v>
       </c>
       <c r="F354" s="9">
-        <v>5170</v>
+        <v>5161</v>
       </c>
       <c r="G354" s="8">
-        <v>143588263.07</v>
+        <v>142948642.81</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -10942,19 +10938,19 @@
         <v>710</v>
       </c>
       <c r="C355" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D355" s="7">
-        <v>0.226347</v>
+        <v>0.224354</v>
       </c>
       <c r="E355" s="8">
-        <v>8775157111.01</v>
+        <v>8768430381.82</v>
       </c>
       <c r="F355" s="9">
-        <v>47712</v>
+        <v>47724</v>
       </c>
       <c r="G355" s="8">
-        <v>1986227276.2</v>
+        <v>1967234418.36</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
@@ -10965,19 +10961,19 @@
         <v>712</v>
       </c>
       <c r="C356" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D356" s="7">
-        <v>0.082345</v>
+        <v>46141</v>
+      </c>
+      <c r="D356" s="10">
+        <v>0.08246</v>
       </c>
       <c r="E356" s="8">
-        <v>11846151833.3</v>
+        <v>11838043704.35</v>
       </c>
       <c r="F356" s="9">
-        <v>21760</v>
+        <v>21777</v>
       </c>
       <c r="G356" s="8">
-        <v>975466898.8</v>
+        <v>976162396.79</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
@@ -10988,19 +10984,19 @@
         <v>714</v>
       </c>
       <c r="C357" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D357" s="10">
-        <v>0.30839</v>
+        <v>46141</v>
+      </c>
+      <c r="D357" s="7">
+        <v>0.306184</v>
       </c>
       <c r="E357" s="8">
-        <v>3861897679.02</v>
+        <v>3860070306.68</v>
       </c>
       <c r="F357" s="9">
-        <v>27637</v>
+        <v>27631</v>
       </c>
       <c r="G357" s="8">
-        <v>1190969176.58</v>
+        <v>1181892672.44</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
@@ -11011,19 +11007,19 @@
         <v>716</v>
       </c>
       <c r="C358" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D358" s="7">
-        <v>1.382147</v>
+        <v>1.361749</v>
       </c>
       <c r="E358" s="8">
-        <v>8831154245.18</v>
+        <v>8836793505.81</v>
       </c>
       <c r="F358" s="9">
-        <v>244811</v>
+        <v>244986</v>
       </c>
       <c r="G358" s="8">
-        <v>12205952945.28</v>
+        <v>12033495741.95</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
@@ -11034,19 +11030,19 @@
         <v>718</v>
       </c>
       <c r="C359" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D359" s="7">
-        <v>0.096512</v>
+        <v>46141</v>
+      </c>
+      <c r="D359" s="10">
+        <v>0.09541</v>
       </c>
       <c r="E359" s="8">
-        <v>534906820780.14</v>
+        <v>534556510216.54</v>
       </c>
       <c r="F359" s="9">
-        <v>2769500</v>
+        <v>2768465</v>
       </c>
       <c r="G359" s="8">
-        <v>51624959230.43</v>
+        <v>51002246886.36</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
@@ -11057,19 +11053,19 @@
         <v>720</v>
       </c>
       <c r="C360" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D360" s="12">
-        <v>0.3222</v>
+        <v>46141</v>
+      </c>
+      <c r="D360" s="7">
+        <v>0.320281</v>
       </c>
       <c r="E360" s="8">
-        <v>23892771297.09</v>
+        <v>23891533680.28</v>
       </c>
       <c r="F360" s="9">
-        <v>423549</v>
+        <v>423375</v>
       </c>
       <c r="G360" s="8">
-        <v>7698246794.35</v>
+        <v>7652007033.84</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
@@ -11080,19 +11076,19 @@
         <v>722</v>
       </c>
       <c r="C361" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D361" s="7">
-        <v>0.347947</v>
+        <v>0.348252</v>
       </c>
       <c r="E361" s="8">
-        <v>83179400115.47</v>
+        <v>83560559727.81</v>
       </c>
       <c r="F361" s="9">
-        <v>425118</v>
+        <v>403463</v>
       </c>
       <c r="G361" s="8">
-        <v>28941994323.8</v>
+        <v>29100106720.56</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
@@ -11103,19 +11099,19 @@
         <v>724</v>
       </c>
       <c r="C362" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D362" s="7">
-        <v>0.222188</v>
+        <v>46141</v>
+      </c>
+      <c r="D362" s="10">
+        <v>0.21881</v>
       </c>
       <c r="E362" s="8">
-        <v>20314820559.14</v>
+        <v>20334449230.39</v>
       </c>
       <c r="F362" s="9">
-        <v>69884</v>
+        <v>69970</v>
       </c>
       <c r="G362" s="8">
-        <v>4513715533.06</v>
+        <v>4449380564.87</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
@@ -11126,19 +11122,19 @@
         <v>726</v>
       </c>
       <c r="C363" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D363" s="7">
-        <v>0.101652</v>
+        <v>0.101545</v>
       </c>
       <c r="E363" s="8">
-        <v>3765539285.07</v>
+        <v>3762885950.77</v>
       </c>
       <c r="F363" s="9">
-        <v>8000</v>
+        <v>8003</v>
       </c>
       <c r="G363" s="8">
-        <v>382775659.2</v>
+        <v>382102490.98</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
@@ -11149,19 +11145,19 @@
         <v>728</v>
       </c>
       <c r="C364" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D364" s="7">
-        <v>0.136689</v>
+        <v>0.135264</v>
       </c>
       <c r="E364" s="8">
-        <v>102361259267.4</v>
+        <v>102311522397.07</v>
       </c>
       <c r="F364" s="9">
-        <v>1887748</v>
+        <v>1887274</v>
       </c>
       <c r="G364" s="8">
-        <v>13991631579.87</v>
+        <v>13839070696.36</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
@@ -11172,19 +11168,19 @@
         <v>730</v>
       </c>
       <c r="C365" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D365" s="7">
-        <v>0.135742</v>
+        <v>46141</v>
+      </c>
+      <c r="D365" s="10">
+        <v>0.13569</v>
       </c>
       <c r="E365" s="8">
-        <v>58260488455.76</v>
+        <v>58306716131.95</v>
       </c>
       <c r="F365" s="9">
-        <v>120062</v>
+        <v>120097</v>
       </c>
       <c r="G365" s="8">
-        <v>7908384229.32</v>
+        <v>7911664125.95</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
@@ -11195,19 +11191,19 @@
         <v>732</v>
       </c>
       <c r="C366" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D366" s="7">
-        <v>0.733663</v>
+        <v>0.732157</v>
       </c>
       <c r="E366" s="8">
-        <v>16788299653.05</v>
+        <v>16792838009.9</v>
       </c>
       <c r="F366" s="9">
-        <v>342141</v>
+        <v>342423</v>
       </c>
       <c r="G366" s="8">
-        <v>12316949610.97</v>
+        <v>12294988080.82</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
@@ -11218,19 +11214,19 @@
         <v>734</v>
       </c>
       <c r="C367" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D367" s="7">
-        <v>0.146636</v>
+        <v>0.146319</v>
       </c>
       <c r="E367" s="8">
-        <v>31261012571.88</v>
+        <v>31267049268.5</v>
       </c>
       <c r="F367" s="9">
-        <v>93595</v>
+        <v>93507</v>
       </c>
       <c r="G367" s="8">
-        <v>4583988361.87</v>
+        <v>4574956964.24</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
@@ -11241,19 +11237,19 @@
         <v>736</v>
       </c>
       <c r="C368" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D368" s="7">
-        <v>0.170582</v>
+        <v>0.169674</v>
       </c>
       <c r="E368" s="8">
-        <v>2085031993.4</v>
+        <v>2082382313.9</v>
       </c>
       <c r="F368" s="9">
-        <v>7376</v>
+        <v>7380</v>
       </c>
       <c r="G368" s="8">
-        <v>355668377.57</v>
+        <v>353326724.71</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
@@ -11264,19 +11260,19 @@
         <v>738</v>
       </c>
       <c r="C369" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D369" s="7">
-        <v>0.381199</v>
+        <v>0.381563</v>
       </c>
       <c r="E369" s="8">
-        <v>4863975922.71</v>
+        <v>4878345284.35</v>
       </c>
       <c r="F369" s="9">
-        <v>18559</v>
+        <v>18602</v>
       </c>
       <c r="G369" s="8">
-        <v>1854144988.42</v>
+        <v>1861394470.47</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
@@ -11287,19 +11283,19 @@
         <v>740</v>
       </c>
       <c r="C370" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D370" s="7">
-        <v>0.787131</v>
+        <v>0.770056</v>
       </c>
       <c r="E370" s="8">
-        <v>329467240000.36</v>
+        <v>329445177557.56</v>
       </c>
       <c r="F370" s="9">
-        <v>2049518</v>
+        <v>2048791</v>
       </c>
       <c r="G370" s="8">
-        <v>259333926329.67</v>
+        <v>253691302721.76</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
@@ -11310,19 +11306,19 @@
         <v>742</v>
       </c>
       <c r="C371" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D371" s="7">
-        <v>0.157514</v>
+        <v>0.156935</v>
       </c>
       <c r="E371" s="8">
-        <v>23881658966.46</v>
+        <v>23907300163.24</v>
       </c>
       <c r="F371" s="9">
-        <v>109352</v>
+        <v>109340</v>
       </c>
       <c r="G371" s="8">
-        <v>3761703587.78</v>
+        <v>3751896649.53</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
@@ -11333,19 +11329,19 @@
         <v>744</v>
       </c>
       <c r="C372" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D372" s="7">
-        <v>0.194225</v>
+        <v>0.192018</v>
       </c>
       <c r="E372" s="8">
-        <v>3620005611.63</v>
+        <v>3612893855.22</v>
       </c>
       <c r="F372" s="9">
-        <v>11576</v>
+        <v>11574</v>
       </c>
       <c r="G372" s="8">
-        <v>703094597.27</v>
+        <v>693742160.42</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
@@ -11356,19 +11352,19 @@
         <v>746</v>
       </c>
       <c r="C373" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D373" s="7">
-        <v>0.423466</v>
+        <v>0.413715</v>
       </c>
       <c r="E373" s="8">
-        <v>56507071120.67</v>
+        <v>56362158154.44</v>
       </c>
       <c r="F373" s="9">
-        <v>292274</v>
+        <v>291607</v>
       </c>
       <c r="G373" s="8">
-        <v>23928817270.81</v>
+        <v>23317853431.92</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
@@ -11379,19 +11375,19 @@
         <v>748</v>
       </c>
       <c r="C374" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D374" s="7">
-        <v>0.525649</v>
+        <v>0.522513</v>
       </c>
       <c r="E374" s="8">
-        <v>1240262230.7</v>
+        <v>1245884515.51</v>
       </c>
       <c r="F374" s="9">
-        <v>13984</v>
+        <v>14091</v>
       </c>
       <c r="G374" s="8">
-        <v>651942026.92</v>
+        <v>650990476.69</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
@@ -11402,19 +11398,19 @@
         <v>750</v>
       </c>
       <c r="C375" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D375" s="7">
-        <v>0.186122</v>
+        <v>0.183995</v>
       </c>
       <c r="E375" s="8">
-        <v>6852910788.36</v>
+        <v>6853208514.87</v>
       </c>
       <c r="F375" s="9">
-        <v>16329</v>
+        <v>16330</v>
       </c>
       <c r="G375" s="8">
-        <v>1275475828.78</v>
+        <v>1260952762.92</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
@@ -11425,19 +11421,19 @@
         <v>752</v>
       </c>
       <c r="C376" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D376" s="10">
-        <v>0.11863</v>
+        <v>46141</v>
+      </c>
+      <c r="D376" s="7">
+        <v>0.118235</v>
       </c>
       <c r="E376" s="8">
-        <v>7635197032.11</v>
+        <v>7627214528.27</v>
       </c>
       <c r="F376" s="9">
-        <v>24013</v>
+        <v>24002</v>
       </c>
       <c r="G376" s="8">
-        <v>905762932.24</v>
+        <v>901804540.57</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
@@ -11448,19 +11444,19 @@
         <v>754</v>
       </c>
       <c r="C377" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D377" s="10">
-        <v>0.17857</v>
+        <v>46141</v>
+      </c>
+      <c r="D377" s="7">
+        <v>0.176542</v>
       </c>
       <c r="E377" s="8">
-        <v>14220243736.92</v>
+        <v>14196048715.58</v>
       </c>
       <c r="F377" s="9">
-        <v>50999</v>
+        <v>50964</v>
       </c>
       <c r="G377" s="8">
-        <v>2539303499.39</v>
+        <v>2506198037.12</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
@@ -11471,19 +11467,19 @@
         <v>756</v>
       </c>
       <c r="C378" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D378" s="7">
-        <v>0.088184</v>
+        <v>46141</v>
+      </c>
+      <c r="D378" s="10">
+        <v>0.08773</v>
       </c>
       <c r="E378" s="8">
-        <v>397259246642.01</v>
+        <v>397059231209.6</v>
       </c>
       <c r="F378" s="9">
-        <v>1945291</v>
+        <v>1945157</v>
       </c>
       <c r="G378" s="8">
-        <v>35031717841.33</v>
+        <v>34834010943.63</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
@@ -11494,19 +11490,19 @@
         <v>758</v>
       </c>
       <c r="C379" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D379" s="7">
-        <v>0.155762</v>
+        <v>46141</v>
+      </c>
+      <c r="D379" s="10">
+        <v>0.15338</v>
       </c>
       <c r="E379" s="8">
-        <v>1163541433.56</v>
+        <v>1165523162.6</v>
       </c>
       <c r="F379" s="9">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="G379" s="8">
-        <v>181235648.94</v>
+        <v>178768027.76</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
@@ -11517,19 +11513,19 @@
         <v>760</v>
       </c>
       <c r="C380" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D380" s="7">
-        <v>0.190896</v>
+        <v>0.189367</v>
       </c>
       <c r="E380" s="8">
-        <v>1031418130.88</v>
+        <v>1031420359.01</v>
       </c>
       <c r="F380" s="9">
         <v>1805</v>
       </c>
       <c r="G380" s="8">
-        <v>196893879.87</v>
+        <v>195317176.15</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
@@ -11540,19 +11536,19 @@
         <v>762</v>
       </c>
       <c r="C381" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D381" s="7">
-        <v>0.174211</v>
+        <v>46141</v>
+      </c>
+      <c r="D381" s="10">
+        <v>0.17271</v>
       </c>
       <c r="E381" s="8">
-        <v>587016860.51</v>
+        <v>587011599.52</v>
       </c>
       <c r="F381" s="9">
         <v>1719</v>
       </c>
       <c r="G381" s="8">
-        <v>102264832.37</v>
+        <v>101382647</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
@@ -11563,19 +11559,19 @@
         <v>764</v>
       </c>
       <c r="C382" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D382" s="7">
-        <v>0.092521</v>
+        <v>0.092053</v>
       </c>
       <c r="E382" s="8">
-        <v>98097587665.2</v>
+        <v>98024552281.85</v>
       </c>
       <c r="F382" s="9">
-        <v>665527</v>
+        <v>665405</v>
       </c>
       <c r="G382" s="8">
-        <v>9076098307.31</v>
+        <v>9023498852.64</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
@@ -11586,19 +11582,19 @@
         <v>766</v>
       </c>
       <c r="C383" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D383" s="7">
-        <v>0.089359</v>
+        <v>0.089449</v>
       </c>
       <c r="E383" s="8">
-        <v>42700129193.37</v>
+        <v>42559097544.15</v>
       </c>
       <c r="F383" s="9">
-        <v>443274</v>
+        <v>443488</v>
       </c>
       <c r="G383" s="8">
-        <v>3815623815.86</v>
+        <v>3806848760.1</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
@@ -11609,19 +11605,19 @@
         <v>768</v>
       </c>
       <c r="C384" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D384" s="7">
-        <v>0.093769</v>
+        <v>0.093855</v>
       </c>
       <c r="E384" s="8">
-        <v>16522129552.61</v>
+        <v>16510384167.56</v>
       </c>
       <c r="F384" s="9">
-        <v>124305</v>
+        <v>124396</v>
       </c>
       <c r="G384" s="8">
-        <v>1549261421.7</v>
+        <v>1549587445.14</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
@@ -11632,19 +11628,19 @@
         <v>770</v>
       </c>
       <c r="C385" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D385" s="7">
-        <v>0.264574</v>
+        <v>0.260812</v>
       </c>
       <c r="E385" s="8">
-        <v>3514341277.9</v>
+        <v>3517595193.33</v>
       </c>
       <c r="F385" s="9">
-        <v>10531</v>
+        <v>10544</v>
       </c>
       <c r="G385" s="8">
-        <v>929804901.38</v>
+        <v>917431479.85</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
@@ -11655,19 +11651,19 @@
         <v>772</v>
       </c>
       <c r="C386" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D386" s="7">
-        <v>0.191012</v>
+        <v>0.189033</v>
       </c>
       <c r="E386" s="8">
-        <v>2310684631.9</v>
+        <v>2313658747.43</v>
       </c>
       <c r="F386" s="9">
-        <v>7102</v>
+        <v>7110</v>
       </c>
       <c r="G386" s="8">
-        <v>441367671.94</v>
+        <v>437356762.86</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
@@ -11678,19 +11674,19 @@
         <v>774</v>
       </c>
       <c r="C387" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D387" s="7">
-        <v>0.173509</v>
+        <v>0.172104</v>
       </c>
       <c r="E387" s="8">
-        <v>2455321364.92</v>
+        <v>2462620313.75</v>
       </c>
       <c r="F387" s="9">
-        <v>7594</v>
+        <v>7610</v>
       </c>
       <c r="G387" s="8">
-        <v>426021568.3</v>
+        <v>423827167.49</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
@@ -11701,19 +11697,19 @@
         <v>776</v>
       </c>
       <c r="C388" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D388" s="7">
-        <v>0.099038</v>
+        <v>0.098741</v>
       </c>
       <c r="E388" s="8">
-        <v>3859453285.66</v>
+        <v>3848949091.11</v>
       </c>
       <c r="F388" s="9">
-        <v>7269</v>
+        <v>7262</v>
       </c>
       <c r="G388" s="8">
-        <v>382231001.43</v>
+        <v>380050946.26</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -11724,19 +11720,19 @@
         <v>778</v>
       </c>
       <c r="C389" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D389" s="7">
-        <v>0.228925</v>
+        <v>0.226526</v>
       </c>
       <c r="E389" s="8">
-        <v>1480498275.36</v>
+        <v>1487617845.14</v>
       </c>
       <c r="F389" s="9">
-        <v>5800</v>
+        <v>5813</v>
       </c>
       <c r="G389" s="8">
-        <v>338923596.72</v>
+        <v>336984805.62</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
@@ -11747,19 +11743,19 @@
         <v>780</v>
       </c>
       <c r="C390" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D390" s="7">
-        <v>0.321931</v>
+        <v>0.318724</v>
       </c>
       <c r="E390" s="8">
-        <v>1899481898.05</v>
+        <v>1901438721.95</v>
       </c>
       <c r="F390" s="9">
-        <v>6291</v>
+        <v>6306</v>
       </c>
       <c r="G390" s="8">
-        <v>611502917.12</v>
+        <v>606033244.05</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
@@ -11770,19 +11766,19 @@
         <v>782</v>
       </c>
       <c r="C391" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D391" s="7">
-        <v>0.273345</v>
+        <v>0.268689</v>
       </c>
       <c r="E391" s="8">
-        <v>13826528805.79</v>
+        <v>13849147382.24</v>
       </c>
       <c r="F391" s="9">
-        <v>66471</v>
+        <v>66657</v>
       </c>
       <c r="G391" s="8">
-        <v>3779413803.17</v>
+        <v>3721108592.18</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
@@ -11793,19 +11789,19 @@
         <v>784</v>
       </c>
       <c r="C392" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D392" s="7">
-        <v>0.058293</v>
+        <v>0.058045</v>
       </c>
       <c r="E392" s="8">
-        <v>54529829713.24</v>
+        <v>54759410919.64</v>
       </c>
       <c r="F392" s="9">
-        <v>40958</v>
+        <v>41084</v>
       </c>
       <c r="G392" s="8">
-        <v>3178697551.58</v>
+        <v>3178530634.7</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
@@ -11816,19 +11812,19 @@
         <v>786</v>
       </c>
       <c r="C393" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D393" s="7">
-        <v>0.340507</v>
+        <v>0.336767</v>
       </c>
       <c r="E393" s="8">
-        <v>13302637141.36</v>
+        <v>13342474295.71</v>
       </c>
       <c r="F393" s="9">
-        <v>215684</v>
+        <v>216134</v>
       </c>
       <c r="G393" s="8">
-        <v>4529640747.44</v>
+        <v>4493307147.44</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
@@ -11839,19 +11835,19 @@
         <v>788</v>
       </c>
       <c r="C394" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D394" s="7">
-        <v>0.371364</v>
+        <v>0.371269</v>
       </c>
       <c r="E394" s="8">
-        <v>4717386906.38</v>
+        <v>4730029505.53</v>
       </c>
       <c r="F394" s="9">
-        <v>52935</v>
+        <v>53061</v>
       </c>
       <c r="G394" s="8">
-        <v>1751865457.02</v>
+        <v>1756111806.17</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
@@ -11862,19 +11858,19 @@
         <v>790</v>
       </c>
       <c r="C395" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D395" s="7">
-        <v>0.220173</v>
+        <v>0.216446</v>
       </c>
       <c r="E395" s="8">
-        <v>69077100308.27</v>
+        <v>69067674968.32</v>
       </c>
       <c r="F395" s="9">
-        <v>519730</v>
+        <v>519483</v>
       </c>
       <c r="G395" s="8">
-        <v>15208882914.13</v>
+        <v>14949427375.17</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
@@ -11885,19 +11881,19 @@
         <v>792</v>
       </c>
       <c r="C396" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D396" s="7">
-        <v>0.131864</v>
+        <v>0.131446</v>
       </c>
       <c r="E396" s="8">
-        <v>12859695611.99</v>
+        <v>12860554483.51</v>
       </c>
       <c r="F396" s="9">
-        <v>45336</v>
+        <v>45327</v>
       </c>
       <c r="G396" s="8">
-        <v>1695727757.4</v>
+        <v>1690468395.49</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -11908,19 +11904,19 @@
         <v>794</v>
       </c>
       <c r="C397" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D397" s="7">
-        <v>0.063338</v>
+        <v>0.063243</v>
       </c>
       <c r="E397" s="8">
-        <v>58528742231.75</v>
+        <v>58590458580.31</v>
       </c>
       <c r="F397" s="9">
-        <v>324264</v>
+        <v>324096</v>
       </c>
       <c r="G397" s="8">
-        <v>3707084839.24</v>
+        <v>3705436061.21</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>29.04.2026 18:50:27</t>
+    <t>30.04.2026 18:47:12</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2402,13 +2402,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
     <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
     <numFmt numFmtId="169" formatCode="###0.0000;-###0.0000;0"/>
+    <numFmt numFmtId="170" formatCode="###0.000;-###0.000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -2478,7 +2479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2507,6 +2508,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2911,19 +2915,19 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D6" s="7">
-        <v>0.101093</v>
+        <v>0.100996</v>
       </c>
       <c r="E6" s="8">
-        <v>47301738951.15</v>
+        <v>47265323728.45</v>
       </c>
       <c r="F6" s="9">
-        <v>644498</v>
+        <v>644237</v>
       </c>
       <c r="G6" s="8">
-        <v>4781858874.26</v>
+        <v>4773608401.08</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2934,19 +2938,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D7" s="7">
-        <v>0.398282</v>
+        <v>0.397799</v>
       </c>
       <c r="E7" s="8">
-        <v>17107112337.73</v>
+        <v>17127574158.02</v>
       </c>
       <c r="F7" s="9">
-        <v>151719</v>
+        <v>151761</v>
       </c>
       <c r="G7" s="8">
-        <v>6813457443.95</v>
+        <v>6813323458.22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2957,19 +2961,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D8" s="7">
-        <v>0.086025</v>
+        <v>0.086211</v>
       </c>
       <c r="E8" s="8">
-        <v>8000764105.4</v>
+        <v>7972214970.17</v>
       </c>
       <c r="F8" s="9">
-        <v>142512</v>
+        <v>142251</v>
       </c>
       <c r="G8" s="8">
-        <v>688262500.81</v>
+        <v>687290174.42</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2980,19 +2984,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D9" s="10">
-        <v>0.36696</v>
+        <v>46142</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.367315</v>
       </c>
       <c r="E9" s="8">
-        <v>140931211819.4</v>
+        <v>141325979650.22</v>
       </c>
       <c r="F9" s="9">
-        <v>487108</v>
+        <v>487582</v>
       </c>
       <c r="G9" s="8">
-        <v>51716134325.98</v>
+        <v>51911084477.92</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3003,19 +3007,19 @@
         <v>20</v>
       </c>
       <c r="C10" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0.332648</v>
+        <v>46142</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.33155</v>
       </c>
       <c r="E10" s="8">
-        <v>23160411515.13</v>
+        <v>23141888763.59</v>
       </c>
       <c r="F10" s="9">
-        <v>329426</v>
+        <v>329375</v>
       </c>
       <c r="G10" s="8">
-        <v>7704268942.78</v>
+        <v>7672693343.15</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3026,19 +3030,19 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0.993106</v>
+        <v>46142</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0.99765</v>
       </c>
       <c r="E11" s="8">
-        <v>11589047161.69</v>
+        <v>11588812770.84</v>
       </c>
       <c r="F11" s="9">
-        <v>289116</v>
+        <v>289038</v>
       </c>
       <c r="G11" s="8">
-        <v>11509149326.45</v>
+        <v>11561574263.33</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3049,19 +3053,19 @@
         <v>24</v>
       </c>
       <c r="C12" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D12" s="7">
-        <v>0.700638</v>
+        <v>0.697959</v>
       </c>
       <c r="E12" s="8">
-        <v>136892499596.86</v>
+        <v>136855917250.63</v>
       </c>
       <c r="F12" s="9">
-        <v>726136</v>
+        <v>726374</v>
       </c>
       <c r="G12" s="8">
-        <v>95912095628.21</v>
+        <v>95519768707.71</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3072,19 +3076,19 @@
         <v>26</v>
       </c>
       <c r="C13" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D13" s="7">
-        <v>1.995602</v>
+        <v>2.001781</v>
       </c>
       <c r="E13" s="8">
-        <v>1361267909.18</v>
+        <v>1360509937.59</v>
       </c>
       <c r="F13" s="9">
-        <v>32521</v>
+        <v>32522</v>
       </c>
       <c r="G13" s="8">
-        <v>2716548613.42</v>
+        <v>2723442408.71</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3095,19 +3099,19 @@
         <v>28</v>
       </c>
       <c r="C14" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D14" s="7">
-        <v>0.136637</v>
+        <v>46142</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0.13678</v>
       </c>
       <c r="E14" s="8">
-        <v>249905599.92</v>
+        <v>249906698.71</v>
       </c>
       <c r="F14" s="9">
         <v>92</v>
       </c>
       <c r="G14" s="8">
-        <v>34146427.53</v>
+        <v>34182350.02</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3118,19 +3122,19 @@
         <v>30</v>
       </c>
       <c r="C15" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D15" s="7">
-        <v>1.365204</v>
+        <v>1.370142</v>
       </c>
       <c r="E15" s="8">
-        <v>16089345194.29</v>
+        <v>16109732586.14</v>
       </c>
       <c r="F15" s="9">
-        <v>486449</v>
+        <v>486633</v>
       </c>
       <c r="G15" s="8">
-        <v>21965239482.45</v>
+        <v>22072628708.14</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3141,19 +3145,19 @@
         <v>32</v>
       </c>
       <c r="C16" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D16" s="7">
-        <v>0.092773</v>
+        <v>0.092617</v>
       </c>
       <c r="E16" s="8">
-        <v>559868215659.5</v>
+        <v>559460646792.99</v>
       </c>
       <c r="F16" s="9">
-        <v>1923799</v>
+        <v>1922621</v>
       </c>
       <c r="G16" s="8">
-        <v>51940694109.56</v>
+        <v>51815473589.05</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3164,19 +3168,19 @@
         <v>34</v>
       </c>
       <c r="C17" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D17" s="7">
-        <v>0.346562</v>
+        <v>0.345281</v>
       </c>
       <c r="E17" s="8">
-        <v>2108770697.87</v>
+        <v>2107056911.21</v>
       </c>
       <c r="F17" s="9">
-        <v>13320</v>
+        <v>13290</v>
       </c>
       <c r="G17" s="8">
-        <v>730820708.77</v>
+        <v>727527693.76</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3187,19 +3191,19 @@
         <v>36</v>
       </c>
       <c r="C18" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D18" s="7">
-        <v>0.144636</v>
+        <v>0.144679</v>
       </c>
       <c r="E18" s="8">
-        <v>33038128097.78</v>
+        <v>33014077854.63</v>
       </c>
       <c r="F18" s="9">
-        <v>239430</v>
+        <v>239207</v>
       </c>
       <c r="G18" s="8">
-        <v>4778512383.6</v>
+        <v>4776444180.59</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3210,19 +3214,19 @@
         <v>38</v>
       </c>
       <c r="C19" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D19" s="7">
-        <v>0.368171</v>
+        <v>0.367564</v>
       </c>
       <c r="E19" s="8">
-        <v>1434511839.18</v>
+        <v>1433418154.26</v>
       </c>
       <c r="F19" s="9">
         <v>537</v>
       </c>
       <c r="G19" s="8">
-        <v>528146210.61</v>
+        <v>526873602.67</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3233,19 +3237,19 @@
         <v>40</v>
       </c>
       <c r="C20" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D20" s="7">
-        <v>0.137129</v>
+        <v>0.137193</v>
       </c>
       <c r="E20" s="8">
-        <v>14503274580.34</v>
+        <v>14491879584.48</v>
       </c>
       <c r="F20" s="9">
-        <v>519070</v>
+        <v>518720</v>
       </c>
       <c r="G20" s="8">
-        <v>1988824975.95</v>
+        <v>1988184621.42</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3256,19 +3260,19 @@
         <v>42</v>
       </c>
       <c r="C21" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D21" s="7">
-        <v>0.096624</v>
+        <v>0.096385</v>
       </c>
       <c r="E21" s="8">
-        <v>501885958699.14</v>
+        <v>501529904310.79</v>
       </c>
       <c r="F21" s="9">
-        <v>2272635</v>
+        <v>2270033</v>
       </c>
       <c r="G21" s="8">
-        <v>48494184589.55</v>
+        <v>48339944915.22</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3279,19 +3283,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D22" s="7">
-        <v>0.396356</v>
+        <v>0.398463</v>
       </c>
       <c r="E22" s="8">
-        <v>3339818323.18</v>
+        <v>3342927672.72</v>
       </c>
       <c r="F22" s="9">
-        <v>19026</v>
+        <v>19049</v>
       </c>
       <c r="G22" s="8">
-        <v>1323756423.23</v>
+        <v>1332033738.04</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3302,19 +3306,19 @@
         <v>46</v>
       </c>
       <c r="C23" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D23" s="7">
-        <v>0.093106</v>
+        <v>0.092836</v>
       </c>
       <c r="E23" s="8">
-        <v>572171617.61</v>
+        <v>571868429.81</v>
       </c>
       <c r="F23" s="9">
-        <v>4545</v>
+        <v>4540</v>
       </c>
       <c r="G23" s="8">
-        <v>53272493.33</v>
+        <v>53089765.79</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3325,19 +3329,19 @@
         <v>48</v>
       </c>
       <c r="C24" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D24" s="7">
-        <v>0.224734</v>
+        <v>46142</v>
+      </c>
+      <c r="D24" s="11">
+        <v>0.2249</v>
       </c>
       <c r="E24" s="8">
-        <v>1214055433.68</v>
+        <v>1215260946.72</v>
       </c>
       <c r="F24" s="9">
-        <v>4993</v>
+        <v>4982</v>
       </c>
       <c r="G24" s="8">
-        <v>272839647.19</v>
+        <v>273312016.21</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3348,19 +3352,19 @@
         <v>50</v>
       </c>
       <c r="C25" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D25" s="7">
-        <v>0.105422</v>
+        <v>0.105299</v>
       </c>
       <c r="E25" s="8">
-        <v>66642617155.49</v>
+        <v>66652250630.27</v>
       </c>
       <c r="F25" s="9">
-        <v>764907</v>
+        <v>765393</v>
       </c>
       <c r="G25" s="8">
-        <v>7025627322.07</v>
+        <v>7018382909.56</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3371,19 +3375,19 @@
         <v>52</v>
       </c>
       <c r="C26" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D26" s="7">
-        <v>0.097462</v>
+        <v>0.097588</v>
       </c>
       <c r="E26" s="8">
-        <v>1676318610.65</v>
+        <v>1675410720.19</v>
       </c>
       <c r="F26" s="9">
-        <v>3243</v>
+        <v>3238</v>
       </c>
       <c r="G26" s="8">
-        <v>163377960.33</v>
+        <v>163499451.39</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3394,19 +3398,19 @@
         <v>54</v>
       </c>
       <c r="C27" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D27" s="7">
-        <v>0.092949</v>
+        <v>0.093185</v>
       </c>
       <c r="E27" s="8">
-        <v>61742973383.22</v>
+        <v>61867048954.93</v>
       </c>
       <c r="F27" s="9">
-        <v>715690</v>
+        <v>716218</v>
       </c>
       <c r="G27" s="8">
-        <v>5738928767.55</v>
+        <v>5765087312.62</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3417,19 +3421,19 @@
         <v>56</v>
       </c>
       <c r="C28" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D28" s="7">
-        <v>0.386578</v>
+        <v>0.385394</v>
       </c>
       <c r="E28" s="8">
-        <v>1050281788.05</v>
+        <v>1050885191.14</v>
       </c>
       <c r="F28" s="9">
-        <v>7922</v>
+        <v>7901</v>
       </c>
       <c r="G28" s="8">
-        <v>406015778.12</v>
+        <v>405005077.11</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3440,19 +3444,19 @@
         <v>58</v>
       </c>
       <c r="C29" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D29" s="7">
-        <v>0.643921</v>
+        <v>0.643435</v>
       </c>
       <c r="E29" s="8">
-        <v>209996741.87</v>
+        <v>211319077.63</v>
       </c>
       <c r="F29" s="9">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="G29" s="8">
-        <v>135221406.99</v>
+        <v>135970058.36</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3463,19 +3467,19 @@
         <v>60</v>
       </c>
       <c r="C30" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D30" s="7">
-        <v>2.344858</v>
+        <v>2.349863</v>
       </c>
       <c r="E30" s="8">
-        <v>843120893.02</v>
+        <v>843816777.87</v>
       </c>
       <c r="F30" s="9">
-        <v>19482</v>
+        <v>19520</v>
       </c>
       <c r="G30" s="8">
-        <v>1976999186.39</v>
+        <v>1982853436.63</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3486,19 +3490,19 @@
         <v>62</v>
       </c>
       <c r="C31" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D31" s="11">
-        <v>0.5215</v>
+        <v>46142</v>
+      </c>
+      <c r="D31" s="7">
+        <v>0.520608</v>
       </c>
       <c r="E31" s="8">
-        <v>2405377461.62</v>
+        <v>2401993323.2</v>
       </c>
       <c r="F31" s="9">
-        <v>13861</v>
+        <v>13845</v>
       </c>
       <c r="G31" s="8">
-        <v>1254405064.47</v>
+        <v>1250496551.38</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3509,19 +3513,19 @@
         <v>64</v>
       </c>
       <c r="C32" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D32" s="7">
-        <v>0.844686</v>
+        <v>0.841753</v>
       </c>
       <c r="E32" s="8">
-        <v>12401023487.12</v>
+        <v>12374685341.87</v>
       </c>
       <c r="F32" s="9">
-        <v>77071</v>
+        <v>77069</v>
       </c>
       <c r="G32" s="8">
-        <v>10474967296.15</v>
+        <v>10416431108.61</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3532,19 +3536,19 @@
         <v>66</v>
       </c>
       <c r="C33" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D33" s="7">
-        <v>0.261192</v>
+        <v>0.260996</v>
       </c>
       <c r="E33" s="8">
-        <v>1311305092.75</v>
+        <v>1309261999.21</v>
       </c>
       <c r="F33" s="9">
         <v>16197</v>
       </c>
       <c r="G33" s="8">
-        <v>342502301.95</v>
+        <v>341711866.29</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3555,19 +3559,19 @@
         <v>68</v>
       </c>
       <c r="C34" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D34" s="7">
-        <v>0.124583</v>
+        <v>0.124627</v>
       </c>
       <c r="E34" s="8">
-        <v>3333312470.66</v>
+        <v>3334226271.75</v>
       </c>
       <c r="F34" s="9">
-        <v>53945</v>
+        <v>53938</v>
       </c>
       <c r="G34" s="8">
-        <v>415275343.77</v>
+        <v>415533797.69</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3578,19 +3582,19 @@
         <v>70</v>
       </c>
       <c r="C35" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D35" s="7">
-        <v>0.174548</v>
+        <v>0.174824</v>
       </c>
       <c r="E35" s="8">
-        <v>10659017489.79</v>
+        <v>10698866014.25</v>
       </c>
       <c r="F35" s="9">
-        <v>36593</v>
+        <v>36572</v>
       </c>
       <c r="G35" s="8">
-        <v>1860514674.22</v>
+        <v>1870418634.74</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3601,19 +3605,19 @@
         <v>72</v>
       </c>
       <c r="C36" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D36" s="7">
-        <v>0.200046</v>
+        <v>0.200385</v>
       </c>
       <c r="E36" s="8">
-        <v>1495509032.29</v>
+        <v>1493650262.72</v>
       </c>
       <c r="F36" s="9">
-        <v>32752</v>
+        <v>32749</v>
       </c>
       <c r="G36" s="8">
-        <v>299170839.6</v>
+        <v>299304938.12</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3624,19 +3628,19 @@
         <v>74</v>
       </c>
       <c r="C37" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D37" s="7">
-        <v>0.819503</v>
+        <v>46142</v>
+      </c>
+      <c r="D37" s="10">
+        <v>0.81912</v>
       </c>
       <c r="E37" s="8">
-        <v>2444382827.56</v>
+        <v>2446994937.04</v>
       </c>
       <c r="F37" s="9">
-        <v>52323</v>
+        <v>52338</v>
       </c>
       <c r="G37" s="8">
-        <v>2003178800.79</v>
+        <v>2004382942.06</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3647,19 +3651,19 @@
         <v>76</v>
       </c>
       <c r="C38" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D38" s="10">
-        <v>0.16874</v>
+        <v>46142</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0.168876</v>
       </c>
       <c r="E38" s="8">
-        <v>3691323338.82</v>
+        <v>3692586408.31</v>
       </c>
       <c r="F38" s="9">
-        <v>53219</v>
+        <v>53216</v>
       </c>
       <c r="G38" s="8">
-        <v>622875534.31</v>
+        <v>623590224.89</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3670,19 +3674,19 @@
         <v>78</v>
       </c>
       <c r="C39" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D39" s="10">
-        <v>0.10547</v>
+        <v>46142</v>
+      </c>
+      <c r="D39" s="7">
+        <v>0.105977</v>
       </c>
       <c r="E39" s="8">
-        <v>8023250683.01</v>
+        <v>8020542292.57</v>
       </c>
       <c r="F39" s="9">
-        <v>95725</v>
+        <v>95721</v>
       </c>
       <c r="G39" s="8">
-        <v>846210613.55</v>
+        <v>849994341.29</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3693,19 +3697,19 @@
         <v>80</v>
       </c>
       <c r="C40" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D40" s="7">
-        <v>0.337902</v>
+        <v>0.336819</v>
       </c>
       <c r="E40" s="8">
-        <v>14163554884.05</v>
+        <v>14164246239.21</v>
       </c>
       <c r="F40" s="9">
-        <v>158289</v>
+        <v>157896</v>
       </c>
       <c r="G40" s="8">
-        <v>4785900172.42</v>
+        <v>4770783727.14</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3716,19 +3720,19 @@
         <v>82</v>
       </c>
       <c r="C41" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D41" s="7">
-        <v>0.363843</v>
+        <v>0.364235</v>
       </c>
       <c r="E41" s="8">
-        <v>76425807769.16</v>
+        <v>76782064688.36</v>
       </c>
       <c r="F41" s="9">
-        <v>166409</v>
+        <v>166183</v>
       </c>
       <c r="G41" s="8">
-        <v>27807031242.49</v>
+        <v>27966735536.56</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3739,19 +3743,19 @@
         <v>84</v>
       </c>
       <c r="C42" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D42" s="7">
-        <v>0.953993</v>
+        <v>0.952416</v>
       </c>
       <c r="E42" s="8">
-        <v>12814148583.73</v>
+        <v>12818226702.1</v>
       </c>
       <c r="F42" s="9">
-        <v>235258</v>
+        <v>235101</v>
       </c>
       <c r="G42" s="8">
-        <v>12224609047.53</v>
+        <v>12208282943.4</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3762,19 +3766,19 @@
         <v>86</v>
       </c>
       <c r="C43" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D43" s="7">
-        <v>0.686792</v>
+        <v>46142</v>
+      </c>
+      <c r="D43" s="12">
+        <v>0.687</v>
       </c>
       <c r="E43" s="8">
-        <v>8861552119.1</v>
+        <v>8867831493.48</v>
       </c>
       <c r="F43" s="9">
-        <v>121453</v>
+        <v>121398</v>
       </c>
       <c r="G43" s="8">
-        <v>6086038764.52</v>
+        <v>6092201096.32</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3785,19 +3789,19 @@
         <v>88</v>
       </c>
       <c r="C44" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D44" s="7">
-        <v>2.946217</v>
+        <v>2.937155</v>
       </c>
       <c r="E44" s="8">
-        <v>8458096028.67</v>
+        <v>8466206439.04</v>
       </c>
       <c r="F44" s="9">
-        <v>364916</v>
+        <v>365892</v>
       </c>
       <c r="G44" s="8">
-        <v>24919388351.9</v>
+        <v>24866559295.83</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3808,19 +3812,19 @@
         <v>90</v>
       </c>
       <c r="C45" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D45" s="7">
-        <v>1.131118</v>
+        <v>46142</v>
+      </c>
+      <c r="D45" s="11">
+        <v>1.1294</v>
       </c>
       <c r="E45" s="8">
-        <v>3663560507.02</v>
+        <v>3664689765.86</v>
       </c>
       <c r="F45" s="9">
-        <v>85784</v>
+        <v>85796</v>
       </c>
       <c r="G45" s="8">
-        <v>4143917580.94</v>
+        <v>4138901487.26</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3831,19 +3835,19 @@
         <v>92</v>
       </c>
       <c r="C46" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D46" s="7">
-        <v>0.421029</v>
+        <v>0.420911</v>
       </c>
       <c r="E46" s="8">
-        <v>23904038767.7</v>
+        <v>23905108094.1</v>
       </c>
       <c r="F46" s="9">
-        <v>219756</v>
+        <v>219692</v>
       </c>
       <c r="G46" s="8">
-        <v>10064286291.16</v>
+        <v>10061925209.22</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3854,19 +3858,19 @@
         <v>94</v>
       </c>
       <c r="C47" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D47" s="7">
-        <v>0.994791</v>
+        <v>0.994665</v>
       </c>
       <c r="E47" s="8">
-        <v>9125792074.81</v>
+        <v>9682390662.61</v>
       </c>
       <c r="F47" s="9">
-        <v>177603</v>
+        <v>207415</v>
       </c>
       <c r="G47" s="8">
-        <v>9078254772.77</v>
+        <v>9630739284.22</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3877,19 +3881,19 @@
         <v>96</v>
       </c>
       <c r="C48" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D48" s="7">
-        <v>1.335108</v>
+        <v>46142</v>
+      </c>
+      <c r="D48" s="11">
+        <v>1.3379</v>
       </c>
       <c r="E48" s="8">
-        <v>712756030.44</v>
+        <v>714222953.31</v>
       </c>
       <c r="F48" s="9">
-        <v>7277</v>
+        <v>7289</v>
       </c>
       <c r="G48" s="8">
-        <v>951606219.28</v>
+        <v>955558574.93</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3900,19 +3904,19 @@
         <v>98</v>
       </c>
       <c r="C49" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D49" s="7">
-        <v>0.129682</v>
+        <v>0.129801</v>
       </c>
       <c r="E49" s="8">
-        <v>93407787666.84</v>
+        <v>93487353817.7</v>
       </c>
       <c r="F49" s="9">
-        <v>207969</v>
+        <v>208255</v>
       </c>
       <c r="G49" s="8">
-        <v>12113302428.13</v>
+        <v>12134724333.5</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3923,19 +3927,19 @@
         <v>100</v>
       </c>
       <c r="C50" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D50" s="7">
-        <v>0.099032</v>
+        <v>0.099133</v>
       </c>
       <c r="E50" s="8">
-        <v>13819444852.85</v>
+        <v>13758934729.47</v>
       </c>
       <c r="F50" s="9">
-        <v>129778</v>
+        <v>129306</v>
       </c>
       <c r="G50" s="8">
-        <v>1368564307.97</v>
+        <v>1363970021.71</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3946,19 +3950,19 @@
         <v>102</v>
       </c>
       <c r="C51" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D51" s="7">
-        <v>0.489457</v>
+        <v>0.488153</v>
       </c>
       <c r="E51" s="8">
-        <v>20446778085.37</v>
+        <v>20440502350.08</v>
       </c>
       <c r="F51" s="9">
-        <v>138130</v>
+        <v>136853</v>
       </c>
       <c r="G51" s="8">
-        <v>10007828158.07</v>
+        <v>9978091974.69</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3969,19 +3973,19 @@
         <v>104</v>
       </c>
       <c r="C52" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D52" s="7">
-        <v>0.210221</v>
+        <v>0.211777</v>
       </c>
       <c r="E52" s="8">
-        <v>2630758140.91</v>
+        <v>2633278776.45</v>
       </c>
       <c r="F52" s="9">
-        <v>10432</v>
+        <v>10436</v>
       </c>
       <c r="G52" s="8">
-        <v>553041616.92</v>
+        <v>557667335.98</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3992,19 +3996,19 @@
         <v>106</v>
       </c>
       <c r="C53" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D53" s="7">
-        <v>0.265003</v>
+        <v>0.266996</v>
       </c>
       <c r="E53" s="8">
-        <v>2882305208.03</v>
+        <v>2883703883.96</v>
       </c>
       <c r="F53" s="9">
-        <v>10733</v>
+        <v>10739</v>
       </c>
       <c r="G53" s="8">
-        <v>763819437.34</v>
+        <v>769938645.43</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -4015,19 +4019,19 @@
         <v>108</v>
       </c>
       <c r="C54" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D54" s="7">
-        <v>0.328737</v>
+        <v>0.327816</v>
       </c>
       <c r="E54" s="8">
-        <v>4537122250.81</v>
+        <v>4537679209.24</v>
       </c>
       <c r="F54" s="9">
-        <v>15945</v>
+        <v>15977</v>
       </c>
       <c r="G54" s="8">
-        <v>1491519884.15</v>
+        <v>1487522743.41</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4038,19 +4042,19 @@
         <v>110</v>
       </c>
       <c r="C55" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D55" s="7">
-        <v>0.310206</v>
+        <v>0.308453</v>
       </c>
       <c r="E55" s="8">
-        <v>2568047389.31</v>
+        <v>2569488420.81</v>
       </c>
       <c r="F55" s="9">
-        <v>10216</v>
+        <v>10237</v>
       </c>
       <c r="G55" s="8">
-        <v>796623952.34</v>
+        <v>792566042.45</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -4061,19 +4065,19 @@
         <v>112</v>
       </c>
       <c r="C56" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D56" s="7">
-        <v>0.220073</v>
+        <v>0.219504</v>
       </c>
       <c r="E56" s="8">
-        <v>1888463997.85</v>
+        <v>1891892426.71</v>
       </c>
       <c r="F56" s="9">
-        <v>6706</v>
+        <v>6719</v>
       </c>
       <c r="G56" s="8">
-        <v>415600239.02</v>
+        <v>415278599.15</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4084,19 +4088,19 @@
         <v>114</v>
       </c>
       <c r="C57" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D57" s="7">
-        <v>0.114107</v>
+        <v>46142</v>
+      </c>
+      <c r="D57" s="10">
+        <v>0.11391</v>
       </c>
       <c r="E57" s="8">
-        <v>1637639018.51</v>
+        <v>1633326662.51</v>
       </c>
       <c r="F57" s="9">
-        <v>3929</v>
+        <v>3931</v>
       </c>
       <c r="G57" s="8">
-        <v>186865978.03</v>
+        <v>186052976.04</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -4107,19 +4111,19 @@
         <v>116</v>
       </c>
       <c r="C58" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D58" s="7">
-        <v>0.304579</v>
+        <v>0.304927</v>
       </c>
       <c r="E58" s="8">
-        <v>4437209996.68</v>
+        <v>4441806562.34</v>
       </c>
       <c r="F58" s="9">
-        <v>16750</v>
+        <v>16820</v>
       </c>
       <c r="G58" s="8">
-        <v>1351482437.21</v>
+        <v>1354426322.6</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -4130,19 +4134,19 @@
         <v>118</v>
       </c>
       <c r="C59" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D59" s="7">
-        <v>0.242175</v>
+        <v>0.242317</v>
       </c>
       <c r="E59" s="8">
-        <v>2802471521.7</v>
+        <v>2806415561.58</v>
       </c>
       <c r="F59" s="9">
-        <v>11296</v>
+        <v>11334</v>
       </c>
       <c r="G59" s="8">
-        <v>678689085.4</v>
+        <v>680042124.47</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -4153,19 +4157,19 @@
         <v>120</v>
       </c>
       <c r="C60" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D60" s="7">
-        <v>0.175816</v>
+        <v>46142</v>
+      </c>
+      <c r="D60" s="10">
+        <v>0.17688</v>
       </c>
       <c r="E60" s="8">
-        <v>180547706.41</v>
+        <v>180641528.92</v>
       </c>
       <c r="F60" s="9">
         <v>452</v>
       </c>
       <c r="G60" s="8">
-        <v>31743197.47</v>
+        <v>31951796.32</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -4176,19 +4180,19 @@
         <v>122</v>
       </c>
       <c r="C61" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D61" s="7">
-        <v>0.375204</v>
+        <v>0.373783</v>
       </c>
       <c r="E61" s="8">
-        <v>859107356.46</v>
+        <v>858462156.77</v>
       </c>
       <c r="F61" s="9">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G61" s="8">
-        <v>322340208.72</v>
+        <v>320878194.68</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -4199,19 +4203,19 @@
         <v>124</v>
       </c>
       <c r="C62" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D62" s="7">
-        <v>0.072952</v>
+        <v>0.072957</v>
       </c>
       <c r="E62" s="8">
-        <v>174048053.33</v>
+        <v>174134511.34</v>
       </c>
       <c r="F62" s="9">
         <v>224</v>
       </c>
       <c r="G62" s="8">
-        <v>12697155.74</v>
+        <v>12704396.41</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -4222,19 +4226,19 @@
         <v>126</v>
       </c>
       <c r="C63" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D63" s="7">
-        <v>0.142185</v>
+        <v>0.142964</v>
       </c>
       <c r="E63" s="8">
-        <v>109474812.33</v>
+        <v>109520801.34</v>
       </c>
       <c r="F63" s="9">
         <v>291</v>
       </c>
       <c r="G63" s="8">
-        <v>15565636.38</v>
+        <v>15657490.44</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -4245,19 +4249,19 @@
         <v>128</v>
       </c>
       <c r="C64" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D64" s="7">
-        <v>0.256206</v>
+        <v>0.256191</v>
       </c>
       <c r="E64" s="8">
-        <v>214838481.26</v>
+        <v>215871674.62</v>
       </c>
       <c r="F64" s="9">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G64" s="8">
-        <v>55042825.85</v>
+        <v>55304355.01</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4268,19 +4272,19 @@
         <v>130</v>
       </c>
       <c r="C65" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D65" s="7">
-        <v>0.330415</v>
+        <v>0.331034</v>
       </c>
       <c r="E65" s="8">
-        <v>639403854.68</v>
+        <v>639056460.92</v>
       </c>
       <c r="F65" s="9">
         <v>445</v>
       </c>
       <c r="G65" s="8">
-        <v>211268561.76</v>
+        <v>211549209.94</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -4291,19 +4295,19 @@
         <v>132</v>
       </c>
       <c r="C66" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D66" s="7">
-        <v>0.582461</v>
+        <v>0.584571</v>
       </c>
       <c r="E66" s="8">
-        <v>12965977058.84</v>
+        <v>12935250179.85</v>
       </c>
       <c r="F66" s="9">
-        <v>127732</v>
+        <v>127608</v>
       </c>
       <c r="G66" s="8">
-        <v>7552176825.24</v>
+        <v>7561574162.82</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4314,19 +4318,19 @@
         <v>134</v>
       </c>
       <c r="C67" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D67" s="10">
-        <v>0.25784</v>
+        <v>46142</v>
+      </c>
+      <c r="D67" s="7">
+        <v>0.258552</v>
       </c>
       <c r="E67" s="8">
-        <v>2016378022.7</v>
+        <v>2016396794.7</v>
       </c>
       <c r="F67" s="9">
         <v>6118</v>
       </c>
       <c r="G67" s="8">
-        <v>519902998.65</v>
+        <v>521343926.58</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -4337,19 +4341,19 @@
         <v>136</v>
       </c>
       <c r="C68" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D68" s="7">
-        <v>1.998937</v>
+        <v>1.996334</v>
       </c>
       <c r="E68" s="8">
-        <v>7020314407.05</v>
+        <v>7006097682.38</v>
       </c>
       <c r="F68" s="9">
-        <v>236318</v>
+        <v>236156</v>
       </c>
       <c r="G68" s="8">
-        <v>14033164651.98</v>
+        <v>13986513840.69</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -4360,19 +4364,19 @@
         <v>138</v>
       </c>
       <c r="C69" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D69" s="7">
-        <v>0.996959</v>
+        <v>0.995376</v>
       </c>
       <c r="E69" s="8">
-        <v>6551630874.17</v>
+        <v>6545126096.75</v>
       </c>
       <c r="F69" s="9">
-        <v>163559</v>
+        <v>163458</v>
       </c>
       <c r="G69" s="8">
-        <v>6531707322.55</v>
+        <v>6514862999.65</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -4383,19 +4387,19 @@
         <v>140</v>
       </c>
       <c r="C70" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D70" s="7">
-        <v>0.321053</v>
+        <v>0.321359</v>
       </c>
       <c r="E70" s="8">
-        <v>12154559315.62</v>
+        <v>12155072720.26</v>
       </c>
       <c r="F70" s="9">
-        <v>189795</v>
+        <v>189606</v>
       </c>
       <c r="G70" s="8">
-        <v>3902259533.82</v>
+        <v>3906136212.05</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4406,19 +4410,19 @@
         <v>142</v>
       </c>
       <c r="C71" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D71" s="10">
-        <v>0.09823</v>
+        <v>46142</v>
+      </c>
+      <c r="D71" s="7">
+        <v>0.098332</v>
       </c>
       <c r="E71" s="8">
-        <v>7412595473.66</v>
+        <v>7401177050.67</v>
       </c>
       <c r="F71" s="9">
-        <v>115882</v>
+        <v>115715</v>
       </c>
       <c r="G71" s="8">
-        <v>728142951.26</v>
+        <v>727773860.2</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -4429,19 +4433,19 @@
         <v>144</v>
       </c>
       <c r="C72" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D72" s="7">
-        <v>0.095556</v>
+        <v>0.095384</v>
       </c>
       <c r="E72" s="8">
-        <v>386032392335.52</v>
+        <v>385802552279.17</v>
       </c>
       <c r="F72" s="9">
-        <v>1407635</v>
+        <v>1406934</v>
       </c>
       <c r="G72" s="8">
-        <v>36887720484.32</v>
+        <v>36799422257.67</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4452,19 +4456,19 @@
         <v>146</v>
       </c>
       <c r="C73" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D73" s="10">
-        <v>1.09395</v>
+        <v>46142</v>
+      </c>
+      <c r="D73" s="7">
+        <v>1.092091</v>
       </c>
       <c r="E73" s="8">
-        <v>6402609436.04</v>
+        <v>6393942260.48</v>
       </c>
       <c r="F73" s="9">
-        <v>262754</v>
+        <v>262520</v>
       </c>
       <c r="G73" s="8">
-        <v>7004133320.05</v>
+        <v>6982766324.39</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4475,19 +4479,19 @@
         <v>148</v>
       </c>
       <c r="C74" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D74" s="7">
-        <v>0.507701</v>
+        <v>0.507211</v>
       </c>
       <c r="E74" s="8">
-        <v>6749848306.22</v>
+        <v>6744356001.56</v>
       </c>
       <c r="F74" s="9">
-        <v>65843</v>
+        <v>65782</v>
       </c>
       <c r="G74" s="8">
-        <v>3426901763.32</v>
+        <v>3420812283.54</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -4498,19 +4502,19 @@
         <v>150</v>
       </c>
       <c r="C75" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D75" s="10">
-        <v>1.53781</v>
+        <v>46142</v>
+      </c>
+      <c r="D75" s="7">
+        <v>1.535719</v>
       </c>
       <c r="E75" s="8">
-        <v>493904197.39</v>
+        <v>493463595.11</v>
       </c>
       <c r="F75" s="9">
-        <v>4991</v>
+        <v>5001</v>
       </c>
       <c r="G75" s="8">
-        <v>759530591.91</v>
+        <v>757821634.81</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4521,19 +4525,19 @@
         <v>152</v>
       </c>
       <c r="C76" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D76" s="7">
-        <v>0.691136</v>
+        <v>46142</v>
+      </c>
+      <c r="D76" s="10">
+        <v>0.68899</v>
       </c>
       <c r="E76" s="8">
-        <v>212689152195.15</v>
+        <v>212592360119.9</v>
       </c>
       <c r="F76" s="9">
-        <v>721070</v>
+        <v>720354</v>
       </c>
       <c r="G76" s="8">
-        <v>146997209934.39</v>
+        <v>146473949327.25</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4544,19 +4548,19 @@
         <v>154</v>
       </c>
       <c r="C77" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D77" s="7">
-        <v>0.574096</v>
+        <v>0.572738</v>
       </c>
       <c r="E77" s="8">
-        <v>194280517.16</v>
+        <v>194264367.15</v>
       </c>
       <c r="F77" s="9">
-        <v>22329</v>
+        <v>22328</v>
       </c>
       <c r="G77" s="8">
-        <v>111535639.56</v>
+        <v>111262509.4</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4567,19 +4571,19 @@
         <v>156</v>
       </c>
       <c r="C78" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D78" s="7">
-        <v>0.299011</v>
+        <v>0.297883</v>
       </c>
       <c r="E78" s="8">
-        <v>395637866.15</v>
+        <v>395555462.07</v>
       </c>
       <c r="F78" s="9">
-        <v>33157</v>
+        <v>33153</v>
       </c>
       <c r="G78" s="8">
-        <v>118299879.66</v>
+        <v>117829094.27</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4590,19 +4594,19 @@
         <v>158</v>
       </c>
       <c r="C79" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D79" s="7">
-        <v>0.158332</v>
+        <v>0.159124</v>
       </c>
       <c r="E79" s="8">
-        <v>3115449349.1</v>
+        <v>3111733499.82</v>
       </c>
       <c r="F79" s="9">
-        <v>6959</v>
+        <v>6953</v>
       </c>
       <c r="G79" s="8">
-        <v>493276376.1</v>
+        <v>495152128.9</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4613,19 +4617,19 @@
         <v>160</v>
       </c>
       <c r="C80" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D80" s="7">
-        <v>0.332829</v>
+        <v>0.333214</v>
       </c>
       <c r="E80" s="8">
-        <v>236522689.35</v>
+        <v>236499975.53</v>
       </c>
       <c r="F80" s="9">
-        <v>20837</v>
+        <v>20833</v>
       </c>
       <c r="G80" s="8">
-        <v>78721531.57</v>
+        <v>78805176.34</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4636,19 +4640,19 @@
         <v>162</v>
       </c>
       <c r="C81" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D81" s="7">
-        <v>0.176667</v>
+        <v>0.177693</v>
       </c>
       <c r="E81" s="8">
-        <v>701679357.94</v>
+        <v>701585604.72</v>
       </c>
       <c r="F81" s="9">
-        <v>2356</v>
+        <v>2353</v>
       </c>
       <c r="G81" s="8">
-        <v>123963545.21</v>
+        <v>124666796.53</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4659,19 +4663,19 @@
         <v>164</v>
       </c>
       <c r="C82" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D82" s="7">
-        <v>1.855609</v>
+        <v>1.847521</v>
       </c>
       <c r="E82" s="8">
-        <v>84219621.14</v>
+        <v>84175257.98</v>
       </c>
       <c r="F82" s="9">
-        <v>13725</v>
+        <v>13723</v>
       </c>
       <c r="G82" s="8">
-        <v>156278656.99</v>
+        <v>155515545.56</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4682,19 +4686,19 @@
         <v>166</v>
       </c>
       <c r="C83" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D83" s="7">
-        <v>0.095077</v>
+        <v>0.095184</v>
       </c>
       <c r="E83" s="8">
-        <v>10102627960.3</v>
+        <v>10033206576.61</v>
       </c>
       <c r="F83" s="9">
-        <v>169371</v>
+        <v>168090</v>
       </c>
       <c r="G83" s="8">
-        <v>960531285.21</v>
+        <v>954996830.75</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4705,19 +4709,19 @@
         <v>168</v>
       </c>
       <c r="C84" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D84" s="7">
-        <v>0.083316</v>
+        <v>0.083416</v>
       </c>
       <c r="E84" s="8">
-        <v>9122976454.11</v>
+        <v>8968613836.18</v>
       </c>
       <c r="F84" s="9">
-        <v>140293</v>
+        <v>139139</v>
       </c>
       <c r="G84" s="8">
-        <v>760085871.82</v>
+        <v>748121694.79</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4728,19 +4732,19 @@
         <v>170</v>
       </c>
       <c r="C85" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D85" s="7">
-        <v>0.267679</v>
+        <v>0.267974</v>
       </c>
       <c r="E85" s="8">
-        <v>4308166554.83</v>
+        <v>4317720680.09</v>
       </c>
       <c r="F85" s="9">
-        <v>79997</v>
+        <v>79988</v>
       </c>
       <c r="G85" s="8">
-        <v>1153206281.48</v>
+        <v>1157035746.18</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4751,19 +4755,19 @@
         <v>172</v>
       </c>
       <c r="C86" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D86" s="7">
-        <v>0.896242</v>
+        <v>0.889379</v>
       </c>
       <c r="E86" s="8">
-        <v>4621876641.38</v>
+        <v>4616279085.3</v>
       </c>
       <c r="F86" s="9">
-        <v>87247</v>
+        <v>87200</v>
       </c>
       <c r="G86" s="8">
-        <v>4142322234.67</v>
+        <v>4105620527.8</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4774,19 +4778,19 @@
         <v>174</v>
       </c>
       <c r="C87" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D87" s="7">
-        <v>0.224082</v>
+        <v>46142</v>
+      </c>
+      <c r="D87" s="10">
+        <v>0.22375</v>
       </c>
       <c r="E87" s="8">
-        <v>12590347802.23</v>
+        <v>12580023783.12</v>
       </c>
       <c r="F87" s="9">
-        <v>143818</v>
+        <v>144125</v>
       </c>
       <c r="G87" s="8">
-        <v>2821266401.35</v>
+        <v>2814774832.5</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4797,19 +4801,19 @@
         <v>176</v>
       </c>
       <c r="C88" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D88" s="7">
-        <v>0.163389</v>
+        <v>0.163275</v>
       </c>
       <c r="E88" s="8">
-        <v>18412068718.98</v>
+        <v>18454762078.54</v>
       </c>
       <c r="F88" s="9">
-        <v>90886</v>
+        <v>90851</v>
       </c>
       <c r="G88" s="8">
-        <v>3008338127.63</v>
+        <v>3013206202.64</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4820,19 +4824,19 @@
         <v>178</v>
       </c>
       <c r="C89" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D89" s="7">
-        <v>0.633692</v>
+        <v>0.632931</v>
       </c>
       <c r="E89" s="8">
-        <v>2277011283.51</v>
+        <v>2273952869.42</v>
       </c>
       <c r="F89" s="9">
-        <v>35997</v>
+        <v>35956</v>
       </c>
       <c r="G89" s="8">
-        <v>1442924313.39</v>
+        <v>1439254949.92</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4843,19 +4847,19 @@
         <v>180</v>
       </c>
       <c r="C90" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D90" s="7">
-        <v>0.843794</v>
+        <v>0.842304</v>
       </c>
       <c r="E90" s="8">
-        <v>19239895962.15</v>
+        <v>19226706655.35</v>
       </c>
       <c r="F90" s="9">
-        <v>273301</v>
+        <v>272964</v>
       </c>
       <c r="G90" s="8">
-        <v>16234513547.48</v>
+        <v>16194722460.78</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4866,19 +4870,19 @@
         <v>182</v>
       </c>
       <c r="C91" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D91" s="10">
-        <v>0.78612</v>
+        <v>46142</v>
+      </c>
+      <c r="D91" s="7">
+        <v>0.784569</v>
       </c>
       <c r="E91" s="8">
-        <v>3476296523.66</v>
+        <v>3474119636.51</v>
       </c>
       <c r="F91" s="9">
-        <v>29185</v>
+        <v>29232</v>
       </c>
       <c r="G91" s="8">
-        <v>2732785625.61</v>
+        <v>2725685124.71</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4889,19 +4893,19 @@
         <v>184</v>
       </c>
       <c r="C92" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D92" s="7">
-        <v>0.830365</v>
+        <v>0.829315</v>
       </c>
       <c r="E92" s="8">
-        <v>12349482013.15</v>
+        <v>12347332910.21</v>
       </c>
       <c r="F92" s="9">
-        <v>189279</v>
+        <v>189082</v>
       </c>
       <c r="G92" s="8">
-        <v>10254576903.85</v>
+        <v>10239828469.8</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4912,19 +4916,19 @@
         <v>186</v>
       </c>
       <c r="C93" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D93" s="7">
-        <v>0.087496</v>
+        <v>0.087691</v>
       </c>
       <c r="E93" s="8">
-        <v>7583910379.02</v>
+        <v>7542463461.64</v>
       </c>
       <c r="F93" s="9">
-        <v>156166</v>
+        <v>155717</v>
       </c>
       <c r="G93" s="8">
-        <v>663561480.63</v>
+        <v>661406934.24</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4935,19 +4939,19 @@
         <v>188</v>
       </c>
       <c r="C94" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D94" s="7">
-        <v>0.119466</v>
+        <v>0.119526</v>
       </c>
       <c r="E94" s="8">
-        <v>11924828338.26</v>
+        <v>11916334420.71</v>
       </c>
       <c r="F94" s="9">
-        <v>33325</v>
+        <v>33293</v>
       </c>
       <c r="G94" s="8">
-        <v>1424613039.77</v>
+        <v>1424313996.12</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4958,19 +4962,19 @@
         <v>190</v>
       </c>
       <c r="C95" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D95" s="7">
-        <v>0.127148</v>
+        <v>0.127281</v>
       </c>
       <c r="E95" s="8">
-        <v>72207867774.75</v>
+        <v>72027501952.51</v>
       </c>
       <c r="F95" s="9">
-        <v>212684</v>
+        <v>212602</v>
       </c>
       <c r="G95" s="8">
-        <v>9181081775.69</v>
+        <v>9167710468.5</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4981,19 +4985,19 @@
         <v>192</v>
       </c>
       <c r="C96" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D96" s="7">
-        <v>0.442173</v>
+        <v>46142</v>
+      </c>
+      <c r="D96" s="10">
+        <v>0.44698</v>
       </c>
       <c r="E96" s="8">
-        <v>31660058299.83</v>
+        <v>31665762558.93</v>
       </c>
       <c r="F96" s="9">
-        <v>281376</v>
+        <v>281784</v>
       </c>
       <c r="G96" s="8">
-        <v>13999235244.96</v>
+        <v>14153973037.47</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -5004,19 +5008,19 @@
         <v>194</v>
       </c>
       <c r="C97" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D97" s="7">
-        <v>0.095688</v>
+        <v>46142</v>
+      </c>
+      <c r="D97" s="10">
+        <v>0.09598</v>
       </c>
       <c r="E97" s="8">
-        <v>24529306243.23</v>
+        <v>24506241629.15</v>
       </c>
       <c r="F97" s="9">
-        <v>442113</v>
+        <v>441970</v>
       </c>
       <c r="G97" s="8">
-        <v>2347166922.89</v>
+        <v>2352117959.41</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -5027,19 +5031,19 @@
         <v>196</v>
       </c>
       <c r="C98" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D98" s="7">
-        <v>0.244085</v>
+        <v>0.243495</v>
       </c>
       <c r="E98" s="8">
-        <v>1294590746.91</v>
+        <v>1289902413.38</v>
       </c>
       <c r="F98" s="9">
-        <v>7098</v>
+        <v>7090</v>
       </c>
       <c r="G98" s="8">
-        <v>315990807.32</v>
+        <v>314084865.19</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -5050,19 +5054,19 @@
         <v>198</v>
       </c>
       <c r="C99" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D99" s="7">
-        <v>1.035365</v>
+        <v>1.032673</v>
       </c>
       <c r="E99" s="8">
-        <v>3618130979.54</v>
+        <v>4046942770.8</v>
       </c>
       <c r="F99" s="9">
-        <v>42318</v>
+        <v>43933</v>
       </c>
       <c r="G99" s="8">
-        <v>3746086568.72</v>
+        <v>4179169499.92</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5073,19 +5077,19 @@
         <v>200</v>
       </c>
       <c r="C100" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D100" s="7">
-        <v>2.569433</v>
+        <v>2.574892</v>
       </c>
       <c r="E100" s="8">
-        <v>12064571974.24</v>
+        <v>12049195202.63</v>
       </c>
       <c r="F100" s="9">
-        <v>305320</v>
+        <v>305348</v>
       </c>
       <c r="G100" s="8">
-        <v>30999107048.69</v>
+        <v>31025371764.05</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5096,19 +5100,19 @@
         <v>202</v>
       </c>
       <c r="C101" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D101" s="7">
-        <v>0.353988</v>
+        <v>0.353175</v>
       </c>
       <c r="E101" s="8">
-        <v>27492156745.99</v>
+        <v>27044487235.24</v>
       </c>
       <c r="F101" s="9">
-        <v>335569</v>
+        <v>334271</v>
       </c>
       <c r="G101" s="8">
-        <v>9731892871.41</v>
+        <v>9551440368.48</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5119,19 +5123,19 @@
         <v>204</v>
       </c>
       <c r="C102" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D102" s="10">
-        <v>0.36631</v>
+        <v>46142</v>
+      </c>
+      <c r="D102" s="7">
+        <v>0.366689</v>
       </c>
       <c r="E102" s="8">
-        <v>203621698682.37</v>
+        <v>202514605446.32</v>
       </c>
       <c r="F102" s="9">
-        <v>346103</v>
+        <v>357152</v>
       </c>
       <c r="G102" s="8">
-        <v>74588569269.66</v>
+        <v>74259819747.72</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5142,19 +5146,19 @@
         <v>206</v>
       </c>
       <c r="C103" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D103" s="7">
-        <v>0.123354</v>
+        <v>0.123469</v>
       </c>
       <c r="E103" s="8">
-        <v>9074234229.47</v>
+        <v>8904265582.31</v>
       </c>
       <c r="F103" s="9">
-        <v>28556</v>
+        <v>28570</v>
       </c>
       <c r="G103" s="8">
-        <v>1119339429.5</v>
+        <v>1099397961.85</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -5165,19 +5169,19 @@
         <v>208</v>
       </c>
       <c r="C104" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D104" s="7">
-        <v>0.278655</v>
+        <v>0.278125</v>
       </c>
       <c r="E104" s="8">
-        <v>1723253869.7</v>
+        <v>1720046204.55</v>
       </c>
       <c r="F104" s="9">
-        <v>7831</v>
+        <v>7829</v>
       </c>
       <c r="G104" s="8">
-        <v>480194026.76</v>
+        <v>478387848.67</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -5188,19 +5192,19 @@
         <v>210</v>
       </c>
       <c r="C105" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D105" s="7">
-        <v>1.040293</v>
+        <v>1.036259</v>
       </c>
       <c r="E105" s="8">
-        <v>248238654.9</v>
+        <v>248369773.98</v>
       </c>
       <c r="F105" s="9">
-        <v>4079</v>
+        <v>4080</v>
       </c>
       <c r="G105" s="8">
-        <v>258240919.09</v>
+        <v>257375537.03</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5211,19 +5215,19 @@
         <v>212</v>
       </c>
       <c r="C106" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D106" s="7">
-        <v>0.981056</v>
+        <v>0.981003</v>
       </c>
       <c r="E106" s="8">
-        <v>602486086.61</v>
+        <v>605743840.04</v>
       </c>
       <c r="F106" s="9">
-        <v>15382</v>
+        <v>15407</v>
       </c>
       <c r="G106" s="8">
-        <v>591072554.66</v>
+        <v>594236388.25</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5234,19 +5238,19 @@
         <v>214</v>
       </c>
       <c r="C107" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D107" s="7">
-        <v>0.176171</v>
+        <v>0.176052</v>
       </c>
       <c r="E107" s="8">
-        <v>375108703.45</v>
+        <v>378092440.93</v>
       </c>
       <c r="F107" s="9">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G107" s="8">
-        <v>66083161.48</v>
+        <v>66563921.34</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -5257,19 +5261,19 @@
         <v>216</v>
       </c>
       <c r="C108" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D108" s="7">
-        <v>1.443027</v>
+        <v>1.442723</v>
       </c>
       <c r="E108" s="8">
-        <v>1015564325.08</v>
+        <v>1014344152.48</v>
       </c>
       <c r="F108" s="9">
-        <v>21935</v>
+        <v>21920</v>
       </c>
       <c r="G108" s="8">
-        <v>1465486235.23</v>
+        <v>1463417561.68</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -5280,19 +5284,19 @@
         <v>218</v>
       </c>
       <c r="C109" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D109" s="7">
-        <v>0.096332</v>
+        <v>0.096258</v>
       </c>
       <c r="E109" s="8">
-        <v>5430182001.47</v>
+        <v>5441649985.44</v>
       </c>
       <c r="F109" s="9">
-        <v>24050</v>
+        <v>24208</v>
       </c>
       <c r="G109" s="8">
-        <v>523097795.44</v>
+        <v>523804690.38</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -5303,19 +5307,19 @@
         <v>220</v>
       </c>
       <c r="C110" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D110" s="10">
-        <v>0.28581</v>
+        <v>46142</v>
+      </c>
+      <c r="D110" s="7">
+        <v>0.284911</v>
       </c>
       <c r="E110" s="8">
-        <v>1640233712.08</v>
+        <v>1638733812.63</v>
       </c>
       <c r="F110" s="9">
-        <v>33199</v>
+        <v>33212</v>
       </c>
       <c r="G110" s="8">
-        <v>468795810.9</v>
+        <v>466893970.96</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5326,19 +5330,19 @@
         <v>222</v>
       </c>
       <c r="C111" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D111" s="10">
-        <v>0.21018</v>
+        <v>46142</v>
+      </c>
+      <c r="D111" s="7">
+        <v>0.209976</v>
       </c>
       <c r="E111" s="8">
-        <v>590183866.73</v>
+        <v>589231877.72</v>
       </c>
       <c r="F111" s="9">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="G111" s="8">
-        <v>124045077.29</v>
+        <v>123724295.71</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -5349,19 +5353,19 @@
         <v>224</v>
       </c>
       <c r="C112" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D112" s="7">
-        <v>0.404248</v>
+        <v>0.407364</v>
       </c>
       <c r="E112" s="8">
-        <v>145362747.9</v>
+        <v>148911117.24</v>
       </c>
       <c r="F112" s="9">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="G112" s="8">
-        <v>58762576.47</v>
+        <v>60661041.82</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -5372,19 +5376,19 @@
         <v>226</v>
       </c>
       <c r="C113" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D113" s="7">
-        <v>0.108599</v>
+        <v>0.108048</v>
       </c>
       <c r="E113" s="8">
-        <v>194581055.56</v>
+        <v>194650771.87</v>
       </c>
       <c r="F113" s="9">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="G113" s="8">
-        <v>21131394.66</v>
+        <v>21031628.37</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5395,19 +5399,19 @@
         <v>228</v>
       </c>
       <c r="C114" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D114" s="10">
-        <v>0.06285</v>
+        <v>46142</v>
+      </c>
+      <c r="D114" s="7">
+        <v>0.062516</v>
       </c>
       <c r="E114" s="8">
-        <v>1218088939523.93</v>
+        <v>1218934020434.03</v>
       </c>
       <c r="F114" s="9">
-        <v>788157</v>
+        <v>789085</v>
       </c>
       <c r="G114" s="8">
-        <v>76556924314.44</v>
+        <v>76202415946.15</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -5418,19 +5422,19 @@
         <v>230</v>
       </c>
       <c r="C115" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D115" s="7">
-        <v>0.015368</v>
+        <v>0.015385</v>
       </c>
       <c r="E115" s="8">
-        <v>6399751054.98</v>
+        <v>6434605824.37</v>
       </c>
       <c r="F115" s="9">
-        <v>1275</v>
+        <v>1295</v>
       </c>
       <c r="G115" s="8">
-        <v>98354430.85</v>
+        <v>98994184.7</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -5441,19 +5445,19 @@
         <v>232</v>
       </c>
       <c r="C116" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D116" s="7">
-        <v>0.123868</v>
+        <v>0.123801</v>
       </c>
       <c r="E116" s="8">
-        <v>7436732971.66</v>
+        <v>7470172616.03</v>
       </c>
       <c r="F116" s="9">
-        <v>24577</v>
+        <v>24672</v>
       </c>
       <c r="G116" s="8">
-        <v>921175019.68</v>
+        <v>924816696.14</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -5464,19 +5468,19 @@
         <v>234</v>
       </c>
       <c r="C117" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D117" s="10">
-        <v>0.12228</v>
+        <v>46142</v>
+      </c>
+      <c r="D117" s="7">
+        <v>0.123285</v>
       </c>
       <c r="E117" s="8">
-        <v>27750180251.25</v>
+        <v>28005965595.92</v>
       </c>
       <c r="F117" s="9">
-        <v>67897</v>
+        <v>68484</v>
       </c>
       <c r="G117" s="8">
-        <v>3393281349.27</v>
+        <v>3452723887.36</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -5487,19 +5491,19 @@
         <v>236</v>
       </c>
       <c r="C118" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D118" s="7">
-        <v>0.569119</v>
+        <v>0.568552</v>
       </c>
       <c r="E118" s="8">
-        <v>91026399.1</v>
+        <v>91013434.11</v>
       </c>
       <c r="F118" s="9">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G118" s="8">
-        <v>51804855.13</v>
+        <v>51745895.12</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -5510,19 +5514,19 @@
         <v>238</v>
       </c>
       <c r="C119" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D119" s="7">
-        <v>0.735433</v>
+        <v>0.733124</v>
       </c>
       <c r="E119" s="8">
-        <v>22913580727.2</v>
+        <v>22903222688.7</v>
       </c>
       <c r="F119" s="9">
-        <v>149317</v>
+        <v>149296</v>
       </c>
       <c r="G119" s="8">
-        <v>16851413649.46</v>
+        <v>16790894181.83</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5533,19 +5537,19 @@
         <v>240</v>
       </c>
       <c r="C120" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D120" s="7">
-        <v>0.122565</v>
+        <v>0.122657</v>
       </c>
       <c r="E120" s="8">
-        <v>14774622696.54</v>
+        <v>14777781285.03</v>
       </c>
       <c r="F120" s="9">
-        <v>44612</v>
+        <v>44586</v>
       </c>
       <c r="G120" s="8">
-        <v>1810853485.8</v>
+        <v>1812591794.92</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5556,19 +5560,19 @@
         <v>242</v>
       </c>
       <c r="C121" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D121" s="7">
-        <v>0.104437</v>
+        <v>0.104319</v>
       </c>
       <c r="E121" s="8">
-        <v>42456724855.67</v>
+        <v>42443293124.89</v>
       </c>
       <c r="F121" s="9">
-        <v>335017</v>
+        <v>334974</v>
       </c>
       <c r="G121" s="8">
-        <v>4434050521.82</v>
+        <v>4427633152.79</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -5579,19 +5583,19 @@
         <v>244</v>
       </c>
       <c r="C122" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D122" s="10">
-        <v>0.09307</v>
+        <v>46142</v>
+      </c>
+      <c r="D122" s="7">
+        <v>0.092772</v>
       </c>
       <c r="E122" s="8">
-        <v>9691223495.54</v>
+        <v>9684079639.11</v>
       </c>
       <c r="F122" s="9">
-        <v>148037</v>
+        <v>148020</v>
       </c>
       <c r="G122" s="8">
-        <v>901964685.95</v>
+        <v>898408859.53</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -5602,19 +5606,19 @@
         <v>246</v>
       </c>
       <c r="C123" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D123" s="10">
-        <v>0.04772</v>
+        <v>46142</v>
+      </c>
+      <c r="D123" s="7">
+        <v>0.047662</v>
       </c>
       <c r="E123" s="8">
-        <v>28035194635.36</v>
+        <v>28025162402.52</v>
       </c>
       <c r="F123" s="9">
-        <v>34420</v>
+        <v>34502</v>
       </c>
       <c r="G123" s="8">
-        <v>1337848918.97</v>
+        <v>1335727992.47</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -5625,19 +5629,19 @@
         <v>248</v>
       </c>
       <c r="C124" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D124" s="7">
-        <v>0.117638</v>
+        <v>0.117286</v>
       </c>
       <c r="E124" s="8">
-        <v>6283842434.12</v>
+        <v>6296709512.01</v>
       </c>
       <c r="F124" s="9">
-        <v>43234</v>
+        <v>43233</v>
       </c>
       <c r="G124" s="8">
-        <v>739218771.25</v>
+        <v>738513915.12</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5648,19 +5652,19 @@
         <v>250</v>
       </c>
       <c r="C125" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D125" s="7">
-        <v>0.090142</v>
+        <v>0.090087</v>
       </c>
       <c r="E125" s="8">
-        <v>2962461852.95</v>
+        <v>2963768533.59</v>
       </c>
       <c r="F125" s="9">
-        <v>83459</v>
+        <v>83451</v>
       </c>
       <c r="G125" s="8">
-        <v>267041651.92</v>
+        <v>266997337.7</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5671,19 +5675,19 @@
         <v>252</v>
       </c>
       <c r="C126" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D126" s="7">
-        <v>0.082376</v>
+        <v>0.082567</v>
       </c>
       <c r="E126" s="8">
-        <v>1120427188.15</v>
+        <v>1120062566.66</v>
       </c>
       <c r="F126" s="9">
-        <v>121870</v>
+        <v>121863</v>
       </c>
       <c r="G126" s="8">
-        <v>92295924.39</v>
+        <v>92479764.27</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5694,19 +5698,19 @@
         <v>254</v>
       </c>
       <c r="C127" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D127" s="10">
-        <v>0.76274</v>
+        <v>46142</v>
+      </c>
+      <c r="D127" s="7">
+        <v>0.759926</v>
       </c>
       <c r="E127" s="8">
-        <v>1639314908.17</v>
+        <v>1633123351.18</v>
       </c>
       <c r="F127" s="9">
         <v>49950</v>
       </c>
       <c r="G127" s="8">
-        <v>1250371140.24</v>
+        <v>1241052605.69</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5717,19 +5721,19 @@
         <v>256</v>
       </c>
       <c r="C128" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D128" s="10">
-        <v>0.14805</v>
+        <v>46142</v>
+      </c>
+      <c r="D128" s="7">
+        <v>0.147648</v>
       </c>
       <c r="E128" s="8">
-        <v>1287933161</v>
+        <v>1288231209.35</v>
       </c>
       <c r="F128" s="9">
-        <v>12562</v>
+        <v>12560</v>
       </c>
       <c r="G128" s="8">
-        <v>190678365.5</v>
+        <v>190204886.65</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5740,19 +5744,19 @@
         <v>258</v>
       </c>
       <c r="C129" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D129" s="7">
-        <v>0.238234</v>
+        <v>0.237577</v>
       </c>
       <c r="E129" s="8">
-        <v>5209001444.94</v>
+        <v>5206924694.71</v>
       </c>
       <c r="F129" s="9">
-        <v>69565</v>
+        <v>69549</v>
       </c>
       <c r="G129" s="8">
-        <v>1240959549.65</v>
+        <v>1237047005.46</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5763,19 +5767,19 @@
         <v>260</v>
       </c>
       <c r="C130" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D130" s="7">
-        <v>1.834265</v>
+        <v>1.821365</v>
       </c>
       <c r="E130" s="8">
-        <v>2364384228.47</v>
+        <v>2368693471.33</v>
       </c>
       <c r="F130" s="9">
-        <v>52834</v>
+        <v>52855</v>
       </c>
       <c r="G130" s="8">
-        <v>4336906512.62</v>
+        <v>4314254460.1</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5786,19 +5790,19 @@
         <v>262</v>
       </c>
       <c r="C131" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D131" s="10">
-        <v>0.34792</v>
+        <v>46142</v>
+      </c>
+      <c r="D131" s="7">
+        <v>0.346878</v>
       </c>
       <c r="E131" s="8">
-        <v>558950926.6</v>
+        <v>559658161.56</v>
       </c>
       <c r="F131" s="9">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="G131" s="8">
-        <v>194470176.03</v>
+        <v>194133195.07</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5809,19 +5813,19 @@
         <v>264</v>
       </c>
       <c r="C132" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D132" s="7">
-        <v>0.159032</v>
+        <v>0.158515</v>
       </c>
       <c r="E132" s="8">
-        <v>132120724.4</v>
+        <v>131900915.58</v>
       </c>
       <c r="F132" s="9">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G132" s="8">
-        <v>21011404.41</v>
+        <v>20908270.87</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5832,19 +5836,19 @@
         <v>266</v>
       </c>
       <c r="C133" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D133" s="7">
-        <v>0.703738</v>
+        <v>46142</v>
+      </c>
+      <c r="D133" s="10">
+        <v>0.70319</v>
       </c>
       <c r="E133" s="8">
-        <v>1255648502.03</v>
+        <v>1256011196.56</v>
       </c>
       <c r="F133" s="9">
-        <v>21207</v>
+        <v>21199</v>
       </c>
       <c r="G133" s="8">
-        <v>883647995.68</v>
+        <v>883214906.47</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5855,19 +5859,19 @@
         <v>268</v>
       </c>
       <c r="C134" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D134" s="7">
-        <v>0.368675</v>
+        <v>46142</v>
+      </c>
+      <c r="D134" s="10">
+        <v>0.36903</v>
       </c>
       <c r="E134" s="8">
-        <v>7358027365.21</v>
+        <v>7362429002.96</v>
       </c>
       <c r="F134" s="9">
-        <v>91874</v>
+        <v>89458</v>
       </c>
       <c r="G134" s="8">
-        <v>2712722852.7</v>
+        <v>2716954115.94</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5878,19 +5882,19 @@
         <v>270</v>
       </c>
       <c r="C135" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D135" s="7">
-        <v>0.201566</v>
+        <v>0.200776</v>
       </c>
       <c r="E135" s="8">
-        <v>199971202.63</v>
+        <v>198538644.25</v>
       </c>
       <c r="F135" s="9">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G135" s="8">
-        <v>40307416.14</v>
+        <v>39861870.06</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5901,19 +5905,19 @@
         <v>272</v>
       </c>
       <c r="C136" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D136" s="7">
-        <v>0.254812</v>
+        <v>0.254402</v>
       </c>
       <c r="E136" s="8">
-        <v>402372807.83</v>
+        <v>402445105.97</v>
       </c>
       <c r="F136" s="9">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G136" s="8">
-        <v>102529560.5</v>
+        <v>102382800.61</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5924,19 +5928,19 @@
         <v>274</v>
       </c>
       <c r="C137" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D137" s="10">
-        <v>0.09996</v>
+        <v>46142</v>
+      </c>
+      <c r="D137" s="7">
+        <v>0.099991</v>
       </c>
       <c r="E137" s="8">
-        <v>296563103.7</v>
+        <v>296173401.13</v>
       </c>
       <c r="F137" s="9">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G137" s="8">
-        <v>29644342.4</v>
+        <v>29614552.56</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5947,19 +5951,19 @@
         <v>276</v>
       </c>
       <c r="C138" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D138" s="7">
-        <v>0.384897</v>
+        <v>0.384148</v>
       </c>
       <c r="E138" s="8">
-        <v>623995432.8</v>
+        <v>626738099.61</v>
       </c>
       <c r="F138" s="9">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="G138" s="8">
-        <v>240173870.05</v>
+        <v>240760091.6</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5970,19 +5974,19 @@
         <v>278</v>
       </c>
       <c r="C139" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D139" s="7">
-        <v>0.695352</v>
+        <v>0.694137</v>
       </c>
       <c r="E139" s="8">
-        <v>2932980750.04</v>
+        <v>2933777114.83</v>
       </c>
       <c r="F139" s="9">
-        <v>42102</v>
+        <v>42068</v>
       </c>
       <c r="G139" s="8">
-        <v>2039454324.02</v>
+        <v>2036444310.75</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5993,19 +5997,19 @@
         <v>280</v>
       </c>
       <c r="C140" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D140" s="7">
-        <v>0.013874</v>
+        <v>0.013869</v>
       </c>
       <c r="E140" s="8">
-        <v>2517262794.2</v>
+        <v>2758698999.84</v>
       </c>
       <c r="F140" s="9">
-        <v>1046</v>
+        <v>1061</v>
       </c>
       <c r="G140" s="8">
-        <v>34925636.88</v>
+        <v>38260537.09</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -6016,19 +6020,19 @@
         <v>282</v>
       </c>
       <c r="C141" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D141" s="7">
-        <v>0.071334</v>
+        <v>0.071579</v>
       </c>
       <c r="E141" s="8">
-        <v>21182808063.74</v>
+        <v>21480584333.65</v>
       </c>
       <c r="F141" s="9">
-        <v>23377</v>
+        <v>23411</v>
       </c>
       <c r="G141" s="8">
-        <v>1511059186.13</v>
+        <v>1537557437.93</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -6039,19 +6043,19 @@
         <v>284</v>
       </c>
       <c r="C142" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D142" s="7">
-        <v>0.280103</v>
+        <v>0.278678</v>
       </c>
       <c r="E142" s="8">
-        <v>20685654488.25</v>
+        <v>20678778650.67</v>
       </c>
       <c r="F142" s="9">
-        <v>4729</v>
+        <v>4728</v>
       </c>
       <c r="G142" s="8">
-        <v>5794113174.17</v>
+        <v>5762730726.27</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -6062,19 +6066,19 @@
         <v>286</v>
       </c>
       <c r="C143" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D143" s="7">
-        <v>0.090163</v>
+        <v>0.090259</v>
       </c>
       <c r="E143" s="8">
-        <v>626110981.33</v>
+        <v>624474552.97</v>
       </c>
       <c r="F143" s="9">
-        <v>10693</v>
+        <v>10713</v>
       </c>
       <c r="G143" s="8">
-        <v>56452244.06</v>
+        <v>56364649.12</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -6085,19 +6089,19 @@
         <v>288</v>
       </c>
       <c r="C144" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D144" s="10">
-        <v>0.05393</v>
+        <v>46142</v>
+      </c>
+      <c r="D144" s="7">
+        <v>0.053728</v>
       </c>
       <c r="E144" s="8">
-        <v>1437914881.59</v>
+        <v>1438619598.22</v>
       </c>
       <c r="F144" s="9">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G144" s="8">
-        <v>77546541.2</v>
+        <v>77293859.5</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -6108,19 +6112,19 @@
         <v>290</v>
       </c>
       <c r="C145" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D145" s="7">
-        <v>0.113271</v>
+        <v>0.113071</v>
       </c>
       <c r="E145" s="8">
-        <v>1823106377.51</v>
+        <v>1823732655.06</v>
       </c>
       <c r="F145" s="9">
         <v>1068</v>
       </c>
       <c r="G145" s="8">
-        <v>206504710.97</v>
+        <v>206210695.55</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -6131,19 +6135,19 @@
         <v>292</v>
       </c>
       <c r="C146" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D146" s="7">
-        <v>0.111902</v>
+        <v>46142</v>
+      </c>
+      <c r="D146" s="10">
+        <v>0.11234</v>
       </c>
       <c r="E146" s="8">
-        <v>1967090564.72</v>
+        <v>1965632597.41</v>
       </c>
       <c r="F146" s="9">
-        <v>65275</v>
+        <v>65256</v>
       </c>
       <c r="G146" s="8">
-        <v>220121251.32</v>
+        <v>220819279.98</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6154,19 +6158,19 @@
         <v>294</v>
       </c>
       <c r="C147" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D147" s="7">
-        <v>0.075465</v>
+        <v>0.075713</v>
       </c>
       <c r="E147" s="8">
-        <v>567959391.85</v>
+        <v>567876089.12</v>
       </c>
       <c r="F147" s="9">
-        <v>51681</v>
+        <v>51667</v>
       </c>
       <c r="G147" s="8">
-        <v>42861083.73</v>
+        <v>42995840.46</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -6177,19 +6181,19 @@
         <v>296</v>
       </c>
       <c r="C148" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D148" s="7">
-        <v>0.081749</v>
+        <v>0.081891</v>
       </c>
       <c r="E148" s="8">
-        <v>356624310.88</v>
+        <v>356848851.01</v>
       </c>
       <c r="F148" s="9">
-        <v>9514</v>
+        <v>9512</v>
       </c>
       <c r="G148" s="8">
-        <v>29153652.18</v>
+        <v>29222663.16</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6200,19 +6204,19 @@
         <v>298</v>
       </c>
       <c r="C149" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D149" s="7">
-        <v>0.361553</v>
+        <v>0.362091</v>
       </c>
       <c r="E149" s="8">
-        <v>147559990.43</v>
+        <v>147564162.3</v>
       </c>
       <c r="F149" s="9">
         <v>1770</v>
       </c>
       <c r="G149" s="8">
-        <v>53350693.15</v>
+        <v>53431648.21</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -6223,19 +6227,19 @@
         <v>300</v>
       </c>
       <c r="C150" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D150" s="7">
-        <v>0.098682</v>
+        <v>0.098346</v>
       </c>
       <c r="E150" s="8">
-        <v>334398931.8</v>
+        <v>334456021.89</v>
       </c>
       <c r="F150" s="9">
         <v>1839</v>
       </c>
       <c r="G150" s="8">
-        <v>32999138.04</v>
+        <v>32892304</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6246,19 +6250,19 @@
         <v>302</v>
       </c>
       <c r="C151" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D151" s="7">
-        <v>0.287079</v>
+        <v>46142</v>
+      </c>
+      <c r="D151" s="11">
+        <v>0.2879</v>
       </c>
       <c r="E151" s="8">
-        <v>142188010.19</v>
+        <v>141991411.08</v>
       </c>
       <c r="F151" s="9">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G151" s="8">
-        <v>40819128.64</v>
+        <v>40879346.5</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -6269,19 +6273,19 @@
         <v>304</v>
       </c>
       <c r="C152" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D152" s="7">
-        <v>0.117058</v>
+        <v>0.117018</v>
       </c>
       <c r="E152" s="8">
-        <v>587042062.35</v>
+        <v>584008161.12</v>
       </c>
       <c r="F152" s="9">
         <v>92</v>
       </c>
       <c r="G152" s="8">
-        <v>68717749.43</v>
+        <v>68339509.47</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -6292,19 +6296,19 @@
         <v>306</v>
       </c>
       <c r="C153" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D153" s="7">
-        <v>0.389583</v>
+        <v>0.390271</v>
       </c>
       <c r="E153" s="8">
-        <v>1307878515.65</v>
+        <v>1306415506.32</v>
       </c>
       <c r="F153" s="9">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G153" s="8">
-        <v>509526791.33</v>
+        <v>509856283.12</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -6315,19 +6319,19 @@
         <v>308</v>
       </c>
       <c r="C154" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D154" s="7">
-        <v>0.504504</v>
+        <v>0.502323</v>
       </c>
       <c r="E154" s="8">
-        <v>594662663.96</v>
+        <v>594155340.02</v>
       </c>
       <c r="F154" s="9">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G154" s="8">
-        <v>300009553.96</v>
+        <v>298457929.41</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -6338,19 +6342,19 @@
         <v>310</v>
       </c>
       <c r="C155" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D155" s="7">
-        <v>1.660314</v>
+        <v>1.664369</v>
       </c>
       <c r="E155" s="8">
-        <v>907404002.61</v>
+        <v>908971420.9</v>
       </c>
       <c r="F155" s="9">
-        <v>10193</v>
+        <v>10194</v>
       </c>
       <c r="G155" s="8">
-        <v>1506575515.88</v>
+        <v>1512863846.48</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -6361,19 +6365,19 @@
         <v>312</v>
       </c>
       <c r="C156" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D156" s="7">
-        <v>0.273955</v>
+        <v>0.275116</v>
       </c>
       <c r="E156" s="8">
-        <v>183411747.1</v>
+        <v>184222013.85</v>
       </c>
       <c r="F156" s="9">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G156" s="8">
-        <v>50246608.09</v>
+        <v>50682460.55</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -6384,19 +6388,19 @@
         <v>314</v>
       </c>
       <c r="C157" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D157" s="7">
-        <v>0.143392</v>
+        <v>0.142857</v>
       </c>
       <c r="E157" s="8">
-        <v>4633018170.82</v>
+        <v>4623633260.96</v>
       </c>
       <c r="F157" s="9">
         <v>28848</v>
       </c>
       <c r="G157" s="8">
-        <v>664336438.72</v>
+        <v>660520018.88</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -6407,19 +6411,19 @@
         <v>316</v>
       </c>
       <c r="C158" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D158" s="7">
-        <v>0.166179</v>
+        <v>0.166378</v>
       </c>
       <c r="E158" s="8">
-        <v>3240752327.86</v>
+        <v>3227757068.27</v>
       </c>
       <c r="F158" s="9">
-        <v>12012</v>
+        <v>11997</v>
       </c>
       <c r="G158" s="8">
-        <v>538544880.99</v>
+        <v>537026371.07</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -6430,19 +6434,19 @@
         <v>318</v>
       </c>
       <c r="C159" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D159" s="7">
-        <v>0.682933</v>
+        <v>0.684357</v>
       </c>
       <c r="E159" s="8">
-        <v>757352707.33</v>
+        <v>757456663.25</v>
       </c>
       <c r="F159" s="9">
-        <v>5165</v>
+        <v>5169</v>
       </c>
       <c r="G159" s="8">
-        <v>517220895.06</v>
+        <v>518371104.98</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -6453,19 +6457,19 @@
         <v>320</v>
       </c>
       <c r="C160" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D160" s="7">
-        <v>0.373442</v>
+        <v>0.372951</v>
       </c>
       <c r="E160" s="8">
-        <v>1353899288</v>
+        <v>1353452306.43</v>
       </c>
       <c r="F160" s="9">
-        <v>23916</v>
+        <v>23915</v>
       </c>
       <c r="G160" s="8">
-        <v>505602219.16</v>
+        <v>504770746.99</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -6476,19 +6480,19 @@
         <v>322</v>
       </c>
       <c r="C161" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D161" s="7">
-        <v>0.366381</v>
+        <v>0.364249</v>
       </c>
       <c r="E161" s="8">
-        <v>167530626.98</v>
+        <v>167509832.24</v>
       </c>
       <c r="F161" s="9">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G161" s="8">
-        <v>61380055.06</v>
+        <v>61015230.63</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -6499,19 +6503,19 @@
         <v>324</v>
       </c>
       <c r="C162" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D162" s="10">
-        <v>0.14241</v>
+        <v>0.14209</v>
       </c>
       <c r="E162" s="8">
-        <v>1027082753.93</v>
+        <v>1026426393.44</v>
       </c>
       <c r="F162" s="9">
-        <v>2968</v>
+        <v>2971</v>
       </c>
       <c r="G162" s="8">
-        <v>146266426.64</v>
+        <v>145845085.86</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -6522,19 +6526,19 @@
         <v>326</v>
       </c>
       <c r="C163" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D163" s="7">
-        <v>0.117108</v>
+        <v>0.116693</v>
       </c>
       <c r="E163" s="8">
-        <v>7516452956</v>
+        <v>7510050970.93</v>
       </c>
       <c r="F163" s="9">
-        <v>79163</v>
+        <v>79152</v>
       </c>
       <c r="G163" s="8">
-        <v>880233276.79</v>
+        <v>876374059.25</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -6545,19 +6549,19 @@
         <v>328</v>
       </c>
       <c r="C164" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D164" s="7">
-        <v>0.107763</v>
+        <v>46142</v>
+      </c>
+      <c r="D164" s="10">
+        <v>0.10763</v>
       </c>
       <c r="E164" s="8">
-        <v>3276559155.42</v>
+        <v>3276580291.02</v>
       </c>
       <c r="F164" s="9">
-        <v>64756</v>
+        <v>64746</v>
       </c>
       <c r="G164" s="8">
-        <v>353093129.57</v>
+        <v>352658289.35</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -6568,19 +6572,19 @@
         <v>330</v>
       </c>
       <c r="C165" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D165" s="7">
-        <v>0.014577</v>
+        <v>0.014456</v>
       </c>
       <c r="E165" s="8">
-        <v>426355760606.58</v>
+        <v>428398631217.82</v>
       </c>
       <c r="F165" s="9">
-        <v>72500</v>
+        <v>72720</v>
       </c>
       <c r="G165" s="8">
-        <v>6215169725.47</v>
+        <v>6192922069.2</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -6591,19 +6595,19 @@
         <v>332</v>
       </c>
       <c r="C166" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D166" s="7">
-        <v>0.358411</v>
+        <v>0.357821</v>
       </c>
       <c r="E166" s="8">
-        <v>686559087.19</v>
+        <v>686064734.04</v>
       </c>
       <c r="F166" s="9">
-        <v>6843</v>
+        <v>6837</v>
       </c>
       <c r="G166" s="8">
-        <v>246070274.33</v>
+        <v>245488426.51</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -6614,19 +6618,19 @@
         <v>334</v>
       </c>
       <c r="C167" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D167" s="7">
-        <v>0.013498</v>
+        <v>0.013654</v>
       </c>
       <c r="E167" s="8">
-        <v>31971898409</v>
+        <v>32730057578.62</v>
       </c>
       <c r="F167" s="9">
-        <v>5563</v>
+        <v>5648</v>
       </c>
       <c r="G167" s="8">
-        <v>431566405.54</v>
+        <v>446881385.82</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6637,19 +6641,19 @@
         <v>336</v>
       </c>
       <c r="C168" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D168" s="7">
-        <v>0.678155</v>
+        <v>0.677808</v>
       </c>
       <c r="E168" s="8">
-        <v>1952177204.81</v>
+        <v>1951481549.18</v>
       </c>
       <c r="F168" s="9">
-        <v>32703</v>
+        <v>32712</v>
       </c>
       <c r="G168" s="8">
-        <v>1323878727.98</v>
+        <v>1322730524.08</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6660,19 +6664,19 @@
         <v>338</v>
       </c>
       <c r="C169" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D169" s="7">
-        <v>0.385259</v>
+        <v>0.384729</v>
       </c>
       <c r="E169" s="8">
-        <v>1982723722.93</v>
+        <v>1975844203.38</v>
       </c>
       <c r="F169" s="9">
-        <v>21019</v>
+        <v>20982</v>
       </c>
       <c r="G169" s="8">
-        <v>763863008.47</v>
+        <v>760165412.88</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6683,19 +6687,19 @@
         <v>340</v>
       </c>
       <c r="C170" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D170" s="7">
-        <v>0.139584</v>
+        <v>46142</v>
+      </c>
+      <c r="D170" s="10">
+        <v>0.13896</v>
       </c>
       <c r="E170" s="8">
-        <v>1586309087</v>
+        <v>1574367815.95</v>
       </c>
       <c r="F170" s="9">
-        <v>16368</v>
+        <v>16356</v>
       </c>
       <c r="G170" s="8">
-        <v>221423653.95</v>
+        <v>218773509.9</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6706,19 +6710,19 @@
         <v>342</v>
       </c>
       <c r="C171" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D171" s="7">
-        <v>1.233349</v>
+        <v>1.231548</v>
       </c>
       <c r="E171" s="8">
-        <v>1388695604.93</v>
+        <v>1383987419.73</v>
       </c>
       <c r="F171" s="9">
-        <v>23800</v>
+        <v>23805</v>
       </c>
       <c r="G171" s="8">
-        <v>1712745836.85</v>
+        <v>1704447535.73</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6729,19 +6733,19 @@
         <v>344</v>
       </c>
       <c r="C172" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D172" s="7">
-        <v>0.567482</v>
+        <v>0.566045</v>
       </c>
       <c r="E172" s="8">
-        <v>2358332962.92</v>
+        <v>2353388678.01</v>
       </c>
       <c r="F172" s="9">
-        <v>35103</v>
+        <v>35034</v>
       </c>
       <c r="G172" s="8">
-        <v>1338312170.64</v>
+        <v>1332124150.89</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6752,19 +6756,19 @@
         <v>346</v>
       </c>
       <c r="C173" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D173" s="7">
-        <v>0.016779</v>
+        <v>0.017027</v>
       </c>
       <c r="E173" s="8">
-        <v>70178099947.71</v>
+        <v>70518100979.43</v>
       </c>
       <c r="F173" s="9">
-        <v>17159</v>
+        <v>17274</v>
       </c>
       <c r="G173" s="8">
-        <v>1177533413.3</v>
+        <v>1200676872.21</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6775,19 +6779,19 @@
         <v>348</v>
       </c>
       <c r="C174" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D174" s="7">
-        <v>0.089042</v>
+        <v>0.088599</v>
       </c>
       <c r="E174" s="8">
-        <v>2175328962.53</v>
+        <v>2167898144.53</v>
       </c>
       <c r="F174" s="9">
-        <v>5154</v>
+        <v>5147</v>
       </c>
       <c r="G174" s="8">
-        <v>193695262.61</v>
+        <v>192072728.61</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6798,19 +6802,19 @@
         <v>350</v>
       </c>
       <c r="C175" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D175" s="7">
-        <v>0.121403</v>
+        <v>0.121424</v>
       </c>
       <c r="E175" s="8">
-        <v>1668453469.5</v>
+        <v>1637228387.91</v>
       </c>
       <c r="F175" s="9">
-        <v>1219</v>
+        <v>1210</v>
       </c>
       <c r="G175" s="8">
-        <v>202556053.93</v>
+        <v>198799121.41</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6821,19 +6825,19 @@
         <v>352</v>
       </c>
       <c r="C176" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D176" s="7">
-        <v>0.308787</v>
+        <v>0.308019</v>
       </c>
       <c r="E176" s="8">
-        <v>757806739.51</v>
+        <v>758091888.18</v>
       </c>
       <c r="F176" s="9">
-        <v>1955</v>
+        <v>1949</v>
       </c>
       <c r="G176" s="8">
-        <v>234000778.69</v>
+        <v>233506692.89</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6844,19 +6848,19 @@
         <v>354</v>
       </c>
       <c r="C177" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D177" s="7">
-        <v>0.090295</v>
+        <v>0.090108</v>
       </c>
       <c r="E177" s="8">
-        <v>41400256444.95</v>
+        <v>41373421121.4</v>
       </c>
       <c r="F177" s="9">
-        <v>281408</v>
+        <v>281327</v>
       </c>
       <c r="G177" s="8">
-        <v>3738244274.95</v>
+        <v>3728096390.76</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6867,19 +6871,19 @@
         <v>356</v>
       </c>
       <c r="C178" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D178" s="7">
-        <v>0.064775</v>
+        <v>0.064611</v>
       </c>
       <c r="E178" s="8">
-        <v>665597639.74</v>
+        <v>662374848.89</v>
       </c>
       <c r="F178" s="9">
-        <v>6089</v>
+        <v>6088</v>
       </c>
       <c r="G178" s="8">
-        <v>43114344.73</v>
+        <v>42797017.74</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6890,19 +6894,19 @@
         <v>358</v>
       </c>
       <c r="C179" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D179" s="10">
-        <v>0.24746</v>
+        <v>46142</v>
+      </c>
+      <c r="D179" s="7">
+        <v>0.249103</v>
       </c>
       <c r="E179" s="8">
-        <v>552293373.31</v>
+        <v>552248867.37</v>
       </c>
       <c r="F179" s="9">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="G179" s="8">
-        <v>136670362.18</v>
+        <v>137566794.11</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6913,19 +6917,19 @@
         <v>360</v>
       </c>
       <c r="C180" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D180" s="7">
-        <v>0.389162</v>
+        <v>0.389382</v>
       </c>
       <c r="E180" s="8">
-        <v>362664863.9</v>
+        <v>362595240.19</v>
       </c>
       <c r="F180" s="9">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G180" s="8">
-        <v>141135467.59</v>
+        <v>141187992.87</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6936,19 +6940,19 @@
         <v>362</v>
       </c>
       <c r="C181" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D181" s="7">
-        <v>0.110601</v>
+        <v>0.110516</v>
       </c>
       <c r="E181" s="8">
-        <v>14659715652.53</v>
+        <v>14656259488.46</v>
       </c>
       <c r="F181" s="9">
-        <v>32214</v>
+        <v>32212</v>
       </c>
       <c r="G181" s="8">
-        <v>1621372465.6</v>
+        <v>1619753337.49</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6959,19 +6963,19 @@
         <v>364</v>
       </c>
       <c r="C182" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D182" s="7">
-        <v>0.115064</v>
+        <v>0.115188</v>
       </c>
       <c r="E182" s="8">
-        <v>22476795869.91</v>
+        <v>22498125986.21</v>
       </c>
       <c r="F182" s="9">
-        <v>41632</v>
+        <v>42375</v>
       </c>
       <c r="G182" s="8">
-        <v>2586279383.38</v>
+        <v>2591504866.46</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6982,19 +6986,19 @@
         <v>366</v>
       </c>
       <c r="C183" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D183" s="11">
-        <v>0.0907</v>
+        <v>46142</v>
+      </c>
+      <c r="D183" s="7">
+        <v>0.091998</v>
       </c>
       <c r="E183" s="8">
-        <v>30727079651.31</v>
+        <v>30766692003.31</v>
       </c>
       <c r="F183" s="9">
-        <v>29670</v>
+        <v>29697</v>
       </c>
       <c r="G183" s="8">
-        <v>2786953983.19</v>
+        <v>2830487576.59</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7005,19 +7009,19 @@
         <v>368</v>
       </c>
       <c r="C184" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D184" s="7">
-        <v>0.083776</v>
+        <v>0.083612</v>
       </c>
       <c r="E184" s="8">
-        <v>6475105120.96</v>
+        <v>6467129882.04</v>
       </c>
       <c r="F184" s="9">
-        <v>5078</v>
+        <v>5070</v>
       </c>
       <c r="G184" s="8">
-        <v>542457193.99</v>
+        <v>540730099.55</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7028,19 +7032,19 @@
         <v>370</v>
       </c>
       <c r="C185" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D185" s="10">
-        <v>0.07296</v>
+        <v>46142</v>
+      </c>
+      <c r="D185" s="7">
+        <v>0.072771</v>
       </c>
       <c r="E185" s="8">
-        <v>13965637896.59</v>
+        <v>13956784517.52</v>
       </c>
       <c r="F185" s="9">
-        <v>184381</v>
+        <v>184345</v>
       </c>
       <c r="G185" s="8">
-        <v>1018926348.71</v>
+        <v>1015646728.2</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7051,19 +7055,19 @@
         <v>372</v>
       </c>
       <c r="C186" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D186" s="7">
-        <v>0.098097</v>
+        <v>0.098347</v>
       </c>
       <c r="E186" s="8">
-        <v>4069654235.32</v>
+        <v>4071227963.53</v>
       </c>
       <c r="F186" s="9">
-        <v>117678</v>
+        <v>117660</v>
       </c>
       <c r="G186" s="8">
-        <v>399220876.41</v>
+        <v>400393712.58</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7074,19 +7078,19 @@
         <v>374</v>
       </c>
       <c r="C187" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D187" s="7">
-        <v>0.236447</v>
+        <v>0.236588</v>
       </c>
       <c r="E187" s="8">
-        <v>667768338.99</v>
+        <v>666132046.26</v>
       </c>
       <c r="F187" s="9">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="G187" s="8">
-        <v>157891814.12</v>
+        <v>157599168.09</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7097,19 +7101,19 @@
         <v>376</v>
       </c>
       <c r="C188" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D188" s="7">
-        <v>0.084376</v>
+        <v>46142</v>
+      </c>
+      <c r="D188" s="10">
+        <v>0.08448</v>
       </c>
       <c r="E188" s="8">
-        <v>2743797823.61</v>
+        <v>2738578232.82</v>
       </c>
       <c r="F188" s="9">
-        <v>42453</v>
+        <v>42347</v>
       </c>
       <c r="G188" s="8">
-        <v>231509485.65</v>
+        <v>231354624.14</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7120,19 +7124,19 @@
         <v>378</v>
       </c>
       <c r="C189" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D189" s="7">
-        <v>0.242317</v>
+        <v>0.243476</v>
       </c>
       <c r="E189" s="8">
-        <v>3445930384.19</v>
+        <v>3434721170.68</v>
       </c>
       <c r="F189" s="9">
-        <v>6526</v>
+        <v>6545</v>
       </c>
       <c r="G189" s="8">
-        <v>835006840.58</v>
+        <v>836271187.87</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7143,19 +7147,19 @@
         <v>380</v>
       </c>
       <c r="C190" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D190" s="7">
-        <v>0.159868</v>
+        <v>0.159904</v>
       </c>
       <c r="E190" s="8">
-        <v>702806935.16</v>
+        <v>698658120.67</v>
       </c>
       <c r="F190" s="9">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="G190" s="8">
-        <v>112356044.92</v>
+        <v>111718527.66</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7166,19 +7170,19 @@
         <v>382</v>
       </c>
       <c r="C191" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D191" s="7">
-        <v>0.148671</v>
+        <v>0.148412</v>
       </c>
       <c r="E191" s="8">
-        <v>491162226.17</v>
+        <v>489823572.29</v>
       </c>
       <c r="F191" s="9">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="G191" s="8">
-        <v>73021422.71</v>
+        <v>72695861.39</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7189,19 +7193,19 @@
         <v>384</v>
       </c>
       <c r="C192" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D192" s="7">
-        <v>0.099615</v>
+        <v>0.099951</v>
       </c>
       <c r="E192" s="8">
-        <v>1155833630.03</v>
+        <v>1155641686.85</v>
       </c>
       <c r="F192" s="9">
-        <v>116526</v>
+        <v>116514</v>
       </c>
       <c r="G192" s="8">
-        <v>115138781.14</v>
+        <v>115508085.67</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7212,19 +7216,19 @@
         <v>386</v>
       </c>
       <c r="C193" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D193" s="7">
-        <v>0.198996</v>
+        <v>0.198603</v>
       </c>
       <c r="E193" s="8">
-        <v>1938944214.5</v>
+        <v>1942996143.7</v>
       </c>
       <c r="F193" s="9">
-        <v>1491</v>
+        <v>1512</v>
       </c>
       <c r="G193" s="8">
-        <v>385841750.71</v>
+        <v>385885521.97</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7235,19 +7239,19 @@
         <v>388</v>
       </c>
       <c r="C194" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D194" s="10">
-        <v>0.15694</v>
+        <v>46142</v>
+      </c>
+      <c r="D194" s="7">
+        <v>0.156916</v>
       </c>
       <c r="E194" s="8">
-        <v>599375716.2</v>
+        <v>599202855.97</v>
       </c>
       <c r="F194" s="9">
         <v>2658</v>
       </c>
       <c r="G194" s="8">
-        <v>94065844.28</v>
+        <v>94024715.7</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7258,19 +7262,19 @@
         <v>390</v>
       </c>
       <c r="C195" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D195" s="7">
-        <v>0.272147</v>
+        <v>0.270893</v>
       </c>
       <c r="E195" s="8">
-        <v>2857011369</v>
+        <v>2836684921.3</v>
       </c>
       <c r="F195" s="9">
-        <v>7759</v>
+        <v>7744</v>
       </c>
       <c r="G195" s="8">
-        <v>777528102.6</v>
+        <v>768437991.12</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7281,19 +7285,19 @@
         <v>392</v>
       </c>
       <c r="C196" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D196" s="7">
-        <v>0.097773</v>
+        <v>0.098064</v>
       </c>
       <c r="E196" s="8">
-        <v>103545411.89</v>
+        <v>103494515.15</v>
       </c>
       <c r="F196" s="9">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="G196" s="8">
-        <v>10123901.59</v>
+        <v>10149114.23</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7304,19 +7308,19 @@
         <v>394</v>
       </c>
       <c r="C197" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D197" s="7">
-        <v>0.213701</v>
+        <v>0.214624</v>
       </c>
       <c r="E197" s="8">
-        <v>320141317.71</v>
+        <v>318794436.54</v>
       </c>
       <c r="F197" s="9">
         <v>971</v>
       </c>
       <c r="G197" s="8">
-        <v>68414553.91</v>
+        <v>68420858.84</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7327,19 +7331,19 @@
         <v>396</v>
       </c>
       <c r="C198" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D198" s="10">
-        <v>0.17055</v>
+        <v>46142</v>
+      </c>
+      <c r="D198" s="7">
+        <v>0.171155</v>
       </c>
       <c r="E198" s="8">
-        <v>269869689.36</v>
+        <v>269865092.16</v>
       </c>
       <c r="F198" s="9">
         <v>838</v>
       </c>
       <c r="G198" s="8">
-        <v>46026298.99</v>
+        <v>46188768.95</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7350,19 +7354,19 @@
         <v>398</v>
       </c>
       <c r="C199" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D199" s="7">
-        <v>0.087438</v>
+        <v>0.087527</v>
       </c>
       <c r="E199" s="8">
-        <v>2652674647.38</v>
+        <v>2647592016.93</v>
       </c>
       <c r="F199" s="9">
-        <v>40238</v>
+        <v>40174</v>
       </c>
       <c r="G199" s="8">
-        <v>231945504.76</v>
+        <v>231736752.23</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7373,19 +7377,19 @@
         <v>400</v>
       </c>
       <c r="C200" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D200" s="10">
-        <v>0.08975</v>
+        <v>46142</v>
+      </c>
+      <c r="D200" s="7">
+        <v>0.089635</v>
       </c>
       <c r="E200" s="8">
-        <v>825211083.77</v>
+        <v>824980902.44</v>
       </c>
       <c r="F200" s="9">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="G200" s="8">
-        <v>74062898.62</v>
+        <v>73946917.53</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7396,19 +7400,19 @@
         <v>402</v>
       </c>
       <c r="C201" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D201" s="7">
-        <v>0.148666</v>
+        <v>0.149218</v>
       </c>
       <c r="E201" s="8">
-        <v>9830823041.45</v>
+        <v>9802060930.8</v>
       </c>
       <c r="F201" s="9">
-        <v>9520</v>
+        <v>9505</v>
       </c>
       <c r="G201" s="8">
-        <v>1461507690.2</v>
+        <v>1462644921.15</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7419,19 +7423,19 @@
         <v>404</v>
       </c>
       <c r="C202" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D202" s="7">
-        <v>0.014373</v>
+        <v>0.014381</v>
       </c>
       <c r="E202" s="8">
-        <v>9019277732.87</v>
+        <v>9291043836.17</v>
       </c>
       <c r="F202" s="9">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="G202" s="8">
-        <v>129637910.72</v>
+        <v>133613713.44</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7442,19 +7446,19 @@
         <v>406</v>
       </c>
       <c r="C203" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D203" s="7">
-        <v>0.027854</v>
+        <v>0.027886</v>
       </c>
       <c r="E203" s="8">
-        <v>1309091019.36</v>
+        <v>1309823817.11</v>
       </c>
       <c r="F203" s="9">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="G203" s="8">
-        <v>36463610.74</v>
+        <v>36525709.49</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7465,19 +7469,19 @@
         <v>408</v>
       </c>
       <c r="C204" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D204" s="7">
-        <v>0.117435</v>
+        <v>0.118043</v>
       </c>
       <c r="E204" s="8">
-        <v>3185988325.47</v>
+        <v>3182797132.55</v>
       </c>
       <c r="F204" s="9">
-        <v>308436</v>
+        <v>308310</v>
       </c>
       <c r="G204" s="8">
-        <v>374145221.39</v>
+        <v>375706701.01</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7488,19 +7492,19 @@
         <v>410</v>
       </c>
       <c r="C205" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D205" s="10">
-        <v>0.15523</v>
+        <v>46142</v>
+      </c>
+      <c r="D205" s="7">
+        <v>0.155854</v>
       </c>
       <c r="E205" s="8">
-        <v>443305955.02</v>
+        <v>456192816.83</v>
       </c>
       <c r="F205" s="9">
-        <v>860</v>
+        <v>877</v>
       </c>
       <c r="G205" s="8">
-        <v>68814191.07</v>
+        <v>71099448.73</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -7511,19 +7515,19 @@
         <v>412</v>
       </c>
       <c r="C206" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D206" s="7">
-        <v>0.131128</v>
+        <v>0.131687</v>
       </c>
       <c r="E206" s="8">
-        <v>2844018973.13</v>
+        <v>2879459510.77</v>
       </c>
       <c r="F206" s="9">
-        <v>5747</v>
+        <v>5745</v>
       </c>
       <c r="G206" s="8">
-        <v>372930737.08</v>
+        <v>379188794.36</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7534,19 +7538,19 @@
         <v>414</v>
       </c>
       <c r="C207" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D207" s="7">
-        <v>0.103225</v>
+        <v>0.103642</v>
       </c>
       <c r="E207" s="8">
-        <v>4272676036.99</v>
+        <v>4269892786.45</v>
       </c>
       <c r="F207" s="9">
-        <v>343280</v>
+        <v>343186</v>
       </c>
       <c r="G207" s="8">
-        <v>441048905.42</v>
+        <v>442542115.34</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7557,19 +7561,19 @@
         <v>416</v>
       </c>
       <c r="C208" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D208" s="7">
-        <v>0.105094</v>
+        <v>0.105356</v>
       </c>
       <c r="E208" s="8">
-        <v>46448190135.49</v>
+        <v>46401871546.04</v>
       </c>
       <c r="F208" s="9">
-        <v>712042</v>
+        <v>711923</v>
       </c>
       <c r="G208" s="8">
-        <v>4881432755.15</v>
+        <v>4888736128.71</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7580,19 +7584,19 @@
         <v>418</v>
       </c>
       <c r="C209" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D209" s="7">
-        <v>0.062393</v>
+        <v>0.062719</v>
       </c>
       <c r="E209" s="8">
-        <v>55667796935.32</v>
+        <v>56516503186.84</v>
       </c>
       <c r="F209" s="9">
-        <v>59497</v>
+        <v>59687</v>
       </c>
       <c r="G209" s="8">
-        <v>3473279847.29</v>
+        <v>3544645854.33</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7603,19 +7607,19 @@
         <v>420</v>
       </c>
       <c r="C210" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D210" s="10">
-        <v>0.10609</v>
+        <v>46142</v>
+      </c>
+      <c r="D210" s="7">
+        <v>0.105891</v>
       </c>
       <c r="E210" s="8">
-        <v>64718454002.69</v>
+        <v>64695974395.66</v>
       </c>
       <c r="F210" s="9">
-        <v>913737</v>
+        <v>913486</v>
       </c>
       <c r="G210" s="8">
-        <v>6866000570.75</v>
+        <v>6850722851.55</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -7626,19 +7630,19 @@
         <v>422</v>
       </c>
       <c r="C211" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D211" s="7">
-        <v>0.069473</v>
+        <v>46142</v>
+      </c>
+      <c r="D211" s="10">
+        <v>0.06953</v>
       </c>
       <c r="E211" s="8">
-        <v>54943757342.75</v>
+        <v>54889780318.6</v>
       </c>
       <c r="F211" s="9">
-        <v>55693</v>
+        <v>55599</v>
       </c>
       <c r="G211" s="8">
-        <v>3817096340.79</v>
+        <v>3816469891.5</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7649,19 +7653,19 @@
         <v>424</v>
       </c>
       <c r="C212" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D212" s="11">
-        <v>0.0968</v>
+        <v>46142</v>
+      </c>
+      <c r="D212" s="7">
+        <v>0.096911</v>
       </c>
       <c r="E212" s="8">
-        <v>16215993278.19</v>
+        <v>16184502364.37</v>
       </c>
       <c r="F212" s="9">
-        <v>342152</v>
+        <v>341685</v>
       </c>
       <c r="G212" s="8">
-        <v>1569710965.25</v>
+        <v>1568455003.77</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7672,19 +7676,19 @@
         <v>426</v>
       </c>
       <c r="C213" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D213" s="7">
-        <v>0.050747</v>
+        <v>0.050525</v>
       </c>
       <c r="E213" s="8">
-        <v>83779499591.35</v>
+        <v>83509445954.89</v>
       </c>
       <c r="F213" s="9">
-        <v>35053</v>
+        <v>34943</v>
       </c>
       <c r="G213" s="8">
-        <v>4251560505.76</v>
+        <v>4219330474.22</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -7695,19 +7699,19 @@
         <v>428</v>
       </c>
       <c r="C214" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D214" s="7">
-        <v>0.085356</v>
+        <v>0.085465</v>
       </c>
       <c r="E214" s="8">
-        <v>13980231807.1</v>
+        <v>14005989347.08</v>
       </c>
       <c r="F214" s="9">
-        <v>237055</v>
+        <v>236477</v>
       </c>
       <c r="G214" s="8">
-        <v>1193295400.99</v>
+        <v>1197026580.05</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7718,19 +7722,19 @@
         <v>430</v>
       </c>
       <c r="C215" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D215" s="7">
-        <v>0.311049</v>
+        <v>0.312965</v>
       </c>
       <c r="E215" s="8">
-        <v>12105327840.67</v>
+        <v>12118205587.38</v>
       </c>
       <c r="F215" s="9">
-        <v>57384</v>
+        <v>57459</v>
       </c>
       <c r="G215" s="8">
-        <v>3765353969.33</v>
+        <v>3792578503.88</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -7741,19 +7745,19 @@
         <v>432</v>
       </c>
       <c r="C216" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D216" s="7">
-        <v>0.217732</v>
+        <v>0.218514</v>
       </c>
       <c r="E216" s="8">
-        <v>10281179919.44</v>
+        <v>10301649681.28</v>
       </c>
       <c r="F216" s="9">
-        <v>39231</v>
+        <v>39334</v>
       </c>
       <c r="G216" s="8">
-        <v>2238542087.05</v>
+        <v>2251050715.76</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -7764,19 +7768,19 @@
         <v>434</v>
       </c>
       <c r="C217" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D217" s="7">
-        <v>1.004845</v>
+        <v>1.003736</v>
       </c>
       <c r="E217" s="8">
-        <v>746388220</v>
+        <v>744757797.72</v>
       </c>
       <c r="F217" s="9">
-        <v>4357</v>
+        <v>4354</v>
       </c>
       <c r="G217" s="8">
-        <v>750004112.63</v>
+        <v>747539881.77</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7787,19 +7791,19 @@
         <v>436</v>
       </c>
       <c r="C218" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D218" s="7">
-        <v>0.714832</v>
+        <v>0.713477</v>
       </c>
       <c r="E218" s="8">
-        <v>5934769759.01</v>
+        <v>5938050334.94</v>
       </c>
       <c r="F218" s="9">
-        <v>10987</v>
+        <v>10975</v>
       </c>
       <c r="G218" s="8">
-        <v>4242365729.53</v>
+        <v>4236664193.71</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -7810,19 +7814,19 @@
         <v>438</v>
       </c>
       <c r="C219" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D219" s="7">
-        <v>2.813218</v>
+        <v>2.806323</v>
       </c>
       <c r="E219" s="8">
-        <v>6296784937.05</v>
+        <v>6297570168.35</v>
       </c>
       <c r="F219" s="9">
-        <v>272726</v>
+        <v>272670</v>
       </c>
       <c r="G219" s="8">
-        <v>17714229723.75</v>
+        <v>17673015212.79</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -7833,19 +7837,19 @@
         <v>440</v>
       </c>
       <c r="C220" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D220" s="7">
-        <v>0.405956</v>
+        <v>0.404338</v>
       </c>
       <c r="E220" s="8">
-        <v>9433717829.88</v>
+        <v>9421159578.24</v>
       </c>
       <c r="F220" s="9">
-        <v>165749</v>
+        <v>165637</v>
       </c>
       <c r="G220" s="8">
-        <v>3829674873.55</v>
+        <v>3809334967.51</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -7856,19 +7860,19 @@
         <v>442</v>
       </c>
       <c r="C221" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D221" s="7">
-        <v>0.393117</v>
+        <v>0.393501</v>
       </c>
       <c r="E221" s="8">
-        <v>173894140656.9</v>
+        <v>174582021577.87</v>
       </c>
       <c r="F221" s="9">
-        <v>380685</v>
+        <v>381014</v>
       </c>
       <c r="G221" s="8">
-        <v>68360757041.88</v>
+        <v>68698192782.99</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -7879,19 +7883,19 @@
         <v>444</v>
       </c>
       <c r="C222" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D222" s="7">
-        <v>0.152202</v>
+        <v>0.152736</v>
       </c>
       <c r="E222" s="8">
-        <v>6420511794.66</v>
+        <v>6430680247.78</v>
       </c>
       <c r="F222" s="9">
-        <v>25256</v>
+        <v>25258</v>
       </c>
       <c r="G222" s="8">
-        <v>977213984.07</v>
+        <v>982197056.36</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -7902,19 +7906,19 @@
         <v>446</v>
       </c>
       <c r="C223" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D223" s="7">
-        <v>0.518782</v>
+        <v>0.519006</v>
       </c>
       <c r="E223" s="8">
-        <v>8113525178.59</v>
+        <v>8075868913.16</v>
       </c>
       <c r="F223" s="9">
-        <v>35791</v>
+        <v>35768</v>
       </c>
       <c r="G223" s="8">
-        <v>4209153058.33</v>
+        <v>4191420477.79</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -7925,19 +7929,19 @@
         <v>448</v>
       </c>
       <c r="C224" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D224" s="7">
-        <v>0.073886</v>
+        <v>0.073453</v>
       </c>
       <c r="E224" s="8">
-        <v>2517793740672.07</v>
+        <v>2515829788852.35</v>
       </c>
       <c r="F224" s="9">
-        <v>1247813</v>
+        <v>1247592</v>
       </c>
       <c r="G224" s="8">
-        <v>186029114361.24</v>
+        <v>184795527398.94</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -7948,19 +7952,19 @@
         <v>450</v>
       </c>
       <c r="C225" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D225" s="7">
-        <v>0.073154</v>
+        <v>0.073264</v>
       </c>
       <c r="E225" s="8">
-        <v>26598433785.77</v>
+        <v>26636392981.38</v>
       </c>
       <c r="F225" s="9">
-        <v>95478</v>
+        <v>95398</v>
       </c>
       <c r="G225" s="8">
-        <v>1945791435.97</v>
+        <v>1951475475.67</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -7971,19 +7975,19 @@
         <v>452</v>
       </c>
       <c r="C226" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D226" s="7">
-        <v>0.015143</v>
+        <v>0.014951</v>
       </c>
       <c r="E226" s="8">
-        <v>519783228917.47</v>
+        <v>519138868458.68</v>
       </c>
       <c r="F226" s="9">
-        <v>50909</v>
+        <v>50833</v>
       </c>
       <c r="G226" s="8">
-        <v>7871270709.54</v>
+        <v>7761804273.9</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -7994,19 +7998,19 @@
         <v>454</v>
       </c>
       <c r="C227" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D227" s="10">
-        <v>0.77916</v>
+        <v>46142</v>
+      </c>
+      <c r="D227" s="7">
+        <v>0.777155</v>
       </c>
       <c r="E227" s="8">
-        <v>171063136658.29</v>
+        <v>170851684102.27</v>
       </c>
       <c r="F227" s="9">
-        <v>822650</v>
+        <v>822585</v>
       </c>
       <c r="G227" s="8">
-        <v>133285558365.09</v>
+        <v>132778263752</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8017,19 +8021,19 @@
         <v>456</v>
       </c>
       <c r="C228" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D228" s="7">
-        <v>0.138172</v>
+        <v>46142</v>
+      </c>
+      <c r="D228" s="10">
+        <v>0.13788</v>
       </c>
       <c r="E228" s="8">
-        <v>27007614721.87</v>
+        <v>26976857046.96</v>
       </c>
       <c r="F228" s="9">
-        <v>194931</v>
+        <v>194847</v>
       </c>
       <c r="G228" s="8">
-        <v>3731695716.49</v>
+        <v>3719568955.45</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8040,19 +8044,19 @@
         <v>458</v>
       </c>
       <c r="C229" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D229" s="7">
-        <v>1.102071</v>
+        <v>1.100612</v>
       </c>
       <c r="E229" s="8">
-        <v>2639997894.37</v>
+        <v>2640618413.73</v>
       </c>
       <c r="F229" s="9">
-        <v>49164</v>
+        <v>49181</v>
       </c>
       <c r="G229" s="8">
-        <v>2909466433.42</v>
+        <v>2906297202.16</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8063,19 +8067,19 @@
         <v>460</v>
       </c>
       <c r="C230" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D230" s="7">
-        <v>0.282346</v>
+        <v>0.281201</v>
       </c>
       <c r="E230" s="8">
-        <v>2536534079.3</v>
+        <v>2536005458.97</v>
       </c>
       <c r="F230" s="9">
-        <v>11239</v>
+        <v>11226</v>
       </c>
       <c r="G230" s="8">
-        <v>716180345.63</v>
+        <v>713128194.03</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8086,19 +8090,19 @@
         <v>462</v>
       </c>
       <c r="C231" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D231" s="7">
-        <v>1.123211</v>
+        <v>1.121441</v>
       </c>
       <c r="E231" s="8">
-        <v>5217940147.84</v>
+        <v>5220206564.18</v>
       </c>
       <c r="F231" s="9">
-        <v>63782</v>
+        <v>63697</v>
       </c>
       <c r="G231" s="8">
-        <v>5860846151.87</v>
+        <v>5854152141.66</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8109,19 +8113,19 @@
         <v>464</v>
       </c>
       <c r="C232" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D232" s="7">
-        <v>0.375143</v>
+        <v>0.375686</v>
       </c>
       <c r="E232" s="8">
-        <v>18542018146.13</v>
+        <v>18661785631.26</v>
       </c>
       <c r="F232" s="9">
-        <v>149588</v>
+        <v>149781</v>
       </c>
       <c r="G232" s="8">
-        <v>6955900831.97</v>
+        <v>7010973857.34</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8132,19 +8136,19 @@
         <v>466</v>
       </c>
       <c r="C233" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D233" s="7">
-        <v>0.107548</v>
+        <v>0.107345</v>
       </c>
       <c r="E233" s="8">
-        <v>278000281558.02</v>
+        <v>277900325185.33</v>
       </c>
       <c r="F233" s="9">
-        <v>1510210</v>
+        <v>1509312</v>
       </c>
       <c r="G233" s="8">
-        <v>29898466579.45</v>
+        <v>29831280882.46</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8155,19 +8159,19 @@
         <v>468</v>
       </c>
       <c r="C234" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D234" s="7">
-        <v>0.262337</v>
+        <v>0.261937</v>
       </c>
       <c r="E234" s="8">
-        <v>3265366887.4</v>
+        <v>3261793326.12</v>
       </c>
       <c r="F234" s="9">
         <v>10508</v>
       </c>
       <c r="G234" s="8">
-        <v>856625444.05</v>
+        <v>854385137.85</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8178,19 +8182,19 @@
         <v>470</v>
       </c>
       <c r="C235" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D235" s="7">
-        <v>0.785263</v>
+        <v>0.784107</v>
       </c>
       <c r="E235" s="8">
-        <v>1344096983.87</v>
+        <v>1343564740.63</v>
       </c>
       <c r="F235" s="9">
-        <v>7642</v>
+        <v>7636</v>
       </c>
       <c r="G235" s="8">
-        <v>1055470279.89</v>
+        <v>1053498032.97</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8201,19 +8205,19 @@
         <v>472</v>
       </c>
       <c r="C236" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D236" s="7">
-        <v>0.151377</v>
+        <v>0.152037</v>
       </c>
       <c r="E236" s="8">
-        <v>71106188111.84</v>
+        <v>71058868804.34</v>
       </c>
       <c r="F236" s="9">
-        <v>824534</v>
+        <v>824006</v>
       </c>
       <c r="G236" s="8">
-        <v>10763815316.91</v>
+        <v>10803602670.81</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8224,19 +8228,19 @@
         <v>474</v>
       </c>
       <c r="C237" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D237" s="7">
-        <v>0.221831</v>
+        <v>0.221533</v>
       </c>
       <c r="E237" s="8">
-        <v>2428402068.08</v>
+        <v>2427601509.45</v>
       </c>
       <c r="F237" s="9">
-        <v>7584</v>
+        <v>7583</v>
       </c>
       <c r="G237" s="8">
-        <v>538694118.32</v>
+        <v>537793079.51</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -8247,19 +8251,19 @@
         <v>476</v>
       </c>
       <c r="C238" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D238" s="7">
-        <v>0.195619</v>
+        <v>0.195191</v>
       </c>
       <c r="E238" s="8">
-        <v>2322066100.25</v>
+        <v>2320766722.29</v>
       </c>
       <c r="F238" s="9">
-        <v>7333</v>
+        <v>7334</v>
       </c>
       <c r="G238" s="8">
-        <v>454240038.32</v>
+        <v>452992576.46</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -8270,19 +8274,19 @@
         <v>478</v>
       </c>
       <c r="C239" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D239" s="7">
-        <v>0.339138</v>
+        <v>0.339043</v>
       </c>
       <c r="E239" s="8">
-        <v>31285651277.78</v>
+        <v>31290084494.79</v>
       </c>
       <c r="F239" s="9">
-        <v>119974</v>
+        <v>119926</v>
       </c>
       <c r="G239" s="8">
-        <v>10610164056.25</v>
+        <v>10608691706.46</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -8293,19 +8297,19 @@
         <v>480</v>
       </c>
       <c r="C240" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D240" s="7">
-        <v>0.125866</v>
+        <v>0.125818</v>
       </c>
       <c r="E240" s="8">
-        <v>3793668407.47</v>
+        <v>3792343938.26</v>
       </c>
       <c r="F240" s="9">
-        <v>7437</v>
+        <v>7435</v>
       </c>
       <c r="G240" s="8">
-        <v>477494358.29</v>
+        <v>477146574.52</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -8316,19 +8320,19 @@
         <v>482</v>
       </c>
       <c r="C241" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D241" s="7">
-        <v>0.127039</v>
+        <v>0.126997</v>
       </c>
       <c r="E241" s="8">
-        <v>89615779460.91</v>
+        <v>89606546481.24</v>
       </c>
       <c r="F241" s="9">
-        <v>403445</v>
+        <v>403224</v>
       </c>
       <c r="G241" s="8">
-        <v>11384694540.32</v>
+        <v>11379768984.1</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -8339,19 +8343,19 @@
         <v>484</v>
       </c>
       <c r="C242" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D242" s="7">
-        <v>0.299947</v>
+        <v>0.302439</v>
       </c>
       <c r="E242" s="8">
-        <v>3853187009.6</v>
+        <v>3856676444.54</v>
       </c>
       <c r="F242" s="9">
-        <v>18075</v>
+        <v>18084</v>
       </c>
       <c r="G242" s="8">
-        <v>1155753485.28</v>
+        <v>1166409513.16</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8362,19 +8366,19 @@
         <v>486</v>
       </c>
       <c r="C243" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D243" s="7">
-        <v>0.080989</v>
+        <v>0.081085</v>
       </c>
       <c r="E243" s="8">
-        <v>3844546281.23</v>
+        <v>3842808537.52</v>
       </c>
       <c r="F243" s="9">
-        <v>9208</v>
+        <v>9192</v>
       </c>
       <c r="G243" s="8">
-        <v>311366625.3</v>
+        <v>311594897.6</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -8385,19 +8389,19 @@
         <v>488</v>
       </c>
       <c r="C244" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D244" s="7">
-        <v>0.241844</v>
+        <v>46142</v>
+      </c>
+      <c r="D244" s="10">
+        <v>0.24359</v>
       </c>
       <c r="E244" s="8">
-        <v>2835432687.44</v>
+        <v>2835644450.99</v>
       </c>
       <c r="F244" s="9">
-        <v>14013</v>
+        <v>14014</v>
       </c>
       <c r="G244" s="8">
-        <v>685732228.39</v>
+        <v>690734182.41</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8408,19 +8412,19 @@
         <v>490</v>
       </c>
       <c r="C245" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D245" s="10">
-        <v>0.06868</v>
+        <v>46142</v>
+      </c>
+      <c r="D245" s="7">
+        <v>0.068763</v>
       </c>
       <c r="E245" s="8">
-        <v>4038059488.43</v>
+        <v>4036434237.38</v>
       </c>
       <c r="F245" s="9">
-        <v>7793</v>
+        <v>7779</v>
       </c>
       <c r="G245" s="8">
-        <v>277334323.24</v>
+        <v>277557643.27</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -8431,19 +8435,19 @@
         <v>492</v>
       </c>
       <c r="C246" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D246" s="7">
-        <v>0.178278</v>
+        <v>46142</v>
+      </c>
+      <c r="D246" s="10">
+        <v>0.17859</v>
       </c>
       <c r="E246" s="8">
-        <v>14275666117.29</v>
+        <v>14278357563.36</v>
       </c>
       <c r="F246" s="9">
-        <v>48620</v>
+        <v>48637</v>
       </c>
       <c r="G246" s="8">
-        <v>2545034807.55</v>
+        <v>2549976731.11</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8454,19 +8458,19 @@
         <v>494</v>
       </c>
       <c r="C247" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D247" s="7">
-        <v>0.023928</v>
+        <v>0.023645</v>
       </c>
       <c r="E247" s="8">
-        <v>967020000578.09</v>
+        <v>964906796345.7</v>
       </c>
       <c r="F247" s="9">
-        <v>187553</v>
+        <v>187471</v>
       </c>
       <c r="G247" s="8">
-        <v>23138997643.39</v>
+        <v>22814895195.43</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8477,19 +8481,19 @@
         <v>496</v>
       </c>
       <c r="C248" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D248" s="7">
-        <v>0.735659</v>
+        <v>0.733571</v>
       </c>
       <c r="E248" s="8">
-        <v>15385417173.43</v>
+        <v>15383081374.81</v>
       </c>
       <c r="F248" s="9">
-        <v>79516</v>
+        <v>79510</v>
       </c>
       <c r="G248" s="8">
-        <v>11318418498.06</v>
+        <v>11284578617.15</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8500,19 +8504,19 @@
         <v>498</v>
       </c>
       <c r="C249" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D249" s="7">
-        <v>0.639305</v>
+        <v>0.636664</v>
       </c>
       <c r="E249" s="8">
-        <v>8210364110.18</v>
+        <v>8209283348.56</v>
       </c>
       <c r="F249" s="9">
-        <v>74457</v>
+        <v>74654</v>
       </c>
       <c r="G249" s="8">
-        <v>5248923628.85</v>
+        <v>5226554384.07</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8523,19 +8527,19 @@
         <v>500</v>
       </c>
       <c r="C250" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D250" s="7">
-        <v>0.160978</v>
+        <v>0.160798</v>
       </c>
       <c r="E250" s="8">
-        <v>2778714335.86</v>
+        <v>2777242549.81</v>
       </c>
       <c r="F250" s="9">
-        <v>11312</v>
+        <v>11314</v>
       </c>
       <c r="G250" s="8">
-        <v>447311806.35</v>
+        <v>446576211.72</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8546,19 +8550,19 @@
         <v>502</v>
       </c>
       <c r="C251" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D251" s="10">
-        <v>0.09599</v>
+        <v>46142</v>
+      </c>
+      <c r="D251" s="7">
+        <v>0.095923</v>
       </c>
       <c r="E251" s="8">
-        <v>4857553745.87</v>
+        <v>4861121217.81</v>
       </c>
       <c r="F251" s="9">
-        <v>69485</v>
+        <v>69471</v>
       </c>
       <c r="G251" s="8">
-        <v>466274757.16</v>
+        <v>466291751.9</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8569,19 +8573,19 @@
         <v>504</v>
       </c>
       <c r="C252" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D252" s="7">
-        <v>0.328574</v>
+        <v>46142</v>
+      </c>
+      <c r="D252" s="10">
+        <v>0.32807</v>
       </c>
       <c r="E252" s="8">
-        <v>2197898273.46</v>
+        <v>2199627706.36</v>
       </c>
       <c r="F252" s="9">
-        <v>20959</v>
+        <v>20991</v>
       </c>
       <c r="G252" s="8">
-        <v>722171923.19</v>
+        <v>721632788.6</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8592,19 +8596,19 @@
         <v>506</v>
       </c>
       <c r="C253" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D253" s="7">
-        <v>0.139984</v>
+        <v>0.140127</v>
       </c>
       <c r="E253" s="8">
-        <v>658499130.57</v>
+        <v>659477798</v>
       </c>
       <c r="F253" s="9">
-        <v>2352</v>
+        <v>2364</v>
       </c>
       <c r="G253" s="8">
-        <v>92179463.02</v>
+        <v>92410501.36</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8615,19 +8619,19 @@
         <v>508</v>
       </c>
       <c r="C254" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D254" s="7">
-        <v>0.082416</v>
+        <v>0.082514</v>
       </c>
       <c r="E254" s="8">
-        <v>640246570.8</v>
+        <v>639053329.41</v>
       </c>
       <c r="F254" s="9">
-        <v>13944</v>
+        <v>13903</v>
       </c>
       <c r="G254" s="8">
-        <v>52766457.71</v>
+        <v>52730720.47</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8638,19 +8642,19 @@
         <v>510</v>
       </c>
       <c r="C255" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D255" s="7">
-        <v>0.095699</v>
+        <v>0.096054</v>
       </c>
       <c r="E255" s="8">
-        <v>4027134800.3</v>
+        <v>4026898356.07</v>
       </c>
       <c r="F255" s="9">
-        <v>78547</v>
+        <v>78527</v>
       </c>
       <c r="G255" s="8">
-        <v>385391441.58</v>
+        <v>386801655.33</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8661,19 +8665,19 @@
         <v>512</v>
       </c>
       <c r="C256" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D256" s="7">
-        <v>0.126809</v>
+        <v>0.126934</v>
       </c>
       <c r="E256" s="8">
-        <v>3758424863.8</v>
+        <v>3759139697.81</v>
       </c>
       <c r="F256" s="9">
-        <v>19630</v>
+        <v>19635</v>
       </c>
       <c r="G256" s="8">
-        <v>476600420.23</v>
+        <v>477162891.44</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8684,19 +8688,19 @@
         <v>514</v>
       </c>
       <c r="C257" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D257" s="7">
-        <v>0.093246</v>
+        <v>0.093348</v>
       </c>
       <c r="E257" s="8">
-        <v>585937224.82</v>
+        <v>577933182.44</v>
       </c>
       <c r="F257" s="9">
-        <v>10594</v>
+        <v>10348</v>
       </c>
       <c r="G257" s="8">
-        <v>54636217.45</v>
+        <v>53949107.37</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -8707,19 +8711,19 @@
         <v>516</v>
       </c>
       <c r="C258" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D258" s="7">
-        <v>0.131911</v>
+        <v>0.132044</v>
       </c>
       <c r="E258" s="8">
-        <v>4428574691.65</v>
+        <v>4430823195</v>
       </c>
       <c r="F258" s="9">
-        <v>18356</v>
+        <v>18048</v>
       </c>
       <c r="G258" s="8">
-        <v>584176817.46</v>
+        <v>585065473.29</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -8730,19 +8734,19 @@
         <v>518</v>
       </c>
       <c r="C259" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D259" s="7">
-        <v>0.153043</v>
+        <v>0.153199</v>
       </c>
       <c r="E259" s="8">
-        <v>1196825814.88</v>
+        <v>1196816626.49</v>
       </c>
       <c r="F259" s="9">
-        <v>58187</v>
+        <v>58181</v>
       </c>
       <c r="G259" s="8">
-        <v>183165673.38</v>
+        <v>183350792.3</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -8753,19 +8757,19 @@
         <v>520</v>
       </c>
       <c r="C260" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D260" s="7">
-        <v>0.764824</v>
+        <v>0.761676</v>
       </c>
       <c r="E260" s="8">
-        <v>8930088711.27</v>
+        <v>8920918906.85</v>
       </c>
       <c r="F260" s="9">
-        <v>25955</v>
+        <v>25962</v>
       </c>
       <c r="G260" s="8">
-        <v>6829949381.75</v>
+        <v>6794849849.68</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -8776,19 +8780,19 @@
         <v>522</v>
       </c>
       <c r="C261" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D261" s="7">
-        <v>0.101851</v>
+        <v>0.101679</v>
       </c>
       <c r="E261" s="8">
-        <v>13792489849.86</v>
+        <v>13782857755.93</v>
       </c>
       <c r="F261" s="9">
-        <v>126055</v>
+        <v>126030</v>
       </c>
       <c r="G261" s="8">
-        <v>1404773379.28</v>
+        <v>1401432097.31</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -8799,19 +8803,19 @@
         <v>524</v>
       </c>
       <c r="C262" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D262" s="7">
-        <v>0.013082</v>
+        <v>0.013095</v>
       </c>
       <c r="E262" s="8">
-        <v>138945963105.6</v>
+        <v>143478313978.47</v>
       </c>
       <c r="F262" s="9">
-        <v>1615</v>
+        <v>1626</v>
       </c>
       <c r="G262" s="8">
-        <v>1817732011.57</v>
+        <v>1878806242.92</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -8822,19 +8826,19 @@
         <v>526</v>
       </c>
       <c r="C263" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D263" s="7">
-        <v>0.279659</v>
+        <v>0.277966</v>
       </c>
       <c r="E263" s="8">
-        <v>5705138568.5</v>
+        <v>5711665454.39</v>
       </c>
       <c r="F263" s="9">
-        <v>44090</v>
+        <v>44076</v>
       </c>
       <c r="G263" s="8">
-        <v>1595496053.16</v>
+        <v>1587648949.88</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -8845,19 +8849,19 @@
         <v>528</v>
       </c>
       <c r="C264" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D264" s="7">
-        <v>0.401815</v>
+        <v>0.403146</v>
       </c>
       <c r="E264" s="8">
-        <v>1949645999.27</v>
+        <v>1951913435.05</v>
       </c>
       <c r="F264" s="9">
-        <v>21817</v>
+        <v>21805</v>
       </c>
       <c r="G264" s="8">
-        <v>783396544.92</v>
+        <v>786905553.47</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -8868,19 +8872,19 @@
         <v>530</v>
       </c>
       <c r="C265" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D265" s="7">
-        <v>0.130539</v>
+        <v>0.130276</v>
       </c>
       <c r="E265" s="8">
-        <v>33759101872.08</v>
+        <v>33867749328.21</v>
       </c>
       <c r="F265" s="9">
-        <v>101934</v>
+        <v>102165</v>
       </c>
       <c r="G265" s="8">
-        <v>4406877482.2</v>
+        <v>4412163853.54</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -8891,19 +8895,19 @@
         <v>532</v>
       </c>
       <c r="C266" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D266" s="7">
-        <v>0.237135</v>
+        <v>0.236204</v>
       </c>
       <c r="E266" s="8">
-        <v>2678688809.22</v>
+        <v>2678522212.07</v>
       </c>
       <c r="F266" s="9">
-        <v>24247</v>
+        <v>24241</v>
       </c>
       <c r="G266" s="8">
-        <v>635210392.57</v>
+        <v>632678679.88</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -8914,19 +8918,19 @@
         <v>534</v>
       </c>
       <c r="C267" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D267" s="7">
-        <v>0.012692</v>
+        <v>0.012659</v>
       </c>
       <c r="E267" s="8">
-        <v>688356287059.04</v>
+        <v>710448887568.42</v>
       </c>
       <c r="F267" s="9">
-        <v>70644</v>
+        <v>71003</v>
       </c>
       <c r="G267" s="8">
-        <v>8736397931.83</v>
+        <v>8993797065.42</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -8937,19 +8941,19 @@
         <v>536</v>
       </c>
       <c r="C268" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D268" s="7">
-        <v>0.499777</v>
+        <v>46142</v>
+      </c>
+      <c r="D268" s="11">
+        <v>0.4995</v>
       </c>
       <c r="E268" s="8">
-        <v>5693178381</v>
+        <v>5696371661.33</v>
       </c>
       <c r="F268" s="9">
-        <v>72424</v>
+        <v>72388</v>
       </c>
       <c r="G268" s="8">
-        <v>2845319439.06</v>
+        <v>2845335891.13</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -8960,19 +8964,19 @@
         <v>538</v>
       </c>
       <c r="C269" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D269" s="7">
-        <v>0.302416</v>
+        <v>0.301521</v>
       </c>
       <c r="E269" s="8">
-        <v>1834552554.35</v>
+        <v>1834134186.9</v>
       </c>
       <c r="F269" s="9">
-        <v>95728</v>
+        <v>95687</v>
       </c>
       <c r="G269" s="8">
-        <v>554797674.44</v>
+        <v>553029666.43</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -8983,19 +8987,19 @@
         <v>540</v>
       </c>
       <c r="C270" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D270" s="10">
-        <v>0.78236</v>
+        <v>46142</v>
+      </c>
+      <c r="D270" s="7">
+        <v>0.779073</v>
       </c>
       <c r="E270" s="8">
-        <v>2055404229.39</v>
+        <v>2053919745.68</v>
       </c>
       <c r="F270" s="9">
-        <v>111780</v>
+        <v>111761</v>
       </c>
       <c r="G270" s="8">
-        <v>1608065759.75</v>
+        <v>1600152520.61</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9006,19 +9010,19 @@
         <v>542</v>
       </c>
       <c r="C271" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D271" s="7">
-        <v>0.527174</v>
+        <v>0.524592</v>
       </c>
       <c r="E271" s="8">
-        <v>1502621742.38</v>
+        <v>1502313969.69</v>
       </c>
       <c r="F271" s="9">
-        <v>37731</v>
+        <v>37721</v>
       </c>
       <c r="G271" s="8">
-        <v>792143516.89</v>
+        <v>788102553.46</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9029,19 +9033,19 @@
         <v>544</v>
       </c>
       <c r="C272" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D272" s="7">
-        <v>0.284569</v>
+        <v>46142</v>
+      </c>
+      <c r="D272" s="11">
+        <v>0.2838</v>
       </c>
       <c r="E272" s="8">
-        <v>2821640674.1</v>
+        <v>2821878758.36</v>
       </c>
       <c r="F272" s="9">
-        <v>87422</v>
+        <v>87333</v>
       </c>
       <c r="G272" s="8">
-        <v>802951202.34</v>
+        <v>800850382.45</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9052,19 +9056,19 @@
         <v>546</v>
       </c>
       <c r="C273" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D273" s="7">
-        <v>2.423214</v>
+        <v>2.406671</v>
       </c>
       <c r="E273" s="8">
-        <v>1895378432.32</v>
+        <v>1896324401.64</v>
       </c>
       <c r="F273" s="9">
-        <v>57654</v>
+        <v>57633</v>
       </c>
       <c r="G273" s="8">
-        <v>4592907724.88</v>
+        <v>4563828201.89</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9075,19 +9079,19 @@
         <v>548</v>
       </c>
       <c r="C274" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D274" s="10">
-        <v>0.90416</v>
+        <v>0.90413</v>
       </c>
       <c r="E274" s="8">
-        <v>768749156.17</v>
+        <v>768973261.32</v>
       </c>
       <c r="F274" s="9">
-        <v>83410</v>
+        <v>83401</v>
       </c>
       <c r="G274" s="8">
-        <v>695072583.21</v>
+        <v>695252080.93</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9098,19 +9102,19 @@
         <v>550</v>
       </c>
       <c r="C275" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D275" s="10">
-        <v>0.37341</v>
+        <v>46142</v>
+      </c>
+      <c r="D275" s="7">
+        <v>0.373765</v>
       </c>
       <c r="E275" s="8">
-        <v>8974941871.71</v>
+        <v>8955233315.4</v>
       </c>
       <c r="F275" s="9">
-        <v>101619</v>
+        <v>100765</v>
       </c>
       <c r="G275" s="8">
-        <v>3351336484.97</v>
+        <v>3347149611.48</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9121,19 +9125,19 @@
         <v>552</v>
       </c>
       <c r="C276" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D276" s="7">
-        <v>0.109958</v>
+        <v>0.109839</v>
       </c>
       <c r="E276" s="8">
-        <v>54265171981.15</v>
+        <v>54221370684.51</v>
       </c>
       <c r="F276" s="9">
-        <v>198172</v>
+        <v>198053</v>
       </c>
       <c r="G276" s="8">
-        <v>5966888738.81</v>
+        <v>5955617505.04</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9144,19 +9148,19 @@
         <v>554</v>
       </c>
       <c r="C277" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D277" s="7">
-        <v>0.113688</v>
+        <v>0.113942</v>
       </c>
       <c r="E277" s="8">
-        <v>82095872418.96</v>
+        <v>82048920262.29</v>
       </c>
       <c r="F277" s="9">
-        <v>1066373</v>
+        <v>1065982</v>
       </c>
       <c r="G277" s="8">
-        <v>9333292510.96</v>
+        <v>9348791002.7</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9167,19 +9171,19 @@
         <v>556</v>
       </c>
       <c r="C278" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D278" s="7">
-        <v>0.140836</v>
+        <v>46142</v>
+      </c>
+      <c r="D278" s="10">
+        <v>0.14159</v>
       </c>
       <c r="E278" s="8">
-        <v>33142021927.7</v>
+        <v>33138727446.89</v>
       </c>
       <c r="F278" s="9">
-        <v>328694</v>
+        <v>328636</v>
       </c>
       <c r="G278" s="8">
-        <v>4667583107.15</v>
+        <v>4692114498.16</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9190,19 +9194,19 @@
         <v>558</v>
       </c>
       <c r="C279" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D279" s="7">
-        <v>0.166843</v>
+        <v>0.167294</v>
       </c>
       <c r="E279" s="8">
-        <v>3122038143.05</v>
+        <v>3134858570.62</v>
       </c>
       <c r="F279" s="9">
-        <v>27399</v>
+        <v>27408</v>
       </c>
       <c r="G279" s="8">
-        <v>520890106.4</v>
+        <v>524441778.19</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9213,19 +9217,19 @@
         <v>560</v>
       </c>
       <c r="C280" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D280" s="7">
-        <v>0.722404</v>
+        <v>0.720852</v>
       </c>
       <c r="E280" s="8">
-        <v>44316728794.72</v>
+        <v>44294043900.09</v>
       </c>
       <c r="F280" s="9">
-        <v>673696</v>
+        <v>673682</v>
       </c>
       <c r="G280" s="8">
-        <v>32014587232.76</v>
+        <v>31929446402.63</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -9236,19 +9240,19 @@
         <v>562</v>
       </c>
       <c r="C281" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D281" s="7">
-        <v>0.260639</v>
+        <v>0.259561</v>
       </c>
       <c r="E281" s="8">
-        <v>8738878558.88</v>
+        <v>8737122301.07</v>
       </c>
       <c r="F281" s="9">
-        <v>108579</v>
+        <v>108595</v>
       </c>
       <c r="G281" s="8">
-        <v>2277691941.16</v>
+        <v>2267814728</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -9259,19 +9263,19 @@
         <v>564</v>
       </c>
       <c r="C282" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D282" s="7">
-        <v>0.529558</v>
+        <v>0.532368</v>
       </c>
       <c r="E282" s="8">
-        <v>11605363993.96</v>
+        <v>11633964009.16</v>
       </c>
       <c r="F282" s="9">
-        <v>138971</v>
+        <v>138997</v>
       </c>
       <c r="G282" s="8">
-        <v>6145718554.64</v>
+        <v>6193551280.76</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -9282,19 +9286,19 @@
         <v>566</v>
       </c>
       <c r="C283" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D283" s="7">
-        <v>0.301243</v>
+        <v>0.301887</v>
       </c>
       <c r="E283" s="8">
-        <v>2288387573.72</v>
+        <v>2287510758.32</v>
       </c>
       <c r="F283" s="9">
-        <v>37408</v>
+        <v>37397</v>
       </c>
       <c r="G283" s="8">
-        <v>689359731.08</v>
+        <v>690569524.82</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -9305,19 +9309,19 @@
         <v>568</v>
       </c>
       <c r="C284" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D284" s="7">
-        <v>0.196737</v>
+        <v>0.196678</v>
       </c>
       <c r="E284" s="8">
-        <v>9520104601.01</v>
+        <v>9518803540.23</v>
       </c>
       <c r="F284" s="9">
-        <v>108282</v>
+        <v>108242</v>
       </c>
       <c r="G284" s="8">
-        <v>1872957847.09</v>
+        <v>1872138108.25</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -9328,19 +9332,19 @@
         <v>570</v>
       </c>
       <c r="C285" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D285" s="7">
-        <v>0.274903</v>
+        <v>0.276234</v>
       </c>
       <c r="E285" s="8">
-        <v>787815582.88</v>
+        <v>789274178.64</v>
       </c>
       <c r="F285" s="9">
-        <v>2807</v>
+        <v>2805</v>
       </c>
       <c r="G285" s="8">
-        <v>216572937.77</v>
+        <v>218024043.98</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -9351,19 +9355,19 @@
         <v>572</v>
       </c>
       <c r="C286" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D286" s="7">
-        <v>0.087341</v>
+        <v>0.087432</v>
       </c>
       <c r="E286" s="8">
-        <v>4171921319.57</v>
+        <v>4161016735.62</v>
       </c>
       <c r="F286" s="9">
-        <v>145692</v>
+        <v>145544</v>
       </c>
       <c r="G286" s="8">
-        <v>364378737.81</v>
+        <v>363807518.63</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -9374,19 +9378,19 @@
         <v>574</v>
       </c>
       <c r="C287" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D287" s="7">
-        <v>0.472332</v>
+        <v>0.474073</v>
       </c>
       <c r="E287" s="8">
-        <v>1574639738.39</v>
+        <v>1576891773.22</v>
       </c>
       <c r="F287" s="9">
-        <v>4274</v>
+        <v>4273</v>
       </c>
       <c r="G287" s="8">
-        <v>743752642.69</v>
+        <v>747561485.68</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -9397,19 +9401,19 @@
         <v>576</v>
       </c>
       <c r="C288" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D288" s="11">
-        <v>0.0155</v>
+        <v>46142</v>
+      </c>
+      <c r="D288" s="7">
+        <v>0.015507</v>
       </c>
       <c r="E288" s="8">
-        <v>5656365496.91</v>
+        <v>5699659003.5</v>
       </c>
       <c r="F288" s="9">
-        <v>3625</v>
+        <v>3637</v>
       </c>
       <c r="G288" s="8">
-        <v>87671054.97</v>
+        <v>88382768.73</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -9420,19 +9424,19 @@
         <v>578</v>
       </c>
       <c r="C289" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D289" s="7">
-        <v>0.017321</v>
+        <v>0.017207</v>
       </c>
       <c r="E289" s="8">
-        <v>152483264046.77</v>
+        <v>152319459239.81</v>
       </c>
       <c r="F289" s="9">
-        <v>31715</v>
+        <v>31687</v>
       </c>
       <c r="G289" s="8">
-        <v>2641108578.27</v>
+        <v>2620970749.68</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -9443,19 +9447,19 @@
         <v>580</v>
       </c>
       <c r="C290" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D290" s="7">
-        <v>0.010584</v>
+        <v>0.010573</v>
       </c>
       <c r="E290" s="8">
-        <v>6055906905.09</v>
+        <v>6561304899</v>
       </c>
       <c r="F290" s="9">
-        <v>933</v>
+        <v>1134</v>
       </c>
       <c r="G290" s="8">
-        <v>64094960.41</v>
+        <v>69375619.24</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -9466,19 +9470,19 @@
         <v>582</v>
       </c>
       <c r="C291" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D291" s="7">
-        <v>0.132272</v>
+        <v>0.131366</v>
       </c>
       <c r="E291" s="8">
-        <v>52919291646.02</v>
+        <v>52832154949.5</v>
       </c>
       <c r="F291" s="9">
-        <v>107862</v>
+        <v>107864</v>
       </c>
       <c r="G291" s="8">
-        <v>6999744863.81</v>
+        <v>6940324096.04</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -9489,19 +9493,19 @@
         <v>584</v>
       </c>
       <c r="C292" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D292" s="7">
-        <v>0.050936</v>
+        <v>0.050991</v>
       </c>
       <c r="E292" s="8">
-        <v>12218901995.93</v>
+        <v>12260534475.79</v>
       </c>
       <c r="F292" s="9">
-        <v>28478</v>
+        <v>28567</v>
       </c>
       <c r="G292" s="8">
-        <v>622379548.89</v>
+        <v>625174798.47</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -9512,19 +9516,19 @@
         <v>586</v>
       </c>
       <c r="C293" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D293" s="7">
-        <v>0.021911</v>
+        <v>0.021936</v>
       </c>
       <c r="E293" s="8">
-        <v>56148025020.09</v>
+        <v>57690584505.43</v>
       </c>
       <c r="F293" s="9">
         <v>10722</v>
       </c>
       <c r="G293" s="8">
-        <v>1230276642.43</v>
+        <v>1265516227.86</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -9535,19 +9539,19 @@
         <v>588</v>
       </c>
       <c r="C294" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D294" s="7">
-        <v>0.031162</v>
+        <v>0.031339</v>
       </c>
       <c r="E294" s="8">
-        <v>54560224838.31</v>
+        <v>54739512284.2</v>
       </c>
       <c r="F294" s="9">
-        <v>33109</v>
+        <v>33200</v>
       </c>
       <c r="G294" s="8">
-        <v>1700220746.88</v>
+        <v>1715472548.12</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -9558,19 +9562,19 @@
         <v>590</v>
       </c>
       <c r="C295" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D295" s="7">
-        <v>0.019247</v>
+        <v>0.019201</v>
       </c>
       <c r="E295" s="8">
-        <v>967605521962.45</v>
+        <v>965588850391.31</v>
       </c>
       <c r="F295" s="9">
-        <v>179400</v>
+        <v>179306</v>
       </c>
       <c r="G295" s="8">
-        <v>18623671053.2</v>
+        <v>18540731258.42</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -9581,19 +9585,19 @@
         <v>592</v>
       </c>
       <c r="C296" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D296" s="7">
-        <v>0.101132</v>
+        <v>0.101041</v>
       </c>
       <c r="E296" s="8">
-        <v>37094236482.2</v>
+        <v>37045829972.36</v>
       </c>
       <c r="F296" s="9">
-        <v>382744</v>
+        <v>382554</v>
       </c>
       <c r="G296" s="8">
-        <v>3751431152.15</v>
+        <v>3743165669.6</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -9604,19 +9608,19 @@
         <v>594</v>
       </c>
       <c r="C297" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D297" s="7">
-        <v>0.085904</v>
+        <v>0.085847</v>
       </c>
       <c r="E297" s="8">
-        <v>38426944921.22</v>
+        <v>38406069828.23</v>
       </c>
       <c r="F297" s="9">
-        <v>48212</v>
+        <v>48186</v>
       </c>
       <c r="G297" s="8">
-        <v>3301024521.17</v>
+        <v>3297046769.65</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -9627,19 +9631,19 @@
         <v>596</v>
       </c>
       <c r="C298" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D298" s="7">
-        <v>0.094154</v>
+        <v>0.094503</v>
       </c>
       <c r="E298" s="8">
-        <v>39136096470.62</v>
+        <v>39092102702.4</v>
       </c>
       <c r="F298" s="9">
-        <v>527622</v>
+        <v>527402</v>
       </c>
       <c r="G298" s="8">
-        <v>3684837734.26</v>
+        <v>3694337923.9</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -9650,19 +9654,19 @@
         <v>598</v>
       </c>
       <c r="C299" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D299" s="7">
-        <v>0.020004</v>
+        <v>0.020061</v>
       </c>
       <c r="E299" s="8">
-        <v>34406609096.89</v>
+        <v>34690049853.8</v>
       </c>
       <c r="F299" s="9">
-        <v>24738</v>
+        <v>24856</v>
       </c>
       <c r="G299" s="8">
-        <v>688260245.26</v>
+        <v>695904586.9</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -9673,19 +9677,19 @@
         <v>600</v>
       </c>
       <c r="C300" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D300" s="7">
-        <v>0.010262</v>
+        <v>0.010276</v>
       </c>
       <c r="E300" s="8">
-        <v>2048890132.37</v>
+        <v>2334162064.25</v>
       </c>
       <c r="F300" s="9">
-        <v>436</v>
+        <v>534</v>
       </c>
       <c r="G300" s="8">
-        <v>21026155.28</v>
+        <v>23985797.48</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -9696,19 +9700,19 @@
         <v>602</v>
       </c>
       <c r="C301" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D301" s="7">
-        <v>0.015178</v>
+        <v>0.015338</v>
       </c>
       <c r="E301" s="8">
-        <v>23792394381.58</v>
+        <v>24160026960.09</v>
       </c>
       <c r="F301" s="9">
-        <v>10946</v>
+        <v>10988</v>
       </c>
       <c r="G301" s="8">
-        <v>361130266.38</v>
+        <v>370560246.3</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -9719,19 +9723,19 @@
         <v>604</v>
       </c>
       <c r="C302" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D302" s="7">
-        <v>0.017716</v>
+        <v>0.017766</v>
       </c>
       <c r="E302" s="8">
-        <v>11889133333.05</v>
+        <v>11890620094.4</v>
       </c>
       <c r="F302" s="9">
-        <v>6664</v>
+        <v>6665</v>
       </c>
       <c r="G302" s="8">
-        <v>210627519.99</v>
+        <v>211248150</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -9742,19 +9746,19 @@
         <v>606</v>
       </c>
       <c r="C303" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D303" s="7">
-        <v>0.093968</v>
+        <v>0.093844</v>
       </c>
       <c r="E303" s="8">
-        <v>21287606753.8</v>
+        <v>21275846184.66</v>
       </c>
       <c r="F303" s="9">
-        <v>347503</v>
+        <v>347591</v>
       </c>
       <c r="G303" s="8">
-        <v>2000351717.98</v>
+        <v>1996619215.6</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -9765,19 +9769,19 @@
         <v>608</v>
       </c>
       <c r="C304" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D304" s="7">
-        <v>0.018851</v>
+        <v>0.018795</v>
       </c>
       <c r="E304" s="8">
-        <v>10528013632.95</v>
+        <v>10440440253.01</v>
       </c>
       <c r="F304" s="9">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G304" s="8">
-        <v>198467214.54</v>
+        <v>196227761.33</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -9788,19 +9792,19 @@
         <v>610</v>
       </c>
       <c r="C305" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D305" s="7">
-        <v>0.015561</v>
+        <v>0.015522</v>
       </c>
       <c r="E305" s="8">
-        <v>9151732155.5</v>
+        <v>9168015480.96</v>
       </c>
       <c r="F305" s="9">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G305" s="8">
-        <v>142414615.18</v>
+        <v>142306128.28</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -9811,19 +9815,19 @@
         <v>612</v>
       </c>
       <c r="C306" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D306" s="11">
-        <v>0.0158</v>
+        <v>46142</v>
+      </c>
+      <c r="D306" s="7">
+        <v>0.015823</v>
       </c>
       <c r="E306" s="8">
-        <v>1225480970.93</v>
+        <v>1228983248.78</v>
       </c>
       <c r="F306" s="9">
         <v>23</v>
       </c>
       <c r="G306" s="8">
-        <v>19362749.4</v>
+        <v>19446199</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -9834,19 +9838,19 @@
         <v>614</v>
       </c>
       <c r="C307" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D307" s="7">
-        <v>0.228535</v>
+        <v>0.226919</v>
       </c>
       <c r="E307" s="8">
-        <v>48694341558.91</v>
+        <v>48620106218.47</v>
       </c>
       <c r="F307" s="9">
-        <v>174379</v>
+        <v>174308</v>
       </c>
       <c r="G307" s="8">
-        <v>11128372467.53</v>
+        <v>11032809568.03</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -9857,19 +9861,19 @@
         <v>616</v>
       </c>
       <c r="C308" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D308" s="7">
-        <v>0.011147</v>
+        <v>46142</v>
+      </c>
+      <c r="D308" s="10">
+        <v>0.01111</v>
       </c>
       <c r="E308" s="8">
-        <v>2104823064.42</v>
+        <v>2302578667.38</v>
       </c>
       <c r="F308" s="9">
-        <v>1915</v>
+        <v>1919</v>
       </c>
       <c r="G308" s="8">
-        <v>23461850.64</v>
+        <v>25582026.91</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -9880,19 +9884,19 @@
         <v>618</v>
       </c>
       <c r="C309" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D309" s="7">
-        <v>0.028694</v>
+        <v>0.028976</v>
       </c>
       <c r="E309" s="8">
-        <v>12302451976.36</v>
+        <v>12453824117.55</v>
       </c>
       <c r="F309" s="9">
-        <v>17327</v>
+        <v>17355</v>
       </c>
       <c r="G309" s="8">
-        <v>353005759.87</v>
+        <v>360858142.33</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -9903,19 +9907,19 @@
         <v>620</v>
       </c>
       <c r="C310" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D310" s="7">
-        <v>0.024743</v>
+        <v>0.024777</v>
       </c>
       <c r="E310" s="8">
-        <v>2948902539.48</v>
+        <v>3043858464.07</v>
       </c>
       <c r="F310" s="9">
-        <v>10201</v>
+        <v>10222</v>
       </c>
       <c r="G310" s="8">
-        <v>72963851.68</v>
+        <v>75417636.63</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -9926,19 +9930,19 @@
         <v>622</v>
       </c>
       <c r="C311" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D311" s="7">
-        <v>0.121808</v>
+        <v>0.122056</v>
       </c>
       <c r="E311" s="8">
-        <v>611138919.5</v>
+        <v>610935090.75</v>
       </c>
       <c r="F311" s="9">
-        <v>92410</v>
+        <v>92383</v>
       </c>
       <c r="G311" s="8">
-        <v>74441606.74</v>
+        <v>74568108.05</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -9949,19 +9953,19 @@
         <v>624</v>
       </c>
       <c r="C312" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D312" s="7">
-        <v>0.090392</v>
+        <v>46142</v>
+      </c>
+      <c r="D312" s="10">
+        <v>0.09049</v>
       </c>
       <c r="E312" s="8">
-        <v>1339390737.37</v>
+        <v>1341230732.54</v>
       </c>
       <c r="F312" s="9">
-        <v>25058</v>
+        <v>25054</v>
       </c>
       <c r="G312" s="8">
-        <v>121070409.54</v>
+        <v>121367341.2</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -9972,19 +9976,19 @@
         <v>626</v>
       </c>
       <c r="C313" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D313" s="7">
-        <v>0.079951</v>
+        <v>0.080063</v>
       </c>
       <c r="E313" s="8">
-        <v>2367582651.71</v>
+        <v>2359511369.07</v>
       </c>
       <c r="F313" s="9">
-        <v>74867</v>
+        <v>74705</v>
       </c>
       <c r="G313" s="8">
-        <v>189290672.08</v>
+        <v>188908753.32</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -9995,19 +9999,19 @@
         <v>628</v>
       </c>
       <c r="C314" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D314" s="7">
-        <v>0.387426</v>
+        <v>0.387599</v>
       </c>
       <c r="E314" s="8">
-        <v>5201816524.95</v>
+        <v>5206575068.24</v>
       </c>
       <c r="F314" s="9">
-        <v>71687</v>
+        <v>71661</v>
       </c>
       <c r="G314" s="8">
-        <v>2015321195.43</v>
+        <v>2018065260.88</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -10018,19 +10022,19 @@
         <v>630</v>
       </c>
       <c r="C315" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D315" s="7">
-        <v>0.204838</v>
+        <v>0.204836</v>
       </c>
       <c r="E315" s="8">
-        <v>5826448523.99</v>
+        <v>5838765190.89</v>
       </c>
       <c r="F315" s="9">
-        <v>56501</v>
+        <v>56481</v>
       </c>
       <c r="G315" s="8">
-        <v>1193480007.19</v>
+        <v>1195990620.7</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -10041,19 +10045,19 @@
         <v>632</v>
       </c>
       <c r="C316" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D316" s="7">
-        <v>0.112067</v>
+        <v>0.111636</v>
       </c>
       <c r="E316" s="8">
-        <v>2289541748.35</v>
+        <v>2288224124.89</v>
       </c>
       <c r="F316" s="9">
-        <v>8346</v>
+        <v>8339</v>
       </c>
       <c r="G316" s="8">
-        <v>256580967.56</v>
+        <v>255448097.9</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -10064,19 +10068,19 @@
         <v>634</v>
       </c>
       <c r="C317" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D317" s="7">
-        <v>0.548666</v>
+        <v>0.547609</v>
       </c>
       <c r="E317" s="8">
-        <v>3983183813.85</v>
+        <v>3995381664.8</v>
       </c>
       <c r="F317" s="9">
-        <v>50416</v>
+        <v>50400</v>
       </c>
       <c r="G317" s="8">
-        <v>2185436990.11</v>
+        <v>2187907706.2</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -10087,19 +10091,19 @@
         <v>636</v>
       </c>
       <c r="C318" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D318" s="7">
-        <v>0.084404</v>
+        <v>0.084594</v>
       </c>
       <c r="E318" s="8">
-        <v>8853817244.09</v>
+        <v>8845522471.32</v>
       </c>
       <c r="F318" s="9">
-        <v>188136</v>
+        <v>188061</v>
       </c>
       <c r="G318" s="8">
-        <v>747297997.05</v>
+        <v>748280404.14</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -10110,19 +10114,19 @@
         <v>638</v>
       </c>
       <c r="C319" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D319" s="7">
-        <v>0.108464</v>
+        <v>0.108076</v>
       </c>
       <c r="E319" s="8">
-        <v>23103713481.23</v>
+        <v>23093733051.2</v>
       </c>
       <c r="F319" s="9">
-        <v>138028</v>
+        <v>138000</v>
       </c>
       <c r="G319" s="8">
-        <v>2505919583.81</v>
+        <v>2495870630.07</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -10133,19 +10137,19 @@
         <v>640</v>
       </c>
       <c r="C320" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D320" s="7">
-        <v>0.151062</v>
+        <v>0.151224</v>
       </c>
       <c r="E320" s="8">
-        <v>13096809631.03</v>
+        <v>12975665001.73</v>
       </c>
       <c r="F320" s="9">
-        <v>33366</v>
+        <v>32478</v>
       </c>
       <c r="G320" s="8">
-        <v>1978436317.01</v>
+        <v>1962235051.05</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -10156,19 +10160,19 @@
         <v>642</v>
       </c>
       <c r="C321" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D321" s="7">
-        <v>0.132731</v>
+        <v>0.132859</v>
       </c>
       <c r="E321" s="8">
-        <v>526651989.45</v>
+        <v>527029899.89</v>
       </c>
       <c r="F321" s="9">
         <v>702</v>
       </c>
       <c r="G321" s="8">
-        <v>69902833.79</v>
+        <v>70020847.72</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -10179,19 +10183,19 @@
         <v>644</v>
       </c>
       <c r="C322" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D322" s="7">
-        <v>0.136493</v>
+        <v>0.136271</v>
       </c>
       <c r="E322" s="8">
-        <v>225378524.35</v>
+        <v>225283385.44</v>
       </c>
       <c r="F322" s="9">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G322" s="8">
-        <v>30762531.77</v>
+        <v>30699635.87</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -10202,19 +10206,19 @@
         <v>646</v>
       </c>
       <c r="C323" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D323" s="7">
-        <v>0.166641</v>
+        <v>0.166381</v>
       </c>
       <c r="E323" s="8">
-        <v>296335531.53</v>
+        <v>295717457.1</v>
       </c>
       <c r="F323" s="9">
         <v>527</v>
       </c>
       <c r="G323" s="8">
-        <v>49381683.57</v>
+        <v>49201732.78</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -10225,19 +10229,19 @@
         <v>648</v>
       </c>
       <c r="C324" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D324" s="7">
-        <v>0.197673</v>
+        <v>0.197378</v>
       </c>
       <c r="E324" s="8">
-        <v>359848968.94</v>
+        <v>359414832.32</v>
       </c>
       <c r="F324" s="9">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G324" s="8">
-        <v>71132483.57</v>
+        <v>70940615.66</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -10248,19 +10252,19 @@
         <v>650</v>
       </c>
       <c r="C325" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D325" s="7">
-        <v>0.140784</v>
+        <v>0.141071</v>
       </c>
       <c r="E325" s="8">
-        <v>412825700.69</v>
+        <v>411694427.17</v>
       </c>
       <c r="F325" s="9">
-        <v>2038</v>
+        <v>2051</v>
       </c>
       <c r="G325" s="8">
-        <v>58119121.96</v>
+        <v>58077988.63</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -10271,19 +10275,19 @@
         <v>652</v>
       </c>
       <c r="C326" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D326" s="7">
-        <v>0.097541</v>
+        <v>0.097156</v>
       </c>
       <c r="E326" s="8">
-        <v>40035656762.98</v>
+        <v>39983675950.35</v>
       </c>
       <c r="F326" s="9">
-        <v>367630</v>
+        <v>367456</v>
       </c>
       <c r="G326" s="8">
-        <v>3905117419.72</v>
+        <v>3884660190.33</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -10294,19 +10298,19 @@
         <v>654</v>
       </c>
       <c r="C327" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D327" s="7">
-        <v>0.170914</v>
+        <v>0.171262</v>
       </c>
       <c r="E327" s="8">
-        <v>192585616.64</v>
+        <v>192557665.11</v>
       </c>
       <c r="F327" s="9">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G327" s="8">
-        <v>32915532.33</v>
+        <v>32977881.51</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -10317,19 +10321,19 @@
         <v>656</v>
       </c>
       <c r="C328" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D328" s="10">
-        <v>0.20018</v>
+        <v>0.20062</v>
       </c>
       <c r="E328" s="8">
-        <v>239051169.55</v>
+        <v>238739863.72</v>
       </c>
       <c r="F328" s="9">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G328" s="8">
-        <v>47853162.59</v>
+        <v>47895913.17</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -10340,19 +10344,19 @@
         <v>658</v>
       </c>
       <c r="C329" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D329" s="7">
-        <v>0.290344</v>
+        <v>0.289954</v>
       </c>
       <c r="E329" s="8">
-        <v>1254197087.51</v>
+        <v>1254026539.22</v>
       </c>
       <c r="F329" s="9">
-        <v>8755</v>
+        <v>8750</v>
       </c>
       <c r="G329" s="8">
-        <v>364148828.92</v>
+        <v>363609747.68</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -10363,19 +10367,19 @@
         <v>660</v>
       </c>
       <c r="C330" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D330" s="7">
-        <v>0.091782</v>
+        <v>0.091501</v>
       </c>
       <c r="E330" s="8">
-        <v>6844986440.23</v>
+        <v>6841969127.41</v>
       </c>
       <c r="F330" s="9">
-        <v>123353</v>
+        <v>123331</v>
       </c>
       <c r="G330" s="8">
-        <v>628249831</v>
+        <v>626048302.42</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
@@ -10386,19 +10390,19 @@
         <v>662</v>
       </c>
       <c r="C331" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D331" s="7">
-        <v>0.073537</v>
+        <v>0.073486</v>
       </c>
       <c r="E331" s="8">
-        <v>103236066790.69</v>
+        <v>103366754607.38</v>
       </c>
       <c r="F331" s="9">
-        <v>148066</v>
+        <v>148078</v>
       </c>
       <c r="G331" s="8">
-        <v>7591624940.83</v>
+        <v>7596007490.43</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
@@ -10409,19 +10413,19 @@
         <v>664</v>
       </c>
       <c r="C332" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D332" s="10">
-        <v>0.06525</v>
+        <v>46142</v>
+      </c>
+      <c r="D332" s="7">
+        <v>0.065192</v>
       </c>
       <c r="E332" s="8">
-        <v>111366672380.88</v>
+        <v>111491517235.64</v>
       </c>
       <c r="F332" s="9">
-        <v>99261</v>
+        <v>99330</v>
       </c>
       <c r="G332" s="8">
-        <v>7266699757.48</v>
+        <v>7268332606.86</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
@@ -10432,19 +10436,19 @@
         <v>666</v>
       </c>
       <c r="C333" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D333" s="7">
-        <v>0.085621</v>
+        <v>0.085594</v>
       </c>
       <c r="E333" s="8">
-        <v>64778912888.54</v>
+        <v>64875562381.06</v>
       </c>
       <c r="F333" s="9">
-        <v>122984</v>
+        <v>123037</v>
       </c>
       <c r="G333" s="8">
-        <v>5546440378.12</v>
+        <v>5552951695.46</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
@@ -10455,19 +10459,19 @@
         <v>668</v>
       </c>
       <c r="C334" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D334" s="7">
-        <v>0.448193</v>
+        <v>0.447162</v>
       </c>
       <c r="E334" s="8">
-        <v>52565706477.75</v>
+        <v>52572713912.46</v>
       </c>
       <c r="F334" s="9">
-        <v>127094</v>
+        <v>126981</v>
       </c>
       <c r="G334" s="8">
-        <v>23559581559.43</v>
+        <v>23508500306.31</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
@@ -10478,19 +10482,19 @@
         <v>670</v>
       </c>
       <c r="C335" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D335" s="7">
-        <v>0.098462</v>
+        <v>0.098673</v>
       </c>
       <c r="E335" s="8">
-        <v>5285506881.7</v>
+        <v>5289894417.71</v>
       </c>
       <c r="F335" s="9">
-        <v>8802</v>
+        <v>8762</v>
       </c>
       <c r="G335" s="8">
-        <v>520422319.34</v>
+        <v>521969697.93</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
@@ -10501,19 +10505,19 @@
         <v>672</v>
       </c>
       <c r="C336" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D336" s="7">
-        <v>0.352613</v>
+        <v>0.350981</v>
       </c>
       <c r="E336" s="8">
-        <v>15879804609.8</v>
+        <v>15857748869.48</v>
       </c>
       <c r="F336" s="9">
-        <v>28637</v>
+        <v>28627</v>
       </c>
       <c r="G336" s="8">
-        <v>5599432290.32</v>
+        <v>5565771214.23</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
@@ -10524,19 +10528,19 @@
         <v>674</v>
       </c>
       <c r="C337" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D337" s="7">
-        <v>0.010145</v>
+        <v>0.010048</v>
       </c>
       <c r="E337" s="8">
-        <v>75180104936.98</v>
+        <v>75885540375.84</v>
       </c>
       <c r="F337" s="9">
-        <v>4166</v>
+        <v>4237</v>
       </c>
       <c r="G337" s="8">
-        <v>762692353.35</v>
+        <v>762510132.99</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
@@ -10547,19 +10551,19 @@
         <v>676</v>
       </c>
       <c r="C338" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D338" s="7">
-        <v>0.081496</v>
+        <v>0.081612</v>
       </c>
       <c r="E338" s="8">
-        <v>3722348905.29</v>
+        <v>3718175702.94</v>
       </c>
       <c r="F338" s="9">
-        <v>78569</v>
+        <v>78539</v>
       </c>
       <c r="G338" s="8">
-        <v>303354857.12</v>
+        <v>303447525.44</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
@@ -10570,19 +10574,19 @@
         <v>678</v>
       </c>
       <c r="C339" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D339" s="7">
-        <v>0.091137</v>
+        <v>0.091228</v>
       </c>
       <c r="E339" s="8">
-        <v>625914567.67</v>
+        <v>626888224.53</v>
       </c>
       <c r="F339" s="9">
-        <v>12385</v>
+        <v>12423</v>
       </c>
       <c r="G339" s="8">
-        <v>57043815.06</v>
+        <v>57189480.56</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
@@ -10593,19 +10597,19 @@
         <v>680</v>
       </c>
       <c r="C340" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D340" s="7">
-        <v>0.042707</v>
+        <v>0.042867</v>
       </c>
       <c r="E340" s="8">
-        <v>1030234085.7</v>
+        <v>1039651345.51</v>
       </c>
       <c r="F340" s="9">
-        <v>2186</v>
+        <v>2200</v>
       </c>
       <c r="G340" s="8">
-        <v>43998190.31</v>
+        <v>44567225</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -10616,19 +10620,19 @@
         <v>682</v>
       </c>
       <c r="C341" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D341" s="7">
-        <v>0.049836</v>
+        <v>46142</v>
+      </c>
+      <c r="D341" s="10">
+        <v>0.04996</v>
       </c>
       <c r="E341" s="8">
-        <v>3915346264.31</v>
+        <v>3917755140.07</v>
       </c>
       <c r="F341" s="9">
-        <v>4282</v>
+        <v>4289</v>
       </c>
       <c r="G341" s="8">
-        <v>195123396.42</v>
+        <v>195731316.45</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
@@ -10639,19 +10643,19 @@
         <v>684</v>
       </c>
       <c r="C342" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D342" s="7">
-        <v>0.013905</v>
+        <v>0.013847</v>
       </c>
       <c r="E342" s="8">
-        <v>34705570611.52</v>
+        <v>34918197272.83</v>
       </c>
       <c r="F342" s="9">
-        <v>27046</v>
+        <v>27177</v>
       </c>
       <c r="G342" s="8">
-        <v>482564124.25</v>
+        <v>483527837.25</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
@@ -10662,19 +10666,19 @@
         <v>686</v>
       </c>
       <c r="C343" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D343" s="7">
-        <v>0.071035</v>
+        <v>46142</v>
+      </c>
+      <c r="D343" s="10">
+        <v>0.07171</v>
       </c>
       <c r="E343" s="8">
-        <v>46965104245.68</v>
+        <v>47340225185.07</v>
       </c>
       <c r="F343" s="9">
-        <v>119940</v>
+        <v>120285</v>
       </c>
       <c r="G343" s="8">
-        <v>3336182749.53</v>
+        <v>3394756127.54</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
@@ -10685,19 +10689,19 @@
         <v>688</v>
       </c>
       <c r="C344" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D344" s="7">
-        <v>0.012727</v>
+        <v>0.012805</v>
       </c>
       <c r="E344" s="8">
-        <v>14608944241.5</v>
+        <v>14691363168.68</v>
       </c>
       <c r="F344" s="9">
-        <v>5299</v>
+        <v>5329</v>
       </c>
       <c r="G344" s="8">
-        <v>185927685.3</v>
+        <v>188117295.68</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
@@ -10708,19 +10712,19 @@
         <v>690</v>
       </c>
       <c r="C345" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D345" s="10">
-        <v>0.01477</v>
+        <v>46142</v>
+      </c>
+      <c r="D345" s="7">
+        <v>0.014787</v>
       </c>
       <c r="E345" s="8">
-        <v>68525006981.54</v>
+        <v>69038391143.1</v>
       </c>
       <c r="F345" s="9">
-        <v>18343</v>
+        <v>18452</v>
       </c>
       <c r="G345" s="8">
-        <v>1012089371.53</v>
+        <v>1020857215.02</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
@@ -10731,19 +10735,19 @@
         <v>692</v>
       </c>
       <c r="C346" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D346" s="7">
-        <v>0.049537</v>
+        <v>0.049518</v>
       </c>
       <c r="E346" s="8">
-        <v>7340426206.33</v>
+        <v>7333470965.55</v>
       </c>
       <c r="F346" s="9">
-        <v>9334</v>
+        <v>9360</v>
       </c>
       <c r="G346" s="8">
-        <v>363622186.5</v>
+        <v>363137315.75</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
@@ -10754,19 +10758,19 @@
         <v>694</v>
       </c>
       <c r="C347" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D347" s="7">
-        <v>0.086462</v>
+        <v>0.086552</v>
       </c>
       <c r="E347" s="8">
-        <v>592289695.11</v>
+        <v>577403409.48</v>
       </c>
       <c r="F347" s="9">
-        <v>6990</v>
+        <v>6832</v>
       </c>
       <c r="G347" s="8">
-        <v>51210559.52</v>
+        <v>49975545.89</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
@@ -10777,19 +10781,19 @@
         <v>696</v>
       </c>
       <c r="C348" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D348" s="7">
-        <v>0.048876</v>
+        <v>0.048778</v>
       </c>
       <c r="E348" s="8">
-        <v>3904236858.64</v>
+        <v>3906068362.05</v>
       </c>
       <c r="F348" s="9">
-        <v>5945</v>
+        <v>5938</v>
       </c>
       <c r="G348" s="8">
-        <v>190822942.54</v>
+        <v>190532106.81</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
@@ -10800,19 +10804,19 @@
         <v>698</v>
       </c>
       <c r="C349" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D349" s="7">
-        <v>0.020358</v>
+        <v>0.020356</v>
       </c>
       <c r="E349" s="8">
-        <v>8719942439.6</v>
+        <v>8796471139.93</v>
       </c>
       <c r="F349" s="9">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G349" s="8">
-        <v>177516329.06</v>
+        <v>179060927.63</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
@@ -10823,19 +10827,19 @@
         <v>700</v>
       </c>
       <c r="C350" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D350" s="7">
-        <v>0.015094</v>
+        <v>0.015023</v>
       </c>
       <c r="E350" s="8">
-        <v>15638325199.75</v>
+        <v>15778706968.09</v>
       </c>
       <c r="F350" s="9">
-        <v>5860</v>
+        <v>5866</v>
       </c>
       <c r="G350" s="8">
-        <v>236050722.12</v>
+        <v>237040096.39</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
@@ -10846,19 +10850,19 @@
         <v>702</v>
       </c>
       <c r="C351" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D351" s="7">
-        <v>0.013651</v>
+        <v>0.013604</v>
       </c>
       <c r="E351" s="8">
-        <v>22118244625.32</v>
+        <v>22176748083.13</v>
       </c>
       <c r="F351" s="9">
-        <v>5658</v>
+        <v>5672</v>
       </c>
       <c r="G351" s="8">
-        <v>301944977.49</v>
+        <v>301692192.33</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -10869,19 +10873,19 @@
         <v>704</v>
       </c>
       <c r="C352" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D352" s="7">
-        <v>0.014302</v>
+        <v>0.014285</v>
       </c>
       <c r="E352" s="8">
-        <v>23344622697.7</v>
+        <v>23378464751.62</v>
       </c>
       <c r="F352" s="9">
-        <v>10558</v>
+        <v>10645</v>
       </c>
       <c r="G352" s="8">
-        <v>333866920.41</v>
+        <v>333952446.06</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -10892,19 +10896,19 @@
         <v>706</v>
       </c>
       <c r="C353" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D353" s="7">
-        <v>0.015135</v>
+        <v>0.015245</v>
       </c>
       <c r="E353" s="8">
-        <v>37084866595.72</v>
+        <v>37533701223.57</v>
       </c>
       <c r="F353" s="9">
-        <v>10073</v>
+        <v>10152</v>
       </c>
       <c r="G353" s="8">
-        <v>561288454.05</v>
+        <v>572195978.92</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
@@ -10915,19 +10919,19 @@
         <v>708</v>
       </c>
       <c r="C354" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D354" s="7">
-        <v>0.049044</v>
+        <v>0.048847</v>
       </c>
       <c r="E354" s="8">
-        <v>2914716422.01</v>
+        <v>2909887618.44</v>
       </c>
       <c r="F354" s="9">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="G354" s="8">
-        <v>142948642.81</v>
+        <v>142140255.18</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -10938,19 +10942,19 @@
         <v>710</v>
       </c>
       <c r="C355" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D355" s="7">
-        <v>0.224354</v>
+        <v>0.225325</v>
       </c>
       <c r="E355" s="8">
-        <v>8768430381.82</v>
+        <v>8773262798.22</v>
       </c>
       <c r="F355" s="9">
-        <v>47724</v>
+        <v>47717</v>
       </c>
       <c r="G355" s="8">
-        <v>1967234418.36</v>
+        <v>1976835172.61</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
@@ -10961,19 +10965,19 @@
         <v>712</v>
       </c>
       <c r="C356" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D356" s="10">
-        <v>0.08246</v>
+        <v>46142</v>
+      </c>
+      <c r="D356" s="7">
+        <v>0.082457</v>
       </c>
       <c r="E356" s="8">
-        <v>11838043704.35</v>
+        <v>11852991663.31</v>
       </c>
       <c r="F356" s="9">
-        <v>21777</v>
+        <v>21795</v>
       </c>
       <c r="G356" s="8">
-        <v>976162396.79</v>
+        <v>977360083.08</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
@@ -10984,19 +10988,19 @@
         <v>714</v>
       </c>
       <c r="C357" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D357" s="7">
-        <v>0.306184</v>
+        <v>0.306381</v>
       </c>
       <c r="E357" s="8">
-        <v>3860070306.68</v>
+        <v>3860787221.08</v>
       </c>
       <c r="F357" s="9">
-        <v>27631</v>
+        <v>27609</v>
       </c>
       <c r="G357" s="8">
-        <v>1181892672.44</v>
+        <v>1182872293.9</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
@@ -11007,19 +11011,19 @@
         <v>716</v>
       </c>
       <c r="C358" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D358" s="7">
-        <v>1.361749</v>
+        <v>1.355222</v>
       </c>
       <c r="E358" s="8">
-        <v>8836793505.81</v>
+        <v>8856150114.4</v>
       </c>
       <c r="F358" s="9">
-        <v>244986</v>
+        <v>245086</v>
       </c>
       <c r="G358" s="8">
-        <v>12033495741.95</v>
+        <v>12002050000.5</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
@@ -11030,19 +11034,19 @@
         <v>718</v>
       </c>
       <c r="C359" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D359" s="10">
-        <v>0.09541</v>
+        <v>46142</v>
+      </c>
+      <c r="D359" s="7">
+        <v>0.094794</v>
       </c>
       <c r="E359" s="8">
-        <v>534556510216.54</v>
+        <v>534071795085.78</v>
       </c>
       <c r="F359" s="9">
-        <v>2768465</v>
+        <v>2767085</v>
       </c>
       <c r="G359" s="8">
-        <v>51002246886.36</v>
+        <v>50626940330.08</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
@@ -11053,19 +11057,19 @@
         <v>720</v>
       </c>
       <c r="C360" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D360" s="7">
-        <v>0.320281</v>
+        <v>0.319554</v>
       </c>
       <c r="E360" s="8">
-        <v>23891533680.28</v>
+        <v>23873855409.08</v>
       </c>
       <c r="F360" s="9">
-        <v>423375</v>
+        <v>423202</v>
       </c>
       <c r="G360" s="8">
-        <v>7652007033.84</v>
+        <v>7628975331.72</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
@@ -11076,19 +11080,19 @@
         <v>722</v>
       </c>
       <c r="C361" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D361" s="7">
-        <v>0.348252</v>
+        <v>0.348619</v>
       </c>
       <c r="E361" s="8">
-        <v>83560559727.81</v>
+        <v>83905271141.78</v>
       </c>
       <c r="F361" s="9">
-        <v>403463</v>
+        <v>378159</v>
       </c>
       <c r="G361" s="8">
-        <v>29100106720.56</v>
+        <v>29251000567.66</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
@@ -11099,19 +11103,19 @@
         <v>724</v>
       </c>
       <c r="C362" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D362" s="10">
-        <v>0.21881</v>
+        <v>46142</v>
+      </c>
+      <c r="D362" s="7">
+        <v>0.219085</v>
       </c>
       <c r="E362" s="8">
-        <v>20334449230.39</v>
+        <v>20345633728.6</v>
       </c>
       <c r="F362" s="9">
-        <v>69970</v>
+        <v>70001</v>
       </c>
       <c r="G362" s="8">
-        <v>4449380564.87</v>
+        <v>4457426884.11</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
@@ -11122,19 +11126,19 @@
         <v>726</v>
       </c>
       <c r="C363" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D363" s="7">
-        <v>0.101545</v>
+        <v>0.101568</v>
       </c>
       <c r="E363" s="8">
-        <v>3762885950.77</v>
+        <v>3759050014.28</v>
       </c>
       <c r="F363" s="9">
-        <v>8003</v>
+        <v>8004</v>
       </c>
       <c r="G363" s="8">
-        <v>382102490.98</v>
+        <v>381798358.73</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
@@ -11145,19 +11149,19 @@
         <v>728</v>
       </c>
       <c r="C364" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D364" s="7">
-        <v>0.135264</v>
+        <v>0.135484</v>
       </c>
       <c r="E364" s="8">
-        <v>102311522397.07</v>
+        <v>102245607302.41</v>
       </c>
       <c r="F364" s="9">
-        <v>1887274</v>
+        <v>1886599</v>
       </c>
       <c r="G364" s="8">
-        <v>13839070696.36</v>
+        <v>13852606448.8</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
@@ -11168,19 +11172,19 @@
         <v>730</v>
       </c>
       <c r="C365" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D365" s="10">
-        <v>0.13569</v>
+        <v>46142</v>
+      </c>
+      <c r="D365" s="7">
+        <v>0.135688</v>
       </c>
       <c r="E365" s="8">
-        <v>58306716131.95</v>
+        <v>58259376871.09</v>
       </c>
       <c r="F365" s="9">
-        <v>120097</v>
+        <v>120096</v>
       </c>
       <c r="G365" s="8">
-        <v>7911664125.95</v>
+        <v>7905102396.46</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
@@ -11191,19 +11195,19 @@
         <v>732</v>
       </c>
       <c r="C366" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D366" s="7">
-        <v>0.732157</v>
+        <v>0.730094</v>
       </c>
       <c r="E366" s="8">
-        <v>16792838009.9</v>
+        <v>16807245594.44</v>
       </c>
       <c r="F366" s="9">
-        <v>342423</v>
+        <v>342260</v>
       </c>
       <c r="G366" s="8">
-        <v>12294988080.82</v>
+        <v>12270867595.54</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
@@ -11214,19 +11218,19 @@
         <v>734</v>
       </c>
       <c r="C367" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D367" s="7">
-        <v>0.146319</v>
+        <v>0.146082</v>
       </c>
       <c r="E367" s="8">
-        <v>31267049268.5</v>
+        <v>31278905516.45</v>
       </c>
       <c r="F367" s="9">
-        <v>93507</v>
+        <v>93430</v>
       </c>
       <c r="G367" s="8">
-        <v>4574956964.24</v>
+        <v>4569281438.29</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
@@ -11237,19 +11241,19 @@
         <v>736</v>
       </c>
       <c r="C368" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D368" s="7">
-        <v>0.169674</v>
+        <v>0.169647</v>
       </c>
       <c r="E368" s="8">
-        <v>2082382313.9</v>
+        <v>2083286894.13</v>
       </c>
       <c r="F368" s="9">
-        <v>7380</v>
+        <v>7383</v>
       </c>
       <c r="G368" s="8">
-        <v>353326724.71</v>
+        <v>353423164.12</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
@@ -11260,19 +11264,19 @@
         <v>738</v>
       </c>
       <c r="C369" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D369" s="7">
-        <v>0.381563</v>
+        <v>0.381985</v>
       </c>
       <c r="E369" s="8">
-        <v>4878345284.35</v>
+        <v>4910781721.93</v>
       </c>
       <c r="F369" s="9">
-        <v>18602</v>
+        <v>18653</v>
       </c>
       <c r="G369" s="8">
-        <v>1861394470.47</v>
+        <v>1875845190.67</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
@@ -11283,19 +11287,19 @@
         <v>740</v>
       </c>
       <c r="C370" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D370" s="7">
-        <v>0.770056</v>
+        <v>0.767085</v>
       </c>
       <c r="E370" s="8">
-        <v>329445177557.56</v>
+        <v>329322040938.68</v>
       </c>
       <c r="F370" s="9">
-        <v>2048791</v>
+        <v>2047480</v>
       </c>
       <c r="G370" s="8">
-        <v>253691302721.76</v>
+        <v>252617918122.16</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
@@ -11306,19 +11310,19 @@
         <v>742</v>
       </c>
       <c r="C371" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D371" s="7">
-        <v>0.156935</v>
+        <v>0.157534</v>
       </c>
       <c r="E371" s="8">
-        <v>23907300163.24</v>
+        <v>23925198040.31</v>
       </c>
       <c r="F371" s="9">
-        <v>109340</v>
+        <v>109330</v>
       </c>
       <c r="G371" s="8">
-        <v>3751896649.53</v>
+        <v>3769036352.87</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
@@ -11329,19 +11333,19 @@
         <v>744</v>
       </c>
       <c r="C372" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D372" s="7">
-        <v>0.192018</v>
+        <v>0.192116</v>
       </c>
       <c r="E372" s="8">
-        <v>3612893855.22</v>
+        <v>3607621016.76</v>
       </c>
       <c r="F372" s="9">
-        <v>11574</v>
+        <v>11554</v>
       </c>
       <c r="G372" s="8">
-        <v>693742160.42</v>
+        <v>693081256.99</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
@@ -11352,19 +11356,19 @@
         <v>746</v>
       </c>
       <c r="C373" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D373" s="7">
-        <v>0.413715</v>
+        <v>0.411964</v>
       </c>
       <c r="E373" s="8">
-        <v>56362158154.44</v>
+        <v>56134318654.83</v>
       </c>
       <c r="F373" s="9">
-        <v>291607</v>
+        <v>290975</v>
       </c>
       <c r="G373" s="8">
-        <v>23317853431.92</v>
+        <v>23125310850.41</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
@@ -11375,19 +11379,19 @@
         <v>748</v>
       </c>
       <c r="C374" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D374" s="7">
-        <v>0.522513</v>
+        <v>0.523065</v>
       </c>
       <c r="E374" s="8">
-        <v>1245884515.51</v>
+        <v>1248469737.89</v>
       </c>
       <c r="F374" s="9">
-        <v>14091</v>
+        <v>14162</v>
       </c>
       <c r="G374" s="8">
-        <v>650990476.69</v>
+        <v>653030735.77</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
@@ -11398,19 +11402,19 @@
         <v>750</v>
       </c>
       <c r="C375" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D375" s="7">
-        <v>0.183995</v>
+        <v>0.184516</v>
       </c>
       <c r="E375" s="8">
-        <v>6853208514.87</v>
+        <v>6848443493.82</v>
       </c>
       <c r="F375" s="9">
-        <v>16330</v>
+        <v>16300</v>
       </c>
       <c r="G375" s="8">
-        <v>1260952762.92</v>
+        <v>1263646070.86</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
@@ -11421,19 +11425,19 @@
         <v>752</v>
       </c>
       <c r="C376" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D376" s="7">
-        <v>0.118235</v>
+        <v>0.118272</v>
       </c>
       <c r="E376" s="8">
-        <v>7627214528.27</v>
+        <v>7616297140.92</v>
       </c>
       <c r="F376" s="9">
-        <v>24002</v>
+        <v>23972</v>
       </c>
       <c r="G376" s="8">
-        <v>901804540.57</v>
+        <v>900792673.61</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
@@ -11444,19 +11448,19 @@
         <v>754</v>
       </c>
       <c r="C377" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D377" s="7">
-        <v>0.176542</v>
+        <v>46142</v>
+      </c>
+      <c r="D377" s="10">
+        <v>0.17714</v>
       </c>
       <c r="E377" s="8">
-        <v>14196048715.58</v>
+        <v>14181924626.07</v>
       </c>
       <c r="F377" s="9">
-        <v>50964</v>
+        <v>50914</v>
       </c>
       <c r="G377" s="8">
-        <v>2506198037.12</v>
+        <v>2512186138.12</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
@@ -11467,19 +11471,19 @@
         <v>756</v>
       </c>
       <c r="C378" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D378" s="10">
-        <v>0.08773</v>
+        <v>46142</v>
+      </c>
+      <c r="D378" s="7">
+        <v>0.087938</v>
       </c>
       <c r="E378" s="8">
-        <v>397059231209.6</v>
+        <v>396952153976.34</v>
       </c>
       <c r="F378" s="9">
-        <v>1945157</v>
+        <v>1945112</v>
       </c>
       <c r="G378" s="8">
-        <v>34834010943.63</v>
+        <v>34907345076.79</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
@@ -11490,19 +11494,19 @@
         <v>758</v>
       </c>
       <c r="C379" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D379" s="10">
-        <v>0.15338</v>
+        <v>0.15194</v>
       </c>
       <c r="E379" s="8">
-        <v>1165523162.6</v>
+        <v>1164066225.96</v>
       </c>
       <c r="F379" s="9">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="G379" s="8">
-        <v>178768027.76</v>
+        <v>176868151.99</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
@@ -11513,19 +11517,19 @@
         <v>760</v>
       </c>
       <c r="C380" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D380" s="7">
-        <v>0.189367</v>
+        <v>0.189191</v>
       </c>
       <c r="E380" s="8">
-        <v>1031420359.01</v>
+        <v>1030251147.52</v>
       </c>
       <c r="F380" s="9">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="G380" s="8">
-        <v>195317176.15</v>
+        <v>194914231.75</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
@@ -11536,19 +11540,19 @@
         <v>762</v>
       </c>
       <c r="C381" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D381" s="10">
-        <v>0.17271</v>
+        <v>46142</v>
+      </c>
+      <c r="D381" s="7">
+        <v>0.172378</v>
       </c>
       <c r="E381" s="8">
-        <v>587011599.52</v>
+        <v>586407180.01</v>
       </c>
       <c r="F381" s="9">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="G381" s="8">
-        <v>101382647</v>
+        <v>101083638.55</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
@@ -11559,19 +11563,19 @@
         <v>764</v>
       </c>
       <c r="C382" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D382" s="7">
-        <v>0.092053</v>
+        <v>0.091866</v>
       </c>
       <c r="E382" s="8">
-        <v>98024552281.85</v>
+        <v>97958093772.54</v>
       </c>
       <c r="F382" s="9">
-        <v>665405</v>
+        <v>665342</v>
       </c>
       <c r="G382" s="8">
-        <v>9023498852.64</v>
+        <v>8998991859.98</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
@@ -11582,19 +11586,19 @@
         <v>766</v>
       </c>
       <c r="C383" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D383" s="7">
-        <v>0.089449</v>
+        <v>0.089539</v>
       </c>
       <c r="E383" s="8">
-        <v>42559097544.15</v>
+        <v>42441008523.42</v>
       </c>
       <c r="F383" s="9">
-        <v>443488</v>
+        <v>442349</v>
       </c>
       <c r="G383" s="8">
-        <v>3806848760.1</v>
+        <v>3800107040.97</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
@@ -11605,19 +11609,19 @@
         <v>768</v>
       </c>
       <c r="C384" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D384" s="7">
-        <v>0.093855</v>
+        <v>0.093955</v>
       </c>
       <c r="E384" s="8">
-        <v>16510384167.56</v>
+        <v>16492563598.74</v>
       </c>
       <c r="F384" s="9">
-        <v>124396</v>
+        <v>124136</v>
       </c>
       <c r="G384" s="8">
-        <v>1549587445.14</v>
+        <v>1549557857.46</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
@@ -11628,19 +11632,19 @@
         <v>770</v>
       </c>
       <c r="C385" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D385" s="7">
-        <v>0.260812</v>
+        <v>46142</v>
+      </c>
+      <c r="D385" s="10">
+        <v>0.26151</v>
       </c>
       <c r="E385" s="8">
-        <v>3517595193.33</v>
+        <v>3521958526.57</v>
       </c>
       <c r="F385" s="9">
-        <v>10544</v>
+        <v>10545</v>
       </c>
       <c r="G385" s="8">
-        <v>917431479.85</v>
+        <v>921028964.42</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
@@ -11651,19 +11655,19 @@
         <v>772</v>
       </c>
       <c r="C386" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D386" s="7">
-        <v>0.189033</v>
+        <v>0.190129</v>
       </c>
       <c r="E386" s="8">
-        <v>2313658747.43</v>
+        <v>2313708460.25</v>
       </c>
       <c r="F386" s="9">
-        <v>7110</v>
+        <v>7127</v>
       </c>
       <c r="G386" s="8">
-        <v>437356762.86</v>
+        <v>439903561.42</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
@@ -11674,19 +11678,19 @@
         <v>774</v>
       </c>
       <c r="C387" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D387" s="7">
-        <v>0.172104</v>
+        <v>0.173043</v>
       </c>
       <c r="E387" s="8">
-        <v>2462620313.75</v>
+        <v>2466902774.31</v>
       </c>
       <c r="F387" s="9">
-        <v>7610</v>
+        <v>7625</v>
       </c>
       <c r="G387" s="8">
-        <v>423827167.49</v>
+        <v>426879160.57</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
@@ -11697,19 +11701,19 @@
         <v>776</v>
       </c>
       <c r="C388" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D388" s="7">
-        <v>0.098741</v>
+        <v>0.098848</v>
       </c>
       <c r="E388" s="8">
-        <v>3848949091.11</v>
+        <v>3840523729.7</v>
       </c>
       <c r="F388" s="9">
-        <v>7262</v>
+        <v>7254</v>
       </c>
       <c r="G388" s="8">
-        <v>380050946.26</v>
+        <v>379629465.63</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -11720,19 +11724,19 @@
         <v>778</v>
       </c>
       <c r="C389" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D389" s="7">
-        <v>0.226526</v>
+        <v>0.228098</v>
       </c>
       <c r="E389" s="8">
-        <v>1487617845.14</v>
+        <v>1488564057.19</v>
       </c>
       <c r="F389" s="9">
-        <v>5813</v>
+        <v>5821</v>
       </c>
       <c r="G389" s="8">
-        <v>336984805.62</v>
+        <v>339537917.17</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
@@ -11743,19 +11747,19 @@
         <v>780</v>
       </c>
       <c r="C390" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D390" s="7">
-        <v>0.318724</v>
+        <v>46142</v>
+      </c>
+      <c r="D390" s="10">
+        <v>0.32109</v>
       </c>
       <c r="E390" s="8">
-        <v>1901438721.95</v>
+        <v>1900038388.05</v>
       </c>
       <c r="F390" s="9">
-        <v>6306</v>
+        <v>6308</v>
       </c>
       <c r="G390" s="8">
-        <v>606033244.05</v>
+        <v>610084213.81</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
@@ -11766,19 +11770,19 @@
         <v>782</v>
       </c>
       <c r="C391" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D391" s="7">
-        <v>0.268689</v>
+        <v>46142</v>
+      </c>
+      <c r="D391" s="10">
+        <v>0.26942</v>
       </c>
       <c r="E391" s="8">
-        <v>13849147382.24</v>
+        <v>13887069794.23</v>
       </c>
       <c r="F391" s="9">
-        <v>66657</v>
+        <v>66775</v>
       </c>
       <c r="G391" s="8">
-        <v>3721108592.18</v>
+        <v>3741448496.31</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
@@ -11789,19 +11793,19 @@
         <v>784</v>
       </c>
       <c r="C392" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D392" s="7">
-        <v>0.058045</v>
+        <v>0.058424</v>
       </c>
       <c r="E392" s="8">
-        <v>54759410919.64</v>
+        <v>55047437654.34</v>
       </c>
       <c r="F392" s="9">
-        <v>41084</v>
+        <v>41173</v>
       </c>
       <c r="G392" s="8">
-        <v>3178530634.7</v>
+        <v>3216069213.32</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
@@ -11812,19 +11816,19 @@
         <v>786</v>
       </c>
       <c r="C393" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D393" s="7">
-        <v>0.336767</v>
+        <v>0.337241</v>
       </c>
       <c r="E393" s="8">
-        <v>13342474295.71</v>
+        <v>13390105318.84</v>
       </c>
       <c r="F393" s="9">
-        <v>216134</v>
+        <v>216334</v>
       </c>
       <c r="G393" s="8">
-        <v>4493307147.44</v>
+        <v>4515698628.81</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
@@ -11835,19 +11839,19 @@
         <v>788</v>
       </c>
       <c r="C394" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D394" s="7">
-        <v>0.371269</v>
+        <v>0.371047</v>
       </c>
       <c r="E394" s="8">
-        <v>4730029505.53</v>
+        <v>4732878635.31</v>
       </c>
       <c r="F394" s="9">
-        <v>53061</v>
+        <v>53109</v>
       </c>
       <c r="G394" s="8">
-        <v>1756111806.17</v>
+        <v>1756120034.93</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
@@ -11858,19 +11862,19 @@
         <v>790</v>
       </c>
       <c r="C395" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D395" s="7">
-        <v>0.216446</v>
+        <v>0.214901</v>
       </c>
       <c r="E395" s="8">
-        <v>69067674968.32</v>
+        <v>68973159165.55</v>
       </c>
       <c r="F395" s="9">
-        <v>519483</v>
+        <v>519156</v>
       </c>
       <c r="G395" s="8">
-        <v>14949427375.17</v>
+        <v>14822413703.89</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
@@ -11881,19 +11885,19 @@
         <v>792</v>
       </c>
       <c r="C396" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D396" s="7">
-        <v>0.131446</v>
+        <v>0.131695</v>
       </c>
       <c r="E396" s="8">
-        <v>12860554483.51</v>
+        <v>12853003895.89</v>
       </c>
       <c r="F396" s="9">
-        <v>45327</v>
+        <v>45314</v>
       </c>
       <c r="G396" s="8">
-        <v>1690468395.49</v>
+        <v>1692675319.03</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -11904,19 +11908,19 @@
         <v>794</v>
       </c>
       <c r="C397" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D397" s="7">
-        <v>0.063243</v>
+        <v>0.063097</v>
       </c>
       <c r="E397" s="8">
-        <v>58590458580.31</v>
+        <v>58498015316.02</v>
       </c>
       <c r="F397" s="9">
-        <v>324096</v>
+        <v>323949</v>
       </c>
       <c r="G397" s="8">
-        <v>3705436061.21</v>
+        <v>3691028009.64</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>04.05.2026 19:05:09</t>
+    <t>05.05.2026 18:25:09</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2408,14 +2408,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
     <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
     <numFmt numFmtId="169" formatCode="###0.0000;-###0.0000;0"/>
-    <numFmt numFmtId="170" formatCode="###0.000;-###0.000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -2485,7 +2484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2514,9 +2513,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2921,19 +2917,19 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D6" s="7">
-        <v>0.101028</v>
+        <v>0.100989</v>
       </c>
       <c r="E6" s="8">
-        <v>47237862772.09</v>
+        <v>47344239875.61</v>
       </c>
       <c r="F6" s="9">
-        <v>643945</v>
+        <v>644229</v>
       </c>
       <c r="G6" s="8">
-        <v>4772367383.39</v>
+        <v>4781255512.53</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2944,19 +2940,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D7" s="7">
-        <v>0.398578</v>
+        <v>0.403774</v>
       </c>
       <c r="E7" s="8">
-        <v>17131775697.26</v>
+        <v>17128958656.19</v>
       </c>
       <c r="F7" s="9">
-        <v>151598</v>
+        <v>151562</v>
       </c>
       <c r="G7" s="8">
-        <v>6828348741.22</v>
+        <v>6916224955.01</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2967,19 +2963,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D8" s="7">
-        <v>0.086469</v>
+        <v>0.086569</v>
       </c>
       <c r="E8" s="8">
-        <v>7955048580.81</v>
+        <v>7955291794.53</v>
       </c>
       <c r="F8" s="9">
-        <v>141908</v>
+        <v>141851</v>
       </c>
       <c r="G8" s="8">
-        <v>687868316.07</v>
+        <v>688681619.28</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2990,19 +2986,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D9" s="7">
-        <v>0.368606</v>
+        <v>0.368919</v>
       </c>
       <c r="E9" s="8">
-        <v>141532980760.8</v>
+        <v>142735406277.45</v>
       </c>
       <c r="F9" s="9">
-        <v>487886</v>
+        <v>488189</v>
       </c>
       <c r="G9" s="8">
-        <v>52169866292.74</v>
+        <v>52657812628.14</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3013,19 +3009,19 @@
         <v>20</v>
       </c>
       <c r="C10" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D10" s="7">
-        <v>0.331313</v>
+        <v>0.332075</v>
       </c>
       <c r="E10" s="8">
-        <v>23130842790.7</v>
+        <v>23058595155.87</v>
       </c>
       <c r="F10" s="9">
-        <v>329359</v>
+        <v>329203</v>
       </c>
       <c r="G10" s="8">
-        <v>7663552834.73</v>
+        <v>7657177647.01</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3036,19 +3032,19 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D11" s="10">
-        <v>0.99899</v>
+        <v>46147</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.999491</v>
       </c>
       <c r="E11" s="8">
-        <v>11586745157.75</v>
+        <v>11578466747.81</v>
       </c>
       <c r="F11" s="9">
-        <v>288961</v>
+        <v>288886</v>
       </c>
       <c r="G11" s="8">
-        <v>11575048147.35</v>
+        <v>11572571333.87</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3059,19 +3055,19 @@
         <v>24</v>
       </c>
       <c r="C12" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D12" s="7">
-        <v>0.702759</v>
+        <v>0.700204</v>
       </c>
       <c r="E12" s="8">
-        <v>136815337217.01</v>
+        <v>136752353306.1</v>
       </c>
       <c r="F12" s="9">
-        <v>726293</v>
+        <v>726088</v>
       </c>
       <c r="G12" s="8">
-        <v>96148220626.48</v>
+        <v>95754500122.41</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3082,19 +3078,19 @@
         <v>26</v>
       </c>
       <c r="C13" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D13" s="10">
-        <v>2.00782</v>
+        <v>46147</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2.004016</v>
       </c>
       <c r="E13" s="8">
-        <v>1362481610.38</v>
+        <v>1363788550.2</v>
       </c>
       <c r="F13" s="9">
-        <v>32518</v>
+        <v>32560</v>
       </c>
       <c r="G13" s="8">
-        <v>2735618421.23</v>
+        <v>2733054065.39</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3105,19 +3101,19 @@
         <v>28</v>
       </c>
       <c r="C14" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D14" s="7">
-        <v>0.137032</v>
+        <v>0.137138</v>
       </c>
       <c r="E14" s="8">
-        <v>250011366.35</v>
+        <v>249831842</v>
       </c>
       <c r="F14" s="9">
         <v>92</v>
       </c>
       <c r="G14" s="8">
-        <v>34259634.71</v>
+        <v>34261471.54</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3128,19 +3124,19 @@
         <v>30</v>
       </c>
       <c r="C15" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D15" s="7">
-        <v>1.373041</v>
+        <v>1.370301</v>
       </c>
       <c r="E15" s="8">
-        <v>16130306835.75</v>
+        <v>16138286135.12</v>
       </c>
       <c r="F15" s="9">
-        <v>486804</v>
+        <v>486864</v>
       </c>
       <c r="G15" s="8">
-        <v>22147573515.17</v>
+        <v>22114314742.08</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3151,19 +3147,19 @@
         <v>32</v>
       </c>
       <c r="C16" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D16" s="7">
-        <v>0.092762</v>
+        <v>0.092503</v>
       </c>
       <c r="E16" s="8">
-        <v>559006179033.2</v>
+        <v>567593050589.75</v>
       </c>
       <c r="F16" s="9">
-        <v>1921440</v>
+        <v>1958593</v>
       </c>
       <c r="G16" s="8">
-        <v>51854519326.64</v>
+        <v>52503960890.6</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3174,19 +3170,19 @@
         <v>34</v>
       </c>
       <c r="C17" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D17" s="7">
-        <v>0.345297</v>
+        <v>0.345915</v>
       </c>
       <c r="E17" s="8">
-        <v>2107583779.17</v>
+        <v>2120019174.47</v>
       </c>
       <c r="F17" s="9">
-        <v>13287</v>
+        <v>13359</v>
       </c>
       <c r="G17" s="8">
-        <v>727742525.33</v>
+        <v>733346305.79</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3197,19 +3193,19 @@
         <v>36</v>
       </c>
       <c r="C18" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D18" s="7">
-        <v>0.145279</v>
+        <v>0.145277</v>
       </c>
       <c r="E18" s="8">
-        <v>33019402188.9</v>
+        <v>32990222939.03</v>
       </c>
       <c r="F18" s="9">
-        <v>239251</v>
+        <v>239170</v>
       </c>
       <c r="G18" s="8">
-        <v>4797019490.97</v>
+        <v>4792722271.72</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3220,19 +3216,19 @@
         <v>38</v>
       </c>
       <c r="C19" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D19" s="7">
-        <v>0.368111</v>
+        <v>0.366301</v>
       </c>
       <c r="E19" s="8">
-        <v>1424926005.39</v>
+        <v>1423563765.39</v>
       </c>
       <c r="F19" s="9">
         <v>537</v>
       </c>
       <c r="G19" s="8">
-        <v>524531498.53</v>
+        <v>521452266.47</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3243,19 +3239,19 @@
         <v>40</v>
       </c>
       <c r="C20" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D20" s="7">
-        <v>0.138112</v>
+        <v>0.138233</v>
       </c>
       <c r="E20" s="8">
-        <v>14498556429.17</v>
+        <v>14754983550.22</v>
       </c>
       <c r="F20" s="9">
-        <v>518710</v>
+        <v>525146</v>
       </c>
       <c r="G20" s="8">
-        <v>2002420192.57</v>
+        <v>2039632999.45</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3266,19 +3262,19 @@
         <v>42</v>
       </c>
       <c r="C21" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D21" s="10">
-        <v>0.09653</v>
+        <v>46147</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.096382</v>
       </c>
       <c r="E21" s="8">
-        <v>501132521610.56</v>
+        <v>510594682399.49</v>
       </c>
       <c r="F21" s="9">
-        <v>2268695</v>
+        <v>2306469</v>
       </c>
       <c r="G21" s="8">
-        <v>48374394726.92</v>
+        <v>49212013174.14</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3289,19 +3285,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D22" s="7">
-        <v>0.400358</v>
+        <v>0.398952</v>
       </c>
       <c r="E22" s="8">
-        <v>3360769379.62</v>
+        <v>3385175182.05</v>
       </c>
       <c r="F22" s="9">
-        <v>19104</v>
+        <v>19200</v>
       </c>
       <c r="G22" s="8">
-        <v>1345509669.24</v>
+        <v>1350522387.91</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3312,19 +3308,19 @@
         <v>46</v>
       </c>
       <c r="C23" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D23" s="7">
-        <v>0.092876</v>
+        <v>0.092608</v>
       </c>
       <c r="E23" s="8">
-        <v>571868429.81</v>
+        <v>577925086.7</v>
       </c>
       <c r="F23" s="9">
-        <v>4540</v>
+        <v>4611</v>
       </c>
       <c r="G23" s="8">
-        <v>53112852.22</v>
+        <v>53520266.64</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3335,19 +3331,19 @@
         <v>48</v>
       </c>
       <c r="C24" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D24" s="10">
-        <v>0.22578</v>
+        <v>46147</v>
+      </c>
+      <c r="D24" s="7">
+        <v>0.224758</v>
       </c>
       <c r="E24" s="8">
-        <v>1213844585.54</v>
+        <v>1213759574.5</v>
       </c>
       <c r="F24" s="9">
-        <v>4966</v>
+        <v>4964</v>
       </c>
       <c r="G24" s="8">
-        <v>274061669.6</v>
+        <v>272802591.73</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3358,19 +3354,19 @@
         <v>50</v>
       </c>
       <c r="C25" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D25" s="7">
-        <v>0.105293</v>
+        <v>0.105333</v>
       </c>
       <c r="E25" s="8">
-        <v>66491666851.52</v>
+        <v>66565128271.21</v>
       </c>
       <c r="F25" s="9">
-        <v>764430</v>
+        <v>764452</v>
       </c>
       <c r="G25" s="8">
-        <v>7001126454.86</v>
+        <v>7011522725.66</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3381,19 +3377,19 @@
         <v>52</v>
       </c>
       <c r="C26" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D26" s="7">
-        <v>0.097822</v>
+        <v>0.097974</v>
       </c>
       <c r="E26" s="8">
-        <v>1672317407.9</v>
+        <v>1672765675.24</v>
       </c>
       <c r="F26" s="9">
-        <v>3231</v>
+        <v>3226</v>
       </c>
       <c r="G26" s="8">
-        <v>163590094.76</v>
+        <v>163887736.8</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3404,19 +3400,19 @@
         <v>54</v>
       </c>
       <c r="C27" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D27" s="7">
-        <v>0.093532</v>
+        <v>0.093578</v>
       </c>
       <c r="E27" s="8">
-        <v>61691233989.34</v>
+        <v>61966627083</v>
       </c>
       <c r="F27" s="9">
-        <v>715304</v>
+        <v>715845</v>
       </c>
       <c r="G27" s="8">
-        <v>5770123630.93</v>
+        <v>5798738184.56</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3427,19 +3423,19 @@
         <v>56</v>
       </c>
       <c r="C28" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D28" s="7">
-        <v>0.385512</v>
+        <v>0.386086</v>
       </c>
       <c r="E28" s="8">
-        <v>1047698435.63</v>
+        <v>1048236878.43</v>
       </c>
       <c r="F28" s="9">
-        <v>7895</v>
+        <v>7874</v>
       </c>
       <c r="G28" s="8">
-        <v>403900717.49</v>
+        <v>404709452.09</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3450,19 +3446,19 @@
         <v>58</v>
       </c>
       <c r="C29" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D29" s="7">
-        <v>0.643732</v>
+        <v>0.645822</v>
       </c>
       <c r="E29" s="8">
-        <v>211549952.61</v>
+        <v>211002761.82</v>
       </c>
       <c r="F29" s="9">
-        <v>1668</v>
+        <v>1663</v>
       </c>
       <c r="G29" s="8">
-        <v>136181559.33</v>
+        <v>136270328.63</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3473,19 +3469,19 @@
         <v>60</v>
       </c>
       <c r="C30" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D30" s="7">
-        <v>2.369743</v>
+        <v>2.355195</v>
       </c>
       <c r="E30" s="8">
-        <v>845604381.17</v>
+        <v>847088960.84</v>
       </c>
       <c r="F30" s="9">
-        <v>19541</v>
+        <v>19542</v>
       </c>
       <c r="G30" s="8">
-        <v>2003865303.33</v>
+        <v>1995060097.42</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3496,19 +3492,19 @@
         <v>62</v>
       </c>
       <c r="C31" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D31" s="7">
-        <v>0.522961</v>
+        <v>0.523707</v>
       </c>
       <c r="E31" s="8">
-        <v>2402304452.51</v>
+        <v>2411101093.34</v>
       </c>
       <c r="F31" s="9">
-        <v>13852</v>
+        <v>14113</v>
       </c>
       <c r="G31" s="8">
-        <v>1256310696.89</v>
+        <v>1262711070.69</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3519,19 +3515,19 @@
         <v>64</v>
       </c>
       <c r="C32" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D32" s="7">
-        <v>0.847273</v>
+        <v>0.846179</v>
       </c>
       <c r="E32" s="8">
-        <v>12359495952.25</v>
+        <v>12372268635.32</v>
       </c>
       <c r="F32" s="9">
-        <v>77062</v>
+        <v>77086</v>
       </c>
       <c r="G32" s="8">
-        <v>10471868809.21</v>
+        <v>10469159499.64</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3542,19 +3538,19 @@
         <v>66</v>
       </c>
       <c r="C33" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D33" s="7">
-        <v>0.263762</v>
+        <v>0.264163</v>
       </c>
       <c r="E33" s="8">
-        <v>1309142537.25</v>
+        <v>1309401045.09</v>
       </c>
       <c r="F33" s="9">
-        <v>16195</v>
+        <v>16187</v>
       </c>
       <c r="G33" s="8">
-        <v>345301948.55</v>
+        <v>345895745.13</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3565,19 +3561,19 @@
         <v>68</v>
       </c>
       <c r="C34" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D34" s="7">
-        <v>0.125408</v>
+        <v>0.125458</v>
       </c>
       <c r="E34" s="8">
-        <v>3328559425.38</v>
+        <v>3327353326.67</v>
       </c>
       <c r="F34" s="9">
-        <v>53930</v>
+        <v>53914</v>
       </c>
       <c r="G34" s="8">
-        <v>417427019.3</v>
+        <v>417441732.23</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3588,19 +3584,19 @@
         <v>70</v>
       </c>
       <c r="C35" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D35" s="7">
-        <v>0.175668</v>
+        <v>0.175452</v>
       </c>
       <c r="E35" s="8">
-        <v>10722376757.22</v>
+        <v>10714917468.79</v>
       </c>
       <c r="F35" s="9">
-        <v>36575</v>
+        <v>36592</v>
       </c>
       <c r="G35" s="8">
-        <v>1883579864.93</v>
+        <v>1879954275.6</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3611,19 +3607,19 @@
         <v>72</v>
       </c>
       <c r="C36" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D36" s="7">
-        <v>0.202112</v>
+        <v>0.202407</v>
       </c>
       <c r="E36" s="8">
-        <v>1493479908.73</v>
+        <v>1493491332.97</v>
       </c>
       <c r="F36" s="9">
-        <v>32747</v>
+        <v>32745</v>
       </c>
       <c r="G36" s="8">
-        <v>301850703.91</v>
+        <v>302293006.06</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3634,19 +3630,19 @@
         <v>74</v>
       </c>
       <c r="C37" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D37" s="7">
-        <v>0.827341</v>
+        <v>0.830276</v>
       </c>
       <c r="E37" s="8">
-        <v>2446438396.65</v>
+        <v>2447614421.88</v>
       </c>
       <c r="F37" s="9">
-        <v>52344</v>
+        <v>52342</v>
       </c>
       <c r="G37" s="8">
-        <v>2024039421.69</v>
+        <v>2032196639.26</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3657,19 +3653,19 @@
         <v>76</v>
       </c>
       <c r="C38" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D38" s="7">
-        <v>0.169449</v>
+        <v>0.169658</v>
       </c>
       <c r="E38" s="8">
-        <v>3691126088.17</v>
+        <v>3692133745.02</v>
       </c>
       <c r="F38" s="9">
-        <v>53213</v>
+        <v>53205</v>
       </c>
       <c r="G38" s="8">
-        <v>625458396.28</v>
+        <v>626398603.87</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3680,19 +3676,19 @@
         <v>78</v>
       </c>
       <c r="C39" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D39" s="7">
-        <v>0.106427</v>
+        <v>0.107163</v>
       </c>
       <c r="E39" s="8">
-        <v>8018389425.14</v>
+        <v>8161693310.31</v>
       </c>
       <c r="F39" s="9">
-        <v>95714</v>
+        <v>96888</v>
       </c>
       <c r="G39" s="8">
-        <v>853369833.87</v>
+        <v>874627560.04</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3703,19 +3699,19 @@
         <v>80</v>
       </c>
       <c r="C40" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0.336541</v>
+        <v>46147</v>
+      </c>
+      <c r="D40" s="10">
+        <v>0.33736</v>
       </c>
       <c r="E40" s="8">
-        <v>14149306383.16</v>
+        <v>14129903383.29</v>
       </c>
       <c r="F40" s="9">
-        <v>157749</v>
+        <v>157530</v>
       </c>
       <c r="G40" s="8">
-        <v>4761816965.47</v>
+        <v>4766858941.85</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3726,19 +3722,19 @@
         <v>82</v>
       </c>
       <c r="C41" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D41" s="10">
-        <v>0.36541</v>
+        <v>46147</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0.365757</v>
       </c>
       <c r="E41" s="8">
-        <v>77013721602.34</v>
+        <v>77866004013.02</v>
       </c>
       <c r="F41" s="9">
-        <v>160397</v>
+        <v>176450</v>
       </c>
       <c r="G41" s="8">
-        <v>28141607510.99</v>
+        <v>28480042007.78</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3749,19 +3745,19 @@
         <v>84</v>
       </c>
       <c r="C42" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D42" s="7">
-        <v>0.952587</v>
+        <v>0.956205</v>
       </c>
       <c r="E42" s="8">
-        <v>12822867411.26</v>
+        <v>12828644089.11</v>
       </c>
       <c r="F42" s="9">
-        <v>234976</v>
+        <v>234889</v>
       </c>
       <c r="G42" s="8">
-        <v>12214903036.7</v>
+        <v>12266816830.51</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3772,19 +3768,19 @@
         <v>86</v>
       </c>
       <c r="C43" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D43" s="7">
-        <v>0.686445</v>
+        <v>0.690224</v>
       </c>
       <c r="E43" s="8">
-        <v>8873595007.25</v>
+        <v>8870243365.66</v>
       </c>
       <c r="F43" s="9">
-        <v>121327</v>
+        <v>121291</v>
       </c>
       <c r="G43" s="8">
-        <v>6091238592.48</v>
+        <v>6122453582.78</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3795,19 +3791,19 @@
         <v>88</v>
       </c>
       <c r="C44" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D44" s="7">
-        <v>2.954878</v>
+        <v>2.938954</v>
       </c>
       <c r="E44" s="8">
-        <v>8472305903.96</v>
+        <v>8473525410.21</v>
       </c>
       <c r="F44" s="9">
-        <v>365900</v>
+        <v>365924</v>
       </c>
       <c r="G44" s="8">
-        <v>25034633318.39</v>
+        <v>24903299224.09</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3818,19 +3814,19 @@
         <v>90</v>
       </c>
       <c r="C45" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D45" s="7">
-        <v>1.129074</v>
+        <v>1.136855</v>
       </c>
       <c r="E45" s="8">
-        <v>3665717160.06</v>
+        <v>3669098523.64</v>
       </c>
       <c r="F45" s="9">
-        <v>85758</v>
+        <v>85772</v>
       </c>
       <c r="G45" s="8">
-        <v>4138864734.39</v>
+        <v>4171231856.06</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3841,19 +3837,19 @@
         <v>92</v>
       </c>
       <c r="C46" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D46" s="7">
-        <v>0.421853</v>
+        <v>0.422042</v>
       </c>
       <c r="E46" s="8">
-        <v>23909277090.44</v>
+        <v>23900292039.23</v>
       </c>
       <c r="F46" s="9">
-        <v>219518</v>
+        <v>219485</v>
       </c>
       <c r="G46" s="8">
-        <v>10086203883.61</v>
+        <v>10086925174.32</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3864,19 +3860,19 @@
         <v>94</v>
       </c>
       <c r="C47" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D47" s="7">
-        <v>0.997752</v>
+        <v>0.999026</v>
       </c>
       <c r="E47" s="8">
-        <v>9681276227.72</v>
+        <v>9668556060.94</v>
       </c>
       <c r="F47" s="9">
-        <v>207458</v>
+        <v>207315</v>
       </c>
       <c r="G47" s="8">
-        <v>9659509325.4</v>
+        <v>9659141335.19</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3887,19 +3883,19 @@
         <v>96</v>
       </c>
       <c r="C48" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D48" s="7">
-        <v>1.349013</v>
+        <v>1.340661</v>
       </c>
       <c r="E48" s="8">
-        <v>714685272.65</v>
+        <v>713987330.83</v>
       </c>
       <c r="F48" s="9">
-        <v>7281</v>
+        <v>7277</v>
       </c>
       <c r="G48" s="8">
-        <v>964119560.45</v>
+        <v>957215035.62</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3910,19 +3906,19 @@
         <v>98</v>
       </c>
       <c r="C49" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D49" s="7">
-        <v>0.130303</v>
+        <v>0.130429</v>
       </c>
       <c r="E49" s="8">
-        <v>93632623326.5</v>
+        <v>93702532960.14</v>
       </c>
       <c r="F49" s="9">
-        <v>208418</v>
+        <v>208870</v>
       </c>
       <c r="G49" s="8">
-        <v>12200645094.64</v>
+        <v>12221552567.86</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3933,19 +3929,19 @@
         <v>100</v>
       </c>
       <c r="C50" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D50" s="10">
-        <v>0.09952</v>
+        <v>46147</v>
+      </c>
+      <c r="D50" s="7">
+        <v>0.099602</v>
       </c>
       <c r="E50" s="8">
-        <v>13779578406.79</v>
+        <v>14091391512.17</v>
       </c>
       <c r="F50" s="9">
-        <v>128916</v>
+        <v>127658</v>
       </c>
       <c r="G50" s="8">
-        <v>1371344768.53</v>
+        <v>1403527122.12</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3956,19 +3952,19 @@
         <v>102</v>
       </c>
       <c r="C51" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D51" s="10">
-        <v>0.49049</v>
+        <v>46147</v>
+      </c>
+      <c r="D51" s="7">
+        <v>0.487911</v>
       </c>
       <c r="E51" s="8">
-        <v>20419322982.83</v>
+        <v>20386496347.74</v>
       </c>
       <c r="F51" s="9">
-        <v>136776</v>
+        <v>136702</v>
       </c>
       <c r="G51" s="8">
-        <v>10015480282.18</v>
+        <v>9946794227.39</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3979,19 +3975,19 @@
         <v>104</v>
       </c>
       <c r="C52" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D52" s="7">
-        <v>0.212397</v>
+        <v>0.213055</v>
       </c>
       <c r="E52" s="8">
-        <v>2631845148.52</v>
+        <v>2632887136.63</v>
       </c>
       <c r="F52" s="9">
-        <v>10432</v>
+        <v>10433</v>
       </c>
       <c r="G52" s="8">
-        <v>558996448.78</v>
+        <v>560950784.67</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -4002,19 +3998,19 @@
         <v>106</v>
       </c>
       <c r="C53" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D53" s="7">
-        <v>0.267964</v>
+        <v>0.269387</v>
       </c>
       <c r="E53" s="8">
-        <v>2888195275.64</v>
+        <v>2888953853.79</v>
       </c>
       <c r="F53" s="9">
-        <v>10735</v>
+        <v>10739</v>
       </c>
       <c r="G53" s="8">
-        <v>773933202.26</v>
+        <v>778247174.54</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -4025,19 +4021,19 @@
         <v>108</v>
       </c>
       <c r="C54" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D54" s="7">
-        <v>0.329692</v>
+        <v>0.326874</v>
       </c>
       <c r="E54" s="8">
-        <v>4525232511.82</v>
+        <v>4531374106.22</v>
       </c>
       <c r="F54" s="9">
-        <v>15907</v>
+        <v>15908</v>
       </c>
       <c r="G54" s="8">
-        <v>1491931990.72</v>
+        <v>1481189120.57</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4048,19 +4044,19 @@
         <v>110</v>
       </c>
       <c r="C55" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D55" s="7">
-        <v>0.310868</v>
+        <v>46147</v>
+      </c>
+      <c r="D55" s="10">
+        <v>0.30915</v>
       </c>
       <c r="E55" s="8">
-        <v>2565411791.14</v>
+        <v>2567248327.81</v>
       </c>
       <c r="F55" s="9">
-        <v>10200</v>
+        <v>10190</v>
       </c>
       <c r="G55" s="8">
-        <v>797505197.47</v>
+        <v>793665806.51</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -4071,19 +4067,19 @@
         <v>112</v>
       </c>
       <c r="C56" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D56" s="7">
-        <v>0.221337</v>
+        <v>0.220054</v>
       </c>
       <c r="E56" s="8">
-        <v>1885936065.92</v>
+        <v>1884490751.3</v>
       </c>
       <c r="F56" s="9">
-        <v>6685</v>
+        <v>6680</v>
       </c>
       <c r="G56" s="8">
-        <v>417427667.03</v>
+        <v>414689090.45</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4094,19 +4090,19 @@
         <v>114</v>
       </c>
       <c r="C57" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D57" s="7">
-        <v>0.114475</v>
+        <v>0.114638</v>
       </c>
       <c r="E57" s="8">
-        <v>1630206376.96</v>
+        <v>1629230390.52</v>
       </c>
       <c r="F57" s="9">
-        <v>3922</v>
+        <v>3914</v>
       </c>
       <c r="G57" s="8">
-        <v>186617435.64</v>
+        <v>186772415.53</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -4117,19 +4113,19 @@
         <v>116</v>
       </c>
       <c r="C58" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D58" s="7">
-        <v>0.307537</v>
+        <v>0.306765</v>
       </c>
       <c r="E58" s="8">
-        <v>4434017000.81</v>
+        <v>4436092683.39</v>
       </c>
       <c r="F58" s="9">
-        <v>16767</v>
+        <v>16762</v>
       </c>
       <c r="G58" s="8">
-        <v>1363626474.8</v>
+        <v>1360837185.94</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -4140,19 +4136,19 @@
         <v>118</v>
       </c>
       <c r="C59" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D59" s="7">
-        <v>0.244677</v>
+        <v>0.243912</v>
       </c>
       <c r="E59" s="8">
-        <v>2805594453.8</v>
+        <v>2806958958.94</v>
       </c>
       <c r="F59" s="9">
-        <v>11310</v>
+        <v>11307</v>
       </c>
       <c r="G59" s="8">
-        <v>686465587.98</v>
+        <v>684650392.34</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -4163,19 +4159,19 @@
         <v>120</v>
       </c>
       <c r="C60" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D60" s="7">
-        <v>0.177154</v>
+        <v>0.177558</v>
       </c>
       <c r="E60" s="8">
-        <v>180153544.55</v>
+        <v>180603512.28</v>
       </c>
       <c r="F60" s="9">
         <v>451</v>
       </c>
       <c r="G60" s="8">
-        <v>31915001.35</v>
+        <v>32067582.55</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -4186,19 +4182,19 @@
         <v>122</v>
       </c>
       <c r="C61" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D61" s="7">
-        <v>0.376769</v>
+        <v>0.374327</v>
       </c>
       <c r="E61" s="8">
-        <v>858009636.94</v>
+        <v>857523924.87</v>
       </c>
       <c r="F61" s="9">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G61" s="8">
-        <v>323271300.69</v>
+        <v>320994203.35</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -4209,19 +4205,19 @@
         <v>124</v>
       </c>
       <c r="C62" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D62" s="7">
-        <v>0.073114</v>
+        <v>0.073262</v>
       </c>
       <c r="E62" s="8">
-        <v>174143078.03</v>
+        <v>172897250.85</v>
       </c>
       <c r="F62" s="9">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G62" s="8">
-        <v>12732375.88</v>
+        <v>12666773.97</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -4232,19 +4228,19 @@
         <v>126</v>
       </c>
       <c r="C63" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D63" s="7">
-        <v>0.143115</v>
+        <v>0.143453</v>
       </c>
       <c r="E63" s="8">
-        <v>109520801.34</v>
+        <v>109574449.12</v>
       </c>
       <c r="F63" s="9">
         <v>291</v>
       </c>
       <c r="G63" s="8">
-        <v>15674057.43</v>
+        <v>15718733.89</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -4255,19 +4251,19 @@
         <v>128</v>
       </c>
       <c r="C64" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D64" s="7">
-        <v>0.258638</v>
+        <v>0.258309</v>
       </c>
       <c r="E64" s="8">
-        <v>212692578.52</v>
+        <v>215525013.32</v>
       </c>
       <c r="F64" s="9">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G64" s="8">
-        <v>55010294.44</v>
+        <v>55672127.7</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4278,19 +4274,19 @@
         <v>130</v>
       </c>
       <c r="C65" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D65" s="10">
-        <v>0.33527</v>
+        <v>46147</v>
+      </c>
+      <c r="D65" s="7">
+        <v>0.333901</v>
       </c>
       <c r="E65" s="8">
-        <v>637835399.23</v>
+        <v>637911785.64</v>
       </c>
       <c r="F65" s="9">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G65" s="8">
-        <v>213847059.18</v>
+        <v>212999556.32</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -4301,19 +4297,19 @@
         <v>132</v>
       </c>
       <c r="C66" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D66" s="7">
-        <v>0.583337</v>
+        <v>0.573909</v>
       </c>
       <c r="E66" s="8">
-        <v>12925082851.07</v>
+        <v>12917037734.97</v>
       </c>
       <c r="F66" s="9">
-        <v>127531</v>
+        <v>127464</v>
       </c>
       <c r="G66" s="8">
-        <v>7539675696.01</v>
+        <v>7413209642.54</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4324,19 +4320,19 @@
         <v>134</v>
       </c>
       <c r="C67" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D67" s="7">
-        <v>0.259307</v>
+        <v>0.258453</v>
       </c>
       <c r="E67" s="8">
-        <v>2016392182.88</v>
+        <v>2018039419.58</v>
       </c>
       <c r="F67" s="9">
-        <v>6112</v>
+        <v>6113</v>
       </c>
       <c r="G67" s="8">
-        <v>522864533.19</v>
+        <v>521567971.54</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -4347,19 +4343,19 @@
         <v>136</v>
       </c>
       <c r="C68" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D68" s="7">
-        <v>2.001907</v>
+        <v>2.019153</v>
       </c>
       <c r="E68" s="8">
-        <v>7008023815.86</v>
+        <v>7006888688.77</v>
       </c>
       <c r="F68" s="9">
-        <v>236135</v>
+        <v>236042</v>
       </c>
       <c r="G68" s="8">
-        <v>14029413025.63</v>
+        <v>14147981144.18</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -4370,19 +4366,19 @@
         <v>138</v>
       </c>
       <c r="C69" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D69" s="7">
-        <v>0.998675</v>
+        <v>0.998859</v>
       </c>
       <c r="E69" s="8">
-        <v>6530711522.07</v>
+        <v>6513097387.62</v>
       </c>
       <c r="F69" s="9">
-        <v>163362</v>
+        <v>163276</v>
       </c>
       <c r="G69" s="8">
-        <v>6522057748.18</v>
+        <v>6505666649.6</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -4393,19 +4389,19 @@
         <v>140</v>
       </c>
       <c r="C70" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D70" s="11">
-        <v>0.3233</v>
+        <v>46147</v>
+      </c>
+      <c r="D70" s="7">
+        <v>0.322083</v>
       </c>
       <c r="E70" s="8">
-        <v>12170778625.82</v>
+        <v>12175964879.36</v>
       </c>
       <c r="F70" s="9">
-        <v>189546</v>
+        <v>189477</v>
       </c>
       <c r="G70" s="8">
-        <v>3934814242.31</v>
+        <v>3921676476.48</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4416,19 +4412,19 @@
         <v>142</v>
       </c>
       <c r="C71" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D71" s="7">
-        <v>0.098699</v>
+        <v>0.098778</v>
       </c>
       <c r="E71" s="8">
-        <v>7396943322.45</v>
+        <v>7675240515.15</v>
       </c>
       <c r="F71" s="9">
-        <v>115558</v>
+        <v>118914</v>
       </c>
       <c r="G71" s="8">
-        <v>730070096.66</v>
+        <v>758145885.36</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -4439,19 +4435,19 @@
         <v>144</v>
       </c>
       <c r="C72" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D72" s="7">
-        <v>0.095472</v>
+        <v>0.095175</v>
       </c>
       <c r="E72" s="8">
-        <v>385559365628.65</v>
+        <v>391150585971.82</v>
       </c>
       <c r="F72" s="9">
-        <v>1406278</v>
+        <v>1424169</v>
       </c>
       <c r="G72" s="8">
-        <v>36810198816.5</v>
+        <v>37227933252.88</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4462,19 +4458,19 @@
         <v>146</v>
       </c>
       <c r="C73" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D73" s="7">
-        <v>1.092482</v>
+        <v>1.096778</v>
       </c>
       <c r="E73" s="8">
-        <v>6396799931.25</v>
+        <v>6395996911.94</v>
       </c>
       <c r="F73" s="9">
-        <v>262464</v>
+        <v>262261</v>
       </c>
       <c r="G73" s="8">
-        <v>6988388215.04</v>
+        <v>7014991482.37</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4485,19 +4481,19 @@
         <v>148</v>
       </c>
       <c r="C74" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D74" s="7">
-        <v>0.507292</v>
+        <v>0.508794</v>
       </c>
       <c r="E74" s="8">
-        <v>6736836767.96</v>
+        <v>6728219699.57</v>
       </c>
       <c r="F74" s="9">
-        <v>65739</v>
+        <v>65676</v>
       </c>
       <c r="G74" s="8">
-        <v>3417543621.78</v>
+        <v>3423280451.2</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -4508,19 +4504,19 @@
         <v>150</v>
       </c>
       <c r="C75" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D75" s="7">
-        <v>1.539867</v>
+        <v>1.553513</v>
       </c>
       <c r="E75" s="8">
-        <v>493509853.48</v>
+        <v>493682134.98</v>
       </c>
       <c r="F75" s="9">
-        <v>4994</v>
+        <v>5004</v>
       </c>
       <c r="G75" s="8">
-        <v>759939726.88</v>
+        <v>766941840.84</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4531,19 +4527,19 @@
         <v>152</v>
       </c>
       <c r="C76" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D76" s="7">
-        <v>0.693314</v>
+        <v>0.693081</v>
       </c>
       <c r="E76" s="8">
-        <v>212538009174.43</v>
+        <v>212430762979.33</v>
       </c>
       <c r="F76" s="9">
-        <v>719977</v>
+        <v>720034</v>
       </c>
       <c r="G76" s="8">
-        <v>147355563416.81</v>
+        <v>147231779547.22</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4554,19 +4550,19 @@
         <v>154</v>
       </c>
       <c r="C77" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D77" s="7">
-        <v>0.574727</v>
+        <v>0.571137</v>
       </c>
       <c r="E77" s="8">
-        <v>194141050.37</v>
+        <v>194128483.9</v>
       </c>
       <c r="F77" s="9">
         <v>22328</v>
       </c>
       <c r="G77" s="8">
-        <v>111578116.27</v>
+        <v>110874051.8</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4577,19 +4573,19 @@
         <v>156</v>
       </c>
       <c r="C78" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D78" s="7">
-        <v>0.297703</v>
+        <v>0.297177</v>
       </c>
       <c r="E78" s="8">
-        <v>395549751.04</v>
+        <v>396494848.33</v>
       </c>
       <c r="F78" s="9">
         <v>33150</v>
       </c>
       <c r="G78" s="8">
-        <v>117756541.74</v>
+        <v>117829045.22</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4600,19 +4596,19 @@
         <v>158</v>
       </c>
       <c r="C79" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D79" s="7">
-        <v>0.159114</v>
+        <v>0.159518</v>
       </c>
       <c r="E79" s="8">
-        <v>3113301074.2</v>
+        <v>3112507181.36</v>
       </c>
       <c r="F79" s="9">
-        <v>6949</v>
+        <v>6950</v>
       </c>
       <c r="G79" s="8">
-        <v>495368488.28</v>
+        <v>496500337.29</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4623,19 +4619,19 @@
         <v>160</v>
       </c>
       <c r="C80" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D80" s="10">
-        <v>0.33431</v>
+        <v>46147</v>
+      </c>
+      <c r="D80" s="7">
+        <v>0.334563</v>
       </c>
       <c r="E80" s="8">
-        <v>237578055.98</v>
+        <v>236965919.22</v>
       </c>
       <c r="F80" s="9">
-        <v>20830</v>
+        <v>20862</v>
       </c>
       <c r="G80" s="8">
-        <v>79424787.93</v>
+        <v>79280141.9</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4646,19 +4642,19 @@
         <v>162</v>
       </c>
       <c r="C81" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D81" s="7">
-        <v>0.177912</v>
+        <v>0.178215</v>
       </c>
       <c r="E81" s="8">
-        <v>700201881.76</v>
+        <v>700493711.47</v>
       </c>
       <c r="F81" s="9">
-        <v>2347</v>
+        <v>2344</v>
       </c>
       <c r="G81" s="8">
-        <v>124574223.61</v>
+        <v>124838190</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4669,19 +4665,19 @@
         <v>164</v>
       </c>
       <c r="C82" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D82" s="11">
-        <v>1.8691</v>
+        <v>46147</v>
+      </c>
+      <c r="D82" s="7">
+        <v>1.844193</v>
       </c>
       <c r="E82" s="8">
-        <v>83963770.09</v>
+        <v>83945765.5</v>
       </c>
       <c r="F82" s="9">
         <v>13723</v>
       </c>
       <c r="G82" s="8">
-        <v>156936689.95</v>
+        <v>154812187.82</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4692,19 +4688,19 @@
         <v>166</v>
       </c>
       <c r="C83" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D83" s="7">
-        <v>0.095498</v>
+        <v>46147</v>
+      </c>
+      <c r="D83" s="10">
+        <v>0.09559</v>
       </c>
       <c r="E83" s="8">
-        <v>10185074375.52</v>
+        <v>10212978800.62</v>
       </c>
       <c r="F83" s="9">
-        <v>168832</v>
+        <v>169655</v>
       </c>
       <c r="G83" s="8">
-        <v>972657333.92</v>
+        <v>976257176.08</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4715,19 +4711,19 @@
         <v>168</v>
       </c>
       <c r="C84" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D84" s="7">
-        <v>0.083748</v>
+        <v>0.083837</v>
       </c>
       <c r="E84" s="8">
-        <v>9039556811.82</v>
+        <v>8875726775.54</v>
       </c>
       <c r="F84" s="9">
-        <v>138777</v>
+        <v>137999</v>
       </c>
       <c r="G84" s="8">
-        <v>757047838.22</v>
+        <v>744117144.23</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4738,19 +4734,19 @@
         <v>170</v>
       </c>
       <c r="C85" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D85" s="7">
-        <v>0.268356</v>
+        <v>0.268561</v>
       </c>
       <c r="E85" s="8">
-        <v>4319076011.55</v>
+        <v>4320643294.18</v>
       </c>
       <c r="F85" s="9">
-        <v>79875</v>
+        <v>79887</v>
       </c>
       <c r="G85" s="8">
-        <v>1159049774.35</v>
+        <v>1160357760.09</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4761,19 +4757,19 @@
         <v>172</v>
       </c>
       <c r="C86" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D86" s="7">
-        <v>0.903682</v>
+        <v>0.893982</v>
       </c>
       <c r="E86" s="8">
-        <v>4610659309.68</v>
+        <v>4610754197.76</v>
       </c>
       <c r="F86" s="9">
-        <v>87149</v>
+        <v>87092</v>
       </c>
       <c r="G86" s="8">
-        <v>4166569459</v>
+        <v>4121929913.43</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4784,19 +4780,19 @@
         <v>174</v>
       </c>
       <c r="C87" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D87" s="10">
-        <v>0.22381</v>
+        <v>46147</v>
+      </c>
+      <c r="D87" s="7">
+        <v>0.223661</v>
       </c>
       <c r="E87" s="8">
-        <v>12561867580.44</v>
+        <v>12553393188.54</v>
       </c>
       <c r="F87" s="9">
-        <v>143945</v>
+        <v>144124</v>
       </c>
       <c r="G87" s="8">
-        <v>2811466286.64</v>
+        <v>2807701546.1</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4807,19 +4803,19 @@
         <v>176</v>
       </c>
       <c r="C88" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D88" s="7">
-        <v>0.164358</v>
+        <v>46147</v>
+      </c>
+      <c r="D88" s="10">
+        <v>0.16443</v>
       </c>
       <c r="E88" s="8">
-        <v>18445495140.9</v>
+        <v>18377333838.39</v>
       </c>
       <c r="F88" s="9">
-        <v>90782</v>
+        <v>90689</v>
       </c>
       <c r="G88" s="8">
-        <v>3031662934.36</v>
+        <v>3021790274.71</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4830,19 +4826,19 @@
         <v>178</v>
       </c>
       <c r="C89" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D89" s="7">
-        <v>0.633294</v>
+        <v>0.634834</v>
       </c>
       <c r="E89" s="8">
-        <v>2273718936.27</v>
+        <v>2268386773.26</v>
       </c>
       <c r="F89" s="9">
-        <v>35924</v>
+        <v>35882</v>
       </c>
       <c r="G89" s="8">
-        <v>1439932413.51</v>
+        <v>1440049232.33</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4853,19 +4849,19 @@
         <v>180</v>
       </c>
       <c r="C90" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D90" s="7">
-        <v>0.840507</v>
+        <v>46147</v>
+      </c>
+      <c r="D90" s="10">
+        <v>0.84566</v>
       </c>
       <c r="E90" s="8">
-        <v>19199983508.64</v>
+        <v>19177825908.08</v>
       </c>
       <c r="F90" s="9">
-        <v>272680</v>
+        <v>272424</v>
       </c>
       <c r="G90" s="8">
-        <v>16137721907.17</v>
+        <v>16217920324.46</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4876,19 +4872,19 @@
         <v>182</v>
       </c>
       <c r="C91" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D91" s="7">
-        <v>0.787317</v>
+        <v>0.787207</v>
       </c>
       <c r="E91" s="8">
-        <v>3483545657.63</v>
+        <v>3486273490.83</v>
       </c>
       <c r="F91" s="9">
-        <v>29317</v>
+        <v>29401</v>
       </c>
       <c r="G91" s="8">
-        <v>2742653124.71</v>
+        <v>2744419228.71</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4899,19 +4895,19 @@
         <v>184</v>
       </c>
       <c r="C92" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D92" s="7">
-        <v>0.828035</v>
+        <v>0.832114</v>
       </c>
       <c r="E92" s="8">
-        <v>12353060322.74</v>
+        <v>12340270408.78</v>
       </c>
       <c r="F92" s="9">
-        <v>188953</v>
+        <v>188723</v>
       </c>
       <c r="G92" s="8">
-        <v>10228769031.58</v>
+        <v>10268508304.13</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4922,19 +4918,19 @@
         <v>186</v>
       </c>
       <c r="C93" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D93" s="7">
-        <v>0.087951</v>
+        <v>0.088053</v>
       </c>
       <c r="E93" s="8">
-        <v>7509692089.37</v>
+        <v>7507626795.38</v>
       </c>
       <c r="F93" s="9">
-        <v>155375</v>
+        <v>154884</v>
       </c>
       <c r="G93" s="8">
-        <v>660483831.52</v>
+        <v>661067412.78</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4945,19 +4941,19 @@
         <v>188</v>
       </c>
       <c r="C94" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D94" s="7">
-        <v>0.119546</v>
+        <v>0.119607</v>
       </c>
       <c r="E94" s="8">
-        <v>11932115864.03</v>
+        <v>11948275146.86</v>
       </c>
       <c r="F94" s="9">
-        <v>33299</v>
+        <v>33306</v>
       </c>
       <c r="G94" s="8">
-        <v>1426435287.45</v>
+        <v>1429099079.82</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4968,19 +4964,19 @@
         <v>190</v>
       </c>
       <c r="C95" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D95" s="7">
-        <v>0.127802</v>
+        <v>0.127933</v>
       </c>
       <c r="E95" s="8">
-        <v>71832948312.87</v>
+        <v>71677577134.38</v>
       </c>
       <c r="F95" s="9">
-        <v>212402</v>
+        <v>212220</v>
       </c>
       <c r="G95" s="8">
-        <v>9180386318.6</v>
+        <v>9169962379.73</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4991,19 +4987,19 @@
         <v>192</v>
       </c>
       <c r="C96" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D96" s="7">
-        <v>0.449382</v>
+        <v>0.467645</v>
       </c>
       <c r="E96" s="8">
-        <v>31789121209.92</v>
+        <v>31802302843.77</v>
       </c>
       <c r="F96" s="9">
-        <v>282158</v>
+        <v>282407</v>
       </c>
       <c r="G96" s="8">
-        <v>14285456138.39</v>
+        <v>14872190984.2</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -5014,19 +5010,19 @@
         <v>194</v>
       </c>
       <c r="C97" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D97" s="10">
-        <v>0.09638</v>
+        <v>46147</v>
+      </c>
+      <c r="D97" s="7">
+        <v>0.096466</v>
       </c>
       <c r="E97" s="8">
-        <v>24471141974.38</v>
+        <v>24473623712.76</v>
       </c>
       <c r="F97" s="9">
-        <v>441829</v>
+        <v>441767</v>
       </c>
       <c r="G97" s="8">
-        <v>2358518093</v>
+        <v>2360868869.22</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -5037,19 +5033,19 @@
         <v>196</v>
       </c>
       <c r="C98" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D98" s="7">
-        <v>0.243375</v>
+        <v>0.243812</v>
       </c>
       <c r="E98" s="8">
-        <v>1287172504.6</v>
+        <v>1289026275.86</v>
       </c>
       <c r="F98" s="9">
-        <v>7185</v>
+        <v>7177</v>
       </c>
       <c r="G98" s="8">
-        <v>313265312.57</v>
+        <v>314280100.45</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -5060,19 +5056,19 @@
         <v>198</v>
       </c>
       <c r="C99" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D99" s="10">
-        <v>1.03292</v>
+        <v>46147</v>
+      </c>
+      <c r="D99" s="7">
+        <v>1.040379</v>
       </c>
       <c r="E99" s="8">
-        <v>4274087522.96</v>
+        <v>4529576701.11</v>
       </c>
       <c r="F99" s="9">
-        <v>45594</v>
+        <v>46717</v>
       </c>
       <c r="G99" s="8">
-        <v>4414790549.59</v>
+        <v>4712475098.21</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5083,19 +5079,19 @@
         <v>200</v>
       </c>
       <c r="C100" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D100" s="7">
-        <v>2.596354</v>
+        <v>2.580359</v>
       </c>
       <c r="E100" s="8">
-        <v>12041623290.98</v>
+        <v>12026977536.95</v>
       </c>
       <c r="F100" s="9">
-        <v>305475</v>
+        <v>305649</v>
       </c>
       <c r="G100" s="8">
-        <v>31264318158.23</v>
+        <v>31033918625.16</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5106,19 +5102,19 @@
         <v>202</v>
       </c>
       <c r="C101" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D101" s="7">
-        <v>0.352822</v>
+        <v>0.353735</v>
       </c>
       <c r="E101" s="8">
-        <v>26514552515.53</v>
+        <v>26215844823.65</v>
       </c>
       <c r="F101" s="9">
-        <v>333377</v>
+        <v>332707</v>
       </c>
       <c r="G101" s="8">
-        <v>9354929056.14</v>
+        <v>9273454952.76</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5129,19 +5125,19 @@
         <v>204</v>
       </c>
       <c r="C102" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D102" s="7">
-        <v>0.367937</v>
+        <v>0.368257</v>
       </c>
       <c r="E102" s="8">
-        <v>202311478188.05</v>
+        <v>202884119319.23</v>
       </c>
       <c r="F102" s="9">
-        <v>338605</v>
+        <v>378054</v>
       </c>
       <c r="G102" s="8">
-        <v>74437780529.26</v>
+        <v>74713409169.58</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5152,19 +5148,19 @@
         <v>206</v>
       </c>
       <c r="C103" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D103" s="7">
-        <v>0.123477</v>
+        <v>0.123545</v>
       </c>
       <c r="E103" s="8">
-        <v>8899779336.99</v>
+        <v>8883480634.3</v>
       </c>
       <c r="F103" s="9">
-        <v>28569</v>
+        <v>28568</v>
       </c>
       <c r="G103" s="8">
-        <v>1098917122.29</v>
+        <v>1097505320.47</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -5175,19 +5171,19 @@
         <v>208</v>
       </c>
       <c r="C104" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D104" s="7">
-        <v>0.281216</v>
+        <v>0.282928</v>
       </c>
       <c r="E104" s="8">
-        <v>1720418246.88</v>
+        <v>1717379176.2</v>
       </c>
       <c r="F104" s="9">
         <v>7834</v>
       </c>
       <c r="G104" s="8">
-        <v>483809742.36</v>
+        <v>485894031.89</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -5198,19 +5194,19 @@
         <v>210</v>
       </c>
       <c r="C105" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D105" s="8">
         <v>0.01</v>
       </c>
       <c r="E105" s="8">
+        <v>19219.8</v>
+      </c>
+      <c r="F105" s="9">
         <v>1</v>
       </c>
-      <c r="F105" s="9">
-        <v>0</v>
-      </c>
       <c r="G105" s="8">
-        <v>0.01</v>
+        <v>192.19</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5221,19 +5217,19 @@
         <v>212</v>
       </c>
       <c r="C106" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D106" s="7">
-        <v>1.050132</v>
+        <v>1.045487</v>
       </c>
       <c r="E106" s="8">
-        <v>248372285.1</v>
+        <v>248908503.07</v>
       </c>
       <c r="F106" s="9">
-        <v>4083</v>
+        <v>4091</v>
       </c>
       <c r="G106" s="8">
-        <v>260823634.24</v>
+        <v>260230677.09</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5244,19 +5240,19 @@
         <v>214</v>
       </c>
       <c r="C107" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D107" s="10">
-        <v>0.99053</v>
+        <v>46147</v>
+      </c>
+      <c r="D107" s="7">
+        <v>0.989839</v>
       </c>
       <c r="E107" s="8">
-        <v>608648308.62</v>
+        <v>605769966.21</v>
       </c>
       <c r="F107" s="9">
-        <v>15416</v>
+        <v>15423</v>
       </c>
       <c r="G107" s="8">
-        <v>602884184.84</v>
+        <v>599614664.01</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -5267,19 +5263,19 @@
         <v>216</v>
       </c>
       <c r="C108" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D108" s="7">
-        <v>0.177827</v>
+        <v>0.178158</v>
       </c>
       <c r="E108" s="8">
-        <v>379589889.2</v>
+        <v>379725028</v>
       </c>
       <c r="F108" s="9">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="G108" s="8">
-        <v>67501285.83</v>
+        <v>67650971.64</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -5290,19 +5286,19 @@
         <v>218</v>
       </c>
       <c r="C109" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D109" s="10">
-        <v>1.44721</v>
+        <v>46147</v>
+      </c>
+      <c r="D109" s="7">
+        <v>1.435486</v>
       </c>
       <c r="E109" s="8">
-        <v>1015255508.16</v>
+        <v>1015883174.92</v>
       </c>
       <c r="F109" s="9">
-        <v>21910</v>
+        <v>21916</v>
       </c>
       <c r="G109" s="8">
-        <v>1469287702.12</v>
+        <v>1458285704.35</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -5313,19 +5309,19 @@
         <v>220</v>
       </c>
       <c r="C110" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D110" s="7">
-        <v>0.096812</v>
+        <v>0.096814</v>
       </c>
       <c r="E110" s="8">
-        <v>5439744061.8</v>
+        <v>5448538052.07</v>
       </c>
       <c r="F110" s="9">
-        <v>24208</v>
+        <v>24302</v>
       </c>
       <c r="G110" s="8">
-        <v>526631242.92</v>
+        <v>527492050.44</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5336,19 +5332,19 @@
         <v>222</v>
       </c>
       <c r="C111" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D111" s="10">
-        <v>0.28478</v>
+        <v>46147</v>
+      </c>
+      <c r="D111" s="7">
+        <v>0.285599</v>
       </c>
       <c r="E111" s="8">
-        <v>1638885272.1</v>
+        <v>1640381231.46</v>
       </c>
       <c r="F111" s="9">
-        <v>33231</v>
+        <v>33257</v>
       </c>
       <c r="G111" s="8">
-        <v>466722390.53</v>
+        <v>468491666.55</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -5359,19 +5355,19 @@
         <v>224</v>
       </c>
       <c r="C112" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D112" s="7">
-        <v>0.212221</v>
+        <v>0.213026</v>
       </c>
       <c r="E112" s="8">
-        <v>589389048.84</v>
+        <v>589020595.94</v>
       </c>
       <c r="F112" s="9">
         <v>1427</v>
       </c>
       <c r="G112" s="8">
-        <v>125080750.06</v>
+        <v>125476650.77</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -5382,19 +5378,19 @@
         <v>226</v>
       </c>
       <c r="C113" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D113" s="7">
-        <v>0.408463</v>
+        <v>0.409531</v>
       </c>
       <c r="E113" s="8">
-        <v>149267574.93</v>
+        <v>149580084.22</v>
       </c>
       <c r="F113" s="9">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="G113" s="8">
-        <v>60970217.96</v>
+        <v>61257665</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5405,19 +5401,19 @@
         <v>228</v>
       </c>
       <c r="C114" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D114" s="7">
-        <v>0.107982</v>
+        <v>0.108255</v>
       </c>
       <c r="E114" s="8">
-        <v>194530556.51</v>
+        <v>194767369.36</v>
       </c>
       <c r="F114" s="9">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="G114" s="8">
-        <v>21005880.19</v>
+        <v>21084473.59</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -5428,19 +5424,19 @@
         <v>230</v>
       </c>
       <c r="C115" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D115" s="7">
-        <v>0.062779</v>
+        <v>0.062783</v>
       </c>
       <c r="E115" s="8">
-        <v>1218688729423.03</v>
+        <v>1217912369381.75</v>
       </c>
       <c r="F115" s="9">
-        <v>789076</v>
+        <v>788786</v>
       </c>
       <c r="G115" s="8">
-        <v>76507906003.87</v>
+        <v>76464395181.93</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -5451,19 +5447,19 @@
         <v>232</v>
       </c>
       <c r="C116" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D116" s="7">
-        <v>0.015445</v>
+        <v>0.015463</v>
       </c>
       <c r="E116" s="8">
-        <v>6500943713.87</v>
+        <v>6434055727.74</v>
       </c>
       <c r="F116" s="9">
-        <v>1309</v>
+        <v>1320</v>
       </c>
       <c r="G116" s="8">
-        <v>100409643.45</v>
+        <v>99492949.27</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -5474,19 +5470,19 @@
         <v>234</v>
       </c>
       <c r="C117" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D117" s="7">
-        <v>0.123834</v>
+        <v>0.123351</v>
       </c>
       <c r="E117" s="8">
-        <v>7494170988.66</v>
+        <v>7517299331.69</v>
       </c>
       <c r="F117" s="9">
-        <v>24692</v>
+        <v>24755</v>
       </c>
       <c r="G117" s="8">
-        <v>928032909.02</v>
+        <v>927268311.63</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -5497,19 +5493,19 @@
         <v>236</v>
       </c>
       <c r="C118" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D118" s="7">
-        <v>0.124211</v>
+        <v>0.126595</v>
       </c>
       <c r="E118" s="8">
-        <v>28307288017.91</v>
+        <v>28635691908.59</v>
       </c>
       <c r="F118" s="9">
-        <v>68769</v>
+        <v>69040</v>
       </c>
       <c r="G118" s="8">
-        <v>3516086953.38</v>
+        <v>3625130294.4</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -5520,19 +5516,19 @@
         <v>238</v>
       </c>
       <c r="C119" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D119" s="11">
-        <v>0.5687</v>
+        <v>46147</v>
+      </c>
+      <c r="D119" s="7">
+        <v>0.570777</v>
       </c>
       <c r="E119" s="8">
-        <v>91019396.9</v>
+        <v>90855434.38</v>
       </c>
       <c r="F119" s="9">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G119" s="8">
-        <v>51762770.62</v>
+        <v>51858205.88</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5543,19 +5539,19 @@
         <v>240</v>
       </c>
       <c r="C120" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D120" s="7">
-        <v>0.737097</v>
+        <v>0.737719</v>
       </c>
       <c r="E120" s="8">
-        <v>22891263620.89</v>
+        <v>22868612619.93</v>
       </c>
       <c r="F120" s="9">
-        <v>149219</v>
+        <v>149152</v>
       </c>
       <c r="G120" s="8">
-        <v>16873079114.22</v>
+        <v>16870608681.53</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5566,19 +5562,19 @@
         <v>242</v>
       </c>
       <c r="C121" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D121" s="7">
-        <v>0.122951</v>
+        <v>0.123098</v>
       </c>
       <c r="E121" s="8">
-        <v>14718348052.25</v>
+        <v>14721189280.84</v>
       </c>
       <c r="F121" s="9">
-        <v>44584</v>
+        <v>44557</v>
       </c>
       <c r="G121" s="8">
-        <v>1809629227</v>
+        <v>1812144701.83</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -5589,19 +5585,19 @@
         <v>244</v>
       </c>
       <c r="C122" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D122" s="7">
-        <v>0.104495</v>
+        <v>46147</v>
+      </c>
+      <c r="D122" s="11">
+        <v>0.1042</v>
       </c>
       <c r="E122" s="8">
-        <v>42420632077.21</v>
+        <v>42907236646.99</v>
       </c>
       <c r="F122" s="9">
-        <v>334869</v>
+        <v>338325</v>
       </c>
       <c r="G122" s="8">
-        <v>4432736328.7</v>
+        <v>4470947354.01</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -5612,19 +5608,19 @@
         <v>246</v>
       </c>
       <c r="C123" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D123" s="7">
-        <v>0.092929</v>
+        <v>0.092647</v>
       </c>
       <c r="E123" s="8">
-        <v>9683443865.82</v>
+        <v>9674419144.21</v>
       </c>
       <c r="F123" s="9">
-        <v>148002</v>
+        <v>147983</v>
       </c>
       <c r="G123" s="8">
-        <v>899868853.48</v>
+        <v>896308025.13</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -5635,19 +5631,19 @@
         <v>248</v>
       </c>
       <c r="C124" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D124" s="7">
-        <v>0.047917</v>
+        <v>46147</v>
+      </c>
+      <c r="D124" s="10">
+        <v>0.04762</v>
       </c>
       <c r="E124" s="8">
-        <v>27987150755.59</v>
+        <v>27955804439.29</v>
       </c>
       <c r="F124" s="9">
-        <v>34515</v>
+        <v>34523</v>
       </c>
       <c r="G124" s="8">
-        <v>1341048337.14</v>
+        <v>1331259971.64</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5658,19 +5654,19 @@
         <v>250</v>
       </c>
       <c r="C125" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D125" s="7">
-        <v>0.117526</v>
+        <v>0.117168</v>
       </c>
       <c r="E125" s="8">
-        <v>6294120657.05</v>
+        <v>6291630621.4</v>
       </c>
       <c r="F125" s="9">
-        <v>43223</v>
+        <v>43210</v>
       </c>
       <c r="G125" s="8">
-        <v>739722025.61</v>
+        <v>737176474.96</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5681,19 +5677,19 @@
         <v>252</v>
       </c>
       <c r="C126" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D126" s="7">
-        <v>0.090557</v>
+        <v>0.090655</v>
       </c>
       <c r="E126" s="8">
-        <v>2961294008.37</v>
+        <v>2962465556.14</v>
       </c>
       <c r="F126" s="9">
-        <v>83455</v>
+        <v>83481</v>
       </c>
       <c r="G126" s="8">
-        <v>268164706.67</v>
+        <v>268561936.33</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5704,19 +5700,19 @@
         <v>254</v>
       </c>
       <c r="C127" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D127" s="7">
-        <v>0.083274</v>
+        <v>0.083494</v>
       </c>
       <c r="E127" s="8">
-        <v>1119889419.11</v>
+        <v>1128427630.49</v>
       </c>
       <c r="F127" s="9">
-        <v>121855</v>
+        <v>122915</v>
       </c>
       <c r="G127" s="8">
-        <v>93257736.43</v>
+        <v>94216470.02</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5727,19 +5723,19 @@
         <v>256</v>
       </c>
       <c r="C128" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D128" s="7">
-        <v>0.762825</v>
+        <v>0.757898</v>
       </c>
       <c r="E128" s="8">
-        <v>1637246210.3</v>
+        <v>1636830206.44</v>
       </c>
       <c r="F128" s="9">
-        <v>49941</v>
+        <v>49927</v>
       </c>
       <c r="G128" s="8">
-        <v>1248932431.95</v>
+        <v>1240550693.9</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5750,19 +5746,19 @@
         <v>258</v>
       </c>
       <c r="C129" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D129" s="7">
-        <v>0.147515</v>
+        <v>0.147822</v>
       </c>
       <c r="E129" s="8">
-        <v>1288246705.17</v>
+        <v>1288968310.99</v>
       </c>
       <c r="F129" s="9">
-        <v>12557</v>
+        <v>12555</v>
       </c>
       <c r="G129" s="8">
-        <v>190035395.11</v>
+        <v>190537359.5</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5773,19 +5769,19 @@
         <v>260</v>
       </c>
       <c r="C130" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D130" s="7">
-        <v>0.237294</v>
+        <v>0.237756</v>
       </c>
       <c r="E130" s="8">
-        <v>5197129415.9</v>
+        <v>5191103772.93</v>
       </c>
       <c r="F130" s="9">
-        <v>69531</v>
+        <v>69515</v>
       </c>
       <c r="G130" s="8">
-        <v>1233245454.37</v>
+        <v>1234217899.16</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5796,19 +5792,19 @@
         <v>262</v>
       </c>
       <c r="C131" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D131" s="7">
-        <v>1.827748</v>
+        <v>1.806407</v>
       </c>
       <c r="E131" s="8">
-        <v>2370094571.5</v>
+        <v>2371458356.23</v>
       </c>
       <c r="F131" s="9">
-        <v>52862</v>
+        <v>52870</v>
       </c>
       <c r="G131" s="8">
-        <v>4331936322.65</v>
+        <v>4283818020.6</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5819,19 +5815,19 @@
         <v>264</v>
       </c>
       <c r="C132" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D132" s="7">
-        <v>0.352092</v>
+        <v>0.349436</v>
       </c>
       <c r="E132" s="8">
-        <v>557094208.21</v>
+        <v>556385404.18</v>
       </c>
       <c r="F132" s="9">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="G132" s="8">
-        <v>196148364.68</v>
+        <v>194421356.3</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5842,19 +5838,19 @@
         <v>266</v>
       </c>
       <c r="C133" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D133" s="7">
-        <v>0.158996</v>
+        <v>0.158027</v>
       </c>
       <c r="E133" s="8">
-        <v>131820546.11</v>
+        <v>131844793.61</v>
       </c>
       <c r="F133" s="9">
         <v>458</v>
       </c>
       <c r="G133" s="8">
-        <v>20959003.38</v>
+        <v>20835030.81</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5865,19 +5861,19 @@
         <v>268</v>
       </c>
       <c r="C134" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D134" s="7">
-        <v>0.703404</v>
+        <v>0.705235</v>
       </c>
       <c r="E134" s="8">
-        <v>1258162609.41</v>
+        <v>1256491730.55</v>
       </c>
       <c r="F134" s="9">
-        <v>21196</v>
+        <v>21180</v>
       </c>
       <c r="G134" s="8">
-        <v>884996180.15</v>
+        <v>886121465.41</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5888,19 +5884,19 @@
         <v>270</v>
       </c>
       <c r="C135" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D135" s="7">
-        <v>0.370261</v>
+        <v>0.370583</v>
       </c>
       <c r="E135" s="8">
-        <v>7375895293.63</v>
+        <v>7521821480.25</v>
       </c>
       <c r="F135" s="9">
-        <v>90002</v>
+        <v>109712</v>
       </c>
       <c r="G135" s="8">
-        <v>2731004675.62</v>
+        <v>2787462076.67</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5911,19 +5907,19 @@
         <v>272</v>
       </c>
       <c r="C136" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D136" s="7">
-        <v>0.201421</v>
+        <v>0.199917</v>
       </c>
       <c r="E136" s="8">
-        <v>198703206.17</v>
+        <v>198898493.68</v>
       </c>
       <c r="F136" s="9">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G136" s="8">
-        <v>40023082.58</v>
+        <v>39763263.76</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5934,19 +5930,19 @@
         <v>274</v>
       </c>
       <c r="C137" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D137" s="7">
-        <v>0.258773</v>
+        <v>46147</v>
+      </c>
+      <c r="D137" s="10">
+        <v>0.25802</v>
       </c>
       <c r="E137" s="8">
-        <v>401623834.43</v>
+        <v>401532826.89</v>
       </c>
       <c r="F137" s="9">
         <v>947</v>
       </c>
       <c r="G137" s="8">
-        <v>103929303.38</v>
+        <v>103603328.63</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5957,19 +5953,19 @@
         <v>276</v>
       </c>
       <c r="C138" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D138" s="7">
-        <v>0.100292</v>
+        <v>0.100302</v>
       </c>
       <c r="E138" s="8">
-        <v>294314147.66</v>
+        <v>294559885.87</v>
       </c>
       <c r="F138" s="9">
         <v>324</v>
       </c>
       <c r="G138" s="8">
-        <v>29517401.67</v>
+        <v>29544833.04</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5980,19 +5976,19 @@
         <v>278</v>
       </c>
       <c r="C139" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D139" s="7">
-        <v>0.391503</v>
+        <v>0.390158</v>
       </c>
       <c r="E139" s="8">
-        <v>627327836.55</v>
+        <v>628133023.88</v>
       </c>
       <c r="F139" s="9">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="G139" s="8">
-        <v>245600677.45</v>
+        <v>245071298.65</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -6003,19 +5999,19 @@
         <v>280</v>
       </c>
       <c r="C140" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D140" s="10">
-        <v>0.69476</v>
+        <v>46147</v>
+      </c>
+      <c r="D140" s="7">
+        <v>0.697035</v>
       </c>
       <c r="E140" s="8">
-        <v>2932848763.87</v>
+        <v>2931267092.03</v>
       </c>
       <c r="F140" s="9">
-        <v>42060</v>
+        <v>42031</v>
       </c>
       <c r="G140" s="8">
-        <v>2037625201.28</v>
+        <v>2043196856.14</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -6026,19 +6022,19 @@
         <v>282</v>
       </c>
       <c r="C141" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D141" s="7">
-        <v>0.013888</v>
+        <v>0.013918</v>
       </c>
       <c r="E141" s="8">
-        <v>2748399943.55</v>
+        <v>2815295713.25</v>
       </c>
       <c r="F141" s="9">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="G141" s="8">
-        <v>38170761.41</v>
+        <v>39184000.9</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -6049,19 +6045,19 @@
         <v>284</v>
       </c>
       <c r="C142" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D142" s="7">
-        <v>0.072032</v>
+        <v>0.073422</v>
       </c>
       <c r="E142" s="8">
-        <v>21620308614.37</v>
+        <v>21877317723.12</v>
       </c>
       <c r="F142" s="9">
-        <v>23432</v>
+        <v>23440</v>
       </c>
       <c r="G142" s="8">
-        <v>1557363994.71</v>
+        <v>1606274288.53</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -6072,19 +6068,19 @@
         <v>286</v>
       </c>
       <c r="C143" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D143" s="7">
-        <v>0.279367</v>
+        <v>0.280428</v>
       </c>
       <c r="E143" s="8">
-        <v>20680574389.89</v>
+        <v>20689854563.24</v>
       </c>
       <c r="F143" s="9">
-        <v>4719</v>
+        <v>4724</v>
       </c>
       <c r="G143" s="8">
-        <v>5777461172.72</v>
+        <v>5802015454.15</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -6095,19 +6091,19 @@
         <v>288</v>
       </c>
       <c r="C144" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D144" s="7">
-        <v>0.090564</v>
+        <v>0.090646</v>
       </c>
       <c r="E144" s="8">
-        <v>630930140.07</v>
+        <v>737096455.83</v>
       </c>
       <c r="F144" s="9">
-        <v>10794</v>
+        <v>12280</v>
       </c>
       <c r="G144" s="8">
-        <v>57139807.36</v>
+        <v>66815147.64</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -6118,19 +6114,19 @@
         <v>290</v>
       </c>
       <c r="C145" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D145" s="10">
-        <v>0.05373</v>
+        <v>46147</v>
+      </c>
+      <c r="D145" s="7">
+        <v>0.053812</v>
       </c>
       <c r="E145" s="8">
-        <v>1451737783.02</v>
+        <v>1420540550.13</v>
       </c>
       <c r="F145" s="9">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G145" s="8">
-        <v>78002151.25</v>
+        <v>76441983.68</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -6141,19 +6137,19 @@
         <v>292</v>
       </c>
       <c r="C146" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D146" s="7">
-        <v>0.113154</v>
+        <v>0.113563</v>
       </c>
       <c r="E146" s="8">
-        <v>1811433895.73</v>
+        <v>1806466359.66</v>
       </c>
       <c r="F146" s="9">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="G146" s="8">
-        <v>204970161.49</v>
+        <v>205146940.47</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6164,19 +6160,19 @@
         <v>294</v>
       </c>
       <c r="C147" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D147" s="7">
-        <v>0.113007</v>
+        <v>0.113084</v>
       </c>
       <c r="E147" s="8">
-        <v>1962971827.7</v>
+        <v>1960693611.45</v>
       </c>
       <c r="F147" s="9">
-        <v>65248</v>
+        <v>65235</v>
       </c>
       <c r="G147" s="8">
-        <v>221829776.31</v>
+        <v>221722251.03</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -6187,19 +6183,19 @@
         <v>296</v>
       </c>
       <c r="C148" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D148" s="7">
-        <v>0.076269</v>
+        <v>0.076443</v>
       </c>
       <c r="E148" s="8">
-        <v>567429876.58</v>
+        <v>571278655.15</v>
       </c>
       <c r="F148" s="9">
-        <v>51661</v>
+        <v>52205</v>
       </c>
       <c r="G148" s="8">
-        <v>43277301.38</v>
+        <v>43670016.35</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6210,19 +6206,19 @@
         <v>298</v>
       </c>
       <c r="C149" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D149" s="7">
-        <v>0.082171</v>
+        <v>0.082263</v>
       </c>
       <c r="E149" s="8">
-        <v>356411005.47</v>
+        <v>355350506.92</v>
       </c>
       <c r="F149" s="9">
-        <v>9484</v>
+        <v>9473</v>
       </c>
       <c r="G149" s="8">
-        <v>29286798.49</v>
+        <v>29232230.34</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -6233,19 +6229,19 @@
         <v>300</v>
       </c>
       <c r="C150" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D150" s="7">
-        <v>0.363091</v>
+        <v>0.361728</v>
       </c>
       <c r="E150" s="8">
-        <v>145409033.52</v>
+        <v>145492665.06</v>
       </c>
       <c r="F150" s="9">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="G150" s="8">
-        <v>52796756.84</v>
+        <v>52628825.57</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6256,19 +6252,19 @@
         <v>302</v>
       </c>
       <c r="C151" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D151" s="10">
-        <v>0.09832</v>
+        <v>46147</v>
+      </c>
+      <c r="D151" s="7">
+        <v>0.098434</v>
       </c>
       <c r="E151" s="8">
-        <v>334524616.13</v>
+        <v>334702156.9</v>
       </c>
       <c r="F151" s="9">
         <v>1839</v>
       </c>
       <c r="G151" s="8">
-        <v>32890411.97</v>
+        <v>32946203.49</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -6279,19 +6275,19 @@
         <v>304</v>
       </c>
       <c r="C152" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D152" s="7">
-        <v>0.289171</v>
+        <v>0.288994</v>
       </c>
       <c r="E152" s="8">
-        <v>142007609.39</v>
+        <v>142131238.46</v>
       </c>
       <c r="F152" s="9">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G152" s="8">
-        <v>41064441.07</v>
+        <v>41075057.6</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -6302,19 +6298,19 @@
         <v>306</v>
       </c>
       <c r="C153" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D153" s="7">
-        <v>0.117338</v>
+        <v>0.117426</v>
       </c>
       <c r="E153" s="8">
-        <v>583558491.68</v>
+        <v>585947593.63</v>
       </c>
       <c r="F153" s="9">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G153" s="8">
-        <v>68473492.02</v>
+        <v>68805726.3</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -6325,19 +6321,19 @@
         <v>308</v>
       </c>
       <c r="C154" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D154" s="11">
-        <v>0.3955</v>
+        <v>46147</v>
+      </c>
+      <c r="D154" s="7">
+        <v>0.397702</v>
       </c>
       <c r="E154" s="8">
-        <v>1305246297.24</v>
+        <v>1302659931.78</v>
       </c>
       <c r="F154" s="9">
         <v>126</v>
       </c>
       <c r="G154" s="8">
-        <v>516225041.58</v>
+        <v>518070379.61</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -6348,19 +6344,19 @@
         <v>310</v>
       </c>
       <c r="C155" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D155" s="7">
-        <v>0.505989</v>
+        <v>0.501518</v>
       </c>
       <c r="E155" s="8">
-        <v>595576386.23</v>
+        <v>595886257.01</v>
       </c>
       <c r="F155" s="9">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G155" s="8">
-        <v>301355295</v>
+        <v>298847713.24</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -6371,19 +6367,19 @@
         <v>312</v>
       </c>
       <c r="C156" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D156" s="7">
-        <v>1.677346</v>
+        <v>1.669007</v>
       </c>
       <c r="E156" s="8">
-        <v>909222013.95</v>
+        <v>909860510.62</v>
       </c>
       <c r="F156" s="9">
-        <v>10189</v>
+        <v>10191</v>
       </c>
       <c r="G156" s="8">
-        <v>1525079576.52</v>
+        <v>1518563142.62</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -6394,19 +6390,19 @@
         <v>314</v>
       </c>
       <c r="C157" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D157" s="7">
-        <v>0.277657</v>
+        <v>0.277922</v>
       </c>
       <c r="E157" s="8">
-        <v>183904094.71</v>
+        <v>184307849.96</v>
       </c>
       <c r="F157" s="9">
         <v>92</v>
       </c>
       <c r="G157" s="8">
-        <v>51062233.48</v>
+        <v>51223157.6</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -6417,19 +6413,19 @@
         <v>316</v>
       </c>
       <c r="C158" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D158" s="7">
-        <v>0.142805</v>
+        <v>0.143081</v>
       </c>
       <c r="E158" s="8">
-        <v>4625774024.06</v>
+        <v>4609604552.06</v>
       </c>
       <c r="F158" s="9">
-        <v>28839</v>
+        <v>28831</v>
       </c>
       <c r="G158" s="8">
-        <v>660581491.23</v>
+        <v>659544870.91</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -6440,19 +6436,19 @@
         <v>318</v>
       </c>
       <c r="C159" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D159" s="7">
-        <v>0.166915</v>
+        <v>0.167045</v>
       </c>
       <c r="E159" s="8">
-        <v>3236847856.18</v>
+        <v>3287713097.18</v>
       </c>
       <c r="F159" s="9">
-        <v>12207</v>
+        <v>12831</v>
       </c>
       <c r="G159" s="8">
-        <v>540278812.34</v>
+        <v>549197248.19</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -6463,19 +6459,19 @@
         <v>320</v>
       </c>
       <c r="C160" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D160" s="7">
-        <v>0.688341</v>
+        <v>0.687288</v>
       </c>
       <c r="E160" s="8">
-        <v>758288140.31</v>
+        <v>760015559.68</v>
       </c>
       <c r="F160" s="9">
-        <v>5166</v>
+        <v>5168</v>
       </c>
       <c r="G160" s="8">
-        <v>521960940.38</v>
+        <v>522349951.38</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -6486,19 +6482,19 @@
         <v>322</v>
       </c>
       <c r="C161" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D161" s="7">
-        <v>0.375157</v>
+        <v>0.373318</v>
       </c>
       <c r="E161" s="8">
-        <v>1347442526.6</v>
+        <v>1341556888.51</v>
       </c>
       <c r="F161" s="9">
-        <v>23908</v>
+        <v>23903</v>
       </c>
       <c r="G161" s="8">
-        <v>505502531.96</v>
+        <v>500827503.7</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -6509,19 +6505,19 @@
         <v>324</v>
       </c>
       <c r="C162" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D162" s="7">
-        <v>0.366043</v>
+        <v>0.363387</v>
       </c>
       <c r="E162" s="8">
-        <v>167596339.85</v>
+        <v>167631436.89</v>
       </c>
       <c r="F162" s="9">
         <v>251</v>
       </c>
       <c r="G162" s="8">
-        <v>61347487.79</v>
+        <v>60915145.55</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -6532,19 +6528,19 @@
         <v>326</v>
       </c>
       <c r="C163" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D163" s="7">
-        <v>0.142435</v>
+        <v>0.142255</v>
       </c>
       <c r="E163" s="8">
-        <v>1025730174.89</v>
+        <v>1024778567.44</v>
       </c>
       <c r="F163" s="9">
-        <v>2962</v>
+        <v>2964</v>
       </c>
       <c r="G163" s="8">
-        <v>146099900.14</v>
+        <v>145779753.4</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -6555,19 +6551,19 @@
         <v>328</v>
       </c>
       <c r="C164" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D164" s="7">
-        <v>0.117075</v>
+        <v>46147</v>
+      </c>
+      <c r="D164" s="10">
+        <v>0.11669</v>
       </c>
       <c r="E164" s="8">
-        <v>7502538302.86</v>
+        <v>7574316074.46</v>
       </c>
       <c r="F164" s="9">
-        <v>79129</v>
+        <v>79766</v>
       </c>
       <c r="G164" s="8">
-        <v>878359585.11</v>
+        <v>883846401.47</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -6578,19 +6574,19 @@
         <v>330</v>
       </c>
       <c r="C165" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D165" s="7">
-        <v>0.107889</v>
+        <v>0.107795</v>
       </c>
       <c r="E165" s="8">
-        <v>3274130718.92</v>
+        <v>3271994580.49</v>
       </c>
       <c r="F165" s="9">
-        <v>64726</v>
+        <v>64725</v>
       </c>
       <c r="G165" s="8">
-        <v>353244162.32</v>
+        <v>352703956.15</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -6601,19 +6597,19 @@
         <v>332</v>
       </c>
       <c r="C166" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D166" s="7">
-        <v>0.014466</v>
+        <v>0.014556</v>
       </c>
       <c r="E166" s="8">
-        <v>429412695810.05</v>
+        <v>428708981359.1</v>
       </c>
       <c r="F166" s="9">
-        <v>72845</v>
+        <v>72968</v>
       </c>
       <c r="G166" s="8">
-        <v>6211935252.04</v>
+        <v>6240167408.67</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -6624,19 +6620,19 @@
         <v>334</v>
       </c>
       <c r="C167" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D167" s="7">
-        <v>0.358963</v>
+        <v>0.357498</v>
       </c>
       <c r="E167" s="8">
-        <v>683169632.64</v>
+        <v>682878752.51</v>
       </c>
       <c r="F167" s="9">
         <v>6825</v>
       </c>
       <c r="G167" s="8">
-        <v>245232515.78</v>
+        <v>244127491.42</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6647,19 +6643,19 @@
         <v>336</v>
       </c>
       <c r="C168" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D168" s="7">
-        <v>0.013789</v>
+        <v>0.013859</v>
       </c>
       <c r="E168" s="8">
-        <v>33468139328.4</v>
+        <v>34600813927.74</v>
       </c>
       <c r="F168" s="9">
-        <v>5753</v>
+        <v>5848</v>
       </c>
       <c r="G168" s="8">
-        <v>461484251.78</v>
+        <v>479530790.03</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6670,19 +6666,19 @@
         <v>338</v>
       </c>
       <c r="C169" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D169" s="7">
-        <v>0.680411</v>
+        <v>0.676612</v>
       </c>
       <c r="E169" s="8">
-        <v>1951063763.04</v>
+        <v>1954795024.28</v>
       </c>
       <c r="F169" s="9">
-        <v>32710</v>
+        <v>32741</v>
       </c>
       <c r="G169" s="8">
-        <v>1327525068.45</v>
+        <v>1322638663.65</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6693,19 +6689,19 @@
         <v>340</v>
       </c>
       <c r="C170" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D170" s="7">
-        <v>0.384751</v>
+        <v>0.386164</v>
       </c>
       <c r="E170" s="8">
-        <v>1975465378.95</v>
+        <v>1974089752.92</v>
       </c>
       <c r="F170" s="9">
-        <v>20978</v>
+        <v>20972</v>
       </c>
       <c r="G170" s="8">
-        <v>760062954.17</v>
+        <v>762323020.21</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6716,19 +6712,19 @@
         <v>342</v>
       </c>
       <c r="C171" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D171" s="7">
-        <v>0.138885</v>
+        <v>0.139331</v>
       </c>
       <c r="E171" s="8">
-        <v>1570023583.21</v>
+        <v>1566712063.51</v>
       </c>
       <c r="F171" s="9">
-        <v>16352</v>
+        <v>16349</v>
       </c>
       <c r="G171" s="8">
-        <v>218052614.73</v>
+        <v>218290925.31</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6739,19 +6735,19 @@
         <v>344</v>
       </c>
       <c r="C172" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D172" s="7">
-        <v>1.236811</v>
+        <v>1.223541</v>
       </c>
       <c r="E172" s="8">
-        <v>1384963039.66</v>
+        <v>1386295730.27</v>
       </c>
       <c r="F172" s="9">
-        <v>23793</v>
+        <v>23818</v>
       </c>
       <c r="G172" s="8">
-        <v>1712936935.39</v>
+        <v>1696190088.23</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6762,19 +6758,19 @@
         <v>346</v>
       </c>
       <c r="C173" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D173" s="7">
-        <v>0.566401</v>
+        <v>0.567349</v>
       </c>
       <c r="E173" s="8">
-        <v>2354083463.38</v>
+        <v>2365222324.63</v>
       </c>
       <c r="F173" s="9">
-        <v>34999</v>
+        <v>34970</v>
       </c>
       <c r="G173" s="8">
-        <v>1333355471.8</v>
+        <v>1341905437.1</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6785,19 +6781,19 @@
         <v>348</v>
       </c>
       <c r="C174" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D174" s="7">
-        <v>0.017079</v>
+        <v>0.017396</v>
       </c>
       <c r="E174" s="8">
-        <v>71627759629.21</v>
+        <v>72827614051.34</v>
       </c>
       <c r="F174" s="9">
-        <v>17391</v>
+        <v>17504</v>
       </c>
       <c r="G174" s="8">
-        <v>1223320697.73</v>
+        <v>1266881992.97</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6808,19 +6804,19 @@
         <v>350</v>
       </c>
       <c r="C175" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D175" s="7">
-        <v>0.088777</v>
+        <v>0.088605</v>
       </c>
       <c r="E175" s="8">
-        <v>2167595058.6</v>
+        <v>2169927907.05</v>
       </c>
       <c r="F175" s="9">
-        <v>5143</v>
+        <v>5136</v>
       </c>
       <c r="G175" s="8">
-        <v>192431688.4</v>
+        <v>192265571.44</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6831,19 +6827,19 @@
         <v>352</v>
       </c>
       <c r="C176" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D176" s="7">
-        <v>0.121861</v>
+        <v>0.122007</v>
       </c>
       <c r="E176" s="8">
-        <v>1626330655.88</v>
+        <v>1624080822.38</v>
       </c>
       <c r="F176" s="9">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="G176" s="8">
-        <v>198186355.82</v>
+        <v>198148571.81</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6854,19 +6850,19 @@
         <v>354</v>
       </c>
       <c r="C177" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D177" s="7">
-        <v>0.309232</v>
+        <v>0.308923</v>
       </c>
       <c r="E177" s="8">
-        <v>758129797.26</v>
+        <v>758722155.88</v>
       </c>
       <c r="F177" s="9">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="G177" s="8">
-        <v>234437787.45</v>
+        <v>234386576.83</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6877,19 +6873,19 @@
         <v>356</v>
       </c>
       <c r="C178" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D178" s="11">
-        <v>0.0904</v>
+        <v>46147</v>
+      </c>
+      <c r="D178" s="7">
+        <v>0.090182</v>
       </c>
       <c r="E178" s="8">
-        <v>41340080156.58</v>
+        <v>41908445494.96</v>
       </c>
       <c r="F178" s="9">
-        <v>281236</v>
+        <v>283699</v>
       </c>
       <c r="G178" s="8">
-        <v>3737124755.52</v>
+        <v>3779376706.13</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6900,19 +6896,19 @@
         <v>358</v>
       </c>
       <c r="C179" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D179" s="7">
-        <v>0.064624</v>
+        <v>0.064699</v>
       </c>
       <c r="E179" s="8">
-        <v>663230200.69</v>
+        <v>668858330.36</v>
       </c>
       <c r="F179" s="9">
-        <v>6091</v>
+        <v>6098</v>
       </c>
       <c r="G179" s="8">
-        <v>42860440.15</v>
+        <v>43274241.85</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6923,19 +6919,19 @@
         <v>360</v>
       </c>
       <c r="C180" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D180" s="10">
-        <v>0.24881</v>
+        <v>46147</v>
+      </c>
+      <c r="D180" s="7">
+        <v>0.247599</v>
       </c>
       <c r="E180" s="8">
-        <v>538326700.99</v>
+        <v>539229874.36</v>
       </c>
       <c r="F180" s="9">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="G180" s="8">
-        <v>133940961.65</v>
+        <v>133512959.05</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6946,19 +6942,19 @@
         <v>362</v>
       </c>
       <c r="C181" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D181" s="7">
-        <v>0.390372</v>
+        <v>0.388025</v>
       </c>
       <c r="E181" s="8">
-        <v>362632613.33</v>
+        <v>363953064.79</v>
       </c>
       <c r="F181" s="9">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="G181" s="8">
-        <v>141561598.46</v>
+        <v>141222826.07</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6969,19 +6965,19 @@
         <v>364</v>
       </c>
       <c r="C182" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D182" s="7">
-        <v>0.110858</v>
+        <v>0.110886</v>
       </c>
       <c r="E182" s="8">
-        <v>14646625438.68</v>
+        <v>14586325026.98</v>
       </c>
       <c r="F182" s="9">
-        <v>32178</v>
+        <v>32165</v>
       </c>
       <c r="G182" s="8">
-        <v>1623702873.19</v>
+        <v>1617422530.68</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6992,19 +6988,19 @@
         <v>366</v>
       </c>
       <c r="C183" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D183" s="7">
-        <v>0.115602</v>
+        <v>0.115701</v>
       </c>
       <c r="E183" s="8">
-        <v>22477537983.71</v>
+        <v>22826939999.91</v>
       </c>
       <c r="F183" s="9">
-        <v>42517</v>
+        <v>49301</v>
       </c>
       <c r="G183" s="8">
-        <v>2598454448.02</v>
+        <v>2641088689.94</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7015,19 +7011,19 @@
         <v>368</v>
       </c>
       <c r="C184" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D184" s="7">
-        <v>0.091103</v>
+        <v>0.093571</v>
       </c>
       <c r="E184" s="8">
-        <v>30716639819.11</v>
+        <v>30998494838.01</v>
       </c>
       <c r="F184" s="9">
-        <v>29768</v>
+        <v>29879</v>
       </c>
       <c r="G184" s="8">
-        <v>2798392341.04</v>
+        <v>2900565455.47</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7038,19 +7034,19 @@
         <v>370</v>
       </c>
       <c r="C185" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D185" s="12">
-        <v>0.084</v>
+        <v>46147</v>
+      </c>
+      <c r="D185" s="7">
+        <v>0.083868</v>
       </c>
       <c r="E185" s="8">
-        <v>6452571676.17</v>
+        <v>6441192543.48</v>
       </c>
       <c r="F185" s="9">
-        <v>5052</v>
+        <v>5050</v>
       </c>
       <c r="G185" s="8">
-        <v>542017403.76</v>
+        <v>540210715.19</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7061,19 +7057,19 @@
         <v>372</v>
       </c>
       <c r="C186" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D186" s="7">
-        <v>0.072765</v>
+        <v>0.072677</v>
       </c>
       <c r="E186" s="8">
-        <v>13948756416.96</v>
+        <v>13948947995.39</v>
       </c>
       <c r="F186" s="9">
-        <v>184349</v>
+        <v>184343</v>
       </c>
       <c r="G186" s="8">
-        <v>1014983605.53</v>
+        <v>1013764545.31</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7084,19 +7080,19 @@
         <v>374</v>
       </c>
       <c r="C187" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D187" s="7">
-        <v>0.098837</v>
+        <v>46147</v>
+      </c>
+      <c r="D187" s="10">
+        <v>0.09888</v>
       </c>
       <c r="E187" s="8">
-        <v>4072372738</v>
+        <v>4073868379.02</v>
       </c>
       <c r="F187" s="9">
-        <v>117663</v>
+        <v>117658</v>
       </c>
       <c r="G187" s="8">
-        <v>402501481.43</v>
+        <v>402824351.18</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7107,19 +7103,19 @@
         <v>376</v>
       </c>
       <c r="C188" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D188" s="7">
-        <v>0.239903</v>
+        <v>0.239096</v>
       </c>
       <c r="E188" s="8">
-        <v>665887963.68</v>
+        <v>666244735.06</v>
       </c>
       <c r="F188" s="9">
         <v>1969</v>
       </c>
       <c r="G188" s="8">
-        <v>159748596.52</v>
+        <v>159296221</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7130,19 +7126,19 @@
         <v>378</v>
       </c>
       <c r="C189" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D189" s="7">
-        <v>0.084806</v>
+        <v>46147</v>
+      </c>
+      <c r="D189" s="10">
+        <v>0.08486</v>
       </c>
       <c r="E189" s="8">
-        <v>2747728985.36</v>
+        <v>2913922306.39</v>
       </c>
       <c r="F189" s="9">
-        <v>42348</v>
+        <v>44620</v>
       </c>
       <c r="G189" s="8">
-        <v>233022901.91</v>
+        <v>247276242.27</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7153,19 +7149,19 @@
         <v>380</v>
       </c>
       <c r="C190" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D190" s="11">
-        <v>0.2446</v>
+        <v>46147</v>
+      </c>
+      <c r="D190" s="10">
+        <v>0.24298</v>
       </c>
       <c r="E190" s="8">
-        <v>3408638210.15</v>
+        <v>3405542122.67</v>
       </c>
       <c r="F190" s="9">
-        <v>6550</v>
+        <v>6565</v>
       </c>
       <c r="G190" s="8">
-        <v>833752942.89</v>
+        <v>827480266.01</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7176,19 +7172,19 @@
         <v>382</v>
       </c>
       <c r="C191" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D191" s="7">
-        <v>0.160475</v>
+        <v>0.159814</v>
       </c>
       <c r="E191" s="8">
-        <v>697786861.89</v>
+        <v>697176126.66</v>
       </c>
       <c r="F191" s="9">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="G191" s="8">
-        <v>111977678.18</v>
+        <v>111418295.3</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7199,19 +7195,19 @@
         <v>384</v>
       </c>
       <c r="C192" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D192" s="7">
-        <v>0.148867</v>
+        <v>0.148105</v>
       </c>
       <c r="E192" s="8">
-        <v>489700250.5</v>
+        <v>488209910.18</v>
       </c>
       <c r="F192" s="9">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="G192" s="8">
-        <v>72899986.09</v>
+        <v>72306239.92</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7222,19 +7218,19 @@
         <v>386</v>
       </c>
       <c r="C193" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D193" s="7">
-        <v>0.100965</v>
+        <v>46147</v>
+      </c>
+      <c r="D193" s="10">
+        <v>0.10141</v>
       </c>
       <c r="E193" s="8">
-        <v>1155578325.8</v>
+        <v>1167190108.84</v>
       </c>
       <c r="F193" s="9">
-        <v>116504</v>
+        <v>117390</v>
       </c>
       <c r="G193" s="8">
-        <v>116673244.24</v>
+        <v>118364631.5</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7245,19 +7241,19 @@
         <v>388</v>
       </c>
       <c r="C194" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D194" s="7">
-        <v>0.199644</v>
+        <v>0.199414</v>
       </c>
       <c r="E194" s="8">
-        <v>1942322540.89</v>
+        <v>1959901023.95</v>
       </c>
       <c r="F194" s="9">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="G194" s="8">
-        <v>387773627.26</v>
+        <v>390832048.95</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7268,19 +7264,19 @@
         <v>390</v>
       </c>
       <c r="C195" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D195" s="7">
-        <v>0.157762</v>
+        <v>0.157789</v>
       </c>
       <c r="E195" s="8">
-        <v>599148751.23</v>
+        <v>592987194.83</v>
       </c>
       <c r="F195" s="9">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="G195" s="8">
-        <v>94522959.26</v>
+        <v>93566734.52</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7291,19 +7287,19 @@
         <v>392</v>
       </c>
       <c r="C196" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D196" s="7">
-        <v>0.272554</v>
+        <v>0.272062</v>
       </c>
       <c r="E196" s="8">
-        <v>2824877087.74</v>
+        <v>2808896685.38</v>
       </c>
       <c r="F196" s="9">
-        <v>7732</v>
+        <v>7701</v>
       </c>
       <c r="G196" s="8">
-        <v>769931189.67</v>
+        <v>764193572.71</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7314,19 +7310,19 @@
         <v>394</v>
       </c>
       <c r="C197" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D197" s="7">
-        <v>0.098777</v>
+        <v>0.098853</v>
       </c>
       <c r="E197" s="8">
-        <v>103566871.92</v>
+        <v>103819646.93</v>
       </c>
       <c r="F197" s="9">
         <v>931</v>
       </c>
       <c r="G197" s="8">
-        <v>10229990.94</v>
+        <v>10262870.58</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7337,19 +7333,19 @@
         <v>396</v>
       </c>
       <c r="C198" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D198" s="7">
-        <v>0.218487</v>
+        <v>46147</v>
+      </c>
+      <c r="D198" s="10">
+        <v>0.21989</v>
       </c>
       <c r="E198" s="8">
-        <v>319070449.12</v>
+        <v>319706496.48</v>
       </c>
       <c r="F198" s="9">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="G198" s="8">
-        <v>69712649.7</v>
+        <v>70300190.28</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7360,19 +7356,19 @@
         <v>398</v>
       </c>
       <c r="C199" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D199" s="7">
-        <v>0.173801</v>
+        <v>0.174735</v>
       </c>
       <c r="E199" s="8">
-        <v>270048965.14</v>
+        <v>270099511.13</v>
       </c>
       <c r="F199" s="9">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G199" s="8">
-        <v>46934698.94</v>
+        <v>47195811.01</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7383,19 +7379,19 @@
         <v>400</v>
       </c>
       <c r="C200" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D200" s="7">
-        <v>0.087898</v>
+        <v>0.087987</v>
       </c>
       <c r="E200" s="8">
-        <v>2663222851.76</v>
+        <v>2681835553.67</v>
       </c>
       <c r="F200" s="9">
-        <v>40644</v>
+        <v>40733</v>
       </c>
       <c r="G200" s="8">
-        <v>234091268.41</v>
+        <v>235966702.66</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7406,19 +7402,19 @@
         <v>402</v>
       </c>
       <c r="C201" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D201" s="10">
-        <v>0.08974</v>
+        <v>0.08985</v>
       </c>
       <c r="E201" s="8">
-        <v>824847438.12</v>
+        <v>825450265.04</v>
       </c>
       <c r="F201" s="9">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G201" s="8">
-        <v>74021398.62</v>
+        <v>74166779.63</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7429,19 +7425,19 @@
         <v>404</v>
       </c>
       <c r="C202" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D202" s="7">
-        <v>0.150506</v>
+        <v>0.151205</v>
       </c>
       <c r="E202" s="8">
-        <v>9761123641.52</v>
+        <v>9669621085.87</v>
       </c>
       <c r="F202" s="9">
-        <v>9464</v>
+        <v>9433</v>
       </c>
       <c r="G202" s="8">
-        <v>1469111570.03</v>
+        <v>1462098332.86</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7452,19 +7448,19 @@
         <v>406</v>
       </c>
       <c r="C203" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D203" s="7">
-        <v>0.014444</v>
+        <v>0.014454</v>
       </c>
       <c r="E203" s="8">
-        <v>9281459089.87</v>
+        <v>9155566016.29</v>
       </c>
       <c r="F203" s="9">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="G203" s="8">
-        <v>134057366.3</v>
+        <v>132337397.34</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7475,19 +7471,19 @@
         <v>408</v>
       </c>
       <c r="C204" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D204" s="7">
-        <v>0.027919</v>
+        <v>0.027866</v>
       </c>
       <c r="E204" s="8">
-        <v>1309863590.97</v>
+        <v>1312474511.14</v>
       </c>
       <c r="F204" s="9">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="G204" s="8">
-        <v>36570183.23</v>
+        <v>36573356.99</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7498,19 +7494,19 @@
         <v>410</v>
       </c>
       <c r="C205" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D205" s="7">
-        <v>0.118511</v>
+        <v>0.119018</v>
       </c>
       <c r="E205" s="8">
-        <v>3181547328.97</v>
+        <v>3217351733.17</v>
       </c>
       <c r="F205" s="9">
-        <v>308202</v>
+        <v>312001</v>
       </c>
       <c r="G205" s="8">
-        <v>377047981.35</v>
+        <v>382922849.75</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -7521,19 +7517,19 @@
         <v>412</v>
       </c>
       <c r="C206" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D206" s="7">
-        <v>0.156345</v>
+        <v>0.156617</v>
       </c>
       <c r="E206" s="8">
-        <v>474864908.35</v>
+        <v>471515033.65</v>
       </c>
       <c r="F206" s="9">
-        <v>888</v>
+        <v>902</v>
       </c>
       <c r="G206" s="8">
-        <v>74242868.61</v>
+        <v>73847041.63</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7544,19 +7540,19 @@
         <v>414</v>
       </c>
       <c r="C207" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D207" s="7">
-        <v>0.132167</v>
+        <v>0.132393</v>
       </c>
       <c r="E207" s="8">
-        <v>2879597767.34</v>
+        <v>2868334866.5</v>
       </c>
       <c r="F207" s="9">
-        <v>5753</v>
+        <v>5764</v>
       </c>
       <c r="G207" s="8">
-        <v>380588483.69</v>
+        <v>379747669.74</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7567,19 +7563,19 @@
         <v>416</v>
       </c>
       <c r="C208" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D208" s="7">
-        <v>0.104368</v>
+        <v>0.104822</v>
       </c>
       <c r="E208" s="8">
-        <v>4264657839.56</v>
+        <v>4330302290.78</v>
       </c>
       <c r="F208" s="9">
-        <v>343092</v>
+        <v>348258</v>
       </c>
       <c r="G208" s="8">
-        <v>445094151.21</v>
+        <v>453912706.18</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7590,19 +7586,19 @@
         <v>418</v>
       </c>
       <c r="C209" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D209" s="7">
-        <v>0.106115</v>
+        <v>0.106321</v>
       </c>
       <c r="E209" s="8">
-        <v>46380871966.36</v>
+        <v>46417612084.76</v>
       </c>
       <c r="F209" s="9">
-        <v>711792</v>
+        <v>711843</v>
       </c>
       <c r="G209" s="8">
-        <v>4921720978.94</v>
+        <v>4935180686.7</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7613,19 +7609,19 @@
         <v>420</v>
       </c>
       <c r="C210" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D210" s="7">
-        <v>0.062922</v>
+        <v>0.064187</v>
       </c>
       <c r="E210" s="8">
-        <v>57216773295.36</v>
+        <v>58045066055.59</v>
       </c>
       <c r="F210" s="9">
-        <v>59872</v>
+        <v>60140</v>
       </c>
       <c r="G210" s="8">
-        <v>3600179880.21</v>
+        <v>3725751007.55</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -7636,19 +7632,19 @@
         <v>422</v>
       </c>
       <c r="C211" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D211" s="7">
-        <v>0.106028</v>
+        <v>0.105953</v>
       </c>
       <c r="E211" s="8">
-        <v>64651578324.36</v>
+        <v>64756269234.79</v>
       </c>
       <c r="F211" s="9">
-        <v>913460</v>
+        <v>913543</v>
       </c>
       <c r="G211" s="8">
-        <v>6854884427.35</v>
+        <v>6861116727.93</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7659,19 +7655,19 @@
         <v>424</v>
       </c>
       <c r="C212" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D212" s="7">
-        <v>0.069602</v>
+        <v>0.069857</v>
       </c>
       <c r="E212" s="8">
-        <v>54828674547.99</v>
+        <v>54901426812.23</v>
       </c>
       <c r="F212" s="9">
-        <v>55490</v>
+        <v>55472</v>
       </c>
       <c r="G212" s="8">
-        <v>3816191447.04</v>
+        <v>3835237018.88</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7682,19 +7678,19 @@
         <v>426</v>
       </c>
       <c r="C213" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D213" s="7">
-        <v>0.097284</v>
+        <v>0.097357</v>
       </c>
       <c r="E213" s="8">
-        <v>16307357335.54</v>
+        <v>16515873385.97</v>
       </c>
       <c r="F213" s="9">
-        <v>344390</v>
+        <v>428798</v>
       </c>
       <c r="G213" s="8">
-        <v>1586446790.5</v>
+        <v>1607933073.06</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -7705,19 +7701,19 @@
         <v>428</v>
       </c>
       <c r="C214" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D214" s="7">
-        <v>0.050447</v>
+        <v>0.050816</v>
       </c>
       <c r="E214" s="8">
-        <v>83083622236.07</v>
+        <v>82911097393.93</v>
       </c>
       <c r="F214" s="9">
-        <v>34818</v>
+        <v>34739</v>
       </c>
       <c r="G214" s="8">
-        <v>4191344877.27</v>
+        <v>4213249878.38</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7728,19 +7724,19 @@
         <v>430</v>
       </c>
       <c r="C215" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D215" s="10">
-        <v>0.08581</v>
+        <v>46147</v>
+      </c>
+      <c r="D215" s="7">
+        <v>0.085903</v>
       </c>
       <c r="E215" s="8">
-        <v>14029076779.16</v>
+        <v>14029141269.82</v>
       </c>
       <c r="F215" s="9">
-        <v>235774</v>
+        <v>236316</v>
       </c>
       <c r="G215" s="8">
-        <v>1203839947.95</v>
+        <v>1205150656.08</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -7751,19 +7747,19 @@
         <v>432</v>
       </c>
       <c r="C216" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D216" s="7">
-        <v>0.315624</v>
+        <v>0.317263</v>
       </c>
       <c r="E216" s="8">
-        <v>12144068870.07</v>
+        <v>12197268016.97</v>
       </c>
       <c r="F216" s="9">
-        <v>57557</v>
+        <v>57766</v>
       </c>
       <c r="G216" s="8">
-        <v>3832956896.32</v>
+        <v>3869742861.75</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -7774,19 +7770,19 @@
         <v>434</v>
       </c>
       <c r="C217" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D217" s="7">
-        <v>0.220054</v>
+        <v>46147</v>
+      </c>
+      <c r="D217" s="10">
+        <v>0.21895</v>
       </c>
       <c r="E217" s="8">
-        <v>10352418821.52</v>
+        <v>10424098764.4</v>
       </c>
       <c r="F217" s="9">
-        <v>39426</v>
+        <v>39547</v>
       </c>
       <c r="G217" s="8">
-        <v>2278087648.57</v>
+        <v>2282354676.35</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7797,19 +7793,19 @@
         <v>436</v>
       </c>
       <c r="C218" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D218" s="7">
-        <v>1.007597</v>
+        <v>1.003964</v>
       </c>
       <c r="E218" s="8">
-        <v>742642782.47</v>
+        <v>744475678.31</v>
       </c>
       <c r="F218" s="9">
-        <v>4350</v>
+        <v>4349</v>
       </c>
       <c r="G218" s="8">
-        <v>748284489.1</v>
+        <v>747426819.72</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -7820,19 +7816,19 @@
         <v>438</v>
       </c>
       <c r="C219" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D219" s="7">
-        <v>0.715436</v>
+        <v>0.709703</v>
       </c>
       <c r="E219" s="8">
-        <v>5938240205.46</v>
+        <v>5942266730.31</v>
       </c>
       <c r="F219" s="9">
-        <v>10968</v>
+        <v>10992</v>
       </c>
       <c r="G219" s="8">
-        <v>4248433331.16</v>
+        <v>4217244885.24</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -7843,19 +7839,19 @@
         <v>440</v>
       </c>
       <c r="C220" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D220" s="10">
-        <v>2.81338</v>
+        <v>46147</v>
+      </c>
+      <c r="D220" s="7">
+        <v>2.790129</v>
       </c>
       <c r="E220" s="8">
-        <v>6250521496.04</v>
+        <v>6249248248.61</v>
       </c>
       <c r="F220" s="9">
-        <v>272670</v>
+        <v>272756</v>
       </c>
       <c r="G220" s="8">
-        <v>17585090823.56</v>
+        <v>17436208244.98</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -7866,19 +7862,19 @@
         <v>442</v>
       </c>
       <c r="C221" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D221" s="7">
-        <v>0.403967</v>
+        <v>0.404812</v>
       </c>
       <c r="E221" s="8">
-        <v>9388287412.65</v>
+        <v>9376143921.25</v>
       </c>
       <c r="F221" s="9">
-        <v>165483</v>
+        <v>165390</v>
       </c>
       <c r="G221" s="8">
-        <v>3792558824.32</v>
+        <v>3795574830.31</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -7889,19 +7885,19 @@
         <v>444</v>
       </c>
       <c r="C222" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D222" s="7">
-        <v>0.394946</v>
+        <v>0.395322</v>
       </c>
       <c r="E222" s="8">
-        <v>176329648541.78</v>
+        <v>177063065177.15</v>
       </c>
       <c r="F222" s="9">
-        <v>390355</v>
+        <v>413578</v>
       </c>
       <c r="G222" s="8">
-        <v>69640662944.11</v>
+        <v>69996917082.66</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -7912,19 +7908,19 @@
         <v>446</v>
       </c>
       <c r="C223" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D223" s="7">
-        <v>0.153675</v>
+        <v>0.153926</v>
       </c>
       <c r="E223" s="8">
-        <v>6427188610.52</v>
+        <v>6440743272.35</v>
       </c>
       <c r="F223" s="9">
-        <v>25262</v>
+        <v>25275</v>
       </c>
       <c r="G223" s="8">
-        <v>987698718.17</v>
+        <v>991398990.89</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -7935,19 +7931,19 @@
         <v>448</v>
       </c>
       <c r="C224" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D224" s="7">
-        <v>0.519564</v>
+        <v>0.520927</v>
       </c>
       <c r="E224" s="8">
-        <v>8081651660.15</v>
+        <v>8118600876.42</v>
       </c>
       <c r="F224" s="9">
-        <v>35724</v>
+        <v>35717</v>
       </c>
       <c r="G224" s="8">
-        <v>4198934017.71</v>
+        <v>4229200478.09</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -7958,19 +7954,19 @@
         <v>450</v>
       </c>
       <c r="C225" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D225" s="7">
-        <v>0.073719</v>
+        <v>0.073913</v>
       </c>
       <c r="E225" s="8">
-        <v>2513058096888.06</v>
+        <v>2509968503868.51</v>
       </c>
       <c r="F225" s="9">
-        <v>1246890</v>
+        <v>1246058</v>
       </c>
       <c r="G225" s="8">
-        <v>185259536061.9</v>
+        <v>185518068106.39</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -7981,19 +7977,19 @@
         <v>452</v>
       </c>
       <c r="C226" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D226" s="7">
-        <v>0.073359</v>
+        <v>0.073156</v>
       </c>
       <c r="E226" s="8">
-        <v>26643690151</v>
+        <v>26653168263.2</v>
       </c>
       <c r="F226" s="9">
-        <v>95325</v>
+        <v>95261</v>
       </c>
       <c r="G226" s="8">
-        <v>1954566817.06</v>
+        <v>1949836893.63</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -8004,19 +8000,19 @@
         <v>454</v>
       </c>
       <c r="C227" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D227" s="7">
-        <v>0.015092</v>
+        <v>0.015191</v>
       </c>
       <c r="E227" s="8">
-        <v>517410763111.05</v>
+        <v>517429046650.35</v>
       </c>
       <c r="F227" s="9">
-        <v>50745</v>
+        <v>50712</v>
       </c>
       <c r="G227" s="8">
-        <v>7808680109.93</v>
+        <v>7860312103.19</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8027,19 +8023,19 @@
         <v>456</v>
       </c>
       <c r="C228" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D228" s="7">
-        <v>0.782207</v>
+        <v>0.780805</v>
       </c>
       <c r="E228" s="8">
-        <v>170714942188.67</v>
+        <v>170635074199.38</v>
       </c>
       <c r="F228" s="9">
-        <v>822820</v>
+        <v>823227</v>
       </c>
       <c r="G228" s="8">
-        <v>133534445592.09</v>
+        <v>133232735993.64</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8050,19 +8046,19 @@
         <v>458</v>
       </c>
       <c r="C229" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D229" s="7">
-        <v>0.137918</v>
+        <v>0.137868</v>
       </c>
       <c r="E229" s="8">
-        <v>26952509187.57</v>
+        <v>26963859360.36</v>
       </c>
       <c r="F229" s="9">
-        <v>194812</v>
+        <v>194801</v>
       </c>
       <c r="G229" s="8">
-        <v>3717227271.61</v>
+        <v>3717443451.43</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8073,19 +8069,19 @@
         <v>460</v>
       </c>
       <c r="C230" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D230" s="7">
-        <v>1.104125</v>
+        <v>1.100235</v>
       </c>
       <c r="E230" s="8">
-        <v>2639362054.75</v>
+        <v>2638491262.18</v>
       </c>
       <c r="F230" s="9">
-        <v>49173</v>
+        <v>49162</v>
       </c>
       <c r="G230" s="8">
-        <v>2914184824.75</v>
+        <v>2902959150.5</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8096,19 +8092,19 @@
         <v>462</v>
       </c>
       <c r="C231" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D231" s="7">
-        <v>0.280844</v>
+        <v>0.281522</v>
       </c>
       <c r="E231" s="8">
-        <v>2528273981.57</v>
+        <v>2513274818.45</v>
       </c>
       <c r="F231" s="9">
-        <v>11215</v>
+        <v>11207</v>
       </c>
       <c r="G231" s="8">
-        <v>710050116.98</v>
+        <v>707541439.04</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8119,19 +8115,19 @@
         <v>464</v>
       </c>
       <c r="C232" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D232" s="7">
-        <v>1.122257</v>
+        <v>1.126972</v>
       </c>
       <c r="E232" s="8">
-        <v>5210677717.32</v>
+        <v>5215992297.34</v>
       </c>
       <c r="F232" s="9">
-        <v>63631</v>
+        <v>63623</v>
       </c>
       <c r="G232" s="8">
-        <v>5847717032.68</v>
+        <v>5878279181.24</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8142,19 +8138,19 @@
         <v>466</v>
       </c>
       <c r="C233" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D233" s="7">
-        <v>0.376255</v>
+        <v>0.376717</v>
       </c>
       <c r="E233" s="8">
-        <v>18718178951.65</v>
+        <v>18817333855.11</v>
       </c>
       <c r="F233" s="9">
-        <v>149994</v>
+        <v>150283</v>
       </c>
       <c r="G233" s="8">
-        <v>7042807528.91</v>
+        <v>7088809409.56</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8165,19 +8161,19 @@
         <v>468</v>
       </c>
       <c r="C234" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D234" s="7">
-        <v>0.107444</v>
+        <v>0.107113</v>
       </c>
       <c r="E234" s="8">
-        <v>277791127043.02</v>
+        <v>282169998878.8</v>
       </c>
       <c r="F234" s="9">
-        <v>1508851</v>
+        <v>1530853</v>
       </c>
       <c r="G234" s="8">
-        <v>29846941457.03</v>
+        <v>30224021282.11</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8188,19 +8184,19 @@
         <v>470</v>
       </c>
       <c r="C235" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D235" s="7">
-        <v>0.263057</v>
+        <v>0.261707</v>
       </c>
       <c r="E235" s="8">
-        <v>3263199433.37</v>
+        <v>3265225135.01</v>
       </c>
       <c r="F235" s="9">
-        <v>10504</v>
+        <v>10500</v>
       </c>
       <c r="G235" s="8">
-        <v>858407948.12</v>
+        <v>854531066.51</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8211,19 +8207,19 @@
         <v>472</v>
       </c>
       <c r="C236" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D236" s="7">
-        <v>0.784655</v>
+        <v>0.787999</v>
       </c>
       <c r="E236" s="8">
-        <v>1340059307.6</v>
+        <v>1340179051.42</v>
       </c>
       <c r="F236" s="9">
-        <v>7631</v>
+        <v>7630</v>
       </c>
       <c r="G236" s="8">
-        <v>1051483952.52</v>
+        <v>1056059700.82</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8234,19 +8230,19 @@
         <v>474</v>
       </c>
       <c r="C237" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D237" s="7">
-        <v>0.153177</v>
+        <v>0.153903</v>
       </c>
       <c r="E237" s="8">
-        <v>70985683319.67</v>
+        <v>72240067575.38</v>
       </c>
       <c r="F237" s="9">
-        <v>823770</v>
+        <v>842921</v>
       </c>
       <c r="G237" s="8">
-        <v>10873371562.56</v>
+        <v>11117986898.46</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -8257,19 +8253,19 @@
         <v>476</v>
       </c>
       <c r="C238" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D238" s="7">
-        <v>0.222289</v>
+        <v>0.221555</v>
       </c>
       <c r="E238" s="8">
-        <v>2428459530.31</v>
+        <v>2430747764.44</v>
       </c>
       <c r="F238" s="9">
-        <v>7578</v>
+        <v>7574</v>
       </c>
       <c r="G238" s="8">
-        <v>539819787.2</v>
+        <v>538543718.88</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -8280,19 +8276,19 @@
         <v>478</v>
       </c>
       <c r="C239" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D239" s="7">
-        <v>0.195867</v>
+        <v>0.195171</v>
       </c>
       <c r="E239" s="8">
-        <v>2322705120.32</v>
+        <v>2329813201.5</v>
       </c>
       <c r="F239" s="9">
-        <v>7337</v>
+        <v>7334</v>
       </c>
       <c r="G239" s="8">
-        <v>454941752.88</v>
+        <v>454711301.97</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -8303,19 +8299,19 @@
         <v>480</v>
       </c>
       <c r="C240" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D240" s="7">
-        <v>0.339993</v>
+        <v>0.343959</v>
       </c>
       <c r="E240" s="8">
-        <v>31306266399.89</v>
+        <v>31350431759.29</v>
       </c>
       <c r="F240" s="9">
-        <v>119932</v>
+        <v>120031</v>
       </c>
       <c r="G240" s="8">
-        <v>10643919210.52</v>
+        <v>10783270179.85</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -8326,19 +8322,19 @@
         <v>482</v>
       </c>
       <c r="C241" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D241" s="7">
-        <v>0.126341</v>
+        <v>0.126372</v>
       </c>
       <c r="E241" s="8">
-        <v>3783578442.1</v>
+        <v>3787742897.33</v>
       </c>
       <c r="F241" s="9">
-        <v>7425</v>
+        <v>7416</v>
       </c>
       <c r="G241" s="8">
-        <v>478022334.84</v>
+        <v>478664193.88</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -8349,19 +8345,19 @@
         <v>484</v>
       </c>
       <c r="C242" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D242" s="7">
-        <v>0.127387</v>
+        <v>0.126833</v>
       </c>
       <c r="E242" s="8">
-        <v>89360892922.74</v>
+        <v>89295443426.92</v>
       </c>
       <c r="F242" s="9">
-        <v>403224</v>
+        <v>403189</v>
       </c>
       <c r="G242" s="8">
-        <v>11383374849.33</v>
+        <v>11325607129.96</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8372,19 +8368,19 @@
         <v>486</v>
       </c>
       <c r="C243" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D243" s="7">
-        <v>0.305723</v>
+        <v>46147</v>
+      </c>
+      <c r="D243" s="10">
+        <v>0.30811</v>
       </c>
       <c r="E243" s="8">
-        <v>3860818037.81</v>
+        <v>3868793871.49</v>
       </c>
       <c r="F243" s="9">
-        <v>18085</v>
+        <v>18100</v>
       </c>
       <c r="G243" s="8">
-        <v>1180339505.32</v>
+        <v>1192014873.39</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -8395,19 +8391,19 @@
         <v>488</v>
       </c>
       <c r="C244" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D244" s="7">
-        <v>0.081385</v>
+        <v>0.081465</v>
       </c>
       <c r="E244" s="8">
-        <v>3838974114</v>
+        <v>3840376304.8</v>
       </c>
       <c r="F244" s="9">
-        <v>9185</v>
+        <v>9176</v>
       </c>
       <c r="G244" s="8">
-        <v>312434065.37</v>
+        <v>312855979.12</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8418,19 +8414,19 @@
         <v>490</v>
       </c>
       <c r="C245" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D245" s="7">
-        <v>0.245754</v>
+        <v>0.247333</v>
       </c>
       <c r="E245" s="8">
-        <v>2833674921.04</v>
+        <v>2836764985.49</v>
       </c>
       <c r="F245" s="9">
-        <v>14016</v>
+        <v>14018</v>
       </c>
       <c r="G245" s="8">
-        <v>696387780.57</v>
+        <v>701625182.97</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -8441,19 +8437,19 @@
         <v>492</v>
       </c>
       <c r="C246" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D246" s="7">
-        <v>0.069019</v>
+        <v>0.069087</v>
       </c>
       <c r="E246" s="8">
-        <v>4033096768.38</v>
+        <v>4033163686.38</v>
       </c>
       <c r="F246" s="9">
-        <v>7768</v>
+        <v>7761</v>
       </c>
       <c r="G246" s="8">
-        <v>278362145.95</v>
+        <v>278640455.98</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8464,19 +8460,19 @@
         <v>494</v>
       </c>
       <c r="C247" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D247" s="7">
-        <v>0.179197</v>
+        <v>0.179301</v>
       </c>
       <c r="E247" s="8">
-        <v>14323469499.24</v>
+        <v>14382028950.61</v>
       </c>
       <c r="F247" s="9">
-        <v>48680</v>
+        <v>48737</v>
       </c>
       <c r="G247" s="8">
-        <v>2566722129.24</v>
+        <v>2578717897.75</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8487,19 +8483,19 @@
         <v>496</v>
       </c>
       <c r="C248" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D248" s="7">
-        <v>0.024019</v>
+        <v>0.024191</v>
       </c>
       <c r="E248" s="8">
-        <v>961559597915.2</v>
+        <v>958890337679.97</v>
       </c>
       <c r="F248" s="9">
-        <v>187192</v>
+        <v>186999</v>
       </c>
       <c r="G248" s="8">
-        <v>23095560583.01</v>
+        <v>23196126746.84</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8510,19 +8506,19 @@
         <v>498</v>
       </c>
       <c r="C249" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D249" s="7">
-        <v>0.737579</v>
+        <v>46147</v>
+      </c>
+      <c r="D249" s="10">
+        <v>0.73811</v>
       </c>
       <c r="E249" s="8">
-        <v>15369077242.14</v>
+        <v>15348206647.69</v>
       </c>
       <c r="F249" s="9">
-        <v>79519</v>
+        <v>79500</v>
       </c>
       <c r="G249" s="8">
-        <v>11335903957.76</v>
+        <v>11328668577.16</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8533,19 +8529,19 @@
         <v>500</v>
       </c>
       <c r="C250" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D250" s="7">
-        <v>0.641246</v>
+        <v>0.639288</v>
       </c>
       <c r="E250" s="8">
-        <v>8195281574.17</v>
+        <v>8196090177.12</v>
       </c>
       <c r="F250" s="9">
-        <v>75239</v>
+        <v>75293</v>
       </c>
       <c r="G250" s="8">
-        <v>5255189923.12</v>
+        <v>5239662771.71</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8556,19 +8552,19 @@
         <v>502</v>
       </c>
       <c r="C251" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D251" s="7">
-        <v>0.161051</v>
+        <v>0.160955</v>
       </c>
       <c r="E251" s="8">
-        <v>2776180247.35</v>
+        <v>2778028636.62</v>
       </c>
       <c r="F251" s="9">
-        <v>11332</v>
+        <v>11334</v>
       </c>
       <c r="G251" s="8">
-        <v>447106369.65</v>
+        <v>447138554.26</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8579,19 +8575,19 @@
         <v>504</v>
       </c>
       <c r="C252" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D252" s="7">
-        <v>0.095916</v>
+        <v>0.095897</v>
       </c>
       <c r="E252" s="8">
-        <v>4859430569.76</v>
+        <v>4856993838.78</v>
       </c>
       <c r="F252" s="9">
-        <v>69470</v>
+        <v>69469</v>
       </c>
       <c r="G252" s="8">
-        <v>466097296.3</v>
+        <v>465770314.88</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8602,19 +8598,19 @@
         <v>506</v>
       </c>
       <c r="C253" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D253" s="7">
-        <v>0.328077</v>
+        <v>0.329484</v>
       </c>
       <c r="E253" s="8">
-        <v>2201982609.99</v>
+        <v>2193508174.75</v>
       </c>
       <c r="F253" s="9">
-        <v>21100</v>
+        <v>21093</v>
       </c>
       <c r="G253" s="8">
-        <v>722420803.01</v>
+        <v>722726425.75</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8625,19 +8621,19 @@
         <v>508</v>
       </c>
       <c r="C254" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D254" s="7">
-        <v>0.141064</v>
+        <v>0.141317</v>
       </c>
       <c r="E254" s="8">
-        <v>659832319.6</v>
+        <v>660417220.75</v>
       </c>
       <c r="F254" s="9">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="G254" s="8">
-        <v>93078625.83</v>
+        <v>93328318.15</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8648,19 +8644,19 @@
         <v>510</v>
       </c>
       <c r="C255" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D255" s="7">
-        <v>0.082834</v>
+        <v>46147</v>
+      </c>
+      <c r="D255" s="10">
+        <v>0.08292</v>
       </c>
       <c r="E255" s="8">
-        <v>635565023.26</v>
+        <v>629837570.15</v>
       </c>
       <c r="F255" s="9">
-        <v>13878</v>
+        <v>13808</v>
       </c>
       <c r="G255" s="8">
-        <v>52646100.87</v>
+        <v>52226325.8</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8671,19 +8667,19 @@
         <v>512</v>
       </c>
       <c r="C256" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D256" s="7">
-        <v>0.096398</v>
+        <v>46147</v>
+      </c>
+      <c r="D256" s="11">
+        <v>0.0966</v>
       </c>
       <c r="E256" s="8">
-        <v>4026114554.61</v>
+        <v>4028718008.11</v>
       </c>
       <c r="F256" s="9">
-        <v>78529</v>
+        <v>78552</v>
       </c>
       <c r="G256" s="8">
-        <v>388108809.71</v>
+        <v>389172446.27</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8694,19 +8690,19 @@
         <v>514</v>
       </c>
       <c r="C257" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D257" s="7">
-        <v>0.126859</v>
+        <v>46147</v>
+      </c>
+      <c r="D257" s="10">
+        <v>0.12698</v>
       </c>
       <c r="E257" s="8">
-        <v>3756471884.79</v>
+        <v>3761280957.93</v>
       </c>
       <c r="F257" s="9">
         <v>19655</v>
       </c>
       <c r="G257" s="8">
-        <v>476542283.57</v>
+        <v>477607795.99</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -8717,19 +8713,19 @@
         <v>516</v>
       </c>
       <c r="C258" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D258" s="10">
-        <v>0.09364</v>
+        <v>46147</v>
+      </c>
+      <c r="D258" s="7">
+        <v>0.093733</v>
       </c>
       <c r="E258" s="8">
-        <v>576755323.08</v>
+        <v>584456377.58</v>
       </c>
       <c r="F258" s="9">
-        <v>10362</v>
+        <v>10802</v>
       </c>
       <c r="G258" s="8">
-        <v>54007290.94</v>
+        <v>54782898.1</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -8740,19 +8736,19 @@
         <v>518</v>
       </c>
       <c r="C259" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D259" s="7">
-        <v>0.132522</v>
+        <v>0.132635</v>
       </c>
       <c r="E259" s="8">
-        <v>4479697927.15</v>
+        <v>4542188927.72</v>
       </c>
       <c r="F259" s="9">
-        <v>18282</v>
+        <v>20108</v>
       </c>
       <c r="G259" s="8">
-        <v>593659547.75</v>
+        <v>602451876.28</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -8763,19 +8759,19 @@
         <v>520</v>
       </c>
       <c r="C260" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D260" s="7">
-        <v>0.154628</v>
+        <v>0.154661</v>
       </c>
       <c r="E260" s="8">
-        <v>1196760640.32</v>
+        <v>1217332732.48</v>
       </c>
       <c r="F260" s="9">
-        <v>58175</v>
+        <v>59053</v>
       </c>
       <c r="G260" s="8">
-        <v>185052864.86</v>
+        <v>188273325.94</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -8786,19 +8782,19 @@
         <v>522</v>
       </c>
       <c r="C261" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D261" s="7">
-        <v>0.765862</v>
+        <v>0.761408</v>
       </c>
       <c r="E261" s="8">
-        <v>8918668632.71</v>
+        <v>8916340681.46</v>
       </c>
       <c r="F261" s="9">
-        <v>26093</v>
+        <v>26118</v>
       </c>
       <c r="G261" s="8">
-        <v>6830471462.42</v>
+        <v>6788973193.5</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -8809,19 +8805,19 @@
         <v>524</v>
       </c>
       <c r="C262" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D262" s="7">
-        <v>0.101763</v>
+        <v>0.101535</v>
       </c>
       <c r="E262" s="8">
-        <v>13775821506.23</v>
+        <v>14037551288.01</v>
       </c>
       <c r="F262" s="9">
-        <v>126017</v>
+        <v>128307</v>
       </c>
       <c r="G262" s="8">
-        <v>1401873214.89</v>
+        <v>1425300419.19</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -8832,19 +8828,19 @@
         <v>526</v>
       </c>
       <c r="C263" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D263" s="10">
-        <v>0.01319</v>
+        <v>46147</v>
+      </c>
+      <c r="D263" s="7">
+        <v>0.013204</v>
       </c>
       <c r="E263" s="8">
-        <v>143985304867.4</v>
+        <v>144971544746.53</v>
       </c>
       <c r="F263" s="9">
-        <v>1635</v>
+        <v>1648</v>
       </c>
       <c r="G263" s="8">
-        <v>1899200242.17</v>
+        <v>1914244548.19</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -8855,19 +8851,19 @@
         <v>528</v>
       </c>
       <c r="C264" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D264" s="7">
-        <v>0.280879</v>
+        <v>46147</v>
+      </c>
+      <c r="D264" s="11">
+        <v>0.2826</v>
       </c>
       <c r="E264" s="8">
-        <v>5721117725.71</v>
+        <v>5718617750.25</v>
       </c>
       <c r="F264" s="9">
-        <v>44059</v>
+        <v>44012</v>
       </c>
       <c r="G264" s="8">
-        <v>1606940564.27</v>
+        <v>1616082833.27</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -8878,19 +8874,19 @@
         <v>530</v>
       </c>
       <c r="C265" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D265" s="7">
-        <v>0.405366</v>
+        <v>0.407697</v>
       </c>
       <c r="E265" s="8">
-        <v>1950563951.39</v>
+        <v>1951787269.02</v>
       </c>
       <c r="F265" s="9">
-        <v>21794</v>
+        <v>21778</v>
       </c>
       <c r="G265" s="8">
-        <v>790692087.48</v>
+        <v>795737167.25</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -8901,19 +8897,19 @@
         <v>532</v>
       </c>
       <c r="C266" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D266" s="7">
-        <v>0.130372</v>
+        <v>0.130653</v>
       </c>
       <c r="E266" s="8">
-        <v>34035452700.56</v>
+        <v>34106181995.43</v>
       </c>
       <c r="F266" s="9">
-        <v>102277</v>
+        <v>102392</v>
       </c>
       <c r="G266" s="8">
-        <v>4437263712.03</v>
+        <v>4456058351.22</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -8924,19 +8920,19 @@
         <v>534</v>
       </c>
       <c r="C267" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D267" s="7">
-        <v>0.236068</v>
+        <v>0.236703</v>
       </c>
       <c r="E267" s="8">
-        <v>2681193225.53</v>
+        <v>2678416402.85</v>
       </c>
       <c r="F267" s="9">
-        <v>24249</v>
+        <v>24240</v>
       </c>
       <c r="G267" s="8">
-        <v>632943984.09</v>
+        <v>633987978.93</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -8947,19 +8943,19 @@
         <v>536</v>
       </c>
       <c r="C268" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D268" s="7">
-        <v>0.012738</v>
+        <v>0.012669</v>
       </c>
       <c r="E268" s="8">
-        <v>723168554612.08</v>
+        <v>737323803361.16</v>
       </c>
       <c r="F268" s="9">
-        <v>71442</v>
+        <v>71850</v>
       </c>
       <c r="G268" s="8">
-        <v>9211665651.54</v>
+        <v>9341123922.76</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -8970,19 +8966,19 @@
         <v>538</v>
       </c>
       <c r="C269" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D269" s="7">
-        <v>0.499501</v>
+        <v>0.501226</v>
       </c>
       <c r="E269" s="8">
-        <v>5696758364.59</v>
+        <v>5696225440.69</v>
       </c>
       <c r="F269" s="9">
-        <v>72342</v>
+        <v>72309</v>
       </c>
       <c r="G269" s="8">
-        <v>2845538292.47</v>
+        <v>2855098353.38</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -8993,19 +8989,19 @@
         <v>540</v>
       </c>
       <c r="C270" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D270" s="7">
-        <v>0.302132</v>
+        <v>0.301197</v>
       </c>
       <c r="E270" s="8">
-        <v>1834368296.09</v>
+        <v>1831782439.26</v>
       </c>
       <c r="F270" s="9">
-        <v>95682</v>
+        <v>95666</v>
       </c>
       <c r="G270" s="8">
-        <v>554222088.43</v>
+        <v>551728287.42</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9016,19 +9012,19 @@
         <v>542</v>
       </c>
       <c r="C271" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D271" s="7">
-        <v>0.781953</v>
+        <v>0.777589</v>
       </c>
       <c r="E271" s="8">
-        <v>2052808967</v>
+        <v>2052451721.8</v>
       </c>
       <c r="F271" s="9">
-        <v>111737</v>
+        <v>111721</v>
       </c>
       <c r="G271" s="8">
-        <v>1605200140.56</v>
+        <v>1595964517.32</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9039,19 +9035,19 @@
         <v>544</v>
       </c>
       <c r="C272" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D272" s="7">
-        <v>0.526605</v>
+        <v>0.522657</v>
       </c>
       <c r="E272" s="8">
-        <v>1500069275.2</v>
+        <v>1503880840.04</v>
       </c>
       <c r="F272" s="9">
-        <v>37708</v>
+        <v>37706</v>
       </c>
       <c r="G272" s="8">
-        <v>789943786.48</v>
+        <v>786013544.13</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9062,19 +9058,19 @@
         <v>546</v>
       </c>
       <c r="C273" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D273" s="7">
-        <v>0.283489</v>
+        <v>0.284108</v>
       </c>
       <c r="E273" s="8">
-        <v>2823661601.17</v>
+        <v>2820909009.36</v>
       </c>
       <c r="F273" s="9">
-        <v>87318</v>
+        <v>87303</v>
       </c>
       <c r="G273" s="8">
-        <v>800476336.65</v>
+        <v>801442212.09</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9085,19 +9081,19 @@
         <v>548</v>
       </c>
       <c r="C274" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D274" s="7">
-        <v>2.414656</v>
+        <v>2.386847</v>
       </c>
       <c r="E274" s="8">
-        <v>1898092708.69</v>
+        <v>1900055963.01</v>
       </c>
       <c r="F274" s="9">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="G274" s="8">
-        <v>4583240582.09</v>
+        <v>4535143450.8</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9108,19 +9104,19 @@
         <v>550</v>
       </c>
       <c r="C275" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D275" s="10">
-        <v>0.90678</v>
+        <v>46147</v>
+      </c>
+      <c r="D275" s="7">
+        <v>0.904791</v>
       </c>
       <c r="E275" s="8">
-        <v>768283064.51</v>
+        <v>768974075.39</v>
       </c>
       <c r="F275" s="9">
-        <v>83388</v>
+        <v>83376</v>
       </c>
       <c r="G275" s="8">
-        <v>696663917.3</v>
+        <v>695760907.58</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9131,19 +9127,19 @@
         <v>552</v>
       </c>
       <c r="C276" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D276" s="7">
-        <v>0.375013</v>
+        <v>0.375338</v>
       </c>
       <c r="E276" s="8">
-        <v>8948674588.92</v>
+        <v>9052111795.99</v>
       </c>
       <c r="F276" s="9">
-        <v>100675</v>
+        <v>107192</v>
       </c>
       <c r="G276" s="8">
-        <v>3355872506.67</v>
+        <v>3397599244.31</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9154,19 +9150,19 @@
         <v>554</v>
       </c>
       <c r="C277" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D277" s="7">
-        <v>0.110052</v>
+        <v>0.109732</v>
       </c>
       <c r="E277" s="8">
-        <v>54165730674.07</v>
+        <v>54737184808.7</v>
       </c>
       <c r="F277" s="9">
-        <v>197939</v>
+        <v>198607</v>
       </c>
       <c r="G277" s="8">
-        <v>5961050281.85</v>
+        <v>6006406126.16</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9177,19 +9173,19 @@
         <v>556</v>
       </c>
       <c r="C278" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D278" s="7">
-        <v>0.114821</v>
+        <v>0.115126</v>
       </c>
       <c r="E278" s="8">
-        <v>82005956508.89</v>
+        <v>83557948005.4</v>
       </c>
       <c r="F278" s="9">
-        <v>1065729</v>
+        <v>1084899</v>
       </c>
       <c r="G278" s="8">
-        <v>9416025527.77</v>
+        <v>9619693056.34</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9200,19 +9196,19 @@
         <v>558</v>
       </c>
       <c r="C279" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D279" s="7">
-        <v>0.142146</v>
+        <v>0.142543</v>
       </c>
       <c r="E279" s="8">
-        <v>33128738099.23</v>
+        <v>33121935674.1</v>
       </c>
       <c r="F279" s="9">
-        <v>328560</v>
+        <v>328522</v>
       </c>
       <c r="G279" s="8">
-        <v>4709107228.29</v>
+        <v>4721285841.92</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9223,19 +9219,19 @@
         <v>560</v>
       </c>
       <c r="C280" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D280" s="7">
-        <v>0.168357</v>
+        <v>0.169072</v>
       </c>
       <c r="E280" s="8">
-        <v>3138452617.88</v>
+        <v>3142126349.58</v>
       </c>
       <c r="F280" s="9">
-        <v>27418</v>
+        <v>27417</v>
       </c>
       <c r="G280" s="8">
-        <v>528381296.12</v>
+        <v>531245590.38</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -9246,19 +9242,19 @@
         <v>562</v>
       </c>
       <c r="C281" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D281" s="7">
-        <v>0.725569</v>
+        <v>0.724825</v>
       </c>
       <c r="E281" s="8">
-        <v>44284740370.91</v>
+        <v>44257319746.84</v>
       </c>
       <c r="F281" s="9">
-        <v>673792</v>
+        <v>674018</v>
       </c>
       <c r="G281" s="8">
-        <v>32131616415.74</v>
+        <v>32078823871.42</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -9269,19 +9265,19 @@
         <v>564</v>
       </c>
       <c r="C282" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D282" s="7">
-        <v>0.261117</v>
+        <v>0.261505</v>
       </c>
       <c r="E282" s="8">
-        <v>8731826918.75</v>
+        <v>8730966278.9</v>
       </c>
       <c r="F282" s="9">
-        <v>108503</v>
+        <v>108538</v>
       </c>
       <c r="G282" s="8">
-        <v>2280030278.33</v>
+        <v>2283188631.42</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -9292,19 +9288,19 @@
         <v>566</v>
       </c>
       <c r="C283" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D283" s="7">
-        <v>0.541432</v>
+        <v>0.542706</v>
       </c>
       <c r="E283" s="8">
-        <v>11644899532.11</v>
+        <v>11680463808.84</v>
       </c>
       <c r="F283" s="9">
-        <v>139003</v>
+        <v>139068</v>
       </c>
       <c r="G283" s="8">
-        <v>6304915796.09</v>
+        <v>6339062713.31</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -9315,19 +9311,19 @@
         <v>568</v>
       </c>
       <c r="C284" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D284" s="10">
-        <v>0.30336</v>
+        <v>0.30481</v>
       </c>
       <c r="E284" s="8">
-        <v>2284401051.08</v>
+        <v>2284280459.6</v>
       </c>
       <c r="F284" s="9">
-        <v>37389</v>
+        <v>37393</v>
       </c>
       <c r="G284" s="8">
-        <v>692996473.96</v>
+        <v>696271991.67</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -9338,19 +9334,19 @@
         <v>570</v>
       </c>
       <c r="C285" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D285" s="7">
-        <v>0.196659</v>
+        <v>0.197185</v>
       </c>
       <c r="E285" s="8">
-        <v>9516342576.48</v>
+        <v>9520859651.96</v>
       </c>
       <c r="F285" s="9">
-        <v>108195</v>
+        <v>108170</v>
       </c>
       <c r="G285" s="8">
-        <v>1871474418.46</v>
+        <v>1877370890.68</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -9361,19 +9357,19 @@
         <v>572</v>
       </c>
       <c r="C286" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D286" s="7">
-        <v>0.277547</v>
+        <v>0.278734</v>
       </c>
       <c r="E286" s="8">
-        <v>788923198.76</v>
+        <v>791918449.61</v>
       </c>
       <c r="F286" s="9">
-        <v>2805</v>
+        <v>2803</v>
       </c>
       <c r="G286" s="8">
-        <v>218963284.31</v>
+        <v>220734468.94</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -9384,19 +9380,19 @@
         <v>574</v>
       </c>
       <c r="C287" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D287" s="7">
-        <v>0.087796</v>
+        <v>0.087888</v>
       </c>
       <c r="E287" s="8">
-        <v>4142462765.33</v>
+        <v>4088306875.8</v>
       </c>
       <c r="F287" s="9">
-        <v>145358</v>
+        <v>144401</v>
       </c>
       <c r="G287" s="8">
-        <v>363692756.32</v>
+        <v>359313686.51</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -9407,19 +9403,19 @@
         <v>576</v>
       </c>
       <c r="C288" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D288" s="7">
-        <v>0.481565</v>
+        <v>46147</v>
+      </c>
+      <c r="D288" s="10">
+        <v>0.48253</v>
       </c>
       <c r="E288" s="8">
-        <v>1576921429.48</v>
+        <v>1575037517.6</v>
       </c>
       <c r="F288" s="9">
-        <v>4275</v>
+        <v>4269</v>
       </c>
       <c r="G288" s="8">
-        <v>759390762.19</v>
+        <v>760002959.56</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -9430,19 +9426,19 @@
         <v>578</v>
       </c>
       <c r="C289" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D289" s="7">
-        <v>0.015624</v>
+        <v>46147</v>
+      </c>
+      <c r="D289" s="10">
+        <v>0.01567</v>
       </c>
       <c r="E289" s="8">
-        <v>5743298730.74</v>
+        <v>5833109286.12</v>
       </c>
       <c r="F289" s="9">
-        <v>3641</v>
+        <v>3654</v>
       </c>
       <c r="G289" s="8">
-        <v>89733182.13</v>
+        <v>91407030.71</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -9453,19 +9449,19 @@
         <v>580</v>
       </c>
       <c r="C290" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D290" s="7">
-        <v>0.017346</v>
+        <v>0.017596</v>
       </c>
       <c r="E290" s="8">
-        <v>151924573327.1</v>
+        <v>152118904163.83</v>
       </c>
       <c r="F290" s="9">
-        <v>31661</v>
+        <v>31610</v>
       </c>
       <c r="G290" s="8">
-        <v>2635313228.51</v>
+        <v>2676703259.14</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -9476,19 +9472,19 @@
         <v>582</v>
       </c>
       <c r="C291" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D291" s="7">
-        <v>0.010725</v>
+        <v>0.010678</v>
       </c>
       <c r="E291" s="8">
-        <v>7148107395.55</v>
+        <v>7482179760.16</v>
       </c>
       <c r="F291" s="9">
-        <v>1220</v>
+        <v>1286</v>
       </c>
       <c r="G291" s="8">
-        <v>76663058.79</v>
+        <v>79895676.3</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -9499,19 +9495,19 @@
         <v>584</v>
       </c>
       <c r="C292" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D292" s="7">
-        <v>0.132092</v>
+        <v>46147</v>
+      </c>
+      <c r="D292" s="10">
+        <v>0.13316</v>
       </c>
       <c r="E292" s="8">
-        <v>52721754362.38</v>
+        <v>52646888196.23</v>
       </c>
       <c r="F292" s="9">
-        <v>107851</v>
+        <v>107839</v>
       </c>
       <c r="G292" s="8">
-        <v>6964148095.97</v>
+        <v>7010449647.36</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -9522,19 +9518,19 @@
         <v>586</v>
       </c>
       <c r="C293" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D293" s="7">
-        <v>0.051205</v>
+        <v>0.051261</v>
       </c>
       <c r="E293" s="8">
-        <v>12306913620.59</v>
+        <v>12390222040.87</v>
       </c>
       <c r="F293" s="9">
-        <v>28601</v>
+        <v>28674</v>
       </c>
       <c r="G293" s="8">
-        <v>630181220.87</v>
+        <v>635133345.18</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -9545,19 +9541,19 @@
         <v>588</v>
       </c>
       <c r="C294" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D294" s="7">
-        <v>0.022014</v>
+        <v>0.022013</v>
       </c>
       <c r="E294" s="8">
-        <v>57519971833.53</v>
+        <v>57770746369.41</v>
       </c>
       <c r="F294" s="9">
-        <v>10730</v>
+        <v>10715</v>
       </c>
       <c r="G294" s="8">
-        <v>1266230374.08</v>
+        <v>1271703817.35</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -9568,19 +9564,19 @@
         <v>590</v>
       </c>
       <c r="C295" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D295" s="7">
-        <v>0.031585</v>
+        <v>0.031688</v>
       </c>
       <c r="E295" s="8">
-        <v>54943625316.49</v>
+        <v>55266951553.84</v>
       </c>
       <c r="F295" s="9">
-        <v>33245</v>
+        <v>33351</v>
       </c>
       <c r="G295" s="8">
-        <v>1735418429.62</v>
+        <v>1751319501.39</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -9591,19 +9587,19 @@
         <v>592</v>
       </c>
       <c r="C296" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D296" s="7">
-        <v>0.019199</v>
+        <v>0.019481</v>
       </c>
       <c r="E296" s="8">
-        <v>962540546344.67</v>
+        <v>960145869118.97</v>
       </c>
       <c r="F296" s="9">
-        <v>179037</v>
+        <v>178817</v>
       </c>
       <c r="G296" s="8">
-        <v>18480264939.65</v>
+        <v>18704642359.42</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -9614,19 +9610,19 @@
         <v>594</v>
       </c>
       <c r="C297" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D297" s="7">
-        <v>0.101074</v>
+        <v>0.101035</v>
       </c>
       <c r="E297" s="8">
-        <v>37027325783.79</v>
+        <v>37004681597.1</v>
       </c>
       <c r="F297" s="9">
-        <v>382584</v>
+        <v>382527</v>
       </c>
       <c r="G297" s="8">
-        <v>3742489184.07</v>
+        <v>3738785271.92</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -9637,19 +9633,19 @@
         <v>596</v>
       </c>
       <c r="C298" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D298" s="7">
-        <v>0.086145</v>
+        <v>0.086201</v>
       </c>
       <c r="E298" s="8">
-        <v>38387939929.99</v>
+        <v>38377264542.92</v>
       </c>
       <c r="F298" s="9">
-        <v>48165</v>
+        <v>48152</v>
       </c>
       <c r="G298" s="8">
-        <v>3306928228.74</v>
+        <v>3308146561.82</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -9660,19 +9656,19 @@
         <v>598</v>
       </c>
       <c r="C299" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D299" s="7">
-        <v>0.094874</v>
+        <v>0.095014</v>
       </c>
       <c r="E299" s="8">
-        <v>39058140422.89</v>
+        <v>39030594063.58</v>
       </c>
       <c r="F299" s="9">
-        <v>527283</v>
+        <v>527186</v>
       </c>
       <c r="G299" s="8">
-        <v>3705592542.99</v>
+        <v>3708457680.06</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -9683,19 +9679,19 @@
         <v>600</v>
       </c>
       <c r="C300" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D300" s="7">
-        <v>0.020117</v>
+        <v>0.020304</v>
       </c>
       <c r="E300" s="8">
-        <v>35082081081.85</v>
+        <v>35672650987.72</v>
       </c>
       <c r="F300" s="9">
-        <v>25005</v>
+        <v>25168</v>
       </c>
       <c r="G300" s="8">
-        <v>705763274.04</v>
+        <v>724280465.07</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -9706,19 +9702,19 @@
         <v>602</v>
       </c>
       <c r="C301" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D301" s="7">
-        <v>0.010317</v>
+        <v>0.010328</v>
       </c>
       <c r="E301" s="8">
-        <v>2557483484.62</v>
+        <v>3038285889.97</v>
       </c>
       <c r="F301" s="9">
-        <v>588</v>
+        <v>656</v>
       </c>
       <c r="G301" s="8">
-        <v>26386337.17</v>
+        <v>31380380.02</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -9729,19 +9725,19 @@
         <v>604</v>
       </c>
       <c r="C302" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D302" s="7">
-        <v>0.015426</v>
+        <v>0.015748</v>
       </c>
       <c r="E302" s="8">
-        <v>24146107347.72</v>
+        <v>23959992779.54</v>
       </c>
       <c r="F302" s="9">
-        <v>10998</v>
+        <v>11033</v>
       </c>
       <c r="G302" s="8">
-        <v>372475795.59</v>
+        <v>377326720.56</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -9752,19 +9748,19 @@
         <v>606</v>
       </c>
       <c r="C303" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D303" s="7">
-        <v>0.018004</v>
+        <v>0.018144</v>
       </c>
       <c r="E303" s="8">
-        <v>11924187961.78</v>
+        <v>11950111160.7</v>
       </c>
       <c r="F303" s="9">
-        <v>6663</v>
+        <v>6660</v>
       </c>
       <c r="G303" s="8">
-        <v>214687770.93</v>
+        <v>216827344.32</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -9775,19 +9771,19 @@
         <v>608</v>
       </c>
       <c r="C304" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D304" s="7">
-        <v>0.094295</v>
+        <v>0.094312</v>
       </c>
       <c r="E304" s="8">
-        <v>21251265550.92</v>
+        <v>21247660382.29</v>
       </c>
       <c r="F304" s="9">
-        <v>347481</v>
+        <v>347456</v>
       </c>
       <c r="G304" s="8">
-        <v>2003879474.27</v>
+        <v>2003907619.55</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -9798,19 +9794,19 @@
         <v>610</v>
       </c>
       <c r="C305" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D305" s="7">
-        <v>0.018931</v>
+        <v>0.018847</v>
       </c>
       <c r="E305" s="8">
-        <v>10439422188.39</v>
+        <v>10490442556.08</v>
       </c>
       <c r="F305" s="9">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G305" s="8">
-        <v>197630457.95</v>
+        <v>197713871.37</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -9821,19 +9817,19 @@
         <v>612</v>
       </c>
       <c r="C306" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D306" s="7">
-        <v>0.015628</v>
+        <v>0.015578</v>
       </c>
       <c r="E306" s="8">
-        <v>9157802920.13</v>
+        <v>9172553683.41</v>
       </c>
       <c r="F306" s="9">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G306" s="8">
-        <v>143113825.34</v>
+        <v>142893051.38</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -9844,19 +9840,19 @@
         <v>614</v>
       </c>
       <c r="C307" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D307" s="7">
-        <v>0.015875</v>
+        <v>46147</v>
+      </c>
+      <c r="D307" s="10">
+        <v>0.01589</v>
       </c>
       <c r="E307" s="8">
-        <v>1242595378.46</v>
+        <v>1260208910.42</v>
       </c>
       <c r="F307" s="9">
         <v>23</v>
       </c>
       <c r="G307" s="8">
-        <v>19725753.82</v>
+        <v>20025114.35</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -9867,19 +9863,19 @@
         <v>616</v>
       </c>
       <c r="C308" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D308" s="7">
-        <v>0.227162</v>
+        <v>0.228382</v>
       </c>
       <c r="E308" s="8">
-        <v>48544139330.89</v>
+        <v>48584906659.2</v>
       </c>
       <c r="F308" s="9">
-        <v>174287</v>
+        <v>174266</v>
       </c>
       <c r="G308" s="8">
-        <v>11027394481.62</v>
+        <v>11095905388.88</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -9890,19 +9886,19 @@
         <v>618</v>
       </c>
       <c r="C309" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D309" s="7">
-        <v>0.011098</v>
+        <v>0.011123</v>
       </c>
       <c r="E309" s="8">
-        <v>2330337533.12</v>
+        <v>2348538389.6</v>
       </c>
       <c r="F309" s="9">
-        <v>1942</v>
+        <v>1960</v>
       </c>
       <c r="G309" s="8">
-        <v>25862865.13</v>
+        <v>26123211.92</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -9913,19 +9909,19 @@
         <v>620</v>
       </c>
       <c r="C310" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D310" s="7">
-        <v>0.029099</v>
+        <v>0.029768</v>
       </c>
       <c r="E310" s="8">
-        <v>12502936455.74</v>
+        <v>12614606459.9</v>
       </c>
       <c r="F310" s="9">
-        <v>17374</v>
+        <v>17435</v>
       </c>
       <c r="G310" s="8">
-        <v>363816979.22</v>
+        <v>375507038.94</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -9936,19 +9932,19 @@
         <v>622</v>
       </c>
       <c r="C311" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D311" s="10">
-        <v>0.02483</v>
+        <v>46147</v>
+      </c>
+      <c r="D311" s="11">
+        <v>0.0248</v>
       </c>
       <c r="E311" s="8">
-        <v>3076841682.4</v>
+        <v>3023139371.24</v>
       </c>
       <c r="F311" s="9">
-        <v>10228</v>
+        <v>10250</v>
       </c>
       <c r="G311" s="8">
-        <v>76396904.55</v>
+        <v>74974736.36</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -9959,19 +9955,19 @@
         <v>624</v>
       </c>
       <c r="C312" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D312" s="7">
-        <v>0.123019</v>
+        <v>46147</v>
+      </c>
+      <c r="D312" s="10">
+        <v>0.12346</v>
       </c>
       <c r="E312" s="8">
-        <v>610469941.26</v>
+        <v>619361004.68</v>
       </c>
       <c r="F312" s="9">
-        <v>92356</v>
+        <v>94294</v>
       </c>
       <c r="G312" s="8">
-        <v>75099673.12</v>
+        <v>76466442.59</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -9982,19 +9978,19 @@
         <v>626</v>
       </c>
       <c r="C313" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D313" s="7">
-        <v>0.090813</v>
+        <v>0.090901</v>
       </c>
       <c r="E313" s="8">
-        <v>1333056228.56</v>
+        <v>1431676407.57</v>
       </c>
       <c r="F313" s="9">
-        <v>24857</v>
+        <v>26345</v>
       </c>
       <c r="G313" s="8">
-        <v>121059238.2</v>
+        <v>130141504.96</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -10005,19 +10001,19 @@
         <v>628</v>
       </c>
       <c r="C314" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D314" s="7">
-        <v>0.080373</v>
+        <v>0.080461</v>
       </c>
       <c r="E314" s="8">
-        <v>2346626206.97</v>
+        <v>2331675898.53</v>
       </c>
       <c r="F314" s="9">
-        <v>74473</v>
+        <v>74110</v>
       </c>
       <c r="G314" s="8">
-        <v>188605384.44</v>
+        <v>187608949.12</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -10028,19 +10024,19 @@
         <v>630</v>
       </c>
       <c r="C315" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D315" s="7">
-        <v>0.387023</v>
+        <v>0.388572</v>
       </c>
       <c r="E315" s="8">
-        <v>5203329769.64</v>
+        <v>5200900281.53</v>
       </c>
       <c r="F315" s="9">
-        <v>71647</v>
+        <v>71654</v>
       </c>
       <c r="G315" s="8">
-        <v>2013806348.43</v>
+        <v>2020924333.81</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -10051,19 +10047,19 @@
         <v>632</v>
       </c>
       <c r="C316" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D316" s="7">
-        <v>0.204952</v>
+        <v>0.204876</v>
       </c>
       <c r="E316" s="8">
-        <v>5833949976.08</v>
+        <v>5834037193.46</v>
       </c>
       <c r="F316" s="9">
-        <v>56445</v>
+        <v>56440</v>
       </c>
       <c r="G316" s="8">
-        <v>1195677227.11</v>
+        <v>1195251715.88</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -10074,19 +10070,19 @@
         <v>634</v>
       </c>
       <c r="C317" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D317" s="10">
-        <v>0.11152</v>
+        <v>46147</v>
+      </c>
+      <c r="D317" s="7">
+        <v>0.111793</v>
       </c>
       <c r="E317" s="8">
-        <v>2285947676.6</v>
+        <v>2285773735.21</v>
       </c>
       <c r="F317" s="9">
-        <v>8333</v>
+        <v>8342</v>
       </c>
       <c r="G317" s="8">
-        <v>254929461.85</v>
+        <v>255533525.48</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -10097,19 +10093,19 @@
         <v>636</v>
       </c>
       <c r="C318" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D318" s="7">
-        <v>0.550785</v>
+        <v>0.545317</v>
       </c>
       <c r="E318" s="8">
-        <v>3997424797.66</v>
+        <v>4004494756.21</v>
       </c>
       <c r="F318" s="9">
-        <v>50388</v>
+        <v>50402</v>
       </c>
       <c r="G318" s="8">
-        <v>2201722660.6</v>
+        <v>2183720581.39</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -10120,19 +10116,19 @@
         <v>638</v>
       </c>
       <c r="C319" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D319" s="10">
-        <v>0.08517</v>
+        <v>46147</v>
+      </c>
+      <c r="D319" s="7">
+        <v>0.085321</v>
       </c>
       <c r="E319" s="8">
-        <v>8838885466.7</v>
+        <v>8823779329.46</v>
       </c>
       <c r="F319" s="9">
-        <v>187990</v>
+        <v>187891</v>
       </c>
       <c r="G319" s="8">
-        <v>752805726.67</v>
+        <v>752853332.71</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -10143,19 +10139,19 @@
         <v>640</v>
       </c>
       <c r="C320" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D320" s="10">
-        <v>0.10814</v>
+        <v>46147</v>
+      </c>
+      <c r="D320" s="7">
+        <v>0.108018</v>
       </c>
       <c r="E320" s="8">
-        <v>23067025431.56</v>
+        <v>23088102418.27</v>
       </c>
       <c r="F320" s="9">
-        <v>137949</v>
+        <v>137885</v>
       </c>
       <c r="G320" s="8">
-        <v>2494478732.32</v>
+        <v>2493926462.63</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -10166,19 +10162,19 @@
         <v>642</v>
       </c>
       <c r="C321" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D321" s="7">
-        <v>0.151726</v>
+        <v>0.151872</v>
       </c>
       <c r="E321" s="8">
-        <v>13203887317.2</v>
+        <v>13640095151.46</v>
       </c>
       <c r="F321" s="9">
-        <v>44043</v>
+        <v>61348</v>
       </c>
       <c r="G321" s="8">
-        <v>2003377828.29</v>
+        <v>2071555313.21</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -10189,19 +10185,19 @@
         <v>644</v>
       </c>
       <c r="C322" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D322" s="7">
-        <v>0.133365</v>
+        <v>0.133262</v>
       </c>
       <c r="E322" s="8">
-        <v>527815840.01</v>
+        <v>527557935.56</v>
       </c>
       <c r="F322" s="9">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G322" s="8">
-        <v>70392070.34</v>
+        <v>70303384.47</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -10212,19 +10208,19 @@
         <v>646</v>
       </c>
       <c r="C323" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D323" s="7">
-        <v>0.136914</v>
+        <v>0.136224</v>
       </c>
       <c r="E323" s="8">
-        <v>225399634.09</v>
+        <v>224790258.32</v>
       </c>
       <c r="F323" s="9">
         <v>418</v>
       </c>
       <c r="G323" s="8">
-        <v>30860287.69</v>
+        <v>30621840.73</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -10235,19 +10231,19 @@
         <v>648</v>
       </c>
       <c r="C324" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D324" s="10">
-        <v>0.16725</v>
+        <v>46147</v>
+      </c>
+      <c r="D324" s="7">
+        <v>0.166151</v>
       </c>
       <c r="E324" s="8">
-        <v>296210734.73</v>
+        <v>296355486.99</v>
       </c>
       <c r="F324" s="9">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G324" s="8">
-        <v>49541254.71</v>
+        <v>49239847.45</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -10258,19 +10254,19 @@
         <v>650</v>
       </c>
       <c r="C325" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D325" s="7">
-        <v>0.198494</v>
+        <v>0.196745</v>
       </c>
       <c r="E325" s="8">
-        <v>359656767.23</v>
+        <v>359894925.09</v>
       </c>
       <c r="F325" s="9">
         <v>596</v>
       </c>
       <c r="G325" s="8">
-        <v>71389739.41</v>
+        <v>70807534.66</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -10281,19 +10277,19 @@
         <v>652</v>
       </c>
       <c r="C326" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D326" s="7">
-        <v>0.141906</v>
+        <v>0.142133</v>
       </c>
       <c r="E326" s="8">
-        <v>413275458.65</v>
+        <v>413474457.34</v>
       </c>
       <c r="F326" s="9">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="G326" s="8">
-        <v>58646171.94</v>
+        <v>58768491.12</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -10304,19 +10300,19 @@
         <v>654</v>
       </c>
       <c r="C327" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D327" s="7">
-        <v>0.097358</v>
+        <v>0.097022</v>
       </c>
       <c r="E327" s="8">
-        <v>39946792912.95</v>
+        <v>40725363091.17</v>
       </c>
       <c r="F327" s="9">
-        <v>367231</v>
+        <v>374551</v>
       </c>
       <c r="G327" s="8">
-        <v>3889147990.56</v>
+        <v>3951269544.65</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -10327,19 +10323,19 @@
         <v>656</v>
       </c>
       <c r="C328" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D328" s="7">
-        <v>0.173014</v>
+        <v>0.173417</v>
       </c>
       <c r="E328" s="8">
-        <v>192616735.39</v>
+        <v>193203335.53</v>
       </c>
       <c r="F328" s="9">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G328" s="8">
-        <v>33325297.18</v>
+        <v>33504767.65</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -10350,19 +10346,19 @@
         <v>658</v>
       </c>
       <c r="C329" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D329" s="7">
-        <v>0.202948</v>
+        <v>0.203394</v>
       </c>
       <c r="E329" s="8">
-        <v>238886332.46</v>
+        <v>238564663.16</v>
       </c>
       <c r="F329" s="9">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G329" s="8">
-        <v>48481502.23</v>
+        <v>48522581.98</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -10373,19 +10369,19 @@
         <v>660</v>
       </c>
       <c r="C330" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D330" s="7">
-        <v>0.291141</v>
+        <v>0.289571</v>
       </c>
       <c r="E330" s="8">
-        <v>1252235110.26</v>
+        <v>1251520848.97</v>
       </c>
       <c r="F330" s="9">
-        <v>8746</v>
+        <v>8756</v>
       </c>
       <c r="G330" s="8">
-        <v>364577516.85</v>
+        <v>362403645.72</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
@@ -10396,19 +10392,19 @@
         <v>662</v>
       </c>
       <c r="C331" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D331" s="7">
-        <v>0.091555</v>
+        <v>0.091478</v>
       </c>
       <c r="E331" s="8">
-        <v>6839777833.28</v>
+        <v>6835954447.63</v>
       </c>
       <c r="F331" s="9">
-        <v>123309</v>
+        <v>123272</v>
       </c>
       <c r="G331" s="8">
-        <v>626219117.75</v>
+        <v>625337858.86</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
@@ -10419,19 +10415,19 @@
         <v>664</v>
       </c>
       <c r="C332" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D332" s="7">
-        <v>0.073702</v>
+        <v>0.073847</v>
       </c>
       <c r="E332" s="8">
-        <v>103496670661.7</v>
+        <v>103572760453.86</v>
       </c>
       <c r="F332" s="9">
-        <v>148079</v>
+        <v>148083</v>
       </c>
       <c r="G332" s="8">
-        <v>7627889561.83</v>
+        <v>7648585477.65</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
@@ -10442,19 +10438,19 @@
         <v>666</v>
       </c>
       <c r="C333" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D333" s="11">
-        <v>0.0654</v>
+        <v>46147</v>
+      </c>
+      <c r="D333" s="7">
+        <v>0.065525</v>
       </c>
       <c r="E333" s="8">
-        <v>111562834769.09</v>
+        <v>111707093186.66</v>
       </c>
       <c r="F333" s="9">
-        <v>99435</v>
+        <v>99408</v>
       </c>
       <c r="G333" s="8">
-        <v>7296178129.14</v>
+        <v>7319580420.91</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
@@ -10465,19 +10461,19 @@
         <v>668</v>
       </c>
       <c r="C334" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D334" s="10">
-        <v>0.08587</v>
+        <v>46147</v>
+      </c>
+      <c r="D334" s="7">
+        <v>0.086038</v>
       </c>
       <c r="E334" s="8">
-        <v>65000856740.64</v>
+        <v>64990903519.87</v>
       </c>
       <c r="F334" s="9">
-        <v>123083</v>
+        <v>123071</v>
       </c>
       <c r="G334" s="8">
-        <v>5581601407.61</v>
+        <v>5591659446.13</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
@@ -10488,19 +10484,19 @@
         <v>670</v>
       </c>
       <c r="C335" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D335" s="7">
-        <v>0.449583</v>
+        <v>0.449894</v>
       </c>
       <c r="E335" s="8">
-        <v>52495400981.57</v>
+        <v>52411821731.06</v>
       </c>
       <c r="F335" s="9">
-        <v>126822</v>
+        <v>126725</v>
       </c>
       <c r="G335" s="8">
-        <v>23601047111.85</v>
+        <v>23579783981.95</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
@@ -10511,19 +10507,19 @@
         <v>672</v>
       </c>
       <c r="C336" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D336" s="7">
-        <v>0.099156</v>
+        <v>0.099217</v>
       </c>
       <c r="E336" s="8">
-        <v>5325981904.12</v>
+        <v>5341337688.84</v>
       </c>
       <c r="F336" s="9">
-        <v>8789</v>
+        <v>8787</v>
       </c>
       <c r="G336" s="8">
-        <v>528104929.6</v>
+        <v>529953176.32</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
@@ -10534,19 +10530,19 @@
         <v>674</v>
       </c>
       <c r="C337" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D337" s="7">
-        <v>0.352213</v>
+        <v>0.354309</v>
       </c>
       <c r="E337" s="8">
-        <v>15809491712.28</v>
+        <v>15803075841.99</v>
       </c>
       <c r="F337" s="9">
-        <v>28619</v>
+        <v>28607</v>
       </c>
       <c r="G337" s="8">
-        <v>5568312829.91</v>
+        <v>5599167169.38</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
@@ -10557,19 +10553,19 @@
         <v>676</v>
       </c>
       <c r="C338" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D338" s="7">
-        <v>0.010073</v>
+        <v>0.010113</v>
       </c>
       <c r="E338" s="8">
-        <v>76385568569.32</v>
+        <v>78589447884.57</v>
       </c>
       <c r="F338" s="9">
-        <v>4271</v>
+        <v>4323</v>
       </c>
       <c r="G338" s="8">
-        <v>769410802.51</v>
+        <v>794791796.28</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
@@ -10580,19 +10576,19 @@
         <v>678</v>
       </c>
       <c r="C339" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D339" s="7">
-        <v>0.081921</v>
+        <v>0.082008</v>
       </c>
       <c r="E339" s="8">
-        <v>3712632696.63</v>
+        <v>3724476327.08</v>
       </c>
       <c r="F339" s="9">
-        <v>78459</v>
+        <v>78430</v>
       </c>
       <c r="G339" s="8">
-        <v>304143736.71</v>
+        <v>305436756.44</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
@@ -10603,19 +10599,19 @@
         <v>680</v>
       </c>
       <c r="C340" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D340" s="7">
-        <v>0.091545</v>
+        <v>0.091631</v>
       </c>
       <c r="E340" s="8">
-        <v>625140454.98</v>
+        <v>645513157.86</v>
       </c>
       <c r="F340" s="9">
-        <v>12418</v>
+        <v>12876</v>
       </c>
       <c r="G340" s="8">
-        <v>57228184.42</v>
+        <v>59149124.32</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -10626,19 +10622,19 @@
         <v>682</v>
       </c>
       <c r="C341" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D341" s="10">
-        <v>0.04306</v>
+        <v>46147</v>
+      </c>
+      <c r="D341" s="7">
+        <v>0.043135</v>
       </c>
       <c r="E341" s="8">
-        <v>1040814121.73</v>
+        <v>1046260459.49</v>
       </c>
       <c r="F341" s="9">
-        <v>2209</v>
+        <v>2214</v>
       </c>
       <c r="G341" s="8">
-        <v>44817830.38</v>
+        <v>45130885.26</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
@@ -10649,19 +10645,19 @@
         <v>684</v>
       </c>
       <c r="C342" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D342" s="7">
-        <v>0.049826</v>
+        <v>0.049779</v>
       </c>
       <c r="E342" s="8">
-        <v>3921638007.11</v>
+        <v>3923974893.77</v>
       </c>
       <c r="F342" s="9">
-        <v>4329</v>
+        <v>4338</v>
       </c>
       <c r="G342" s="8">
-        <v>195400520.6</v>
+        <v>195330530.31</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
@@ -10672,19 +10668,19 @@
         <v>686</v>
       </c>
       <c r="C343" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D343" s="7">
-        <v>0.013877</v>
+        <v>0.013749</v>
       </c>
       <c r="E343" s="8">
-        <v>34953493529.67</v>
+        <v>34526011617.38</v>
       </c>
       <c r="F343" s="9">
-        <v>27284</v>
+        <v>27370</v>
       </c>
       <c r="G343" s="8">
-        <v>485062038.19</v>
+        <v>474693285.88</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
@@ -10695,19 +10691,19 @@
         <v>688</v>
       </c>
       <c r="C344" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D344" s="7">
-        <v>0.071027</v>
+        <v>0.072893</v>
       </c>
       <c r="E344" s="8">
-        <v>48089364749.11</v>
+        <v>48789199866.39</v>
       </c>
       <c r="F344" s="9">
-        <v>120754</v>
+        <v>121331</v>
       </c>
       <c r="G344" s="8">
-        <v>3415626694.96</v>
+        <v>3556404778.77</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
@@ -10718,19 +10714,19 @@
         <v>690</v>
       </c>
       <c r="C345" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D345" s="7">
-        <v>0.012836</v>
+        <v>46147</v>
+      </c>
+      <c r="D345" s="10">
+        <v>0.01291</v>
       </c>
       <c r="E345" s="8">
-        <v>14562246052.6</v>
+        <v>14745359307.24</v>
       </c>
       <c r="F345" s="9">
-        <v>5390</v>
+        <v>5496</v>
       </c>
       <c r="G345" s="8">
-        <v>186917157.36</v>
+        <v>190356324.64</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
@@ -10741,19 +10737,19 @@
         <v>692</v>
       </c>
       <c r="C346" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D346" s="7">
-        <v>0.014848</v>
+        <v>0.014866</v>
       </c>
       <c r="E346" s="8">
-        <v>69869125466.52</v>
+        <v>70369446553.81</v>
       </c>
       <c r="F346" s="9">
-        <v>18573</v>
+        <v>18714</v>
       </c>
       <c r="G346" s="8">
-        <v>1037406520.1</v>
+        <v>1046088964.93</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
@@ -10764,19 +10760,19 @@
         <v>694</v>
       </c>
       <c r="C347" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D347" s="7">
-        <v>0.049594</v>
+        <v>0.049682</v>
       </c>
       <c r="E347" s="8">
-        <v>7303306735.22</v>
+        <v>7410431215.51</v>
       </c>
       <c r="F347" s="9">
-        <v>9388</v>
+        <v>9427</v>
       </c>
       <c r="G347" s="8">
-        <v>362200998.22</v>
+        <v>368161358.16</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
@@ -10787,19 +10783,19 @@
         <v>696</v>
       </c>
       <c r="C348" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D348" s="7">
-        <v>0.086918</v>
+        <v>46147</v>
+      </c>
+      <c r="D348" s="10">
+        <v>0.08701</v>
       </c>
       <c r="E348" s="8">
-        <v>577419532.46</v>
+        <v>580813109.92</v>
       </c>
       <c r="F348" s="9">
-        <v>6840</v>
+        <v>6845</v>
       </c>
       <c r="G348" s="8">
-        <v>50188372.27</v>
+        <v>50536746.84</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
@@ -10810,19 +10806,19 @@
         <v>698</v>
       </c>
       <c r="C349" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D349" s="7">
-        <v>0.048869</v>
+        <v>0.048477</v>
       </c>
       <c r="E349" s="8">
-        <v>3894718114.09</v>
+        <v>3894674315.37</v>
       </c>
       <c r="F349" s="9">
-        <v>5943</v>
+        <v>5931</v>
       </c>
       <c r="G349" s="8">
-        <v>190332837.32</v>
+        <v>188801786.87</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
@@ -10833,19 +10829,19 @@
         <v>700</v>
       </c>
       <c r="C350" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D350" s="7">
-        <v>0.020556</v>
+        <v>0.020562</v>
       </c>
       <c r="E350" s="8">
-        <v>8784807794.94</v>
+        <v>8792926649.37</v>
       </c>
       <c r="F350" s="9">
         <v>339</v>
       </c>
       <c r="G350" s="8">
-        <v>180579174.78</v>
+        <v>180800303.87</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
@@ -10856,19 +10852,19 @@
         <v>702</v>
       </c>
       <c r="C351" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D351" s="7">
-        <v>0.015069</v>
+        <v>0.014993</v>
       </c>
       <c r="E351" s="8">
-        <v>15824257798.43</v>
+        <v>15798545752.64</v>
       </c>
       <c r="F351" s="9">
-        <v>5870</v>
+        <v>5869</v>
       </c>
       <c r="G351" s="8">
-        <v>238457169.49</v>
+        <v>236869124.89</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -10879,19 +10875,19 @@
         <v>704</v>
       </c>
       <c r="C352" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D352" s="11">
-        <v>0.0137</v>
+        <v>46147</v>
+      </c>
+      <c r="D352" s="7">
+        <v>0.013779</v>
       </c>
       <c r="E352" s="8">
-        <v>22259039001.57</v>
+        <v>22250140748.7</v>
       </c>
       <c r="F352" s="9">
-        <v>5690</v>
+        <v>5713</v>
       </c>
       <c r="G352" s="8">
-        <v>304937953.66</v>
+        <v>306581398.69</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -10902,19 +10898,19 @@
         <v>706</v>
       </c>
       <c r="C353" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D353" s="10">
-        <v>0.01432</v>
+        <v>46147</v>
+      </c>
+      <c r="D353" s="7">
+        <v>0.014407</v>
       </c>
       <c r="E353" s="8">
-        <v>23411423860.33</v>
+        <v>23502988333.69</v>
       </c>
       <c r="F353" s="9">
-        <v>10653</v>
+        <v>10678</v>
       </c>
       <c r="G353" s="8">
-        <v>335243190.87</v>
+        <v>338608939.32</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
@@ -10925,19 +10921,19 @@
         <v>708</v>
       </c>
       <c r="C354" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D354" s="7">
-        <v>0.015321</v>
+        <v>0.015729</v>
       </c>
       <c r="E354" s="8">
-        <v>38472500823.6</v>
+        <v>38532791977.07</v>
       </c>
       <c r="F354" s="9">
-        <v>10259</v>
+        <v>10339</v>
       </c>
       <c r="G354" s="8">
-        <v>589430889.09</v>
+        <v>606063366.18</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -10948,19 +10944,19 @@
         <v>710</v>
       </c>
       <c r="C355" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D355" s="7">
-        <v>0.048999</v>
+        <v>0.048796</v>
       </c>
       <c r="E355" s="8">
-        <v>2888760140.95</v>
+        <v>2900508908.58</v>
       </c>
       <c r="F355" s="9">
-        <v>5146</v>
+        <v>5147</v>
       </c>
       <c r="G355" s="8">
-        <v>141547293.3</v>
+        <v>141532057.33</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
@@ -10971,19 +10967,19 @@
         <v>712</v>
       </c>
       <c r="C356" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D356" s="7">
-        <v>0.226525</v>
+        <v>0.227853</v>
       </c>
       <c r="E356" s="8">
-        <v>8788670709.68</v>
+        <v>8784748155.95</v>
       </c>
       <c r="F356" s="9">
-        <v>47747</v>
+        <v>47759</v>
       </c>
       <c r="G356" s="8">
-        <v>1990850182.59</v>
+        <v>2001634241.52</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
@@ -10994,19 +10990,19 @@
         <v>714</v>
       </c>
       <c r="C357" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D357" s="7">
-        <v>0.082776</v>
+        <v>0.082892</v>
       </c>
       <c r="E357" s="8">
-        <v>11870405546.09</v>
+        <v>11895683936.31</v>
       </c>
       <c r="F357" s="9">
-        <v>21833</v>
+        <v>21868</v>
       </c>
       <c r="G357" s="8">
-        <v>982583390.31</v>
+        <v>986060542.51</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
@@ -11017,19 +11013,19 @@
         <v>716</v>
       </c>
       <c r="C358" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D358" s="7">
-        <v>0.306508</v>
+        <v>0.307619</v>
       </c>
       <c r="E358" s="8">
-        <v>3858473955.37</v>
+        <v>3857488420.48</v>
       </c>
       <c r="F358" s="9">
-        <v>27565</v>
+        <v>27529</v>
       </c>
       <c r="G358" s="8">
-        <v>1182652387.03</v>
+        <v>1186635292.92</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
@@ -11040,19 +11036,19 @@
         <v>718</v>
       </c>
       <c r="C359" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D359" s="7">
-        <v>1.362992</v>
+        <v>1.354247</v>
       </c>
       <c r="E359" s="8">
-        <v>8858019116.31</v>
+        <v>8860805744.44</v>
       </c>
       <c r="F359" s="9">
-        <v>245164</v>
+        <v>245129</v>
       </c>
       <c r="G359" s="8">
-        <v>12073410817.52</v>
+        <v>11999718078.25</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
@@ -11063,19 +11059,19 @@
         <v>720</v>
       </c>
       <c r="C360" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D360" s="7">
-        <v>0.094975</v>
+        <v>0.094398</v>
       </c>
       <c r="E360" s="8">
-        <v>533671923611.2</v>
+        <v>542419874321.37</v>
       </c>
       <c r="F360" s="9">
-        <v>2765447</v>
+        <v>2782574</v>
       </c>
       <c r="G360" s="8">
-        <v>50685379160.3</v>
+        <v>51203093645.51</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
@@ -11086,19 +11082,19 @@
         <v>722</v>
       </c>
       <c r="C361" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D361" s="7">
-        <v>0.319769</v>
+        <v>0.320402</v>
       </c>
       <c r="E361" s="8">
-        <v>23846992773.03</v>
+        <v>23847313249.53</v>
       </c>
       <c r="F361" s="9">
-        <v>422948</v>
+        <v>422745</v>
       </c>
       <c r="G361" s="8">
-        <v>7625537934.38</v>
+        <v>7640723132.96</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
@@ -11109,19 +11105,19 @@
         <v>724</v>
       </c>
       <c r="C362" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D362" s="7">
-        <v>0.349821</v>
+        <v>0.350126</v>
       </c>
       <c r="E362" s="8">
-        <v>85046260269.63</v>
+        <v>85942824576.52</v>
       </c>
       <c r="F362" s="9">
-        <v>379572</v>
+        <v>432237</v>
       </c>
       <c r="G362" s="8">
-        <v>29750957928.53</v>
+        <v>30090858975.73</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
@@ -11132,19 +11128,19 @@
         <v>726</v>
       </c>
       <c r="C363" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D363" s="7">
-        <v>0.221339</v>
+        <v>46147</v>
+      </c>
+      <c r="D363" s="10">
+        <v>0.22203</v>
       </c>
       <c r="E363" s="8">
-        <v>20355795195.84</v>
+        <v>20363733191.76</v>
       </c>
       <c r="F363" s="9">
-        <v>70031</v>
+        <v>70049</v>
       </c>
       <c r="G363" s="8">
-        <v>4505535400.11</v>
+        <v>4521352824.2</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
@@ -11155,19 +11151,19 @@
         <v>728</v>
       </c>
       <c r="C364" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D364" s="7">
-        <v>0.101865</v>
+        <v>0.101822</v>
       </c>
       <c r="E364" s="8">
-        <v>3761153470.4</v>
+        <v>3765192665.89</v>
       </c>
       <c r="F364" s="9">
-        <v>8004</v>
+        <v>8002</v>
       </c>
       <c r="G364" s="8">
-        <v>383131755.3</v>
+        <v>383379513.77</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
@@ -11178,19 +11174,19 @@
         <v>730</v>
       </c>
       <c r="C365" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D365" s="7">
-        <v>0.136655</v>
+        <v>0.137243</v>
       </c>
       <c r="E365" s="8">
-        <v>102190150482.52</v>
+        <v>104111234092.62</v>
       </c>
       <c r="F365" s="9">
-        <v>1885755</v>
+        <v>1909280</v>
       </c>
       <c r="G365" s="8">
-        <v>13964749617.41</v>
+        <v>14288498052.94</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
@@ -11201,19 +11197,19 @@
         <v>732</v>
       </c>
       <c r="C366" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D366" s="7">
-        <v>0.136064</v>
+        <v>0.136265</v>
       </c>
       <c r="E366" s="8">
-        <v>57774586407.72</v>
+        <v>57781264617.66</v>
       </c>
       <c r="F366" s="9">
-        <v>120148</v>
+        <v>120299</v>
       </c>
       <c r="G366" s="8">
-        <v>7861018044.81</v>
+        <v>7873545666.26</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
@@ -11224,19 +11220,19 @@
         <v>734</v>
       </c>
       <c r="C367" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D367" s="7">
-        <v>0.730928</v>
+        <v>0.733668</v>
       </c>
       <c r="E367" s="8">
-        <v>16794155361.54</v>
+        <v>16797498911.65</v>
       </c>
       <c r="F367" s="9">
-        <v>342211</v>
+        <v>342098</v>
       </c>
       <c r="G367" s="8">
-        <v>12275318620.73</v>
+        <v>12323786785.84</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
@@ -11247,19 +11243,19 @@
         <v>736</v>
       </c>
       <c r="C368" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D368" s="10">
-        <v>0.14659</v>
+        <v>46147</v>
+      </c>
+      <c r="D368" s="7">
+        <v>0.146717</v>
       </c>
       <c r="E368" s="8">
-        <v>31245034487.91</v>
+        <v>31183749020.61</v>
       </c>
       <c r="F368" s="9">
-        <v>93328</v>
+        <v>93266</v>
       </c>
       <c r="G368" s="8">
-        <v>4580206101.62</v>
+        <v>4575175378.92</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
@@ -11270,19 +11266,19 @@
         <v>738</v>
       </c>
       <c r="C369" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D369" s="7">
-        <v>0.170611</v>
+        <v>0.170468</v>
       </c>
       <c r="E369" s="8">
-        <v>2082973766.6</v>
+        <v>2083070979.82</v>
       </c>
       <c r="F369" s="9">
-        <v>7374</v>
+        <v>7378</v>
       </c>
       <c r="G369" s="8">
-        <v>355378635.69</v>
+        <v>355096769.99</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
@@ -11293,19 +11289,19 @@
         <v>740</v>
       </c>
       <c r="C370" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D370" s="7">
-        <v>0.383555</v>
+        <v>0.383961</v>
       </c>
       <c r="E370" s="8">
-        <v>4941256014.51</v>
+        <v>4954376966.19</v>
       </c>
       <c r="F370" s="9">
-        <v>18691</v>
+        <v>18775</v>
       </c>
       <c r="G370" s="8">
-        <v>1895245635.03</v>
+        <v>1902285988</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
@@ -11316,19 +11312,19 @@
         <v>742</v>
       </c>
       <c r="C371" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D371" s="7">
-        <v>0.772081</v>
+        <v>0.770339</v>
       </c>
       <c r="E371" s="8">
-        <v>329121064571.92</v>
+        <v>328999077775.19</v>
       </c>
       <c r="F371" s="9">
-        <v>2045939</v>
+        <v>2044869</v>
       </c>
       <c r="G371" s="8">
-        <v>254108188726.21</v>
+        <v>253440764815.35</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
@@ -11339,19 +11335,19 @@
         <v>744</v>
       </c>
       <c r="C372" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D372" s="7">
-        <v>0.158567</v>
+        <v>0.158792</v>
       </c>
       <c r="E372" s="8">
-        <v>23930960780.49</v>
+        <v>23940344803.47</v>
       </c>
       <c r="F372" s="9">
-        <v>109267</v>
+        <v>109336</v>
       </c>
       <c r="G372" s="8">
-        <v>3794668846.42</v>
+        <v>3801529928.67</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
@@ -11362,19 +11358,19 @@
         <v>746</v>
       </c>
       <c r="C373" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D373" s="7">
-        <v>0.193945</v>
+        <v>0.193036</v>
       </c>
       <c r="E373" s="8">
-        <v>3608222522.49</v>
+        <v>3602346928.3</v>
       </c>
       <c r="F373" s="9">
-        <v>11544</v>
+        <v>11527</v>
       </c>
       <c r="G373" s="8">
-        <v>699798239.46</v>
+        <v>695382821.55</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
@@ -11385,19 +11381,19 @@
         <v>748</v>
       </c>
       <c r="C374" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D374" s="7">
-        <v>0.414436</v>
+        <v>0.416505</v>
       </c>
       <c r="E374" s="8">
-        <v>55920332839.9</v>
+        <v>55769154239.97</v>
       </c>
       <c r="F374" s="9">
-        <v>290357</v>
+        <v>289753</v>
       </c>
       <c r="G374" s="8">
-        <v>23175373731.47</v>
+        <v>23228139817.21</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
@@ -11408,19 +11404,19 @@
         <v>750</v>
       </c>
       <c r="C375" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D375" s="7">
-        <v>0.525925</v>
+        <v>0.525022</v>
       </c>
       <c r="E375" s="8">
-        <v>1258614722.43</v>
+        <v>1259671913.61</v>
       </c>
       <c r="F375" s="9">
-        <v>14245</v>
+        <v>14257</v>
       </c>
       <c r="G375" s="8">
-        <v>661937413.44</v>
+        <v>661356002.61</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
@@ -11431,19 +11427,19 @@
         <v>752</v>
       </c>
       <c r="C376" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D376" s="7">
-        <v>0.186321</v>
+        <v>0.185364</v>
       </c>
       <c r="E376" s="8">
-        <v>6839246587.42</v>
+        <v>6832756865.79</v>
       </c>
       <c r="F376" s="9">
-        <v>16272</v>
+        <v>16267</v>
       </c>
       <c r="G376" s="8">
-        <v>1274295260.37</v>
+        <v>1266547443.46</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
@@ -11454,19 +11450,19 @@
         <v>754</v>
       </c>
       <c r="C377" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D377" s="7">
-        <v>0.118929</v>
+        <v>0.119187</v>
       </c>
       <c r="E377" s="8">
-        <v>7604671763.19</v>
+        <v>7590001627.61</v>
       </c>
       <c r="F377" s="9">
-        <v>23955</v>
+        <v>23930</v>
       </c>
       <c r="G377" s="8">
-        <v>904412906.48</v>
+        <v>904627268.49</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
@@ -11477,19 +11473,19 @@
         <v>756</v>
       </c>
       <c r="C378" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D378" s="7">
-        <v>0.179023</v>
+        <v>46147</v>
+      </c>
+      <c r="D378" s="10">
+        <v>0.17985</v>
       </c>
       <c r="E378" s="8">
-        <v>14162111330.75</v>
+        <v>14153979899.28</v>
       </c>
       <c r="F378" s="9">
-        <v>50881</v>
+        <v>50834</v>
       </c>
       <c r="G378" s="8">
-        <v>2535343842.53</v>
+        <v>2545592397.6</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
@@ -11500,19 +11496,19 @@
         <v>758</v>
       </c>
       <c r="C379" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D379" s="7">
-        <v>0.088517</v>
+        <v>46147</v>
+      </c>
+      <c r="D379" s="10">
+        <v>0.08854</v>
       </c>
       <c r="E379" s="8">
-        <v>396762348338.77</v>
+        <v>396658536209.31</v>
       </c>
       <c r="F379" s="9">
-        <v>1945566</v>
+        <v>1945312</v>
       </c>
       <c r="G379" s="8">
-        <v>35120186433.37</v>
+        <v>35120084076.15</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
@@ -11523,19 +11519,19 @@
         <v>760</v>
       </c>
       <c r="C380" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D380" s="7">
-        <v>0.152093</v>
+        <v>0.151229</v>
       </c>
       <c r="E380" s="8">
-        <v>1164066225.96</v>
+        <v>1163865783.24</v>
       </c>
       <c r="F380" s="9">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="G380" s="8">
-        <v>177046514.51</v>
+        <v>176009955.82</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
@@ -11546,19 +11542,19 @@
         <v>762</v>
       </c>
       <c r="C381" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D381" s="7">
-        <v>0.189725</v>
+        <v>0.189749</v>
       </c>
       <c r="E381" s="8">
-        <v>1030272531.84</v>
+        <v>1029491627.93</v>
       </c>
       <c r="F381" s="9">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="G381" s="8">
-        <v>195468121.68</v>
+        <v>195345490.06</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
@@ -11569,19 +11565,19 @@
         <v>764</v>
       </c>
       <c r="C382" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D382" s="10">
-        <v>0.17303</v>
+        <v>46147</v>
+      </c>
+      <c r="D382" s="7">
+        <v>0.172873</v>
       </c>
       <c r="E382" s="8">
-        <v>586648870.86</v>
+        <v>586717246.36</v>
       </c>
       <c r="F382" s="9">
         <v>1720</v>
       </c>
       <c r="G382" s="8">
-        <v>101507743.83</v>
+        <v>101427340.77</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
@@ -11592,19 +11588,19 @@
         <v>766</v>
       </c>
       <c r="C383" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D383" s="7">
-        <v>0.091872</v>
+        <v>0.091841</v>
       </c>
       <c r="E383" s="8">
-        <v>97849083488.23</v>
+        <v>97864130166.62</v>
       </c>
       <c r="F383" s="9">
-        <v>665090</v>
+        <v>665082</v>
       </c>
       <c r="G383" s="8">
-        <v>8989612276.7</v>
+        <v>8987918210.11</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
@@ -11615,19 +11611,19 @@
         <v>768</v>
       </c>
       <c r="C384" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D384" s="7">
-        <v>0.089903</v>
+        <v>0.089995</v>
       </c>
       <c r="E384" s="8">
-        <v>42306597292.82</v>
+        <v>42199884701</v>
       </c>
       <c r="F384" s="9">
-        <v>441724</v>
+        <v>440755</v>
       </c>
       <c r="G384" s="8">
-        <v>3803508237.16</v>
+        <v>3797769522.92</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
@@ -11638,19 +11634,19 @@
         <v>770</v>
       </c>
       <c r="C385" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D385" s="10">
-        <v>0.09427</v>
+        <v>46147</v>
+      </c>
+      <c r="D385" s="7">
+        <v>0.094361</v>
       </c>
       <c r="E385" s="8">
-        <v>16515522140.27</v>
+        <v>16531878822.34</v>
       </c>
       <c r="F385" s="9">
-        <v>124527</v>
+        <v>127257</v>
       </c>
       <c r="G385" s="8">
-        <v>1556915288.43</v>
+        <v>1559964483.36</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
@@ -11661,19 +11657,19 @@
         <v>772</v>
       </c>
       <c r="C386" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D386" s="7">
-        <v>0.262294</v>
+        <v>0.261368</v>
       </c>
       <c r="E386" s="8">
-        <v>3524448097.93</v>
+        <v>3523823806.95</v>
       </c>
       <c r="F386" s="9">
-        <v>10557</v>
+        <v>10558</v>
       </c>
       <c r="G386" s="8">
-        <v>924439964.26</v>
+        <v>921014104.62</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
@@ -11684,19 +11680,19 @@
         <v>774</v>
       </c>
       <c r="C387" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D387" s="7">
-        <v>0.190354</v>
+        <v>0.190662</v>
       </c>
       <c r="E387" s="8">
-        <v>2311692860.84</v>
+        <v>2309885205.63</v>
       </c>
       <c r="F387" s="9">
-        <v>7139</v>
+        <v>7128</v>
       </c>
       <c r="G387" s="8">
-        <v>440040223.03</v>
+        <v>440407951.8</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
@@ -11707,19 +11703,19 @@
         <v>776</v>
       </c>
       <c r="C388" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D388" s="7">
-        <v>0.173107</v>
+        <v>0.173515</v>
       </c>
       <c r="E388" s="8">
-        <v>2469272213.58</v>
+        <v>2471745980.17</v>
       </c>
       <c r="F388" s="9">
-        <v>7638</v>
+        <v>7636</v>
       </c>
       <c r="G388" s="8">
-        <v>427448501.16</v>
+        <v>428885688.82</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -11730,19 +11726,19 @@
         <v>778</v>
       </c>
       <c r="C389" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D389" s="7">
-        <v>0.099114</v>
+        <v>0.099249</v>
       </c>
       <c r="E389" s="8">
-        <v>3836091155.17</v>
+        <v>3831158030.87</v>
       </c>
       <c r="F389" s="9">
-        <v>7252</v>
+        <v>7243</v>
       </c>
       <c r="G389" s="8">
-        <v>380208742.47</v>
+        <v>380240214.01</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
@@ -11753,19 +11749,19 @@
         <v>780</v>
       </c>
       <c r="C390" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D390" s="7">
-        <v>0.228804</v>
+        <v>0.229683</v>
       </c>
       <c r="E390" s="8">
-        <v>1489318204.21</v>
+        <v>1491949055.86</v>
       </c>
       <c r="F390" s="9">
-        <v>5824</v>
+        <v>5827</v>
       </c>
       <c r="G390" s="8">
-        <v>340761341.45</v>
+        <v>342674882.09</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
@@ -11776,19 +11772,19 @@
         <v>782</v>
       </c>
       <c r="C391" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D391" s="7">
-        <v>0.322247</v>
+        <v>0.323954</v>
       </c>
       <c r="E391" s="8">
-        <v>1902077404.49</v>
+        <v>1904494978.17</v>
       </c>
       <c r="F391" s="9">
-        <v>6310</v>
+        <v>6315</v>
       </c>
       <c r="G391" s="8">
-        <v>612939676.93</v>
+        <v>616968745.82</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
@@ -11799,19 +11795,19 @@
         <v>784</v>
       </c>
       <c r="C392" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D392" s="7">
-        <v>0.272937</v>
+        <v>0.273916</v>
       </c>
       <c r="E392" s="8">
-        <v>13950428415.23</v>
+        <v>13991885614.65</v>
       </c>
       <c r="F392" s="9">
-        <v>66951</v>
+        <v>67144</v>
       </c>
       <c r="G392" s="8">
-        <v>3807585130.56</v>
+        <v>3832596020.95</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
@@ -11822,19 +11818,19 @@
         <v>786</v>
       </c>
       <c r="C393" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D393" s="7">
-        <v>0.058439</v>
+        <v>0.059903</v>
       </c>
       <c r="E393" s="8">
-        <v>55376697487.44</v>
+        <v>55978319364.95</v>
       </c>
       <c r="F393" s="9">
-        <v>41279</v>
+        <v>41424</v>
       </c>
       <c r="G393" s="8">
-        <v>3236162495.8</v>
+        <v>3353271343.45</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
@@ -11845,19 +11841,19 @@
         <v>788</v>
       </c>
       <c r="C394" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D394" s="7">
-        <v>0.336834</v>
+        <v>0.337757</v>
       </c>
       <c r="E394" s="8">
-        <v>13433793150.45</v>
+        <v>13437187621.62</v>
       </c>
       <c r="F394" s="9">
-        <v>216540</v>
+        <v>216629</v>
       </c>
       <c r="G394" s="8">
-        <v>4524953226.76</v>
+        <v>4538508186.49</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
@@ -11868,19 +11864,19 @@
         <v>790</v>
       </c>
       <c r="C395" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D395" s="7">
-        <v>0.371049</v>
+        <v>0.372104</v>
       </c>
       <c r="E395" s="8">
-        <v>4736254908.93</v>
+        <v>4742691649.08</v>
       </c>
       <c r="F395" s="9">
-        <v>53146</v>
+        <v>53183</v>
       </c>
       <c r="G395" s="8">
-        <v>1757381064.3</v>
+        <v>1764772874.44</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
@@ -11891,19 +11887,19 @@
         <v>792</v>
       </c>
       <c r="C396" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D396" s="7">
-        <v>0.215722</v>
+        <v>0.213926</v>
       </c>
       <c r="E396" s="8">
-        <v>68928230698.1</v>
+        <v>68891125376.45</v>
       </c>
       <c r="F396" s="9">
-        <v>518832</v>
+        <v>518516</v>
       </c>
       <c r="G396" s="8">
-        <v>14869369453.17</v>
+        <v>14737581270.68</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -11914,19 +11910,19 @@
         <v>794</v>
       </c>
       <c r="C397" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D397" s="7">
-        <v>0.132198</v>
+        <v>46147</v>
+      </c>
+      <c r="D397" s="10">
+        <v>0.13255</v>
       </c>
       <c r="E397" s="8">
-        <v>12844947506.65</v>
+        <v>12837136009.29</v>
       </c>
       <c r="F397" s="9">
-        <v>45296</v>
+        <v>45271</v>
       </c>
       <c r="G397" s="8">
-        <v>1698075415.84</v>
+        <v>1701562885.93</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
@@ -11937,19 +11933,19 @@
         <v>796</v>
       </c>
       <c r="C398" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D398" s="7">
-        <v>0.063137</v>
+        <v>0.063271</v>
       </c>
       <c r="E398" s="8">
-        <v>58476366264.57</v>
+        <v>58488858527.81</v>
       </c>
       <c r="F398" s="9">
-        <v>323737</v>
+        <v>323582</v>
       </c>
       <c r="G398" s="8">
-        <v>3692043154.63</v>
+        <v>3700652087.64</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>05.05.2026 18:25:09</t>
+    <t>06.05.2026 18:19:52</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2917,19 +2917,19 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D6" s="7">
-        <v>0.100989</v>
+        <v>0.101226</v>
       </c>
       <c r="E6" s="8">
-        <v>47344239875.61</v>
+        <v>47579628598.11</v>
       </c>
       <c r="F6" s="9">
-        <v>644229</v>
+        <v>645057</v>
       </c>
       <c r="G6" s="8">
-        <v>4781255512.53</v>
+        <v>4816296800.18</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2940,19 +2940,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D7" s="7">
-        <v>0.403774</v>
+        <v>0.404792</v>
       </c>
       <c r="E7" s="8">
-        <v>17128958656.19</v>
+        <v>17151022173.55</v>
       </c>
       <c r="F7" s="9">
-        <v>151562</v>
+        <v>151584</v>
       </c>
       <c r="G7" s="8">
-        <v>6916224955.01</v>
+        <v>6942604489.57</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2963,19 +2963,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D8" s="7">
-        <v>0.086569</v>
+        <v>0.086747</v>
       </c>
       <c r="E8" s="8">
-        <v>7955291794.53</v>
+        <v>8009359340.36</v>
       </c>
       <c r="F8" s="9">
-        <v>141851</v>
+        <v>142365</v>
       </c>
       <c r="G8" s="8">
-        <v>688681619.28</v>
+        <v>694785455.31</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2986,19 +2986,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D9" s="7">
-        <v>0.368919</v>
+        <v>0.369276</v>
       </c>
       <c r="E9" s="8">
-        <v>142735406277.45</v>
+        <v>142567907399.95</v>
       </c>
       <c r="F9" s="9">
-        <v>488189</v>
+        <v>489261</v>
       </c>
       <c r="G9" s="8">
-        <v>52657812628.14</v>
+        <v>52646940382.91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3009,19 +3009,19 @@
         <v>20</v>
       </c>
       <c r="C10" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D10" s="7">
-        <v>0.332075</v>
+        <v>0.331841</v>
       </c>
       <c r="E10" s="8">
-        <v>23058595155.87</v>
+        <v>23093993324.31</v>
       </c>
       <c r="F10" s="9">
-        <v>329203</v>
+        <v>329505</v>
       </c>
       <c r="G10" s="8">
-        <v>7657177647.01</v>
+        <v>7663541380.75</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3032,19 +3032,19 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D11" s="7">
-        <v>0.999491</v>
+        <v>1.007249</v>
       </c>
       <c r="E11" s="8">
-        <v>11578466747.81</v>
+        <v>11585860336.04</v>
       </c>
       <c r="F11" s="9">
-        <v>288886</v>
+        <v>289147</v>
       </c>
       <c r="G11" s="8">
-        <v>11572571333.87</v>
+        <v>11669844335.29</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3055,19 +3055,19 @@
         <v>24</v>
       </c>
       <c r="C12" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D12" s="7">
-        <v>0.700204</v>
+        <v>0.698334</v>
       </c>
       <c r="E12" s="8">
-        <v>136752353306.1</v>
+        <v>136686976660.39</v>
       </c>
       <c r="F12" s="9">
-        <v>726088</v>
+        <v>726359</v>
       </c>
       <c r="G12" s="8">
-        <v>95754500122.41</v>
+        <v>95453154490.24</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3078,19 +3078,19 @@
         <v>26</v>
       </c>
       <c r="C13" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D13" s="7">
-        <v>2.004016</v>
+        <v>2.027999</v>
       </c>
       <c r="E13" s="8">
-        <v>1363788550.2</v>
+        <v>1369522219.3</v>
       </c>
       <c r="F13" s="9">
-        <v>32560</v>
+        <v>32847</v>
       </c>
       <c r="G13" s="8">
-        <v>2733054065.39</v>
+        <v>2777390352.43</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3101,19 +3101,19 @@
         <v>28</v>
       </c>
       <c r="C14" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D14" s="7">
-        <v>0.137138</v>
+        <v>0.137429</v>
       </c>
       <c r="E14" s="8">
-        <v>249831842</v>
+        <v>242548524.25</v>
       </c>
       <c r="F14" s="9">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G14" s="8">
-        <v>34261471.54</v>
+        <v>33333087.7</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3124,19 +3124,19 @@
         <v>30</v>
       </c>
       <c r="C15" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D15" s="7">
-        <v>1.370301</v>
+        <v>1.385911</v>
       </c>
       <c r="E15" s="8">
-        <v>16138286135.12</v>
+        <v>16179289126.89</v>
       </c>
       <c r="F15" s="9">
-        <v>486864</v>
+        <v>487798</v>
       </c>
       <c r="G15" s="8">
-        <v>22114314742.08</v>
+        <v>22423056264.69</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3147,19 +3147,19 @@
         <v>32</v>
       </c>
       <c r="C16" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D16" s="7">
-        <v>0.092503</v>
+        <v>0.092697</v>
       </c>
       <c r="E16" s="8">
-        <v>567593050589.75</v>
+        <v>567159202767.67</v>
       </c>
       <c r="F16" s="9">
-        <v>1958593</v>
+        <v>1957515</v>
       </c>
       <c r="G16" s="8">
-        <v>52503960890.6</v>
+        <v>52573904422.5</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3170,19 +3170,19 @@
         <v>34</v>
       </c>
       <c r="C17" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D17" s="7">
-        <v>0.345915</v>
+        <v>0.345792</v>
       </c>
       <c r="E17" s="8">
-        <v>2120019174.47</v>
+        <v>2128769113.85</v>
       </c>
       <c r="F17" s="9">
-        <v>13359</v>
+        <v>13490</v>
       </c>
       <c r="G17" s="8">
-        <v>733346305.79</v>
+        <v>736110917.49</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3193,19 +3193,19 @@
         <v>36</v>
       </c>
       <c r="C18" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D18" s="7">
-        <v>0.145277</v>
+        <v>0.145644</v>
       </c>
       <c r="E18" s="8">
-        <v>32990222939.03</v>
+        <v>33017693822.63</v>
       </c>
       <c r="F18" s="9">
-        <v>239170</v>
+        <v>239065</v>
       </c>
       <c r="G18" s="8">
-        <v>4792722271.72</v>
+        <v>4808818638.48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3216,19 +3216,19 @@
         <v>38</v>
       </c>
       <c r="C19" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D19" s="7">
-        <v>0.366301</v>
+        <v>0.367852</v>
       </c>
       <c r="E19" s="8">
-        <v>1423563765.39</v>
+        <v>1424496083.79</v>
       </c>
       <c r="F19" s="9">
         <v>537</v>
       </c>
       <c r="G19" s="8">
-        <v>521452266.47</v>
+        <v>524003523.32</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3239,19 +3239,19 @@
         <v>40</v>
       </c>
       <c r="C20" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D20" s="7">
-        <v>0.138233</v>
+        <v>0.138748</v>
       </c>
       <c r="E20" s="8">
-        <v>14754983550.22</v>
+        <v>14755172104.43</v>
       </c>
       <c r="F20" s="9">
-        <v>525146</v>
+        <v>524953</v>
       </c>
       <c r="G20" s="8">
-        <v>2039632999.45</v>
+        <v>2047254536</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3262,19 +3262,19 @@
         <v>42</v>
       </c>
       <c r="C21" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0.096382</v>
+        <v>46148</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0.09647</v>
       </c>
       <c r="E21" s="8">
-        <v>510594682399.49</v>
+        <v>510074270425.21</v>
       </c>
       <c r="F21" s="9">
-        <v>2306469</v>
+        <v>2304430</v>
       </c>
       <c r="G21" s="8">
-        <v>49212013174.14</v>
+        <v>49206925797.46</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3285,19 +3285,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D22" s="7">
-        <v>0.398952</v>
+        <v>0.402535</v>
       </c>
       <c r="E22" s="8">
-        <v>3385175182.05</v>
+        <v>3413958065.1</v>
       </c>
       <c r="F22" s="9">
-        <v>19200</v>
+        <v>19300</v>
       </c>
       <c r="G22" s="8">
-        <v>1350522387.91</v>
+        <v>1374236617.04</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3308,19 +3308,19 @@
         <v>46</v>
       </c>
       <c r="C23" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D23" s="7">
-        <v>0.092608</v>
+        <v>0.092981</v>
       </c>
       <c r="E23" s="8">
-        <v>577925086.7</v>
+        <v>576664141.18</v>
       </c>
       <c r="F23" s="9">
-        <v>4611</v>
+        <v>4609</v>
       </c>
       <c r="G23" s="8">
-        <v>53520266.64</v>
+        <v>53618714.11</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3331,19 +3331,19 @@
         <v>48</v>
       </c>
       <c r="C24" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D24" s="7">
-        <v>0.224758</v>
+        <v>0.226001</v>
       </c>
       <c r="E24" s="8">
-        <v>1213759574.5</v>
+        <v>1216450225.59</v>
       </c>
       <c r="F24" s="9">
-        <v>4964</v>
+        <v>4970</v>
       </c>
       <c r="G24" s="8">
-        <v>272802591.73</v>
+        <v>274918918.11</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3354,19 +3354,19 @@
         <v>50</v>
       </c>
       <c r="C25" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D25" s="7">
-        <v>0.105333</v>
+        <v>0.105376</v>
       </c>
       <c r="E25" s="8">
-        <v>66565128271.21</v>
+        <v>66640492097.62</v>
       </c>
       <c r="F25" s="9">
-        <v>764452</v>
+        <v>764641</v>
       </c>
       <c r="G25" s="8">
-        <v>7011522725.66</v>
+        <v>7022282839.2</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3377,19 +3377,19 @@
         <v>52</v>
       </c>
       <c r="C26" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D26" s="7">
-        <v>0.097974</v>
+        <v>46148</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0.09813</v>
       </c>
       <c r="E26" s="8">
-        <v>1672765675.24</v>
+        <v>1677153468.76</v>
       </c>
       <c r="F26" s="9">
-        <v>3226</v>
+        <v>3223</v>
       </c>
       <c r="G26" s="8">
-        <v>163887736.8</v>
+        <v>164578921.6</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3400,19 +3400,19 @@
         <v>54</v>
       </c>
       <c r="C27" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D27" s="7">
-        <v>0.093578</v>
+        <v>46148</v>
+      </c>
+      <c r="D27" s="10">
+        <v>0.09366</v>
       </c>
       <c r="E27" s="8">
-        <v>61966627083</v>
+        <v>61898279000.13</v>
       </c>
       <c r="F27" s="9">
-        <v>715845</v>
+        <v>715460</v>
       </c>
       <c r="G27" s="8">
-        <v>5798738184.56</v>
+        <v>5797363282.87</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3423,19 +3423,19 @@
         <v>56</v>
       </c>
       <c r="C28" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D28" s="7">
-        <v>0.386086</v>
+        <v>0.385979</v>
       </c>
       <c r="E28" s="8">
-        <v>1048236878.43</v>
+        <v>1045186947.96</v>
       </c>
       <c r="F28" s="9">
-        <v>7874</v>
+        <v>7911</v>
       </c>
       <c r="G28" s="8">
-        <v>404709452.09</v>
+        <v>403420427.7</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3446,19 +3446,19 @@
         <v>58</v>
       </c>
       <c r="C29" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D29" s="7">
-        <v>0.645822</v>
+        <v>0.645635</v>
       </c>
       <c r="E29" s="8">
-        <v>211002761.82</v>
+        <v>211358494.86</v>
       </c>
       <c r="F29" s="9">
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="G29" s="8">
-        <v>136270328.63</v>
+        <v>136460391.46</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3469,19 +3469,19 @@
         <v>60</v>
       </c>
       <c r="C30" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D30" s="7">
-        <v>2.355195</v>
+        <v>2.380953</v>
       </c>
       <c r="E30" s="8">
-        <v>847088960.84</v>
+        <v>846955510.71</v>
       </c>
       <c r="F30" s="9">
-        <v>19542</v>
+        <v>19595</v>
       </c>
       <c r="G30" s="8">
-        <v>1995060097.42</v>
+        <v>2016561015.49</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3492,19 +3492,19 @@
         <v>62</v>
       </c>
       <c r="C31" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D31" s="7">
-        <v>0.523707</v>
+        <v>46148</v>
+      </c>
+      <c r="D31" s="10">
+        <v>0.52437</v>
       </c>
       <c r="E31" s="8">
-        <v>2411101093.34</v>
+        <v>2408324691.06</v>
       </c>
       <c r="F31" s="9">
-        <v>14113</v>
+        <v>14232</v>
       </c>
       <c r="G31" s="8">
-        <v>1262711070.69</v>
+        <v>1262853480.57</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3515,19 +3515,19 @@
         <v>64</v>
       </c>
       <c r="C32" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D32" s="7">
-        <v>0.846179</v>
+        <v>0.843486</v>
       </c>
       <c r="E32" s="8">
-        <v>12372268635.32</v>
+        <v>12365413198.33</v>
       </c>
       <c r="F32" s="9">
-        <v>77086</v>
+        <v>77239</v>
       </c>
       <c r="G32" s="8">
-        <v>10469159499.64</v>
+        <v>10430055099.24</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3538,19 +3538,19 @@
         <v>66</v>
       </c>
       <c r="C33" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D33" s="7">
-        <v>0.264163</v>
+        <v>0.264883</v>
       </c>
       <c r="E33" s="8">
-        <v>1309401045.09</v>
+        <v>1310059237.45</v>
       </c>
       <c r="F33" s="9">
-        <v>16187</v>
+        <v>16195</v>
       </c>
       <c r="G33" s="8">
-        <v>345895745.13</v>
+        <v>347012964.31</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3561,19 +3561,19 @@
         <v>68</v>
       </c>
       <c r="C34" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D34" s="7">
-        <v>0.125458</v>
+        <v>46148</v>
+      </c>
+      <c r="D34" s="10">
+        <v>0.12577</v>
       </c>
       <c r="E34" s="8">
-        <v>3327353326.67</v>
+        <v>3330589592.87</v>
       </c>
       <c r="F34" s="9">
-        <v>53914</v>
+        <v>53925</v>
       </c>
       <c r="G34" s="8">
-        <v>417441732.23</v>
+        <v>418888568.42</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3584,19 +3584,19 @@
         <v>70</v>
       </c>
       <c r="C35" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D35" s="7">
-        <v>0.175452</v>
+        <v>0.175775</v>
       </c>
       <c r="E35" s="8">
-        <v>10714917468.79</v>
+        <v>10732355431.38</v>
       </c>
       <c r="F35" s="9">
-        <v>36592</v>
+        <v>36647</v>
       </c>
       <c r="G35" s="8">
-        <v>1879954275.6</v>
+        <v>1886479887.76</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3607,19 +3607,19 @@
         <v>72</v>
       </c>
       <c r="C36" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D36" s="7">
-        <v>0.202407</v>
+        <v>46148</v>
+      </c>
+      <c r="D36" s="10">
+        <v>0.20371</v>
       </c>
       <c r="E36" s="8">
-        <v>1493491332.97</v>
+        <v>1493919849.53</v>
       </c>
       <c r="F36" s="9">
-        <v>32745</v>
+        <v>32744</v>
       </c>
       <c r="G36" s="8">
-        <v>302293006.06</v>
+        <v>304327033.22</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3630,19 +3630,19 @@
         <v>74</v>
       </c>
       <c r="C37" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D37" s="7">
-        <v>0.830276</v>
+        <v>0.839074</v>
       </c>
       <c r="E37" s="8">
-        <v>2447614421.88</v>
+        <v>2446821152.37</v>
       </c>
       <c r="F37" s="9">
-        <v>52342</v>
+        <v>52354</v>
       </c>
       <c r="G37" s="8">
-        <v>2032196639.26</v>
+        <v>2053063982.03</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3653,19 +3653,19 @@
         <v>76</v>
       </c>
       <c r="C38" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D38" s="7">
-        <v>0.169658</v>
+        <v>0.169903</v>
       </c>
       <c r="E38" s="8">
-        <v>3692133745.02</v>
+        <v>3690827715.74</v>
       </c>
       <c r="F38" s="9">
-        <v>53205</v>
+        <v>53198</v>
       </c>
       <c r="G38" s="8">
-        <v>626398603.87</v>
+        <v>627082178.17</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3676,19 +3676,19 @@
         <v>78</v>
       </c>
       <c r="C39" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D39" s="7">
-        <v>0.107163</v>
+        <v>46148</v>
+      </c>
+      <c r="D39" s="10">
+        <v>0.10767</v>
       </c>
       <c r="E39" s="8">
-        <v>8161693310.31</v>
+        <v>8162041319.18</v>
       </c>
       <c r="F39" s="9">
-        <v>96888</v>
+        <v>96889</v>
       </c>
       <c r="G39" s="8">
-        <v>874627560.04</v>
+        <v>878806526.93</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3699,19 +3699,19 @@
         <v>80</v>
       </c>
       <c r="C40" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D40" s="10">
-        <v>0.33736</v>
+        <v>46148</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0.336995</v>
       </c>
       <c r="E40" s="8">
-        <v>14129903383.29</v>
+        <v>14078210718.44</v>
       </c>
       <c r="F40" s="9">
-        <v>157530</v>
+        <v>157186</v>
       </c>
       <c r="G40" s="8">
-        <v>4766858941.85</v>
+        <v>4744282034.49</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3722,19 +3722,19 @@
         <v>82</v>
       </c>
       <c r="C41" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D41" s="7">
-        <v>0.365757</v>
+        <v>0.366119</v>
       </c>
       <c r="E41" s="8">
-        <v>77866004013.02</v>
+        <v>78125325752.82</v>
       </c>
       <c r="F41" s="9">
-        <v>176450</v>
+        <v>199738</v>
       </c>
       <c r="G41" s="8">
-        <v>28480042007.78</v>
+        <v>28603185052.01</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3745,19 +3745,19 @@
         <v>84</v>
       </c>
       <c r="C42" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D42" s="7">
-        <v>0.956205</v>
+        <v>46148</v>
+      </c>
+      <c r="D42" s="10">
+        <v>0.95623</v>
       </c>
       <c r="E42" s="8">
-        <v>12828644089.11</v>
+        <v>12811301243.95</v>
       </c>
       <c r="F42" s="9">
-        <v>234889</v>
+        <v>234412</v>
       </c>
       <c r="G42" s="8">
-        <v>12266816830.51</v>
+        <v>12250553045.49</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3768,19 +3768,19 @@
         <v>86</v>
       </c>
       <c r="C43" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D43" s="7">
-        <v>0.690224</v>
+        <v>0.688614</v>
       </c>
       <c r="E43" s="8">
-        <v>8870243365.66</v>
+        <v>8862437482.59</v>
       </c>
       <c r="F43" s="9">
-        <v>121291</v>
+        <v>121216</v>
       </c>
       <c r="G43" s="8">
-        <v>6122453582.78</v>
+        <v>6102796936.99</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3791,19 +3791,19 @@
         <v>88</v>
       </c>
       <c r="C44" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D44" s="7">
-        <v>2.938954</v>
+        <v>2.961703</v>
       </c>
       <c r="E44" s="8">
-        <v>8473525410.21</v>
+        <v>8446862601.05</v>
       </c>
       <c r="F44" s="9">
-        <v>365924</v>
+        <v>366137</v>
       </c>
       <c r="G44" s="8">
-        <v>24903299224.09</v>
+        <v>25017098384.52</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3814,19 +3814,19 @@
         <v>90</v>
       </c>
       <c r="C45" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D45" s="7">
-        <v>1.136855</v>
+        <v>1.139951</v>
       </c>
       <c r="E45" s="8">
-        <v>3669098523.64</v>
+        <v>3671631864.25</v>
       </c>
       <c r="F45" s="9">
-        <v>85772</v>
+        <v>85794</v>
       </c>
       <c r="G45" s="8">
-        <v>4171231856.06</v>
+        <v>4185478625.93</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3837,19 +3837,19 @@
         <v>92</v>
       </c>
       <c r="C46" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D46" s="7">
-        <v>0.422042</v>
+        <v>46148</v>
+      </c>
+      <c r="D46" s="10">
+        <v>0.42246</v>
       </c>
       <c r="E46" s="8">
-        <v>23900292039.23</v>
+        <v>23860885986.27</v>
       </c>
       <c r="F46" s="9">
-        <v>219485</v>
+        <v>219382</v>
       </c>
       <c r="G46" s="8">
-        <v>10086925174.32</v>
+        <v>10080272962.39</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3860,19 +3860,19 @@
         <v>94</v>
       </c>
       <c r="C47" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D47" s="7">
-        <v>0.999026</v>
+        <v>1.002621</v>
       </c>
       <c r="E47" s="8">
-        <v>9668556060.94</v>
+        <v>9667273082.92</v>
       </c>
       <c r="F47" s="9">
-        <v>207315</v>
+        <v>207418</v>
       </c>
       <c r="G47" s="8">
-        <v>9659141335.19</v>
+        <v>9692614810.69</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3883,19 +3883,19 @@
         <v>96</v>
       </c>
       <c r="C48" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D48" s="7">
-        <v>1.340661</v>
+        <v>1.355304</v>
       </c>
       <c r="E48" s="8">
-        <v>713987330.83</v>
+        <v>715519370.2</v>
       </c>
       <c r="F48" s="9">
-        <v>7277</v>
+        <v>7291</v>
       </c>
       <c r="G48" s="8">
-        <v>957215035.62</v>
+        <v>969745915.24</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3906,19 +3906,19 @@
         <v>98</v>
       </c>
       <c r="C49" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D49" s="7">
-        <v>0.130429</v>
+        <v>0.130586</v>
       </c>
       <c r="E49" s="8">
-        <v>93702532960.14</v>
+        <v>93836404680.74</v>
       </c>
       <c r="F49" s="9">
-        <v>208870</v>
+        <v>209139</v>
       </c>
       <c r="G49" s="8">
-        <v>12221552567.86</v>
+        <v>12253724402.13</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3929,19 +3929,19 @@
         <v>100</v>
       </c>
       <c r="C50" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D50" s="7">
-        <v>0.099602</v>
+        <v>46148</v>
+      </c>
+      <c r="D50" s="10">
+        <v>0.09971</v>
       </c>
       <c r="E50" s="8">
-        <v>14091391512.17</v>
+        <v>14019421649.81</v>
       </c>
       <c r="F50" s="9">
-        <v>127658</v>
+        <v>128351</v>
       </c>
       <c r="G50" s="8">
-        <v>1403527122.12</v>
+        <v>1397872782.72</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3952,19 +3952,19 @@
         <v>102</v>
       </c>
       <c r="C51" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D51" s="7">
-        <v>0.487911</v>
+        <v>46148</v>
+      </c>
+      <c r="D51" s="10">
+        <v>0.48967</v>
       </c>
       <c r="E51" s="8">
-        <v>20386496347.74</v>
+        <v>20375289871.46</v>
       </c>
       <c r="F51" s="9">
-        <v>136702</v>
+        <v>136647</v>
       </c>
       <c r="G51" s="8">
-        <v>9946794227.39</v>
+        <v>9977161484.02</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3975,19 +3975,19 @@
         <v>104</v>
       </c>
       <c r="C52" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D52" s="7">
-        <v>0.213055</v>
+        <v>46148</v>
+      </c>
+      <c r="D52" s="10">
+        <v>0.21415</v>
       </c>
       <c r="E52" s="8">
-        <v>2632887136.63</v>
+        <v>2641649851.16</v>
       </c>
       <c r="F52" s="9">
-        <v>10433</v>
+        <v>10454</v>
       </c>
       <c r="G52" s="8">
-        <v>560950784.67</v>
+        <v>565708037.41</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3998,19 +3998,19 @@
         <v>106</v>
       </c>
       <c r="C53" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D53" s="7">
-        <v>0.269387</v>
+        <v>0.271493</v>
       </c>
       <c r="E53" s="8">
-        <v>2888953853.79</v>
+        <v>2898889707.75</v>
       </c>
       <c r="F53" s="9">
-        <v>10739</v>
+        <v>10767</v>
       </c>
       <c r="G53" s="8">
-        <v>778247174.54</v>
+        <v>787027040.79</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -4021,19 +4021,19 @@
         <v>108</v>
       </c>
       <c r="C54" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D54" s="7">
-        <v>0.326874</v>
+        <v>0.328296</v>
       </c>
       <c r="E54" s="8">
-        <v>4531374106.22</v>
+        <v>4543644111.21</v>
       </c>
       <c r="F54" s="9">
-        <v>15908</v>
+        <v>15917</v>
       </c>
       <c r="G54" s="8">
-        <v>1481189120.57</v>
+        <v>1491662099.18</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4044,19 +4044,19 @@
         <v>110</v>
       </c>
       <c r="C55" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D55" s="10">
-        <v>0.30915</v>
+        <v>46148</v>
+      </c>
+      <c r="D55" s="11">
+        <v>0.3107</v>
       </c>
       <c r="E55" s="8">
-        <v>2567248327.81</v>
+        <v>2579014247.19</v>
       </c>
       <c r="F55" s="9">
-        <v>10190</v>
+        <v>10212</v>
       </c>
       <c r="G55" s="8">
-        <v>793665806.51</v>
+        <v>801300451.42</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -4067,19 +4067,19 @@
         <v>112</v>
       </c>
       <c r="C56" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D56" s="7">
-        <v>0.220054</v>
+        <v>46148</v>
+      </c>
+      <c r="D56" s="10">
+        <v>0.22139</v>
       </c>
       <c r="E56" s="8">
-        <v>1884490751.3</v>
+        <v>1890529309.13</v>
       </c>
       <c r="F56" s="9">
-        <v>6680</v>
+        <v>6686</v>
       </c>
       <c r="G56" s="8">
-        <v>414689090.45</v>
+        <v>418544853.28</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4090,19 +4090,19 @@
         <v>114</v>
       </c>
       <c r="C57" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D57" s="7">
-        <v>0.114638</v>
+        <v>0.114784</v>
       </c>
       <c r="E57" s="8">
-        <v>1629230390.52</v>
+        <v>1627634618.28</v>
       </c>
       <c r="F57" s="9">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="G57" s="8">
-        <v>186772415.53</v>
+        <v>186825607.75</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -4113,19 +4113,19 @@
         <v>116</v>
       </c>
       <c r="C58" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D58" s="7">
-        <v>0.306765</v>
+        <v>0.309002</v>
       </c>
       <c r="E58" s="8">
-        <v>4436092683.39</v>
+        <v>4449995044.37</v>
       </c>
       <c r="F58" s="9">
-        <v>16762</v>
+        <v>16805</v>
       </c>
       <c r="G58" s="8">
-        <v>1360837185.94</v>
+        <v>1375056056.98</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -4136,19 +4136,19 @@
         <v>118</v>
       </c>
       <c r="C59" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D59" s="7">
-        <v>0.243912</v>
+        <v>0.244745</v>
       </c>
       <c r="E59" s="8">
-        <v>2806958958.94</v>
+        <v>2814740079.2</v>
       </c>
       <c r="F59" s="9">
-        <v>11307</v>
+        <v>11341</v>
       </c>
       <c r="G59" s="8">
-        <v>684650392.34</v>
+        <v>688894405.39</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -4159,19 +4159,19 @@
         <v>120</v>
       </c>
       <c r="C60" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D60" s="7">
-        <v>0.177558</v>
+        <v>0.178795</v>
       </c>
       <c r="E60" s="8">
-        <v>180603512.28</v>
+        <v>183201808.19</v>
       </c>
       <c r="F60" s="9">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="G60" s="8">
-        <v>32067582.55</v>
+        <v>32755614.8</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -4182,19 +4182,19 @@
         <v>122</v>
       </c>
       <c r="C61" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D61" s="7">
-        <v>0.374327</v>
+        <v>0.377063</v>
       </c>
       <c r="E61" s="8">
-        <v>857523924.87</v>
+        <v>858575463.98</v>
       </c>
       <c r="F61" s="9">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="G61" s="8">
-        <v>320994203.35</v>
+        <v>323737147.25</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -4205,19 +4205,19 @@
         <v>124</v>
       </c>
       <c r="C62" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D62" s="7">
-        <v>0.073262</v>
+        <v>0.073389</v>
       </c>
       <c r="E62" s="8">
-        <v>172897250.85</v>
+        <v>173502024.4</v>
       </c>
       <c r="F62" s="9">
         <v>223</v>
       </c>
       <c r="G62" s="8">
-        <v>12666773.97</v>
+        <v>12733158.71</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -4228,19 +4228,19 @@
         <v>126</v>
       </c>
       <c r="C63" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D63" s="7">
-        <v>0.143453</v>
+        <v>0.144318</v>
       </c>
       <c r="E63" s="8">
-        <v>109574449.12</v>
+        <v>111067962.1</v>
       </c>
       <c r="F63" s="9">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G63" s="8">
-        <v>15718733.89</v>
+        <v>16029127.96</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -4251,19 +4251,19 @@
         <v>128</v>
       </c>
       <c r="C64" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D64" s="7">
-        <v>0.258309</v>
+        <v>0.259252</v>
       </c>
       <c r="E64" s="8">
-        <v>215525013.32</v>
+        <v>216031600.41</v>
       </c>
       <c r="F64" s="9">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G64" s="8">
-        <v>55672127.7</v>
+        <v>56006705.47</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4274,19 +4274,19 @@
         <v>130</v>
       </c>
       <c r="C65" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D65" s="7">
-        <v>0.333901</v>
+        <v>0.335634</v>
       </c>
       <c r="E65" s="8">
-        <v>637911785.64</v>
+        <v>638312800.68</v>
       </c>
       <c r="F65" s="9">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G65" s="8">
-        <v>212999556.32</v>
+        <v>214239763.12</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -4297,19 +4297,19 @@
         <v>132</v>
       </c>
       <c r="C66" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D66" s="7">
-        <v>0.573909</v>
+        <v>0.580594</v>
       </c>
       <c r="E66" s="8">
-        <v>12917037734.97</v>
+        <v>12902558766.14</v>
       </c>
       <c r="F66" s="9">
-        <v>127464</v>
+        <v>127379</v>
       </c>
       <c r="G66" s="8">
-        <v>7413209642.54</v>
+        <v>7491150486.56</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4320,19 +4320,19 @@
         <v>134</v>
       </c>
       <c r="C67" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D67" s="7">
-        <v>0.258453</v>
+        <v>0.260893</v>
       </c>
       <c r="E67" s="8">
-        <v>2018039419.58</v>
+        <v>2012802814.19</v>
       </c>
       <c r="F67" s="9">
         <v>6113</v>
       </c>
       <c r="G67" s="8">
-        <v>521567971.54</v>
+        <v>525125591.37</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -4343,19 +4343,19 @@
         <v>136</v>
       </c>
       <c r="C68" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D68" s="7">
-        <v>2.019153</v>
+        <v>2.027413</v>
       </c>
       <c r="E68" s="8">
-        <v>7006888688.77</v>
+        <v>7015482475.05</v>
       </c>
       <c r="F68" s="9">
-        <v>236042</v>
+        <v>236076</v>
       </c>
       <c r="G68" s="8">
-        <v>14147981144.18</v>
+        <v>14223283344.05</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -4366,19 +4366,19 @@
         <v>138</v>
       </c>
       <c r="C69" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D69" s="7">
-        <v>0.998859</v>
+        <v>1.001855</v>
       </c>
       <c r="E69" s="8">
-        <v>6513097387.62</v>
+        <v>6510156926.86</v>
       </c>
       <c r="F69" s="9">
-        <v>163276</v>
+        <v>163330</v>
       </c>
       <c r="G69" s="8">
-        <v>6505666649.6</v>
+        <v>6522232781.83</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -4389,19 +4389,19 @@
         <v>140</v>
       </c>
       <c r="C70" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D70" s="7">
-        <v>0.322083</v>
+        <v>0.325601</v>
       </c>
       <c r="E70" s="8">
-        <v>12175964879.36</v>
+        <v>12184518661.7</v>
       </c>
       <c r="F70" s="9">
-        <v>189477</v>
+        <v>189433</v>
       </c>
       <c r="G70" s="8">
-        <v>3921676476.48</v>
+        <v>3967292084.6</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4412,19 +4412,19 @@
         <v>142</v>
       </c>
       <c r="C71" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D71" s="7">
-        <v>0.098778</v>
+        <v>0.098889</v>
       </c>
       <c r="E71" s="8">
-        <v>7675240515.15</v>
+        <v>7537641443.35</v>
       </c>
       <c r="F71" s="9">
-        <v>118914</v>
+        <v>118282</v>
       </c>
       <c r="G71" s="8">
-        <v>758145885.36</v>
+        <v>745387495.13</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -4435,19 +4435,19 @@
         <v>144</v>
       </c>
       <c r="C72" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D72" s="7">
-        <v>0.095175</v>
+        <v>0.095489</v>
       </c>
       <c r="E72" s="8">
-        <v>391150585971.82</v>
+        <v>390936275891.39</v>
       </c>
       <c r="F72" s="9">
-        <v>1424169</v>
+        <v>1423660</v>
       </c>
       <c r="G72" s="8">
-        <v>37227933252.88</v>
+        <v>37330080932.62</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4458,19 +4458,19 @@
         <v>146</v>
       </c>
       <c r="C73" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D73" s="7">
-        <v>1.096778</v>
+        <v>1.095911</v>
       </c>
       <c r="E73" s="8">
-        <v>6395996911.94</v>
+        <v>6403855017.55</v>
       </c>
       <c r="F73" s="9">
-        <v>262261</v>
+        <v>262267</v>
       </c>
       <c r="G73" s="8">
-        <v>7014991482.37</v>
+        <v>7018055002.76</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4481,19 +4481,19 @@
         <v>148</v>
       </c>
       <c r="C74" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D74" s="7">
-        <v>0.508794</v>
+        <v>0.508661</v>
       </c>
       <c r="E74" s="8">
-        <v>6728219699.57</v>
+        <v>6736232682.53</v>
       </c>
       <c r="F74" s="9">
-        <v>65676</v>
+        <v>65680</v>
       </c>
       <c r="G74" s="8">
-        <v>3423280451.2</v>
+        <v>3426457842.2</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -4504,19 +4504,19 @@
         <v>150</v>
       </c>
       <c r="C75" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D75" s="7">
-        <v>1.553513</v>
+        <v>46148</v>
+      </c>
+      <c r="D75" s="10">
+        <v>1.55949</v>
       </c>
       <c r="E75" s="8">
-        <v>493682134.98</v>
+        <v>495387188.23</v>
       </c>
       <c r="F75" s="9">
-        <v>5004</v>
+        <v>5009</v>
       </c>
       <c r="G75" s="8">
-        <v>766941840.84</v>
+        <v>772551568.99</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4527,19 +4527,19 @@
         <v>152</v>
       </c>
       <c r="C76" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D76" s="7">
-        <v>0.693081</v>
+        <v>0.690825</v>
       </c>
       <c r="E76" s="8">
-        <v>212430762979.33</v>
+        <v>212640768064.73</v>
       </c>
       <c r="F76" s="9">
-        <v>720034</v>
+        <v>720612</v>
       </c>
       <c r="G76" s="8">
-        <v>147231779547.22</v>
+        <v>146897516499.65</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4550,19 +4550,19 @@
         <v>154</v>
       </c>
       <c r="C77" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D77" s="7">
-        <v>0.571137</v>
+        <v>0.574275</v>
       </c>
       <c r="E77" s="8">
-        <v>194128483.9</v>
+        <v>194094900.97</v>
       </c>
       <c r="F77" s="9">
-        <v>22328</v>
+        <v>22326</v>
       </c>
       <c r="G77" s="8">
-        <v>110874051.8</v>
+        <v>111463886.23</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4573,19 +4573,19 @@
         <v>156</v>
       </c>
       <c r="C78" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D78" s="7">
-        <v>0.297177</v>
+        <v>0.297753</v>
       </c>
       <c r="E78" s="8">
-        <v>396494848.33</v>
+        <v>395847378.68</v>
       </c>
       <c r="F78" s="9">
-        <v>33150</v>
+        <v>33146</v>
       </c>
       <c r="G78" s="8">
-        <v>117829045.22</v>
+        <v>117864567.76</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4596,19 +4596,19 @@
         <v>158</v>
       </c>
       <c r="C79" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D79" s="7">
-        <v>0.159518</v>
+        <v>0.160499</v>
       </c>
       <c r="E79" s="8">
-        <v>3112507181.36</v>
+        <v>3130729904.64</v>
       </c>
       <c r="F79" s="9">
-        <v>6950</v>
+        <v>6962</v>
       </c>
       <c r="G79" s="8">
-        <v>496500337.29</v>
+        <v>502480261.35</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4619,19 +4619,19 @@
         <v>160</v>
       </c>
       <c r="C80" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D80" s="7">
-        <v>0.334563</v>
+        <v>0.334947</v>
       </c>
       <c r="E80" s="8">
-        <v>236965919.22</v>
+        <v>239492469.14</v>
       </c>
       <c r="F80" s="9">
-        <v>20862</v>
+        <v>20848</v>
       </c>
       <c r="G80" s="8">
-        <v>79280141.9</v>
+        <v>80217319.99</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4642,19 +4642,19 @@
         <v>162</v>
       </c>
       <c r="C81" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D81" s="7">
-        <v>0.178215</v>
+        <v>0.179548</v>
       </c>
       <c r="E81" s="8">
-        <v>700493711.47</v>
+        <v>701451630.99</v>
       </c>
       <c r="F81" s="9">
         <v>2344</v>
       </c>
       <c r="G81" s="8">
-        <v>124838190</v>
+        <v>125944446.78</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4665,19 +4665,19 @@
         <v>164</v>
       </c>
       <c r="C82" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D82" s="7">
-        <v>1.844193</v>
+        <v>1.867747</v>
       </c>
       <c r="E82" s="8">
-        <v>83945765.5</v>
+        <v>83821054.58</v>
       </c>
       <c r="F82" s="9">
-        <v>13723</v>
+        <v>13722</v>
       </c>
       <c r="G82" s="8">
-        <v>154812187.82</v>
+        <v>156556549.03</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4688,19 +4688,19 @@
         <v>166</v>
       </c>
       <c r="C83" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D83" s="10">
-        <v>0.09559</v>
+        <v>46148</v>
+      </c>
+      <c r="D83" s="7">
+        <v>0.095697</v>
       </c>
       <c r="E83" s="8">
-        <v>10212978800.62</v>
+        <v>10252419882.5</v>
       </c>
       <c r="F83" s="9">
-        <v>169655</v>
+        <v>172583</v>
       </c>
       <c r="G83" s="8">
-        <v>976257176.08</v>
+        <v>981126677.6</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4711,19 +4711,19 @@
         <v>168</v>
       </c>
       <c r="C84" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D84" s="7">
-        <v>0.083837</v>
+        <v>0.083953</v>
       </c>
       <c r="E84" s="8">
-        <v>8875726775.54</v>
+        <v>9009507093.73</v>
       </c>
       <c r="F84" s="9">
-        <v>137999</v>
+        <v>138118</v>
       </c>
       <c r="G84" s="8">
-        <v>744117144.23</v>
+        <v>756371026.65</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4734,19 +4734,19 @@
         <v>170</v>
       </c>
       <c r="C85" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D85" s="7">
-        <v>0.268561</v>
+        <v>0.269417</v>
       </c>
       <c r="E85" s="8">
-        <v>4320643294.18</v>
+        <v>4343954976.72</v>
       </c>
       <c r="F85" s="9">
-        <v>79887</v>
+        <v>80216</v>
       </c>
       <c r="G85" s="8">
-        <v>1160357760.09</v>
+        <v>1170336741.8</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4757,19 +4757,19 @@
         <v>172</v>
       </c>
       <c r="C86" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D86" s="7">
-        <v>0.893982</v>
+        <v>0.903257</v>
       </c>
       <c r="E86" s="8">
-        <v>4610754197.76</v>
+        <v>4610722214.13</v>
       </c>
       <c r="F86" s="9">
-        <v>87092</v>
+        <v>87564</v>
       </c>
       <c r="G86" s="8">
-        <v>4121929913.43</v>
+        <v>4164666855.57</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4780,19 +4780,19 @@
         <v>174</v>
       </c>
       <c r="C87" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D87" s="7">
-        <v>0.223661</v>
+        <v>0.223823</v>
       </c>
       <c r="E87" s="8">
-        <v>12553393188.54</v>
+        <v>12590994855.7</v>
       </c>
       <c r="F87" s="9">
-        <v>144124</v>
+        <v>144682</v>
       </c>
       <c r="G87" s="8">
-        <v>2807701546.1</v>
+        <v>2818154569.43</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4803,19 +4803,19 @@
         <v>176</v>
       </c>
       <c r="C88" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D88" s="10">
-        <v>0.16443</v>
+        <v>46148</v>
+      </c>
+      <c r="D88" s="7">
+        <v>0.164917</v>
       </c>
       <c r="E88" s="8">
-        <v>18377333838.39</v>
+        <v>18636080343.95</v>
       </c>
       <c r="F88" s="9">
-        <v>90689</v>
+        <v>91290</v>
       </c>
       <c r="G88" s="8">
-        <v>3021790274.71</v>
+        <v>3073400249.77</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4826,19 +4826,19 @@
         <v>178</v>
       </c>
       <c r="C89" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D89" s="7">
-        <v>0.634834</v>
+        <v>0.634957</v>
       </c>
       <c r="E89" s="8">
-        <v>2268386773.26</v>
+        <v>2269649211.5</v>
       </c>
       <c r="F89" s="9">
-        <v>35882</v>
+        <v>35864</v>
       </c>
       <c r="G89" s="8">
-        <v>1440049232.33</v>
+        <v>1441129508.4</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4849,19 +4849,19 @@
         <v>180</v>
       </c>
       <c r="C90" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D90" s="10">
-        <v>0.84566</v>
+        <v>46148</v>
+      </c>
+      <c r="D90" s="7">
+        <v>0.844123</v>
       </c>
       <c r="E90" s="8">
-        <v>19177825908.08</v>
+        <v>19182892326.47</v>
       </c>
       <c r="F90" s="9">
-        <v>272424</v>
+        <v>272361</v>
       </c>
       <c r="G90" s="8">
-        <v>16217920324.46</v>
+        <v>16192729063.53</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4872,19 +4872,19 @@
         <v>182</v>
       </c>
       <c r="C91" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D91" s="7">
-        <v>0.787207</v>
+        <v>0.789075</v>
       </c>
       <c r="E91" s="8">
-        <v>3486273490.83</v>
+        <v>3492080422.73</v>
       </c>
       <c r="F91" s="9">
-        <v>29401</v>
+        <v>29616</v>
       </c>
       <c r="G91" s="8">
-        <v>2744419228.71</v>
+        <v>2755514625.51</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4895,19 +4895,19 @@
         <v>184</v>
       </c>
       <c r="C92" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D92" s="7">
-        <v>0.832114</v>
+        <v>0.831038</v>
       </c>
       <c r="E92" s="8">
-        <v>12340270408.78</v>
+        <v>12345175395.43</v>
       </c>
       <c r="F92" s="9">
-        <v>188723</v>
+        <v>188658</v>
       </c>
       <c r="G92" s="8">
-        <v>10268508304.13</v>
+        <v>10259315042.98</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4918,19 +4918,19 @@
         <v>186</v>
       </c>
       <c r="C93" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D93" s="7">
-        <v>0.088053</v>
+        <v>0.088239</v>
       </c>
       <c r="E93" s="8">
-        <v>7507626795.38</v>
+        <v>7521378062.44</v>
       </c>
       <c r="F93" s="9">
-        <v>154884</v>
+        <v>154918</v>
       </c>
       <c r="G93" s="8">
-        <v>661067412.78</v>
+        <v>663677524.78</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4941,19 +4941,19 @@
         <v>188</v>
       </c>
       <c r="C94" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D94" s="7">
-        <v>0.119607</v>
+        <v>46148</v>
+      </c>
+      <c r="D94" s="10">
+        <v>0.11994</v>
       </c>
       <c r="E94" s="8">
-        <v>11948275146.86</v>
+        <v>11957757550.21</v>
       </c>
       <c r="F94" s="9">
-        <v>33306</v>
+        <v>33332</v>
       </c>
       <c r="G94" s="8">
-        <v>1429099079.82</v>
+        <v>1434207722.19</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4964,19 +4964,19 @@
         <v>190</v>
       </c>
       <c r="C95" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D95" s="7">
-        <v>0.127933</v>
+        <v>0.128066</v>
       </c>
       <c r="E95" s="8">
-        <v>71677577134.38</v>
+        <v>71588330672.27</v>
       </c>
       <c r="F95" s="9">
-        <v>212220</v>
+        <v>212347</v>
       </c>
       <c r="G95" s="8">
-        <v>9169962379.73</v>
+        <v>9168009025.58</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4987,19 +4987,19 @@
         <v>192</v>
       </c>
       <c r="C96" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D96" s="7">
-        <v>0.467645</v>
+        <v>0.472949</v>
       </c>
       <c r="E96" s="8">
-        <v>31802302843.77</v>
+        <v>31939640562.02</v>
       </c>
       <c r="F96" s="9">
-        <v>282407</v>
+        <v>283467</v>
       </c>
       <c r="G96" s="8">
-        <v>14872190984.2</v>
+        <v>15105811232.31</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -5010,19 +5010,19 @@
         <v>194</v>
       </c>
       <c r="C97" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D97" s="7">
-        <v>0.096466</v>
+        <v>0.096727</v>
       </c>
       <c r="E97" s="8">
-        <v>24473623712.76</v>
+        <v>24500697721.73</v>
       </c>
       <c r="F97" s="9">
-        <v>441767</v>
+        <v>441823</v>
       </c>
       <c r="G97" s="8">
-        <v>2360868869.22</v>
+        <v>2369869837.33</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -5033,19 +5033,19 @@
         <v>196</v>
       </c>
       <c r="C98" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D98" s="7">
-        <v>0.243812</v>
+        <v>0.243694</v>
       </c>
       <c r="E98" s="8">
-        <v>1289026275.86</v>
+        <v>1294028689.01</v>
       </c>
       <c r="F98" s="9">
-        <v>7177</v>
+        <v>7202</v>
       </c>
       <c r="G98" s="8">
-        <v>314280100.45</v>
+        <v>315347364.63</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -5056,19 +5056,19 @@
         <v>198</v>
       </c>
       <c r="C99" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D99" s="7">
-        <v>1.040379</v>
+        <v>1.040135</v>
       </c>
       <c r="E99" s="8">
-        <v>4529576701.11</v>
+        <v>4661055445.99</v>
       </c>
       <c r="F99" s="9">
-        <v>46717</v>
+        <v>47724</v>
       </c>
       <c r="G99" s="8">
-        <v>4712475098.21</v>
+        <v>4848128175.34</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5079,19 +5079,19 @@
         <v>200</v>
       </c>
       <c r="C100" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D100" s="7">
-        <v>2.580359</v>
+        <v>2.608657</v>
       </c>
       <c r="E100" s="8">
-        <v>12026977536.95</v>
+        <v>12025988296.4</v>
       </c>
       <c r="F100" s="9">
-        <v>305649</v>
+        <v>305917</v>
       </c>
       <c r="G100" s="8">
-        <v>31033918625.16</v>
+        <v>31371683724.05</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5102,19 +5102,19 @@
         <v>202</v>
       </c>
       <c r="C101" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D101" s="7">
-        <v>0.353735</v>
+        <v>0.353762</v>
       </c>
       <c r="E101" s="8">
-        <v>26215844823.65</v>
+        <v>25971059825.06</v>
       </c>
       <c r="F101" s="9">
-        <v>332707</v>
+        <v>332189</v>
       </c>
       <c r="G101" s="8">
-        <v>9273454952.76</v>
+        <v>9187585440.17</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5125,19 +5125,19 @@
         <v>204</v>
       </c>
       <c r="C102" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D102" s="7">
-        <v>0.368257</v>
+        <v>0.368662</v>
       </c>
       <c r="E102" s="8">
-        <v>202884119319.23</v>
+        <v>201611069674.29</v>
       </c>
       <c r="F102" s="9">
-        <v>378054</v>
+        <v>354575</v>
       </c>
       <c r="G102" s="8">
-        <v>74713409169.58</v>
+        <v>74326346096.24</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5148,19 +5148,19 @@
         <v>206</v>
       </c>
       <c r="C103" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D103" s="7">
-        <v>0.123545</v>
+        <v>0.123923</v>
       </c>
       <c r="E103" s="8">
-        <v>8883480634.3</v>
+        <v>8884343690.88</v>
       </c>
       <c r="F103" s="9">
-        <v>28568</v>
+        <v>28583</v>
       </c>
       <c r="G103" s="8">
-        <v>1097505320.47</v>
+        <v>1100977502.37</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -5171,19 +5171,19 @@
         <v>208</v>
       </c>
       <c r="C104" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D104" s="7">
-        <v>0.282928</v>
+        <v>0.286657</v>
       </c>
       <c r="E104" s="8">
-        <v>1717379176.2</v>
+        <v>1720196604.92</v>
       </c>
       <c r="F104" s="9">
-        <v>7834</v>
+        <v>7828</v>
       </c>
       <c r="G104" s="8">
-        <v>485894031.89</v>
+        <v>493107223.33</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -5194,19 +5194,19 @@
         <v>210</v>
       </c>
       <c r="C105" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D105" s="8">
-        <v>0.01</v>
+        <v>46148</v>
+      </c>
+      <c r="D105" s="7">
+        <v>0.009999</v>
       </c>
       <c r="E105" s="8">
-        <v>19219.8</v>
+        <v>81368114.56</v>
       </c>
       <c r="F105" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" s="8">
-        <v>192.19</v>
+        <v>813634.76</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5217,19 +5217,19 @@
         <v>212</v>
       </c>
       <c r="C106" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D106" s="7">
-        <v>1.045487</v>
+        <v>1.053466</v>
       </c>
       <c r="E106" s="8">
-        <v>248908503.07</v>
+        <v>249331738.86</v>
       </c>
       <c r="F106" s="9">
-        <v>4091</v>
+        <v>4096</v>
       </c>
       <c r="G106" s="8">
-        <v>260230677.09</v>
+        <v>262662439.54</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5240,19 +5240,19 @@
         <v>214</v>
       </c>
       <c r="C107" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D107" s="7">
-        <v>0.989839</v>
+        <v>0.999333</v>
       </c>
       <c r="E107" s="8">
-        <v>605769966.21</v>
+        <v>613456407.01</v>
       </c>
       <c r="F107" s="9">
-        <v>15423</v>
+        <v>15478</v>
       </c>
       <c r="G107" s="8">
-        <v>599614664.01</v>
+        <v>613047128.61</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -5263,19 +5263,19 @@
         <v>216</v>
       </c>
       <c r="C108" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D108" s="7">
-        <v>0.178158</v>
+        <v>0.179642</v>
       </c>
       <c r="E108" s="8">
-        <v>379725028</v>
+        <v>381377996.49</v>
       </c>
       <c r="F108" s="9">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="G108" s="8">
-        <v>67650971.64</v>
+        <v>68511467.65</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -5286,19 +5286,19 @@
         <v>218</v>
       </c>
       <c r="C109" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D109" s="7">
-        <v>1.435486</v>
+        <v>1.448256</v>
       </c>
       <c r="E109" s="8">
-        <v>1015883174.92</v>
+        <v>1020218026.58</v>
       </c>
       <c r="F109" s="9">
-        <v>21916</v>
+        <v>21951</v>
       </c>
       <c r="G109" s="8">
-        <v>1458285704.35</v>
+        <v>1477536827.12</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -5309,19 +5309,19 @@
         <v>220</v>
       </c>
       <c r="C110" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D110" s="7">
-        <v>0.096814</v>
+        <v>0.097279</v>
       </c>
       <c r="E110" s="8">
-        <v>5448538052.07</v>
+        <v>5465554179.47</v>
       </c>
       <c r="F110" s="9">
-        <v>24302</v>
+        <v>24350</v>
       </c>
       <c r="G110" s="8">
-        <v>527492050.44</v>
+        <v>531681499.36</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5332,19 +5332,19 @@
         <v>222</v>
       </c>
       <c r="C111" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D111" s="7">
-        <v>0.285599</v>
+        <v>0.285727</v>
       </c>
       <c r="E111" s="8">
-        <v>1640381231.46</v>
+        <v>1640635550.61</v>
       </c>
       <c r="F111" s="9">
-        <v>33257</v>
+        <v>33288</v>
       </c>
       <c r="G111" s="8">
-        <v>468491666.55</v>
+        <v>468773585.75</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -5355,19 +5355,19 @@
         <v>224</v>
       </c>
       <c r="C112" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D112" s="7">
-        <v>0.213026</v>
+        <v>46148</v>
+      </c>
+      <c r="D112" s="11">
+        <v>0.2151</v>
       </c>
       <c r="E112" s="8">
-        <v>589020595.94</v>
+        <v>589406191.8</v>
       </c>
       <c r="F112" s="9">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="G112" s="8">
-        <v>125476650.77</v>
+        <v>126781283.17</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -5378,19 +5378,19 @@
         <v>226</v>
       </c>
       <c r="C113" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D113" s="7">
-        <v>0.409531</v>
+        <v>0.411715</v>
       </c>
       <c r="E113" s="8">
-        <v>149580084.22</v>
+        <v>150874677.19</v>
       </c>
       <c r="F113" s="9">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="G113" s="8">
-        <v>61257665</v>
+        <v>62117392.24</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5401,19 +5401,19 @@
         <v>228</v>
       </c>
       <c r="C114" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D114" s="7">
-        <v>0.108255</v>
+        <v>0.108186</v>
       </c>
       <c r="E114" s="8">
-        <v>194767369.36</v>
+        <v>196150017.68</v>
       </c>
       <c r="F114" s="9">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="G114" s="8">
-        <v>21084473.59</v>
+        <v>21220657.09</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -5424,19 +5424,19 @@
         <v>230</v>
       </c>
       <c r="C115" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D115" s="7">
-        <v>0.062783</v>
+        <v>0.062566</v>
       </c>
       <c r="E115" s="8">
-        <v>1217912369381.75</v>
+        <v>1218411778510.52</v>
       </c>
       <c r="F115" s="9">
-        <v>788786</v>
+        <v>789381</v>
       </c>
       <c r="G115" s="8">
-        <v>76464395181.93</v>
+        <v>76231692577.3</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -5447,19 +5447,19 @@
         <v>232</v>
       </c>
       <c r="C116" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D116" s="7">
-        <v>0.015463</v>
+        <v>0.015481</v>
       </c>
       <c r="E116" s="8">
-        <v>6434055727.74</v>
+        <v>6611585167.1</v>
       </c>
       <c r="F116" s="9">
-        <v>1320</v>
+        <v>1336</v>
       </c>
       <c r="G116" s="8">
-        <v>99492949.27</v>
+        <v>102356236.59</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -5470,19 +5470,19 @@
         <v>234</v>
       </c>
       <c r="C117" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D117" s="7">
-        <v>0.123351</v>
+        <v>0.124113</v>
       </c>
       <c r="E117" s="8">
-        <v>7517299331.69</v>
+        <v>7553534317.07</v>
       </c>
       <c r="F117" s="9">
-        <v>24755</v>
+        <v>24858</v>
       </c>
       <c r="G117" s="8">
-        <v>927268311.63</v>
+        <v>937494992.57</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -5493,19 +5493,19 @@
         <v>236</v>
       </c>
       <c r="C118" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D118" s="7">
-        <v>0.126595</v>
+        <v>46148</v>
+      </c>
+      <c r="D118" s="10">
+        <v>0.12926</v>
       </c>
       <c r="E118" s="8">
-        <v>28635691908.59</v>
+        <v>29129584645.12</v>
       </c>
       <c r="F118" s="9">
-        <v>69040</v>
+        <v>70089</v>
       </c>
       <c r="G118" s="8">
-        <v>3625130294.4</v>
+        <v>3765302949.7</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -5516,19 +5516,19 @@
         <v>238</v>
       </c>
       <c r="C119" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D119" s="7">
-        <v>0.570777</v>
+        <v>0.570662</v>
       </c>
       <c r="E119" s="8">
-        <v>90855434.38</v>
+        <v>90975733.7</v>
       </c>
       <c r="F119" s="9">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="G119" s="8">
-        <v>51858205.88</v>
+        <v>51916416.47</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5539,19 +5539,19 @@
         <v>240</v>
       </c>
       <c r="C120" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D120" s="7">
-        <v>0.737719</v>
+        <v>0.735079</v>
       </c>
       <c r="E120" s="8">
-        <v>22868612619.93</v>
+        <v>22892672928.82</v>
       </c>
       <c r="F120" s="9">
-        <v>149152</v>
+        <v>149436</v>
       </c>
       <c r="G120" s="8">
-        <v>16870608681.53</v>
+        <v>16827917892.66</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5562,19 +5562,19 @@
         <v>242</v>
       </c>
       <c r="C121" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D121" s="7">
-        <v>0.123098</v>
+        <v>0.123193</v>
       </c>
       <c r="E121" s="8">
-        <v>14721189280.84</v>
+        <v>14739073125.53</v>
       </c>
       <c r="F121" s="9">
-        <v>44557</v>
+        <v>44624</v>
       </c>
       <c r="G121" s="8">
-        <v>1812144701.83</v>
+        <v>1815750204.35</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -5585,19 +5585,19 @@
         <v>244</v>
       </c>
       <c r="C122" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D122" s="11">
-        <v>0.1042</v>
+        <v>46148</v>
+      </c>
+      <c r="D122" s="7">
+        <v>0.104498</v>
       </c>
       <c r="E122" s="8">
-        <v>42907236646.99</v>
+        <v>42877344749.4</v>
       </c>
       <c r="F122" s="9">
-        <v>338325</v>
+        <v>338215</v>
       </c>
       <c r="G122" s="8">
-        <v>4470947354.01</v>
+        <v>4480584362.3</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -5608,19 +5608,19 @@
         <v>246</v>
       </c>
       <c r="C123" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D123" s="7">
-        <v>0.092647</v>
+        <v>0.092924</v>
       </c>
       <c r="E123" s="8">
-        <v>9674419144.21</v>
+        <v>9698406915.03</v>
       </c>
       <c r="F123" s="9">
-        <v>147983</v>
+        <v>148035</v>
       </c>
       <c r="G123" s="8">
-        <v>896308025.13</v>
+        <v>901216761.1</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -5631,19 +5631,19 @@
         <v>248</v>
       </c>
       <c r="C124" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D124" s="10">
-        <v>0.04762</v>
+        <v>46148</v>
+      </c>
+      <c r="D124" s="7">
+        <v>0.047919</v>
       </c>
       <c r="E124" s="8">
-        <v>27955804439.29</v>
+        <v>27960554819.46</v>
       </c>
       <c r="F124" s="9">
-        <v>34523</v>
+        <v>34591</v>
       </c>
       <c r="G124" s="8">
-        <v>1331259971.64</v>
+        <v>1339841012.8</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5654,19 +5654,19 @@
         <v>250</v>
       </c>
       <c r="C125" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D125" s="7">
-        <v>0.117168</v>
+        <v>46148</v>
+      </c>
+      <c r="D125" s="11">
+        <v>0.1176</v>
       </c>
       <c r="E125" s="8">
-        <v>6291630621.4</v>
+        <v>6291741555.99</v>
       </c>
       <c r="F125" s="9">
-        <v>43210</v>
+        <v>43200</v>
       </c>
       <c r="G125" s="8">
-        <v>737176474.96</v>
+        <v>739907898.87</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5677,19 +5677,19 @@
         <v>252</v>
       </c>
       <c r="C126" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D126" s="7">
-        <v>0.090655</v>
+        <v>0.090876</v>
       </c>
       <c r="E126" s="8">
-        <v>2962465556.14</v>
+        <v>2968465325.26</v>
       </c>
       <c r="F126" s="9">
-        <v>83481</v>
+        <v>83537</v>
       </c>
       <c r="G126" s="8">
-        <v>268561936.33</v>
+        <v>269761722.86</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5700,19 +5700,19 @@
         <v>254</v>
       </c>
       <c r="C127" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D127" s="7">
-        <v>0.083494</v>
+        <v>0.083976</v>
       </c>
       <c r="E127" s="8">
-        <v>1128427630.49</v>
+        <v>1128373212.07</v>
       </c>
       <c r="F127" s="9">
-        <v>122915</v>
+        <v>122904</v>
       </c>
       <c r="G127" s="8">
-        <v>94216470.02</v>
+        <v>94756357.57</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5723,19 +5723,19 @@
         <v>256</v>
       </c>
       <c r="C128" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D128" s="7">
-        <v>0.757898</v>
+        <v>0.762212</v>
       </c>
       <c r="E128" s="8">
-        <v>1636830206.44</v>
+        <v>1638328098.3</v>
       </c>
       <c r="F128" s="9">
-        <v>49927</v>
+        <v>49943</v>
       </c>
       <c r="G128" s="8">
-        <v>1240550693.9</v>
+        <v>1248752953.37</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5746,19 +5746,19 @@
         <v>258</v>
       </c>
       <c r="C129" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D129" s="7">
-        <v>0.147822</v>
+        <v>0.147791</v>
       </c>
       <c r="E129" s="8">
-        <v>1288968310.99</v>
+        <v>1296944436.14</v>
       </c>
       <c r="F129" s="9">
-        <v>12555</v>
+        <v>12554</v>
       </c>
       <c r="G129" s="8">
-        <v>190537359.5</v>
+        <v>191676997.76</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5769,19 +5769,19 @@
         <v>260</v>
       </c>
       <c r="C130" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D130" s="7">
-        <v>0.237756</v>
+        <v>0.237711</v>
       </c>
       <c r="E130" s="8">
-        <v>5191103772.93</v>
+        <v>5192476999.71</v>
       </c>
       <c r="F130" s="9">
-        <v>69515</v>
+        <v>69513</v>
       </c>
       <c r="G130" s="8">
-        <v>1234217899.16</v>
+        <v>1234307976.38</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5792,19 +5792,19 @@
         <v>262</v>
       </c>
       <c r="C131" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D131" s="7">
-        <v>1.806407</v>
+        <v>1.821692</v>
       </c>
       <c r="E131" s="8">
-        <v>2371458356.23</v>
+        <v>2373431130.75</v>
       </c>
       <c r="F131" s="9">
-        <v>52870</v>
+        <v>52943</v>
       </c>
       <c r="G131" s="8">
-        <v>4283818020.6</v>
+        <v>4323661508.27</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5815,19 +5815,19 @@
         <v>264</v>
       </c>
       <c r="C132" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D132" s="7">
-        <v>0.349436</v>
+        <v>46148</v>
+      </c>
+      <c r="D132" s="10">
+        <v>0.35113</v>
       </c>
       <c r="E132" s="8">
-        <v>556385404.18</v>
+        <v>557179937.88</v>
       </c>
       <c r="F132" s="9">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="G132" s="8">
-        <v>194421356.3</v>
+        <v>195642416.43</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5838,19 +5838,19 @@
         <v>266</v>
       </c>
       <c r="C133" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D133" s="7">
-        <v>0.158027</v>
+        <v>0.158977</v>
       </c>
       <c r="E133" s="8">
-        <v>131844793.61</v>
+        <v>132303463.27</v>
       </c>
       <c r="F133" s="9">
         <v>458</v>
       </c>
       <c r="G133" s="8">
-        <v>20835030.81</v>
+        <v>21033234.34</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,19 +5861,19 @@
         <v>268</v>
       </c>
       <c r="C134" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D134" s="7">
-        <v>0.705235</v>
+        <v>0.705405</v>
       </c>
       <c r="E134" s="8">
-        <v>1256491730.55</v>
+        <v>1259264754.83</v>
       </c>
       <c r="F134" s="9">
-        <v>21180</v>
+        <v>21173</v>
       </c>
       <c r="G134" s="8">
-        <v>886121465.41</v>
+        <v>888291720.93</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5884,19 +5884,19 @@
         <v>270</v>
       </c>
       <c r="C135" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D135" s="7">
-        <v>0.370583</v>
+        <v>0.370926</v>
       </c>
       <c r="E135" s="8">
-        <v>7521821480.25</v>
+        <v>7462935189.45</v>
       </c>
       <c r="F135" s="9">
-        <v>109712</v>
+        <v>101123</v>
       </c>
       <c r="G135" s="8">
-        <v>2787462076.67</v>
+        <v>2768199535.74</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5907,19 +5907,19 @@
         <v>272</v>
       </c>
       <c r="C136" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D136" s="7">
-        <v>0.199917</v>
+        <v>0.201261</v>
       </c>
       <c r="E136" s="8">
-        <v>198898493.68</v>
+        <v>198903737.77</v>
       </c>
       <c r="F136" s="9">
         <v>614</v>
       </c>
       <c r="G136" s="8">
-        <v>39763263.76</v>
+        <v>40031593.7</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5930,19 +5930,19 @@
         <v>274</v>
       </c>
       <c r="C137" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D137" s="10">
-        <v>0.25802</v>
+        <v>46148</v>
+      </c>
+      <c r="D137" s="7">
+        <v>0.261483</v>
       </c>
       <c r="E137" s="8">
-        <v>401532826.89</v>
+        <v>402771298.13</v>
       </c>
       <c r="F137" s="9">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="G137" s="8">
-        <v>103603328.63</v>
+        <v>105317700.43</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5953,19 +5953,19 @@
         <v>276</v>
       </c>
       <c r="C138" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D138" s="7">
-        <v>0.100302</v>
+        <v>0.100489</v>
       </c>
       <c r="E138" s="8">
-        <v>294559885.87</v>
+        <v>294958936.32</v>
       </c>
       <c r="F138" s="9">
         <v>324</v>
       </c>
       <c r="G138" s="8">
-        <v>29544833.04</v>
+        <v>29639994.67</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5976,19 +5976,19 @@
         <v>278</v>
       </c>
       <c r="C139" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D139" s="7">
-        <v>0.390158</v>
+        <v>0.396212</v>
       </c>
       <c r="E139" s="8">
-        <v>628133023.88</v>
+        <v>629313815.76</v>
       </c>
       <c r="F139" s="9">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="G139" s="8">
-        <v>245071298.65</v>
+        <v>249341603.16</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5999,19 +5999,19 @@
         <v>280</v>
       </c>
       <c r="C140" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D140" s="7">
-        <v>0.697035</v>
+        <v>0.696904</v>
       </c>
       <c r="E140" s="8">
-        <v>2931267092.03</v>
+        <v>2930592383.91</v>
       </c>
       <c r="F140" s="9">
-        <v>42031</v>
+        <v>42030</v>
       </c>
       <c r="G140" s="8">
-        <v>2043196856.14</v>
+        <v>2042340256.91</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -6022,19 +6022,19 @@
         <v>282</v>
       </c>
       <c r="C141" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D141" s="7">
-        <v>0.013918</v>
+        <v>0.013967</v>
       </c>
       <c r="E141" s="8">
-        <v>2815295713.25</v>
+        <v>2853414461.1</v>
       </c>
       <c r="F141" s="9">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="G141" s="8">
-        <v>39184000.9</v>
+        <v>39852806.77</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -6045,19 +6045,19 @@
         <v>284</v>
       </c>
       <c r="C142" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D142" s="7">
-        <v>0.073422</v>
+        <v>0.074885</v>
       </c>
       <c r="E142" s="8">
-        <v>21877317723.12</v>
+        <v>22101879892.22</v>
       </c>
       <c r="F142" s="9">
-        <v>23440</v>
+        <v>23514</v>
       </c>
       <c r="G142" s="8">
-        <v>1606274288.53</v>
+        <v>1655101775.84</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -6068,19 +6068,19 @@
         <v>286</v>
       </c>
       <c r="C143" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D143" s="7">
-        <v>0.280428</v>
+        <v>0.279137</v>
       </c>
       <c r="E143" s="8">
-        <v>20689854563.24</v>
+        <v>20696954474.98</v>
       </c>
       <c r="F143" s="9">
-        <v>4724</v>
+        <v>4725</v>
       </c>
       <c r="G143" s="8">
-        <v>5802015454.15</v>
+        <v>5777292784.39</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -6091,19 +6091,19 @@
         <v>288</v>
       </c>
       <c r="C144" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D144" s="7">
-        <v>0.090646</v>
+        <v>0.090752</v>
       </c>
       <c r="E144" s="8">
-        <v>737096455.83</v>
+        <v>676599649.29</v>
       </c>
       <c r="F144" s="9">
-        <v>12280</v>
+        <v>11119</v>
       </c>
       <c r="G144" s="8">
-        <v>66815147.64</v>
+        <v>61402724.34</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -6114,19 +6114,19 @@
         <v>290</v>
       </c>
       <c r="C145" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D145" s="7">
-        <v>0.053812</v>
+        <v>0.053755</v>
       </c>
       <c r="E145" s="8">
-        <v>1420540550.13</v>
+        <v>1402260864.75</v>
       </c>
       <c r="F145" s="9">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G145" s="8">
-        <v>76441983.68</v>
+        <v>75378749.72</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -6137,19 +6137,19 @@
         <v>292</v>
       </c>
       <c r="C146" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D146" s="7">
-        <v>0.113563</v>
+        <v>0.113508</v>
       </c>
       <c r="E146" s="8">
-        <v>1806466359.66</v>
+        <v>1807701316.27</v>
       </c>
       <c r="F146" s="9">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="G146" s="8">
-        <v>205146940.47</v>
+        <v>205188432.65</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6160,19 +6160,19 @@
         <v>294</v>
       </c>
       <c r="C147" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D147" s="7">
-        <v>0.113084</v>
+        <v>0.113495</v>
       </c>
       <c r="E147" s="8">
-        <v>1960693611.45</v>
+        <v>1964327759.79</v>
       </c>
       <c r="F147" s="9">
-        <v>65235</v>
+        <v>65279</v>
       </c>
       <c r="G147" s="8">
-        <v>221722251.03</v>
+        <v>222941659.24</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -6183,19 +6183,19 @@
         <v>296</v>
       </c>
       <c r="C148" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D148" s="7">
-        <v>0.076443</v>
+        <v>0.076873</v>
       </c>
       <c r="E148" s="8">
         <v>571278655.15</v>
       </c>
       <c r="F148" s="9">
-        <v>52205</v>
+        <v>52202</v>
       </c>
       <c r="G148" s="8">
-        <v>43670016.35</v>
+        <v>43915864.79</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6206,19 +6206,19 @@
         <v>298</v>
       </c>
       <c r="C149" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D149" s="7">
-        <v>0.082263</v>
+        <v>0.082404</v>
       </c>
       <c r="E149" s="8">
-        <v>355350506.92</v>
+        <v>357013457.43</v>
       </c>
       <c r="F149" s="9">
-        <v>9473</v>
+        <v>9526</v>
       </c>
       <c r="G149" s="8">
-        <v>29232230.34</v>
+        <v>29419415.7</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -6229,19 +6229,19 @@
         <v>300</v>
       </c>
       <c r="C150" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D150" s="7">
-        <v>0.361728</v>
+        <v>0.363293</v>
       </c>
       <c r="E150" s="8">
-        <v>145492665.06</v>
+        <v>145633608.93</v>
       </c>
       <c r="F150" s="9">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="G150" s="8">
-        <v>52628825.57</v>
+        <v>52907671.7</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6252,19 +6252,19 @@
         <v>302</v>
       </c>
       <c r="C151" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D151" s="7">
-        <v>0.098434</v>
+        <v>0.098282</v>
       </c>
       <c r="E151" s="8">
-        <v>334702156.9</v>
+        <v>335220148.31</v>
       </c>
       <c r="F151" s="9">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="G151" s="8">
-        <v>32946203.49</v>
+        <v>32946148.38</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -6275,19 +6275,19 @@
         <v>304</v>
       </c>
       <c r="C152" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D152" s="7">
-        <v>0.288994</v>
+        <v>0.290822</v>
       </c>
       <c r="E152" s="8">
-        <v>142131238.46</v>
+        <v>142660038.68</v>
       </c>
       <c r="F152" s="9">
         <v>203</v>
       </c>
       <c r="G152" s="8">
-        <v>41075057.6</v>
+        <v>41488713.73</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -6298,19 +6298,19 @@
         <v>306</v>
       </c>
       <c r="C153" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D153" s="7">
-        <v>0.117426</v>
+        <v>0.117506</v>
       </c>
       <c r="E153" s="8">
-        <v>585947593.63</v>
+        <v>588222168.5</v>
       </c>
       <c r="F153" s="9">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G153" s="8">
-        <v>68805726.3</v>
+        <v>69119862.64</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -6321,19 +6321,19 @@
         <v>308</v>
       </c>
       <c r="C154" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D154" s="7">
-        <v>0.397702</v>
+        <v>0.401665</v>
       </c>
       <c r="E154" s="8">
-        <v>1302659931.78</v>
+        <v>1303721457.15</v>
       </c>
       <c r="F154" s="9">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G154" s="8">
-        <v>518070379.61</v>
+        <v>523659450.26</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -6344,19 +6344,19 @@
         <v>310</v>
       </c>
       <c r="C155" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D155" s="7">
-        <v>0.501518</v>
+        <v>0.507053</v>
       </c>
       <c r="E155" s="8">
-        <v>595886257.01</v>
+        <v>592860409.26</v>
       </c>
       <c r="F155" s="9">
         <v>380</v>
       </c>
       <c r="G155" s="8">
-        <v>298847713.24</v>
+        <v>300611704.87</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -6367,19 +6367,19 @@
         <v>312</v>
       </c>
       <c r="C156" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D156" s="7">
-        <v>1.669007</v>
+        <v>1.688882</v>
       </c>
       <c r="E156" s="8">
-        <v>909860510.62</v>
+        <v>912313565.94</v>
       </c>
       <c r="F156" s="9">
-        <v>10191</v>
+        <v>10184</v>
       </c>
       <c r="G156" s="8">
-        <v>1518563142.62</v>
+        <v>1540789988.06</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -6390,19 +6390,19 @@
         <v>314</v>
       </c>
       <c r="C157" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D157" s="7">
-        <v>0.277922</v>
+        <v>0.280476</v>
       </c>
       <c r="E157" s="8">
-        <v>184307849.96</v>
+        <v>184472793.29</v>
       </c>
       <c r="F157" s="9">
         <v>92</v>
       </c>
       <c r="G157" s="8">
-        <v>51223157.6</v>
+        <v>51740184.58</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -6413,19 +6413,19 @@
         <v>316</v>
       </c>
       <c r="C158" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D158" s="7">
-        <v>0.143081</v>
+        <v>46148</v>
+      </c>
+      <c r="D158" s="10">
+        <v>0.14289</v>
       </c>
       <c r="E158" s="8">
-        <v>4609604552.06</v>
+        <v>4599278346.77</v>
       </c>
       <c r="F158" s="9">
-        <v>28831</v>
+        <v>28822</v>
       </c>
       <c r="G158" s="8">
-        <v>659544870.91</v>
+        <v>657191528.17</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -6436,19 +6436,19 @@
         <v>318</v>
       </c>
       <c r="C159" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D159" s="7">
-        <v>0.167045</v>
+        <v>0.167213</v>
       </c>
       <c r="E159" s="8">
-        <v>3287713097.18</v>
+        <v>3260190471.63</v>
       </c>
       <c r="F159" s="9">
-        <v>12831</v>
+        <v>12144</v>
       </c>
       <c r="G159" s="8">
-        <v>549197248.19</v>
+        <v>545147219.87</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -6459,19 +6459,19 @@
         <v>320</v>
       </c>
       <c r="C160" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D160" s="7">
-        <v>0.687288</v>
+        <v>0.693737</v>
       </c>
       <c r="E160" s="8">
-        <v>760015559.68</v>
+        <v>765438953.86</v>
       </c>
       <c r="F160" s="9">
-        <v>5168</v>
+        <v>5169</v>
       </c>
       <c r="G160" s="8">
-        <v>522349951.38</v>
+        <v>531013463.67</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -6482,19 +6482,19 @@
         <v>322</v>
       </c>
       <c r="C161" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D161" s="7">
-        <v>0.373318</v>
+        <v>0.374713</v>
       </c>
       <c r="E161" s="8">
-        <v>1341556888.51</v>
+        <v>1341683545.63</v>
       </c>
       <c r="F161" s="9">
-        <v>23903</v>
+        <v>23894</v>
       </c>
       <c r="G161" s="8">
-        <v>500827503.7</v>
+        <v>502746198.33</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -6505,19 +6505,19 @@
         <v>324</v>
       </c>
       <c r="C162" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D162" s="7">
-        <v>0.363387</v>
+        <v>0.366591</v>
       </c>
       <c r="E162" s="8">
-        <v>167631436.89</v>
+        <v>168387624.52</v>
       </c>
       <c r="F162" s="9">
         <v>251</v>
       </c>
       <c r="G162" s="8">
-        <v>60915145.55</v>
+        <v>61729347.28</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -6528,19 +6528,19 @@
         <v>326</v>
       </c>
       <c r="C163" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D163" s="7">
-        <v>0.142255</v>
+        <v>46148</v>
+      </c>
+      <c r="D163" s="10">
+        <v>0.14253</v>
       </c>
       <c r="E163" s="8">
-        <v>1024778567.44</v>
+        <v>1028060527.51</v>
       </c>
       <c r="F163" s="9">
-        <v>2964</v>
+        <v>2971</v>
       </c>
       <c r="G163" s="8">
-        <v>145779753.4</v>
+        <v>146529134.28</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -6551,19 +6551,19 @@
         <v>328</v>
       </c>
       <c r="C164" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D164" s="10">
-        <v>0.11669</v>
+        <v>46148</v>
+      </c>
+      <c r="D164" s="7">
+        <v>0.117071</v>
       </c>
       <c r="E164" s="8">
-        <v>7574316074.46</v>
+        <v>7574060633.19</v>
       </c>
       <c r="F164" s="9">
-        <v>79766</v>
+        <v>79742</v>
       </c>
       <c r="G164" s="8">
-        <v>883846401.47</v>
+        <v>886705554.83</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -6574,19 +6574,19 @@
         <v>330</v>
       </c>
       <c r="C165" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D165" s="7">
-        <v>0.107795</v>
+        <v>0.107998</v>
       </c>
       <c r="E165" s="8">
-        <v>3271994580.49</v>
+        <v>3312365127.74</v>
       </c>
       <c r="F165" s="9">
-        <v>64725</v>
+        <v>64833</v>
       </c>
       <c r="G165" s="8">
-        <v>352703956.15</v>
+        <v>357729470.57</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -6597,19 +6597,19 @@
         <v>332</v>
       </c>
       <c r="C166" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D166" s="7">
-        <v>0.014556</v>
+        <v>0.014475</v>
       </c>
       <c r="E166" s="8">
-        <v>428708981359.1</v>
+        <v>429853016545.65</v>
       </c>
       <c r="F166" s="9">
-        <v>72968</v>
+        <v>73536</v>
       </c>
       <c r="G166" s="8">
-        <v>6240167408.67</v>
+        <v>6222034222.05</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -6620,19 +6620,19 @@
         <v>334</v>
       </c>
       <c r="C167" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D167" s="7">
-        <v>0.357498</v>
+        <v>46148</v>
+      </c>
+      <c r="D167" s="10">
+        <v>0.35928</v>
       </c>
       <c r="E167" s="8">
-        <v>682878752.51</v>
+        <v>685794453.12</v>
       </c>
       <c r="F167" s="9">
-        <v>6825</v>
+        <v>6846</v>
       </c>
       <c r="G167" s="8">
-        <v>244127491.42</v>
+        <v>246391974.42</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6643,19 +6643,19 @@
         <v>336</v>
       </c>
       <c r="C168" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D168" s="7">
-        <v>0.013859</v>
+        <v>0.013979</v>
       </c>
       <c r="E168" s="8">
-        <v>34600813927.74</v>
+        <v>35271662622.64</v>
       </c>
       <c r="F168" s="9">
-        <v>5848</v>
+        <v>6010</v>
       </c>
       <c r="G168" s="8">
-        <v>479530790.03</v>
+        <v>493069082.95</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6666,19 +6666,19 @@
         <v>338</v>
       </c>
       <c r="C169" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D169" s="7">
-        <v>0.676612</v>
+        <v>0.682788</v>
       </c>
       <c r="E169" s="8">
-        <v>1954795024.28</v>
+        <v>1942694548.02</v>
       </c>
       <c r="F169" s="9">
-        <v>32741</v>
+        <v>32761</v>
       </c>
       <c r="G169" s="8">
-        <v>1322638663.65</v>
+        <v>1326447556.06</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6689,19 +6689,19 @@
         <v>340</v>
       </c>
       <c r="C170" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D170" s="7">
-        <v>0.386164</v>
+        <v>0.385596</v>
       </c>
       <c r="E170" s="8">
-        <v>1974089752.92</v>
+        <v>1981201017.14</v>
       </c>
       <c r="F170" s="9">
-        <v>20972</v>
+        <v>20967</v>
       </c>
       <c r="G170" s="8">
-        <v>762323020.21</v>
+        <v>763942217.39</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6712,19 +6712,19 @@
         <v>342</v>
       </c>
       <c r="C171" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D171" s="7">
-        <v>0.139331</v>
+        <v>0.139364</v>
       </c>
       <c r="E171" s="8">
-        <v>1566712063.51</v>
+        <v>1568490067.55</v>
       </c>
       <c r="F171" s="9">
         <v>16349</v>
       </c>
       <c r="G171" s="8">
-        <v>218290925.31</v>
+        <v>218590344.48</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6735,19 +6735,19 @@
         <v>344</v>
       </c>
       <c r="C172" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D172" s="7">
-        <v>1.223541</v>
+        <v>1.237758</v>
       </c>
       <c r="E172" s="8">
-        <v>1386295730.27</v>
+        <v>1396597227.71</v>
       </c>
       <c r="F172" s="9">
-        <v>23818</v>
+        <v>23858</v>
       </c>
       <c r="G172" s="8">
-        <v>1696190088.23</v>
+        <v>1728649942.33</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6758,19 +6758,19 @@
         <v>346</v>
       </c>
       <c r="C173" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D173" s="7">
-        <v>0.567349</v>
+        <v>0.568405</v>
       </c>
       <c r="E173" s="8">
-        <v>2365222324.63</v>
+        <v>2362909070.66</v>
       </c>
       <c r="F173" s="9">
-        <v>34970</v>
+        <v>34921</v>
       </c>
       <c r="G173" s="8">
-        <v>1341905437.1</v>
+        <v>1343090490.04</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6781,19 +6781,19 @@
         <v>348</v>
       </c>
       <c r="C174" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D174" s="7">
-        <v>0.017396</v>
+        <v>0.017481</v>
       </c>
       <c r="E174" s="8">
-        <v>72827614051.34</v>
+        <v>74180233142.33</v>
       </c>
       <c r="F174" s="9">
-        <v>17504</v>
+        <v>17819</v>
       </c>
       <c r="G174" s="8">
-        <v>1266881992.97</v>
+        <v>1296778246.63</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6804,19 +6804,19 @@
         <v>350</v>
       </c>
       <c r="C175" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D175" s="7">
-        <v>0.088605</v>
+        <v>0.088865</v>
       </c>
       <c r="E175" s="8">
-        <v>2169927907.05</v>
+        <v>2183053862</v>
       </c>
       <c r="F175" s="9">
-        <v>5136</v>
+        <v>5160</v>
       </c>
       <c r="G175" s="8">
-        <v>192265571.44</v>
+        <v>193997861.52</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6827,19 +6827,19 @@
         <v>352</v>
       </c>
       <c r="C176" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D176" s="7">
-        <v>0.122007</v>
+        <v>0.122147</v>
       </c>
       <c r="E176" s="8">
-        <v>1624080822.38</v>
+        <v>1624637943.52</v>
       </c>
       <c r="F176" s="9">
         <v>1207</v>
       </c>
       <c r="G176" s="8">
-        <v>198148571.81</v>
+        <v>198444177.15</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6850,19 +6850,19 @@
         <v>354</v>
       </c>
       <c r="C177" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D177" s="7">
-        <v>0.308923</v>
+        <v>0.311426</v>
       </c>
       <c r="E177" s="8">
-        <v>758722155.88</v>
+        <v>750748788.48</v>
       </c>
       <c r="F177" s="9">
-        <v>1950</v>
+        <v>1944</v>
       </c>
       <c r="G177" s="8">
-        <v>234386576.83</v>
+        <v>233802521.23</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6873,19 +6873,19 @@
         <v>356</v>
       </c>
       <c r="C178" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D178" s="7">
-        <v>0.090182</v>
+        <v>0.090281</v>
       </c>
       <c r="E178" s="8">
-        <v>41908445494.96</v>
+        <v>41914570558.69</v>
       </c>
       <c r="F178" s="9">
-        <v>283699</v>
+        <v>283677</v>
       </c>
       <c r="G178" s="8">
-        <v>3779376706.13</v>
+        <v>3784080020.98</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6896,19 +6896,19 @@
         <v>358</v>
       </c>
       <c r="C179" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D179" s="7">
-        <v>0.064699</v>
+        <v>0.064751</v>
       </c>
       <c r="E179" s="8">
-        <v>668858330.36</v>
+        <v>669802614.94</v>
       </c>
       <c r="F179" s="9">
-        <v>6098</v>
+        <v>6099</v>
       </c>
       <c r="G179" s="8">
-        <v>43274241.85</v>
+        <v>43370344.5</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6919,19 +6919,19 @@
         <v>360</v>
       </c>
       <c r="C180" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D180" s="7">
-        <v>0.247599</v>
+        <v>0.248705</v>
       </c>
       <c r="E180" s="8">
-        <v>539229874.36</v>
+        <v>548599095.76</v>
       </c>
       <c r="F180" s="9">
-        <v>1757</v>
+        <v>1767</v>
       </c>
       <c r="G180" s="8">
-        <v>133512959.05</v>
+        <v>136439606.32</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6942,19 +6942,19 @@
         <v>362</v>
       </c>
       <c r="C181" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D181" s="7">
-        <v>0.388025</v>
+        <v>0.391476</v>
       </c>
       <c r="E181" s="8">
-        <v>363953064.79</v>
+        <v>365874701.39</v>
       </c>
       <c r="F181" s="9">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="G181" s="8">
-        <v>141222826.07</v>
+        <v>143231257</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6965,19 +6965,19 @@
         <v>364</v>
       </c>
       <c r="C182" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D182" s="7">
-        <v>0.110886</v>
+        <v>0.111244</v>
       </c>
       <c r="E182" s="8">
-        <v>14586325026.98</v>
+        <v>14367136359.54</v>
       </c>
       <c r="F182" s="9">
-        <v>32165</v>
+        <v>32185</v>
       </c>
       <c r="G182" s="8">
-        <v>1617422530.68</v>
+        <v>1598256688.04</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6988,19 +6988,19 @@
         <v>366</v>
       </c>
       <c r="C183" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D183" s="7">
-        <v>0.115701</v>
+        <v>0.115824</v>
       </c>
       <c r="E183" s="8">
-        <v>22826939999.91</v>
+        <v>22933085309.71</v>
       </c>
       <c r="F183" s="9">
-        <v>49301</v>
+        <v>47449</v>
       </c>
       <c r="G183" s="8">
-        <v>2641088689.94</v>
+        <v>2656212270.57</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7011,19 +7011,19 @@
         <v>368</v>
       </c>
       <c r="C184" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D184" s="7">
-        <v>0.093571</v>
+        <v>0.095774</v>
       </c>
       <c r="E184" s="8">
-        <v>30998494838.01</v>
+        <v>31280403232.42</v>
       </c>
       <c r="F184" s="9">
-        <v>29879</v>
+        <v>30006</v>
       </c>
       <c r="G184" s="8">
-        <v>2900565455.47</v>
+        <v>2995841021.53</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7034,19 +7034,19 @@
         <v>370</v>
       </c>
       <c r="C185" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D185" s="7">
-        <v>0.083868</v>
+        <v>0.084152</v>
       </c>
       <c r="E185" s="8">
-        <v>6441192543.48</v>
+        <v>6426275246.4</v>
       </c>
       <c r="F185" s="9">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="G185" s="8">
-        <v>540210715.19</v>
+        <v>540783631.65</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7057,19 +7057,19 @@
         <v>372</v>
       </c>
       <c r="C186" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D186" s="7">
-        <v>0.072677</v>
+        <v>0.072845</v>
       </c>
       <c r="E186" s="8">
-        <v>13948947995.39</v>
+        <v>14041819454.87</v>
       </c>
       <c r="F186" s="9">
-        <v>184343</v>
+        <v>184437</v>
       </c>
       <c r="G186" s="8">
-        <v>1013764545.31</v>
+        <v>1022874474.69</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7080,19 +7080,19 @@
         <v>374</v>
       </c>
       <c r="C187" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D187" s="10">
-        <v>0.09888</v>
+        <v>46148</v>
+      </c>
+      <c r="D187" s="7">
+        <v>0.099271</v>
       </c>
       <c r="E187" s="8">
-        <v>4073868379.02</v>
+        <v>4081590656.53</v>
       </c>
       <c r="F187" s="9">
-        <v>117658</v>
+        <v>117677</v>
       </c>
       <c r="G187" s="8">
-        <v>402824351.18</v>
+        <v>405184631.65</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7103,19 +7103,19 @@
         <v>376</v>
       </c>
       <c r="C188" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D188" s="7">
-        <v>0.239096</v>
+        <v>0.240753</v>
       </c>
       <c r="E188" s="8">
-        <v>666244735.06</v>
+        <v>666821783.03</v>
       </c>
       <c r="F188" s="9">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="G188" s="8">
-        <v>159296221</v>
+        <v>160539281.28</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7126,19 +7126,19 @@
         <v>378</v>
       </c>
       <c r="C189" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D189" s="10">
-        <v>0.08486</v>
+        <v>0.08498</v>
       </c>
       <c r="E189" s="8">
-        <v>2913922306.39</v>
+        <v>2895625278.19</v>
       </c>
       <c r="F189" s="9">
-        <v>44620</v>
+        <v>44038</v>
       </c>
       <c r="G189" s="8">
-        <v>247276242.27</v>
+        <v>246070598.34</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7149,19 +7149,19 @@
         <v>380</v>
       </c>
       <c r="C190" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D190" s="10">
-        <v>0.24298</v>
+        <v>46148</v>
+      </c>
+      <c r="D190" s="7">
+        <v>0.244549</v>
       </c>
       <c r="E190" s="8">
-        <v>3405542122.67</v>
+        <v>3424604430.96</v>
       </c>
       <c r="F190" s="9">
-        <v>6565</v>
+        <v>6605</v>
       </c>
       <c r="G190" s="8">
-        <v>827480266.01</v>
+        <v>837484213.11</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7172,19 +7172,19 @@
         <v>382</v>
       </c>
       <c r="C191" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D191" s="7">
-        <v>0.159814</v>
+        <v>0.160866</v>
       </c>
       <c r="E191" s="8">
-        <v>697176126.66</v>
+        <v>704404728.19</v>
       </c>
       <c r="F191" s="9">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="G191" s="8">
-        <v>111418295.3</v>
+        <v>113314469.36</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7195,19 +7195,19 @@
         <v>384</v>
       </c>
       <c r="C192" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D192" s="7">
-        <v>0.148105</v>
+        <v>46148</v>
+      </c>
+      <c r="D192" s="10">
+        <v>0.14909</v>
       </c>
       <c r="E192" s="8">
-        <v>488209910.18</v>
+        <v>489523250.36</v>
       </c>
       <c r="F192" s="9">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="G192" s="8">
-        <v>72306239.92</v>
+        <v>72982858.15</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7218,19 +7218,19 @@
         <v>386</v>
       </c>
       <c r="C193" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D193" s="10">
-        <v>0.10141</v>
+        <v>46148</v>
+      </c>
+      <c r="D193" s="7">
+        <v>0.101962</v>
       </c>
       <c r="E193" s="8">
-        <v>1167190108.84</v>
+        <v>1167043649.75</v>
       </c>
       <c r="F193" s="9">
-        <v>117390</v>
+        <v>117376</v>
       </c>
       <c r="G193" s="8">
-        <v>118364631.5</v>
+        <v>118994345.38</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7241,19 +7241,19 @@
         <v>388</v>
       </c>
       <c r="C194" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D194" s="7">
-        <v>0.199414</v>
+        <v>0.200644</v>
       </c>
       <c r="E194" s="8">
-        <v>1959901023.95</v>
+        <v>1979238071.55</v>
       </c>
       <c r="F194" s="9">
-        <v>1530</v>
+        <v>1577</v>
       </c>
       <c r="G194" s="8">
-        <v>390832048.95</v>
+        <v>397121515.71</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7264,19 +7264,19 @@
         <v>390</v>
       </c>
       <c r="C195" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D195" s="7">
-        <v>0.157789</v>
+        <v>46148</v>
+      </c>
+      <c r="D195" s="10">
+        <v>0.15836</v>
       </c>
       <c r="E195" s="8">
-        <v>592987194.83</v>
+        <v>592849402.12</v>
       </c>
       <c r="F195" s="9">
-        <v>2655</v>
+        <v>2660</v>
       </c>
       <c r="G195" s="8">
-        <v>93566734.52</v>
+        <v>93883508.29</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7287,19 +7287,19 @@
         <v>392</v>
       </c>
       <c r="C196" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D196" s="7">
-        <v>0.272062</v>
+        <v>0.272665</v>
       </c>
       <c r="E196" s="8">
-        <v>2808896685.38</v>
+        <v>2786128880.55</v>
       </c>
       <c r="F196" s="9">
-        <v>7701</v>
+        <v>7688</v>
       </c>
       <c r="G196" s="8">
-        <v>764193572.71</v>
+        <v>759681204.54</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7310,19 +7310,19 @@
         <v>394</v>
       </c>
       <c r="C197" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D197" s="7">
-        <v>0.098853</v>
+        <v>46148</v>
+      </c>
+      <c r="D197" s="10">
+        <v>0.09932</v>
       </c>
       <c r="E197" s="8">
-        <v>103819646.93</v>
+        <v>104673956.94</v>
       </c>
       <c r="F197" s="9">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="G197" s="8">
-        <v>10262870.58</v>
+        <v>10396168.9</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7333,19 +7333,19 @@
         <v>396</v>
       </c>
       <c r="C198" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D198" s="10">
-        <v>0.21989</v>
+        <v>46148</v>
+      </c>
+      <c r="D198" s="7">
+        <v>0.222742</v>
       </c>
       <c r="E198" s="8">
-        <v>319706496.48</v>
+        <v>322934137.07</v>
       </c>
       <c r="F198" s="9">
-        <v>978</v>
+        <v>991</v>
       </c>
       <c r="G198" s="8">
-        <v>70300190.28</v>
+        <v>71930995.56</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7356,19 +7356,19 @@
         <v>398</v>
       </c>
       <c r="C199" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D199" s="7">
-        <v>0.174735</v>
+        <v>0.176627</v>
       </c>
       <c r="E199" s="8">
-        <v>270099511.13</v>
+        <v>271574022.99</v>
       </c>
       <c r="F199" s="9">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="G199" s="8">
-        <v>47195811.01</v>
+        <v>47967404.42</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7379,19 +7379,19 @@
         <v>400</v>
       </c>
       <c r="C200" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D200" s="7">
-        <v>0.087987</v>
+        <v>0.088076</v>
       </c>
       <c r="E200" s="8">
-        <v>2681835553.67</v>
+        <v>2710251611.88</v>
       </c>
       <c r="F200" s="9">
-        <v>40733</v>
+        <v>40853</v>
       </c>
       <c r="G200" s="8">
-        <v>235966702.66</v>
+        <v>238708213.56</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7402,19 +7402,19 @@
         <v>402</v>
       </c>
       <c r="C201" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D201" s="10">
-        <v>0.08985</v>
+        <v>46148</v>
+      </c>
+      <c r="D201" s="7">
+        <v>0.089935</v>
       </c>
       <c r="E201" s="8">
-        <v>825450265.04</v>
+        <v>829983180.1</v>
       </c>
       <c r="F201" s="9">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="G201" s="8">
-        <v>74166779.63</v>
+        <v>74644428.3</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7425,19 +7425,19 @@
         <v>404</v>
       </c>
       <c r="C202" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D202" s="7">
-        <v>0.151205</v>
+        <v>0.151764</v>
       </c>
       <c r="E202" s="8">
-        <v>9669621085.87</v>
+        <v>9580540310.56</v>
       </c>
       <c r="F202" s="9">
-        <v>9433</v>
+        <v>9398</v>
       </c>
       <c r="G202" s="8">
-        <v>1462098332.86</v>
+        <v>1453977993.2</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7448,19 +7448,19 @@
         <v>406</v>
       </c>
       <c r="C203" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D203" s="7">
-        <v>0.014454</v>
+        <v>46148</v>
+      </c>
+      <c r="D203" s="10">
+        <v>0.01455</v>
       </c>
       <c r="E203" s="8">
-        <v>9155566016.29</v>
+        <v>9151972292.73</v>
       </c>
       <c r="F203" s="9">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="G203" s="8">
-        <v>132337397.34</v>
+        <v>133161304.99</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7471,19 +7471,19 @@
         <v>408</v>
       </c>
       <c r="C204" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D204" s="7">
-        <v>0.027866</v>
+        <v>0.028016</v>
       </c>
       <c r="E204" s="8">
-        <v>1312474511.14</v>
+        <v>1319755610.2</v>
       </c>
       <c r="F204" s="9">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="G204" s="8">
-        <v>36573356.99</v>
+        <v>36974449.2</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7494,19 +7494,19 @@
         <v>410</v>
       </c>
       <c r="C205" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D205" s="7">
-        <v>0.119018</v>
+        <v>0.119528</v>
       </c>
       <c r="E205" s="8">
-        <v>3217351733.17</v>
+        <v>3214637637.32</v>
       </c>
       <c r="F205" s="9">
-        <v>312001</v>
+        <v>311923</v>
       </c>
       <c r="G205" s="8">
-        <v>382922849.75</v>
+        <v>384239961.9</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -7517,19 +7517,19 @@
         <v>412</v>
       </c>
       <c r="C206" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D206" s="7">
-        <v>0.156617</v>
+        <v>0.157268</v>
       </c>
       <c r="E206" s="8">
-        <v>471515033.65</v>
+        <v>492839951.31</v>
       </c>
       <c r="F206" s="9">
-        <v>902</v>
+        <v>967</v>
       </c>
       <c r="G206" s="8">
-        <v>73847041.63</v>
+        <v>77507929</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7540,19 +7540,19 @@
         <v>414</v>
       </c>
       <c r="C207" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D207" s="7">
-        <v>0.132393</v>
+        <v>0.132924</v>
       </c>
       <c r="E207" s="8">
-        <v>2868334866.5</v>
+        <v>2874175883.71</v>
       </c>
       <c r="F207" s="9">
-        <v>5764</v>
+        <v>5772</v>
       </c>
       <c r="G207" s="8">
-        <v>379747669.74</v>
+        <v>382046730.9</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7563,19 +7563,19 @@
         <v>416</v>
       </c>
       <c r="C208" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D208" s="7">
-        <v>0.104822</v>
+        <v>0.105221</v>
       </c>
       <c r="E208" s="8">
-        <v>4330302290.78</v>
+        <v>4328731384.79</v>
       </c>
       <c r="F208" s="9">
-        <v>348258</v>
+        <v>348166</v>
       </c>
       <c r="G208" s="8">
-        <v>453912706.18</v>
+        <v>455475411.78</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7586,19 +7586,19 @@
         <v>418</v>
       </c>
       <c r="C209" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D209" s="7">
-        <v>0.106321</v>
+        <v>0.106649</v>
       </c>
       <c r="E209" s="8">
-        <v>46417612084.76</v>
+        <v>46467425192.82</v>
       </c>
       <c r="F209" s="9">
-        <v>711843</v>
+        <v>711879</v>
       </c>
       <c r="G209" s="8">
-        <v>4935180686.7</v>
+        <v>4955709291.08</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7609,19 +7609,19 @@
         <v>420</v>
       </c>
       <c r="C210" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D210" s="7">
-        <v>0.064187</v>
+        <v>0.065308</v>
       </c>
       <c r="E210" s="8">
-        <v>58045066055.59</v>
+        <v>58690887529.75</v>
       </c>
       <c r="F210" s="9">
-        <v>60140</v>
+        <v>60540</v>
       </c>
       <c r="G210" s="8">
-        <v>3725751007.55</v>
+        <v>3833005800.77</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -7632,19 +7632,19 @@
         <v>422</v>
       </c>
       <c r="C211" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D211" s="7">
-        <v>0.105953</v>
+        <v>0.106246</v>
       </c>
       <c r="E211" s="8">
-        <v>64756269234.79</v>
+        <v>64887259664.03</v>
       </c>
       <c r="F211" s="9">
-        <v>913543</v>
+        <v>913878</v>
       </c>
       <c r="G211" s="8">
-        <v>6861116727.93</v>
+        <v>6894023190.06</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7655,19 +7655,19 @@
         <v>424</v>
       </c>
       <c r="C212" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D212" s="7">
-        <v>0.069857</v>
+        <v>0.069936</v>
       </c>
       <c r="E212" s="8">
-        <v>54901426812.23</v>
+        <v>54512327539.17</v>
       </c>
       <c r="F212" s="9">
-        <v>55472</v>
+        <v>55491</v>
       </c>
       <c r="G212" s="8">
-        <v>3835237018.88</v>
+        <v>3812389774.67</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7678,19 +7678,19 @@
         <v>426</v>
       </c>
       <c r="C213" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D213" s="7">
-        <v>0.097357</v>
+        <v>0.097433</v>
       </c>
       <c r="E213" s="8">
-        <v>16515873385.97</v>
+        <v>16684609670.79</v>
       </c>
       <c r="F213" s="9">
-        <v>428798</v>
+        <v>352317</v>
       </c>
       <c r="G213" s="8">
-        <v>1607933073.06</v>
+        <v>1625628674.79</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -7701,19 +7701,19 @@
         <v>428</v>
       </c>
       <c r="C214" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D214" s="7">
-        <v>0.050816</v>
+        <v>0.050705</v>
       </c>
       <c r="E214" s="8">
-        <v>82911097393.93</v>
+        <v>82599454430.93</v>
       </c>
       <c r="F214" s="9">
-        <v>34739</v>
+        <v>34676</v>
       </c>
       <c r="G214" s="8">
-        <v>4213249878.38</v>
+        <v>4188218347.93</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7724,19 +7724,19 @@
         <v>430</v>
       </c>
       <c r="C215" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D215" s="7">
-        <v>0.085903</v>
+        <v>0.086013</v>
       </c>
       <c r="E215" s="8">
-        <v>14029141269.82</v>
+        <v>14016993353.42</v>
       </c>
       <c r="F215" s="9">
-        <v>236316</v>
+        <v>236496</v>
       </c>
       <c r="G215" s="8">
-        <v>1205150656.08</v>
+        <v>1205649010.16</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -7747,19 +7747,19 @@
         <v>432</v>
       </c>
       <c r="C216" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D216" s="7">
-        <v>0.317263</v>
+        <v>0.319548</v>
       </c>
       <c r="E216" s="8">
-        <v>12197268016.97</v>
+        <v>12238797885.26</v>
       </c>
       <c r="F216" s="9">
-        <v>57766</v>
+        <v>58037</v>
       </c>
       <c r="G216" s="8">
-        <v>3869742861.75</v>
+        <v>3910878318.8</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -7770,19 +7770,19 @@
         <v>434</v>
       </c>
       <c r="C217" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D217" s="10">
-        <v>0.21895</v>
+        <v>46148</v>
+      </c>
+      <c r="D217" s="7">
+        <v>0.221433</v>
       </c>
       <c r="E217" s="8">
-        <v>10424098764.4</v>
+        <v>10468444482.85</v>
       </c>
       <c r="F217" s="9">
-        <v>39547</v>
+        <v>39769</v>
       </c>
       <c r="G217" s="8">
-        <v>2282354676.35</v>
+        <v>2318054922.8</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7793,19 +7793,19 @@
         <v>436</v>
       </c>
       <c r="C218" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D218" s="7">
-        <v>1.003964</v>
+        <v>1.011393</v>
       </c>
       <c r="E218" s="8">
-        <v>744475678.31</v>
+        <v>744010832.05</v>
       </c>
       <c r="F218" s="9">
-        <v>4349</v>
+        <v>4359</v>
       </c>
       <c r="G218" s="8">
-        <v>747426819.72</v>
+        <v>752487446.04</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -7816,19 +7816,19 @@
         <v>438</v>
       </c>
       <c r="C219" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D219" s="7">
-        <v>0.709703</v>
+        <v>0.719522</v>
       </c>
       <c r="E219" s="8">
-        <v>5942266730.31</v>
+        <v>5948997287.64</v>
       </c>
       <c r="F219" s="9">
-        <v>10992</v>
+        <v>11100</v>
       </c>
       <c r="G219" s="8">
-        <v>4217244885.24</v>
+        <v>4280433585.53</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -7839,19 +7839,19 @@
         <v>440</v>
       </c>
       <c r="C220" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D220" s="7">
-        <v>2.790129</v>
+        <v>2.828788</v>
       </c>
       <c r="E220" s="8">
-        <v>6249248248.61</v>
+        <v>6246386941.19</v>
       </c>
       <c r="F220" s="9">
-        <v>272756</v>
+        <v>273193</v>
       </c>
       <c r="G220" s="8">
-        <v>17436208244.98</v>
+        <v>17669702753.48</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -7862,19 +7862,19 @@
         <v>442</v>
       </c>
       <c r="C221" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D221" s="7">
-        <v>0.404812</v>
+        <v>46148</v>
+      </c>
+      <c r="D221" s="11">
+        <v>0.4044</v>
       </c>
       <c r="E221" s="8">
-        <v>9376143921.25</v>
+        <v>9351997876.91</v>
       </c>
       <c r="F221" s="9">
-        <v>165390</v>
+        <v>165245</v>
       </c>
       <c r="G221" s="8">
-        <v>3795574830.31</v>
+        <v>3781949329.05</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -7885,19 +7885,19 @@
         <v>444</v>
       </c>
       <c r="C222" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D222" s="7">
-        <v>0.395322</v>
+        <v>0.395723</v>
       </c>
       <c r="E222" s="8">
-        <v>177063065177.15</v>
+        <v>177777178206.29</v>
       </c>
       <c r="F222" s="9">
-        <v>413578</v>
+        <v>385020</v>
       </c>
       <c r="G222" s="8">
-        <v>69996917082.66</v>
+        <v>70350523977.71</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -7908,19 +7908,19 @@
         <v>446</v>
       </c>
       <c r="C223" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D223" s="7">
-        <v>0.153926</v>
+        <v>0.154494</v>
       </c>
       <c r="E223" s="8">
-        <v>6440743272.35</v>
+        <v>6438873327.09</v>
       </c>
       <c r="F223" s="9">
-        <v>25275</v>
+        <v>25300</v>
       </c>
       <c r="G223" s="8">
-        <v>991398990.89</v>
+        <v>994764242.85</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -7931,19 +7931,19 @@
         <v>448</v>
       </c>
       <c r="C224" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D224" s="7">
-        <v>0.520927</v>
+        <v>0.521191</v>
       </c>
       <c r="E224" s="8">
-        <v>8118600876.42</v>
+        <v>8111047939.7</v>
       </c>
       <c r="F224" s="9">
-        <v>35717</v>
+        <v>35711</v>
       </c>
       <c r="G224" s="8">
-        <v>4229200478.09</v>
+        <v>4227407357.19</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -7954,19 +7954,19 @@
         <v>450</v>
       </c>
       <c r="C225" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D225" s="7">
-        <v>0.073913</v>
+        <v>0.073562</v>
       </c>
       <c r="E225" s="8">
-        <v>2509968503868.51</v>
+        <v>2510651769490.34</v>
       </c>
       <c r="F225" s="9">
-        <v>1246058</v>
+        <v>1246600</v>
       </c>
       <c r="G225" s="8">
-        <v>185518068106.39</v>
+        <v>184687883265.22</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -7977,19 +7977,19 @@
         <v>452</v>
       </c>
       <c r="C226" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D226" s="7">
-        <v>0.073156</v>
+        <v>0.073641</v>
       </c>
       <c r="E226" s="8">
-        <v>26653168263.2</v>
+        <v>26733061119.96</v>
       </c>
       <c r="F226" s="9">
-        <v>95261</v>
+        <v>95305</v>
       </c>
       <c r="G226" s="8">
-        <v>1949836893.63</v>
+        <v>1968648368.61</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -8000,19 +8000,19 @@
         <v>454</v>
       </c>
       <c r="C227" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D227" s="7">
-        <v>0.015191</v>
+        <v>0.015217</v>
       </c>
       <c r="E227" s="8">
-        <v>517429046650.35</v>
+        <v>515914860027.48</v>
       </c>
       <c r="F227" s="9">
-        <v>50712</v>
+        <v>50718</v>
       </c>
       <c r="G227" s="8">
-        <v>7860312103.19</v>
+        <v>7850825965.34</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8023,19 +8023,19 @@
         <v>456</v>
       </c>
       <c r="C228" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D228" s="7">
-        <v>0.780805</v>
+        <v>0.778292</v>
       </c>
       <c r="E228" s="8">
-        <v>170635074199.38</v>
+        <v>170582603444.45</v>
       </c>
       <c r="F228" s="9">
-        <v>823227</v>
+        <v>824446</v>
       </c>
       <c r="G228" s="8">
-        <v>133232735993.64</v>
+        <v>132763112254.8</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8046,19 +8046,19 @@
         <v>458</v>
       </c>
       <c r="C229" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D229" s="7">
-        <v>0.137868</v>
+        <v>0.138281</v>
       </c>
       <c r="E229" s="8">
-        <v>26963859360.36</v>
+        <v>26959173955.19</v>
       </c>
       <c r="F229" s="9">
-        <v>194801</v>
+        <v>194808</v>
       </c>
       <c r="G229" s="8">
-        <v>3717443451.43</v>
+        <v>3727936428.73</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8069,19 +8069,19 @@
         <v>460</v>
       </c>
       <c r="C230" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D230" s="7">
-        <v>1.100235</v>
+        <v>1.108987</v>
       </c>
       <c r="E230" s="8">
-        <v>2638491262.18</v>
+        <v>2637469490.79</v>
       </c>
       <c r="F230" s="9">
-        <v>49162</v>
+        <v>49172</v>
       </c>
       <c r="G230" s="8">
-        <v>2902959150.5</v>
+        <v>2924919060.71</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8092,19 +8092,19 @@
         <v>462</v>
       </c>
       <c r="C231" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D231" s="7">
-        <v>0.281522</v>
+        <v>0.281224</v>
       </c>
       <c r="E231" s="8">
-        <v>2513274818.45</v>
+        <v>2506885930.25</v>
       </c>
       <c r="F231" s="9">
-        <v>11207</v>
+        <v>11254</v>
       </c>
       <c r="G231" s="8">
-        <v>707541439.04</v>
+        <v>704996173.42</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8115,19 +8115,19 @@
         <v>464</v>
       </c>
       <c r="C232" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D232" s="7">
-        <v>1.126972</v>
+        <v>1.126147</v>
       </c>
       <c r="E232" s="8">
-        <v>5215992297.34</v>
+        <v>5218122142.31</v>
       </c>
       <c r="F232" s="9">
-        <v>63623</v>
+        <v>63599</v>
       </c>
       <c r="G232" s="8">
-        <v>5878279181.24</v>
+        <v>5876373195.4</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8138,19 +8138,19 @@
         <v>466</v>
       </c>
       <c r="C233" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D233" s="7">
-        <v>0.376717</v>
+        <v>0.379183</v>
       </c>
       <c r="E233" s="8">
-        <v>18817333855.11</v>
+        <v>18872855308.92</v>
       </c>
       <c r="F233" s="9">
-        <v>150283</v>
+        <v>150952</v>
       </c>
       <c r="G233" s="8">
-        <v>7088809409.56</v>
+        <v>7156268709.93</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8161,19 +8161,19 @@
         <v>468</v>
       </c>
       <c r="C234" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D234" s="7">
-        <v>0.107113</v>
+        <v>0.107468</v>
       </c>
       <c r="E234" s="8">
-        <v>282169998878.8</v>
+        <v>281976971850.5</v>
       </c>
       <c r="F234" s="9">
-        <v>1530853</v>
+        <v>1530193</v>
       </c>
       <c r="G234" s="8">
-        <v>30224021282.11</v>
+        <v>30303360723.08</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8184,19 +8184,19 @@
         <v>470</v>
       </c>
       <c r="C235" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D235" s="7">
-        <v>0.261707</v>
+        <v>46148</v>
+      </c>
+      <c r="D235" s="11">
+        <v>0.2642</v>
       </c>
       <c r="E235" s="8">
-        <v>3265225135.01</v>
+        <v>3272386028.52</v>
       </c>
       <c r="F235" s="9">
-        <v>10500</v>
+        <v>10519</v>
       </c>
       <c r="G235" s="8">
-        <v>854531066.51</v>
+        <v>864563804.25</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8207,19 +8207,19 @@
         <v>472</v>
       </c>
       <c r="C236" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D236" s="7">
-        <v>0.787999</v>
+        <v>0.787395</v>
       </c>
       <c r="E236" s="8">
-        <v>1340179051.42</v>
+        <v>1344244683.64</v>
       </c>
       <c r="F236" s="9">
-        <v>7630</v>
+        <v>7627</v>
       </c>
       <c r="G236" s="8">
-        <v>1056059700.82</v>
+        <v>1058451562.52</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8230,19 +8230,19 @@
         <v>474</v>
       </c>
       <c r="C237" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D237" s="7">
-        <v>0.153903</v>
+        <v>0.154515</v>
       </c>
       <c r="E237" s="8">
-        <v>72240067575.38</v>
+        <v>72079266988.48</v>
       </c>
       <c r="F237" s="9">
-        <v>842921</v>
+        <v>842492</v>
       </c>
       <c r="G237" s="8">
-        <v>11117986898.46</v>
+        <v>11137325412.87</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -8253,19 +8253,19 @@
         <v>476</v>
       </c>
       <c r="C238" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D238" s="7">
-        <v>0.221555</v>
+        <v>0.223167</v>
       </c>
       <c r="E238" s="8">
-        <v>2430747764.44</v>
+        <v>2439702219.91</v>
       </c>
       <c r="F238" s="9">
-        <v>7574</v>
+        <v>7583</v>
       </c>
       <c r="G238" s="8">
-        <v>538543718.88</v>
+        <v>544462011.8</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -8276,19 +8276,19 @@
         <v>478</v>
       </c>
       <c r="C239" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D239" s="7">
-        <v>0.195171</v>
+        <v>0.196578</v>
       </c>
       <c r="E239" s="8">
-        <v>2329813201.5</v>
+        <v>2336607416.34</v>
       </c>
       <c r="F239" s="9">
-        <v>7334</v>
+        <v>7369</v>
       </c>
       <c r="G239" s="8">
-        <v>454711301.97</v>
+        <v>459326215.3</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,19 +8299,19 @@
         <v>480</v>
       </c>
       <c r="C240" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D240" s="7">
-        <v>0.343959</v>
+        <v>0.344701</v>
       </c>
       <c r="E240" s="8">
-        <v>31350431759.29</v>
+        <v>31352074524.59</v>
       </c>
       <c r="F240" s="9">
-        <v>120031</v>
+        <v>120305</v>
       </c>
       <c r="G240" s="8">
-        <v>10783270179.85</v>
+        <v>10807082254.78</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -8322,19 +8322,19 @@
         <v>482</v>
       </c>
       <c r="C241" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D241" s="7">
-        <v>0.126372</v>
+        <v>0.126579</v>
       </c>
       <c r="E241" s="8">
-        <v>3787742897.33</v>
+        <v>3786172159.94</v>
       </c>
       <c r="F241" s="9">
-        <v>7416</v>
+        <v>7414</v>
       </c>
       <c r="G241" s="8">
-        <v>478664193.88</v>
+        <v>479250272.6</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -8345,19 +8345,19 @@
         <v>484</v>
       </c>
       <c r="C242" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D242" s="7">
-        <v>0.126833</v>
+        <v>0.127613</v>
       </c>
       <c r="E242" s="8">
-        <v>89295443426.92</v>
+        <v>89270952086.14</v>
       </c>
       <c r="F242" s="9">
-        <v>403189</v>
+        <v>403282</v>
       </c>
       <c r="G242" s="8">
-        <v>11325607129.96</v>
+        <v>11392175514.24</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8368,19 +8368,19 @@
         <v>486</v>
       </c>
       <c r="C243" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D243" s="10">
-        <v>0.30811</v>
+        <v>46148</v>
+      </c>
+      <c r="D243" s="7">
+        <v>0.311994</v>
       </c>
       <c r="E243" s="8">
-        <v>3868793871.49</v>
+        <v>3892351555.92</v>
       </c>
       <c r="F243" s="9">
-        <v>18100</v>
+        <v>18207</v>
       </c>
       <c r="G243" s="8">
-        <v>1192014873.39</v>
+        <v>1214391910.12</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -8391,19 +8391,19 @@
         <v>488</v>
       </c>
       <c r="C244" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D244" s="7">
-        <v>0.081465</v>
+        <v>46148</v>
+      </c>
+      <c r="D244" s="10">
+        <v>0.08156</v>
       </c>
       <c r="E244" s="8">
-        <v>3840376304.8</v>
+        <v>3837592085.83</v>
       </c>
       <c r="F244" s="9">
-        <v>9176</v>
+        <v>9187</v>
       </c>
       <c r="G244" s="8">
-        <v>312855979.12</v>
+        <v>312993632.32</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8414,19 +8414,19 @@
         <v>490</v>
       </c>
       <c r="C245" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D245" s="7">
-        <v>0.247333</v>
+        <v>0.249754</v>
       </c>
       <c r="E245" s="8">
-        <v>2836764985.49</v>
+        <v>2845428160.45</v>
       </c>
       <c r="F245" s="9">
-        <v>14018</v>
+        <v>14093</v>
       </c>
       <c r="G245" s="8">
-        <v>701625182.97</v>
+        <v>710658139.13</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -8437,19 +8437,19 @@
         <v>492</v>
       </c>
       <c r="C246" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D246" s="7">
-        <v>0.069087</v>
+        <v>0.069169</v>
       </c>
       <c r="E246" s="8">
-        <v>4033163686.38</v>
+        <v>4028896720.67</v>
       </c>
       <c r="F246" s="9">
-        <v>7761</v>
+        <v>7769</v>
       </c>
       <c r="G246" s="8">
-        <v>278640455.98</v>
+        <v>278673265.21</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8460,19 +8460,19 @@
         <v>494</v>
       </c>
       <c r="C247" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D247" s="7">
-        <v>0.179301</v>
+        <v>0.179447</v>
       </c>
       <c r="E247" s="8">
-        <v>14382028950.61</v>
+        <v>14401000576.07</v>
       </c>
       <c r="F247" s="9">
-        <v>48737</v>
+        <v>48830</v>
       </c>
       <c r="G247" s="8">
-        <v>2578717897.75</v>
+        <v>2584220895.92</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8483,19 +8483,19 @@
         <v>496</v>
       </c>
       <c r="C248" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D248" s="7">
-        <v>0.024191</v>
+        <v>46148</v>
+      </c>
+      <c r="D248" s="11">
+        <v>0.0242</v>
       </c>
       <c r="E248" s="8">
-        <v>958890337679.97</v>
+        <v>955938729872.57</v>
       </c>
       <c r="F248" s="9">
-        <v>186999</v>
+        <v>186749</v>
       </c>
       <c r="G248" s="8">
-        <v>23196126746.84</v>
+        <v>23133572184.54</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8506,19 +8506,19 @@
         <v>498</v>
       </c>
       <c r="C249" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D249" s="10">
-        <v>0.73811</v>
+        <v>46148</v>
+      </c>
+      <c r="D249" s="7">
+        <v>0.735635</v>
       </c>
       <c r="E249" s="8">
-        <v>15348206647.69</v>
+        <v>15363782925.04</v>
       </c>
       <c r="F249" s="9">
-        <v>79500</v>
+        <v>79555</v>
       </c>
       <c r="G249" s="8">
-        <v>11328668577.16</v>
+        <v>11302140757.66</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8529,19 +8529,19 @@
         <v>500</v>
       </c>
       <c r="C250" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D250" s="7">
-        <v>0.639288</v>
+        <v>0.637807</v>
       </c>
       <c r="E250" s="8">
-        <v>8196090177.12</v>
+        <v>8207924031.58</v>
       </c>
       <c r="F250" s="9">
-        <v>75293</v>
+        <v>75455</v>
       </c>
       <c r="G250" s="8">
-        <v>5239662771.71</v>
+        <v>5235070848.89</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8552,19 +8552,19 @@
         <v>502</v>
       </c>
       <c r="C251" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D251" s="7">
-        <v>0.160955</v>
+        <v>0.161128</v>
       </c>
       <c r="E251" s="8">
-        <v>2778028636.62</v>
+        <v>2783390623.27</v>
       </c>
       <c r="F251" s="9">
-        <v>11334</v>
+        <v>11354</v>
       </c>
       <c r="G251" s="8">
-        <v>447138554.26</v>
+        <v>448482231.86</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8575,19 +8575,19 @@
         <v>504</v>
       </c>
       <c r="C252" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D252" s="7">
-        <v>0.095897</v>
+        <v>0.096121</v>
       </c>
       <c r="E252" s="8">
-        <v>4856993838.78</v>
+        <v>4873790814.18</v>
       </c>
       <c r="F252" s="9">
-        <v>69469</v>
+        <v>69543</v>
       </c>
       <c r="G252" s="8">
-        <v>465770314.88</v>
+        <v>468472791.11</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8598,19 +8598,19 @@
         <v>506</v>
       </c>
       <c r="C253" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D253" s="7">
-        <v>0.329484</v>
+        <v>0.329276</v>
       </c>
       <c r="E253" s="8">
-        <v>2193508174.75</v>
+        <v>2196197810.6</v>
       </c>
       <c r="F253" s="9">
-        <v>21093</v>
+        <v>21120</v>
       </c>
       <c r="G253" s="8">
-        <v>722726425.75</v>
+        <v>723154144.1</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8621,19 +8621,19 @@
         <v>508</v>
       </c>
       <c r="C254" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D254" s="7">
-        <v>0.141317</v>
+        <v>0.141675</v>
       </c>
       <c r="E254" s="8">
-        <v>660417220.75</v>
+        <v>661586544.65</v>
       </c>
       <c r="F254" s="9">
-        <v>2390</v>
+        <v>2395</v>
       </c>
       <c r="G254" s="8">
-        <v>93328318.15</v>
+        <v>93730179.45</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8644,19 +8644,19 @@
         <v>510</v>
       </c>
       <c r="C255" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D255" s="10">
-        <v>0.08292</v>
+        <v>46148</v>
+      </c>
+      <c r="D255" s="7">
+        <v>0.083032</v>
       </c>
       <c r="E255" s="8">
-        <v>629837570.15</v>
+        <v>631970853.95</v>
       </c>
       <c r="F255" s="9">
-        <v>13808</v>
+        <v>13858</v>
       </c>
       <c r="G255" s="8">
-        <v>52226325.8</v>
+        <v>52473993.78</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8667,19 +8667,19 @@
         <v>512</v>
       </c>
       <c r="C256" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D256" s="11">
-        <v>0.0966</v>
+        <v>46148</v>
+      </c>
+      <c r="D256" s="7">
+        <v>0.096898</v>
       </c>
       <c r="E256" s="8">
-        <v>4028718008.11</v>
+        <v>4027744122.05</v>
       </c>
       <c r="F256" s="9">
-        <v>78552</v>
+        <v>78597</v>
       </c>
       <c r="G256" s="8">
-        <v>389172446.27</v>
+        <v>390281448.87</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8690,19 +8690,19 @@
         <v>514</v>
       </c>
       <c r="C257" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D257" s="10">
-        <v>0.12698</v>
+        <v>46148</v>
+      </c>
+      <c r="D257" s="7">
+        <v>0.127346</v>
       </c>
       <c r="E257" s="8">
-        <v>3761280957.93</v>
+        <v>3766272379.7</v>
       </c>
       <c r="F257" s="9">
-        <v>19655</v>
+        <v>19669</v>
       </c>
       <c r="G257" s="8">
-        <v>477607795.99</v>
+        <v>479619396.85</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -8713,19 +8713,19 @@
         <v>516</v>
       </c>
       <c r="C258" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D258" s="7">
-        <v>0.093733</v>
+        <v>0.093831</v>
       </c>
       <c r="E258" s="8">
-        <v>584456377.58</v>
+        <v>580231325.28</v>
       </c>
       <c r="F258" s="9">
-        <v>10802</v>
+        <v>10892</v>
       </c>
       <c r="G258" s="8">
-        <v>54782898.1</v>
+        <v>54443622.28</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -8736,19 +8736,19 @@
         <v>518</v>
       </c>
       <c r="C259" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D259" s="7">
-        <v>0.132635</v>
+        <v>0.132773</v>
       </c>
       <c r="E259" s="8">
-        <v>4542188927.72</v>
+        <v>4482558126.45</v>
       </c>
       <c r="F259" s="9">
-        <v>20108</v>
+        <v>18213</v>
       </c>
       <c r="G259" s="8">
-        <v>602451876.28</v>
+        <v>595163416.9</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -8759,19 +8759,19 @@
         <v>520</v>
       </c>
       <c r="C260" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D260" s="7">
-        <v>0.154661</v>
+        <v>0.155188</v>
       </c>
       <c r="E260" s="8">
-        <v>1217332732.48</v>
+        <v>1217264303.63</v>
       </c>
       <c r="F260" s="9">
-        <v>59053</v>
+        <v>59043</v>
       </c>
       <c r="G260" s="8">
-        <v>188273325.94</v>
+        <v>188904631.54</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -8782,19 +8782,19 @@
         <v>522</v>
       </c>
       <c r="C261" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D261" s="7">
-        <v>0.761408</v>
+        <v>0.768047</v>
       </c>
       <c r="E261" s="8">
-        <v>8916340681.46</v>
+        <v>8890122107.2</v>
       </c>
       <c r="F261" s="9">
-        <v>26118</v>
+        <v>26137</v>
       </c>
       <c r="G261" s="8">
-        <v>6788973193.5</v>
+        <v>6828033980.53</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -8805,19 +8805,19 @@
         <v>524</v>
       </c>
       <c r="C262" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D262" s="7">
-        <v>0.101535</v>
+        <v>0.101748</v>
       </c>
       <c r="E262" s="8">
-        <v>14037551288.01</v>
+        <v>14018541093.66</v>
       </c>
       <c r="F262" s="9">
-        <v>128307</v>
+        <v>128276</v>
       </c>
       <c r="G262" s="8">
-        <v>1425300419.19</v>
+        <v>1426352847.13</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -8828,19 +8828,19 @@
         <v>526</v>
       </c>
       <c r="C263" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D263" s="7">
-        <v>0.013204</v>
+        <v>46148</v>
+      </c>
+      <c r="D263" s="10">
+        <v>0.01329</v>
       </c>
       <c r="E263" s="8">
-        <v>144971544746.53</v>
+        <v>146341709534.14</v>
       </c>
       <c r="F263" s="9">
-        <v>1648</v>
+        <v>1655</v>
       </c>
       <c r="G263" s="8">
-        <v>1914244548.19</v>
+        <v>1944855906.98</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -8851,19 +8851,19 @@
         <v>528</v>
       </c>
       <c r="C264" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D264" s="11">
-        <v>0.2826</v>
+        <v>46148</v>
+      </c>
+      <c r="D264" s="7">
+        <v>0.286221</v>
       </c>
       <c r="E264" s="8">
-        <v>5718617750.25</v>
+        <v>5709830867</v>
       </c>
       <c r="F264" s="9">
-        <v>44012</v>
+        <v>43965</v>
       </c>
       <c r="G264" s="8">
-        <v>1616082833.27</v>
+        <v>1634275219.85</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -8874,19 +8874,19 @@
         <v>530</v>
       </c>
       <c r="C265" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D265" s="7">
-        <v>0.407697</v>
+        <v>0.413142</v>
       </c>
       <c r="E265" s="8">
-        <v>1951787269.02</v>
+        <v>1955645201.56</v>
       </c>
       <c r="F265" s="9">
-        <v>21778</v>
+        <v>21794</v>
       </c>
       <c r="G265" s="8">
-        <v>795737167.25</v>
+        <v>807959815.07</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -8897,19 +8897,19 @@
         <v>532</v>
       </c>
       <c r="C266" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D266" s="7">
-        <v>0.130653</v>
+        <v>0.130667</v>
       </c>
       <c r="E266" s="8">
-        <v>34106181995.43</v>
+        <v>34220662985.72</v>
       </c>
       <c r="F266" s="9">
-        <v>102392</v>
+        <v>102641</v>
       </c>
       <c r="G266" s="8">
-        <v>4456058351.22</v>
+        <v>4471509982.28</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -8920,19 +8920,19 @@
         <v>534</v>
       </c>
       <c r="C267" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D267" s="7">
-        <v>0.236703</v>
+        <v>0.236554</v>
       </c>
       <c r="E267" s="8">
-        <v>2678416402.85</v>
+        <v>2681981591.49</v>
       </c>
       <c r="F267" s="9">
-        <v>24240</v>
+        <v>24246</v>
       </c>
       <c r="G267" s="8">
-        <v>633987978.93</v>
+        <v>634432782.57</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -8943,19 +8943,19 @@
         <v>536</v>
       </c>
       <c r="C268" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D268" s="7">
-        <v>0.012669</v>
+        <v>0.012779</v>
       </c>
       <c r="E268" s="8">
-        <v>737323803361.16</v>
+        <v>744985268532.7</v>
       </c>
       <c r="F268" s="9">
-        <v>71850</v>
+        <v>72308</v>
       </c>
       <c r="G268" s="8">
-        <v>9341123922.76</v>
+        <v>9520153928.9</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -8966,19 +8966,19 @@
         <v>538</v>
       </c>
       <c r="C269" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D269" s="7">
-        <v>0.501226</v>
+        <v>0.501284</v>
       </c>
       <c r="E269" s="8">
-        <v>5696225440.69</v>
+        <v>5711741305.87</v>
       </c>
       <c r="F269" s="9">
-        <v>72309</v>
+        <v>72312</v>
       </c>
       <c r="G269" s="8">
-        <v>2855098353.38</v>
+        <v>2863203169.72</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -8989,19 +8989,19 @@
         <v>540</v>
       </c>
       <c r="C270" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D270" s="7">
-        <v>0.301197</v>
+        <v>0.302371</v>
       </c>
       <c r="E270" s="8">
-        <v>1831782439.26</v>
+        <v>1834946484.28</v>
       </c>
       <c r="F270" s="9">
-        <v>95666</v>
+        <v>95658</v>
       </c>
       <c r="G270" s="8">
-        <v>551728287.42</v>
+        <v>554833929.82</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9012,19 +9012,19 @@
         <v>542</v>
       </c>
       <c r="C271" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D271" s="7">
-        <v>0.777589</v>
+        <v>0.782032</v>
       </c>
       <c r="E271" s="8">
-        <v>2052451721.8</v>
+        <v>2051560120.59</v>
       </c>
       <c r="F271" s="9">
-        <v>111721</v>
+        <v>111700</v>
       </c>
       <c r="G271" s="8">
-        <v>1595964517.32</v>
+        <v>1604385337.55</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9035,19 +9035,19 @@
         <v>544</v>
       </c>
       <c r="C272" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D272" s="7">
-        <v>0.522657</v>
+        <v>0.526631</v>
       </c>
       <c r="E272" s="8">
-        <v>1503880840.04</v>
+        <v>1501785307.26</v>
       </c>
       <c r="F272" s="9">
-        <v>37706</v>
+        <v>37702</v>
       </c>
       <c r="G272" s="8">
-        <v>786013544.13</v>
+        <v>790887116.49</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9058,19 +9058,19 @@
         <v>546</v>
       </c>
       <c r="C273" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D273" s="7">
-        <v>0.284108</v>
+        <v>0.284031</v>
       </c>
       <c r="E273" s="8">
-        <v>2820909009.36</v>
+        <v>2819561921.18</v>
       </c>
       <c r="F273" s="9">
-        <v>87303</v>
+        <v>87292</v>
       </c>
       <c r="G273" s="8">
-        <v>801442212.09</v>
+        <v>800843522.12</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9081,19 +9081,19 @@
         <v>548</v>
       </c>
       <c r="C274" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D274" s="7">
-        <v>2.386847</v>
+        <v>2.408187</v>
       </c>
       <c r="E274" s="8">
-        <v>1900055963.01</v>
+        <v>1903013261.78</v>
       </c>
       <c r="F274" s="9">
-        <v>57631</v>
+        <v>57654</v>
       </c>
       <c r="G274" s="8">
-        <v>4535143450.8</v>
+        <v>4582812697.38</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9104,19 +9104,19 @@
         <v>550</v>
       </c>
       <c r="C275" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D275" s="7">
-        <v>0.904791</v>
+        <v>0.909683</v>
       </c>
       <c r="E275" s="8">
-        <v>768974075.39</v>
+        <v>769347744.97</v>
       </c>
       <c r="F275" s="9">
-        <v>83376</v>
+        <v>83369</v>
       </c>
       <c r="G275" s="8">
-        <v>695760907.58</v>
+        <v>699862270.97</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9127,19 +9127,19 @@
         <v>552</v>
       </c>
       <c r="C276" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D276" s="7">
-        <v>0.375338</v>
+        <v>0.375685</v>
       </c>
       <c r="E276" s="8">
-        <v>9052111795.99</v>
+        <v>8977578634.16</v>
       </c>
       <c r="F276" s="9">
-        <v>107192</v>
+        <v>101101</v>
       </c>
       <c r="G276" s="8">
-        <v>3397599244.31</v>
+        <v>3372744799.67</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9150,19 +9150,19 @@
         <v>554</v>
       </c>
       <c r="C277" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D277" s="7">
-        <v>0.109732</v>
+        <v>0.110047</v>
       </c>
       <c r="E277" s="8">
-        <v>54737184808.7</v>
+        <v>54729428092.14</v>
       </c>
       <c r="F277" s="9">
-        <v>198607</v>
+        <v>198558</v>
       </c>
       <c r="G277" s="8">
-        <v>6006406126.16</v>
+        <v>6022803674.63</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9173,19 +9173,19 @@
         <v>556</v>
       </c>
       <c r="C278" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D278" s="7">
-        <v>0.115126</v>
+        <v>0.115359</v>
       </c>
       <c r="E278" s="8">
-        <v>83557948005.4</v>
+        <v>83549155682.87</v>
       </c>
       <c r="F278" s="9">
-        <v>1084899</v>
+        <v>1084740</v>
       </c>
       <c r="G278" s="8">
-        <v>9619693056.34</v>
+        <v>9638145623</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9196,19 +9196,19 @@
         <v>558</v>
       </c>
       <c r="C279" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D279" s="7">
-        <v>0.142543</v>
+        <v>0.142902</v>
       </c>
       <c r="E279" s="8">
-        <v>33121935674.1</v>
+        <v>33160837339.92</v>
       </c>
       <c r="F279" s="9">
-        <v>328522</v>
+        <v>328699</v>
       </c>
       <c r="G279" s="8">
-        <v>4721285841.92</v>
+        <v>4738745987.38</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9219,19 +9219,19 @@
         <v>560</v>
       </c>
       <c r="C280" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D280" s="7">
-        <v>0.169072</v>
+        <v>0.169943</v>
       </c>
       <c r="E280" s="8">
-        <v>3142126349.58</v>
+        <v>3158293249.39</v>
       </c>
       <c r="F280" s="9">
-        <v>27417</v>
+        <v>27435</v>
       </c>
       <c r="G280" s="8">
-        <v>531245590.38</v>
+        <v>536730298.23</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -9242,19 +9242,19 @@
         <v>562</v>
       </c>
       <c r="C281" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D281" s="7">
-        <v>0.724825</v>
+        <v>0.722502</v>
       </c>
       <c r="E281" s="8">
-        <v>44257319746.84</v>
+        <v>44344852517.71</v>
       </c>
       <c r="F281" s="9">
-        <v>674018</v>
+        <v>674921</v>
       </c>
       <c r="G281" s="8">
-        <v>32078823871.42</v>
+        <v>32039237034.26</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -9265,19 +9265,19 @@
         <v>564</v>
       </c>
       <c r="C282" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D282" s="7">
-        <v>0.261505</v>
+        <v>0.262739</v>
       </c>
       <c r="E282" s="8">
-        <v>8730966278.9</v>
+        <v>8740263137.27</v>
       </c>
       <c r="F282" s="9">
-        <v>108538</v>
+        <v>108548</v>
       </c>
       <c r="G282" s="8">
-        <v>2283188631.42</v>
+        <v>2296409901.1</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -9288,19 +9288,19 @@
         <v>566</v>
       </c>
       <c r="C283" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D283" s="7">
-        <v>0.542706</v>
+        <v>0.547835</v>
       </c>
       <c r="E283" s="8">
-        <v>11680463808.84</v>
+        <v>11724910688.71</v>
       </c>
       <c r="F283" s="9">
-        <v>139068</v>
+        <v>139145</v>
       </c>
       <c r="G283" s="8">
-        <v>6339062713.31</v>
+        <v>6423315721.12</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -9311,19 +9311,19 @@
         <v>568</v>
       </c>
       <c r="C284" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D284" s="10">
-        <v>0.30481</v>
+        <v>46148</v>
+      </c>
+      <c r="D284" s="7">
+        <v>0.305708</v>
       </c>
       <c r="E284" s="8">
-        <v>2284280459.6</v>
+        <v>2302946726.77</v>
       </c>
       <c r="F284" s="9">
-        <v>37393</v>
+        <v>37510</v>
       </c>
       <c r="G284" s="8">
-        <v>696271991.67</v>
+        <v>704028182.47</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -9334,19 +9334,19 @@
         <v>570</v>
       </c>
       <c r="C285" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D285" s="7">
-        <v>0.197185</v>
+        <v>0.197377</v>
       </c>
       <c r="E285" s="8">
-        <v>9520859651.96</v>
+        <v>9524514510.8</v>
       </c>
       <c r="F285" s="9">
-        <v>108170</v>
+        <v>108160</v>
       </c>
       <c r="G285" s="8">
-        <v>1877370890.68</v>
+        <v>1879921453.97</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -9357,19 +9357,19 @@
         <v>572</v>
       </c>
       <c r="C286" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D286" s="7">
-        <v>0.278734</v>
+        <v>0.279545</v>
       </c>
       <c r="E286" s="8">
-        <v>791918449.61</v>
+        <v>799649630.47</v>
       </c>
       <c r="F286" s="9">
-        <v>2803</v>
+        <v>2809</v>
       </c>
       <c r="G286" s="8">
-        <v>220734468.94</v>
+        <v>223538328.19</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -9380,19 +9380,19 @@
         <v>574</v>
       </c>
       <c r="C287" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D287" s="7">
-        <v>0.087888</v>
+        <v>0.087987</v>
       </c>
       <c r="E287" s="8">
-        <v>4088306875.8</v>
+        <v>4338787534.15</v>
       </c>
       <c r="F287" s="9">
-        <v>144401</v>
+        <v>147490</v>
       </c>
       <c r="G287" s="8">
-        <v>359313686.51</v>
+        <v>381758968.44</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -9403,19 +9403,19 @@
         <v>576</v>
       </c>
       <c r="C288" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D288" s="10">
-        <v>0.48253</v>
+        <v>46148</v>
+      </c>
+      <c r="D288" s="7">
+        <v>0.487692</v>
       </c>
       <c r="E288" s="8">
-        <v>1575037517.6</v>
+        <v>1584813548.68</v>
       </c>
       <c r="F288" s="9">
-        <v>4269</v>
+        <v>4275</v>
       </c>
       <c r="G288" s="8">
-        <v>760002959.56</v>
+        <v>772901077.83</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -9426,19 +9426,19 @@
         <v>578</v>
       </c>
       <c r="C289" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D289" s="10">
-        <v>0.01567</v>
+        <v>46148</v>
+      </c>
+      <c r="D289" s="7">
+        <v>0.015723</v>
       </c>
       <c r="E289" s="8">
-        <v>5833109286.12</v>
+        <v>5750124483.54</v>
       </c>
       <c r="F289" s="9">
-        <v>3654</v>
+        <v>3684</v>
       </c>
       <c r="G289" s="8">
-        <v>91407030.71</v>
+        <v>90409143.5</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -9449,19 +9449,19 @@
         <v>580</v>
       </c>
       <c r="C290" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D290" s="7">
-        <v>0.017596</v>
+        <v>0.017331</v>
       </c>
       <c r="E290" s="8">
-        <v>152118904163.83</v>
+        <v>153617180589.83</v>
       </c>
       <c r="F290" s="9">
-        <v>31610</v>
+        <v>31628</v>
       </c>
       <c r="G290" s="8">
-        <v>2676703259.14</v>
+        <v>2662374721.35</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -9472,19 +9472,19 @@
         <v>582</v>
       </c>
       <c r="C291" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D291" s="7">
-        <v>0.010678</v>
+        <v>0.010811</v>
       </c>
       <c r="E291" s="8">
-        <v>7482179760.16</v>
+        <v>8591713994.45</v>
       </c>
       <c r="F291" s="9">
-        <v>1286</v>
+        <v>1588</v>
       </c>
       <c r="G291" s="8">
-        <v>79895676.3</v>
+        <v>92888479.83</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -9495,19 +9495,19 @@
         <v>584</v>
       </c>
       <c r="C292" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D292" s="10">
-        <v>0.13316</v>
+        <v>46148</v>
+      </c>
+      <c r="D292" s="7">
+        <v>0.132001</v>
       </c>
       <c r="E292" s="8">
-        <v>52646888196.23</v>
+        <v>52665872053.26</v>
       </c>
       <c r="F292" s="9">
-        <v>107839</v>
+        <v>107905</v>
       </c>
       <c r="G292" s="8">
-        <v>7010449647.36</v>
+        <v>6951946282.81</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -9518,19 +9518,19 @@
         <v>586</v>
       </c>
       <c r="C293" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D293" s="7">
-        <v>0.051261</v>
+        <v>0.051314</v>
       </c>
       <c r="E293" s="8">
-        <v>12390222040.87</v>
+        <v>12382078963.26</v>
       </c>
       <c r="F293" s="9">
-        <v>28674</v>
+        <v>28782</v>
       </c>
       <c r="G293" s="8">
-        <v>635133345.18</v>
+        <v>635375119.55</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -9541,19 +9541,19 @@
         <v>588</v>
       </c>
       <c r="C294" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D294" s="7">
-        <v>0.022013</v>
+        <v>0.022038</v>
       </c>
       <c r="E294" s="8">
-        <v>57770746369.41</v>
+        <v>57932067966.88</v>
       </c>
       <c r="F294" s="9">
-        <v>10715</v>
+        <v>10720</v>
       </c>
       <c r="G294" s="8">
-        <v>1271703817.35</v>
+        <v>1276707348.33</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -9564,19 +9564,19 @@
         <v>590</v>
       </c>
       <c r="C295" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D295" s="7">
-        <v>0.031688</v>
+        <v>0.032221</v>
       </c>
       <c r="E295" s="8">
-        <v>55266951553.84</v>
+        <v>55650545277.4</v>
       </c>
       <c r="F295" s="9">
-        <v>33351</v>
+        <v>33455</v>
       </c>
       <c r="G295" s="8">
-        <v>1751319501.39</v>
+        <v>1793135205.32</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -9587,19 +9587,19 @@
         <v>592</v>
       </c>
       <c r="C296" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D296" s="7">
-        <v>0.019481</v>
+        <v>0.019198</v>
       </c>
       <c r="E296" s="8">
-        <v>960145869118.97</v>
+        <v>957802618873.89</v>
       </c>
       <c r="F296" s="9">
-        <v>178817</v>
+        <v>178911</v>
       </c>
       <c r="G296" s="8">
-        <v>18704642359.42</v>
+        <v>18388090672.17</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -9610,19 +9610,19 @@
         <v>594</v>
       </c>
       <c r="C297" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D297" s="7">
-        <v>0.101035</v>
+        <v>0.101268</v>
       </c>
       <c r="E297" s="8">
-        <v>37004681597.1</v>
+        <v>37184969090.64</v>
       </c>
       <c r="F297" s="9">
-        <v>382527</v>
+        <v>383207</v>
       </c>
       <c r="G297" s="8">
-        <v>3738785271.92</v>
+        <v>3765648406.59</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -9633,19 +9633,19 @@
         <v>596</v>
       </c>
       <c r="C298" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D298" s="7">
-        <v>0.086201</v>
+        <v>0.086358</v>
       </c>
       <c r="E298" s="8">
-        <v>38377264542.92</v>
+        <v>38355847275.55</v>
       </c>
       <c r="F298" s="9">
-        <v>48152</v>
+        <v>48135</v>
       </c>
       <c r="G298" s="8">
-        <v>3308146561.82</v>
+        <v>3312350131.3</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -9656,19 +9656,19 @@
         <v>598</v>
       </c>
       <c r="C299" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D299" s="7">
-        <v>0.095014</v>
+        <v>0.095264</v>
       </c>
       <c r="E299" s="8">
-        <v>39030594063.58</v>
+        <v>39047564040.98</v>
       </c>
       <c r="F299" s="9">
-        <v>527186</v>
+        <v>527317</v>
       </c>
       <c r="G299" s="8">
-        <v>3708457680.06</v>
+        <v>3719810952.96</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -9679,19 +9679,19 @@
         <v>600</v>
       </c>
       <c r="C300" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D300" s="7">
-        <v>0.020304</v>
+        <v>0.020402</v>
       </c>
       <c r="E300" s="8">
-        <v>35672650987.72</v>
+        <v>36233649793.67</v>
       </c>
       <c r="F300" s="9">
-        <v>25168</v>
+        <v>25576</v>
       </c>
       <c r="G300" s="8">
-        <v>724280465.07</v>
+        <v>739228429.81</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -9702,19 +9702,19 @@
         <v>602</v>
       </c>
       <c r="C301" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D301" s="7">
-        <v>0.010328</v>
+        <v>0.010344</v>
       </c>
       <c r="E301" s="8">
-        <v>3038285889.97</v>
+        <v>3715059235.16</v>
       </c>
       <c r="F301" s="9">
-        <v>656</v>
+        <v>896</v>
       </c>
       <c r="G301" s="8">
-        <v>31380380.02</v>
+        <v>38427139.27</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -9725,19 +9725,19 @@
         <v>604</v>
       </c>
       <c r="C302" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D302" s="7">
-        <v>0.015748</v>
+        <v>0.016082</v>
       </c>
       <c r="E302" s="8">
-        <v>23959992779.54</v>
+        <v>24233592711.55</v>
       </c>
       <c r="F302" s="9">
-        <v>11033</v>
+        <v>11057</v>
       </c>
       <c r="G302" s="8">
-        <v>377326720.56</v>
+        <v>389733566.94</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -9748,19 +9748,19 @@
         <v>606</v>
       </c>
       <c r="C303" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D303" s="7">
-        <v>0.018144</v>
+        <v>0.018289</v>
       </c>
       <c r="E303" s="8">
-        <v>11950111160.7</v>
+        <v>11964403955.86</v>
       </c>
       <c r="F303" s="9">
-        <v>6660</v>
+        <v>6653</v>
       </c>
       <c r="G303" s="8">
-        <v>216827344.32</v>
+        <v>218815570.15</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -9771,19 +9771,19 @@
         <v>608</v>
       </c>
       <c r="C304" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D304" s="7">
-        <v>0.094312</v>
+        <v>0.094712</v>
       </c>
       <c r="E304" s="8">
-        <v>21247660382.29</v>
+        <v>21400992497.27</v>
       </c>
       <c r="F304" s="9">
-        <v>347456</v>
+        <v>348734</v>
       </c>
       <c r="G304" s="8">
-        <v>2003907619.55</v>
+        <v>2026923677.71</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -9794,19 +9794,19 @@
         <v>610</v>
       </c>
       <c r="C305" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D305" s="7">
-        <v>0.018847</v>
+        <v>0.018918</v>
       </c>
       <c r="E305" s="8">
-        <v>10490442556.08</v>
+        <v>10494018544.53</v>
       </c>
       <c r="F305" s="9">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G305" s="8">
-        <v>197713871.37</v>
+        <v>198525170.49</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -9817,19 +9817,19 @@
         <v>612</v>
       </c>
       <c r="C306" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D306" s="7">
-        <v>0.015578</v>
+        <v>0.015597</v>
       </c>
       <c r="E306" s="8">
-        <v>9172553683.41</v>
+        <v>9196778107.66</v>
       </c>
       <c r="F306" s="9">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G306" s="8">
-        <v>142893051.38</v>
+        <v>143437701.26</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -9840,19 +9840,19 @@
         <v>614</v>
       </c>
       <c r="C307" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D307" s="10">
-        <v>0.01589</v>
+        <v>46148</v>
+      </c>
+      <c r="D307" s="7">
+        <v>0.015913</v>
       </c>
       <c r="E307" s="8">
-        <v>1260208910.42</v>
+        <v>1265506481.22</v>
       </c>
       <c r="F307" s="9">
         <v>23</v>
       </c>
       <c r="G307" s="8">
-        <v>20025114.35</v>
+        <v>20138613.98</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -9863,19 +9863,19 @@
         <v>616</v>
       </c>
       <c r="C308" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D308" s="7">
-        <v>0.228382</v>
+        <v>0.227185</v>
       </c>
       <c r="E308" s="8">
-        <v>48584906659.2</v>
+        <v>48745809737.99</v>
       </c>
       <c r="F308" s="9">
-        <v>174266</v>
+        <v>175189</v>
       </c>
       <c r="G308" s="8">
-        <v>11095905388.88</v>
+        <v>11074326062.83</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -9886,19 +9886,19 @@
         <v>618</v>
       </c>
       <c r="C309" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D309" s="7">
-        <v>0.011123</v>
+        <v>0.011112</v>
       </c>
       <c r="E309" s="8">
-        <v>2348538389.6</v>
+        <v>2373814161.05</v>
       </c>
       <c r="F309" s="9">
-        <v>1960</v>
+        <v>2038</v>
       </c>
       <c r="G309" s="8">
-        <v>26123211.92</v>
+        <v>26377939.47</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -9909,19 +9909,19 @@
         <v>620</v>
       </c>
       <c r="C310" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D310" s="7">
-        <v>0.029768</v>
+        <v>0.030365</v>
       </c>
       <c r="E310" s="8">
-        <v>12614606459.9</v>
+        <v>12804009344.2</v>
       </c>
       <c r="F310" s="9">
-        <v>17435</v>
+        <v>17600</v>
       </c>
       <c r="G310" s="8">
-        <v>375507038.94</v>
+        <v>388797271.56</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -9932,19 +9932,19 @@
         <v>622</v>
       </c>
       <c r="C311" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D311" s="11">
-        <v>0.0248</v>
+        <v>46148</v>
+      </c>
+      <c r="D311" s="7">
+        <v>0.024917</v>
       </c>
       <c r="E311" s="8">
-        <v>3023139371.24</v>
+        <v>3041305202.99</v>
       </c>
       <c r="F311" s="9">
-        <v>10250</v>
+        <v>10297</v>
       </c>
       <c r="G311" s="8">
-        <v>74974736.36</v>
+        <v>75780228.02</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -9955,19 +9955,19 @@
         <v>624</v>
       </c>
       <c r="C312" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D312" s="10">
-        <v>0.12346</v>
+        <v>46148</v>
+      </c>
+      <c r="D312" s="7">
+        <v>0.124058</v>
       </c>
       <c r="E312" s="8">
-        <v>619361004.68</v>
+        <v>618936204.09</v>
       </c>
       <c r="F312" s="9">
-        <v>94294</v>
+        <v>94260</v>
       </c>
       <c r="G312" s="8">
-        <v>76466442.59</v>
+        <v>76783884.84</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -9978,19 +9978,19 @@
         <v>626</v>
       </c>
       <c r="C313" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D313" s="7">
-        <v>0.090901</v>
+        <v>0.091008</v>
       </c>
       <c r="E313" s="8">
-        <v>1431676407.57</v>
+        <v>1377461890.07</v>
       </c>
       <c r="F313" s="9">
-        <v>26345</v>
+        <v>29002</v>
       </c>
       <c r="G313" s="8">
-        <v>130141504.96</v>
+        <v>125360004.94</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -10001,19 +10001,19 @@
         <v>628</v>
       </c>
       <c r="C314" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D314" s="7">
-        <v>0.080461</v>
+        <v>0.080571</v>
       </c>
       <c r="E314" s="8">
-        <v>2331675898.53</v>
+        <v>2467711310.35</v>
       </c>
       <c r="F314" s="9">
-        <v>74110</v>
+        <v>78430</v>
       </c>
       <c r="G314" s="8">
-        <v>187608949.12</v>
+        <v>198825797.11</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -10024,19 +10024,19 @@
         <v>630</v>
       </c>
       <c r="C315" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D315" s="7">
-        <v>0.388572</v>
+        <v>0.388492</v>
       </c>
       <c r="E315" s="8">
-        <v>5200900281.53</v>
+        <v>5219727986.14</v>
       </c>
       <c r="F315" s="9">
-        <v>71654</v>
+        <v>71848</v>
       </c>
       <c r="G315" s="8">
-        <v>2020924333.81</v>
+        <v>2027820549.15</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -10047,19 +10047,19 @@
         <v>632</v>
       </c>
       <c r="C316" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D316" s="7">
-        <v>0.204876</v>
+        <v>46148</v>
+      </c>
+      <c r="D316" s="10">
+        <v>0.20514</v>
       </c>
       <c r="E316" s="8">
-        <v>5834037193.46</v>
+        <v>5836293069.33</v>
       </c>
       <c r="F316" s="9">
-        <v>56440</v>
+        <v>56517</v>
       </c>
       <c r="G316" s="8">
-        <v>1195251715.88</v>
+        <v>1197254258.96</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -10070,19 +10070,19 @@
         <v>634</v>
       </c>
       <c r="C317" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D317" s="7">
-        <v>0.111793</v>
+        <v>46148</v>
+      </c>
+      <c r="D317" s="10">
+        <v>0.11174</v>
       </c>
       <c r="E317" s="8">
-        <v>2285773735.21</v>
+        <v>2329903458.07</v>
       </c>
       <c r="F317" s="9">
-        <v>8342</v>
+        <v>8462</v>
       </c>
       <c r="G317" s="8">
-        <v>255533525.48</v>
+        <v>260343028.35</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -10093,19 +10093,19 @@
         <v>636</v>
       </c>
       <c r="C318" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D318" s="7">
-        <v>0.545317</v>
+        <v>0.551094</v>
       </c>
       <c r="E318" s="8">
-        <v>4004494756.21</v>
+        <v>4012089835.87</v>
       </c>
       <c r="F318" s="9">
-        <v>50402</v>
+        <v>50534</v>
       </c>
       <c r="G318" s="8">
-        <v>2183720581.39</v>
+        <v>2211037541.34</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -10116,19 +10116,19 @@
         <v>638</v>
       </c>
       <c r="C319" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D319" s="7">
-        <v>0.085321</v>
+        <v>0.085576</v>
       </c>
       <c r="E319" s="8">
-        <v>8823779329.46</v>
+        <v>8915662982.92</v>
       </c>
       <c r="F319" s="9">
-        <v>187891</v>
+        <v>190320</v>
       </c>
       <c r="G319" s="8">
-        <v>752853332.71</v>
+        <v>762968634.94</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -10139,19 +10139,19 @@
         <v>640</v>
       </c>
       <c r="C320" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D320" s="7">
-        <v>0.108018</v>
+        <v>0.108332</v>
       </c>
       <c r="E320" s="8">
-        <v>23088102418.27</v>
+        <v>23129302460.53</v>
       </c>
       <c r="F320" s="9">
-        <v>137885</v>
+        <v>138141</v>
       </c>
       <c r="G320" s="8">
-        <v>2493926462.63</v>
+        <v>2505651125.64</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -10162,19 +10162,19 @@
         <v>642</v>
       </c>
       <c r="C321" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D321" s="7">
-        <v>0.151872</v>
+        <v>0.152035</v>
       </c>
       <c r="E321" s="8">
-        <v>13640095151.46</v>
+        <v>13091441538.09</v>
       </c>
       <c r="F321" s="9">
-        <v>61348</v>
+        <v>33578</v>
       </c>
       <c r="G321" s="8">
-        <v>2071555313.21</v>
+        <v>1990363120.58</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -10185,19 +10185,19 @@
         <v>644</v>
       </c>
       <c r="C322" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D322" s="7">
-        <v>0.133262</v>
+        <v>46148</v>
+      </c>
+      <c r="D322" s="11">
+        <v>0.1334</v>
       </c>
       <c r="E322" s="8">
-        <v>527557935.56</v>
+        <v>529675080.63</v>
       </c>
       <c r="F322" s="9">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G322" s="8">
-        <v>70303384.47</v>
+        <v>70658882.65</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -10208,19 +10208,19 @@
         <v>646</v>
       </c>
       <c r="C323" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D323" s="7">
-        <v>0.136224</v>
+        <v>0.137116</v>
       </c>
       <c r="E323" s="8">
-        <v>224790258.32</v>
+        <v>226635218.68</v>
       </c>
       <c r="F323" s="9">
         <v>418</v>
       </c>
       <c r="G323" s="8">
-        <v>30621840.73</v>
+        <v>31075273.86</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -10231,19 +10231,19 @@
         <v>648</v>
       </c>
       <c r="C324" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D324" s="7">
-        <v>0.166151</v>
+        <v>0.167498</v>
       </c>
       <c r="E324" s="8">
-        <v>296355486.99</v>
+        <v>299917151.4</v>
       </c>
       <c r="F324" s="9">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="G324" s="8">
-        <v>49239847.45</v>
+        <v>50235463.03</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -10254,19 +10254,19 @@
         <v>650</v>
       </c>
       <c r="C325" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D325" s="7">
-        <v>0.196745</v>
+        <v>0.198781</v>
       </c>
       <c r="E325" s="8">
-        <v>359894925.09</v>
+        <v>361027812.58</v>
       </c>
       <c r="F325" s="9">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G325" s="8">
-        <v>70807534.66</v>
+        <v>71765474.92</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -10277,19 +10277,19 @@
         <v>652</v>
       </c>
       <c r="C326" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D326" s="7">
-        <v>0.142133</v>
+        <v>0.142788</v>
       </c>
       <c r="E326" s="8">
-        <v>413474457.34</v>
+        <v>421247561.35</v>
       </c>
       <c r="F326" s="9">
-        <v>2061</v>
+        <v>2106</v>
       </c>
       <c r="G326" s="8">
-        <v>58768491.12</v>
+        <v>60149114.06</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -10300,19 +10300,19 @@
         <v>654</v>
       </c>
       <c r="C327" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D327" s="7">
-        <v>0.097022</v>
+        <v>0.097429</v>
       </c>
       <c r="E327" s="8">
-        <v>40725363091.17</v>
+        <v>40710184940.33</v>
       </c>
       <c r="F327" s="9">
-        <v>374551</v>
+        <v>374355</v>
       </c>
       <c r="G327" s="8">
-        <v>3951269544.65</v>
+        <v>3966372117.16</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -10323,19 +10323,19 @@
         <v>656</v>
       </c>
       <c r="C328" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D328" s="7">
-        <v>0.173417</v>
+        <v>46148</v>
+      </c>
+      <c r="D328" s="10">
+        <v>0.17493</v>
       </c>
       <c r="E328" s="8">
-        <v>193203335.53</v>
+        <v>192864836.5</v>
       </c>
       <c r="F328" s="9">
         <v>471</v>
       </c>
       <c r="G328" s="8">
-        <v>33504767.65</v>
+        <v>33737817.82</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -10346,19 +10346,19 @@
         <v>658</v>
       </c>
       <c r="C329" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D329" s="7">
-        <v>0.203394</v>
+        <v>0.205452</v>
       </c>
       <c r="E329" s="8">
-        <v>238564663.16</v>
+        <v>239996059.9</v>
       </c>
       <c r="F329" s="9">
         <v>496</v>
       </c>
       <c r="G329" s="8">
-        <v>48522581.98</v>
+        <v>49307702.2</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -10369,19 +10369,19 @@
         <v>660</v>
       </c>
       <c r="C330" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D330" s="7">
-        <v>0.289571</v>
+        <v>0.291493</v>
       </c>
       <c r="E330" s="8">
-        <v>1251520848.97</v>
+        <v>1269373494.29</v>
       </c>
       <c r="F330" s="9">
-        <v>8756</v>
+        <v>8876</v>
       </c>
       <c r="G330" s="8">
-        <v>362403645.72</v>
+        <v>370013593.19</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
@@ -10392,19 +10392,19 @@
         <v>662</v>
       </c>
       <c r="C331" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D331" s="7">
-        <v>0.091478</v>
+        <v>0.091688</v>
       </c>
       <c r="E331" s="8">
-        <v>6835954447.63</v>
+        <v>6866593616.44</v>
       </c>
       <c r="F331" s="9">
-        <v>123272</v>
+        <v>123326</v>
       </c>
       <c r="G331" s="8">
-        <v>625337858.86</v>
+        <v>629581126.01</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
@@ -10415,19 +10415,19 @@
         <v>664</v>
       </c>
       <c r="C332" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D332" s="7">
-        <v>0.073847</v>
+        <v>0.074032</v>
       </c>
       <c r="E332" s="8">
-        <v>103572760453.86</v>
+        <v>103737972713.69</v>
       </c>
       <c r="F332" s="9">
-        <v>148083</v>
+        <v>148387</v>
       </c>
       <c r="G332" s="8">
-        <v>7648585477.65</v>
+        <v>7679905473.11</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
@@ -10438,19 +10438,19 @@
         <v>666</v>
       </c>
       <c r="C333" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D333" s="7">
-        <v>0.065525</v>
+        <v>0.065604</v>
       </c>
       <c r="E333" s="8">
-        <v>111707093186.66</v>
+        <v>112005417282.97</v>
       </c>
       <c r="F333" s="9">
-        <v>99408</v>
+        <v>99725</v>
       </c>
       <c r="G333" s="8">
-        <v>7319580420.91</v>
+        <v>7348010784.96</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
@@ -10461,19 +10461,19 @@
         <v>668</v>
       </c>
       <c r="C334" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D334" s="7">
-        <v>0.086038</v>
+        <v>0.086378</v>
       </c>
       <c r="E334" s="8">
-        <v>64990903519.87</v>
+        <v>65105398525.42</v>
       </c>
       <c r="F334" s="9">
-        <v>123071</v>
+        <v>123389</v>
       </c>
       <c r="G334" s="8">
-        <v>5591659446.13</v>
+        <v>5623667023.78</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
@@ -10484,19 +10484,19 @@
         <v>670</v>
       </c>
       <c r="C335" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D335" s="7">
-        <v>0.449894</v>
+        <v>0.448201</v>
       </c>
       <c r="E335" s="8">
-        <v>52411821731.06</v>
+        <v>52408563953.5</v>
       </c>
       <c r="F335" s="9">
-        <v>126725</v>
+        <v>126731</v>
       </c>
       <c r="G335" s="8">
-        <v>23579783981.95</v>
+        <v>23489566592.03</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
@@ -10507,19 +10507,19 @@
         <v>672</v>
       </c>
       <c r="C336" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D336" s="7">
-        <v>0.099217</v>
+        <v>0.099359</v>
       </c>
       <c r="E336" s="8">
-        <v>5341337688.84</v>
+        <v>5337212876.06</v>
       </c>
       <c r="F336" s="9">
-        <v>8787</v>
+        <v>8789</v>
       </c>
       <c r="G336" s="8">
-        <v>529953176.32</v>
+        <v>530300287.75</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
@@ -10530,19 +10530,19 @@
         <v>674</v>
       </c>
       <c r="C337" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D337" s="7">
-        <v>0.354309</v>
+        <v>0.356979</v>
       </c>
       <c r="E337" s="8">
-        <v>15803075841.99</v>
+        <v>15776814739.47</v>
       </c>
       <c r="F337" s="9">
-        <v>28607</v>
+        <v>28623</v>
       </c>
       <c r="G337" s="8">
-        <v>5599167169.38</v>
+        <v>5631991645.86</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
@@ -10553,19 +10553,19 @@
         <v>676</v>
       </c>
       <c r="C338" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D338" s="7">
-        <v>0.010113</v>
+        <v>0.010071</v>
       </c>
       <c r="E338" s="8">
-        <v>78589447884.57</v>
+        <v>79550414930.04</v>
       </c>
       <c r="F338" s="9">
-        <v>4323</v>
+        <v>4391</v>
       </c>
       <c r="G338" s="8">
-        <v>794791796.28</v>
+        <v>801126546.55</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
@@ -10576,19 +10576,19 @@
         <v>678</v>
       </c>
       <c r="C339" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D339" s="7">
-        <v>0.082008</v>
+        <v>0.082116</v>
       </c>
       <c r="E339" s="8">
-        <v>3724476327.08</v>
+        <v>3716713201.95</v>
       </c>
       <c r="F339" s="9">
-        <v>78430</v>
+        <v>78389</v>
       </c>
       <c r="G339" s="8">
-        <v>305436756.44</v>
+        <v>305201484.09</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
@@ -10599,19 +10599,19 @@
         <v>680</v>
       </c>
       <c r="C340" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D340" s="7">
-        <v>0.091631</v>
+        <v>0.091697</v>
       </c>
       <c r="E340" s="8">
-        <v>645513157.86</v>
+        <v>648457712.86</v>
       </c>
       <c r="F340" s="9">
-        <v>12876</v>
+        <v>13145</v>
       </c>
       <c r="G340" s="8">
-        <v>59149124.32</v>
+        <v>59461923.79</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -10622,19 +10622,19 @@
         <v>682</v>
       </c>
       <c r="C341" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D341" s="7">
-        <v>0.043135</v>
+        <v>0.043331</v>
       </c>
       <c r="E341" s="8">
-        <v>1046260459.49</v>
+        <v>1050167437.3</v>
       </c>
       <c r="F341" s="9">
-        <v>2214</v>
+        <v>2224</v>
       </c>
       <c r="G341" s="8">
-        <v>45130885.26</v>
+        <v>45504420.72</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
@@ -10645,19 +10645,19 @@
         <v>684</v>
       </c>
       <c r="C342" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D342" s="7">
-        <v>0.049779</v>
+        <v>0.049764</v>
       </c>
       <c r="E342" s="8">
-        <v>3923974893.77</v>
+        <v>3934680328.25</v>
       </c>
       <c r="F342" s="9">
-        <v>4338</v>
+        <v>4345</v>
       </c>
       <c r="G342" s="8">
-        <v>195330530.31</v>
+        <v>195804724.45</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
@@ -10668,19 +10668,19 @@
         <v>686</v>
       </c>
       <c r="C343" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D343" s="7">
-        <v>0.013749</v>
+        <v>0.013686</v>
       </c>
       <c r="E343" s="8">
-        <v>34526011617.38</v>
+        <v>34684822996.44</v>
       </c>
       <c r="F343" s="9">
-        <v>27370</v>
+        <v>27794</v>
       </c>
       <c r="G343" s="8">
-        <v>474693285.88</v>
+        <v>474701778.08</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
@@ -10691,19 +10691,19 @@
         <v>688</v>
       </c>
       <c r="C344" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D344" s="7">
-        <v>0.072893</v>
+        <v>0.073898</v>
       </c>
       <c r="E344" s="8">
-        <v>48789199866.39</v>
+        <v>49688037980.23</v>
       </c>
       <c r="F344" s="9">
-        <v>121331</v>
+        <v>122317</v>
       </c>
       <c r="G344" s="8">
-        <v>3556404778.77</v>
+        <v>3671826701.76</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
@@ -10714,19 +10714,19 @@
         <v>690</v>
       </c>
       <c r="C345" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D345" s="10">
-        <v>0.01291</v>
+        <v>46148</v>
+      </c>
+      <c r="D345" s="7">
+        <v>0.013038</v>
       </c>
       <c r="E345" s="8">
-        <v>14745359307.24</v>
+        <v>15254088929.66</v>
       </c>
       <c r="F345" s="9">
-        <v>5496</v>
+        <v>5740</v>
       </c>
       <c r="G345" s="8">
-        <v>190356324.64</v>
+        <v>198884256.6</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
@@ -10737,19 +10737,19 @@
         <v>692</v>
       </c>
       <c r="C346" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D346" s="7">
-        <v>0.014866</v>
+        <v>0.014882</v>
       </c>
       <c r="E346" s="8">
-        <v>70369446553.81</v>
+        <v>71783008431.94</v>
       </c>
       <c r="F346" s="9">
-        <v>18714</v>
+        <v>19089</v>
       </c>
       <c r="G346" s="8">
-        <v>1046088964.93</v>
+        <v>1068243355.49</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
@@ -10760,19 +10760,19 @@
         <v>694</v>
       </c>
       <c r="C347" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D347" s="7">
-        <v>0.049682</v>
+        <v>0.049677</v>
       </c>
       <c r="E347" s="8">
-        <v>7410431215.51</v>
+        <v>7378391014.42</v>
       </c>
       <c r="F347" s="9">
-        <v>9427</v>
+        <v>9453</v>
       </c>
       <c r="G347" s="8">
-        <v>368161358.16</v>
+        <v>366537298.4</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
@@ -10783,19 +10783,19 @@
         <v>696</v>
       </c>
       <c r="C348" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D348" s="10">
-        <v>0.08701</v>
+        <v>46148</v>
+      </c>
+      <c r="D348" s="7">
+        <v>0.087101</v>
       </c>
       <c r="E348" s="8">
-        <v>580813109.92</v>
+        <v>589739308.1</v>
       </c>
       <c r="F348" s="9">
-        <v>6845</v>
+        <v>6976</v>
       </c>
       <c r="G348" s="8">
-        <v>50536746.84</v>
+        <v>51366826.99</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
@@ -10806,19 +10806,19 @@
         <v>698</v>
       </c>
       <c r="C349" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D349" s="7">
-        <v>0.048477</v>
+        <v>0.048641</v>
       </c>
       <c r="E349" s="8">
-        <v>3894674315.37</v>
+        <v>3882091755.91</v>
       </c>
       <c r="F349" s="9">
-        <v>5931</v>
+        <v>5929</v>
       </c>
       <c r="G349" s="8">
-        <v>188801786.87</v>
+        <v>188829212.51</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
@@ -10829,19 +10829,19 @@
         <v>700</v>
       </c>
       <c r="C350" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D350" s="7">
-        <v>0.020562</v>
+        <v>0.020649</v>
       </c>
       <c r="E350" s="8">
-        <v>8792926649.37</v>
+        <v>8753630300.72</v>
       </c>
       <c r="F350" s="9">
         <v>339</v>
       </c>
       <c r="G350" s="8">
-        <v>180800303.87</v>
+        <v>180751419.72</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
@@ -10852,19 +10852,19 @@
         <v>702</v>
       </c>
       <c r="C351" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D351" s="7">
-        <v>0.014993</v>
+        <v>46148</v>
+      </c>
+      <c r="D351" s="10">
+        <v>0.01502</v>
       </c>
       <c r="E351" s="8">
-        <v>15798545752.64</v>
+        <v>15833479454.21</v>
       </c>
       <c r="F351" s="9">
-        <v>5869</v>
+        <v>5907</v>
       </c>
       <c r="G351" s="8">
-        <v>236869124.89</v>
+        <v>237821352.01</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -10875,19 +10875,19 @@
         <v>704</v>
       </c>
       <c r="C352" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D352" s="7">
-        <v>0.013779</v>
+        <v>0.013907</v>
       </c>
       <c r="E352" s="8">
-        <v>22250140748.7</v>
+        <v>22173176680.7</v>
       </c>
       <c r="F352" s="9">
-        <v>5713</v>
+        <v>5794</v>
       </c>
       <c r="G352" s="8">
-        <v>306581398.69</v>
+        <v>308361783.64</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -10898,19 +10898,19 @@
         <v>706</v>
       </c>
       <c r="C353" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D353" s="7">
-        <v>0.014407</v>
+        <v>46148</v>
+      </c>
+      <c r="D353" s="10">
+        <v>0.01452</v>
       </c>
       <c r="E353" s="8">
-        <v>23502988333.69</v>
+        <v>23613349866.26</v>
       </c>
       <c r="F353" s="9">
-        <v>10678</v>
+        <v>10749</v>
       </c>
       <c r="G353" s="8">
-        <v>338608939.32</v>
+        <v>342864779.52</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
@@ -10921,19 +10921,19 @@
         <v>708</v>
       </c>
       <c r="C354" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D354" s="7">
-        <v>0.015729</v>
+        <v>0.016086</v>
       </c>
       <c r="E354" s="8">
-        <v>38532791977.07</v>
+        <v>38996696023.15</v>
       </c>
       <c r="F354" s="9">
-        <v>10339</v>
+        <v>10580</v>
       </c>
       <c r="G354" s="8">
-        <v>606063366.18</v>
+        <v>627292140.54</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -10944,19 +10944,19 @@
         <v>710</v>
       </c>
       <c r="C355" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D355" s="7">
-        <v>0.048796</v>
+        <v>0.048944</v>
       </c>
       <c r="E355" s="8">
-        <v>2900508908.58</v>
+        <v>2897363796.43</v>
       </c>
       <c r="F355" s="9">
-        <v>5147</v>
+        <v>5134</v>
       </c>
       <c r="G355" s="8">
-        <v>141532057.33</v>
+        <v>141809178.55</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
@@ -10967,19 +10967,19 @@
         <v>712</v>
       </c>
       <c r="C356" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D356" s="7">
-        <v>0.227853</v>
+        <v>46148</v>
+      </c>
+      <c r="D356" s="10">
+        <v>0.22872</v>
       </c>
       <c r="E356" s="8">
-        <v>8784748155.95</v>
+        <v>8791205610.44</v>
       </c>
       <c r="F356" s="9">
-        <v>47759</v>
+        <v>47791</v>
       </c>
       <c r="G356" s="8">
-        <v>2001634241.52</v>
+        <v>2010726347.93</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
@@ -10990,19 +10990,19 @@
         <v>714</v>
       </c>
       <c r="C357" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D357" s="7">
-        <v>0.082892</v>
+        <v>0.082974</v>
       </c>
       <c r="E357" s="8">
-        <v>11895683936.31</v>
+        <v>11930003826.75</v>
       </c>
       <c r="F357" s="9">
-        <v>21868</v>
+        <v>21924</v>
       </c>
       <c r="G357" s="8">
-        <v>986060542.51</v>
+        <v>989880709.02</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
@@ -11013,19 +11013,19 @@
         <v>716</v>
       </c>
       <c r="C358" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D358" s="7">
-        <v>0.307619</v>
+        <v>0.307363</v>
       </c>
       <c r="E358" s="8">
-        <v>3857488420.48</v>
+        <v>3852096888.1</v>
       </c>
       <c r="F358" s="9">
-        <v>27529</v>
+        <v>27509</v>
       </c>
       <c r="G358" s="8">
-        <v>1186635292.92</v>
+        <v>1183992975.61</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
@@ -11036,19 +11036,19 @@
         <v>718</v>
       </c>
       <c r="C359" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D359" s="7">
-        <v>1.354247</v>
+        <v>1.365824</v>
       </c>
       <c r="E359" s="8">
-        <v>8860805744.44</v>
+        <v>8847120044.63</v>
       </c>
       <c r="F359" s="9">
-        <v>245129</v>
+        <v>245062</v>
       </c>
       <c r="G359" s="8">
-        <v>11999718078.25</v>
+        <v>12083607675.32</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
@@ -11059,19 +11059,19 @@
         <v>720</v>
       </c>
       <c r="C360" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D360" s="7">
-        <v>0.094398</v>
+        <v>0.094676</v>
       </c>
       <c r="E360" s="8">
-        <v>542419874321.37</v>
+        <v>542018616734.05</v>
       </c>
       <c r="F360" s="9">
-        <v>2782574</v>
+        <v>2781036</v>
       </c>
       <c r="G360" s="8">
-        <v>51203093645.51</v>
+        <v>51316052770.95</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
@@ -11082,19 +11082,19 @@
         <v>722</v>
       </c>
       <c r="C361" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D361" s="7">
-        <v>0.320402</v>
+        <v>0.321281</v>
       </c>
       <c r="E361" s="8">
-        <v>23847313249.53</v>
+        <v>23835773310.03</v>
       </c>
       <c r="F361" s="9">
-        <v>422745</v>
+        <v>422557</v>
       </c>
       <c r="G361" s="8">
-        <v>7640723132.96</v>
+        <v>7657982068.82</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
@@ -11105,19 +11105,19 @@
         <v>724</v>
       </c>
       <c r="C362" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D362" s="7">
-        <v>0.350126</v>
+        <v>0.350496</v>
       </c>
       <c r="E362" s="8">
-        <v>85942824576.52</v>
+        <v>86790882307.59</v>
       </c>
       <c r="F362" s="9">
-        <v>432237</v>
+        <v>491742</v>
       </c>
       <c r="G362" s="8">
-        <v>30090858975.73</v>
+        <v>30419848452.04</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
@@ -11128,19 +11128,19 @@
         <v>726</v>
       </c>
       <c r="C363" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D363" s="10">
-        <v>0.22203</v>
+        <v>46148</v>
+      </c>
+      <c r="D363" s="7">
+        <v>0.223016</v>
       </c>
       <c r="E363" s="8">
-        <v>20363733191.76</v>
+        <v>20377370364.26</v>
       </c>
       <c r="F363" s="9">
-        <v>70049</v>
+        <v>70116</v>
       </c>
       <c r="G363" s="8">
-        <v>4521352824.2</v>
+        <v>4544485133.58</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
@@ -11151,19 +11151,19 @@
         <v>728</v>
       </c>
       <c r="C364" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D364" s="7">
-        <v>0.101822</v>
+        <v>0.101968</v>
       </c>
       <c r="E364" s="8">
-        <v>3765192665.89</v>
+        <v>3767497931.63</v>
       </c>
       <c r="F364" s="9">
-        <v>8002</v>
+        <v>8018</v>
       </c>
       <c r="G364" s="8">
-        <v>383379513.77</v>
+        <v>384163967.68</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
@@ -11174,19 +11174,19 @@
         <v>730</v>
       </c>
       <c r="C365" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D365" s="7">
-        <v>0.137243</v>
+        <v>0.138217</v>
       </c>
       <c r="E365" s="8">
-        <v>104111234092.62</v>
+        <v>104035265266.05</v>
       </c>
       <c r="F365" s="9">
-        <v>1909280</v>
+        <v>1908209</v>
       </c>
       <c r="G365" s="8">
-        <v>14288498052.94</v>
+        <v>14379461445.84</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
@@ -11197,19 +11197,19 @@
         <v>732</v>
       </c>
       <c r="C366" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D366" s="7">
-        <v>0.136265</v>
+        <v>0.136347</v>
       </c>
       <c r="E366" s="8">
-        <v>57781264617.66</v>
+        <v>57845650100.66</v>
       </c>
       <c r="F366" s="9">
-        <v>120299</v>
+        <v>120530</v>
       </c>
       <c r="G366" s="8">
-        <v>7873545666.26</v>
+        <v>7887058620.78</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
@@ -11220,19 +11220,19 @@
         <v>734</v>
       </c>
       <c r="C367" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D367" s="7">
-        <v>0.733668</v>
+        <v>0.733552</v>
       </c>
       <c r="E367" s="8">
-        <v>16797498911.65</v>
+        <v>16807225791.24</v>
       </c>
       <c r="F367" s="9">
-        <v>342098</v>
+        <v>342249</v>
       </c>
       <c r="G367" s="8">
-        <v>12323786785.84</v>
+        <v>12328966352.06</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
@@ -11243,19 +11243,19 @@
         <v>736</v>
       </c>
       <c r="C368" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D368" s="7">
-        <v>0.146717</v>
+        <v>0.146817</v>
       </c>
       <c r="E368" s="8">
-        <v>31183749020.61</v>
+        <v>31119562930.55</v>
       </c>
       <c r="F368" s="9">
-        <v>93266</v>
+        <v>93199</v>
       </c>
       <c r="G368" s="8">
-        <v>4575175378.92</v>
+        <v>4568895317.2</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
@@ -11266,19 +11266,19 @@
         <v>738</v>
       </c>
       <c r="C369" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D369" s="7">
-        <v>0.170468</v>
+        <v>0.171581</v>
       </c>
       <c r="E369" s="8">
-        <v>2083070979.82</v>
+        <v>2082839732.97</v>
       </c>
       <c r="F369" s="9">
-        <v>7378</v>
+        <v>7376</v>
       </c>
       <c r="G369" s="8">
-        <v>355096769.99</v>
+        <v>357374936.66</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
@@ -11289,19 +11289,19 @@
         <v>740</v>
       </c>
       <c r="C370" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D370" s="7">
-        <v>0.383961</v>
+        <v>0.384391</v>
       </c>
       <c r="E370" s="8">
-        <v>4954376966.19</v>
+        <v>5019249678.7</v>
       </c>
       <c r="F370" s="9">
-        <v>18775</v>
+        <v>19094</v>
       </c>
       <c r="G370" s="8">
-        <v>1902285988</v>
+        <v>1929355359.65</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
@@ -11312,19 +11312,19 @@
         <v>742</v>
       </c>
       <c r="C371" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D371" s="7">
-        <v>0.770339</v>
+        <v>0.768132</v>
       </c>
       <c r="E371" s="8">
-        <v>328999077775.19</v>
+        <v>329042245019.24</v>
       </c>
       <c r="F371" s="9">
-        <v>2044869</v>
+        <v>2043823</v>
       </c>
       <c r="G371" s="8">
-        <v>253440764815.35</v>
+        <v>252747893967.75</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
@@ -11335,19 +11335,19 @@
         <v>744</v>
       </c>
       <c r="C372" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D372" s="7">
-        <v>0.158792</v>
+        <v>46148</v>
+      </c>
+      <c r="D372" s="11">
+        <v>0.1594</v>
       </c>
       <c r="E372" s="8">
-        <v>23940344803.47</v>
+        <v>23983314823</v>
       </c>
       <c r="F372" s="9">
-        <v>109336</v>
+        <v>109400</v>
       </c>
       <c r="G372" s="8">
-        <v>3801529928.67</v>
+        <v>3822934404.09</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
@@ -11358,19 +11358,19 @@
         <v>746</v>
       </c>
       <c r="C373" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D373" s="7">
-        <v>0.193036</v>
+        <v>0.195211</v>
       </c>
       <c r="E373" s="8">
-        <v>3602346928.3</v>
+        <v>3593936953.85</v>
       </c>
       <c r="F373" s="9">
-        <v>11527</v>
+        <v>11497</v>
       </c>
       <c r="G373" s="8">
-        <v>695382821.55</v>
+        <v>701576972.22</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
@@ -11381,19 +11381,19 @@
         <v>748</v>
       </c>
       <c r="C374" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D374" s="7">
-        <v>0.416505</v>
+        <v>0.413877</v>
       </c>
       <c r="E374" s="8">
-        <v>55769154239.97</v>
+        <v>55619251186.21</v>
       </c>
       <c r="F374" s="9">
-        <v>289753</v>
+        <v>289066</v>
       </c>
       <c r="G374" s="8">
-        <v>23228139817.21</v>
+        <v>23019509565.7</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
@@ -11404,19 +11404,19 @@
         <v>750</v>
       </c>
       <c r="C375" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D375" s="7">
-        <v>0.525022</v>
+        <v>0.525823</v>
       </c>
       <c r="E375" s="8">
-        <v>1259671913.61</v>
+        <v>1262960755.05</v>
       </c>
       <c r="F375" s="9">
-        <v>14257</v>
+        <v>14383</v>
       </c>
       <c r="G375" s="8">
-        <v>661356002.61</v>
+        <v>664094412.88</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
@@ -11427,19 +11427,19 @@
         <v>752</v>
       </c>
       <c r="C376" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D376" s="7">
-        <v>0.185364</v>
+        <v>0.187455</v>
       </c>
       <c r="E376" s="8">
-        <v>6832756865.79</v>
+        <v>6817666996.84</v>
       </c>
       <c r="F376" s="9">
-        <v>16267</v>
+        <v>16238</v>
       </c>
       <c r="G376" s="8">
-        <v>1266547443.46</v>
+        <v>1278003321.26</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
@@ -11450,19 +11450,19 @@
         <v>754</v>
       </c>
       <c r="C377" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D377" s="7">
-        <v>0.119187</v>
+        <v>0.119706</v>
       </c>
       <c r="E377" s="8">
-        <v>7590001627.61</v>
+        <v>7584650682.56</v>
       </c>
       <c r="F377" s="9">
-        <v>23930</v>
+        <v>23901</v>
       </c>
       <c r="G377" s="8">
-        <v>904627268.49</v>
+        <v>907930473.42</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
@@ -11473,19 +11473,19 @@
         <v>756</v>
       </c>
       <c r="C378" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D378" s="10">
-        <v>0.17985</v>
+        <v>46148</v>
+      </c>
+      <c r="D378" s="7">
+        <v>0.181383</v>
       </c>
       <c r="E378" s="8">
-        <v>14153979899.28</v>
+        <v>14141367461.5</v>
       </c>
       <c r="F378" s="9">
-        <v>50834</v>
+        <v>50784</v>
       </c>
       <c r="G378" s="8">
-        <v>2545592397.6</v>
+        <v>2565003544.42</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
@@ -11496,19 +11496,19 @@
         <v>758</v>
       </c>
       <c r="C379" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D379" s="10">
-        <v>0.08854</v>
+        <v>0.08899</v>
       </c>
       <c r="E379" s="8">
-        <v>396658536209.31</v>
+        <v>396405139971.63</v>
       </c>
       <c r="F379" s="9">
-        <v>1945312</v>
+        <v>1944782</v>
       </c>
       <c r="G379" s="8">
-        <v>35120084076.15</v>
+        <v>35275960591.4</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
@@ -11519,19 +11519,19 @@
         <v>760</v>
       </c>
       <c r="C380" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D380" s="7">
-        <v>0.151229</v>
+        <v>0.154951</v>
       </c>
       <c r="E380" s="8">
-        <v>1163865783.24</v>
+        <v>1154795922.54</v>
       </c>
       <c r="F380" s="9">
-        <v>1869</v>
+        <v>1866</v>
       </c>
       <c r="G380" s="8">
-        <v>176009955.82</v>
+        <v>178936209.68</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
@@ -11542,19 +11542,19 @@
         <v>762</v>
       </c>
       <c r="C381" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D381" s="7">
-        <v>0.189749</v>
+        <v>0.190751</v>
       </c>
       <c r="E381" s="8">
-        <v>1029491627.93</v>
+        <v>1024398893.82</v>
       </c>
       <c r="F381" s="9">
-        <v>1802</v>
+        <v>1797</v>
       </c>
       <c r="G381" s="8">
-        <v>195345490.06</v>
+        <v>195405208.32</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
@@ -11565,19 +11565,19 @@
         <v>764</v>
       </c>
       <c r="C382" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D382" s="7">
-        <v>0.172873</v>
+        <v>0.174365</v>
       </c>
       <c r="E382" s="8">
-        <v>586717246.36</v>
+        <v>584724096.4</v>
       </c>
       <c r="F382" s="9">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="G382" s="8">
-        <v>101427340.77</v>
+        <v>101955335.58</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
@@ -11588,19 +11588,19 @@
         <v>766</v>
       </c>
       <c r="C383" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D383" s="7">
-        <v>0.091841</v>
+        <v>0.092101</v>
       </c>
       <c r="E383" s="8">
-        <v>97864130166.62</v>
+        <v>97825501477.57</v>
       </c>
       <c r="F383" s="9">
-        <v>665082</v>
+        <v>665219</v>
       </c>
       <c r="G383" s="8">
-        <v>8987918210.11</v>
+        <v>9009787301.56</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
@@ -11611,19 +11611,19 @@
         <v>768</v>
       </c>
       <c r="C384" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D384" s="7">
-        <v>0.089995</v>
+        <v>0.090086</v>
       </c>
       <c r="E384" s="8">
-        <v>42199884701</v>
+        <v>42285883316.21</v>
       </c>
       <c r="F384" s="9">
-        <v>440755</v>
+        <v>441684</v>
       </c>
       <c r="G384" s="8">
-        <v>3797769522.92</v>
+        <v>3809374915.55</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
@@ -11634,19 +11634,19 @@
         <v>770</v>
       </c>
       <c r="C385" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D385" s="7">
-        <v>0.094361</v>
+        <v>0.094456</v>
       </c>
       <c r="E385" s="8">
-        <v>16531878822.34</v>
+        <v>16639267027.49</v>
       </c>
       <c r="F385" s="9">
-        <v>127257</v>
+        <v>129215</v>
       </c>
       <c r="G385" s="8">
-        <v>1559964483.36</v>
+        <v>1571676254.1</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
@@ -11657,19 +11657,19 @@
         <v>772</v>
       </c>
       <c r="C386" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D386" s="7">
-        <v>0.261368</v>
+        <v>0.263876</v>
       </c>
       <c r="E386" s="8">
-        <v>3523823806.95</v>
+        <v>3538787521.38</v>
       </c>
       <c r="F386" s="9">
-        <v>10558</v>
+        <v>10579</v>
       </c>
       <c r="G386" s="8">
-        <v>921014104.62</v>
+        <v>933801034.77</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
@@ -11680,19 +11680,19 @@
         <v>774</v>
       </c>
       <c r="C387" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D387" s="7">
-        <v>0.190662</v>
+        <v>0.192091</v>
       </c>
       <c r="E387" s="8">
-        <v>2309885205.63</v>
+        <v>2329648452.64</v>
       </c>
       <c r="F387" s="9">
-        <v>7128</v>
+        <v>7172</v>
       </c>
       <c r="G387" s="8">
-        <v>440407951.8</v>
+        <v>447504569.86</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
@@ -11703,19 +11703,19 @@
         <v>776</v>
       </c>
       <c r="C388" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D388" s="7">
-        <v>0.173515</v>
+        <v>0.174519</v>
       </c>
       <c r="E388" s="8">
-        <v>2471745980.17</v>
+        <v>2498933950.47</v>
       </c>
       <c r="F388" s="9">
-        <v>7636</v>
+        <v>7672</v>
       </c>
       <c r="G388" s="8">
-        <v>428885688.82</v>
+        <v>436112545.11</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -11726,19 +11726,19 @@
         <v>778</v>
       </c>
       <c r="C389" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D389" s="7">
-        <v>0.099249</v>
+        <v>0.099417</v>
       </c>
       <c r="E389" s="8">
-        <v>3831158030.87</v>
+        <v>3845971372.79</v>
       </c>
       <c r="F389" s="9">
-        <v>7243</v>
+        <v>7238</v>
       </c>
       <c r="G389" s="8">
-        <v>380240214.01</v>
+        <v>382356033.87</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
@@ -11749,19 +11749,19 @@
         <v>780</v>
       </c>
       <c r="C390" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D390" s="7">
-        <v>0.229683</v>
+        <v>0.230859</v>
       </c>
       <c r="E390" s="8">
-        <v>1491949055.86</v>
+        <v>1495634927.47</v>
       </c>
       <c r="F390" s="9">
-        <v>5827</v>
+        <v>5847</v>
       </c>
       <c r="G390" s="8">
-        <v>342674882.09</v>
+        <v>345280703.15</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
@@ -11772,19 +11772,19 @@
         <v>782</v>
       </c>
       <c r="C391" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D391" s="7">
-        <v>0.323954</v>
+        <v>0.326482</v>
       </c>
       <c r="E391" s="8">
-        <v>1904494978.17</v>
+        <v>1911700758.93</v>
       </c>
       <c r="F391" s="9">
-        <v>6315</v>
+        <v>6345</v>
       </c>
       <c r="G391" s="8">
-        <v>616968745.82</v>
+        <v>624135102.15</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
@@ -11795,19 +11795,19 @@
         <v>784</v>
       </c>
       <c r="C392" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D392" s="7">
-        <v>0.273916</v>
+        <v>0.275507</v>
       </c>
       <c r="E392" s="8">
-        <v>13991885614.65</v>
+        <v>14044458495.18</v>
       </c>
       <c r="F392" s="9">
-        <v>67144</v>
+        <v>67576</v>
       </c>
       <c r="G392" s="8">
-        <v>3832596020.95</v>
+        <v>3869349225.15</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
@@ -11818,19 +11818,19 @@
         <v>786</v>
       </c>
       <c r="C393" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D393" s="7">
-        <v>0.059903</v>
+        <v>0.060735</v>
       </c>
       <c r="E393" s="8">
-        <v>55978319364.95</v>
+        <v>56459222953.45</v>
       </c>
       <c r="F393" s="9">
-        <v>41424</v>
+        <v>41648</v>
       </c>
       <c r="G393" s="8">
-        <v>3353271343.45</v>
+        <v>3429075280.52</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
@@ -11841,19 +11841,19 @@
         <v>788</v>
       </c>
       <c r="C394" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D394" s="7">
-        <v>0.337757</v>
+        <v>46148</v>
+      </c>
+      <c r="D394" s="10">
+        <v>0.33957</v>
       </c>
       <c r="E394" s="8">
-        <v>13437187621.62</v>
+        <v>13434500341.5</v>
       </c>
       <c r="F394" s="9">
-        <v>216629</v>
+        <v>216737</v>
       </c>
       <c r="G394" s="8">
-        <v>4538508186.49</v>
+        <v>4561959126.86</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
@@ -11864,19 +11864,19 @@
         <v>790</v>
       </c>
       <c r="C395" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D395" s="7">
-        <v>0.372104</v>
+        <v>0.372394</v>
       </c>
       <c r="E395" s="8">
-        <v>4742691649.08</v>
+        <v>4749674371.79</v>
       </c>
       <c r="F395" s="9">
-        <v>53183</v>
+        <v>53294</v>
       </c>
       <c r="G395" s="8">
-        <v>1764772874.44</v>
+        <v>1768752278.93</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
@@ -11887,19 +11887,19 @@
         <v>792</v>
       </c>
       <c r="C396" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D396" s="7">
-        <v>0.213926</v>
+        <v>0.214673</v>
       </c>
       <c r="E396" s="8">
-        <v>68891125376.45</v>
+        <v>68856575447.87</v>
       </c>
       <c r="F396" s="9">
-        <v>518516</v>
+        <v>518131</v>
       </c>
       <c r="G396" s="8">
-        <v>14737581270.68</v>
+        <v>14781656102.8</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -11910,19 +11910,19 @@
         <v>794</v>
       </c>
       <c r="C397" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D397" s="10">
-        <v>0.13255</v>
+        <v>46148</v>
+      </c>
+      <c r="D397" s="7">
+        <v>0.132769</v>
       </c>
       <c r="E397" s="8">
-        <v>12837136009.29</v>
+        <v>12858861071.08</v>
       </c>
       <c r="F397" s="9">
-        <v>45271</v>
+        <v>45279</v>
       </c>
       <c r="G397" s="8">
-        <v>1701562885.93</v>
+        <v>1707256502.08</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
@@ -11933,19 +11933,19 @@
         <v>796</v>
       </c>
       <c r="C398" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D398" s="7">
-        <v>0.063271</v>
+        <v>0.063252</v>
       </c>
       <c r="E398" s="8">
-        <v>58488858527.81</v>
+        <v>58485988244.69</v>
       </c>
       <c r="F398" s="9">
-        <v>323582</v>
+        <v>323423</v>
       </c>
       <c r="G398" s="8">
-        <v>3700652087.64</v>
+        <v>3699329509.91</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>06.05.2026 18:19:52</t>
+    <t>07.05.2026 18:22:38</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2917,19 +2917,19 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D6" s="7">
-        <v>0.101226</v>
+        <v>0.102498</v>
       </c>
       <c r="E6" s="8">
-        <v>47579628598.11</v>
+        <v>47768595341.11</v>
       </c>
       <c r="F6" s="9">
-        <v>645057</v>
+        <v>645916</v>
       </c>
       <c r="G6" s="8">
-        <v>4816296800.18</v>
+        <v>4896178280.9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2940,19 +2940,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D7" s="7">
-        <v>0.404792</v>
+        <v>0.408707</v>
       </c>
       <c r="E7" s="8">
-        <v>17151022173.55</v>
+        <v>17236612061.79</v>
       </c>
       <c r="F7" s="9">
-        <v>151584</v>
+        <v>151821</v>
       </c>
       <c r="G7" s="8">
-        <v>6942604489.57</v>
+        <v>7044720858.84</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2963,19 +2963,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D8" s="7">
-        <v>0.086747</v>
+        <v>0.086931</v>
       </c>
       <c r="E8" s="8">
-        <v>8009359340.36</v>
+        <v>8083796587.42</v>
       </c>
       <c r="F8" s="9">
-        <v>142365</v>
+        <v>143963</v>
       </c>
       <c r="G8" s="8">
-        <v>694785455.31</v>
+        <v>702735981.17</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2986,19 +2986,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D9" s="7">
-        <v>0.369276</v>
+        <v>0.369916</v>
       </c>
       <c r="E9" s="8">
-        <v>142567907399.95</v>
+        <v>142779118798.59</v>
       </c>
       <c r="F9" s="9">
-        <v>489261</v>
+        <v>489844</v>
       </c>
       <c r="G9" s="8">
-        <v>52646940382.91</v>
+        <v>52816242969.79</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3009,19 +3009,19 @@
         <v>20</v>
       </c>
       <c r="C10" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D10" s="7">
-        <v>0.331841</v>
+        <v>0.335381</v>
       </c>
       <c r="E10" s="8">
-        <v>23093993324.31</v>
+        <v>23076866385.93</v>
       </c>
       <c r="F10" s="9">
-        <v>329505</v>
+        <v>329546</v>
       </c>
       <c r="G10" s="8">
-        <v>7663541380.75</v>
+        <v>7739548889.99</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3032,19 +3032,19 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D11" s="7">
-        <v>1.007249</v>
+        <v>1.028735</v>
       </c>
       <c r="E11" s="8">
-        <v>11585860336.04</v>
+        <v>11590858965.36</v>
       </c>
       <c r="F11" s="9">
-        <v>289147</v>
+        <v>289186</v>
       </c>
       <c r="G11" s="8">
-        <v>11669844335.29</v>
+        <v>11923927408.57</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3055,19 +3055,19 @@
         <v>24</v>
       </c>
       <c r="C12" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D12" s="7">
-        <v>0.698334</v>
+        <v>0.715115</v>
       </c>
       <c r="E12" s="8">
-        <v>136686976660.39</v>
+        <v>136595231484.15</v>
       </c>
       <c r="F12" s="9">
-        <v>726359</v>
+        <v>726283</v>
       </c>
       <c r="G12" s="8">
-        <v>95453154490.24</v>
+        <v>97681268470.98</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3078,19 +3078,19 @@
         <v>26</v>
       </c>
       <c r="C13" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D13" s="7">
-        <v>2.027999</v>
+        <v>2.081179</v>
       </c>
       <c r="E13" s="8">
-        <v>1369522219.3</v>
+        <v>1370727072.23</v>
       </c>
       <c r="F13" s="9">
-        <v>32847</v>
+        <v>32850</v>
       </c>
       <c r="G13" s="8">
-        <v>2777390352.43</v>
+        <v>2852727978.21</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3101,19 +3101,19 @@
         <v>28</v>
       </c>
       <c r="C14" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D14" s="7">
-        <v>0.137429</v>
+        <v>0.138023</v>
       </c>
       <c r="E14" s="8">
-        <v>242548524.25</v>
+        <v>249859828.37</v>
       </c>
       <c r="F14" s="9">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G14" s="8">
-        <v>33333087.7</v>
+        <v>34486322.82</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3124,19 +3124,19 @@
         <v>30</v>
       </c>
       <c r="C15" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D15" s="7">
-        <v>1.385911</v>
+        <v>1.420973</v>
       </c>
       <c r="E15" s="8">
-        <v>16179289126.89</v>
+        <v>16211958119.02</v>
       </c>
       <c r="F15" s="9">
-        <v>487798</v>
+        <v>488129</v>
       </c>
       <c r="G15" s="8">
-        <v>22423056264.69</v>
+        <v>23036748749.34</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3147,19 +3147,19 @@
         <v>32</v>
       </c>
       <c r="C16" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D16" s="7">
-        <v>0.092697</v>
+        <v>0.094848</v>
       </c>
       <c r="E16" s="8">
-        <v>567159202767.67</v>
+        <v>566673027424.68</v>
       </c>
       <c r="F16" s="9">
-        <v>1957515</v>
+        <v>1956202</v>
       </c>
       <c r="G16" s="8">
-        <v>52573904422.5</v>
+        <v>53747662699.47</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3170,19 +3170,19 @@
         <v>34</v>
       </c>
       <c r="C17" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D17" s="7">
-        <v>0.345792</v>
+        <v>0.349091</v>
       </c>
       <c r="E17" s="8">
-        <v>2128769113.85</v>
+        <v>2126247617.16</v>
       </c>
       <c r="F17" s="9">
-        <v>13490</v>
+        <v>13436</v>
       </c>
       <c r="G17" s="8">
-        <v>736110917.49</v>
+        <v>742254490.02</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3193,19 +3193,19 @@
         <v>36</v>
       </c>
       <c r="C18" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D18" s="7">
-        <v>0.145644</v>
+        <v>0.146742</v>
       </c>
       <c r="E18" s="8">
-        <v>33017693822.63</v>
+        <v>33002904102.58</v>
       </c>
       <c r="F18" s="9">
-        <v>239065</v>
+        <v>239020</v>
       </c>
       <c r="G18" s="8">
-        <v>4808818638.48</v>
+        <v>4842904751.44</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3216,19 +3216,19 @@
         <v>38</v>
       </c>
       <c r="C19" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D19" s="7">
-        <v>0.367852</v>
+        <v>0.375264</v>
       </c>
       <c r="E19" s="8">
-        <v>1424496083.79</v>
+        <v>1424445548.93</v>
       </c>
       <c r="F19" s="9">
         <v>537</v>
       </c>
       <c r="G19" s="8">
-        <v>524003523.32</v>
+        <v>534542911.7</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3239,19 +3239,19 @@
         <v>40</v>
       </c>
       <c r="C20" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D20" s="7">
-        <v>0.138748</v>
+        <v>0.139238</v>
       </c>
       <c r="E20" s="8">
-        <v>14755172104.43</v>
+        <v>14777741562.38</v>
       </c>
       <c r="F20" s="9">
-        <v>524953</v>
+        <v>524875</v>
       </c>
       <c r="G20" s="8">
-        <v>2047254536</v>
+        <v>2057623465.62</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3262,19 +3262,19 @@
         <v>42</v>
       </c>
       <c r="C21" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D21" s="10">
-        <v>0.09647</v>
+        <v>46149</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.098378</v>
       </c>
       <c r="E21" s="8">
-        <v>510074270425.21</v>
+        <v>509686821482.16</v>
       </c>
       <c r="F21" s="9">
-        <v>2304430</v>
+        <v>2303269</v>
       </c>
       <c r="G21" s="8">
-        <v>49206925797.46</v>
+        <v>50142135467.14</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3285,19 +3285,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D22" s="7">
-        <v>0.402535</v>
+        <v>46149</v>
+      </c>
+      <c r="D22" s="10">
+        <v>0.41284</v>
       </c>
       <c r="E22" s="8">
-        <v>3413958065.1</v>
+        <v>3444934878.24</v>
       </c>
       <c r="F22" s="9">
-        <v>19300</v>
+        <v>19381</v>
       </c>
       <c r="G22" s="8">
-        <v>1374236617.04</v>
+        <v>1422208171.9</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3308,19 +3308,19 @@
         <v>46</v>
       </c>
       <c r="C23" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D23" s="7">
-        <v>0.092981</v>
+        <v>0.094867</v>
       </c>
       <c r="E23" s="8">
-        <v>576664141.18</v>
+        <v>576452313.3</v>
       </c>
       <c r="F23" s="9">
-        <v>4609</v>
+        <v>4607</v>
       </c>
       <c r="G23" s="8">
-        <v>53618714.11</v>
+        <v>54686310.26</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3331,19 +3331,19 @@
         <v>48</v>
       </c>
       <c r="C24" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D24" s="7">
-        <v>0.226001</v>
+        <v>0.230507</v>
       </c>
       <c r="E24" s="8">
-        <v>1216450225.59</v>
+        <v>1221779171.02</v>
       </c>
       <c r="F24" s="9">
-        <v>4970</v>
+        <v>4987</v>
       </c>
       <c r="G24" s="8">
-        <v>274918918.11</v>
+        <v>281628682</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3354,19 +3354,19 @@
         <v>50</v>
       </c>
       <c r="C25" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D25" s="7">
-        <v>0.105376</v>
+        <v>0.106626</v>
       </c>
       <c r="E25" s="8">
-        <v>66640492097.62</v>
+        <v>66702443494.58</v>
       </c>
       <c r="F25" s="9">
-        <v>764641</v>
+        <v>764895</v>
       </c>
       <c r="G25" s="8">
-        <v>7022282839.2</v>
+        <v>7112189766.93</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3377,19 +3377,19 @@
         <v>52</v>
       </c>
       <c r="C26" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D26" s="10">
-        <v>0.09813</v>
+        <v>46149</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0.098808</v>
       </c>
       <c r="E26" s="8">
-        <v>1677153468.76</v>
+        <v>1679191411.7</v>
       </c>
       <c r="F26" s="9">
-        <v>3223</v>
+        <v>3215</v>
       </c>
       <c r="G26" s="8">
-        <v>164578921.6</v>
+        <v>165917758.15</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3400,19 +3400,19 @@
         <v>54</v>
       </c>
       <c r="C27" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D27" s="10">
-        <v>0.09366</v>
+        <v>46149</v>
+      </c>
+      <c r="D27" s="7">
+        <v>0.094081</v>
       </c>
       <c r="E27" s="8">
-        <v>61898279000.13</v>
+        <v>61929612277.8</v>
       </c>
       <c r="F27" s="9">
-        <v>715460</v>
+        <v>715355</v>
       </c>
       <c r="G27" s="8">
-        <v>5797363282.87</v>
+        <v>5826400025.37</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3423,19 +3423,19 @@
         <v>56</v>
       </c>
       <c r="C28" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D28" s="7">
-        <v>0.385979</v>
+        <v>0.389441</v>
       </c>
       <c r="E28" s="8">
-        <v>1045186947.96</v>
+        <v>1046438154.95</v>
       </c>
       <c r="F28" s="9">
-        <v>7911</v>
+        <v>7896</v>
       </c>
       <c r="G28" s="8">
-        <v>403420427.7</v>
+        <v>407525509.8</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3446,19 +3446,19 @@
         <v>58</v>
       </c>
       <c r="C29" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D29" s="7">
-        <v>0.645635</v>
+        <v>0.650439</v>
       </c>
       <c r="E29" s="8">
-        <v>211358494.86</v>
+        <v>211731209.69</v>
       </c>
       <c r="F29" s="9">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="G29" s="8">
-        <v>136460391.46</v>
+        <v>137718282.62</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3469,19 +3469,19 @@
         <v>60</v>
       </c>
       <c r="C30" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D30" s="7">
-        <v>2.380953</v>
+        <v>2.447826</v>
       </c>
       <c r="E30" s="8">
-        <v>846955510.71</v>
+        <v>849115067.38</v>
       </c>
       <c r="F30" s="9">
-        <v>19595</v>
+        <v>19598</v>
       </c>
       <c r="G30" s="8">
-        <v>2016561015.49</v>
+        <v>2078485894.59</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3492,19 +3492,19 @@
         <v>62</v>
       </c>
       <c r="C31" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D31" s="10">
-        <v>0.52437</v>
+        <v>46149</v>
+      </c>
+      <c r="D31" s="7">
+        <v>0.527899</v>
       </c>
       <c r="E31" s="8">
-        <v>2408324691.06</v>
+        <v>2410407571.48</v>
       </c>
       <c r="F31" s="9">
-        <v>14232</v>
+        <v>14208</v>
       </c>
       <c r="G31" s="8">
-        <v>1262853480.57</v>
+        <v>1272450914.75</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3515,19 +3515,19 @@
         <v>64</v>
       </c>
       <c r="C32" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D32" s="7">
-        <v>0.843486</v>
+        <v>46149</v>
+      </c>
+      <c r="D32" s="10">
+        <v>0.86373</v>
       </c>
       <c r="E32" s="8">
-        <v>12365413198.33</v>
+        <v>12351139233.4</v>
       </c>
       <c r="F32" s="9">
-        <v>77239</v>
+        <v>77316</v>
       </c>
       <c r="G32" s="8">
-        <v>10430055099.24</v>
+        <v>10668047397.17</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3538,19 +3538,19 @@
         <v>66</v>
       </c>
       <c r="C33" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D33" s="7">
-        <v>0.264883</v>
+        <v>0.267816</v>
       </c>
       <c r="E33" s="8">
-        <v>1310059237.45</v>
+        <v>1312018496.93</v>
       </c>
       <c r="F33" s="9">
-        <v>16195</v>
+        <v>16191</v>
       </c>
       <c r="G33" s="8">
-        <v>347012964.31</v>
+        <v>351379287.08</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3561,19 +3561,19 @@
         <v>68</v>
       </c>
       <c r="C34" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D34" s="10">
-        <v>0.12577</v>
+        <v>46149</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0.126783</v>
       </c>
       <c r="E34" s="8">
-        <v>3330589592.87</v>
+        <v>3327786052</v>
       </c>
       <c r="F34" s="9">
-        <v>53925</v>
+        <v>54019</v>
       </c>
       <c r="G34" s="8">
-        <v>418888568.42</v>
+        <v>421905327.03</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3584,19 +3584,19 @@
         <v>70</v>
       </c>
       <c r="C35" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D35" s="7">
-        <v>0.175775</v>
+        <v>0.176437</v>
       </c>
       <c r="E35" s="8">
-        <v>10732355431.38</v>
+        <v>10757455402.23</v>
       </c>
       <c r="F35" s="9">
-        <v>36647</v>
+        <v>36644</v>
       </c>
       <c r="G35" s="8">
-        <v>1886479887.76</v>
+        <v>1898018420.64</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3607,19 +3607,19 @@
         <v>72</v>
       </c>
       <c r="C36" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D36" s="10">
-        <v>0.20371</v>
+        <v>46149</v>
+      </c>
+      <c r="D36" s="7">
+        <v>0.206666</v>
       </c>
       <c r="E36" s="8">
-        <v>1493919849.53</v>
+        <v>1497553113.27</v>
       </c>
       <c r="F36" s="9">
-        <v>32744</v>
+        <v>32847</v>
       </c>
       <c r="G36" s="8">
-        <v>304327033.22</v>
+        <v>309493548.82</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3630,19 +3630,19 @@
         <v>74</v>
       </c>
       <c r="C37" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D37" s="7">
-        <v>0.839074</v>
+        <v>0.852645</v>
       </c>
       <c r="E37" s="8">
-        <v>2446821152.37</v>
+        <v>2449808911.95</v>
       </c>
       <c r="F37" s="9">
-        <v>52354</v>
+        <v>52474</v>
       </c>
       <c r="G37" s="8">
-        <v>2053063982.03</v>
+        <v>2088817831.3</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3653,19 +3653,19 @@
         <v>76</v>
       </c>
       <c r="C38" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D38" s="7">
-        <v>0.169903</v>
+        <v>46149</v>
+      </c>
+      <c r="D38" s="10">
+        <v>0.17013</v>
       </c>
       <c r="E38" s="8">
-        <v>3690827715.74</v>
+        <v>3692021583.48</v>
       </c>
       <c r="F38" s="9">
-        <v>53198</v>
+        <v>53293</v>
       </c>
       <c r="G38" s="8">
-        <v>627082178.17</v>
+        <v>628123386.87</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3676,19 +3676,19 @@
         <v>78</v>
       </c>
       <c r="C39" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D39" s="10">
-        <v>0.10767</v>
+        <v>46149</v>
+      </c>
+      <c r="D39" s="7">
+        <v>0.108348</v>
       </c>
       <c r="E39" s="8">
-        <v>8162041319.18</v>
+        <v>8146660542.96</v>
       </c>
       <c r="F39" s="9">
-        <v>96889</v>
+        <v>96867</v>
       </c>
       <c r="G39" s="8">
-        <v>878806526.93</v>
+        <v>882671426.42</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3699,19 +3699,19 @@
         <v>80</v>
       </c>
       <c r="C40" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D40" s="7">
-        <v>0.336995</v>
+        <v>0.340735</v>
       </c>
       <c r="E40" s="8">
-        <v>14078210718.44</v>
+        <v>14040961067.85</v>
       </c>
       <c r="F40" s="9">
-        <v>157186</v>
+        <v>156983</v>
       </c>
       <c r="G40" s="8">
-        <v>4744282034.49</v>
+        <v>4784250682.44</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3722,19 +3722,19 @@
         <v>82</v>
       </c>
       <c r="C41" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D41" s="7">
-        <v>0.366119</v>
+        <v>0.366844</v>
       </c>
       <c r="E41" s="8">
-        <v>78125325752.82</v>
+        <v>77389700525.54</v>
       </c>
       <c r="F41" s="9">
-        <v>199738</v>
+        <v>175168</v>
       </c>
       <c r="G41" s="8">
-        <v>28603185052.01</v>
+        <v>28389937919.39</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3745,19 +3745,19 @@
         <v>84</v>
       </c>
       <c r="C42" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D42" s="10">
-        <v>0.95623</v>
+        <v>46149</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0.963467</v>
       </c>
       <c r="E42" s="8">
-        <v>12811301243.95</v>
+        <v>12807879543.37</v>
       </c>
       <c r="F42" s="9">
-        <v>234412</v>
+        <v>234364</v>
       </c>
       <c r="G42" s="8">
-        <v>12250553045.49</v>
+        <v>12339968111.21</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3768,19 +3768,19 @@
         <v>86</v>
       </c>
       <c r="C43" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D43" s="7">
-        <v>0.688614</v>
+        <v>0.696166</v>
       </c>
       <c r="E43" s="8">
-        <v>8862437482.59</v>
+        <v>8800075425.75</v>
       </c>
       <c r="F43" s="9">
-        <v>121216</v>
+        <v>121231</v>
       </c>
       <c r="G43" s="8">
-        <v>6102796936.99</v>
+        <v>6126316946.53</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3791,19 +3791,19 @@
         <v>88</v>
       </c>
       <c r="C44" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D44" s="7">
-        <v>2.961703</v>
+        <v>3.055004</v>
       </c>
       <c r="E44" s="8">
-        <v>8446862601.05</v>
+        <v>8444703447.82</v>
       </c>
       <c r="F44" s="9">
-        <v>366137</v>
+        <v>366306</v>
       </c>
       <c r="G44" s="8">
-        <v>25017098384.52</v>
+        <v>25798600441.82</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3814,19 +3814,19 @@
         <v>90</v>
       </c>
       <c r="C45" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D45" s="7">
-        <v>1.139951</v>
+        <v>1.159979</v>
       </c>
       <c r="E45" s="8">
-        <v>3671631864.25</v>
+        <v>3677789987.95</v>
       </c>
       <c r="F45" s="9">
-        <v>85794</v>
+        <v>85803</v>
       </c>
       <c r="G45" s="8">
-        <v>4185478625.93</v>
+        <v>4266159995.87</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3837,19 +3837,19 @@
         <v>92</v>
       </c>
       <c r="C46" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D46" s="10">
-        <v>0.42246</v>
+        <v>46149</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0.425381</v>
       </c>
       <c r="E46" s="8">
-        <v>23860885986.27</v>
+        <v>23847778764.48</v>
       </c>
       <c r="F46" s="9">
-        <v>219382</v>
+        <v>219281</v>
       </c>
       <c r="G46" s="8">
-        <v>10080272962.39</v>
+        <v>10144387163.63</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3860,19 +3860,19 @@
         <v>94</v>
       </c>
       <c r="C47" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D47" s="7">
-        <v>1.002621</v>
+        <v>1.020405</v>
       </c>
       <c r="E47" s="8">
-        <v>9667273082.92</v>
+        <v>9657328648.41</v>
       </c>
       <c r="F47" s="9">
-        <v>207418</v>
+        <v>207403</v>
       </c>
       <c r="G47" s="8">
-        <v>9692614810.69</v>
+        <v>9854385710.1</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3883,19 +3883,19 @@
         <v>96</v>
       </c>
       <c r="C48" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D48" s="7">
-        <v>1.355304</v>
+        <v>1.393359</v>
       </c>
       <c r="E48" s="8">
-        <v>715519370.2</v>
+        <v>714973713.63</v>
       </c>
       <c r="F48" s="9">
-        <v>7291</v>
+        <v>7287</v>
       </c>
       <c r="G48" s="8">
-        <v>969745915.24</v>
+        <v>996214976.65</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3906,19 +3906,19 @@
         <v>98</v>
       </c>
       <c r="C49" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D49" s="7">
-        <v>0.130586</v>
+        <v>0.130742</v>
       </c>
       <c r="E49" s="8">
-        <v>93836404680.74</v>
+        <v>94269286394.84</v>
       </c>
       <c r="F49" s="9">
-        <v>209139</v>
+        <v>209156</v>
       </c>
       <c r="G49" s="8">
-        <v>12253724402.13</v>
+        <v>12324918120.42</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3929,19 +3929,19 @@
         <v>100</v>
       </c>
       <c r="C50" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D50" s="10">
-        <v>0.09971</v>
+        <v>46149</v>
+      </c>
+      <c r="D50" s="7">
+        <v>0.099862</v>
       </c>
       <c r="E50" s="8">
-        <v>14019421649.81</v>
+        <v>13904569479.47</v>
       </c>
       <c r="F50" s="9">
-        <v>128351</v>
+        <v>130037</v>
       </c>
       <c r="G50" s="8">
-        <v>1397872782.72</v>
+        <v>1388532130.24</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3952,19 +3952,19 @@
         <v>102</v>
       </c>
       <c r="C51" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D51" s="10">
-        <v>0.48967</v>
+        <v>46149</v>
+      </c>
+      <c r="D51" s="7">
+        <v>0.501523</v>
       </c>
       <c r="E51" s="8">
-        <v>20375289871.46</v>
+        <v>20381777364.58</v>
       </c>
       <c r="F51" s="9">
-        <v>136647</v>
+        <v>136659</v>
       </c>
       <c r="G51" s="8">
-        <v>9977161484.02</v>
+        <v>10221933555.68</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3975,19 +3975,19 @@
         <v>104</v>
       </c>
       <c r="C52" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D52" s="10">
-        <v>0.21415</v>
+        <v>46149</v>
+      </c>
+      <c r="D52" s="7">
+        <v>0.216929</v>
       </c>
       <c r="E52" s="8">
-        <v>2641649851.16</v>
+        <v>2646305037.59</v>
       </c>
       <c r="F52" s="9">
-        <v>10454</v>
+        <v>10463</v>
       </c>
       <c r="G52" s="8">
-        <v>565708037.41</v>
+        <v>574059593.33</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3998,19 +3998,19 @@
         <v>106</v>
       </c>
       <c r="C53" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D53" s="7">
-        <v>0.271493</v>
+        <v>46149</v>
+      </c>
+      <c r="D53" s="10">
+        <v>0.27585</v>
       </c>
       <c r="E53" s="8">
-        <v>2898889707.75</v>
+        <v>2905387763.52</v>
       </c>
       <c r="F53" s="9">
-        <v>10767</v>
+        <v>10773</v>
       </c>
       <c r="G53" s="8">
-        <v>787027040.79</v>
+        <v>801449924.2</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -4021,19 +4021,19 @@
         <v>108</v>
       </c>
       <c r="C54" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D54" s="7">
-        <v>0.328296</v>
+        <v>0.335854</v>
       </c>
       <c r="E54" s="8">
-        <v>4543644111.21</v>
+        <v>4559785204.98</v>
       </c>
       <c r="F54" s="9">
-        <v>15917</v>
+        <v>15926</v>
       </c>
       <c r="G54" s="8">
-        <v>1491662099.18</v>
+        <v>1531420498.76</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4044,19 +4044,19 @@
         <v>110</v>
       </c>
       <c r="C55" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D55" s="11">
-        <v>0.3107</v>
+        <v>0.3166</v>
       </c>
       <c r="E55" s="8">
-        <v>2579014247.19</v>
+        <v>2591081282.04</v>
       </c>
       <c r="F55" s="9">
-        <v>10212</v>
+        <v>10226</v>
       </c>
       <c r="G55" s="8">
-        <v>801300451.42</v>
+        <v>820335107.89</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -4067,19 +4067,19 @@
         <v>112</v>
       </c>
       <c r="C56" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D56" s="10">
-        <v>0.22139</v>
+        <v>46149</v>
+      </c>
+      <c r="D56" s="7">
+        <v>0.224993</v>
       </c>
       <c r="E56" s="8">
-        <v>1890529309.13</v>
+        <v>1896938881.93</v>
       </c>
       <c r="F56" s="9">
-        <v>6686</v>
+        <v>6703</v>
       </c>
       <c r="G56" s="8">
-        <v>418544853.28</v>
+        <v>426798031.99</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4090,19 +4090,19 @@
         <v>114</v>
       </c>
       <c r="C57" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D57" s="7">
-        <v>0.114784</v>
+        <v>0.115588</v>
       </c>
       <c r="E57" s="8">
-        <v>1627634618.28</v>
+        <v>1630635570.19</v>
       </c>
       <c r="F57" s="9">
-        <v>3913</v>
+        <v>3912</v>
       </c>
       <c r="G57" s="8">
-        <v>186825607.75</v>
+        <v>188482695.48</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -4113,19 +4113,19 @@
         <v>116</v>
       </c>
       <c r="C58" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D58" s="7">
-        <v>0.309002</v>
+        <v>0.311631</v>
       </c>
       <c r="E58" s="8">
-        <v>4449995044.37</v>
+        <v>4461079324.04</v>
       </c>
       <c r="F58" s="9">
-        <v>16805</v>
+        <v>16830</v>
       </c>
       <c r="G58" s="8">
-        <v>1375056056.98</v>
+        <v>1390209952.15</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -4136,19 +4136,19 @@
         <v>118</v>
       </c>
       <c r="C59" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D59" s="7">
-        <v>0.244745</v>
+        <v>0.247023</v>
       </c>
       <c r="E59" s="8">
-        <v>2814740079.2</v>
+        <v>2824138641</v>
       </c>
       <c r="F59" s="9">
-        <v>11341</v>
+        <v>11368</v>
       </c>
       <c r="G59" s="8">
-        <v>688894405.39</v>
+        <v>697626688.91</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -4159,19 +4159,19 @@
         <v>120</v>
       </c>
       <c r="C60" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D60" s="7">
-        <v>0.178795</v>
+        <v>0.182226</v>
       </c>
       <c r="E60" s="8">
-        <v>183201808.19</v>
+        <v>183372870.07</v>
       </c>
       <c r="F60" s="9">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G60" s="8">
-        <v>32755614.8</v>
+        <v>33415383.21</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -4182,19 +4182,19 @@
         <v>122</v>
       </c>
       <c r="C61" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D61" s="7">
-        <v>0.377063</v>
+        <v>0.385814</v>
       </c>
       <c r="E61" s="8">
-        <v>858575463.98</v>
+        <v>859065206.88</v>
       </c>
       <c r="F61" s="9">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G61" s="8">
-        <v>323737147.25</v>
+        <v>331439709.21</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -4205,19 +4205,19 @@
         <v>124</v>
       </c>
       <c r="C62" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D62" s="7">
-        <v>0.073389</v>
+        <v>46149</v>
+      </c>
+      <c r="D62" s="10">
+        <v>0.07382</v>
       </c>
       <c r="E62" s="8">
-        <v>173502024.4</v>
+        <v>173610895.03</v>
       </c>
       <c r="F62" s="9">
         <v>223</v>
       </c>
       <c r="G62" s="8">
-        <v>12733158.71</v>
+        <v>12815945.68</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -4228,19 +4228,19 @@
         <v>126</v>
       </c>
       <c r="C63" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D63" s="7">
-        <v>0.144318</v>
+        <v>0.146833</v>
       </c>
       <c r="E63" s="8">
-        <v>111067962.1</v>
+        <v>111329099.97</v>
       </c>
       <c r="F63" s="9">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G63" s="8">
-        <v>16029127.96</v>
+        <v>16346837.1</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -4251,19 +4251,19 @@
         <v>128</v>
       </c>
       <c r="C64" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D64" s="7">
-        <v>0.259252</v>
+        <v>0.261664</v>
       </c>
       <c r="E64" s="8">
-        <v>216031600.41</v>
+        <v>217278199.34</v>
       </c>
       <c r="F64" s="9">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G64" s="8">
-        <v>56006705.47</v>
+        <v>56853849.59</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4274,19 +4274,19 @@
         <v>130</v>
       </c>
       <c r="C65" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D65" s="7">
-        <v>0.335634</v>
+        <v>0.339497</v>
       </c>
       <c r="E65" s="8">
-        <v>638312800.68</v>
+        <v>639776426.4</v>
       </c>
       <c r="F65" s="9">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G65" s="8">
-        <v>214239763.12</v>
+        <v>217202220.36</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -4297,19 +4297,19 @@
         <v>132</v>
       </c>
       <c r="C66" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D66" s="7">
-        <v>0.580594</v>
+        <v>0.591204</v>
       </c>
       <c r="E66" s="8">
-        <v>12902558766.14</v>
+        <v>12890491061.41</v>
       </c>
       <c r="F66" s="9">
-        <v>127379</v>
+        <v>127305</v>
       </c>
       <c r="G66" s="8">
-        <v>7491150486.56</v>
+        <v>7620910426.85</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4320,19 +4320,19 @@
         <v>134</v>
       </c>
       <c r="C67" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D67" s="7">
-        <v>0.260893</v>
+        <v>0.268082</v>
       </c>
       <c r="E67" s="8">
-        <v>2012802814.19</v>
+        <v>2014291239.58</v>
       </c>
       <c r="F67" s="9">
-        <v>6113</v>
+        <v>6125</v>
       </c>
       <c r="G67" s="8">
-        <v>525125591.37</v>
+        <v>539994431.48</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -4343,19 +4343,19 @@
         <v>136</v>
       </c>
       <c r="C68" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D68" s="7">
-        <v>2.027413</v>
+        <v>2.062709</v>
       </c>
       <c r="E68" s="8">
-        <v>7015482475.05</v>
+        <v>7007732154.52</v>
       </c>
       <c r="F68" s="9">
-        <v>236076</v>
+        <v>236021</v>
       </c>
       <c r="G68" s="8">
-        <v>14223283344.05</v>
+        <v>14454911812.2</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -4366,19 +4366,19 @@
         <v>138</v>
       </c>
       <c r="C69" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D69" s="7">
-        <v>1.001855</v>
+        <v>1.014164</v>
       </c>
       <c r="E69" s="8">
-        <v>6510156926.86</v>
+        <v>6503707652.76</v>
       </c>
       <c r="F69" s="9">
-        <v>163330</v>
+        <v>163287</v>
       </c>
       <c r="G69" s="8">
-        <v>6522232781.83</v>
+        <v>6595824842.93</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -4389,19 +4389,19 @@
         <v>140</v>
       </c>
       <c r="C70" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D70" s="7">
-        <v>0.325601</v>
+        <v>0.334367</v>
       </c>
       <c r="E70" s="8">
-        <v>12184518661.7</v>
+        <v>12174179703.19</v>
       </c>
       <c r="F70" s="9">
-        <v>189433</v>
+        <v>189412</v>
       </c>
       <c r="G70" s="8">
-        <v>3967292084.6</v>
+        <v>4070647831.37</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4412,19 +4412,19 @@
         <v>142</v>
       </c>
       <c r="C71" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D71" s="7">
-        <v>0.098889</v>
+        <v>46149</v>
+      </c>
+      <c r="D71" s="10">
+        <v>0.09904</v>
       </c>
       <c r="E71" s="8">
-        <v>7537641443.35</v>
+        <v>7785151000.65</v>
       </c>
       <c r="F71" s="9">
-        <v>118282</v>
+        <v>124890</v>
       </c>
       <c r="G71" s="8">
-        <v>745387495.13</v>
+        <v>771043619.97</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -4435,19 +4435,19 @@
         <v>144</v>
       </c>
       <c r="C72" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D72" s="7">
-        <v>0.095489</v>
+        <v>0.097427</v>
       </c>
       <c r="E72" s="8">
-        <v>390936275891.39</v>
+        <v>390733902925.58</v>
       </c>
       <c r="F72" s="9">
-        <v>1423660</v>
+        <v>1423043</v>
       </c>
       <c r="G72" s="8">
-        <v>37330080932.62</v>
+        <v>38068161600.6</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4458,19 +4458,19 @@
         <v>146</v>
       </c>
       <c r="C73" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D73" s="7">
-        <v>1.095911</v>
+        <v>1.107664</v>
       </c>
       <c r="E73" s="8">
-        <v>6403855017.55</v>
+        <v>6404244193.02</v>
       </c>
       <c r="F73" s="9">
-        <v>262267</v>
+        <v>262188</v>
       </c>
       <c r="G73" s="8">
-        <v>7018055002.76</v>
+        <v>7093752141.09</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4481,19 +4481,19 @@
         <v>148</v>
       </c>
       <c r="C74" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D74" s="7">
-        <v>0.508661</v>
+        <v>0.511506</v>
       </c>
       <c r="E74" s="8">
-        <v>6736232682.53</v>
+        <v>6740081879.39</v>
       </c>
       <c r="F74" s="9">
-        <v>65680</v>
+        <v>65650</v>
       </c>
       <c r="G74" s="8">
-        <v>3426457842.2</v>
+        <v>3447595458.7</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -4504,19 +4504,19 @@
         <v>150</v>
       </c>
       <c r="C75" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D75" s="10">
-        <v>1.55949</v>
+        <v>46149</v>
+      </c>
+      <c r="D75" s="7">
+        <v>1.585392</v>
       </c>
       <c r="E75" s="8">
-        <v>495387188.23</v>
+        <v>495634608.85</v>
       </c>
       <c r="F75" s="9">
-        <v>5009</v>
+        <v>5016</v>
       </c>
       <c r="G75" s="8">
-        <v>772551568.99</v>
+        <v>785775270.03</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4527,19 +4527,19 @@
         <v>152</v>
       </c>
       <c r="C76" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D76" s="7">
-        <v>0.690825</v>
+        <v>46149</v>
+      </c>
+      <c r="D76" s="10">
+        <v>0.70827</v>
       </c>
       <c r="E76" s="8">
-        <v>212640768064.73</v>
+        <v>212574579464.87</v>
       </c>
       <c r="F76" s="9">
-        <v>720612</v>
+        <v>720792</v>
       </c>
       <c r="G76" s="8">
-        <v>146897516499.65</v>
+        <v>150560281149.83</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4550,19 +4550,19 @@
         <v>154</v>
       </c>
       <c r="C77" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D77" s="7">
-        <v>0.574275</v>
+        <v>0.587265</v>
       </c>
       <c r="E77" s="8">
-        <v>194094900.97</v>
+        <v>194110655.97</v>
       </c>
       <c r="F77" s="9">
         <v>22326</v>
       </c>
       <c r="G77" s="8">
-        <v>111463886.23</v>
+        <v>113994485.09</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4573,19 +4573,19 @@
         <v>156</v>
       </c>
       <c r="C78" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D78" s="7">
-        <v>0.297753</v>
+        <v>0.302319</v>
       </c>
       <c r="E78" s="8">
-        <v>395847378.68</v>
+        <v>397406594.94</v>
       </c>
       <c r="F78" s="9">
-        <v>33146</v>
+        <v>33152</v>
       </c>
       <c r="G78" s="8">
-        <v>117864567.76</v>
+        <v>120143734.16</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4596,19 +4596,19 @@
         <v>158</v>
       </c>
       <c r="C79" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D79" s="7">
-        <v>0.160499</v>
+        <v>46149</v>
+      </c>
+      <c r="D79" s="10">
+        <v>0.16321</v>
       </c>
       <c r="E79" s="8">
-        <v>3130729904.64</v>
+        <v>3136026020.53</v>
       </c>
       <c r="F79" s="9">
-        <v>6962</v>
+        <v>6970</v>
       </c>
       <c r="G79" s="8">
-        <v>502480261.35</v>
+        <v>511830975.52</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4619,19 +4619,19 @@
         <v>160</v>
       </c>
       <c r="C80" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D80" s="7">
-        <v>0.334947</v>
+        <v>0.335667</v>
       </c>
       <c r="E80" s="8">
-        <v>239492469.14</v>
+        <v>237992853.37</v>
       </c>
       <c r="F80" s="9">
-        <v>20848</v>
+        <v>20869</v>
       </c>
       <c r="G80" s="8">
-        <v>80217319.99</v>
+        <v>79886364.84</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4642,19 +4642,19 @@
         <v>162</v>
       </c>
       <c r="C81" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D81" s="7">
-        <v>0.179548</v>
+        <v>0.183175</v>
       </c>
       <c r="E81" s="8">
-        <v>701451630.99</v>
+        <v>702439456.47</v>
       </c>
       <c r="F81" s="9">
         <v>2344</v>
       </c>
       <c r="G81" s="8">
-        <v>125944446.78</v>
+        <v>128669151.29</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4665,19 +4665,19 @@
         <v>164</v>
       </c>
       <c r="C82" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D82" s="7">
-        <v>1.867747</v>
+        <v>1.922376</v>
       </c>
       <c r="E82" s="8">
-        <v>83821054.58</v>
+        <v>83860586.99</v>
       </c>
       <c r="F82" s="9">
         <v>13722</v>
       </c>
       <c r="G82" s="8">
-        <v>156556549.03</v>
+        <v>161211606.64</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4688,19 +4688,19 @@
         <v>166</v>
       </c>
       <c r="C83" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D83" s="7">
-        <v>0.095697</v>
+        <v>0.095876</v>
       </c>
       <c r="E83" s="8">
-        <v>10252419882.5</v>
+        <v>10276427518.55</v>
       </c>
       <c r="F83" s="9">
-        <v>172583</v>
+        <v>173504</v>
       </c>
       <c r="G83" s="8">
-        <v>981126677.6</v>
+        <v>985261228.96</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4711,19 +4711,19 @@
         <v>168</v>
       </c>
       <c r="C84" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D84" s="7">
-        <v>0.083953</v>
+        <v>0.084095</v>
       </c>
       <c r="E84" s="8">
-        <v>9009507093.73</v>
+        <v>9095710148.33</v>
       </c>
       <c r="F84" s="9">
-        <v>138118</v>
+        <v>138536</v>
       </c>
       <c r="G84" s="8">
-        <v>756371026.65</v>
+        <v>764903386.42</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4734,19 +4734,19 @@
         <v>170</v>
       </c>
       <c r="C85" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D85" s="7">
-        <v>0.269417</v>
+        <v>0.274492</v>
       </c>
       <c r="E85" s="8">
-        <v>4343954976.72</v>
+        <v>4353968387.79</v>
       </c>
       <c r="F85" s="9">
-        <v>80216</v>
+        <v>80526</v>
       </c>
       <c r="G85" s="8">
-        <v>1170336741.8</v>
+        <v>1195130287.38</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4757,19 +4757,19 @@
         <v>172</v>
       </c>
       <c r="C86" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D86" s="7">
-        <v>0.903257</v>
+        <v>0.926643</v>
       </c>
       <c r="E86" s="8">
-        <v>4610722214.13</v>
+        <v>4620691309.77</v>
       </c>
       <c r="F86" s="9">
-        <v>87564</v>
+        <v>87581</v>
       </c>
       <c r="G86" s="8">
-        <v>4164666855.57</v>
+        <v>4281732487.81</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4780,19 +4780,19 @@
         <v>174</v>
       </c>
       <c r="C87" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D87" s="7">
-        <v>0.223823</v>
+        <v>0.226948</v>
       </c>
       <c r="E87" s="8">
-        <v>12590994855.7</v>
+        <v>12608931329.92</v>
       </c>
       <c r="F87" s="9">
-        <v>144682</v>
+        <v>144759</v>
       </c>
       <c r="G87" s="8">
-        <v>2818154569.43</v>
+        <v>2861566174.03</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4803,19 +4803,19 @@
         <v>176</v>
       </c>
       <c r="C88" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D88" s="7">
-        <v>0.164917</v>
+        <v>0.167955</v>
       </c>
       <c r="E88" s="8">
-        <v>18636080343.95</v>
+        <v>18622715968.85</v>
       </c>
       <c r="F88" s="9">
-        <v>91290</v>
+        <v>91387</v>
       </c>
       <c r="G88" s="8">
-        <v>3073400249.77</v>
+        <v>3127786845.9</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4826,19 +4826,19 @@
         <v>178</v>
       </c>
       <c r="C89" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D89" s="7">
-        <v>0.634957</v>
+        <v>0.638609</v>
       </c>
       <c r="E89" s="8">
-        <v>2269649211.5</v>
+        <v>2267322335.54</v>
       </c>
       <c r="F89" s="9">
-        <v>35864</v>
+        <v>35826</v>
       </c>
       <c r="G89" s="8">
-        <v>1441129508.4</v>
+        <v>1447931569.45</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4849,19 +4849,19 @@
         <v>180</v>
       </c>
       <c r="C90" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D90" s="7">
-        <v>0.844123</v>
+        <v>0.853145</v>
       </c>
       <c r="E90" s="8">
-        <v>19182892326.47</v>
+        <v>19169105652.7</v>
       </c>
       <c r="F90" s="9">
-        <v>272361</v>
+        <v>272019</v>
       </c>
       <c r="G90" s="8">
-        <v>16192729063.53</v>
+        <v>16354027243.1</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4872,19 +4872,19 @@
         <v>182</v>
       </c>
       <c r="C91" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D91" s="7">
-        <v>0.789075</v>
+        <v>0.804647</v>
       </c>
       <c r="E91" s="8">
-        <v>3492080422.73</v>
+        <v>3496258698.45</v>
       </c>
       <c r="F91" s="9">
-        <v>29616</v>
+        <v>29725</v>
       </c>
       <c r="G91" s="8">
-        <v>2755514625.51</v>
+        <v>2813252399.5</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4895,19 +4895,19 @@
         <v>184</v>
       </c>
       <c r="C92" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D92" s="7">
-        <v>0.831038</v>
+        <v>0.838331</v>
       </c>
       <c r="E92" s="8">
-        <v>12345175395.43</v>
+        <v>12335922204.96</v>
       </c>
       <c r="F92" s="9">
-        <v>188658</v>
+        <v>188485</v>
       </c>
       <c r="G92" s="8">
-        <v>10259315042.98</v>
+        <v>10341585577.84</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4918,19 +4918,19 @@
         <v>186</v>
       </c>
       <c r="C93" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D93" s="7">
-        <v>0.088239</v>
+        <v>0.088431</v>
       </c>
       <c r="E93" s="8">
-        <v>7521378062.44</v>
+        <v>7555002353.89</v>
       </c>
       <c r="F93" s="9">
-        <v>154918</v>
+        <v>154807</v>
       </c>
       <c r="G93" s="8">
-        <v>663677524.78</v>
+        <v>668093507.54</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4941,19 +4941,19 @@
         <v>188</v>
       </c>
       <c r="C94" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D94" s="10">
-        <v>0.11994</v>
+        <v>46149</v>
+      </c>
+      <c r="D94" s="7">
+        <v>0.121604</v>
       </c>
       <c r="E94" s="8">
-        <v>11957757550.21</v>
+        <v>11941078541.2</v>
       </c>
       <c r="F94" s="9">
-        <v>33332</v>
+        <v>33315</v>
       </c>
       <c r="G94" s="8">
-        <v>1434207722.19</v>
+        <v>1452083895.23</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4964,19 +4964,19 @@
         <v>190</v>
       </c>
       <c r="C95" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D95" s="7">
-        <v>0.128066</v>
+        <v>0.128197</v>
       </c>
       <c r="E95" s="8">
-        <v>71588330672.27</v>
+        <v>71467359764.4</v>
       </c>
       <c r="F95" s="9">
-        <v>212347</v>
+        <v>212351</v>
       </c>
       <c r="G95" s="8">
-        <v>9168009025.58</v>
+        <v>9161931668.3</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4987,19 +4987,19 @@
         <v>192</v>
       </c>
       <c r="C96" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D96" s="7">
-        <v>0.472949</v>
+        <v>46149</v>
+      </c>
+      <c r="D96" s="10">
+        <v>0.48045</v>
       </c>
       <c r="E96" s="8">
-        <v>31939640562.02</v>
+        <v>32038664189.88</v>
       </c>
       <c r="F96" s="9">
-        <v>283467</v>
+        <v>284064</v>
       </c>
       <c r="G96" s="8">
-        <v>15105811232.31</v>
+        <v>15392974055.47</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -5010,19 +5010,19 @@
         <v>194</v>
       </c>
       <c r="C97" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D97" s="7">
-        <v>0.096727</v>
+        <v>46149</v>
+      </c>
+      <c r="D97" s="10">
+        <v>0.09723</v>
       </c>
       <c r="E97" s="8">
-        <v>24500697721.73</v>
+        <v>24549504624.79</v>
       </c>
       <c r="F97" s="9">
-        <v>441823</v>
+        <v>442390</v>
       </c>
       <c r="G97" s="8">
-        <v>2369869837.33</v>
+        <v>2386956301.64</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -5033,19 +5033,19 @@
         <v>196</v>
       </c>
       <c r="C98" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D98" s="7">
-        <v>0.243694</v>
+        <v>46149</v>
+      </c>
+      <c r="D98" s="10">
+        <v>0.24541</v>
       </c>
       <c r="E98" s="8">
-        <v>1294028689.01</v>
+        <v>1286314983.26</v>
       </c>
       <c r="F98" s="9">
-        <v>7202</v>
+        <v>7157</v>
       </c>
       <c r="G98" s="8">
-        <v>315347364.63</v>
+        <v>315674979.11</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -5056,19 +5056,19 @@
         <v>198</v>
       </c>
       <c r="C99" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D99" s="7">
-        <v>1.040135</v>
+        <v>1.060861</v>
       </c>
       <c r="E99" s="8">
-        <v>4661055445.99</v>
+        <v>4741875430.24</v>
       </c>
       <c r="F99" s="9">
-        <v>47724</v>
+        <v>48444</v>
       </c>
       <c r="G99" s="8">
-        <v>4848128175.34</v>
+        <v>5030469317.25</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5079,19 +5079,19 @@
         <v>200</v>
       </c>
       <c r="C100" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D100" s="7">
-        <v>2.608657</v>
+        <v>2.682165</v>
       </c>
       <c r="E100" s="8">
-        <v>12025988296.4</v>
+        <v>12017974352.05</v>
       </c>
       <c r="F100" s="9">
-        <v>305917</v>
+        <v>305972</v>
       </c>
       <c r="G100" s="8">
-        <v>31371683724.05</v>
+        <v>32234189335.27</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5102,19 +5102,19 @@
         <v>202</v>
       </c>
       <c r="C101" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D101" s="7">
-        <v>0.353762</v>
+        <v>0.356258</v>
       </c>
       <c r="E101" s="8">
-        <v>25971059825.06</v>
+        <v>25780955799.87</v>
       </c>
       <c r="F101" s="9">
-        <v>332189</v>
+        <v>331635</v>
       </c>
       <c r="G101" s="8">
-        <v>9187585440.17</v>
+        <v>9184661296.89</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5125,19 +5125,19 @@
         <v>204</v>
       </c>
       <c r="C102" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D102" s="7">
-        <v>0.368662</v>
+        <v>0.369306</v>
       </c>
       <c r="E102" s="8">
-        <v>201611069674.29</v>
+        <v>202185679194.84</v>
       </c>
       <c r="F102" s="9">
-        <v>354575</v>
+        <v>371239</v>
       </c>
       <c r="G102" s="8">
-        <v>74326346096.24</v>
+        <v>74668307638.31</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5148,19 +5148,19 @@
         <v>206</v>
       </c>
       <c r="C103" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D103" s="7">
-        <v>0.123923</v>
+        <v>0.125604</v>
       </c>
       <c r="E103" s="8">
-        <v>8884343690.88</v>
+        <v>9011692540.9</v>
       </c>
       <c r="F103" s="9">
-        <v>28583</v>
+        <v>28591</v>
       </c>
       <c r="G103" s="8">
-        <v>1100977502.37</v>
+        <v>1131900964.82</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -5171,19 +5171,19 @@
         <v>208</v>
       </c>
       <c r="C104" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D104" s="7">
-        <v>0.286657</v>
+        <v>0.288988</v>
       </c>
       <c r="E104" s="8">
-        <v>1720196604.92</v>
+        <v>1709744707.26</v>
       </c>
       <c r="F104" s="9">
-        <v>7828</v>
+        <v>7823</v>
       </c>
       <c r="G104" s="8">
-        <v>493107223.33</v>
+        <v>494095841.9</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -5194,19 +5194,19 @@
         <v>210</v>
       </c>
       <c r="C105" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D105" s="7">
-        <v>0.009999</v>
+        <v>0.010009</v>
       </c>
       <c r="E105" s="8">
-        <v>81368114.56</v>
+        <v>119081896.75</v>
       </c>
       <c r="F105" s="9">
         <v>0</v>
       </c>
       <c r="G105" s="8">
-        <v>813634.76</v>
+        <v>1191899.12</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5217,19 +5217,19 @@
         <v>212</v>
       </c>
       <c r="C106" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D106" s="7">
-        <v>1.053466</v>
+        <v>1.084953</v>
       </c>
       <c r="E106" s="8">
-        <v>249331738.86</v>
+        <v>254016599.22</v>
       </c>
       <c r="F106" s="9">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="G106" s="8">
-        <v>262662439.54</v>
+        <v>275596070.45</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5240,19 +5240,19 @@
         <v>214</v>
       </c>
       <c r="C107" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D107" s="7">
-        <v>0.999333</v>
+        <v>1.008659</v>
       </c>
       <c r="E107" s="8">
-        <v>613456407.01</v>
+        <v>619921686.03</v>
       </c>
       <c r="F107" s="9">
-        <v>15478</v>
+        <v>15505</v>
       </c>
       <c r="G107" s="8">
-        <v>613047128.61</v>
+        <v>625289826.03</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -5263,19 +5263,19 @@
         <v>216</v>
       </c>
       <c r="C108" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D108" s="7">
-        <v>0.179642</v>
+        <v>0.181089</v>
       </c>
       <c r="E108" s="8">
-        <v>381377996.49</v>
+        <v>382029930.49</v>
       </c>
       <c r="F108" s="9">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="G108" s="8">
-        <v>68511467.65</v>
+        <v>69181446.33</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -5286,19 +5286,19 @@
         <v>218</v>
       </c>
       <c r="C109" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D109" s="7">
-        <v>1.448256</v>
+        <v>1.488158</v>
       </c>
       <c r="E109" s="8">
-        <v>1020218026.58</v>
+        <v>1023647980.26</v>
       </c>
       <c r="F109" s="9">
-        <v>21951</v>
+        <v>21967</v>
       </c>
       <c r="G109" s="8">
-        <v>1477536827.12</v>
+        <v>1523350228.45</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -5309,19 +5309,19 @@
         <v>220</v>
       </c>
       <c r="C110" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D110" s="7">
-        <v>0.097279</v>
+        <v>0.097775</v>
       </c>
       <c r="E110" s="8">
-        <v>5465554179.47</v>
+        <v>5473466049.3</v>
       </c>
       <c r="F110" s="9">
-        <v>24350</v>
+        <v>24355</v>
       </c>
       <c r="G110" s="8">
-        <v>531681499.36</v>
+        <v>535169002.85</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5332,19 +5332,19 @@
         <v>222</v>
       </c>
       <c r="C111" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D111" s="7">
-        <v>0.285727</v>
+        <v>0.288089</v>
       </c>
       <c r="E111" s="8">
-        <v>1640635550.61</v>
+        <v>1643520648.12</v>
       </c>
       <c r="F111" s="9">
-        <v>33288</v>
+        <v>33315</v>
       </c>
       <c r="G111" s="8">
-        <v>468773585.75</v>
+        <v>473480692.74</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -5355,19 +5355,19 @@
         <v>224</v>
       </c>
       <c r="C112" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D112" s="11">
-        <v>0.2151</v>
+        <v>46149</v>
+      </c>
+      <c r="D112" s="7">
+        <v>0.217502</v>
       </c>
       <c r="E112" s="8">
-        <v>589406191.8</v>
+        <v>590490399.81</v>
       </c>
       <c r="F112" s="9">
         <v>1426</v>
       </c>
       <c r="G112" s="8">
-        <v>126781283.17</v>
+        <v>128433053.01</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -5378,19 +5378,19 @@
         <v>226</v>
       </c>
       <c r="C113" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D113" s="7">
-        <v>0.411715</v>
+        <v>0.412799</v>
       </c>
       <c r="E113" s="8">
-        <v>150874677.19</v>
+        <v>151283987.31</v>
       </c>
       <c r="F113" s="9">
-        <v>1213</v>
+        <v>1222</v>
       </c>
       <c r="G113" s="8">
-        <v>62117392.24</v>
+        <v>62449931.02</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5401,19 +5401,19 @@
         <v>228</v>
       </c>
       <c r="C114" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D114" s="7">
-        <v>0.108186</v>
+        <v>0.109143</v>
       </c>
       <c r="E114" s="8">
-        <v>196150017.68</v>
+        <v>195680441.63</v>
       </c>
       <c r="F114" s="9">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G114" s="8">
-        <v>21220657.09</v>
+        <v>21357089.33</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -5424,19 +5424,19 @@
         <v>230</v>
       </c>
       <c r="C115" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D115" s="7">
-        <v>0.062566</v>
+        <v>0.064045</v>
       </c>
       <c r="E115" s="8">
-        <v>1218411778510.52</v>
+        <v>1221038141420.98</v>
       </c>
       <c r="F115" s="9">
-        <v>789381</v>
+        <v>789295</v>
       </c>
       <c r="G115" s="8">
-        <v>76231692577.3</v>
+        <v>78201751800.61</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -5447,19 +5447,19 @@
         <v>232</v>
       </c>
       <c r="C116" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D116" s="7">
-        <v>0.015481</v>
+        <v>0.015495</v>
       </c>
       <c r="E116" s="8">
-        <v>6611585167.1</v>
+        <v>6818931272.91</v>
       </c>
       <c r="F116" s="9">
-        <v>1336</v>
+        <v>1365</v>
       </c>
       <c r="G116" s="8">
-        <v>102356236.59</v>
+        <v>105656498.58</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -5470,19 +5470,19 @@
         <v>234</v>
       </c>
       <c r="C117" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D117" s="7">
-        <v>0.124113</v>
+        <v>0.127137</v>
       </c>
       <c r="E117" s="8">
-        <v>7553534317.07</v>
+        <v>7588565290.55</v>
       </c>
       <c r="F117" s="9">
-        <v>24858</v>
+        <v>24897</v>
       </c>
       <c r="G117" s="8">
-        <v>937494992.57</v>
+        <v>964786425.77</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -5493,19 +5493,19 @@
         <v>236</v>
       </c>
       <c r="C118" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D118" s="10">
-        <v>0.12926</v>
+        <v>46149</v>
+      </c>
+      <c r="D118" s="7">
+        <v>0.130357</v>
       </c>
       <c r="E118" s="8">
-        <v>29129584645.12</v>
+        <v>29750933699.75</v>
       </c>
       <c r="F118" s="9">
-        <v>70089</v>
+        <v>70501</v>
       </c>
       <c r="G118" s="8">
-        <v>3765302949.7</v>
+        <v>3878241088.04</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -5516,19 +5516,19 @@
         <v>238</v>
       </c>
       <c r="C119" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D119" s="7">
-        <v>0.570662</v>
+        <v>0.574771</v>
       </c>
       <c r="E119" s="8">
-        <v>90975733.7</v>
+        <v>91329672.85</v>
       </c>
       <c r="F119" s="9">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="G119" s="8">
-        <v>51916416.47</v>
+        <v>52493648.33</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5539,19 +5539,19 @@
         <v>240</v>
       </c>
       <c r="C120" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D120" s="7">
-        <v>0.735079</v>
+        <v>0.752912</v>
       </c>
       <c r="E120" s="8">
-        <v>22892672928.82</v>
+        <v>22909549299.91</v>
       </c>
       <c r="F120" s="9">
-        <v>149436</v>
+        <v>149776</v>
       </c>
       <c r="G120" s="8">
-        <v>16827917892.66</v>
+        <v>17248870686.08</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5562,19 +5562,19 @@
         <v>242</v>
       </c>
       <c r="C121" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D121" s="7">
-        <v>0.123193</v>
+        <v>0.123532</v>
       </c>
       <c r="E121" s="8">
-        <v>14739073125.53</v>
+        <v>14714699269.85</v>
       </c>
       <c r="F121" s="9">
-        <v>44624</v>
+        <v>44612</v>
       </c>
       <c r="G121" s="8">
-        <v>1815750204.35</v>
+        <v>1817743197.45</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -5585,19 +5585,19 @@
         <v>244</v>
       </c>
       <c r="C122" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D122" s="7">
-        <v>0.104498</v>
+        <v>0.106514</v>
       </c>
       <c r="E122" s="8">
-        <v>42877344749.4</v>
+        <v>42860005411.4</v>
       </c>
       <c r="F122" s="9">
-        <v>338215</v>
+        <v>338137</v>
       </c>
       <c r="G122" s="8">
-        <v>4480584362.3</v>
+        <v>4565200711.13</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -5608,19 +5608,19 @@
         <v>246</v>
       </c>
       <c r="C123" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D123" s="7">
-        <v>0.092924</v>
+        <v>0.093859</v>
       </c>
       <c r="E123" s="8">
-        <v>9698406915.03</v>
+        <v>9714228312.98</v>
       </c>
       <c r="F123" s="9">
-        <v>148035</v>
+        <v>148016</v>
       </c>
       <c r="G123" s="8">
-        <v>901216761.1</v>
+        <v>911765343.67</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -5631,19 +5631,19 @@
         <v>248</v>
       </c>
       <c r="C124" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D124" s="7">
-        <v>0.047919</v>
+        <v>0.048788</v>
       </c>
       <c r="E124" s="8">
-        <v>27960554819.46</v>
+        <v>28015667646.57</v>
       </c>
       <c r="F124" s="9">
-        <v>34591</v>
+        <v>34646</v>
       </c>
       <c r="G124" s="8">
-        <v>1339841012.8</v>
+        <v>1366822735.22</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5654,19 +5654,19 @@
         <v>250</v>
       </c>
       <c r="C125" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D125" s="11">
-        <v>0.1176</v>
+        <v>46149</v>
+      </c>
+      <c r="D125" s="7">
+        <v>0.119022</v>
       </c>
       <c r="E125" s="8">
-        <v>6291741555.99</v>
+        <v>6295578001.25</v>
       </c>
       <c r="F125" s="9">
-        <v>43200</v>
+        <v>43195</v>
       </c>
       <c r="G125" s="8">
-        <v>739907898.87</v>
+        <v>749314238.8</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5677,19 +5677,19 @@
         <v>252</v>
       </c>
       <c r="C126" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D126" s="7">
-        <v>0.090876</v>
+        <v>0.091397</v>
       </c>
       <c r="E126" s="8">
-        <v>2968465325.26</v>
+        <v>2968794572.58</v>
       </c>
       <c r="F126" s="9">
-        <v>83537</v>
+        <v>83532</v>
       </c>
       <c r="G126" s="8">
-        <v>269761722.86</v>
+        <v>271340294.61</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5700,19 +5700,19 @@
         <v>254</v>
       </c>
       <c r="C127" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D127" s="7">
-        <v>0.083976</v>
+        <v>0.084587</v>
       </c>
       <c r="E127" s="8">
-        <v>1128373212.07</v>
+        <v>1128155178.56</v>
       </c>
       <c r="F127" s="9">
-        <v>122904</v>
+        <v>122899</v>
       </c>
       <c r="G127" s="8">
-        <v>94756357.57</v>
+        <v>95427412.44</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5723,19 +5723,19 @@
         <v>256</v>
       </c>
       <c r="C128" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D128" s="7">
-        <v>0.762212</v>
+        <v>46149</v>
+      </c>
+      <c r="D128" s="10">
+        <v>0.77669</v>
       </c>
       <c r="E128" s="8">
-        <v>1638328098.3</v>
+        <v>1638316790.8</v>
       </c>
       <c r="F128" s="9">
-        <v>49943</v>
+        <v>49930</v>
       </c>
       <c r="G128" s="8">
-        <v>1248752953.37</v>
+        <v>1272464007.19</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5746,19 +5746,19 @@
         <v>258</v>
       </c>
       <c r="C129" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D129" s="7">
-        <v>0.147791</v>
+        <v>0.148856</v>
       </c>
       <c r="E129" s="8">
-        <v>1296944436.14</v>
+        <v>1298235667.08</v>
       </c>
       <c r="F129" s="9">
-        <v>12554</v>
+        <v>12560</v>
       </c>
       <c r="G129" s="8">
-        <v>191676997.76</v>
+        <v>193249629.98</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5769,19 +5769,19 @@
         <v>260</v>
       </c>
       <c r="C130" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D130" s="7">
-        <v>0.237711</v>
+        <v>0.239459</v>
       </c>
       <c r="E130" s="8">
-        <v>5192476999.71</v>
+        <v>5189405759.69</v>
       </c>
       <c r="F130" s="9">
-        <v>69513</v>
+        <v>69496</v>
       </c>
       <c r="G130" s="8">
-        <v>1234307976.38</v>
+        <v>1242650049.22</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5792,19 +5792,19 @@
         <v>262</v>
       </c>
       <c r="C131" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D131" s="7">
-        <v>1.821692</v>
+        <v>1.879445</v>
       </c>
       <c r="E131" s="8">
-        <v>2373431130.75</v>
+        <v>2372424151.46</v>
       </c>
       <c r="F131" s="9">
-        <v>52943</v>
+        <v>52974</v>
       </c>
       <c r="G131" s="8">
-        <v>4323661508.27</v>
+        <v>4458840657.93</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5815,19 +5815,19 @@
         <v>264</v>
       </c>
       <c r="C132" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D132" s="10">
-        <v>0.35113</v>
+        <v>46149</v>
+      </c>
+      <c r="D132" s="7">
+        <v>0.357403</v>
       </c>
       <c r="E132" s="8">
-        <v>557179937.88</v>
+        <v>556520232.91</v>
       </c>
       <c r="F132" s="9">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="G132" s="8">
-        <v>195642416.43</v>
+        <v>198901969.8</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5838,19 +5838,19 @@
         <v>266</v>
       </c>
       <c r="C133" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D133" s="7">
-        <v>0.158977</v>
+        <v>0.161927</v>
       </c>
       <c r="E133" s="8">
-        <v>132303463.27</v>
+        <v>132522243.19</v>
       </c>
       <c r="F133" s="9">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G133" s="8">
-        <v>21033234.34</v>
+        <v>21458948.29</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,19 +5861,19 @@
         <v>268</v>
       </c>
       <c r="C134" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D134" s="7">
-        <v>0.705405</v>
+        <v>0.707543</v>
       </c>
       <c r="E134" s="8">
-        <v>1259264754.83</v>
+        <v>1257408026.82</v>
       </c>
       <c r="F134" s="9">
-        <v>21173</v>
+        <v>21164</v>
       </c>
       <c r="G134" s="8">
-        <v>888291720.93</v>
+        <v>889670737.48</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5884,19 +5884,19 @@
         <v>270</v>
       </c>
       <c r="C135" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D135" s="7">
-        <v>0.370926</v>
+        <v>0.371589</v>
       </c>
       <c r="E135" s="8">
-        <v>7462935189.45</v>
+        <v>7438502397.88</v>
       </c>
       <c r="F135" s="9">
-        <v>101123</v>
+        <v>90723</v>
       </c>
       <c r="G135" s="8">
-        <v>2768199535.74</v>
+        <v>2764065891.86</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5907,19 +5907,19 @@
         <v>272</v>
       </c>
       <c r="C136" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D136" s="7">
-        <v>0.201261</v>
+        <v>0.205619</v>
       </c>
       <c r="E136" s="8">
-        <v>198903737.77</v>
+        <v>199077640.63</v>
       </c>
       <c r="F136" s="9">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="G136" s="8">
-        <v>40031593.7</v>
+        <v>40934187.7</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5930,19 +5930,19 @@
         <v>274</v>
       </c>
       <c r="C137" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D137" s="7">
-        <v>0.261483</v>
+        <v>0.266268</v>
       </c>
       <c r="E137" s="8">
-        <v>402771298.13</v>
+        <v>404767982.87</v>
       </c>
       <c r="F137" s="9">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="G137" s="8">
-        <v>105317700.43</v>
+        <v>107776948.62</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5953,19 +5953,19 @@
         <v>276</v>
       </c>
       <c r="C138" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D138" s="7">
-        <v>0.100489</v>
+        <v>0.101136</v>
       </c>
       <c r="E138" s="8">
-        <v>294958936.32</v>
+        <v>295406079.77</v>
       </c>
       <c r="F138" s="9">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G138" s="8">
-        <v>29639994.67</v>
+        <v>29876091.08</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5976,19 +5976,19 @@
         <v>278</v>
       </c>
       <c r="C139" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D139" s="7">
-        <v>0.396212</v>
+        <v>0.404042</v>
       </c>
       <c r="E139" s="8">
-        <v>629313815.76</v>
+        <v>630538168.58</v>
       </c>
       <c r="F139" s="9">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="G139" s="8">
-        <v>249341603.16</v>
+        <v>254763990.98</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5999,19 +5999,19 @@
         <v>280</v>
       </c>
       <c r="C140" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D140" s="7">
-        <v>0.696904</v>
+        <v>0.702328</v>
       </c>
       <c r="E140" s="8">
-        <v>2930592383.91</v>
+        <v>2932809723.24</v>
       </c>
       <c r="F140" s="9">
-        <v>42030</v>
+        <v>42012</v>
       </c>
       <c r="G140" s="8">
-        <v>2042340256.91</v>
+        <v>2059794924.91</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -6022,19 +6022,19 @@
         <v>282</v>
       </c>
       <c r="C141" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D141" s="7">
-        <v>0.013967</v>
+        <v>0.014252</v>
       </c>
       <c r="E141" s="8">
-        <v>2853414461.1</v>
+        <v>2874514460.59</v>
       </c>
       <c r="F141" s="9">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="G141" s="8">
-        <v>39852806.77</v>
+        <v>40966308.3</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -6045,19 +6045,19 @@
         <v>284</v>
       </c>
       <c r="C142" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D142" s="7">
-        <v>0.074885</v>
+        <v>0.076375</v>
       </c>
       <c r="E142" s="8">
-        <v>22101879892.22</v>
+        <v>22239381445.22</v>
       </c>
       <c r="F142" s="9">
-        <v>23514</v>
+        <v>23555</v>
       </c>
       <c r="G142" s="8">
-        <v>1655101775.84</v>
+        <v>1698533405.33</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -6068,19 +6068,19 @@
         <v>286</v>
       </c>
       <c r="C143" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D143" s="7">
-        <v>0.279137</v>
+        <v>46149</v>
+      </c>
+      <c r="D143" s="10">
+        <v>0.28631</v>
       </c>
       <c r="E143" s="8">
-        <v>20696954474.98</v>
+        <v>20716363049.97</v>
       </c>
       <c r="F143" s="9">
         <v>4725</v>
       </c>
       <c r="G143" s="8">
-        <v>5777292784.39</v>
+        <v>5931307552.01</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -6091,19 +6091,19 @@
         <v>288</v>
       </c>
       <c r="C144" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D144" s="7">
-        <v>0.090752</v>
+        <v>0.090903</v>
       </c>
       <c r="E144" s="8">
-        <v>676599649.29</v>
+        <v>652853993.67</v>
       </c>
       <c r="F144" s="9">
-        <v>11119</v>
+        <v>11030</v>
       </c>
       <c r="G144" s="8">
-        <v>61402724.34</v>
+        <v>59346547.63</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -6114,19 +6114,19 @@
         <v>290</v>
       </c>
       <c r="C145" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D145" s="7">
-        <v>0.053755</v>
+        <v>0.054312</v>
       </c>
       <c r="E145" s="8">
-        <v>1402260864.75</v>
+        <v>1422152327.93</v>
       </c>
       <c r="F145" s="9">
         <v>316</v>
       </c>
       <c r="G145" s="8">
-        <v>75378749.72</v>
+        <v>77239476.17</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -6137,19 +6137,19 @@
         <v>292</v>
       </c>
       <c r="C146" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D146" s="7">
-        <v>0.113508</v>
+        <v>0.114329</v>
       </c>
       <c r="E146" s="8">
-        <v>1807701316.27</v>
+        <v>1809987757.49</v>
       </c>
       <c r="F146" s="9">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="G146" s="8">
-        <v>205188432.65</v>
+        <v>206933302.63</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6160,19 +6160,19 @@
         <v>294</v>
       </c>
       <c r="C147" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D147" s="7">
-        <v>0.113495</v>
+        <v>0.114326</v>
       </c>
       <c r="E147" s="8">
-        <v>1964327759.79</v>
+        <v>1966256581.28</v>
       </c>
       <c r="F147" s="9">
-        <v>65279</v>
+        <v>65271</v>
       </c>
       <c r="G147" s="8">
-        <v>222941659.24</v>
+        <v>224793590.77</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -6183,19 +6183,19 @@
         <v>296</v>
       </c>
       <c r="C148" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D148" s="7">
-        <v>0.076873</v>
+        <v>0.077339</v>
       </c>
       <c r="E148" s="8">
-        <v>571278655.15</v>
+        <v>571255665.49</v>
       </c>
       <c r="F148" s="9">
         <v>52202</v>
       </c>
       <c r="G148" s="8">
-        <v>43915864.79</v>
+        <v>44180315.54</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6206,19 +6206,19 @@
         <v>298</v>
       </c>
       <c r="C149" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D149" s="7">
-        <v>0.082404</v>
+        <v>0.082561</v>
       </c>
       <c r="E149" s="8">
-        <v>357013457.43</v>
+        <v>359688320.98</v>
       </c>
       <c r="F149" s="9">
-        <v>9526</v>
+        <v>9528</v>
       </c>
       <c r="G149" s="8">
-        <v>29419415.7</v>
+        <v>29696352.06</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -6229,19 +6229,19 @@
         <v>300</v>
       </c>
       <c r="C150" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D150" s="7">
-        <v>0.363293</v>
+        <v>0.371849</v>
       </c>
       <c r="E150" s="8">
-        <v>145633608.93</v>
+        <v>145647084.28</v>
       </c>
       <c r="F150" s="9">
         <v>1767</v>
       </c>
       <c r="G150" s="8">
-        <v>52907671.7</v>
+        <v>54158655.77</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6252,19 +6252,19 @@
         <v>302</v>
       </c>
       <c r="C151" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D151" s="7">
-        <v>0.098282</v>
+        <v>0.099297</v>
       </c>
       <c r="E151" s="8">
-        <v>335220148.31</v>
+        <v>335382392.88</v>
       </c>
       <c r="F151" s="9">
         <v>1838</v>
       </c>
       <c r="G151" s="8">
-        <v>32946148.38</v>
+        <v>33302460.07</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -6275,19 +6275,19 @@
         <v>304</v>
       </c>
       <c r="C152" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D152" s="7">
-        <v>0.290822</v>
+        <v>46149</v>
+      </c>
+      <c r="D152" s="10">
+        <v>0.29742</v>
       </c>
       <c r="E152" s="8">
-        <v>142660038.68</v>
+        <v>142310737.35</v>
       </c>
       <c r="F152" s="9">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G152" s="8">
-        <v>41488713.73</v>
+        <v>42326054.37</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -6298,19 +6298,19 @@
         <v>306</v>
       </c>
       <c r="C153" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D153" s="7">
-        <v>0.117506</v>
+        <v>0.118094</v>
       </c>
       <c r="E153" s="8">
-        <v>588222168.5</v>
+        <v>589345421.92</v>
       </c>
       <c r="F153" s="9">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G153" s="8">
-        <v>69119862.64</v>
+        <v>69598160.54</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -6321,19 +6321,19 @@
         <v>308</v>
       </c>
       <c r="C154" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D154" s="7">
-        <v>0.401665</v>
+        <v>0.406413</v>
       </c>
       <c r="E154" s="8">
-        <v>1303721457.15</v>
+        <v>1303315599.83</v>
       </c>
       <c r="F154" s="9">
         <v>127</v>
       </c>
       <c r="G154" s="8">
-        <v>523659450.26</v>
+        <v>529684545.16</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -6344,19 +6344,19 @@
         <v>310</v>
       </c>
       <c r="C155" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D155" s="7">
-        <v>0.507053</v>
+        <v>0.519524</v>
       </c>
       <c r="E155" s="8">
-        <v>592860409.26</v>
+        <v>593663442.68</v>
       </c>
       <c r="F155" s="9">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G155" s="8">
-        <v>300611704.87</v>
+        <v>308422622.41</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -6367,19 +6367,19 @@
         <v>312</v>
       </c>
       <c r="C156" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D156" s="7">
-        <v>1.688882</v>
+        <v>1.738748</v>
       </c>
       <c r="E156" s="8">
-        <v>912313565.94</v>
+        <v>912543060.5</v>
       </c>
       <c r="F156" s="9">
-        <v>10184</v>
+        <v>10187</v>
       </c>
       <c r="G156" s="8">
-        <v>1540789988.06</v>
+        <v>1586681984.79</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -6390,19 +6390,19 @@
         <v>314</v>
       </c>
       <c r="C157" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D157" s="7">
-        <v>0.280476</v>
+        <v>0.283231</v>
       </c>
       <c r="E157" s="8">
-        <v>184472793.29</v>
+        <v>185011822.91</v>
       </c>
       <c r="F157" s="9">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G157" s="8">
-        <v>51740184.58</v>
+        <v>52401096.33</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -6413,19 +6413,19 @@
         <v>316</v>
       </c>
       <c r="C158" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D158" s="10">
-        <v>0.14289</v>
+        <v>46149</v>
+      </c>
+      <c r="D158" s="7">
+        <v>0.144389</v>
       </c>
       <c r="E158" s="8">
-        <v>4599278346.77</v>
+        <v>4600642586.23</v>
       </c>
       <c r="F158" s="9">
         <v>28822</v>
       </c>
       <c r="G158" s="8">
-        <v>657191528.17</v>
+        <v>664284003.84</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -6436,19 +6436,19 @@
         <v>318</v>
       </c>
       <c r="C159" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D159" s="7">
-        <v>0.167213</v>
+        <v>0.167544</v>
       </c>
       <c r="E159" s="8">
-        <v>3260190471.63</v>
+        <v>3289667050.24</v>
       </c>
       <c r="F159" s="9">
-        <v>12144</v>
+        <v>12071</v>
       </c>
       <c r="G159" s="8">
-        <v>545147219.87</v>
+        <v>551162811.28</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -6459,19 +6459,19 @@
         <v>320</v>
       </c>
       <c r="C160" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D160" s="7">
-        <v>0.693737</v>
+        <v>0.708039</v>
       </c>
       <c r="E160" s="8">
-        <v>765438953.86</v>
+        <v>766311723.02</v>
       </c>
       <c r="F160" s="9">
-        <v>5169</v>
+        <v>5171</v>
       </c>
       <c r="G160" s="8">
-        <v>531013463.67</v>
+        <v>542578537.67</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -6482,19 +6482,19 @@
         <v>322</v>
       </c>
       <c r="C161" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D161" s="7">
-        <v>0.374713</v>
+        <v>0.382881</v>
       </c>
       <c r="E161" s="8">
-        <v>1341683545.63</v>
+        <v>1341079135.48</v>
       </c>
       <c r="F161" s="9">
-        <v>23894</v>
+        <v>23893</v>
       </c>
       <c r="G161" s="8">
-        <v>502746198.33</v>
+        <v>513474105.07</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -6505,19 +6505,19 @@
         <v>324</v>
       </c>
       <c r="C162" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D162" s="7">
-        <v>0.366591</v>
+        <v>46149</v>
+      </c>
+      <c r="D162" s="10">
+        <v>0.37657</v>
       </c>
       <c r="E162" s="8">
-        <v>168387624.52</v>
+        <v>168480863.33</v>
       </c>
       <c r="F162" s="9">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G162" s="8">
-        <v>61729347.28</v>
+        <v>63444906.55</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -6528,19 +6528,19 @@
         <v>326</v>
       </c>
       <c r="C163" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D163" s="10">
-        <v>0.14253</v>
+        <v>46149</v>
+      </c>
+      <c r="D163" s="7">
+        <v>0.144811</v>
       </c>
       <c r="E163" s="8">
-        <v>1028060527.51</v>
+        <v>1026666583.99</v>
       </c>
       <c r="F163" s="9">
-        <v>2971</v>
+        <v>2973</v>
       </c>
       <c r="G163" s="8">
-        <v>146529134.28</v>
+        <v>148672577.18</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -6551,19 +6551,19 @@
         <v>328</v>
       </c>
       <c r="C164" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D164" s="7">
-        <v>0.117071</v>
+        <v>0.119729</v>
       </c>
       <c r="E164" s="8">
-        <v>7574060633.19</v>
+        <v>7567145891.84</v>
       </c>
       <c r="F164" s="9">
-        <v>79742</v>
+        <v>79740</v>
       </c>
       <c r="G164" s="8">
-        <v>886705554.83</v>
+        <v>906003226.04</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -6574,19 +6574,19 @@
         <v>330</v>
       </c>
       <c r="C165" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D165" s="7">
-        <v>0.107998</v>
+        <v>0.109532</v>
       </c>
       <c r="E165" s="8">
-        <v>3312365127.74</v>
+        <v>3331717479.64</v>
       </c>
       <c r="F165" s="9">
-        <v>64833</v>
+        <v>64872</v>
       </c>
       <c r="G165" s="8">
-        <v>357729470.57</v>
+        <v>364930266.58</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -6597,19 +6597,19 @@
         <v>332</v>
       </c>
       <c r="C166" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D166" s="7">
-        <v>0.014475</v>
+        <v>0.014865</v>
       </c>
       <c r="E166" s="8">
-        <v>429853016545.65</v>
+        <v>429915174732.2</v>
       </c>
       <c r="F166" s="9">
-        <v>73536</v>
+        <v>73844</v>
       </c>
       <c r="G166" s="8">
-        <v>6222034222.05</v>
+        <v>6390507872.03</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -6620,19 +6620,19 @@
         <v>334</v>
       </c>
       <c r="C167" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D167" s="10">
-        <v>0.35928</v>
+        <v>46149</v>
+      </c>
+      <c r="D167" s="7">
+        <v>0.364857</v>
       </c>
       <c r="E167" s="8">
-        <v>685794453.12</v>
+        <v>691801222.85</v>
       </c>
       <c r="F167" s="9">
-        <v>6846</v>
+        <v>6876</v>
       </c>
       <c r="G167" s="8">
-        <v>246391974.42</v>
+        <v>252408618.55</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6643,19 +6643,19 @@
         <v>336</v>
       </c>
       <c r="C168" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D168" s="7">
-        <v>0.013979</v>
+        <v>0.014211</v>
       </c>
       <c r="E168" s="8">
-        <v>35271662622.64</v>
+        <v>36031790269.18</v>
       </c>
       <c r="F168" s="9">
-        <v>6010</v>
+        <v>6102</v>
       </c>
       <c r="G168" s="8">
-        <v>493069082.95</v>
+        <v>512038046.24</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6666,19 +6666,19 @@
         <v>338</v>
       </c>
       <c r="C169" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D169" s="7">
-        <v>0.682788</v>
+        <v>0.697667</v>
       </c>
       <c r="E169" s="8">
-        <v>1942694548.02</v>
+        <v>1941433538.84</v>
       </c>
       <c r="F169" s="9">
-        <v>32761</v>
+        <v>32778</v>
       </c>
       <c r="G169" s="8">
-        <v>1326447556.06</v>
+        <v>1354473202.7</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6689,19 +6689,19 @@
         <v>340</v>
       </c>
       <c r="C170" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D170" s="7">
-        <v>0.385596</v>
+        <v>0.389289</v>
       </c>
       <c r="E170" s="8">
-        <v>1981201017.14</v>
+        <v>1984541260.1</v>
       </c>
       <c r="F170" s="9">
-        <v>20967</v>
+        <v>21003</v>
       </c>
       <c r="G170" s="8">
-        <v>763942217.39</v>
+        <v>772560394.3</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6712,19 +6712,19 @@
         <v>342</v>
       </c>
       <c r="C171" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D171" s="7">
-        <v>0.139364</v>
+        <v>0.140961</v>
       </c>
       <c r="E171" s="8">
-        <v>1568490067.55</v>
+        <v>1566809784.57</v>
       </c>
       <c r="F171" s="9">
-        <v>16349</v>
+        <v>16344</v>
       </c>
       <c r="G171" s="8">
-        <v>218590344.48</v>
+        <v>220858346.51</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6735,19 +6735,19 @@
         <v>344</v>
       </c>
       <c r="C172" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D172" s="7">
-        <v>1.237758</v>
+        <v>1.273356</v>
       </c>
       <c r="E172" s="8">
-        <v>1396597227.71</v>
+        <v>1397103360.42</v>
       </c>
       <c r="F172" s="9">
-        <v>23858</v>
+        <v>23894</v>
       </c>
       <c r="G172" s="8">
-        <v>1728649942.33</v>
+        <v>1779009820.61</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6758,19 +6758,19 @@
         <v>346</v>
       </c>
       <c r="C173" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D173" s="7">
-        <v>0.568405</v>
+        <v>0.573284</v>
       </c>
       <c r="E173" s="8">
-        <v>2362909070.66</v>
+        <v>2358193429.94</v>
       </c>
       <c r="F173" s="9">
-        <v>34921</v>
+        <v>34874</v>
       </c>
       <c r="G173" s="8">
-        <v>1343090490.04</v>
+        <v>1351915629.91</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6781,19 +6781,19 @@
         <v>348</v>
       </c>
       <c r="C174" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D174" s="7">
-        <v>0.017481</v>
+        <v>0.017646</v>
       </c>
       <c r="E174" s="8">
-        <v>74180233142.33</v>
+        <v>74964377808.5</v>
       </c>
       <c r="F174" s="9">
-        <v>17819</v>
+        <v>18002</v>
       </c>
       <c r="G174" s="8">
-        <v>1296778246.63</v>
+        <v>1322815672.78</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6804,19 +6804,19 @@
         <v>350</v>
       </c>
       <c r="C175" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D175" s="7">
-        <v>0.088865</v>
+        <v>0.090051</v>
       </c>
       <c r="E175" s="8">
-        <v>2183053862</v>
+        <v>2209331109.01</v>
       </c>
       <c r="F175" s="9">
-        <v>5160</v>
+        <v>5198</v>
       </c>
       <c r="G175" s="8">
-        <v>193997861.52</v>
+        <v>198952276.19</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6827,19 +6827,19 @@
         <v>352</v>
       </c>
       <c r="C176" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D176" s="7">
-        <v>0.122147</v>
+        <v>0.122252</v>
       </c>
       <c r="E176" s="8">
-        <v>1624637943.52</v>
+        <v>1636074762.6</v>
       </c>
       <c r="F176" s="9">
         <v>1207</v>
       </c>
       <c r="G176" s="8">
-        <v>198444177.15</v>
+        <v>200013981.7</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6850,19 +6850,19 @@
         <v>354</v>
       </c>
       <c r="C177" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D177" s="7">
-        <v>0.311426</v>
+        <v>0.315881</v>
       </c>
       <c r="E177" s="8">
-        <v>750748788.48</v>
+        <v>749542167.66</v>
       </c>
       <c r="F177" s="9">
         <v>1944</v>
       </c>
       <c r="G177" s="8">
-        <v>233802521.23</v>
+        <v>236766021.86</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6873,19 +6873,19 @@
         <v>356</v>
       </c>
       <c r="C178" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D178" s="7">
-        <v>0.090281</v>
+        <v>0.091728</v>
       </c>
       <c r="E178" s="8">
-        <v>41914570558.69</v>
+        <v>41876476157.66</v>
       </c>
       <c r="F178" s="9">
-        <v>283677</v>
+        <v>283604</v>
       </c>
       <c r="G178" s="8">
-        <v>3784080020.98</v>
+        <v>3841262637.95</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6896,19 +6896,19 @@
         <v>358</v>
       </c>
       <c r="C179" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D179" s="7">
-        <v>0.064751</v>
+        <v>0.065632</v>
       </c>
       <c r="E179" s="8">
-        <v>669802614.94</v>
+        <v>670307394.4</v>
       </c>
       <c r="F179" s="9">
-        <v>6099</v>
+        <v>6098</v>
       </c>
       <c r="G179" s="8">
-        <v>43370344.5</v>
+        <v>43993698.31</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6919,19 +6919,19 @@
         <v>360</v>
       </c>
       <c r="C180" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D180" s="7">
-        <v>0.248705</v>
+        <v>0.252359</v>
       </c>
       <c r="E180" s="8">
-        <v>548599095.76</v>
+        <v>549744958.44</v>
       </c>
       <c r="F180" s="9">
         <v>1767</v>
       </c>
       <c r="G180" s="8">
-        <v>136439606.32</v>
+        <v>138732939.67</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6942,19 +6942,19 @@
         <v>362</v>
       </c>
       <c r="C181" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D181" s="7">
-        <v>0.391476</v>
+        <v>0.399349</v>
       </c>
       <c r="E181" s="8">
-        <v>365874701.39</v>
+        <v>369653486.74</v>
       </c>
       <c r="F181" s="9">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="G181" s="8">
-        <v>143231257</v>
+        <v>147620577.25</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6965,19 +6965,19 @@
         <v>364</v>
       </c>
       <c r="C182" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D182" s="7">
-        <v>0.111244</v>
+        <v>0.112166</v>
       </c>
       <c r="E182" s="8">
-        <v>14367136359.54</v>
+        <v>14346562715.78</v>
       </c>
       <c r="F182" s="9">
-        <v>32185</v>
+        <v>32173</v>
       </c>
       <c r="G182" s="8">
-        <v>1598256688.04</v>
+        <v>1609196839.4</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6988,19 +6988,19 @@
         <v>366</v>
       </c>
       <c r="C183" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D183" s="7">
-        <v>0.115824</v>
+        <v>0.116063</v>
       </c>
       <c r="E183" s="8">
-        <v>22933085309.71</v>
+        <v>23298175959.61</v>
       </c>
       <c r="F183" s="9">
-        <v>47449</v>
+        <v>42183</v>
       </c>
       <c r="G183" s="8">
-        <v>2656212270.57</v>
+        <v>2704062436.59</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7011,19 +7011,19 @@
         <v>368</v>
       </c>
       <c r="C184" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D184" s="7">
-        <v>0.095774</v>
+        <v>0.097336</v>
       </c>
       <c r="E184" s="8">
-        <v>31280403232.42</v>
+        <v>31473375092.69</v>
       </c>
       <c r="F184" s="9">
-        <v>30006</v>
+        <v>30109</v>
       </c>
       <c r="G184" s="8">
-        <v>2995841021.53</v>
+        <v>3063477394.87</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7034,19 +7034,19 @@
         <v>370</v>
       </c>
       <c r="C185" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D185" s="7">
-        <v>0.084152</v>
+        <v>0.085948</v>
       </c>
       <c r="E185" s="8">
-        <v>6426275246.4</v>
+        <v>6420642577.08</v>
       </c>
       <c r="F185" s="9">
-        <v>5040</v>
+        <v>5035</v>
       </c>
       <c r="G185" s="8">
-        <v>540783631.65</v>
+        <v>551839892.96</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7057,19 +7057,19 @@
         <v>372</v>
       </c>
       <c r="C186" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D186" s="7">
-        <v>0.072845</v>
+        <v>0.073561</v>
       </c>
       <c r="E186" s="8">
-        <v>14041819454.87</v>
+        <v>14116376889.64</v>
       </c>
       <c r="F186" s="9">
-        <v>184437</v>
+        <v>184447</v>
       </c>
       <c r="G186" s="8">
-        <v>1022874474.69</v>
+        <v>1038418976.95</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7080,19 +7080,19 @@
         <v>374</v>
       </c>
       <c r="C187" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D187" s="7">
-        <v>0.099271</v>
+        <v>0.099658</v>
       </c>
       <c r="E187" s="8">
-        <v>4081590656.53</v>
+        <v>4089747856.28</v>
       </c>
       <c r="F187" s="9">
-        <v>117677</v>
+        <v>117648</v>
       </c>
       <c r="G187" s="8">
-        <v>405184631.65</v>
+        <v>407575011.58</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7103,19 +7103,19 @@
         <v>376</v>
       </c>
       <c r="C188" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D188" s="7">
-        <v>0.240753</v>
+        <v>0.246151</v>
       </c>
       <c r="E188" s="8">
-        <v>666821783.03</v>
+        <v>669703264.62</v>
       </c>
       <c r="F188" s="9">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="G188" s="8">
-        <v>160539281.28</v>
+        <v>164847849.8</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7126,19 +7126,19 @@
         <v>378</v>
       </c>
       <c r="C189" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D189" s="10">
-        <v>0.08498</v>
+        <v>46149</v>
+      </c>
+      <c r="D189" s="7">
+        <v>0.085144</v>
       </c>
       <c r="E189" s="8">
-        <v>2895625278.19</v>
+        <v>2837636560.25</v>
       </c>
       <c r="F189" s="9">
-        <v>44038</v>
+        <v>43577</v>
       </c>
       <c r="G189" s="8">
-        <v>246070598.34</v>
+        <v>241606494.24</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7149,19 +7149,19 @@
         <v>380</v>
       </c>
       <c r="C190" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D190" s="7">
-        <v>0.244549</v>
+        <v>0.246442</v>
       </c>
       <c r="E190" s="8">
-        <v>3424604430.96</v>
+        <v>3389280599.11</v>
       </c>
       <c r="F190" s="9">
-        <v>6605</v>
+        <v>6640</v>
       </c>
       <c r="G190" s="8">
-        <v>837484213.11</v>
+        <v>835260933.56</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7172,19 +7172,19 @@
         <v>382</v>
       </c>
       <c r="C191" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D191" s="7">
-        <v>0.160866</v>
+        <v>0.163573</v>
       </c>
       <c r="E191" s="8">
-        <v>704404728.19</v>
+        <v>708015323.76</v>
       </c>
       <c r="F191" s="9">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="G191" s="8">
-        <v>113314469.36</v>
+        <v>115812133.61</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7195,19 +7195,19 @@
         <v>384</v>
       </c>
       <c r="C192" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D192" s="10">
-        <v>0.14909</v>
+        <v>46149</v>
+      </c>
+      <c r="D192" s="7">
+        <v>0.151777</v>
       </c>
       <c r="E192" s="8">
-        <v>489523250.36</v>
+        <v>491503823.48</v>
       </c>
       <c r="F192" s="9">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="G192" s="8">
-        <v>72982858.15</v>
+        <v>74599002.9</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7218,19 +7218,19 @@
         <v>386</v>
       </c>
       <c r="C193" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D193" s="7">
-        <v>0.101962</v>
+        <v>0.102669</v>
       </c>
       <c r="E193" s="8">
-        <v>1167043649.75</v>
+        <v>1166853199.17</v>
       </c>
       <c r="F193" s="9">
-        <v>117376</v>
+        <v>117361</v>
       </c>
       <c r="G193" s="8">
-        <v>118994345.38</v>
+        <v>119799273.15</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7241,19 +7241,19 @@
         <v>388</v>
       </c>
       <c r="C194" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D194" s="7">
-        <v>0.200644</v>
+        <v>0.204395</v>
       </c>
       <c r="E194" s="8">
-        <v>1979238071.55</v>
+        <v>1999540238.22</v>
       </c>
       <c r="F194" s="9">
-        <v>1577</v>
+        <v>1601</v>
       </c>
       <c r="G194" s="8">
-        <v>397121515.71</v>
+        <v>408696670.92</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7264,19 +7264,19 @@
         <v>390</v>
       </c>
       <c r="C195" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D195" s="10">
-        <v>0.15836</v>
+        <v>46149</v>
+      </c>
+      <c r="D195" s="7">
+        <v>0.159316</v>
       </c>
       <c r="E195" s="8">
-        <v>592849402.12</v>
+        <v>596667517.77</v>
       </c>
       <c r="F195" s="9">
-        <v>2660</v>
+        <v>2662</v>
       </c>
       <c r="G195" s="8">
-        <v>93883508.29</v>
+        <v>95058412.45</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7287,19 +7287,19 @@
         <v>392</v>
       </c>
       <c r="C196" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D196" s="7">
-        <v>0.272665</v>
+        <v>0.276581</v>
       </c>
       <c r="E196" s="8">
-        <v>2786128880.55</v>
+        <v>2773306816.86</v>
       </c>
       <c r="F196" s="9">
-        <v>7688</v>
+        <v>7677</v>
       </c>
       <c r="G196" s="8">
-        <v>759681204.54</v>
+        <v>767043400.17</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7310,19 +7310,19 @@
         <v>394</v>
       </c>
       <c r="C197" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D197" s="10">
-        <v>0.09932</v>
+        <v>46149</v>
+      </c>
+      <c r="D197" s="7">
+        <v>0.099843</v>
       </c>
       <c r="E197" s="8">
-        <v>104673956.94</v>
+        <v>104280898.99</v>
       </c>
       <c r="F197" s="9">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="G197" s="8">
-        <v>10396168.9</v>
+        <v>10411672.17</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7333,19 +7333,19 @@
         <v>396</v>
       </c>
       <c r="C198" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D198" s="7">
-        <v>0.222742</v>
+        <v>0.226244</v>
       </c>
       <c r="E198" s="8">
-        <v>322934137.07</v>
+        <v>324740843.14</v>
       </c>
       <c r="F198" s="9">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="G198" s="8">
-        <v>71930995.56</v>
+        <v>73470621.61</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7356,19 +7356,19 @@
         <v>398</v>
       </c>
       <c r="C199" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D199" s="7">
-        <v>0.176627</v>
+        <v>0.178946</v>
       </c>
       <c r="E199" s="8">
-        <v>271574022.99</v>
+        <v>273125635.62</v>
       </c>
       <c r="F199" s="9">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="G199" s="8">
-        <v>47967404.42</v>
+        <v>48874716.69</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7379,19 +7379,19 @@
         <v>400</v>
       </c>
       <c r="C200" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D200" s="7">
-        <v>0.088076</v>
+        <v>0.088166</v>
       </c>
       <c r="E200" s="8">
-        <v>2710251611.88</v>
+        <v>2710842293.57</v>
       </c>
       <c r="F200" s="9">
-        <v>40853</v>
+        <v>40818</v>
       </c>
       <c r="G200" s="8">
-        <v>238708213.56</v>
+        <v>239005213.25</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7402,19 +7402,19 @@
         <v>402</v>
       </c>
       <c r="C201" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D201" s="7">
-        <v>0.089935</v>
+        <v>46149</v>
+      </c>
+      <c r="D201" s="10">
+        <v>0.09037</v>
       </c>
       <c r="E201" s="8">
-        <v>829983180.1</v>
+        <v>832459092.48</v>
       </c>
       <c r="F201" s="9">
         <v>1373</v>
       </c>
       <c r="G201" s="8">
-        <v>74644428.3</v>
+        <v>75229068.47</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7425,19 +7425,19 @@
         <v>404</v>
       </c>
       <c r="C202" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D202" s="7">
-        <v>0.151764</v>
+        <v>0.153519</v>
       </c>
       <c r="E202" s="8">
-        <v>9580540310.56</v>
+        <v>9564542554</v>
       </c>
       <c r="F202" s="9">
-        <v>9398</v>
+        <v>9376</v>
       </c>
       <c r="G202" s="8">
-        <v>1453977993.2</v>
+        <v>1468340630.76</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7448,19 +7448,19 @@
         <v>406</v>
       </c>
       <c r="C203" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D203" s="10">
-        <v>0.01455</v>
+        <v>46149</v>
+      </c>
+      <c r="D203" s="7">
+        <v>0.014728</v>
       </c>
       <c r="E203" s="8">
-        <v>9151972292.73</v>
+        <v>8841692998.14</v>
       </c>
       <c r="F203" s="9">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="G203" s="8">
-        <v>133161304.99</v>
+        <v>130220732.6</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7471,19 +7471,19 @@
         <v>408</v>
       </c>
       <c r="C204" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D204" s="7">
-        <v>0.028016</v>
+        <v>0.028654</v>
       </c>
       <c r="E204" s="8">
-        <v>1319755610.2</v>
+        <v>1333213673.34</v>
       </c>
       <c r="F204" s="9">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="G204" s="8">
-        <v>36974449.2</v>
+        <v>38201719.59</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7494,19 +7494,19 @@
         <v>410</v>
       </c>
       <c r="C205" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D205" s="7">
-        <v>0.119528</v>
+        <v>46149</v>
+      </c>
+      <c r="D205" s="10">
+        <v>0.12046</v>
       </c>
       <c r="E205" s="8">
-        <v>3214637637.32</v>
+        <v>3212156838.31</v>
       </c>
       <c r="F205" s="9">
-        <v>311923</v>
+        <v>311777</v>
       </c>
       <c r="G205" s="8">
-        <v>384239961.9</v>
+        <v>386937161.61</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -7517,19 +7517,19 @@
         <v>412</v>
       </c>
       <c r="C206" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D206" s="7">
-        <v>0.157268</v>
+        <v>0.158446</v>
       </c>
       <c r="E206" s="8">
-        <v>492839951.31</v>
+        <v>525690686.51</v>
       </c>
       <c r="F206" s="9">
-        <v>967</v>
+        <v>985</v>
       </c>
       <c r="G206" s="8">
-        <v>77507929</v>
+        <v>83293461.86</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7540,19 +7540,19 @@
         <v>414</v>
       </c>
       <c r="C207" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D207" s="7">
-        <v>0.132924</v>
+        <v>0.133979</v>
       </c>
       <c r="E207" s="8">
-        <v>2874175883.71</v>
+        <v>2879037208.78</v>
       </c>
       <c r="F207" s="9">
-        <v>5772</v>
+        <v>5777</v>
       </c>
       <c r="G207" s="8">
-        <v>382046730.9</v>
+        <v>385730565.98</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7563,19 +7563,19 @@
         <v>416</v>
       </c>
       <c r="C208" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D208" s="7">
-        <v>0.105221</v>
+        <v>0.105695</v>
       </c>
       <c r="E208" s="8">
-        <v>4328731384.79</v>
+        <v>4322073196.21</v>
       </c>
       <c r="F208" s="9">
-        <v>348166</v>
+        <v>348043</v>
       </c>
       <c r="G208" s="8">
-        <v>455475411.78</v>
+        <v>456822093.41</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7586,19 +7586,19 @@
         <v>418</v>
       </c>
       <c r="C209" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D209" s="7">
-        <v>0.106649</v>
+        <v>0.107175</v>
       </c>
       <c r="E209" s="8">
-        <v>46467425192.82</v>
+        <v>46584181917.18</v>
       </c>
       <c r="F209" s="9">
-        <v>711879</v>
+        <v>712946</v>
       </c>
       <c r="G209" s="8">
-        <v>4955709291.08</v>
+        <v>4992656980.25</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7609,19 +7609,19 @@
         <v>420</v>
       </c>
       <c r="C210" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D210" s="7">
-        <v>0.065308</v>
+        <v>0.066308</v>
       </c>
       <c r="E210" s="8">
-        <v>58690887529.75</v>
+        <v>59567611813.45</v>
       </c>
       <c r="F210" s="9">
-        <v>60540</v>
+        <v>60932</v>
       </c>
       <c r="G210" s="8">
-        <v>3833005800.77</v>
+        <v>3949807326.85</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -7632,19 +7632,19 @@
         <v>422</v>
       </c>
       <c r="C211" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D211" s="7">
-        <v>0.106246</v>
+        <v>0.107465</v>
       </c>
       <c r="E211" s="8">
-        <v>64887259664.03</v>
+        <v>65102116711.92</v>
       </c>
       <c r="F211" s="9">
-        <v>913878</v>
+        <v>914990</v>
       </c>
       <c r="G211" s="8">
-        <v>6894023190.06</v>
+        <v>6996191010.94</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7655,19 +7655,19 @@
         <v>424</v>
       </c>
       <c r="C212" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D212" s="7">
-        <v>0.069936</v>
+        <v>46149</v>
+      </c>
+      <c r="D212" s="10">
+        <v>0.07002</v>
       </c>
       <c r="E212" s="8">
-        <v>54512327539.17</v>
+        <v>54451457214.73</v>
       </c>
       <c r="F212" s="9">
-        <v>55491</v>
+        <v>55475</v>
       </c>
       <c r="G212" s="8">
-        <v>3812389774.67</v>
+        <v>3812682895.51</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7678,19 +7678,19 @@
         <v>426</v>
       </c>
       <c r="C213" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D213" s="7">
-        <v>0.097433</v>
+        <v>46149</v>
+      </c>
+      <c r="D213" s="10">
+        <v>0.09759</v>
       </c>
       <c r="E213" s="8">
-        <v>16684609670.79</v>
+        <v>16681723463.59</v>
       </c>
       <c r="F213" s="9">
-        <v>352317</v>
+        <v>355773</v>
       </c>
       <c r="G213" s="8">
-        <v>1625628674.79</v>
+        <v>1627964968.55</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -7701,19 +7701,19 @@
         <v>428</v>
       </c>
       <c r="C214" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D214" s="7">
-        <v>0.050705</v>
+        <v>0.052023</v>
       </c>
       <c r="E214" s="8">
-        <v>82599454430.93</v>
+        <v>82401478640.36</v>
       </c>
       <c r="F214" s="9">
-        <v>34676</v>
+        <v>34583</v>
       </c>
       <c r="G214" s="8">
-        <v>4188218347.93</v>
+        <v>4286813263.55</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7724,19 +7724,19 @@
         <v>430</v>
       </c>
       <c r="C215" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D215" s="7">
-        <v>0.086013</v>
+        <v>0.086134</v>
       </c>
       <c r="E215" s="8">
-        <v>14016993353.42</v>
+        <v>14077629084.75</v>
       </c>
       <c r="F215" s="9">
-        <v>236496</v>
+        <v>239866</v>
       </c>
       <c r="G215" s="8">
-        <v>1205649010.16</v>
+        <v>1212567327.2</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -7747,19 +7747,19 @@
         <v>432</v>
       </c>
       <c r="C216" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D216" s="7">
-        <v>0.319548</v>
+        <v>0.323301</v>
       </c>
       <c r="E216" s="8">
-        <v>12238797885.26</v>
+        <v>12278510439.75</v>
       </c>
       <c r="F216" s="9">
-        <v>58037</v>
+        <v>58168</v>
       </c>
       <c r="G216" s="8">
-        <v>3910878318.8</v>
+        <v>3969659353.13</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -7770,19 +7770,19 @@
         <v>434</v>
       </c>
       <c r="C217" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D217" s="7">
-        <v>0.221433</v>
+        <v>0.228574</v>
       </c>
       <c r="E217" s="8">
-        <v>10468444482.85</v>
+        <v>10516647808.31</v>
       </c>
       <c r="F217" s="9">
-        <v>39769</v>
+        <v>39874</v>
       </c>
       <c r="G217" s="8">
-        <v>2318054922.8</v>
+        <v>2403827424.51</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7793,19 +7793,19 @@
         <v>436</v>
       </c>
       <c r="C218" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D218" s="7">
-        <v>1.011393</v>
+        <v>1.032568</v>
       </c>
       <c r="E218" s="8">
-        <v>744010832.05</v>
+        <v>744900010.76</v>
       </c>
       <c r="F218" s="9">
-        <v>4359</v>
+        <v>4355</v>
       </c>
       <c r="G218" s="8">
-        <v>752487446.04</v>
+        <v>769159707.67</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -7816,19 +7816,19 @@
         <v>438</v>
       </c>
       <c r="C219" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D219" s="7">
-        <v>0.719522</v>
+        <v>0.743126</v>
       </c>
       <c r="E219" s="8">
-        <v>5948997287.64</v>
+        <v>5942613020.42</v>
       </c>
       <c r="F219" s="9">
-        <v>11100</v>
+        <v>11085</v>
       </c>
       <c r="G219" s="8">
-        <v>4280433585.53</v>
+        <v>4416107656.75</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -7839,19 +7839,19 @@
         <v>440</v>
       </c>
       <c r="C220" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D220" s="7">
-        <v>2.828788</v>
+        <v>2.922205</v>
       </c>
       <c r="E220" s="8">
-        <v>6246386941.19</v>
+        <v>6243934754.81</v>
       </c>
       <c r="F220" s="9">
-        <v>273193</v>
+        <v>273111</v>
       </c>
       <c r="G220" s="8">
-        <v>17669702753.48</v>
+        <v>18246056606.72</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -7862,19 +7862,19 @@
         <v>442</v>
       </c>
       <c r="C221" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D221" s="11">
-        <v>0.4044</v>
+        <v>46149</v>
+      </c>
+      <c r="D221" s="7">
+        <v>0.407764</v>
       </c>
       <c r="E221" s="8">
-        <v>9351997876.91</v>
+        <v>9345801414.39</v>
       </c>
       <c r="F221" s="9">
-        <v>165245</v>
+        <v>165092</v>
       </c>
       <c r="G221" s="8">
-        <v>3781949329.05</v>
+        <v>3810878333.19</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -7885,19 +7885,19 @@
         <v>444</v>
       </c>
       <c r="C222" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D222" s="7">
-        <v>0.395723</v>
+        <v>0.396451</v>
       </c>
       <c r="E222" s="8">
-        <v>177777178206.29</v>
+        <v>178410279765.12</v>
       </c>
       <c r="F222" s="9">
-        <v>385020</v>
+        <v>393977</v>
       </c>
       <c r="G222" s="8">
-        <v>70350523977.71</v>
+        <v>70730997487.36</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -7908,19 +7908,19 @@
         <v>446</v>
       </c>
       <c r="C223" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D223" s="7">
-        <v>0.154494</v>
+        <v>0.155304</v>
       </c>
       <c r="E223" s="8">
-        <v>6438873327.09</v>
+        <v>6423078703.83</v>
       </c>
       <c r="F223" s="9">
-        <v>25300</v>
+        <v>25308</v>
       </c>
       <c r="G223" s="8">
-        <v>994764242.85</v>
+        <v>997530116.88</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -7931,19 +7931,19 @@
         <v>448</v>
       </c>
       <c r="C224" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D224" s="7">
-        <v>0.521191</v>
+        <v>0.521746</v>
       </c>
       <c r="E224" s="8">
-        <v>8111047939.7</v>
+        <v>8115563695.93</v>
       </c>
       <c r="F224" s="9">
-        <v>35711</v>
+        <v>35682</v>
       </c>
       <c r="G224" s="8">
-        <v>4227407357.19</v>
+        <v>4234266866.51</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -7954,19 +7954,19 @@
         <v>450</v>
       </c>
       <c r="C225" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D225" s="7">
-        <v>0.073562</v>
+        <v>46149</v>
+      </c>
+      <c r="D225" s="10">
+        <v>0.07549</v>
       </c>
       <c r="E225" s="8">
-        <v>2510651769490.34</v>
+        <v>2508767269157.75</v>
       </c>
       <c r="F225" s="9">
-        <v>1246600</v>
+        <v>1246445</v>
       </c>
       <c r="G225" s="8">
-        <v>184687883265.22</v>
+        <v>189386861948.34</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -7977,19 +7977,19 @@
         <v>452</v>
       </c>
       <c r="C226" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D226" s="7">
-        <v>0.073641</v>
+        <v>0.075428</v>
       </c>
       <c r="E226" s="8">
-        <v>26733061119.96</v>
+        <v>26772877737.59</v>
       </c>
       <c r="F226" s="9">
-        <v>95305</v>
+        <v>95246</v>
       </c>
       <c r="G226" s="8">
-        <v>1968648368.61</v>
+        <v>2019412053.4</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -8000,19 +8000,19 @@
         <v>454</v>
       </c>
       <c r="C227" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D227" s="7">
-        <v>0.015217</v>
+        <v>0.015674</v>
       </c>
       <c r="E227" s="8">
-        <v>515914860027.48</v>
+        <v>516535408120.48</v>
       </c>
       <c r="F227" s="9">
-        <v>50718</v>
+        <v>50712</v>
       </c>
       <c r="G227" s="8">
-        <v>7850825965.34</v>
+        <v>8096427388.66</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8023,19 +8023,19 @@
         <v>456</v>
       </c>
       <c r="C228" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D228" s="7">
-        <v>0.778292</v>
+        <v>0.797026</v>
       </c>
       <c r="E228" s="8">
-        <v>170582603444.45</v>
+        <v>170496040204.36</v>
       </c>
       <c r="F228" s="9">
-        <v>824446</v>
+        <v>824633</v>
       </c>
       <c r="G228" s="8">
-        <v>132763112254.8</v>
+        <v>135889756664.64</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8046,19 +8046,19 @@
         <v>458</v>
       </c>
       <c r="C229" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D229" s="7">
-        <v>0.138281</v>
+        <v>0.140383</v>
       </c>
       <c r="E229" s="8">
-        <v>26959173955.19</v>
+        <v>26932191052.58</v>
       </c>
       <c r="F229" s="9">
-        <v>194808</v>
+        <v>194686</v>
       </c>
       <c r="G229" s="8">
-        <v>3727936428.73</v>
+        <v>3780818039.97</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8069,19 +8069,19 @@
         <v>460</v>
       </c>
       <c r="C230" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D230" s="7">
-        <v>1.108987</v>
+        <v>1.132637</v>
       </c>
       <c r="E230" s="8">
-        <v>2637469490.79</v>
+        <v>2630230561.67</v>
       </c>
       <c r="F230" s="9">
-        <v>49172</v>
+        <v>49117</v>
       </c>
       <c r="G230" s="8">
-        <v>2924919060.71</v>
+        <v>2979097533.45</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8092,19 +8092,19 @@
         <v>462</v>
       </c>
       <c r="C231" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D231" s="7">
-        <v>0.281224</v>
+        <v>0.283651</v>
       </c>
       <c r="E231" s="8">
-        <v>2506885930.25</v>
+        <v>2497539748.36</v>
       </c>
       <c r="F231" s="9">
-        <v>11254</v>
+        <v>11234</v>
       </c>
       <c r="G231" s="8">
-        <v>704996173.42</v>
+        <v>708430422.1</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8115,19 +8115,19 @@
         <v>464</v>
       </c>
       <c r="C232" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D232" s="7">
-        <v>1.126147</v>
+        <v>1.136039</v>
       </c>
       <c r="E232" s="8">
-        <v>5218122142.31</v>
+        <v>5219221658.95</v>
       </c>
       <c r="F232" s="9">
-        <v>63599</v>
+        <v>63528</v>
       </c>
       <c r="G232" s="8">
-        <v>5876373195.4</v>
+        <v>5929237819.34</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8138,19 +8138,19 @@
         <v>466</v>
       </c>
       <c r="C233" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D233" s="7">
-        <v>0.379183</v>
+        <v>0.387433</v>
       </c>
       <c r="E233" s="8">
-        <v>18872855308.92</v>
+        <v>18900609652.22</v>
       </c>
       <c r="F233" s="9">
-        <v>150952</v>
+        <v>151249</v>
       </c>
       <c r="G233" s="8">
-        <v>7156268709.93</v>
+        <v>7322727495.08</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8161,19 +8161,19 @@
         <v>468</v>
       </c>
       <c r="C234" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D234" s="7">
-        <v>0.107468</v>
+        <v>0.109666</v>
       </c>
       <c r="E234" s="8">
-        <v>281976971850.5</v>
+        <v>281834531667.72</v>
       </c>
       <c r="F234" s="9">
-        <v>1530193</v>
+        <v>1528947</v>
       </c>
       <c r="G234" s="8">
-        <v>30303360723.08</v>
+        <v>30907665077.37</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8184,19 +8184,19 @@
         <v>470</v>
       </c>
       <c r="C235" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D235" s="11">
-        <v>0.2642</v>
+        <v>46149</v>
+      </c>
+      <c r="D235" s="7">
+        <v>0.271022</v>
       </c>
       <c r="E235" s="8">
-        <v>3272386028.52</v>
+        <v>3288037594.32</v>
       </c>
       <c r="F235" s="9">
-        <v>10519</v>
+        <v>10547</v>
       </c>
       <c r="G235" s="8">
-        <v>864563804.25</v>
+        <v>891131165.43</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8207,19 +8207,19 @@
         <v>472</v>
       </c>
       <c r="C236" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D236" s="7">
-        <v>0.787395</v>
+        <v>0.794292</v>
       </c>
       <c r="E236" s="8">
-        <v>1344244683.64</v>
+        <v>1340017828.88</v>
       </c>
       <c r="F236" s="9">
-        <v>7627</v>
+        <v>7629</v>
       </c>
       <c r="G236" s="8">
-        <v>1058451562.52</v>
+        <v>1064365322.56</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8230,19 +8230,19 @@
         <v>474</v>
       </c>
       <c r="C237" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D237" s="7">
-        <v>0.154515</v>
+        <v>0.155265</v>
       </c>
       <c r="E237" s="8">
-        <v>72079266988.48</v>
+        <v>72046067031.07</v>
       </c>
       <c r="F237" s="9">
-        <v>842492</v>
+        <v>841553</v>
       </c>
       <c r="G237" s="8">
-        <v>11137325412.87</v>
+        <v>11186223232.04</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -8253,19 +8253,19 @@
         <v>476</v>
       </c>
       <c r="C238" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D238" s="7">
-        <v>0.223167</v>
+        <v>0.227602</v>
       </c>
       <c r="E238" s="8">
-        <v>2439702219.91</v>
+        <v>2451882239.22</v>
       </c>
       <c r="F238" s="9">
-        <v>7583</v>
+        <v>7595</v>
       </c>
       <c r="G238" s="8">
-        <v>544462011.8</v>
+        <v>558054524.66</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -8276,19 +8276,19 @@
         <v>478</v>
       </c>
       <c r="C239" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D239" s="7">
-        <v>0.196578</v>
+        <v>0.200523</v>
       </c>
       <c r="E239" s="8">
-        <v>2336607416.34</v>
+        <v>2343249191.72</v>
       </c>
       <c r="F239" s="9">
-        <v>7369</v>
+        <v>7377</v>
       </c>
       <c r="G239" s="8">
-        <v>459326215.3</v>
+        <v>469875047.22</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,19 +8299,19 @@
         <v>480</v>
       </c>
       <c r="C240" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D240" s="7">
-        <v>0.344701</v>
+        <v>0.349343</v>
       </c>
       <c r="E240" s="8">
-        <v>31352074524.59</v>
+        <v>31374160355.56</v>
       </c>
       <c r="F240" s="9">
-        <v>120305</v>
+        <v>120407</v>
       </c>
       <c r="G240" s="8">
-        <v>10807082254.78</v>
+        <v>10960336404</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -8322,19 +8322,19 @@
         <v>482</v>
       </c>
       <c r="C241" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D241" s="7">
-        <v>0.126579</v>
+        <v>0.127294</v>
       </c>
       <c r="E241" s="8">
-        <v>3786172159.94</v>
+        <v>3797026685.1</v>
       </c>
       <c r="F241" s="9">
-        <v>7414</v>
+        <v>7399</v>
       </c>
       <c r="G241" s="8">
-        <v>479250272.6</v>
+        <v>483340513.44</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -8345,19 +8345,19 @@
         <v>484</v>
       </c>
       <c r="C242" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D242" s="7">
-        <v>0.127613</v>
+        <v>0.129679</v>
       </c>
       <c r="E242" s="8">
-        <v>89270952086.14</v>
+        <v>89192062901.37</v>
       </c>
       <c r="F242" s="9">
-        <v>403282</v>
+        <v>402992</v>
       </c>
       <c r="G242" s="8">
-        <v>11392175514.24</v>
+        <v>11566295340.84</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8368,19 +8368,19 @@
         <v>486</v>
       </c>
       <c r="C243" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D243" s="7">
-        <v>0.311994</v>
+        <v>0.315916</v>
       </c>
       <c r="E243" s="8">
-        <v>3892351555.92</v>
+        <v>3915871947</v>
       </c>
       <c r="F243" s="9">
-        <v>18207</v>
+        <v>18298</v>
       </c>
       <c r="G243" s="8">
-        <v>1214391910.12</v>
+        <v>1237088064.62</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -8391,19 +8391,19 @@
         <v>488</v>
       </c>
       <c r="C244" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D244" s="10">
-        <v>0.08156</v>
+        <v>46149</v>
+      </c>
+      <c r="D244" s="7">
+        <v>0.081661</v>
       </c>
       <c r="E244" s="8">
-        <v>3837592085.83</v>
+        <v>3841385939.96</v>
       </c>
       <c r="F244" s="9">
-        <v>9187</v>
+        <v>9184</v>
       </c>
       <c r="G244" s="8">
-        <v>312993632.32</v>
+        <v>313690079.28</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8414,19 +8414,19 @@
         <v>490</v>
       </c>
       <c r="C245" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D245" s="7">
-        <v>0.249754</v>
+        <v>0.252278</v>
       </c>
       <c r="E245" s="8">
-        <v>2845428160.45</v>
+        <v>2858453228.07</v>
       </c>
       <c r="F245" s="9">
-        <v>14093</v>
+        <v>14145</v>
       </c>
       <c r="G245" s="8">
-        <v>710658139.13</v>
+        <v>721125750.85</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -8437,19 +8437,19 @@
         <v>492</v>
       </c>
       <c r="C246" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D246" s="7">
-        <v>0.069169</v>
+        <v>0.069253</v>
       </c>
       <c r="E246" s="8">
-        <v>4028896720.67</v>
+        <v>4029451050.58</v>
       </c>
       <c r="F246" s="9">
-        <v>7769</v>
+        <v>7754</v>
       </c>
       <c r="G246" s="8">
-        <v>278673265.21</v>
+        <v>279052810.56</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8460,19 +8460,19 @@
         <v>494</v>
       </c>
       <c r="C247" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D247" s="7">
-        <v>0.179447</v>
+        <v>0.179595</v>
       </c>
       <c r="E247" s="8">
-        <v>14401000576.07</v>
+        <v>14478659867.64</v>
       </c>
       <c r="F247" s="9">
-        <v>48830</v>
+        <v>48880</v>
       </c>
       <c r="G247" s="8">
-        <v>2584220895.92</v>
+        <v>2600288998.61</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8483,19 +8483,19 @@
         <v>496</v>
       </c>
       <c r="C248" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D248" s="11">
-        <v>0.0242</v>
+        <v>46149</v>
+      </c>
+      <c r="D248" s="7">
+        <v>0.025065</v>
       </c>
       <c r="E248" s="8">
-        <v>955938729872.57</v>
+        <v>954184865198.59</v>
       </c>
       <c r="F248" s="9">
-        <v>186749</v>
+        <v>186707</v>
       </c>
       <c r="G248" s="8">
-        <v>23133572184.54</v>
+        <v>23916589312.28</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8506,19 +8506,19 @@
         <v>498</v>
       </c>
       <c r="C249" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D249" s="7">
-        <v>0.735635</v>
+        <v>0.751575</v>
       </c>
       <c r="E249" s="8">
-        <v>15363782925.04</v>
+        <v>15370922230.4</v>
       </c>
       <c r="F249" s="9">
-        <v>79555</v>
+        <v>79618</v>
       </c>
       <c r="G249" s="8">
-        <v>11302140757.66</v>
+        <v>11552404104.41</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8529,19 +8529,19 @@
         <v>500</v>
       </c>
       <c r="C250" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D250" s="7">
-        <v>0.637807</v>
+        <v>0.653256</v>
       </c>
       <c r="E250" s="8">
-        <v>8207924031.58</v>
+        <v>8201462272.01</v>
       </c>
       <c r="F250" s="9">
-        <v>75455</v>
+        <v>75508</v>
       </c>
       <c r="G250" s="8">
-        <v>5235070848.89</v>
+        <v>5357651887.65</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8552,19 +8552,19 @@
         <v>502</v>
       </c>
       <c r="C251" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D251" s="7">
-        <v>0.161128</v>
+        <v>0.163244</v>
       </c>
       <c r="E251" s="8">
-        <v>2783390623.27</v>
+        <v>2789790910.73</v>
       </c>
       <c r="F251" s="9">
-        <v>11354</v>
+        <v>11367</v>
       </c>
       <c r="G251" s="8">
-        <v>448482231.86</v>
+        <v>455416257.72</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8575,19 +8575,19 @@
         <v>504</v>
       </c>
       <c r="C252" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D252" s="7">
-        <v>0.096121</v>
+        <v>0.097359</v>
       </c>
       <c r="E252" s="8">
-        <v>4873790814.18</v>
+        <v>4879180743.23</v>
       </c>
       <c r="F252" s="9">
-        <v>69543</v>
+        <v>69521</v>
       </c>
       <c r="G252" s="8">
-        <v>468472791.11</v>
+        <v>475031129.65</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8598,19 +8598,19 @@
         <v>506</v>
       </c>
       <c r="C253" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D253" s="7">
-        <v>0.329276</v>
+        <v>0.332055</v>
       </c>
       <c r="E253" s="8">
-        <v>2196197810.6</v>
+        <v>2183740606.26</v>
       </c>
       <c r="F253" s="9">
-        <v>21120</v>
+        <v>21123</v>
       </c>
       <c r="G253" s="8">
-        <v>723154144.1</v>
+        <v>725121330.33</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8621,19 +8621,19 @@
         <v>508</v>
       </c>
       <c r="C254" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D254" s="7">
-        <v>0.141675</v>
+        <v>0.142375</v>
       </c>
       <c r="E254" s="8">
-        <v>661586544.65</v>
+        <v>661930935.61</v>
       </c>
       <c r="F254" s="9">
-        <v>2395</v>
+        <v>2401</v>
       </c>
       <c r="G254" s="8">
-        <v>93730179.45</v>
+        <v>94242401.6</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8644,19 +8644,19 @@
         <v>510</v>
       </c>
       <c r="C255" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D255" s="7">
-        <v>0.083032</v>
+        <v>0.083169</v>
       </c>
       <c r="E255" s="8">
-        <v>631970853.95</v>
+        <v>644686800.81</v>
       </c>
       <c r="F255" s="9">
-        <v>13858</v>
+        <v>14185</v>
       </c>
       <c r="G255" s="8">
-        <v>52473993.78</v>
+        <v>53617899.68</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8667,19 +8667,19 @@
         <v>512</v>
       </c>
       <c r="C256" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D256" s="7">
-        <v>0.096898</v>
+        <v>0.097469</v>
       </c>
       <c r="E256" s="8">
-        <v>4027744122.05</v>
+        <v>4024656230.21</v>
       </c>
       <c r="F256" s="9">
-        <v>78597</v>
+        <v>78569</v>
       </c>
       <c r="G256" s="8">
-        <v>390281448.87</v>
+        <v>392279566.13</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8690,19 +8690,19 @@
         <v>514</v>
       </c>
       <c r="C257" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D257" s="7">
-        <v>0.127346</v>
+        <v>0.129106</v>
       </c>
       <c r="E257" s="8">
-        <v>3766272379.7</v>
+        <v>3766357014.04</v>
       </c>
       <c r="F257" s="9">
-        <v>19669</v>
+        <v>19674</v>
       </c>
       <c r="G257" s="8">
-        <v>479619396.85</v>
+        <v>486258360.8</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -8713,19 +8713,19 @@
         <v>516</v>
       </c>
       <c r="C258" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D258" s="7">
-        <v>0.093831</v>
+        <v>0.094009</v>
       </c>
       <c r="E258" s="8">
-        <v>580231325.28</v>
+        <v>584136670.33</v>
       </c>
       <c r="F258" s="9">
-        <v>10892</v>
+        <v>10848</v>
       </c>
       <c r="G258" s="8">
-        <v>54443622.28</v>
+        <v>54914063.82</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -8736,19 +8736,19 @@
         <v>518</v>
       </c>
       <c r="C259" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D259" s="7">
-        <v>0.132773</v>
+        <v>0.132998</v>
       </c>
       <c r="E259" s="8">
-        <v>4482558126.45</v>
+        <v>4457574174.46</v>
       </c>
       <c r="F259" s="9">
-        <v>18213</v>
+        <v>18215</v>
       </c>
       <c r="G259" s="8">
-        <v>595163416.9</v>
+        <v>592847714.88</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -8759,19 +8759,19 @@
         <v>520</v>
       </c>
       <c r="C260" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D260" s="7">
-        <v>0.155188</v>
+        <v>0.156021</v>
       </c>
       <c r="E260" s="8">
-        <v>1217264303.63</v>
+        <v>1216613334.63</v>
       </c>
       <c r="F260" s="9">
-        <v>59043</v>
+        <v>59029</v>
       </c>
       <c r="G260" s="8">
-        <v>188904631.54</v>
+        <v>189816894.01</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -8782,19 +8782,19 @@
         <v>522</v>
       </c>
       <c r="C261" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D261" s="7">
-        <v>0.768047</v>
+        <v>0.791225</v>
       </c>
       <c r="E261" s="8">
-        <v>8890122107.2</v>
+        <v>8886512509.31</v>
       </c>
       <c r="F261" s="9">
-        <v>26137</v>
+        <v>26144</v>
       </c>
       <c r="G261" s="8">
-        <v>6828033980.53</v>
+        <v>7031233831</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -8805,19 +8805,19 @@
         <v>524</v>
       </c>
       <c r="C262" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D262" s="7">
-        <v>0.101748</v>
+        <v>0.104097</v>
       </c>
       <c r="E262" s="8">
-        <v>14018541093.66</v>
+        <v>14006378805.17</v>
       </c>
       <c r="F262" s="9">
-        <v>128276</v>
+        <v>128242</v>
       </c>
       <c r="G262" s="8">
-        <v>1426352847.13</v>
+        <v>1458022916.87</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -8828,19 +8828,19 @@
         <v>526</v>
       </c>
       <c r="C263" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D263" s="10">
-        <v>0.01329</v>
+        <v>0.01352</v>
       </c>
       <c r="E263" s="8">
-        <v>146341709534.14</v>
+        <v>147321018578.04</v>
       </c>
       <c r="F263" s="9">
-        <v>1655</v>
+        <v>1673</v>
       </c>
       <c r="G263" s="8">
-        <v>1944855906.98</v>
+        <v>1991797372.97</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -8851,19 +8851,19 @@
         <v>528</v>
       </c>
       <c r="C264" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D264" s="7">
-        <v>0.286221</v>
+        <v>0.293008</v>
       </c>
       <c r="E264" s="8">
-        <v>5709830867</v>
+        <v>5717498104.73</v>
       </c>
       <c r="F264" s="9">
-        <v>43965</v>
+        <v>43929</v>
       </c>
       <c r="G264" s="8">
-        <v>1634275219.85</v>
+        <v>1675273632.8</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -8874,19 +8874,19 @@
         <v>530</v>
       </c>
       <c r="C265" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D265" s="7">
-        <v>0.413142</v>
+        <v>46149</v>
+      </c>
+      <c r="D265" s="10">
+        <v>0.41593</v>
       </c>
       <c r="E265" s="8">
-        <v>1955645201.56</v>
+        <v>1962976871.28</v>
       </c>
       <c r="F265" s="9">
-        <v>21794</v>
+        <v>21823</v>
       </c>
       <c r="G265" s="8">
-        <v>807959815.07</v>
+        <v>816460869.8</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -8897,19 +8897,19 @@
         <v>532</v>
       </c>
       <c r="C266" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D266" s="7">
-        <v>0.130667</v>
+        <v>0.132066</v>
       </c>
       <c r="E266" s="8">
-        <v>34220662985.72</v>
+        <v>34360758217.34</v>
       </c>
       <c r="F266" s="9">
-        <v>102641</v>
+        <v>102736</v>
       </c>
       <c r="G266" s="8">
-        <v>4471509982.28</v>
+        <v>4537895341.19</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -8920,19 +8920,19 @@
         <v>534</v>
       </c>
       <c r="C267" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D267" s="7">
-        <v>0.236554</v>
+        <v>0.238279</v>
       </c>
       <c r="E267" s="8">
-        <v>2681981591.49</v>
+        <v>2684511653.03</v>
       </c>
       <c r="F267" s="9">
-        <v>24246</v>
+        <v>24245</v>
       </c>
       <c r="G267" s="8">
-        <v>634432782.57</v>
+        <v>639663757.79</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -8943,19 +8943,19 @@
         <v>536</v>
       </c>
       <c r="C268" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D268" s="7">
-        <v>0.012779</v>
+        <v>0.013168</v>
       </c>
       <c r="E268" s="8">
-        <v>744985268532.7</v>
+        <v>747635904945.29</v>
       </c>
       <c r="F268" s="9">
-        <v>72308</v>
+        <v>72519</v>
       </c>
       <c r="G268" s="8">
-        <v>9520153928.9</v>
+        <v>9844852820.53</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -8966,19 +8966,19 @@
         <v>538</v>
       </c>
       <c r="C269" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D269" s="7">
-        <v>0.501284</v>
+        <v>0.504537</v>
       </c>
       <c r="E269" s="8">
-        <v>5711741305.87</v>
+        <v>5712975859.39</v>
       </c>
       <c r="F269" s="9">
-        <v>72312</v>
+        <v>72279</v>
       </c>
       <c r="G269" s="8">
-        <v>2863203169.72</v>
+        <v>2882406317.25</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -8989,19 +8989,19 @@
         <v>540</v>
       </c>
       <c r="C270" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D270" s="7">
-        <v>0.302371</v>
+        <v>0.305925</v>
       </c>
       <c r="E270" s="8">
-        <v>1834946484.28</v>
+        <v>1834520751.17</v>
       </c>
       <c r="F270" s="9">
-        <v>95658</v>
+        <v>95652</v>
       </c>
       <c r="G270" s="8">
-        <v>554833929.82</v>
+        <v>561224999.12</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9012,19 +9012,19 @@
         <v>542</v>
       </c>
       <c r="C271" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D271" s="7">
-        <v>0.782032</v>
+        <v>0.795788</v>
       </c>
       <c r="E271" s="8">
-        <v>2051560120.59</v>
+        <v>2051938272.5</v>
       </c>
       <c r="F271" s="9">
-        <v>111700</v>
+        <v>111696</v>
       </c>
       <c r="G271" s="8">
-        <v>1604385337.55</v>
+        <v>1632907579.57</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9035,19 +9035,19 @@
         <v>544</v>
       </c>
       <c r="C272" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D272" s="7">
-        <v>0.526631</v>
+        <v>0.539014</v>
       </c>
       <c r="E272" s="8">
-        <v>1501785307.26</v>
+        <v>1500876338.23</v>
       </c>
       <c r="F272" s="9">
-        <v>37702</v>
+        <v>37700</v>
       </c>
       <c r="G272" s="8">
-        <v>790887116.49</v>
+        <v>808993346.72</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9058,19 +9058,19 @@
         <v>546</v>
       </c>
       <c r="C273" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D273" s="7">
-        <v>0.284031</v>
+        <v>0.286365</v>
       </c>
       <c r="E273" s="8">
-        <v>2819561921.18</v>
+        <v>2817142435.85</v>
       </c>
       <c r="F273" s="9">
-        <v>87292</v>
+        <v>87282</v>
       </c>
       <c r="G273" s="8">
-        <v>800843522.12</v>
+        <v>806729751.73</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9081,19 +9081,19 @@
         <v>548</v>
       </c>
       <c r="C274" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D274" s="7">
-        <v>2.408187</v>
+        <v>2.484154</v>
       </c>
       <c r="E274" s="8">
-        <v>1903013261.78</v>
+        <v>1902400073.04</v>
       </c>
       <c r="F274" s="9">
-        <v>57654</v>
+        <v>57646</v>
       </c>
       <c r="G274" s="8">
-        <v>4582812697.38</v>
+        <v>4725855018.82</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9104,19 +9104,19 @@
         <v>550</v>
       </c>
       <c r="C275" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D275" s="7">
-        <v>0.909683</v>
+        <v>0.924064</v>
       </c>
       <c r="E275" s="8">
-        <v>769347744.97</v>
+        <v>769605053.17</v>
       </c>
       <c r="F275" s="9">
-        <v>83369</v>
+        <v>83367</v>
       </c>
       <c r="G275" s="8">
-        <v>699862270.97</v>
+        <v>711164165.72</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9127,19 +9127,19 @@
         <v>552</v>
       </c>
       <c r="C276" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D276" s="7">
-        <v>0.375685</v>
+        <v>46149</v>
+      </c>
+      <c r="D276" s="10">
+        <v>0.37636</v>
       </c>
       <c r="E276" s="8">
-        <v>8977578634.16</v>
+        <v>8956753925.62</v>
       </c>
       <c r="F276" s="9">
-        <v>101101</v>
+        <v>100010</v>
       </c>
       <c r="G276" s="8">
-        <v>3372744799.67</v>
+        <v>3370961141.34</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9150,19 +9150,19 @@
         <v>554</v>
       </c>
       <c r="C277" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D277" s="7">
-        <v>0.110047</v>
+        <v>0.112166</v>
       </c>
       <c r="E277" s="8">
-        <v>54729428092.14</v>
+        <v>54696328865.63</v>
       </c>
       <c r="F277" s="9">
-        <v>198558</v>
+        <v>198477</v>
       </c>
       <c r="G277" s="8">
-        <v>6022803674.63</v>
+        <v>6135054618.77</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9173,19 +9173,19 @@
         <v>556</v>
       </c>
       <c r="C278" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D278" s="7">
-        <v>0.115359</v>
+        <v>0.115871</v>
       </c>
       <c r="E278" s="8">
-        <v>83549155682.87</v>
+        <v>83469449353.94</v>
       </c>
       <c r="F278" s="9">
-        <v>1084740</v>
+        <v>1083989</v>
       </c>
       <c r="G278" s="8">
-        <v>9638145623</v>
+        <v>9671730099.65</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9196,19 +9196,19 @@
         <v>558</v>
       </c>
       <c r="C279" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D279" s="7">
-        <v>0.142902</v>
+        <v>46149</v>
+      </c>
+      <c r="D279" s="10">
+        <v>0.14376</v>
       </c>
       <c r="E279" s="8">
-        <v>33160837339.92</v>
+        <v>33222146674.6</v>
       </c>
       <c r="F279" s="9">
-        <v>328699</v>
+        <v>328763</v>
       </c>
       <c r="G279" s="8">
-        <v>4738745987.38</v>
+        <v>4775999738.58</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9219,19 +9219,19 @@
         <v>560</v>
       </c>
       <c r="C280" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D280" s="7">
-        <v>0.169943</v>
+        <v>0.172361</v>
       </c>
       <c r="E280" s="8">
-        <v>3158293249.39</v>
+        <v>3167041667.25</v>
       </c>
       <c r="F280" s="9">
-        <v>27435</v>
+        <v>27461</v>
       </c>
       <c r="G280" s="8">
-        <v>536730298.23</v>
+        <v>545874585.2</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -9242,19 +9242,19 @@
         <v>562</v>
       </c>
       <c r="C281" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D281" s="7">
-        <v>0.722502</v>
+        <v>0.739998</v>
       </c>
       <c r="E281" s="8">
-        <v>44344852517.71</v>
+        <v>44367588852.19</v>
       </c>
       <c r="F281" s="9">
-        <v>674921</v>
+        <v>675187</v>
       </c>
       <c r="G281" s="8">
-        <v>32039237034.26</v>
+        <v>32831913972.57</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -9265,19 +9265,19 @@
         <v>564</v>
       </c>
       <c r="C282" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D282" s="7">
-        <v>0.262739</v>
+        <v>0.265379</v>
       </c>
       <c r="E282" s="8">
-        <v>8740263137.27</v>
+        <v>8745439871.97</v>
       </c>
       <c r="F282" s="9">
-        <v>108548</v>
+        <v>108573</v>
       </c>
       <c r="G282" s="8">
-        <v>2296409901.1</v>
+        <v>2320857427.34</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -9288,19 +9288,19 @@
         <v>566</v>
       </c>
       <c r="C283" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D283" s="7">
-        <v>0.547835</v>
+        <v>0.556758</v>
       </c>
       <c r="E283" s="8">
-        <v>11724910688.71</v>
+        <v>11742747007</v>
       </c>
       <c r="F283" s="9">
-        <v>139145</v>
+        <v>139230</v>
       </c>
       <c r="G283" s="8">
-        <v>6423315721.12</v>
+        <v>6537873391.6</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -9311,19 +9311,19 @@
         <v>568</v>
       </c>
       <c r="C284" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D284" s="7">
-        <v>0.305708</v>
+        <v>0.311195</v>
       </c>
       <c r="E284" s="8">
-        <v>2302946726.77</v>
+        <v>2307187931.98</v>
       </c>
       <c r="F284" s="9">
         <v>37510</v>
       </c>
       <c r="G284" s="8">
-        <v>704028182.47</v>
+        <v>717984715.53</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -9334,19 +9334,19 @@
         <v>570</v>
       </c>
       <c r="C285" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D285" s="7">
-        <v>0.197377</v>
+        <v>0.197802</v>
       </c>
       <c r="E285" s="8">
-        <v>9524514510.8</v>
+        <v>9531849107.35</v>
       </c>
       <c r="F285" s="9">
-        <v>108160</v>
+        <v>108131</v>
       </c>
       <c r="G285" s="8">
-        <v>1879921453.97</v>
+        <v>1885422855.64</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -9357,19 +9357,19 @@
         <v>572</v>
       </c>
       <c r="C286" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D286" s="7">
-        <v>0.279545</v>
+        <v>46149</v>
+      </c>
+      <c r="D286" s="10">
+        <v>0.28196</v>
       </c>
       <c r="E286" s="8">
-        <v>799649630.47</v>
+        <v>801672609.43</v>
       </c>
       <c r="F286" s="9">
-        <v>2809</v>
+        <v>2815</v>
       </c>
       <c r="G286" s="8">
-        <v>223538328.19</v>
+        <v>226039588.79</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -9380,19 +9380,19 @@
         <v>574</v>
       </c>
       <c r="C287" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D287" s="7">
-        <v>0.087987</v>
+        <v>0.088078</v>
       </c>
       <c r="E287" s="8">
-        <v>4338787534.15</v>
+        <v>4340411095.59</v>
       </c>
       <c r="F287" s="9">
-        <v>147490</v>
+        <v>147394</v>
       </c>
       <c r="G287" s="8">
-        <v>381758968.44</v>
+        <v>382294732.17</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -9403,19 +9403,19 @@
         <v>576</v>
       </c>
       <c r="C288" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D288" s="7">
-        <v>0.487692</v>
+        <v>0.493814</v>
       </c>
       <c r="E288" s="8">
-        <v>1584813548.68</v>
+        <v>1584043462.48</v>
       </c>
       <c r="F288" s="9">
-        <v>4275</v>
+        <v>4272</v>
       </c>
       <c r="G288" s="8">
-        <v>772901077.83</v>
+        <v>782222164.19</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -9426,19 +9426,19 @@
         <v>578</v>
       </c>
       <c r="C289" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D289" s="7">
-        <v>0.015723</v>
+        <v>0.015863</v>
       </c>
       <c r="E289" s="8">
-        <v>5750124483.54</v>
+        <v>5934655217.61</v>
       </c>
       <c r="F289" s="9">
-        <v>3684</v>
+        <v>3707</v>
       </c>
       <c r="G289" s="8">
-        <v>90409143.5</v>
+        <v>94140492.21</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -9449,19 +9449,19 @@
         <v>580</v>
       </c>
       <c r="C290" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D290" s="7">
-        <v>0.017331</v>
+        <v>0.017394</v>
       </c>
       <c r="E290" s="8">
-        <v>153617180589.83</v>
+        <v>151825988221.85</v>
       </c>
       <c r="F290" s="9">
-        <v>31628</v>
+        <v>31609</v>
       </c>
       <c r="G290" s="8">
-        <v>2662374721.35</v>
+        <v>2640833859.72</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -9472,19 +9472,19 @@
         <v>582</v>
       </c>
       <c r="C291" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D291" s="7">
-        <v>0.010811</v>
+        <v>0.010973</v>
       </c>
       <c r="E291" s="8">
-        <v>8591713994.45</v>
+        <v>9477243703.05</v>
       </c>
       <c r="F291" s="9">
-        <v>1588</v>
+        <v>1730</v>
       </c>
       <c r="G291" s="8">
-        <v>92888479.83</v>
+        <v>103989706.7</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -9495,19 +9495,19 @@
         <v>584</v>
       </c>
       <c r="C292" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D292" s="7">
-        <v>0.132001</v>
+        <v>0.134574</v>
       </c>
       <c r="E292" s="8">
-        <v>52665872053.26</v>
+        <v>52512864529.58</v>
       </c>
       <c r="F292" s="9">
-        <v>107905</v>
+        <v>107935</v>
       </c>
       <c r="G292" s="8">
-        <v>6951946282.81</v>
+        <v>7066865920.07</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -9518,19 +9518,19 @@
         <v>586</v>
       </c>
       <c r="C293" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D293" s="7">
-        <v>0.051314</v>
+        <v>0.051366</v>
       </c>
       <c r="E293" s="8">
-        <v>12382078963.26</v>
+        <v>12530565628.49</v>
       </c>
       <c r="F293" s="9">
-        <v>28782</v>
+        <v>28952</v>
       </c>
       <c r="G293" s="8">
-        <v>635375119.55</v>
+        <v>643648405.94</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -9541,19 +9541,19 @@
         <v>588</v>
       </c>
       <c r="C294" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D294" s="7">
-        <v>0.022038</v>
+        <v>0.022064</v>
       </c>
       <c r="E294" s="8">
-        <v>57932067966.88</v>
+        <v>57785079686.39</v>
       </c>
       <c r="F294" s="9">
-        <v>10720</v>
+        <v>10721</v>
       </c>
       <c r="G294" s="8">
-        <v>1276707348.33</v>
+        <v>1274991610.74</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -9564,19 +9564,19 @@
         <v>590</v>
       </c>
       <c r="C295" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D295" s="7">
-        <v>0.032221</v>
+        <v>46149</v>
+      </c>
+      <c r="D295" s="10">
+        <v>0.03261</v>
       </c>
       <c r="E295" s="8">
-        <v>55650545277.4</v>
+        <v>55780798290.24</v>
       </c>
       <c r="F295" s="9">
-        <v>33455</v>
+        <v>33587</v>
       </c>
       <c r="G295" s="8">
-        <v>1793135205.32</v>
+        <v>1819005774.74</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -9587,19 +9587,19 @@
         <v>592</v>
       </c>
       <c r="C296" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D296" s="7">
-        <v>0.019198</v>
+        <v>0.019488</v>
       </c>
       <c r="E296" s="8">
-        <v>957802618873.89</v>
+        <v>955520302453.97</v>
       </c>
       <c r="F296" s="9">
-        <v>178911</v>
+        <v>178832</v>
       </c>
       <c r="G296" s="8">
-        <v>18388090672.17</v>
+        <v>18621096642.86</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -9610,19 +9610,19 @@
         <v>594</v>
       </c>
       <c r="C297" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D297" s="7">
-        <v>0.101268</v>
+        <v>0.102548</v>
       </c>
       <c r="E297" s="8">
-        <v>37184969090.64</v>
+        <v>37213608830.12</v>
       </c>
       <c r="F297" s="9">
-        <v>383207</v>
+        <v>382981</v>
       </c>
       <c r="G297" s="8">
-        <v>3765648406.59</v>
+        <v>3816191128.9</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -9633,19 +9633,19 @@
         <v>596</v>
       </c>
       <c r="C298" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D298" s="7">
-        <v>0.086358</v>
+        <v>0.087158</v>
       </c>
       <c r="E298" s="8">
-        <v>38355847275.55</v>
+        <v>38342123522.34</v>
       </c>
       <c r="F298" s="9">
-        <v>48135</v>
+        <v>48125</v>
       </c>
       <c r="G298" s="8">
-        <v>3312350131.3</v>
+        <v>3341835996.93</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -9656,19 +9656,19 @@
         <v>598</v>
       </c>
       <c r="C299" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D299" s="7">
-        <v>0.095264</v>
+        <v>0.095763</v>
       </c>
       <c r="E299" s="8">
-        <v>39047564040.98</v>
+        <v>39021126949.47</v>
       </c>
       <c r="F299" s="9">
-        <v>527317</v>
+        <v>526990</v>
       </c>
       <c r="G299" s="8">
-        <v>3719810952.96</v>
+        <v>3736765407.12</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -9679,19 +9679,19 @@
         <v>600</v>
       </c>
       <c r="C300" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D300" s="7">
-        <v>0.020402</v>
+        <v>46149</v>
+      </c>
+      <c r="D300" s="10">
+        <v>0.02061</v>
       </c>
       <c r="E300" s="8">
-        <v>36233649793.67</v>
+        <v>36681712854.4</v>
       </c>
       <c r="F300" s="9">
-        <v>25576</v>
+        <v>25806</v>
       </c>
       <c r="G300" s="8">
-        <v>739228429.81</v>
+        <v>756025320.12</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -9702,19 +9702,19 @@
         <v>602</v>
       </c>
       <c r="C301" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D301" s="7">
-        <v>0.010344</v>
+        <v>0.010352</v>
       </c>
       <c r="E301" s="8">
-        <v>3715059235.16</v>
+        <v>4315128685.97</v>
       </c>
       <c r="F301" s="9">
-        <v>896</v>
+        <v>966</v>
       </c>
       <c r="G301" s="8">
-        <v>38427139.27</v>
+        <v>44670210.28</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -9725,19 +9725,19 @@
         <v>604</v>
       </c>
       <c r="C302" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D302" s="7">
-        <v>0.016082</v>
+        <v>46149</v>
+      </c>
+      <c r="D302" s="10">
+        <v>0.01625</v>
       </c>
       <c r="E302" s="8">
-        <v>24233592711.55</v>
+        <v>24357587523.01</v>
       </c>
       <c r="F302" s="9">
-        <v>11057</v>
+        <v>11148</v>
       </c>
       <c r="G302" s="8">
-        <v>389733566.94</v>
+        <v>395811989.56</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -9748,19 +9748,19 @@
         <v>606</v>
       </c>
       <c r="C303" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D303" s="7">
-        <v>0.018289</v>
+        <v>0.018578</v>
       </c>
       <c r="E303" s="8">
-        <v>11964403955.86</v>
+        <v>12022580852.23</v>
       </c>
       <c r="F303" s="9">
-        <v>6653</v>
+        <v>6660</v>
       </c>
       <c r="G303" s="8">
-        <v>218815570.15</v>
+        <v>223361339.63</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -9771,19 +9771,19 @@
         <v>608</v>
       </c>
       <c r="C304" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D304" s="7">
-        <v>0.094712</v>
+        <v>0.095188</v>
       </c>
       <c r="E304" s="8">
-        <v>21400992497.27</v>
+        <v>21522586184.88</v>
       </c>
       <c r="F304" s="9">
-        <v>348734</v>
+        <v>348822</v>
       </c>
       <c r="G304" s="8">
-        <v>2026923677.71</v>
+        <v>2048689131.42</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -9794,19 +9794,19 @@
         <v>610</v>
       </c>
       <c r="C305" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D305" s="7">
-        <v>0.018918</v>
+        <v>0.019258</v>
       </c>
       <c r="E305" s="8">
-        <v>10494018544.53</v>
+        <v>10421502768.23</v>
       </c>
       <c r="F305" s="9">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G305" s="8">
-        <v>198525170.49</v>
+        <v>200695706.52</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -9817,19 +9817,19 @@
         <v>612</v>
       </c>
       <c r="C306" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D306" s="7">
-        <v>0.015597</v>
+        <v>0.015768</v>
       </c>
       <c r="E306" s="8">
-        <v>9196778107.66</v>
+        <v>9074126452.56</v>
       </c>
       <c r="F306" s="9">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G306" s="8">
-        <v>143437701.26</v>
+        <v>143082537.81</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -9840,19 +9840,19 @@
         <v>614</v>
       </c>
       <c r="C307" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D307" s="7">
-        <v>0.015913</v>
+        <v>0.015912</v>
       </c>
       <c r="E307" s="8">
-        <v>1265506481.22</v>
+        <v>1270990954.6</v>
       </c>
       <c r="F307" s="9">
         <v>23</v>
       </c>
       <c r="G307" s="8">
-        <v>20138613.98</v>
+        <v>20224341.78</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -9863,19 +9863,19 @@
         <v>616</v>
       </c>
       <c r="C308" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D308" s="7">
-        <v>0.227185</v>
+        <v>0.233088</v>
       </c>
       <c r="E308" s="8">
-        <v>48745809737.99</v>
+        <v>48774920667.94</v>
       </c>
       <c r="F308" s="9">
-        <v>175189</v>
+        <v>175267</v>
       </c>
       <c r="G308" s="8">
-        <v>11074326062.83</v>
+        <v>11368857446.27</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -9886,19 +9886,19 @@
         <v>618</v>
       </c>
       <c r="C309" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D309" s="7">
-        <v>0.011112</v>
+        <v>0.011198</v>
       </c>
       <c r="E309" s="8">
-        <v>2373814161.05</v>
+        <v>2685185858.69</v>
       </c>
       <c r="F309" s="9">
-        <v>2038</v>
+        <v>2058</v>
       </c>
       <c r="G309" s="8">
-        <v>26377939.47</v>
+        <v>30069920.65</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -9909,19 +9909,19 @@
         <v>620</v>
       </c>
       <c r="C310" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D310" s="7">
-        <v>0.030365</v>
+        <v>0.030779</v>
       </c>
       <c r="E310" s="8">
-        <v>12804009344.2</v>
+        <v>12873400842.74</v>
       </c>
       <c r="F310" s="9">
-        <v>17600</v>
+        <v>17641</v>
       </c>
       <c r="G310" s="8">
-        <v>388797271.56</v>
+        <v>396234369.38</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -9932,19 +9932,19 @@
         <v>622</v>
       </c>
       <c r="C311" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D311" s="7">
-        <v>0.024917</v>
+        <v>0.025442</v>
       </c>
       <c r="E311" s="8">
-        <v>3041305202.99</v>
+        <v>3003097209.93</v>
       </c>
       <c r="F311" s="9">
-        <v>10297</v>
+        <v>10300</v>
       </c>
       <c r="G311" s="8">
-        <v>75780228.02</v>
+        <v>76404557.04</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -9955,19 +9955,19 @@
         <v>624</v>
       </c>
       <c r="C312" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D312" s="7">
-        <v>0.124058</v>
+        <v>0.124842</v>
       </c>
       <c r="E312" s="8">
-        <v>618936204.09</v>
+        <v>618712824.74</v>
       </c>
       <c r="F312" s="9">
-        <v>94260</v>
+        <v>94219</v>
       </c>
       <c r="G312" s="8">
-        <v>76783884.84</v>
+        <v>77241313.04</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -9978,19 +9978,19 @@
         <v>626</v>
       </c>
       <c r="C313" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D313" s="7">
-        <v>0.091008</v>
+        <v>0.091167</v>
       </c>
       <c r="E313" s="8">
-        <v>1377461890.07</v>
+        <v>1370358342.01</v>
       </c>
       <c r="F313" s="9">
-        <v>29002</v>
+        <v>24952</v>
       </c>
       <c r="G313" s="8">
-        <v>125360004.94</v>
+        <v>124931295.04</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -10001,19 +10001,19 @@
         <v>628</v>
       </c>
       <c r="C314" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D314" s="7">
-        <v>0.080571</v>
+        <v>46149</v>
+      </c>
+      <c r="D314" s="10">
+        <v>0.08069</v>
       </c>
       <c r="E314" s="8">
-        <v>2467711310.35</v>
+        <v>2461656416.41</v>
       </c>
       <c r="F314" s="9">
-        <v>78430</v>
+        <v>77994</v>
       </c>
       <c r="G314" s="8">
-        <v>198825797.11</v>
+        <v>198631883.14</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -10024,19 +10024,19 @@
         <v>630</v>
       </c>
       <c r="C315" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D315" s="7">
-        <v>0.388492</v>
+        <v>0.389993</v>
       </c>
       <c r="E315" s="8">
-        <v>5219727986.14</v>
+        <v>5207844981.07</v>
       </c>
       <c r="F315" s="9">
-        <v>71848</v>
+        <v>71821</v>
       </c>
       <c r="G315" s="8">
-        <v>2027820549.15</v>
+        <v>2031022477.7</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -10047,19 +10047,19 @@
         <v>632</v>
       </c>
       <c r="C316" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D316" s="10">
-        <v>0.20514</v>
+        <v>46149</v>
+      </c>
+      <c r="D316" s="7">
+        <v>0.206589</v>
       </c>
       <c r="E316" s="8">
-        <v>5836293069.33</v>
+        <v>5827255485.79</v>
       </c>
       <c r="F316" s="9">
-        <v>56517</v>
+        <v>56507</v>
       </c>
       <c r="G316" s="8">
-        <v>1197254258.96</v>
+        <v>1203848285.74</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -10070,19 +10070,19 @@
         <v>634</v>
       </c>
       <c r="C317" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D317" s="10">
-        <v>0.11174</v>
+        <v>46149</v>
+      </c>
+      <c r="D317" s="7">
+        <v>0.112759</v>
       </c>
       <c r="E317" s="8">
-        <v>2329903458.07</v>
+        <v>2332878437</v>
       </c>
       <c r="F317" s="9">
         <v>8462</v>
       </c>
       <c r="G317" s="8">
-        <v>260343028.35</v>
+        <v>263052836.39</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -10093,19 +10093,19 @@
         <v>636</v>
       </c>
       <c r="C318" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D318" s="7">
-        <v>0.551094</v>
+        <v>0.568142</v>
       </c>
       <c r="E318" s="8">
-        <v>4012089835.87</v>
+        <v>4012592991.87</v>
       </c>
       <c r="F318" s="9">
-        <v>50534</v>
+        <v>50511</v>
       </c>
       <c r="G318" s="8">
-        <v>2211037541.34</v>
+        <v>2279724013.61</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -10116,19 +10116,19 @@
         <v>638</v>
       </c>
       <c r="C319" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D319" s="7">
-        <v>0.085576</v>
+        <v>0.085999</v>
       </c>
       <c r="E319" s="8">
-        <v>8915662982.92</v>
+        <v>9003817102.96</v>
       </c>
       <c r="F319" s="9">
-        <v>190320</v>
+        <v>190203</v>
       </c>
       <c r="G319" s="8">
-        <v>762968634.94</v>
+        <v>774317957.55</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -10139,19 +10139,19 @@
         <v>640</v>
       </c>
       <c r="C320" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D320" s="7">
-        <v>0.108332</v>
+        <v>0.109892</v>
       </c>
       <c r="E320" s="8">
-        <v>23129302460.53</v>
+        <v>23132873052.83</v>
       </c>
       <c r="F320" s="9">
-        <v>138141</v>
+        <v>138114</v>
       </c>
       <c r="G320" s="8">
-        <v>2505651125.64</v>
+        <v>2542108573.55</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -10162,19 +10162,19 @@
         <v>642</v>
       </c>
       <c r="C321" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D321" s="7">
-        <v>0.152035</v>
+        <v>0.152333</v>
       </c>
       <c r="E321" s="8">
-        <v>13091441538.09</v>
+        <v>13075173959.86</v>
       </c>
       <c r="F321" s="9">
-        <v>33578</v>
+        <v>32637</v>
       </c>
       <c r="G321" s="8">
-        <v>1990363120.58</v>
+        <v>1991782530.64</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -10185,19 +10185,19 @@
         <v>644</v>
       </c>
       <c r="C322" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D322" s="11">
-        <v>0.1334</v>
+        <v>46149</v>
+      </c>
+      <c r="D322" s="7">
+        <v>0.134015</v>
       </c>
       <c r="E322" s="8">
-        <v>529675080.63</v>
+        <v>530980024.26</v>
       </c>
       <c r="F322" s="9">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G322" s="8">
-        <v>70658882.65</v>
+        <v>71159424.94</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -10208,19 +10208,19 @@
         <v>646</v>
       </c>
       <c r="C323" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D323" s="7">
-        <v>0.137116</v>
+        <v>0.139577</v>
       </c>
       <c r="E323" s="8">
-        <v>226635218.68</v>
+        <v>227669970.36</v>
       </c>
       <c r="F323" s="9">
         <v>418</v>
       </c>
       <c r="G323" s="8">
-        <v>31075273.86</v>
+        <v>31777526.84</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -10231,19 +10231,19 @@
         <v>648</v>
       </c>
       <c r="C324" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D324" s="7">
-        <v>0.167498</v>
+        <v>0.171212</v>
       </c>
       <c r="E324" s="8">
-        <v>299917151.4</v>
+        <v>300569096.37</v>
       </c>
       <c r="F324" s="9">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G324" s="8">
-        <v>50235463.03</v>
+        <v>51461174.85</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -10254,19 +10254,19 @@
         <v>650</v>
       </c>
       <c r="C325" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D325" s="7">
-        <v>0.198781</v>
+        <v>0.204157</v>
       </c>
       <c r="E325" s="8">
-        <v>361027812.58</v>
+        <v>362041762.89</v>
       </c>
       <c r="F325" s="9">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G325" s="8">
-        <v>71765474.92</v>
+        <v>73913352.53</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -10277,19 +10277,19 @@
         <v>652</v>
       </c>
       <c r="C326" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D326" s="7">
-        <v>0.142788</v>
+        <v>0.143702</v>
       </c>
       <c r="E326" s="8">
-        <v>421247561.35</v>
+        <v>421116958.47</v>
       </c>
       <c r="F326" s="9">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="G326" s="8">
-        <v>60149114.06</v>
+        <v>60515232.15</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -10300,19 +10300,19 @@
         <v>654</v>
       </c>
       <c r="C327" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D327" s="7">
-        <v>0.097429</v>
+        <v>0.099539</v>
       </c>
       <c r="E327" s="8">
-        <v>40710184940.33</v>
+        <v>40694171355.6</v>
       </c>
       <c r="F327" s="9">
-        <v>374355</v>
+        <v>374243</v>
       </c>
       <c r="G327" s="8">
-        <v>3966372117.16</v>
+        <v>4050655341.06</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -10323,19 +10323,19 @@
         <v>656</v>
       </c>
       <c r="C328" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D328" s="10">
-        <v>0.17493</v>
+        <v>46149</v>
+      </c>
+      <c r="D328" s="7">
+        <v>0.177175</v>
       </c>
       <c r="E328" s="8">
-        <v>192864836.5</v>
+        <v>193791953.16</v>
       </c>
       <c r="F328" s="9">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G328" s="8">
-        <v>33737817.82</v>
+        <v>34335000.6</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -10346,19 +10346,19 @@
         <v>658</v>
       </c>
       <c r="C329" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D329" s="7">
-        <v>0.205452</v>
+        <v>0.208552</v>
       </c>
       <c r="E329" s="8">
-        <v>239996059.9</v>
+        <v>240689671.87</v>
       </c>
       <c r="F329" s="9">
         <v>496</v>
       </c>
       <c r="G329" s="8">
-        <v>49307702.2</v>
+        <v>50196279.56</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -10369,19 +10369,19 @@
         <v>660</v>
       </c>
       <c r="C330" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D330" s="7">
-        <v>0.291493</v>
+        <v>0.296713</v>
       </c>
       <c r="E330" s="8">
-        <v>1269373494.29</v>
+        <v>1271390224.04</v>
       </c>
       <c r="F330" s="9">
-        <v>8876</v>
+        <v>8879</v>
       </c>
       <c r="G330" s="8">
-        <v>370013593.19</v>
+        <v>377238197.6</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
@@ -10392,19 +10392,19 @@
         <v>662</v>
       </c>
       <c r="C331" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D331" s="7">
-        <v>0.091688</v>
+        <v>0.092812</v>
       </c>
       <c r="E331" s="8">
-        <v>6866593616.44</v>
+        <v>6875937323.47</v>
       </c>
       <c r="F331" s="9">
-        <v>123326</v>
+        <v>123299</v>
       </c>
       <c r="G331" s="8">
-        <v>629581126.01</v>
+        <v>638166463.57</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
@@ -10415,19 +10415,19 @@
         <v>664</v>
       </c>
       <c r="C332" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D332" s="7">
-        <v>0.074032</v>
+        <v>0.075127</v>
       </c>
       <c r="E332" s="8">
-        <v>103737972713.69</v>
+        <v>103852054455.64</v>
       </c>
       <c r="F332" s="9">
-        <v>148387</v>
+        <v>148752</v>
       </c>
       <c r="G332" s="8">
-        <v>7679905473.11</v>
+        <v>7802069239.03</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
@@ -10438,19 +10438,19 @@
         <v>666</v>
       </c>
       <c r="C333" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D333" s="7">
-        <v>0.065604</v>
+        <v>0.066362</v>
       </c>
       <c r="E333" s="8">
-        <v>112005417282.97</v>
+        <v>112164701865.31</v>
       </c>
       <c r="F333" s="9">
-        <v>99725</v>
+        <v>100056</v>
       </c>
       <c r="G333" s="8">
-        <v>7348010784.96</v>
+        <v>7443490204.97</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
@@ -10461,19 +10461,19 @@
         <v>668</v>
       </c>
       <c r="C334" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D334" s="7">
-        <v>0.086378</v>
+        <v>0.087852</v>
       </c>
       <c r="E334" s="8">
-        <v>65105398525.42</v>
+        <v>65050749596.98</v>
       </c>
       <c r="F334" s="9">
-        <v>123389</v>
+        <v>123453</v>
       </c>
       <c r="G334" s="8">
-        <v>5623667023.78</v>
+        <v>5714826577.55</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
@@ -10484,19 +10484,19 @@
         <v>670</v>
       </c>
       <c r="C335" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D335" s="7">
-        <v>0.448201</v>
+        <v>0.458965</v>
       </c>
       <c r="E335" s="8">
-        <v>52408563953.5</v>
+        <v>52407319173.77</v>
       </c>
       <c r="F335" s="9">
-        <v>126731</v>
+        <v>126674</v>
       </c>
       <c r="G335" s="8">
-        <v>23489566592.03</v>
+        <v>24053126981.9</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
@@ -10507,19 +10507,19 @@
         <v>672</v>
       </c>
       <c r="C336" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D336" s="7">
-        <v>0.099359</v>
+        <v>0.100028</v>
       </c>
       <c r="E336" s="8">
-        <v>5337212876.06</v>
+        <v>5346958630.71</v>
       </c>
       <c r="F336" s="9">
-        <v>8789</v>
+        <v>8794</v>
       </c>
       <c r="G336" s="8">
-        <v>530300287.75</v>
+        <v>534844222.32</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
@@ -10530,19 +10530,19 @@
         <v>674</v>
       </c>
       <c r="C337" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D337" s="7">
-        <v>0.356979</v>
+        <v>0.365123</v>
       </c>
       <c r="E337" s="8">
-        <v>15776814739.47</v>
+        <v>15787714001.66</v>
       </c>
       <c r="F337" s="9">
-        <v>28623</v>
+        <v>28604</v>
       </c>
       <c r="G337" s="8">
-        <v>5631991645.86</v>
+        <v>5764449703.22</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
@@ -10553,19 +10553,19 @@
         <v>676</v>
       </c>
       <c r="C338" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D338" s="7">
-        <v>0.010071</v>
+        <v>0.010355</v>
       </c>
       <c r="E338" s="8">
-        <v>79550414930.04</v>
+        <v>79808284423.04</v>
       </c>
       <c r="F338" s="9">
-        <v>4391</v>
+        <v>4400</v>
       </c>
       <c r="G338" s="8">
-        <v>801126546.55</v>
+        <v>826421120.79</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
@@ -10576,19 +10576,19 @@
         <v>678</v>
       </c>
       <c r="C339" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D339" s="7">
-        <v>0.082116</v>
+        <v>0.082237</v>
       </c>
       <c r="E339" s="8">
-        <v>3716713201.95</v>
+        <v>3718766233.8</v>
       </c>
       <c r="F339" s="9">
-        <v>78389</v>
+        <v>78490</v>
       </c>
       <c r="G339" s="8">
-        <v>305201484.09</v>
+        <v>305821157.42</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
@@ -10599,19 +10599,19 @@
         <v>680</v>
       </c>
       <c r="C340" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D340" s="7">
-        <v>0.091697</v>
+        <v>0.091841</v>
       </c>
       <c r="E340" s="8">
-        <v>648457712.86</v>
+        <v>626458191.77</v>
       </c>
       <c r="F340" s="9">
-        <v>13145</v>
+        <v>12568</v>
       </c>
       <c r="G340" s="8">
-        <v>59461923.79</v>
+        <v>57534592.23</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -10622,19 +10622,19 @@
         <v>682</v>
       </c>
       <c r="C341" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D341" s="7">
-        <v>0.043331</v>
+        <v>0.043714</v>
       </c>
       <c r="E341" s="8">
-        <v>1050167437.3</v>
+        <v>1066963727.06</v>
       </c>
       <c r="F341" s="9">
-        <v>2224</v>
+        <v>2229</v>
       </c>
       <c r="G341" s="8">
-        <v>45504420.72</v>
+        <v>46640833.86</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
@@ -10645,19 +10645,19 @@
         <v>684</v>
       </c>
       <c r="C342" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D342" s="7">
-        <v>0.049764</v>
+        <v>0.049923</v>
       </c>
       <c r="E342" s="8">
-        <v>3934680328.25</v>
+        <v>3942984998.31</v>
       </c>
       <c r="F342" s="9">
-        <v>4345</v>
+        <v>4348</v>
       </c>
       <c r="G342" s="8">
-        <v>195804724.45</v>
+        <v>196846511.95</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
@@ -10668,19 +10668,19 @@
         <v>686</v>
       </c>
       <c r="C343" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D343" s="7">
-        <v>0.013686</v>
+        <v>0.014063</v>
       </c>
       <c r="E343" s="8">
-        <v>34684822996.44</v>
+        <v>34408860561.09</v>
       </c>
       <c r="F343" s="9">
-        <v>27794</v>
+        <v>27999</v>
       </c>
       <c r="G343" s="8">
-        <v>474701778.08</v>
+        <v>483885386.51</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
@@ -10691,19 +10691,19 @@
         <v>688</v>
       </c>
       <c r="C344" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D344" s="7">
-        <v>0.073898</v>
+        <v>0.074912</v>
       </c>
       <c r="E344" s="8">
-        <v>49688037980.23</v>
+        <v>50496067946.92</v>
       </c>
       <c r="F344" s="9">
-        <v>122317</v>
+        <v>122887</v>
       </c>
       <c r="G344" s="8">
-        <v>3671826701.76</v>
+        <v>3782760888.13</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
@@ -10714,19 +10714,19 @@
         <v>690</v>
       </c>
       <c r="C345" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D345" s="7">
-        <v>0.013038</v>
+        <v>0.013015</v>
       </c>
       <c r="E345" s="8">
-        <v>15254088929.66</v>
+        <v>15893806326.72</v>
       </c>
       <c r="F345" s="9">
-        <v>5740</v>
+        <v>5885</v>
       </c>
       <c r="G345" s="8">
-        <v>198884256.6</v>
+        <v>206851286.99</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
@@ -10737,19 +10737,19 @@
         <v>692</v>
       </c>
       <c r="C346" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D346" s="7">
-        <v>0.014882</v>
+        <v>0.014897</v>
       </c>
       <c r="E346" s="8">
-        <v>71783008431.94</v>
+        <v>73292290987.98</v>
       </c>
       <c r="F346" s="9">
-        <v>19089</v>
+        <v>19275</v>
       </c>
       <c r="G346" s="8">
-        <v>1068243355.49</v>
+        <v>1091839237.81</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
@@ -10760,19 +10760,19 @@
         <v>694</v>
       </c>
       <c r="C347" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D347" s="7">
-        <v>0.049677</v>
+        <v>0.049702</v>
       </c>
       <c r="E347" s="8">
-        <v>7378391014.42</v>
+        <v>7308557347.01</v>
       </c>
       <c r="F347" s="9">
-        <v>9453</v>
+        <v>9446</v>
       </c>
       <c r="G347" s="8">
-        <v>366537298.4</v>
+        <v>363252168.03</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
@@ -10783,19 +10783,19 @@
         <v>696</v>
       </c>
       <c r="C348" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D348" s="7">
-        <v>0.087101</v>
+        <v>0.087193</v>
       </c>
       <c r="E348" s="8">
-        <v>589739308.1</v>
+        <v>587419234.03</v>
       </c>
       <c r="F348" s="9">
-        <v>6976</v>
+        <v>6969</v>
       </c>
       <c r="G348" s="8">
-        <v>51366826.99</v>
+        <v>51218853.41</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
@@ -10806,19 +10806,19 @@
         <v>698</v>
       </c>
       <c r="C349" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D349" s="7">
-        <v>0.048641</v>
+        <v>0.049007</v>
       </c>
       <c r="E349" s="8">
-        <v>3882091755.91</v>
+        <v>3857964420.95</v>
       </c>
       <c r="F349" s="9">
-        <v>5929</v>
+        <v>5900</v>
       </c>
       <c r="G349" s="8">
-        <v>188829212.51</v>
+        <v>189068371.14</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
@@ -10829,19 +10829,19 @@
         <v>700</v>
       </c>
       <c r="C350" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D350" s="7">
-        <v>0.020649</v>
+        <v>0.020877</v>
       </c>
       <c r="E350" s="8">
-        <v>8753630300.72</v>
+        <v>8746975040.59</v>
       </c>
       <c r="F350" s="9">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G350" s="8">
-        <v>180751419.72</v>
+        <v>182610890.08</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
@@ -10852,19 +10852,19 @@
         <v>702</v>
       </c>
       <c r="C351" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D351" s="10">
-        <v>0.01502</v>
+        <v>46149</v>
+      </c>
+      <c r="D351" s="7">
+        <v>0.015356</v>
       </c>
       <c r="E351" s="8">
-        <v>15833479454.21</v>
+        <v>15895998136.68</v>
       </c>
       <c r="F351" s="9">
-        <v>5907</v>
+        <v>5914</v>
       </c>
       <c r="G351" s="8">
-        <v>237821352.01</v>
+        <v>244106880.53</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -10875,19 +10875,19 @@
         <v>704</v>
       </c>
       <c r="C352" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D352" s="7">
-        <v>0.013907</v>
+        <v>0.014141</v>
       </c>
       <c r="E352" s="8">
-        <v>22173176680.7</v>
+        <v>22292686425.57</v>
       </c>
       <c r="F352" s="9">
-        <v>5794</v>
+        <v>5810</v>
       </c>
       <c r="G352" s="8">
-        <v>308361783.64</v>
+        <v>315250463.3</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -10898,19 +10898,19 @@
         <v>706</v>
       </c>
       <c r="C353" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D353" s="10">
-        <v>0.01452</v>
+        <v>46149</v>
+      </c>
+      <c r="D353" s="7">
+        <v>0.014598</v>
       </c>
       <c r="E353" s="8">
-        <v>23613349866.26</v>
+        <v>23877543852.89</v>
       </c>
       <c r="F353" s="9">
-        <v>10749</v>
+        <v>10819</v>
       </c>
       <c r="G353" s="8">
-        <v>342864779.52</v>
+        <v>348563842.59</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
@@ -10921,19 +10921,19 @@
         <v>708</v>
       </c>
       <c r="C354" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D354" s="7">
-        <v>0.016086</v>
+        <v>0.016274</v>
       </c>
       <c r="E354" s="8">
-        <v>38996696023.15</v>
+        <v>39489856551.25</v>
       </c>
       <c r="F354" s="9">
-        <v>10580</v>
+        <v>10716</v>
       </c>
       <c r="G354" s="8">
-        <v>627292140.54</v>
+        <v>642650171.8</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -10944,19 +10944,19 @@
         <v>710</v>
       </c>
       <c r="C355" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D355" s="7">
-        <v>0.048944</v>
+        <v>0.049287</v>
       </c>
       <c r="E355" s="8">
-        <v>2897363796.43</v>
+        <v>2880734166.46</v>
       </c>
       <c r="F355" s="9">
-        <v>5134</v>
+        <v>5125</v>
       </c>
       <c r="G355" s="8">
-        <v>141809178.55</v>
+        <v>141982386.68</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
@@ -10967,19 +10967,19 @@
         <v>712</v>
       </c>
       <c r="C356" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D356" s="10">
-        <v>0.22872</v>
+        <v>46149</v>
+      </c>
+      <c r="D356" s="7">
+        <v>0.230609</v>
       </c>
       <c r="E356" s="8">
-        <v>8791205610.44</v>
+        <v>8829597355.9</v>
       </c>
       <c r="F356" s="9">
-        <v>47791</v>
+        <v>47853</v>
       </c>
       <c r="G356" s="8">
-        <v>2010726347.93</v>
+        <v>2036183731.78</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
@@ -10990,19 +10990,19 @@
         <v>714</v>
       </c>
       <c r="C357" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D357" s="7">
-        <v>0.082974</v>
+        <v>0.083091</v>
       </c>
       <c r="E357" s="8">
-        <v>11930003826.75</v>
+        <v>11989259271.99</v>
       </c>
       <c r="F357" s="9">
-        <v>21924</v>
+        <v>21992</v>
       </c>
       <c r="G357" s="8">
-        <v>989880709.02</v>
+        <v>996196777.72</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
@@ -11013,19 +11013,19 @@
         <v>716</v>
       </c>
       <c r="C358" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D358" s="7">
-        <v>0.307363</v>
+        <v>46149</v>
+      </c>
+      <c r="D358" s="10">
+        <v>0.31314</v>
       </c>
       <c r="E358" s="8">
-        <v>3852096888.1</v>
+        <v>3858919498.01</v>
       </c>
       <c r="F358" s="9">
-        <v>27509</v>
+        <v>27489</v>
       </c>
       <c r="G358" s="8">
-        <v>1183992975.61</v>
+        <v>1208383841.22</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
@@ -11036,19 +11036,19 @@
         <v>718</v>
       </c>
       <c r="C359" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D359" s="7">
-        <v>1.365824</v>
+        <v>1.401348</v>
       </c>
       <c r="E359" s="8">
-        <v>8847120044.63</v>
+        <v>8851352584.12</v>
       </c>
       <c r="F359" s="9">
-        <v>245062</v>
+        <v>245255</v>
       </c>
       <c r="G359" s="8">
-        <v>12083607675.32</v>
+        <v>12403825621.43</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
@@ -11059,19 +11059,19 @@
         <v>720</v>
       </c>
       <c r="C360" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D360" s="7">
-        <v>0.094676</v>
+        <v>0.096822</v>
       </c>
       <c r="E360" s="8">
-        <v>542018616734.05</v>
+        <v>541569975832.4</v>
       </c>
       <c r="F360" s="9">
-        <v>2781036</v>
+        <v>2779767</v>
       </c>
       <c r="G360" s="8">
-        <v>51316052770.95</v>
+        <v>52436136594.47</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
@@ -11082,19 +11082,19 @@
         <v>722</v>
       </c>
       <c r="C361" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D361" s="7">
-        <v>0.321281</v>
+        <v>0.325833</v>
       </c>
       <c r="E361" s="8">
-        <v>23835773310.03</v>
+        <v>23900574353.09</v>
       </c>
       <c r="F361" s="9">
-        <v>422557</v>
+        <v>423179</v>
       </c>
       <c r="G361" s="8">
-        <v>7657982068.82</v>
+        <v>7787588818.27</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
@@ -11105,19 +11105,19 @@
         <v>724</v>
       </c>
       <c r="C362" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D362" s="7">
-        <v>0.350496</v>
+        <v>0.351125</v>
       </c>
       <c r="E362" s="8">
-        <v>86790882307.59</v>
+        <v>86008742273.48</v>
       </c>
       <c r="F362" s="9">
-        <v>491742</v>
+        <v>434077</v>
       </c>
       <c r="G362" s="8">
-        <v>30419848452.04</v>
+        <v>30199838752.96</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
@@ -11128,19 +11128,19 @@
         <v>726</v>
       </c>
       <c r="C363" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D363" s="7">
-        <v>0.223016</v>
+        <v>0.226261</v>
       </c>
       <c r="E363" s="8">
-        <v>20377370364.26</v>
+        <v>20418111331.21</v>
       </c>
       <c r="F363" s="9">
-        <v>70116</v>
+        <v>70162</v>
       </c>
       <c r="G363" s="8">
-        <v>4544485133.58</v>
+        <v>4619827831.99</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
@@ -11151,19 +11151,19 @@
         <v>728</v>
       </c>
       <c r="C364" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D364" s="7">
-        <v>0.101968</v>
+        <v>0.102486</v>
       </c>
       <c r="E364" s="8">
-        <v>3767497931.63</v>
+        <v>3773736784.59</v>
       </c>
       <c r="F364" s="9">
-        <v>8018</v>
+        <v>8027</v>
       </c>
       <c r="G364" s="8">
-        <v>384163967.68</v>
+        <v>386756335.72</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
@@ -11174,19 +11174,19 @@
         <v>730</v>
       </c>
       <c r="C365" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D365" s="7">
-        <v>0.138217</v>
+        <v>0.139032</v>
       </c>
       <c r="E365" s="8">
-        <v>104035265266.05</v>
+        <v>103974177615.54</v>
       </c>
       <c r="F365" s="9">
-        <v>1908209</v>
+        <v>1907626</v>
       </c>
       <c r="G365" s="8">
-        <v>14379461445.84</v>
+        <v>14455740977.87</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
@@ -11197,19 +11197,19 @@
         <v>732</v>
       </c>
       <c r="C366" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D366" s="7">
-        <v>0.136347</v>
+        <v>0.136795</v>
       </c>
       <c r="E366" s="8">
-        <v>57845650100.66</v>
+        <v>57945083681.75</v>
       </c>
       <c r="F366" s="9">
-        <v>120530</v>
+        <v>120658</v>
       </c>
       <c r="G366" s="8">
-        <v>7887058620.78</v>
+        <v>7926572619.05</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
@@ -11220,19 +11220,19 @@
         <v>734</v>
       </c>
       <c r="C367" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D367" s="7">
-        <v>0.733552</v>
+        <v>46149</v>
+      </c>
+      <c r="D367" s="10">
+        <v>0.73948</v>
       </c>
       <c r="E367" s="8">
-        <v>16807225791.24</v>
+        <v>16819132258.23</v>
       </c>
       <c r="F367" s="9">
-        <v>342249</v>
+        <v>342366</v>
       </c>
       <c r="G367" s="8">
-        <v>12328966352.06</v>
+        <v>12437418343.65</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
@@ -11243,19 +11243,19 @@
         <v>736</v>
       </c>
       <c r="C368" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D368" s="7">
-        <v>0.146817</v>
+        <v>0.147366</v>
       </c>
       <c r="E368" s="8">
-        <v>31119562930.55</v>
+        <v>31118221453.66</v>
       </c>
       <c r="F368" s="9">
-        <v>93199</v>
+        <v>93157</v>
       </c>
       <c r="G368" s="8">
-        <v>4568895317.2</v>
+        <v>4585767603.37</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
@@ -11266,19 +11266,19 @@
         <v>738</v>
       </c>
       <c r="C369" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D369" s="7">
-        <v>0.171581</v>
+        <v>0.173616</v>
       </c>
       <c r="E369" s="8">
-        <v>2082839732.97</v>
+        <v>2083180916.6</v>
       </c>
       <c r="F369" s="9">
-        <v>7376</v>
+        <v>7381</v>
       </c>
       <c r="G369" s="8">
-        <v>357374936.66</v>
+        <v>361673917.95</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
@@ -11289,19 +11289,19 @@
         <v>740</v>
       </c>
       <c r="C370" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D370" s="7">
-        <v>0.384391</v>
+        <v>46149</v>
+      </c>
+      <c r="D370" s="10">
+        <v>0.38483</v>
       </c>
       <c r="E370" s="8">
-        <v>5019249678.7</v>
+        <v>5048368491.42</v>
       </c>
       <c r="F370" s="9">
-        <v>19094</v>
+        <v>19141</v>
       </c>
       <c r="G370" s="8">
-        <v>1929355359.65</v>
+        <v>1942764684.48</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
@@ -11312,19 +11312,19 @@
         <v>742</v>
       </c>
       <c r="C371" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D371" s="7">
-        <v>0.768132</v>
+        <v>0.786235</v>
       </c>
       <c r="E371" s="8">
-        <v>329042245019.24</v>
+        <v>329269755677.66</v>
       </c>
       <c r="F371" s="9">
-        <v>2043823</v>
+        <v>2043644</v>
       </c>
       <c r="G371" s="8">
-        <v>252747893967.75</v>
+        <v>258883396339.9</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
@@ -11335,19 +11335,19 @@
         <v>744</v>
       </c>
       <c r="C372" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D372" s="11">
-        <v>0.1594</v>
+        <v>46149</v>
+      </c>
+      <c r="D372" s="7">
+        <v>0.160157</v>
       </c>
       <c r="E372" s="8">
-        <v>23983314823</v>
+        <v>24051793343.15</v>
       </c>
       <c r="F372" s="9">
-        <v>109400</v>
+        <v>109576</v>
       </c>
       <c r="G372" s="8">
-        <v>3822934404.09</v>
+        <v>3852066120.22</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
@@ -11358,19 +11358,19 @@
         <v>746</v>
       </c>
       <c r="C373" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D373" s="7">
-        <v>0.195211</v>
+        <v>46149</v>
+      </c>
+      <c r="D373" s="10">
+        <v>0.20041</v>
       </c>
       <c r="E373" s="8">
-        <v>3593936953.85</v>
+        <v>3590303707.07</v>
       </c>
       <c r="F373" s="9">
-        <v>11497</v>
+        <v>11484</v>
       </c>
       <c r="G373" s="8">
-        <v>701576972.22</v>
+        <v>719531463.54</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
@@ -11381,19 +11381,19 @@
         <v>748</v>
       </c>
       <c r="C374" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D374" s="7">
-        <v>0.413877</v>
+        <v>0.428177</v>
       </c>
       <c r="E374" s="8">
-        <v>55619251186.21</v>
+        <v>55672197761.8</v>
       </c>
       <c r="F374" s="9">
-        <v>289066</v>
+        <v>288989</v>
       </c>
       <c r="G374" s="8">
-        <v>23019509565.7</v>
+        <v>23837573740.96</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
@@ -11404,19 +11404,19 @@
         <v>750</v>
       </c>
       <c r="C375" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D375" s="7">
-        <v>0.525823</v>
+        <v>0.541249</v>
       </c>
       <c r="E375" s="8">
-        <v>1262960755.05</v>
+        <v>1277109555.43</v>
       </c>
       <c r="F375" s="9">
-        <v>14383</v>
+        <v>14541</v>
       </c>
       <c r="G375" s="8">
-        <v>664094412.88</v>
+        <v>691234311.9</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
@@ -11427,19 +11427,19 @@
         <v>752</v>
       </c>
       <c r="C376" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D376" s="7">
-        <v>0.187455</v>
+        <v>0.192052</v>
       </c>
       <c r="E376" s="8">
-        <v>6817666996.84</v>
+        <v>6817016442.9</v>
       </c>
       <c r="F376" s="9">
-        <v>16238</v>
+        <v>16214</v>
       </c>
       <c r="G376" s="8">
-        <v>1278003321.26</v>
+        <v>1309223210.16</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
@@ -11450,19 +11450,19 @@
         <v>754</v>
       </c>
       <c r="C377" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D377" s="7">
-        <v>0.119706</v>
+        <v>0.120423</v>
       </c>
       <c r="E377" s="8">
-        <v>7584650682.56</v>
+        <v>7593167272.15</v>
       </c>
       <c r="F377" s="9">
-        <v>23901</v>
+        <v>23894</v>
       </c>
       <c r="G377" s="8">
-        <v>907930473.42</v>
+        <v>914393989.55</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
@@ -11473,19 +11473,19 @@
         <v>756</v>
       </c>
       <c r="C378" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D378" s="7">
-        <v>0.181383</v>
+        <v>0.184402</v>
       </c>
       <c r="E378" s="8">
-        <v>14141367461.5</v>
+        <v>14141655268.82</v>
       </c>
       <c r="F378" s="9">
-        <v>50784</v>
+        <v>50763</v>
       </c>
       <c r="G378" s="8">
-        <v>2565003544.42</v>
+        <v>2607744546.95</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
@@ -11496,19 +11496,19 @@
         <v>758</v>
       </c>
       <c r="C379" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D379" s="10">
-        <v>0.08899</v>
+        <v>46149</v>
+      </c>
+      <c r="D379" s="7">
+        <v>0.089523</v>
       </c>
       <c r="E379" s="8">
-        <v>396405139971.63</v>
+        <v>396523448793.17</v>
       </c>
       <c r="F379" s="9">
-        <v>1944782</v>
+        <v>1946550</v>
       </c>
       <c r="G379" s="8">
-        <v>35275960591.4</v>
+        <v>35497965143.5</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
@@ -11519,19 +11519,19 @@
         <v>760</v>
       </c>
       <c r="C380" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D380" s="7">
-        <v>0.154951</v>
+        <v>0.157197</v>
       </c>
       <c r="E380" s="8">
-        <v>1154795922.54</v>
+        <v>1154960978.34</v>
       </c>
       <c r="F380" s="9">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="G380" s="8">
-        <v>178936209.68</v>
+        <v>181556221.67</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
@@ -11542,19 +11542,19 @@
         <v>762</v>
       </c>
       <c r="C381" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D381" s="7">
-        <v>0.190751</v>
+        <v>0.193267</v>
       </c>
       <c r="E381" s="8">
-        <v>1024398893.82</v>
+        <v>1023047590.88</v>
       </c>
       <c r="F381" s="9">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="G381" s="8">
-        <v>195405208.32</v>
+        <v>197720942.99</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
@@ -11565,19 +11565,19 @@
         <v>764</v>
       </c>
       <c r="C382" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D382" s="7">
-        <v>0.174365</v>
+        <v>46149</v>
+      </c>
+      <c r="D382" s="10">
+        <v>0.17676</v>
       </c>
       <c r="E382" s="8">
-        <v>584724096.4</v>
+        <v>585926295.5</v>
       </c>
       <c r="F382" s="9">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G382" s="8">
-        <v>101955335.58</v>
+        <v>103568564.48</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
@@ -11588,19 +11588,19 @@
         <v>766</v>
       </c>
       <c r="C383" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D383" s="7">
-        <v>0.092101</v>
+        <v>0.092968</v>
       </c>
       <c r="E383" s="8">
-        <v>97825501477.57</v>
+        <v>97921756701.14</v>
       </c>
       <c r="F383" s="9">
-        <v>665219</v>
+        <v>665770</v>
       </c>
       <c r="G383" s="8">
-        <v>9009787301.56</v>
+        <v>9103601479.84</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
@@ -11611,19 +11611,19 @@
         <v>768</v>
       </c>
       <c r="C384" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D384" s="7">
-        <v>0.090086</v>
+        <v>0.090178</v>
       </c>
       <c r="E384" s="8">
-        <v>42285883316.21</v>
+        <v>42377231785.79</v>
       </c>
       <c r="F384" s="9">
-        <v>441684</v>
+        <v>443396</v>
       </c>
       <c r="G384" s="8">
-        <v>3809374915.55</v>
+        <v>3821482449.82</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
@@ -11634,19 +11634,19 @@
         <v>770</v>
       </c>
       <c r="C385" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D385" s="7">
-        <v>0.094456</v>
+        <v>0.094622</v>
       </c>
       <c r="E385" s="8">
-        <v>16639267027.49</v>
+        <v>16713467882.92</v>
       </c>
       <c r="F385" s="9">
-        <v>129215</v>
+        <v>142578</v>
       </c>
       <c r="G385" s="8">
-        <v>1571676254.1</v>
+        <v>1581464548.5</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
@@ -11657,19 +11657,19 @@
         <v>772</v>
       </c>
       <c r="C386" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D386" s="7">
-        <v>0.263876</v>
+        <v>0.271151</v>
       </c>
       <c r="E386" s="8">
-        <v>3538787521.38</v>
+        <v>3544742125.67</v>
       </c>
       <c r="F386" s="9">
-        <v>10579</v>
+        <v>10567</v>
       </c>
       <c r="G386" s="8">
-        <v>933801034.77</v>
+        <v>961158885.46</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
@@ -11680,19 +11680,19 @@
         <v>774</v>
       </c>
       <c r="C387" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D387" s="7">
-        <v>0.192091</v>
+        <v>0.195937</v>
       </c>
       <c r="E387" s="8">
-        <v>2329648452.64</v>
+        <v>2338600038.99</v>
       </c>
       <c r="F387" s="9">
-        <v>7172</v>
+        <v>7183</v>
       </c>
       <c r="G387" s="8">
-        <v>447504569.86</v>
+        <v>458217837.92</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
@@ -11703,19 +11703,19 @@
         <v>776</v>
       </c>
       <c r="C388" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D388" s="7">
-        <v>0.174519</v>
+        <v>46149</v>
+      </c>
+      <c r="D388" s="10">
+        <v>0.17743</v>
       </c>
       <c r="E388" s="8">
-        <v>2498933950.47</v>
+        <v>2516071177.39</v>
       </c>
       <c r="F388" s="9">
-        <v>7672</v>
+        <v>7685</v>
       </c>
       <c r="G388" s="8">
-        <v>436112545.11</v>
+        <v>446426599.59</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -11726,19 +11726,19 @@
         <v>778</v>
       </c>
       <c r="C389" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D389" s="7">
-        <v>0.099417</v>
+        <v>0.100113</v>
       </c>
       <c r="E389" s="8">
-        <v>3845971372.79</v>
+        <v>3850168906.17</v>
       </c>
       <c r="F389" s="9">
-        <v>7238</v>
+        <v>7232</v>
       </c>
       <c r="G389" s="8">
-        <v>382356033.87</v>
+        <v>385452292.24</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
@@ -11749,19 +11749,19 @@
         <v>780</v>
       </c>
       <c r="C390" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D390" s="7">
-        <v>0.230859</v>
+        <v>0.233807</v>
       </c>
       <c r="E390" s="8">
-        <v>1495634927.47</v>
+        <v>1494391545.13</v>
       </c>
       <c r="F390" s="9">
-        <v>5847</v>
+        <v>5845</v>
       </c>
       <c r="G390" s="8">
-        <v>345280703.15</v>
+        <v>349399316.25</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
@@ -11772,19 +11772,19 @@
         <v>782</v>
       </c>
       <c r="C391" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D391" s="7">
-        <v>0.326482</v>
+        <v>46149</v>
+      </c>
+      <c r="D391" s="10">
+        <v>0.33171</v>
       </c>
       <c r="E391" s="8">
-        <v>1911700758.93</v>
+        <v>1910671313.63</v>
       </c>
       <c r="F391" s="9">
-        <v>6345</v>
+        <v>6337</v>
       </c>
       <c r="G391" s="8">
-        <v>624135102.15</v>
+        <v>633787868.83</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
@@ -11795,19 +11795,19 @@
         <v>784</v>
       </c>
       <c r="C392" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D392" s="7">
-        <v>0.275507</v>
+        <v>0.279548</v>
       </c>
       <c r="E392" s="8">
-        <v>14044458495.18</v>
+        <v>14103288858.81</v>
       </c>
       <c r="F392" s="9">
-        <v>67576</v>
+        <v>67809</v>
       </c>
       <c r="G392" s="8">
-        <v>3869349225.15</v>
+        <v>3942540384.01</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
@@ -11818,19 +11818,19 @@
         <v>786</v>
       </c>
       <c r="C393" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D393" s="7">
-        <v>0.060735</v>
+        <v>0.061598</v>
       </c>
       <c r="E393" s="8">
-        <v>56459222953.45</v>
+        <v>56745007590.55</v>
       </c>
       <c r="F393" s="9">
-        <v>41648</v>
+        <v>41809</v>
       </c>
       <c r="G393" s="8">
-        <v>3429075280.52</v>
+        <v>3495387867.49</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
@@ -11841,19 +11841,19 @@
         <v>788</v>
       </c>
       <c r="C394" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D394" s="10">
-        <v>0.33957</v>
+        <v>46149</v>
+      </c>
+      <c r="D394" s="7">
+        <v>0.347013</v>
       </c>
       <c r="E394" s="8">
-        <v>13434500341.5</v>
+        <v>13428638212.07</v>
       </c>
       <c r="F394" s="9">
-        <v>216737</v>
+        <v>216684</v>
       </c>
       <c r="G394" s="8">
-        <v>4561959126.86</v>
+        <v>4659906111.31</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
@@ -11864,19 +11864,19 @@
         <v>790</v>
       </c>
       <c r="C395" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D395" s="7">
-        <v>0.372394</v>
+        <v>0.373322</v>
       </c>
       <c r="E395" s="8">
-        <v>4749674371.79</v>
+        <v>4761035628.65</v>
       </c>
       <c r="F395" s="9">
-        <v>53294</v>
+        <v>53514</v>
       </c>
       <c r="G395" s="8">
-        <v>1768752278.93</v>
+        <v>1777397549.22</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
@@ -11887,19 +11887,19 @@
         <v>792</v>
       </c>
       <c r="C396" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D396" s="7">
-        <v>0.214673</v>
+        <v>0.219411</v>
       </c>
       <c r="E396" s="8">
-        <v>68856575447.87</v>
+        <v>68909792741.6</v>
       </c>
       <c r="F396" s="9">
-        <v>518131</v>
+        <v>518439</v>
       </c>
       <c r="G396" s="8">
-        <v>14781656102.8</v>
+        <v>15119579144.44</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -11910,19 +11910,19 @@
         <v>794</v>
       </c>
       <c r="C397" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D397" s="7">
-        <v>0.132769</v>
+        <v>0.133371</v>
       </c>
       <c r="E397" s="8">
-        <v>12858861071.08</v>
+        <v>12877667358.05</v>
       </c>
       <c r="F397" s="9">
-        <v>45279</v>
+        <v>45417</v>
       </c>
       <c r="G397" s="8">
-        <v>1707256502.08</v>
+        <v>1717511213.36</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
@@ -11933,19 +11933,19 @@
         <v>796</v>
       </c>
       <c r="C398" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D398" s="7">
-        <v>0.063252</v>
+        <v>0.063604</v>
       </c>
       <c r="E398" s="8">
-        <v>58485988244.69</v>
+        <v>58473180731.06</v>
       </c>
       <c r="F398" s="9">
-        <v>323423</v>
+        <v>323278</v>
       </c>
       <c r="G398" s="8">
-        <v>3699329509.91</v>
+        <v>3719144244.86</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>07.05.2026 18:22:38</t>
+    <t>08.05.2026 18:20:04</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2917,19 +2917,19 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D6" s="7">
-        <v>0.102498</v>
+        <v>0.103127</v>
       </c>
       <c r="E6" s="8">
-        <v>47768595341.11</v>
+        <v>47845399000.87</v>
       </c>
       <c r="F6" s="9">
-        <v>645916</v>
+        <v>646357</v>
       </c>
       <c r="G6" s="8">
-        <v>4896178280.9</v>
+        <v>4934156609.92</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2940,19 +2940,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D7" s="7">
-        <v>0.408707</v>
+        <v>0.411651</v>
       </c>
       <c r="E7" s="8">
-        <v>17236612061.79</v>
+        <v>17346314689.75</v>
       </c>
       <c r="F7" s="9">
-        <v>151821</v>
+        <v>151933</v>
       </c>
       <c r="G7" s="8">
-        <v>7044720858.84</v>
+        <v>7140629729.38</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2963,19 +2963,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D8" s="7">
-        <v>0.086931</v>
+        <v>0.087035</v>
       </c>
       <c r="E8" s="8">
-        <v>8083796587.42</v>
+        <v>8286136763.74</v>
       </c>
       <c r="F8" s="9">
-        <v>143963</v>
+        <v>148293</v>
       </c>
       <c r="G8" s="8">
-        <v>702735981.17</v>
+        <v>721187392.29</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2986,19 +2986,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D9" s="7">
-        <v>0.369916</v>
+        <v>0.370889</v>
       </c>
       <c r="E9" s="8">
-        <v>142779118798.59</v>
+        <v>142864695000.36</v>
       </c>
       <c r="F9" s="9">
-        <v>489844</v>
+        <v>490305</v>
       </c>
       <c r="G9" s="8">
-        <v>52816242969.79</v>
+        <v>52986989240.11</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3009,19 +3009,19 @@
         <v>20</v>
       </c>
       <c r="C10" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D10" s="7">
-        <v>0.335381</v>
+        <v>0.338661</v>
       </c>
       <c r="E10" s="8">
-        <v>23076866385.93</v>
+        <v>23064770488.13</v>
       </c>
       <c r="F10" s="9">
-        <v>329546</v>
+        <v>329525</v>
       </c>
       <c r="G10" s="8">
-        <v>7739548889.99</v>
+        <v>7811139204.69</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3032,19 +3032,19 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D11" s="7">
-        <v>1.028735</v>
+        <v>1.031166</v>
       </c>
       <c r="E11" s="8">
-        <v>11590858965.36</v>
+        <v>11590702719.47</v>
       </c>
       <c r="F11" s="9">
-        <v>289186</v>
+        <v>289158</v>
       </c>
       <c r="G11" s="8">
-        <v>11923927408.57</v>
+        <v>11951934946.61</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3055,19 +3055,19 @@
         <v>24</v>
       </c>
       <c r="C12" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D12" s="7">
-        <v>0.715115</v>
+        <v>0.725785</v>
       </c>
       <c r="E12" s="8">
-        <v>136595231484.15</v>
+        <v>136553052854.98</v>
       </c>
       <c r="F12" s="9">
-        <v>726283</v>
+        <v>726256</v>
       </c>
       <c r="G12" s="8">
-        <v>97681268470.98</v>
+        <v>99108163610.65</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3078,19 +3078,19 @@
         <v>26</v>
       </c>
       <c r="C13" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D13" s="7">
-        <v>2.081179</v>
+        <v>2.089618</v>
       </c>
       <c r="E13" s="8">
-        <v>1370727072.23</v>
+        <v>1372867868.41</v>
       </c>
       <c r="F13" s="9">
-        <v>32850</v>
+        <v>32895</v>
       </c>
       <c r="G13" s="8">
-        <v>2852727978.21</v>
+        <v>2868769187.24</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3101,19 +3101,19 @@
         <v>28</v>
       </c>
       <c r="C14" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D14" s="7">
-        <v>0.138023</v>
+        <v>0.138331</v>
       </c>
       <c r="E14" s="8">
-        <v>249859828.37</v>
+        <v>249861824.28</v>
       </c>
       <c r="F14" s="9">
         <v>90</v>
       </c>
       <c r="G14" s="8">
-        <v>34486322.82</v>
+        <v>34563724.52</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3124,19 +3124,19 @@
         <v>30</v>
       </c>
       <c r="C15" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D15" s="7">
-        <v>1.420973</v>
+        <v>46150</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1.42649</v>
       </c>
       <c r="E15" s="8">
-        <v>16211958119.02</v>
+        <v>16222456619.3</v>
       </c>
       <c r="F15" s="9">
-        <v>488129</v>
+        <v>488585</v>
       </c>
       <c r="G15" s="8">
-        <v>23036748749.34</v>
+        <v>23141179939</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3147,19 +3147,19 @@
         <v>32</v>
       </c>
       <c r="C16" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D16" s="7">
-        <v>0.094848</v>
+        <v>0.095416</v>
       </c>
       <c r="E16" s="8">
-        <v>566673027424.68</v>
+        <v>566155444703.72</v>
       </c>
       <c r="F16" s="9">
-        <v>1956202</v>
+        <v>1955079</v>
       </c>
       <c r="G16" s="8">
-        <v>53747662699.47</v>
+        <v>54020513535.01</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3170,19 +3170,19 @@
         <v>34</v>
       </c>
       <c r="C17" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D17" s="7">
-        <v>0.349091</v>
+        <v>0.352575</v>
       </c>
       <c r="E17" s="8">
-        <v>2126247617.16</v>
+        <v>2123656613.27</v>
       </c>
       <c r="F17" s="9">
-        <v>13436</v>
+        <v>13420</v>
       </c>
       <c r="G17" s="8">
-        <v>742254490.02</v>
+        <v>748748402.71</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3193,19 +3193,19 @@
         <v>36</v>
       </c>
       <c r="C18" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D18" s="7">
-        <v>0.146742</v>
+        <v>0.147125</v>
       </c>
       <c r="E18" s="8">
-        <v>33002904102.58</v>
+        <v>32976976615.33</v>
       </c>
       <c r="F18" s="9">
-        <v>239020</v>
+        <v>238984</v>
       </c>
       <c r="G18" s="8">
-        <v>4842904751.44</v>
+        <v>4851721737.52</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3216,19 +3216,19 @@
         <v>38</v>
       </c>
       <c r="C19" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D19" s="7">
-        <v>0.375264</v>
+        <v>0.379759</v>
       </c>
       <c r="E19" s="8">
-        <v>1424445548.93</v>
+        <v>1425221135.43</v>
       </c>
       <c r="F19" s="9">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G19" s="8">
-        <v>534542911.7</v>
+        <v>541240810.47</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3239,19 +3239,19 @@
         <v>40</v>
       </c>
       <c r="C20" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D20" s="7">
-        <v>0.139238</v>
+        <v>0.140686</v>
       </c>
       <c r="E20" s="8">
-        <v>14777741562.38</v>
+        <v>14776034274.11</v>
       </c>
       <c r="F20" s="9">
-        <v>524875</v>
+        <v>524782</v>
       </c>
       <c r="G20" s="8">
-        <v>2057623465.62</v>
+        <v>2078776934.34</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3262,19 +3262,19 @@
         <v>42</v>
       </c>
       <c r="C21" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D21" s="7">
-        <v>0.098378</v>
+        <v>0.099204</v>
       </c>
       <c r="E21" s="8">
-        <v>509686821482.16</v>
+        <v>509380171256.4</v>
       </c>
       <c r="F21" s="9">
-        <v>2303269</v>
+        <v>2302196</v>
       </c>
       <c r="G21" s="8">
-        <v>50142135467.14</v>
+        <v>50532696178.92</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3285,19 +3285,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D22" s="10">
-        <v>0.41284</v>
+        <v>46150</v>
+      </c>
+      <c r="D22" s="7">
+        <v>0.413811</v>
       </c>
       <c r="E22" s="8">
-        <v>3444934878.24</v>
+        <v>3453415244.5</v>
       </c>
       <c r="F22" s="9">
-        <v>19381</v>
+        <v>19480</v>
       </c>
       <c r="G22" s="8">
-        <v>1422208171.9</v>
+        <v>1429062357.75</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3308,19 +3308,19 @@
         <v>46</v>
       </c>
       <c r="C23" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D23" s="7">
-        <v>0.094867</v>
+        <v>0.096103</v>
       </c>
       <c r="E23" s="8">
-        <v>576452313.3</v>
+        <v>576051838.57</v>
       </c>
       <c r="F23" s="9">
-        <v>4607</v>
+        <v>4604</v>
       </c>
       <c r="G23" s="8">
-        <v>54686310.26</v>
+        <v>55360387.49</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3331,19 +3331,19 @@
         <v>48</v>
       </c>
       <c r="C24" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D24" s="7">
-        <v>0.230507</v>
+        <v>0.231537</v>
       </c>
       <c r="E24" s="8">
-        <v>1221779171.02</v>
+        <v>1218038786.5</v>
       </c>
       <c r="F24" s="9">
-        <v>4987</v>
+        <v>4982</v>
       </c>
       <c r="G24" s="8">
-        <v>281628682</v>
+        <v>282021480.21</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3354,19 +3354,19 @@
         <v>50</v>
       </c>
       <c r="C25" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D25" s="7">
-        <v>0.106626</v>
+        <v>46150</v>
+      </c>
+      <c r="D25" s="10">
+        <v>0.10741</v>
       </c>
       <c r="E25" s="8">
-        <v>66702443494.58</v>
+        <v>66782376410.41</v>
       </c>
       <c r="F25" s="9">
-        <v>764895</v>
+        <v>765176</v>
       </c>
       <c r="G25" s="8">
-        <v>7112189766.93</v>
+        <v>7173067055.94</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3377,19 +3377,19 @@
         <v>52</v>
       </c>
       <c r="C26" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D26" s="7">
-        <v>0.098808</v>
+        <v>0.099114</v>
       </c>
       <c r="E26" s="8">
-        <v>1679191411.7</v>
+        <v>1680204320.76</v>
       </c>
       <c r="F26" s="9">
-        <v>3215</v>
+        <v>3212</v>
       </c>
       <c r="G26" s="8">
-        <v>165917758.15</v>
+        <v>166532561.54</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3400,19 +3400,19 @@
         <v>54</v>
       </c>
       <c r="C27" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D27" s="7">
-        <v>0.094081</v>
+        <v>0.094342</v>
       </c>
       <c r="E27" s="8">
-        <v>61929612277.8</v>
+        <v>61991786915.8</v>
       </c>
       <c r="F27" s="9">
-        <v>715355</v>
+        <v>715723</v>
       </c>
       <c r="G27" s="8">
-        <v>5826400025.37</v>
+        <v>5848434848.46</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3423,19 +3423,19 @@
         <v>56</v>
       </c>
       <c r="C28" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D28" s="7">
-        <v>0.389441</v>
+        <v>0.392645</v>
       </c>
       <c r="E28" s="8">
-        <v>1046438154.95</v>
+        <v>1041718399.88</v>
       </c>
       <c r="F28" s="9">
-        <v>7896</v>
+        <v>7883</v>
       </c>
       <c r="G28" s="8">
-        <v>407525509.8</v>
+        <v>409025107.55</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3446,19 +3446,19 @@
         <v>58</v>
       </c>
       <c r="C29" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D29" s="7">
-        <v>0.650439</v>
+        <v>0.652205</v>
       </c>
       <c r="E29" s="8">
-        <v>211731209.69</v>
+        <v>214124045.33</v>
       </c>
       <c r="F29" s="9">
         <v>1652</v>
       </c>
       <c r="G29" s="8">
-        <v>137718282.62</v>
+        <v>139652803.57</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3469,19 +3469,19 @@
         <v>60</v>
       </c>
       <c r="C30" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D30" s="7">
-        <v>2.447826</v>
+        <v>2.479514</v>
       </c>
       <c r="E30" s="8">
-        <v>849115067.38</v>
+        <v>846198749.34</v>
       </c>
       <c r="F30" s="9">
-        <v>19598</v>
+        <v>19650</v>
       </c>
       <c r="G30" s="8">
-        <v>2078485894.59</v>
+        <v>2098161859.17</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3492,19 +3492,19 @@
         <v>62</v>
       </c>
       <c r="C31" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D31" s="7">
-        <v>0.527899</v>
+        <v>0.529961</v>
       </c>
       <c r="E31" s="8">
-        <v>2410407571.48</v>
+        <v>2404497614.57</v>
       </c>
       <c r="F31" s="9">
-        <v>14208</v>
+        <v>14185</v>
       </c>
       <c r="G31" s="8">
-        <v>1272450914.75</v>
+        <v>1274290733.57</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3515,19 +3515,19 @@
         <v>64</v>
       </c>
       <c r="C32" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D32" s="10">
-        <v>0.86373</v>
+        <v>46150</v>
+      </c>
+      <c r="D32" s="7">
+        <v>0.876252</v>
       </c>
       <c r="E32" s="8">
-        <v>12351139233.4</v>
+        <v>12317203211.81</v>
       </c>
       <c r="F32" s="9">
-        <v>77316</v>
+        <v>77307</v>
       </c>
       <c r="G32" s="8">
-        <v>10668047397.17</v>
+        <v>10792978069.14</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3538,19 +3538,19 @@
         <v>66</v>
       </c>
       <c r="C33" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D33" s="7">
-        <v>0.267816</v>
+        <v>0.271776</v>
       </c>
       <c r="E33" s="8">
-        <v>1312018496.93</v>
+        <v>1313176550.77</v>
       </c>
       <c r="F33" s="9">
-        <v>16191</v>
+        <v>16187</v>
       </c>
       <c r="G33" s="8">
-        <v>351379287.08</v>
+        <v>356890270.47</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3561,19 +3561,19 @@
         <v>68</v>
       </c>
       <c r="C34" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D34" s="7">
-        <v>0.126783</v>
+        <v>0.127391</v>
       </c>
       <c r="E34" s="8">
-        <v>3327786052</v>
+        <v>3325845400.83</v>
       </c>
       <c r="F34" s="9">
-        <v>54019</v>
+        <v>54013</v>
       </c>
       <c r="G34" s="8">
-        <v>421905327.03</v>
+        <v>423682098.23</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3584,19 +3584,19 @@
         <v>70</v>
       </c>
       <c r="C35" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D35" s="7">
-        <v>0.176437</v>
+        <v>0.177344</v>
       </c>
       <c r="E35" s="8">
-        <v>10757455402.23</v>
+        <v>10760860350.57</v>
       </c>
       <c r="F35" s="9">
-        <v>36644</v>
+        <v>36653</v>
       </c>
       <c r="G35" s="8">
-        <v>1898018420.64</v>
+        <v>1908371773.13</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3607,19 +3607,19 @@
         <v>72</v>
       </c>
       <c r="C36" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D36" s="7">
-        <v>0.206666</v>
+        <v>0.208376</v>
       </c>
       <c r="E36" s="8">
-        <v>1497553113.27</v>
+        <v>1497532573.31</v>
       </c>
       <c r="F36" s="9">
-        <v>32847</v>
+        <v>32846</v>
       </c>
       <c r="G36" s="8">
-        <v>309493548.82</v>
+        <v>312049839.81</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3630,19 +3630,19 @@
         <v>74</v>
       </c>
       <c r="C37" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D37" s="7">
-        <v>0.852645</v>
+        <v>0.862831</v>
       </c>
       <c r="E37" s="8">
-        <v>2449808911.95</v>
+        <v>2452816530.52</v>
       </c>
       <c r="F37" s="9">
-        <v>52474</v>
+        <v>52483</v>
       </c>
       <c r="G37" s="8">
-        <v>2088817831.3</v>
+        <v>2116365273.55</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3653,19 +3653,19 @@
         <v>76</v>
       </c>
       <c r="C38" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D38" s="10">
-        <v>0.17013</v>
+        <v>0.17036</v>
       </c>
       <c r="E38" s="8">
-        <v>3692021583.48</v>
+        <v>3693157195.13</v>
       </c>
       <c r="F38" s="9">
-        <v>53293</v>
+        <v>53288</v>
       </c>
       <c r="G38" s="8">
-        <v>628123386.87</v>
+        <v>629164491.21</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3676,19 +3676,19 @@
         <v>78</v>
       </c>
       <c r="C39" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D39" s="7">
-        <v>0.108348</v>
+        <v>0.108793</v>
       </c>
       <c r="E39" s="8">
-        <v>8146660542.96</v>
+        <v>8146474832.78</v>
       </c>
       <c r="F39" s="9">
-        <v>96867</v>
+        <v>96863</v>
       </c>
       <c r="G39" s="8">
-        <v>882671426.42</v>
+        <v>886276319.33</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3699,19 +3699,19 @@
         <v>80</v>
       </c>
       <c r="C40" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D40" s="7">
-        <v>0.340735</v>
+        <v>0.343953</v>
       </c>
       <c r="E40" s="8">
-        <v>14040961067.85</v>
+        <v>13959603661.07</v>
       </c>
       <c r="F40" s="9">
-        <v>156983</v>
+        <v>156799</v>
       </c>
       <c r="G40" s="8">
-        <v>4784250682.44</v>
+        <v>4801448064.11</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3722,19 +3722,19 @@
         <v>82</v>
       </c>
       <c r="C41" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D41" s="7">
-        <v>0.366844</v>
+        <v>0.367818</v>
       </c>
       <c r="E41" s="8">
-        <v>77389700525.54</v>
+        <v>77550254775.26</v>
       </c>
       <c r="F41" s="9">
-        <v>175168</v>
+        <v>161590</v>
       </c>
       <c r="G41" s="8">
-        <v>28389937919.39</v>
+        <v>28524409876.22</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3745,19 +3745,19 @@
         <v>84</v>
       </c>
       <c r="C42" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D42" s="7">
-        <v>0.963467</v>
+        <v>0.965888</v>
       </c>
       <c r="E42" s="8">
-        <v>12807879543.37</v>
+        <v>12805818135.13</v>
       </c>
       <c r="F42" s="9">
-        <v>234364</v>
+        <v>234224</v>
       </c>
       <c r="G42" s="8">
-        <v>12339968111.21</v>
+        <v>12368983658.34</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3768,19 +3768,19 @@
         <v>86</v>
       </c>
       <c r="C43" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D43" s="7">
-        <v>0.696166</v>
+        <v>0.697396</v>
       </c>
       <c r="E43" s="8">
-        <v>8800075425.75</v>
+        <v>8796740294.89</v>
       </c>
       <c r="F43" s="9">
-        <v>121231</v>
+        <v>121196</v>
       </c>
       <c r="G43" s="8">
-        <v>6126316946.53</v>
+        <v>6134807709.92</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3791,19 +3791,19 @@
         <v>88</v>
       </c>
       <c r="C44" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D44" s="7">
-        <v>3.055004</v>
+        <v>3.087802</v>
       </c>
       <c r="E44" s="8">
-        <v>8444703447.82</v>
+        <v>8446784645.98</v>
       </c>
       <c r="F44" s="9">
-        <v>366306</v>
+        <v>366479</v>
       </c>
       <c r="G44" s="8">
-        <v>25798600441.82</v>
+        <v>26081998231.64</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3814,19 +3814,19 @@
         <v>90</v>
       </c>
       <c r="C45" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D45" s="7">
-        <v>1.159979</v>
+        <v>1.169341</v>
       </c>
       <c r="E45" s="8">
-        <v>3677789987.95</v>
+        <v>3677251425.76</v>
       </c>
       <c r="F45" s="9">
-        <v>85803</v>
+        <v>85812</v>
       </c>
       <c r="G45" s="8">
-        <v>4266159995.87</v>
+        <v>4299959797.34</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3837,19 +3837,19 @@
         <v>92</v>
       </c>
       <c r="C46" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D46" s="7">
-        <v>0.425381</v>
+        <v>46150</v>
+      </c>
+      <c r="D46" s="10">
+        <v>0.42725</v>
       </c>
       <c r="E46" s="8">
-        <v>23847778764.48</v>
+        <v>23803237422.39</v>
       </c>
       <c r="F46" s="9">
-        <v>219281</v>
+        <v>219159</v>
       </c>
       <c r="G46" s="8">
-        <v>10144387163.63</v>
+        <v>10169938884.22</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3860,19 +3860,19 @@
         <v>94</v>
       </c>
       <c r="C47" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D47" s="7">
-        <v>1.020405</v>
+        <v>1.028081</v>
       </c>
       <c r="E47" s="8">
-        <v>9657328648.41</v>
+        <v>9653678140.9</v>
       </c>
       <c r="F47" s="9">
-        <v>207403</v>
+        <v>207397</v>
       </c>
       <c r="G47" s="8">
-        <v>9854385710.1</v>
+        <v>9924767353.89</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3883,19 +3883,19 @@
         <v>96</v>
       </c>
       <c r="C48" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D48" s="7">
-        <v>1.393359</v>
+        <v>1.411347</v>
       </c>
       <c r="E48" s="8">
-        <v>714973713.63</v>
+        <v>714672911.85</v>
       </c>
       <c r="F48" s="9">
-        <v>7287</v>
+        <v>7288</v>
       </c>
       <c r="G48" s="8">
-        <v>996214976.65</v>
+        <v>1008651519.58</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3906,19 +3906,19 @@
         <v>98</v>
       </c>
       <c r="C49" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D49" s="7">
-        <v>0.130742</v>
+        <v>0.130878</v>
       </c>
       <c r="E49" s="8">
-        <v>94269286394.84</v>
+        <v>94354981019.1</v>
       </c>
       <c r="F49" s="9">
-        <v>209156</v>
+        <v>209073</v>
       </c>
       <c r="G49" s="8">
-        <v>12324918120.42</v>
+        <v>12349008244.55</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3929,19 +3929,19 @@
         <v>100</v>
       </c>
       <c r="C50" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D50" s="7">
-        <v>0.099862</v>
+        <v>0.100081</v>
       </c>
       <c r="E50" s="8">
-        <v>13904569479.47</v>
+        <v>13849702369.62</v>
       </c>
       <c r="F50" s="9">
-        <v>130037</v>
+        <v>131803</v>
       </c>
       <c r="G50" s="8">
-        <v>1388532130.24</v>
+        <v>1386086298.61</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3952,19 +3952,19 @@
         <v>102</v>
       </c>
       <c r="C51" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D51" s="7">
-        <v>0.501523</v>
+        <v>0.507371</v>
       </c>
       <c r="E51" s="8">
-        <v>20381777364.58</v>
+        <v>20372435662.55</v>
       </c>
       <c r="F51" s="9">
-        <v>136659</v>
+        <v>136636</v>
       </c>
       <c r="G51" s="8">
-        <v>10221933555.68</v>
+        <v>10336377330.15</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3975,19 +3975,19 @@
         <v>104</v>
       </c>
       <c r="C52" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D52" s="7">
-        <v>0.216929</v>
+        <v>0.217543</v>
       </c>
       <c r="E52" s="8">
-        <v>2646305037.59</v>
+        <v>2655452436.66</v>
       </c>
       <c r="F52" s="9">
-        <v>10463</v>
+        <v>10467</v>
       </c>
       <c r="G52" s="8">
-        <v>574059593.33</v>
+        <v>577675580.49</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3998,19 +3998,19 @@
         <v>106</v>
       </c>
       <c r="C53" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D53" s="10">
-        <v>0.27585</v>
+        <v>46150</v>
+      </c>
+      <c r="D53" s="7">
+        <v>0.276567</v>
       </c>
       <c r="E53" s="8">
-        <v>2905387763.52</v>
+        <v>2925175367.89</v>
       </c>
       <c r="F53" s="9">
-        <v>10773</v>
+        <v>10787</v>
       </c>
       <c r="G53" s="8">
-        <v>801449924.2</v>
+        <v>809007756.84</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -4021,19 +4021,19 @@
         <v>108</v>
       </c>
       <c r="C54" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D54" s="7">
-        <v>0.335854</v>
+        <v>0.340062</v>
       </c>
       <c r="E54" s="8">
-        <v>4559785204.98</v>
+        <v>4563539261.61</v>
       </c>
       <c r="F54" s="9">
-        <v>15926</v>
+        <v>15924</v>
       </c>
       <c r="G54" s="8">
-        <v>1531420498.76</v>
+        <v>1551884963.95</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4044,19 +4044,19 @@
         <v>110</v>
       </c>
       <c r="C55" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D55" s="11">
-        <v>0.3166</v>
+        <v>46150</v>
+      </c>
+      <c r="D55" s="7">
+        <v>0.319945</v>
       </c>
       <c r="E55" s="8">
-        <v>2591081282.04</v>
+        <v>2594077428.15</v>
       </c>
       <c r="F55" s="9">
-        <v>10226</v>
+        <v>10222</v>
       </c>
       <c r="G55" s="8">
-        <v>820335107.89</v>
+        <v>829961183.44</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -4067,19 +4067,19 @@
         <v>112</v>
       </c>
       <c r="C56" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D56" s="7">
-        <v>0.224993</v>
+        <v>0.226645</v>
       </c>
       <c r="E56" s="8">
-        <v>1896938881.93</v>
+        <v>1898271261.01</v>
       </c>
       <c r="F56" s="9">
-        <v>6703</v>
+        <v>6697</v>
       </c>
       <c r="G56" s="8">
-        <v>426798031.99</v>
+        <v>430233540.42</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4090,19 +4090,19 @@
         <v>114</v>
       </c>
       <c r="C57" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D57" s="7">
-        <v>0.115588</v>
+        <v>0.116124</v>
       </c>
       <c r="E57" s="8">
-        <v>1630635570.19</v>
+        <v>1628699845.12</v>
       </c>
       <c r="F57" s="9">
-        <v>3912</v>
+        <v>3903</v>
       </c>
       <c r="G57" s="8">
-        <v>188482695.48</v>
+        <v>189131791.12</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -4113,19 +4113,19 @@
         <v>116</v>
       </c>
       <c r="C58" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D58" s="7">
-        <v>0.311631</v>
+        <v>0.316089</v>
       </c>
       <c r="E58" s="8">
-        <v>4461079324.04</v>
+        <v>4469793399.31</v>
       </c>
       <c r="F58" s="9">
-        <v>16830</v>
+        <v>16843</v>
       </c>
       <c r="G58" s="8">
-        <v>1390209952.15</v>
+        <v>1412851972.94</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -4136,19 +4136,19 @@
         <v>118</v>
       </c>
       <c r="C59" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D59" s="7">
-        <v>0.247023</v>
+        <v>0.250209</v>
       </c>
       <c r="E59" s="8">
-        <v>2824138641</v>
+        <v>2819624087.72</v>
       </c>
       <c r="F59" s="9">
-        <v>11368</v>
+        <v>11373</v>
       </c>
       <c r="G59" s="8">
-        <v>697626688.91</v>
+        <v>705495015.62</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -4159,19 +4159,19 @@
         <v>120</v>
       </c>
       <c r="C60" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D60" s="7">
-        <v>0.182226</v>
+        <v>0.182622</v>
       </c>
       <c r="E60" s="8">
-        <v>183372870.07</v>
+        <v>182897989.61</v>
       </c>
       <c r="F60" s="9">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="G60" s="8">
-        <v>33415383.21</v>
+        <v>33401216.31</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -4182,19 +4182,19 @@
         <v>122</v>
       </c>
       <c r="C61" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D61" s="7">
-        <v>0.385814</v>
+        <v>0.390249</v>
       </c>
       <c r="E61" s="8">
-        <v>859065206.88</v>
+        <v>858790007.86</v>
       </c>
       <c r="F61" s="9">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G61" s="8">
-        <v>331439709.21</v>
+        <v>335141989.78</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -4205,19 +4205,19 @@
         <v>124</v>
       </c>
       <c r="C62" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D62" s="10">
-        <v>0.07382</v>
+        <v>46150</v>
+      </c>
+      <c r="D62" s="7">
+        <v>0.074204</v>
       </c>
       <c r="E62" s="8">
-        <v>173610895.03</v>
+        <v>171966432.92</v>
       </c>
       <c r="F62" s="9">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G62" s="8">
-        <v>12815945.68</v>
+        <v>12760665.38</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -4228,19 +4228,19 @@
         <v>126</v>
       </c>
       <c r="C63" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D63" s="7">
-        <v>0.146833</v>
+        <v>0.147079</v>
       </c>
       <c r="E63" s="8">
-        <v>111329099.97</v>
+        <v>111708292.9</v>
       </c>
       <c r="F63" s="9">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G63" s="8">
-        <v>16346837.1</v>
+        <v>16429916.93</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -4251,19 +4251,19 @@
         <v>128</v>
       </c>
       <c r="C64" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D64" s="7">
-        <v>0.261664</v>
+        <v>0.264942</v>
       </c>
       <c r="E64" s="8">
-        <v>217278199.34</v>
+        <v>218178771.9</v>
       </c>
       <c r="F64" s="9">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G64" s="8">
-        <v>56853849.59</v>
+        <v>57804699.09</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4274,19 +4274,19 @@
         <v>130</v>
       </c>
       <c r="C65" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D65" s="7">
-        <v>0.339497</v>
+        <v>0.343866</v>
       </c>
       <c r="E65" s="8">
-        <v>639776426.4</v>
+        <v>640020979.33</v>
       </c>
       <c r="F65" s="9">
         <v>449</v>
       </c>
       <c r="G65" s="8">
-        <v>217202220.36</v>
+        <v>220081712.1</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -4297,19 +4297,19 @@
         <v>132</v>
       </c>
       <c r="C66" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D66" s="7">
-        <v>0.591204</v>
+        <v>0.597185</v>
       </c>
       <c r="E66" s="8">
-        <v>12890491061.41</v>
+        <v>12860826755.09</v>
       </c>
       <c r="F66" s="9">
-        <v>127305</v>
+        <v>127206</v>
       </c>
       <c r="G66" s="8">
-        <v>7620910426.85</v>
+        <v>7680295893.96</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4320,19 +4320,19 @@
         <v>134</v>
       </c>
       <c r="C67" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D67" s="7">
-        <v>0.268082</v>
+        <v>0.269475</v>
       </c>
       <c r="E67" s="8">
-        <v>2014291239.58</v>
+        <v>2020719598.65</v>
       </c>
       <c r="F67" s="9">
         <v>6125</v>
       </c>
       <c r="G67" s="8">
-        <v>539994431.48</v>
+        <v>544533121.61</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -4343,19 +4343,19 @@
         <v>136</v>
       </c>
       <c r="C68" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D68" s="7">
-        <v>2.062709</v>
+        <v>2.079029</v>
       </c>
       <c r="E68" s="8">
-        <v>7007732154.52</v>
+        <v>7001786448.44</v>
       </c>
       <c r="F68" s="9">
-        <v>236021</v>
+        <v>235908</v>
       </c>
       <c r="G68" s="8">
-        <v>14454911812.2</v>
+        <v>14556918457.06</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -4366,19 +4366,19 @@
         <v>138</v>
       </c>
       <c r="C69" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D69" s="7">
-        <v>1.014164</v>
+        <v>1.025001</v>
       </c>
       <c r="E69" s="8">
-        <v>6503707652.76</v>
+        <v>6495035397.1</v>
       </c>
       <c r="F69" s="9">
-        <v>163287</v>
+        <v>163231</v>
       </c>
       <c r="G69" s="8">
-        <v>6595824842.93</v>
+        <v>6657417725.99</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -4389,19 +4389,19 @@
         <v>140</v>
       </c>
       <c r="C70" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D70" s="7">
-        <v>0.334367</v>
+        <v>0.337797</v>
       </c>
       <c r="E70" s="8">
-        <v>12174179703.19</v>
+        <v>12174881686.48</v>
       </c>
       <c r="F70" s="9">
-        <v>189412</v>
+        <v>189404</v>
       </c>
       <c r="G70" s="8">
-        <v>4070647831.37</v>
+        <v>4112637172.04</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4412,19 +4412,19 @@
         <v>142</v>
       </c>
       <c r="C71" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D71" s="10">
-        <v>0.09904</v>
+        <v>46150</v>
+      </c>
+      <c r="D71" s="7">
+        <v>0.099261</v>
       </c>
       <c r="E71" s="8">
-        <v>7785151000.65</v>
+        <v>7773984867.65</v>
       </c>
       <c r="F71" s="9">
-        <v>124890</v>
+        <v>125554</v>
       </c>
       <c r="G71" s="8">
-        <v>771043619.97</v>
+        <v>771651687.67</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -4435,19 +4435,19 @@
         <v>144</v>
       </c>
       <c r="C72" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D72" s="7">
-        <v>0.097427</v>
+        <v>0.098029</v>
       </c>
       <c r="E72" s="8">
-        <v>390733902925.58</v>
+        <v>390405298761.8</v>
       </c>
       <c r="F72" s="9">
-        <v>1423043</v>
+        <v>1421962</v>
       </c>
       <c r="G72" s="8">
-        <v>38068161600.6</v>
+        <v>38271027604.75</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4458,19 +4458,19 @@
         <v>146</v>
       </c>
       <c r="C73" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D73" s="7">
-        <v>1.107664</v>
+        <v>1.111006</v>
       </c>
       <c r="E73" s="8">
-        <v>6404244193.02</v>
+        <v>6407486918.91</v>
       </c>
       <c r="F73" s="9">
-        <v>262188</v>
+        <v>261982</v>
       </c>
       <c r="G73" s="8">
-        <v>7093752141.09</v>
+        <v>7118757278.83</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4481,19 +4481,19 @@
         <v>148</v>
       </c>
       <c r="C74" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D74" s="7">
-        <v>0.511506</v>
+        <v>0.512492</v>
       </c>
       <c r="E74" s="8">
-        <v>6740081879.39</v>
+        <v>6729932372.7</v>
       </c>
       <c r="F74" s="9">
-        <v>65650</v>
+        <v>65596</v>
       </c>
       <c r="G74" s="8">
-        <v>3447595458.7</v>
+        <v>3449037871.47</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -4504,19 +4504,19 @@
         <v>150</v>
       </c>
       <c r="C75" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D75" s="7">
-        <v>1.585392</v>
+        <v>46150</v>
+      </c>
+      <c r="D75" s="10">
+        <v>1.59729</v>
       </c>
       <c r="E75" s="8">
-        <v>495634608.85</v>
+        <v>494490211.89</v>
       </c>
       <c r="F75" s="9">
-        <v>5016</v>
+        <v>5014</v>
       </c>
       <c r="G75" s="8">
-        <v>785775270.03</v>
+        <v>789844100.17</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4527,19 +4527,19 @@
         <v>152</v>
       </c>
       <c r="C76" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D76" s="10">
-        <v>0.70827</v>
+        <v>46150</v>
+      </c>
+      <c r="D76" s="7">
+        <v>0.718494</v>
       </c>
       <c r="E76" s="8">
-        <v>212574579464.87</v>
+        <v>212574134606.86</v>
       </c>
       <c r="F76" s="9">
-        <v>720792</v>
+        <v>721344</v>
       </c>
       <c r="G76" s="8">
-        <v>150560281149.83</v>
+        <v>152733241551.56</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4550,19 +4550,19 @@
         <v>154</v>
       </c>
       <c r="C77" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D77" s="7">
-        <v>0.587265</v>
+        <v>0.592307</v>
       </c>
       <c r="E77" s="8">
-        <v>194110655.97</v>
+        <v>194095302.98</v>
       </c>
       <c r="F77" s="9">
-        <v>22326</v>
+        <v>22325</v>
       </c>
       <c r="G77" s="8">
-        <v>113994485.09</v>
+        <v>114963929.34</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4573,19 +4573,19 @@
         <v>156</v>
       </c>
       <c r="C78" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D78" s="7">
-        <v>0.302319</v>
+        <v>46150</v>
+      </c>
+      <c r="D78" s="10">
+        <v>0.30582</v>
       </c>
       <c r="E78" s="8">
-        <v>397406594.94</v>
+        <v>397117564.51</v>
       </c>
       <c r="F78" s="9">
-        <v>33152</v>
+        <v>33149</v>
       </c>
       <c r="G78" s="8">
-        <v>120143734.16</v>
+        <v>121446475.57</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4596,19 +4596,19 @@
         <v>158</v>
       </c>
       <c r="C79" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D79" s="10">
-        <v>0.16321</v>
+        <v>46150</v>
+      </c>
+      <c r="D79" s="7">
+        <v>0.163565</v>
       </c>
       <c r="E79" s="8">
-        <v>3136026020.53</v>
+        <v>3136093538.7</v>
       </c>
       <c r="F79" s="9">
-        <v>6970</v>
+        <v>6978</v>
       </c>
       <c r="G79" s="8">
-        <v>511830975.52</v>
+        <v>512956605.04</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4619,19 +4619,19 @@
         <v>160</v>
       </c>
       <c r="C80" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D80" s="7">
-        <v>0.335667</v>
+        <v>0.336428</v>
       </c>
       <c r="E80" s="8">
-        <v>237992853.37</v>
+        <v>237546118.27</v>
       </c>
       <c r="F80" s="9">
-        <v>20869</v>
+        <v>20833</v>
       </c>
       <c r="G80" s="8">
-        <v>79886364.84</v>
+        <v>79917083.49</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4642,19 +4642,19 @@
         <v>162</v>
       </c>
       <c r="C81" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D81" s="7">
-        <v>0.183175</v>
+        <v>46150</v>
+      </c>
+      <c r="D81" s="10">
+        <v>0.18349</v>
       </c>
       <c r="E81" s="8">
-        <v>702439456.47</v>
+        <v>703075250.43</v>
       </c>
       <c r="F81" s="9">
         <v>2344</v>
       </c>
       <c r="G81" s="8">
-        <v>128669151.29</v>
+        <v>129007304.33</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4665,19 +4665,19 @@
         <v>164</v>
       </c>
       <c r="C82" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D82" s="7">
-        <v>1.922376</v>
+        <v>46150</v>
+      </c>
+      <c r="D82" s="10">
+        <v>1.95804</v>
       </c>
       <c r="E82" s="8">
-        <v>83860586.99</v>
+        <v>83877328.7</v>
       </c>
       <c r="F82" s="9">
-        <v>13722</v>
+        <v>13721</v>
       </c>
       <c r="G82" s="8">
-        <v>161211606.64</v>
+        <v>164235202.33</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4688,19 +4688,19 @@
         <v>166</v>
       </c>
       <c r="C83" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D83" s="7">
-        <v>0.095876</v>
+        <v>0.096111</v>
       </c>
       <c r="E83" s="8">
-        <v>10276427518.55</v>
+        <v>10345477982.52</v>
       </c>
       <c r="F83" s="9">
-        <v>173504</v>
+        <v>176437</v>
       </c>
       <c r="G83" s="8">
-        <v>985261228.96</v>
+        <v>994314358.83</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4711,19 +4711,19 @@
         <v>168</v>
       </c>
       <c r="C84" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D84" s="7">
-        <v>0.084095</v>
+        <v>0.084211</v>
       </c>
       <c r="E84" s="8">
-        <v>9095710148.33</v>
+        <v>9123999102.59</v>
       </c>
       <c r="F84" s="9">
-        <v>138536</v>
+        <v>140107</v>
       </c>
       <c r="G84" s="8">
-        <v>764903386.42</v>
+        <v>768340164.79</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4734,19 +4734,19 @@
         <v>170</v>
       </c>
       <c r="C85" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D85" s="7">
-        <v>0.274492</v>
+        <v>0.276402</v>
       </c>
       <c r="E85" s="8">
-        <v>4353968387.79</v>
+        <v>4368682414.98</v>
       </c>
       <c r="F85" s="9">
-        <v>80526</v>
+        <v>80842</v>
       </c>
       <c r="G85" s="8">
-        <v>1195130287.38</v>
+        <v>1207511998.26</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4757,19 +4757,19 @@
         <v>172</v>
       </c>
       <c r="C86" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D86" s="7">
-        <v>0.926643</v>
+        <v>0.931913</v>
       </c>
       <c r="E86" s="8">
-        <v>4620691309.77</v>
+        <v>4622216221.06</v>
       </c>
       <c r="F86" s="9">
-        <v>87581</v>
+        <v>87599</v>
       </c>
       <c r="G86" s="8">
-        <v>4281732487.81</v>
+        <v>4307502116.84</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4780,19 +4780,19 @@
         <v>174</v>
       </c>
       <c r="C87" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D87" s="7">
-        <v>0.226948</v>
+        <v>0.228921</v>
       </c>
       <c r="E87" s="8">
-        <v>12608931329.92</v>
+        <v>12601846776.95</v>
       </c>
       <c r="F87" s="9">
-        <v>144759</v>
+        <v>144729</v>
       </c>
       <c r="G87" s="8">
-        <v>2861566174.03</v>
+        <v>2884822677.76</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4803,19 +4803,19 @@
         <v>176</v>
       </c>
       <c r="C88" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D88" s="7">
-        <v>0.167955</v>
+        <v>0.169477</v>
       </c>
       <c r="E88" s="8">
-        <v>18622715968.85</v>
+        <v>18614699935.77</v>
       </c>
       <c r="F88" s="9">
-        <v>91387</v>
+        <v>91408</v>
       </c>
       <c r="G88" s="8">
-        <v>3127786845.9</v>
+        <v>3154758670.54</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4826,19 +4826,19 @@
         <v>178</v>
       </c>
       <c r="C89" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D89" s="7">
-        <v>0.638609</v>
+        <v>0.639956</v>
       </c>
       <c r="E89" s="8">
-        <v>2267322335.54</v>
+        <v>2267297720.12</v>
       </c>
       <c r="F89" s="9">
-        <v>35826</v>
+        <v>35796</v>
       </c>
       <c r="G89" s="8">
-        <v>1447931569.45</v>
+        <v>1450971370.72</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4849,19 +4849,19 @@
         <v>180</v>
       </c>
       <c r="C90" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D90" s="7">
-        <v>0.853145</v>
+        <v>0.856157</v>
       </c>
       <c r="E90" s="8">
-        <v>19169105652.7</v>
+        <v>19146669798.07</v>
       </c>
       <c r="F90" s="9">
-        <v>272019</v>
+        <v>271744</v>
       </c>
       <c r="G90" s="8">
-        <v>16354027243.1</v>
+        <v>16392553854.49</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4872,19 +4872,19 @@
         <v>182</v>
       </c>
       <c r="C91" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D91" s="7">
-        <v>0.804647</v>
+        <v>0.808095</v>
       </c>
       <c r="E91" s="8">
-        <v>3496258698.45</v>
+        <v>3497961193.65</v>
       </c>
       <c r="F91" s="9">
-        <v>29725</v>
+        <v>29828</v>
       </c>
       <c r="G91" s="8">
-        <v>2813252399.5</v>
+        <v>2826683829.95</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4895,19 +4895,19 @@
         <v>184</v>
       </c>
       <c r="C92" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D92" s="7">
-        <v>0.838331</v>
+        <v>0.840263</v>
       </c>
       <c r="E92" s="8">
-        <v>12335922204.96</v>
+        <v>12331789343.02</v>
       </c>
       <c r="F92" s="9">
-        <v>188485</v>
+        <v>188367</v>
       </c>
       <c r="G92" s="8">
-        <v>10341585577.84</v>
+        <v>10361952248.25</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4918,19 +4918,19 @@
         <v>186</v>
       </c>
       <c r="C93" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D93" s="7">
-        <v>0.088431</v>
+        <v>0.088536</v>
       </c>
       <c r="E93" s="8">
-        <v>7555002353.89</v>
+        <v>7576142445.63</v>
       </c>
       <c r="F93" s="9">
-        <v>154807</v>
+        <v>155400</v>
       </c>
       <c r="G93" s="8">
-        <v>668093507.54</v>
+        <v>670758972.25</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4941,19 +4941,19 @@
         <v>188</v>
       </c>
       <c r="C94" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D94" s="7">
-        <v>0.121604</v>
+        <v>46150</v>
+      </c>
+      <c r="D94" s="10">
+        <v>0.12228</v>
       </c>
       <c r="E94" s="8">
-        <v>11941078541.2</v>
+        <v>11898990412.4</v>
       </c>
       <c r="F94" s="9">
-        <v>33315</v>
+        <v>33305</v>
       </c>
       <c r="G94" s="8">
-        <v>1452083895.23</v>
+        <v>1455014177.9</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4964,19 +4964,19 @@
         <v>190</v>
       </c>
       <c r="C95" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D95" s="7">
-        <v>0.128197</v>
+        <v>46150</v>
+      </c>
+      <c r="D95" s="10">
+        <v>0.12833</v>
       </c>
       <c r="E95" s="8">
-        <v>71467359764.4</v>
+        <v>71284769530.83</v>
       </c>
       <c r="F95" s="9">
-        <v>212351</v>
+        <v>212337</v>
       </c>
       <c r="G95" s="8">
-        <v>9161931668.3</v>
+        <v>9147986496.95</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4987,19 +4987,19 @@
         <v>192</v>
       </c>
       <c r="C96" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D96" s="10">
-        <v>0.48045</v>
+        <v>46150</v>
+      </c>
+      <c r="D96" s="7">
+        <v>0.489602</v>
       </c>
       <c r="E96" s="8">
-        <v>32038664189.88</v>
+        <v>32141592043.95</v>
       </c>
       <c r="F96" s="9">
-        <v>284064</v>
+        <v>284670</v>
       </c>
       <c r="G96" s="8">
-        <v>15392974055.47</v>
+        <v>15736579598.09</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -5010,19 +5010,19 @@
         <v>194</v>
       </c>
       <c r="C97" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D97" s="10">
-        <v>0.09723</v>
+        <v>46150</v>
+      </c>
+      <c r="D97" s="7">
+        <v>0.097258</v>
       </c>
       <c r="E97" s="8">
-        <v>24549504624.79</v>
+        <v>24629668915.23</v>
       </c>
       <c r="F97" s="9">
-        <v>442390</v>
+        <v>443052</v>
       </c>
       <c r="G97" s="8">
-        <v>2386956301.64</v>
+        <v>2395435347.87</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -5033,19 +5033,19 @@
         <v>196</v>
       </c>
       <c r="C98" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D98" s="10">
-        <v>0.24541</v>
+        <v>46150</v>
+      </c>
+      <c r="D98" s="7">
+        <v>0.247754</v>
       </c>
       <c r="E98" s="8">
-        <v>1286314983.26</v>
+        <v>1266859072.13</v>
       </c>
       <c r="F98" s="9">
-        <v>7157</v>
+        <v>7142</v>
       </c>
       <c r="G98" s="8">
-        <v>315674979.11</v>
+        <v>313869069.87</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -5056,19 +5056,19 @@
         <v>198</v>
       </c>
       <c r="C99" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D99" s="7">
-        <v>1.060861</v>
+        <v>1.070352</v>
       </c>
       <c r="E99" s="8">
-        <v>4741875430.24</v>
+        <v>4838259049.96</v>
       </c>
       <c r="F99" s="9">
-        <v>48444</v>
+        <v>49280</v>
       </c>
       <c r="G99" s="8">
-        <v>5030469317.25</v>
+        <v>5178640270.8</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5079,19 +5079,19 @@
         <v>200</v>
       </c>
       <c r="C100" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D100" s="7">
-        <v>2.682165</v>
+        <v>2.716789</v>
       </c>
       <c r="E100" s="8">
-        <v>12017974352.05</v>
+        <v>12010183510.22</v>
       </c>
       <c r="F100" s="9">
-        <v>305972</v>
+        <v>306063</v>
       </c>
       <c r="G100" s="8">
-        <v>32234189335.27</v>
+        <v>32629139259.34</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5102,19 +5102,19 @@
         <v>202</v>
       </c>
       <c r="C101" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D101" s="7">
-        <v>0.356258</v>
+        <v>46150</v>
+      </c>
+      <c r="D101" s="10">
+        <v>0.36018</v>
       </c>
       <c r="E101" s="8">
-        <v>25780955799.87</v>
+        <v>25640243620.83</v>
       </c>
       <c r="F101" s="9">
-        <v>331635</v>
+        <v>331204</v>
       </c>
       <c r="G101" s="8">
-        <v>9184661296.89</v>
+        <v>9235109116.21</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5125,19 +5125,19 @@
         <v>204</v>
       </c>
       <c r="C102" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D102" s="7">
-        <v>0.369306</v>
+        <v>0.370288</v>
       </c>
       <c r="E102" s="8">
-        <v>202185679194.84</v>
+        <v>201844082193.83</v>
       </c>
       <c r="F102" s="9">
-        <v>371239</v>
+        <v>348142</v>
       </c>
       <c r="G102" s="8">
-        <v>74668307638.31</v>
+        <v>74740515215.2</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5148,19 +5148,19 @@
         <v>206</v>
       </c>
       <c r="C103" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D103" s="7">
-        <v>0.125604</v>
+        <v>46150</v>
+      </c>
+      <c r="D103" s="10">
+        <v>0.12632</v>
       </c>
       <c r="E103" s="8">
-        <v>9011692540.9</v>
+        <v>9029898220.86</v>
       </c>
       <c r="F103" s="9">
-        <v>28591</v>
+        <v>28599</v>
       </c>
       <c r="G103" s="8">
-        <v>1131900964.82</v>
+        <v>1140654794.56</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -5171,19 +5171,19 @@
         <v>208</v>
       </c>
       <c r="C104" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D104" s="7">
-        <v>0.288988</v>
+        <v>0.288727</v>
       </c>
       <c r="E104" s="8">
-        <v>1709744707.26</v>
+        <v>1706873054.3</v>
       </c>
       <c r="F104" s="9">
-        <v>7823</v>
+        <v>7822</v>
       </c>
       <c r="G104" s="8">
-        <v>494095841.9</v>
+        <v>492821052.33</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -5194,19 +5194,19 @@
         <v>210</v>
       </c>
       <c r="C105" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D105" s="7">
-        <v>0.010009</v>
+        <v>0.010019</v>
       </c>
       <c r="E105" s="8">
-        <v>119081896.75</v>
+        <v>160128666.15</v>
       </c>
       <c r="F105" s="9">
         <v>0</v>
       </c>
       <c r="G105" s="8">
-        <v>1191899.12</v>
+        <v>1604327.12</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5217,19 +5217,19 @@
         <v>212</v>
       </c>
       <c r="C106" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D106" s="7">
-        <v>1.084953</v>
+        <v>1.094633</v>
       </c>
       <c r="E106" s="8">
-        <v>254016599.22</v>
+        <v>254440244.45</v>
       </c>
       <c r="F106" s="9">
-        <v>4095</v>
+        <v>4103</v>
       </c>
       <c r="G106" s="8">
-        <v>275596070.45</v>
+        <v>278518565</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5240,19 +5240,19 @@
         <v>214</v>
       </c>
       <c r="C107" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D107" s="7">
-        <v>1.008659</v>
+        <v>1.014385</v>
       </c>
       <c r="E107" s="8">
-        <v>619921686.03</v>
+        <v>620784681.95</v>
       </c>
       <c r="F107" s="9">
-        <v>15505</v>
+        <v>15532</v>
       </c>
       <c r="G107" s="8">
-        <v>625289826.03</v>
+        <v>629714481.93</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -5263,19 +5263,19 @@
         <v>216</v>
       </c>
       <c r="C108" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D108" s="7">
-        <v>0.181089</v>
+        <v>0.183013</v>
       </c>
       <c r="E108" s="8">
-        <v>382029930.49</v>
+        <v>381733178.58</v>
       </c>
       <c r="F108" s="9">
         <v>1244</v>
       </c>
       <c r="G108" s="8">
-        <v>69181446.33</v>
+        <v>69861975.41</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -5286,19 +5286,19 @@
         <v>218</v>
       </c>
       <c r="C109" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D109" s="7">
-        <v>1.488158</v>
+        <v>1.496666</v>
       </c>
       <c r="E109" s="8">
-        <v>1023647980.26</v>
+        <v>1026685653.62</v>
       </c>
       <c r="F109" s="9">
-        <v>21967</v>
+        <v>21965</v>
       </c>
       <c r="G109" s="8">
-        <v>1523350228.45</v>
+        <v>1536605023.82</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -5309,19 +5309,19 @@
         <v>220</v>
       </c>
       <c r="C110" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D110" s="7">
-        <v>0.097775</v>
+        <v>0.098321</v>
       </c>
       <c r="E110" s="8">
-        <v>5473466049.3</v>
+        <v>5471229054.98</v>
       </c>
       <c r="F110" s="9">
-        <v>24355</v>
+        <v>24362</v>
       </c>
       <c r="G110" s="8">
-        <v>535169002.85</v>
+        <v>537937473.43</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5332,19 +5332,19 @@
         <v>222</v>
       </c>
       <c r="C111" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D111" s="7">
-        <v>0.288089</v>
+        <v>0.291408</v>
       </c>
       <c r="E111" s="8">
-        <v>1643520648.12</v>
+        <v>1644282707.97</v>
       </c>
       <c r="F111" s="9">
-        <v>33315</v>
+        <v>33333</v>
       </c>
       <c r="G111" s="8">
-        <v>473480692.74</v>
+        <v>479157766</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -5355,19 +5355,19 @@
         <v>224</v>
       </c>
       <c r="C112" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D112" s="7">
-        <v>0.217502</v>
+        <v>0.220491</v>
       </c>
       <c r="E112" s="8">
-        <v>590490399.81</v>
+        <v>590258075.49</v>
       </c>
       <c r="F112" s="9">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="G112" s="8">
-        <v>128433053.01</v>
+        <v>130146796</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -5378,19 +5378,19 @@
         <v>226</v>
       </c>
       <c r="C113" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D113" s="7">
-        <v>0.412799</v>
+        <v>0.414948</v>
       </c>
       <c r="E113" s="8">
-        <v>151283987.31</v>
+        <v>151450271.56</v>
       </c>
       <c r="F113" s="9">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="G113" s="8">
-        <v>62449931.02</v>
+        <v>62843936.87</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5401,19 +5401,19 @@
         <v>228</v>
       </c>
       <c r="C114" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D114" s="7">
-        <v>0.109143</v>
+        <v>0.110394</v>
       </c>
       <c r="E114" s="8">
-        <v>195680441.63</v>
+        <v>195682089.1</v>
       </c>
       <c r="F114" s="9">
         <v>888</v>
       </c>
       <c r="G114" s="8">
-        <v>21357089.33</v>
+        <v>21602180.75</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -5424,19 +5424,19 @@
         <v>230</v>
       </c>
       <c r="C115" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D115" s="7">
-        <v>0.064045</v>
+        <v>0.064947</v>
       </c>
       <c r="E115" s="8">
-        <v>1221038141420.98</v>
+        <v>1220651541204.3</v>
       </c>
       <c r="F115" s="9">
-        <v>789295</v>
+        <v>789358</v>
       </c>
       <c r="G115" s="8">
-        <v>78201751800.61</v>
+        <v>79278166195.31</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -5447,19 +5447,19 @@
         <v>232</v>
       </c>
       <c r="C116" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D116" s="7">
-        <v>0.015495</v>
+        <v>46150</v>
+      </c>
+      <c r="D116" s="10">
+        <v>0.01551</v>
       </c>
       <c r="E116" s="8">
-        <v>6818931272.91</v>
+        <v>6882839513.81</v>
       </c>
       <c r="F116" s="9">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="G116" s="8">
-        <v>105656498.58</v>
+        <v>106753881.03</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -5470,19 +5470,19 @@
         <v>234</v>
       </c>
       <c r="C117" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D117" s="7">
-        <v>0.127137</v>
+        <v>0.127579</v>
       </c>
       <c r="E117" s="8">
-        <v>7588565290.55</v>
+        <v>7612704373.79</v>
       </c>
       <c r="F117" s="9">
-        <v>24897</v>
+        <v>24923</v>
       </c>
       <c r="G117" s="8">
-        <v>964786425.77</v>
+        <v>971223484.62</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -5493,19 +5493,19 @@
         <v>236</v>
       </c>
       <c r="C118" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D118" s="7">
-        <v>0.130357</v>
+        <v>0.132026</v>
       </c>
       <c r="E118" s="8">
-        <v>29750933699.75</v>
+        <v>30268971190.16</v>
       </c>
       <c r="F118" s="9">
-        <v>70501</v>
+        <v>70879</v>
       </c>
       <c r="G118" s="8">
-        <v>3878241088.04</v>
+        <v>3996279892.77</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -5516,19 +5516,19 @@
         <v>238</v>
       </c>
       <c r="C119" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D119" s="7">
-        <v>0.574771</v>
+        <v>0.575794</v>
       </c>
       <c r="E119" s="8">
-        <v>91329672.85</v>
+        <v>91401396.95</v>
       </c>
       <c r="F119" s="9">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G119" s="8">
-        <v>52493648.33</v>
+        <v>52628342.05</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5539,19 +5539,19 @@
         <v>240</v>
       </c>
       <c r="C120" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D120" s="7">
-        <v>0.752912</v>
+        <v>46150</v>
+      </c>
+      <c r="D120" s="10">
+        <v>0.76238</v>
       </c>
       <c r="E120" s="8">
-        <v>22909549299.91</v>
+        <v>22905718841.14</v>
       </c>
       <c r="F120" s="9">
-        <v>149776</v>
+        <v>149766</v>
       </c>
       <c r="G120" s="8">
-        <v>17248870686.08</v>
+        <v>17462860645.86</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5562,19 +5562,19 @@
         <v>242</v>
       </c>
       <c r="C121" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D121" s="7">
-        <v>0.123532</v>
+        <v>0.123915</v>
       </c>
       <c r="E121" s="8">
-        <v>14714699269.85</v>
+        <v>14556892557.33</v>
       </c>
       <c r="F121" s="9">
-        <v>44612</v>
+        <v>44596</v>
       </c>
       <c r="G121" s="8">
-        <v>1817743197.45</v>
+        <v>1803822213.26</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -5585,19 +5585,19 @@
         <v>244</v>
       </c>
       <c r="C122" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D122" s="7">
-        <v>0.106514</v>
+        <v>0.107279</v>
       </c>
       <c r="E122" s="8">
-        <v>42860005411.4</v>
+        <v>42824864809.27</v>
       </c>
       <c r="F122" s="9">
-        <v>338137</v>
+        <v>338026</v>
       </c>
       <c r="G122" s="8">
-        <v>4565200711.13</v>
+        <v>4594213026.85</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -5608,19 +5608,19 @@
         <v>246</v>
       </c>
       <c r="C123" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D123" s="7">
-        <v>0.093859</v>
+        <v>0.094631</v>
       </c>
       <c r="E123" s="8">
-        <v>9714228312.98</v>
+        <v>9715190213.78</v>
       </c>
       <c r="F123" s="9">
-        <v>148016</v>
+        <v>148094</v>
       </c>
       <c r="G123" s="8">
-        <v>911765343.67</v>
+        <v>919359882.44</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -5631,19 +5631,19 @@
         <v>248</v>
       </c>
       <c r="C124" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D124" s="7">
-        <v>0.048788</v>
+        <v>0.048816</v>
       </c>
       <c r="E124" s="8">
-        <v>28015667646.57</v>
+        <v>28053393731.79</v>
       </c>
       <c r="F124" s="9">
-        <v>34646</v>
+        <v>34663</v>
       </c>
       <c r="G124" s="8">
-        <v>1366822735.22</v>
+        <v>1369461614.88</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5654,19 +5654,19 @@
         <v>250</v>
       </c>
       <c r="C125" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D125" s="7">
-        <v>0.119022</v>
+        <v>0.120163</v>
       </c>
       <c r="E125" s="8">
-        <v>6295578001.25</v>
+        <v>6292228740.58</v>
       </c>
       <c r="F125" s="9">
-        <v>43195</v>
+        <v>43181</v>
       </c>
       <c r="G125" s="8">
-        <v>749314238.8</v>
+        <v>756093237.86</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5677,19 +5677,19 @@
         <v>252</v>
       </c>
       <c r="C126" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D126" s="7">
-        <v>0.091397</v>
+        <v>0.091827</v>
       </c>
       <c r="E126" s="8">
-        <v>2968794572.58</v>
+        <v>2976836665.76</v>
       </c>
       <c r="F126" s="9">
-        <v>83532</v>
+        <v>83624</v>
       </c>
       <c r="G126" s="8">
-        <v>271340294.61</v>
+        <v>273355004.37</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5700,19 +5700,19 @@
         <v>254</v>
       </c>
       <c r="C127" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D127" s="7">
-        <v>0.084587</v>
+        <v>0.085187</v>
       </c>
       <c r="E127" s="8">
-        <v>1128155178.56</v>
+        <v>1127968576.55</v>
       </c>
       <c r="F127" s="9">
-        <v>122899</v>
+        <v>122891</v>
       </c>
       <c r="G127" s="8">
-        <v>95427412.44</v>
+        <v>96088804.27</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5723,19 +5723,19 @@
         <v>256</v>
       </c>
       <c r="C128" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D128" s="10">
-        <v>0.77669</v>
+        <v>46150</v>
+      </c>
+      <c r="D128" s="7">
+        <v>0.781992</v>
       </c>
       <c r="E128" s="8">
-        <v>1638316790.8</v>
+        <v>1637521567.32</v>
       </c>
       <c r="F128" s="9">
-        <v>49930</v>
+        <v>49927</v>
       </c>
       <c r="G128" s="8">
-        <v>1272464007.19</v>
+        <v>1280528004.88</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5746,19 +5746,19 @@
         <v>258</v>
       </c>
       <c r="C129" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D129" s="7">
-        <v>0.148856</v>
+        <v>0.150258</v>
       </c>
       <c r="E129" s="8">
-        <v>1298235667.08</v>
+        <v>1297284164.54</v>
       </c>
       <c r="F129" s="9">
-        <v>12560</v>
+        <v>12557</v>
       </c>
       <c r="G129" s="8">
-        <v>193249629.98</v>
+        <v>194926969.92</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5769,19 +5769,19 @@
         <v>260</v>
       </c>
       <c r="C130" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D130" s="7">
-        <v>0.239459</v>
+        <v>0.241736</v>
       </c>
       <c r="E130" s="8">
-        <v>5189405759.69</v>
+        <v>5188346889.48</v>
       </c>
       <c r="F130" s="9">
-        <v>69496</v>
+        <v>69488</v>
       </c>
       <c r="G130" s="8">
-        <v>1242650049.22</v>
+        <v>1254207802.24</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5792,19 +5792,19 @@
         <v>262</v>
       </c>
       <c r="C131" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D131" s="7">
-        <v>1.879445</v>
+        <v>1.902875</v>
       </c>
       <c r="E131" s="8">
-        <v>2372424151.46</v>
+        <v>2374373481.78</v>
       </c>
       <c r="F131" s="9">
-        <v>52974</v>
+        <v>52990</v>
       </c>
       <c r="G131" s="8">
-        <v>4458840657.93</v>
+        <v>4518135212.8</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5815,19 +5815,19 @@
         <v>264</v>
       </c>
       <c r="C132" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D132" s="7">
-        <v>0.357403</v>
+        <v>0.362194</v>
       </c>
       <c r="E132" s="8">
-        <v>556520232.91</v>
+        <v>553891808.81</v>
       </c>
       <c r="F132" s="9">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G132" s="8">
-        <v>198901969.8</v>
+        <v>200616282.66</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5838,19 +5838,19 @@
         <v>266</v>
       </c>
       <c r="C133" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D133" s="7">
-        <v>0.161927</v>
+        <v>0.163046</v>
       </c>
       <c r="E133" s="8">
-        <v>132522243.19</v>
+        <v>133106869.86</v>
       </c>
       <c r="F133" s="9">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G133" s="8">
-        <v>21458948.29</v>
+        <v>21702592.55</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,19 +5861,19 @@
         <v>268</v>
       </c>
       <c r="C134" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D134" s="7">
-        <v>0.707543</v>
+        <v>0.708369</v>
       </c>
       <c r="E134" s="8">
-        <v>1257408026.82</v>
+        <v>1256641469.42</v>
       </c>
       <c r="F134" s="9">
-        <v>21164</v>
+        <v>21150</v>
       </c>
       <c r="G134" s="8">
-        <v>889670737.48</v>
+        <v>890166312.44</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5884,19 +5884,19 @@
         <v>270</v>
       </c>
       <c r="C135" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D135" s="7">
-        <v>0.371589</v>
+        <v>0.372602</v>
       </c>
       <c r="E135" s="8">
-        <v>7438502397.88</v>
+        <v>7401122466.5</v>
       </c>
       <c r="F135" s="9">
-        <v>90723</v>
+        <v>89571</v>
       </c>
       <c r="G135" s="8">
-        <v>2764065891.86</v>
+        <v>2757674875.95</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5907,19 +5907,19 @@
         <v>272</v>
       </c>
       <c r="C136" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D136" s="7">
-        <v>0.205619</v>
+        <v>0.207041</v>
       </c>
       <c r="E136" s="8">
-        <v>199077640.63</v>
+        <v>199891057.23</v>
       </c>
       <c r="F136" s="9">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G136" s="8">
-        <v>40934187.7</v>
+        <v>41385586.05</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5930,19 +5930,19 @@
         <v>274</v>
       </c>
       <c r="C137" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D137" s="7">
-        <v>0.266268</v>
+        <v>0.269684</v>
       </c>
       <c r="E137" s="8">
-        <v>404767982.87</v>
+        <v>403726642.45</v>
       </c>
       <c r="F137" s="9">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="G137" s="8">
-        <v>107776948.62</v>
+        <v>108878674.09</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5953,19 +5953,19 @@
         <v>276</v>
       </c>
       <c r="C138" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D138" s="7">
-        <v>0.101136</v>
+        <v>0.101305</v>
       </c>
       <c r="E138" s="8">
-        <v>295406079.77</v>
+        <v>295208405.4</v>
       </c>
       <c r="F138" s="9">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G138" s="8">
-        <v>29876091.08</v>
+        <v>29905988.92</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5976,19 +5976,19 @@
         <v>278</v>
       </c>
       <c r="C139" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D139" s="7">
-        <v>0.404042</v>
+        <v>0.410069</v>
       </c>
       <c r="E139" s="8">
-        <v>630538168.58</v>
+        <v>629521236.76</v>
       </c>
       <c r="F139" s="9">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="G139" s="8">
-        <v>254763990.98</v>
+        <v>258147303.36</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5999,19 +5999,19 @@
         <v>280</v>
       </c>
       <c r="C140" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D140" s="7">
-        <v>0.702328</v>
+        <v>0.704213</v>
       </c>
       <c r="E140" s="8">
-        <v>2932809723.24</v>
+        <v>2931436906.69</v>
       </c>
       <c r="F140" s="9">
-        <v>42012</v>
+        <v>41994</v>
       </c>
       <c r="G140" s="8">
-        <v>2059794924.91</v>
+        <v>2064357180.87</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -6022,19 +6022,19 @@
         <v>282</v>
       </c>
       <c r="C141" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D141" s="7">
-        <v>0.014252</v>
+        <v>0.014381</v>
       </c>
       <c r="E141" s="8">
-        <v>2874514460.59</v>
+        <v>2922760157.91</v>
       </c>
       <c r="F141" s="9">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="G141" s="8">
-        <v>40966308.3</v>
+        <v>42031879.99</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -6045,19 +6045,19 @@
         <v>284</v>
       </c>
       <c r="C142" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D142" s="7">
-        <v>0.076375</v>
+        <v>0.077649</v>
       </c>
       <c r="E142" s="8">
-        <v>22239381445.22</v>
+        <v>22391491969.24</v>
       </c>
       <c r="F142" s="9">
-        <v>23555</v>
+        <v>23581</v>
       </c>
       <c r="G142" s="8">
-        <v>1698533405.33</v>
+        <v>1738679931.87</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -6068,19 +6068,19 @@
         <v>286</v>
       </c>
       <c r="C143" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D143" s="10">
-        <v>0.28631</v>
+        <v>46150</v>
+      </c>
+      <c r="D143" s="7">
+        <v>0.289662</v>
       </c>
       <c r="E143" s="8">
-        <v>20716363049.97</v>
+        <v>20751706142.13</v>
       </c>
       <c r="F143" s="9">
-        <v>4725</v>
+        <v>4722</v>
       </c>
       <c r="G143" s="8">
-        <v>5931307552.01</v>
+        <v>6010976167.11</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -6091,19 +6091,19 @@
         <v>288</v>
       </c>
       <c r="C144" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D144" s="7">
-        <v>0.090903</v>
+        <v>0.091103</v>
       </c>
       <c r="E144" s="8">
-        <v>652853993.67</v>
+        <v>655883756.65</v>
       </c>
       <c r="F144" s="9">
-        <v>11030</v>
+        <v>11120</v>
       </c>
       <c r="G144" s="8">
-        <v>59346547.63</v>
+        <v>59753233.74</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -6114,19 +6114,19 @@
         <v>290</v>
       </c>
       <c r="C145" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D145" s="7">
-        <v>0.054312</v>
+        <v>0.054762</v>
       </c>
       <c r="E145" s="8">
-        <v>1422152327.93</v>
+        <v>1444946832.01</v>
       </c>
       <c r="F145" s="9">
         <v>316</v>
       </c>
       <c r="G145" s="8">
-        <v>77239476.17</v>
+        <v>79128858.37</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -6137,19 +6137,19 @@
         <v>292</v>
       </c>
       <c r="C146" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D146" s="7">
-        <v>0.114329</v>
+        <v>0.114594</v>
       </c>
       <c r="E146" s="8">
-        <v>1809987757.49</v>
+        <v>1799189079.45</v>
       </c>
       <c r="F146" s="9">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="G146" s="8">
-        <v>206933302.63</v>
+        <v>206176098.9</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6160,19 +6160,19 @@
         <v>294</v>
       </c>
       <c r="C147" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D147" s="7">
-        <v>0.114326</v>
+        <v>0.114772</v>
       </c>
       <c r="E147" s="8">
-        <v>1966256581.28</v>
+        <v>1969923994.26</v>
       </c>
       <c r="F147" s="9">
-        <v>65271</v>
+        <v>65319</v>
       </c>
       <c r="G147" s="8">
-        <v>224793590.77</v>
+        <v>226092862.59</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -6183,19 +6183,19 @@
         <v>296</v>
       </c>
       <c r="C148" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D148" s="7">
-        <v>0.077339</v>
+        <v>46150</v>
+      </c>
+      <c r="D148" s="10">
+        <v>0.07783</v>
       </c>
       <c r="E148" s="8">
-        <v>571255665.49</v>
+        <v>571128155.18</v>
       </c>
       <c r="F148" s="9">
-        <v>52202</v>
+        <v>52198</v>
       </c>
       <c r="G148" s="8">
-        <v>44180315.54</v>
+        <v>44451118.74</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6206,19 +6206,19 @@
         <v>298</v>
       </c>
       <c r="C149" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D149" s="7">
-        <v>0.082561</v>
+        <v>0.082666</v>
       </c>
       <c r="E149" s="8">
-        <v>359688320.98</v>
+        <v>359843196.94</v>
       </c>
       <c r="F149" s="9">
-        <v>9528</v>
+        <v>9529</v>
       </c>
       <c r="G149" s="8">
-        <v>29696352.06</v>
+        <v>29746863.35</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -6229,19 +6229,19 @@
         <v>300</v>
       </c>
       <c r="C150" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D150" s="7">
-        <v>0.371849</v>
+        <v>46150</v>
+      </c>
+      <c r="D150" s="10">
+        <v>0.37263</v>
       </c>
       <c r="E150" s="8">
-        <v>145647084.28</v>
+        <v>145664338.5</v>
       </c>
       <c r="F150" s="9">
         <v>1767</v>
       </c>
       <c r="G150" s="8">
-        <v>54158655.77</v>
+        <v>54278971.61</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6252,19 +6252,19 @@
         <v>302</v>
       </c>
       <c r="C151" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D151" s="7">
-        <v>0.099297</v>
+        <v>0.100114</v>
       </c>
       <c r="E151" s="8">
-        <v>335382392.88</v>
+        <v>339710223.95</v>
       </c>
       <c r="F151" s="9">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="G151" s="8">
-        <v>33302460.07</v>
+        <v>34009749.18</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -6275,19 +6275,19 @@
         <v>304</v>
       </c>
       <c r="C152" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D152" s="10">
-        <v>0.29742</v>
+        <v>46150</v>
+      </c>
+      <c r="D152" s="7">
+        <v>0.299053</v>
       </c>
       <c r="E152" s="8">
-        <v>142310737.35</v>
+        <v>142166395.48</v>
       </c>
       <c r="F152" s="9">
         <v>204</v>
       </c>
       <c r="G152" s="8">
-        <v>42326054.37</v>
+        <v>42515292.31</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -6298,19 +6298,19 @@
         <v>306</v>
       </c>
       <c r="C153" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D153" s="7">
-        <v>0.118094</v>
+        <v>0.118403</v>
       </c>
       <c r="E153" s="8">
-        <v>589345421.92</v>
+        <v>584766465.87</v>
       </c>
       <c r="F153" s="9">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G153" s="8">
-        <v>69598160.54</v>
+        <v>69237881.24</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -6321,19 +6321,19 @@
         <v>308</v>
       </c>
       <c r="C154" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D154" s="7">
-        <v>0.406413</v>
+        <v>0.409638</v>
       </c>
       <c r="E154" s="8">
-        <v>1303315599.83</v>
+        <v>1302581819.51</v>
       </c>
       <c r="F154" s="9">
         <v>127</v>
       </c>
       <c r="G154" s="8">
-        <v>529684545.16</v>
+        <v>533587085.05</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -6344,19 +6344,19 @@
         <v>310</v>
       </c>
       <c r="C155" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D155" s="7">
-        <v>0.519524</v>
+        <v>0.526554</v>
       </c>
       <c r="E155" s="8">
-        <v>593663442.68</v>
+        <v>591068636.76</v>
       </c>
       <c r="F155" s="9">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G155" s="8">
-        <v>308422622.41</v>
+        <v>311229438.27</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -6367,19 +6367,19 @@
         <v>312</v>
       </c>
       <c r="C156" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D156" s="7">
-        <v>1.738748</v>
+        <v>1.753384</v>
       </c>
       <c r="E156" s="8">
-        <v>912543060.5</v>
+        <v>913288141.5</v>
       </c>
       <c r="F156" s="9">
-        <v>10187</v>
+        <v>10182</v>
       </c>
       <c r="G156" s="8">
-        <v>1586681984.79</v>
+        <v>1601345072.24</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -6390,19 +6390,19 @@
         <v>314</v>
       </c>
       <c r="C157" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D157" s="7">
-        <v>0.283231</v>
+        <v>0.284468</v>
       </c>
       <c r="E157" s="8">
-        <v>185011822.91</v>
+        <v>185236093.82</v>
       </c>
       <c r="F157" s="9">
         <v>94</v>
       </c>
       <c r="G157" s="8">
-        <v>52401096.33</v>
+        <v>52693653.28</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -6413,19 +6413,19 @@
         <v>316</v>
       </c>
       <c r="C158" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D158" s="7">
-        <v>0.144389</v>
+        <v>0.145577</v>
       </c>
       <c r="E158" s="8">
-        <v>4600642586.23</v>
+        <v>4600469471.17</v>
       </c>
       <c r="F158" s="9">
-        <v>28822</v>
+        <v>28811</v>
       </c>
       <c r="G158" s="8">
-        <v>664284003.84</v>
+        <v>669722061.66</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -6436,19 +6436,19 @@
         <v>318</v>
       </c>
       <c r="C159" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D159" s="7">
-        <v>0.167544</v>
+        <v>0.167995</v>
       </c>
       <c r="E159" s="8">
-        <v>3289667050.24</v>
+        <v>3257171963.03</v>
       </c>
       <c r="F159" s="9">
-        <v>12071</v>
+        <v>12079</v>
       </c>
       <c r="G159" s="8">
-        <v>551162811.28</v>
+        <v>547189314.35</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -6459,19 +6459,19 @@
         <v>320</v>
       </c>
       <c r="C160" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D160" s="7">
-        <v>0.708039</v>
+        <v>0.713643</v>
       </c>
       <c r="E160" s="8">
-        <v>766311723.02</v>
+        <v>768922555.94</v>
       </c>
       <c r="F160" s="9">
         <v>5171</v>
       </c>
       <c r="G160" s="8">
-        <v>542578537.67</v>
+        <v>548736459.2</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -6482,19 +6482,19 @@
         <v>322</v>
       </c>
       <c r="C161" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D161" s="7">
-        <v>0.382881</v>
+        <v>0.386167</v>
       </c>
       <c r="E161" s="8">
-        <v>1341079135.48</v>
+        <v>1341636565.63</v>
       </c>
       <c r="F161" s="9">
-        <v>23893</v>
+        <v>23884</v>
       </c>
       <c r="G161" s="8">
-        <v>513474105.07</v>
+        <v>518095607.83</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -6505,19 +6505,19 @@
         <v>324</v>
       </c>
       <c r="C162" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D162" s="10">
-        <v>0.37657</v>
+        <v>46150</v>
+      </c>
+      <c r="D162" s="7">
+        <v>0.383448</v>
       </c>
       <c r="E162" s="8">
-        <v>168480863.33</v>
+        <v>167986884.35</v>
       </c>
       <c r="F162" s="9">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G162" s="8">
-        <v>63444906.55</v>
+        <v>64414210.98</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -6528,19 +6528,19 @@
         <v>326</v>
       </c>
       <c r="C163" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D163" s="7">
-        <v>0.144811</v>
+        <v>0.146014</v>
       </c>
       <c r="E163" s="8">
-        <v>1026666583.99</v>
+        <v>1029640914.05</v>
       </c>
       <c r="F163" s="9">
-        <v>2973</v>
+        <v>2967</v>
       </c>
       <c r="G163" s="8">
-        <v>148672577.18</v>
+        <v>150341523.03</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -6551,19 +6551,19 @@
         <v>328</v>
       </c>
       <c r="C164" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D164" s="7">
-        <v>0.119729</v>
+        <v>0.120604</v>
       </c>
       <c r="E164" s="8">
-        <v>7567145891.84</v>
+        <v>7564667867.1</v>
       </c>
       <c r="F164" s="9">
-        <v>79740</v>
+        <v>79719</v>
       </c>
       <c r="G164" s="8">
-        <v>906003226.04</v>
+        <v>912331781.77</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -6574,19 +6574,19 @@
         <v>330</v>
       </c>
       <c r="C165" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D165" s="7">
-        <v>0.109532</v>
+        <v>0.110368</v>
       </c>
       <c r="E165" s="8">
-        <v>3331717479.64</v>
+        <v>3332013971.03</v>
       </c>
       <c r="F165" s="9">
-        <v>64872</v>
+        <v>64871</v>
       </c>
       <c r="G165" s="8">
-        <v>364930266.58</v>
+        <v>367747960.23</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -6597,19 +6597,19 @@
         <v>332</v>
       </c>
       <c r="C166" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D166" s="7">
-        <v>0.014865</v>
+        <v>0.015044</v>
       </c>
       <c r="E166" s="8">
-        <v>429915174732.2</v>
+        <v>430264096515.55</v>
       </c>
       <c r="F166" s="9">
-        <v>73844</v>
+        <v>74116</v>
       </c>
       <c r="G166" s="8">
-        <v>6390507872.03</v>
+        <v>6473018776.66</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -6620,19 +6620,19 @@
         <v>334</v>
       </c>
       <c r="C167" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D167" s="7">
-        <v>0.364857</v>
+        <v>0.367573</v>
       </c>
       <c r="E167" s="8">
-        <v>691801222.85</v>
+        <v>692504655.12</v>
       </c>
       <c r="F167" s="9">
-        <v>6876</v>
+        <v>6867</v>
       </c>
       <c r="G167" s="8">
-        <v>252408618.55</v>
+        <v>254546119.52</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6643,19 +6643,19 @@
         <v>336</v>
       </c>
       <c r="C168" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D168" s="7">
-        <v>0.014211</v>
+        <v>0.014279</v>
       </c>
       <c r="E168" s="8">
-        <v>36031790269.18</v>
+        <v>37329423540.19</v>
       </c>
       <c r="F168" s="9">
-        <v>6102</v>
+        <v>6217</v>
       </c>
       <c r="G168" s="8">
-        <v>512038046.24</v>
+        <v>533036152.44</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6666,19 +6666,19 @@
         <v>338</v>
       </c>
       <c r="C169" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D169" s="7">
-        <v>0.697667</v>
+        <v>0.703421</v>
       </c>
       <c r="E169" s="8">
-        <v>1941433538.84</v>
+        <v>1941739652.41</v>
       </c>
       <c r="F169" s="9">
-        <v>32778</v>
+        <v>32780</v>
       </c>
       <c r="G169" s="8">
-        <v>1354473202.7</v>
+        <v>1365859881.19</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6689,19 +6689,19 @@
         <v>340</v>
       </c>
       <c r="C170" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D170" s="7">
-        <v>0.389289</v>
+        <v>0.390277</v>
       </c>
       <c r="E170" s="8">
-        <v>1984541260.1</v>
+        <v>1985688575.1</v>
       </c>
       <c r="F170" s="9">
-        <v>21003</v>
+        <v>20989</v>
       </c>
       <c r="G170" s="8">
-        <v>772560394.3</v>
+        <v>774969368.88</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6712,19 +6712,19 @@
         <v>342</v>
       </c>
       <c r="C171" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D171" s="7">
-        <v>0.140961</v>
+        <v>0.142943</v>
       </c>
       <c r="E171" s="8">
-        <v>1566809784.57</v>
+        <v>1570228424.04</v>
       </c>
       <c r="F171" s="9">
-        <v>16344</v>
+        <v>16337</v>
       </c>
       <c r="G171" s="8">
-        <v>220858346.51</v>
+        <v>224452391.98</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6735,19 +6735,19 @@
         <v>344</v>
       </c>
       <c r="C172" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D172" s="7">
-        <v>1.273356</v>
+        <v>1.287107</v>
       </c>
       <c r="E172" s="8">
-        <v>1397103360.42</v>
+        <v>1396211302.83</v>
       </c>
       <c r="F172" s="9">
-        <v>23894</v>
+        <v>23897</v>
       </c>
       <c r="G172" s="8">
-        <v>1779009820.61</v>
+        <v>1797072912.6</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6758,19 +6758,19 @@
         <v>346</v>
       </c>
       <c r="C173" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D173" s="7">
-        <v>0.573284</v>
+        <v>0.574793</v>
       </c>
       <c r="E173" s="8">
-        <v>2358193429.94</v>
+        <v>2358794522.61</v>
       </c>
       <c r="F173" s="9">
-        <v>34874</v>
+        <v>34854</v>
       </c>
       <c r="G173" s="8">
-        <v>1351915629.91</v>
+        <v>1355818927.03</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6781,19 +6781,19 @@
         <v>348</v>
       </c>
       <c r="C174" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D174" s="7">
-        <v>0.017646</v>
+        <v>0.017726</v>
       </c>
       <c r="E174" s="8">
-        <v>74964377808.5</v>
+        <v>76621808152.66</v>
       </c>
       <c r="F174" s="9">
-        <v>18002</v>
+        <v>18176</v>
       </c>
       <c r="G174" s="8">
-        <v>1322815672.78</v>
+        <v>1358226874.75</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6804,19 +6804,19 @@
         <v>350</v>
       </c>
       <c r="C175" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D175" s="7">
-        <v>0.090051</v>
+        <v>0.090755</v>
       </c>
       <c r="E175" s="8">
-        <v>2209331109.01</v>
+        <v>2210112565.92</v>
       </c>
       <c r="F175" s="9">
-        <v>5198</v>
+        <v>5188</v>
       </c>
       <c r="G175" s="8">
-        <v>198952276.19</v>
+        <v>200578202.5</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6827,19 +6827,19 @@
         <v>352</v>
       </c>
       <c r="C176" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D176" s="7">
-        <v>0.122252</v>
+        <v>0.122495</v>
       </c>
       <c r="E176" s="8">
-        <v>1636074762.6</v>
+        <v>1645424448.87</v>
       </c>
       <c r="F176" s="9">
         <v>1207</v>
       </c>
       <c r="G176" s="8">
-        <v>200013981.7</v>
+        <v>201556910.5</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6850,19 +6850,19 @@
         <v>354</v>
       </c>
       <c r="C177" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D177" s="7">
-        <v>0.315881</v>
+        <v>0.319584</v>
       </c>
       <c r="E177" s="8">
-        <v>749542167.66</v>
+        <v>747940786.57</v>
       </c>
       <c r="F177" s="9">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="G177" s="8">
-        <v>236766021.86</v>
+        <v>239029773.9</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6873,19 +6873,19 @@
         <v>356</v>
       </c>
       <c r="C178" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D178" s="7">
-        <v>0.091728</v>
+        <v>0.092378</v>
       </c>
       <c r="E178" s="8">
-        <v>41876476157.66</v>
+        <v>41857770756.89</v>
       </c>
       <c r="F178" s="9">
-        <v>283604</v>
+        <v>283513</v>
       </c>
       <c r="G178" s="8">
-        <v>3841262637.95</v>
+        <v>3866753900.13</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6896,19 +6896,19 @@
         <v>358</v>
       </c>
       <c r="C179" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D179" s="7">
-        <v>0.065632</v>
+        <v>0.066288</v>
       </c>
       <c r="E179" s="8">
-        <v>670307394.4</v>
+        <v>671606758.11</v>
       </c>
       <c r="F179" s="9">
-        <v>6098</v>
+        <v>6096</v>
       </c>
       <c r="G179" s="8">
-        <v>43993698.31</v>
+        <v>44519707.93</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6919,19 +6919,19 @@
         <v>360</v>
       </c>
       <c r="C180" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D180" s="7">
-        <v>0.252359</v>
+        <v>0.254887</v>
       </c>
       <c r="E180" s="8">
-        <v>549744958.44</v>
+        <v>550481589.68</v>
       </c>
       <c r="F180" s="9">
-        <v>1767</v>
+        <v>1771</v>
       </c>
       <c r="G180" s="8">
-        <v>138732939.67</v>
+        <v>140310631.21</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6942,19 +6942,19 @@
         <v>362</v>
       </c>
       <c r="C181" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D181" s="7">
-        <v>0.399349</v>
+        <v>0.401244</v>
       </c>
       <c r="E181" s="8">
-        <v>369653486.74</v>
+        <v>368800463.5</v>
       </c>
       <c r="F181" s="9">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="G181" s="8">
-        <v>147620577.25</v>
+        <v>147979031.15</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6965,19 +6965,19 @@
         <v>364</v>
       </c>
       <c r="C182" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D182" s="7">
-        <v>0.112166</v>
+        <v>0.112956</v>
       </c>
       <c r="E182" s="8">
-        <v>14346562715.78</v>
+        <v>14384830435.97</v>
       </c>
       <c r="F182" s="9">
-        <v>32173</v>
+        <v>32165</v>
       </c>
       <c r="G182" s="8">
-        <v>1609196839.4</v>
+        <v>1624858604.41</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6988,19 +6988,19 @@
         <v>366</v>
       </c>
       <c r="C183" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D183" s="7">
-        <v>0.116063</v>
+        <v>0.116338</v>
       </c>
       <c r="E183" s="8">
-        <v>23298175959.61</v>
+        <v>23347380027.81</v>
       </c>
       <c r="F183" s="9">
-        <v>42183</v>
+        <v>43228</v>
       </c>
       <c r="G183" s="8">
-        <v>2704062436.59</v>
+        <v>2716182827.13</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7011,19 +7011,19 @@
         <v>368</v>
       </c>
       <c r="C184" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D184" s="7">
-        <v>0.097336</v>
+        <v>0.098619</v>
       </c>
       <c r="E184" s="8">
-        <v>31473375092.69</v>
+        <v>31718299258.14</v>
       </c>
       <c r="F184" s="9">
-        <v>30109</v>
+        <v>30189</v>
       </c>
       <c r="G184" s="8">
-        <v>3063477394.87</v>
+        <v>3128017243.91</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7034,19 +7034,19 @@
         <v>370</v>
       </c>
       <c r="C185" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D185" s="7">
-        <v>0.085948</v>
+        <v>0.086751</v>
       </c>
       <c r="E185" s="8">
-        <v>6420642577.08</v>
+        <v>6419711190.68</v>
       </c>
       <c r="F185" s="9">
-        <v>5035</v>
+        <v>5032</v>
       </c>
       <c r="G185" s="8">
-        <v>551839892.96</v>
+        <v>556914461.45</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7057,19 +7057,19 @@
         <v>372</v>
       </c>
       <c r="C186" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D186" s="7">
-        <v>0.073561</v>
+        <v>0.074013</v>
       </c>
       <c r="E186" s="8">
-        <v>14116376889.64</v>
+        <v>14150842904.22</v>
       </c>
       <c r="F186" s="9">
-        <v>184447</v>
+        <v>184494</v>
       </c>
       <c r="G186" s="8">
-        <v>1038418976.95</v>
+        <v>1047345897.28</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7080,19 +7080,19 @@
         <v>374</v>
       </c>
       <c r="C187" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D187" s="7">
-        <v>0.099658</v>
+        <v>0.099804</v>
       </c>
       <c r="E187" s="8">
-        <v>4089747856.28</v>
+        <v>4091813935.09</v>
       </c>
       <c r="F187" s="9">
-        <v>117648</v>
+        <v>117655</v>
       </c>
       <c r="G187" s="8">
-        <v>407575011.58</v>
+        <v>408377399.58</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7103,19 +7103,19 @@
         <v>376</v>
       </c>
       <c r="C188" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D188" s="7">
-        <v>0.246151</v>
+        <v>0.246319</v>
       </c>
       <c r="E188" s="8">
-        <v>669703264.62</v>
+        <v>669705038.39</v>
       </c>
       <c r="F188" s="9">
-        <v>1964</v>
+        <v>1960</v>
       </c>
       <c r="G188" s="8">
-        <v>164847849.8</v>
+        <v>164961242.47</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7126,19 +7126,19 @@
         <v>378</v>
       </c>
       <c r="C189" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D189" s="7">
-        <v>0.085144</v>
+        <v>0.085314</v>
       </c>
       <c r="E189" s="8">
-        <v>2837636560.25</v>
+        <v>2820086267.8</v>
       </c>
       <c r="F189" s="9">
-        <v>43577</v>
+        <v>43634</v>
       </c>
       <c r="G189" s="8">
-        <v>241606494.24</v>
+        <v>240594240.62</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7149,19 +7149,19 @@
         <v>380</v>
       </c>
       <c r="C190" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D190" s="7">
-        <v>0.246442</v>
+        <v>0.247215</v>
       </c>
       <c r="E190" s="8">
-        <v>3389280599.11</v>
+        <v>3380816216.46</v>
       </c>
       <c r="F190" s="9">
-        <v>6640</v>
+        <v>6656</v>
       </c>
       <c r="G190" s="8">
-        <v>835260933.56</v>
+        <v>835788878.61</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7172,19 +7172,19 @@
         <v>382</v>
       </c>
       <c r="C191" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D191" s="7">
-        <v>0.163573</v>
+        <v>0.164394</v>
       </c>
       <c r="E191" s="8">
-        <v>708015323.76</v>
+        <v>705967565.52</v>
       </c>
       <c r="F191" s="9">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="G191" s="8">
-        <v>115812133.61</v>
+        <v>116056600.68</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7195,19 +7195,19 @@
         <v>384</v>
       </c>
       <c r="C192" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D192" s="7">
-        <v>0.151777</v>
+        <v>0.152768</v>
       </c>
       <c r="E192" s="8">
-        <v>491503823.48</v>
+        <v>491029668.92</v>
       </c>
       <c r="F192" s="9">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="G192" s="8">
-        <v>74599002.9</v>
+        <v>75013819</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7218,19 +7218,19 @@
         <v>386</v>
       </c>
       <c r="C193" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D193" s="7">
-        <v>0.102669</v>
+        <v>0.103051</v>
       </c>
       <c r="E193" s="8">
-        <v>1166853199.17</v>
+        <v>1166207275.68</v>
       </c>
       <c r="F193" s="9">
-        <v>117361</v>
+        <v>117344</v>
       </c>
       <c r="G193" s="8">
-        <v>119799273.15</v>
+        <v>120179365.39</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7241,19 +7241,19 @@
         <v>388</v>
       </c>
       <c r="C194" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D194" s="7">
-        <v>0.204395</v>
+        <v>0.206349</v>
       </c>
       <c r="E194" s="8">
-        <v>1999540238.22</v>
+        <v>2001950031.65</v>
       </c>
       <c r="F194" s="9">
-        <v>1601</v>
+        <v>1607</v>
       </c>
       <c r="G194" s="8">
-        <v>408696670.92</v>
+        <v>413099387.34</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7264,19 +7264,19 @@
         <v>390</v>
       </c>
       <c r="C195" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D195" s="7">
-        <v>0.159316</v>
+        <v>0.159915</v>
       </c>
       <c r="E195" s="8">
-        <v>596667517.77</v>
+        <v>597348055.97</v>
       </c>
       <c r="F195" s="9">
         <v>2662</v>
       </c>
       <c r="G195" s="8">
-        <v>95058412.45</v>
+        <v>95524819.25</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7287,19 +7287,19 @@
         <v>392</v>
       </c>
       <c r="C196" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D196" s="7">
-        <v>0.276581</v>
+        <v>0.279006</v>
       </c>
       <c r="E196" s="8">
-        <v>2773306816.86</v>
+        <v>2759113409.56</v>
       </c>
       <c r="F196" s="9">
-        <v>7677</v>
+        <v>7655</v>
       </c>
       <c r="G196" s="8">
-        <v>767043400.17</v>
+        <v>769808096.38</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7310,19 +7310,19 @@
         <v>394</v>
       </c>
       <c r="C197" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D197" s="7">
-        <v>0.099843</v>
+        <v>0.099963</v>
       </c>
       <c r="E197" s="8">
-        <v>104280898.99</v>
+        <v>104564320.35</v>
       </c>
       <c r="F197" s="9">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="G197" s="8">
-        <v>10411672.17</v>
+        <v>10452572.99</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7333,19 +7333,19 @@
         <v>396</v>
       </c>
       <c r="C198" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D198" s="7">
-        <v>0.226244</v>
+        <v>0.227046</v>
       </c>
       <c r="E198" s="8">
-        <v>324740843.14</v>
+        <v>326653641.77</v>
       </c>
       <c r="F198" s="9">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="G198" s="8">
-        <v>73470621.61</v>
+        <v>74165321.14</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7356,19 +7356,19 @@
         <v>398</v>
       </c>
       <c r="C199" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D199" s="7">
-        <v>0.178946</v>
+        <v>0.179536</v>
       </c>
       <c r="E199" s="8">
-        <v>273125635.62</v>
+        <v>272491889.39</v>
       </c>
       <c r="F199" s="9">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G199" s="8">
-        <v>48874716.69</v>
+        <v>48922005.59</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7379,19 +7379,19 @@
         <v>400</v>
       </c>
       <c r="C200" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D200" s="7">
-        <v>0.088166</v>
+        <v>0.088257</v>
       </c>
       <c r="E200" s="8">
-        <v>2710842293.57</v>
+        <v>2725097908.49</v>
       </c>
       <c r="F200" s="9">
-        <v>40818</v>
+        <v>41148</v>
       </c>
       <c r="G200" s="8">
-        <v>239005213.25</v>
+        <v>240508486.95</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7402,19 +7402,19 @@
         <v>402</v>
       </c>
       <c r="C201" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D201" s="10">
-        <v>0.09037</v>
+        <v>46150</v>
+      </c>
+      <c r="D201" s="7">
+        <v>0.090738</v>
       </c>
       <c r="E201" s="8">
-        <v>832459092.48</v>
+        <v>831484470.96</v>
       </c>
       <c r="F201" s="9">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="G201" s="8">
-        <v>75229068.47</v>
+        <v>75447383.27</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7425,19 +7425,19 @@
         <v>404</v>
       </c>
       <c r="C202" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D202" s="7">
-        <v>0.153519</v>
+        <v>0.154747</v>
       </c>
       <c r="E202" s="8">
-        <v>9564542554</v>
+        <v>9536203304.11</v>
       </c>
       <c r="F202" s="9">
-        <v>9376</v>
+        <v>9365</v>
       </c>
       <c r="G202" s="8">
-        <v>1468340630.76</v>
+        <v>1475699642.8</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7448,19 +7448,19 @@
         <v>406</v>
       </c>
       <c r="C203" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D203" s="7">
-        <v>0.014728</v>
+        <v>0.014821</v>
       </c>
       <c r="E203" s="8">
-        <v>8841692998.14</v>
+        <v>8818195864.33</v>
       </c>
       <c r="F203" s="9">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="G203" s="8">
-        <v>130220732.6</v>
+        <v>130698029.05</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7471,19 +7471,19 @@
         <v>408</v>
       </c>
       <c r="C204" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D204" s="7">
-        <v>0.028654</v>
+        <v>0.028815</v>
       </c>
       <c r="E204" s="8">
-        <v>1333213673.34</v>
+        <v>1382173180.06</v>
       </c>
       <c r="F204" s="9">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="G204" s="8">
-        <v>38201719.59</v>
+        <v>39827978.32</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7494,19 +7494,19 @@
         <v>410</v>
       </c>
       <c r="C205" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D205" s="10">
-        <v>0.12046</v>
+        <v>0.12113</v>
       </c>
       <c r="E205" s="8">
-        <v>3212156838.31</v>
+        <v>3211316539.11</v>
       </c>
       <c r="F205" s="9">
-        <v>311777</v>
+        <v>311709</v>
       </c>
       <c r="G205" s="8">
-        <v>386937161.61</v>
+        <v>388985767.88</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -7517,19 +7517,19 @@
         <v>412</v>
       </c>
       <c r="C206" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D206" s="7">
-        <v>0.158446</v>
+        <v>0.158849</v>
       </c>
       <c r="E206" s="8">
-        <v>525690686.51</v>
+        <v>522322804.49</v>
       </c>
       <c r="F206" s="9">
-        <v>985</v>
+        <v>1028</v>
       </c>
       <c r="G206" s="8">
-        <v>83293461.86</v>
+        <v>82970713.44</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7540,19 +7540,19 @@
         <v>414</v>
       </c>
       <c r="C207" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D207" s="7">
-        <v>0.133979</v>
+        <v>0.134375</v>
       </c>
       <c r="E207" s="8">
-        <v>2879037208.78</v>
+        <v>2871320094.65</v>
       </c>
       <c r="F207" s="9">
-        <v>5777</v>
+        <v>5785</v>
       </c>
       <c r="G207" s="8">
-        <v>385730565.98</v>
+        <v>385832500.29</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7563,19 +7563,19 @@
         <v>416</v>
       </c>
       <c r="C208" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D208" s="7">
-        <v>0.105695</v>
+        <v>0.106201</v>
       </c>
       <c r="E208" s="8">
-        <v>4322073196.21</v>
+        <v>4319441794.28</v>
       </c>
       <c r="F208" s="9">
-        <v>348043</v>
+        <v>347903</v>
       </c>
       <c r="G208" s="8">
-        <v>456822093.41</v>
+        <v>458730583.86</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7586,19 +7586,19 @@
         <v>418</v>
       </c>
       <c r="C209" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D209" s="7">
-        <v>0.107175</v>
+        <v>0.107372</v>
       </c>
       <c r="E209" s="8">
-        <v>46584181917.18</v>
+        <v>46723624827.08</v>
       </c>
       <c r="F209" s="9">
-        <v>712946</v>
+        <v>713941</v>
       </c>
       <c r="G209" s="8">
-        <v>4992656980.25</v>
+        <v>5016807440.95</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7609,19 +7609,19 @@
         <v>420</v>
       </c>
       <c r="C210" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D210" s="7">
-        <v>0.066308</v>
+        <v>0.067194</v>
       </c>
       <c r="E210" s="8">
-        <v>59567611813.45</v>
+        <v>60483583800.12</v>
       </c>
       <c r="F210" s="9">
-        <v>60932</v>
+        <v>61150</v>
       </c>
       <c r="G210" s="8">
-        <v>3949807326.85</v>
+        <v>4064143878.63</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -7632,19 +7632,19 @@
         <v>422</v>
       </c>
       <c r="C211" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D211" s="7">
-        <v>0.107465</v>
+        <v>0.108205</v>
       </c>
       <c r="E211" s="8">
-        <v>65102116711.92</v>
+        <v>65312951351.97</v>
       </c>
       <c r="F211" s="9">
-        <v>914990</v>
+        <v>916174</v>
       </c>
       <c r="G211" s="8">
-        <v>6996191010.94</v>
+        <v>7067187877.49</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7655,19 +7655,19 @@
         <v>424</v>
       </c>
       <c r="C212" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D212" s="10">
-        <v>0.07002</v>
+        <v>46150</v>
+      </c>
+      <c r="D212" s="7">
+        <v>0.070108</v>
       </c>
       <c r="E212" s="8">
-        <v>54451457214.73</v>
+        <v>54414424164.45</v>
       </c>
       <c r="F212" s="9">
-        <v>55475</v>
+        <v>55368</v>
       </c>
       <c r="G212" s="8">
-        <v>3812682895.51</v>
+        <v>3814898602.47</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7678,19 +7678,19 @@
         <v>426</v>
       </c>
       <c r="C213" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D213" s="10">
-        <v>0.09759</v>
+        <v>46150</v>
+      </c>
+      <c r="D213" s="7">
+        <v>0.097821</v>
       </c>
       <c r="E213" s="8">
-        <v>16681723463.59</v>
+        <v>16593260702.87</v>
       </c>
       <c r="F213" s="9">
-        <v>355773</v>
+        <v>353424</v>
       </c>
       <c r="G213" s="8">
-        <v>1627964968.55</v>
+        <v>1623166357.4</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -7701,19 +7701,19 @@
         <v>428</v>
       </c>
       <c r="C214" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D214" s="7">
-        <v>0.052023</v>
+        <v>0.052357</v>
       </c>
       <c r="E214" s="8">
-        <v>82401478640.36</v>
+        <v>82047091893.47</v>
       </c>
       <c r="F214" s="9">
-        <v>34583</v>
+        <v>34387</v>
       </c>
       <c r="G214" s="8">
-        <v>4286813263.55</v>
+        <v>4295743383.36</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7724,19 +7724,19 @@
         <v>430</v>
       </c>
       <c r="C215" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D215" s="7">
-        <v>0.086134</v>
+        <v>0.086229</v>
       </c>
       <c r="E215" s="8">
-        <v>14077629084.75</v>
+        <v>14088405239.86</v>
       </c>
       <c r="F215" s="9">
-        <v>239866</v>
+        <v>240892</v>
       </c>
       <c r="G215" s="8">
-        <v>1212567327.2</v>
+        <v>1214833673.5</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -7747,19 +7747,19 @@
         <v>432</v>
       </c>
       <c r="C216" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D216" s="7">
-        <v>0.323301</v>
+        <v>0.324995</v>
       </c>
       <c r="E216" s="8">
-        <v>12278510439.75</v>
+        <v>12295542427.21</v>
       </c>
       <c r="F216" s="9">
-        <v>58168</v>
+        <v>58329</v>
       </c>
       <c r="G216" s="8">
-        <v>3969659353.13</v>
+        <v>3995986219.11</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -7770,19 +7770,19 @@
         <v>434</v>
       </c>
       <c r="C217" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D217" s="7">
-        <v>0.228574</v>
+        <v>0.229714</v>
       </c>
       <c r="E217" s="8">
-        <v>10516647808.31</v>
+        <v>10576662587.73</v>
       </c>
       <c r="F217" s="9">
-        <v>39874</v>
+        <v>40030</v>
       </c>
       <c r="G217" s="8">
-        <v>2403827424.51</v>
+        <v>2429604311.78</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7793,19 +7793,19 @@
         <v>436</v>
       </c>
       <c r="C218" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D218" s="7">
-        <v>1.032568</v>
+        <v>46150</v>
+      </c>
+      <c r="D218" s="10">
+        <v>1.04064</v>
       </c>
       <c r="E218" s="8">
-        <v>744900010.76</v>
+        <v>742518994.81</v>
       </c>
       <c r="F218" s="9">
-        <v>4355</v>
+        <v>4348</v>
       </c>
       <c r="G218" s="8">
-        <v>769159707.67</v>
+        <v>772695046.34</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -7816,19 +7816,19 @@
         <v>438</v>
       </c>
       <c r="C219" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D219" s="7">
-        <v>0.743126</v>
+        <v>46150</v>
+      </c>
+      <c r="D219" s="10">
+        <v>0.74846</v>
       </c>
       <c r="E219" s="8">
-        <v>5942613020.42</v>
+        <v>5924499081.71</v>
       </c>
       <c r="F219" s="9">
-        <v>11085</v>
+        <v>11080</v>
       </c>
       <c r="G219" s="8">
-        <v>4416107656.75</v>
+        <v>4434253344.34</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -7839,19 +7839,19 @@
         <v>440</v>
       </c>
       <c r="C220" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D220" s="7">
-        <v>2.922205</v>
+        <v>2.942882</v>
       </c>
       <c r="E220" s="8">
-        <v>6243934754.81</v>
+        <v>6240124205.58</v>
       </c>
       <c r="F220" s="9">
-        <v>273111</v>
+        <v>273147</v>
       </c>
       <c r="G220" s="8">
-        <v>18246056606.72</v>
+        <v>18363951867.92</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -7862,19 +7862,19 @@
         <v>442</v>
       </c>
       <c r="C221" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D221" s="7">
-        <v>0.407764</v>
+        <v>46150</v>
+      </c>
+      <c r="D221" s="10">
+        <v>0.41214</v>
       </c>
       <c r="E221" s="8">
-        <v>9345801414.39</v>
+        <v>9304832434.92</v>
       </c>
       <c r="F221" s="9">
-        <v>165092</v>
+        <v>164990</v>
       </c>
       <c r="G221" s="8">
-        <v>3810878333.19</v>
+        <v>3834891946.66</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -7885,19 +7885,19 @@
         <v>444</v>
       </c>
       <c r="C222" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D222" s="7">
-        <v>0.396451</v>
+        <v>0.397371</v>
       </c>
       <c r="E222" s="8">
-        <v>178410279765.12</v>
+        <v>179023802942.09</v>
       </c>
       <c r="F222" s="9">
-        <v>393977</v>
+        <v>389376</v>
       </c>
       <c r="G222" s="8">
-        <v>70730997487.36</v>
+        <v>71138844987.55</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -7908,19 +7908,19 @@
         <v>446</v>
       </c>
       <c r="C223" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D223" s="7">
-        <v>0.155304</v>
+        <v>0.155506</v>
       </c>
       <c r="E223" s="8">
-        <v>6423078703.83</v>
+        <v>6445019648.37</v>
       </c>
       <c r="F223" s="9">
-        <v>25308</v>
+        <v>25333</v>
       </c>
       <c r="G223" s="8">
-        <v>997530116.88</v>
+        <v>1002237167.88</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -7931,19 +7931,19 @@
         <v>448</v>
       </c>
       <c r="C224" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D224" s="7">
-        <v>0.521746</v>
+        <v>0.522133</v>
       </c>
       <c r="E224" s="8">
-        <v>8115563695.93</v>
+        <v>8118545582.44</v>
       </c>
       <c r="F224" s="9">
-        <v>35682</v>
+        <v>35622</v>
       </c>
       <c r="G224" s="8">
-        <v>4234266866.51</v>
+        <v>4238960776.57</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -7954,19 +7954,19 @@
         <v>450</v>
       </c>
       <c r="C225" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D225" s="10">
-        <v>0.07549</v>
+        <v>46150</v>
+      </c>
+      <c r="D225" s="7">
+        <v>0.076435</v>
       </c>
       <c r="E225" s="8">
-        <v>2508767269157.75</v>
+        <v>2507060473433.83</v>
       </c>
       <c r="F225" s="9">
-        <v>1246445</v>
+        <v>1246439</v>
       </c>
       <c r="G225" s="8">
-        <v>189386861948.34</v>
+        <v>191626605441.81</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -7977,19 +7977,19 @@
         <v>452</v>
       </c>
       <c r="C226" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D226" s="7">
-        <v>0.075428</v>
+        <v>0.075928</v>
       </c>
       <c r="E226" s="8">
-        <v>26772877737.59</v>
+        <v>26765085154.1</v>
       </c>
       <c r="F226" s="9">
-        <v>95246</v>
+        <v>95215</v>
       </c>
       <c r="G226" s="8">
-        <v>2019412053.4</v>
+        <v>2032229230.81</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -8000,19 +8000,19 @@
         <v>454</v>
       </c>
       <c r="C227" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D227" s="7">
-        <v>0.015674</v>
+        <v>0.016345</v>
       </c>
       <c r="E227" s="8">
-        <v>516535408120.48</v>
+        <v>515435195849.71</v>
       </c>
       <c r="F227" s="9">
-        <v>50712</v>
+        <v>50504</v>
       </c>
       <c r="G227" s="8">
-        <v>8096427388.66</v>
+        <v>8424702240.91</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8023,19 +8023,19 @@
         <v>456</v>
       </c>
       <c r="C228" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D228" s="7">
-        <v>0.797026</v>
+        <v>0.808958</v>
       </c>
       <c r="E228" s="8">
-        <v>170496040204.36</v>
+        <v>170535540887.52</v>
       </c>
       <c r="F228" s="9">
-        <v>824633</v>
+        <v>825575</v>
       </c>
       <c r="G228" s="8">
-        <v>135889756664.64</v>
+        <v>137956068432.97</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8046,19 +8046,19 @@
         <v>458</v>
       </c>
       <c r="C229" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D229" s="7">
-        <v>0.140383</v>
+        <v>0.141555</v>
       </c>
       <c r="E229" s="8">
-        <v>26932191052.58</v>
+        <v>26943726090.06</v>
       </c>
       <c r="F229" s="9">
-        <v>194686</v>
+        <v>194674</v>
       </c>
       <c r="G229" s="8">
-        <v>3780818039.97</v>
+        <v>3814015534.98</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8069,19 +8069,19 @@
         <v>460</v>
       </c>
       <c r="C230" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D230" s="7">
-        <v>1.132637</v>
+        <v>46150</v>
+      </c>
+      <c r="D230" s="10">
+        <v>1.14178</v>
       </c>
       <c r="E230" s="8">
-        <v>2630230561.67</v>
+        <v>2626367425.42</v>
       </c>
       <c r="F230" s="9">
-        <v>49117</v>
+        <v>49096</v>
       </c>
       <c r="G230" s="8">
-        <v>2979097533.45</v>
+        <v>2998734540.57</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8092,19 +8092,19 @@
         <v>462</v>
       </c>
       <c r="C231" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D231" s="7">
-        <v>0.283651</v>
+        <v>0.286908</v>
       </c>
       <c r="E231" s="8">
-        <v>2497539748.36</v>
+        <v>2495069521.58</v>
       </c>
       <c r="F231" s="9">
-        <v>11234</v>
+        <v>11224</v>
       </c>
       <c r="G231" s="8">
-        <v>708430422.1</v>
+        <v>715854523.87</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8115,19 +8115,19 @@
         <v>464</v>
       </c>
       <c r="C232" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D232" s="7">
-        <v>1.136039</v>
+        <v>1.138231</v>
       </c>
       <c r="E232" s="8">
-        <v>5219221658.95</v>
+        <v>5209814669.13</v>
       </c>
       <c r="F232" s="9">
-        <v>63528</v>
+        <v>63428</v>
       </c>
       <c r="G232" s="8">
-        <v>5929237819.34</v>
+        <v>5929974579.67</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8138,19 +8138,19 @@
         <v>466</v>
       </c>
       <c r="C233" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D233" s="7">
-        <v>0.387433</v>
+        <v>0.390069</v>
       </c>
       <c r="E233" s="8">
-        <v>18900609652.22</v>
+        <v>18977095021.61</v>
       </c>
       <c r="F233" s="9">
-        <v>151249</v>
+        <v>151508</v>
       </c>
       <c r="G233" s="8">
-        <v>7322727495.08</v>
+        <v>7402378451.15</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8161,19 +8161,19 @@
         <v>468</v>
       </c>
       <c r="C234" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D234" s="7">
-        <v>0.109666</v>
+        <v>0.110371</v>
       </c>
       <c r="E234" s="8">
-        <v>281834531667.72</v>
+        <v>281672040270.51</v>
       </c>
       <c r="F234" s="9">
-        <v>1528947</v>
+        <v>1528521</v>
       </c>
       <c r="G234" s="8">
-        <v>30907665077.37</v>
+        <v>31088311292.73</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8184,19 +8184,19 @@
         <v>470</v>
       </c>
       <c r="C235" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D235" s="7">
-        <v>0.271022</v>
+        <v>0.273363</v>
       </c>
       <c r="E235" s="8">
-        <v>3288037594.32</v>
+        <v>3290829201.44</v>
       </c>
       <c r="F235" s="9">
-        <v>10547</v>
+        <v>10543</v>
       </c>
       <c r="G235" s="8">
-        <v>891131165.43</v>
+        <v>899591504.32</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8207,19 +8207,19 @@
         <v>472</v>
       </c>
       <c r="C236" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D236" s="7">
-        <v>0.794292</v>
+        <v>46150</v>
+      </c>
+      <c r="D236" s="10">
+        <v>0.79582</v>
       </c>
       <c r="E236" s="8">
-        <v>1340017828.88</v>
+        <v>1337975831.24</v>
       </c>
       <c r="F236" s="9">
-        <v>7629</v>
+        <v>7626</v>
       </c>
       <c r="G236" s="8">
-        <v>1064365322.56</v>
+        <v>1064788473.1</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8230,19 +8230,19 @@
         <v>474</v>
       </c>
       <c r="C237" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D237" s="7">
-        <v>0.155265</v>
+        <v>46150</v>
+      </c>
+      <c r="D237" s="10">
+        <v>0.15605</v>
       </c>
       <c r="E237" s="8">
-        <v>72046067031.07</v>
+        <v>71964353110.16</v>
       </c>
       <c r="F237" s="9">
-        <v>841553</v>
+        <v>841317</v>
       </c>
       <c r="G237" s="8">
-        <v>11186223232.04</v>
+        <v>11230071684.03</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -8253,19 +8253,19 @@
         <v>476</v>
       </c>
       <c r="C238" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D238" s="7">
-        <v>0.227602</v>
+        <v>0.229247</v>
       </c>
       <c r="E238" s="8">
-        <v>2451882239.22</v>
+        <v>2441066461.42</v>
       </c>
       <c r="F238" s="9">
-        <v>7595</v>
+        <v>7585</v>
       </c>
       <c r="G238" s="8">
-        <v>558054524.66</v>
+        <v>559608359.34</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -8276,19 +8276,19 @@
         <v>478</v>
       </c>
       <c r="C239" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D239" s="7">
-        <v>0.200523</v>
+        <v>0.201929</v>
       </c>
       <c r="E239" s="8">
-        <v>2343249191.72</v>
+        <v>2346664763.22</v>
       </c>
       <c r="F239" s="9">
-        <v>7377</v>
+        <v>7369</v>
       </c>
       <c r="G239" s="8">
-        <v>469875047.22</v>
+        <v>473859259.82</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,19 +8299,19 @@
         <v>480</v>
       </c>
       <c r="C240" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D240" s="7">
-        <v>0.349343</v>
+        <v>0.352764</v>
       </c>
       <c r="E240" s="8">
-        <v>31374160355.56</v>
+        <v>31366276907.91</v>
       </c>
       <c r="F240" s="9">
-        <v>120407</v>
+        <v>120324</v>
       </c>
       <c r="G240" s="8">
-        <v>10960336404</v>
+        <v>11064904163.83</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -8322,19 +8322,19 @@
         <v>482</v>
       </c>
       <c r="C241" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D241" s="7">
-        <v>0.127294</v>
+        <v>0.127714</v>
       </c>
       <c r="E241" s="8">
-        <v>3797026685.1</v>
+        <v>3795761983.71</v>
       </c>
       <c r="F241" s="9">
-        <v>7399</v>
+        <v>7384</v>
       </c>
       <c r="G241" s="8">
-        <v>483340513.44</v>
+        <v>484773492.15</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -8345,19 +8345,19 @@
         <v>484</v>
       </c>
       <c r="C242" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D242" s="7">
-        <v>0.129679</v>
+        <v>0.130204</v>
       </c>
       <c r="E242" s="8">
-        <v>89192062901.37</v>
+        <v>89150841292.3</v>
       </c>
       <c r="F242" s="9">
-        <v>402992</v>
+        <v>403070</v>
       </c>
       <c r="G242" s="8">
-        <v>11566295340.84</v>
+        <v>11607838820.7</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8368,19 +8368,19 @@
         <v>486</v>
       </c>
       <c r="C243" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D243" s="7">
-        <v>0.315916</v>
+        <v>0.318463</v>
       </c>
       <c r="E243" s="8">
-        <v>3915871947</v>
+        <v>3944887495.81</v>
       </c>
       <c r="F243" s="9">
-        <v>18298</v>
+        <v>18324</v>
       </c>
       <c r="G243" s="8">
-        <v>1237088064.62</v>
+        <v>1256302220.2</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -8391,19 +8391,19 @@
         <v>488</v>
       </c>
       <c r="C244" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D244" s="7">
-        <v>0.081661</v>
+        <v>46150</v>
+      </c>
+      <c r="D244" s="10">
+        <v>0.08175</v>
       </c>
       <c r="E244" s="8">
-        <v>3841385939.96</v>
+        <v>3847754173.23</v>
       </c>
       <c r="F244" s="9">
-        <v>9184</v>
+        <v>9174</v>
       </c>
       <c r="G244" s="8">
-        <v>313690079.28</v>
+        <v>314552311.25</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8414,19 +8414,19 @@
         <v>490</v>
       </c>
       <c r="C245" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D245" s="7">
-        <v>0.252278</v>
+        <v>0.253936</v>
       </c>
       <c r="E245" s="8">
-        <v>2858453228.07</v>
+        <v>2869544211.02</v>
       </c>
       <c r="F245" s="9">
-        <v>14145</v>
+        <v>14169</v>
       </c>
       <c r="G245" s="8">
-        <v>721125750.85</v>
+        <v>728681394.63</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -8437,19 +8437,19 @@
         <v>492</v>
       </c>
       <c r="C246" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D246" s="7">
-        <v>0.069253</v>
+        <v>0.069325</v>
       </c>
       <c r="E246" s="8">
-        <v>4029451050.58</v>
+        <v>4028072427.11</v>
       </c>
       <c r="F246" s="9">
-        <v>7754</v>
+        <v>7739</v>
       </c>
       <c r="G246" s="8">
-        <v>279052810.56</v>
+        <v>279245589.01</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8460,19 +8460,19 @@
         <v>494</v>
       </c>
       <c r="C247" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D247" s="7">
-        <v>0.179595</v>
+        <v>0.179618</v>
       </c>
       <c r="E247" s="8">
-        <v>14478659867.64</v>
+        <v>14513426639.54</v>
       </c>
       <c r="F247" s="9">
-        <v>48880</v>
+        <v>48942</v>
       </c>
       <c r="G247" s="8">
-        <v>2600288998.61</v>
+        <v>2606867390.39</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8483,19 +8483,19 @@
         <v>496</v>
       </c>
       <c r="C248" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D248" s="7">
-        <v>0.025065</v>
+        <v>0.026083</v>
       </c>
       <c r="E248" s="8">
-        <v>954184865198.59</v>
+        <v>952459391674.64</v>
       </c>
       <c r="F248" s="9">
-        <v>186707</v>
+        <v>186648</v>
       </c>
       <c r="G248" s="8">
-        <v>23916589312.28</v>
+        <v>24842843255.8</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8506,19 +8506,19 @@
         <v>498</v>
       </c>
       <c r="C249" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D249" s="7">
-        <v>0.751575</v>
+        <v>46150</v>
+      </c>
+      <c r="D249" s="10">
+        <v>0.76297</v>
       </c>
       <c r="E249" s="8">
-        <v>15370922230.4</v>
+        <v>15354454559.06</v>
       </c>
       <c r="F249" s="9">
-        <v>79618</v>
+        <v>79637</v>
       </c>
       <c r="G249" s="8">
-        <v>11552404104.41</v>
+        <v>11714988646.46</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8529,19 +8529,19 @@
         <v>500</v>
       </c>
       <c r="C250" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D250" s="7">
-        <v>0.653256</v>
+        <v>0.662391</v>
       </c>
       <c r="E250" s="8">
-        <v>8201462272.01</v>
+        <v>8198159583.54</v>
       </c>
       <c r="F250" s="9">
-        <v>75508</v>
+        <v>75572</v>
       </c>
       <c r="G250" s="8">
-        <v>5357651887.65</v>
+        <v>5430386989.4</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8552,19 +8552,19 @@
         <v>502</v>
       </c>
       <c r="C251" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D251" s="7">
-        <v>0.163244</v>
+        <v>0.164369</v>
       </c>
       <c r="E251" s="8">
-        <v>2789790910.73</v>
+        <v>2791265752.18</v>
       </c>
       <c r="F251" s="9">
-        <v>11367</v>
+        <v>11360</v>
       </c>
       <c r="G251" s="8">
-        <v>455416257.72</v>
+        <v>458796550.81</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8575,19 +8575,19 @@
         <v>504</v>
       </c>
       <c r="C252" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D252" s="7">
-        <v>0.097359</v>
+        <v>0.097999</v>
       </c>
       <c r="E252" s="8">
-        <v>4879180743.23</v>
+        <v>4876637791.44</v>
       </c>
       <c r="F252" s="9">
-        <v>69521</v>
+        <v>69518</v>
       </c>
       <c r="G252" s="8">
-        <v>475031129.65</v>
+        <v>477904031.26</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8598,19 +8598,19 @@
         <v>506</v>
       </c>
       <c r="C253" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D253" s="7">
-        <v>0.332055</v>
+        <v>0.332793</v>
       </c>
       <c r="E253" s="8">
-        <v>2183740606.26</v>
+        <v>2181899198.3</v>
       </c>
       <c r="F253" s="9">
         <v>21123</v>
       </c>
       <c r="G253" s="8">
-        <v>725121330.33</v>
+        <v>726120920.61</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8621,19 +8621,19 @@
         <v>508</v>
       </c>
       <c r="C254" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D254" s="7">
-        <v>0.142375</v>
+        <v>0.143042</v>
       </c>
       <c r="E254" s="8">
-        <v>661930935.61</v>
+        <v>661764865.88</v>
       </c>
       <c r="F254" s="9">
         <v>2401</v>
       </c>
       <c r="G254" s="8">
-        <v>94242401.6</v>
+        <v>94659943.74</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8644,19 +8644,19 @@
         <v>510</v>
       </c>
       <c r="C255" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D255" s="7">
-        <v>0.083169</v>
+        <v>0.083278</v>
       </c>
       <c r="E255" s="8">
-        <v>644686800.81</v>
+        <v>650589614.55</v>
       </c>
       <c r="F255" s="9">
-        <v>14185</v>
+        <v>14270</v>
       </c>
       <c r="G255" s="8">
-        <v>53617899.68</v>
+        <v>54179957.97</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8667,19 +8667,19 @@
         <v>512</v>
       </c>
       <c r="C256" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D256" s="7">
-        <v>0.097469</v>
+        <v>0.097602</v>
       </c>
       <c r="E256" s="8">
-        <v>4024656230.21</v>
+        <v>4027582242.43</v>
       </c>
       <c r="F256" s="9">
-        <v>78569</v>
+        <v>78617</v>
       </c>
       <c r="G256" s="8">
-        <v>392279566.13</v>
+        <v>393101975.84</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8690,19 +8690,19 @@
         <v>514</v>
       </c>
       <c r="C257" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D257" s="7">
-        <v>0.129106</v>
+        <v>0.129801</v>
       </c>
       <c r="E257" s="8">
-        <v>3766357014.04</v>
+        <v>3764400770.55</v>
       </c>
       <c r="F257" s="9">
-        <v>19674</v>
+        <v>19677</v>
       </c>
       <c r="G257" s="8">
-        <v>486258360.8</v>
+        <v>488624595.17</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -8713,19 +8713,19 @@
         <v>516</v>
       </c>
       <c r="C258" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D258" s="7">
-        <v>0.094009</v>
+        <v>46150</v>
+      </c>
+      <c r="D258" s="10">
+        <v>0.09422</v>
       </c>
       <c r="E258" s="8">
-        <v>584136670.33</v>
+        <v>589631385.3</v>
       </c>
       <c r="F258" s="9">
-        <v>10848</v>
+        <v>10815</v>
       </c>
       <c r="G258" s="8">
-        <v>54914063.82</v>
+        <v>55555360.74</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -8736,19 +8736,19 @@
         <v>518</v>
       </c>
       <c r="C259" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D259" s="7">
-        <v>0.132998</v>
+        <v>0.133312</v>
       </c>
       <c r="E259" s="8">
-        <v>4457574174.46</v>
+        <v>4464260549.12</v>
       </c>
       <c r="F259" s="9">
-        <v>18215</v>
+        <v>18153</v>
       </c>
       <c r="G259" s="8">
-        <v>592847714.88</v>
+        <v>595138231.39</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -8759,19 +8759,19 @@
         <v>520</v>
       </c>
       <c r="C260" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D260" s="7">
-        <v>0.156021</v>
+        <v>0.157393</v>
       </c>
       <c r="E260" s="8">
-        <v>1216613334.63</v>
+        <v>1215818908.34</v>
       </c>
       <c r="F260" s="9">
-        <v>59029</v>
+        <v>59016</v>
       </c>
       <c r="G260" s="8">
-        <v>189816894.01</v>
+        <v>191361369.58</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -8782,19 +8782,19 @@
         <v>522</v>
       </c>
       <c r="C261" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D261" s="7">
-        <v>0.791225</v>
+        <v>0.800892</v>
       </c>
       <c r="E261" s="8">
-        <v>8886512509.31</v>
+        <v>8876647117.28</v>
       </c>
       <c r="F261" s="9">
-        <v>26144</v>
+        <v>26149</v>
       </c>
       <c r="G261" s="8">
-        <v>7031233831</v>
+        <v>7109235146.2</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -8805,19 +8805,19 @@
         <v>524</v>
       </c>
       <c r="C262" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D262" s="7">
-        <v>0.104097</v>
+        <v>46150</v>
+      </c>
+      <c r="D262" s="11">
+        <v>0.1048</v>
       </c>
       <c r="E262" s="8">
-        <v>14006378805.17</v>
+        <v>13989472317.75</v>
       </c>
       <c r="F262" s="9">
-        <v>128242</v>
+        <v>128214</v>
       </c>
       <c r="G262" s="8">
-        <v>1458022916.87</v>
+        <v>1466103463.69</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -8828,19 +8828,19 @@
         <v>526</v>
       </c>
       <c r="C263" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D263" s="10">
-        <v>0.01352</v>
+        <v>46150</v>
+      </c>
+      <c r="D263" s="7">
+        <v>0.013647</v>
       </c>
       <c r="E263" s="8">
-        <v>147321018578.04</v>
+        <v>150359245920.56</v>
       </c>
       <c r="F263" s="9">
-        <v>1673</v>
+        <v>1685</v>
       </c>
       <c r="G263" s="8">
-        <v>1991797372.97</v>
+        <v>2051976300.81</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -8851,19 +8851,19 @@
         <v>528</v>
       </c>
       <c r="C264" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D264" s="7">
-        <v>0.293008</v>
+        <v>0.299075</v>
       </c>
       <c r="E264" s="8">
-        <v>5717498104.73</v>
+        <v>5725833503.97</v>
       </c>
       <c r="F264" s="9">
-        <v>43929</v>
+        <v>43927</v>
       </c>
       <c r="G264" s="8">
-        <v>1675273632.8</v>
+        <v>1712454662.61</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -8874,19 +8874,19 @@
         <v>530</v>
       </c>
       <c r="C265" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D265" s="10">
-        <v>0.41593</v>
+        <v>46150</v>
+      </c>
+      <c r="D265" s="7">
+        <v>0.421657</v>
       </c>
       <c r="E265" s="8">
-        <v>1962976871.28</v>
+        <v>1964952807.04</v>
       </c>
       <c r="F265" s="9">
-        <v>21823</v>
+        <v>21842</v>
       </c>
       <c r="G265" s="8">
-        <v>816460869.8</v>
+        <v>828536190.77</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -8897,19 +8897,19 @@
         <v>532</v>
       </c>
       <c r="C266" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D266" s="7">
-        <v>0.132066</v>
+        <v>0.132367</v>
       </c>
       <c r="E266" s="8">
-        <v>34360758217.34</v>
+        <v>34917886587.33</v>
       </c>
       <c r="F266" s="9">
-        <v>102736</v>
+        <v>103415</v>
       </c>
       <c r="G266" s="8">
-        <v>4537895341.19</v>
+        <v>4621984100.23</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -8920,19 +8920,19 @@
         <v>534</v>
       </c>
       <c r="C267" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D267" s="7">
-        <v>0.238279</v>
+        <v>0.240552</v>
       </c>
       <c r="E267" s="8">
-        <v>2684511653.03</v>
+        <v>2683292001.03</v>
       </c>
       <c r="F267" s="9">
-        <v>24245</v>
+        <v>24238</v>
       </c>
       <c r="G267" s="8">
-        <v>639663757.79</v>
+        <v>645472520.21</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -8943,19 +8943,19 @@
         <v>536</v>
       </c>
       <c r="C268" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D268" s="7">
-        <v>0.013168</v>
+        <v>0.013309</v>
       </c>
       <c r="E268" s="8">
-        <v>747635904945.29</v>
+        <v>752708043209.82</v>
       </c>
       <c r="F268" s="9">
-        <v>72519</v>
+        <v>72800</v>
       </c>
       <c r="G268" s="8">
-        <v>9844852820.53</v>
+        <v>10018088285.8</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -8966,19 +8966,19 @@
         <v>538</v>
       </c>
       <c r="C269" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D269" s="7">
-        <v>0.504537</v>
+        <v>0.505532</v>
       </c>
       <c r="E269" s="8">
-        <v>5712975859.39</v>
+        <v>5706200639.22</v>
       </c>
       <c r="F269" s="9">
-        <v>72279</v>
+        <v>72209</v>
       </c>
       <c r="G269" s="8">
-        <v>2882406317.25</v>
+        <v>2884667236.64</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -8989,19 +8989,19 @@
         <v>540</v>
       </c>
       <c r="C270" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D270" s="7">
-        <v>0.305925</v>
+        <v>0.308883</v>
       </c>
       <c r="E270" s="8">
-        <v>1834520751.17</v>
+        <v>1835823264.16</v>
       </c>
       <c r="F270" s="9">
-        <v>95652</v>
+        <v>95650</v>
       </c>
       <c r="G270" s="8">
-        <v>561224999.12</v>
+        <v>567054786.06</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9012,19 +9012,19 @@
         <v>542</v>
       </c>
       <c r="C271" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D271" s="7">
-        <v>0.795788</v>
+        <v>0.801179</v>
       </c>
       <c r="E271" s="8">
-        <v>2051938272.5</v>
+        <v>2049041120.05</v>
       </c>
       <c r="F271" s="9">
-        <v>111696</v>
+        <v>111677</v>
       </c>
       <c r="G271" s="8">
-        <v>1632907579.57</v>
+        <v>1641649006.04</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9035,19 +9035,19 @@
         <v>544</v>
       </c>
       <c r="C272" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D272" s="7">
-        <v>0.539014</v>
+        <v>0.543876</v>
       </c>
       <c r="E272" s="8">
-        <v>1500876338.23</v>
+        <v>1500696813.68</v>
       </c>
       <c r="F272" s="9">
-        <v>37700</v>
+        <v>37688</v>
       </c>
       <c r="G272" s="8">
-        <v>808993346.72</v>
+        <v>816192877.69</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9058,19 +9058,19 @@
         <v>546</v>
       </c>
       <c r="C273" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D273" s="7">
-        <v>0.286365</v>
+        <v>0.288996</v>
       </c>
       <c r="E273" s="8">
-        <v>2817142435.85</v>
+        <v>2817974960.16</v>
       </c>
       <c r="F273" s="9">
-        <v>87282</v>
+        <v>87281</v>
       </c>
       <c r="G273" s="8">
-        <v>806729751.73</v>
+        <v>814382845.12</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9081,19 +9081,19 @@
         <v>548</v>
       </c>
       <c r="C274" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D274" s="7">
-        <v>2.484154</v>
+        <v>2.515001</v>
       </c>
       <c r="E274" s="8">
-        <v>1902400073.04</v>
+        <v>1902386641.65</v>
       </c>
       <c r="F274" s="9">
-        <v>57646</v>
+        <v>57622</v>
       </c>
       <c r="G274" s="8">
-        <v>4725855018.82</v>
+        <v>4784503843.87</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9104,19 +9104,19 @@
         <v>550</v>
       </c>
       <c r="C275" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D275" s="7">
-        <v>0.924064</v>
+        <v>0.928328</v>
       </c>
       <c r="E275" s="8">
-        <v>769605053.17</v>
+        <v>769536421.93</v>
       </c>
       <c r="F275" s="9">
-        <v>83367</v>
+        <v>83357</v>
       </c>
       <c r="G275" s="8">
-        <v>711164165.72</v>
+        <v>714381850.33</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9127,19 +9127,19 @@
         <v>552</v>
       </c>
       <c r="C276" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D276" s="10">
-        <v>0.37636</v>
+        <v>46150</v>
+      </c>
+      <c r="D276" s="7">
+        <v>0.377386</v>
       </c>
       <c r="E276" s="8">
-        <v>8956753925.62</v>
+        <v>8959377539.07</v>
       </c>
       <c r="F276" s="9">
-        <v>100010</v>
+        <v>100005</v>
       </c>
       <c r="G276" s="8">
-        <v>3370961141.34</v>
+        <v>3381142189.12</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9150,19 +9150,19 @@
         <v>554</v>
       </c>
       <c r="C277" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D277" s="7">
-        <v>0.112166</v>
+        <v>0.112983</v>
       </c>
       <c r="E277" s="8">
-        <v>54696328865.63</v>
+        <v>54649465891.48</v>
       </c>
       <c r="F277" s="9">
-        <v>198477</v>
+        <v>198364</v>
       </c>
       <c r="G277" s="8">
-        <v>6135054618.77</v>
+        <v>6174450120.04</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9173,19 +9173,19 @@
         <v>556</v>
       </c>
       <c r="C278" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D278" s="7">
-        <v>0.115871</v>
+        <v>0.116659</v>
       </c>
       <c r="E278" s="8">
-        <v>83469449353.94</v>
+        <v>83371892852.64</v>
       </c>
       <c r="F278" s="9">
-        <v>1083989</v>
+        <v>1083493</v>
       </c>
       <c r="G278" s="8">
-        <v>9671730099.65</v>
+        <v>9726121939.9</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9196,19 +9196,19 @@
         <v>558</v>
       </c>
       <c r="C279" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D279" s="10">
-        <v>0.14376</v>
+        <v>46150</v>
+      </c>
+      <c r="D279" s="7">
+        <v>0.143836</v>
       </c>
       <c r="E279" s="8">
-        <v>33222146674.6</v>
+        <v>33239330201.9</v>
       </c>
       <c r="F279" s="9">
-        <v>328763</v>
+        <v>328722</v>
       </c>
       <c r="G279" s="8">
-        <v>4775999738.58</v>
+        <v>4781011573.44</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9219,19 +9219,19 @@
         <v>560</v>
       </c>
       <c r="C280" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D280" s="7">
-        <v>0.172361</v>
+        <v>0.173095</v>
       </c>
       <c r="E280" s="8">
-        <v>3167041667.25</v>
+        <v>3156789684.08</v>
       </c>
       <c r="F280" s="9">
-        <v>27461</v>
+        <v>27449</v>
       </c>
       <c r="G280" s="8">
-        <v>545874585.2</v>
+        <v>546424546.04</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -9242,19 +9242,19 @@
         <v>562</v>
       </c>
       <c r="C281" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D281" s="7">
-        <v>0.739998</v>
+        <v>0.751072</v>
       </c>
       <c r="E281" s="8">
-        <v>44367588852.19</v>
+        <v>44398728100.71</v>
       </c>
       <c r="F281" s="9">
-        <v>675187</v>
+        <v>675058</v>
       </c>
       <c r="G281" s="8">
-        <v>32831913972.57</v>
+        <v>33346663640.26</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -9265,19 +9265,19 @@
         <v>564</v>
       </c>
       <c r="C282" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D282" s="7">
-        <v>0.265379</v>
+        <v>0.267799</v>
       </c>
       <c r="E282" s="8">
-        <v>8745439871.97</v>
+        <v>8731033485.38</v>
       </c>
       <c r="F282" s="9">
-        <v>108573</v>
+        <v>108631</v>
       </c>
       <c r="G282" s="8">
-        <v>2320857427.34</v>
+        <v>2338161616.58</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -9288,19 +9288,19 @@
         <v>566</v>
       </c>
       <c r="C283" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D283" s="7">
-        <v>0.556758</v>
+        <v>0.564307</v>
       </c>
       <c r="E283" s="8">
-        <v>11742747007</v>
+        <v>11770048692.95</v>
       </c>
       <c r="F283" s="9">
-        <v>139230</v>
+        <v>139303</v>
       </c>
       <c r="G283" s="8">
-        <v>6537873391.6</v>
+        <v>6641921623.27</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -9311,19 +9311,19 @@
         <v>568</v>
       </c>
       <c r="C284" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D284" s="7">
-        <v>0.311195</v>
+        <v>0.312961</v>
       </c>
       <c r="E284" s="8">
-        <v>2307187931.98</v>
+        <v>2297430005.36</v>
       </c>
       <c r="F284" s="9">
-        <v>37510</v>
+        <v>37459</v>
       </c>
       <c r="G284" s="8">
-        <v>717984715.53</v>
+        <v>719006522.78</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -9334,19 +9334,19 @@
         <v>570</v>
       </c>
       <c r="C285" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D285" s="7">
-        <v>0.197802</v>
+        <v>46150</v>
+      </c>
+      <c r="D285" s="10">
+        <v>0.19808</v>
       </c>
       <c r="E285" s="8">
-        <v>9531849107.35</v>
+        <v>9536592454.73</v>
       </c>
       <c r="F285" s="9">
-        <v>108131</v>
+        <v>108053</v>
       </c>
       <c r="G285" s="8">
-        <v>1885422855.64</v>
+        <v>1889006860.09</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -9357,19 +9357,19 @@
         <v>572</v>
       </c>
       <c r="C286" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D286" s="10">
-        <v>0.28196</v>
+        <v>46150</v>
+      </c>
+      <c r="D286" s="7">
+        <v>0.282472</v>
       </c>
       <c r="E286" s="8">
-        <v>801672609.43</v>
+        <v>801882033.34</v>
       </c>
       <c r="F286" s="9">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="G286" s="8">
-        <v>226039588.79</v>
+        <v>226508834.1</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -9380,19 +9380,19 @@
         <v>574</v>
       </c>
       <c r="C287" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D287" s="7">
-        <v>0.088078</v>
+        <v>46150</v>
+      </c>
+      <c r="D287" s="10">
+        <v>0.08817</v>
       </c>
       <c r="E287" s="8">
-        <v>4340411095.59</v>
+        <v>4347945992.66</v>
       </c>
       <c r="F287" s="9">
-        <v>147394</v>
+        <v>147646</v>
       </c>
       <c r="G287" s="8">
-        <v>382294732.17</v>
+        <v>383358210.44</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -9403,19 +9403,19 @@
         <v>576</v>
       </c>
       <c r="C288" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D288" s="7">
-        <v>0.493814</v>
+        <v>0.499009</v>
       </c>
       <c r="E288" s="8">
-        <v>1584043462.48</v>
+        <v>1585961911.66</v>
       </c>
       <c r="F288" s="9">
-        <v>4272</v>
+        <v>4266</v>
       </c>
       <c r="G288" s="8">
-        <v>782222164.19</v>
+        <v>791409561.52</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -9426,19 +9426,19 @@
         <v>578</v>
       </c>
       <c r="C289" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D289" s="7">
-        <v>0.015863</v>
+        <v>0.015978</v>
       </c>
       <c r="E289" s="8">
-        <v>5934655217.61</v>
+        <v>6183194094.94</v>
       </c>
       <c r="F289" s="9">
-        <v>3707</v>
+        <v>3681</v>
       </c>
       <c r="G289" s="8">
-        <v>94140492.21</v>
+        <v>98794624.47</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -9449,19 +9449,19 @@
         <v>580</v>
       </c>
       <c r="C290" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D290" s="7">
-        <v>0.017394</v>
+        <v>0.018688</v>
       </c>
       <c r="E290" s="8">
-        <v>151825988221.85</v>
+        <v>151598357804.63</v>
       </c>
       <c r="F290" s="9">
-        <v>31609</v>
+        <v>31515</v>
       </c>
       <c r="G290" s="8">
-        <v>2640833859.72</v>
+        <v>2833029065.29</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -9472,19 +9472,19 @@
         <v>582</v>
       </c>
       <c r="C291" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D291" s="7">
-        <v>0.010973</v>
+        <v>0.011223</v>
       </c>
       <c r="E291" s="8">
-        <v>9477243703.05</v>
+        <v>10632093316.26</v>
       </c>
       <c r="F291" s="9">
-        <v>1730</v>
+        <v>1816</v>
       </c>
       <c r="G291" s="8">
-        <v>103989706.7</v>
+        <v>119325505.01</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -9495,19 +9495,19 @@
         <v>584</v>
       </c>
       <c r="C292" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D292" s="7">
-        <v>0.134574</v>
+        <v>46150</v>
+      </c>
+      <c r="D292" s="10">
+        <v>0.13993</v>
       </c>
       <c r="E292" s="8">
-        <v>52512864529.58</v>
+        <v>52354456901.23</v>
       </c>
       <c r="F292" s="9">
-        <v>107935</v>
+        <v>107796</v>
       </c>
       <c r="G292" s="8">
-        <v>7066865920.07</v>
+        <v>7325956243.4</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -9518,19 +9518,19 @@
         <v>586</v>
       </c>
       <c r="C293" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D293" s="7">
-        <v>0.051366</v>
+        <v>0.051418</v>
       </c>
       <c r="E293" s="8">
-        <v>12530565628.49</v>
+        <v>12974788106.83</v>
       </c>
       <c r="F293" s="9">
-        <v>28952</v>
+        <v>28966</v>
       </c>
       <c r="G293" s="8">
-        <v>643648405.94</v>
+        <v>667132867.14</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -9541,19 +9541,19 @@
         <v>588</v>
       </c>
       <c r="C294" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D294" s="7">
-        <v>0.022064</v>
+        <v>0.022088</v>
       </c>
       <c r="E294" s="8">
-        <v>57785079686.39</v>
+        <v>58176240138.5</v>
       </c>
       <c r="F294" s="9">
-        <v>10721</v>
+        <v>10682</v>
       </c>
       <c r="G294" s="8">
-        <v>1274991610.74</v>
+        <v>1284993085.09</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -9564,19 +9564,19 @@
         <v>590</v>
       </c>
       <c r="C295" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D295" s="10">
-        <v>0.03261</v>
+        <v>46150</v>
+      </c>
+      <c r="D295" s="7">
+        <v>0.032892</v>
       </c>
       <c r="E295" s="8">
-        <v>55780798290.24</v>
+        <v>53687414511.97</v>
       </c>
       <c r="F295" s="9">
-        <v>33587</v>
+        <v>33073</v>
       </c>
       <c r="G295" s="8">
-        <v>1819005774.74</v>
+        <v>1765873877.54</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -9587,19 +9587,19 @@
         <v>592</v>
       </c>
       <c r="C296" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D296" s="7">
-        <v>0.019488</v>
+        <v>0.020383</v>
       </c>
       <c r="E296" s="8">
-        <v>955520302453.97</v>
+        <v>954664215717.11</v>
       </c>
       <c r="F296" s="9">
-        <v>178832</v>
+        <v>178741</v>
       </c>
       <c r="G296" s="8">
-        <v>18621096642.86</v>
+        <v>19459290155.8</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -9610,19 +9610,19 @@
         <v>594</v>
       </c>
       <c r="C297" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D297" s="7">
-        <v>0.102548</v>
+        <v>0.103183</v>
       </c>
       <c r="E297" s="8">
-        <v>37213608830.12</v>
+        <v>37288051667.53</v>
       </c>
       <c r="F297" s="9">
-        <v>382981</v>
+        <v>383069</v>
       </c>
       <c r="G297" s="8">
-        <v>3816191128.9</v>
+        <v>3847479885.72</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -9633,19 +9633,19 @@
         <v>596</v>
       </c>
       <c r="C298" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D298" s="7">
-        <v>0.087158</v>
+        <v>46150</v>
+      </c>
+      <c r="D298" s="10">
+        <v>0.08759</v>
       </c>
       <c r="E298" s="8">
-        <v>38342123522.34</v>
+        <v>38330242211.87</v>
       </c>
       <c r="F298" s="9">
-        <v>48125</v>
+        <v>48115</v>
       </c>
       <c r="G298" s="8">
-        <v>3341835996.93</v>
+        <v>3357348642.4</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -9656,19 +9656,19 @@
         <v>598</v>
       </c>
       <c r="C299" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D299" s="7">
-        <v>0.095763</v>
+        <v>0.095776</v>
       </c>
       <c r="E299" s="8">
-        <v>39021126949.47</v>
+        <v>39055012658.65</v>
       </c>
       <c r="F299" s="9">
-        <v>526990</v>
+        <v>527012</v>
       </c>
       <c r="G299" s="8">
-        <v>3736765407.12</v>
+        <v>3740519268.57</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -9679,19 +9679,19 @@
         <v>600</v>
       </c>
       <c r="C300" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D300" s="10">
-        <v>0.02061</v>
+        <v>46150</v>
+      </c>
+      <c r="D300" s="7">
+        <v>0.020792</v>
       </c>
       <c r="E300" s="8">
-        <v>36681712854.4</v>
+        <v>36609353657.52</v>
       </c>
       <c r="F300" s="9">
-        <v>25806</v>
+        <v>25048</v>
       </c>
       <c r="G300" s="8">
-        <v>756025320.12</v>
+        <v>761197893.88</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -9702,19 +9702,19 @@
         <v>602</v>
       </c>
       <c r="C301" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D301" s="7">
-        <v>0.010352</v>
+        <v>0.010372</v>
       </c>
       <c r="E301" s="8">
-        <v>4315128685.97</v>
+        <v>4938072936.55</v>
       </c>
       <c r="F301" s="9">
-        <v>966</v>
+        <v>1030</v>
       </c>
       <c r="G301" s="8">
-        <v>44670210.28</v>
+        <v>51219380.7</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -9725,19 +9725,19 @@
         <v>604</v>
       </c>
       <c r="C302" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D302" s="10">
-        <v>0.01625</v>
+        <v>46150</v>
+      </c>
+      <c r="D302" s="7">
+        <v>0.016464</v>
       </c>
       <c r="E302" s="8">
-        <v>24357587523.01</v>
+        <v>24094439795.59</v>
       </c>
       <c r="F302" s="9">
-        <v>11148</v>
+        <v>11235</v>
       </c>
       <c r="G302" s="8">
-        <v>395811989.56</v>
+        <v>396694908.27</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -9748,19 +9748,19 @@
         <v>606</v>
       </c>
       <c r="C303" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D303" s="7">
-        <v>0.018578</v>
+        <v>46150</v>
+      </c>
+      <c r="D303" s="10">
+        <v>0.01876</v>
       </c>
       <c r="E303" s="8">
-        <v>12022580852.23</v>
+        <v>12432023158.03</v>
       </c>
       <c r="F303" s="9">
-        <v>6660</v>
+        <v>6725</v>
       </c>
       <c r="G303" s="8">
-        <v>223361339.63</v>
+        <v>233227189.85</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -9771,19 +9771,19 @@
         <v>608</v>
       </c>
       <c r="C304" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D304" s="7">
-        <v>0.095188</v>
+        <v>0.095713</v>
       </c>
       <c r="E304" s="8">
-        <v>21522586184.88</v>
+        <v>21528902767.51</v>
       </c>
       <c r="F304" s="9">
-        <v>348822</v>
+        <v>348885</v>
       </c>
       <c r="G304" s="8">
-        <v>2048689131.42</v>
+        <v>2060588604.66</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -9794,19 +9794,19 @@
         <v>610</v>
       </c>
       <c r="C305" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D305" s="7">
-        <v>0.019258</v>
+        <v>0.019417</v>
       </c>
       <c r="E305" s="8">
-        <v>10421502768.23</v>
+        <v>10302793606.55</v>
       </c>
       <c r="F305" s="9">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="G305" s="8">
-        <v>200695706.52</v>
+        <v>200051760</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -9817,19 +9817,19 @@
         <v>612</v>
       </c>
       <c r="C306" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D306" s="7">
-        <v>0.015768</v>
+        <v>0.015887</v>
       </c>
       <c r="E306" s="8">
-        <v>9074126452.56</v>
+        <v>9038805114.12</v>
       </c>
       <c r="F306" s="9">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G306" s="8">
-        <v>143082537.81</v>
+        <v>143603027.19</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -9840,19 +9840,19 @@
         <v>614</v>
       </c>
       <c r="C307" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D307" s="7">
-        <v>0.015912</v>
+        <v>46150</v>
+      </c>
+      <c r="D307" s="10">
+        <v>0.01596</v>
       </c>
       <c r="E307" s="8">
-        <v>1270990954.6</v>
+        <v>1264833815.1</v>
       </c>
       <c r="F307" s="9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G307" s="8">
-        <v>20224341.78</v>
+        <v>20187355.12</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -9863,19 +9863,19 @@
         <v>616</v>
       </c>
       <c r="C308" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D308" s="7">
-        <v>0.233088</v>
+        <v>0.235865</v>
       </c>
       <c r="E308" s="8">
-        <v>48774920667.94</v>
+        <v>48732775809.05</v>
       </c>
       <c r="F308" s="9">
-        <v>175267</v>
+        <v>175274</v>
       </c>
       <c r="G308" s="8">
-        <v>11368857446.27</v>
+        <v>11494345053.44</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -9886,19 +9886,19 @@
         <v>618</v>
       </c>
       <c r="C309" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D309" s="7">
-        <v>0.011198</v>
+        <v>0.011315</v>
       </c>
       <c r="E309" s="8">
-        <v>2685185858.69</v>
+        <v>2699866748.43</v>
       </c>
       <c r="F309" s="9">
-        <v>2058</v>
+        <v>2076</v>
       </c>
       <c r="G309" s="8">
-        <v>30069920.65</v>
+        <v>30548175.05</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -9909,19 +9909,19 @@
         <v>620</v>
       </c>
       <c r="C310" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D310" s="7">
-        <v>0.030779</v>
+        <v>0.031222</v>
       </c>
       <c r="E310" s="8">
-        <v>12873400842.74</v>
+        <v>13066672630.91</v>
       </c>
       <c r="F310" s="9">
-        <v>17641</v>
+        <v>17679</v>
       </c>
       <c r="G310" s="8">
-        <v>396234369.38</v>
+        <v>407962502.77</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -9932,19 +9932,19 @@
         <v>622</v>
       </c>
       <c r="C311" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D311" s="7">
-        <v>0.025442</v>
+        <v>0.025622</v>
       </c>
       <c r="E311" s="8">
-        <v>3003097209.93</v>
+        <v>3003362449.06</v>
       </c>
       <c r="F311" s="9">
-        <v>10300</v>
+        <v>10303</v>
       </c>
       <c r="G311" s="8">
-        <v>76404557.04</v>
+        <v>76953603.42</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -9955,19 +9955,19 @@
         <v>624</v>
       </c>
       <c r="C312" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D312" s="7">
-        <v>0.124842</v>
+        <v>0.125869</v>
       </c>
       <c r="E312" s="8">
-        <v>618712824.74</v>
+        <v>618106888.43</v>
       </c>
       <c r="F312" s="9">
-        <v>94219</v>
+        <v>94177</v>
       </c>
       <c r="G312" s="8">
-        <v>77241313.04</v>
+        <v>77800237.9</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -9978,19 +9978,19 @@
         <v>626</v>
       </c>
       <c r="C313" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D313" s="7">
-        <v>0.091167</v>
+        <v>0.091398</v>
       </c>
       <c r="E313" s="8">
-        <v>1370358342.01</v>
+        <v>1411513712.81</v>
       </c>
       <c r="F313" s="9">
-        <v>24952</v>
+        <v>26953</v>
       </c>
       <c r="G313" s="8">
-        <v>124931295.04</v>
+        <v>129009734.35</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -10001,19 +10001,19 @@
         <v>628</v>
       </c>
       <c r="C314" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D314" s="10">
-        <v>0.08069</v>
+        <v>46150</v>
+      </c>
+      <c r="D314" s="7">
+        <v>0.080786</v>
       </c>
       <c r="E314" s="8">
-        <v>2461656416.41</v>
+        <v>2459962978.45</v>
       </c>
       <c r="F314" s="9">
-        <v>77994</v>
+        <v>78033</v>
       </c>
       <c r="G314" s="8">
-        <v>198631883.14</v>
+        <v>198730796.8</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -10024,19 +10024,19 @@
         <v>630</v>
       </c>
       <c r="C315" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D315" s="7">
-        <v>0.389993</v>
+        <v>0.390531</v>
       </c>
       <c r="E315" s="8">
-        <v>5207844981.07</v>
+        <v>5194165316.38</v>
       </c>
       <c r="F315" s="9">
-        <v>71821</v>
+        <v>71817</v>
       </c>
       <c r="G315" s="8">
-        <v>2031022477.7</v>
+        <v>2028485018.16</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -10047,19 +10047,19 @@
         <v>632</v>
       </c>
       <c r="C316" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D316" s="7">
-        <v>0.206589</v>
+        <v>0.207472</v>
       </c>
       <c r="E316" s="8">
-        <v>5827255485.79</v>
+        <v>5787217201.57</v>
       </c>
       <c r="F316" s="9">
-        <v>56507</v>
+        <v>56497</v>
       </c>
       <c r="G316" s="8">
-        <v>1203848285.74</v>
+        <v>1200684795.6</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -10070,19 +10070,19 @@
         <v>634</v>
       </c>
       <c r="C317" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D317" s="7">
-        <v>0.112759</v>
+        <v>0.113932</v>
       </c>
       <c r="E317" s="8">
-        <v>2332878437</v>
+        <v>2332890953.59</v>
       </c>
       <c r="F317" s="9">
-        <v>8462</v>
+        <v>8460</v>
       </c>
       <c r="G317" s="8">
-        <v>263052836.39</v>
+        <v>265790430.95</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -10093,19 +10093,19 @@
         <v>636</v>
       </c>
       <c r="C318" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D318" s="7">
-        <v>0.568142</v>
+        <v>0.574608</v>
       </c>
       <c r="E318" s="8">
-        <v>4012592991.87</v>
+        <v>4003004021.86</v>
       </c>
       <c r="F318" s="9">
-        <v>50511</v>
+        <v>50515</v>
       </c>
       <c r="G318" s="8">
-        <v>2279724013.61</v>
+        <v>2300159077.13</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -10116,19 +10116,19 @@
         <v>638</v>
       </c>
       <c r="C319" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D319" s="7">
-        <v>0.085999</v>
+        <v>46150</v>
+      </c>
+      <c r="D319" s="10">
+        <v>0.08614</v>
       </c>
       <c r="E319" s="8">
-        <v>9003817102.96</v>
+        <v>9010311561.8</v>
       </c>
       <c r="F319" s="9">
-        <v>190203</v>
+        <v>190227</v>
       </c>
       <c r="G319" s="8">
-        <v>774317957.55</v>
+        <v>776151601.54</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -10139,19 +10139,19 @@
         <v>640</v>
       </c>
       <c r="C320" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D320" s="7">
-        <v>0.109892</v>
+        <v>0.111089</v>
       </c>
       <c r="E320" s="8">
-        <v>23132873052.83</v>
+        <v>23102295702.84</v>
       </c>
       <c r="F320" s="9">
-        <v>138114</v>
+        <v>138080</v>
       </c>
       <c r="G320" s="8">
-        <v>2542108573.55</v>
+        <v>2566417125.07</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -10162,19 +10162,19 @@
         <v>642</v>
       </c>
       <c r="C321" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D321" s="7">
-        <v>0.152333</v>
+        <v>0.152746</v>
       </c>
       <c r="E321" s="8">
-        <v>13075173959.86</v>
+        <v>13231115212.93</v>
       </c>
       <c r="F321" s="9">
-        <v>32637</v>
+        <v>41529</v>
       </c>
       <c r="G321" s="8">
-        <v>1991782530.64</v>
+        <v>2020994447.26</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -10185,19 +10185,19 @@
         <v>644</v>
       </c>
       <c r="C322" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D322" s="7">
-        <v>0.134015</v>
+        <v>0.134167</v>
       </c>
       <c r="E322" s="8">
-        <v>530980024.26</v>
+        <v>530802437.34</v>
       </c>
       <c r="F322" s="9">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="G322" s="8">
-        <v>71159424.94</v>
+        <v>71215935.49</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -10208,19 +10208,19 @@
         <v>646</v>
       </c>
       <c r="C323" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D323" s="7">
-        <v>0.139577</v>
+        <v>0.140553</v>
       </c>
       <c r="E323" s="8">
-        <v>227669970.36</v>
+        <v>228120666.71</v>
       </c>
       <c r="F323" s="9">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G323" s="8">
-        <v>31777526.84</v>
+        <v>32063030.64</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -10231,19 +10231,19 @@
         <v>648</v>
       </c>
       <c r="C324" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D324" s="7">
-        <v>0.171212</v>
+        <v>0.172579</v>
       </c>
       <c r="E324" s="8">
-        <v>300569096.37</v>
+        <v>302165794.22</v>
       </c>
       <c r="F324" s="9">
         <v>535</v>
       </c>
       <c r="G324" s="8">
-        <v>51461174.85</v>
+        <v>52147486.4</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -10254,19 +10254,19 @@
         <v>650</v>
       </c>
       <c r="C325" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D325" s="7">
-        <v>0.204157</v>
+        <v>0.206111</v>
       </c>
       <c r="E325" s="8">
-        <v>362041762.89</v>
+        <v>361784090.04</v>
       </c>
       <c r="F325" s="9">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G325" s="8">
-        <v>73913352.53</v>
+        <v>74567512.01</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -10277,19 +10277,19 @@
         <v>652</v>
       </c>
       <c r="C326" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D326" s="7">
-        <v>0.143702</v>
+        <v>0.144299</v>
       </c>
       <c r="E326" s="8">
-        <v>421116958.47</v>
+        <v>424484209.57</v>
       </c>
       <c r="F326" s="9">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="G326" s="8">
-        <v>60515232.15</v>
+        <v>61252749.34</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -10300,19 +10300,19 @@
         <v>654</v>
       </c>
       <c r="C327" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D327" s="7">
-        <v>0.099539</v>
+        <v>0.100652</v>
       </c>
       <c r="E327" s="8">
-        <v>40694171355.6</v>
+        <v>40624638536</v>
       </c>
       <c r="F327" s="9">
-        <v>374243</v>
+        <v>374107</v>
       </c>
       <c r="G327" s="8">
-        <v>4050655341.06</v>
+        <v>4088967929.61</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -10323,19 +10323,19 @@
         <v>656</v>
       </c>
       <c r="C328" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D328" s="7">
-        <v>0.177175</v>
+        <v>0.178983</v>
       </c>
       <c r="E328" s="8">
-        <v>193791953.16</v>
+        <v>193823734.55</v>
       </c>
       <c r="F328" s="9">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G328" s="8">
-        <v>34335000.6</v>
+        <v>34691138.76</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -10346,19 +10346,19 @@
         <v>658</v>
       </c>
       <c r="C329" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D329" s="7">
-        <v>0.208552</v>
+        <v>0.210898</v>
       </c>
       <c r="E329" s="8">
-        <v>240689671.87</v>
+        <v>241246817.35</v>
       </c>
       <c r="F329" s="9">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="G329" s="8">
-        <v>50196279.56</v>
+        <v>50878470.66</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -10369,19 +10369,19 @@
         <v>660</v>
       </c>
       <c r="C330" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D330" s="7">
-        <v>0.296713</v>
+        <v>0.298772</v>
       </c>
       <c r="E330" s="8">
-        <v>1271390224.04</v>
+        <v>1267326041.09</v>
       </c>
       <c r="F330" s="9">
-        <v>8879</v>
+        <v>8876</v>
       </c>
       <c r="G330" s="8">
-        <v>377238197.6</v>
+        <v>378641870.68</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
@@ -10392,19 +10392,19 @@
         <v>662</v>
       </c>
       <c r="C331" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D331" s="7">
-        <v>0.092812</v>
+        <v>0.093722</v>
       </c>
       <c r="E331" s="8">
-        <v>6875937323.47</v>
+        <v>6888183797.74</v>
       </c>
       <c r="F331" s="9">
-        <v>123299</v>
+        <v>123468</v>
       </c>
       <c r="G331" s="8">
-        <v>638166463.57</v>
+        <v>645571855.51</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
@@ -10415,19 +10415,19 @@
         <v>664</v>
       </c>
       <c r="C332" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D332" s="7">
-        <v>0.075127</v>
+        <v>0.075608</v>
       </c>
       <c r="E332" s="8">
-        <v>103852054455.64</v>
+        <v>103795837403.35</v>
       </c>
       <c r="F332" s="9">
-        <v>148752</v>
+        <v>148847</v>
       </c>
       <c r="G332" s="8">
-        <v>7802069239.03</v>
+        <v>7847846535.55</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
@@ -10438,19 +10438,19 @@
         <v>666</v>
       </c>
       <c r="C333" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D333" s="7">
-        <v>0.066362</v>
+        <v>0.066773</v>
       </c>
       <c r="E333" s="8">
-        <v>112164701865.31</v>
+        <v>112013718303.9</v>
       </c>
       <c r="F333" s="9">
-        <v>100056</v>
+        <v>100136</v>
       </c>
       <c r="G333" s="8">
-        <v>7443490204.97</v>
+        <v>7479463210.12</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
@@ -10461,19 +10461,19 @@
         <v>668</v>
       </c>
       <c r="C334" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D334" s="7">
-        <v>0.087852</v>
+        <v>0.088474</v>
       </c>
       <c r="E334" s="8">
-        <v>65050749596.98</v>
+        <v>65131970566.91</v>
       </c>
       <c r="F334" s="9">
-        <v>123453</v>
+        <v>123551</v>
       </c>
       <c r="G334" s="8">
-        <v>5714826577.55</v>
+        <v>5762511728.79</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
@@ -10484,19 +10484,19 @@
         <v>670</v>
       </c>
       <c r="C335" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D335" s="7">
-        <v>0.458965</v>
+        <v>0.464951</v>
       </c>
       <c r="E335" s="8">
-        <v>52407319173.77</v>
+        <v>52352584505.58</v>
       </c>
       <c r="F335" s="9">
-        <v>126674</v>
+        <v>126613</v>
       </c>
       <c r="G335" s="8">
-        <v>24053126981.9</v>
+        <v>24341408192.86</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
@@ -10507,19 +10507,19 @@
         <v>672</v>
       </c>
       <c r="C336" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D336" s="7">
-        <v>0.100028</v>
+        <v>0.100626</v>
       </c>
       <c r="E336" s="8">
-        <v>5346958630.71</v>
+        <v>5338275889.37</v>
       </c>
       <c r="F336" s="9">
-        <v>8794</v>
+        <v>8789</v>
       </c>
       <c r="G336" s="8">
-        <v>534844222.32</v>
+        <v>537169180.94</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
@@ -10530,19 +10530,19 @@
         <v>674</v>
       </c>
       <c r="C337" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D337" s="7">
-        <v>0.365123</v>
+        <v>0.370648</v>
       </c>
       <c r="E337" s="8">
-        <v>15787714001.66</v>
+        <v>15793380901.92</v>
       </c>
       <c r="F337" s="9">
-        <v>28604</v>
+        <v>28578</v>
       </c>
       <c r="G337" s="8">
-        <v>5764449703.22</v>
+        <v>5853784413.38</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
@@ -10553,19 +10553,19 @@
         <v>676</v>
       </c>
       <c r="C338" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D338" s="7">
-        <v>0.010355</v>
+        <v>0.010472</v>
       </c>
       <c r="E338" s="8">
-        <v>79808284423.04</v>
+        <v>80528920546.69</v>
       </c>
       <c r="F338" s="9">
-        <v>4400</v>
+        <v>4448</v>
       </c>
       <c r="G338" s="8">
-        <v>826421120.79</v>
+        <v>843258631.52</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
@@ -10576,19 +10576,19 @@
         <v>678</v>
       </c>
       <c r="C339" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D339" s="7">
-        <v>0.082237</v>
+        <v>0.082336</v>
       </c>
       <c r="E339" s="8">
-        <v>3718766233.8</v>
+        <v>3717486733.9</v>
       </c>
       <c r="F339" s="9">
-        <v>78490</v>
+        <v>78511</v>
       </c>
       <c r="G339" s="8">
-        <v>305821157.42</v>
+        <v>306081131.74</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
@@ -10599,19 +10599,19 @@
         <v>680</v>
       </c>
       <c r="C340" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D340" s="7">
-        <v>0.091841</v>
+        <v>0.092148</v>
       </c>
       <c r="E340" s="8">
-        <v>626458191.77</v>
+        <v>626464524.99</v>
       </c>
       <c r="F340" s="9">
-        <v>12568</v>
+        <v>12912</v>
       </c>
       <c r="G340" s="8">
-        <v>57534592.23</v>
+        <v>57727689.19</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -10622,19 +10622,19 @@
         <v>682</v>
       </c>
       <c r="C341" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D341" s="7">
-        <v>0.043714</v>
+        <v>0.043877</v>
       </c>
       <c r="E341" s="8">
-        <v>1066963727.06</v>
+        <v>1066499971.45</v>
       </c>
       <c r="F341" s="9">
         <v>2229</v>
       </c>
       <c r="G341" s="8">
-        <v>46640833.86</v>
+        <v>46794447.78</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
@@ -10645,19 +10645,19 @@
         <v>684</v>
       </c>
       <c r="C342" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D342" s="7">
-        <v>0.049923</v>
+        <v>0.049753</v>
       </c>
       <c r="E342" s="8">
-        <v>3942984998.31</v>
+        <v>3940629035.35</v>
       </c>
       <c r="F342" s="9">
-        <v>4348</v>
+        <v>4349</v>
       </c>
       <c r="G342" s="8">
-        <v>196846511.95</v>
+        <v>196059730.17</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
@@ -10668,19 +10668,19 @@
         <v>686</v>
       </c>
       <c r="C343" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D343" s="7">
-        <v>0.014063</v>
+        <v>0.014159</v>
       </c>
       <c r="E343" s="8">
-        <v>34408860561.09</v>
+        <v>34410872957.08</v>
       </c>
       <c r="F343" s="9">
-        <v>27999</v>
+        <v>28230</v>
       </c>
       <c r="G343" s="8">
-        <v>483885386.51</v>
+        <v>487207033.23</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
@@ -10691,19 +10691,19 @@
         <v>688</v>
       </c>
       <c r="C344" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D344" s="7">
-        <v>0.074912</v>
+        <v>0.076413</v>
       </c>
       <c r="E344" s="8">
-        <v>50496067946.92</v>
+        <v>51157062971.81</v>
       </c>
       <c r="F344" s="9">
-        <v>122887</v>
+        <v>123358</v>
       </c>
       <c r="G344" s="8">
-        <v>3782760888.13</v>
+        <v>3909071249.26</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
@@ -10714,19 +10714,19 @@
         <v>690</v>
       </c>
       <c r="C345" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D345" s="7">
-        <v>0.013015</v>
+        <v>0.012933</v>
       </c>
       <c r="E345" s="8">
-        <v>15893806326.72</v>
+        <v>16197289473.01</v>
       </c>
       <c r="F345" s="9">
-        <v>5885</v>
+        <v>5998</v>
       </c>
       <c r="G345" s="8">
-        <v>206851286.99</v>
+        <v>209475188.55</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
@@ -10737,19 +10737,19 @@
         <v>692</v>
       </c>
       <c r="C346" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D346" s="7">
-        <v>0.014897</v>
+        <v>0.014913</v>
       </c>
       <c r="E346" s="8">
-        <v>73292290987.98</v>
+        <v>71077348206.53</v>
       </c>
       <c r="F346" s="9">
-        <v>19275</v>
+        <v>19246</v>
       </c>
       <c r="G346" s="8">
-        <v>1091839237.81</v>
+        <v>1059945584.23</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
@@ -10760,19 +10760,19 @@
         <v>694</v>
       </c>
       <c r="C347" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D347" s="7">
-        <v>0.049702</v>
+        <v>0.049905</v>
       </c>
       <c r="E347" s="8">
-        <v>7308557347.01</v>
+        <v>7308095231.07</v>
       </c>
       <c r="F347" s="9">
-        <v>9446</v>
+        <v>9448</v>
       </c>
       <c r="G347" s="8">
-        <v>363252168.03</v>
+        <v>364709559.74</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
@@ -10783,19 +10783,19 @@
         <v>696</v>
       </c>
       <c r="C348" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D348" s="7">
-        <v>0.087193</v>
+        <v>0.087456</v>
       </c>
       <c r="E348" s="8">
-        <v>587419234.03</v>
+        <v>592218651.66</v>
       </c>
       <c r="F348" s="9">
-        <v>6969</v>
+        <v>7018</v>
       </c>
       <c r="G348" s="8">
-        <v>51218853.41</v>
+        <v>51793046.12</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
@@ -10806,19 +10806,19 @@
         <v>698</v>
       </c>
       <c r="C349" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D349" s="7">
-        <v>0.049007</v>
+        <v>0.049093</v>
       </c>
       <c r="E349" s="8">
-        <v>3857964420.95</v>
+        <v>3815294242.96</v>
       </c>
       <c r="F349" s="9">
-        <v>5900</v>
+        <v>5877</v>
       </c>
       <c r="G349" s="8">
-        <v>189068371.14</v>
+        <v>187304222.06</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
@@ -10829,19 +10829,19 @@
         <v>700</v>
       </c>
       <c r="C350" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D350" s="7">
-        <v>0.020877</v>
+        <v>0.021102</v>
       </c>
       <c r="E350" s="8">
-        <v>8746975040.59</v>
+        <v>8775738463.02</v>
       </c>
       <c r="F350" s="9">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G350" s="8">
-        <v>182610890.08</v>
+        <v>185187554.95</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
@@ -10852,19 +10852,19 @@
         <v>702</v>
       </c>
       <c r="C351" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D351" s="7">
-        <v>0.015356</v>
+        <v>0.015411</v>
       </c>
       <c r="E351" s="8">
-        <v>15895998136.68</v>
+        <v>15912615135.14</v>
       </c>
       <c r="F351" s="9">
-        <v>5914</v>
+        <v>5916</v>
       </c>
       <c r="G351" s="8">
-        <v>244106880.53</v>
+        <v>245236136.01</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -10875,19 +10875,19 @@
         <v>704</v>
       </c>
       <c r="C352" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D352" s="7">
-        <v>0.014141</v>
+        <v>46150</v>
+      </c>
+      <c r="D352" s="10">
+        <v>0.01419</v>
       </c>
       <c r="E352" s="8">
-        <v>22292686425.57</v>
+        <v>22385626900.31</v>
       </c>
       <c r="F352" s="9">
-        <v>5810</v>
+        <v>5830</v>
       </c>
       <c r="G352" s="8">
-        <v>315250463.3</v>
+        <v>317659040.45</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -10898,19 +10898,19 @@
         <v>706</v>
       </c>
       <c r="C353" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D353" s="7">
-        <v>0.014598</v>
+        <v>0.014665</v>
       </c>
       <c r="E353" s="8">
-        <v>23877543852.89</v>
+        <v>24122923563.29</v>
       </c>
       <c r="F353" s="9">
-        <v>10819</v>
+        <v>10870</v>
       </c>
       <c r="G353" s="8">
-        <v>348563842.59</v>
+        <v>353771931.58</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
@@ -10921,19 +10921,19 @@
         <v>708</v>
       </c>
       <c r="C354" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D354" s="7">
-        <v>0.016274</v>
+        <v>0.016595</v>
       </c>
       <c r="E354" s="8">
-        <v>39489856551.25</v>
+        <v>40424911062.8</v>
       </c>
       <c r="F354" s="9">
-        <v>10716</v>
+        <v>10862</v>
       </c>
       <c r="G354" s="8">
-        <v>642650171.8</v>
+        <v>670853632.27</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -10944,19 +10944,19 @@
         <v>710</v>
       </c>
       <c r="C355" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D355" s="7">
-        <v>0.049287</v>
+        <v>0.049646</v>
       </c>
       <c r="E355" s="8">
-        <v>2880734166.46</v>
+        <v>2869349251.13</v>
       </c>
       <c r="F355" s="9">
-        <v>5125</v>
+        <v>5120</v>
       </c>
       <c r="G355" s="8">
-        <v>141982386.68</v>
+        <v>142453146.63</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
@@ -10967,19 +10967,19 @@
         <v>712</v>
       </c>
       <c r="C356" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D356" s="7">
-        <v>0.230609</v>
+        <v>0.232096</v>
       </c>
       <c r="E356" s="8">
-        <v>8829597355.9</v>
+        <v>8849801580.95</v>
       </c>
       <c r="F356" s="9">
-        <v>47853</v>
+        <v>47903</v>
       </c>
       <c r="G356" s="8">
-        <v>2036183731.78</v>
+        <v>2054002974.46</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
@@ -10990,19 +10990,19 @@
         <v>714</v>
       </c>
       <c r="C357" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D357" s="7">
-        <v>0.083091</v>
+        <v>0.083243</v>
       </c>
       <c r="E357" s="8">
-        <v>11989259271.99</v>
+        <v>11992459733.17</v>
       </c>
       <c r="F357" s="9">
-        <v>21992</v>
+        <v>21979</v>
       </c>
       <c r="G357" s="8">
-        <v>996196777.72</v>
+        <v>998286660.86</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
@@ -11013,19 +11013,19 @@
         <v>716</v>
       </c>
       <c r="C358" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D358" s="10">
-        <v>0.31314</v>
+        <v>46150</v>
+      </c>
+      <c r="D358" s="7">
+        <v>0.313209</v>
       </c>
       <c r="E358" s="8">
-        <v>3858919498.01</v>
+        <v>3855603022.3</v>
       </c>
       <c r="F358" s="9">
-        <v>27489</v>
+        <v>27476</v>
       </c>
       <c r="G358" s="8">
-        <v>1208383841.22</v>
+        <v>1207608325.64</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
@@ -11036,19 +11036,19 @@
         <v>718</v>
       </c>
       <c r="C359" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D359" s="7">
-        <v>1.401348</v>
+        <v>1.418431</v>
       </c>
       <c r="E359" s="8">
-        <v>8851352584.12</v>
+        <v>8839450299.29</v>
       </c>
       <c r="F359" s="9">
-        <v>245255</v>
+        <v>245798</v>
       </c>
       <c r="G359" s="8">
-        <v>12403825621.43</v>
+        <v>12538152110.07</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
@@ -11059,19 +11059,19 @@
         <v>720</v>
       </c>
       <c r="C360" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D360" s="7">
-        <v>0.096822</v>
+        <v>0.098215</v>
       </c>
       <c r="E360" s="8">
-        <v>541569975832.4</v>
+        <v>541123728462.15</v>
       </c>
       <c r="F360" s="9">
-        <v>2779767</v>
+        <v>2778494</v>
       </c>
       <c r="G360" s="8">
-        <v>52436136594.47</v>
+        <v>53146303776.16</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
@@ -11082,19 +11082,19 @@
         <v>722</v>
       </c>
       <c r="C361" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D361" s="7">
-        <v>0.325833</v>
+        <v>46150</v>
+      </c>
+      <c r="D361" s="10">
+        <v>0.32854</v>
       </c>
       <c r="E361" s="8">
-        <v>23900574353.09</v>
+        <v>23893944773.2</v>
       </c>
       <c r="F361" s="9">
-        <v>423179</v>
+        <v>423295</v>
       </c>
       <c r="G361" s="8">
-        <v>7787588818.27</v>
+        <v>7850117139.41</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
@@ -11105,19 +11105,19 @@
         <v>724</v>
       </c>
       <c r="C362" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D362" s="7">
-        <v>0.351125</v>
+        <v>0.351984</v>
       </c>
       <c r="E362" s="8">
-        <v>86008742273.48</v>
+        <v>86157607522.74</v>
       </c>
       <c r="F362" s="9">
-        <v>434077</v>
+        <v>399404</v>
       </c>
       <c r="G362" s="8">
-        <v>30199838752.96</v>
+        <v>30326129055.36</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
@@ -11128,19 +11128,19 @@
         <v>726</v>
       </c>
       <c r="C363" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D363" s="7">
-        <v>0.226261</v>
+        <v>0.229488</v>
       </c>
       <c r="E363" s="8">
-        <v>20418111331.21</v>
+        <v>20469076023.4</v>
       </c>
       <c r="F363" s="9">
-        <v>70162</v>
+        <v>70276</v>
       </c>
       <c r="G363" s="8">
-        <v>4619827831.99</v>
+        <v>4697405564.67</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
@@ -11151,19 +11151,19 @@
         <v>728</v>
       </c>
       <c r="C364" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D364" s="7">
-        <v>0.102486</v>
+        <v>0.102781</v>
       </c>
       <c r="E364" s="8">
-        <v>3773736784.59</v>
+        <v>3781783652.97</v>
       </c>
       <c r="F364" s="9">
-        <v>8027</v>
+        <v>8029</v>
       </c>
       <c r="G364" s="8">
-        <v>386756335.72</v>
+        <v>388695167.72</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
@@ -11174,19 +11174,19 @@
         <v>730</v>
       </c>
       <c r="C365" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D365" s="7">
-        <v>0.139032</v>
+        <v>0.140112</v>
       </c>
       <c r="E365" s="8">
-        <v>103974177615.54</v>
+        <v>103920779828.54</v>
       </c>
       <c r="F365" s="9">
-        <v>1907626</v>
+        <v>1907180</v>
       </c>
       <c r="G365" s="8">
-        <v>14455740977.87</v>
+        <v>14560563575.81</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
@@ -11197,19 +11197,19 @@
         <v>732</v>
       </c>
       <c r="C366" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D366" s="7">
-        <v>0.136795</v>
+        <v>46150</v>
+      </c>
+      <c r="D366" s="10">
+        <v>0.13732</v>
       </c>
       <c r="E366" s="8">
-        <v>57945083681.75</v>
+        <v>57617488298.5</v>
       </c>
       <c r="F366" s="9">
-        <v>120658</v>
+        <v>120920</v>
       </c>
       <c r="G366" s="8">
-        <v>7926572619.05</v>
+        <v>7912026471.78</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
@@ -11220,19 +11220,19 @@
         <v>734</v>
       </c>
       <c r="C367" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D367" s="10">
-        <v>0.73948</v>
+        <v>46150</v>
+      </c>
+      <c r="D367" s="7">
+        <v>0.742334</v>
       </c>
       <c r="E367" s="8">
-        <v>16819132258.23</v>
+        <v>16761074779.11</v>
       </c>
       <c r="F367" s="9">
-        <v>342366</v>
+        <v>337294</v>
       </c>
       <c r="G367" s="8">
-        <v>12437418343.65</v>
+        <v>12442321215.91</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
@@ -11243,19 +11243,19 @@
         <v>736</v>
       </c>
       <c r="C368" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D368" s="7">
-        <v>0.147366</v>
+        <v>0.148524</v>
       </c>
       <c r="E368" s="8">
-        <v>31118221453.66</v>
+        <v>31090179945.63</v>
       </c>
       <c r="F368" s="9">
-        <v>93157</v>
+        <v>93099</v>
       </c>
       <c r="G368" s="8">
-        <v>4585767603.37</v>
+        <v>4617644605.41</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
@@ -11266,19 +11266,19 @@
         <v>738</v>
       </c>
       <c r="C369" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D369" s="7">
-        <v>0.173616</v>
+        <v>0.174865</v>
       </c>
       <c r="E369" s="8">
-        <v>2083180916.6</v>
+        <v>2090746546.55</v>
       </c>
       <c r="F369" s="9">
-        <v>7381</v>
+        <v>7387</v>
       </c>
       <c r="G369" s="8">
-        <v>361673917.95</v>
+        <v>365599028.71</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
@@ -11289,19 +11289,19 @@
         <v>740</v>
       </c>
       <c r="C370" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D370" s="10">
-        <v>0.38483</v>
+        <v>46150</v>
+      </c>
+      <c r="D370" s="7">
+        <v>0.385244</v>
       </c>
       <c r="E370" s="8">
-        <v>5048368491.42</v>
+        <v>5032243710.89</v>
       </c>
       <c r="F370" s="9">
         <v>19141</v>
       </c>
       <c r="G370" s="8">
-        <v>1942764684.48</v>
+        <v>1938643938.5</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
@@ -11312,19 +11312,19 @@
         <v>742</v>
       </c>
       <c r="C371" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D371" s="7">
-        <v>0.786235</v>
+        <v>0.797873</v>
       </c>
       <c r="E371" s="8">
-        <v>329269755677.66</v>
+        <v>329165204817.81</v>
       </c>
       <c r="F371" s="9">
-        <v>2043644</v>
+        <v>2043143</v>
       </c>
       <c r="G371" s="8">
-        <v>258883396339.9</v>
+        <v>262632050363.03</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
@@ -11335,19 +11335,19 @@
         <v>744</v>
       </c>
       <c r="C372" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D372" s="7">
-        <v>0.160157</v>
+        <v>0.160382</v>
       </c>
       <c r="E372" s="8">
-        <v>24051793343.15</v>
+        <v>24031340942.32</v>
       </c>
       <c r="F372" s="9">
-        <v>109576</v>
+        <v>109540</v>
       </c>
       <c r="G372" s="8">
-        <v>3852066120.22</v>
+        <v>3854204929.8</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
@@ -11358,19 +11358,19 @@
         <v>746</v>
       </c>
       <c r="C373" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D373" s="10">
-        <v>0.20041</v>
+        <v>46150</v>
+      </c>
+      <c r="D373" s="7">
+        <v>0.202384</v>
       </c>
       <c r="E373" s="8">
-        <v>3590303707.07</v>
+        <v>3590964658.65</v>
       </c>
       <c r="F373" s="9">
-        <v>11484</v>
+        <v>11475</v>
       </c>
       <c r="G373" s="8">
-        <v>719531463.54</v>
+        <v>726752634.29</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
@@ -11381,19 +11381,19 @@
         <v>748</v>
       </c>
       <c r="C374" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D374" s="7">
-        <v>0.428177</v>
+        <v>0.434836</v>
       </c>
       <c r="E374" s="8">
-        <v>55672197761.8</v>
+        <v>55344159339.83</v>
       </c>
       <c r="F374" s="9">
-        <v>288989</v>
+        <v>287959</v>
       </c>
       <c r="G374" s="8">
-        <v>23837573740.96</v>
+        <v>24065634546.5</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
@@ -11404,19 +11404,19 @@
         <v>750</v>
       </c>
       <c r="C375" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D375" s="7">
-        <v>0.541249</v>
+        <v>46150</v>
+      </c>
+      <c r="D375" s="10">
+        <v>0.54498</v>
       </c>
       <c r="E375" s="8">
-        <v>1277109555.43</v>
+        <v>1291976193.17</v>
       </c>
       <c r="F375" s="9">
-        <v>14541</v>
+        <v>14687</v>
       </c>
       <c r="G375" s="8">
-        <v>691234311.9</v>
+        <v>704100594.99</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
@@ -11427,19 +11427,19 @@
         <v>752</v>
       </c>
       <c r="C376" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D376" s="7">
-        <v>0.192052</v>
+        <v>0.194466</v>
       </c>
       <c r="E376" s="8">
-        <v>6817016442.9</v>
+        <v>6822218975.35</v>
       </c>
       <c r="F376" s="9">
-        <v>16214</v>
+        <v>16202</v>
       </c>
       <c r="G376" s="8">
-        <v>1309223210.16</v>
+        <v>1326692475.68</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
@@ -11450,19 +11450,19 @@
         <v>754</v>
       </c>
       <c r="C377" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D377" s="7">
-        <v>0.120423</v>
+        <v>0.121017</v>
       </c>
       <c r="E377" s="8">
-        <v>7593167272.15</v>
+        <v>7591292945.07</v>
       </c>
       <c r="F377" s="9">
-        <v>23894</v>
+        <v>23874</v>
       </c>
       <c r="G377" s="8">
-        <v>914393989.55</v>
+        <v>918675216.66</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
@@ -11473,19 +11473,19 @@
         <v>756</v>
       </c>
       <c r="C378" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D378" s="7">
-        <v>0.184402</v>
+        <v>0.185638</v>
       </c>
       <c r="E378" s="8">
-        <v>14141655268.82</v>
+        <v>14145240889.05</v>
       </c>
       <c r="F378" s="9">
-        <v>50763</v>
+        <v>50758</v>
       </c>
       <c r="G378" s="8">
-        <v>2607744546.95</v>
+        <v>2625893736.22</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
@@ -11496,19 +11496,19 @@
         <v>758</v>
       </c>
       <c r="C379" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D379" s="7">
-        <v>0.089523</v>
+        <v>0.089993</v>
       </c>
       <c r="E379" s="8">
-        <v>396523448793.17</v>
+        <v>396696577633.96</v>
       </c>
       <c r="F379" s="9">
-        <v>1946550</v>
+        <v>1947523</v>
       </c>
       <c r="G379" s="8">
-        <v>35497965143.5</v>
+        <v>35699804054.05</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
@@ -11519,19 +11519,19 @@
         <v>760</v>
       </c>
       <c r="C380" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D380" s="7">
-        <v>0.157197</v>
+        <v>0.158041</v>
       </c>
       <c r="E380" s="8">
-        <v>1154960978.34</v>
+        <v>1154077976.78</v>
       </c>
       <c r="F380" s="9">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="G380" s="8">
-        <v>181556221.67</v>
+        <v>182391199.2</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
@@ -11542,19 +11542,19 @@
         <v>762</v>
       </c>
       <c r="C381" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D381" s="7">
-        <v>0.193267</v>
+        <v>0.194808</v>
       </c>
       <c r="E381" s="8">
-        <v>1023047590.88</v>
+        <v>1023152568.87</v>
       </c>
       <c r="F381" s="9">
         <v>1796</v>
       </c>
       <c r="G381" s="8">
-        <v>197720942.99</v>
+        <v>199318162.87</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
@@ -11565,19 +11565,19 @@
         <v>764</v>
       </c>
       <c r="C382" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D382" s="10">
-        <v>0.17676</v>
+        <v>46150</v>
+      </c>
+      <c r="D382" s="7">
+        <v>0.178372</v>
       </c>
       <c r="E382" s="8">
-        <v>585926295.5</v>
+        <v>586050594.76</v>
       </c>
       <c r="F382" s="9">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="G382" s="8">
-        <v>103568564.48</v>
+        <v>104534857.06</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
@@ -11588,19 +11588,19 @@
         <v>766</v>
       </c>
       <c r="C383" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D383" s="7">
-        <v>0.092968</v>
+        <v>0.093582</v>
       </c>
       <c r="E383" s="8">
-        <v>97921756701.14</v>
+        <v>98037847397.7</v>
       </c>
       <c r="F383" s="9">
-        <v>665770</v>
+        <v>666279</v>
       </c>
       <c r="G383" s="8">
-        <v>9103601479.84</v>
+        <v>9174574537.07</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
@@ -11611,19 +11611,19 @@
         <v>768</v>
       </c>
       <c r="C384" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D384" s="7">
-        <v>0.090178</v>
+        <v>0.090269</v>
       </c>
       <c r="E384" s="8">
-        <v>42377231785.79</v>
+        <v>42414034959.31</v>
       </c>
       <c r="F384" s="9">
-        <v>443396</v>
+        <v>446163</v>
       </c>
       <c r="G384" s="8">
-        <v>3821482449.82</v>
+        <v>3828682453.25</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
@@ -11634,19 +11634,19 @@
         <v>770</v>
       </c>
       <c r="C385" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D385" s="7">
-        <v>0.094622</v>
+        <v>0.094847</v>
       </c>
       <c r="E385" s="8">
-        <v>16713467882.92</v>
+        <v>16650362042.84</v>
       </c>
       <c r="F385" s="9">
-        <v>142578</v>
+        <v>299531</v>
       </c>
       <c r="G385" s="8">
-        <v>1581464548.5</v>
+        <v>1579237221.05</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
@@ -11657,19 +11657,19 @@
         <v>772</v>
       </c>
       <c r="C386" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D386" s="7">
-        <v>0.271151</v>
+        <v>0.272605</v>
       </c>
       <c r="E386" s="8">
-        <v>3544742125.67</v>
+        <v>3540291307.85</v>
       </c>
       <c r="F386" s="9">
-        <v>10567</v>
+        <v>10570</v>
       </c>
       <c r="G386" s="8">
-        <v>961158885.46</v>
+        <v>965100955.39</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
@@ -11680,19 +11680,19 @@
         <v>774</v>
       </c>
       <c r="C387" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D387" s="7">
-        <v>0.195937</v>
+        <v>46150</v>
+      </c>
+      <c r="D387" s="10">
+        <v>0.19625</v>
       </c>
       <c r="E387" s="8">
-        <v>2338600038.99</v>
+        <v>2342711063.92</v>
       </c>
       <c r="F387" s="9">
-        <v>7183</v>
+        <v>7195</v>
       </c>
       <c r="G387" s="8">
-        <v>458217837.92</v>
+        <v>459756060.04</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
@@ -11703,19 +11703,19 @@
         <v>776</v>
       </c>
       <c r="C388" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D388" s="10">
-        <v>0.17743</v>
+        <v>46150</v>
+      </c>
+      <c r="D388" s="7">
+        <v>0.177707</v>
       </c>
       <c r="E388" s="8">
-        <v>2516071177.39</v>
+        <v>2524033821.92</v>
       </c>
       <c r="F388" s="9">
-        <v>7685</v>
+        <v>7684</v>
       </c>
       <c r="G388" s="8">
-        <v>446426599.59</v>
+        <v>448539580.89</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -11726,19 +11726,19 @@
         <v>778</v>
       </c>
       <c r="C389" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D389" s="7">
-        <v>0.100113</v>
+        <v>0.100436</v>
       </c>
       <c r="E389" s="8">
-        <v>3850168906.17</v>
+        <v>3844412883.92</v>
       </c>
       <c r="F389" s="9">
-        <v>7232</v>
+        <v>7221</v>
       </c>
       <c r="G389" s="8">
-        <v>385452292.24</v>
+        <v>386116022.91</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
@@ -11749,19 +11749,19 @@
         <v>780</v>
       </c>
       <c r="C390" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D390" s="7">
-        <v>0.233807</v>
+        <v>0.234625</v>
       </c>
       <c r="E390" s="8">
-        <v>1494391545.13</v>
+        <v>1499948869.15</v>
       </c>
       <c r="F390" s="9">
-        <v>5845</v>
+        <v>5850</v>
       </c>
       <c r="G390" s="8">
-        <v>349399316.25</v>
+        <v>351926000.8</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
@@ -11772,19 +11772,19 @@
         <v>782</v>
       </c>
       <c r="C391" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D391" s="10">
-        <v>0.33171</v>
+        <v>46150</v>
+      </c>
+      <c r="D391" s="7">
+        <v>0.332604</v>
       </c>
       <c r="E391" s="8">
-        <v>1910671313.63</v>
+        <v>1917735525.71</v>
       </c>
       <c r="F391" s="9">
-        <v>6337</v>
+        <v>6338</v>
       </c>
       <c r="G391" s="8">
-        <v>633787868.83</v>
+        <v>637847072.28</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
@@ -11795,19 +11795,19 @@
         <v>784</v>
       </c>
       <c r="C392" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D392" s="7">
-        <v>0.279548</v>
+        <v>0.283685</v>
       </c>
       <c r="E392" s="8">
-        <v>14103288858.81</v>
+        <v>14243794842.25</v>
       </c>
       <c r="F392" s="9">
-        <v>67809</v>
+        <v>67912</v>
       </c>
       <c r="G392" s="8">
-        <v>3942540384.01</v>
+        <v>4040752364.41</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
@@ -11818,19 +11818,19 @@
         <v>786</v>
       </c>
       <c r="C393" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D393" s="7">
-        <v>0.061598</v>
+        <v>46150</v>
+      </c>
+      <c r="D393" s="10">
+        <v>0.06294</v>
       </c>
       <c r="E393" s="8">
-        <v>56745007590.55</v>
+        <v>57159048785.05</v>
       </c>
       <c r="F393" s="9">
-        <v>41809</v>
+        <v>41959</v>
       </c>
       <c r="G393" s="8">
-        <v>3495387867.49</v>
+        <v>3597564279.17</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
@@ -11841,19 +11841,19 @@
         <v>788</v>
       </c>
       <c r="C394" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D394" s="7">
-        <v>0.347013</v>
+        <v>0.349627</v>
       </c>
       <c r="E394" s="8">
-        <v>13428638212.07</v>
+        <v>13402494764.15</v>
       </c>
       <c r="F394" s="9">
-        <v>216684</v>
+        <v>217133</v>
       </c>
       <c r="G394" s="8">
-        <v>4659906111.31</v>
+        <v>4685877014.52</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
@@ -11864,19 +11864,19 @@
         <v>790</v>
       </c>
       <c r="C395" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D395" s="7">
-        <v>0.373322</v>
+        <v>0.373818</v>
       </c>
       <c r="E395" s="8">
-        <v>4761035628.65</v>
+        <v>4734238730.27</v>
       </c>
       <c r="F395" s="9">
-        <v>53514</v>
+        <v>53707</v>
       </c>
       <c r="G395" s="8">
-        <v>1777397549.22</v>
+        <v>1769743457.67</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
@@ -11887,19 +11887,19 @@
         <v>792</v>
       </c>
       <c r="C396" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D396" s="7">
-        <v>0.219411</v>
+        <v>0.221359</v>
       </c>
       <c r="E396" s="8">
-        <v>68909792741.6</v>
+        <v>68854272868.66</v>
       </c>
       <c r="F396" s="9">
-        <v>518439</v>
+        <v>518426</v>
       </c>
       <c r="G396" s="8">
-        <v>15119579144.44</v>
+        <v>15241517435.45</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -11910,19 +11910,19 @@
         <v>794</v>
       </c>
       <c r="C397" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D397" s="7">
-        <v>0.133371</v>
+        <v>0.133822</v>
       </c>
       <c r="E397" s="8">
-        <v>12877667358.05</v>
+        <v>12867395453.79</v>
       </c>
       <c r="F397" s="9">
-        <v>45417</v>
+        <v>45410</v>
       </c>
       <c r="G397" s="8">
-        <v>1717511213.36</v>
+        <v>1721935096.38</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
@@ -11933,19 +11933,19 @@
         <v>796</v>
       </c>
       <c r="C398" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D398" s="7">
-        <v>0.063604</v>
+        <v>0.064135</v>
       </c>
       <c r="E398" s="8">
-        <v>58473180731.06</v>
+        <v>58438663620.17</v>
       </c>
       <c r="F398" s="9">
-        <v>323278</v>
+        <v>323084</v>
       </c>
       <c r="G398" s="8">
-        <v>3719144244.86</v>
+        <v>3747950468.35</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>08.05.2026 18:20:04</t>
+    <t>11.05.2026 18:29:01</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2408,13 +2408,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
-    <numFmt numFmtId="169" formatCode="###0.0000;-###0.0000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.0000;-###0.0000;0"/>
+    <numFmt numFmtId="169" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="170" formatCode="###0.000;-###0.000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -2484,7 +2485,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2513,6 +2514,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2917,19 +2921,19 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D6" s="7">
-        <v>0.103127</v>
+        <v>0.103287</v>
       </c>
       <c r="E6" s="8">
-        <v>47845399000.87</v>
+        <v>47844628139.64</v>
       </c>
       <c r="F6" s="9">
-        <v>646357</v>
+        <v>646429</v>
       </c>
       <c r="G6" s="8">
-        <v>4934156609.92</v>
+        <v>4941739883.25</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2940,19 +2944,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D7" s="7">
-        <v>0.411651</v>
+        <v>0.412492</v>
       </c>
       <c r="E7" s="8">
-        <v>17346314689.75</v>
+        <v>17433523550.23</v>
       </c>
       <c r="F7" s="9">
-        <v>151933</v>
+        <v>152150</v>
       </c>
       <c r="G7" s="8">
-        <v>7140629729.38</v>
+        <v>7191193469.85</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2963,19 +2967,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D8" s="7">
-        <v>0.087035</v>
+        <v>0.087307</v>
       </c>
       <c r="E8" s="8">
-        <v>8286136763.74</v>
+        <v>8123655482.13</v>
       </c>
       <c r="F8" s="9">
-        <v>148293</v>
+        <v>146282</v>
       </c>
       <c r="G8" s="8">
-        <v>721187392.29</v>
+        <v>709251834.6</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2986,19 +2990,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D9" s="7">
-        <v>0.370889</v>
+        <v>0.371848</v>
       </c>
       <c r="E9" s="8">
-        <v>142864695000.36</v>
+        <v>142744253153.02</v>
       </c>
       <c r="F9" s="9">
-        <v>490305</v>
+        <v>490628</v>
       </c>
       <c r="G9" s="8">
-        <v>52986989240.11</v>
+        <v>53079105650.02</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3009,19 +3013,19 @@
         <v>20</v>
       </c>
       <c r="C10" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D10" s="7">
-        <v>0.338661</v>
+        <v>0.338478</v>
       </c>
       <c r="E10" s="8">
-        <v>23064770488.13</v>
+        <v>23030648317.05</v>
       </c>
       <c r="F10" s="9">
-        <v>329525</v>
+        <v>329514</v>
       </c>
       <c r="G10" s="8">
-        <v>7811139204.69</v>
+        <v>7795370659.65</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3032,19 +3036,19 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D11" s="7">
-        <v>1.031166</v>
+        <v>1.037541</v>
       </c>
       <c r="E11" s="8">
-        <v>11590702719.47</v>
+        <v>11594160300</v>
       </c>
       <c r="F11" s="9">
-        <v>289158</v>
+        <v>289136</v>
       </c>
       <c r="G11" s="8">
-        <v>11951934946.61</v>
+        <v>12029413942.35</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3055,19 +3059,19 @@
         <v>24</v>
       </c>
       <c r="C12" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D12" s="7">
-        <v>0.725785</v>
+        <v>0.720422</v>
       </c>
       <c r="E12" s="8">
-        <v>136553052854.98</v>
+        <v>136486195072.47</v>
       </c>
       <c r="F12" s="9">
-        <v>726256</v>
+        <v>726306</v>
       </c>
       <c r="G12" s="8">
-        <v>99108163610.65</v>
+        <v>98327647117.87</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3078,19 +3082,19 @@
         <v>26</v>
       </c>
       <c r="C13" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D13" s="7">
-        <v>2.089618</v>
+        <v>2.115388</v>
       </c>
       <c r="E13" s="8">
-        <v>1372867868.41</v>
+        <v>1368307702.23</v>
       </c>
       <c r="F13" s="9">
-        <v>32895</v>
+        <v>32886</v>
       </c>
       <c r="G13" s="8">
-        <v>2868769187.24</v>
+        <v>2894501737.27</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3101,19 +3105,19 @@
         <v>28</v>
       </c>
       <c r="C14" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D14" s="7">
-        <v>0.138331</v>
+        <v>0.138667</v>
       </c>
       <c r="E14" s="8">
-        <v>249861824.28</v>
+        <v>248854978.93</v>
       </c>
       <c r="F14" s="9">
         <v>90</v>
       </c>
       <c r="G14" s="8">
-        <v>34563724.52</v>
+        <v>34508012.08</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3124,19 +3128,19 @@
         <v>30</v>
       </c>
       <c r="C15" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D15" s="10">
-        <v>1.42649</v>
+        <v>46153</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.443246</v>
       </c>
       <c r="E15" s="8">
-        <v>16222456619.3</v>
+        <v>16252205660.13</v>
       </c>
       <c r="F15" s="9">
-        <v>488585</v>
+        <v>488899</v>
       </c>
       <c r="G15" s="8">
-        <v>23141179939</v>
+        <v>23455933882.2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3147,19 +3151,19 @@
         <v>32</v>
       </c>
       <c r="C16" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D16" s="7">
-        <v>0.095416</v>
+        <v>0.095583</v>
       </c>
       <c r="E16" s="8">
-        <v>566155444703.72</v>
+        <v>565705434129.62</v>
       </c>
       <c r="F16" s="9">
-        <v>1955079</v>
+        <v>1953887</v>
       </c>
       <c r="G16" s="8">
-        <v>54020513535.01</v>
+        <v>54071752273.45</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3170,19 +3174,19 @@
         <v>34</v>
       </c>
       <c r="C17" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D17" s="7">
-        <v>0.352575</v>
+        <v>0.352447</v>
       </c>
       <c r="E17" s="8">
-        <v>2123656613.27</v>
+        <v>2119913591.03</v>
       </c>
       <c r="F17" s="9">
-        <v>13420</v>
+        <v>13366</v>
       </c>
       <c r="G17" s="8">
-        <v>748748402.71</v>
+        <v>747157794.06</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3193,19 +3197,19 @@
         <v>36</v>
       </c>
       <c r="C18" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0.147125</v>
+        <v>46153</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.1474</v>
       </c>
       <c r="E18" s="8">
-        <v>32976976615.33</v>
+        <v>32950137071.2</v>
       </c>
       <c r="F18" s="9">
-        <v>238984</v>
+        <v>238746</v>
       </c>
       <c r="G18" s="8">
-        <v>4851721737.52</v>
+        <v>4856859507.79</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3216,19 +3220,19 @@
         <v>38</v>
       </c>
       <c r="C19" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D19" s="7">
-        <v>0.379759</v>
+        <v>0.382652</v>
       </c>
       <c r="E19" s="8">
-        <v>1425221135.43</v>
+        <v>1423507548.34</v>
       </c>
       <c r="F19" s="9">
         <v>538</v>
       </c>
       <c r="G19" s="8">
-        <v>541240810.47</v>
+        <v>544708636.62</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3239,19 +3243,19 @@
         <v>40</v>
       </c>
       <c r="C20" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D20" s="7">
-        <v>0.140686</v>
+        <v>0.141483</v>
       </c>
       <c r="E20" s="8">
-        <v>14776034274.11</v>
+        <v>14772055470.48</v>
       </c>
       <c r="F20" s="9">
-        <v>524782</v>
+        <v>524657</v>
       </c>
       <c r="G20" s="8">
-        <v>2078776934.34</v>
+        <v>2089997148.3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3262,19 +3266,19 @@
         <v>42</v>
       </c>
       <c r="C21" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D21" s="7">
-        <v>0.099204</v>
+        <v>0.099238</v>
       </c>
       <c r="E21" s="8">
-        <v>509380171256.4</v>
+        <v>509018047489.74</v>
       </c>
       <c r="F21" s="9">
-        <v>2302196</v>
+        <v>2301083</v>
       </c>
       <c r="G21" s="8">
-        <v>50532696178.92</v>
+        <v>50513772094.81</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3285,19 +3289,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D22" s="7">
-        <v>0.413811</v>
+        <v>0.413939</v>
       </c>
       <c r="E22" s="8">
-        <v>3453415244.5</v>
+        <v>3480430275.33</v>
       </c>
       <c r="F22" s="9">
-        <v>19480</v>
+        <v>19558</v>
       </c>
       <c r="G22" s="8">
-        <v>1429062357.75</v>
+        <v>1440684907.16</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3308,10 +3312,10 @@
         <v>46</v>
       </c>
       <c r="C23" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D23" s="7">
-        <v>0.096103</v>
+        <v>0.096139</v>
       </c>
       <c r="E23" s="8">
         <v>576051838.57</v>
@@ -3320,7 +3324,7 @@
         <v>4604</v>
       </c>
       <c r="G23" s="8">
-        <v>55360387.49</v>
+        <v>55381095.61</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3331,19 +3335,19 @@
         <v>48</v>
       </c>
       <c r="C24" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D24" s="7">
-        <v>0.231537</v>
+        <v>0.231628</v>
       </c>
       <c r="E24" s="8">
-        <v>1218038786.5</v>
+        <v>1215876250.24</v>
       </c>
       <c r="F24" s="9">
-        <v>4982</v>
+        <v>4978</v>
       </c>
       <c r="G24" s="8">
-        <v>282021480.21</v>
+        <v>281630615.86</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3354,19 +3358,19 @@
         <v>50</v>
       </c>
       <c r="C25" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D25" s="10">
-        <v>0.10741</v>
+        <v>46153</v>
+      </c>
+      <c r="D25" s="7">
+        <v>0.107439</v>
       </c>
       <c r="E25" s="8">
-        <v>66782376410.41</v>
+        <v>66837903700.38</v>
       </c>
       <c r="F25" s="9">
-        <v>765176</v>
+        <v>765498</v>
       </c>
       <c r="G25" s="8">
-        <v>7173067055.94</v>
+        <v>7180980573.5</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3377,19 +3381,19 @@
         <v>52</v>
       </c>
       <c r="C26" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D26" s="7">
-        <v>0.099114</v>
+        <v>0.099257</v>
       </c>
       <c r="E26" s="8">
-        <v>1680204320.76</v>
+        <v>1680601250.93</v>
       </c>
       <c r="F26" s="9">
-        <v>3212</v>
+        <v>3203</v>
       </c>
       <c r="G26" s="8">
-        <v>166532561.54</v>
+        <v>166810816.54</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3400,19 +3404,19 @@
         <v>54</v>
       </c>
       <c r="C27" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D27" s="7">
-        <v>0.094342</v>
+        <v>0.094635</v>
       </c>
       <c r="E27" s="8">
-        <v>61991786915.8</v>
+        <v>62042618441.41</v>
       </c>
       <c r="F27" s="9">
-        <v>715723</v>
+        <v>715738</v>
       </c>
       <c r="G27" s="8">
-        <v>5848434848.46</v>
+        <v>5871388098.82</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3423,19 +3427,19 @@
         <v>56</v>
       </c>
       <c r="C28" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D28" s="7">
-        <v>0.392645</v>
+        <v>0.392442</v>
       </c>
       <c r="E28" s="8">
-        <v>1041718399.88</v>
+        <v>1035774614.35</v>
       </c>
       <c r="F28" s="9">
-        <v>7883</v>
+        <v>7866</v>
       </c>
       <c r="G28" s="8">
-        <v>409025107.55</v>
+        <v>406481675.66</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3446,19 +3450,19 @@
         <v>58</v>
       </c>
       <c r="C29" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D29" s="7">
-        <v>0.652205</v>
+        <v>0.652735</v>
       </c>
       <c r="E29" s="8">
-        <v>214124045.33</v>
+        <v>214652298.86</v>
       </c>
       <c r="F29" s="9">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="G29" s="8">
-        <v>139652803.57</v>
+        <v>140111028.52</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3469,19 +3473,19 @@
         <v>60</v>
       </c>
       <c r="C30" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D30" s="7">
-        <v>2.479514</v>
+        <v>2.496087</v>
       </c>
       <c r="E30" s="8">
-        <v>846198749.34</v>
+        <v>843948204.04</v>
       </c>
       <c r="F30" s="9">
-        <v>19650</v>
+        <v>19654</v>
       </c>
       <c r="G30" s="8">
-        <v>2098161859.17</v>
+        <v>2106568448.87</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3492,19 +3496,19 @@
         <v>62</v>
       </c>
       <c r="C31" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D31" s="7">
-        <v>0.529961</v>
+        <v>0.531128</v>
       </c>
       <c r="E31" s="8">
-        <v>2404497614.57</v>
+        <v>2399766360.65</v>
       </c>
       <c r="F31" s="9">
-        <v>14185</v>
+        <v>14153</v>
       </c>
       <c r="G31" s="8">
-        <v>1274290733.57</v>
+        <v>1274582050.28</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3515,19 +3519,19 @@
         <v>64</v>
       </c>
       <c r="C32" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D32" s="7">
-        <v>0.876252</v>
+        <v>46153</v>
+      </c>
+      <c r="D32" s="11">
+        <v>0.87069</v>
       </c>
       <c r="E32" s="8">
-        <v>12317203211.81</v>
+        <v>12304985635.47</v>
       </c>
       <c r="F32" s="9">
-        <v>77307</v>
+        <v>77438</v>
       </c>
       <c r="G32" s="8">
-        <v>10792978069.14</v>
+        <v>10713828166.61</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3538,19 +3542,19 @@
         <v>66</v>
       </c>
       <c r="C33" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D33" s="7">
-        <v>0.271776</v>
+        <v>0.273414</v>
       </c>
       <c r="E33" s="8">
-        <v>1313176550.77</v>
+        <v>1313952018.69</v>
       </c>
       <c r="F33" s="9">
-        <v>16187</v>
+        <v>16195</v>
       </c>
       <c r="G33" s="8">
-        <v>356890270.47</v>
+        <v>359252782.78</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3561,19 +3565,19 @@
         <v>68</v>
       </c>
       <c r="C34" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D34" s="7">
-        <v>0.127391</v>
+        <v>0.127873</v>
       </c>
       <c r="E34" s="8">
-        <v>3325845400.83</v>
+        <v>3342113426.67</v>
       </c>
       <c r="F34" s="9">
-        <v>54013</v>
+        <v>54756</v>
       </c>
       <c r="G34" s="8">
-        <v>423682098.23</v>
+        <v>427365658.51</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3584,19 +3588,19 @@
         <v>70</v>
       </c>
       <c r="C35" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D35" s="7">
-        <v>0.177344</v>
+        <v>0.177946</v>
       </c>
       <c r="E35" s="8">
-        <v>10760860350.57</v>
+        <v>10720896601.26</v>
       </c>
       <c r="F35" s="9">
-        <v>36653</v>
+        <v>36668</v>
       </c>
       <c r="G35" s="8">
-        <v>1908371773.13</v>
+        <v>1907739143.64</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3607,19 +3611,19 @@
         <v>72</v>
       </c>
       <c r="C36" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D36" s="7">
-        <v>0.208376</v>
+        <v>0.209755</v>
       </c>
       <c r="E36" s="8">
-        <v>1497532573.31</v>
+        <v>1496970025.29</v>
       </c>
       <c r="F36" s="9">
-        <v>32846</v>
+        <v>32833</v>
       </c>
       <c r="G36" s="8">
-        <v>312049839.81</v>
+        <v>313996350.43</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3630,19 +3634,19 @@
         <v>74</v>
       </c>
       <c r="C37" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D37" s="7">
-        <v>0.862831</v>
+        <v>0.874462</v>
       </c>
       <c r="E37" s="8">
-        <v>2452816530.52</v>
+        <v>2457662175.61</v>
       </c>
       <c r="F37" s="9">
-        <v>52483</v>
+        <v>52588</v>
       </c>
       <c r="G37" s="8">
-        <v>2116365273.55</v>
+        <v>2149133382.24</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3653,19 +3657,19 @@
         <v>76</v>
       </c>
       <c r="C38" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D38" s="10">
-        <v>0.17036</v>
+        <v>46153</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0.170862</v>
       </c>
       <c r="E38" s="8">
-        <v>3693157195.13</v>
+        <v>3694866732.93</v>
       </c>
       <c r="F38" s="9">
-        <v>53288</v>
+        <v>53369</v>
       </c>
       <c r="G38" s="8">
-        <v>629164491.21</v>
+        <v>631314011.77</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3676,19 +3680,19 @@
         <v>78</v>
       </c>
       <c r="C39" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D39" s="7">
-        <v>0.108793</v>
+        <v>0.109596</v>
       </c>
       <c r="E39" s="8">
-        <v>8146474832.78</v>
+        <v>8140501637.3</v>
       </c>
       <c r="F39" s="9">
-        <v>96863</v>
+        <v>96851</v>
       </c>
       <c r="G39" s="8">
-        <v>886276319.33</v>
+        <v>892164258.66</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3699,19 +3703,19 @@
         <v>80</v>
       </c>
       <c r="C40" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D40" s="7">
-        <v>0.343953</v>
+        <v>0.343478</v>
       </c>
       <c r="E40" s="8">
-        <v>13959603661.07</v>
+        <v>13924201386.99</v>
       </c>
       <c r="F40" s="9">
-        <v>156799</v>
+        <v>156609</v>
       </c>
       <c r="G40" s="8">
-        <v>4801448064.11</v>
+        <v>4782660800</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3722,19 +3726,19 @@
         <v>82</v>
       </c>
       <c r="C41" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D41" s="7">
-        <v>0.367818</v>
+        <v>0.368847</v>
       </c>
       <c r="E41" s="8">
-        <v>77550254775.26</v>
+        <v>77745578944.98</v>
       </c>
       <c r="F41" s="9">
-        <v>161590</v>
+        <v>167691</v>
       </c>
       <c r="G41" s="8">
-        <v>28524409876.22</v>
+        <v>28676216456.34</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3745,19 +3749,19 @@
         <v>84</v>
       </c>
       <c r="C42" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D42" s="7">
-        <v>0.965888</v>
+        <v>0.965482</v>
       </c>
       <c r="E42" s="8">
-        <v>12805818135.13</v>
+        <v>12810162815.96</v>
       </c>
       <c r="F42" s="9">
-        <v>234224</v>
+        <v>234111</v>
       </c>
       <c r="G42" s="8">
-        <v>12368983658.34</v>
+        <v>12367984479.3</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3768,19 +3772,19 @@
         <v>86</v>
       </c>
       <c r="C43" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D43" s="7">
-        <v>0.697396</v>
+        <v>0.697438</v>
       </c>
       <c r="E43" s="8">
-        <v>8796740294.89</v>
+        <v>8793534689.8</v>
       </c>
       <c r="F43" s="9">
-        <v>121196</v>
+        <v>121163</v>
       </c>
       <c r="G43" s="8">
-        <v>6134807709.92</v>
+        <v>6132946000.33</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3791,19 +3795,19 @@
         <v>88</v>
       </c>
       <c r="C44" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D44" s="7">
-        <v>3.087802</v>
+        <v>46153</v>
+      </c>
+      <c r="D44" s="11">
+        <v>3.09084</v>
       </c>
       <c r="E44" s="8">
-        <v>8446784645.98</v>
+        <v>8440161810.17</v>
       </c>
       <c r="F44" s="9">
-        <v>366479</v>
+        <v>366543</v>
       </c>
       <c r="G44" s="8">
-        <v>26081998231.64</v>
+        <v>26087187364.92</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3814,19 +3818,19 @@
         <v>90</v>
       </c>
       <c r="C45" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D45" s="7">
-        <v>1.169341</v>
+        <v>1.167097</v>
       </c>
       <c r="E45" s="8">
-        <v>3677251425.76</v>
+        <v>3685119571.85</v>
       </c>
       <c r="F45" s="9">
-        <v>85812</v>
+        <v>85824</v>
       </c>
       <c r="G45" s="8">
-        <v>4299959797.34</v>
+        <v>4300892121.64</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3837,19 +3841,19 @@
         <v>92</v>
       </c>
       <c r="C46" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D46" s="10">
-        <v>0.42725</v>
+        <v>46153</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0.427685</v>
       </c>
       <c r="E46" s="8">
-        <v>23803237422.39</v>
+        <v>23764935905.78</v>
       </c>
       <c r="F46" s="9">
-        <v>219159</v>
+        <v>219001</v>
       </c>
       <c r="G46" s="8">
-        <v>10169938884.22</v>
+        <v>10163900087.51</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3860,19 +3864,19 @@
         <v>94</v>
       </c>
       <c r="C47" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D47" s="7">
-        <v>1.028081</v>
+        <v>1.028879</v>
       </c>
       <c r="E47" s="8">
-        <v>9653678140.9</v>
+        <v>9647932380.76</v>
       </c>
       <c r="F47" s="9">
-        <v>207397</v>
+        <v>207357</v>
       </c>
       <c r="G47" s="8">
-        <v>9924767353.89</v>
+        <v>9926556012.97</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3883,19 +3887,19 @@
         <v>96</v>
       </c>
       <c r="C48" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D48" s="7">
-        <v>1.411347</v>
+        <v>1.420652</v>
       </c>
       <c r="E48" s="8">
-        <v>714672911.85</v>
+        <v>714244090.1</v>
       </c>
       <c r="F48" s="9">
         <v>7288</v>
       </c>
       <c r="G48" s="8">
-        <v>1008651519.58</v>
+        <v>1014692536.29</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3906,19 +3910,19 @@
         <v>98</v>
       </c>
       <c r="C49" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D49" s="7">
-        <v>0.130878</v>
+        <v>0.131241</v>
       </c>
       <c r="E49" s="8">
-        <v>94354981019.1</v>
+        <v>94411573885.99</v>
       </c>
       <c r="F49" s="9">
-        <v>209073</v>
+        <v>208985</v>
       </c>
       <c r="G49" s="8">
-        <v>12349008244.55</v>
+        <v>12390631174.66</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3929,19 +3933,19 @@
         <v>100</v>
       </c>
       <c r="C50" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D50" s="7">
-        <v>0.100081</v>
+        <v>0.100356</v>
       </c>
       <c r="E50" s="8">
-        <v>13849702369.62</v>
+        <v>13787614394.43</v>
       </c>
       <c r="F50" s="9">
-        <v>131803</v>
+        <v>133662</v>
       </c>
       <c r="G50" s="8">
-        <v>1386086298.61</v>
+        <v>1383669414.05</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3952,19 +3956,19 @@
         <v>102</v>
       </c>
       <c r="C51" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D51" s="7">
-        <v>0.507371</v>
+        <v>0.507481</v>
       </c>
       <c r="E51" s="8">
-        <v>20372435662.55</v>
+        <v>20356121452.65</v>
       </c>
       <c r="F51" s="9">
-        <v>136636</v>
+        <v>136594</v>
       </c>
       <c r="G51" s="8">
-        <v>10336377330.15</v>
+        <v>10330337328.05</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3975,19 +3979,19 @@
         <v>104</v>
       </c>
       <c r="C52" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D52" s="7">
-        <v>0.217543</v>
+        <v>0.219221</v>
       </c>
       <c r="E52" s="8">
-        <v>2655452436.66</v>
+        <v>2666861290.59</v>
       </c>
       <c r="F52" s="9">
-        <v>10467</v>
+        <v>10480</v>
       </c>
       <c r="G52" s="8">
-        <v>577675580.49</v>
+        <v>584632758.84</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3998,19 +4002,19 @@
         <v>106</v>
       </c>
       <c r="C53" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D53" s="7">
-        <v>0.276567</v>
+        <v>0.279032</v>
       </c>
       <c r="E53" s="8">
-        <v>2925175367.89</v>
+        <v>2937720984.26</v>
       </c>
       <c r="F53" s="9">
-        <v>10787</v>
+        <v>10802</v>
       </c>
       <c r="G53" s="8">
-        <v>809007756.84</v>
+        <v>819718247.47</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -4021,19 +4025,19 @@
         <v>108</v>
       </c>
       <c r="C54" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D54" s="7">
-        <v>0.340062</v>
+        <v>0.340165</v>
       </c>
       <c r="E54" s="8">
-        <v>4563539261.61</v>
+        <v>4562519321.95</v>
       </c>
       <c r="F54" s="9">
-        <v>15924</v>
+        <v>15920</v>
       </c>
       <c r="G54" s="8">
-        <v>1551884963.95</v>
+        <v>1552009094.54</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4044,19 +4048,19 @@
         <v>110</v>
       </c>
       <c r="C55" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D55" s="7">
-        <v>0.319945</v>
+        <v>0.320696</v>
       </c>
       <c r="E55" s="8">
-        <v>2594077428.15</v>
+        <v>2597888249.53</v>
       </c>
       <c r="F55" s="9">
-        <v>10222</v>
+        <v>10232</v>
       </c>
       <c r="G55" s="8">
-        <v>829961183.44</v>
+        <v>833132523.97</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -4067,19 +4071,19 @@
         <v>112</v>
       </c>
       <c r="C56" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D56" s="7">
-        <v>0.226645</v>
+        <v>0.227095</v>
       </c>
       <c r="E56" s="8">
-        <v>1898271261.01</v>
+        <v>1898650893.58</v>
       </c>
       <c r="F56" s="9">
-        <v>6697</v>
+        <v>6692</v>
       </c>
       <c r="G56" s="8">
-        <v>430233540.42</v>
+        <v>431173269.3</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4090,19 +4094,19 @@
         <v>114</v>
       </c>
       <c r="C57" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D57" s="7">
-        <v>0.116124</v>
+        <v>0.116401</v>
       </c>
       <c r="E57" s="8">
-        <v>1628699845.12</v>
+        <v>1626242174.97</v>
       </c>
       <c r="F57" s="9">
-        <v>3903</v>
+        <v>3896</v>
       </c>
       <c r="G57" s="8">
-        <v>189131791.12</v>
+        <v>189296396.33</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -4113,19 +4117,19 @@
         <v>116</v>
       </c>
       <c r="C58" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D58" s="7">
-        <v>0.316089</v>
+        <v>0.318032</v>
       </c>
       <c r="E58" s="8">
-        <v>4469793399.31</v>
+        <v>4477518126.05</v>
       </c>
       <c r="F58" s="9">
-        <v>16843</v>
+        <v>16861</v>
       </c>
       <c r="G58" s="8">
-        <v>1412851972.94</v>
+        <v>1423991984.88</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -4136,19 +4140,19 @@
         <v>118</v>
       </c>
       <c r="C59" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D59" s="7">
-        <v>0.250209</v>
+        <v>0.252037</v>
       </c>
       <c r="E59" s="8">
-        <v>2819624087.72</v>
+        <v>2823589203.47</v>
       </c>
       <c r="F59" s="9">
-        <v>11373</v>
+        <v>11382</v>
       </c>
       <c r="G59" s="8">
-        <v>705495015.62</v>
+        <v>711648118.82</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -4159,19 +4163,19 @@
         <v>120</v>
       </c>
       <c r="C60" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D60" s="7">
-        <v>0.182622</v>
+        <v>0.183619</v>
       </c>
       <c r="E60" s="8">
-        <v>182897989.61</v>
+        <v>184339428.62</v>
       </c>
       <c r="F60" s="9">
         <v>453</v>
       </c>
       <c r="G60" s="8">
-        <v>33401216.31</v>
+        <v>33848161.79</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -4182,19 +4186,19 @@
         <v>122</v>
       </c>
       <c r="C61" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D61" s="7">
-        <v>0.390249</v>
+        <v>0.391022</v>
       </c>
       <c r="E61" s="8">
-        <v>858790007.86</v>
+        <v>858432583.1</v>
       </c>
       <c r="F61" s="9">
         <v>615</v>
       </c>
       <c r="G61" s="8">
-        <v>335141989.78</v>
+        <v>335665630.41</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -4205,19 +4209,19 @@
         <v>124</v>
       </c>
       <c r="C62" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D62" s="7">
-        <v>0.074204</v>
+        <v>0.074336</v>
       </c>
       <c r="E62" s="8">
-        <v>171966432.92</v>
+        <v>171731462</v>
       </c>
       <c r="F62" s="9">
         <v>222</v>
       </c>
       <c r="G62" s="8">
-        <v>12760665.38</v>
+        <v>12765840.8</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -4228,19 +4232,19 @@
         <v>126</v>
       </c>
       <c r="C63" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D63" s="7">
-        <v>0.147079</v>
+        <v>46153</v>
+      </c>
+      <c r="D63" s="11">
+        <v>0.14772</v>
       </c>
       <c r="E63" s="8">
-        <v>111708292.9</v>
+        <v>111972580.16</v>
       </c>
       <c r="F63" s="9">
         <v>292</v>
       </c>
       <c r="G63" s="8">
-        <v>16429916.93</v>
+        <v>16540617.34</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -4251,19 +4255,19 @@
         <v>128</v>
       </c>
       <c r="C64" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D64" s="7">
-        <v>0.264942</v>
+        <v>0.266868</v>
       </c>
       <c r="E64" s="8">
-        <v>218178771.9</v>
+        <v>218383603.05</v>
       </c>
       <c r="F64" s="9">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G64" s="8">
-        <v>57804699.09</v>
+        <v>58279577.25</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4274,19 +4278,19 @@
         <v>130</v>
       </c>
       <c r="C65" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D65" s="7">
-        <v>0.343866</v>
+        <v>46153</v>
+      </c>
+      <c r="D65" s="11">
+        <v>0.34735</v>
       </c>
       <c r="E65" s="8">
-        <v>640020979.33</v>
+        <v>638718422.51</v>
       </c>
       <c r="F65" s="9">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G65" s="8">
-        <v>220081712.1</v>
+        <v>221859007.05</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -4297,19 +4301,19 @@
         <v>132</v>
       </c>
       <c r="C66" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D66" s="7">
-        <v>0.597185</v>
+        <v>0.595679</v>
       </c>
       <c r="E66" s="8">
-        <v>12860826755.09</v>
+        <v>12857918342.34</v>
       </c>
       <c r="F66" s="9">
-        <v>127206</v>
+        <v>127110</v>
       </c>
       <c r="G66" s="8">
-        <v>7680295893.96</v>
+        <v>7659192543.53</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4320,19 +4324,19 @@
         <v>134</v>
       </c>
       <c r="C67" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D67" s="7">
-        <v>0.269475</v>
+        <v>0.271927</v>
       </c>
       <c r="E67" s="8">
-        <v>2020719598.65</v>
+        <v>2026995435.37</v>
       </c>
       <c r="F67" s="9">
-        <v>6125</v>
+        <v>6126</v>
       </c>
       <c r="G67" s="8">
-        <v>544533121.61</v>
+        <v>551194503.1</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -4343,19 +4347,19 @@
         <v>136</v>
       </c>
       <c r="C68" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D68" s="7">
-        <v>2.079029</v>
+        <v>2.084212</v>
       </c>
       <c r="E68" s="8">
-        <v>7001786448.44</v>
+        <v>6999425666.04</v>
       </c>
       <c r="F68" s="9">
-        <v>235908</v>
+        <v>235797</v>
       </c>
       <c r="G68" s="8">
-        <v>14556918457.06</v>
+        <v>14588288018.77</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -4366,19 +4370,19 @@
         <v>138</v>
       </c>
       <c r="C69" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D69" s="7">
-        <v>1.025001</v>
+        <v>1.026844</v>
       </c>
       <c r="E69" s="8">
-        <v>6495035397.1</v>
+        <v>6491241395.28</v>
       </c>
       <c r="F69" s="9">
-        <v>163231</v>
+        <v>163201</v>
       </c>
       <c r="G69" s="8">
-        <v>6657417725.99</v>
+        <v>6665490485.46</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -4389,19 +4393,19 @@
         <v>140</v>
       </c>
       <c r="C70" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D70" s="7">
-        <v>0.337797</v>
+        <v>0.340295</v>
       </c>
       <c r="E70" s="8">
-        <v>12174881686.48</v>
+        <v>12181192494.37</v>
       </c>
       <c r="F70" s="9">
-        <v>189404</v>
+        <v>189245</v>
       </c>
       <c r="G70" s="8">
-        <v>4112637172.04</v>
+        <v>4145197215.85</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4412,19 +4416,19 @@
         <v>142</v>
       </c>
       <c r="C71" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D71" s="7">
-        <v>0.099261</v>
+        <v>0.099534</v>
       </c>
       <c r="E71" s="8">
-        <v>7773984867.65</v>
+        <v>7703301642.25</v>
       </c>
       <c r="F71" s="9">
-        <v>125554</v>
+        <v>124468</v>
       </c>
       <c r="G71" s="8">
-        <v>771651687.67</v>
+        <v>766737310.8</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -4435,19 +4439,19 @@
         <v>144</v>
       </c>
       <c r="C72" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D72" s="7">
-        <v>0.098029</v>
+        <v>0.098148</v>
       </c>
       <c r="E72" s="8">
-        <v>390405298761.8</v>
+        <v>390018638690.42</v>
       </c>
       <c r="F72" s="9">
-        <v>1421962</v>
+        <v>1420871</v>
       </c>
       <c r="G72" s="8">
-        <v>38271027604.75</v>
+        <v>38279634833.73</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4458,19 +4462,19 @@
         <v>146</v>
       </c>
       <c r="C73" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D73" s="7">
-        <v>1.111006</v>
+        <v>1.109923</v>
       </c>
       <c r="E73" s="8">
-        <v>6407486918.91</v>
+        <v>6409720955.94</v>
       </c>
       <c r="F73" s="9">
-        <v>261982</v>
+        <v>261835</v>
       </c>
       <c r="G73" s="8">
-        <v>7118757278.83</v>
+        <v>7114293585.24</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4481,19 +4485,19 @@
         <v>148</v>
       </c>
       <c r="C74" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D74" s="7">
-        <v>0.512492</v>
+        <v>0.512181</v>
       </c>
       <c r="E74" s="8">
-        <v>6729932372.7</v>
+        <v>6731580457.91</v>
       </c>
       <c r="F74" s="9">
-        <v>65596</v>
+        <v>65560</v>
       </c>
       <c r="G74" s="8">
-        <v>3449037871.47</v>
+        <v>3447785378.6</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -4504,19 +4508,19 @@
         <v>150</v>
       </c>
       <c r="C75" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D75" s="10">
-        <v>1.59729</v>
+        <v>46153</v>
+      </c>
+      <c r="D75" s="7">
+        <v>1.601625</v>
       </c>
       <c r="E75" s="8">
-        <v>494490211.89</v>
+        <v>493996079.89</v>
       </c>
       <c r="F75" s="9">
-        <v>5014</v>
+        <v>5013</v>
       </c>
       <c r="G75" s="8">
-        <v>789844100.17</v>
+        <v>791196667.32</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4527,19 +4531,19 @@
         <v>152</v>
       </c>
       <c r="C76" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D76" s="7">
-        <v>0.718494</v>
+        <v>0.714466</v>
       </c>
       <c r="E76" s="8">
-        <v>212574134606.86</v>
+        <v>212479781083.13</v>
       </c>
       <c r="F76" s="9">
-        <v>721344</v>
+        <v>721277</v>
       </c>
       <c r="G76" s="8">
-        <v>152733241551.56</v>
+        <v>151809537672.86</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4550,19 +4554,19 @@
         <v>154</v>
       </c>
       <c r="C77" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D77" s="7">
-        <v>0.592307</v>
+        <v>46153</v>
+      </c>
+      <c r="D77" s="11">
+        <v>0.59279</v>
       </c>
       <c r="E77" s="8">
-        <v>194095302.98</v>
+        <v>194092785.08</v>
       </c>
       <c r="F77" s="9">
-        <v>22325</v>
+        <v>22324</v>
       </c>
       <c r="G77" s="8">
-        <v>114963929.34</v>
+        <v>115056322.39</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4573,19 +4577,19 @@
         <v>156</v>
       </c>
       <c r="C78" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D78" s="10">
-        <v>0.30582</v>
+        <v>46153</v>
+      </c>
+      <c r="D78" s="7">
+        <v>0.305538</v>
       </c>
       <c r="E78" s="8">
-        <v>397117564.51</v>
+        <v>397114311.62</v>
       </c>
       <c r="F78" s="9">
-        <v>33149</v>
+        <v>33147</v>
       </c>
       <c r="G78" s="8">
-        <v>121446475.57</v>
+        <v>121333423.97</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4596,19 +4600,19 @@
         <v>158</v>
       </c>
       <c r="C79" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D79" s="7">
-        <v>0.163565</v>
+        <v>0.164433</v>
       </c>
       <c r="E79" s="8">
-        <v>3136093538.7</v>
+        <v>3136917680.48</v>
       </c>
       <c r="F79" s="9">
-        <v>6978</v>
+        <v>6964</v>
       </c>
       <c r="G79" s="8">
-        <v>512956605.04</v>
+        <v>515812699.06</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4619,19 +4623,19 @@
         <v>160</v>
       </c>
       <c r="C80" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D80" s="7">
-        <v>0.336428</v>
+        <v>0.337461</v>
       </c>
       <c r="E80" s="8">
-        <v>237546118.27</v>
+        <v>237596006.86</v>
       </c>
       <c r="F80" s="9">
-        <v>20833</v>
+        <v>20831</v>
       </c>
       <c r="G80" s="8">
-        <v>79917083.49</v>
+        <v>80179343.65</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4642,19 +4646,19 @@
         <v>162</v>
       </c>
       <c r="C81" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D81" s="10">
-        <v>0.18349</v>
+        <v>46153</v>
+      </c>
+      <c r="D81" s="7">
+        <v>0.184583</v>
       </c>
       <c r="E81" s="8">
-        <v>703075250.43</v>
+        <v>704050207.89</v>
       </c>
       <c r="F81" s="9">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="G81" s="8">
-        <v>129007304.33</v>
+        <v>129955767.76</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4665,19 +4669,19 @@
         <v>164</v>
       </c>
       <c r="C82" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D82" s="10">
-        <v>1.95804</v>
+        <v>46153</v>
+      </c>
+      <c r="D82" s="7">
+        <v>1.965412</v>
       </c>
       <c r="E82" s="8">
-        <v>83877328.7</v>
+        <v>83830380.38</v>
       </c>
       <c r="F82" s="9">
-        <v>13721</v>
+        <v>13720</v>
       </c>
       <c r="G82" s="8">
-        <v>164235202.33</v>
+        <v>164761263.28</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4688,19 +4692,19 @@
         <v>166</v>
       </c>
       <c r="C83" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D83" s="7">
-        <v>0.096111</v>
+        <v>0.096389</v>
       </c>
       <c r="E83" s="8">
-        <v>10345477982.52</v>
+        <v>10326129993.79</v>
       </c>
       <c r="F83" s="9">
-        <v>176437</v>
+        <v>176362</v>
       </c>
       <c r="G83" s="8">
-        <v>994314358.83</v>
+        <v>995322567.1</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4711,19 +4715,19 @@
         <v>168</v>
       </c>
       <c r="C84" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D84" s="7">
-        <v>0.084211</v>
+        <v>0.084475</v>
       </c>
       <c r="E84" s="8">
-        <v>9123999102.59</v>
+        <v>9233168247.75</v>
       </c>
       <c r="F84" s="9">
-        <v>140107</v>
+        <v>141618</v>
       </c>
       <c r="G84" s="8">
-        <v>768340164.79</v>
+        <v>779969501.19</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4734,19 +4738,19 @@
         <v>170</v>
       </c>
       <c r="C85" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D85" s="7">
-        <v>0.276402</v>
+        <v>0.277081</v>
       </c>
       <c r="E85" s="8">
-        <v>4368682414.98</v>
+        <v>4377805556.06</v>
       </c>
       <c r="F85" s="9">
-        <v>80842</v>
+        <v>80942</v>
       </c>
       <c r="G85" s="8">
-        <v>1207511998.26</v>
+        <v>1213008667.47</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4757,19 +4761,19 @@
         <v>172</v>
       </c>
       <c r="C86" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D86" s="7">
-        <v>0.931913</v>
+        <v>0.941119</v>
       </c>
       <c r="E86" s="8">
-        <v>4622216221.06</v>
+        <v>4622954140.61</v>
       </c>
       <c r="F86" s="9">
-        <v>87599</v>
+        <v>87562</v>
       </c>
       <c r="G86" s="8">
-        <v>4307502116.84</v>
+        <v>4350750535.95</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4780,19 +4784,19 @@
         <v>174</v>
       </c>
       <c r="C87" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D87" s="7">
-        <v>0.228921</v>
+        <v>0.228926</v>
       </c>
       <c r="E87" s="8">
-        <v>12601846776.95</v>
+        <v>12608719798.68</v>
       </c>
       <c r="F87" s="9">
-        <v>144729</v>
+        <v>144837</v>
       </c>
       <c r="G87" s="8">
-        <v>2884822677.76</v>
+        <v>2886461222.4</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4803,19 +4807,19 @@
         <v>176</v>
       </c>
       <c r="C88" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D88" s="7">
-        <v>0.169477</v>
+        <v>0.169647</v>
       </c>
       <c r="E88" s="8">
-        <v>18614699935.77</v>
+        <v>18538912525.58</v>
       </c>
       <c r="F88" s="9">
-        <v>91408</v>
+        <v>91456</v>
       </c>
       <c r="G88" s="8">
-        <v>3154758670.54</v>
+        <v>3145069594</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4826,19 +4830,19 @@
         <v>178</v>
       </c>
       <c r="C89" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D89" s="7">
-        <v>0.639956</v>
+        <v>0.639952</v>
       </c>
       <c r="E89" s="8">
-        <v>2267297720.12</v>
+        <v>2265820732.21</v>
       </c>
       <c r="F89" s="9">
-        <v>35796</v>
+        <v>35765</v>
       </c>
       <c r="G89" s="8">
-        <v>1450971370.72</v>
+        <v>1450016173.05</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4849,19 +4853,19 @@
         <v>180</v>
       </c>
       <c r="C90" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D90" s="7">
-        <v>0.856157</v>
+        <v>0.855204</v>
       </c>
       <c r="E90" s="8">
-        <v>19146669798.07</v>
+        <v>19122652340.16</v>
       </c>
       <c r="F90" s="9">
-        <v>271744</v>
+        <v>271429</v>
       </c>
       <c r="G90" s="8">
-        <v>16392553854.49</v>
+        <v>16353763386.02</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4872,19 +4876,19 @@
         <v>182</v>
       </c>
       <c r="C91" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D91" s="7">
-        <v>0.808095</v>
+        <v>0.808205</v>
       </c>
       <c r="E91" s="8">
-        <v>3497961193.65</v>
+        <v>3493909316.66</v>
       </c>
       <c r="F91" s="9">
-        <v>29828</v>
+        <v>29876</v>
       </c>
       <c r="G91" s="8">
-        <v>2826683829.95</v>
+        <v>2823794909</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4895,19 +4899,19 @@
         <v>184</v>
       </c>
       <c r="C92" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D92" s="7">
-        <v>0.840263</v>
+        <v>0.839855</v>
       </c>
       <c r="E92" s="8">
-        <v>12331789343.02</v>
+        <v>12320643294.04</v>
       </c>
       <c r="F92" s="9">
-        <v>188367</v>
+        <v>188175</v>
       </c>
       <c r="G92" s="8">
-        <v>10361952248.25</v>
+        <v>10347550123.46</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4918,19 +4922,19 @@
         <v>186</v>
       </c>
       <c r="C93" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D93" s="7">
-        <v>0.088536</v>
+        <v>0.088812</v>
       </c>
       <c r="E93" s="8">
-        <v>7576142445.63</v>
+        <v>7580569680.74</v>
       </c>
       <c r="F93" s="9">
-        <v>155400</v>
+        <v>157448</v>
       </c>
       <c r="G93" s="8">
-        <v>670758972.25</v>
+        <v>673245379.94</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4941,19 +4945,19 @@
         <v>188</v>
       </c>
       <c r="C94" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D94" s="10">
-        <v>0.12228</v>
+        <v>46153</v>
+      </c>
+      <c r="D94" s="7">
+        <v>0.122446</v>
       </c>
       <c r="E94" s="8">
-        <v>11898990412.4</v>
+        <v>11843624174.97</v>
       </c>
       <c r="F94" s="9">
-        <v>33305</v>
+        <v>33277</v>
       </c>
       <c r="G94" s="8">
-        <v>1455014177.9</v>
+        <v>1450201904.87</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4964,19 +4968,19 @@
         <v>190</v>
       </c>
       <c r="C95" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D95" s="10">
-        <v>0.12833</v>
+        <v>46153</v>
+      </c>
+      <c r="D95" s="7">
+        <v>0.128726</v>
       </c>
       <c r="E95" s="8">
-        <v>71284769530.83</v>
+        <v>70975523796.11</v>
       </c>
       <c r="F95" s="9">
-        <v>212337</v>
+        <v>212259</v>
       </c>
       <c r="G95" s="8">
-        <v>9147986496.95</v>
+        <v>9136408010.33</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4987,19 +4991,19 @@
         <v>192</v>
       </c>
       <c r="C96" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D96" s="7">
-        <v>0.489602</v>
+        <v>46153</v>
+      </c>
+      <c r="D96" s="11">
+        <v>0.49271</v>
       </c>
       <c r="E96" s="8">
-        <v>32141592043.95</v>
+        <v>32249129179.16</v>
       </c>
       <c r="F96" s="9">
-        <v>284670</v>
+        <v>285244</v>
       </c>
       <c r="G96" s="8">
-        <v>15736579598.09</v>
+        <v>15889471753.96</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -5010,19 +5014,19 @@
         <v>194</v>
       </c>
       <c r="C97" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D97" s="7">
-        <v>0.097258</v>
+        <v>0.097724</v>
       </c>
       <c r="E97" s="8">
-        <v>24629668915.23</v>
+        <v>24679504285.9</v>
       </c>
       <c r="F97" s="9">
-        <v>443052</v>
+        <v>443193</v>
       </c>
       <c r="G97" s="8">
-        <v>2395435347.87</v>
+        <v>2411791295.87</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -5033,19 +5037,19 @@
         <v>196</v>
       </c>
       <c r="C98" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D98" s="7">
-        <v>0.247754</v>
+        <v>46153</v>
+      </c>
+      <c r="D98" s="11">
+        <v>0.24764</v>
       </c>
       <c r="E98" s="8">
-        <v>1266859072.13</v>
+        <v>1265177951.42</v>
       </c>
       <c r="F98" s="9">
-        <v>7142</v>
+        <v>7128</v>
       </c>
       <c r="G98" s="8">
-        <v>313869069.87</v>
+        <v>313309239.44</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -5056,19 +5060,19 @@
         <v>198</v>
       </c>
       <c r="C99" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D99" s="7">
-        <v>1.070352</v>
+        <v>1.069762</v>
       </c>
       <c r="E99" s="8">
-        <v>4838259049.96</v>
+        <v>4934697620.13</v>
       </c>
       <c r="F99" s="9">
-        <v>49280</v>
+        <v>49907</v>
       </c>
       <c r="G99" s="8">
-        <v>5178640270.8</v>
+        <v>5278949621.4</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5079,19 +5083,19 @@
         <v>200</v>
       </c>
       <c r="C100" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D100" s="7">
-        <v>2.716789</v>
+        <v>46153</v>
+      </c>
+      <c r="D100" s="11">
+        <v>2.73471</v>
       </c>
       <c r="E100" s="8">
-        <v>12010183510.22</v>
+        <v>12013880905.78</v>
       </c>
       <c r="F100" s="9">
-        <v>306063</v>
+        <v>306013</v>
       </c>
       <c r="G100" s="8">
-        <v>32629139259.34</v>
+        <v>32854476222.16</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5102,19 +5106,19 @@
         <v>202</v>
       </c>
       <c r="C101" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D101" s="10">
-        <v>0.36018</v>
+        <v>46153</v>
+      </c>
+      <c r="D101" s="7">
+        <v>0.359845</v>
       </c>
       <c r="E101" s="8">
-        <v>25640243620.83</v>
+        <v>25529404362.54</v>
       </c>
       <c r="F101" s="9">
-        <v>331204</v>
+        <v>330757</v>
       </c>
       <c r="G101" s="8">
-        <v>9235109116.21</v>
+        <v>9186623027.57</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5125,19 +5129,19 @@
         <v>204</v>
       </c>
       <c r="C102" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D102" s="7">
-        <v>0.370288</v>
+        <v>0.371316</v>
       </c>
       <c r="E102" s="8">
-        <v>201844082193.83</v>
+        <v>202565149045.21</v>
       </c>
       <c r="F102" s="9">
-        <v>348142</v>
+        <v>344436</v>
       </c>
       <c r="G102" s="8">
-        <v>74740515215.2</v>
+        <v>75215712827.95</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5148,19 +5152,19 @@
         <v>206</v>
       </c>
       <c r="C103" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D103" s="10">
-        <v>0.12632</v>
+        <v>46153</v>
+      </c>
+      <c r="D103" s="7">
+        <v>0.126461</v>
       </c>
       <c r="E103" s="8">
-        <v>9029898220.86</v>
+        <v>9034746540.44</v>
       </c>
       <c r="F103" s="9">
-        <v>28599</v>
+        <v>28606</v>
       </c>
       <c r="G103" s="8">
-        <v>1140654794.56</v>
+        <v>1142538764.08</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -5171,19 +5175,19 @@
         <v>208</v>
       </c>
       <c r="C104" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D104" s="7">
-        <v>0.288727</v>
+        <v>0.288056</v>
       </c>
       <c r="E104" s="8">
-        <v>1706873054.3</v>
+        <v>1702638348.08</v>
       </c>
       <c r="F104" s="9">
         <v>7822</v>
       </c>
       <c r="G104" s="8">
-        <v>492821052.33</v>
+        <v>490455011.07</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -5194,19 +5198,19 @@
         <v>210</v>
       </c>
       <c r="C105" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D105" s="7">
-        <v>0.010019</v>
+        <v>46153</v>
+      </c>
+      <c r="D105" s="11">
+        <v>0.01005</v>
       </c>
       <c r="E105" s="8">
-        <v>160128666.15</v>
+        <v>201307097.87</v>
       </c>
       <c r="F105" s="9">
         <v>0</v>
       </c>
       <c r="G105" s="8">
-        <v>1604327.12</v>
+        <v>2023130.09</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5217,19 +5221,19 @@
         <v>212</v>
       </c>
       <c r="C106" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D106" s="7">
-        <v>1.094633</v>
+        <v>1.098011</v>
       </c>
       <c r="E106" s="8">
-        <v>254440244.45</v>
+        <v>256869935.16</v>
       </c>
       <c r="F106" s="9">
-        <v>4103</v>
+        <v>4142</v>
       </c>
       <c r="G106" s="8">
-        <v>278518565</v>
+        <v>282045947.48</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5240,19 +5244,19 @@
         <v>214</v>
       </c>
       <c r="C107" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D107" s="7">
-        <v>1.014385</v>
+        <v>1.024973</v>
       </c>
       <c r="E107" s="8">
-        <v>620784681.95</v>
+        <v>622867859.78</v>
       </c>
       <c r="F107" s="9">
-        <v>15532</v>
+        <v>15553</v>
       </c>
       <c r="G107" s="8">
-        <v>629714481.93</v>
+        <v>638422870.34</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -5263,19 +5267,19 @@
         <v>216</v>
       </c>
       <c r="C108" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D108" s="7">
-        <v>0.183013</v>
+        <v>0.185137</v>
       </c>
       <c r="E108" s="8">
-        <v>381733178.58</v>
+        <v>382454266.93</v>
       </c>
       <c r="F108" s="9">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="G108" s="8">
-        <v>69861975.41</v>
+        <v>70806588.77</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -5286,19 +5290,19 @@
         <v>218</v>
       </c>
       <c r="C109" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D109" s="7">
-        <v>1.496666</v>
+        <v>1.504645</v>
       </c>
       <c r="E109" s="8">
-        <v>1026685653.62</v>
+        <v>1027645921.57</v>
       </c>
       <c r="F109" s="9">
-        <v>21965</v>
+        <v>21966</v>
       </c>
       <c r="G109" s="8">
-        <v>1536605023.82</v>
+        <v>1546242320.77</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -5309,19 +5313,19 @@
         <v>220</v>
       </c>
       <c r="C110" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D110" s="7">
-        <v>0.098321</v>
+        <v>0.098932</v>
       </c>
       <c r="E110" s="8">
-        <v>5471229054.98</v>
+        <v>5478059949.61</v>
       </c>
       <c r="F110" s="9">
-        <v>24362</v>
+        <v>24366</v>
       </c>
       <c r="G110" s="8">
-        <v>537937473.43</v>
+        <v>541957657.3</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5332,19 +5336,19 @@
         <v>222</v>
       </c>
       <c r="C111" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D111" s="7">
-        <v>0.291408</v>
+        <v>0.291561</v>
       </c>
       <c r="E111" s="8">
-        <v>1644282707.97</v>
+        <v>1645192923.75</v>
       </c>
       <c r="F111" s="9">
-        <v>33333</v>
+        <v>33340</v>
       </c>
       <c r="G111" s="8">
-        <v>479157766</v>
+        <v>479674094.94</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -5355,19 +5359,19 @@
         <v>224</v>
       </c>
       <c r="C112" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D112" s="7">
-        <v>0.220491</v>
+        <v>0.223149</v>
       </c>
       <c r="E112" s="8">
-        <v>590258075.49</v>
+        <v>590473971.21</v>
       </c>
       <c r="F112" s="9">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G112" s="8">
-        <v>130146796</v>
+        <v>131763657.75</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -5378,19 +5382,19 @@
         <v>226</v>
       </c>
       <c r="C113" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D113" s="7">
-        <v>0.414948</v>
+        <v>0.416614</v>
       </c>
       <c r="E113" s="8">
-        <v>151450271.56</v>
+        <v>151896888.45</v>
       </c>
       <c r="F113" s="9">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="G113" s="8">
-        <v>62843936.87</v>
+        <v>63282320.88</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5401,19 +5405,19 @@
         <v>228</v>
       </c>
       <c r="C114" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D114" s="7">
-        <v>0.110394</v>
+        <v>46153</v>
+      </c>
+      <c r="D114" s="11">
+        <v>0.11042</v>
       </c>
       <c r="E114" s="8">
-        <v>195682089.1</v>
+        <v>194006957.47</v>
       </c>
       <c r="F114" s="9">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="G114" s="8">
-        <v>21602180.75</v>
+        <v>21422305.55</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -5424,19 +5428,19 @@
         <v>230</v>
       </c>
       <c r="C115" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D115" s="7">
-        <v>0.064947</v>
+        <v>0.064597</v>
       </c>
       <c r="E115" s="8">
-        <v>1220651541204.3</v>
+        <v>1220932948988.99</v>
       </c>
       <c r="F115" s="9">
-        <v>789358</v>
+        <v>789428</v>
       </c>
       <c r="G115" s="8">
-        <v>79278166195.31</v>
+        <v>78868172205.9</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -5447,19 +5451,19 @@
         <v>232</v>
       </c>
       <c r="C116" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D116" s="10">
-        <v>0.01551</v>
+        <v>46153</v>
+      </c>
+      <c r="D116" s="7">
+        <v>0.015556</v>
       </c>
       <c r="E116" s="8">
-        <v>6882839513.81</v>
+        <v>7022439555.67</v>
       </c>
       <c r="F116" s="9">
-        <v>1377</v>
+        <v>1394</v>
       </c>
       <c r="G116" s="8">
-        <v>106753881.03</v>
+        <v>109244009.97</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -5470,19 +5474,19 @@
         <v>234</v>
       </c>
       <c r="C117" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D117" s="7">
-        <v>0.127579</v>
+        <v>0.127923</v>
       </c>
       <c r="E117" s="8">
-        <v>7612704373.79</v>
+        <v>7631807540.59</v>
       </c>
       <c r="F117" s="9">
-        <v>24923</v>
+        <v>24944</v>
       </c>
       <c r="G117" s="8">
-        <v>971223484.62</v>
+        <v>976281338.28</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -5493,19 +5497,19 @@
         <v>236</v>
       </c>
       <c r="C118" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D118" s="7">
-        <v>0.132026</v>
+        <v>46153</v>
+      </c>
+      <c r="D118" s="10">
+        <v>0.1338</v>
       </c>
       <c r="E118" s="8">
-        <v>30268971190.16</v>
+        <v>30624328387.29</v>
       </c>
       <c r="F118" s="9">
-        <v>70879</v>
+        <v>71244</v>
       </c>
       <c r="G118" s="8">
-        <v>3996279892.77</v>
+        <v>4097536727.66</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -5516,19 +5520,19 @@
         <v>238</v>
       </c>
       <c r="C119" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D119" s="7">
-        <v>0.575794</v>
+        <v>0.575944</v>
       </c>
       <c r="E119" s="8">
-        <v>91401396.95</v>
+        <v>90860106.68</v>
       </c>
       <c r="F119" s="9">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="G119" s="8">
-        <v>52628342.05</v>
+        <v>52330354.2</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5539,19 +5543,19 @@
         <v>240</v>
       </c>
       <c r="C120" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D120" s="10">
-        <v>0.76238</v>
+        <v>46153</v>
+      </c>
+      <c r="D120" s="7">
+        <v>0.758928</v>
       </c>
       <c r="E120" s="8">
-        <v>22905718841.14</v>
+        <v>22891456954.21</v>
       </c>
       <c r="F120" s="9">
-        <v>149766</v>
+        <v>149716</v>
       </c>
       <c r="G120" s="8">
-        <v>17462860645.86</v>
+        <v>17372971132.03</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5562,19 +5566,19 @@
         <v>242</v>
       </c>
       <c r="C121" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D121" s="7">
-        <v>0.123915</v>
+        <v>46153</v>
+      </c>
+      <c r="D121" s="11">
+        <v>0.12413</v>
       </c>
       <c r="E121" s="8">
-        <v>14556892557.33</v>
+        <v>14560353652.02</v>
       </c>
       <c r="F121" s="9">
-        <v>44596</v>
+        <v>44584</v>
       </c>
       <c r="G121" s="8">
-        <v>1803822213.26</v>
+        <v>1807372545.69</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -5585,19 +5589,19 @@
         <v>244</v>
       </c>
       <c r="C122" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D122" s="7">
-        <v>0.107279</v>
+        <v>0.107358</v>
       </c>
       <c r="E122" s="8">
-        <v>42824864809.27</v>
+        <v>42795053631.27</v>
       </c>
       <c r="F122" s="9">
-        <v>338026</v>
+        <v>337924</v>
       </c>
       <c r="G122" s="8">
-        <v>4594213026.85</v>
+        <v>4594400133.97</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -5608,19 +5612,19 @@
         <v>246</v>
       </c>
       <c r="C123" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D123" s="7">
-        <v>0.094631</v>
+        <v>0.094701</v>
       </c>
       <c r="E123" s="8">
-        <v>9715190213.78</v>
+        <v>9715393869.54</v>
       </c>
       <c r="F123" s="9">
-        <v>148094</v>
+        <v>148102</v>
       </c>
       <c r="G123" s="8">
-        <v>919359882.44</v>
+        <v>920061301.11</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -5631,19 +5635,19 @@
         <v>248</v>
       </c>
       <c r="C124" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D124" s="7">
-        <v>0.048816</v>
+        <v>0.048858</v>
       </c>
       <c r="E124" s="8">
-        <v>28053393731.79</v>
+        <v>28076797472.18</v>
       </c>
       <c r="F124" s="9">
-        <v>34663</v>
+        <v>34705</v>
       </c>
       <c r="G124" s="8">
-        <v>1369461614.88</v>
+        <v>1371780745.89</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5654,19 +5658,19 @@
         <v>250</v>
       </c>
       <c r="C125" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D125" s="7">
-        <v>0.120163</v>
+        <v>0.120287</v>
       </c>
       <c r="E125" s="8">
-        <v>6292228740.58</v>
+        <v>6282742832.45</v>
       </c>
       <c r="F125" s="9">
-        <v>43181</v>
+        <v>43172</v>
       </c>
       <c r="G125" s="8">
-        <v>756093237.86</v>
+        <v>755730810.99</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5677,19 +5681,19 @@
         <v>252</v>
       </c>
       <c r="C126" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D126" s="7">
-        <v>0.091827</v>
+        <v>0.092202</v>
       </c>
       <c r="E126" s="8">
-        <v>2976836665.76</v>
+        <v>2981838513.73</v>
       </c>
       <c r="F126" s="9">
-        <v>83624</v>
+        <v>83680</v>
       </c>
       <c r="G126" s="8">
-        <v>273355004.37</v>
+        <v>274932012.06</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5700,19 +5704,19 @@
         <v>254</v>
       </c>
       <c r="C127" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D127" s="7">
-        <v>0.085187</v>
+        <v>0.085936</v>
       </c>
       <c r="E127" s="8">
-        <v>1127968576.55</v>
+        <v>1127655165.71</v>
       </c>
       <c r="F127" s="9">
-        <v>122891</v>
+        <v>122880</v>
       </c>
       <c r="G127" s="8">
-        <v>96088804.27</v>
+        <v>96905695</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5723,19 +5727,19 @@
         <v>256</v>
       </c>
       <c r="C128" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D128" s="7">
-        <v>0.781992</v>
+        <v>0.783495</v>
       </c>
       <c r="E128" s="8">
-        <v>1637521567.32</v>
+        <v>1638122144.92</v>
       </c>
       <c r="F128" s="9">
-        <v>49927</v>
+        <v>49915</v>
       </c>
       <c r="G128" s="8">
-        <v>1280528004.88</v>
+        <v>1283460530.83</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5746,19 +5750,19 @@
         <v>258</v>
       </c>
       <c r="C129" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D129" s="7">
-        <v>0.150258</v>
+        <v>0.150201</v>
       </c>
       <c r="E129" s="8">
-        <v>1297284164.54</v>
+        <v>1297391526.25</v>
       </c>
       <c r="F129" s="9">
         <v>12557</v>
       </c>
       <c r="G129" s="8">
-        <v>194926969.92</v>
+        <v>194869506.87</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5769,19 +5773,19 @@
         <v>260</v>
       </c>
       <c r="C130" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D130" s="7">
-        <v>0.241736</v>
+        <v>0.241597</v>
       </c>
       <c r="E130" s="8">
-        <v>5188346889.48</v>
+        <v>5177618572.99</v>
       </c>
       <c r="F130" s="9">
-        <v>69488</v>
+        <v>69482</v>
       </c>
       <c r="G130" s="8">
-        <v>1254207802.24</v>
+        <v>1250897000.55</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5792,19 +5796,19 @@
         <v>262</v>
       </c>
       <c r="C131" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D131" s="7">
-        <v>1.902875</v>
+        <v>1.910944</v>
       </c>
       <c r="E131" s="8">
-        <v>2374373481.78</v>
+        <v>2373553038.62</v>
       </c>
       <c r="F131" s="9">
-        <v>52990</v>
+        <v>52980</v>
       </c>
       <c r="G131" s="8">
-        <v>4518135212.8</v>
+        <v>4535727362.42</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5815,19 +5819,19 @@
         <v>264</v>
       </c>
       <c r="C132" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D132" s="7">
-        <v>0.362194</v>
+        <v>0.361176</v>
       </c>
       <c r="E132" s="8">
-        <v>553891808.81</v>
+        <v>553306429.86</v>
       </c>
       <c r="F132" s="9">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="G132" s="8">
-        <v>200616282.66</v>
+        <v>199840871.27</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5838,19 +5842,19 @@
         <v>266</v>
       </c>
       <c r="C133" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D133" s="7">
-        <v>0.163046</v>
+        <v>0.163351</v>
       </c>
       <c r="E133" s="8">
-        <v>133106869.86</v>
+        <v>132605008.62</v>
       </c>
       <c r="F133" s="9">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G133" s="8">
-        <v>21702592.55</v>
+        <v>21661127.52</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,19 +5865,19 @@
         <v>268</v>
       </c>
       <c r="C134" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D134" s="7">
-        <v>0.708369</v>
+        <v>46153</v>
+      </c>
+      <c r="D134" s="11">
+        <v>0.70896</v>
       </c>
       <c r="E134" s="8">
-        <v>1256641469.42</v>
+        <v>1255647138.54</v>
       </c>
       <c r="F134" s="9">
-        <v>21150</v>
+        <v>21132</v>
       </c>
       <c r="G134" s="8">
-        <v>890166312.44</v>
+        <v>890203458.3</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5884,19 +5888,19 @@
         <v>270</v>
       </c>
       <c r="C135" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D135" s="7">
-        <v>0.372602</v>
+        <v>0.373551</v>
       </c>
       <c r="E135" s="8">
-        <v>7401122466.5</v>
+        <v>7472863585.49</v>
       </c>
       <c r="F135" s="9">
-        <v>89571</v>
+        <v>89885</v>
       </c>
       <c r="G135" s="8">
-        <v>2757674875.95</v>
+        <v>2791495173.73</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5907,19 +5911,19 @@
         <v>272</v>
       </c>
       <c r="C136" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D136" s="7">
-        <v>0.207041</v>
+        <v>0.207512</v>
       </c>
       <c r="E136" s="8">
-        <v>199891057.23</v>
+        <v>199965424.17</v>
       </c>
       <c r="F136" s="9">
         <v>618</v>
       </c>
       <c r="G136" s="8">
-        <v>41385586.05</v>
+        <v>41495207.85</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5930,19 +5934,19 @@
         <v>274</v>
       </c>
       <c r="C137" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D137" s="7">
-        <v>0.269684</v>
+        <v>0.272281</v>
       </c>
       <c r="E137" s="8">
-        <v>403726642.45</v>
+        <v>403394640.47</v>
       </c>
       <c r="F137" s="9">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G137" s="8">
-        <v>108878674.09</v>
+        <v>109836503.1</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5953,19 +5957,19 @@
         <v>276</v>
       </c>
       <c r="C138" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D138" s="7">
-        <v>0.101305</v>
+        <v>0.101549</v>
       </c>
       <c r="E138" s="8">
-        <v>295208405.4</v>
+        <v>295742438.3</v>
       </c>
       <c r="F138" s="9">
         <v>325</v>
       </c>
       <c r="G138" s="8">
-        <v>29905988.92</v>
+        <v>30032268.05</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5976,19 +5980,19 @@
         <v>278</v>
       </c>
       <c r="C139" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D139" s="7">
-        <v>0.410069</v>
+        <v>0.414547</v>
       </c>
       <c r="E139" s="8">
-        <v>629521236.76</v>
+        <v>630930534.33</v>
       </c>
       <c r="F139" s="9">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="G139" s="8">
-        <v>258147303.36</v>
+        <v>261550518.73</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5999,19 +6003,19 @@
         <v>280</v>
       </c>
       <c r="C140" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D140" s="7">
-        <v>0.704213</v>
+        <v>0.704365</v>
       </c>
       <c r="E140" s="8">
-        <v>2931436906.69</v>
+        <v>2931771877.3</v>
       </c>
       <c r="F140" s="9">
-        <v>41994</v>
+        <v>41964</v>
       </c>
       <c r="G140" s="8">
-        <v>2064357180.87</v>
+        <v>2065036966.68</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -6022,19 +6026,19 @@
         <v>282</v>
       </c>
       <c r="C141" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D141" s="7">
-        <v>0.014381</v>
+        <v>0.014394</v>
       </c>
       <c r="E141" s="8">
-        <v>2922760157.91</v>
+        <v>2996813022.98</v>
       </c>
       <c r="F141" s="9">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="G141" s="8">
-        <v>42031879.99</v>
+        <v>43136959.89</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -6045,19 +6049,19 @@
         <v>284</v>
       </c>
       <c r="C142" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D142" s="7">
-        <v>0.077649</v>
+        <v>0.078524</v>
       </c>
       <c r="E142" s="8">
-        <v>22391491969.24</v>
+        <v>22575383182.07</v>
       </c>
       <c r="F142" s="9">
-        <v>23581</v>
+        <v>23598</v>
       </c>
       <c r="G142" s="8">
-        <v>1738679931.87</v>
+        <v>1772704586.23</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -6068,19 +6072,19 @@
         <v>286</v>
       </c>
       <c r="C143" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D143" s="7">
-        <v>0.289662</v>
+        <v>0.288724</v>
       </c>
       <c r="E143" s="8">
-        <v>20751706142.13</v>
+        <v>20777051300.87</v>
       </c>
       <c r="F143" s="9">
         <v>4722</v>
       </c>
       <c r="G143" s="8">
-        <v>6010976167.11</v>
+        <v>5998839491.25</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -6091,19 +6095,19 @@
         <v>288</v>
       </c>
       <c r="C144" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D144" s="7">
-        <v>0.091103</v>
+        <v>0.091357</v>
       </c>
       <c r="E144" s="8">
-        <v>655883756.65</v>
+        <v>658210259.06</v>
       </c>
       <c r="F144" s="9">
-        <v>11120</v>
+        <v>10963</v>
       </c>
       <c r="G144" s="8">
-        <v>59753233.74</v>
+        <v>60131901.39</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -6114,19 +6118,19 @@
         <v>290</v>
       </c>
       <c r="C145" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D145" s="7">
-        <v>0.054762</v>
+        <v>0.054756</v>
       </c>
       <c r="E145" s="8">
-        <v>1444946832.01</v>
+        <v>1443215946.22</v>
       </c>
       <c r="F145" s="9">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G145" s="8">
-        <v>79128858.37</v>
+        <v>79024274.78</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -6137,19 +6141,19 @@
         <v>292</v>
       </c>
       <c r="C146" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D146" s="7">
-        <v>0.114594</v>
+        <v>0.114699</v>
       </c>
       <c r="E146" s="8">
-        <v>1799189079.45</v>
+        <v>1797404844.98</v>
       </c>
       <c r="F146" s="9">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="G146" s="8">
-        <v>206176098.9</v>
+        <v>206159710.41</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6160,19 +6164,19 @@
         <v>294</v>
       </c>
       <c r="C147" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D147" s="7">
-        <v>0.114772</v>
+        <v>0.115535</v>
       </c>
       <c r="E147" s="8">
-        <v>1969923994.26</v>
+        <v>1970975705.87</v>
       </c>
       <c r="F147" s="9">
-        <v>65319</v>
+        <v>65337</v>
       </c>
       <c r="G147" s="8">
-        <v>226092862.59</v>
+        <v>227717502.85</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -6183,19 +6187,19 @@
         <v>296</v>
       </c>
       <c r="C148" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D148" s="10">
-        <v>0.07783</v>
+        <v>46153</v>
+      </c>
+      <c r="D148" s="7">
+        <v>0.078573</v>
       </c>
       <c r="E148" s="8">
-        <v>571128155.18</v>
+        <v>571028595.79</v>
       </c>
       <c r="F148" s="9">
-        <v>52198</v>
+        <v>52192</v>
       </c>
       <c r="G148" s="8">
-        <v>44451118.74</v>
+        <v>44867632.81</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6206,19 +6210,19 @@
         <v>298</v>
       </c>
       <c r="C149" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D149" s="7">
-        <v>0.082666</v>
+        <v>0.082925</v>
       </c>
       <c r="E149" s="8">
-        <v>359843196.94</v>
+        <v>358523428.67</v>
       </c>
       <c r="F149" s="9">
-        <v>9529</v>
+        <v>9592</v>
       </c>
       <c r="G149" s="8">
-        <v>29746863.35</v>
+        <v>29730718.45</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -6229,19 +6233,19 @@
         <v>300</v>
       </c>
       <c r="C150" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D150" s="10">
-        <v>0.37263</v>
+        <v>46153</v>
+      </c>
+      <c r="D150" s="7">
+        <v>0.373518</v>
       </c>
       <c r="E150" s="8">
-        <v>145664338.5</v>
+        <v>145377749.29</v>
       </c>
       <c r="F150" s="9">
         <v>1767</v>
       </c>
       <c r="G150" s="8">
-        <v>54278971.61</v>
+        <v>54301148.36</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6252,19 +6256,19 @@
         <v>302</v>
       </c>
       <c r="C151" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D151" s="7">
-        <v>0.100114</v>
+        <v>0.100119</v>
       </c>
       <c r="E151" s="8">
-        <v>339710223.95</v>
+        <v>339880945.67</v>
       </c>
       <c r="F151" s="9">
         <v>1839</v>
       </c>
       <c r="G151" s="8">
-        <v>34009749.18</v>
+        <v>34028518.96</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -6275,19 +6279,19 @@
         <v>304</v>
       </c>
       <c r="C152" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D152" s="7">
-        <v>0.299053</v>
+        <v>0.300733</v>
       </c>
       <c r="E152" s="8">
-        <v>142166395.48</v>
+        <v>142253525.92</v>
       </c>
       <c r="F152" s="9">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G152" s="8">
-        <v>42515292.31</v>
+        <v>42780349.67</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -6298,19 +6302,19 @@
         <v>306</v>
       </c>
       <c r="C153" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D153" s="7">
-        <v>0.118403</v>
+        <v>0.118713</v>
       </c>
       <c r="E153" s="8">
-        <v>584766465.87</v>
+        <v>583013323.22</v>
       </c>
       <c r="F153" s="9">
         <v>92</v>
       </c>
       <c r="G153" s="8">
-        <v>69237881.24</v>
+        <v>69211266.38</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -6321,19 +6325,19 @@
         <v>308</v>
       </c>
       <c r="C154" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D154" s="7">
-        <v>0.409638</v>
+        <v>0.414157</v>
       </c>
       <c r="E154" s="8">
-        <v>1302581819.51</v>
+        <v>1305237978.62</v>
       </c>
       <c r="F154" s="9">
         <v>127</v>
       </c>
       <c r="G154" s="8">
-        <v>533587085.05</v>
+        <v>540574024.49</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -6344,19 +6348,19 @@
         <v>310</v>
       </c>
       <c r="C155" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D155" s="7">
-        <v>0.526554</v>
+        <v>0.532182</v>
       </c>
       <c r="E155" s="8">
-        <v>591068636.76</v>
+        <v>591210696.55</v>
       </c>
       <c r="F155" s="9">
         <v>381</v>
       </c>
       <c r="G155" s="8">
-        <v>311229438.27</v>
+        <v>314631824.85</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -6367,19 +6371,19 @@
         <v>312</v>
       </c>
       <c r="C156" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D156" s="7">
-        <v>1.753384</v>
+        <v>1.766477</v>
       </c>
       <c r="E156" s="8">
-        <v>913288141.5</v>
+        <v>915607439.83</v>
       </c>
       <c r="F156" s="9">
-        <v>10182</v>
+        <v>10184</v>
       </c>
       <c r="G156" s="8">
-        <v>1601345072.24</v>
+        <v>1617399522.52</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -6390,19 +6394,19 @@
         <v>314</v>
       </c>
       <c r="C157" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D157" s="7">
-        <v>0.284468</v>
+        <v>0.286799</v>
       </c>
       <c r="E157" s="8">
-        <v>185236093.82</v>
+        <v>184876202.45</v>
       </c>
       <c r="F157" s="9">
         <v>94</v>
       </c>
       <c r="G157" s="8">
-        <v>52693653.28</v>
+        <v>53022284.02</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -6413,19 +6417,19 @@
         <v>316</v>
       </c>
       <c r="C158" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D158" s="7">
-        <v>0.145577</v>
+        <v>46153</v>
+      </c>
+      <c r="D158" s="11">
+        <v>0.14563</v>
       </c>
       <c r="E158" s="8">
-        <v>4600469471.17</v>
+        <v>4599742661.05</v>
       </c>
       <c r="F158" s="9">
-        <v>28811</v>
+        <v>28798</v>
       </c>
       <c r="G158" s="8">
-        <v>669722061.66</v>
+        <v>669862452</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -6436,19 +6440,19 @@
         <v>318</v>
       </c>
       <c r="C159" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D159" s="7">
-        <v>0.167995</v>
+        <v>0.168433</v>
       </c>
       <c r="E159" s="8">
-        <v>3257171963.03</v>
+        <v>3242168138.91</v>
       </c>
       <c r="F159" s="9">
-        <v>12079</v>
+        <v>11918</v>
       </c>
       <c r="G159" s="8">
-        <v>547189314.35</v>
+        <v>546089675.65</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -6459,19 +6463,19 @@
         <v>320</v>
       </c>
       <c r="C160" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D160" s="7">
-        <v>0.713643</v>
+        <v>0.719302</v>
       </c>
       <c r="E160" s="8">
-        <v>768922555.94</v>
+        <v>771859052.15</v>
       </c>
       <c r="F160" s="9">
-        <v>5171</v>
+        <v>5174</v>
       </c>
       <c r="G160" s="8">
-        <v>548736459.2</v>
+        <v>555199467.62</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -6482,19 +6486,19 @@
         <v>322</v>
       </c>
       <c r="C161" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D161" s="7">
-        <v>0.386167</v>
+        <v>0.386768</v>
       </c>
       <c r="E161" s="8">
-        <v>1341636565.63</v>
+        <v>1340985274.04</v>
       </c>
       <c r="F161" s="9">
-        <v>23884</v>
+        <v>23871</v>
       </c>
       <c r="G161" s="8">
-        <v>518095607.83</v>
+        <v>518650186.88</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -6505,19 +6509,19 @@
         <v>324</v>
       </c>
       <c r="C162" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D162" s="7">
-        <v>0.383448</v>
+        <v>0.385019</v>
       </c>
       <c r="E162" s="8">
-        <v>167986884.35</v>
+        <v>168110790.13</v>
       </c>
       <c r="F162" s="9">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G162" s="8">
-        <v>64414210.98</v>
+        <v>64725886.18</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -6528,19 +6532,19 @@
         <v>326</v>
       </c>
       <c r="C163" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D163" s="7">
-        <v>0.146014</v>
+        <v>0.146144</v>
       </c>
       <c r="E163" s="8">
-        <v>1029640914.05</v>
+        <v>1026543580.83</v>
       </c>
       <c r="F163" s="9">
-        <v>2967</v>
+        <v>2962</v>
       </c>
       <c r="G163" s="8">
-        <v>150341523.03</v>
+        <v>150023557.14</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -6551,19 +6555,19 @@
         <v>328</v>
       </c>
       <c r="C164" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D164" s="7">
-        <v>0.120604</v>
+        <v>0.120803</v>
       </c>
       <c r="E164" s="8">
-        <v>7564667867.1</v>
+        <v>7557669506.49</v>
       </c>
       <c r="F164" s="9">
-        <v>79719</v>
+        <v>79693</v>
       </c>
       <c r="G164" s="8">
-        <v>912331781.77</v>
+        <v>912991490.09</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -6574,19 +6578,19 @@
         <v>330</v>
       </c>
       <c r="C165" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D165" s="7">
-        <v>0.110368</v>
+        <v>0.110504</v>
       </c>
       <c r="E165" s="8">
-        <v>3332013971.03</v>
+        <v>3334847265.35</v>
       </c>
       <c r="F165" s="9">
-        <v>64871</v>
+        <v>64931</v>
       </c>
       <c r="G165" s="8">
-        <v>367747960.23</v>
+        <v>368515400.45</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -6597,19 +6601,19 @@
         <v>332</v>
       </c>
       <c r="C166" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D166" s="7">
-        <v>0.015044</v>
+        <v>0.014999</v>
       </c>
       <c r="E166" s="8">
-        <v>430264096515.55</v>
+        <v>431883404894.63</v>
       </c>
       <c r="F166" s="9">
-        <v>74116</v>
+        <v>74399</v>
       </c>
       <c r="G166" s="8">
-        <v>6473018776.66</v>
+        <v>6477991952.22</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -6620,19 +6624,19 @@
         <v>334</v>
       </c>
       <c r="C167" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D167" s="7">
-        <v>0.367573</v>
+        <v>46153</v>
+      </c>
+      <c r="D167" s="11">
+        <v>0.36828</v>
       </c>
       <c r="E167" s="8">
-        <v>692504655.12</v>
+        <v>694321231.36</v>
       </c>
       <c r="F167" s="9">
-        <v>6867</v>
+        <v>6864</v>
       </c>
       <c r="G167" s="8">
-        <v>254546119.52</v>
+        <v>255704442.69</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6643,19 +6647,19 @@
         <v>336</v>
       </c>
       <c r="C168" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D168" s="7">
-        <v>0.014279</v>
+        <v>0.014471</v>
       </c>
       <c r="E168" s="8">
-        <v>37329423540.19</v>
+        <v>37678645823.55</v>
       </c>
       <c r="F168" s="9">
-        <v>6217</v>
+        <v>6286</v>
       </c>
       <c r="G168" s="8">
-        <v>533036152.44</v>
+        <v>545255635.81</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6666,19 +6670,19 @@
         <v>338</v>
       </c>
       <c r="C169" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D169" s="7">
-        <v>0.703421</v>
+        <v>46153</v>
+      </c>
+      <c r="D169" s="11">
+        <v>0.70713</v>
       </c>
       <c r="E169" s="8">
-        <v>1941739652.41</v>
+        <v>1942965263.77</v>
       </c>
       <c r="F169" s="9">
-        <v>32780</v>
+        <v>32785</v>
       </c>
       <c r="G169" s="8">
-        <v>1365859881.19</v>
+        <v>1373928607.56</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6689,19 +6693,19 @@
         <v>340</v>
       </c>
       <c r="C170" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D170" s="7">
-        <v>0.390277</v>
+        <v>0.389899</v>
       </c>
       <c r="E170" s="8">
-        <v>1985688575.1</v>
+        <v>1978012864.91</v>
       </c>
       <c r="F170" s="9">
-        <v>20989</v>
+        <v>20961</v>
       </c>
       <c r="G170" s="8">
-        <v>774969368.88</v>
+        <v>771224636.05</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6712,19 +6716,19 @@
         <v>342</v>
       </c>
       <c r="C171" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D171" s="7">
-        <v>0.142943</v>
+        <v>0.142926</v>
       </c>
       <c r="E171" s="8">
-        <v>1570228424.04</v>
+        <v>1569098507.52</v>
       </c>
       <c r="F171" s="9">
-        <v>16337</v>
+        <v>16335</v>
       </c>
       <c r="G171" s="8">
-        <v>224452391.98</v>
+        <v>224264401.06</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6735,19 +6739,19 @@
         <v>344</v>
       </c>
       <c r="C172" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D172" s="7">
-        <v>1.287107</v>
+        <v>1.289538</v>
       </c>
       <c r="E172" s="8">
-        <v>1396211302.83</v>
+        <v>1398413520.35</v>
       </c>
       <c r="F172" s="9">
-        <v>23897</v>
+        <v>23896</v>
       </c>
       <c r="G172" s="8">
-        <v>1797072912.6</v>
+        <v>1803307963.84</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6758,19 +6762,19 @@
         <v>346</v>
       </c>
       <c r="C173" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D173" s="7">
-        <v>0.574793</v>
+        <v>0.575053</v>
       </c>
       <c r="E173" s="8">
-        <v>2358794522.61</v>
+        <v>2354619874.82</v>
       </c>
       <c r="F173" s="9">
-        <v>34854</v>
+        <v>34829</v>
       </c>
       <c r="G173" s="8">
-        <v>1355818927.03</v>
+        <v>1354031517.22</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6781,19 +6785,19 @@
         <v>348</v>
       </c>
       <c r="C174" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D174" s="7">
-        <v>0.017726</v>
+        <v>0.017598</v>
       </c>
       <c r="E174" s="8">
-        <v>76621808152.66</v>
+        <v>77562746075.58</v>
       </c>
       <c r="F174" s="9">
-        <v>18176</v>
+        <v>18348</v>
       </c>
       <c r="G174" s="8">
-        <v>1358226874.75</v>
+        <v>1364953383.15</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6804,19 +6808,19 @@
         <v>350</v>
       </c>
       <c r="C175" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D175" s="7">
-        <v>0.090755</v>
+        <v>0.090896</v>
       </c>
       <c r="E175" s="8">
-        <v>2210112565.92</v>
+        <v>2217351912.91</v>
       </c>
       <c r="F175" s="9">
-        <v>5188</v>
+        <v>5185</v>
       </c>
       <c r="G175" s="8">
-        <v>200578202.5</v>
+        <v>201548693.75</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6827,19 +6831,19 @@
         <v>352</v>
       </c>
       <c r="C176" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D176" s="7">
-        <v>0.122495</v>
+        <v>0.122969</v>
       </c>
       <c r="E176" s="8">
-        <v>1645424448.87</v>
+        <v>1644858309.6</v>
       </c>
       <c r="F176" s="9">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="G176" s="8">
-        <v>201556910.5</v>
+        <v>202266560.39</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6850,19 +6854,19 @@
         <v>354</v>
       </c>
       <c r="C177" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D177" s="7">
-        <v>0.319584</v>
+        <v>0.320791</v>
       </c>
       <c r="E177" s="8">
-        <v>747940786.57</v>
+        <v>745550861.83</v>
       </c>
       <c r="F177" s="9">
-        <v>1942</v>
+        <v>1939</v>
       </c>
       <c r="G177" s="8">
-        <v>239029773.9</v>
+        <v>239165872.79</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6873,19 +6877,19 @@
         <v>356</v>
       </c>
       <c r="C178" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D178" s="7">
-        <v>0.092378</v>
+        <v>0.092553</v>
       </c>
       <c r="E178" s="8">
-        <v>41857770756.89</v>
+        <v>41844008863.93</v>
       </c>
       <c r="F178" s="9">
-        <v>283513</v>
+        <v>283443</v>
       </c>
       <c r="G178" s="8">
-        <v>3866753900.13</v>
+        <v>3872797763.91</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6896,19 +6900,19 @@
         <v>358</v>
       </c>
       <c r="C179" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D179" s="7">
-        <v>0.066288</v>
+        <v>0.066276</v>
       </c>
       <c r="E179" s="8">
-        <v>671606758.11</v>
+        <v>673049487.18</v>
       </c>
       <c r="F179" s="9">
         <v>6096</v>
       </c>
       <c r="G179" s="8">
-        <v>44519707.93</v>
+        <v>44607275.26</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6919,19 +6923,19 @@
         <v>360</v>
       </c>
       <c r="C180" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D180" s="7">
-        <v>0.254887</v>
+        <v>0.255797</v>
       </c>
       <c r="E180" s="8">
-        <v>550481589.68</v>
+        <v>550196756.06</v>
       </c>
       <c r="F180" s="9">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="G180" s="8">
-        <v>140310631.21</v>
+        <v>140738645.23</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6942,19 +6946,19 @@
         <v>362</v>
       </c>
       <c r="C181" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D181" s="7">
-        <v>0.401244</v>
+        <v>46153</v>
+      </c>
+      <c r="D181" s="10">
+        <v>0.4025</v>
       </c>
       <c r="E181" s="8">
-        <v>368800463.5</v>
+        <v>367734292.04</v>
       </c>
       <c r="F181" s="9">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="G181" s="8">
-        <v>147979031.15</v>
+        <v>148013180.31</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6965,19 +6969,19 @@
         <v>364</v>
       </c>
       <c r="C182" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D182" s="7">
-        <v>0.112956</v>
+        <v>0.113322</v>
       </c>
       <c r="E182" s="8">
-        <v>14384830435.97</v>
+        <v>14366160253.72</v>
       </c>
       <c r="F182" s="9">
-        <v>32165</v>
+        <v>32161</v>
       </c>
       <c r="G182" s="8">
-        <v>1624858604.41</v>
+        <v>1628000043.14</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6988,19 +6992,19 @@
         <v>366</v>
       </c>
       <c r="C183" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D183" s="7">
-        <v>0.116338</v>
+        <v>0.116664</v>
       </c>
       <c r="E183" s="8">
-        <v>23347380027.81</v>
+        <v>23373509721.31</v>
       </c>
       <c r="F183" s="9">
-        <v>43228</v>
+        <v>41511</v>
       </c>
       <c r="G183" s="8">
-        <v>2716182827.13</v>
+        <v>2726854519.66</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7011,19 +7015,19 @@
         <v>368</v>
       </c>
       <c r="C184" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D184" s="7">
-        <v>0.098619</v>
+        <v>0.099452</v>
       </c>
       <c r="E184" s="8">
-        <v>31718299258.14</v>
+        <v>31921368303.63</v>
       </c>
       <c r="F184" s="9">
-        <v>30189</v>
+        <v>30285</v>
       </c>
       <c r="G184" s="8">
-        <v>3128017243.91</v>
+        <v>3174651072.45</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7034,19 +7038,19 @@
         <v>370</v>
       </c>
       <c r="C185" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D185" s="7">
-        <v>0.086751</v>
+        <v>0.087006</v>
       </c>
       <c r="E185" s="8">
-        <v>6419711190.68</v>
+        <v>6437106004.84</v>
       </c>
       <c r="F185" s="9">
-        <v>5032</v>
+        <v>5023</v>
       </c>
       <c r="G185" s="8">
-        <v>556914461.45</v>
+        <v>560068523.67</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7057,19 +7061,19 @@
         <v>372</v>
       </c>
       <c r="C186" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D186" s="7">
-        <v>0.074013</v>
+        <v>46153</v>
+      </c>
+      <c r="D186" s="11">
+        <v>0.07412</v>
       </c>
       <c r="E186" s="8">
-        <v>14150842904.22</v>
+        <v>14165395222.36</v>
       </c>
       <c r="F186" s="9">
-        <v>184494</v>
+        <v>184595</v>
       </c>
       <c r="G186" s="8">
-        <v>1047345897.28</v>
+        <v>1049941554.36</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7080,19 +7084,19 @@
         <v>374</v>
       </c>
       <c r="C187" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D187" s="7">
-        <v>0.099804</v>
+        <v>0.100079</v>
       </c>
       <c r="E187" s="8">
-        <v>4091813935.09</v>
+        <v>4094074632.84</v>
       </c>
       <c r="F187" s="9">
-        <v>117655</v>
+        <v>117710</v>
       </c>
       <c r="G187" s="8">
-        <v>408377399.58</v>
+        <v>409732484.2</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7103,19 +7107,19 @@
         <v>376</v>
       </c>
       <c r="C188" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D188" s="7">
-        <v>0.246319</v>
+        <v>46153</v>
+      </c>
+      <c r="D188" s="12">
+        <v>0.247</v>
       </c>
       <c r="E188" s="8">
-        <v>669705038.39</v>
+        <v>669786934.64</v>
       </c>
       <c r="F188" s="9">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="G188" s="8">
-        <v>164961242.47</v>
+        <v>165437348.26</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7126,19 +7130,19 @@
         <v>378</v>
       </c>
       <c r="C189" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D189" s="7">
-        <v>0.085314</v>
+        <v>0.085529</v>
       </c>
       <c r="E189" s="8">
-        <v>2820086267.8</v>
+        <v>2803537310.13</v>
       </c>
       <c r="F189" s="9">
-        <v>43634</v>
+        <v>43430</v>
       </c>
       <c r="G189" s="8">
-        <v>240594240.62</v>
+        <v>239784646.56</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7149,19 +7153,19 @@
         <v>380</v>
       </c>
       <c r="C190" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D190" s="7">
-        <v>0.247215</v>
+        <v>46153</v>
+      </c>
+      <c r="D190" s="11">
+        <v>0.24699</v>
       </c>
       <c r="E190" s="8">
-        <v>3380816216.46</v>
+        <v>3377133593.2</v>
       </c>
       <c r="F190" s="9">
-        <v>6656</v>
+        <v>6663</v>
       </c>
       <c r="G190" s="8">
-        <v>835788878.61</v>
+        <v>834118000.38</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7172,19 +7176,19 @@
         <v>382</v>
       </c>
       <c r="C191" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D191" s="7">
-        <v>0.164394</v>
+        <v>0.164927</v>
       </c>
       <c r="E191" s="8">
-        <v>705967565.52</v>
+        <v>705516358.48</v>
       </c>
       <c r="F191" s="9">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="G191" s="8">
-        <v>116056600.68</v>
+        <v>116358904.3</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7195,19 +7199,19 @@
         <v>384</v>
       </c>
       <c r="C192" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D192" s="7">
-        <v>0.152768</v>
+        <v>0.153133</v>
       </c>
       <c r="E192" s="8">
-        <v>491029668.92</v>
+        <v>490702155.59</v>
       </c>
       <c r="F192" s="9">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="G192" s="8">
-        <v>75013819</v>
+        <v>75142700.23</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7218,19 +7222,19 @@
         <v>386</v>
       </c>
       <c r="C193" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D193" s="7">
-        <v>0.103051</v>
+        <v>46153</v>
+      </c>
+      <c r="D193" s="11">
+        <v>0.10391</v>
       </c>
       <c r="E193" s="8">
-        <v>1166207275.68</v>
+        <v>1165452979.07</v>
       </c>
       <c r="F193" s="9">
-        <v>117344</v>
+        <v>117328</v>
       </c>
       <c r="G193" s="8">
-        <v>120179365.39</v>
+        <v>121102082.7</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7241,19 +7245,19 @@
         <v>388</v>
       </c>
       <c r="C194" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D194" s="7">
-        <v>0.206349</v>
+        <v>0.206616</v>
       </c>
       <c r="E194" s="8">
-        <v>2001950031.65</v>
+        <v>2006763123.1</v>
       </c>
       <c r="F194" s="9">
-        <v>1607</v>
+        <v>1623</v>
       </c>
       <c r="G194" s="8">
-        <v>413099387.34</v>
+        <v>414629452.48</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7264,19 +7268,19 @@
         <v>390</v>
       </c>
       <c r="C195" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D195" s="7">
-        <v>0.159915</v>
+        <v>0.160748</v>
       </c>
       <c r="E195" s="8">
-        <v>597348055.97</v>
+        <v>597646656.75</v>
       </c>
       <c r="F195" s="9">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="G195" s="8">
-        <v>95524819.25</v>
+        <v>96070425.82</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7287,19 +7291,19 @@
         <v>392</v>
       </c>
       <c r="C196" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D196" s="7">
-        <v>0.279006</v>
+        <v>0.279547</v>
       </c>
       <c r="E196" s="8">
-        <v>2759113409.56</v>
+        <v>2755096352.03</v>
       </c>
       <c r="F196" s="9">
-        <v>7655</v>
+        <v>7646</v>
       </c>
       <c r="G196" s="8">
-        <v>769808096.38</v>
+        <v>770178298.27</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7310,19 +7314,19 @@
         <v>394</v>
       </c>
       <c r="C197" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D197" s="7">
-        <v>0.099963</v>
+        <v>46153</v>
+      </c>
+      <c r="D197" s="11">
+        <v>0.10049</v>
       </c>
       <c r="E197" s="8">
-        <v>104564320.35</v>
+        <v>104583837.64</v>
       </c>
       <c r="F197" s="9">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G197" s="8">
-        <v>10452572.99</v>
+        <v>10509627.35</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7333,19 +7337,19 @@
         <v>396</v>
       </c>
       <c r="C198" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D198" s="7">
-        <v>0.227046</v>
+        <v>0.229104</v>
       </c>
       <c r="E198" s="8">
-        <v>326653641.77</v>
+        <v>328944856.43</v>
       </c>
       <c r="F198" s="9">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="G198" s="8">
-        <v>74165321.14</v>
+        <v>75362739.84</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7356,19 +7360,19 @@
         <v>398</v>
       </c>
       <c r="C199" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D199" s="7">
-        <v>0.179536</v>
+        <v>0.180952</v>
       </c>
       <c r="E199" s="8">
-        <v>272491889.39</v>
+        <v>273008912.11</v>
       </c>
       <c r="F199" s="9">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="G199" s="8">
-        <v>48922005.59</v>
+        <v>49401496.21</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7379,19 +7383,19 @@
         <v>400</v>
       </c>
       <c r="C200" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D200" s="7">
-        <v>0.088257</v>
+        <v>0.088528</v>
       </c>
       <c r="E200" s="8">
-        <v>2725097908.49</v>
+        <v>2713881061.05</v>
       </c>
       <c r="F200" s="9">
-        <v>41148</v>
+        <v>41061</v>
       </c>
       <c r="G200" s="8">
-        <v>240508486.95</v>
+        <v>240253980.76</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7402,19 +7406,19 @@
         <v>402</v>
       </c>
       <c r="C201" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D201" s="7">
-        <v>0.090738</v>
+        <v>0.091005</v>
       </c>
       <c r="E201" s="8">
-        <v>831484470.96</v>
+        <v>827870502.96</v>
       </c>
       <c r="F201" s="9">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="G201" s="8">
-        <v>75447383.27</v>
+        <v>75340241.7</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7425,19 +7429,19 @@
         <v>404</v>
       </c>
       <c r="C202" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D202" s="7">
-        <v>0.154747</v>
+        <v>0.156228</v>
       </c>
       <c r="E202" s="8">
-        <v>9536203304.11</v>
+        <v>9480616703.76</v>
       </c>
       <c r="F202" s="9">
-        <v>9365</v>
+        <v>9351</v>
       </c>
       <c r="G202" s="8">
-        <v>1475699642.8</v>
+        <v>1481133831.77</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7448,19 +7452,19 @@
         <v>406</v>
       </c>
       <c r="C203" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D203" s="7">
-        <v>0.014821</v>
+        <v>0.014871</v>
       </c>
       <c r="E203" s="8">
-        <v>8818195864.33</v>
+        <v>8842199600.8</v>
       </c>
       <c r="F203" s="9">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="G203" s="8">
-        <v>130698029.05</v>
+        <v>131491342.53</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7471,19 +7475,19 @@
         <v>408</v>
       </c>
       <c r="C204" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D204" s="7">
-        <v>0.028815</v>
+        <v>0.028885</v>
       </c>
       <c r="E204" s="8">
-        <v>1382173180.06</v>
+        <v>1384185487.3</v>
       </c>
       <c r="F204" s="9">
         <v>979</v>
       </c>
       <c r="G204" s="8">
-        <v>39827978.32</v>
+        <v>39981920.43</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7494,19 +7498,19 @@
         <v>410</v>
       </c>
       <c r="C205" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D205" s="10">
-        <v>0.12113</v>
+        <v>46153</v>
+      </c>
+      <c r="D205" s="7">
+        <v>0.122073</v>
       </c>
       <c r="E205" s="8">
-        <v>3211316539.11</v>
+        <v>3209770929.22</v>
       </c>
       <c r="F205" s="9">
-        <v>311709</v>
+        <v>311646</v>
       </c>
       <c r="G205" s="8">
-        <v>388985767.88</v>
+        <v>391826326.47</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -7517,19 +7521,19 @@
         <v>412</v>
       </c>
       <c r="C206" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D206" s="7">
-        <v>0.158849</v>
+        <v>0.159606</v>
       </c>
       <c r="E206" s="8">
-        <v>522322804.49</v>
+        <v>528048342.38</v>
       </c>
       <c r="F206" s="9">
-        <v>1028</v>
+        <v>1047</v>
       </c>
       <c r="G206" s="8">
-        <v>82970713.44</v>
+        <v>84279681.17</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7540,19 +7544,19 @@
         <v>414</v>
       </c>
       <c r="C207" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D207" s="7">
-        <v>0.134375</v>
+        <v>0.135092</v>
       </c>
       <c r="E207" s="8">
-        <v>2871320094.65</v>
+        <v>2885845330.45</v>
       </c>
       <c r="F207" s="9">
-        <v>5785</v>
+        <v>5797</v>
       </c>
       <c r="G207" s="8">
-        <v>385832500.29</v>
+        <v>389854315.43</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7563,19 +7567,19 @@
         <v>416</v>
       </c>
       <c r="C208" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D208" s="7">
-        <v>0.106201</v>
+        <v>0.107214</v>
       </c>
       <c r="E208" s="8">
-        <v>4319441794.28</v>
+        <v>4318757351.79</v>
       </c>
       <c r="F208" s="9">
-        <v>347903</v>
+        <v>347806</v>
       </c>
       <c r="G208" s="8">
-        <v>458730583.86</v>
+        <v>463032918.15</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7586,19 +7590,19 @@
         <v>418</v>
       </c>
       <c r="C209" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D209" s="7">
-        <v>0.107372</v>
+        <v>0.107883</v>
       </c>
       <c r="E209" s="8">
-        <v>46723624827.08</v>
+        <v>46772035338.55</v>
       </c>
       <c r="F209" s="9">
-        <v>713941</v>
+        <v>714336</v>
       </c>
       <c r="G209" s="8">
-        <v>5016807440.95</v>
+        <v>5045896728.19</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7609,19 +7613,19 @@
         <v>420</v>
       </c>
       <c r="C210" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D210" s="7">
-        <v>0.067194</v>
+        <v>0.067783</v>
       </c>
       <c r="E210" s="8">
-        <v>60483583800.12</v>
+        <v>61318917903.39</v>
       </c>
       <c r="F210" s="9">
-        <v>61150</v>
+        <v>61408</v>
       </c>
       <c r="G210" s="8">
-        <v>4064143878.63</v>
+        <v>4156404144.29</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -7632,19 +7636,19 @@
         <v>422</v>
       </c>
       <c r="C211" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D211" s="7">
-        <v>0.108205</v>
+        <v>0.108358</v>
       </c>
       <c r="E211" s="8">
-        <v>65312951351.97</v>
+        <v>65350152668.56</v>
       </c>
       <c r="F211" s="9">
-        <v>916174</v>
+        <v>916597</v>
       </c>
       <c r="G211" s="8">
-        <v>7067187877.49</v>
+        <v>7081234831.53</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7655,19 +7659,19 @@
         <v>424</v>
       </c>
       <c r="C212" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D212" s="7">
-        <v>0.070108</v>
+        <v>0.070207</v>
       </c>
       <c r="E212" s="8">
-        <v>54414424164.45</v>
+        <v>54392654534.93</v>
       </c>
       <c r="F212" s="9">
-        <v>55368</v>
+        <v>55312</v>
       </c>
       <c r="G212" s="8">
-        <v>3814898602.47</v>
+        <v>3818743205.45</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7678,19 +7682,19 @@
         <v>426</v>
       </c>
       <c r="C213" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D213" s="7">
-        <v>0.097821</v>
+        <v>0.098105</v>
       </c>
       <c r="E213" s="8">
-        <v>16593260702.87</v>
+        <v>16563738473.94</v>
       </c>
       <c r="F213" s="9">
-        <v>353424</v>
+        <v>353535</v>
       </c>
       <c r="G213" s="8">
-        <v>1623166357.4</v>
+        <v>1624993550.85</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -7701,19 +7705,19 @@
         <v>428</v>
       </c>
       <c r="C214" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D214" s="7">
-        <v>0.052357</v>
+        <v>0.051925</v>
       </c>
       <c r="E214" s="8">
-        <v>82047091893.47</v>
+        <v>81963572911.52</v>
       </c>
       <c r="F214" s="9">
-        <v>34387</v>
+        <v>34271</v>
       </c>
       <c r="G214" s="8">
-        <v>4295743383.36</v>
+        <v>4255975872.32</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7724,19 +7728,19 @@
         <v>430</v>
       </c>
       <c r="C215" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D215" s="7">
-        <v>0.086229</v>
+        <v>0.086504</v>
       </c>
       <c r="E215" s="8">
-        <v>14088405239.86</v>
+        <v>14133088199.7</v>
       </c>
       <c r="F215" s="9">
-        <v>240892</v>
+        <v>242262</v>
       </c>
       <c r="G215" s="8">
-        <v>1214833673.5</v>
+        <v>1222562761.67</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -7747,19 +7751,19 @@
         <v>432</v>
       </c>
       <c r="C216" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D216" s="7">
-        <v>0.324995</v>
+        <v>0.328212</v>
       </c>
       <c r="E216" s="8">
-        <v>12295542427.21</v>
+        <v>12323174480.85</v>
       </c>
       <c r="F216" s="9">
-        <v>58329</v>
+        <v>58453</v>
       </c>
       <c r="G216" s="8">
-        <v>3995986219.11</v>
+        <v>4044607888.5</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -7770,19 +7774,19 @@
         <v>434</v>
       </c>
       <c r="C217" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D217" s="7">
-        <v>0.229714</v>
+        <v>0.230405</v>
       </c>
       <c r="E217" s="8">
-        <v>10576662587.73</v>
+        <v>10598228024.94</v>
       </c>
       <c r="F217" s="9">
-        <v>40030</v>
+        <v>40144</v>
       </c>
       <c r="G217" s="8">
-        <v>2429604311.78</v>
+        <v>2441879573.1</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7793,19 +7797,19 @@
         <v>436</v>
       </c>
       <c r="C218" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D218" s="10">
-        <v>1.04064</v>
+        <v>46153</v>
+      </c>
+      <c r="D218" s="7">
+        <v>1.043475</v>
       </c>
       <c r="E218" s="8">
-        <v>742518994.81</v>
+        <v>737041563.74</v>
       </c>
       <c r="F218" s="9">
-        <v>4348</v>
+        <v>4356</v>
       </c>
       <c r="G218" s="8">
-        <v>772695046.34</v>
+        <v>769084368.65</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -7816,19 +7820,19 @@
         <v>438</v>
       </c>
       <c r="C219" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D219" s="10">
-        <v>0.74846</v>
+        <v>46153</v>
+      </c>
+      <c r="D219" s="11">
+        <v>0.75277</v>
       </c>
       <c r="E219" s="8">
-        <v>5924499081.71</v>
+        <v>5932115814.63</v>
       </c>
       <c r="F219" s="9">
-        <v>11080</v>
+        <v>11089</v>
       </c>
       <c r="G219" s="8">
-        <v>4434253344.34</v>
+        <v>4465519579.94</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -7839,19 +7843,19 @@
         <v>440</v>
       </c>
       <c r="C220" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D220" s="7">
-        <v>2.942882</v>
+        <v>2.959393</v>
       </c>
       <c r="E220" s="8">
-        <v>6240124205.58</v>
+        <v>6234566574.08</v>
       </c>
       <c r="F220" s="9">
-        <v>273147</v>
+        <v>273162</v>
       </c>
       <c r="G220" s="8">
-        <v>18363951867.92</v>
+        <v>18450532316.51</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -7862,19 +7866,19 @@
         <v>442</v>
       </c>
       <c r="C221" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D221" s="10">
-        <v>0.41214</v>
+        <v>46153</v>
+      </c>
+      <c r="D221" s="7">
+        <v>0.411905</v>
       </c>
       <c r="E221" s="8">
-        <v>9304832434.92</v>
+        <v>9295179449.75</v>
       </c>
       <c r="F221" s="9">
-        <v>164990</v>
+        <v>164925</v>
       </c>
       <c r="G221" s="8">
-        <v>3834891946.66</v>
+        <v>3828729001.7</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -7885,19 +7889,19 @@
         <v>444</v>
       </c>
       <c r="C222" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D222" s="7">
-        <v>0.397371</v>
+        <v>0.398444</v>
       </c>
       <c r="E222" s="8">
-        <v>179023802942.09</v>
+        <v>179059378241.71</v>
       </c>
       <c r="F222" s="9">
-        <v>389376</v>
+        <v>390736</v>
       </c>
       <c r="G222" s="8">
-        <v>71138844987.55</v>
+        <v>71345162487.59</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -7908,19 +7912,19 @@
         <v>446</v>
       </c>
       <c r="C223" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D223" s="7">
-        <v>0.155506</v>
+        <v>0.156444</v>
       </c>
       <c r="E223" s="8">
-        <v>6445019648.37</v>
+        <v>6432231459</v>
       </c>
       <c r="F223" s="9">
-        <v>25333</v>
+        <v>25352</v>
       </c>
       <c r="G223" s="8">
-        <v>1002237167.88</v>
+        <v>1006282519.1</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -7931,19 +7935,19 @@
         <v>448</v>
       </c>
       <c r="C224" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D224" s="7">
-        <v>0.522133</v>
+        <v>0.522973</v>
       </c>
       <c r="E224" s="8">
-        <v>8118545582.44</v>
+        <v>8189781596.75</v>
       </c>
       <c r="F224" s="9">
-        <v>35622</v>
+        <v>35608</v>
       </c>
       <c r="G224" s="8">
-        <v>4238960776.57</v>
+        <v>4283038201.84</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -7954,19 +7958,19 @@
         <v>450</v>
       </c>
       <c r="C225" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D225" s="7">
-        <v>0.076435</v>
+        <v>0.076183</v>
       </c>
       <c r="E225" s="8">
-        <v>2507060473433.83</v>
+        <v>2506178247414.87</v>
       </c>
       <c r="F225" s="9">
-        <v>1246439</v>
+        <v>1246412</v>
       </c>
       <c r="G225" s="8">
-        <v>191626605441.81</v>
+        <v>190928466832.74</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -7977,19 +7981,19 @@
         <v>452</v>
       </c>
       <c r="C226" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D226" s="7">
-        <v>0.075928</v>
+        <v>0.076238</v>
       </c>
       <c r="E226" s="8">
-        <v>26765085154.1</v>
+        <v>26808782042.82</v>
       </c>
       <c r="F226" s="9">
-        <v>95215</v>
+        <v>95156</v>
       </c>
       <c r="G226" s="8">
-        <v>2032229230.81</v>
+        <v>2043841192.81</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -8000,19 +8004,19 @@
         <v>454</v>
       </c>
       <c r="C227" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D227" s="7">
-        <v>0.016345</v>
+        <v>0.016542</v>
       </c>
       <c r="E227" s="8">
-        <v>515435195849.71</v>
+        <v>515311923223.76</v>
       </c>
       <c r="F227" s="9">
-        <v>50504</v>
+        <v>50441</v>
       </c>
       <c r="G227" s="8">
-        <v>8424702240.91</v>
+        <v>8524191888.09</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8023,19 +8027,19 @@
         <v>456</v>
       </c>
       <c r="C228" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D228" s="7">
-        <v>0.808958</v>
+        <v>0.803748</v>
       </c>
       <c r="E228" s="8">
-        <v>170535540887.52</v>
+        <v>170404621853.29</v>
       </c>
       <c r="F228" s="9">
-        <v>825575</v>
+        <v>826114</v>
       </c>
       <c r="G228" s="8">
-        <v>137956068432.97</v>
+        <v>136962291939.83</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8046,19 +8050,19 @@
         <v>458</v>
       </c>
       <c r="C229" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D229" s="7">
-        <v>0.141555</v>
+        <v>0.141699</v>
       </c>
       <c r="E229" s="8">
-        <v>26943726090.06</v>
+        <v>26946076349.16</v>
       </c>
       <c r="F229" s="9">
-        <v>194674</v>
+        <v>194664</v>
       </c>
       <c r="G229" s="8">
-        <v>3814015534.98</v>
+        <v>3818236842.48</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8069,19 +8073,19 @@
         <v>460</v>
       </c>
       <c r="C230" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D230" s="10">
-        <v>1.14178</v>
+        <v>46153</v>
+      </c>
+      <c r="D230" s="7">
+        <v>1.145042</v>
       </c>
       <c r="E230" s="8">
-        <v>2626367425.42</v>
+        <v>2625156252.51</v>
       </c>
       <c r="F230" s="9">
-        <v>49096</v>
+        <v>49090</v>
       </c>
       <c r="G230" s="8">
-        <v>2998734540.57</v>
+        <v>3005913547.85</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8092,19 +8096,19 @@
         <v>462</v>
       </c>
       <c r="C231" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D231" s="7">
-        <v>0.286908</v>
+        <v>0.286686</v>
       </c>
       <c r="E231" s="8">
-        <v>2495069521.58</v>
+        <v>2484203719.09</v>
       </c>
       <c r="F231" s="9">
-        <v>11224</v>
+        <v>11220</v>
       </c>
       <c r="G231" s="8">
-        <v>715854523.87</v>
+        <v>712187005.25</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8115,19 +8119,19 @@
         <v>464</v>
       </c>
       <c r="C232" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D232" s="7">
-        <v>1.138231</v>
+        <v>1.139022</v>
       </c>
       <c r="E232" s="8">
-        <v>5209814669.13</v>
+        <v>5203524849.17</v>
       </c>
       <c r="F232" s="9">
-        <v>63428</v>
+        <v>63403</v>
       </c>
       <c r="G232" s="8">
-        <v>5929974579.67</v>
+        <v>5926927945.9</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8138,19 +8142,19 @@
         <v>466</v>
       </c>
       <c r="C233" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D233" s="7">
-        <v>0.390069</v>
+        <v>0.392042</v>
       </c>
       <c r="E233" s="8">
-        <v>18977095021.61</v>
+        <v>19033291624.03</v>
       </c>
       <c r="F233" s="9">
-        <v>151508</v>
+        <v>151688</v>
       </c>
       <c r="G233" s="8">
-        <v>7402378451.15</v>
+        <v>7461857317.38</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8161,19 +8165,19 @@
         <v>468</v>
       </c>
       <c r="C234" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D234" s="7">
-        <v>0.110371</v>
+        <v>0.110492</v>
       </c>
       <c r="E234" s="8">
-        <v>281672040270.51</v>
+        <v>281422895667.81</v>
       </c>
       <c r="F234" s="9">
-        <v>1528521</v>
+        <v>1527828</v>
       </c>
       <c r="G234" s="8">
-        <v>31088311292.73</v>
+        <v>31094839084.04</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8184,19 +8188,19 @@
         <v>470</v>
       </c>
       <c r="C235" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D235" s="7">
-        <v>0.273363</v>
+        <v>0.274402</v>
       </c>
       <c r="E235" s="8">
-        <v>3290829201.44</v>
+        <v>3293808529.46</v>
       </c>
       <c r="F235" s="9">
-        <v>10543</v>
+        <v>10537</v>
       </c>
       <c r="G235" s="8">
-        <v>899591504.32</v>
+        <v>903828326.96</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8207,19 +8211,19 @@
         <v>472</v>
       </c>
       <c r="C236" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D236" s="10">
-        <v>0.79582</v>
+        <v>46153</v>
+      </c>
+      <c r="D236" s="11">
+        <v>0.79635</v>
       </c>
       <c r="E236" s="8">
-        <v>1337975831.24</v>
+        <v>1338133790.36</v>
       </c>
       <c r="F236" s="9">
-        <v>7626</v>
+        <v>7620</v>
       </c>
       <c r="G236" s="8">
-        <v>1064788473.1</v>
+        <v>1065622192.14</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8230,19 +8234,19 @@
         <v>474</v>
       </c>
       <c r="C237" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D237" s="10">
-        <v>0.15605</v>
+        <v>46153</v>
+      </c>
+      <c r="D237" s="7">
+        <v>0.157475</v>
       </c>
       <c r="E237" s="8">
-        <v>71964353110.16</v>
+        <v>71884210822.59</v>
       </c>
       <c r="F237" s="9">
-        <v>841317</v>
+        <v>840789</v>
       </c>
       <c r="G237" s="8">
-        <v>11230071684.03</v>
+        <v>11319941210.81</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -8253,19 +8257,19 @@
         <v>476</v>
       </c>
       <c r="C238" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D238" s="7">
-        <v>0.229247</v>
+        <v>0.230018</v>
       </c>
       <c r="E238" s="8">
-        <v>2441066461.42</v>
+        <v>2442507881.3</v>
       </c>
       <c r="F238" s="9">
-        <v>7585</v>
+        <v>7571</v>
       </c>
       <c r="G238" s="8">
-        <v>559608359.34</v>
+        <v>561821667.74</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -8276,19 +8280,19 @@
         <v>478</v>
       </c>
       <c r="C239" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D239" s="7">
-        <v>0.201929</v>
+        <v>0.202885</v>
       </c>
       <c r="E239" s="8">
-        <v>2346664763.22</v>
+        <v>2349518573.32</v>
       </c>
       <c r="F239" s="9">
-        <v>7369</v>
+        <v>7367</v>
       </c>
       <c r="G239" s="8">
-        <v>473859259.82</v>
+        <v>476681351.61</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,19 +8303,19 @@
         <v>480</v>
       </c>
       <c r="C240" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D240" s="7">
-        <v>0.352764</v>
+        <v>0.354054</v>
       </c>
       <c r="E240" s="8">
-        <v>31366276907.91</v>
+        <v>31393887360.01</v>
       </c>
       <c r="F240" s="9">
-        <v>120324</v>
+        <v>120330</v>
       </c>
       <c r="G240" s="8">
-        <v>11064904163.83</v>
+        <v>11115131782.19</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -8322,19 +8326,19 @@
         <v>482</v>
       </c>
       <c r="C241" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D241" s="7">
-        <v>0.127714</v>
+        <v>0.128112</v>
       </c>
       <c r="E241" s="8">
-        <v>3795761983.71</v>
+        <v>3786426278.17</v>
       </c>
       <c r="F241" s="9">
-        <v>7384</v>
+        <v>7364</v>
       </c>
       <c r="G241" s="8">
-        <v>484773492.15</v>
+        <v>485086753.59</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -8345,19 +8349,19 @@
         <v>484</v>
       </c>
       <c r="C242" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D242" s="7">
-        <v>0.130204</v>
+        <v>46153</v>
+      </c>
+      <c r="D242" s="11">
+        <v>0.13026</v>
       </c>
       <c r="E242" s="8">
-        <v>89150841292.3</v>
+        <v>89098724476.62</v>
       </c>
       <c r="F242" s="9">
-        <v>403070</v>
+        <v>403076</v>
       </c>
       <c r="G242" s="8">
-        <v>11607838820.7</v>
+        <v>11605973952.21</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8368,19 +8372,19 @@
         <v>486</v>
       </c>
       <c r="C243" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D243" s="7">
-        <v>0.318463</v>
+        <v>0.323281</v>
       </c>
       <c r="E243" s="8">
-        <v>3944887495.81</v>
+        <v>3969582103.11</v>
       </c>
       <c r="F243" s="9">
-        <v>18324</v>
+        <v>18372</v>
       </c>
       <c r="G243" s="8">
-        <v>1256302220.2</v>
+        <v>1283292092.3</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -8391,19 +8395,19 @@
         <v>488</v>
       </c>
       <c r="C244" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D244" s="10">
-        <v>0.08175</v>
+        <v>46153</v>
+      </c>
+      <c r="D244" s="7">
+        <v>0.081991</v>
       </c>
       <c r="E244" s="8">
-        <v>3847754173.23</v>
+        <v>3839907273.38</v>
       </c>
       <c r="F244" s="9">
-        <v>9174</v>
+        <v>9158</v>
       </c>
       <c r="G244" s="8">
-        <v>314552311.25</v>
+        <v>314836680.06</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8414,19 +8418,19 @@
         <v>490</v>
       </c>
       <c r="C245" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D245" s="7">
-        <v>0.253936</v>
+        <v>46153</v>
+      </c>
+      <c r="D245" s="11">
+        <v>0.25711</v>
       </c>
       <c r="E245" s="8">
-        <v>2869544211.02</v>
+        <v>2878202531.17</v>
       </c>
       <c r="F245" s="9">
-        <v>14169</v>
+        <v>14188</v>
       </c>
       <c r="G245" s="8">
-        <v>728681394.63</v>
+        <v>740015396.92</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -8437,19 +8441,19 @@
         <v>492</v>
       </c>
       <c r="C246" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D246" s="7">
-        <v>0.069325</v>
+        <v>0.069531</v>
       </c>
       <c r="E246" s="8">
-        <v>4028072427.11</v>
+        <v>4028853911.56</v>
       </c>
       <c r="F246" s="9">
-        <v>7739</v>
+        <v>7728</v>
       </c>
       <c r="G246" s="8">
-        <v>279245589.01</v>
+        <v>280130712.92</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8460,19 +8464,19 @@
         <v>494</v>
       </c>
       <c r="C247" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D247" s="7">
-        <v>0.179618</v>
+        <v>0.180053</v>
       </c>
       <c r="E247" s="8">
-        <v>14513426639.54</v>
+        <v>14508068535.06</v>
       </c>
       <c r="F247" s="9">
-        <v>48942</v>
+        <v>48977</v>
       </c>
       <c r="G247" s="8">
-        <v>2606867390.39</v>
+        <v>2612217570.37</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8483,19 +8487,19 @@
         <v>496</v>
       </c>
       <c r="C248" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D248" s="7">
-        <v>0.026083</v>
+        <v>0.026208</v>
       </c>
       <c r="E248" s="8">
-        <v>952459391674.64</v>
+        <v>951884670366.34</v>
       </c>
       <c r="F248" s="9">
-        <v>186648</v>
+        <v>186629</v>
       </c>
       <c r="G248" s="8">
-        <v>24842843255.8</v>
+        <v>24947258729.31</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8506,19 +8510,19 @@
         <v>498</v>
       </c>
       <c r="C249" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D249" s="10">
-        <v>0.76297</v>
+        <v>46153</v>
+      </c>
+      <c r="D249" s="7">
+        <v>0.759366</v>
       </c>
       <c r="E249" s="8">
-        <v>15354454559.06</v>
+        <v>15337935109.48</v>
       </c>
       <c r="F249" s="9">
-        <v>79637</v>
+        <v>79658</v>
       </c>
       <c r="G249" s="8">
-        <v>11714988646.46</v>
+        <v>11647110159.66</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8529,19 +8533,19 @@
         <v>500</v>
       </c>
       <c r="C250" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D250" s="7">
-        <v>0.662391</v>
+        <v>0.657759</v>
       </c>
       <c r="E250" s="8">
-        <v>8198159583.54</v>
+        <v>8189715452.41</v>
       </c>
       <c r="F250" s="9">
-        <v>75572</v>
+        <v>75620</v>
       </c>
       <c r="G250" s="8">
-        <v>5430386989.4</v>
+        <v>5386858555.04</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8552,19 +8556,19 @@
         <v>502</v>
       </c>
       <c r="C251" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D251" s="7">
-        <v>0.164369</v>
+        <v>0.164349</v>
       </c>
       <c r="E251" s="8">
-        <v>2791265752.18</v>
+        <v>2786062664.14</v>
       </c>
       <c r="F251" s="9">
-        <v>11360</v>
+        <v>11365</v>
       </c>
       <c r="G251" s="8">
-        <v>458796550.81</v>
+        <v>457887020.12</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8575,19 +8579,19 @@
         <v>504</v>
       </c>
       <c r="C252" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D252" s="7">
-        <v>0.097999</v>
+        <v>0.098122</v>
       </c>
       <c r="E252" s="8">
-        <v>4876637791.44</v>
+        <v>4887482568.3</v>
       </c>
       <c r="F252" s="9">
-        <v>69518</v>
+        <v>69544</v>
       </c>
       <c r="G252" s="8">
-        <v>477904031.26</v>
+        <v>479568730.18</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8598,19 +8602,19 @@
         <v>506</v>
       </c>
       <c r="C253" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D253" s="7">
-        <v>0.332793</v>
+        <v>0.332758</v>
       </c>
       <c r="E253" s="8">
-        <v>2181899198.3</v>
+        <v>2181818215.96</v>
       </c>
       <c r="F253" s="9">
-        <v>21123</v>
+        <v>21136</v>
       </c>
       <c r="G253" s="8">
-        <v>726120920.61</v>
+        <v>726017020.35</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8621,19 +8625,19 @@
         <v>508</v>
       </c>
       <c r="C254" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D254" s="7">
-        <v>0.143042</v>
+        <v>0.143916</v>
       </c>
       <c r="E254" s="8">
-        <v>661764865.88</v>
+        <v>660973075.58</v>
       </c>
       <c r="F254" s="9">
-        <v>2401</v>
+        <v>2407</v>
       </c>
       <c r="G254" s="8">
-        <v>94659943.74</v>
+        <v>95124660.22</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8644,19 +8648,19 @@
         <v>510</v>
       </c>
       <c r="C255" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D255" s="7">
-        <v>0.083278</v>
+        <v>0.083539</v>
       </c>
       <c r="E255" s="8">
-        <v>650589614.55</v>
+        <v>641131216.87</v>
       </c>
       <c r="F255" s="9">
-        <v>14270</v>
+        <v>14140</v>
       </c>
       <c r="G255" s="8">
-        <v>54179957.97</v>
+        <v>53559142.11</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8667,19 +8671,19 @@
         <v>512</v>
       </c>
       <c r="C256" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D256" s="7">
-        <v>0.097602</v>
+        <v>0.098073</v>
       </c>
       <c r="E256" s="8">
-        <v>4027582242.43</v>
+        <v>4030873279.11</v>
       </c>
       <c r="F256" s="9">
-        <v>78617</v>
+        <v>78629</v>
       </c>
       <c r="G256" s="8">
-        <v>393101975.84</v>
+        <v>395318424.91</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8690,19 +8694,19 @@
         <v>514</v>
       </c>
       <c r="C257" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D257" s="7">
-        <v>0.129801</v>
+        <v>0.129991</v>
       </c>
       <c r="E257" s="8">
-        <v>3764400770.55</v>
+        <v>3761829208.57</v>
       </c>
       <c r="F257" s="9">
         <v>19677</v>
       </c>
       <c r="G257" s="8">
-        <v>488624595.17</v>
+        <v>489005465.91</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -8713,19 +8717,19 @@
         <v>516</v>
       </c>
       <c r="C258" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D258" s="10">
-        <v>0.09422</v>
+        <v>46153</v>
+      </c>
+      <c r="D258" s="7">
+        <v>0.094489</v>
       </c>
       <c r="E258" s="8">
-        <v>589631385.3</v>
+        <v>599417823.2</v>
       </c>
       <c r="F258" s="9">
-        <v>10815</v>
+        <v>11748</v>
       </c>
       <c r="G258" s="8">
-        <v>55555360.74</v>
+        <v>56638233.29</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -8736,19 +8740,19 @@
         <v>518</v>
       </c>
       <c r="C259" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D259" s="7">
-        <v>0.133312</v>
+        <v>0.133683</v>
       </c>
       <c r="E259" s="8">
-        <v>4464260549.12</v>
+        <v>4480020699.45</v>
       </c>
       <c r="F259" s="9">
-        <v>18153</v>
+        <v>18104</v>
       </c>
       <c r="G259" s="8">
-        <v>595138231.39</v>
+        <v>598902143.54</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -8759,19 +8763,19 @@
         <v>520</v>
       </c>
       <c r="C260" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D260" s="7">
-        <v>0.157393</v>
+        <v>46153</v>
+      </c>
+      <c r="D260" s="11">
+        <v>0.15871</v>
       </c>
       <c r="E260" s="8">
-        <v>1215818908.34</v>
+        <v>1215208055.51</v>
       </c>
       <c r="F260" s="9">
-        <v>59016</v>
+        <v>58999</v>
       </c>
       <c r="G260" s="8">
-        <v>191361369.58</v>
+        <v>192865778.46</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -8782,19 +8786,19 @@
         <v>522</v>
       </c>
       <c r="C261" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D261" s="7">
-        <v>0.800892</v>
+        <v>0.801649</v>
       </c>
       <c r="E261" s="8">
-        <v>8876647117.28</v>
+        <v>8863461592.56</v>
       </c>
       <c r="F261" s="9">
-        <v>26149</v>
+        <v>26169</v>
       </c>
       <c r="G261" s="8">
-        <v>7109235146.2</v>
+        <v>7105387667.03</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -8805,19 +8809,19 @@
         <v>524</v>
       </c>
       <c r="C262" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D262" s="11">
-        <v>0.1048</v>
+        <v>46153</v>
+      </c>
+      <c r="D262" s="7">
+        <v>0.104993</v>
       </c>
       <c r="E262" s="8">
-        <v>13989472317.75</v>
+        <v>13978569095.02</v>
       </c>
       <c r="F262" s="9">
-        <v>128214</v>
+        <v>128187</v>
       </c>
       <c r="G262" s="8">
-        <v>1466103463.69</v>
+        <v>1467650666.7</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -8828,19 +8832,19 @@
         <v>526</v>
       </c>
       <c r="C263" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D263" s="7">
-        <v>0.013647</v>
+        <v>0.013747</v>
       </c>
       <c r="E263" s="8">
-        <v>150359245920.56</v>
+        <v>151737181347.93</v>
       </c>
       <c r="F263" s="9">
-        <v>1685</v>
+        <v>1692</v>
       </c>
       <c r="G263" s="8">
-        <v>2051976300.81</v>
+        <v>2085912104.04</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -8851,19 +8855,19 @@
         <v>528</v>
       </c>
       <c r="C264" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D264" s="7">
-        <v>0.299075</v>
+        <v>0.298444</v>
       </c>
       <c r="E264" s="8">
-        <v>5725833503.97</v>
+        <v>5720186620.95</v>
       </c>
       <c r="F264" s="9">
         <v>43927</v>
       </c>
       <c r="G264" s="8">
-        <v>1712454662.61</v>
+        <v>1707157158.56</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -8874,19 +8878,19 @@
         <v>530</v>
       </c>
       <c r="C265" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D265" s="7">
-        <v>0.421657</v>
+        <v>0.428628</v>
       </c>
       <c r="E265" s="8">
-        <v>1964952807.04</v>
+        <v>1971021557.12</v>
       </c>
       <c r="F265" s="9">
         <v>21842</v>
       </c>
       <c r="G265" s="8">
-        <v>828536190.77</v>
+        <v>844834429.98</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -8897,19 +8901,19 @@
         <v>532</v>
       </c>
       <c r="C266" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D266" s="7">
-        <v>0.132367</v>
+        <v>0.131943</v>
       </c>
       <c r="E266" s="8">
-        <v>34917886587.33</v>
+        <v>35137106859.82</v>
       </c>
       <c r="F266" s="9">
         <v>103415</v>
       </c>
       <c r="G266" s="8">
-        <v>4621984100.23</v>
+        <v>4636100711.96</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -8920,19 +8924,19 @@
         <v>534</v>
       </c>
       <c r="C267" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D267" s="7">
-        <v>0.240552</v>
+        <v>0.240269</v>
       </c>
       <c r="E267" s="8">
-        <v>2683292001.03</v>
+        <v>2681521841.82</v>
       </c>
       <c r="F267" s="9">
-        <v>24238</v>
+        <v>24232</v>
       </c>
       <c r="G267" s="8">
-        <v>645472520.21</v>
+        <v>644287681.81</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -8943,19 +8947,19 @@
         <v>536</v>
       </c>
       <c r="C268" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D268" s="7">
-        <v>0.013309</v>
+        <v>46153</v>
+      </c>
+      <c r="D268" s="11">
+        <v>0.01333</v>
       </c>
       <c r="E268" s="8">
-        <v>752708043209.82</v>
+        <v>756699301246.3</v>
       </c>
       <c r="F268" s="9">
-        <v>72800</v>
+        <v>73005</v>
       </c>
       <c r="G268" s="8">
-        <v>10018088285.8</v>
+        <v>10086524176.95</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -8966,19 +8970,19 @@
         <v>538</v>
       </c>
       <c r="C269" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D269" s="7">
-        <v>0.505532</v>
+        <v>0.505858</v>
       </c>
       <c r="E269" s="8">
-        <v>5706200639.22</v>
+        <v>5699876538.8</v>
       </c>
       <c r="F269" s="9">
-        <v>72209</v>
+        <v>72171</v>
       </c>
       <c r="G269" s="8">
-        <v>2884667236.64</v>
+        <v>2883326266.26</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -8989,19 +8993,19 @@
         <v>540</v>
       </c>
       <c r="C270" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D270" s="7">
-        <v>0.308883</v>
+        <v>0.309223</v>
       </c>
       <c r="E270" s="8">
-        <v>1835823264.16</v>
+        <v>1834431311.34</v>
       </c>
       <c r="F270" s="9">
-        <v>95650</v>
+        <v>95642</v>
       </c>
       <c r="G270" s="8">
-        <v>567054786.06</v>
+        <v>567247824.35</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9012,19 +9016,19 @@
         <v>542</v>
       </c>
       <c r="C271" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D271" s="7">
-        <v>0.801179</v>
+        <v>0.802284</v>
       </c>
       <c r="E271" s="8">
-        <v>2049041120.05</v>
+        <v>2047702841.95</v>
       </c>
       <c r="F271" s="9">
-        <v>111677</v>
+        <v>111652</v>
       </c>
       <c r="G271" s="8">
-        <v>1641649006.04</v>
+        <v>1642840166.29</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9035,19 +9039,19 @@
         <v>544</v>
       </c>
       <c r="C272" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D272" s="7">
-        <v>0.543876</v>
+        <v>0.544483</v>
       </c>
       <c r="E272" s="8">
-        <v>1500696813.68</v>
+        <v>1501218837.97</v>
       </c>
       <c r="F272" s="9">
-        <v>37688</v>
+        <v>37683</v>
       </c>
       <c r="G272" s="8">
-        <v>816192877.69</v>
+        <v>817388297.08</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9058,19 +9062,19 @@
         <v>546</v>
       </c>
       <c r="C273" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D273" s="7">
-        <v>0.288996</v>
+        <v>0.288637</v>
       </c>
       <c r="E273" s="8">
-        <v>2817974960.16</v>
+        <v>2807683361.16</v>
       </c>
       <c r="F273" s="9">
-        <v>87281</v>
+        <v>87272</v>
       </c>
       <c r="G273" s="8">
-        <v>814382845.12</v>
+        <v>810400299.42</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9081,19 +9085,19 @@
         <v>548</v>
       </c>
       <c r="C274" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D274" s="7">
-        <v>2.515001</v>
+        <v>2.525722</v>
       </c>
       <c r="E274" s="8">
-        <v>1902386641.65</v>
+        <v>1903356598.72</v>
       </c>
       <c r="F274" s="9">
-        <v>57622</v>
+        <v>57600</v>
       </c>
       <c r="G274" s="8">
-        <v>4784503843.87</v>
+        <v>4807348994.61</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9104,19 +9108,19 @@
         <v>550</v>
       </c>
       <c r="C275" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D275" s="7">
-        <v>0.928328</v>
+        <v>0.931161</v>
       </c>
       <c r="E275" s="8">
-        <v>769536421.93</v>
+        <v>769069883.1</v>
       </c>
       <c r="F275" s="9">
-        <v>83357</v>
+        <v>83340</v>
       </c>
       <c r="G275" s="8">
-        <v>714381850.33</v>
+        <v>716128154.5</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9127,19 +9131,19 @@
         <v>552</v>
       </c>
       <c r="C276" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D276" s="7">
-        <v>0.377386</v>
+        <v>0.378339</v>
       </c>
       <c r="E276" s="8">
-        <v>8959377539.07</v>
+        <v>8947398914.01</v>
       </c>
       <c r="F276" s="9">
-        <v>100005</v>
+        <v>99985</v>
       </c>
       <c r="G276" s="8">
-        <v>3381142189.12</v>
+        <v>3385146382.39</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9150,19 +9154,19 @@
         <v>554</v>
       </c>
       <c r="C277" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D277" s="7">
-        <v>0.112983</v>
+        <v>0.113056</v>
       </c>
       <c r="E277" s="8">
-        <v>54649465891.48</v>
+        <v>54591218221.24</v>
       </c>
       <c r="F277" s="9">
-        <v>198364</v>
+        <v>198246</v>
       </c>
       <c r="G277" s="8">
-        <v>6174450120.04</v>
+        <v>6171873604.95</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9173,19 +9177,19 @@
         <v>556</v>
       </c>
       <c r="C278" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D278" s="7">
-        <v>0.116659</v>
+        <v>0.117724</v>
       </c>
       <c r="E278" s="8">
-        <v>83371892852.64</v>
+        <v>83294825793.91</v>
       </c>
       <c r="F278" s="9">
-        <v>1083493</v>
+        <v>1083105</v>
       </c>
       <c r="G278" s="8">
-        <v>9726121939.9</v>
+        <v>9805823303.3</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9196,19 +9200,19 @@
         <v>558</v>
       </c>
       <c r="C279" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D279" s="7">
-        <v>0.143836</v>
+        <v>0.144571</v>
       </c>
       <c r="E279" s="8">
-        <v>33239330201.9</v>
+        <v>33340760007.68</v>
       </c>
       <c r="F279" s="9">
-        <v>328722</v>
+        <v>329406</v>
       </c>
       <c r="G279" s="8">
-        <v>4781011573.44</v>
+        <v>4820107751.83</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9219,19 +9223,19 @@
         <v>560</v>
       </c>
       <c r="C280" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D280" s="7">
-        <v>0.173095</v>
+        <v>0.174214</v>
       </c>
       <c r="E280" s="8">
-        <v>3156789684.08</v>
+        <v>3152244170.83</v>
       </c>
       <c r="F280" s="9">
-        <v>27449</v>
+        <v>27447</v>
       </c>
       <c r="G280" s="8">
-        <v>546424546.04</v>
+        <v>549166460.66</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -9242,19 +9246,19 @@
         <v>562</v>
       </c>
       <c r="C281" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D281" s="7">
-        <v>0.751072</v>
+        <v>0.746531</v>
       </c>
       <c r="E281" s="8">
-        <v>44398728100.71</v>
+        <v>44321488778.56</v>
       </c>
       <c r="F281" s="9">
-        <v>675058</v>
+        <v>674401</v>
       </c>
       <c r="G281" s="8">
-        <v>33346663640.26</v>
+        <v>33087368688.21</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -9265,19 +9269,19 @@
         <v>564</v>
       </c>
       <c r="C282" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D282" s="7">
-        <v>0.267799</v>
+        <v>0.269487</v>
       </c>
       <c r="E282" s="8">
-        <v>8731033485.38</v>
+        <v>8723565966.61</v>
       </c>
       <c r="F282" s="9">
-        <v>108631</v>
+        <v>108643</v>
       </c>
       <c r="G282" s="8">
-        <v>2338161616.58</v>
+        <v>2350887328.39</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -9288,19 +9292,19 @@
         <v>566</v>
       </c>
       <c r="C283" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D283" s="7">
-        <v>0.564307</v>
+        <v>0.569786</v>
       </c>
       <c r="E283" s="8">
-        <v>11770048692.95</v>
+        <v>11861166043.09</v>
       </c>
       <c r="F283" s="9">
-        <v>139303</v>
+        <v>140316</v>
       </c>
       <c r="G283" s="8">
-        <v>6641921623.27</v>
+        <v>6758321362.89</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -9311,19 +9315,19 @@
         <v>568</v>
       </c>
       <c r="C284" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D284" s="7">
-        <v>0.312961</v>
+        <v>0.314397</v>
       </c>
       <c r="E284" s="8">
-        <v>2297430005.36</v>
+        <v>2296599113.29</v>
       </c>
       <c r="F284" s="9">
-        <v>37459</v>
+        <v>37452</v>
       </c>
       <c r="G284" s="8">
-        <v>719006522.78</v>
+        <v>722044569.88</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -9334,19 +9338,19 @@
         <v>570</v>
       </c>
       <c r="C285" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D285" s="10">
-        <v>0.19808</v>
+        <v>46153</v>
+      </c>
+      <c r="D285" s="7">
+        <v>0.198321</v>
       </c>
       <c r="E285" s="8">
-        <v>9536592454.73</v>
+        <v>9440252514.39</v>
       </c>
       <c r="F285" s="9">
-        <v>108053</v>
+        <v>108145</v>
       </c>
       <c r="G285" s="8">
-        <v>1889006860.09</v>
+        <v>1872202596.39</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -9357,19 +9361,19 @@
         <v>572</v>
       </c>
       <c r="C286" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D286" s="7">
-        <v>0.282472</v>
+        <v>0.283714</v>
       </c>
       <c r="E286" s="8">
-        <v>801882033.34</v>
+        <v>802253303.38</v>
       </c>
       <c r="F286" s="9">
-        <v>2814</v>
+        <v>2818</v>
       </c>
       <c r="G286" s="8">
-        <v>226508834.1</v>
+        <v>227610431.63</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -9380,19 +9384,19 @@
         <v>574</v>
       </c>
       <c r="C287" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D287" s="10">
-        <v>0.08817</v>
+        <v>46153</v>
+      </c>
+      <c r="D287" s="7">
+        <v>0.088446</v>
       </c>
       <c r="E287" s="8">
-        <v>4347945992.66</v>
+        <v>4351188691.04</v>
       </c>
       <c r="F287" s="9">
-        <v>147646</v>
+        <v>147707</v>
       </c>
       <c r="G287" s="8">
-        <v>383358210.44</v>
+        <v>384847282.22</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -9403,19 +9407,19 @@
         <v>576</v>
       </c>
       <c r="C288" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D288" s="7">
-        <v>0.499009</v>
+        <v>0.503717</v>
       </c>
       <c r="E288" s="8">
-        <v>1585961911.66</v>
+        <v>1589274848.17</v>
       </c>
       <c r="F288" s="9">
-        <v>4266</v>
+        <v>4269</v>
       </c>
       <c r="G288" s="8">
-        <v>791409561.52</v>
+        <v>800544260.84</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -9426,19 +9430,19 @@
         <v>578</v>
       </c>
       <c r="C289" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D289" s="7">
-        <v>0.015978</v>
+        <v>0.016062</v>
       </c>
       <c r="E289" s="8">
-        <v>6183194094.94</v>
+        <v>6513588682.27</v>
       </c>
       <c r="F289" s="9">
-        <v>3681</v>
+        <v>3810</v>
       </c>
       <c r="G289" s="8">
-        <v>98794624.47</v>
+        <v>104623470.46</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -9449,19 +9453,19 @@
         <v>580</v>
       </c>
       <c r="C290" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D290" s="7">
-        <v>0.018688</v>
+        <v>0.018722</v>
       </c>
       <c r="E290" s="8">
-        <v>151598357804.63</v>
+        <v>151214386396.89</v>
       </c>
       <c r="F290" s="9">
-        <v>31515</v>
+        <v>31315</v>
       </c>
       <c r="G290" s="8">
-        <v>2833029065.29</v>
+        <v>2831068451.4</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -9472,19 +9476,19 @@
         <v>582</v>
       </c>
       <c r="C291" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D291" s="7">
-        <v>0.011223</v>
+        <v>46153</v>
+      </c>
+      <c r="D291" s="11">
+        <v>0.01136</v>
       </c>
       <c r="E291" s="8">
-        <v>10632093316.26</v>
+        <v>11383822759.55</v>
       </c>
       <c r="F291" s="9">
-        <v>1816</v>
+        <v>1908</v>
       </c>
       <c r="G291" s="8">
-        <v>119325505.01</v>
+        <v>129318511.06</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -9495,19 +9499,19 @@
         <v>584</v>
       </c>
       <c r="C292" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D292" s="10">
-        <v>0.13993</v>
+        <v>46153</v>
+      </c>
+      <c r="D292" s="7">
+        <v>0.139605</v>
       </c>
       <c r="E292" s="8">
-        <v>52354456901.23</v>
+        <v>52284874501.31</v>
       </c>
       <c r="F292" s="9">
-        <v>107796</v>
+        <v>107678</v>
       </c>
       <c r="G292" s="8">
-        <v>7325956243.4</v>
+        <v>7299205386.32</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -9518,19 +9522,19 @@
         <v>586</v>
       </c>
       <c r="C293" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D293" s="7">
-        <v>0.051418</v>
+        <v>0.051572</v>
       </c>
       <c r="E293" s="8">
-        <v>12974788106.83</v>
+        <v>12862722037.37</v>
       </c>
       <c r="F293" s="9">
-        <v>28966</v>
+        <v>28596</v>
       </c>
       <c r="G293" s="8">
-        <v>667132867.14</v>
+        <v>663353748.15</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -9541,19 +9545,19 @@
         <v>588</v>
       </c>
       <c r="C294" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D294" s="7">
-        <v>0.022088</v>
+        <v>0.022151</v>
       </c>
       <c r="E294" s="8">
-        <v>58176240138.5</v>
+        <v>57900785896.12</v>
       </c>
       <c r="F294" s="9">
-        <v>10682</v>
+        <v>10644</v>
       </c>
       <c r="G294" s="8">
-        <v>1284993085.09</v>
+        <v>1282548638.57</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -9564,19 +9568,19 @@
         <v>590</v>
       </c>
       <c r="C295" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D295" s="7">
-        <v>0.032892</v>
+        <v>46153</v>
+      </c>
+      <c r="D295" s="11">
+        <v>0.03308</v>
       </c>
       <c r="E295" s="8">
-        <v>53687414511.97</v>
+        <v>52647607773.02</v>
       </c>
       <c r="F295" s="9">
-        <v>33073</v>
+        <v>32953</v>
       </c>
       <c r="G295" s="8">
-        <v>1765873877.54</v>
+        <v>1741571398.11</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -9587,19 +9591,19 @@
         <v>592</v>
       </c>
       <c r="C296" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D296" s="7">
-        <v>0.020383</v>
+        <v>0.020476</v>
       </c>
       <c r="E296" s="8">
-        <v>954664215717.11</v>
+        <v>953325954475.15</v>
       </c>
       <c r="F296" s="9">
-        <v>178741</v>
+        <v>178651</v>
       </c>
       <c r="G296" s="8">
-        <v>19459290155.8</v>
+        <v>19520500536.39</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -9610,19 +9614,19 @@
         <v>594</v>
       </c>
       <c r="C297" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D297" s="7">
-        <v>0.103183</v>
+        <v>46153</v>
+      </c>
+      <c r="D297" s="11">
+        <v>0.10334</v>
       </c>
       <c r="E297" s="8">
-        <v>37288051667.53</v>
+        <v>37349716817.15</v>
       </c>
       <c r="F297" s="9">
-        <v>383069</v>
+        <v>383288</v>
       </c>
       <c r="G297" s="8">
-        <v>3847479885.72</v>
+        <v>3859716821.2</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -9633,19 +9637,19 @@
         <v>596</v>
       </c>
       <c r="C298" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D298" s="10">
-        <v>0.08759</v>
+        <v>46153</v>
+      </c>
+      <c r="D298" s="11">
+        <v>0.08769</v>
       </c>
       <c r="E298" s="8">
-        <v>38330242211.87</v>
+        <v>38322919198.48</v>
       </c>
       <c r="F298" s="9">
-        <v>48115</v>
+        <v>48104</v>
       </c>
       <c r="G298" s="8">
-        <v>3357348642.4</v>
+        <v>3360539087.46</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -9656,19 +9660,19 @@
         <v>598</v>
       </c>
       <c r="C299" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D299" s="7">
-        <v>0.095776</v>
+        <v>0.096226</v>
       </c>
       <c r="E299" s="8">
-        <v>39055012658.65</v>
+        <v>39185160197.61</v>
       </c>
       <c r="F299" s="9">
-        <v>527012</v>
+        <v>527381</v>
       </c>
       <c r="G299" s="8">
-        <v>3740519268.57</v>
+        <v>3770630147.18</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -9679,19 +9683,19 @@
         <v>600</v>
       </c>
       <c r="C300" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D300" s="7">
-        <v>0.020792</v>
+        <v>0.020957</v>
       </c>
       <c r="E300" s="8">
-        <v>36609353657.52</v>
+        <v>36985422472.22</v>
       </c>
       <c r="F300" s="9">
         <v>25048</v>
       </c>
       <c r="G300" s="8">
-        <v>761197893.88</v>
+        <v>775103285.11</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -9702,19 +9706,19 @@
         <v>602</v>
       </c>
       <c r="C301" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D301" s="7">
-        <v>0.010372</v>
+        <v>0.010406</v>
       </c>
       <c r="E301" s="8">
-        <v>4938072936.55</v>
+        <v>5063102767.6</v>
       </c>
       <c r="F301" s="9">
-        <v>1030</v>
+        <v>1058</v>
       </c>
       <c r="G301" s="8">
-        <v>51219380.7</v>
+        <v>52685866.72</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -9725,19 +9729,19 @@
         <v>604</v>
       </c>
       <c r="C302" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D302" s="7">
-        <v>0.016464</v>
+        <v>0.016621</v>
       </c>
       <c r="E302" s="8">
-        <v>24094439795.59</v>
+        <v>24738194540.39</v>
       </c>
       <c r="F302" s="9">
-        <v>11235</v>
+        <v>12116</v>
       </c>
       <c r="G302" s="8">
-        <v>396694908.27</v>
+        <v>411176309.47</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -9748,19 +9752,19 @@
         <v>606</v>
       </c>
       <c r="C303" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D303" s="10">
-        <v>0.01876</v>
+        <v>46153</v>
+      </c>
+      <c r="D303" s="7">
+        <v>0.018819</v>
       </c>
       <c r="E303" s="8">
-        <v>12432023158.03</v>
+        <v>13979373824.37</v>
       </c>
       <c r="F303" s="9">
-        <v>6725</v>
+        <v>7670</v>
       </c>
       <c r="G303" s="8">
-        <v>233227189.85</v>
+        <v>263081347.35</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -9771,19 +9775,19 @@
         <v>608</v>
       </c>
       <c r="C304" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D304" s="7">
-        <v>0.095713</v>
+        <v>0.096132</v>
       </c>
       <c r="E304" s="8">
-        <v>21528902767.51</v>
+        <v>21542694023.53</v>
       </c>
       <c r="F304" s="9">
-        <v>348885</v>
+        <v>349094</v>
       </c>
       <c r="G304" s="8">
-        <v>2060588604.66</v>
+        <v>2070948844.36</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -9794,19 +9798,19 @@
         <v>610</v>
       </c>
       <c r="C305" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D305" s="7">
-        <v>0.019417</v>
+        <v>0.019451</v>
       </c>
       <c r="E305" s="8">
-        <v>10302793606.55</v>
+        <v>10302502963.26</v>
       </c>
       <c r="F305" s="9">
         <v>509</v>
       </c>
       <c r="G305" s="8">
-        <v>200051760</v>
+        <v>200391982.89</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -9817,19 +9821,19 @@
         <v>612</v>
       </c>
       <c r="C306" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D306" s="7">
-        <v>0.015887</v>
+        <v>0.015952</v>
       </c>
       <c r="E306" s="8">
-        <v>9038805114.12</v>
+        <v>9073872762.2</v>
       </c>
       <c r="F306" s="9">
         <v>399</v>
       </c>
       <c r="G306" s="8">
-        <v>143603027.19</v>
+        <v>144750261.49</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -9840,19 +9844,19 @@
         <v>614</v>
       </c>
       <c r="C307" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D307" s="10">
-        <v>0.01596</v>
+        <v>46153</v>
+      </c>
+      <c r="D307" s="7">
+        <v>0.016006</v>
       </c>
       <c r="E307" s="8">
-        <v>1264833815.1</v>
+        <v>1262449813.5</v>
       </c>
       <c r="F307" s="9">
         <v>24</v>
       </c>
       <c r="G307" s="8">
-        <v>20187355.12</v>
+        <v>20207378.18</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -9863,19 +9867,19 @@
         <v>616</v>
       </c>
       <c r="C308" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D308" s="7">
-        <v>0.235865</v>
+        <v>0.235081</v>
       </c>
       <c r="E308" s="8">
-        <v>48732775809.05</v>
+        <v>48736889625.3</v>
       </c>
       <c r="F308" s="9">
-        <v>175274</v>
+        <v>175279</v>
       </c>
       <c r="G308" s="8">
-        <v>11494345053.44</v>
+        <v>11457131809.78</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -9886,19 +9890,19 @@
         <v>618</v>
       </c>
       <c r="C309" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D309" s="7">
-        <v>0.011315</v>
+        <v>0.011306</v>
       </c>
       <c r="E309" s="8">
-        <v>2699866748.43</v>
+        <v>2723839081.97</v>
       </c>
       <c r="F309" s="9">
-        <v>2076</v>
+        <v>2093</v>
       </c>
       <c r="G309" s="8">
-        <v>30548175.05</v>
+        <v>30795368.3</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -9909,19 +9913,19 @@
         <v>620</v>
       </c>
       <c r="C310" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D310" s="7">
-        <v>0.031222</v>
+        <v>46153</v>
+      </c>
+      <c r="D310" s="11">
+        <v>0.03157</v>
       </c>
       <c r="E310" s="8">
-        <v>13066672630.91</v>
+        <v>13289821442.09</v>
       </c>
       <c r="F310" s="9">
-        <v>17679</v>
+        <v>17740</v>
       </c>
       <c r="G310" s="8">
-        <v>407962502.77</v>
+        <v>419558730</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -9932,19 +9936,19 @@
         <v>622</v>
       </c>
       <c r="C311" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D311" s="7">
-        <v>0.025622</v>
+        <v>46153</v>
+      </c>
+      <c r="D311" s="10">
+        <v>0.0257</v>
       </c>
       <c r="E311" s="8">
-        <v>3003362449.06</v>
+        <v>3145090569.6</v>
       </c>
       <c r="F311" s="9">
-        <v>10303</v>
+        <v>10319</v>
       </c>
       <c r="G311" s="8">
-        <v>76953603.42</v>
+        <v>80827680.38</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -9955,19 +9959,19 @@
         <v>624</v>
       </c>
       <c r="C312" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D312" s="7">
-        <v>0.125869</v>
+        <v>0.126921</v>
       </c>
       <c r="E312" s="8">
-        <v>618106888.43</v>
+        <v>617266247.78</v>
       </c>
       <c r="F312" s="9">
-        <v>94177</v>
+        <v>94159</v>
       </c>
       <c r="G312" s="8">
-        <v>77800237.9</v>
+        <v>78344199.67</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -9978,19 +9982,19 @@
         <v>626</v>
       </c>
       <c r="C313" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D313" s="7">
-        <v>0.091398</v>
+        <v>0.091651</v>
       </c>
       <c r="E313" s="8">
-        <v>1411513712.81</v>
+        <v>1381672010.24</v>
       </c>
       <c r="F313" s="9">
-        <v>26953</v>
+        <v>25726</v>
       </c>
       <c r="G313" s="8">
-        <v>129009734.35</v>
+        <v>126632206.3</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -10001,19 +10005,19 @@
         <v>628</v>
       </c>
       <c r="C314" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D314" s="7">
-        <v>0.080786</v>
+        <v>0.081039</v>
       </c>
       <c r="E314" s="8">
-        <v>2459962978.45</v>
+        <v>2459776511.09</v>
       </c>
       <c r="F314" s="9">
-        <v>78033</v>
+        <v>78041</v>
       </c>
       <c r="G314" s="8">
-        <v>198730796.8</v>
+        <v>199337699.87</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -10024,19 +10028,19 @@
         <v>630</v>
       </c>
       <c r="C315" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D315" s="7">
-        <v>0.390531</v>
+        <v>0.390537</v>
       </c>
       <c r="E315" s="8">
-        <v>5194165316.38</v>
+        <v>5197521918.86</v>
       </c>
       <c r="F315" s="9">
-        <v>71817</v>
+        <v>71806</v>
       </c>
       <c r="G315" s="8">
-        <v>2028485018.16</v>
+        <v>2029826441.17</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -10047,19 +10051,19 @@
         <v>632</v>
       </c>
       <c r="C316" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D316" s="7">
-        <v>0.207472</v>
+        <v>0.208027</v>
       </c>
       <c r="E316" s="8">
-        <v>5787217201.57</v>
+        <v>5788861809.59</v>
       </c>
       <c r="F316" s="9">
-        <v>56497</v>
+        <v>56470</v>
       </c>
       <c r="G316" s="8">
-        <v>1200684795.6</v>
+        <v>1204239504.87</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -10070,19 +10074,19 @@
         <v>634</v>
       </c>
       <c r="C317" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D317" s="7">
-        <v>0.113932</v>
+        <v>0.113831</v>
       </c>
       <c r="E317" s="8">
-        <v>2332890953.59</v>
+        <v>2322840870.2</v>
       </c>
       <c r="F317" s="9">
-        <v>8460</v>
+        <v>8443</v>
       </c>
       <c r="G317" s="8">
-        <v>265790430.95</v>
+        <v>264412372.63</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -10093,19 +10097,19 @@
         <v>636</v>
       </c>
       <c r="C318" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D318" s="7">
-        <v>0.574608</v>
+        <v>0.576656</v>
       </c>
       <c r="E318" s="8">
-        <v>4003004021.86</v>
+        <v>4009981505.43</v>
       </c>
       <c r="F318" s="9">
-        <v>50515</v>
+        <v>50512</v>
       </c>
       <c r="G318" s="8">
-        <v>2300159077.13</v>
+        <v>2312381465.68</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -10116,19 +10120,19 @@
         <v>638</v>
       </c>
       <c r="C319" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D319" s="10">
-        <v>0.08614</v>
+        <v>46153</v>
+      </c>
+      <c r="D319" s="7">
+        <v>0.086587</v>
       </c>
       <c r="E319" s="8">
-        <v>9010311561.8</v>
+        <v>8990531098</v>
       </c>
       <c r="F319" s="9">
-        <v>190227</v>
+        <v>190072</v>
       </c>
       <c r="G319" s="8">
-        <v>776151601.54</v>
+        <v>778467066.75</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -10139,19 +10143,19 @@
         <v>640</v>
       </c>
       <c r="C320" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D320" s="7">
-        <v>0.111089</v>
+        <v>0.111096</v>
       </c>
       <c r="E320" s="8">
-        <v>23102295702.84</v>
+        <v>23074085169.6</v>
       </c>
       <c r="F320" s="9">
-        <v>138080</v>
+        <v>137984</v>
       </c>
       <c r="G320" s="8">
-        <v>2566417125.07</v>
+        <v>2563429402.34</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -10162,19 +10166,19 @@
         <v>642</v>
       </c>
       <c r="C321" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D321" s="7">
-        <v>0.152746</v>
+        <v>0.153174</v>
       </c>
       <c r="E321" s="8">
-        <v>13231115212.93</v>
+        <v>13142524977.06</v>
       </c>
       <c r="F321" s="9">
-        <v>41529</v>
+        <v>34150</v>
       </c>
       <c r="G321" s="8">
-        <v>2020994447.26</v>
+        <v>2013098342.78</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -10185,19 +10189,19 @@
         <v>644</v>
       </c>
       <c r="C322" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D322" s="7">
-        <v>0.134167</v>
+        <v>46153</v>
+      </c>
+      <c r="D322" s="11">
+        <v>0.13461</v>
       </c>
       <c r="E322" s="8">
-        <v>530802437.34</v>
+        <v>531747366.53</v>
       </c>
       <c r="F322" s="9">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G322" s="8">
-        <v>71215935.49</v>
+        <v>71578581.59</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -10208,19 +10212,19 @@
         <v>646</v>
       </c>
       <c r="C323" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D323" s="7">
-        <v>0.140553</v>
+        <v>0.140862</v>
       </c>
       <c r="E323" s="8">
-        <v>228120666.71</v>
+        <v>228716606.49</v>
       </c>
       <c r="F323" s="9">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G323" s="8">
-        <v>32063030.64</v>
+        <v>32217502.2</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -10231,19 +10235,19 @@
         <v>648</v>
       </c>
       <c r="C324" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D324" s="7">
-        <v>0.172579</v>
+        <v>0.172996</v>
       </c>
       <c r="E324" s="8">
-        <v>302165794.22</v>
+        <v>302845930.44</v>
       </c>
       <c r="F324" s="9">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G324" s="8">
-        <v>52147486.4</v>
+        <v>52391177.12</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -10254,19 +10258,19 @@
         <v>650</v>
       </c>
       <c r="C325" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D325" s="7">
-        <v>0.206111</v>
+        <v>0.206657</v>
       </c>
       <c r="E325" s="8">
-        <v>361784090.04</v>
+        <v>361862287.5</v>
       </c>
       <c r="F325" s="9">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G325" s="8">
-        <v>74567512.01</v>
+        <v>74781459.47</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -10277,19 +10281,19 @@
         <v>652</v>
       </c>
       <c r="C326" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D326" s="7">
-        <v>0.144299</v>
+        <v>0.145077</v>
       </c>
       <c r="E326" s="8">
-        <v>424484209.57</v>
+        <v>424391704.74</v>
       </c>
       <c r="F326" s="9">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="G326" s="8">
-        <v>61252749.34</v>
+        <v>61569557.52</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -10300,19 +10304,19 @@
         <v>654</v>
       </c>
       <c r="C327" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D327" s="7">
-        <v>0.100652</v>
+        <v>0.100771</v>
       </c>
       <c r="E327" s="8">
-        <v>40624638536</v>
+        <v>40571298845.96</v>
       </c>
       <c r="F327" s="9">
-        <v>374107</v>
+        <v>373748</v>
       </c>
       <c r="G327" s="8">
-        <v>4088967929.61</v>
+        <v>4088420730.76</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -10323,19 +10327,19 @@
         <v>656</v>
       </c>
       <c r="C328" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D328" s="7">
-        <v>0.178983</v>
+        <v>0.180567</v>
       </c>
       <c r="E328" s="8">
-        <v>193823734.55</v>
+        <v>194012428.92</v>
       </c>
       <c r="F328" s="9">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G328" s="8">
-        <v>34691138.76</v>
+        <v>35032261.91</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -10346,19 +10350,19 @@
         <v>658</v>
       </c>
       <c r="C329" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D329" s="7">
-        <v>0.210898</v>
+        <v>0.212967</v>
       </c>
       <c r="E329" s="8">
-        <v>241246817.35</v>
+        <v>242288752.83</v>
       </c>
       <c r="F329" s="9">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="G329" s="8">
-        <v>50878470.66</v>
+        <v>51599500.64</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -10369,19 +10373,19 @@
         <v>660</v>
       </c>
       <c r="C330" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D330" s="7">
-        <v>0.298772</v>
+        <v>46153</v>
+      </c>
+      <c r="D330" s="11">
+        <v>0.29937</v>
       </c>
       <c r="E330" s="8">
-        <v>1267326041.09</v>
+        <v>1266777877.16</v>
       </c>
       <c r="F330" s="9">
-        <v>8876</v>
+        <v>8864</v>
       </c>
       <c r="G330" s="8">
-        <v>378641870.68</v>
+        <v>379235275.13</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
@@ -10392,19 +10396,19 @@
         <v>662</v>
       </c>
       <c r="C331" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D331" s="7">
-        <v>0.093722</v>
+        <v>0.093734</v>
       </c>
       <c r="E331" s="8">
-        <v>6888183797.74</v>
+        <v>6902171578.73</v>
       </c>
       <c r="F331" s="9">
-        <v>123468</v>
+        <v>123535</v>
       </c>
       <c r="G331" s="8">
-        <v>645571855.51</v>
+        <v>646967238.84</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
@@ -10415,19 +10419,19 @@
         <v>664</v>
       </c>
       <c r="C332" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D332" s="7">
-        <v>0.075608</v>
+        <v>0.075856</v>
       </c>
       <c r="E332" s="8">
-        <v>103795837403.35</v>
+        <v>103686055884.93</v>
       </c>
       <c r="F332" s="9">
-        <v>148847</v>
+        <v>148892</v>
       </c>
       <c r="G332" s="8">
-        <v>7847846535.55</v>
+        <v>7865172185.6</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
@@ -10438,19 +10442,19 @@
         <v>666</v>
       </c>
       <c r="C333" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D333" s="7">
-        <v>0.066773</v>
+        <v>0.066917</v>
       </c>
       <c r="E333" s="8">
-        <v>112013718303.9</v>
+        <v>111719980606.08</v>
       </c>
       <c r="F333" s="9">
-        <v>100136</v>
+        <v>100140</v>
       </c>
       <c r="G333" s="8">
-        <v>7479463210.12</v>
+        <v>7475939538.09</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
@@ -10461,19 +10465,19 @@
         <v>668</v>
       </c>
       <c r="C334" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D334" s="7">
-        <v>0.088474</v>
+        <v>0.088833</v>
       </c>
       <c r="E334" s="8">
-        <v>65131970566.91</v>
+        <v>65111996820.04</v>
       </c>
       <c r="F334" s="9">
-        <v>123551</v>
+        <v>123624</v>
       </c>
       <c r="G334" s="8">
-        <v>5762511728.79</v>
+        <v>5784099261.46</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
@@ -10484,19 +10488,19 @@
         <v>670</v>
       </c>
       <c r="C335" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D335" s="7">
-        <v>0.464951</v>
+        <v>0.462749</v>
       </c>
       <c r="E335" s="8">
-        <v>52352584505.58</v>
+        <v>52328080272.81</v>
       </c>
       <c r="F335" s="9">
-        <v>126613</v>
+        <v>126533</v>
       </c>
       <c r="G335" s="8">
-        <v>24341408192.86</v>
+        <v>24214763828.46</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
@@ -10507,19 +10511,19 @@
         <v>672</v>
       </c>
       <c r="C336" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D336" s="7">
-        <v>0.100626</v>
+        <v>0.101348</v>
       </c>
       <c r="E336" s="8">
-        <v>5338275889.37</v>
+        <v>5339959498.15</v>
       </c>
       <c r="F336" s="9">
-        <v>8789</v>
+        <v>8776</v>
       </c>
       <c r="G336" s="8">
-        <v>537169180.94</v>
+        <v>541195339.7</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
@@ -10530,19 +10534,19 @@
         <v>674</v>
       </c>
       <c r="C337" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D337" s="7">
-        <v>0.370648</v>
+        <v>0.372248</v>
       </c>
       <c r="E337" s="8">
-        <v>15793380901.92</v>
+        <v>15777107358.17</v>
       </c>
       <c r="F337" s="9">
-        <v>28578</v>
+        <v>28552</v>
       </c>
       <c r="G337" s="8">
-        <v>5853784413.38</v>
+        <v>5872999183.48</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
@@ -10553,19 +10557,19 @@
         <v>676</v>
       </c>
       <c r="C338" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D338" s="7">
-        <v>0.010472</v>
+        <v>0.010434</v>
       </c>
       <c r="E338" s="8">
-        <v>80528920546.69</v>
+        <v>81285339575.99</v>
       </c>
       <c r="F338" s="9">
-        <v>4448</v>
+        <v>4472</v>
       </c>
       <c r="G338" s="8">
-        <v>843258631.52</v>
+        <v>848138426.29</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
@@ -10576,19 +10580,19 @@
         <v>678</v>
       </c>
       <c r="C339" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D339" s="7">
-        <v>0.082336</v>
+        <v>0.082591</v>
       </c>
       <c r="E339" s="8">
-        <v>3717486733.9</v>
+        <v>3717362589.84</v>
       </c>
       <c r="F339" s="9">
-        <v>78511</v>
+        <v>78566</v>
       </c>
       <c r="G339" s="8">
-        <v>306081131.74</v>
+        <v>307020106.03</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
@@ -10599,19 +10603,19 @@
         <v>680</v>
       </c>
       <c r="C340" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D340" s="7">
-        <v>0.092148</v>
+        <v>0.092393</v>
       </c>
       <c r="E340" s="8">
-        <v>626464524.99</v>
+        <v>627829831.58</v>
       </c>
       <c r="F340" s="9">
-        <v>12912</v>
+        <v>12928</v>
       </c>
       <c r="G340" s="8">
-        <v>57727689.19</v>
+        <v>58007367.96</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -10622,19 +10626,19 @@
         <v>682</v>
       </c>
       <c r="C341" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D341" s="7">
-        <v>0.043877</v>
+        <v>0.044101</v>
       </c>
       <c r="E341" s="8">
-        <v>1066499971.45</v>
+        <v>1092492389.08</v>
       </c>
       <c r="F341" s="9">
-        <v>2229</v>
+        <v>2238</v>
       </c>
       <c r="G341" s="8">
-        <v>46794447.78</v>
+        <v>48179843.44</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
@@ -10645,19 +10649,19 @@
         <v>684</v>
       </c>
       <c r="C342" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D342" s="7">
-        <v>0.049753</v>
+        <v>0.049775</v>
       </c>
       <c r="E342" s="8">
-        <v>3940629035.35</v>
+        <v>3944390688.54</v>
       </c>
       <c r="F342" s="9">
-        <v>4349</v>
+        <v>4347</v>
       </c>
       <c r="G342" s="8">
-        <v>196059730.17</v>
+        <v>196332345.51</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
@@ -10668,19 +10672,19 @@
         <v>686</v>
       </c>
       <c r="C343" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D343" s="7">
-        <v>0.014159</v>
+        <v>0.014135</v>
       </c>
       <c r="E343" s="8">
-        <v>34410872957.08</v>
+        <v>34578807866.75</v>
       </c>
       <c r="F343" s="9">
-        <v>28230</v>
+        <v>28441</v>
       </c>
       <c r="G343" s="8">
-        <v>487207033.23</v>
+        <v>488771625.49</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
@@ -10691,19 +10695,19 @@
         <v>688</v>
       </c>
       <c r="C344" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D344" s="7">
-        <v>0.076413</v>
+        <v>0.076994</v>
       </c>
       <c r="E344" s="8">
-        <v>51157062971.81</v>
+        <v>51789022863.99</v>
       </c>
       <c r="F344" s="9">
         <v>123358</v>
       </c>
       <c r="G344" s="8">
-        <v>3909071249.26</v>
+        <v>3987424852.38</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
@@ -10714,19 +10718,19 @@
         <v>690</v>
       </c>
       <c r="C345" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D345" s="7">
-        <v>0.012933</v>
+        <v>0.012956</v>
       </c>
       <c r="E345" s="8">
-        <v>16197289473.01</v>
+        <v>16273523601.36</v>
       </c>
       <c r="F345" s="9">
         <v>5998</v>
       </c>
       <c r="G345" s="8">
-        <v>209475188.55</v>
+        <v>210832638.25</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
@@ -10737,19 +10741,19 @@
         <v>692</v>
       </c>
       <c r="C346" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D346" s="7">
-        <v>0.014913</v>
+        <v>46153</v>
+      </c>
+      <c r="D346" s="11">
+        <v>0.01496</v>
       </c>
       <c r="E346" s="8">
-        <v>71077348206.53</v>
+        <v>69584231561.38</v>
       </c>
       <c r="F346" s="9">
         <v>19246</v>
       </c>
       <c r="G346" s="8">
-        <v>1059945584.23</v>
+        <v>1040983757.56</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
@@ -10760,19 +10764,19 @@
         <v>694</v>
       </c>
       <c r="C347" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D347" s="7">
-        <v>0.049905</v>
+        <v>0.049919</v>
       </c>
       <c r="E347" s="8">
-        <v>7308095231.07</v>
+        <v>7255617530.21</v>
       </c>
       <c r="F347" s="9">
         <v>9448</v>
       </c>
       <c r="G347" s="8">
-        <v>364709559.74</v>
+        <v>362195219.86</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
@@ -10783,19 +10787,19 @@
         <v>696</v>
       </c>
       <c r="C348" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D348" s="7">
-        <v>0.087456</v>
+        <v>0.087748</v>
       </c>
       <c r="E348" s="8">
-        <v>592218651.66</v>
+        <v>592157130.66</v>
       </c>
       <c r="F348" s="9">
-        <v>7018</v>
+        <v>7055</v>
       </c>
       <c r="G348" s="8">
-        <v>51793046.12</v>
+        <v>51960705.46</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
@@ -10806,19 +10810,19 @@
         <v>698</v>
       </c>
       <c r="C349" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D349" s="7">
-        <v>0.049093</v>
+        <v>0.049128</v>
       </c>
       <c r="E349" s="8">
-        <v>3815294242.96</v>
+        <v>3811872938</v>
       </c>
       <c r="F349" s="9">
         <v>5877</v>
       </c>
       <c r="G349" s="8">
-        <v>187304222.06</v>
+        <v>187269918.04</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
@@ -10829,19 +10833,19 @@
         <v>700</v>
       </c>
       <c r="C350" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D350" s="7">
-        <v>0.021102</v>
+        <v>0.021232</v>
       </c>
       <c r="E350" s="8">
-        <v>8775738463.02</v>
+        <v>8785760387.62</v>
       </c>
       <c r="F350" s="9">
         <v>337</v>
       </c>
       <c r="G350" s="8">
-        <v>185187554.95</v>
+        <v>186539616.48</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
@@ -10852,19 +10856,19 @@
         <v>702</v>
       </c>
       <c r="C351" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D351" s="7">
-        <v>0.015411</v>
+        <v>0.015373</v>
       </c>
       <c r="E351" s="8">
-        <v>15912615135.14</v>
+        <v>15927077711.39</v>
       </c>
       <c r="F351" s="9">
-        <v>5916</v>
+        <v>5922</v>
       </c>
       <c r="G351" s="8">
-        <v>245236136.01</v>
+        <v>244839957.32</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -10875,19 +10879,19 @@
         <v>704</v>
       </c>
       <c r="C352" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D352" s="10">
-        <v>0.01419</v>
+        <v>46153</v>
+      </c>
+      <c r="D352" s="7">
+        <v>0.014174</v>
       </c>
       <c r="E352" s="8">
-        <v>22385626900.31</v>
+        <v>22520478072.12</v>
       </c>
       <c r="F352" s="9">
-        <v>5830</v>
+        <v>5858</v>
       </c>
       <c r="G352" s="8">
-        <v>317659040.45</v>
+        <v>319206618.48</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -10898,19 +10902,19 @@
         <v>706</v>
       </c>
       <c r="C353" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D353" s="7">
-        <v>0.014665</v>
+        <v>0.014676</v>
       </c>
       <c r="E353" s="8">
-        <v>24122923563.29</v>
+        <v>23677860115.01</v>
       </c>
       <c r="F353" s="9">
-        <v>10870</v>
+        <v>10888</v>
       </c>
       <c r="G353" s="8">
-        <v>353771931.58</v>
+        <v>347494020.32</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
@@ -10921,19 +10925,19 @@
         <v>708</v>
       </c>
       <c r="C354" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D354" s="7">
-        <v>0.016595</v>
+        <v>0.016941</v>
       </c>
       <c r="E354" s="8">
-        <v>40424911062.8</v>
+        <v>41645547660.81</v>
       </c>
       <c r="F354" s="9">
-        <v>10862</v>
+        <v>11001</v>
       </c>
       <c r="G354" s="8">
-        <v>670853632.27</v>
+        <v>705525782.2</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -10944,19 +10948,19 @@
         <v>710</v>
       </c>
       <c r="C355" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D355" s="7">
-        <v>0.049646</v>
+        <v>0.049629</v>
       </c>
       <c r="E355" s="8">
-        <v>2869349251.13</v>
+        <v>2857314711.13</v>
       </c>
       <c r="F355" s="9">
         <v>5120</v>
       </c>
       <c r="G355" s="8">
-        <v>142453146.63</v>
+        <v>141804721.4</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
@@ -10967,19 +10971,19 @@
         <v>712</v>
       </c>
       <c r="C356" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D356" s="7">
-        <v>0.232096</v>
+        <v>0.233932</v>
       </c>
       <c r="E356" s="8">
-        <v>8849801580.95</v>
+        <v>8864343302.72</v>
       </c>
       <c r="F356" s="9">
         <v>47903</v>
       </c>
       <c r="G356" s="8">
-        <v>2054002974.46</v>
+        <v>2073652786.51</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
@@ -10990,19 +10994,19 @@
         <v>714</v>
       </c>
       <c r="C357" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D357" s="7">
-        <v>0.083243</v>
+        <v>0.083538</v>
       </c>
       <c r="E357" s="8">
-        <v>11992459733.17</v>
+        <v>11986632252.68</v>
       </c>
       <c r="F357" s="9">
         <v>21979</v>
       </c>
       <c r="G357" s="8">
-        <v>998286660.86</v>
+        <v>1001339626.28</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
@@ -11013,19 +11017,19 @@
         <v>716</v>
       </c>
       <c r="C358" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D358" s="7">
-        <v>0.313209</v>
+        <v>0.311987</v>
       </c>
       <c r="E358" s="8">
-        <v>3855603022.3</v>
+        <v>3856196761.78</v>
       </c>
       <c r="F358" s="9">
         <v>27476</v>
       </c>
       <c r="G358" s="8">
-        <v>1207608325.64</v>
+        <v>1203082897.51</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
@@ -11036,19 +11040,19 @@
         <v>718</v>
       </c>
       <c r="C359" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D359" s="7">
-        <v>1.418431</v>
+        <v>1.422118</v>
       </c>
       <c r="E359" s="8">
-        <v>8839450299.29</v>
+        <v>8840179482.7</v>
       </c>
       <c r="F359" s="9">
         <v>245798</v>
       </c>
       <c r="G359" s="8">
-        <v>12538152110.07</v>
+        <v>12571776634.12</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
@@ -11059,19 +11063,19 @@
         <v>720</v>
       </c>
       <c r="C360" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D360" s="7">
-        <v>0.098215</v>
+        <v>0.097987</v>
       </c>
       <c r="E360" s="8">
-        <v>541123728462.15</v>
+        <v>540512794206.07</v>
       </c>
       <c r="F360" s="9">
         <v>2778494</v>
       </c>
       <c r="G360" s="8">
-        <v>53146303776.16</v>
+        <v>52963098975.71</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
@@ -11082,19 +11086,19 @@
         <v>722</v>
       </c>
       <c r="C361" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D361" s="10">
-        <v>0.32854</v>
+        <v>46153</v>
+      </c>
+      <c r="D361" s="7">
+        <v>0.328255</v>
       </c>
       <c r="E361" s="8">
-        <v>23893944773.2</v>
+        <v>23866409111.45</v>
       </c>
       <c r="F361" s="9">
         <v>423295</v>
       </c>
       <c r="G361" s="8">
-        <v>7850117139.41</v>
+        <v>7834264341.9</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
@@ -11105,19 +11109,19 @@
         <v>724</v>
       </c>
       <c r="C362" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D362" s="7">
-        <v>0.351984</v>
+        <v>0.352993</v>
       </c>
       <c r="E362" s="8">
-        <v>86157607522.74</v>
+        <v>86533225856.82</v>
       </c>
       <c r="F362" s="9">
         <v>399404</v>
       </c>
       <c r="G362" s="8">
-        <v>30326129055.36</v>
+        <v>30545607728.62</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
@@ -11128,19 +11132,19 @@
         <v>726</v>
       </c>
       <c r="C363" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D363" s="7">
-        <v>0.229488</v>
+        <v>0.231625</v>
       </c>
       <c r="E363" s="8">
-        <v>20469076023.4</v>
+        <v>20501667144.11</v>
       </c>
       <c r="F363" s="9">
         <v>70276</v>
       </c>
       <c r="G363" s="8">
-        <v>4697405564.67</v>
+        <v>4748695040.31</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
@@ -11151,19 +11155,19 @@
         <v>728</v>
       </c>
       <c r="C364" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D364" s="7">
-        <v>0.102781</v>
+        <v>0.102995</v>
       </c>
       <c r="E364" s="8">
-        <v>3781783652.97</v>
+        <v>3781540259.27</v>
       </c>
       <c r="F364" s="9">
         <v>8029</v>
       </c>
       <c r="G364" s="8">
-        <v>388695167.72</v>
+        <v>389479697.63</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
@@ -11174,19 +11178,19 @@
         <v>730</v>
       </c>
       <c r="C365" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D365" s="7">
-        <v>0.140112</v>
+        <v>0.141271</v>
       </c>
       <c r="E365" s="8">
-        <v>103920779828.54</v>
+        <v>103859994176.5</v>
       </c>
       <c r="F365" s="9">
         <v>1907180</v>
       </c>
       <c r="G365" s="8">
-        <v>14560563575.81</v>
+        <v>14672395608.41</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
@@ -11197,19 +11201,19 @@
         <v>732</v>
       </c>
       <c r="C366" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D366" s="10">
-        <v>0.13732</v>
+        <v>46153</v>
+      </c>
+      <c r="D366" s="7">
+        <v>0.137567</v>
       </c>
       <c r="E366" s="8">
-        <v>57617488298.5</v>
+        <v>56953573564.55</v>
       </c>
       <c r="F366" s="9">
         <v>120920</v>
       </c>
       <c r="G366" s="8">
-        <v>7912026471.78</v>
+        <v>7834957043.31</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
@@ -11220,19 +11224,19 @@
         <v>734</v>
       </c>
       <c r="C367" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D367" s="7">
-        <v>0.742334</v>
+        <v>0.742638</v>
       </c>
       <c r="E367" s="8">
-        <v>16761074779.11</v>
+        <v>16730155979.06</v>
       </c>
       <c r="F367" s="9">
         <v>337294</v>
       </c>
       <c r="G367" s="8">
-        <v>12442321215.91</v>
+        <v>12424457520.72</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
@@ -11243,19 +11247,19 @@
         <v>736</v>
       </c>
       <c r="C368" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D368" s="7">
-        <v>0.148524</v>
+        <v>0.148353</v>
       </c>
       <c r="E368" s="8">
-        <v>31090179945.63</v>
+        <v>31073181537.14</v>
       </c>
       <c r="F368" s="9">
         <v>93099</v>
       </c>
       <c r="G368" s="8">
-        <v>4617644605.41</v>
+        <v>4609808707.47</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
@@ -11266,19 +11270,19 @@
         <v>738</v>
       </c>
       <c r="C369" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D369" s="7">
-        <v>0.174865</v>
+        <v>0.175446</v>
       </c>
       <c r="E369" s="8">
-        <v>2090746546.55</v>
+        <v>2092129558.36</v>
       </c>
       <c r="F369" s="9">
         <v>7387</v>
       </c>
       <c r="G369" s="8">
-        <v>365599028.71</v>
+        <v>367055891.69</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
@@ -11289,19 +11293,19 @@
         <v>740</v>
       </c>
       <c r="C370" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D370" s="7">
-        <v>0.385244</v>
+        <v>0.386461</v>
       </c>
       <c r="E370" s="8">
-        <v>5032243710.89</v>
+        <v>5063048230.42</v>
       </c>
       <c r="F370" s="9">
         <v>19141</v>
       </c>
       <c r="G370" s="8">
-        <v>1938643938.5</v>
+        <v>1956670607.87</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
@@ -11312,19 +11316,19 @@
         <v>742</v>
       </c>
       <c r="C371" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D371" s="7">
-        <v>0.797873</v>
+        <v>0.792546</v>
       </c>
       <c r="E371" s="8">
-        <v>329165204817.81</v>
+        <v>328948495906.44</v>
       </c>
       <c r="F371" s="9">
         <v>2043143</v>
       </c>
       <c r="G371" s="8">
-        <v>262632050363.03</v>
+        <v>260706841532.19</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
@@ -11335,19 +11339,19 @@
         <v>744</v>
       </c>
       <c r="C372" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D372" s="7">
-        <v>0.160382</v>
+        <v>0.161417</v>
       </c>
       <c r="E372" s="8">
-        <v>24031340942.32</v>
+        <v>23976334281</v>
       </c>
       <c r="F372" s="9">
         <v>109540</v>
       </c>
       <c r="G372" s="8">
-        <v>3854204929.8</v>
+        <v>3870197204.14</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
@@ -11358,19 +11362,19 @@
         <v>746</v>
       </c>
       <c r="C373" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D373" s="7">
-        <v>0.202384</v>
+        <v>0.202849</v>
       </c>
       <c r="E373" s="8">
-        <v>3590964658.65</v>
+        <v>3590635378.73</v>
       </c>
       <c r="F373" s="9">
         <v>11475</v>
       </c>
       <c r="G373" s="8">
-        <v>726752634.29</v>
+        <v>728357965.34</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
@@ -11381,19 +11385,19 @@
         <v>748</v>
       </c>
       <c r="C374" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D374" s="7">
-        <v>0.434836</v>
+        <v>0.433314</v>
       </c>
       <c r="E374" s="8">
-        <v>55344159339.83</v>
+        <v>55191169290.35</v>
       </c>
       <c r="F374" s="9">
         <v>287959</v>
       </c>
       <c r="G374" s="8">
-        <v>24065634546.5</v>
+        <v>23915091306.25</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
@@ -11404,19 +11408,19 @@
         <v>750</v>
       </c>
       <c r="C375" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D375" s="10">
-        <v>0.54498</v>
+        <v>46153</v>
+      </c>
+      <c r="D375" s="7">
+        <v>0.545215</v>
       </c>
       <c r="E375" s="8">
-        <v>1291976193.17</v>
+        <v>1321721921.71</v>
       </c>
       <c r="F375" s="9">
         <v>14687</v>
       </c>
       <c r="G375" s="8">
-        <v>704100594.99</v>
+        <v>720622003.3</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
@@ -11427,19 +11431,19 @@
         <v>752</v>
       </c>
       <c r="C376" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D376" s="7">
-        <v>0.194466</v>
+        <v>0.196263</v>
       </c>
       <c r="E376" s="8">
-        <v>6822218975.35</v>
+        <v>6823421345.27</v>
       </c>
       <c r="F376" s="9">
         <v>16202</v>
       </c>
       <c r="G376" s="8">
-        <v>1326692475.68</v>
+        <v>1339182186.92</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
@@ -11450,19 +11454,19 @@
         <v>754</v>
       </c>
       <c r="C377" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D377" s="7">
-        <v>0.121017</v>
+        <v>0.121719</v>
       </c>
       <c r="E377" s="8">
-        <v>7591292945.07</v>
+        <v>7596599687.97</v>
       </c>
       <c r="F377" s="9">
         <v>23874</v>
       </c>
       <c r="G377" s="8">
-        <v>918675216.66</v>
+        <v>924653295.89</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
@@ -11473,19 +11477,19 @@
         <v>756</v>
       </c>
       <c r="C378" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D378" s="7">
-        <v>0.185638</v>
+        <v>0.187014</v>
       </c>
       <c r="E378" s="8">
-        <v>14145240889.05</v>
+        <v>14160123157.29</v>
       </c>
       <c r="F378" s="9">
         <v>50758</v>
       </c>
       <c r="G378" s="8">
-        <v>2625893736.22</v>
+        <v>2648137573.91</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
@@ -11496,19 +11500,19 @@
         <v>758</v>
       </c>
       <c r="C379" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D379" s="7">
-        <v>0.089993</v>
+        <v>0.090417</v>
       </c>
       <c r="E379" s="8">
-        <v>396696577633.96</v>
+        <v>396932585941.73</v>
       </c>
       <c r="F379" s="9">
         <v>1947523</v>
       </c>
       <c r="G379" s="8">
-        <v>35699804054.05</v>
+        <v>35889426599.61</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
@@ -11519,19 +11523,19 @@
         <v>760</v>
       </c>
       <c r="C380" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D380" s="7">
-        <v>0.158041</v>
+        <v>0.159394</v>
       </c>
       <c r="E380" s="8">
-        <v>1154077976.78</v>
+        <v>1153761320.03</v>
       </c>
       <c r="F380" s="9">
         <v>1866</v>
       </c>
       <c r="G380" s="8">
-        <v>182391199.2</v>
+        <v>183902830.21</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
@@ -11542,19 +11546,19 @@
         <v>762</v>
       </c>
       <c r="C381" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D381" s="7">
-        <v>0.194808</v>
+        <v>0.195347</v>
       </c>
       <c r="E381" s="8">
-        <v>1023152568.87</v>
+        <v>1023180621.61</v>
       </c>
       <c r="F381" s="9">
         <v>1796</v>
       </c>
       <c r="G381" s="8">
-        <v>199318162.87</v>
+        <v>199875734.68</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
@@ -11565,19 +11569,19 @@
         <v>764</v>
       </c>
       <c r="C382" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D382" s="7">
-        <v>0.178372</v>
+        <v>0.179078</v>
       </c>
       <c r="E382" s="8">
-        <v>586050594.76</v>
+        <v>586257717.58</v>
       </c>
       <c r="F382" s="9">
         <v>1720</v>
       </c>
       <c r="G382" s="8">
-        <v>104534857.06</v>
+        <v>104985659.13</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
@@ -11588,19 +11592,19 @@
         <v>766</v>
       </c>
       <c r="C383" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D383" s="7">
-        <v>0.093582</v>
+        <v>0.093669</v>
       </c>
       <c r="E383" s="8">
-        <v>98037847397.7</v>
+        <v>98071364460.25</v>
       </c>
       <c r="F383" s="9">
         <v>666279</v>
       </c>
       <c r="G383" s="8">
-        <v>9174574537.07</v>
+        <v>9186230395.08</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
@@ -11611,19 +11615,19 @@
         <v>768</v>
       </c>
       <c r="C384" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D384" s="7">
-        <v>0.090269</v>
+        <v>0.090548</v>
       </c>
       <c r="E384" s="8">
-        <v>42414034959.31</v>
+        <v>42426902245.51</v>
       </c>
       <c r="F384" s="9">
         <v>446163</v>
       </c>
       <c r="G384" s="8">
-        <v>3828682453.25</v>
+        <v>3841650251.16</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
@@ -11634,19 +11638,19 @@
         <v>770</v>
       </c>
       <c r="C385" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D385" s="7">
-        <v>0.094847</v>
+        <v>0.095122</v>
       </c>
       <c r="E385" s="8">
-        <v>16650362042.84</v>
+        <v>16572229481.56</v>
       </c>
       <c r="F385" s="9">
         <v>299531</v>
       </c>
       <c r="G385" s="8">
-        <v>1579237221.05</v>
+        <v>1576390278.6</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
@@ -11657,19 +11661,19 @@
         <v>772</v>
       </c>
       <c r="C386" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D386" s="7">
-        <v>0.272605</v>
+        <v>0.275096</v>
       </c>
       <c r="E386" s="8">
-        <v>3540291307.85</v>
+        <v>3541658664.32</v>
       </c>
       <c r="F386" s="9">
-        <v>10570</v>
+        <v>10572</v>
       </c>
       <c r="G386" s="8">
-        <v>965100955.39</v>
+        <v>974295501.46</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
@@ -11680,19 +11684,19 @@
         <v>774</v>
       </c>
       <c r="C387" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D387" s="10">
-        <v>0.19625</v>
+        <v>46153</v>
+      </c>
+      <c r="D387" s="7">
+        <v>0.197391</v>
       </c>
       <c r="E387" s="8">
-        <v>2342711063.92</v>
+        <v>2346163095.28</v>
       </c>
       <c r="F387" s="9">
-        <v>7195</v>
+        <v>7217</v>
       </c>
       <c r="G387" s="8">
-        <v>459756060.04</v>
+        <v>463111541.58</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
@@ -11703,19 +11707,19 @@
         <v>776</v>
       </c>
       <c r="C388" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D388" s="7">
-        <v>0.177707</v>
+        <v>46153</v>
+      </c>
+      <c r="D388" s="11">
+        <v>0.17855</v>
       </c>
       <c r="E388" s="8">
-        <v>2524033821.92</v>
+        <v>2526057763.15</v>
       </c>
       <c r="F388" s="9">
-        <v>7684</v>
+        <v>7688</v>
       </c>
       <c r="G388" s="8">
-        <v>448539580.89</v>
+        <v>451027469.35</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -11726,19 +11730,19 @@
         <v>778</v>
       </c>
       <c r="C389" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D389" s="7">
-        <v>0.100436</v>
+        <v>0.100596</v>
       </c>
       <c r="E389" s="8">
-        <v>3844412883.92</v>
+        <v>3833812745.3</v>
       </c>
       <c r="F389" s="9">
-        <v>7221</v>
+        <v>7207</v>
       </c>
       <c r="G389" s="8">
-        <v>386116022.91</v>
+        <v>385664832.6</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
@@ -11749,19 +11753,19 @@
         <v>780</v>
       </c>
       <c r="C390" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D390" s="7">
-        <v>0.234625</v>
+        <v>0.236504</v>
       </c>
       <c r="E390" s="8">
-        <v>1499948869.15</v>
+        <v>1502978996.33</v>
       </c>
       <c r="F390" s="9">
-        <v>5850</v>
+        <v>5848</v>
       </c>
       <c r="G390" s="8">
-        <v>351926000.8</v>
+        <v>355460267.3</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
@@ -11772,19 +11776,19 @@
         <v>782</v>
       </c>
       <c r="C391" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D391" s="7">
-        <v>0.332604</v>
+        <v>0.335593</v>
       </c>
       <c r="E391" s="8">
-        <v>1917735525.71</v>
+        <v>1922613414.27</v>
       </c>
       <c r="F391" s="9">
-        <v>6338</v>
+        <v>6344</v>
       </c>
       <c r="G391" s="8">
-        <v>637847072.28</v>
+        <v>645215989.34</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
@@ -11795,19 +11799,19 @@
         <v>784</v>
       </c>
       <c r="C392" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D392" s="7">
-        <v>0.283685</v>
+        <v>46153</v>
+      </c>
+      <c r="D392" s="10">
+        <v>0.2877</v>
       </c>
       <c r="E392" s="8">
-        <v>14243794842.25</v>
+        <v>14364090928.38</v>
       </c>
       <c r="F392" s="9">
         <v>67912</v>
       </c>
       <c r="G392" s="8">
-        <v>4040752364.41</v>
+        <v>4132552548.91</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
@@ -11818,19 +11822,19 @@
         <v>786</v>
       </c>
       <c r="C393" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D393" s="10">
-        <v>0.06294</v>
+        <v>46153</v>
+      </c>
+      <c r="D393" s="7">
+        <v>0.063656</v>
       </c>
       <c r="E393" s="8">
-        <v>57159048785.05</v>
+        <v>57634011536.94</v>
       </c>
       <c r="F393" s="9">
-        <v>41959</v>
+        <v>42112</v>
       </c>
       <c r="G393" s="8">
-        <v>3597564279.17</v>
+        <v>3668728017.19</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
@@ -11841,19 +11845,19 @@
         <v>788</v>
       </c>
       <c r="C394" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D394" s="7">
-        <v>0.349627</v>
+        <v>46153</v>
+      </c>
+      <c r="D394" s="11">
+        <v>0.34973</v>
       </c>
       <c r="E394" s="8">
-        <v>13402494764.15</v>
+        <v>13397793829.62</v>
       </c>
       <c r="F394" s="9">
         <v>217133</v>
       </c>
       <c r="G394" s="8">
-        <v>4685877014.52</v>
+        <v>4685606618.27</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
@@ -11864,19 +11868,19 @@
         <v>790</v>
       </c>
       <c r="C395" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D395" s="7">
-        <v>0.373818</v>
+        <v>0.374273</v>
       </c>
       <c r="E395" s="8">
-        <v>4734238730.27</v>
+        <v>4734852329.4</v>
       </c>
       <c r="F395" s="9">
         <v>53707</v>
       </c>
       <c r="G395" s="8">
-        <v>1769743457.67</v>
+        <v>1772128811.67</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
@@ -11887,19 +11891,19 @@
         <v>792</v>
       </c>
       <c r="C396" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D396" s="7">
-        <v>0.221359</v>
+        <v>0.220913</v>
       </c>
       <c r="E396" s="8">
-        <v>68854272868.66</v>
+        <v>68776803224.92</v>
       </c>
       <c r="F396" s="9">
         <v>518426</v>
       </c>
       <c r="G396" s="8">
-        <v>15241517435.45</v>
+        <v>15193690168.86</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -11910,19 +11914,19 @@
         <v>794</v>
       </c>
       <c r="C397" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D397" s="7">
-        <v>0.133822</v>
+        <v>0.134254</v>
       </c>
       <c r="E397" s="8">
-        <v>12867395453.79</v>
+        <v>12837979020.99</v>
       </c>
       <c r="F397" s="9">
         <v>45410</v>
       </c>
       <c r="G397" s="8">
-        <v>1721935096.38</v>
+        <v>1723555799.72</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
@@ -11933,19 +11937,19 @@
         <v>796</v>
       </c>
       <c r="C398" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D398" s="7">
-        <v>0.064135</v>
+        <v>0.064091</v>
       </c>
       <c r="E398" s="8">
-        <v>58438663620.17</v>
+        <v>58382492335.85</v>
       </c>
       <c r="F398" s="9">
         <v>323084</v>
       </c>
       <c r="G398" s="8">
-        <v>3747950468.35</v>
+        <v>3741800063.81</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/emeklilik-fonlari-tarihsel/data/emeklilik-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>17.06.2026 10:04:35</t>
+    <t>18.06.2026 10:31:23</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2917,19 +2917,19 @@
         <v>12</v>
       </c>
       <c r="C6" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D6" s="7">
-        <v>0.104519</v>
+        <v>0.104424</v>
       </c>
       <c r="E6" s="8">
-        <v>48382032816.52</v>
+        <v>48331040040.06</v>
       </c>
       <c r="F6" s="9">
-        <v>651425</v>
+        <v>99979</v>
       </c>
       <c r="G6" s="8">
-        <v>5056832598.29</v>
+        <v>5046925461.85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2940,19 +2940,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D7" s="7">
-        <v>0.429711</v>
+        <v>0.427981</v>
       </c>
       <c r="E7" s="8">
-        <v>24775280736.82</v>
+        <v>24860691610.69</v>
       </c>
       <c r="F7" s="9">
-        <v>211965</v>
+        <v>212439</v>
       </c>
       <c r="G7" s="8">
-        <v>10646221346.03</v>
+        <v>10639900765.68</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2963,19 +2963,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D8" s="7">
-        <v>0.090567</v>
+        <v>0.090662</v>
       </c>
       <c r="E8" s="8">
-        <v>8099834338.97</v>
+        <v>8235593780.76</v>
       </c>
       <c r="F8" s="9">
-        <v>145048</v>
+        <v>144684</v>
       </c>
       <c r="G8" s="8">
-        <v>733579032.84</v>
+        <v>746659474.85</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2986,19 +2986,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D9" s="7">
-        <v>0.386827</v>
+        <v>0.387205</v>
       </c>
       <c r="E9" s="8">
-        <v>151424818425.79</v>
+        <v>151283778708.4</v>
       </c>
       <c r="F9" s="9">
-        <v>503819</v>
+        <v>504145</v>
       </c>
       <c r="G9" s="8">
-        <v>58575139243.58</v>
+        <v>58577891990.33</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3009,19 +3009,19 @@
         <v>20</v>
       </c>
       <c r="C10" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D10" s="7">
-        <v>0.346926</v>
+        <v>0.347327</v>
       </c>
       <c r="E10" s="8">
-        <v>22043257067.12</v>
+        <v>21993883660.67</v>
       </c>
       <c r="F10" s="9">
-        <v>313824</v>
+        <v>313521</v>
       </c>
       <c r="G10" s="8">
-        <v>7647375139.97</v>
+        <v>7639074537.17</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3032,19 +3032,19 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D11" s="7">
-        <v>0.982509</v>
+        <v>0.978028</v>
       </c>
       <c r="E11" s="8">
-        <v>11483532586.53</v>
+        <v>11467154517.89</v>
       </c>
       <c r="F11" s="9">
-        <v>286783</v>
+        <v>286606</v>
       </c>
       <c r="G11" s="8">
-        <v>11282668939.48</v>
+        <v>11215200740.37</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3055,19 +3055,19 @@
         <v>24</v>
       </c>
       <c r="C12" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D12" s="10">
-        <v>0.68116</v>
+        <v>46191</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.678925</v>
       </c>
       <c r="E12" s="8">
-        <v>135228316014.91</v>
+        <v>135380990226.3</v>
       </c>
       <c r="F12" s="9">
-        <v>726351</v>
+        <v>726746</v>
       </c>
       <c r="G12" s="8">
-        <v>92112076928.46</v>
+        <v>91913584339.42</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3078,19 +3078,19 @@
         <v>26</v>
       </c>
       <c r="C13" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D13" s="7">
-        <v>1.994195</v>
+        <v>1.978546</v>
       </c>
       <c r="E13" s="8">
-        <v>1357808345.86</v>
+        <v>1357176398.33</v>
       </c>
       <c r="F13" s="9">
-        <v>32900</v>
+        <v>32890</v>
       </c>
       <c r="G13" s="8">
-        <v>2707735119.72</v>
+        <v>2685235857.95</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3101,19 +3101,19 @@
         <v>28</v>
       </c>
       <c r="C14" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D14" s="7">
-        <v>0.142987</v>
+        <v>46191</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0.14308</v>
       </c>
       <c r="E14" s="8">
-        <v>247016355.77</v>
+        <v>247460504.73</v>
       </c>
       <c r="F14" s="9">
         <v>93</v>
       </c>
       <c r="G14" s="8">
-        <v>35320243.04</v>
+        <v>35406536.64</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3124,19 +3124,19 @@
         <v>30</v>
       </c>
       <c r="C15" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D15" s="10">
-        <v>1.36171</v>
+        <v>46191</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.351661</v>
       </c>
       <c r="E15" s="8">
-        <v>16534088784.98</v>
+        <v>16569184822.23</v>
       </c>
       <c r="F15" s="9">
-        <v>493180</v>
+        <v>493139</v>
       </c>
       <c r="G15" s="8">
-        <v>22514627816.19</v>
+        <v>22395928392.29</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3147,19 +3147,19 @@
         <v>32</v>
       </c>
       <c r="C16" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D16" s="7">
-        <v>0.094828</v>
+        <v>0.094658</v>
       </c>
       <c r="E16" s="8">
-        <v>563404321376.32</v>
+        <v>562927977713.41</v>
       </c>
       <c r="F16" s="9">
-        <v>1961557</v>
+        <v>1960350</v>
       </c>
       <c r="G16" s="8">
-        <v>53426276465.37</v>
+        <v>53285362467.95</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3170,19 +3170,19 @@
         <v>34</v>
       </c>
       <c r="C17" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D17" s="7">
-        <v>0.362177</v>
+        <v>0.362586</v>
       </c>
       <c r="E17" s="8">
-        <v>2070535698.59</v>
+        <v>2068293238.42</v>
       </c>
       <c r="F17" s="9">
-        <v>13099</v>
+        <v>13085</v>
       </c>
       <c r="G17" s="8">
-        <v>749900205.2</v>
+        <v>749934722.81</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3193,19 +3193,19 @@
         <v>36</v>
       </c>
       <c r="C18" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D18" s="7">
-        <v>0.149928</v>
+        <v>0.149965</v>
       </c>
       <c r="E18" s="8">
-        <v>32932592027.66</v>
+        <v>32918150183.33</v>
       </c>
       <c r="F18" s="9">
-        <v>235862</v>
+        <v>235820</v>
       </c>
       <c r="G18" s="8">
-        <v>4937515668.41</v>
+        <v>4936584668.05</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3216,19 +3216,19 @@
         <v>38</v>
       </c>
       <c r="C19" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D19" s="7">
-        <v>0.378762</v>
+        <v>0.379427</v>
       </c>
       <c r="E19" s="8">
-        <v>1408542546.19</v>
+        <v>1405853739.21</v>
       </c>
       <c r="F19" s="9">
         <v>548</v>
       </c>
       <c r="G19" s="8">
-        <v>533502442.67</v>
+        <v>533418319.15</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3239,19 +3239,19 @@
         <v>40</v>
       </c>
       <c r="C20" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D20" s="7">
-        <v>0.141582</v>
+        <v>0.141443</v>
       </c>
       <c r="E20" s="8">
-        <v>15061878971.59</v>
+        <v>15063311280.4</v>
       </c>
       <c r="F20" s="9">
-        <v>534821</v>
+        <v>534942</v>
       </c>
       <c r="G20" s="8">
-        <v>2132496054.01</v>
+        <v>2130596386.57</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3262,19 +3262,19 @@
         <v>42</v>
       </c>
       <c r="C21" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D21" s="7">
-        <v>0.099966</v>
+        <v>0.099733</v>
       </c>
       <c r="E21" s="8">
-        <v>508830130600.75</v>
+        <v>508443395926.3</v>
       </c>
       <c r="F21" s="9">
-        <v>2312626</v>
+        <v>2311722</v>
       </c>
       <c r="G21" s="8">
-        <v>50865839501.22</v>
+        <v>50708550511.07</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3285,19 +3285,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D22" s="7">
-        <v>0.401513</v>
+        <v>0.399353</v>
       </c>
       <c r="E22" s="8">
-        <v>3607091537.7</v>
+        <v>3617975894.92</v>
       </c>
       <c r="F22" s="9">
-        <v>20742</v>
+        <v>20800</v>
       </c>
       <c r="G22" s="8">
-        <v>1448294668.1</v>
+        <v>1444851089.34</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3308,19 +3308,19 @@
         <v>46</v>
       </c>
       <c r="C23" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D23" s="10">
-        <v>0.09837</v>
+        <v>46191</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.098152</v>
       </c>
       <c r="E23" s="8">
-        <v>569886090.26</v>
+        <v>569175314.7</v>
       </c>
       <c r="F23" s="9">
-        <v>4568</v>
+        <v>4566</v>
       </c>
       <c r="G23" s="8">
-        <v>56059558.09</v>
+        <v>55865742.84</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3331,19 +3331,19 @@
         <v>48</v>
       </c>
       <c r="C24" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D24" s="7">
-        <v>0.227848</v>
+        <v>46191</v>
+      </c>
+      <c r="D24" s="11">
+        <v>0.2279</v>
       </c>
       <c r="E24" s="8">
-        <v>1174747191.19</v>
+        <v>1171433199.21</v>
       </c>
       <c r="F24" s="9">
-        <v>4869</v>
+        <v>4867</v>
       </c>
       <c r="G24" s="8">
-        <v>267663638.98</v>
+        <v>266969114.18</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3354,19 +3354,19 @@
         <v>50</v>
       </c>
       <c r="C25" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D25" s="7">
-        <v>0.108428</v>
+        <v>0.108373</v>
       </c>
       <c r="E25" s="8">
-        <v>68050986221.12</v>
+        <v>68228993407.77</v>
       </c>
       <c r="F25" s="9">
-        <v>773789</v>
+        <v>774037</v>
       </c>
       <c r="G25" s="8">
-        <v>7378654237.4</v>
+        <v>7394195494.87</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3377,19 +3377,19 @@
         <v>52</v>
       </c>
       <c r="C26" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D26" s="7">
-        <v>0.102314</v>
+        <v>46191</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0.10234</v>
       </c>
       <c r="E26" s="8">
-        <v>1626707742.63</v>
+        <v>1623029472.61</v>
       </c>
       <c r="F26" s="9">
-        <v>3103</v>
+        <v>3098</v>
       </c>
       <c r="G26" s="8">
-        <v>166435477.97</v>
+        <v>166101420.9</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3400,19 +3400,19 @@
         <v>54</v>
       </c>
       <c r="C27" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D27" s="7">
-        <v>0.095787</v>
+        <v>0.095764</v>
       </c>
       <c r="E27" s="8">
-        <v>66034060934.16</v>
+        <v>66193393152.03</v>
       </c>
       <c r="F27" s="9">
-        <v>726051</v>
+        <v>726111</v>
       </c>
       <c r="G27" s="8">
-        <v>6325223138.07</v>
+        <v>6338929532.89</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3423,19 +3423,19 @@
         <v>56</v>
       </c>
       <c r="C28" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D28" s="10">
-        <v>0.40344</v>
+        <v>0.40391</v>
       </c>
       <c r="E28" s="8">
-        <v>1020915093.96</v>
+        <v>1021286893.68</v>
       </c>
       <c r="F28" s="9">
-        <v>7620</v>
+        <v>7613</v>
       </c>
       <c r="G28" s="8">
-        <v>411877632.48</v>
+        <v>412508109.46</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3446,19 +3446,19 @@
         <v>58</v>
       </c>
       <c r="C29" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D29" s="7">
-        <v>0.672183</v>
+        <v>0.673235</v>
       </c>
       <c r="E29" s="8">
-        <v>213232328.97</v>
+        <v>213270937.63</v>
       </c>
       <c r="F29" s="9">
         <v>1640</v>
       </c>
       <c r="G29" s="8">
-        <v>143331096.17</v>
+        <v>143581540.5</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3469,19 +3469,19 @@
         <v>60</v>
       </c>
       <c r="C30" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D30" s="7">
-        <v>2.399459</v>
+        <v>46191</v>
+      </c>
+      <c r="D30" s="11">
+        <v>2.3793</v>
       </c>
       <c r="E30" s="8">
-        <v>836228377.45</v>
+        <v>837567969.25</v>
       </c>
       <c r="F30" s="9">
-        <v>19707</v>
+        <v>19695</v>
       </c>
       <c r="G30" s="8">
-        <v>2006495590.24</v>
+        <v>1992825416.36</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3492,19 +3492,19 @@
         <v>62</v>
       </c>
       <c r="C31" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D31" s="7">
-        <v>0.543282</v>
+        <v>0.543357</v>
       </c>
       <c r="E31" s="8">
-        <v>2376658807.49</v>
+        <v>2374379413.53</v>
       </c>
       <c r="F31" s="9">
-        <v>14141</v>
+        <v>14122</v>
       </c>
       <c r="G31" s="8">
-        <v>1291195125.7</v>
+        <v>1290135417.84</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3515,19 +3515,19 @@
         <v>64</v>
       </c>
       <c r="C32" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D32" s="7">
-        <v>0.827685</v>
+        <v>46191</v>
+      </c>
+      <c r="D32" s="11">
+        <v>0.8252</v>
       </c>
       <c r="E32" s="8">
-        <v>11733783920.94</v>
+        <v>11706127573.31</v>
       </c>
       <c r="F32" s="9">
-        <v>78140</v>
+        <v>78124</v>
       </c>
       <c r="G32" s="8">
-        <v>9711873939.28</v>
+        <v>9659899777.51</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3538,19 +3538,19 @@
         <v>66</v>
       </c>
       <c r="C33" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D33" s="7">
-        <v>0.266603</v>
+        <v>0.265653</v>
       </c>
       <c r="E33" s="8">
-        <v>1300501307.83</v>
+        <v>1300578289.76</v>
       </c>
       <c r="F33" s="9">
         <v>16153</v>
       </c>
       <c r="G33" s="8">
-        <v>346716940.07</v>
+        <v>345502373.48</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3561,19 +3561,19 @@
         <v>68</v>
       </c>
       <c r="C34" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D34" s="7">
-        <v>0.129751</v>
+        <v>0.129843</v>
       </c>
       <c r="E34" s="8">
-        <v>3520286284.31</v>
+        <v>3527163212.1</v>
       </c>
       <c r="F34" s="9">
-        <v>55206</v>
+        <v>55220</v>
       </c>
       <c r="G34" s="8">
-        <v>456761406.94</v>
+        <v>457977461.62</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3584,19 +3584,19 @@
         <v>70</v>
       </c>
       <c r="C35" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D35" s="7">
-        <v>0.180092</v>
+        <v>0.180148</v>
       </c>
       <c r="E35" s="8">
-        <v>10456628549.59</v>
+        <v>10433502644.22</v>
       </c>
       <c r="F35" s="9">
-        <v>36844</v>
+        <v>36813</v>
       </c>
       <c r="G35" s="8">
-        <v>1883152326.83</v>
+        <v>1879575777.03</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3607,19 +3607,19 @@
         <v>72</v>
       </c>
       <c r="C36" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D36" s="7">
-        <v>0.207369</v>
+        <v>46191</v>
+      </c>
+      <c r="D36" s="10">
+        <v>0.20643</v>
       </c>
       <c r="E36" s="8">
-        <v>1487778796.03</v>
+        <v>1487660051.6</v>
       </c>
       <c r="F36" s="9">
-        <v>32804</v>
+        <v>32798</v>
       </c>
       <c r="G36" s="8">
-        <v>308519871.82</v>
+        <v>307097207.17</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3630,19 +3630,19 @@
         <v>74</v>
       </c>
       <c r="C37" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D37" s="7">
-        <v>0.841991</v>
+        <v>0.837135</v>
       </c>
       <c r="E37" s="8">
-        <v>2467267475.71</v>
+        <v>2473247758.35</v>
       </c>
       <c r="F37" s="9">
-        <v>52841</v>
+        <v>52852</v>
       </c>
       <c r="G37" s="8">
-        <v>2077417056.85</v>
+        <v>2070443233.73</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3653,19 +3653,19 @@
         <v>76</v>
       </c>
       <c r="C38" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D38" s="7">
-        <v>0.176666</v>
+        <v>0.176763</v>
       </c>
       <c r="E38" s="8">
-        <v>3691506709.66</v>
+        <v>3688531327.51</v>
       </c>
       <c r="F38" s="9">
-        <v>53250</v>
+        <v>53232</v>
       </c>
       <c r="G38" s="8">
-        <v>652165481.99</v>
+        <v>651995177.59</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3676,19 +3676,19 @@
         <v>78</v>
       </c>
       <c r="C39" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D39" s="7">
-        <v>0.108511</v>
+        <v>0.108123</v>
       </c>
       <c r="E39" s="8">
-        <v>8132481184.56</v>
+        <v>8124755029.83</v>
       </c>
       <c r="F39" s="9">
-        <v>97122</v>
+        <v>97077</v>
       </c>
       <c r="G39" s="8">
-        <v>882460464.34</v>
+        <v>878476844.1</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3699,19 +3699,19 @@
         <v>80</v>
       </c>
       <c r="C40" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D40" s="10">
-        <v>0.35123</v>
+        <v>46191</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0.351876</v>
       </c>
       <c r="E40" s="8">
-        <v>13426930791.23</v>
+        <v>13408559758.41</v>
       </c>
       <c r="F40" s="9">
-        <v>150665</v>
+        <v>150549</v>
       </c>
       <c r="G40" s="8">
-        <v>4715936686.86</v>
+        <v>4718151397.12</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3722,19 +3722,19 @@
         <v>82</v>
       </c>
       <c r="C41" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D41" s="7">
-        <v>0.383534</v>
+        <v>0.383969</v>
       </c>
       <c r="E41" s="8">
-        <v>84539620812.57</v>
+        <v>84177068961.53</v>
       </c>
       <c r="F41" s="9">
-        <v>247092</v>
+        <v>175758</v>
       </c>
       <c r="G41" s="8">
-        <v>32423791014.17</v>
+        <v>32321387222.79</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3745,19 +3745,19 @@
         <v>84</v>
       </c>
       <c r="C42" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D42" s="7">
-        <v>0.992234</v>
+        <v>0.992503</v>
       </c>
       <c r="E42" s="8">
-        <v>12721456322.76</v>
+        <v>12715747787.54</v>
       </c>
       <c r="F42" s="9">
-        <v>231631</v>
+        <v>231519</v>
       </c>
       <c r="G42" s="8">
-        <v>12622659382.1</v>
+        <v>12620416318.45</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3768,19 +3768,19 @@
         <v>86</v>
       </c>
       <c r="C43" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D43" s="7">
-        <v>0.710444</v>
+        <v>0.710676</v>
       </c>
       <c r="E43" s="8">
-        <v>8722883753</v>
+        <v>8721937602.84</v>
       </c>
       <c r="F43" s="9">
-        <v>120072</v>
+        <v>120064</v>
       </c>
       <c r="G43" s="8">
-        <v>6197120203.75</v>
+        <v>6198475213.83</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3791,19 +3791,19 @@
         <v>88</v>
       </c>
       <c r="C44" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D44" s="7">
-        <v>3.010182</v>
+        <v>2.981414</v>
       </c>
       <c r="E44" s="8">
-        <v>8332243457.47</v>
+        <v>8338748018.81</v>
       </c>
       <c r="F44" s="9">
-        <v>369295</v>
+        <v>369444</v>
       </c>
       <c r="G44" s="8">
-        <v>25081568212.62</v>
+        <v>24861263359.3</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3814,19 +3814,19 @@
         <v>90</v>
       </c>
       <c r="C45" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D45" s="7">
-        <v>1.199076</v>
+        <v>1.197412</v>
       </c>
       <c r="E45" s="8">
-        <v>3901123825.88</v>
+        <v>3902382002.18</v>
       </c>
       <c r="F45" s="9">
-        <v>98794</v>
+        <v>98795</v>
       </c>
       <c r="G45" s="8">
-        <v>4677742275.6</v>
+        <v>4672759261.38</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3837,19 +3837,19 @@
         <v>92</v>
       </c>
       <c r="C46" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D46" s="7">
-        <v>0.439569</v>
+        <v>46191</v>
+      </c>
+      <c r="D46" s="10">
+        <v>0.43981</v>
       </c>
       <c r="E46" s="8">
-        <v>23241799554.41</v>
+        <v>23230262749.65</v>
       </c>
       <c r="F46" s="9">
-        <v>217948</v>
+        <v>217893</v>
       </c>
       <c r="G46" s="8">
-        <v>10216385801.7</v>
+        <v>10216912885.06</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3860,19 +3860,19 @@
         <v>94</v>
       </c>
       <c r="C47" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D47" s="7">
-        <v>1.020309</v>
+        <v>1.014553</v>
       </c>
       <c r="E47" s="8">
-        <v>9251491845.82</v>
+        <v>9246262315.92</v>
       </c>
       <c r="F47" s="9">
-        <v>193683</v>
+        <v>193601</v>
       </c>
       <c r="G47" s="8">
-        <v>9439384778.57</v>
+        <v>9380823716.33</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3883,19 +3883,19 @@
         <v>96</v>
       </c>
       <c r="C48" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D48" s="7">
-        <v>1.363356</v>
+        <v>1.351745</v>
       </c>
       <c r="E48" s="8">
-        <v>695084211.95</v>
+        <v>691271787.77</v>
       </c>
       <c r="F48" s="9">
-        <v>7258</v>
+        <v>7253</v>
       </c>
       <c r="G48" s="8">
-        <v>947647164.45</v>
+        <v>934423352.63</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3906,19 +3906,19 @@
         <v>98</v>
       </c>
       <c r="C49" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D49" s="7">
-        <v>0.135693</v>
+        <v>0.135829</v>
       </c>
       <c r="E49" s="8">
-        <v>97153444275.18</v>
+        <v>97157037839.39</v>
       </c>
       <c r="F49" s="9">
-        <v>212528</v>
+        <v>212672</v>
       </c>
       <c r="G49" s="8">
-        <v>13183075836</v>
+        <v>13196783152.22</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3929,19 +3929,19 @@
         <v>100</v>
       </c>
       <c r="C50" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D50" s="7">
-        <v>0.104548</v>
+        <v>46191</v>
+      </c>
+      <c r="D50" s="10">
+        <v>0.10466</v>
       </c>
       <c r="E50" s="8">
-        <v>13506890537.98</v>
+        <v>13473967164.6</v>
       </c>
       <c r="F50" s="9">
-        <v>129035</v>
+        <v>314723</v>
       </c>
       <c r="G50" s="8">
-        <v>1412120339.91</v>
+        <v>1410179222.37</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3952,19 +3952,19 @@
         <v>102</v>
       </c>
       <c r="C51" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D51" s="7">
-        <v>0.500144</v>
+        <v>0.496745</v>
       </c>
       <c r="E51" s="8">
-        <v>20103516956.28</v>
+        <v>20100261827.05</v>
       </c>
       <c r="F51" s="9">
-        <v>133237</v>
+        <v>133210</v>
       </c>
       <c r="G51" s="8">
-        <v>10054649737.09</v>
+        <v>9984704171.45</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3975,19 +3975,19 @@
         <v>104</v>
       </c>
       <c r="C52" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D52" s="7">
-        <v>0.210808</v>
+        <v>0.209924</v>
       </c>
       <c r="E52" s="8">
-        <v>2716709966.15</v>
+        <v>2723165948.5</v>
       </c>
       <c r="F52" s="9">
-        <v>10595</v>
+        <v>10610</v>
       </c>
       <c r="G52" s="8">
-        <v>572703341.5</v>
+        <v>571657129.91</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3998,19 +3998,19 @@
         <v>106</v>
       </c>
       <c r="C53" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D53" s="7">
-        <v>0.267619</v>
+        <v>0.266398</v>
       </c>
       <c r="E53" s="8">
-        <v>3031661818.91</v>
+        <v>3030948007.99</v>
       </c>
       <c r="F53" s="9">
-        <v>11034</v>
+        <v>11016</v>
       </c>
       <c r="G53" s="8">
-        <v>811328966.58</v>
+        <v>807438687.65</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -4021,19 +4021,19 @@
         <v>108</v>
       </c>
       <c r="C54" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D54" s="7">
-        <v>0.339629</v>
+        <v>0.337804</v>
       </c>
       <c r="E54" s="8">
-        <v>4568639179.27</v>
+        <v>4583788058.19</v>
       </c>
       <c r="F54" s="9">
-        <v>15767</v>
+        <v>15763</v>
       </c>
       <c r="G54" s="8">
-        <v>1551642189.25</v>
+        <v>1548421791.56</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4044,19 +4044,19 @@
         <v>110</v>
       </c>
       <c r="C55" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D55" s="7">
-        <v>0.321335</v>
+        <v>0.320205</v>
       </c>
       <c r="E55" s="8">
-        <v>2630992669.07</v>
+        <v>2640313289.52</v>
       </c>
       <c r="F55" s="9">
-        <v>10147</v>
+        <v>10149</v>
       </c>
       <c r="G55" s="8">
-        <v>845429674.63</v>
+        <v>845442234.02</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -4067,19 +4067,19 @@
         <v>112</v>
       </c>
       <c r="C56" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D56" s="7">
-        <v>0.228491</v>
+        <v>0.227619</v>
       </c>
       <c r="E56" s="8">
-        <v>1907317905.34</v>
+        <v>1908810312.55</v>
       </c>
       <c r="F56" s="9">
-        <v>6643</v>
+        <v>6645</v>
       </c>
       <c r="G56" s="8">
-        <v>435804754.89</v>
+        <v>434482442.33</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4090,19 +4090,19 @@
         <v>114</v>
       </c>
       <c r="C57" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D57" s="7">
-        <v>0.119425</v>
+        <v>46191</v>
+      </c>
+      <c r="D57" s="10">
+        <v>0.11944</v>
       </c>
       <c r="E57" s="8">
-        <v>1593647040.01</v>
+        <v>1597066831.99</v>
       </c>
       <c r="F57" s="9">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="G57" s="8">
-        <v>190321990.04</v>
+        <v>190754271.25</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -4113,19 +4113,19 @@
         <v>116</v>
       </c>
       <c r="C58" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D58" s="7">
-        <v>0.312239</v>
+        <v>0.311814</v>
       </c>
       <c r="E58" s="8">
-        <v>4577203311.31</v>
+        <v>4600531390.83</v>
       </c>
       <c r="F58" s="9">
-        <v>16932</v>
+        <v>16946</v>
       </c>
       <c r="G58" s="8">
-        <v>1429181369.72</v>
+        <v>1434511399.49</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -4136,19 +4136,19 @@
         <v>118</v>
       </c>
       <c r="C59" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D59" s="7">
-        <v>0.246344</v>
+        <v>0.245555</v>
       </c>
       <c r="E59" s="8">
-        <v>2861116922.93</v>
+        <v>2871311403.1</v>
       </c>
       <c r="F59" s="9">
-        <v>11401</v>
+        <v>11399</v>
       </c>
       <c r="G59" s="8">
-        <v>704819328.9</v>
+        <v>705065056.92</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -4159,19 +4159,19 @@
         <v>120</v>
       </c>
       <c r="C60" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D60" s="7">
-        <v>0.175042</v>
+        <v>0.174143</v>
       </c>
       <c r="E60" s="8">
-        <v>192374384.52</v>
+        <v>192166471.77</v>
       </c>
       <c r="F60" s="9">
         <v>451</v>
       </c>
       <c r="G60" s="8">
-        <v>33673572.07</v>
+        <v>33464496.57</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -4182,19 +4182,19 @@
         <v>122</v>
       </c>
       <c r="C61" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D61" s="7">
-        <v>0.387005</v>
+        <v>46191</v>
+      </c>
+      <c r="D61" s="11">
+        <v>0.3859</v>
       </c>
       <c r="E61" s="8">
-        <v>837926388.76</v>
+        <v>839097760.31</v>
       </c>
       <c r="F61" s="9">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="G61" s="8">
-        <v>324281879.13</v>
+        <v>323807538.82</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -4205,19 +4205,19 @@
         <v>124</v>
       </c>
       <c r="C62" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D62" s="7">
-        <v>0.076756</v>
+        <v>0.076781</v>
       </c>
       <c r="E62" s="8">
-        <v>173040976.47</v>
+        <v>172400976.99</v>
       </c>
       <c r="F62" s="9">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G62" s="8">
-        <v>13281851.29</v>
+        <v>13237115.94</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -4228,19 +4228,19 @@
         <v>126</v>
       </c>
       <c r="C63" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D63" s="7">
-        <v>0.142684</v>
+        <v>0.142119</v>
       </c>
       <c r="E63" s="8">
-        <v>118550732.79</v>
+        <v>118574751.17</v>
       </c>
       <c r="F63" s="9">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G63" s="8">
-        <v>16915264.09</v>
+        <v>16851732.12</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -4251,19 +4251,19 @@
         <v>128</v>
       </c>
       <c r="C64" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D64" s="7">
-        <v>0.263074</v>
+        <v>0.262887</v>
       </c>
       <c r="E64" s="8">
-        <v>217034358.89</v>
+        <v>217162467.55</v>
       </c>
       <c r="F64" s="9">
         <v>341</v>
       </c>
       <c r="G64" s="8">
-        <v>57096092.19</v>
+        <v>57089282.46</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4274,19 +4274,19 @@
         <v>130</v>
       </c>
       <c r="C65" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D65" s="7">
-        <v>0.334799</v>
+        <v>0.333734</v>
       </c>
       <c r="E65" s="8">
-        <v>630809815.65</v>
+        <v>631424425.64</v>
       </c>
       <c r="F65" s="9">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G65" s="8">
-        <v>211194526.22</v>
+        <v>210727734.89</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -4297,19 +4297,19 @@
         <v>132</v>
       </c>
       <c r="C66" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D66" s="7">
-        <v>0.558138</v>
+        <v>0.554768</v>
       </c>
       <c r="E66" s="8">
-        <v>12724250250</v>
+        <v>12937078273.45</v>
       </c>
       <c r="F66" s="9">
-        <v>125257</v>
+        <v>125281</v>
       </c>
       <c r="G66" s="8">
-        <v>7101884467.29</v>
+        <v>7177071633.05</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4320,19 +4320,19 @@
         <v>134</v>
       </c>
       <c r="C67" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D67" s="7">
-        <v>0.257786</v>
+        <v>0.256218</v>
       </c>
       <c r="E67" s="8">
-        <v>2038809201.4</v>
+        <v>2040380812.94</v>
       </c>
       <c r="F67" s="9">
-        <v>6089</v>
+        <v>6080</v>
       </c>
       <c r="G67" s="8">
-        <v>525576331.91</v>
+        <v>522782570.14</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -4343,19 +4343,19 @@
         <v>136</v>
       </c>
       <c r="C68" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D68" s="7">
-        <v>2.133867</v>
+        <v>2.126797</v>
       </c>
       <c r="E68" s="8">
-        <v>6992230605</v>
+        <v>6990655455.12</v>
       </c>
       <c r="F68" s="9">
-        <v>234102</v>
+        <v>234140</v>
       </c>
       <c r="G68" s="8">
-        <v>14920492477.76</v>
+        <v>14867702434.94</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -4366,19 +4366,19 @@
         <v>138</v>
       </c>
       <c r="C69" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D69" s="7">
-        <v>1.024069</v>
+        <v>46191</v>
+      </c>
+      <c r="D69" s="10">
+        <v>1.02309</v>
       </c>
       <c r="E69" s="8">
-        <v>6396552202.44</v>
+        <v>6393683417.54</v>
       </c>
       <c r="F69" s="9">
-        <v>162304</v>
+        <v>162282</v>
       </c>
       <c r="G69" s="8">
-        <v>6550508940.71</v>
+        <v>6541316026.24</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -4389,19 +4389,19 @@
         <v>140</v>
       </c>
       <c r="C70" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D70" s="7">
-        <v>0.330733</v>
+        <v>0.328881</v>
       </c>
       <c r="E70" s="8">
-        <v>12249777578.52</v>
+        <v>12241749656.14</v>
       </c>
       <c r="F70" s="9">
-        <v>186755</v>
+        <v>186714</v>
       </c>
       <c r="G70" s="8">
-        <v>4051399984.9</v>
+        <v>4026083049.62</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -4412,19 +4412,19 @@
         <v>142</v>
       </c>
       <c r="C71" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D71" s="7">
-        <v>0.103713</v>
+        <v>0.103823</v>
       </c>
       <c r="E71" s="8">
-        <v>7593680037.91</v>
+        <v>7510707976.04</v>
       </c>
       <c r="F71" s="9">
-        <v>122068</v>
+        <v>121165</v>
       </c>
       <c r="G71" s="8">
-        <v>787566098.05</v>
+        <v>779786827.08</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -4435,19 +4435,19 @@
         <v>144</v>
       </c>
       <c r="C72" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D72" s="7">
-        <v>0.098503</v>
+        <v>0.098343</v>
       </c>
       <c r="E72" s="8">
-        <v>389979729896.78</v>
+        <v>389717223213.77</v>
       </c>
       <c r="F72" s="9">
-        <v>1425263</v>
+        <v>1424535</v>
       </c>
       <c r="G72" s="8">
-        <v>38414259161.36</v>
+        <v>38326041651.52</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4458,19 +4458,19 @@
         <v>146</v>
       </c>
       <c r="C73" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D73" s="7">
-        <v>1.143395</v>
+        <v>1.143729</v>
       </c>
       <c r="E73" s="8">
-        <v>6397226866.39</v>
+        <v>6392264924.77</v>
       </c>
       <c r="F73" s="9">
-        <v>258622</v>
+        <v>258528</v>
       </c>
       <c r="G73" s="8">
-        <v>7314558973.46</v>
+        <v>7311017011.22</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4481,19 +4481,19 @@
         <v>148</v>
       </c>
       <c r="C74" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D74" s="10">
-        <v>0.52599</v>
+        <v>46191</v>
+      </c>
+      <c r="D74" s="7">
+        <v>0.526245</v>
       </c>
       <c r="E74" s="8">
-        <v>6772086350.18</v>
+        <v>6770576225.78</v>
       </c>
       <c r="F74" s="9">
-        <v>64698</v>
+        <v>64705</v>
       </c>
       <c r="G74" s="8">
-        <v>3562049049.18</v>
+        <v>3562984677.15</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -4504,19 +4504,19 @@
         <v>150</v>
       </c>
       <c r="C75" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D75" s="10">
-        <v>1.63881</v>
+        <v>46191</v>
+      </c>
+      <c r="D75" s="7">
+        <v>1.632974</v>
       </c>
       <c r="E75" s="8">
-        <v>495680077.41</v>
+        <v>495802132.09</v>
       </c>
       <c r="F75" s="9">
-        <v>5022</v>
+        <v>5029</v>
       </c>
       <c r="G75" s="8">
-        <v>812325343.29</v>
+        <v>809631744.08</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4527,19 +4527,19 @@
         <v>152</v>
       </c>
       <c r="C76" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D76" s="7">
-        <v>0.679845</v>
+        <v>0.678515</v>
       </c>
       <c r="E76" s="8">
-        <v>210428568836.94</v>
+        <v>210479093736.15</v>
       </c>
       <c r="F76" s="9">
-        <v>721946</v>
+        <v>722253</v>
       </c>
       <c r="G76" s="8">
-        <v>143058802000.94</v>
+        <v>142813176025.86</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4550,19 +4550,19 @@
         <v>154</v>
       </c>
       <c r="C77" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D77" s="7">
-        <v>0.602903</v>
+        <v>0.598734</v>
       </c>
       <c r="E77" s="8">
-        <v>192419547.27</v>
+        <v>192361580.71</v>
       </c>
       <c r="F77" s="9">
-        <v>22296</v>
+        <v>22295</v>
       </c>
       <c r="G77" s="8">
-        <v>116010371.25</v>
+        <v>115173463.14</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4573,19 +4573,19 @@
         <v>156</v>
       </c>
       <c r="C78" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D78" s="7">
-        <v>0.318296</v>
+        <v>0.317713</v>
       </c>
       <c r="E78" s="8">
-        <v>395328740.03</v>
+        <v>395028437.49</v>
       </c>
       <c r="F78" s="9">
-        <v>33095</v>
+        <v>33092</v>
       </c>
       <c r="G78" s="8">
-        <v>125831400.75</v>
+        <v>125505731.74</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4596,19 +4596,19 @@
         <v>158</v>
       </c>
       <c r="C79" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D79" s="7">
-        <v>0.157877</v>
+        <v>0.157331</v>
       </c>
       <c r="E79" s="8">
-        <v>3173940588.69</v>
+        <v>3182328617.59</v>
       </c>
       <c r="F79" s="9">
-        <v>6968</v>
+        <v>6960</v>
       </c>
       <c r="G79" s="8">
-        <v>501091738.02</v>
+        <v>500679824.09</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4619,19 +4619,19 @@
         <v>160</v>
       </c>
       <c r="C80" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D80" s="7">
-        <v>0.350581</v>
+        <v>46191</v>
+      </c>
+      <c r="D80" s="10">
+        <v>0.35084</v>
       </c>
       <c r="E80" s="8">
-        <v>237558593.4</v>
+        <v>237881210.42</v>
       </c>
       <c r="F80" s="9">
-        <v>20787</v>
+        <v>20825</v>
       </c>
       <c r="G80" s="8">
-        <v>83283601.58</v>
+        <v>83458345.64</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4642,19 +4642,19 @@
         <v>162</v>
       </c>
       <c r="C81" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D81" s="7">
-        <v>0.175504</v>
+        <v>0.174727</v>
       </c>
       <c r="E81" s="8">
-        <v>707013009.54</v>
+        <v>706319412.65</v>
       </c>
       <c r="F81" s="9">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="G81" s="8">
-        <v>124083335.83</v>
+        <v>123413376.49</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4665,19 +4665,19 @@
         <v>164</v>
       </c>
       <c r="C82" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D82" s="7">
-        <v>1.956343</v>
+        <v>1.936444</v>
       </c>
       <c r="E82" s="8">
-        <v>82562688</v>
+        <v>82580680.37</v>
       </c>
       <c r="F82" s="9">
         <v>13704</v>
       </c>
       <c r="G82" s="8">
-        <v>161520955.17</v>
+        <v>159912893.1</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4688,19 +4688,19 @@
         <v>166</v>
       </c>
       <c r="C83" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D83" s="7">
-        <v>0.100204</v>
+        <v>0.100293</v>
       </c>
       <c r="E83" s="8">
-        <v>10429323536.8</v>
+        <v>10588042672.79</v>
       </c>
       <c r="F83" s="9">
-        <v>169591</v>
+        <v>174405</v>
       </c>
       <c r="G83" s="8">
-        <v>1045054949.04</v>
+        <v>1061904174.37</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4711,19 +4711,19 @@
         <v>168</v>
       </c>
       <c r="C84" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D84" s="7">
-        <v>0.087861</v>
+        <v>0.087956</v>
       </c>
       <c r="E84" s="8">
-        <v>9214790757.9</v>
+        <v>9381932015.04</v>
       </c>
       <c r="F84" s="9">
-        <v>140336</v>
+        <v>139964</v>
       </c>
       <c r="G84" s="8">
-        <v>809617852.13</v>
+        <v>825200325.07</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4734,19 +4734,19 @@
         <v>170</v>
       </c>
       <c r="C85" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D85" s="7">
-        <v>0.280349</v>
+        <v>0.279017</v>
       </c>
       <c r="E85" s="8">
-        <v>4545533902.8</v>
+        <v>4562639938.44</v>
       </c>
       <c r="F85" s="9">
-        <v>81401</v>
+        <v>81511</v>
       </c>
       <c r="G85" s="8">
-        <v>1274334839.03</v>
+        <v>1273054245.13</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4757,19 +4757,19 @@
         <v>172</v>
       </c>
       <c r="C86" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D86" s="7">
-        <v>0.893105</v>
+        <v>46191</v>
+      </c>
+      <c r="D86" s="10">
+        <v>0.88263</v>
       </c>
       <c r="E86" s="8">
-        <v>4554416245.89</v>
+        <v>4552743766.43</v>
       </c>
       <c r="F86" s="9">
-        <v>86069</v>
+        <v>86016</v>
       </c>
       <c r="G86" s="8">
-        <v>4067574058.85</v>
+        <v>4018390406.49</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4780,19 +4780,19 @@
         <v>174</v>
       </c>
       <c r="C87" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D87" s="7">
-        <v>0.231506</v>
+        <v>0.231216</v>
       </c>
       <c r="E87" s="8">
-        <v>12861801717.56</v>
+        <v>12897408074.22</v>
       </c>
       <c r="F87" s="9">
-        <v>150199</v>
+        <v>150503</v>
       </c>
       <c r="G87" s="8">
-        <v>2977587891.13</v>
+        <v>2982089084.27</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4803,19 +4803,19 @@
         <v>176</v>
       </c>
       <c r="C88" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D88" s="7">
-        <v>0.167604</v>
+        <v>0.167489</v>
       </c>
       <c r="E88" s="8">
-        <v>18675875534.77</v>
+        <v>18768771644.12</v>
       </c>
       <c r="F88" s="9">
-        <v>92040</v>
+        <v>92153</v>
       </c>
       <c r="G88" s="8">
-        <v>3130146597.95</v>
+        <v>3143553538.19</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4826,19 +4826,19 @@
         <v>178</v>
       </c>
       <c r="C89" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D89" s="7">
-        <v>0.650937</v>
+        <v>0.650244</v>
       </c>
       <c r="E89" s="8">
-        <v>2228091629.49</v>
+        <v>2227722118.7</v>
       </c>
       <c r="F89" s="9">
-        <v>35086</v>
+        <v>35056</v>
       </c>
       <c r="G89" s="8">
-        <v>1450346951.3</v>
+        <v>1448561894.94</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4849,19 +4849,19 @@
         <v>180</v>
       </c>
       <c r="C90" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D90" s="7">
-        <v>0.882907</v>
+        <v>0.882982</v>
       </c>
       <c r="E90" s="8">
-        <v>18636236705.68</v>
+        <v>18607675903.54</v>
       </c>
       <c r="F90" s="9">
-        <v>264478</v>
+        <v>128430</v>
       </c>
       <c r="G90" s="8">
-        <v>16454069388.67</v>
+        <v>16430245600.21</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4872,19 +4872,19 @@
         <v>182</v>
       </c>
       <c r="C91" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D91" s="7">
-        <v>0.795745</v>
+        <v>0.794178</v>
       </c>
       <c r="E91" s="8">
-        <v>3460817447.98</v>
+        <v>3455716687.38</v>
       </c>
       <c r="F91" s="9">
-        <v>30706</v>
+        <v>30672</v>
       </c>
       <c r="G91" s="8">
-        <v>2753929792.86</v>
+        <v>2744453606.3</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4895,19 +4895,19 @@
         <v>184</v>
       </c>
       <c r="C92" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D92" s="7">
-        <v>0.863109</v>
+        <v>0.863339</v>
       </c>
       <c r="E92" s="8">
-        <v>12141102203.14</v>
+        <v>12123500092.81</v>
       </c>
       <c r="F92" s="9">
-        <v>184646</v>
+        <v>184438</v>
       </c>
       <c r="G92" s="8">
-        <v>10479091116.01</v>
+        <v>10466689584.13</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4918,19 +4918,19 @@
         <v>186</v>
       </c>
       <c r="C93" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D93" s="7">
-        <v>0.092126</v>
+        <v>0.092222</v>
       </c>
       <c r="E93" s="8">
-        <v>7292184880.35</v>
+        <v>7290901587.61</v>
       </c>
       <c r="F93" s="9">
-        <v>154704</v>
+        <v>154379</v>
       </c>
       <c r="G93" s="8">
-        <v>671797907.85</v>
+        <v>672383603.61</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4941,19 +4941,19 @@
         <v>188</v>
       </c>
       <c r="C94" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D94" s="7">
-        <v>0.122659</v>
+        <v>0.122558</v>
       </c>
       <c r="E94" s="8">
-        <v>11732396179.01</v>
+        <v>11725563760.24</v>
       </c>
       <c r="F94" s="9">
-        <v>32846</v>
+        <v>1444</v>
       </c>
       <c r="G94" s="8">
-        <v>1439086095.68</v>
+        <v>1437063018.16</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4964,19 +4964,19 @@
         <v>190</v>
       </c>
       <c r="C95" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D95" s="7">
-        <v>0.133729</v>
+        <v>0.133866</v>
       </c>
       <c r="E95" s="8">
-        <v>67987841055.77</v>
+        <v>67894080741.77</v>
       </c>
       <c r="F95" s="9">
-        <v>210540</v>
+        <v>210450</v>
       </c>
       <c r="G95" s="8">
-        <v>9091928765.2</v>
+        <v>9088725217.6</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4987,19 +4987,19 @@
         <v>192</v>
       </c>
       <c r="C96" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D96" s="7">
-        <v>0.573729</v>
+        <v>0.565534</v>
       </c>
       <c r="E96" s="8">
-        <v>34151277807.56</v>
+        <v>34267318287.46</v>
       </c>
       <c r="F96" s="9">
-        <v>298490</v>
+        <v>32812</v>
       </c>
       <c r="G96" s="8">
-        <v>19593584004.75</v>
+        <v>19379331982.74</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -5010,19 +5010,19 @@
         <v>194</v>
       </c>
       <c r="C97" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D97" s="7">
-        <v>0.097922</v>
+        <v>0.097792</v>
       </c>
       <c r="E97" s="8">
-        <v>24855074541.52</v>
+        <v>24844860590.96</v>
       </c>
       <c r="F97" s="9">
-        <v>445978</v>
+        <v>149426</v>
       </c>
       <c r="G97" s="8">
-        <v>2433862610.68</v>
+        <v>2429625201.78</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -5033,19 +5033,19 @@
         <v>196</v>
       </c>
       <c r="C98" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D98" s="7">
-        <v>0.258049</v>
+        <v>0.258559</v>
       </c>
       <c r="E98" s="8">
-        <v>1246323905.8</v>
+        <v>1246644841.28</v>
       </c>
       <c r="F98" s="9">
-        <v>6910</v>
+        <v>6899</v>
       </c>
       <c r="G98" s="8">
-        <v>321612241.41</v>
+        <v>322331745.68</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -5056,19 +5056,19 @@
         <v>198</v>
       </c>
       <c r="C99" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D99" s="10">
-        <v>1.07428</v>
+        <v>46191</v>
+      </c>
+      <c r="D99" s="7">
+        <v>1.071154</v>
       </c>
       <c r="E99" s="8">
-        <v>5597042254.5</v>
+        <v>5608169778.37</v>
       </c>
       <c r="F99" s="9">
-        <v>60986</v>
+        <v>61423</v>
       </c>
       <c r="G99" s="8">
-        <v>6012793197.6</v>
+        <v>6007214575.46</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5079,19 +5079,19 @@
         <v>200</v>
       </c>
       <c r="C100" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D100" s="7">
-        <v>2.626847</v>
+        <v>2.604878</v>
       </c>
       <c r="E100" s="8">
-        <v>11853772224.83</v>
+        <v>11853841126.13</v>
       </c>
       <c r="F100" s="9">
-        <v>306890</v>
+        <v>307041</v>
       </c>
       <c r="G100" s="8">
-        <v>31138044307.79</v>
+        <v>30877805184.1</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5102,19 +5102,19 @@
         <v>202</v>
       </c>
       <c r="C101" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D101" s="7">
-        <v>0.373567</v>
+        <v>0.374306</v>
       </c>
       <c r="E101" s="8">
-        <v>22217136240.5</v>
+        <v>22174406701.13</v>
       </c>
       <c r="F101" s="9">
-        <v>286072</v>
+        <v>285811</v>
       </c>
       <c r="G101" s="8">
-        <v>8299591139.21</v>
+        <v>8300017903.88</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5125,19 +5125,19 @@
         <v>204</v>
       </c>
       <c r="C102" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D102" s="7">
-        <v>0.386192</v>
+        <v>0.386633</v>
       </c>
       <c r="E102" s="8">
-        <v>209218534908.56</v>
+        <v>209606092663.64</v>
       </c>
       <c r="F102" s="9">
-        <v>380736</v>
+        <v>370354</v>
       </c>
       <c r="G102" s="8">
-        <v>80798626116.37</v>
+        <v>81040601122.63</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5148,19 +5148,19 @@
         <v>206</v>
       </c>
       <c r="C103" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D103" s="7">
-        <v>0.126516</v>
+        <v>0.126363</v>
       </c>
       <c r="E103" s="8">
-        <v>8989979633.93</v>
+        <v>9001662808.08</v>
       </c>
       <c r="F103" s="9">
-        <v>28891</v>
+        <v>28880</v>
       </c>
       <c r="G103" s="8">
-        <v>1137375041.23</v>
+        <v>1137480274.39</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -5171,19 +5171,19 @@
         <v>208</v>
       </c>
       <c r="C104" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D104" s="7">
-        <v>0.283192</v>
+        <v>0.283146</v>
       </c>
       <c r="E104" s="8">
-        <v>1666464986.08</v>
+        <v>1668363046.64</v>
       </c>
       <c r="F104" s="9">
-        <v>7729</v>
+        <v>7723</v>
       </c>
       <c r="G104" s="8">
-        <v>471929471.8</v>
+        <v>472390411.39</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -5194,19 +5194,19 @@
         <v>210</v>
       </c>
       <c r="C105" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D105" s="7">
-        <v>0.009889</v>
+        <v>0.009851</v>
       </c>
       <c r="E105" s="8">
-        <v>5182458649.67</v>
+        <v>5422739571.91</v>
       </c>
       <c r="F105" s="9">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="G105" s="8">
-        <v>51248556.79</v>
+        <v>53418730.46</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5217,19 +5217,19 @@
         <v>212</v>
       </c>
       <c r="C106" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D106" s="7">
-        <v>1.100063</v>
+        <v>1.090216</v>
       </c>
       <c r="E106" s="8">
-        <v>295205459.66</v>
+        <v>297609810.24</v>
       </c>
       <c r="F106" s="9">
-        <v>4261</v>
+        <v>4269</v>
       </c>
       <c r="G106" s="8">
-        <v>324744549.84</v>
+        <v>324458878.89</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5240,19 +5240,19 @@
         <v>214</v>
       </c>
       <c r="C107" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D107" s="7">
-        <v>1.040061</v>
+        <v>46191</v>
+      </c>
+      <c r="D107" s="10">
+        <v>1.04355</v>
       </c>
       <c r="E107" s="8">
-        <v>704902163.93</v>
+        <v>705993702.51</v>
       </c>
       <c r="F107" s="9">
-        <v>16067</v>
+        <v>16066</v>
       </c>
       <c r="G107" s="8">
-        <v>733140912.17</v>
+        <v>736739773.62</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -5263,19 +5263,19 @@
         <v>216</v>
       </c>
       <c r="C108" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D108" s="7">
-        <v>0.184397</v>
+        <v>0.183735</v>
       </c>
       <c r="E108" s="8">
-        <v>371410272.83</v>
+        <v>370953633.67</v>
       </c>
       <c r="F108" s="9">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="G108" s="8">
-        <v>68486843.64</v>
+        <v>68157208.08</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -5286,19 +5286,19 @@
         <v>218</v>
       </c>
       <c r="C109" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D109" s="7">
-        <v>1.483994</v>
+        <v>1.475612</v>
       </c>
       <c r="E109" s="8">
-        <v>1011670168.5</v>
+        <v>1009201211.34</v>
       </c>
       <c r="F109" s="9">
-        <v>21729</v>
+        <v>21718</v>
       </c>
       <c r="G109" s="8">
-        <v>1501312741.19</v>
+        <v>1489189258.18</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -5309,19 +5309,19 @@
         <v>220</v>
       </c>
       <c r="C110" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D110" s="7">
-        <v>0.100634</v>
+        <v>0.100649</v>
       </c>
       <c r="E110" s="8">
-        <v>5515489661.89</v>
+        <v>5505058050.38</v>
       </c>
       <c r="F110" s="9">
-        <v>24456</v>
+        <v>24423</v>
       </c>
       <c r="G110" s="8">
-        <v>555046131.92</v>
+        <v>554076973.37</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5332,19 +5332,19 @@
         <v>222</v>
       </c>
       <c r="C111" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D111" s="7">
-        <v>0.300091</v>
+        <v>0.300267</v>
       </c>
       <c r="E111" s="8">
-        <v>1667018451.67</v>
+        <v>1667230975.99</v>
       </c>
       <c r="F111" s="9">
-        <v>33657</v>
+        <v>33684</v>
       </c>
       <c r="G111" s="8">
-        <v>500256547.95</v>
+        <v>500614641.51</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -5355,19 +5355,19 @@
         <v>224</v>
       </c>
       <c r="C112" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D112" s="7">
-        <v>0.219676</v>
+        <v>0.218628</v>
       </c>
       <c r="E112" s="8">
-        <v>596620381.22</v>
+        <v>596187019.15</v>
       </c>
       <c r="F112" s="9">
         <v>1432</v>
       </c>
       <c r="G112" s="8">
-        <v>131063258.21</v>
+        <v>130343259.27</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -5378,19 +5378,19 @@
         <v>226</v>
       </c>
       <c r="C113" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D113" s="7">
-        <v>0.446212</v>
+        <v>46191</v>
+      </c>
+      <c r="D113" s="10">
+        <v>0.44754</v>
       </c>
       <c r="E113" s="8">
-        <v>188300652.52</v>
+        <v>188477754.21</v>
       </c>
       <c r="F113" s="9">
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="G113" s="8">
-        <v>84022043.51</v>
+        <v>84351395.98</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5401,19 +5401,19 @@
         <v>228</v>
       </c>
       <c r="C114" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D114" s="7">
-        <v>0.113575</v>
+        <v>0.113666</v>
       </c>
       <c r="E114" s="8">
-        <v>178236951.57</v>
+        <v>177850394.54</v>
       </c>
       <c r="F114" s="9">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G114" s="8">
-        <v>20243267.27</v>
+        <v>20215521.71</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -5424,19 +5424,19 @@
         <v>230</v>
       </c>
       <c r="C115" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D115" s="7">
-        <v>0.061478</v>
+        <v>0.061324</v>
       </c>
       <c r="E115" s="8">
-        <v>1180208627870.93</v>
+        <v>1182011065610.64</v>
       </c>
       <c r="F115" s="9">
-        <v>792557</v>
+        <v>793110</v>
       </c>
       <c r="G115" s="8">
-        <v>72556811139.79</v>
+        <v>72485066608.15</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -5447,19 +5447,19 @@
         <v>232</v>
       </c>
       <c r="C116" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D116" s="7">
-        <v>0.016163</v>
+        <v>46191</v>
+      </c>
+      <c r="D116" s="10">
+        <v>0.01618</v>
       </c>
       <c r="E116" s="8">
-        <v>8162088793.19</v>
+        <v>8433467549.37</v>
       </c>
       <c r="F116" s="9">
-        <v>1568</v>
+        <v>1578</v>
       </c>
       <c r="G116" s="8">
-        <v>131921439.25</v>
+        <v>136452629.65</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -5470,19 +5470,19 @@
         <v>234</v>
       </c>
       <c r="C117" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D117" s="10">
-        <v>0.12813</v>
+        <v>46191</v>
+      </c>
+      <c r="D117" s="7">
+        <v>0.127466</v>
       </c>
       <c r="E117" s="8">
-        <v>7631611427.05</v>
+        <v>7652569083.52</v>
       </c>
       <c r="F117" s="9">
-        <v>25015</v>
+        <v>25034</v>
       </c>
       <c r="G117" s="8">
-        <v>977837324.56</v>
+        <v>975445549.37</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -5493,19 +5493,19 @@
         <v>236</v>
       </c>
       <c r="C118" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D118" s="7">
-        <v>0.139101</v>
+        <v>0.138809</v>
       </c>
       <c r="E118" s="8">
-        <v>37135652606.09</v>
+        <v>37254181254.43</v>
       </c>
       <c r="F118" s="9">
-        <v>79645</v>
+        <v>80014</v>
       </c>
       <c r="G118" s="8">
-        <v>5165607884.78</v>
+        <v>5171229160.97</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -5516,19 +5516,19 @@
         <v>238</v>
       </c>
       <c r="C119" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D119" s="7">
-        <v>0.588339</v>
+        <v>0.588712</v>
       </c>
       <c r="E119" s="8">
-        <v>92199410.01</v>
+        <v>92218866.34</v>
       </c>
       <c r="F119" s="9">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="G119" s="8">
-        <v>54244533.98</v>
+        <v>54290371.77</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5539,19 +5539,19 @@
         <v>240</v>
       </c>
       <c r="C120" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D120" s="7">
-        <v>0.724438</v>
+        <v>0.722117</v>
       </c>
       <c r="E120" s="8">
-        <v>22577084645.19</v>
+        <v>22581331594.43</v>
       </c>
       <c r="F120" s="9">
-        <v>154202</v>
+        <v>154201</v>
       </c>
       <c r="G120" s="8">
-        <v>16355690899.37</v>
+        <v>16306353746.68</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5562,19 +5562,19 @@
         <v>242</v>
       </c>
       <c r="C121" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D121" s="7">
-        <v>0.128876</v>
+        <v>0.128986</v>
       </c>
       <c r="E121" s="8">
-        <v>14393923378.71</v>
+        <v>14398372647.56</v>
       </c>
       <c r="F121" s="9">
-        <v>44813</v>
+        <v>44806</v>
       </c>
       <c r="G121" s="8">
-        <v>1855030033.17</v>
+        <v>1857193283.52</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -5585,19 +5585,19 @@
         <v>244</v>
       </c>
       <c r="C122" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D122" s="7">
-        <v>0.107831</v>
+        <v>0.107634</v>
       </c>
       <c r="E122" s="8">
-        <v>42721198576.92</v>
+        <v>42677248279.4</v>
       </c>
       <c r="F122" s="9">
-        <v>341095</v>
+        <v>341001</v>
       </c>
       <c r="G122" s="8">
-        <v>4606661157.62</v>
+        <v>4593543927.83</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -5608,19 +5608,19 @@
         <v>246</v>
       </c>
       <c r="C123" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D123" s="7">
-        <v>0.097107</v>
+        <v>0.097025</v>
       </c>
       <c r="E123" s="8">
-        <v>9729946127.23</v>
+        <v>9725350919.98</v>
       </c>
       <c r="F123" s="9">
-        <v>148878</v>
+        <v>148856</v>
       </c>
       <c r="G123" s="8">
-        <v>944843446.82</v>
+        <v>943598801.41</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -5631,19 +5631,19 @@
         <v>248</v>
       </c>
       <c r="C124" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D124" s="7">
-        <v>0.049415</v>
+        <v>0.049193</v>
       </c>
       <c r="E124" s="8">
-        <v>28719925624.06</v>
+        <v>28606792548.03</v>
       </c>
       <c r="F124" s="9">
-        <v>34888</v>
+        <v>34903</v>
       </c>
       <c r="G124" s="8">
-        <v>1419204875.01</v>
+        <v>1407251877.62</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5654,19 +5654,19 @@
         <v>250</v>
       </c>
       <c r="C125" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D125" s="7">
-        <v>0.122602</v>
+        <v>0.122369</v>
       </c>
       <c r="E125" s="8">
-        <v>6220698835.69</v>
+        <v>6205355312.13</v>
       </c>
       <c r="F125" s="9">
-        <v>43346</v>
+        <v>43331</v>
       </c>
       <c r="G125" s="8">
-        <v>762667354.82</v>
+        <v>759341355.59</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5677,19 +5677,19 @@
         <v>252</v>
       </c>
       <c r="C126" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D126" s="10">
-        <v>0.09333</v>
+        <v>46191</v>
+      </c>
+      <c r="D126" s="7">
+        <v>0.093273</v>
       </c>
       <c r="E126" s="8">
-        <v>3015292798.59</v>
+        <v>3016329331.43</v>
       </c>
       <c r="F126" s="9">
-        <v>84526</v>
+        <v>84512</v>
       </c>
       <c r="G126" s="8">
-        <v>281418381.22</v>
+        <v>281341992.86</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5700,19 +5700,19 @@
         <v>254</v>
       </c>
       <c r="C127" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D127" s="7">
-        <v>0.085676</v>
+        <v>0.085415</v>
       </c>
       <c r="E127" s="8">
-        <v>1130524720.36</v>
+        <v>1130457333.13</v>
       </c>
       <c r="F127" s="9">
-        <v>123752</v>
+        <v>123744</v>
       </c>
       <c r="G127" s="8">
-        <v>96858756.51</v>
+        <v>96558574.44</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5723,19 +5723,19 @@
         <v>256</v>
       </c>
       <c r="C128" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D128" s="7">
-        <v>0.776601</v>
+        <v>0.774792</v>
       </c>
       <c r="E128" s="8">
-        <v>1612347966.11</v>
+        <v>1605770624.11</v>
       </c>
       <c r="F128" s="9">
-        <v>49792</v>
+        <v>49785</v>
       </c>
       <c r="G128" s="8">
-        <v>1252151831.51</v>
+        <v>1244137588.74</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5746,19 +5746,19 @@
         <v>258</v>
       </c>
       <c r="C129" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D129" s="7">
-        <v>0.155158</v>
+        <v>46191</v>
+      </c>
+      <c r="D129" s="10">
+        <v>0.15536</v>
       </c>
       <c r="E129" s="8">
-        <v>1288649784.31</v>
+        <v>1289132880.51</v>
       </c>
       <c r="F129" s="9">
-        <v>12553</v>
+        <v>12555</v>
       </c>
       <c r="G129" s="8">
-        <v>199943738.25</v>
+        <v>200279146.9</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5769,19 +5769,19 @@
         <v>260</v>
       </c>
       <c r="C130" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D130" s="7">
-        <v>0.249411</v>
+        <v>0.249613</v>
       </c>
       <c r="E130" s="8">
-        <v>4984006455.74</v>
+        <v>4963399475.82</v>
       </c>
       <c r="F130" s="9">
-        <v>69333</v>
+        <v>69320</v>
       </c>
       <c r="G130" s="8">
-        <v>1243068236.86</v>
+        <v>1238929034.45</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5792,19 +5792,19 @@
         <v>262</v>
       </c>
       <c r="C131" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D131" s="7">
-        <v>1.843294</v>
+        <v>46191</v>
+      </c>
+      <c r="D131" s="10">
+        <v>1.83178</v>
       </c>
       <c r="E131" s="8">
-        <v>2352040281</v>
+        <v>2352529394.38</v>
       </c>
       <c r="F131" s="9">
-        <v>53474</v>
+        <v>53444</v>
       </c>
       <c r="G131" s="8">
-        <v>4335502766.55</v>
+        <v>4309316895.4</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5815,19 +5815,19 @@
         <v>264</v>
       </c>
       <c r="C132" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D132" s="7">
-        <v>0.352699</v>
+        <v>0.350651</v>
       </c>
       <c r="E132" s="8">
-        <v>527582343.32</v>
+        <v>527968217.66</v>
       </c>
       <c r="F132" s="9">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G132" s="8">
-        <v>186077961.78</v>
+        <v>185132560.41</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5838,19 +5838,19 @@
         <v>266</v>
       </c>
       <c r="C133" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D133" s="7">
-        <v>0.165134</v>
+        <v>0.164627</v>
       </c>
       <c r="E133" s="8">
-        <v>130927969.45</v>
+        <v>131527170.06</v>
       </c>
       <c r="F133" s="9">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G133" s="8">
-        <v>21620609.88</v>
+        <v>21652945.64</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,19 +5861,19 @@
         <v>268</v>
       </c>
       <c r="C134" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D134" s="7">
-        <v>0.728086</v>
+        <v>0.728775</v>
       </c>
       <c r="E134" s="8">
-        <v>1225550754.56</v>
+        <v>1226007235.62</v>
       </c>
       <c r="F134" s="9">
         <v>20994</v>
       </c>
       <c r="G134" s="8">
-        <v>892306788.5</v>
+        <v>893483134.74</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5884,19 +5884,19 @@
         <v>270</v>
       </c>
       <c r="C135" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D135" s="7">
-        <v>0.388725</v>
+        <v>46191</v>
+      </c>
+      <c r="D135" s="10">
+        <v>0.38919</v>
       </c>
       <c r="E135" s="8">
-        <v>7606563896.75</v>
+        <v>7605543208.99</v>
       </c>
       <c r="F135" s="9">
-        <v>91869</v>
+        <v>90734</v>
       </c>
       <c r="G135" s="8">
-        <v>2956861427.71</v>
+        <v>2959998408.35</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5907,19 +5907,19 @@
         <v>272</v>
       </c>
       <c r="C136" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D136" s="7">
-        <v>0.206705</v>
+        <v>0.205889</v>
       </c>
       <c r="E136" s="8">
-        <v>194790069.12</v>
+        <v>196363605.01</v>
       </c>
       <c r="F136" s="9">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="G136" s="8">
-        <v>40264104.74</v>
+        <v>40429142.92</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5930,19 +5930,19 @@
         <v>274</v>
       </c>
       <c r="C137" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D137" s="10">
-        <v>0.26955</v>
+        <v>46191</v>
+      </c>
+      <c r="D137" s="7">
+        <v>0.267403</v>
       </c>
       <c r="E137" s="8">
-        <v>402863437.31</v>
+        <v>401557255.86</v>
       </c>
       <c r="F137" s="9">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="G137" s="8">
-        <v>108591821.49</v>
+        <v>107377420.25</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5953,19 +5953,19 @@
         <v>276</v>
       </c>
       <c r="C138" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D138" s="7">
-        <v>0.105752</v>
+        <v>0.105787</v>
       </c>
       <c r="E138" s="8">
-        <v>306497789.63</v>
+        <v>304245646.38</v>
       </c>
       <c r="F138" s="9">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G138" s="8">
-        <v>32412624.11</v>
+        <v>32185112.42</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5976,19 +5976,19 @@
         <v>278</v>
       </c>
       <c r="C139" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D139" s="7">
-        <v>0.409115</v>
+        <v>0.405243</v>
       </c>
       <c r="E139" s="8">
-        <v>634782215.1</v>
+        <v>634539503.11</v>
       </c>
       <c r="F139" s="9">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="G139" s="8">
-        <v>259698944.97</v>
+        <v>257142517.1</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5999,19 +5999,19 @@
         <v>280</v>
       </c>
       <c r="C140" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D140" s="7">
-        <v>0.724538</v>
+        <v>46191</v>
+      </c>
+      <c r="D140" s="10">
+        <v>0.72501</v>
       </c>
       <c r="E140" s="8">
-        <v>2888842436.9</v>
+        <v>2885320596.3</v>
       </c>
       <c r="F140" s="9">
-        <v>41756</v>
+        <v>41736</v>
       </c>
       <c r="G140" s="8">
-        <v>2093075350.13</v>
+        <v>2091885910.57</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -6022,19 +6022,19 @@
         <v>282</v>
       </c>
       <c r="C141" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D141" s="7">
-        <v>0.086166</v>
+        <v>0.086173</v>
       </c>
       <c r="E141" s="8">
-        <v>29146596493.39</v>
+        <v>29554119461.12</v>
       </c>
       <c r="F141" s="9">
-        <v>24976</v>
+        <v>25033</v>
       </c>
       <c r="G141" s="8">
-        <v>2511443145.58</v>
+        <v>2546759945.45</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -6045,19 +6045,19 @@
         <v>284</v>
       </c>
       <c r="C142" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D142" s="7">
-        <v>0.276807</v>
+        <v>0.276054</v>
       </c>
       <c r="E142" s="8">
-        <v>21235221048.76</v>
+        <v>21296886285.91</v>
       </c>
       <c r="F142" s="9">
-        <v>4694</v>
+        <v>4691</v>
       </c>
       <c r="G142" s="8">
-        <v>5878048337.96</v>
+        <v>5879083742.1</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -6068,19 +6068,19 @@
         <v>286</v>
       </c>
       <c r="C143" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D143" s="7">
-        <v>0.094957</v>
+        <v>0.095039</v>
       </c>
       <c r="E143" s="8">
-        <v>642961842.47</v>
+        <v>640964031.3</v>
       </c>
       <c r="F143" s="9">
-        <v>10569</v>
+        <v>10515</v>
       </c>
       <c r="G143" s="8">
-        <v>61053788.04</v>
+        <v>60916472.57</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -6091,19 +6091,19 @@
         <v>288</v>
       </c>
       <c r="C144" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D144" s="7">
-        <v>0.056059</v>
+        <v>0.056162</v>
       </c>
       <c r="E144" s="8">
-        <v>1370884177.22</v>
+        <v>1366302985.44</v>
       </c>
       <c r="F144" s="9">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G144" s="8">
-        <v>76849734.05</v>
+        <v>76734240.51</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -6114,19 +6114,19 @@
         <v>290</v>
       </c>
       <c r="C145" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D145" s="7">
-        <v>0.116917</v>
+        <v>0.116931</v>
       </c>
       <c r="E145" s="8">
-        <v>1766927683.37</v>
+        <v>1770195350.19</v>
       </c>
       <c r="F145" s="9">
         <v>1064</v>
       </c>
       <c r="G145" s="8">
-        <v>206584675.86</v>
+        <v>206991056.04</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -6137,19 +6137,19 @@
         <v>292</v>
       </c>
       <c r="C146" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D146" s="7">
-        <v>0.116155</v>
+        <v>0.116081</v>
       </c>
       <c r="E146" s="8">
-        <v>1979940249.82</v>
+        <v>1979333878.41</v>
       </c>
       <c r="F146" s="9">
-        <v>65735</v>
+        <v>65721</v>
       </c>
       <c r="G146" s="8">
-        <v>229980175.09</v>
+        <v>229763928.39</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6160,19 +6160,19 @@
         <v>294</v>
       </c>
       <c r="C147" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D147" s="7">
-        <v>0.077967</v>
+        <v>0.077761</v>
       </c>
       <c r="E147" s="8">
-        <v>570654610.73</v>
+        <v>570520749.71</v>
       </c>
       <c r="F147" s="9">
-        <v>52588</v>
+        <v>52581</v>
       </c>
       <c r="G147" s="8">
-        <v>44492462.59</v>
+        <v>44364216.2</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -6183,19 +6183,19 @@
         <v>296</v>
       </c>
       <c r="C148" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D148" s="7">
-        <v>0.086306</v>
+        <v>46191</v>
+      </c>
+      <c r="D148" s="11">
+        <v>0.0864</v>
       </c>
       <c r="E148" s="8">
-        <v>349971298.84</v>
+        <v>347041232.25</v>
       </c>
       <c r="F148" s="9">
-        <v>9563</v>
+        <v>9493</v>
       </c>
       <c r="G148" s="8">
-        <v>30204485.88</v>
+        <v>29984478.43</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6206,19 +6206,19 @@
         <v>298</v>
       </c>
       <c r="C149" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D149" s="7">
-        <v>0.368549</v>
+        <v>0.367845</v>
       </c>
       <c r="E149" s="8">
-        <v>146228715.61</v>
+        <v>146426171.42</v>
       </c>
       <c r="F149" s="9">
         <v>1761</v>
       </c>
       <c r="G149" s="8">
-        <v>53892411.59</v>
+        <v>53862161.79</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -6229,19 +6229,19 @@
         <v>300</v>
       </c>
       <c r="C150" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D150" s="10">
-        <v>0.10223</v>
+        <v>46191</v>
+      </c>
+      <c r="D150" s="7">
+        <v>0.102413</v>
       </c>
       <c r="E150" s="8">
-        <v>331792701.59</v>
+        <v>332151786.94</v>
       </c>
       <c r="F150" s="9">
         <v>1827</v>
       </c>
       <c r="G150" s="8">
-        <v>33919166.12</v>
+        <v>34016647.27</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6252,19 +6252,19 @@
         <v>302</v>
       </c>
       <c r="C151" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D151" s="7">
-        <v>0.294308</v>
+        <v>0.293097</v>
       </c>
       <c r="E151" s="8">
-        <v>140014448.93</v>
+        <v>140095992.9</v>
       </c>
       <c r="F151" s="9">
         <v>209</v>
       </c>
       <c r="G151" s="8">
-        <v>41207397.55</v>
+        <v>41061709.63</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -6275,19 +6275,19 @@
         <v>304</v>
       </c>
       <c r="C152" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D152" s="7">
-        <v>0.121138</v>
+        <v>46191</v>
+      </c>
+      <c r="D152" s="10">
+        <v>0.12126</v>
       </c>
       <c r="E152" s="8">
-        <v>544337970.92</v>
+        <v>543153964.86</v>
       </c>
       <c r="F152" s="9">
         <v>91</v>
       </c>
       <c r="G152" s="8">
-        <v>65940283.76</v>
+        <v>65863058.05</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -6298,19 +6298,19 @@
         <v>306</v>
       </c>
       <c r="C153" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D153" s="7">
-        <v>0.407818</v>
+        <v>0.405252</v>
       </c>
       <c r="E153" s="8">
-        <v>1288471556.06</v>
+        <v>1289295199.25</v>
       </c>
       <c r="F153" s="9">
         <v>125</v>
       </c>
       <c r="G153" s="8">
-        <v>525461705.57</v>
+        <v>522489076.7</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -6321,19 +6321,19 @@
         <v>308</v>
       </c>
       <c r="C154" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D154" s="7">
-        <v>0.494606</v>
+        <v>0.491494</v>
       </c>
       <c r="E154" s="8">
-        <v>588288639.47</v>
+        <v>588353088.46</v>
       </c>
       <c r="F154" s="9">
         <v>375</v>
       </c>
       <c r="G154" s="8">
-        <v>290971338.78</v>
+        <v>289172020.95</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -6344,19 +6344,19 @@
         <v>310</v>
       </c>
       <c r="C155" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D155" s="7">
-        <v>1.689857</v>
+        <v>1.679073</v>
       </c>
       <c r="E155" s="8">
-        <v>924781607.87</v>
+        <v>925509628.75</v>
       </c>
       <c r="F155" s="9">
-        <v>10156</v>
+        <v>10153</v>
       </c>
       <c r="G155" s="8">
-        <v>1562748687.06</v>
+        <v>1553998493.51</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -6367,19 +6367,19 @@
         <v>312</v>
       </c>
       <c r="C156" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D156" s="7">
-        <v>0.278141</v>
+        <v>0.276938</v>
       </c>
       <c r="E156" s="8">
-        <v>184953061.34</v>
+        <v>185135799.24</v>
       </c>
       <c r="F156" s="9">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G156" s="8">
-        <v>51443119.41</v>
+        <v>51271080.53</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -6390,19 +6390,19 @@
         <v>314</v>
       </c>
       <c r="C157" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D157" s="7">
-        <v>0.149002</v>
+        <v>0.149248</v>
       </c>
       <c r="E157" s="8">
-        <v>4561569258.2</v>
+        <v>4561217255.01</v>
       </c>
       <c r="F157" s="9">
-        <v>28657</v>
+        <v>28641</v>
       </c>
       <c r="G157" s="8">
-        <v>679680784.24</v>
+        <v>680751925.04</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -6413,19 +6413,19 @@
         <v>316</v>
       </c>
       <c r="C158" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D158" s="7">
-        <v>0.175052</v>
+        <v>0.175245</v>
       </c>
       <c r="E158" s="8">
-        <v>3228029528.29</v>
+        <v>3230714736.03</v>
       </c>
       <c r="F158" s="9">
-        <v>12109</v>
+        <v>12014</v>
       </c>
       <c r="G158" s="8">
-        <v>565072703.72</v>
+        <v>566166540.02</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -6436,19 +6436,19 @@
         <v>318</v>
       </c>
       <c r="C159" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D159" s="7">
-        <v>0.697043</v>
+        <v>0.694634</v>
       </c>
       <c r="E159" s="8">
-        <v>760071821.38</v>
+        <v>760638106.36</v>
       </c>
       <c r="F159" s="9">
-        <v>5148</v>
+        <v>5146</v>
       </c>
       <c r="G159" s="8">
-        <v>529802647.57</v>
+        <v>528365093.97</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -6459,19 +6459,19 @@
         <v>320</v>
       </c>
       <c r="C160" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D160" s="7">
-        <v>0.378497</v>
+        <v>0.377298</v>
       </c>
       <c r="E160" s="8">
-        <v>1331868385.66</v>
+        <v>1330157995.22</v>
       </c>
       <c r="F160" s="9">
-        <v>23754</v>
+        <v>23742</v>
       </c>
       <c r="G160" s="8">
-        <v>504107679.86</v>
+        <v>501865469.65</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -6482,19 +6482,19 @@
         <v>322</v>
       </c>
       <c r="C161" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D161" s="7">
-        <v>0.377083</v>
+        <v>0.374979</v>
       </c>
       <c r="E161" s="8">
-        <v>166065755.41</v>
+        <v>165463365.56</v>
       </c>
       <c r="F161" s="9">
         <v>248</v>
       </c>
       <c r="G161" s="8">
-        <v>62620572.87</v>
+        <v>62045358.57</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -6505,19 +6505,19 @@
         <v>324</v>
       </c>
       <c r="C162" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D162" s="7">
-        <v>0.147234</v>
+        <v>46191</v>
+      </c>
+      <c r="D162" s="10">
+        <v>0.14715</v>
       </c>
       <c r="E162" s="8">
-        <v>1044138503.89</v>
+        <v>1044663762.31</v>
       </c>
       <c r="F162" s="9">
-        <v>2986</v>
+        <v>2991</v>
       </c>
       <c r="G162" s="8">
-        <v>153733167.31</v>
+        <v>153721850.02</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -6528,19 +6528,19 @@
         <v>326</v>
       </c>
       <c r="C163" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D163" s="7">
-        <v>0.119624</v>
+        <v>0.119411</v>
       </c>
       <c r="E163" s="8">
-        <v>7528248107.6</v>
+        <v>7525966151.14</v>
       </c>
       <c r="F163" s="9">
-        <v>79921</v>
+        <v>79896</v>
       </c>
       <c r="G163" s="8">
-        <v>900559645.74</v>
+        <v>898680971.49</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -6551,19 +6551,19 @@
         <v>328</v>
       </c>
       <c r="C164" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D164" s="7">
-        <v>0.111779</v>
+        <v>0.111666</v>
       </c>
       <c r="E164" s="8">
-        <v>3361854498.46</v>
+        <v>3359306683.57</v>
       </c>
       <c r="F164" s="9">
-        <v>65186</v>
+        <v>65168</v>
       </c>
       <c r="G164" s="8">
-        <v>375783462.25</v>
+        <v>375121926.25</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -6574,19 +6574,19 @@
         <v>330</v>
       </c>
       <c r="C165" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D165" s="7">
-        <v>0.014288</v>
+        <v>0.014237</v>
       </c>
       <c r="E165" s="8">
-        <v>450705061805.8</v>
+        <v>452547129194.6</v>
       </c>
       <c r="F165" s="9">
-        <v>79640</v>
+        <v>61070</v>
       </c>
       <c r="G165" s="8">
-        <v>6439762624.62</v>
+        <v>6442694219.55</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -6597,19 +6597,19 @@
         <v>332</v>
       </c>
       <c r="C166" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D166" s="7">
-        <v>0.370594</v>
+        <v>0.369694</v>
       </c>
       <c r="E166" s="8">
-        <v>695880336.68</v>
+        <v>697025963.83</v>
       </c>
       <c r="F166" s="9">
-        <v>6805</v>
+        <v>6804</v>
       </c>
       <c r="G166" s="8">
-        <v>257889338.27</v>
+        <v>257686448.96</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -6620,19 +6620,19 @@
         <v>334</v>
       </c>
       <c r="C167" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D167" s="7">
-        <v>0.013975</v>
+        <v>0.013915</v>
       </c>
       <c r="E167" s="8">
-        <v>46280020515.14</v>
+        <v>46394297514.33</v>
       </c>
       <c r="F167" s="9">
-        <v>8062</v>
+        <v>6500</v>
       </c>
       <c r="G167" s="8">
-        <v>646741305.44</v>
+        <v>645563536.17</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6643,19 +6643,19 @@
         <v>336</v>
       </c>
       <c r="C168" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D168" s="7">
-        <v>0.710586</v>
+        <v>0.708338</v>
       </c>
       <c r="E168" s="8">
-        <v>1969189719.08</v>
+        <v>1969247583.41</v>
       </c>
       <c r="F168" s="9">
-        <v>32881</v>
+        <v>32887</v>
       </c>
       <c r="G168" s="8">
-        <v>1399279437.15</v>
+        <v>1394892201.67</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6666,19 +6666,19 @@
         <v>338</v>
       </c>
       <c r="C169" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D169" s="7">
-        <v>0.396044</v>
+        <v>0.396315</v>
       </c>
       <c r="E169" s="8">
-        <v>1898188761.81</v>
+        <v>1903305688.02</v>
       </c>
       <c r="F169" s="9">
-        <v>20658</v>
+        <v>20644</v>
       </c>
       <c r="G169" s="8">
-        <v>751767017.11</v>
+        <v>754308104.45</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6689,19 +6689,19 @@
         <v>340</v>
       </c>
       <c r="C170" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D170" s="7">
-        <v>0.147064</v>
+        <v>0.146915</v>
       </c>
       <c r="E170" s="8">
-        <v>1480358710.75</v>
+        <v>1480016886.75</v>
       </c>
       <c r="F170" s="9">
-        <v>16258</v>
+        <v>16251</v>
       </c>
       <c r="G170" s="8">
-        <v>217707918.44</v>
+        <v>217435956</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6712,19 +6712,19 @@
         <v>342</v>
       </c>
       <c r="C171" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D171" s="7">
-        <v>1.263625</v>
+        <v>1.257269</v>
       </c>
       <c r="E171" s="8">
-        <v>1362500292.94</v>
+        <v>1362722643.17</v>
       </c>
       <c r="F171" s="9">
-        <v>23851</v>
+        <v>23830</v>
       </c>
       <c r="G171" s="8">
-        <v>1721689055.3</v>
+        <v>1713308631.36</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6735,19 +6735,19 @@
         <v>344</v>
       </c>
       <c r="C172" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D172" s="10">
-        <v>0.58401</v>
+        <v>0.59118</v>
       </c>
       <c r="E172" s="8">
-        <v>2324312723.07</v>
+        <v>2322708423.3</v>
       </c>
       <c r="F172" s="9">
-        <v>34095</v>
+        <v>34077</v>
       </c>
       <c r="G172" s="8">
-        <v>1357421357.19</v>
+        <v>1373139079.75</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6758,19 +6758,19 @@
         <v>346</v>
       </c>
       <c r="C173" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D173" s="7">
-        <v>0.009977</v>
+        <v>0.009981</v>
       </c>
       <c r="E173" s="8">
-        <v>4607606297</v>
+        <v>4804230198.77</v>
       </c>
       <c r="F173" s="9">
-        <v>1203</v>
+        <v>1254</v>
       </c>
       <c r="G173" s="8">
-        <v>45969323.41</v>
+        <v>47949911.77</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6781,19 +6781,19 @@
         <v>348</v>
       </c>
       <c r="C174" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D174" s="7">
-        <v>0.010511</v>
+        <v>0.010475</v>
       </c>
       <c r="E174" s="8">
-        <v>80043700351.55</v>
+        <v>84495324967.77</v>
       </c>
       <c r="F174" s="9">
-        <v>6463</v>
+        <v>6786</v>
       </c>
       <c r="G174" s="8">
-        <v>841360357.03</v>
+        <v>885091118.53</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6804,19 +6804,19 @@
         <v>350</v>
       </c>
       <c r="C175" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D175" s="7">
-        <v>0.017957</v>
+        <v>0.017834</v>
       </c>
       <c r="E175" s="8">
-        <v>96527856818.9</v>
+        <v>96837477877.05</v>
       </c>
       <c r="F175" s="9">
-        <v>22859</v>
+        <v>14698</v>
       </c>
       <c r="G175" s="8">
-        <v>1733388868.1</v>
+        <v>1727016259.82</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6827,19 +6827,19 @@
         <v>352</v>
       </c>
       <c r="C176" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D176" s="7">
-        <v>0.092379</v>
+        <v>0.092459</v>
       </c>
       <c r="E176" s="8">
-        <v>2211344468.59</v>
+        <v>2215774984.01</v>
       </c>
       <c r="F176" s="9">
-        <v>5126</v>
+        <v>5119</v>
       </c>
       <c r="G176" s="8">
-        <v>204282626.9</v>
+        <v>204867263.05</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6850,19 +6850,19 @@
         <v>354</v>
       </c>
       <c r="C177" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D177" s="7">
-        <v>0.127142</v>
+        <v>0.127292</v>
       </c>
       <c r="E177" s="8">
-        <v>1541525687.99</v>
+        <v>1526255125.08</v>
       </c>
       <c r="F177" s="9">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="G177" s="8">
-        <v>195993015.02</v>
+        <v>194279920.6</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6873,19 +6873,19 @@
         <v>356</v>
       </c>
       <c r="C178" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D178" s="7">
-        <v>0.323533</v>
+        <v>0.322492</v>
       </c>
       <c r="E178" s="8">
-        <v>711897594.15</v>
+        <v>711971770.57</v>
       </c>
       <c r="F178" s="9">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="G178" s="8">
-        <v>230322521.97</v>
+        <v>229604911.78</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6896,19 +6896,19 @@
         <v>358</v>
       </c>
       <c r="C179" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D179" s="7">
-        <v>0.092193</v>
+        <v>0.092159</v>
       </c>
       <c r="E179" s="8">
-        <v>41917686773.19</v>
+        <v>41897865816.47</v>
       </c>
       <c r="F179" s="9">
-        <v>284077</v>
+        <v>283999</v>
       </c>
       <c r="G179" s="8">
-        <v>3864526866.16</v>
+        <v>3861257416.27</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6919,19 +6919,19 @@
         <v>360</v>
       </c>
       <c r="C180" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D180" s="7">
-        <v>0.067443</v>
+        <v>0.067342</v>
       </c>
       <c r="E180" s="8">
-        <v>680758749.25</v>
+        <v>680409524.04</v>
       </c>
       <c r="F180" s="9">
-        <v>6081</v>
+        <v>6086</v>
       </c>
       <c r="G180" s="8">
-        <v>45912424.79</v>
+        <v>45819933.44</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6942,19 +6942,19 @@
         <v>362</v>
       </c>
       <c r="C181" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D181" s="7">
-        <v>0.253866</v>
+        <v>0.253926</v>
       </c>
       <c r="E181" s="8">
-        <v>535002790.8</v>
+        <v>533724587.09</v>
       </c>
       <c r="F181" s="9">
         <v>1720</v>
       </c>
       <c r="G181" s="8">
-        <v>135819063.05</v>
+        <v>135526437.41</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6965,19 +6965,19 @@
         <v>364</v>
       </c>
       <c r="C182" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D182" s="7">
-        <v>0.404527</v>
+        <v>0.402046</v>
       </c>
       <c r="E182" s="8">
-        <v>368796287.78</v>
+        <v>368803301.6</v>
       </c>
       <c r="F182" s="9">
         <v>1255</v>
       </c>
       <c r="G182" s="8">
-        <v>149187912.36</v>
+        <v>148276072.3</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6988,19 +6988,19 @@
         <v>366</v>
       </c>
       <c r="C183" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D183" s="7">
-        <v>0.115835</v>
+        <v>0.115684</v>
       </c>
       <c r="E183" s="8">
-        <v>14322401345.82</v>
+        <v>14321804736.14</v>
       </c>
       <c r="F183" s="9">
-        <v>32067</v>
+        <v>32072</v>
       </c>
       <c r="G183" s="8">
-        <v>1659039202.66</v>
+        <v>1656798018.14</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7011,19 +7011,19 @@
         <v>368</v>
       </c>
       <c r="C184" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D184" s="7">
-        <v>0.121386</v>
+        <v>0.121474</v>
       </c>
       <c r="E184" s="8">
-        <v>26866011337.21</v>
+        <v>26920240916.01</v>
       </c>
       <c r="F184" s="9">
-        <v>42000</v>
+        <v>42148</v>
       </c>
       <c r="G184" s="8">
-        <v>3261167090.56</v>
+        <v>3270110076.53</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7034,19 +7034,19 @@
         <v>370</v>
       </c>
       <c r="C185" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D185" s="7">
-        <v>0.103821</v>
+        <v>0.103285</v>
       </c>
       <c r="E185" s="8">
-        <v>34406165371.98</v>
+        <v>34473610498.76</v>
       </c>
       <c r="F185" s="9">
-        <v>31493</v>
+        <v>31520</v>
       </c>
       <c r="G185" s="8">
-        <v>3572087487.8</v>
+        <v>3560604642.56</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7057,19 +7057,19 @@
         <v>372</v>
       </c>
       <c r="C186" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D186" s="7">
-        <v>0.088808</v>
+        <v>0.088417</v>
       </c>
       <c r="E186" s="8">
-        <v>6475327309.91</v>
+        <v>6475663470.8</v>
       </c>
       <c r="F186" s="9">
-        <v>4922</v>
+        <v>4915</v>
       </c>
       <c r="G186" s="8">
-        <v>575058736.79</v>
+        <v>572557062.66</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7080,19 +7080,19 @@
         <v>374</v>
       </c>
       <c r="C187" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D187" s="7">
-        <v>0.075401</v>
+        <v>0.075451</v>
       </c>
       <c r="E187" s="8">
-        <v>14268882647.09</v>
+        <v>14258003624.48</v>
       </c>
       <c r="F187" s="9">
-        <v>185629</v>
+        <v>185610</v>
       </c>
       <c r="G187" s="8">
-        <v>1075886847.62</v>
+        <v>1075778768.95</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7103,19 +7103,19 @@
         <v>376</v>
       </c>
       <c r="C188" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D188" s="7">
-        <v>0.102334</v>
+        <v>0.102186</v>
       </c>
       <c r="E188" s="8">
-        <v>4141797715.07</v>
+        <v>4139949956.46</v>
       </c>
       <c r="F188" s="9">
-        <v>118149</v>
+        <v>118134</v>
       </c>
       <c r="G188" s="8">
-        <v>423845228.53</v>
+        <v>423045617.5</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7126,19 +7126,19 @@
         <v>378</v>
       </c>
       <c r="C189" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D189" s="7">
-        <v>0.241441</v>
+        <v>0.238997</v>
       </c>
       <c r="E189" s="8">
-        <v>664972072.98</v>
+        <v>664746776.28</v>
       </c>
       <c r="F189" s="9">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="G189" s="8">
-        <v>160551557.63</v>
+        <v>158872307.89</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7149,19 +7149,19 @@
         <v>380</v>
       </c>
       <c r="C190" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D190" s="7">
-        <v>0.088934</v>
+        <v>0.088982</v>
       </c>
       <c r="E190" s="8">
-        <v>2713486427.16</v>
+        <v>2713705317.19</v>
       </c>
       <c r="F190" s="9">
-        <v>41934</v>
+        <v>42059</v>
       </c>
       <c r="G190" s="8">
-        <v>241321242.63</v>
+        <v>241471896.22</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7172,19 +7172,19 @@
         <v>382</v>
       </c>
       <c r="C191" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D191" s="7">
-        <v>0.240956</v>
+        <v>0.240916</v>
       </c>
       <c r="E191" s="8">
-        <v>3210947134.11</v>
+        <v>3202304898.79</v>
       </c>
       <c r="F191" s="9">
-        <v>6680</v>
+        <v>6666</v>
       </c>
       <c r="G191" s="8">
-        <v>773695912.68</v>
+        <v>771485533.91</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7195,19 +7195,19 @@
         <v>384</v>
       </c>
       <c r="C192" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D192" s="7">
-        <v>0.166928</v>
+        <v>0.166053</v>
       </c>
       <c r="E192" s="8">
-        <v>694713968.98</v>
+        <v>694829641.07</v>
       </c>
       <c r="F192" s="9">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="G192" s="8">
-        <v>115967227.08</v>
+        <v>115378722.58</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7218,19 +7218,19 @@
         <v>386</v>
       </c>
       <c r="C193" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D193" s="10">
-        <v>0.15245</v>
+        <v>0.15219</v>
       </c>
       <c r="E193" s="8">
-        <v>515587752.29</v>
+        <v>515659179.2</v>
       </c>
       <c r="F193" s="9">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="G193" s="8">
-        <v>78601370.73</v>
+        <v>78478064.75</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7241,19 +7241,19 @@
         <v>388</v>
       </c>
       <c r="C194" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D194" s="7">
-        <v>0.105352</v>
+        <v>0.104822</v>
       </c>
       <c r="E194" s="8">
-        <v>1169143509.04</v>
+        <v>1168465238.68</v>
       </c>
       <c r="F194" s="9">
-        <v>117940</v>
+        <v>117927</v>
       </c>
       <c r="G194" s="8">
-        <v>123171210.3</v>
+        <v>122480652.99</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7264,19 +7264,19 @@
         <v>390</v>
       </c>
       <c r="C195" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D195" s="7">
-        <v>0.190931</v>
+        <v>0.190534</v>
       </c>
       <c r="E195" s="8">
-        <v>1785219698.36</v>
+        <v>1741664390.45</v>
       </c>
       <c r="F195" s="9">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="G195" s="8">
-        <v>340853788.87</v>
+        <v>331846679.68</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7287,19 +7287,19 @@
         <v>392</v>
       </c>
       <c r="C196" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D196" s="7">
-        <v>0.162359</v>
+        <v>0.162687</v>
       </c>
       <c r="E196" s="8">
-        <v>586633817.07</v>
+        <v>586227058.19</v>
       </c>
       <c r="F196" s="9">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="G196" s="8">
-        <v>95245276.28</v>
+        <v>95371357.75</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7310,19 +7310,19 @@
         <v>394</v>
       </c>
       <c r="C197" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D197" s="7">
-        <v>0.274215</v>
+        <v>0.274811</v>
       </c>
       <c r="E197" s="8">
-        <v>2519154190.08</v>
+        <v>2507137605.07</v>
       </c>
       <c r="F197" s="9">
-        <v>7145</v>
+        <v>7121</v>
       </c>
       <c r="G197" s="8">
-        <v>690788649.38</v>
+        <v>688990127.89</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7333,19 +7333,19 @@
         <v>396</v>
       </c>
       <c r="C198" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D198" s="7">
-        <v>0.102231</v>
+        <v>0.102017</v>
       </c>
       <c r="E198" s="8">
-        <v>113624065.52</v>
+        <v>113850973.54</v>
       </c>
       <c r="F198" s="9">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G198" s="8">
-        <v>11615944.71</v>
+        <v>11614697.95</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7356,19 +7356,19 @@
         <v>398</v>
       </c>
       <c r="C199" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D199" s="7">
-        <v>0.231298</v>
+        <v>0.228881</v>
       </c>
       <c r="E199" s="8">
-        <v>353122920.13</v>
+        <v>352633494.52</v>
       </c>
       <c r="F199" s="9">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="G199" s="8">
-        <v>81676741.62</v>
+        <v>80711013.82</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7379,19 +7379,19 @@
         <v>400</v>
       </c>
       <c r="C200" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D200" s="7">
-        <v>0.183437</v>
+        <v>0.181784</v>
       </c>
       <c r="E200" s="8">
-        <v>279476509.64</v>
+        <v>279472481.36</v>
       </c>
       <c r="F200" s="9">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G200" s="8">
-        <v>51266303.2</v>
+        <v>50803584.9</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7402,19 +7402,19 @@
         <v>402</v>
       </c>
       <c r="C201" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D201" s="7">
-        <v>0.092017</v>
+        <v>0.092114</v>
       </c>
       <c r="E201" s="8">
-        <v>2720409252.96</v>
+        <v>2717033213.18</v>
       </c>
       <c r="F201" s="9">
-        <v>40427</v>
+        <v>40381</v>
       </c>
       <c r="G201" s="8">
-        <v>250322559.43</v>
+        <v>250277780.39</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7425,19 +7425,19 @@
         <v>404</v>
       </c>
       <c r="C202" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D202" s="10">
-        <v>0.09366</v>
+        <v>46191</v>
+      </c>
+      <c r="D202" s="7">
+        <v>0.093788</v>
       </c>
       <c r="E202" s="8">
-        <v>818261159.2</v>
+        <v>818497537.64</v>
       </c>
       <c r="F202" s="9">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="G202" s="8">
-        <v>76638721.7</v>
+        <v>76765157.75</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7448,19 +7448,19 @@
         <v>406</v>
       </c>
       <c r="C203" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D203" s="7">
-        <v>0.158992</v>
+        <v>0.158819</v>
       </c>
       <c r="E203" s="8">
-        <v>9716194314.78</v>
+        <v>9719844571.72</v>
       </c>
       <c r="F203" s="9">
-        <v>8918</v>
+        <v>8893</v>
       </c>
       <c r="G203" s="8">
-        <v>1544798224.12</v>
+        <v>1543697805.05</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7471,19 +7471,19 @@
         <v>408</v>
       </c>
       <c r="C204" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D204" s="7">
-        <v>0.015074</v>
+        <v>0.015098</v>
       </c>
       <c r="E204" s="8">
-        <v>11219539289.98</v>
+        <v>10812994550.28</v>
       </c>
       <c r="F204" s="9">
-        <v>1535</v>
+        <v>1577</v>
       </c>
       <c r="G204" s="8">
-        <v>169128796.94</v>
+        <v>163259159.09</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7494,19 +7494,19 @@
         <v>410</v>
       </c>
       <c r="C205" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D205" s="7">
-        <v>0.029688</v>
+        <v>0.029555</v>
       </c>
       <c r="E205" s="8">
-        <v>1410008961.07</v>
+        <v>1408707466.43</v>
       </c>
       <c r="F205" s="9">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="G205" s="8">
-        <v>41859707.86</v>
+        <v>41634039.05</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -7517,19 +7517,19 @@
         <v>412</v>
       </c>
       <c r="C206" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D206" s="7">
-        <v>0.120667</v>
+        <v>0.120222</v>
       </c>
       <c r="E206" s="8">
-        <v>3210880080.29</v>
+        <v>3208583025.34</v>
       </c>
       <c r="F206" s="9">
-        <v>314842</v>
+        <v>298995</v>
       </c>
       <c r="G206" s="8">
-        <v>387446863.27</v>
+        <v>385742695.87</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7540,19 +7540,19 @@
         <v>414</v>
       </c>
       <c r="C207" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D207" s="7">
-        <v>0.159993</v>
+        <v>0.159682</v>
       </c>
       <c r="E207" s="8">
-        <v>661765859.49</v>
+        <v>650721922.34</v>
       </c>
       <c r="F207" s="9">
-        <v>1444</v>
+        <v>264127</v>
       </c>
       <c r="G207" s="8">
-        <v>105878082.6</v>
+        <v>103908322.06</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7563,19 +7563,19 @@
         <v>416</v>
       </c>
       <c r="C208" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D208" s="7">
-        <v>0.135186</v>
+        <v>0.134939</v>
       </c>
       <c r="E208" s="8">
-        <v>3012864816.32</v>
+        <v>3037520858.26</v>
       </c>
       <c r="F208" s="9">
-        <v>6224</v>
+        <v>6259</v>
       </c>
       <c r="G208" s="8">
-        <v>407296757.59</v>
+        <v>409878738.05</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7586,19 +7586,19 @@
         <v>418</v>
       </c>
       <c r="C209" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D209" s="7">
-        <v>0.106946</v>
+        <v>0.106588</v>
       </c>
       <c r="E209" s="8">
-        <v>4343745390.91</v>
+        <v>4353160604.97</v>
       </c>
       <c r="F209" s="9">
-        <v>352754</v>
+        <v>352776</v>
       </c>
       <c r="G209" s="8">
-        <v>464544090.92</v>
+        <v>463993110.7</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7609,19 +7609,19 @@
         <v>420</v>
       </c>
       <c r="C210" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D210" s="7">
-        <v>0.108748</v>
+        <v>0.108657</v>
       </c>
       <c r="E210" s="8">
-        <v>46994896691.9</v>
+        <v>46994676767.27</v>
       </c>
       <c r="F210" s="9">
-        <v>722079</v>
+        <v>722382</v>
       </c>
       <c r="G210" s="8">
-        <v>5110602054.75</v>
+        <v>5106278728.82</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -7632,19 +7632,19 @@
         <v>422</v>
       </c>
       <c r="C211" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D211" s="7">
-        <v>0.071066</v>
+        <v>0.070625</v>
       </c>
       <c r="E211" s="8">
-        <v>73827505652.22</v>
+        <v>74297846000.28</v>
       </c>
       <c r="F211" s="9">
-        <v>66485</v>
+        <v>66694</v>
       </c>
       <c r="G211" s="8">
-        <v>5246606720.05</v>
+        <v>5247313526.27</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7655,19 +7655,19 @@
         <v>424</v>
       </c>
       <c r="C212" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D212" s="7">
-        <v>0.109932</v>
+        <v>0.110017</v>
       </c>
       <c r="E212" s="8">
-        <v>66125447928.81</v>
+        <v>66097621051.57</v>
       </c>
       <c r="F212" s="9">
-        <v>930401</v>
+        <v>930601</v>
       </c>
       <c r="G212" s="8">
-        <v>7269301470</v>
+        <v>7271842416.16</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7678,19 +7678,19 @@
         <v>426</v>
       </c>
       <c r="C213" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D213" s="10">
-        <v>0.07293</v>
+        <v>46191</v>
+      </c>
+      <c r="D213" s="7">
+        <v>0.073026</v>
       </c>
       <c r="E213" s="8">
-        <v>54088051386.38</v>
+        <v>54450528339.85</v>
       </c>
       <c r="F213" s="9">
-        <v>54837</v>
+        <v>54873</v>
       </c>
       <c r="G213" s="8">
-        <v>3944630179.25</v>
+        <v>3976301071.29</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -7701,19 +7701,19 @@
         <v>428</v>
       </c>
       <c r="C214" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D214" s="7">
-        <v>0.102701</v>
+        <v>0.102891</v>
       </c>
       <c r="E214" s="8">
-        <v>17100143270.88</v>
+        <v>17059152118.49</v>
       </c>
       <c r="F214" s="9">
-        <v>354832</v>
+        <v>352860</v>
       </c>
       <c r="G214" s="8">
-        <v>1756200653</v>
+        <v>1755239799.96</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7724,19 +7724,19 @@
         <v>430</v>
       </c>
       <c r="C215" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D215" s="7">
-        <v>0.053406</v>
+        <v>0.053471</v>
       </c>
       <c r="E215" s="8">
-        <v>73771339325.22</v>
+        <v>73414522643.54</v>
       </c>
       <c r="F215" s="9">
-        <v>31788</v>
+        <v>31699</v>
       </c>
       <c r="G215" s="8">
-        <v>3939834896.99</v>
+        <v>3925522600.38</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -7747,19 +7747,19 @@
         <v>432</v>
       </c>
       <c r="C216" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D216" s="7">
-        <v>0.089962</v>
+        <v>0.090059</v>
       </c>
       <c r="E216" s="8">
-        <v>14463252125.83</v>
+        <v>14457362587.94</v>
       </c>
       <c r="F216" s="9">
-        <v>237090</v>
+        <v>236331</v>
       </c>
       <c r="G216" s="8">
-        <v>1301148886.69</v>
+        <v>1302011483.55</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -7770,19 +7770,19 @@
         <v>434</v>
       </c>
       <c r="C217" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D217" s="7">
-        <v>0.324879</v>
+        <v>0.322805</v>
       </c>
       <c r="E217" s="8">
-        <v>12752568888.54</v>
+        <v>12753943127.42</v>
       </c>
       <c r="F217" s="9">
-        <v>61132</v>
+        <v>61207</v>
       </c>
       <c r="G217" s="8">
-        <v>4143043632.59</v>
+        <v>4117039360.13</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7793,19 +7793,19 @@
         <v>436</v>
       </c>
       <c r="C218" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D218" s="7">
-        <v>0.220548</v>
+        <v>0.219256</v>
       </c>
       <c r="E218" s="8">
-        <v>10912061728.18</v>
+        <v>10925435760.44</v>
       </c>
       <c r="F218" s="9">
-        <v>40885</v>
+        <v>40938</v>
       </c>
       <c r="G218" s="8">
-        <v>2406634185.45</v>
+        <v>2395462371.18</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -7816,19 +7816,19 @@
         <v>438</v>
       </c>
       <c r="C219" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D219" s="7">
-        <v>1.033404</v>
+        <v>1.031188</v>
       </c>
       <c r="E219" s="8">
-        <v>722175956.36</v>
+        <v>722401351.25</v>
       </c>
       <c r="F219" s="9">
-        <v>4304</v>
+        <v>4303</v>
       </c>
       <c r="G219" s="8">
-        <v>746299353.64</v>
+        <v>744931652.71</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -7839,19 +7839,19 @@
         <v>440</v>
       </c>
       <c r="C220" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D220" s="7">
-        <v>0.735282</v>
+        <v>0.731404</v>
       </c>
       <c r="E220" s="8">
-        <v>5897286882.37</v>
+        <v>5900334840.78</v>
       </c>
       <c r="F220" s="9">
-        <v>10925</v>
+        <v>10923</v>
       </c>
       <c r="G220" s="8">
-        <v>4336169906.19</v>
+        <v>4315527703.8</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -7862,19 +7862,19 @@
         <v>442</v>
       </c>
       <c r="C221" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D221" s="7">
-        <v>2.885162</v>
+        <v>2.869604</v>
       </c>
       <c r="E221" s="8">
-        <v>6149209492.77</v>
+        <v>6149234293.04</v>
       </c>
       <c r="F221" s="9">
-        <v>272799</v>
+        <v>272619</v>
       </c>
       <c r="G221" s="8">
-        <v>17741462592.39</v>
+        <v>17645867106.1</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -7885,19 +7885,19 @@
         <v>444</v>
       </c>
       <c r="C222" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D222" s="7">
-        <v>0.421796</v>
+        <v>46191</v>
+      </c>
+      <c r="D222" s="10">
+        <v>0.42257</v>
       </c>
       <c r="E222" s="8">
-        <v>8835214260.3</v>
+        <v>8804265408.87</v>
       </c>
       <c r="F222" s="9">
-        <v>162119</v>
+        <v>162023</v>
       </c>
       <c r="G222" s="8">
-        <v>3726661454.64</v>
+        <v>3720418108.44</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -7908,19 +7908,19 @@
         <v>446</v>
       </c>
       <c r="C223" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D223" s="7">
-        <v>0.414584</v>
+        <v>0.414935</v>
       </c>
       <c r="E223" s="8">
-        <v>189031541834.04</v>
+        <v>189715714778.43</v>
       </c>
       <c r="F223" s="9">
-        <v>396805</v>
+        <v>396247</v>
       </c>
       <c r="G223" s="8">
-        <v>78369504001.18</v>
+        <v>78719642795.58</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -7931,19 +7931,19 @@
         <v>448</v>
       </c>
       <c r="C224" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D224" s="7">
-        <v>0.157201</v>
+        <v>46191</v>
+      </c>
+      <c r="D224" s="10">
+        <v>0.15689</v>
       </c>
       <c r="E224" s="8">
-        <v>6920389847.83</v>
+        <v>6904679862.91</v>
       </c>
       <c r="F224" s="9">
-        <v>25651</v>
+        <v>25681</v>
       </c>
       <c r="G224" s="8">
-        <v>1087893283.59</v>
+        <v>1083276745.34</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -7954,19 +7954,19 @@
         <v>450</v>
       </c>
       <c r="C225" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D225" s="7">
-        <v>0.538157</v>
+        <v>0.538394</v>
       </c>
       <c r="E225" s="8">
-        <v>8360767675.72</v>
+        <v>8190378621.49</v>
       </c>
       <c r="F225" s="9">
-        <v>34873</v>
+        <v>34829</v>
       </c>
       <c r="G225" s="8">
-        <v>4499402279.04</v>
+        <v>4409651398.67</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -7977,19 +7977,19 @@
         <v>452</v>
       </c>
       <c r="C226" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D226" s="7">
-        <v>0.072382</v>
+        <v>46191</v>
+      </c>
+      <c r="D226" s="10">
+        <v>0.07212</v>
       </c>
       <c r="E226" s="8">
-        <v>2453085650169.16</v>
+        <v>2452338777957.7</v>
       </c>
       <c r="F226" s="9">
-        <v>1235591</v>
+        <v>6190</v>
       </c>
       <c r="G226" s="8">
-        <v>177558806777.47</v>
+        <v>176862074030.3</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -8000,19 +8000,19 @@
         <v>454</v>
       </c>
       <c r="C227" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D227" s="7">
-        <v>0.074476</v>
+        <v>0.074051</v>
       </c>
       <c r="E227" s="8">
-        <v>26490396624.39</v>
+        <v>26414779965.36</v>
       </c>
       <c r="F227" s="9">
-        <v>93362</v>
+        <v>22951</v>
       </c>
       <c r="G227" s="8">
-        <v>1972908544.25</v>
+        <v>1956035275.97</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8023,19 +8023,19 @@
         <v>456</v>
       </c>
       <c r="C228" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D228" s="7">
-        <v>0.014733</v>
+        <v>0.014754</v>
       </c>
       <c r="E228" s="8">
-        <v>587204075409.18</v>
+        <v>589983746798.21</v>
       </c>
       <c r="F228" s="9">
-        <v>136796</v>
+        <v>136897</v>
       </c>
       <c r="G228" s="8">
-        <v>8651316831.5</v>
+        <v>8704545053.86</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8046,19 +8046,19 @@
         <v>458</v>
       </c>
       <c r="C229" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D229" s="7">
-        <v>0.762196</v>
+        <v>0.759914</v>
       </c>
       <c r="E229" s="8">
-        <v>168875083797.22</v>
+        <v>168843116705.17</v>
       </c>
       <c r="F229" s="9">
-        <v>854268</v>
+        <v>854201</v>
       </c>
       <c r="G229" s="8">
-        <v>128715989020.29</v>
+        <v>128306191641.58</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8069,19 +8069,19 @@
         <v>460</v>
       </c>
       <c r="C230" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D230" s="7">
-        <v>0.143231</v>
+        <v>0.143272</v>
       </c>
       <c r="E230" s="8">
-        <v>26729184522.46</v>
+        <v>26702648230.11</v>
       </c>
       <c r="F230" s="9">
-        <v>193340</v>
+        <v>193222</v>
       </c>
       <c r="G230" s="8">
-        <v>3828458444.58</v>
+        <v>3825745033.4</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8092,19 +8092,19 @@
         <v>462</v>
       </c>
       <c r="C231" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D231" s="7">
-        <v>1.134894</v>
+        <v>1.132618</v>
       </c>
       <c r="E231" s="8">
-        <v>2570714117.48</v>
+        <v>2569613177.01</v>
       </c>
       <c r="F231" s="9">
-        <v>48578</v>
+        <v>48553</v>
       </c>
       <c r="G231" s="8">
-        <v>2917488570.02</v>
+        <v>2910389481.16</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8115,19 +8115,19 @@
         <v>464</v>
       </c>
       <c r="C232" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D232" s="7">
-        <v>0.293122</v>
+        <v>0.293659</v>
       </c>
       <c r="E232" s="8">
-        <v>2357277580.09</v>
+        <v>2357070902.41</v>
       </c>
       <c r="F232" s="9">
-        <v>11260</v>
+        <v>11254</v>
       </c>
       <c r="G232" s="8">
-        <v>690969720.27</v>
+        <v>692174484.51</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8138,19 +8138,19 @@
         <v>466</v>
       </c>
       <c r="C233" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D233" s="7">
-        <v>1.170923</v>
+        <v>1.170991</v>
       </c>
       <c r="E233" s="8">
-        <v>5100743223.19</v>
+        <v>5096252669.95</v>
       </c>
       <c r="F233" s="9">
-        <v>62051</v>
+        <v>61999</v>
       </c>
       <c r="G233" s="8">
-        <v>5972575716.32</v>
+        <v>5967667583.44</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8161,19 +8161,19 @@
         <v>468</v>
       </c>
       <c r="C234" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D234" s="7">
-        <v>0.397047</v>
+        <v>46191</v>
+      </c>
+      <c r="D234" s="10">
+        <v>0.39531</v>
       </c>
       <c r="E234" s="8">
-        <v>19132773919.48</v>
+        <v>19131149607.27</v>
       </c>
       <c r="F234" s="9">
-        <v>155383</v>
+        <v>155434</v>
       </c>
       <c r="G234" s="8">
-        <v>7596612144.26</v>
+        <v>7562744114.8</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8184,19 +8184,19 @@
         <v>470</v>
       </c>
       <c r="C235" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D235" s="7">
-        <v>0.110913</v>
+        <v>0.110742</v>
       </c>
       <c r="E235" s="8">
-        <v>282851635026.7</v>
+        <v>282644782751.96</v>
       </c>
       <c r="F235" s="9">
-        <v>1539308</v>
+        <v>1538319</v>
       </c>
       <c r="G235" s="8">
-        <v>31371996295.31</v>
+        <v>31300630364.22</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8207,19 +8207,19 @@
         <v>472</v>
       </c>
       <c r="C236" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D236" s="7">
-        <v>0.269804</v>
+        <v>0.268829</v>
       </c>
       <c r="E236" s="8">
-        <v>3296643938.71</v>
+        <v>3297712979.35</v>
       </c>
       <c r="F236" s="9">
-        <v>10595</v>
+        <v>10584</v>
       </c>
       <c r="G236" s="8">
-        <v>889449185.47</v>
+        <v>886520027.17</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8230,19 +8230,19 @@
         <v>474</v>
       </c>
       <c r="C237" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D237" s="7">
-        <v>0.819211</v>
+        <v>0.819249</v>
       </c>
       <c r="E237" s="8">
-        <v>1354289827.32</v>
+        <v>1354428868.21</v>
       </c>
       <c r="F237" s="9">
-        <v>7730</v>
+        <v>7725</v>
       </c>
       <c r="G237" s="8">
-        <v>1109449369.08</v>
+        <v>1109614347.75</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -8253,19 +8253,19 @@
         <v>476</v>
       </c>
       <c r="C238" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D238" s="7">
-        <v>0.157149</v>
+        <v>0.156677</v>
       </c>
       <c r="E238" s="8">
-        <v>71325974190.22</v>
+        <v>71283597187</v>
       </c>
       <c r="F238" s="9">
-        <v>852076</v>
+        <v>851318</v>
       </c>
       <c r="G238" s="8">
-        <v>11208799755.18</v>
+        <v>11168516259.22</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -8276,19 +8276,19 @@
         <v>478</v>
       </c>
       <c r="C239" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D239" s="7">
-        <v>0.229111</v>
+        <v>0.228678</v>
       </c>
       <c r="E239" s="8">
-        <v>2450890343.26</v>
+        <v>2451106946.22</v>
       </c>
       <c r="F239" s="9">
-        <v>7559</v>
+        <v>7552</v>
       </c>
       <c r="G239" s="8">
-        <v>561526208.51</v>
+        <v>560515128.96</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,19 +8299,19 @@
         <v>480</v>
       </c>
       <c r="C240" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D240" s="11">
-        <v>0.2036</v>
+        <v>46191</v>
+      </c>
+      <c r="D240" s="7">
+        <v>0.203349</v>
       </c>
       <c r="E240" s="8">
-        <v>2345349792.51</v>
+        <v>2352350863.17</v>
       </c>
       <c r="F240" s="9">
-        <v>7418</v>
+        <v>7417</v>
       </c>
       <c r="G240" s="8">
-        <v>477512808.02</v>
+        <v>478347293.46</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -8322,19 +8322,19 @@
         <v>482</v>
       </c>
       <c r="C241" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D241" s="10">
-        <v>0.36889</v>
+        <v>46191</v>
+      </c>
+      <c r="D241" s="7">
+        <v>0.367351</v>
       </c>
       <c r="E241" s="8">
-        <v>34091520881.97</v>
+        <v>34153199936.45</v>
       </c>
       <c r="F241" s="9">
-        <v>168427</v>
+        <v>168557</v>
       </c>
       <c r="G241" s="8">
-        <v>12576006535.51</v>
+        <v>12546209206.24</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -8345,19 +8345,19 @@
         <v>484</v>
       </c>
       <c r="C242" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D242" s="7">
-        <v>0.131945</v>
+        <v>0.132011</v>
       </c>
       <c r="E242" s="8">
-        <v>3597684499.37</v>
+        <v>3586100701.19</v>
       </c>
       <c r="F242" s="9">
-        <v>7021</v>
+        <v>7007</v>
       </c>
       <c r="G242" s="8">
-        <v>474698135.49</v>
+        <v>473404864.21</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8368,19 +8368,19 @@
         <v>486</v>
       </c>
       <c r="C243" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D243" s="7">
-        <v>0.129796</v>
+        <v>0.129729</v>
       </c>
       <c r="E243" s="8">
-        <v>88075426810.72</v>
+        <v>88048891010.48</v>
       </c>
       <c r="F243" s="9">
-        <v>402210</v>
+        <v>401945</v>
       </c>
       <c r="G243" s="8">
-        <v>11431822005.54</v>
+        <v>11422502190.49</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -8391,19 +8391,19 @@
         <v>488</v>
       </c>
       <c r="C244" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D244" s="7">
-        <v>0.326789</v>
+        <v>0.324672</v>
       </c>
       <c r="E244" s="8">
-        <v>4335931891.41</v>
+        <v>4344021264.06</v>
       </c>
       <c r="F244" s="9">
-        <v>19217</v>
+        <v>19249</v>
       </c>
       <c r="G244" s="8">
-        <v>1416932997.38</v>
+        <v>1410381867.52</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8414,19 +8414,19 @@
         <v>490</v>
       </c>
       <c r="C245" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D245" s="7">
-        <v>0.085022</v>
+        <v>0.085102</v>
       </c>
       <c r="E245" s="8">
-        <v>3803693284.97</v>
+        <v>3806483703.62</v>
       </c>
       <c r="F245" s="9">
-        <v>9014</v>
+        <v>9015</v>
       </c>
       <c r="G245" s="8">
-        <v>323396198.62</v>
+        <v>323937706.59</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -8437,19 +8437,19 @@
         <v>492</v>
       </c>
       <c r="C246" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D246" s="7">
-        <v>0.259719</v>
+        <v>0.258559</v>
       </c>
       <c r="E246" s="8">
-        <v>3009139352.9</v>
+        <v>3013357475.63</v>
       </c>
       <c r="F246" s="9">
-        <v>14664</v>
+        <v>14679</v>
       </c>
       <c r="G246" s="8">
-        <v>781531785.26</v>
+        <v>779131490.64</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8460,19 +8460,19 @@
         <v>494</v>
       </c>
       <c r="C247" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D247" s="10">
-        <v>0.07209</v>
+        <v>46191</v>
+      </c>
+      <c r="D247" s="7">
+        <v>0.072158</v>
       </c>
       <c r="E247" s="8">
-        <v>3942910126.97</v>
+        <v>3918154468.86</v>
       </c>
       <c r="F247" s="9">
-        <v>7578</v>
+        <v>7572</v>
       </c>
       <c r="G247" s="8">
-        <v>284244740.49</v>
+        <v>282727491.3</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8483,19 +8483,19 @@
         <v>496</v>
       </c>
       <c r="C248" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D248" s="10">
-        <v>0.18398</v>
+        <v>46191</v>
+      </c>
+      <c r="D248" s="7">
+        <v>0.184138</v>
       </c>
       <c r="E248" s="8">
-        <v>11415323464.16</v>
+        <v>11422064111.82</v>
       </c>
       <c r="F248" s="9">
-        <v>50171</v>
+        <v>50186</v>
       </c>
       <c r="G248" s="8">
-        <v>2100194163</v>
+        <v>2103238772.23</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8506,19 +8506,19 @@
         <v>498</v>
       </c>
       <c r="C249" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D249" s="7">
-        <v>0.023758</v>
+        <v>46191</v>
+      </c>
+      <c r="D249" s="10">
+        <v>0.02379</v>
       </c>
       <c r="E249" s="8">
-        <v>931761726449.05</v>
+        <v>932959253151.98</v>
       </c>
       <c r="F249" s="9">
-        <v>185898</v>
+        <v>186106</v>
       </c>
       <c r="G249" s="8">
-        <v>22136863740.19</v>
+        <v>22195481288.63</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8529,19 +8529,19 @@
         <v>500</v>
       </c>
       <c r="C250" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D250" s="10">
-        <v>0.72173</v>
+        <v>0.71972</v>
       </c>
       <c r="E250" s="8">
-        <v>15013662273.2</v>
+        <v>15001655031.36</v>
       </c>
       <c r="F250" s="9">
-        <v>79354</v>
+        <v>79366</v>
       </c>
       <c r="G250" s="8">
-        <v>10835808597.01</v>
+        <v>10796985140.51</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8552,19 +8552,19 @@
         <v>502</v>
       </c>
       <c r="C251" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D251" s="7">
-        <v>0.627141</v>
+        <v>0.625127</v>
       </c>
       <c r="E251" s="8">
-        <v>8183724876.58</v>
+        <v>8180648823.48</v>
       </c>
       <c r="F251" s="9">
-        <v>76752</v>
+        <v>76802</v>
       </c>
       <c r="G251" s="8">
-        <v>5132351208.91</v>
+        <v>5113944499.21</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8575,19 +8575,19 @@
         <v>504</v>
       </c>
       <c r="C252" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D252" s="7">
-        <v>0.166625</v>
+        <v>46191</v>
+      </c>
+      <c r="D252" s="11">
+        <v>0.1668</v>
       </c>
       <c r="E252" s="8">
-        <v>2806815614.13</v>
+        <v>2810365142.27</v>
       </c>
       <c r="F252" s="9">
-        <v>11419</v>
+        <v>11421</v>
       </c>
       <c r="G252" s="8">
-        <v>467687022.92</v>
+        <v>468768523.96</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8598,19 +8598,19 @@
         <v>506</v>
       </c>
       <c r="C253" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D253" s="7">
-        <v>0.099517</v>
+        <v>0.099396</v>
       </c>
       <c r="E253" s="8">
-        <v>4921382339.77</v>
+        <v>4917240629.81</v>
       </c>
       <c r="F253" s="9">
-        <v>69993</v>
+        <v>69970</v>
       </c>
       <c r="G253" s="8">
-        <v>489760960.33</v>
+        <v>488755141.06</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8621,19 +8621,19 @@
         <v>508</v>
       </c>
       <c r="C254" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D254" s="7">
-        <v>0.341401</v>
+        <v>0.341569</v>
       </c>
       <c r="E254" s="8">
-        <v>2224132660.67</v>
+        <v>2184352603.73</v>
       </c>
       <c r="F254" s="9">
-        <v>21216</v>
+        <v>21218</v>
       </c>
       <c r="G254" s="8">
-        <v>759320442.38</v>
+        <v>746107081.92</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8644,19 +8644,19 @@
         <v>510</v>
       </c>
       <c r="C255" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D255" s="7">
-        <v>0.143922</v>
+        <v>0.143799</v>
       </c>
       <c r="E255" s="8">
-        <v>687558646.25</v>
+        <v>682596942.23</v>
       </c>
       <c r="F255" s="9">
         <v>2468</v>
       </c>
       <c r="G255" s="8">
-        <v>98954905.65</v>
+        <v>98156507.38</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8667,19 +8667,19 @@
         <v>512</v>
       </c>
       <c r="C256" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D256" s="7">
-        <v>0.086799</v>
+        <v>0.086891</v>
       </c>
       <c r="E256" s="8">
-        <v>650252207.56</v>
+        <v>642286882.27</v>
       </c>
       <c r="F256" s="9">
-        <v>14324</v>
+        <v>14245</v>
       </c>
       <c r="G256" s="8">
-        <v>56441295.18</v>
+        <v>55808839.11</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8690,19 +8690,19 @@
         <v>514</v>
       </c>
       <c r="C257" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D257" s="7">
-        <v>0.098351</v>
+        <v>0.098227</v>
       </c>
       <c r="E257" s="8">
-        <v>4091181573.31</v>
+        <v>4086642118.44</v>
       </c>
       <c r="F257" s="9">
-        <v>79460</v>
+        <v>79435</v>
       </c>
       <c r="G257" s="8">
-        <v>402370337.16</v>
+        <v>401417216.07</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -8713,19 +8713,19 @@
         <v>516</v>
       </c>
       <c r="C258" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D258" s="7">
-        <v>0.130021</v>
+        <v>0.129903</v>
       </c>
       <c r="E258" s="8">
-        <v>3768848964.52</v>
+        <v>3762457047.3</v>
       </c>
       <c r="F258" s="9">
-        <v>19679</v>
+        <v>19694</v>
       </c>
       <c r="G258" s="8">
-        <v>490028263.62</v>
+        <v>488752726.46</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -8736,19 +8736,19 @@
         <v>518</v>
       </c>
       <c r="C259" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D259" s="7">
-        <v>0.098236</v>
+        <v>46191</v>
+      </c>
+      <c r="D259" s="10">
+        <v>0.09834</v>
       </c>
       <c r="E259" s="8">
-        <v>587906047.65</v>
+        <v>584512228.94</v>
       </c>
       <c r="F259" s="9">
-        <v>10707</v>
+        <v>10620</v>
       </c>
       <c r="G259" s="8">
-        <v>57753692.37</v>
+        <v>57480744.85</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -8759,19 +8759,19 @@
         <v>520</v>
       </c>
       <c r="C260" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D260" s="7">
-        <v>0.138903</v>
+        <v>0.139004</v>
       </c>
       <c r="E260" s="8">
-        <v>4703937530.47</v>
+        <v>4689596589.28</v>
       </c>
       <c r="F260" s="9">
-        <v>18822</v>
+        <v>18660</v>
       </c>
       <c r="G260" s="8">
-        <v>653390962.58</v>
+        <v>651872189.05</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -8782,19 +8782,19 @@
         <v>522</v>
       </c>
       <c r="C261" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D261" s="7">
-        <v>0.157479</v>
+        <v>0.157205</v>
       </c>
       <c r="E261" s="8">
-        <v>1218056489.89</v>
+        <v>1217648571.84</v>
       </c>
       <c r="F261" s="9">
-        <v>60097</v>
+        <v>60087</v>
       </c>
       <c r="G261" s="8">
-        <v>191817928.21</v>
+        <v>191419915.94</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -8805,19 +8805,19 @@
         <v>524</v>
       </c>
       <c r="C262" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D262" s="7">
-        <v>0.778036</v>
+        <v>0.771366</v>
       </c>
       <c r="E262" s="8">
-        <v>8578063602.19</v>
+        <v>8573446557.62</v>
       </c>
       <c r="F262" s="9">
-        <v>26501</v>
+        <v>26512</v>
       </c>
       <c r="G262" s="8">
-        <v>6674038243.21</v>
+        <v>6613264915.17</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -8828,19 +8828,19 @@
         <v>526</v>
       </c>
       <c r="C263" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D263" s="7">
-        <v>0.104436</v>
+        <v>0.104221</v>
       </c>
       <c r="E263" s="8">
-        <v>14053002358.65</v>
+        <v>14038792810.38</v>
       </c>
       <c r="F263" s="9">
-        <v>131275</v>
+        <v>131236</v>
       </c>
       <c r="G263" s="8">
-        <v>1467637938.49</v>
+        <v>1463139280.6</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -8851,19 +8851,19 @@
         <v>528</v>
       </c>
       <c r="C264" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D264" s="7">
-        <v>0.013754</v>
+        <v>46191</v>
+      </c>
+      <c r="D264" s="10">
+        <v>0.01368</v>
       </c>
       <c r="E264" s="8">
-        <v>160846222847.21</v>
+        <v>160648522007.65</v>
       </c>
       <c r="F264" s="9">
-        <v>1890</v>
+        <v>1886</v>
       </c>
       <c r="G264" s="8">
-        <v>2212225059.75</v>
+        <v>2197680572.47</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -8874,19 +8874,19 @@
         <v>530</v>
       </c>
       <c r="C265" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D265" s="7">
-        <v>0.285519</v>
+        <v>0.282629</v>
       </c>
       <c r="E265" s="8">
-        <v>5708718108.13</v>
+        <v>5738586518.28</v>
       </c>
       <c r="F265" s="9">
-        <v>43874</v>
+        <v>43889</v>
       </c>
       <c r="G265" s="8">
-        <v>1629944709.87</v>
+        <v>1621893296.24</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -8897,19 +8897,19 @@
         <v>532</v>
       </c>
       <c r="C266" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D266" s="7">
-        <v>0.452491</v>
+        <v>0.448316</v>
       </c>
       <c r="E266" s="8">
-        <v>2632258483.13</v>
+        <v>2654897758.07</v>
       </c>
       <c r="F266" s="9">
-        <v>26258</v>
+        <v>26472</v>
       </c>
       <c r="G266" s="8">
-        <v>1191073598.99</v>
+        <v>1190232960.87</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -8920,19 +8920,19 @@
         <v>534</v>
       </c>
       <c r="C267" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D267" s="7">
-        <v>0.131109</v>
+        <v>0.130729</v>
       </c>
       <c r="E267" s="8">
-        <v>36873128753.5</v>
+        <v>36959087609.79</v>
       </c>
       <c r="F267" s="9">
-        <v>106441</v>
+        <v>106507</v>
       </c>
       <c r="G267" s="8">
-        <v>4834409792.38</v>
+        <v>4831637197.64</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -8943,19 +8943,19 @@
         <v>536</v>
       </c>
       <c r="C268" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D268" s="7">
-        <v>0.247486</v>
+        <v>0.247828</v>
       </c>
       <c r="E268" s="8">
-        <v>2652937188.71</v>
+        <v>2655298294.34</v>
       </c>
       <c r="F268" s="9">
-        <v>24102</v>
+        <v>24107</v>
       </c>
       <c r="G268" s="8">
-        <v>656564484.58</v>
+        <v>658057740.26</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -8966,19 +8966,19 @@
         <v>538</v>
       </c>
       <c r="C269" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D269" s="7">
-        <v>0.012896</v>
+        <v>0.012784</v>
       </c>
       <c r="E269" s="8">
-        <v>795052044507.51</v>
+        <v>797276770957.17</v>
       </c>
       <c r="F269" s="9">
-        <v>78267</v>
+        <v>78557</v>
       </c>
       <c r="G269" s="8">
-        <v>10252935140.92</v>
+        <v>10192208306.16</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -8989,19 +8989,19 @@
         <v>540</v>
       </c>
       <c r="C270" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D270" s="7">
-        <v>0.519135</v>
+        <v>46191</v>
+      </c>
+      <c r="D270" s="10">
+        <v>0.51953</v>
       </c>
       <c r="E270" s="8">
-        <v>5621116994.01</v>
+        <v>5622458294.64</v>
       </c>
       <c r="F270" s="9">
-        <v>71326</v>
+        <v>71303</v>
       </c>
       <c r="G270" s="8">
-        <v>2918117684.91</v>
+        <v>2921036697.82</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9012,19 +9012,19 @@
         <v>542</v>
       </c>
       <c r="C271" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D271" s="7">
-        <v>0.315405</v>
+        <v>0.314819</v>
       </c>
       <c r="E271" s="8">
-        <v>1804101069.36</v>
+        <v>1803000898.87</v>
       </c>
       <c r="F271" s="9">
-        <v>95440</v>
+        <v>95431</v>
       </c>
       <c r="G271" s="8">
-        <v>569023115.81</v>
+        <v>567619150.83</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9035,19 +9035,19 @@
         <v>544</v>
       </c>
       <c r="C272" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D272" s="7">
-        <v>0.785568</v>
+        <v>0.783033</v>
       </c>
       <c r="E272" s="8">
-        <v>2006877157.15</v>
+        <v>2006806068.36</v>
       </c>
       <c r="F272" s="9">
-        <v>111142</v>
+        <v>111124</v>
       </c>
       <c r="G272" s="8">
-        <v>1576539091.59</v>
+        <v>1571395811.23</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9058,19 +9058,19 @@
         <v>546</v>
       </c>
       <c r="C273" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D273" s="7">
-        <v>0.535877</v>
+        <v>0.534008</v>
       </c>
       <c r="E273" s="8">
-        <v>1504151679.32</v>
+        <v>1505384131.46</v>
       </c>
       <c r="F273" s="9">
-        <v>37587</v>
+        <v>37588</v>
       </c>
       <c r="G273" s="8">
-        <v>806039693.8</v>
+        <v>803887103.31</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9081,19 +9081,19 @@
         <v>548</v>
       </c>
       <c r="C274" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D274" s="7">
-        <v>0.296609</v>
+        <v>0.296804</v>
       </c>
       <c r="E274" s="8">
-        <v>2696408367.03</v>
+        <v>2689243333.4</v>
       </c>
       <c r="F274" s="9">
-        <v>86869</v>
+        <v>86837</v>
       </c>
       <c r="G274" s="8">
-        <v>799779671.11</v>
+        <v>798179479.12</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9104,19 +9104,19 @@
         <v>550</v>
       </c>
       <c r="C275" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D275" s="7">
-        <v>2.434046</v>
+        <v>2.418045</v>
       </c>
       <c r="E275" s="8">
-        <v>1894958746.82</v>
+        <v>1895569337.38</v>
       </c>
       <c r="F275" s="9">
-        <v>57205</v>
+        <v>57180</v>
       </c>
       <c r="G275" s="8">
-        <v>4612416300</v>
+        <v>4583571288.78</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9127,19 +9127,19 @@
         <v>552</v>
       </c>
       <c r="C276" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D276" s="10">
-        <v>0.93315</v>
+        <v>46191</v>
+      </c>
+      <c r="D276" s="7">
+        <v>0.931027</v>
       </c>
       <c r="E276" s="8">
-        <v>754885354.05</v>
+        <v>752858588.54</v>
       </c>
       <c r="F276" s="9">
-        <v>82956</v>
+        <v>82935</v>
       </c>
       <c r="G276" s="8">
-        <v>704421327.14</v>
+        <v>700931973.65</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9150,19 +9150,19 @@
         <v>554</v>
       </c>
       <c r="C277" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D277" s="7">
-        <v>0.393704</v>
+        <v>0.394165</v>
       </c>
       <c r="E277" s="8">
-        <v>9037418096.22</v>
+        <v>9001180077.95</v>
       </c>
       <c r="F277" s="9">
-        <v>100803</v>
+        <v>100485</v>
       </c>
       <c r="G277" s="8">
-        <v>3558070533.69</v>
+        <v>3547951912.02</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9173,19 +9173,19 @@
         <v>556</v>
       </c>
       <c r="C278" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D278" s="7">
-        <v>0.113707</v>
+        <v>0.113498</v>
       </c>
       <c r="E278" s="8">
-        <v>54142633256</v>
+        <v>54095631850.54</v>
       </c>
       <c r="F278" s="9">
-        <v>196543</v>
+        <v>196432</v>
       </c>
       <c r="G278" s="8">
-        <v>6156398681.43</v>
+        <v>6139770107.13</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9196,19 +9196,19 @@
         <v>558</v>
       </c>
       <c r="C279" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D279" s="7">
-        <v>0.119049</v>
+        <v>46191</v>
+      </c>
+      <c r="D279" s="10">
+        <v>0.11888</v>
       </c>
       <c r="E279" s="8">
-        <v>83622321796.24</v>
+        <v>83532542697.11</v>
       </c>
       <c r="F279" s="9">
-        <v>1093673</v>
+        <v>1093251</v>
       </c>
       <c r="G279" s="8">
-        <v>9955194042.99</v>
+        <v>9930346821.56</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9219,19 +9219,19 @@
         <v>560</v>
       </c>
       <c r="C280" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D280" s="7">
-        <v>0.145499</v>
+        <v>0.145318</v>
       </c>
       <c r="E280" s="8">
-        <v>33032507738.83</v>
+        <v>32981723871.9</v>
       </c>
       <c r="F280" s="9">
-        <v>334788</v>
+        <v>335294</v>
       </c>
       <c r="G280" s="8">
-        <v>4806191879.15</v>
+        <v>4792842406.61</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -9242,19 +9242,19 @@
         <v>562</v>
       </c>
       <c r="C281" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D281" s="7">
-        <v>0.171664</v>
+        <v>0.170986</v>
       </c>
       <c r="E281" s="8">
-        <v>3181680606.04</v>
+        <v>3174786475.41</v>
       </c>
       <c r="F281" s="9">
-        <v>27497</v>
+        <v>27519</v>
       </c>
       <c r="G281" s="8">
-        <v>546178473.4</v>
+        <v>542843694.74</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -9265,19 +9265,19 @@
         <v>564</v>
       </c>
       <c r="C282" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D282" s="7">
-        <v>0.709642</v>
+        <v>46191</v>
+      </c>
+      <c r="D282" s="10">
+        <v>0.70762</v>
       </c>
       <c r="E282" s="8">
-        <v>44504682824.76</v>
+        <v>44514189303.32</v>
       </c>
       <c r="F282" s="9">
-        <v>683643</v>
+        <v>684402</v>
       </c>
       <c r="G282" s="8">
-        <v>31582413496.88</v>
+        <v>31499149267.47</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -9288,19 +9288,19 @@
         <v>566</v>
       </c>
       <c r="C283" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D283" s="7">
-        <v>0.270332</v>
+        <v>0.269708</v>
       </c>
       <c r="E283" s="8">
-        <v>8561594033.93</v>
+        <v>8550174963.46</v>
       </c>
       <c r="F283" s="9">
-        <v>108122</v>
+        <v>108101</v>
       </c>
       <c r="G283" s="8">
-        <v>2314475923.82</v>
+        <v>2306053788.64</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -9311,19 +9311,19 @@
         <v>568</v>
       </c>
       <c r="C284" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D284" s="7">
-        <v>0.567661</v>
+        <v>0.566172</v>
       </c>
       <c r="E284" s="8">
-        <v>12336970099.02</v>
+        <v>12353329728.53</v>
       </c>
       <c r="F284" s="9">
-        <v>142765</v>
+        <v>142688</v>
       </c>
       <c r="G284" s="8">
-        <v>7003212559.04</v>
+        <v>6994106485.7</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -9334,19 +9334,19 @@
         <v>570</v>
       </c>
       <c r="C285" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D285" s="7">
-        <v>0.304445</v>
+        <v>0.303021</v>
       </c>
       <c r="E285" s="8">
-        <v>2205182847.59</v>
+        <v>2199801856.2</v>
       </c>
       <c r="F285" s="9">
-        <v>37139</v>
+        <v>37121</v>
       </c>
       <c r="G285" s="8">
-        <v>671356745.46</v>
+        <v>666585730.03</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -9357,19 +9357,19 @@
         <v>572</v>
       </c>
       <c r="C286" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D286" s="10">
-        <v>0.20383</v>
+        <v>0.20302</v>
       </c>
       <c r="E286" s="8">
-        <v>10231597498.55</v>
+        <v>10271736617.39</v>
       </c>
       <c r="F286" s="9">
-        <v>112156</v>
+        <v>112402</v>
       </c>
       <c r="G286" s="8">
-        <v>2085504145.61</v>
+        <v>2085366070.99</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -9380,19 +9380,19 @@
         <v>574</v>
       </c>
       <c r="C287" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D287" s="7">
-        <v>0.284431</v>
+        <v>0.283905</v>
       </c>
       <c r="E287" s="8">
-        <v>806949335.93</v>
+        <v>805345134.9</v>
       </c>
       <c r="F287" s="9">
-        <v>2807</v>
+        <v>2795</v>
       </c>
       <c r="G287" s="8">
-        <v>229521356.96</v>
+        <v>228641199.17</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -9403,19 +9403,19 @@
         <v>576</v>
       </c>
       <c r="C288" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D288" s="7">
-        <v>0.091952</v>
+        <v>46191</v>
+      </c>
+      <c r="D288" s="10">
+        <v>0.09205</v>
       </c>
       <c r="E288" s="8">
-        <v>4317301944.41</v>
+        <v>4315448600.82</v>
       </c>
       <c r="F288" s="9">
-        <v>144372</v>
+        <v>144214</v>
       </c>
       <c r="G288" s="8">
-        <v>396984722.64</v>
+        <v>397237093.52</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -9426,19 +9426,19 @@
         <v>578</v>
       </c>
       <c r="C289" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D289" s="7">
-        <v>0.514037</v>
+        <v>0.514756</v>
       </c>
       <c r="E289" s="8">
-        <v>1629836673.26</v>
+        <v>1628799719.72</v>
       </c>
       <c r="F289" s="9">
-        <v>4297</v>
+        <v>4271</v>
       </c>
       <c r="G289" s="8">
-        <v>837795882.41</v>
+        <v>838434959.21</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -9449,19 +9449,19 @@
         <v>580</v>
       </c>
       <c r="C290" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D290" s="7">
-        <v>0.016239</v>
+        <v>0.016229</v>
       </c>
       <c r="E290" s="8">
-        <v>8884631178.08</v>
+        <v>8885355038.01</v>
       </c>
       <c r="F290" s="9">
-        <v>4416</v>
+        <v>4442</v>
       </c>
       <c r="G290" s="8">
-        <v>144277937.66</v>
+        <v>144197817.97</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -9472,19 +9472,19 @@
         <v>582</v>
       </c>
       <c r="C291" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D291" s="7">
-        <v>0.017111</v>
+        <v>46191</v>
+      </c>
+      <c r="D291" s="10">
+        <v>0.01711</v>
       </c>
       <c r="E291" s="8">
-        <v>170703257100.57</v>
+        <v>171548434474.07</v>
       </c>
       <c r="F291" s="9">
-        <v>35141</v>
+        <v>35472</v>
       </c>
       <c r="G291" s="8">
-        <v>2920978769.44</v>
+        <v>2935197692.05</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -9495,19 +9495,19 @@
         <v>584</v>
       </c>
       <c r="C292" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D292" s="10">
-        <v>0.01113</v>
+        <v>46191</v>
+      </c>
+      <c r="D292" s="7">
+        <v>0.011137</v>
       </c>
       <c r="E292" s="8">
-        <v>22344416725.12</v>
+        <v>22333723085.89</v>
       </c>
       <c r="F292" s="9">
-        <v>4035</v>
+        <v>4114</v>
       </c>
       <c r="G292" s="8">
-        <v>248700820.39</v>
+        <v>248740372.53</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -9518,19 +9518,19 @@
         <v>586</v>
       </c>
       <c r="C293" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D293" s="7">
-        <v>0.130073</v>
+        <v>0.129871</v>
       </c>
       <c r="E293" s="8">
-        <v>50993470016.6</v>
+        <v>50940599904.92</v>
       </c>
       <c r="F293" s="9">
-        <v>109136</v>
+        <v>109325</v>
       </c>
       <c r="G293" s="8">
-        <v>6632861742.55</v>
+        <v>6615718431.01</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -9541,19 +9541,19 @@
         <v>588</v>
       </c>
       <c r="C294" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D294" s="7">
-        <v>0.053604</v>
+        <v>0.053663</v>
       </c>
       <c r="E294" s="8">
-        <v>10929468690.49</v>
+        <v>10930404412.56</v>
       </c>
       <c r="F294" s="9">
-        <v>27331</v>
+        <v>27320</v>
       </c>
       <c r="G294" s="8">
-        <v>585861557.07</v>
+        <v>586554999.37</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -9564,19 +9564,19 @@
         <v>590</v>
       </c>
       <c r="C295" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D295" s="7">
-        <v>0.022938</v>
+        <v>46191</v>
+      </c>
+      <c r="D295" s="10">
+        <v>0.02296</v>
       </c>
       <c r="E295" s="8">
-        <v>56187852018.98</v>
+        <v>55873281672.33</v>
       </c>
       <c r="F295" s="9">
-        <v>10756</v>
+        <v>10774</v>
       </c>
       <c r="G295" s="8">
-        <v>1288829209.02</v>
+        <v>1282874210.54</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -9587,19 +9587,19 @@
         <v>592</v>
       </c>
       <c r="C296" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D296" s="7">
-        <v>0.033688</v>
+        <v>0.033647</v>
       </c>
       <c r="E296" s="8">
-        <v>47640262864.98</v>
+        <v>47618947598.36</v>
       </c>
       <c r="F296" s="9">
-        <v>31336</v>
+        <v>31324</v>
       </c>
       <c r="G296" s="8">
-        <v>1604897933.98</v>
+        <v>1602242604.4</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -9610,19 +9610,19 @@
         <v>594</v>
       </c>
       <c r="C297" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D297" s="7">
-        <v>0.019143</v>
+        <v>0.019034</v>
       </c>
       <c r="E297" s="8">
-        <v>924942247988.26</v>
+        <v>926385916379.42</v>
       </c>
       <c r="F297" s="9">
-        <v>177052</v>
+        <v>177096</v>
       </c>
       <c r="G297" s="8">
-        <v>17705882671.45</v>
+        <v>17632470985.97</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -9633,19 +9633,19 @@
         <v>596</v>
       </c>
       <c r="C298" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D298" s="7">
-        <v>0.009646</v>
+        <v>0.009628</v>
       </c>
       <c r="E298" s="8">
-        <v>9302790040.87</v>
+        <v>9442684654.11</v>
       </c>
       <c r="F298" s="9">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="G298" s="8">
-        <v>89733235.11</v>
+        <v>90918831.3</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -9656,19 +9656,19 @@
         <v>598</v>
       </c>
       <c r="C299" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D299" s="7">
-        <v>0.104609</v>
+        <v>0.104511</v>
       </c>
       <c r="E299" s="8">
-        <v>37760912487.9</v>
+        <v>37756682534.11</v>
       </c>
       <c r="F299" s="9">
-        <v>387502</v>
+        <v>387286</v>
       </c>
       <c r="G299" s="8">
-        <v>3950140536.67</v>
+        <v>3945982661.94</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -9679,19 +9679,19 @@
         <v>600</v>
       </c>
       <c r="C300" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D300" s="7">
-        <v>0.089668</v>
+        <v>0.089701</v>
       </c>
       <c r="E300" s="8">
-        <v>37644413511.41</v>
+        <v>37742905886.37</v>
       </c>
       <c r="F300" s="9">
-        <v>47766</v>
+        <v>47830</v>
       </c>
       <c r="G300" s="8">
-        <v>3375490735.75</v>
+        <v>3385558918.92</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -9702,19 +9702,19 @@
         <v>602</v>
       </c>
       <c r="C301" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D301" s="7">
-        <v>0.096407</v>
+        <v>0.096275</v>
       </c>
       <c r="E301" s="8">
-        <v>39614412215.94</v>
+        <v>39580596752.8</v>
       </c>
       <c r="F301" s="9">
-        <v>534707</v>
+        <v>534387</v>
       </c>
       <c r="G301" s="8">
-        <v>3819097219.97</v>
+        <v>3810609500.93</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -9725,19 +9725,19 @@
         <v>604</v>
       </c>
       <c r="C302" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D302" s="7">
-        <v>0.021462</v>
+        <v>0.021403</v>
       </c>
       <c r="E302" s="8">
-        <v>49946695090.56</v>
+        <v>50173522436.91</v>
       </c>
       <c r="F302" s="9">
-        <v>29903</v>
+        <v>30056</v>
       </c>
       <c r="G302" s="8">
-        <v>1071977601.59</v>
+        <v>1073877539.08</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -9748,19 +9748,19 @@
         <v>606</v>
       </c>
       <c r="C303" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D303" s="7">
-        <v>0.010825</v>
+        <v>0.010837</v>
       </c>
       <c r="E303" s="8">
-        <v>24147849007.98</v>
+        <v>26423407890.46</v>
       </c>
       <c r="F303" s="9">
-        <v>2885</v>
+        <v>2952</v>
       </c>
       <c r="G303" s="8">
-        <v>261397247.36</v>
+        <v>286342705.98</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -9771,19 +9771,19 @@
         <v>608</v>
       </c>
       <c r="C304" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D304" s="7">
-        <v>0.017168</v>
+        <v>0.016997</v>
       </c>
       <c r="E304" s="8">
-        <v>33595679955.91</v>
+        <v>34543684022.52</v>
       </c>
       <c r="F304" s="9">
-        <v>14517</v>
+        <v>14526</v>
       </c>
       <c r="G304" s="8">
-        <v>576756375.71</v>
+        <v>587150131.29</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -9794,19 +9794,19 @@
         <v>610</v>
       </c>
       <c r="C305" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D305" s="7">
-        <v>0.019061</v>
+        <v>0.019058</v>
       </c>
       <c r="E305" s="8">
-        <v>26212279541.89</v>
+        <v>26507989474.41</v>
       </c>
       <c r="F305" s="9">
-        <v>13763</v>
+        <v>13975</v>
       </c>
       <c r="G305" s="8">
-        <v>499640602.56</v>
+        <v>505186267.28</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -9817,19 +9817,19 @@
         <v>612</v>
       </c>
       <c r="C306" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D306" s="7">
-        <v>0.097794</v>
+        <v>0.097701</v>
       </c>
       <c r="E306" s="8">
-        <v>21689009454.83</v>
+        <v>21639808768.25</v>
       </c>
       <c r="F306" s="9">
-        <v>351333</v>
+        <v>351300</v>
       </c>
       <c r="G306" s="8">
-        <v>2121053999.95</v>
+        <v>2114233624.3</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -9840,19 +9840,19 @@
         <v>614</v>
       </c>
       <c r="C307" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D307" s="7">
-        <v>0.019496</v>
+        <v>0.019401</v>
       </c>
       <c r="E307" s="8">
-        <v>10065004689.9</v>
+        <v>10062966633.23</v>
       </c>
       <c r="F307" s="9">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G307" s="8">
-        <v>196231075.19</v>
+        <v>195231227.4</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -9863,19 +9863,19 @@
         <v>616</v>
       </c>
       <c r="C308" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D308" s="7">
-        <v>0.016266</v>
+        <v>0.016249</v>
       </c>
       <c r="E308" s="8">
-        <v>9247241206.15</v>
+        <v>9267171048.92</v>
       </c>
       <c r="F308" s="9">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="G308" s="8">
-        <v>150413312.32</v>
+        <v>150586324.82</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -9886,19 +9886,19 @@
         <v>618</v>
       </c>
       <c r="C309" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D309" s="7">
-        <v>0.016565</v>
+        <v>0.016581</v>
       </c>
       <c r="E309" s="8">
-        <v>1301858912.43</v>
+        <v>1567282725.4</v>
       </c>
       <c r="F309" s="9">
         <v>22</v>
       </c>
       <c r="G309" s="8">
-        <v>21565440.83</v>
+        <v>25987065.44</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -9909,19 +9909,19 @@
         <v>620</v>
       </c>
       <c r="C310" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D310" s="7">
-        <v>0.224423</v>
+        <v>0.223643</v>
       </c>
       <c r="E310" s="8">
-        <v>48697626538.44</v>
+        <v>48681926890.59</v>
       </c>
       <c r="F310" s="9">
-        <v>177747</v>
+        <v>177847</v>
       </c>
       <c r="G310" s="8">
-        <v>10928852600.64</v>
+        <v>10887382104.53</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -9932,19 +9932,19 @@
         <v>622</v>
       </c>
       <c r="C311" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D311" s="7">
-        <v>0.011738</v>
+        <v>0.011758</v>
       </c>
       <c r="E311" s="8">
-        <v>3571685072.5</v>
+        <v>3588186129.96</v>
       </c>
       <c r="F311" s="9">
-        <v>2424</v>
+        <v>2437</v>
       </c>
       <c r="G311" s="8">
-        <v>41926207.84</v>
+        <v>42189087.85</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -9955,19 +9955,19 @@
         <v>624</v>
       </c>
       <c r="C312" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D312" s="7">
-        <v>0.032914</v>
+        <v>0.032751</v>
       </c>
       <c r="E312" s="8">
-        <v>16769474182.94</v>
+        <v>16821622594.73</v>
       </c>
       <c r="F312" s="9">
-        <v>19425</v>
+        <v>19468</v>
       </c>
       <c r="G312" s="8">
-        <v>551958137.92</v>
+        <v>550930391.67</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
@@ -9978,19 +9978,19 @@
         <v>626</v>
       </c>
       <c r="C313" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D313" s="7">
-        <v>0.025864</v>
+        <v>0.025713</v>
       </c>
       <c r="E313" s="8">
-        <v>3479215851.61</v>
+        <v>3470818972.46</v>
       </c>
       <c r="F313" s="9">
-        <v>10719</v>
+        <v>10743</v>
       </c>
       <c r="G313" s="8">
-        <v>89986833.87</v>
+        <v>89243725.69</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -10001,19 +10001,19 @@
         <v>628</v>
       </c>
       <c r="C314" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D314" s="7">
-        <v>0.126897</v>
+        <v>0.126459</v>
       </c>
       <c r="E314" s="8">
-        <v>621886767.16</v>
+        <v>621423330.58</v>
       </c>
       <c r="F314" s="9">
-        <v>96130</v>
+        <v>96095</v>
       </c>
       <c r="G314" s="8">
-        <v>78915705.5</v>
+        <v>78584451.5</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -10024,19 +10024,19 @@
         <v>630</v>
       </c>
       <c r="C315" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D315" s="7">
-        <v>0.095325</v>
+        <v>0.095405</v>
       </c>
       <c r="E315" s="8">
-        <v>1368948534.7</v>
+        <v>1381682100.62</v>
       </c>
       <c r="F315" s="9">
-        <v>25433</v>
+        <v>25710</v>
       </c>
       <c r="G315" s="8">
-        <v>130495616.96</v>
+        <v>131819611.73</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -10047,19 +10047,19 @@
         <v>632</v>
       </c>
       <c r="C316" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D316" s="10">
-        <v>0.08423</v>
+        <v>46191</v>
+      </c>
+      <c r="D316" s="7">
+        <v>0.084321</v>
       </c>
       <c r="E316" s="8">
-        <v>2400808267.28</v>
+        <v>2391549775.1</v>
       </c>
       <c r="F316" s="9">
-        <v>76121</v>
+        <v>75947</v>
       </c>
       <c r="G316" s="8">
-        <v>202220522.4</v>
+        <v>201657766.74</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -10070,19 +10070,19 @@
         <v>634</v>
       </c>
       <c r="C317" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D317" s="7">
-        <v>0.400442</v>
+        <v>0.400538</v>
       </c>
       <c r="E317" s="8">
-        <v>5181697231.6</v>
+        <v>5172844845.72</v>
       </c>
       <c r="F317" s="9">
-        <v>71668</v>
+        <v>71673</v>
       </c>
       <c r="G317" s="8">
-        <v>2074971012.08</v>
+        <v>2071921333.94</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -10093,19 +10093,19 @@
         <v>636</v>
       </c>
       <c r="C318" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D318" s="11">
-        <v>0.2116</v>
+        <v>46191</v>
+      </c>
+      <c r="D318" s="7">
+        <v>0.211684</v>
       </c>
       <c r="E318" s="8">
-        <v>5730793424.2</v>
+        <v>5724600632.65</v>
       </c>
       <c r="F318" s="9">
-        <v>56149</v>
+        <v>56128</v>
       </c>
       <c r="G318" s="8">
-        <v>1212633721.33</v>
+        <v>1211804954.93</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -10116,19 +10116,19 @@
         <v>638</v>
       </c>
       <c r="C319" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D319" s="7">
-        <v>0.117539</v>
+        <v>0.117707</v>
       </c>
       <c r="E319" s="8">
-        <v>2303132497.46</v>
+        <v>2298054855.01</v>
       </c>
       <c r="F319" s="9">
-        <v>8349</v>
+        <v>8341</v>
       </c>
       <c r="G319" s="8">
-        <v>270707631.28</v>
+        <v>270496731.92</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -10139,19 +10139,19 @@
         <v>640</v>
       </c>
       <c r="C320" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D320" s="10">
-        <v>0.55987</v>
+        <v>46191</v>
+      </c>
+      <c r="D320" s="7">
+        <v>0.555007</v>
       </c>
       <c r="E320" s="8">
-        <v>4031858291.71</v>
+        <v>4032488961.45</v>
       </c>
       <c r="F320" s="9">
         <v>50698</v>
       </c>
       <c r="G320" s="8">
-        <v>2257315444.63</v>
+        <v>2238061512.53</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -10162,19 +10162,19 @@
         <v>642</v>
       </c>
       <c r="C321" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D321" s="10">
-        <v>0.08727</v>
+        <v>46191</v>
+      </c>
+      <c r="D321" s="7">
+        <v>0.087126</v>
       </c>
       <c r="E321" s="8">
-        <v>9026318550.99</v>
+        <v>9014093882.73</v>
       </c>
       <c r="F321" s="9">
-        <v>192395</v>
+        <v>192290</v>
       </c>
       <c r="G321" s="8">
-        <v>787726625.26</v>
+        <v>785362372.91</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -10185,19 +10185,19 @@
         <v>644</v>
       </c>
       <c r="C322" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D322" s="7">
-        <v>0.112506</v>
+        <v>0.112319</v>
       </c>
       <c r="E322" s="8">
-        <v>22886289575.58</v>
+        <v>22848477704.92</v>
       </c>
       <c r="F322" s="9">
-        <v>137718</v>
+        <v>137708</v>
       </c>
       <c r="G322" s="8">
-        <v>2574854019</v>
+        <v>2566327216.86</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -10208,19 +10208,19 @@
         <v>646</v>
       </c>
       <c r="C323" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D323" s="7">
-        <v>0.159254</v>
+        <v>0.159394</v>
       </c>
       <c r="E323" s="8">
-        <v>13461641903.66</v>
+        <v>13417836118</v>
       </c>
       <c r="F323" s="9">
-        <v>33795</v>
+        <v>33226</v>
       </c>
       <c r="G323" s="8">
-        <v>2143817502.23</v>
+        <v>2138720709</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -10231,19 +10231,19 @@
         <v>648</v>
       </c>
       <c r="C324" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D324" s="7">
-        <v>0.139659</v>
+        <v>0.139827</v>
       </c>
       <c r="E324" s="8">
-        <v>518226646.46</v>
+        <v>518189191.06</v>
       </c>
       <c r="F324" s="9">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G324" s="8">
-        <v>72374833.18</v>
+        <v>72457080.3</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -10254,19 +10254,19 @@
         <v>650</v>
       </c>
       <c r="C325" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D325" s="7">
-        <v>0.142445</v>
+        <v>0.141877</v>
       </c>
       <c r="E325" s="8">
-        <v>223975347.05</v>
+        <v>222740653.33</v>
       </c>
       <c r="F325" s="9">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G325" s="8">
-        <v>31904140.97</v>
+        <v>31601830.2</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -10277,19 +10277,19 @@
         <v>652</v>
       </c>
       <c r="C326" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D326" s="7">
-        <v>0.172633</v>
+        <v>0.171786</v>
       </c>
       <c r="E326" s="8">
-        <v>301869383.59</v>
+        <v>301818292.69</v>
       </c>
       <c r="F326" s="9">
         <v>528</v>
       </c>
       <c r="G326" s="8">
-        <v>52112583.48</v>
+        <v>51848116.31</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -10300,19 +10300,19 @@
         <v>654</v>
       </c>
       <c r="C327" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D327" s="7">
-        <v>0.203111</v>
+        <v>0.201602</v>
       </c>
       <c r="E327" s="8">
-        <v>356282829.69</v>
+        <v>356177122.43</v>
       </c>
       <c r="F327" s="9">
         <v>574</v>
       </c>
       <c r="G327" s="8">
-        <v>72364866.84</v>
+        <v>71805856.02</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -10323,19 +10323,19 @@
         <v>656</v>
       </c>
       <c r="C328" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D328" s="7">
-        <v>0.146596</v>
+        <v>0.146332</v>
       </c>
       <c r="E328" s="8">
-        <v>495551636.59</v>
+        <v>495429855.69</v>
       </c>
       <c r="F328" s="9">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="G328" s="8">
-        <v>72646126.77</v>
+        <v>72497062.42</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -10346,19 +10346,19 @@
         <v>658</v>
       </c>
       <c r="C329" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D329" s="7">
-        <v>0.101038</v>
+        <v>0.100724</v>
       </c>
       <c r="E329" s="8">
-        <v>40655652480.06</v>
+        <v>40610454107.31</v>
       </c>
       <c r="F329" s="9">
-        <v>375285</v>
+        <v>375106</v>
       </c>
       <c r="G329" s="8">
-        <v>4107756080.45</v>
+        <v>4090461512.84</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -10369,19 +10369,19 @@
         <v>660</v>
       </c>
       <c r="C330" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D330" s="10">
-        <v>0.17791</v>
+        <v>46191</v>
+      </c>
+      <c r="D330" s="7">
+        <v>0.176991</v>
       </c>
       <c r="E330" s="8">
-        <v>198013671.93</v>
+        <v>198408268.54</v>
       </c>
       <c r="F330" s="9">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G330" s="8">
-        <v>35228597.88</v>
+        <v>35116520.49</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
@@ -10392,19 +10392,19 @@
         <v>662</v>
       </c>
       <c r="C331" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D331" s="7">
-        <v>0.208459</v>
+        <v>0.207201</v>
       </c>
       <c r="E331" s="8">
-        <v>252939980.29</v>
+        <v>253289559.82</v>
       </c>
       <c r="F331" s="9">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="G331" s="8">
-        <v>52727642.78</v>
+        <v>52481901.74</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
@@ -10415,19 +10415,19 @@
         <v>664</v>
       </c>
       <c r="C332" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D332" s="7">
-        <v>0.297413</v>
+        <v>0.296121</v>
       </c>
       <c r="E332" s="8">
-        <v>1277843358.46</v>
+        <v>1277355699.97</v>
       </c>
       <c r="F332" s="9">
-        <v>8795</v>
+        <v>8787</v>
       </c>
       <c r="G332" s="8">
-        <v>380047378.77</v>
+        <v>378252135.45</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
@@ -10438,19 +10438,19 @@
         <v>666</v>
       </c>
       <c r="C333" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D333" s="7">
-        <v>0.095194</v>
+        <v>0.095133</v>
       </c>
       <c r="E333" s="8">
-        <v>7005647737.2</v>
+        <v>6995645315.67</v>
       </c>
       <c r="F333" s="9">
-        <v>125166</v>
+        <v>125120</v>
       </c>
       <c r="G333" s="8">
-        <v>666896335.5</v>
+        <v>665516880.6</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
@@ -10461,19 +10461,19 @@
         <v>668</v>
       </c>
       <c r="C334" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D334" s="10">
-        <v>0.44157</v>
+        <v>46191</v>
+      </c>
+      <c r="D334" s="7">
+        <v>0.440127</v>
  